--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1457"/>
+  <dimension ref="A1:F1458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44095</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59559631347656</v>
+        <v>12.59559726715088</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80832961567333</v>
+        <v>12.80833058545472</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45377411201205</v>
+        <v>12.45377505494831</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46706941506998</v>
+        <v>12.46707035901289</v>
       </c>
       <c r="F3" t="n">
         <v>1323800</v>
@@ -492,16 +492,16 @@
         <v>44096</v>
       </c>
       <c r="B4" t="n">
-        <v>12.58673191070557</v>
+        <v>12.58673286437988</v>
       </c>
       <c r="C4" t="n">
-        <v>12.77287375696596</v>
+        <v>12.77287472474392</v>
       </c>
       <c r="D4" t="n">
-        <v>12.43161356460074</v>
+        <v>12.43161450652202</v>
       </c>
       <c r="E4" t="n">
-        <v>12.44490971266469</v>
+        <v>12.44491065559339</v>
       </c>
       <c r="F4" t="n">
         <v>1698000</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513519287109</v>
+        <v>12.36513614654541</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366209522167</v>
+        <v>12.49366305880876</v>
       </c>
       <c r="D7" t="n">
-        <v>12.32081554222169</v>
+        <v>12.3208164924778</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377449416991</v>
+        <v>12.45377545468063</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -592,16 +592,16 @@
         <v>44103</v>
       </c>
       <c r="B9" t="n">
-        <v>11.29703617095947</v>
+        <v>11.29703712463379</v>
       </c>
       <c r="C9" t="n">
-        <v>11.83330235747354</v>
+        <v>11.83330335641843</v>
       </c>
       <c r="D9" t="n">
-        <v>11.07987080462801</v>
+        <v>11.07987173996964</v>
       </c>
       <c r="E9" t="n">
-        <v>11.83330235747354</v>
+        <v>11.83330335641843</v>
       </c>
       <c r="F9" t="n">
         <v>897600</v>
@@ -612,16 +612,16 @@
         <v>44104</v>
       </c>
       <c r="B10" t="n">
-        <v>11.26158046722412</v>
+        <v>11.26158142089844</v>
       </c>
       <c r="C10" t="n">
-        <v>11.49647402945097</v>
+        <v>11.49647500301699</v>
       </c>
       <c r="D10" t="n">
-        <v>11.19510141235299</v>
+        <v>11.1951023603976</v>
       </c>
       <c r="E10" t="n">
-        <v>11.28373987040548</v>
+        <v>11.28374082595634</v>
       </c>
       <c r="F10" t="n">
         <v>764200</v>
@@ -632,16 +632,16 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>11.68261623382568</v>
+        <v>11.68261528015137</v>
       </c>
       <c r="C11" t="n">
-        <v>11.68261623382568</v>
+        <v>11.68261528015137</v>
       </c>
       <c r="D11" t="n">
-        <v>10.92918466892529</v>
+        <v>10.92918377675503</v>
       </c>
       <c r="E11" t="n">
-        <v>11.22612524505344</v>
+        <v>11.22612432864335</v>
       </c>
       <c r="F11" t="n">
         <v>1726600</v>
@@ -652,16 +652,16 @@
         <v>44106</v>
       </c>
       <c r="B12" t="n">
-        <v>11.29703617095947</v>
+        <v>11.29703712463379</v>
       </c>
       <c r="C12" t="n">
-        <v>11.55408913981376</v>
+        <v>11.554090115188</v>
       </c>
       <c r="D12" t="n">
-        <v>11.19953361219649</v>
+        <v>11.19953455763982</v>
       </c>
       <c r="E12" t="n">
-        <v>11.51420153729093</v>
+        <v>11.51420250929794</v>
       </c>
       <c r="F12" t="n">
         <v>878600</v>
@@ -692,16 +692,16 @@
         <v>44110</v>
       </c>
       <c r="B14" t="n">
-        <v>11.43885898590088</v>
+        <v>11.43885803222656</v>
       </c>
       <c r="C14" t="n">
-        <v>12.05490040998342</v>
+        <v>12.05489940494884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.38124402661904</v>
+        <v>11.38124307774816</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5895453044252</v>
+        <v>11.58954433818795</v>
       </c>
       <c r="F14" t="n">
         <v>472800</v>
@@ -712,16 +712,16 @@
         <v>44111</v>
       </c>
       <c r="B15" t="n">
-        <v>11.68261623382568</v>
+        <v>11.68261528015137</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82443844714174</v>
+        <v>11.82443748189021</v>
       </c>
       <c r="D15" t="n">
-        <v>11.35465215420053</v>
+        <v>11.35465122729855</v>
       </c>
       <c r="E15" t="n">
-        <v>11.62943248116863</v>
+        <v>11.6294315318358</v>
       </c>
       <c r="F15" t="n">
         <v>437200</v>
@@ -732,16 +732,16 @@
         <v>44112</v>
       </c>
       <c r="B16" t="n">
-        <v>11.52306461334229</v>
+        <v>11.5230655670166</v>
       </c>
       <c r="C16" t="n">
-        <v>11.90421240567286</v>
+        <v>11.90421339089181</v>
       </c>
       <c r="D16" t="n">
-        <v>11.39010651362682</v>
+        <v>11.39010745629723</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68261500926243</v>
+        <v>11.68261597614149</v>
       </c>
       <c r="F16" t="n">
         <v>595200</v>
@@ -752,16 +752,16 @@
         <v>44113</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10365009307861</v>
+        <v>12.1036491394043</v>
       </c>
       <c r="C17" t="n">
-        <v>12.29422399771216</v>
+        <v>12.29422302902209</v>
       </c>
       <c r="D17" t="n">
-        <v>11.531929224505</v>
+        <v>11.53192831587788</v>
       </c>
       <c r="E17" t="n">
-        <v>11.53636127406939</v>
+        <v>11.53636036509305</v>
       </c>
       <c r="F17" t="n">
         <v>672400</v>
@@ -772,16 +772,16 @@
         <v>44117</v>
       </c>
       <c r="B18" t="n">
-        <v>12.18785858154297</v>
+        <v>12.18785762786865</v>
       </c>
       <c r="C18" t="n">
-        <v>12.44934361510042</v>
+        <v>12.44934264096545</v>
       </c>
       <c r="D18" t="n">
-        <v>12.18785858154297</v>
+        <v>12.18785762786865</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36956840549617</v>
+        <v>12.36956743760344</v>
       </c>
       <c r="F18" t="n">
         <v>440800</v>
@@ -852,16 +852,16 @@
         <v>44123</v>
       </c>
       <c r="B22" t="n">
-        <v>12.5379810333252</v>
+        <v>12.53798198699951</v>
       </c>
       <c r="C22" t="n">
-        <v>12.78616987939922</v>
+        <v>12.78617085195148</v>
       </c>
       <c r="D22" t="n">
-        <v>12.30751953930725</v>
+        <v>12.30752047545202</v>
       </c>
       <c r="E22" t="n">
-        <v>12.40945413827893</v>
+        <v>12.40945508217713</v>
       </c>
       <c r="F22" t="n">
         <v>521200</v>
@@ -872,16 +872,16 @@
         <v>44124</v>
       </c>
       <c r="B23" t="n">
-        <v>12.85264873504639</v>
+        <v>12.8526496887207</v>
       </c>
       <c r="C23" t="n">
-        <v>12.87037693216201</v>
+        <v>12.87037788715177</v>
       </c>
       <c r="D23" t="n">
-        <v>12.41388600035818</v>
+        <v>12.41388692147603</v>
       </c>
       <c r="E23" t="n">
-        <v>12.53798084418668</v>
+        <v>12.53798177451245</v>
       </c>
       <c r="F23" t="n">
         <v>729200</v>
@@ -892,16 +892,16 @@
         <v>44125</v>
       </c>
       <c r="B24" t="n">
-        <v>12.85264873504639</v>
+        <v>12.8526496887207</v>
       </c>
       <c r="C24" t="n">
-        <v>12.94571923392254</v>
+        <v>12.94572019450274</v>
       </c>
       <c r="D24" t="n">
-        <v>12.51138854851324</v>
+        <v>12.51138947686584</v>
       </c>
       <c r="E24" t="n">
-        <v>12.85264873504639</v>
+        <v>12.8526496887207</v>
       </c>
       <c r="F24" t="n">
         <v>501200</v>
@@ -932,16 +932,16 @@
         <v>44127</v>
       </c>
       <c r="B26" t="n">
-        <v>12.94128799438477</v>
+        <v>12.94128704071045</v>
       </c>
       <c r="C26" t="n">
-        <v>13.18061273749889</v>
+        <v>13.18061176618817</v>
       </c>
       <c r="D26" t="n">
-        <v>12.86151279823773</v>
+        <v>12.86151185044224</v>
       </c>
       <c r="E26" t="n">
-        <v>13.08754223887867</v>
+        <v>13.08754127442653</v>
       </c>
       <c r="F26" t="n">
         <v>543600</v>
@@ -952,16 +952,16 @@
         <v>44130</v>
       </c>
       <c r="B27" t="n">
-        <v>12.60002994537354</v>
+        <v>12.60002899169922</v>
       </c>
       <c r="C27" t="n">
-        <v>12.87481028388888</v>
+        <v>12.87480930941692</v>
       </c>
       <c r="D27" t="n">
-        <v>12.41832012126036</v>
+        <v>12.41831918133934</v>
       </c>
       <c r="E27" t="n">
-        <v>12.84821882910642</v>
+        <v>12.84821785664712</v>
       </c>
       <c r="F27" t="n">
         <v>307600</v>
@@ -972,16 +972,16 @@
         <v>44131</v>
       </c>
       <c r="B28" t="n">
-        <v>12.22774600982666</v>
+        <v>12.22774505615234</v>
       </c>
       <c r="C28" t="n">
-        <v>12.77730752376721</v>
+        <v>12.77730652723113</v>
       </c>
       <c r="D28" t="n">
-        <v>12.19229045555073</v>
+        <v>12.19228950464168</v>
       </c>
       <c r="E28" t="n">
-        <v>12.67537291088978</v>
+        <v>12.67537192230385</v>
       </c>
       <c r="F28" t="n">
         <v>652400</v>
@@ -992,16 +992,16 @@
         <v>44132</v>
       </c>
       <c r="B29" t="n">
-        <v>11.43885898590088</v>
+        <v>11.43885803222656</v>
       </c>
       <c r="C29" t="n">
-        <v>11.9263734961074</v>
+        <v>11.92637250178829</v>
       </c>
       <c r="D29" t="n">
-        <v>11.30146881736179</v>
+        <v>11.3014678751419</v>
       </c>
       <c r="E29" t="n">
-        <v>11.9263734961074</v>
+        <v>11.92637250178829</v>
       </c>
       <c r="F29" t="n">
         <v>860400</v>
@@ -1092,16 +1092,16 @@
         <v>44140</v>
       </c>
       <c r="B34" t="n">
-        <v>12.79503440856934</v>
+        <v>12.79503536224365</v>
       </c>
       <c r="C34" t="n">
-        <v>13.02992711450884</v>
+        <v>13.02992808569082</v>
       </c>
       <c r="D34" t="n">
-        <v>12.63991605755662</v>
+        <v>12.63991699966924</v>
       </c>
       <c r="E34" t="n">
-        <v>12.78617030957958</v>
+        <v>12.78617126259321</v>
       </c>
       <c r="F34" t="n">
         <v>682600</v>
@@ -1192,16 +1192,16 @@
         <v>44147</v>
       </c>
       <c r="B39" t="n">
-        <v>12.94128799438477</v>
+        <v>12.94128704071045</v>
       </c>
       <c r="C39" t="n">
-        <v>13.35345843226615</v>
+        <v>13.35345744821801</v>
       </c>
       <c r="D39" t="n">
-        <v>12.75071410255063</v>
+        <v>12.75071316292016</v>
       </c>
       <c r="E39" t="n">
-        <v>13.12299778768546</v>
+        <v>13.12299682062052</v>
       </c>
       <c r="F39" t="n">
         <v>656600</v>
@@ -1212,16 +1212,16 @@
         <v>44148</v>
       </c>
       <c r="B40" t="n">
-        <v>13.10970211029053</v>
+        <v>13.10970306396484</v>
       </c>
       <c r="C40" t="n">
-        <v>13.53073750714</v>
+        <v>13.53073849144283</v>
       </c>
       <c r="D40" t="n">
-        <v>12.84378506203439</v>
+        <v>12.84378599636438</v>
       </c>
       <c r="E40" t="n">
-        <v>13.29584395953713</v>
+        <v>13.29584492675246</v>
       </c>
       <c r="F40" t="n">
         <v>720400</v>
@@ -1232,16 +1232,16 @@
         <v>44151</v>
       </c>
       <c r="B41" t="n">
-        <v>13.02106475830078</v>
+        <v>13.02106380462646</v>
       </c>
       <c r="C41" t="n">
-        <v>13.37118910731489</v>
+        <v>13.37118812799716</v>
       </c>
       <c r="D41" t="n">
-        <v>12.65321305426148</v>
+        <v>12.65321212752895</v>
       </c>
       <c r="E41" t="n">
-        <v>13.20720663536447</v>
+        <v>13.20720566805696</v>
       </c>
       <c r="F41" t="n">
         <v>631800</v>
@@ -1252,16 +1252,16 @@
         <v>44152</v>
       </c>
       <c r="B42" t="n">
-        <v>13.02106475830078</v>
+        <v>13.02106380462646</v>
       </c>
       <c r="C42" t="n">
-        <v>13.09197671438291</v>
+        <v>13.09197575551494</v>
       </c>
       <c r="D42" t="n">
-        <v>12.69753270981514</v>
+        <v>12.6975317798366</v>
       </c>
       <c r="E42" t="n">
-        <v>12.93242629252057</v>
+        <v>12.93242534533822</v>
       </c>
       <c r="F42" t="n">
         <v>784800</v>
@@ -1292,16 +1292,16 @@
         <v>44154</v>
       </c>
       <c r="B44" t="n">
-        <v>12.99447154998779</v>
+        <v>12.99447059631348</v>
       </c>
       <c r="C44" t="n">
-        <v>13.07424675015632</v>
+        <v>13.07424579062724</v>
       </c>
       <c r="D44" t="n">
-        <v>12.4803656437095</v>
+        <v>12.48036472776582</v>
       </c>
       <c r="E44" t="n">
-        <v>12.74185064633879</v>
+        <v>12.74184971120452</v>
       </c>
       <c r="F44" t="n">
         <v>711400</v>
@@ -1332,16 +1332,16 @@
         <v>44159</v>
       </c>
       <c r="B46" t="n">
-        <v>13.73903846740723</v>
+        <v>13.73903751373291</v>
       </c>
       <c r="C46" t="n">
-        <v>13.82767776339226</v>
+        <v>13.82767680356518</v>
       </c>
       <c r="D46" t="n">
-        <v>13.27368427680326</v>
+        <v>13.27368335543079</v>
       </c>
       <c r="E46" t="n">
-        <v>13.47312142477911</v>
+        <v>13.47312048956302</v>
       </c>
       <c r="F46" t="n">
         <v>798800</v>
@@ -1352,16 +1352,16 @@
         <v>44160</v>
       </c>
       <c r="B47" t="n">
-        <v>13.65039920806885</v>
+        <v>13.65040016174316</v>
       </c>
       <c r="C47" t="n">
-        <v>13.77449405371565</v>
+        <v>13.77449501605975</v>
       </c>
       <c r="D47" t="n">
-        <v>13.34016336194231</v>
+        <v>13.34016429394225</v>
       </c>
       <c r="E47" t="n">
-        <v>13.61494365864504</v>
+        <v>13.61494460984229</v>
       </c>
       <c r="F47" t="n">
         <v>724200</v>
@@ -1372,16 +1372,16 @@
         <v>44161</v>
       </c>
       <c r="B48" t="n">
-        <v>13.53073883056641</v>
+        <v>13.53073787689209</v>
       </c>
       <c r="C48" t="n">
-        <v>13.73904010198848</v>
+        <v>13.73903913363267</v>
       </c>
       <c r="D48" t="n">
-        <v>13.4465315738949</v>
+        <v>13.44653062615568</v>
       </c>
       <c r="E48" t="n">
-        <v>13.65040079545773</v>
+        <v>13.65039983334939</v>
       </c>
       <c r="F48" t="n">
         <v>209800</v>
@@ -1392,16 +1392,16 @@
         <v>44162</v>
       </c>
       <c r="B49" t="n">
-        <v>13.39334869384766</v>
+        <v>13.39334774017334</v>
       </c>
       <c r="C49" t="n">
-        <v>13.71688159204283</v>
+        <v>13.71688061533133</v>
       </c>
       <c r="D49" t="n">
-        <v>13.38891664369954</v>
+        <v>13.38891569034081</v>
       </c>
       <c r="E49" t="n">
-        <v>13.53073971245775</v>
+        <v>13.5307387490005</v>
       </c>
       <c r="F49" t="n">
         <v>510000</v>
@@ -1432,16 +1432,16 @@
         <v>44166</v>
       </c>
       <c r="B51" t="n">
-        <v>14.1822338104248</v>
+        <v>14.18223285675049</v>
       </c>
       <c r="C51" t="n">
-        <v>14.40383121371269</v>
+        <v>14.40383024513721</v>
       </c>
       <c r="D51" t="n">
-        <v>13.47755400034316</v>
+        <v>13.47755309405454</v>
       </c>
       <c r="E51" t="n">
-        <v>13.73460695434403</v>
+        <v>13.73460603077007</v>
       </c>
       <c r="F51" t="n">
         <v>2351000</v>
@@ -1452,16 +1452,16 @@
         <v>44167</v>
       </c>
       <c r="B52" t="n">
-        <v>14.1822338104248</v>
+        <v>14.18223285675049</v>
       </c>
       <c r="C52" t="n">
-        <v>14.37280771250471</v>
+        <v>14.37280674601539</v>
       </c>
       <c r="D52" t="n">
-        <v>13.93404495543393</v>
+        <v>13.9340440184489</v>
       </c>
       <c r="E52" t="n">
-        <v>14.1822338104248</v>
+        <v>14.18223285675049</v>
       </c>
       <c r="F52" t="n">
         <v>767800</v>
@@ -1472,16 +1472,16 @@
         <v>44168</v>
       </c>
       <c r="B53" t="n">
-        <v>14.35951328277588</v>
+        <v>14.35951232910156</v>
       </c>
       <c r="C53" t="n">
-        <v>14.44371969251193</v>
+        <v>14.44371873324512</v>
       </c>
       <c r="D53" t="n">
-        <v>14.0581398153931</v>
+        <v>14.05813888173424</v>
       </c>
       <c r="E53" t="n">
-        <v>14.31519278502997</v>
+        <v>14.31519183429916</v>
       </c>
       <c r="F53" t="n">
         <v>1033200</v>
@@ -1532,16 +1532,16 @@
         <v>44173</v>
       </c>
       <c r="B56" t="n">
-        <v>14.09359455108643</v>
+        <v>14.09359550476074</v>
       </c>
       <c r="C56" t="n">
-        <v>14.53678935892345</v>
+        <v>14.53679034258752</v>
       </c>
       <c r="D56" t="n">
-        <v>13.89858944427358</v>
+        <v>13.89859038475245</v>
       </c>
       <c r="E56" t="n">
-        <v>14.09359455108643</v>
+        <v>14.09359550476074</v>
       </c>
       <c r="F56" t="n">
         <v>767200</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.00495719909668</v>
+        <v>14.004958152771</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10245976017788</v>
+        <v>14.10246072049168</v>
       </c>
       <c r="D58" t="n">
-        <v>13.5174427030365</v>
+        <v>13.51744362351329</v>
       </c>
       <c r="E58" t="n">
-        <v>13.8852943886831</v>
+        <v>13.88529533420892</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1612,16 +1612,16 @@
         <v>44179</v>
       </c>
       <c r="B60" t="n">
-        <v>13.75676727294922</v>
+        <v>13.7567663192749</v>
       </c>
       <c r="C60" t="n">
-        <v>14.05813903290322</v>
+        <v>14.05813805833661</v>
       </c>
       <c r="D60" t="n">
-        <v>13.61494422403749</v>
+        <v>13.61494328019492</v>
       </c>
       <c r="E60" t="n">
-        <v>13.74347112436552</v>
+        <v>13.74347017161295</v>
       </c>
       <c r="F60" t="n">
         <v>525000</v>
@@ -1672,16 +1672,16 @@
         <v>44182</v>
       </c>
       <c r="B63" t="n">
-        <v>13.73903846740723</v>
+        <v>13.73903751373291</v>
       </c>
       <c r="C63" t="n">
-        <v>14.13348155935396</v>
+        <v>14.13348057829998</v>
       </c>
       <c r="D63" t="n">
-        <v>13.67255941808194</v>
+        <v>13.67255846902217</v>
       </c>
       <c r="E63" t="n">
-        <v>13.91631621405031</v>
+        <v>13.91631524807053</v>
       </c>
       <c r="F63" t="n">
         <v>633000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294364929199</v>
+        <v>15.11294269561768</v>
       </c>
       <c r="C68" t="n">
-        <v>15.13067184897926</v>
+        <v>15.13067089418624</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586848207222</v>
+        <v>14.07586759384061</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348344040167</v>
+        <v>14.13348254853438</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.19715404510498</v>
+        <v>15.19715023040771</v>
       </c>
       <c r="C69" t="n">
-        <v>15.3478403838708</v>
+        <v>15.34783653134916</v>
       </c>
       <c r="D69" t="n">
-        <v>14.74952623407074</v>
+        <v>14.74952253173429</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510702749337</v>
+        <v>15.13510322837077</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1812,16 +1812,16 @@
         <v>44195</v>
       </c>
       <c r="B70" t="n">
-        <v>15.72011947631836</v>
+        <v>15.72012138366699</v>
       </c>
       <c r="C70" t="n">
-        <v>15.91512457198337</v>
+        <v>15.9151265029923</v>
       </c>
       <c r="D70" t="n">
-        <v>15.25033239823193</v>
+        <v>15.2503342485805</v>
       </c>
       <c r="E70" t="n">
-        <v>15.37885929091415</v>
+        <v>15.37886115685711</v>
       </c>
       <c r="F70" t="n">
         <v>2946000</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884868621826</v>
+        <v>14.98884773254395</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171822605652</v>
+        <v>15.94171721175532</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952307751646</v>
+        <v>14.74952213906937</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069472389008</v>
+        <v>15.91069371156276</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.5899715423584</v>
+        <v>14.58997344970703</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135601709469</v>
+        <v>15.28135801482809</v>
       </c>
       <c r="D73" t="n">
-        <v>14.5899715423584</v>
+        <v>14.58997344970703</v>
       </c>
       <c r="E73" t="n">
-        <v>15.13953382083913</v>
+        <v>15.1395358000321</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1892,16 +1892,16 @@
         <v>44203</v>
       </c>
       <c r="B74" t="n">
-        <v>14.40512943267822</v>
+        <v>14.40513038635254</v>
       </c>
       <c r="C74" t="n">
-        <v>14.96994947955643</v>
+        <v>14.96995047062398</v>
       </c>
       <c r="D74" t="n">
-        <v>14.39623442841062</v>
+        <v>14.39623538149606</v>
       </c>
       <c r="E74" t="n">
-        <v>14.68531612918757</v>
+        <v>14.68531710141131</v>
       </c>
       <c r="F74" t="n">
         <v>1215000</v>
@@ -1932,16 +1932,16 @@
         <v>44207</v>
       </c>
       <c r="B76" t="n">
-        <v>15.83274364471436</v>
+        <v>15.83274555206299</v>
       </c>
       <c r="C76" t="n">
-        <v>15.83274364471436</v>
+        <v>15.83274555206299</v>
       </c>
       <c r="D76" t="n">
-        <v>14.80539530952503</v>
+        <v>14.80539709311043</v>
       </c>
       <c r="E76" t="n">
-        <v>14.95215863031701</v>
+        <v>14.95216043158278</v>
       </c>
       <c r="F76" t="n">
         <v>1758200</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422393798828</v>
+        <v>16.38422584533691</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538227998573</v>
+        <v>16.45538419561817</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169386673051</v>
+        <v>15.92169572023429</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93503722223226</v>
+        <v>15.93503907728939</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2052,16 +2052,16 @@
         <v>44215</v>
       </c>
       <c r="B82" t="n">
-        <v>16.63327789306641</v>
+        <v>16.63327980041504</v>
       </c>
       <c r="C82" t="n">
-        <v>17.07801792553825</v>
+        <v>17.07801988388551</v>
       </c>
       <c r="D82" t="n">
-        <v>16.09514116439855</v>
+        <v>16.0951430100387</v>
       </c>
       <c r="E82" t="n">
-        <v>17.07801792553825</v>
+        <v>17.07801988388551</v>
       </c>
       <c r="F82" t="n">
         <v>1918400</v>
@@ -2072,16 +2072,16 @@
         <v>44216</v>
       </c>
       <c r="B83" t="n">
-        <v>16.2552490234375</v>
+        <v>16.25525093078613</v>
       </c>
       <c r="C83" t="n">
-        <v>16.81117410424281</v>
+        <v>16.81117607682225</v>
       </c>
       <c r="D83" t="n">
-        <v>16.0106423271929</v>
+        <v>16.01064420584002</v>
       </c>
       <c r="E83" t="n">
-        <v>16.69998908808175</v>
+        <v>16.69999104761502</v>
       </c>
       <c r="F83" t="n">
         <v>1073000</v>
@@ -2092,16 +2092,16 @@
         <v>44217</v>
       </c>
       <c r="B84" t="n">
-        <v>15.85498523712158</v>
+        <v>15.85498332977295</v>
       </c>
       <c r="C84" t="n">
-        <v>16.36643533398266</v>
+        <v>16.36643336510678</v>
       </c>
       <c r="D84" t="n">
-        <v>15.53032347129166</v>
+        <v>15.53032160299971</v>
       </c>
       <c r="E84" t="n">
-        <v>16.25969866009376</v>
+        <v>16.25969670405826</v>
       </c>
       <c r="F84" t="n">
         <v>928200</v>
@@ -2132,16 +2132,16 @@
         <v>44222</v>
       </c>
       <c r="B86" t="n">
-        <v>14.67197704315186</v>
+        <v>14.67197608947754</v>
       </c>
       <c r="C86" t="n">
-        <v>15.52587724395259</v>
+        <v>15.525876234775</v>
       </c>
       <c r="D86" t="n">
-        <v>14.63639701984405</v>
+        <v>14.63639606848242</v>
       </c>
       <c r="E86" t="n">
-        <v>15.38356054381913</v>
+        <v>15.38355954389209</v>
       </c>
       <c r="F86" t="n">
         <v>1156000</v>
@@ -2152,16 +2152,16 @@
         <v>44223</v>
       </c>
       <c r="B87" t="n">
-        <v>15.00553131103516</v>
+        <v>15.00552940368652</v>
       </c>
       <c r="C87" t="n">
-        <v>15.57034972966033</v>
+        <v>15.5703477505178</v>
       </c>
       <c r="D87" t="n">
-        <v>14.53410620714105</v>
+        <v>14.53410435971512</v>
       </c>
       <c r="E87" t="n">
-        <v>14.74313459133305</v>
+        <v>14.74313271733759</v>
       </c>
       <c r="F87" t="n">
         <v>1909000</v>
@@ -2172,16 +2172,16 @@
         <v>44224</v>
       </c>
       <c r="B88" t="n">
-        <v>15.65929889678955</v>
+        <v>15.65929698944092</v>
       </c>
       <c r="C88" t="n">
-        <v>15.98840732531967</v>
+        <v>15.98840537788466</v>
       </c>
       <c r="D88" t="n">
-        <v>14.95216205263397</v>
+        <v>14.95216023141669</v>
       </c>
       <c r="E88" t="n">
-        <v>15.13450543023138</v>
+        <v>15.13450358680413</v>
       </c>
       <c r="F88" t="n">
         <v>3941600</v>
@@ -2212,16 +2212,16 @@
         <v>44228</v>
       </c>
       <c r="B90" t="n">
-        <v>16.76670074462891</v>
+        <v>16.76670265197754</v>
       </c>
       <c r="C90" t="n">
-        <v>17.02909745013378</v>
+        <v>17.02909938733217</v>
       </c>
       <c r="D90" t="n">
-        <v>15.65929723928157</v>
+        <v>15.65929902065404</v>
       </c>
       <c r="E90" t="n">
-        <v>16.0106422968565</v>
+        <v>16.01064411819733</v>
       </c>
       <c r="F90" t="n">
         <v>3072200</v>
@@ -2232,16 +2232,16 @@
         <v>44229</v>
       </c>
       <c r="B91" t="n">
-        <v>17.08246612548828</v>
+        <v>17.08246803283691</v>
       </c>
       <c r="C91" t="n">
-        <v>17.32262617193124</v>
+        <v>17.32262810609502</v>
       </c>
       <c r="D91" t="n">
-        <v>16.76670108102554</v>
+        <v>16.76670295311732</v>
       </c>
       <c r="E91" t="n">
-        <v>16.76670108102554</v>
+        <v>16.76670295311732</v>
       </c>
       <c r="F91" t="n">
         <v>2620800</v>
@@ -2292,16 +2292,16 @@
         <v>44232</v>
       </c>
       <c r="B94" t="n">
-        <v>18.80806159973145</v>
+        <v>18.80805969238281</v>
       </c>
       <c r="C94" t="n">
-        <v>19.56856685913042</v>
+        <v>19.56856487465802</v>
       </c>
       <c r="D94" t="n">
-        <v>17.78960623557311</v>
+        <v>17.78960443150729</v>
       </c>
       <c r="E94" t="n">
-        <v>17.99863465173679</v>
+        <v>17.99863282647314</v>
       </c>
       <c r="F94" t="n">
         <v>14342200</v>
@@ -2312,16 +2312,16 @@
         <v>44235</v>
       </c>
       <c r="B95" t="n">
-        <v>19.23056221008301</v>
+        <v>19.23056030273438</v>
       </c>
       <c r="C95" t="n">
-        <v>19.36843055199105</v>
+        <v>19.36842863096819</v>
       </c>
       <c r="D95" t="n">
-        <v>18.46560871350112</v>
+        <v>18.46560688202301</v>
       </c>
       <c r="E95" t="n">
-        <v>18.81250544030044</v>
+        <v>18.81250357441601</v>
       </c>
       <c r="F95" t="n">
         <v>1758400</v>
@@ -2332,16 +2332,16 @@
         <v>44236</v>
       </c>
       <c r="B96" t="n">
-        <v>18.84808731079102</v>
+        <v>18.84808540344238</v>
       </c>
       <c r="C96" t="n">
-        <v>19.45293416309373</v>
+        <v>19.4529321945371</v>
       </c>
       <c r="D96" t="n">
-        <v>18.82585064345173</v>
+        <v>18.82584873835336</v>
       </c>
       <c r="E96" t="n">
-        <v>19.45293416309373</v>
+        <v>19.4529321945371</v>
       </c>
       <c r="F96" t="n">
         <v>1201800</v>
@@ -2392,16 +2392,16 @@
         <v>44239</v>
       </c>
       <c r="B99" t="n">
-        <v>18.51897621154785</v>
+        <v>18.51897811889648</v>
       </c>
       <c r="C99" t="n">
-        <v>18.72355623622481</v>
+        <v>18.72355816464402</v>
       </c>
       <c r="D99" t="n">
-        <v>18.16318449546863</v>
+        <v>18.16318636617275</v>
       </c>
       <c r="E99" t="n">
-        <v>18.58123954979312</v>
+        <v>18.58124146355452</v>
       </c>
       <c r="F99" t="n">
         <v>849600</v>
@@ -2492,16 +2492,16 @@
         <v>44250</v>
       </c>
       <c r="B104" t="n">
-        <v>17.70065498352051</v>
+        <v>17.70065689086914</v>
       </c>
       <c r="C104" t="n">
-        <v>18.1009217372794</v>
+        <v>18.1009236877591</v>
       </c>
       <c r="D104" t="n">
-        <v>17.5183116171523</v>
+        <v>17.51831350485237</v>
       </c>
       <c r="E104" t="n">
-        <v>17.86076168502407</v>
+        <v>17.86076360962512</v>
       </c>
       <c r="F104" t="n">
         <v>1151400</v>
@@ -2532,16 +2532,16 @@
         <v>44252</v>
       </c>
       <c r="B106" t="n">
-        <v>16.94459533691406</v>
+        <v>16.9445972442627</v>
       </c>
       <c r="C106" t="n">
-        <v>17.7940487700933</v>
+        <v>17.79405077305967</v>
       </c>
       <c r="D106" t="n">
-        <v>16.6377253111698</v>
+        <v>16.63772718397596</v>
       </c>
       <c r="E106" t="n">
-        <v>17.68731210746428</v>
+        <v>17.68731409841596</v>
       </c>
       <c r="F106" t="n">
         <v>1207600</v>
@@ -2552,16 +2552,16 @@
         <v>44253</v>
       </c>
       <c r="B107" t="n">
-        <v>16.69998931884766</v>
+        <v>16.69998741149902</v>
       </c>
       <c r="C107" t="n">
-        <v>17.20699272810024</v>
+        <v>17.20699076284545</v>
       </c>
       <c r="D107" t="n">
-        <v>16.40201428576187</v>
+        <v>16.40201241244574</v>
       </c>
       <c r="E107" t="n">
-        <v>17.13583438463582</v>
+        <v>17.13583242750821</v>
       </c>
       <c r="F107" t="n">
         <v>1586600</v>
@@ -2612,16 +2612,16 @@
         <v>44258</v>
       </c>
       <c r="B110" t="n">
-        <v>16.1929874420166</v>
+        <v>16.19298934936523</v>
       </c>
       <c r="C110" t="n">
-        <v>16.80228092162542</v>
+        <v>16.80228290074185</v>
       </c>
       <c r="D110" t="n">
-        <v>15.61927228923258</v>
+        <v>15.61927412900413</v>
       </c>
       <c r="E110" t="n">
-        <v>16.80228092162542</v>
+        <v>16.80228290074185</v>
       </c>
       <c r="F110" t="n">
         <v>1368800</v>
@@ -2632,16 +2632,16 @@
         <v>44259</v>
       </c>
       <c r="B111" t="n">
-        <v>16.05066871643066</v>
+        <v>16.0506706237793</v>
       </c>
       <c r="C111" t="n">
-        <v>16.75780547454543</v>
+        <v>16.75780746592523</v>
       </c>
       <c r="D111" t="n">
-        <v>15.79271866916489</v>
+        <v>15.79272054586055</v>
       </c>
       <c r="E111" t="n">
-        <v>16.23301207184145</v>
+        <v>16.23301400085849</v>
       </c>
       <c r="F111" t="n">
         <v>1300400</v>
@@ -2832,16 +2832,16 @@
         <v>44273</v>
       </c>
       <c r="B121" t="n">
-        <v>16.21967315673828</v>
+        <v>16.21967124938965</v>
       </c>
       <c r="C121" t="n">
-        <v>17.29149680698328</v>
+        <v>17.2914947735938</v>
       </c>
       <c r="D121" t="n">
-        <v>16.07735645022393</v>
+        <v>16.077354559611</v>
       </c>
       <c r="E121" t="n">
-        <v>16.58880658408833</v>
+        <v>16.58880463333153</v>
       </c>
       <c r="F121" t="n">
         <v>1568800</v>
@@ -2852,16 +2852,16 @@
         <v>44274</v>
       </c>
       <c r="B122" t="n">
-        <v>16.32196426391602</v>
+        <v>16.32196235656738</v>
       </c>
       <c r="C122" t="n">
-        <v>16.54433434463272</v>
+        <v>16.54433241129841</v>
       </c>
       <c r="D122" t="n">
-        <v>15.8905657644299</v>
+        <v>15.89056390749354</v>
       </c>
       <c r="E122" t="n">
-        <v>16.17519919629943</v>
+        <v>16.17519730610144</v>
       </c>
       <c r="F122" t="n">
         <v>1059200</v>
@@ -2892,16 +2892,16 @@
         <v>44278</v>
       </c>
       <c r="B124" t="n">
-        <v>16.09959030151367</v>
+        <v>16.0995922088623</v>
       </c>
       <c r="C124" t="n">
-        <v>16.49985533236855</v>
+        <v>16.49985728713733</v>
       </c>
       <c r="D124" t="n">
-        <v>15.87277192380211</v>
+        <v>15.87277380427914</v>
       </c>
       <c r="E124" t="n">
-        <v>16.45538200556756</v>
+        <v>16.4553839550675</v>
       </c>
       <c r="F124" t="n">
         <v>855200</v>
@@ -2912,16 +2912,16 @@
         <v>44279</v>
       </c>
       <c r="B125" t="n">
-        <v>15.41024208068848</v>
+        <v>15.41024494171143</v>
       </c>
       <c r="C125" t="n">
-        <v>16.21077376226548</v>
+        <v>16.21077677191293</v>
       </c>
       <c r="D125" t="n">
-        <v>15.21455538979179</v>
+        <v>15.21455821448409</v>
       </c>
       <c r="E125" t="n">
-        <v>16.05066708664038</v>
+        <v>16.05067006656286</v>
       </c>
       <c r="F125" t="n">
         <v>1010400</v>
@@ -2952,16 +2952,16 @@
         <v>44281</v>
       </c>
       <c r="B127" t="n">
-        <v>15.85498523712158</v>
+        <v>15.85498332977295</v>
       </c>
       <c r="C127" t="n">
-        <v>16.41535701641043</v>
+        <v>16.41535504164929</v>
       </c>
       <c r="D127" t="n">
-        <v>15.67264186405827</v>
+        <v>15.67263997864547</v>
       </c>
       <c r="E127" t="n">
-        <v>16.10403860722825</v>
+        <v>16.1040366699186</v>
       </c>
       <c r="F127" t="n">
         <v>1078200</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.5836935043335</v>
+        <v>15.58369445800781</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174858739247</v>
+        <v>16.00174956665047</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245512569351</v>
+        <v>15.39245606766462</v>
       </c>
       <c r="E128" t="n">
-        <v>15.74380021171105</v>
+        <v>15.74380117518341</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514427185059</v>
+        <v>16.09514236450195</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23746097399444</v>
+        <v>16.23745904978063</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48585078476289</v>
+        <v>15.48584894961834</v>
       </c>
       <c r="E129" t="n">
-        <v>15.58814080839448</v>
+        <v>15.58813896112809</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3012,16 +3012,16 @@
         <v>44286</v>
       </c>
       <c r="B130" t="n">
-        <v>16.61549186706543</v>
+        <v>16.6154899597168</v>
       </c>
       <c r="C130" t="n">
-        <v>16.71778189546542</v>
+        <v>16.71777997637457</v>
       </c>
       <c r="D130" t="n">
-        <v>15.94393330700381</v>
+        <v>15.94393147674567</v>
       </c>
       <c r="E130" t="n">
-        <v>16.10848837997462</v>
+        <v>16.10848653082663</v>
       </c>
       <c r="F130" t="n">
         <v>1491400</v>
@@ -3032,16 +3032,16 @@
         <v>44287</v>
       </c>
       <c r="B131" t="n">
-        <v>16.59325408935547</v>
+        <v>16.59325218200684</v>
       </c>
       <c r="C131" t="n">
-        <v>17.04244085328361</v>
+        <v>17.0424388943022</v>
       </c>
       <c r="D131" t="n">
-        <v>16.48651571663801</v>
+        <v>16.48651382155865</v>
       </c>
       <c r="E131" t="n">
-        <v>17.03799419867195</v>
+        <v>17.03799224020167</v>
       </c>
       <c r="F131" t="n">
         <v>1225400</v>
@@ -3052,16 +3052,16 @@
         <v>44291</v>
       </c>
       <c r="B132" t="n">
-        <v>16.86454200744629</v>
+        <v>16.86454582214355</v>
       </c>
       <c r="C132" t="n">
-        <v>17.01130703938433</v>
+        <v>17.01131088727931</v>
       </c>
       <c r="D132" t="n">
-        <v>16.60214700467584</v>
+        <v>16.60215076002032</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90012202605503</v>
+        <v>16.90012584880036</v>
       </c>
       <c r="F132" t="n">
         <v>838600</v>
@@ -3072,16 +3072,16 @@
         <v>44292</v>
       </c>
       <c r="B133" t="n">
-        <v>17.52275848388672</v>
+        <v>17.52276039123535</v>
       </c>
       <c r="C133" t="n">
-        <v>17.56723180984916</v>
+        <v>17.5672337220387</v>
       </c>
       <c r="D133" t="n">
-        <v>16.82896340165162</v>
+        <v>16.8289652334808</v>
       </c>
       <c r="E133" t="n">
-        <v>16.8912267366185</v>
+        <v>16.89122857522503</v>
       </c>
       <c r="F133" t="n">
         <v>1684600</v>
@@ -3092,16 +3092,16 @@
         <v>44293</v>
       </c>
       <c r="B134" t="n">
-        <v>17.37154769897461</v>
+        <v>17.37154579162598</v>
       </c>
       <c r="C134" t="n">
-        <v>17.63839106164878</v>
+        <v>17.63838912500147</v>
       </c>
       <c r="D134" t="n">
-        <v>17.11359764471402</v>
+        <v>17.1135957656876</v>
       </c>
       <c r="E134" t="n">
-        <v>17.47828436542479</v>
+        <v>17.47828244635676</v>
       </c>
       <c r="F134" t="n">
         <v>869400</v>
@@ -3132,16 +3132,16 @@
         <v>44295</v>
       </c>
       <c r="B136" t="n">
-        <v>18.03420829772949</v>
+        <v>18.03421020507812</v>
       </c>
       <c r="C136" t="n">
-        <v>18.25657831791493</v>
+        <v>18.25658024878204</v>
       </c>
       <c r="D136" t="n">
-        <v>17.41157325913943</v>
+        <v>17.41157510063643</v>
       </c>
       <c r="E136" t="n">
-        <v>17.6428365871695</v>
+        <v>17.64283845312556</v>
       </c>
       <c r="F136" t="n">
         <v>1023600</v>
@@ -3152,16 +3152,16 @@
         <v>44298</v>
       </c>
       <c r="B137" t="n">
-        <v>17.74513244628906</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="C137" t="n">
-        <v>18.05644919023704</v>
+        <v>18.05644724942629</v>
       </c>
       <c r="D137" t="n">
-        <v>17.58947237776606</v>
+        <v>17.58947048714867</v>
       </c>
       <c r="E137" t="n">
-        <v>18.05644919023704</v>
+        <v>18.05644724942629</v>
       </c>
       <c r="F137" t="n">
         <v>810600</v>
@@ -3232,16 +3232,16 @@
         <v>44302</v>
       </c>
       <c r="B141" t="n">
-        <v>17.74513244628906</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="C141" t="n">
-        <v>17.74513244628906</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="D141" t="n">
-        <v>17.12249556529509</v>
+        <v>17.12249372487104</v>
       </c>
       <c r="E141" t="n">
-        <v>17.38489231844339</v>
+        <v>17.38489044981543</v>
       </c>
       <c r="F141" t="n">
         <v>774600</v>
@@ -3312,16 +3312,16 @@
         <v>44309</v>
       </c>
       <c r="B145" t="n">
-        <v>17.21144104003906</v>
+        <v>17.2114429473877</v>
       </c>
       <c r="C145" t="n">
-        <v>17.57167941077477</v>
+        <v>17.57168135804453</v>
       </c>
       <c r="D145" t="n">
-        <v>16.88233264191577</v>
+        <v>16.88233451279305</v>
       </c>
       <c r="E145" t="n">
-        <v>17.52275942819921</v>
+        <v>17.52276137004772</v>
       </c>
       <c r="F145" t="n">
         <v>903000</v>
@@ -3372,16 +3372,16 @@
         <v>44314</v>
       </c>
       <c r="B148" t="n">
-        <v>18.56789588928223</v>
+        <v>18.56789779663086</v>
       </c>
       <c r="C148" t="n">
-        <v>18.63905422482831</v>
+        <v>18.63905613948654</v>
       </c>
       <c r="D148" t="n">
-        <v>17.32707082268309</v>
+        <v>17.32707260257054</v>
       </c>
       <c r="E148" t="n">
-        <v>17.33596582669492</v>
+        <v>17.33596760749609</v>
       </c>
       <c r="F148" t="n">
         <v>2195600</v>
@@ -3452,16 +3452,16 @@
         <v>44320</v>
       </c>
       <c r="B152" t="n">
-        <v>19.79606819152832</v>
+        <v>19.79606628417969</v>
       </c>
       <c r="C152" t="n">
-        <v>20.00618961139364</v>
+        <v>20.00618768379984</v>
       </c>
       <c r="D152" t="n">
-        <v>19.25959072829643</v>
+        <v>19.25958887263734</v>
       </c>
       <c r="E152" t="n">
-        <v>19.45182740585503</v>
+        <v>19.45182553167395</v>
       </c>
       <c r="F152" t="n">
         <v>1635200</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.83326148986816</v>
+        <v>20.8332633972168</v>
       </c>
       <c r="C155" t="n">
-        <v>20.877969084305</v>
+        <v>20.87797099574675</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384283351365</v>
+        <v>20.36384469788557</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902756541763</v>
+        <v>20.86902947604076</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3552,16 +3552,16 @@
         <v>44327</v>
       </c>
       <c r="B157" t="n">
-        <v>20.60078620910645</v>
+        <v>20.60078811645508</v>
       </c>
       <c r="C157" t="n">
-        <v>20.60972602144025</v>
+        <v>20.60972792961658</v>
       </c>
       <c r="D157" t="n">
-        <v>19.78265524153291</v>
+        <v>19.7826570731339</v>
       </c>
       <c r="E157" t="n">
-        <v>20.25207383838357</v>
+        <v>20.25207571344624</v>
       </c>
       <c r="F157" t="n">
         <v>1012800</v>
@@ -3572,16 +3572,16 @@
         <v>44328</v>
       </c>
       <c r="B158" t="n">
-        <v>20.15818977355957</v>
+        <v>20.1581916809082</v>
       </c>
       <c r="C158" t="n">
-        <v>20.5963138960601</v>
+        <v>20.59631584486362</v>
       </c>
       <c r="D158" t="n">
-        <v>19.57253317127392</v>
+        <v>19.57253502320829</v>
       </c>
       <c r="E158" t="n">
-        <v>20.5963138960601</v>
+        <v>20.59631584486362</v>
       </c>
       <c r="F158" t="n">
         <v>1344400</v>
@@ -3592,16 +3592,16 @@
         <v>44329</v>
       </c>
       <c r="B159" t="n">
-        <v>20.90478897094727</v>
+        <v>20.9047908782959</v>
       </c>
       <c r="C159" t="n">
-        <v>20.9718495003822</v>
+        <v>20.97185141384942</v>
       </c>
       <c r="D159" t="n">
-        <v>20.1581901566442</v>
+        <v>20.15819199587331</v>
       </c>
       <c r="E159" t="n">
-        <v>20.25654514503674</v>
+        <v>20.25654699323974</v>
       </c>
       <c r="F159" t="n">
         <v>1469200</v>
@@ -3612,16 +3612,16 @@
         <v>44330</v>
       </c>
       <c r="B160" t="n">
-        <v>20.29678153991699</v>
+        <v>20.29678344726562</v>
       </c>
       <c r="C160" t="n">
-        <v>21.23561873883424</v>
+        <v>21.23562073440818</v>
       </c>
       <c r="D160" t="n">
-        <v>20.22972100909998</v>
+        <v>20.22972291014674</v>
       </c>
       <c r="E160" t="n">
-        <v>21.01655581619614</v>
+        <v>21.01655779118409</v>
       </c>
       <c r="F160" t="n">
         <v>1009800</v>
@@ -3632,16 +3632,16 @@
         <v>44333</v>
       </c>
       <c r="B161" t="n">
-        <v>20.98526191711426</v>
+        <v>20.98526000976562</v>
       </c>
       <c r="C161" t="n">
-        <v>21.13279440668424</v>
+        <v>21.13279248592639</v>
       </c>
       <c r="D161" t="n">
-        <v>20.03748317507803</v>
+        <v>20.03748135387293</v>
       </c>
       <c r="E161" t="n">
-        <v>20.16266101683182</v>
+        <v>20.16265918424931</v>
       </c>
       <c r="F161" t="n">
         <v>1096800</v>
@@ -3652,16 +3652,16 @@
         <v>44334</v>
       </c>
       <c r="B162" t="n">
-        <v>21.12385368347168</v>
+        <v>21.12385177612305</v>
       </c>
       <c r="C162" t="n">
-        <v>21.74080480825265</v>
+        <v>21.74080284519728</v>
       </c>
       <c r="D162" t="n">
-        <v>20.88243780350257</v>
+        <v>20.88243591795225</v>
       </c>
       <c r="E162" t="n">
-        <v>21.15067823860833</v>
+        <v>21.15067632883762</v>
       </c>
       <c r="F162" t="n">
         <v>1192600</v>
@@ -3692,16 +3692,16 @@
         <v>44336</v>
       </c>
       <c r="B164" t="n">
-        <v>21.86151504516602</v>
+        <v>21.86151313781738</v>
       </c>
       <c r="C164" t="n">
-        <v>21.9375154012413</v>
+        <v>21.93751348726187</v>
       </c>
       <c r="D164" t="n">
-        <v>21.378683234498</v>
+        <v>21.37868136927493</v>
       </c>
       <c r="E164" t="n">
-        <v>21.49044966784666</v>
+        <v>21.49044779287232</v>
       </c>
       <c r="F164" t="n">
         <v>917400</v>
@@ -3752,16 +3752,16 @@
         <v>44341</v>
       </c>
       <c r="B167" t="n">
-        <v>22.17893028259277</v>
+        <v>22.17892837524414</v>
       </c>
       <c r="C167" t="n">
-        <v>22.3622271566051</v>
+        <v>22.36222523349326</v>
       </c>
       <c r="D167" t="n">
-        <v>21.77210055220345</v>
+        <v>21.77209867984146</v>
       </c>
       <c r="E167" t="n">
-        <v>21.98222027751199</v>
+        <v>21.98221838708007</v>
       </c>
       <c r="F167" t="n">
         <v>773000</v>
@@ -3932,16 +3932,16 @@
         <v>44355</v>
       </c>
       <c r="B176" t="n">
-        <v>23.40388870239258</v>
+        <v>23.40389060974121</v>
       </c>
       <c r="C176" t="n">
-        <v>23.68107066417156</v>
+        <v>23.68107259410971</v>
       </c>
       <c r="D176" t="n">
-        <v>22.95235309597892</v>
+        <v>22.95235496652872</v>
       </c>
       <c r="E176" t="n">
-        <v>23.47094923953079</v>
+        <v>23.47095115234466</v>
       </c>
       <c r="F176" t="n">
         <v>1006800</v>
@@ -4092,16 +4092,16 @@
         <v>44365</v>
       </c>
       <c r="B184" t="n">
-        <v>24.89708709716797</v>
+        <v>24.89709091186523</v>
       </c>
       <c r="C184" t="n">
-        <v>25.19215037765539</v>
+        <v>25.19215423756184</v>
       </c>
       <c r="D184" t="n">
-        <v>24.25778303854185</v>
+        <v>24.25778675528583</v>
       </c>
       <c r="E184" t="n">
-        <v>24.6780258690744</v>
+        <v>24.6780296502074</v>
       </c>
       <c r="F184" t="n">
         <v>1737600</v>
@@ -4152,16 +4152,16 @@
         <v>44370</v>
       </c>
       <c r="B187" t="n">
-        <v>24.72273063659668</v>
+        <v>24.72273254394531</v>
       </c>
       <c r="C187" t="n">
-        <v>24.87920464072016</v>
+        <v>24.87920656014071</v>
       </c>
       <c r="D187" t="n">
-        <v>24.28013658859573</v>
+        <v>24.28013846179841</v>
       </c>
       <c r="E187" t="n">
-        <v>24.71378911875361</v>
+        <v>24.71379102541241</v>
       </c>
       <c r="F187" t="n">
         <v>1264600</v>
@@ -4192,16 +4192,16 @@
         <v>44372</v>
       </c>
       <c r="B189" t="n">
-        <v>24.35166931152344</v>
+        <v>24.3516674041748</v>
       </c>
       <c r="C189" t="n">
-        <v>24.5886135876334</v>
+        <v>24.58861166172607</v>
       </c>
       <c r="D189" t="n">
-        <v>24.00295690459483</v>
+        <v>24.00295502455915</v>
       </c>
       <c r="E189" t="n">
-        <v>24.27119734880301</v>
+        <v>24.27119544775736</v>
       </c>
       <c r="F189" t="n">
         <v>926400</v>
@@ -4272,16 +4272,16 @@
         <v>44378</v>
       </c>
       <c r="B193" t="n">
-        <v>24.92838096618652</v>
+        <v>24.92838287353516</v>
       </c>
       <c r="C193" t="n">
-        <v>25.96557488779945</v>
+        <v>25.96557687450705</v>
       </c>
       <c r="D193" t="n">
-        <v>24.91049963553645</v>
+        <v>24.91050154151692</v>
       </c>
       <c r="E193" t="n">
-        <v>25.25921031180567</v>
+        <v>25.2592122444671</v>
       </c>
       <c r="F193" t="n">
         <v>1991200</v>
@@ -4472,16 +4472,16 @@
         <v>44393</v>
       </c>
       <c r="B203" t="n">
-        <v>28.79102897644043</v>
+        <v>28.7910270690918</v>
       </c>
       <c r="C203" t="n">
-        <v>29.03244484038268</v>
+        <v>29.03244291704072</v>
       </c>
       <c r="D203" t="n">
-        <v>28.15172495086382</v>
+        <v>28.15172308586781</v>
       </c>
       <c r="E203" t="n">
-        <v>28.72844005736358</v>
+        <v>28.72843815416134</v>
       </c>
       <c r="F203" t="n">
         <v>1048600</v>
@@ -4492,16 +4492,16 @@
         <v>44396</v>
       </c>
       <c r="B204" t="n">
-        <v>28.77314567565918</v>
+        <v>28.77314758300781</v>
       </c>
       <c r="C204" t="n">
-        <v>29.12185633897039</v>
+        <v>29.12185826943477</v>
       </c>
       <c r="D204" t="n">
-        <v>28.02207524281956</v>
+        <v>28.02207710038034</v>
       </c>
       <c r="E204" t="n">
-        <v>28.38419903539513</v>
+        <v>28.3842009169608</v>
       </c>
       <c r="F204" t="n">
         <v>866800</v>
@@ -4512,16 +4512,16 @@
         <v>44397</v>
       </c>
       <c r="B205" t="n">
-        <v>29.3990421295166</v>
+        <v>29.39903831481934</v>
       </c>
       <c r="C205" t="n">
-        <v>29.60469194740947</v>
+        <v>29.60468810602794</v>
       </c>
       <c r="D205" t="n">
-        <v>28.66138302371869</v>
+        <v>28.661379304737</v>
       </c>
       <c r="E205" t="n">
-        <v>28.84020999040314</v>
+        <v>28.8402062482176</v>
       </c>
       <c r="F205" t="n">
         <v>665800</v>
@@ -4532,16 +4532,16 @@
         <v>44398</v>
       </c>
       <c r="B206" t="n">
-        <v>29.60469055175781</v>
+        <v>29.60468864440918</v>
       </c>
       <c r="C206" t="n">
-        <v>29.78351751001183</v>
+        <v>29.78351559114187</v>
       </c>
       <c r="D206" t="n">
-        <v>29.05926986396128</v>
+        <v>29.0592679917526</v>
       </c>
       <c r="E206" t="n">
-        <v>29.52869020302303</v>
+        <v>29.52868830057088</v>
       </c>
       <c r="F206" t="n">
         <v>1050200</v>
@@ -4592,16 +4592,16 @@
         <v>44403</v>
       </c>
       <c r="B209" t="n">
-        <v>30.08752250671387</v>
+        <v>30.0875244140625</v>
       </c>
       <c r="C209" t="n">
-        <v>30.48987890178793</v>
+        <v>30.48988083464328</v>
       </c>
       <c r="D209" t="n">
-        <v>29.56445305360459</v>
+        <v>29.5644549277941</v>
       </c>
       <c r="E209" t="n">
-        <v>30.48987890178793</v>
+        <v>30.48988083464328</v>
       </c>
       <c r="F209" t="n">
         <v>1240800</v>
@@ -4652,16 +4652,16 @@
         <v>44406</v>
       </c>
       <c r="B212" t="n">
-        <v>30.8475284576416</v>
+        <v>30.84753227233887</v>
       </c>
       <c r="C212" t="n">
-        <v>31.51365529103951</v>
+        <v>31.51365918811201</v>
       </c>
       <c r="D212" t="n">
-        <v>29.56444887215321</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="E212" t="n">
-        <v>29.56444887215321</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="F212" t="n">
         <v>1386000</v>
@@ -4672,16 +4672,16 @@
         <v>44407</v>
       </c>
       <c r="B213" t="n">
-        <v>31.13812446594238</v>
+        <v>31.13812637329102</v>
       </c>
       <c r="C213" t="n">
-        <v>31.58071852233474</v>
+        <v>31.58072045679423</v>
       </c>
       <c r="D213" t="n">
-        <v>30.41387685570368</v>
+        <v>30.41387871868892</v>
       </c>
       <c r="E213" t="n">
-        <v>30.80282521486082</v>
+        <v>30.80282710167089</v>
       </c>
       <c r="F213" t="n">
         <v>1548200</v>
@@ -4712,16 +4712,16 @@
         <v>44411</v>
       </c>
       <c r="B215" t="n">
-        <v>30.62400245666504</v>
+        <v>30.62400054931641</v>
       </c>
       <c r="C215" t="n">
-        <v>31.14260033985012</v>
+        <v>31.14259840020176</v>
       </c>
       <c r="D215" t="n">
-        <v>30.20375957965926</v>
+        <v>30.20375769848453</v>
       </c>
       <c r="E215" t="n">
-        <v>31.13812872752174</v>
+        <v>31.13812678815189</v>
       </c>
       <c r="F215" t="n">
         <v>1467200</v>
@@ -4732,16 +4732,16 @@
         <v>44412</v>
       </c>
       <c r="B216" t="n">
-        <v>29.78798484802246</v>
+        <v>29.78798675537109</v>
       </c>
       <c r="C216" t="n">
-        <v>30.84753173103446</v>
+        <v>30.84753370622673</v>
       </c>
       <c r="D216" t="n">
-        <v>29.75669038704778</v>
+        <v>29.7566922923926</v>
       </c>
       <c r="E216" t="n">
-        <v>30.62399889240378</v>
+        <v>30.62400085328306</v>
       </c>
       <c r="F216" t="n">
         <v>1263400</v>
@@ -4752,16 +4752,16 @@
         <v>44413</v>
       </c>
       <c r="B217" t="n">
-        <v>29.48397827148438</v>
+        <v>29.48398208618164</v>
       </c>
       <c r="C217" t="n">
-        <v>30.38705279511604</v>
+        <v>30.38705672665493</v>
       </c>
       <c r="D217" t="n">
-        <v>29.13973922154018</v>
+        <v>29.13974299169909</v>
       </c>
       <c r="E217" t="n">
-        <v>29.82374912073076</v>
+        <v>29.82375297938827</v>
       </c>
       <c r="F217" t="n">
         <v>1197200</v>
@@ -4772,16 +4772,16 @@
         <v>44414</v>
       </c>
       <c r="B218" t="n">
-        <v>29.46163177490234</v>
+        <v>29.46162986755371</v>
       </c>
       <c r="C218" t="n">
-        <v>29.99810927720156</v>
+        <v>29.99810733512132</v>
       </c>
       <c r="D218" t="n">
-        <v>29.10397783280902</v>
+        <v>29.10397594861493</v>
       </c>
       <c r="E218" t="n">
-        <v>29.97575803759621</v>
+        <v>29.975756096963</v>
       </c>
       <c r="F218" t="n">
         <v>684400</v>
@@ -4792,16 +4792,16 @@
         <v>44417</v>
       </c>
       <c r="B219" t="n">
-        <v>30.23952293395996</v>
+        <v>30.23952102661133</v>
       </c>
       <c r="C219" t="n">
-        <v>30.40493846680823</v>
+        <v>30.40493654902606</v>
       </c>
       <c r="D219" t="n">
-        <v>29.5421015505228</v>
+        <v>29.54209968716381</v>
       </c>
       <c r="E219" t="n">
-        <v>29.85951778044203</v>
+        <v>29.85951589706211</v>
       </c>
       <c r="F219" t="n">
         <v>1023000</v>
@@ -4812,16 +4812,16 @@
         <v>44418</v>
       </c>
       <c r="B220" t="n">
-        <v>29.59574890136719</v>
+        <v>29.59574699401855</v>
       </c>
       <c r="C220" t="n">
-        <v>30.78494533776667</v>
+        <v>30.78494335377824</v>
       </c>
       <c r="D220" t="n">
-        <v>29.59574890136719</v>
+        <v>29.59574699401855</v>
       </c>
       <c r="E220" t="n">
-        <v>30.48988032933406</v>
+        <v>30.4898783643616</v>
       </c>
       <c r="F220" t="n">
         <v>1186200</v>
@@ -4832,16 +4832,16 @@
         <v>44419</v>
       </c>
       <c r="B221" t="n">
-        <v>29.11291885375977</v>
+        <v>29.1129207611084</v>
       </c>
       <c r="C221" t="n">
-        <v>30.38258377149235</v>
+        <v>30.38258576202377</v>
       </c>
       <c r="D221" t="n">
-        <v>28.14725532970356</v>
+        <v>28.14725717378623</v>
       </c>
       <c r="E221" t="n">
-        <v>29.68516238912321</v>
+        <v>29.68516433396269</v>
       </c>
       <c r="F221" t="n">
         <v>1237750</v>
@@ -4852,16 +4852,16 @@
         <v>44420</v>
       </c>
       <c r="B222" t="n">
-        <v>29.32750701904297</v>
+        <v>29.32750511169434</v>
       </c>
       <c r="C222" t="n">
-        <v>31.18730182754265</v>
+        <v>31.18729979924009</v>
       </c>
       <c r="D222" t="n">
-        <v>28.46914175858482</v>
+        <v>28.46913990706097</v>
       </c>
       <c r="E222" t="n">
-        <v>28.48702479453274</v>
+        <v>28.48702294184585</v>
       </c>
       <c r="F222" t="n">
         <v>1567750</v>
@@ -4872,16 +4872,16 @@
         <v>44421</v>
       </c>
       <c r="B223" t="n">
-        <v>28.34396743774414</v>
+        <v>28.34396362304688</v>
       </c>
       <c r="C223" t="n">
-        <v>29.59574941199067</v>
+        <v>29.59574542882125</v>
       </c>
       <c r="D223" t="n">
-        <v>27.18159553808027</v>
+        <v>27.18159187982183</v>
       </c>
       <c r="E223" t="n">
-        <v>29.50633763198762</v>
+        <v>29.50633366085176</v>
       </c>
       <c r="F223" t="n">
         <v>1962050</v>
@@ -4892,16 +4892,16 @@
         <v>44424</v>
       </c>
       <c r="B224" t="n">
-        <v>25.6436882019043</v>
+        <v>25.64369010925293</v>
       </c>
       <c r="C224" t="n">
-        <v>28.14725537891694</v>
+        <v>28.14725747247807</v>
       </c>
       <c r="D224" t="n">
-        <v>24.26672506075316</v>
+        <v>24.26672686568483</v>
       </c>
       <c r="E224" t="n">
-        <v>28.14725537891694</v>
+        <v>28.14725747247807</v>
       </c>
       <c r="F224" t="n">
         <v>6674400</v>
@@ -4932,16 +4932,16 @@
         <v>44426</v>
       </c>
       <c r="B226" t="n">
-        <v>25.75098419189453</v>
+        <v>25.7509822845459</v>
       </c>
       <c r="C226" t="n">
-        <v>26.43052427516607</v>
+        <v>26.43052231748461</v>
       </c>
       <c r="D226" t="n">
-        <v>24.89261884802754</v>
+        <v>24.89261700425713</v>
       </c>
       <c r="E226" t="n">
-        <v>25.39333196528328</v>
+        <v>25.39333008442558</v>
       </c>
       <c r="F226" t="n">
         <v>2048900</v>
@@ -4952,16 +4952,16 @@
         <v>44427</v>
       </c>
       <c r="B227" t="n">
-        <v>26.4662914276123</v>
+        <v>26.46628952026367</v>
       </c>
       <c r="C227" t="n">
-        <v>26.73453018213193</v>
+        <v>26.73452825545211</v>
       </c>
       <c r="D227" t="n">
-        <v>24.30249323678068</v>
+        <v>24.30249148537069</v>
       </c>
       <c r="E227" t="n">
-        <v>24.85685378423334</v>
+        <v>24.8568519928722</v>
       </c>
       <c r="F227" t="n">
         <v>1738450</v>
@@ -5012,16 +5012,16 @@
         <v>44432</v>
       </c>
       <c r="B230" t="n">
-        <v>27.48559761047363</v>
+        <v>27.48559951782227</v>
       </c>
       <c r="C230" t="n">
-        <v>27.84324981090064</v>
+        <v>27.84325174306836</v>
       </c>
       <c r="D230" t="n">
-        <v>27.00276756625223</v>
+        <v>27.00276944009512</v>
       </c>
       <c r="E230" t="n">
-        <v>27.64654152702084</v>
+        <v>27.64654344553809</v>
       </c>
       <c r="F230" t="n">
         <v>835550</v>
@@ -5032,16 +5032,16 @@
         <v>44433</v>
       </c>
       <c r="B231" t="n">
-        <v>27.89689826965332</v>
+        <v>27.89690017700195</v>
       </c>
       <c r="C231" t="n">
-        <v>28.4154943745372</v>
+        <v>28.41549631734295</v>
       </c>
       <c r="D231" t="n">
-        <v>27.2710056544327</v>
+        <v>27.27100751898821</v>
       </c>
       <c r="E231" t="n">
-        <v>27.48559696968601</v>
+        <v>27.48559884891342</v>
       </c>
       <c r="F231" t="n">
         <v>1098800</v>
@@ -5092,16 +5092,16 @@
         <v>44438</v>
       </c>
       <c r="B234" t="n">
-        <v>27.68230819702148</v>
+        <v>27.68230628967285</v>
       </c>
       <c r="C234" t="n">
-        <v>29.68516409685458</v>
+        <v>29.68516205150646</v>
       </c>
       <c r="D234" t="n">
-        <v>27.55713034281455</v>
+        <v>27.55712844409084</v>
       </c>
       <c r="E234" t="n">
-        <v>28.96985963650016</v>
+        <v>28.96985764043749</v>
       </c>
       <c r="F234" t="n">
         <v>1402700</v>
@@ -5132,16 +5132,16 @@
         <v>44440</v>
       </c>
       <c r="B236" t="n">
-        <v>26.59146690368652</v>
+        <v>26.59146499633789</v>
       </c>
       <c r="C236" t="n">
-        <v>27.25312391693015</v>
+        <v>27.25312196212229</v>
       </c>
       <c r="D236" t="n">
-        <v>25.71521856496552</v>
+        <v>25.71521672046829</v>
       </c>
       <c r="E236" t="n">
-        <v>26.55570253548375</v>
+        <v>26.55570063070043</v>
       </c>
       <c r="F236" t="n">
         <v>1751800</v>
@@ -5172,16 +5172,16 @@
         <v>44442</v>
       </c>
       <c r="B238" t="n">
-        <v>25.03567695617676</v>
+        <v>25.03567886352539</v>
       </c>
       <c r="C238" t="n">
-        <v>25.84039480296984</v>
+        <v>25.84039677162608</v>
       </c>
       <c r="D238" t="n">
-        <v>24.80320260836184</v>
+        <v>24.80320449799936</v>
       </c>
       <c r="E238" t="n">
-        <v>25.57215608917886</v>
+        <v>25.57215803739928</v>
       </c>
       <c r="F238" t="n">
         <v>2369000</v>
@@ -5212,16 +5212,16 @@
         <v>44447</v>
       </c>
       <c r="B240" t="n">
-        <v>24.4813175201416</v>
+        <v>24.48131561279297</v>
       </c>
       <c r="C240" t="n">
-        <v>26.10863813649156</v>
+        <v>26.10863610235777</v>
       </c>
       <c r="D240" t="n">
-        <v>24.32037529715434</v>
+        <v>24.32037340234477</v>
       </c>
       <c r="E240" t="n">
-        <v>25.59004198130058</v>
+        <v>25.59003998757081</v>
       </c>
       <c r="F240" t="n">
         <v>1259500</v>
@@ -5232,16 +5232,16 @@
         <v>44448</v>
       </c>
       <c r="B241" t="n">
-        <v>25.03567695617676</v>
+        <v>25.03567886352539</v>
       </c>
       <c r="C241" t="n">
-        <v>25.75098132989946</v>
+        <v>25.75098329174372</v>
       </c>
       <c r="D241" t="n">
-        <v>23.80177648515005</v>
+        <v>23.8017782984937</v>
       </c>
       <c r="E241" t="n">
-        <v>23.99848476156876</v>
+        <v>23.99848658989868</v>
       </c>
       <c r="F241" t="n">
         <v>1540350</v>
@@ -5272,16 +5272,16 @@
         <v>44452</v>
       </c>
       <c r="B243" t="n">
-        <v>26.48417091369629</v>
+        <v>26.48417282104492</v>
       </c>
       <c r="C243" t="n">
-        <v>26.82394007087584</v>
+        <v>26.82394200269411</v>
       </c>
       <c r="D243" t="n">
-        <v>25.16085524074708</v>
+        <v>25.16085705279258</v>
       </c>
       <c r="E243" t="n">
-        <v>25.37544655666366</v>
+        <v>25.3754483841637</v>
       </c>
       <c r="F243" t="n">
         <v>1238850</v>
@@ -5292,16 +5292,16 @@
         <v>44453</v>
       </c>
       <c r="B244" t="n">
-        <v>26.34110832214355</v>
+        <v>26.34111022949219</v>
       </c>
       <c r="C244" t="n">
-        <v>27.0206483416944</v>
+        <v>27.02065029824824</v>
       </c>
       <c r="D244" t="n">
-        <v>25.84039525183984</v>
+        <v>25.84039712293205</v>
       </c>
       <c r="E244" t="n">
-        <v>26.60934874601425</v>
+        <v>26.60935067278606</v>
       </c>
       <c r="F244" t="n">
         <v>937200</v>
@@ -5332,16 +5332,16 @@
         <v>44455</v>
       </c>
       <c r="B246" t="n">
-        <v>25.75098419189453</v>
+        <v>25.7509822845459</v>
       </c>
       <c r="C246" t="n">
-        <v>26.66299864881847</v>
+        <v>26.66299667391787</v>
       </c>
       <c r="D246" t="n">
-        <v>25.73310285962922</v>
+        <v>25.73310095360504</v>
       </c>
       <c r="E246" t="n">
-        <v>26.16228553156272</v>
+        <v>26.16228359374943</v>
       </c>
       <c r="F246" t="n">
         <v>615650</v>
@@ -5352,16 +5352,16 @@
         <v>44456</v>
       </c>
       <c r="B247" t="n">
-        <v>24.98203086853027</v>
+        <v>24.98203277587891</v>
       </c>
       <c r="C247" t="n">
-        <v>26.00134008105472</v>
+        <v>26.00134206622641</v>
       </c>
       <c r="D247" t="n">
-        <v>24.98203086853027</v>
+        <v>24.98203277587891</v>
       </c>
       <c r="E247" t="n">
-        <v>25.64368787538125</v>
+        <v>25.64368983324662</v>
       </c>
       <c r="F247" t="n">
         <v>2806100</v>
@@ -5472,16 +5472,16 @@
         <v>44466</v>
       </c>
       <c r="B253" t="n">
-        <v>26.01922416687012</v>
+        <v>26.01922225952148</v>
       </c>
       <c r="C253" t="n">
-        <v>26.34111031224558</v>
+        <v>26.34110838130097</v>
       </c>
       <c r="D253" t="n">
-        <v>25.57215846539613</v>
+        <v>25.57215659081981</v>
       </c>
       <c r="E253" t="n">
-        <v>26.21593246156736</v>
+        <v>26.21593053979895</v>
       </c>
       <c r="F253" t="n">
         <v>663500</v>
@@ -5512,16 +5512,16 @@
         <v>44468</v>
       </c>
       <c r="B255" t="n">
-        <v>24.67803001403809</v>
+        <v>24.67802810668945</v>
       </c>
       <c r="C255" t="n">
-        <v>25.39333453978159</v>
+        <v>25.39333257714754</v>
       </c>
       <c r="D255" t="n">
-        <v>24.46343865631503</v>
+        <v>24.46343676555203</v>
       </c>
       <c r="E255" t="n">
-        <v>25.10721272948419</v>
+        <v>25.10721078896431</v>
       </c>
       <c r="F255" t="n">
         <v>580300</v>
@@ -5532,16 +5532,16 @@
         <v>44469</v>
       </c>
       <c r="B256" t="n">
-        <v>24.4455509185791</v>
+        <v>24.44555473327637</v>
       </c>
       <c r="C256" t="n">
-        <v>24.89261658760151</v>
+        <v>24.89262047206281</v>
       </c>
       <c r="D256" t="n">
-        <v>24.07001568838347</v>
+        <v>24.07001944447894</v>
       </c>
       <c r="E256" t="n">
-        <v>24.85685051547803</v>
+        <v>24.85685439435808</v>
       </c>
       <c r="F256" t="n">
         <v>989250</v>
@@ -5552,16 +5552,16 @@
         <v>44470</v>
       </c>
       <c r="B257" t="n">
-        <v>25.03567695617676</v>
+        <v>25.03567886352539</v>
       </c>
       <c r="C257" t="n">
-        <v>25.10720739354903</v>
+        <v>25.10720930634723</v>
       </c>
       <c r="D257" t="n">
-        <v>24.23095910938368</v>
+        <v>24.2309609554247</v>
       </c>
       <c r="E257" t="n">
-        <v>24.74955520668767</v>
+        <v>24.74955709223806</v>
       </c>
       <c r="F257" t="n">
         <v>904400</v>
@@ -5612,16 +5612,16 @@
         <v>44475</v>
       </c>
       <c r="B260" t="n">
-        <v>23.60506820678711</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="C260" t="n">
-        <v>23.60506820678711</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="D260" t="n">
-        <v>22.37116764671513</v>
+        <v>22.37116583906875</v>
       </c>
       <c r="E260" t="n">
-        <v>22.97917726096693</v>
+        <v>22.97917540419186</v>
       </c>
       <c r="F260" t="n">
         <v>1199850</v>
@@ -5632,16 +5632,16 @@
         <v>44476</v>
       </c>
       <c r="B261" t="n">
-        <v>23.62295150756836</v>
+        <v>23.62294960021973</v>
       </c>
       <c r="C261" t="n">
-        <v>24.26672549756607</v>
+        <v>24.26672353823827</v>
       </c>
       <c r="D261" t="n">
-        <v>23.42624321475746</v>
+        <v>23.42624132329132</v>
       </c>
       <c r="E261" t="n">
-        <v>24.1594306852766</v>
+        <v>24.15942873461192</v>
       </c>
       <c r="F261" t="n">
         <v>699850</v>
@@ -5672,16 +5672,16 @@
         <v>44480</v>
       </c>
       <c r="B263" t="n">
-        <v>24.08790016174316</v>
+        <v>24.0879020690918</v>
       </c>
       <c r="C263" t="n">
-        <v>24.60649630053641</v>
+        <v>24.60649824894896</v>
       </c>
       <c r="D263" t="n">
-        <v>23.73024794626857</v>
+        <v>23.73024982529728</v>
       </c>
       <c r="E263" t="n">
-        <v>24.03425105035676</v>
+        <v>24.0342529534573</v>
       </c>
       <c r="F263" t="n">
         <v>770500</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35613632202148</v>
+        <v>24.35613822937012</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991024181488</v>
+        <v>24.99991219957796</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848414435849</v>
+        <v>23.99848602369909</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307545095629</v>
+        <v>24.21307734710171</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5712,16 +5712,16 @@
         <v>44483</v>
       </c>
       <c r="B265" t="n">
-        <v>24.37401962280273</v>
+        <v>24.37402153015137</v>
       </c>
       <c r="C265" t="n">
-        <v>24.91049874785196</v>
+        <v>24.91050069718188</v>
       </c>
       <c r="D265" t="n">
-        <v>23.9269539694984</v>
+        <v>23.92695584186265</v>
       </c>
       <c r="E265" t="n">
-        <v>24.51708049542651</v>
+        <v>24.51708241397014</v>
       </c>
       <c r="F265" t="n">
         <v>635500</v>
@@ -5732,16 +5732,16 @@
         <v>44484</v>
       </c>
       <c r="B266" t="n">
-        <v>26.16228485107422</v>
+        <v>26.16228675842285</v>
       </c>
       <c r="C266" t="n">
-        <v>26.59146751184455</v>
+        <v>26.59146945048253</v>
       </c>
       <c r="D266" t="n">
-        <v>24.44555250257259</v>
+        <v>24.44555428476369</v>
       </c>
       <c r="E266" t="n">
-        <v>24.76744035086049</v>
+        <v>24.76744215651866</v>
       </c>
       <c r="F266" t="n">
         <v>2075800</v>
@@ -5812,16 +5812,16 @@
         <v>44490</v>
       </c>
       <c r="B270" t="n">
-        <v>22.44269943237305</v>
+        <v>22.44269752502441</v>
       </c>
       <c r="C270" t="n">
-        <v>23.46200872584448</v>
+        <v>23.46200673186731</v>
       </c>
       <c r="D270" t="n">
-        <v>21.67374585004456</v>
+        <v>21.67374400804736</v>
       </c>
       <c r="E270" t="n">
-        <v>22.88976515132303</v>
+        <v>22.8897632059794</v>
       </c>
       <c r="F270" t="n">
         <v>1908000</v>
@@ -5832,16 +5832,16 @@
         <v>44491</v>
       </c>
       <c r="B271" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="C271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563060373434</v>
       </c>
       <c r="D271" t="n">
-        <v>19.81395151866856</v>
+        <v>19.81394972618147</v>
       </c>
       <c r="E271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563060373434</v>
       </c>
       <c r="F271" t="n">
         <v>3185950</v>
@@ -5852,16 +5852,16 @@
         <v>44494</v>
       </c>
       <c r="B272" t="n">
-        <v>21.62009620666504</v>
+        <v>21.62009811401367</v>
       </c>
       <c r="C272" t="n">
-        <v>22.28175319767261</v>
+        <v>22.28175516339335</v>
       </c>
       <c r="D272" t="n">
-        <v>20.79749530060315</v>
+        <v>20.79749713538103</v>
       </c>
       <c r="E272" t="n">
-        <v>20.833259667604</v>
+        <v>20.83326150553705</v>
       </c>
       <c r="F272" t="n">
         <v>1833600</v>
@@ -5872,16 +5872,16 @@
         <v>44495</v>
       </c>
       <c r="B273" t="n">
-        <v>20.29678153991699</v>
+        <v>20.29678344726562</v>
       </c>
       <c r="C273" t="n">
-        <v>21.53068200467281</v>
+        <v>21.53068402797473</v>
       </c>
       <c r="D273" t="n">
-        <v>20.17160199608659</v>
+        <v>20.17160389167173</v>
       </c>
       <c r="E273" t="n">
-        <v>21.45915156766407</v>
+        <v>21.45915358424406</v>
       </c>
       <c r="F273" t="n">
         <v>1532000</v>
@@ -5892,16 +5892,16 @@
         <v>44496</v>
       </c>
       <c r="B274" t="n">
-        <v>20.49349212646484</v>
+        <v>20.49348831176758</v>
       </c>
       <c r="C274" t="n">
-        <v>21.10150176231677</v>
+        <v>21.10149783444344</v>
       </c>
       <c r="D274" t="n">
-        <v>20.31466516106592</v>
+        <v>20.31466137965585</v>
       </c>
       <c r="E274" t="n">
-        <v>20.42196168138934</v>
+        <v>20.42195788000689</v>
       </c>
       <c r="F274" t="n">
         <v>1013650</v>
@@ -5912,16 +5912,16 @@
         <v>44497</v>
       </c>
       <c r="B275" t="n">
-        <v>19.29535484313965</v>
+        <v>19.29535675048828</v>
       </c>
       <c r="C275" t="n">
-        <v>20.76172974015886</v>
+        <v>20.76173179245886</v>
       </c>
       <c r="D275" t="n">
-        <v>19.29535484313965</v>
+        <v>19.29535675048828</v>
       </c>
       <c r="E275" t="n">
-        <v>20.74384840892759</v>
+        <v>20.74385045946002</v>
       </c>
       <c r="F275" t="n">
         <v>1280700</v>
@@ -5952,16 +5952,16 @@
         <v>44501</v>
       </c>
       <c r="B277" t="n">
-        <v>18.77676010131836</v>
+        <v>18.77675819396973</v>
       </c>
       <c r="C277" t="n">
-        <v>19.40265278686379</v>
+        <v>19.40265081593679</v>
       </c>
       <c r="D277" t="n">
-        <v>18.68734661689468</v>
+        <v>18.68734471862869</v>
       </c>
       <c r="E277" t="n">
-        <v>18.77676010131836</v>
+        <v>18.77675819396973</v>
       </c>
       <c r="F277" t="n">
         <v>1843300</v>
@@ -5972,16 +5972,16 @@
         <v>44503</v>
       </c>
       <c r="B278" t="n">
-        <v>20.11795425415039</v>
+        <v>20.11795616149902</v>
       </c>
       <c r="C278" t="n">
-        <v>20.36831163215328</v>
+        <v>20.36831356323787</v>
       </c>
       <c r="D278" t="n">
-        <v>18.41910512488394</v>
+        <v>18.41910687116761</v>
       </c>
       <c r="E278" t="n">
-        <v>18.47275252537737</v>
+        <v>18.47275427674726</v>
       </c>
       <c r="F278" t="n">
         <v>1851600</v>
@@ -5992,16 +5992,16 @@
         <v>44504</v>
       </c>
       <c r="B279" t="n">
-        <v>19.97489547729492</v>
+        <v>19.97489356994629</v>
       </c>
       <c r="C279" t="n">
-        <v>21.31609256822115</v>
+        <v>21.31609053280524</v>
       </c>
       <c r="D279" t="n">
-        <v>19.58147718643888</v>
+        <v>19.58147531665669</v>
       </c>
       <c r="E279" t="n">
-        <v>20.04642592059417</v>
+        <v>20.04642400641529</v>
       </c>
       <c r="F279" t="n">
         <v>1953350</v>
@@ -6012,16 +6012,16 @@
         <v>44505</v>
       </c>
       <c r="B280" t="n">
-        <v>20.42196083068848</v>
+        <v>20.42196273803711</v>
       </c>
       <c r="C280" t="n">
-        <v>20.94055696223821</v>
+        <v>20.94055891802213</v>
       </c>
       <c r="D280" t="n">
-        <v>19.99277817811358</v>
+        <v>19.99278004537787</v>
       </c>
       <c r="E280" t="n">
-        <v>20.20736950440103</v>
+        <v>20.20737139170749</v>
       </c>
       <c r="F280" t="n">
         <v>901950</v>
@@ -6072,16 +6072,16 @@
         <v>44510</v>
       </c>
       <c r="B283" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="C283" t="n">
-        <v>21.65586170945009</v>
+        <v>21.65585975033293</v>
       </c>
       <c r="D283" t="n">
-        <v>20.49349158152647</v>
+        <v>20.49348972756417</v>
       </c>
       <c r="E283" t="n">
-        <v>20.88690987169059</v>
+        <v>20.88690798213735</v>
       </c>
       <c r="F283" t="n">
         <v>1309800</v>
@@ -6092,16 +6092,16 @@
         <v>44511</v>
       </c>
       <c r="B284" t="n">
-        <v>21.94198608398438</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C284" t="n">
-        <v>22.99705973754176</v>
+        <v>22.99705773847886</v>
       </c>
       <c r="D284" t="n">
-        <v>21.78104215391382</v>
+        <v>21.78104026055555</v>
       </c>
       <c r="E284" t="n">
-        <v>21.95986741644305</v>
+        <v>21.95986550754004</v>
       </c>
       <c r="F284" t="n">
         <v>2031350</v>
@@ -6112,16 +6112,16 @@
         <v>44512</v>
       </c>
       <c r="B285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="C285" t="n">
-        <v>22.12081044278765</v>
+        <v>22.12080844160848</v>
       </c>
       <c r="D285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="E285" t="n">
-        <v>21.76315822692041</v>
+        <v>21.76315625809657</v>
       </c>
       <c r="F285" t="n">
         <v>1307150</v>
@@ -6252,16 +6252,16 @@
         <v>44524</v>
       </c>
       <c r="B292" t="n">
-        <v>19.58147430419922</v>
+        <v>19.58147621154785</v>
       </c>
       <c r="C292" t="n">
-        <v>20.33254470099985</v>
+        <v>20.33254668150708</v>
       </c>
       <c r="D292" t="n">
-        <v>19.02711387658259</v>
+        <v>19.02711572993332</v>
       </c>
       <c r="E292" t="n">
-        <v>19.04499520571019</v>
+        <v>19.04499706080266</v>
       </c>
       <c r="F292" t="n">
         <v>1594900</v>
@@ -6272,16 +6272,16 @@
         <v>44525</v>
       </c>
       <c r="B293" t="n">
-        <v>20.29678153991699</v>
+        <v>20.29678344726562</v>
       </c>
       <c r="C293" t="n">
-        <v>20.43984241393447</v>
+        <v>20.43984433472696</v>
       </c>
       <c r="D293" t="n">
-        <v>19.65300590141818</v>
+        <v>19.65300774826931</v>
       </c>
       <c r="E293" t="n">
-        <v>19.65300590141818</v>
+        <v>19.65300774826931</v>
       </c>
       <c r="F293" t="n">
         <v>787900</v>
@@ -6292,16 +6292,16 @@
         <v>44526</v>
       </c>
       <c r="B294" t="n">
-        <v>19.76030158996582</v>
+        <v>19.76030349731445</v>
       </c>
       <c r="C294" t="n">
-        <v>19.90336245804901</v>
+        <v>19.90336437920648</v>
       </c>
       <c r="D294" t="n">
-        <v>19.18805641221301</v>
+        <v>19.18805826432609</v>
       </c>
       <c r="E294" t="n">
-        <v>19.6530050861934</v>
+        <v>19.65300698318531</v>
       </c>
       <c r="F294" t="n">
         <v>1033400</v>
@@ -6392,16 +6392,16 @@
         <v>44533</v>
       </c>
       <c r="B299" t="n">
-        <v>19.76030158996582</v>
+        <v>19.76030349731445</v>
       </c>
       <c r="C299" t="n">
-        <v>20.20736722908079</v>
+        <v>20.20736917958211</v>
       </c>
       <c r="D299" t="n">
-        <v>18.77675684282887</v>
+        <v>18.77675865524156</v>
       </c>
       <c r="E299" t="n">
-        <v>18.77675684282887</v>
+        <v>18.77675865524156</v>
       </c>
       <c r="F299" t="n">
         <v>1496100</v>
@@ -6412,16 +6412,16 @@
         <v>44536</v>
       </c>
       <c r="B300" t="n">
-        <v>19.97489547729492</v>
+        <v>19.97489356994629</v>
       </c>
       <c r="C300" t="n">
-        <v>20.38619509991056</v>
+        <v>20.38619315328804</v>
       </c>
       <c r="D300" t="n">
-        <v>19.56359414925899</v>
+        <v>19.56359228118441</v>
       </c>
       <c r="E300" t="n">
-        <v>20.08219028953366</v>
+        <v>20.08218837193973</v>
       </c>
       <c r="F300" t="n">
         <v>963750</v>
@@ -6472,16 +6472,16 @@
         <v>44539</v>
       </c>
       <c r="B303" t="n">
-        <v>20.90478897094727</v>
+        <v>20.9047908782959</v>
       </c>
       <c r="C303" t="n">
-        <v>21.36973765463187</v>
+        <v>21.36973960440232</v>
       </c>
       <c r="D303" t="n">
-        <v>20.72596373482095</v>
+        <v>20.72596562585361</v>
       </c>
       <c r="E303" t="n">
-        <v>21.24455981880144</v>
+        <v>21.24456175715069</v>
       </c>
       <c r="F303" t="n">
         <v>669550</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78104209899902</v>
+        <v>21.78104019165039</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422959598714</v>
+        <v>22.51422762443386</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550683158799</v>
+        <v>21.40550495712469</v>
       </c>
       <c r="E305" t="n">
-        <v>22.13869432857611</v>
+        <v>22.13869238990815</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6552,16 +6552,16 @@
         <v>44545</v>
       </c>
       <c r="B307" t="n">
-        <v>22.03139686584473</v>
+        <v>22.03139877319336</v>
       </c>
       <c r="C307" t="n">
-        <v>22.37116774849373</v>
+        <v>22.37116968525772</v>
       </c>
       <c r="D307" t="n">
-        <v>21.11938414573805</v>
+        <v>21.11938597412999</v>
       </c>
       <c r="E307" t="n">
-        <v>21.45915332296677</v>
+        <v>21.45915518077393</v>
       </c>
       <c r="F307" t="n">
         <v>1028800</v>
@@ -6572,16 +6572,16 @@
         <v>44546</v>
       </c>
       <c r="B308" t="n">
-        <v>21.94198608398438</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C308" t="n">
-        <v>22.97917840508309</v>
+        <v>22.97917640757456</v>
       </c>
       <c r="D308" t="n">
-        <v>21.53068473986848</v>
+        <v>21.53068286827299</v>
       </c>
       <c r="E308" t="n">
-        <v>22.5321126906295</v>
+        <v>22.53211073198299</v>
       </c>
       <c r="F308" t="n">
         <v>888550</v>
@@ -6612,16 +6612,16 @@
         <v>44550</v>
       </c>
       <c r="B310" t="n">
-        <v>22.01351356506348</v>
+        <v>22.01351547241211</v>
       </c>
       <c r="C310" t="n">
-        <v>22.42481314836077</v>
+        <v>22.42481509134622</v>
       </c>
       <c r="D310" t="n">
-        <v>21.13726358663772</v>
+        <v>21.13726541806416</v>
       </c>
       <c r="E310" t="n">
-        <v>22.35328271189949</v>
+        <v>22.35328464868723</v>
       </c>
       <c r="F310" t="n">
         <v>1565700</v>
@@ -6632,16 +6632,16 @@
         <v>44551</v>
       </c>
       <c r="B311" t="n">
-        <v>21.38762474060059</v>
+        <v>21.38762283325195</v>
       </c>
       <c r="C311" t="n">
-        <v>22.1923427191296</v>
+        <v>22.19234074001621</v>
       </c>
       <c r="D311" t="n">
-        <v>21.38762474060059</v>
+        <v>21.38762283325195</v>
       </c>
       <c r="E311" t="n">
-        <v>22.03139878233971</v>
+        <v>22.0313968175793</v>
       </c>
       <c r="F311" t="n">
         <v>785250</v>
@@ -6652,16 +6652,16 @@
         <v>44552</v>
       </c>
       <c r="B312" t="n">
-        <v>21.45915031433105</v>
+        <v>21.45915222167969</v>
       </c>
       <c r="C312" t="n">
-        <v>21.78103811478044</v>
+        <v>21.78104005073934</v>
       </c>
       <c r="D312" t="n">
-        <v>20.65443251862765</v>
+        <v>20.65443435445074</v>
       </c>
       <c r="E312" t="n">
-        <v>21.42338424520555</v>
+        <v>21.42338614937519</v>
       </c>
       <c r="F312" t="n">
         <v>1154200</v>
@@ -6732,16 +6732,16 @@
         <v>44559</v>
       </c>
       <c r="B316" t="n">
-        <v>20.29230880737305</v>
+        <v>20.29231071472168</v>
       </c>
       <c r="C316" t="n">
-        <v>20.90558774878349</v>
+        <v>20.90558971377646</v>
       </c>
       <c r="D316" t="n">
-        <v>20.05781969917492</v>
+        <v>20.05782158448306</v>
       </c>
       <c r="E316" t="n">
-        <v>20.70717296173873</v>
+        <v>20.70717490808197</v>
       </c>
       <c r="F316" t="n">
         <v>541350</v>
@@ -6752,16 +6752,16 @@
         <v>44560</v>
       </c>
       <c r="B317" t="n">
-        <v>21.06792640686035</v>
+        <v>21.06792449951172</v>
       </c>
       <c r="C317" t="n">
-        <v>21.15811306946891</v>
+        <v>21.15811115395539</v>
       </c>
       <c r="D317" t="n">
-        <v>19.93155691194919</v>
+        <v>19.93155510747982</v>
       </c>
       <c r="E317" t="n">
-        <v>20.2923087229844</v>
+        <v>20.29230688585499</v>
       </c>
       <c r="F317" t="n">
         <v>1399700</v>
@@ -6772,16 +6772,16 @@
         <v>44564</v>
       </c>
       <c r="B318" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C318" t="n">
-        <v>21.32045357690026</v>
+        <v>21.32045154948475</v>
       </c>
       <c r="D318" t="n">
-        <v>19.8774462134759</v>
+        <v>19.87744432327959</v>
       </c>
       <c r="E318" t="n">
-        <v>21.26634123082196</v>
+        <v>21.26633920855213</v>
       </c>
       <c r="F318" t="n">
         <v>905200</v>
@@ -6792,16 +6792,16 @@
         <v>44565</v>
       </c>
       <c r="B319" t="n">
-        <v>18.99359893798828</v>
+        <v>18.99360084533691</v>
       </c>
       <c r="C319" t="n">
-        <v>20.23819473506625</v>
+        <v>20.23819676739794</v>
       </c>
       <c r="D319" t="n">
-        <v>18.8492982253126</v>
+        <v>18.84930011817047</v>
       </c>
       <c r="E319" t="n">
-        <v>20.07585600325606</v>
+        <v>20.0758580192856</v>
       </c>
       <c r="F319" t="n">
         <v>1398150</v>
@@ -6872,16 +6872,16 @@
         <v>44571</v>
       </c>
       <c r="B323" t="n">
-        <v>16.36010932922363</v>
+        <v>16.360107421875</v>
       </c>
       <c r="C323" t="n">
-        <v>17.13572699636531</v>
+        <v>17.13572499859104</v>
       </c>
       <c r="D323" t="n">
-        <v>16.10758392704749</v>
+        <v>16.10758204913961</v>
       </c>
       <c r="E323" t="n">
-        <v>17.11768897615265</v>
+        <v>17.11768698048135</v>
       </c>
       <c r="F323" t="n">
         <v>1820150</v>
@@ -6892,16 +6892,16 @@
         <v>44572</v>
       </c>
       <c r="B324" t="n">
-        <v>16.77497482299805</v>
+        <v>16.77497673034668</v>
       </c>
       <c r="C324" t="n">
-        <v>17.04553823941727</v>
+        <v>17.04554017752951</v>
       </c>
       <c r="D324" t="n">
-        <v>16.17973393071556</v>
+        <v>16.1797357703841</v>
       </c>
       <c r="E324" t="n">
-        <v>16.19777023032999</v>
+        <v>16.19777207204929</v>
       </c>
       <c r="F324" t="n">
         <v>629400</v>
@@ -6932,16 +6932,16 @@
         <v>44574</v>
       </c>
       <c r="B326" t="n">
-        <v>16.64871215820312</v>
+        <v>16.64871406555176</v>
       </c>
       <c r="C326" t="n">
-        <v>17.62274468839355</v>
+        <v>17.62274670733157</v>
       </c>
       <c r="D326" t="n">
-        <v>16.57656179154462</v>
+        <v>16.5765636906274</v>
       </c>
       <c r="E326" t="n">
-        <v>17.58666864496408</v>
+        <v>17.58667065976908</v>
       </c>
       <c r="F326" t="n">
         <v>921200</v>
@@ -6952,16 +6952,16 @@
         <v>44575</v>
       </c>
       <c r="B327" t="n">
-        <v>17.00946426391602</v>
+        <v>17.00946617126465</v>
       </c>
       <c r="C327" t="n">
-        <v>17.02750056389514</v>
+        <v>17.02750247326626</v>
       </c>
       <c r="D327" t="n">
-        <v>16.17973425786645</v>
+        <v>16.17973607217368</v>
       </c>
       <c r="E327" t="n">
-        <v>16.55852408063256</v>
+        <v>16.55852593741522</v>
       </c>
       <c r="F327" t="n">
         <v>789200</v>
@@ -6992,16 +6992,16 @@
         <v>44579</v>
       </c>
       <c r="B329" t="n">
-        <v>16.30599594116211</v>
+        <v>16.30599784851074</v>
       </c>
       <c r="C329" t="n">
-        <v>16.79301213441261</v>
+        <v>16.79301409872861</v>
       </c>
       <c r="D329" t="n">
-        <v>16.07150685406374</v>
+        <v>16.07150873398366</v>
       </c>
       <c r="E329" t="n">
-        <v>16.73889807725132</v>
+        <v>16.73890003523749</v>
       </c>
       <c r="F329" t="n">
         <v>670850</v>
@@ -7012,16 +7012,16 @@
         <v>44580</v>
       </c>
       <c r="B330" t="n">
-        <v>16.41422462463379</v>
+        <v>16.41422653198242</v>
       </c>
       <c r="C330" t="n">
-        <v>16.72086411051511</v>
+        <v>16.72086605349554</v>
       </c>
       <c r="D330" t="n">
-        <v>16.19777180619957</v>
+        <v>16.19777368839618</v>
       </c>
       <c r="E330" t="n">
-        <v>16.41422462463379</v>
+        <v>16.41422653198242</v>
       </c>
       <c r="F330" t="n">
         <v>847250</v>
@@ -7032,16 +7032,16 @@
         <v>44581</v>
       </c>
       <c r="B331" t="n">
-        <v>17.42432975769043</v>
+        <v>17.4243278503418</v>
       </c>
       <c r="C331" t="n">
-        <v>18.12779711742218</v>
+        <v>18.12779513306872</v>
       </c>
       <c r="D331" t="n">
-        <v>16.48637499824851</v>
+        <v>16.48637319357279</v>
       </c>
       <c r="E331" t="n">
-        <v>16.48637499824851</v>
+        <v>16.48637319357279</v>
       </c>
       <c r="F331" t="n">
         <v>2219300</v>
@@ -7052,16 +7052,16 @@
         <v>44582</v>
       </c>
       <c r="B332" t="n">
-        <v>18.14583206176758</v>
+        <v>18.14583396911621</v>
       </c>
       <c r="C332" t="n">
-        <v>18.34424510487493</v>
+        <v>18.3442470330792</v>
       </c>
       <c r="D332" t="n">
-        <v>17.24395177822486</v>
+        <v>17.24395359077485</v>
       </c>
       <c r="E332" t="n">
-        <v>17.33413843041903</v>
+        <v>17.33414025244875</v>
       </c>
       <c r="F332" t="n">
         <v>1316050</v>
@@ -7072,16 +7072,16 @@
         <v>44585</v>
       </c>
       <c r="B333" t="n">
-        <v>17.85722923278809</v>
+        <v>17.85723114013672</v>
       </c>
       <c r="C333" t="n">
-        <v>18.09171831696088</v>
+        <v>18.09172024935553</v>
       </c>
       <c r="D333" t="n">
-        <v>17.47843943838591</v>
+        <v>17.47844130527562</v>
       </c>
       <c r="E333" t="n">
-        <v>18.09171831696088</v>
+        <v>18.09172024935553</v>
       </c>
       <c r="F333" t="n">
         <v>692150</v>
@@ -7112,16 +7112,16 @@
         <v>44587</v>
       </c>
       <c r="B335" t="n">
-        <v>19.3543529510498</v>
+        <v>19.35435485839844</v>
       </c>
       <c r="C335" t="n">
-        <v>19.80529316020046</v>
+        <v>19.80529511198872</v>
       </c>
       <c r="D335" t="n">
-        <v>18.84930039845718</v>
+        <v>18.84930225603348</v>
       </c>
       <c r="E335" t="n">
-        <v>18.92145076311327</v>
+        <v>18.9214526277999</v>
       </c>
       <c r="F335" t="n">
         <v>1494250</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96763229370117</v>
+        <v>19.96763038635254</v>
       </c>
       <c r="C338" t="n">
-        <v>20.27427177942092</v>
+        <v>20.27426984278146</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44454170986168</v>
+        <v>19.44453985247972</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706885110159</v>
+        <v>19.69706696959773</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7192,16 +7192,16 @@
         <v>44593</v>
       </c>
       <c r="B339" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C339" t="n">
-        <v>20.38249879067443</v>
+        <v>20.38249685245139</v>
       </c>
       <c r="D339" t="n">
-        <v>19.75118177902592</v>
+        <v>19.75117990083641</v>
       </c>
       <c r="E339" t="n">
-        <v>20.29231040041029</v>
+        <v>20.29230847076349</v>
       </c>
       <c r="F339" t="n">
         <v>629350</v>
@@ -7292,16 +7292,16 @@
         <v>44600</v>
       </c>
       <c r="B344" t="n">
-        <v>19.46257781982422</v>
+        <v>19.46257972717285</v>
       </c>
       <c r="C344" t="n">
-        <v>20.03978069145118</v>
+        <v>20.03978265536617</v>
       </c>
       <c r="D344" t="n">
-        <v>19.40846548065925</v>
+        <v>19.40846738270483</v>
       </c>
       <c r="E344" t="n">
-        <v>19.66099087689592</v>
+        <v>19.6609928036892</v>
       </c>
       <c r="F344" t="n">
         <v>697700</v>
@@ -7332,16 +7332,16 @@
         <v>44602</v>
       </c>
       <c r="B346" t="n">
-        <v>19.98567008972168</v>
+        <v>19.98566818237305</v>
       </c>
       <c r="C346" t="n">
-        <v>20.59894905424028</v>
+        <v>20.59894708836287</v>
       </c>
       <c r="D346" t="n">
-        <v>19.82333133791377</v>
+        <v>19.82332944605806</v>
       </c>
       <c r="E346" t="n">
-        <v>20.18408316404224</v>
+        <v>20.18408123775789</v>
       </c>
       <c r="F346" t="n">
         <v>563100</v>
@@ -7432,16 +7432,16 @@
         <v>44609</v>
       </c>
       <c r="B351" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C351" t="n">
-        <v>20.72521260943759</v>
+        <v>20.72521063862504</v>
       </c>
       <c r="D351" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="E351" t="n">
-        <v>20.72521260943759</v>
+        <v>20.72521063862504</v>
       </c>
       <c r="F351" t="n">
         <v>544250</v>
@@ -7452,16 +7452,16 @@
         <v>44610</v>
       </c>
       <c r="B352" t="n">
-        <v>19.93155479431152</v>
+        <v>19.93155670166016</v>
       </c>
       <c r="C352" t="n">
-        <v>20.50875763064267</v>
+        <v>20.50875959322669</v>
       </c>
       <c r="D352" t="n">
-        <v>19.64295337614595</v>
+        <v>19.64295525587689</v>
       </c>
       <c r="E352" t="n">
-        <v>20.47268331347204</v>
+        <v>20.47268527260393</v>
       </c>
       <c r="F352" t="n">
         <v>904300</v>
@@ -7472,16 +7472,16 @@
         <v>44613</v>
       </c>
       <c r="B353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892242431641</v>
       </c>
       <c r="C353" t="n">
-        <v>19.94959452481559</v>
+        <v>19.94959248662468</v>
       </c>
       <c r="D353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892242431641</v>
       </c>
       <c r="E353" t="n">
-        <v>19.85940614385</v>
+        <v>19.85940411487337</v>
       </c>
       <c r="F353" t="n">
         <v>728950</v>
@@ -7492,16 +7492,16 @@
         <v>44614</v>
       </c>
       <c r="B354" t="n">
-        <v>19.69706916809082</v>
+        <v>19.69706726074219</v>
       </c>
       <c r="C354" t="n">
-        <v>19.80529385879217</v>
+        <v>19.80529194096369</v>
       </c>
       <c r="D354" t="n">
-        <v>18.99360179773027</v>
+        <v>18.9935999585013</v>
       </c>
       <c r="E354" t="n">
-        <v>19.08379018678169</v>
+        <v>19.0837883388194</v>
       </c>
       <c r="F354" t="n">
         <v>1292450</v>
@@ -7552,16 +7552,16 @@
         <v>44617</v>
       </c>
       <c r="B357" t="n">
-        <v>19.02967834472656</v>
+        <v>19.02967643737793</v>
       </c>
       <c r="C357" t="n">
-        <v>19.62491931992821</v>
+        <v>19.62491735291844</v>
       </c>
       <c r="D357" t="n">
-        <v>18.65088847685275</v>
+        <v>18.6508866074703</v>
       </c>
       <c r="E357" t="n">
-        <v>19.28220377650878</v>
+        <v>19.28220184384947</v>
       </c>
       <c r="F357" t="n">
         <v>1262850</v>
@@ -7632,16 +7632,16 @@
         <v>44627</v>
       </c>
       <c r="B361" t="n">
-        <v>16.77497482299805</v>
+        <v>16.77497673034668</v>
       </c>
       <c r="C361" t="n">
-        <v>18.00153092699214</v>
+        <v>18.00153297380269</v>
       </c>
       <c r="D361" t="n">
-        <v>16.77497482299805</v>
+        <v>16.77497673034668</v>
       </c>
       <c r="E361" t="n">
-        <v>17.60470481227065</v>
+        <v>17.60470681396126</v>
       </c>
       <c r="F361" t="n">
         <v>1173850</v>
@@ -7692,16 +7692,16 @@
         <v>44630</v>
       </c>
       <c r="B364" t="n">
-        <v>18.14583206176758</v>
+        <v>18.14583396911621</v>
       </c>
       <c r="C364" t="n">
-        <v>18.45246977558799</v>
+        <v>18.45247171516799</v>
       </c>
       <c r="D364" t="n">
-        <v>17.74900425535275</v>
+        <v>17.74900612098993</v>
       </c>
       <c r="E364" t="n">
-        <v>18.10975602472981</v>
+        <v>18.10975792828641</v>
       </c>
       <c r="F364" t="n">
         <v>592800</v>
@@ -7712,16 +7712,16 @@
         <v>44631</v>
       </c>
       <c r="B365" t="n">
-        <v>17.22591590881348</v>
+        <v>17.22591781616211</v>
       </c>
       <c r="C365" t="n">
-        <v>18.4524720777208</v>
+        <v>18.45247412088051</v>
       </c>
       <c r="D365" t="n">
-        <v>17.02750112075174</v>
+        <v>17.02750300613079</v>
       </c>
       <c r="E365" t="n">
-        <v>18.30817135196699</v>
+        <v>18.30817337914893</v>
       </c>
       <c r="F365" t="n">
         <v>837400</v>
@@ -7752,16 +7752,16 @@
         <v>44635</v>
       </c>
       <c r="B367" t="n">
-        <v>17.46040534973145</v>
+        <v>17.46040725708008</v>
       </c>
       <c r="C367" t="n">
-        <v>17.56863003600147</v>
+        <v>17.56863195517241</v>
       </c>
       <c r="D367" t="n">
-        <v>16.93731477889199</v>
+        <v>16.93731662909899</v>
       </c>
       <c r="E367" t="n">
-        <v>17.04553946516202</v>
+        <v>17.04554132719132</v>
       </c>
       <c r="F367" t="n">
         <v>763850</v>
@@ -7812,16 +7812,16 @@
         <v>44638</v>
       </c>
       <c r="B370" t="n">
-        <v>18.4344367980957</v>
+        <v>18.43443489074707</v>
       </c>
       <c r="C370" t="n">
-        <v>18.90341332266845</v>
+        <v>18.90341136679641</v>
       </c>
       <c r="D370" t="n">
-        <v>18.01957089842698</v>
+        <v>18.01956903400312</v>
       </c>
       <c r="E370" t="n">
-        <v>18.16387163217251</v>
+        <v>18.16386975281834</v>
       </c>
       <c r="F370" t="n">
         <v>2000150</v>
@@ -7832,16 +7832,16 @@
         <v>44641</v>
       </c>
       <c r="B371" t="n">
-        <v>18.56069946289062</v>
+        <v>18.56069755554199</v>
       </c>
       <c r="C371" t="n">
-        <v>18.86733895137048</v>
+        <v>18.86733701251073</v>
       </c>
       <c r="D371" t="n">
-        <v>18.23602195268832</v>
+        <v>18.23602007870444</v>
       </c>
       <c r="E371" t="n">
-        <v>18.65088785130242</v>
+        <v>18.65088593468579</v>
       </c>
       <c r="F371" t="n">
         <v>689900</v>
@@ -7872,16 +7872,16 @@
         <v>44643</v>
       </c>
       <c r="B373" t="n">
-        <v>19.60688018798828</v>
+        <v>19.60687828063965</v>
       </c>
       <c r="C373" t="n">
-        <v>19.80529326175987</v>
+        <v>19.8052913351097</v>
       </c>
       <c r="D373" t="n">
-        <v>18.92145086014044</v>
+        <v>18.92144901947007</v>
       </c>
       <c r="E373" t="n">
-        <v>19.48061747924276</v>
+        <v>19.48061558417691</v>
       </c>
       <c r="F373" t="n">
         <v>823600</v>
@@ -7892,16 +7892,16 @@
         <v>44644</v>
       </c>
       <c r="B374" t="n">
-        <v>20.79735946655273</v>
+        <v>20.79736137390137</v>
       </c>
       <c r="C374" t="n">
-        <v>20.79735946655273</v>
+        <v>20.79736137390137</v>
       </c>
       <c r="D374" t="n">
-        <v>19.49865305872129</v>
+        <v>19.49865484696414</v>
       </c>
       <c r="E374" t="n">
-        <v>19.7151041266932</v>
+        <v>19.71510593478701</v>
       </c>
       <c r="F374" t="n">
         <v>1624000</v>
@@ -7912,16 +7912,16 @@
         <v>44645</v>
       </c>
       <c r="B375" t="n">
-        <v>21.19419097900391</v>
+        <v>21.19418907165527</v>
       </c>
       <c r="C375" t="n">
-        <v>21.44671812908974</v>
+        <v>21.4467161990152</v>
       </c>
       <c r="D375" t="n">
-        <v>20.81540111397539</v>
+        <v>20.81539924071555</v>
       </c>
       <c r="E375" t="n">
-        <v>20.9236275269266</v>
+        <v>20.92362564392704</v>
       </c>
       <c r="F375" t="n">
         <v>911550</v>
@@ -8012,16 +8012,16 @@
         <v>44652</v>
       </c>
       <c r="B380" t="n">
-        <v>21.78943061828613</v>
+        <v>21.7894287109375</v>
       </c>
       <c r="C380" t="n">
-        <v>21.84354296135495</v>
+        <v>21.84354104926957</v>
       </c>
       <c r="D380" t="n">
-        <v>21.17615166283828</v>
+        <v>21.17614980917333</v>
       </c>
       <c r="E380" t="n">
-        <v>21.42867879749339</v>
+        <v>21.42867692172335</v>
       </c>
       <c r="F380" t="n">
         <v>746250</v>
@@ -8032,16 +8032,16 @@
         <v>44655</v>
       </c>
       <c r="B381" t="n">
-        <v>21.89765548706055</v>
+        <v>21.89765739440918</v>
       </c>
       <c r="C381" t="n">
-        <v>21.91569178668347</v>
+        <v>21.91569369560312</v>
       </c>
       <c r="D381" t="n">
-        <v>21.32045089412073</v>
+        <v>21.32045275119318</v>
       </c>
       <c r="E381" t="n">
-        <v>21.78942908832175</v>
+        <v>21.78943098624356</v>
       </c>
       <c r="F381" t="n">
         <v>503500</v>
@@ -8132,16 +8132,16 @@
         <v>44662</v>
       </c>
       <c r="B386" t="n">
-        <v>18.93948936462402</v>
+        <v>18.93948745727539</v>
       </c>
       <c r="C386" t="n">
-        <v>19.37239156582447</v>
+        <v>19.37238961487934</v>
       </c>
       <c r="D386" t="n">
-        <v>18.86733899775728</v>
+        <v>18.86733709767473</v>
       </c>
       <c r="E386" t="n">
-        <v>19.24612885385778</v>
+        <v>19.24612691562825</v>
       </c>
       <c r="F386" t="n">
         <v>1033000</v>
@@ -8152,16 +8152,16 @@
         <v>44663</v>
       </c>
       <c r="B387" t="n">
-        <v>19.13790130615234</v>
+        <v>19.13789939880371</v>
       </c>
       <c r="C387" t="n">
-        <v>19.84136863144855</v>
+        <v>19.84136665398996</v>
       </c>
       <c r="D387" t="n">
-        <v>18.9936005809942</v>
+        <v>18.99359868802707</v>
       </c>
       <c r="E387" t="n">
-        <v>19.33631609339504</v>
+        <v>19.33631416627171</v>
       </c>
       <c r="F387" t="n">
         <v>1155250</v>
@@ -8172,16 +8172,16 @@
         <v>44664</v>
       </c>
       <c r="B388" t="n">
-        <v>19.17397880554199</v>
+        <v>19.17397689819336</v>
       </c>
       <c r="C388" t="n">
-        <v>19.73314372799893</v>
+        <v>19.73314176502687</v>
       </c>
       <c r="D388" t="n">
-        <v>18.95752770134571</v>
+        <v>18.95752581552875</v>
       </c>
       <c r="E388" t="n">
-        <v>19.11986645954304</v>
+        <v>19.11986455757728</v>
       </c>
       <c r="F388" t="n">
         <v>1163900</v>
@@ -8212,16 +8212,16 @@
         <v>44669</v>
       </c>
       <c r="B390" t="n">
-        <v>19.55276679992676</v>
+        <v>19.55276870727539</v>
       </c>
       <c r="C390" t="n">
-        <v>20.0037069873044</v>
+        <v>20.0037089386417</v>
       </c>
       <c r="D390" t="n">
-        <v>19.49865445909752</v>
+        <v>19.49865636116756</v>
       </c>
       <c r="E390" t="n">
-        <v>19.6790295019284</v>
+        <v>19.67903142159381</v>
       </c>
       <c r="F390" t="n">
         <v>1023750</v>
@@ -8272,16 +8272,16 @@
         <v>44673</v>
       </c>
       <c r="B393" t="n">
-        <v>19.55276679992676</v>
+        <v>19.55276870727539</v>
       </c>
       <c r="C393" t="n">
-        <v>20.4907214951681</v>
+        <v>20.49072349401308</v>
       </c>
       <c r="D393" t="n">
-        <v>19.3543520165524</v>
+        <v>19.35435390454591</v>
       </c>
       <c r="E393" t="n">
-        <v>20.09389536881999</v>
+        <v>20.09389732895506</v>
       </c>
       <c r="F393" t="n">
         <v>931750</v>
@@ -8292,16 +8292,16 @@
         <v>44676</v>
       </c>
       <c r="B394" t="n">
-        <v>19.30024147033691</v>
+        <v>19.30023956298828</v>
       </c>
       <c r="C394" t="n">
-        <v>19.57080664004192</v>
+        <v>19.57080470595465</v>
       </c>
       <c r="D394" t="n">
-        <v>18.61481211536489</v>
+        <v>18.61481027575389</v>
       </c>
       <c r="E394" t="n">
-        <v>19.28220344831649</v>
+        <v>19.28220154275046</v>
       </c>
       <c r="F394" t="n">
         <v>1378800</v>
@@ -8332,16 +8332,16 @@
         <v>44678</v>
       </c>
       <c r="B396" t="n">
-        <v>19.49865531921387</v>
+        <v>19.49865341186523</v>
       </c>
       <c r="C396" t="n">
-        <v>19.55276766243008</v>
+        <v>19.55276574978821</v>
       </c>
       <c r="D396" t="n">
-        <v>19.10182745516075</v>
+        <v>19.10182558662962</v>
       </c>
       <c r="E396" t="n">
-        <v>19.46257927693614</v>
+        <v>19.46257737311645</v>
       </c>
       <c r="F396" t="n">
         <v>619300</v>
@@ -8452,16 +8452,16 @@
         <v>44686</v>
       </c>
       <c r="B402" t="n">
-        <v>20.09389495849609</v>
+        <v>20.09389305114746</v>
       </c>
       <c r="C402" t="n">
-        <v>20.47268477696631</v>
+        <v>20.47268283366227</v>
       </c>
       <c r="D402" t="n">
-        <v>19.73314143980044</v>
+        <v>19.73313956669518</v>
       </c>
       <c r="E402" t="n">
-        <v>20.41857071704181</v>
+        <v>20.41856877887437</v>
       </c>
       <c r="F402" t="n">
         <v>1134600</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.51903343200684</v>
+        <v>19.5190315246582</v>
       </c>
       <c r="C403" t="n">
-        <v>19.93473455484336</v>
+        <v>19.9347326068735</v>
       </c>
       <c r="D403" t="n">
-        <v>18.8199007902444</v>
+        <v>18.81989895121317</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019714903581</v>
+        <v>19.67019522691586</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8532,16 +8532,16 @@
         <v>44692</v>
       </c>
       <c r="B406" t="n">
-        <v>19.10333061218262</v>
+        <v>19.10333251953125</v>
       </c>
       <c r="C406" t="n">
-        <v>19.57571763643849</v>
+        <v>19.57571959095203</v>
       </c>
       <c r="D406" t="n">
-        <v>18.93327279714184</v>
+        <v>18.93327468751125</v>
       </c>
       <c r="E406" t="n">
-        <v>19.14112243908956</v>
+        <v>19.14112435021147</v>
       </c>
       <c r="F406" t="n">
         <v>1048200</v>
@@ -8552,16 +8552,16 @@
         <v>44693</v>
       </c>
       <c r="B407" t="n">
-        <v>19.33007621765137</v>
+        <v>19.33007431030273</v>
       </c>
       <c r="C407" t="n">
-        <v>19.7079872796457</v>
+        <v>19.7079853350076</v>
       </c>
       <c r="D407" t="n">
-        <v>18.81989916718061</v>
+        <v>18.81989731017247</v>
       </c>
       <c r="E407" t="n">
-        <v>18.93327284618161</v>
+        <v>18.93327097798659</v>
       </c>
       <c r="F407" t="n">
         <v>1412250</v>
@@ -8652,16 +8652,16 @@
         <v>44700</v>
       </c>
       <c r="B412" t="n">
-        <v>20.7850284576416</v>
+        <v>20.78503036499023</v>
       </c>
       <c r="C412" t="n">
-        <v>20.91729624390957</v>
+        <v>20.91729816339582</v>
       </c>
       <c r="D412" t="n">
-        <v>20.0103140489062</v>
+        <v>20.01031588516278</v>
       </c>
       <c r="E412" t="n">
-        <v>20.36932738392501</v>
+        <v>20.36932925312662</v>
       </c>
       <c r="F412" t="n">
         <v>1388850</v>
@@ -8732,16 +8732,16 @@
         <v>44706</v>
       </c>
       <c r="B416" t="n">
-        <v>20.7850284576416</v>
+        <v>20.78503036499023</v>
       </c>
       <c r="C416" t="n">
-        <v>20.80392437054087</v>
+        <v>20.80392627962349</v>
       </c>
       <c r="D416" t="n">
-        <v>20.08589589848982</v>
+        <v>20.0858977416822</v>
       </c>
       <c r="E416" t="n">
-        <v>20.2559555105563</v>
+        <v>20.25595736935429</v>
       </c>
       <c r="F416" t="n">
         <v>1116800</v>
@@ -8772,16 +8772,16 @@
         <v>44708</v>
       </c>
       <c r="B418" t="n">
-        <v>22.7879524230957</v>
+        <v>22.78795051574707</v>
       </c>
       <c r="C418" t="n">
-        <v>22.86353428013691</v>
+        <v>22.86353236646209</v>
       </c>
       <c r="D418" t="n">
-        <v>21.35189533729906</v>
+        <v>21.35189355014821</v>
       </c>
       <c r="E418" t="n">
-        <v>21.5975368231864</v>
+        <v>21.59753501547539</v>
       </c>
       <c r="F418" t="n">
         <v>2973300</v>
@@ -8832,16 +8832,16 @@
         <v>44713</v>
       </c>
       <c r="B421" t="n">
-        <v>23.43039512634277</v>
+        <v>23.43039703369141</v>
       </c>
       <c r="C421" t="n">
-        <v>23.61935065236709</v>
+        <v>23.61935257509763</v>
       </c>
       <c r="D421" t="n">
-        <v>22.31556328924234</v>
+        <v>22.31556510583822</v>
       </c>
       <c r="E421" t="n">
-        <v>22.78795030228968</v>
+        <v>22.78795215734017</v>
       </c>
       <c r="F421" t="n">
         <v>2603350</v>
@@ -8892,16 +8892,16 @@
         <v>44718</v>
       </c>
       <c r="B424" t="n">
-        <v>22.03212928771973</v>
+        <v>22.03212738037109</v>
       </c>
       <c r="C424" t="n">
-        <v>22.63678406822239</v>
+        <v>22.63678210852805</v>
       </c>
       <c r="D424" t="n">
-        <v>21.52195226717395</v>
+        <v>21.52195040399197</v>
       </c>
       <c r="E424" t="n">
-        <v>22.52341219788483</v>
+        <v>22.52341024800523</v>
       </c>
       <c r="F424" t="n">
         <v>1535250</v>
@@ -8912,16 +8912,16 @@
         <v>44719</v>
       </c>
       <c r="B425" t="n">
-        <v>21.59753608703613</v>
+        <v>21.5975341796875</v>
       </c>
       <c r="C425" t="n">
-        <v>21.93765353112191</v>
+        <v>21.93765159373639</v>
       </c>
       <c r="D425" t="n">
-        <v>21.25741684093681</v>
+        <v>21.25741496362521</v>
       </c>
       <c r="E425" t="n">
-        <v>21.72980388184651</v>
+        <v>21.72980196281688</v>
       </c>
       <c r="F425" t="n">
         <v>1412350</v>
@@ -8932,16 +8932,16 @@
         <v>44720</v>
       </c>
       <c r="B426" t="n">
-        <v>21.20073127746582</v>
+        <v>21.20072937011719</v>
       </c>
       <c r="C426" t="n">
-        <v>21.82428203839009</v>
+        <v>21.82428007494298</v>
       </c>
       <c r="D426" t="n">
-        <v>21.0306716513931</v>
+        <v>21.03066975934408</v>
       </c>
       <c r="E426" t="n">
-        <v>21.48416278624464</v>
+        <v>21.48416085339676</v>
       </c>
       <c r="F426" t="n">
         <v>863650</v>
@@ -8972,16 +8972,16 @@
         <v>44722</v>
       </c>
       <c r="B428" t="n">
-        <v>20.63386726379395</v>
+        <v>20.63386535644531</v>
       </c>
       <c r="C428" t="n">
-        <v>21.52195545574124</v>
+        <v>21.52195346629971</v>
       </c>
       <c r="D428" t="n">
-        <v>20.33153982875154</v>
+        <v>20.33153794934939</v>
       </c>
       <c r="E428" t="n">
-        <v>21.44637359698064</v>
+        <v>21.44637161452573</v>
       </c>
       <c r="F428" t="n">
         <v>1577850</v>
@@ -9012,16 +9012,16 @@
         <v>44726</v>
       </c>
       <c r="B430" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C430" t="n">
-        <v>19.51903189147468</v>
+        <v>19.51902994454667</v>
       </c>
       <c r="D430" t="n">
-        <v>18.89548115744023</v>
+        <v>18.89547927270836</v>
       </c>
       <c r="E430" t="n">
-        <v>19.51903189147468</v>
+        <v>19.51902994454667</v>
       </c>
       <c r="F430" t="n">
         <v>1027150</v>
@@ -9132,16 +9132,16 @@
         <v>44735</v>
       </c>
       <c r="B436" t="n">
-        <v>18.81990051269531</v>
+        <v>18.81989860534668</v>
       </c>
       <c r="C436" t="n">
-        <v>18.89548237009515</v>
+        <v>18.89548045508649</v>
       </c>
       <c r="D436" t="n">
-        <v>18.4986771682426</v>
+        <v>18.49867529344914</v>
       </c>
       <c r="E436" t="n">
-        <v>18.72542274044211</v>
+        <v>18.72542084266856</v>
       </c>
       <c r="F436" t="n">
         <v>1280500</v>
@@ -9212,16 +9212,16 @@
         <v>44741</v>
       </c>
       <c r="B440" t="n">
-        <v>17.81843757629395</v>
+        <v>17.81843948364258</v>
       </c>
       <c r="C440" t="n">
-        <v>18.13966086891105</v>
+        <v>18.13966281064456</v>
       </c>
       <c r="D440" t="n">
-        <v>17.51611019548098</v>
+        <v>17.51611207046742</v>
       </c>
       <c r="E440" t="n">
-        <v>18.13966086891105</v>
+        <v>18.13966281064456</v>
       </c>
       <c r="F440" t="n">
         <v>939650</v>
@@ -9292,16 +9292,16 @@
         <v>44747</v>
       </c>
       <c r="B444" t="n">
-        <v>17.10041046142578</v>
+        <v>17.10041236877441</v>
       </c>
       <c r="C444" t="n">
-        <v>17.25157416346159</v>
+        <v>17.25157608767075</v>
       </c>
       <c r="D444" t="n">
-        <v>16.57133750430044</v>
+        <v>16.57133935263724</v>
       </c>
       <c r="E444" t="n">
-        <v>17.15709639918584</v>
+        <v>17.15709831285712</v>
       </c>
       <c r="F444" t="n">
         <v>2077700</v>
@@ -9352,16 +9352,16 @@
         <v>44750</v>
       </c>
       <c r="B447" t="n">
-        <v>17.72396278381348</v>
+        <v>17.72396087646484</v>
       </c>
       <c r="C447" t="n">
-        <v>18.12076798800384</v>
+        <v>18.12076603795336</v>
       </c>
       <c r="D447" t="n">
-        <v>17.64838092596834</v>
+        <v>17.64837902675339</v>
       </c>
       <c r="E447" t="n">
-        <v>17.8184405566233</v>
+        <v>17.81843863910753</v>
       </c>
       <c r="F447" t="n">
         <v>701700</v>
@@ -9372,16 +9372,16 @@
         <v>44753</v>
       </c>
       <c r="B448" t="n">
-        <v>16.76029396057129</v>
+        <v>16.76029205322266</v>
       </c>
       <c r="C448" t="n">
-        <v>17.61059037351305</v>
+        <v>17.61058836939931</v>
       </c>
       <c r="D448" t="n">
-        <v>16.62802615025099</v>
+        <v>16.62802425795465</v>
       </c>
       <c r="E448" t="n">
-        <v>17.61059037351305</v>
+        <v>17.61058836939931</v>
       </c>
       <c r="F448" t="n">
         <v>1587350</v>
@@ -9432,16 +9432,16 @@
         <v>44756</v>
       </c>
       <c r="B451" t="n">
-        <v>17.02482795715332</v>
+        <v>17.02482986450195</v>
       </c>
       <c r="C451" t="n">
-        <v>17.13819982832328</v>
+        <v>17.13820174837335</v>
       </c>
       <c r="D451" t="n">
-        <v>16.53354504338107</v>
+        <v>16.53354689568962</v>
       </c>
       <c r="E451" t="n">
-        <v>16.70360465214942</v>
+        <v>16.70360652351032</v>
       </c>
       <c r="F451" t="n">
         <v>750250</v>
@@ -9532,16 +9532,16 @@
         <v>44763</v>
       </c>
       <c r="B456" t="n">
-        <v>18.02628898620605</v>
+        <v>18.02628707885742</v>
       </c>
       <c r="C456" t="n">
-        <v>18.23413863060609</v>
+        <v>18.23413670126503</v>
       </c>
       <c r="D456" t="n">
-        <v>17.66727563642172</v>
+        <v>17.66727376706003</v>
       </c>
       <c r="E456" t="n">
-        <v>18.04518489988247</v>
+        <v>18.04518299053447</v>
       </c>
       <c r="F456" t="n">
         <v>845300</v>
@@ -9572,16 +9572,16 @@
         <v>44767</v>
       </c>
       <c r="B458" t="n">
-        <v>17.95070648193359</v>
+        <v>17.95070838928223</v>
       </c>
       <c r="C458" t="n">
-        <v>18.30971981868635</v>
+        <v>18.30972176418187</v>
       </c>
       <c r="D458" t="n">
-        <v>17.87512463198494</v>
+        <v>17.87512653130264</v>
       </c>
       <c r="E458" t="n">
-        <v>18.17745203177956</v>
+        <v>18.177453963221</v>
       </c>
       <c r="F458" t="n">
         <v>615900</v>
@@ -9592,16 +9592,16 @@
         <v>44768</v>
       </c>
       <c r="B459" t="n">
-        <v>17.40273666381836</v>
+        <v>17.40273857116699</v>
       </c>
       <c r="C459" t="n">
-        <v>18.15855512180728</v>
+        <v>18.158557111994</v>
       </c>
       <c r="D459" t="n">
-        <v>17.25157297222058</v>
+        <v>17.25157486300159</v>
       </c>
       <c r="E459" t="n">
-        <v>18.04518325411562</v>
+        <v>18.04518523187672</v>
       </c>
       <c r="F459" t="n">
         <v>578050</v>
@@ -9612,16 +9612,16 @@
         <v>44769</v>
       </c>
       <c r="B460" t="n">
-        <v>18.23414039611816</v>
+        <v>18.23413848876953</v>
       </c>
       <c r="C460" t="n">
-        <v>18.38530411613882</v>
+        <v>18.38530219297798</v>
       </c>
       <c r="D460" t="n">
-        <v>17.34605399150023</v>
+        <v>17.34605217704824</v>
       </c>
       <c r="E460" t="n">
-        <v>17.44052996500288</v>
+        <v>17.4405281406684</v>
       </c>
       <c r="F460" t="n">
         <v>704800</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.51903343200684</v>
+        <v>19.5190315246582</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65130123390378</v>
+        <v>19.65129931363029</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431893172991</v>
+        <v>18.74431710008434</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658673362685</v>
+        <v>18.87658488905642</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9672,16 +9672,16 @@
         <v>44774</v>
       </c>
       <c r="B463" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C463" t="n">
-        <v>19.74577744912234</v>
+        <v>19.74577547957757</v>
       </c>
       <c r="D463" t="n">
-        <v>19.04664486253867</v>
+        <v>19.04664296272896</v>
       </c>
       <c r="E463" t="n">
-        <v>19.50013597783399</v>
+        <v>19.50013403279076</v>
       </c>
       <c r="F463" t="n">
         <v>811600</v>
@@ -9692,16 +9692,16 @@
         <v>44775</v>
       </c>
       <c r="B464" t="n">
-        <v>19.08443641662598</v>
+        <v>19.08443832397461</v>
       </c>
       <c r="C464" t="n">
-        <v>19.38676382249504</v>
+        <v>19.38676576005906</v>
       </c>
       <c r="D464" t="n">
-        <v>18.89548088695107</v>
+        <v>18.895482775415</v>
       </c>
       <c r="E464" t="n">
-        <v>19.12222644135287</v>
+        <v>19.12222835247834</v>
       </c>
       <c r="F464" t="n">
         <v>867500</v>
@@ -9712,16 +9712,16 @@
         <v>44776</v>
       </c>
       <c r="B465" t="n">
-        <v>19.68909072875977</v>
+        <v>19.6890926361084</v>
       </c>
       <c r="C465" t="n">
-        <v>19.74577666541846</v>
+        <v>19.74577857825845</v>
       </c>
       <c r="D465" t="n">
-        <v>19.02774819369244</v>
+        <v>19.02775003697459</v>
       </c>
       <c r="E465" t="n">
-        <v>19.08443593236457</v>
+        <v>19.08443778113825</v>
       </c>
       <c r="F465" t="n">
         <v>1095050</v>
@@ -9812,16 +9812,16 @@
         <v>44783</v>
       </c>
       <c r="B470" t="n">
-        <v>21.82428169250488</v>
+        <v>21.82428359985352</v>
       </c>
       <c r="C470" t="n">
-        <v>22.12660911094776</v>
+        <v>22.12661104471852</v>
       </c>
       <c r="D470" t="n">
-        <v>21.08735725854019</v>
+        <v>21.08735910148479</v>
       </c>
       <c r="E470" t="n">
-        <v>21.16293911315091</v>
+        <v>21.16294096270104</v>
       </c>
       <c r="F470" t="n">
         <v>1851300</v>
@@ -9852,16 +9852,16 @@
         <v>44785</v>
       </c>
       <c r="B472" t="n">
-        <v>22.92021751403809</v>
+        <v>22.92021942138672</v>
       </c>
       <c r="C472" t="n">
-        <v>22.99579936214814</v>
+        <v>22.99580127578646</v>
       </c>
       <c r="D472" t="n">
-        <v>21.74869796732555</v>
+        <v>21.748699777184</v>
       </c>
       <c r="E472" t="n">
-        <v>21.74869796732555</v>
+        <v>21.748699777184</v>
       </c>
       <c r="F472" t="n">
         <v>1189950</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75015830993652</v>
+        <v>22.75015640258789</v>
       </c>
       <c r="C474" t="n">
-        <v>23.12806755720854</v>
+        <v>23.1280656181764</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341276157331</v>
+        <v>22.52341087323478</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027753348805</v>
+        <v>23.09027559762419</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9972,16 +9972,16 @@
         <v>44795</v>
       </c>
       <c r="B478" t="n">
-        <v>20.67165565490723</v>
+        <v>20.67165756225586</v>
       </c>
       <c r="C478" t="n">
-        <v>20.86061118784968</v>
+        <v>20.86061311263301</v>
       </c>
       <c r="D478" t="n">
-        <v>20.46380601028133</v>
+        <v>20.46380789845194</v>
       </c>
       <c r="E478" t="n">
-        <v>20.80392524877235</v>
+        <v>20.80392716832534</v>
       </c>
       <c r="F478" t="n">
         <v>1246950</v>
@@ -10012,16 +10012,16 @@
         <v>44797</v>
       </c>
       <c r="B480" t="n">
-        <v>20.80392646789551</v>
+        <v>20.80392456054688</v>
       </c>
       <c r="C480" t="n">
-        <v>21.16293983910836</v>
+        <v>21.16293789884462</v>
       </c>
       <c r="D480" t="n">
-        <v>20.48270312427755</v>
+        <v>20.48270124637937</v>
       </c>
       <c r="E480" t="n">
-        <v>20.76613463828699</v>
+        <v>20.76613273440319</v>
       </c>
       <c r="F480" t="n">
         <v>1050450</v>
@@ -10132,16 +10132,16 @@
         <v>44805</v>
       </c>
       <c r="B486" t="n">
-        <v>20.7850284576416</v>
+        <v>20.78503036499023</v>
       </c>
       <c r="C486" t="n">
-        <v>20.84171439432595</v>
+        <v>20.8417163068764</v>
       </c>
       <c r="D486" t="n">
-        <v>20.16147774807343</v>
+        <v>20.16147959820162</v>
       </c>
       <c r="E486" t="n">
-        <v>20.16147774807343</v>
+        <v>20.16147959820162</v>
       </c>
       <c r="F486" t="n">
         <v>609050</v>
@@ -10172,16 +10172,16 @@
         <v>44809</v>
       </c>
       <c r="B488" t="n">
-        <v>21.72980308532715</v>
+        <v>21.72980117797852</v>
       </c>
       <c r="C488" t="n">
-        <v>21.84317676387566</v>
+        <v>21.84317484657557</v>
       </c>
       <c r="D488" t="n">
-        <v>20.87950680326052</v>
+        <v>20.87950497054724</v>
       </c>
       <c r="E488" t="n">
-        <v>21.01177459322254</v>
+        <v>21.01177274889936</v>
       </c>
       <c r="F488" t="n">
         <v>878600</v>
@@ -10192,16 +10192,16 @@
         <v>44810</v>
       </c>
       <c r="B489" t="n">
-        <v>20.55828475952148</v>
+        <v>20.55828285217285</v>
       </c>
       <c r="C489" t="n">
-        <v>21.67311849274579</v>
+        <v>21.67311648196554</v>
       </c>
       <c r="D489" t="n">
-        <v>20.35043510495954</v>
+        <v>20.3504332168947</v>
       </c>
       <c r="E489" t="n">
-        <v>21.55974480715789</v>
+        <v>21.55974280689618</v>
       </c>
       <c r="F489" t="n">
         <v>1564950</v>
@@ -10212,16 +10212,16 @@
         <v>44812</v>
       </c>
       <c r="B490" t="n">
-        <v>19.76467323303223</v>
+        <v>19.76467514038086</v>
       </c>
       <c r="C490" t="n">
-        <v>20.72834319821961</v>
+        <v>20.7283451985652</v>
       </c>
       <c r="D490" t="n">
-        <v>19.63240544244264</v>
+        <v>19.63240733702705</v>
       </c>
       <c r="E490" t="n">
-        <v>20.72834319821961</v>
+        <v>20.7283451985652</v>
       </c>
       <c r="F490" t="n">
         <v>1701700</v>
@@ -10292,16 +10292,16 @@
         <v>44818</v>
       </c>
       <c r="B494" t="n">
-        <v>20.42601585388184</v>
+        <v>20.4260139465332</v>
       </c>
       <c r="C494" t="n">
-        <v>20.52049181773355</v>
+        <v>20.5204899015629</v>
       </c>
       <c r="D494" t="n">
-        <v>19.51903182439467</v>
+        <v>19.51903000173875</v>
       </c>
       <c r="E494" t="n">
-        <v>19.7079873561251</v>
+        <v>19.70798551582482</v>
       </c>
       <c r="F494" t="n">
         <v>1153500</v>
@@ -10332,16 +10332,16 @@
         <v>44820</v>
       </c>
       <c r="B496" t="n">
-        <v>20.02921104431152</v>
+        <v>20.02920913696289</v>
       </c>
       <c r="C496" t="n">
-        <v>20.27485071722412</v>
+        <v>20.27484878648363</v>
       </c>
       <c r="D496" t="n">
-        <v>19.55682400837977</v>
+        <v>19.55682214601578</v>
       </c>
       <c r="E496" t="n">
-        <v>20.27485071722412</v>
+        <v>20.27484878648363</v>
       </c>
       <c r="F496" t="n">
         <v>1629800</v>
@@ -10372,16 +10372,16 @@
         <v>44824</v>
       </c>
       <c r="B498" t="n">
-        <v>19.84025573730469</v>
+        <v>19.84025382995605</v>
       </c>
       <c r="C498" t="n">
-        <v>20.63386611095796</v>
+        <v>20.63386412731537</v>
       </c>
       <c r="D498" t="n">
-        <v>19.7457779686291</v>
+        <v>19.74577607036311</v>
       </c>
       <c r="E498" t="n">
-        <v>20.36932871906902</v>
+        <v>20.3693267608578</v>
       </c>
       <c r="F498" t="n">
         <v>1041050</v>
@@ -10392,16 +10392,16 @@
         <v>44825</v>
       </c>
       <c r="B499" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C499" t="n">
-        <v>20.08589668660058</v>
+        <v>20.08589468313058</v>
       </c>
       <c r="D499" t="n">
-        <v>19.04664486253867</v>
+        <v>19.04664296272896</v>
       </c>
       <c r="E499" t="n">
-        <v>19.84025521531224</v>
+        <v>19.84025323634378</v>
       </c>
       <c r="F499" t="n">
         <v>1245900</v>
@@ -10452,16 +10452,16 @@
         <v>44830</v>
       </c>
       <c r="B502" t="n">
-        <v>18.70652389526367</v>
+        <v>18.7065258026123</v>
       </c>
       <c r="C502" t="n">
-        <v>19.48124006477188</v>
+        <v>19.48124205111187</v>
       </c>
       <c r="D502" t="n">
-        <v>18.63094204970352</v>
+        <v>18.6309439493457</v>
       </c>
       <c r="E502" t="n">
-        <v>19.34897048353161</v>
+        <v>19.34897245638518</v>
       </c>
       <c r="F502" t="n">
         <v>1198500</v>
@@ -10492,16 +10492,16 @@
         <v>44832</v>
       </c>
       <c r="B504" t="n">
-        <v>18.44199180603027</v>
+        <v>18.44198989868164</v>
       </c>
       <c r="C504" t="n">
-        <v>18.66873738536503</v>
+        <v>18.66873545456541</v>
       </c>
       <c r="D504" t="n">
-        <v>18.15855848035157</v>
+        <v>18.15855660231681</v>
       </c>
       <c r="E504" t="n">
-        <v>18.49867775036054</v>
+        <v>18.49867583714921</v>
       </c>
       <c r="F504" t="n">
         <v>784750</v>
@@ -10592,16 +10592,16 @@
         <v>44839</v>
       </c>
       <c r="B509" t="n">
-        <v>19.63240623474121</v>
+        <v>19.63240814208984</v>
       </c>
       <c r="C509" t="n">
-        <v>19.84025588577203</v>
+        <v>19.8402578133139</v>
       </c>
       <c r="D509" t="n">
-        <v>19.38676475515193</v>
+        <v>19.38676663863574</v>
       </c>
       <c r="E509" t="n">
-        <v>19.72688220211023</v>
+        <v>19.72688411863749</v>
       </c>
       <c r="F509" t="n">
         <v>721150</v>
@@ -10632,16 +10632,16 @@
         <v>44841</v>
       </c>
       <c r="B511" t="n">
-        <v>19.63240623474121</v>
+        <v>19.63240814208984</v>
       </c>
       <c r="C511" t="n">
-        <v>20.38822478577472</v>
+        <v>20.38822676655345</v>
       </c>
       <c r="D511" t="n">
-        <v>19.55682437963786</v>
+        <v>19.55682627964348</v>
       </c>
       <c r="E511" t="n">
-        <v>20.38822478577472</v>
+        <v>20.38822676655345</v>
       </c>
       <c r="F511" t="n">
         <v>673950</v>
@@ -10672,16 +10672,16 @@
         <v>44845</v>
       </c>
       <c r="B513" t="n">
-        <v>19.59461212158203</v>
+        <v>19.59461402893066</v>
       </c>
       <c r="C513" t="n">
-        <v>19.78356763831624</v>
+        <v>19.78356956405789</v>
       </c>
       <c r="D513" t="n">
-        <v>19.16001695591205</v>
+        <v>19.16001882095698</v>
       </c>
       <c r="E513" t="n">
-        <v>19.50013436321493</v>
+        <v>19.50013626136705</v>
       </c>
       <c r="F513" t="n">
         <v>1130250</v>
@@ -10732,16 +10732,16 @@
         <v>44851</v>
       </c>
       <c r="B516" t="n">
-        <v>19.17891120910645</v>
+        <v>19.17891311645508</v>
       </c>
       <c r="C516" t="n">
-        <v>19.70798593910536</v>
+        <v>19.70798789907064</v>
       </c>
       <c r="D516" t="n">
-        <v>19.06553933983051</v>
+        <v>19.06554123590428</v>
       </c>
       <c r="E516" t="n">
-        <v>19.23559894575778</v>
+        <v>19.23560085874403</v>
       </c>
       <c r="F516" t="n">
         <v>780550</v>
@@ -10752,16 +10752,16 @@
         <v>44852</v>
       </c>
       <c r="B517" t="n">
-        <v>19.53792953491211</v>
+        <v>19.53792762756348</v>
       </c>
       <c r="C517" t="n">
-        <v>19.7835710279484</v>
+        <v>19.78356909661954</v>
       </c>
       <c r="D517" t="n">
-        <v>19.23560209794857</v>
+        <v>19.23560022011401</v>
       </c>
       <c r="E517" t="n">
-        <v>19.55682545022575</v>
+        <v>19.55682354103244</v>
       </c>
       <c r="F517" t="n">
         <v>665900</v>
@@ -10852,16 +10852,16 @@
         <v>44859</v>
       </c>
       <c r="B522" t="n">
-        <v>19.17891120910645</v>
+        <v>19.17891311645508</v>
       </c>
       <c r="C522" t="n">
-        <v>19.78356778596044</v>
+        <v>19.78356975344236</v>
       </c>
       <c r="D522" t="n">
-        <v>19.06553933983051</v>
+        <v>19.06554123590428</v>
       </c>
       <c r="E522" t="n">
-        <v>19.51903042096098</v>
+        <v>19.51903236213458</v>
       </c>
       <c r="F522" t="n">
         <v>967800</v>
@@ -11092,16 +11092,16 @@
         <v>44876</v>
       </c>
       <c r="B534" t="n">
-        <v>15.51319026947021</v>
+        <v>15.5131893157959</v>
       </c>
       <c r="C534" t="n">
-        <v>16.96814139722099</v>
+        <v>16.96814035410347</v>
       </c>
       <c r="D534" t="n">
-        <v>15.05969824828244</v>
+        <v>15.05969732248658</v>
       </c>
       <c r="E534" t="n">
-        <v>16.94924728539026</v>
+        <v>16.94924624343426</v>
       </c>
       <c r="F534" t="n">
         <v>6426800</v>
@@ -11112,16 +11112,16 @@
         <v>44879</v>
       </c>
       <c r="B535" t="n">
-        <v>15.45650482177734</v>
+        <v>15.45650577545166</v>
       </c>
       <c r="C535" t="n">
-        <v>16.26900932078551</v>
+        <v>16.26901032459178</v>
       </c>
       <c r="D535" t="n">
-        <v>14.88964000250667</v>
+        <v>14.88964092120513</v>
       </c>
       <c r="E535" t="n">
-        <v>15.96668189771144</v>
+        <v>15.96668288286395</v>
       </c>
       <c r="F535" t="n">
         <v>3328550</v>
@@ -11172,16 +11172,16 @@
         <v>44883</v>
       </c>
       <c r="B538" t="n">
-        <v>13.83149337768555</v>
+        <v>13.83149242401123</v>
       </c>
       <c r="C538" t="n">
-        <v>14.88964027910857</v>
+        <v>14.88963925247558</v>
       </c>
       <c r="D538" t="n">
-        <v>13.73701560571641</v>
+        <v>13.73701465855629</v>
       </c>
       <c r="E538" t="n">
-        <v>14.26608950693133</v>
+        <v>14.26608852329183</v>
       </c>
       <c r="F538" t="n">
         <v>3266800</v>
@@ -11232,16 +11232,16 @@
         <v>44888</v>
       </c>
       <c r="B541" t="n">
-        <v>14.02044677734375</v>
+        <v>14.02044773101807</v>
       </c>
       <c r="C541" t="n">
-        <v>14.07713271469312</v>
+        <v>14.07713367222323</v>
       </c>
       <c r="D541" t="n">
-        <v>13.62364161187125</v>
+        <v>13.62364253855478</v>
       </c>
       <c r="E541" t="n">
-        <v>14.05823770257891</v>
+        <v>14.05823865882377</v>
       </c>
       <c r="F541" t="n">
         <v>1795300</v>
@@ -11372,16 +11372,16 @@
         <v>44897</v>
       </c>
       <c r="B548" t="n">
-        <v>14.28498363494873</v>
+        <v>14.28498268127441</v>
       </c>
       <c r="C548" t="n">
-        <v>14.58731104489259</v>
+        <v>14.58731007103471</v>
       </c>
       <c r="D548" t="n">
-        <v>14.05823807749083</v>
+        <v>14.05823713895419</v>
       </c>
       <c r="E548" t="n">
-        <v>14.17161085621978</v>
+        <v>14.1716099101143</v>
       </c>
       <c r="F548" t="n">
         <v>1219600</v>
@@ -11472,16 +11472,16 @@
         <v>44904</v>
       </c>
       <c r="B553" t="n">
-        <v>12.18758583068848</v>
+        <v>12.18758487701416</v>
       </c>
       <c r="C553" t="n">
-        <v>12.56549602062873</v>
+        <v>12.56549503738307</v>
       </c>
       <c r="D553" t="n">
-        <v>12.09310895895853</v>
+        <v>12.09310801267699</v>
       </c>
       <c r="E553" t="n">
-        <v>12.54660010567865</v>
+        <v>12.54659912391159</v>
       </c>
       <c r="F553" t="n">
         <v>1681850</v>
@@ -11612,16 +11612,16 @@
         <v>44915</v>
       </c>
       <c r="B560" t="n">
-        <v>12.56549453735352</v>
+        <v>12.56549549102783</v>
       </c>
       <c r="C560" t="n">
-        <v>12.86782193281247</v>
+        <v>12.86782290943231</v>
       </c>
       <c r="D560" t="n">
-        <v>11.67740646168276</v>
+        <v>11.6774073479545</v>
       </c>
       <c r="E560" t="n">
-        <v>11.79077923497987</v>
+        <v>11.79078012985618</v>
       </c>
       <c r="F560" t="n">
         <v>2603950</v>
@@ -11692,16 +11692,16 @@
         <v>44921</v>
       </c>
       <c r="B564" t="n">
-        <v>13.17014980316162</v>
+        <v>13.17015075683594</v>
       </c>
       <c r="C564" t="n">
-        <v>13.49137312292281</v>
+        <v>13.49137409985749</v>
       </c>
       <c r="D564" t="n">
-        <v>12.83003147100628</v>
+        <v>12.83003240005202</v>
       </c>
       <c r="E564" t="n">
-        <v>13.41579127133274</v>
+        <v>13.4157922427944</v>
       </c>
       <c r="F564" t="n">
         <v>1094200</v>
@@ -11772,16 +11772,16 @@
         <v>44928</v>
       </c>
       <c r="B568" t="n">
-        <v>12.21331119537354</v>
+        <v>12.21331024169922</v>
       </c>
       <c r="C568" t="n">
-        <v>12.83073010946179</v>
+        <v>12.83072910757643</v>
       </c>
       <c r="D568" t="n">
-        <v>11.98177944759996</v>
+        <v>11.98177851200476</v>
       </c>
       <c r="E568" t="n">
-        <v>12.83073010946179</v>
+        <v>12.83072910757643</v>
       </c>
       <c r="F568" t="n">
         <v>1499800</v>
@@ -11792,16 +11792,16 @@
         <v>44929</v>
       </c>
       <c r="B569" t="n">
-        <v>11.65377616882324</v>
+        <v>11.65377521514893</v>
       </c>
       <c r="C569" t="n">
-        <v>12.21331170950984</v>
+        <v>12.21331071004653</v>
       </c>
       <c r="D569" t="n">
-        <v>11.5958936894559</v>
+        <v>11.59589274051833</v>
       </c>
       <c r="E569" t="n">
-        <v>12.21331170950984</v>
+        <v>12.21331071004653</v>
       </c>
       <c r="F569" t="n">
         <v>2015100</v>
@@ -11852,16 +11852,16 @@
         <v>44932</v>
       </c>
       <c r="B572" t="n">
-        <v>13.08155632019043</v>
+        <v>13.08155727386475</v>
       </c>
       <c r="C572" t="n">
-        <v>13.13943879575224</v>
+        <v>13.13943975364632</v>
       </c>
       <c r="D572" t="n">
-        <v>12.44484264883297</v>
+        <v>12.44484355608945</v>
       </c>
       <c r="E572" t="n">
-        <v>12.73425778671811</v>
+        <v>12.7342587150736</v>
       </c>
       <c r="F572" t="n">
         <v>1382000</v>
@@ -11912,16 +11912,16 @@
         <v>44937</v>
       </c>
       <c r="B575" t="n">
-        <v>14.00768375396729</v>
+        <v>14.0076847076416</v>
       </c>
       <c r="C575" t="n">
-        <v>14.18133209503215</v>
+        <v>14.18133306052883</v>
       </c>
       <c r="D575" t="n">
-        <v>13.71826862549207</v>
+        <v>13.71826955946236</v>
       </c>
       <c r="E575" t="n">
-        <v>14.02697760518546</v>
+        <v>14.02697856017334</v>
       </c>
       <c r="F575" t="n">
         <v>1780450</v>
@@ -11952,16 +11952,16 @@
         <v>44939</v>
       </c>
       <c r="B577" t="n">
-        <v>13.33238220214844</v>
+        <v>13.33238124847412</v>
       </c>
       <c r="C577" t="n">
-        <v>13.4867367003459</v>
+        <v>13.4867357356305</v>
       </c>
       <c r="D577" t="n">
-        <v>13.13943907940161</v>
+        <v>13.13943813952864</v>
       </c>
       <c r="E577" t="n">
-        <v>13.42885422353454</v>
+        <v>13.42885326295952</v>
       </c>
       <c r="F577" t="n">
         <v>1373850</v>
@@ -11972,16 +11972,16 @@
         <v>44942</v>
       </c>
       <c r="B578" t="n">
-        <v>12.88861179351807</v>
+        <v>12.88861274719238</v>
       </c>
       <c r="C578" t="n">
-        <v>13.4867358984841</v>
+        <v>13.48673689641575</v>
       </c>
       <c r="D578" t="n">
-        <v>12.69566868224278</v>
+        <v>12.69566962164055</v>
       </c>
       <c r="E578" t="n">
-        <v>13.29379278720882</v>
+        <v>13.29379377086392</v>
       </c>
       <c r="F578" t="n">
         <v>1617800</v>
@@ -12132,16 +12132,16 @@
         <v>44952</v>
       </c>
       <c r="B586" t="n">
-        <v>14.56721973419189</v>
+        <v>14.56722068786621</v>
       </c>
       <c r="C586" t="n">
-        <v>14.68298560550685</v>
+        <v>14.68298656676003</v>
       </c>
       <c r="D586" t="n">
-        <v>14.20062734834852</v>
+        <v>14.20062827802307</v>
       </c>
       <c r="E586" t="n">
-        <v>14.49004248664859</v>
+        <v>14.49004343527033</v>
       </c>
       <c r="F586" t="n">
         <v>1715850</v>
@@ -12192,16 +12192,16 @@
         <v>44957</v>
       </c>
       <c r="B589" t="n">
-        <v>14.99169540405273</v>
+        <v>14.99169445037842</v>
       </c>
       <c r="C589" t="n">
-        <v>15.04957880284405</v>
+        <v>15.04957784548756</v>
       </c>
       <c r="D589" t="n">
-        <v>14.39357124332777</v>
+        <v>14.39357032770223</v>
       </c>
       <c r="E589" t="n">
-        <v>14.41286509624127</v>
+        <v>14.41286417938838</v>
       </c>
       <c r="F589" t="n">
         <v>1759050</v>
@@ -12212,16 +12212,16 @@
         <v>44958</v>
       </c>
       <c r="B590" t="n">
-        <v>14.99169540405273</v>
+        <v>14.99169445037842</v>
       </c>
       <c r="C590" t="n">
-        <v>15.16534468040126</v>
+        <v>15.1653437156805</v>
       </c>
       <c r="D590" t="n">
-        <v>14.7408688759994</v>
+        <v>14.74086793828104</v>
       </c>
       <c r="E590" t="n">
-        <v>14.97240155113924</v>
+        <v>14.97240059869227</v>
       </c>
       <c r="F590" t="n">
         <v>1831550</v>
@@ -12372,16 +12372,16 @@
         <v>44970</v>
       </c>
       <c r="B598" t="n">
-        <v>14.12345123291016</v>
+        <v>14.12345027923584</v>
       </c>
       <c r="C598" t="n">
-        <v>14.62510338215298</v>
+        <v>14.62510239460502</v>
       </c>
       <c r="D598" t="n">
-        <v>13.96909580542539</v>
+        <v>13.9690948621738</v>
       </c>
       <c r="E598" t="n">
-        <v>14.04627397918049</v>
+        <v>14.04627303071751</v>
       </c>
       <c r="F598" t="n">
         <v>1583800</v>
@@ -12452,16 +12452,16 @@
         <v>44974</v>
       </c>
       <c r="B602" t="n">
-        <v>14.54792499542236</v>
+        <v>14.54792594909668</v>
       </c>
       <c r="C602" t="n">
-        <v>14.79875151052197</v>
+        <v>14.79875248063897</v>
       </c>
       <c r="D602" t="n">
-        <v>14.47074774770331</v>
+        <v>14.47074869631835</v>
       </c>
       <c r="E602" t="n">
-        <v>14.77945673857953</v>
+        <v>14.77945770743167</v>
       </c>
       <c r="F602" t="n">
         <v>1002450</v>
@@ -12632,16 +12632,16 @@
         <v>44991</v>
       </c>
       <c r="B611" t="n">
-        <v>14.12345123291016</v>
+        <v>14.12345027923584</v>
       </c>
       <c r="C611" t="n">
-        <v>14.25851096692435</v>
+        <v>14.25851000413024</v>
       </c>
       <c r="D611" t="n">
-        <v>13.35167777558807</v>
+        <v>13.35167687402712</v>
       </c>
       <c r="E611" t="n">
-        <v>13.35167777558807</v>
+        <v>13.35167687402712</v>
       </c>
       <c r="F611" t="n">
         <v>2062900</v>
@@ -12652,16 +12652,16 @@
         <v>44992</v>
       </c>
       <c r="B612" t="n">
-        <v>14.54792499542236</v>
+        <v>14.54792594909668</v>
       </c>
       <c r="C612" t="n">
-        <v>14.64439701508386</v>
+        <v>14.6443979750823</v>
       </c>
       <c r="D612" t="n">
-        <v>13.50603123118975</v>
+        <v>13.50603211656379</v>
       </c>
       <c r="E612" t="n">
-        <v>13.79544637014889</v>
+        <v>13.79544727449524</v>
       </c>
       <c r="F612" t="n">
         <v>3753550</v>
@@ -12672,16 +12672,16 @@
         <v>44993</v>
       </c>
       <c r="B613" t="n">
-        <v>15.85994052886963</v>
+        <v>15.85993957519531</v>
       </c>
       <c r="C613" t="n">
-        <v>15.85994052886963</v>
+        <v>15.85993957519531</v>
       </c>
       <c r="D613" t="n">
-        <v>14.16203918738023</v>
+        <v>14.16203833580244</v>
       </c>
       <c r="E613" t="n">
-        <v>14.68298608533432</v>
+        <v>14.68298520243147</v>
       </c>
       <c r="F613" t="n">
         <v>5225650</v>
@@ -12932,16 +12932,16 @@
         <v>45012</v>
       </c>
       <c r="B626" t="n">
-        <v>13.98838996887207</v>
+        <v>13.98839092254639</v>
       </c>
       <c r="C626" t="n">
-        <v>14.12345061702205</v>
+        <v>14.12345157990428</v>
       </c>
       <c r="D626" t="n">
-        <v>13.5639150918692</v>
+        <v>13.56391601660446</v>
       </c>
       <c r="E626" t="n">
-        <v>13.83403546814375</v>
+        <v>13.83403641129478</v>
       </c>
       <c r="F626" t="n">
         <v>1142000</v>
@@ -12992,16 +12992,16 @@
         <v>45015</v>
       </c>
       <c r="B629" t="n">
-        <v>14.54792499542236</v>
+        <v>14.54792594909668</v>
       </c>
       <c r="C629" t="n">
-        <v>15.03028325367914</v>
+        <v>15.03028423897396</v>
       </c>
       <c r="D629" t="n">
-        <v>14.33568710418228</v>
+        <v>14.33568804394356</v>
       </c>
       <c r="E629" t="n">
-        <v>14.58651361928189</v>
+        <v>14.58651457548584</v>
       </c>
       <c r="F629" t="n">
         <v>2623900</v>
@@ -13012,16 +13012,16 @@
         <v>45016</v>
       </c>
       <c r="B630" t="n">
-        <v>14.43216037750244</v>
+        <v>14.43215942382812</v>
       </c>
       <c r="C630" t="n">
-        <v>14.66369214077176</v>
+        <v>14.66369117179787</v>
       </c>
       <c r="D630" t="n">
-        <v>14.23921724144468</v>
+        <v>14.23921630052</v>
       </c>
       <c r="E630" t="n">
-        <v>14.62510351356021</v>
+        <v>14.62510254713624</v>
       </c>
       <c r="F630" t="n">
         <v>1751150</v>
@@ -13132,16 +13132,16 @@
         <v>45027</v>
       </c>
       <c r="B636" t="n">
-        <v>15.10746002197266</v>
+        <v>15.10746097564697</v>
       </c>
       <c r="C636" t="n">
-        <v>15.20393203857268</v>
+        <v>15.20393299833689</v>
       </c>
       <c r="D636" t="n">
-        <v>14.1813321587087</v>
+        <v>14.18133305392022</v>
       </c>
       <c r="E636" t="n">
-        <v>14.25850940397859</v>
+        <v>14.258510304062</v>
       </c>
       <c r="F636" t="n">
         <v>3158700</v>
@@ -13172,16 +13172,16 @@
         <v>45029</v>
       </c>
       <c r="B638" t="n">
-        <v>15.70558547973633</v>
+        <v>15.70558643341064</v>
       </c>
       <c r="C638" t="n">
-        <v>15.93711722183911</v>
+        <v>15.93711818957249</v>
       </c>
       <c r="D638" t="n">
-        <v>15.10746043259944</v>
+        <v>15.10746134995442</v>
       </c>
       <c r="E638" t="n">
-        <v>15.49334666943741</v>
+        <v>15.49334761022416</v>
       </c>
       <c r="F638" t="n">
         <v>2173500</v>
@@ -13192,16 +13192,16 @@
         <v>45030</v>
       </c>
       <c r="B639" t="n">
-        <v>15.60911464691162</v>
+        <v>15.6091136932373</v>
       </c>
       <c r="C639" t="n">
-        <v>15.91782365984595</v>
+        <v>15.91782268731036</v>
       </c>
       <c r="D639" t="n">
-        <v>15.12675635418902</v>
+        <v>15.12675542998548</v>
       </c>
       <c r="E639" t="n">
-        <v>15.6862919001452</v>
+        <v>15.68629094175557</v>
       </c>
       <c r="F639" t="n">
         <v>1580050</v>
@@ -13232,16 +13232,16 @@
         <v>45034</v>
       </c>
       <c r="B641" t="n">
-        <v>15.06887149810791</v>
+        <v>15.06887245178223</v>
       </c>
       <c r="C641" t="n">
-        <v>15.74417285865839</v>
+        <v>15.74417385507098</v>
       </c>
       <c r="D641" t="n">
-        <v>14.87592838366854</v>
+        <v>14.87592932513193</v>
       </c>
       <c r="E641" t="n">
-        <v>15.62840791002011</v>
+        <v>15.6284088991062</v>
       </c>
       <c r="F641" t="n">
         <v>1695600</v>
@@ -13252,16 +13252,16 @@
         <v>45035</v>
       </c>
       <c r="B642" t="n">
-        <v>14.43216037750244</v>
+        <v>14.43215942382812</v>
       </c>
       <c r="C642" t="n">
-        <v>14.85663527682952</v>
+        <v>14.85663429510599</v>
       </c>
       <c r="D642" t="n">
-        <v>14.27780586865623</v>
+        <v>14.27780492518163</v>
       </c>
       <c r="E642" t="n">
-        <v>14.85663527682952</v>
+        <v>14.85663429510599</v>
       </c>
       <c r="F642" t="n">
         <v>1793400</v>
@@ -13312,16 +13312,16 @@
         <v>45041</v>
       </c>
       <c r="B645" t="n">
-        <v>14.54792499542236</v>
+        <v>14.54792594909668</v>
       </c>
       <c r="C645" t="n">
-        <v>14.77945673857953</v>
+        <v>14.77945770743167</v>
       </c>
       <c r="D645" t="n">
-        <v>14.27780462840567</v>
+        <v>14.27780556437252</v>
       </c>
       <c r="E645" t="n">
-        <v>14.70227949086047</v>
+        <v>14.70228045465334</v>
       </c>
       <c r="F645" t="n">
         <v>1083300</v>
@@ -13392,16 +13392,16 @@
         <v>45048</v>
       </c>
       <c r="B649" t="n">
-        <v>14.31639289855957</v>
+        <v>14.31639385223389</v>
       </c>
       <c r="C649" t="n">
-        <v>14.68298527618061</v>
+        <v>14.68298625427517</v>
       </c>
       <c r="D649" t="n">
-        <v>14.14274363546925</v>
+        <v>14.14274457757607</v>
       </c>
       <c r="E649" t="n">
-        <v>14.62510188180872</v>
+        <v>14.62510285604742</v>
       </c>
       <c r="F649" t="n">
         <v>2334400</v>
@@ -13492,16 +13492,16 @@
         <v>45055</v>
       </c>
       <c r="B654" t="n">
-        <v>15.43829154968262</v>
+        <v>15.43829250335693</v>
       </c>
       <c r="C654" t="n">
-        <v>15.4769839727144</v>
+        <v>15.47698492877887</v>
       </c>
       <c r="D654" t="n">
-        <v>14.72248126234461</v>
+        <v>14.72248217180096</v>
       </c>
       <c r="E654" t="n">
-        <v>14.87725095447173</v>
+        <v>14.87725187348872</v>
       </c>
       <c r="F654" t="n">
         <v>1653500</v>
@@ -13532,16 +13532,16 @@
         <v>45057</v>
       </c>
       <c r="B656" t="n">
-        <v>15.94129467010498</v>
+        <v>15.94129371643066</v>
       </c>
       <c r="C656" t="n">
-        <v>16.21214258136906</v>
+        <v>16.2121416114915</v>
       </c>
       <c r="D656" t="n">
-        <v>15.28352341167847</v>
+        <v>15.28352249735475</v>
       </c>
       <c r="E656" t="n">
-        <v>15.43829311954353</v>
+        <v>15.43829219596085</v>
       </c>
       <c r="F656" t="n">
         <v>2077100</v>
@@ -13552,16 +13552,16 @@
         <v>45058</v>
       </c>
       <c r="B657" t="n">
-        <v>15.55436897277832</v>
+        <v>15.55436992645264</v>
       </c>
       <c r="C657" t="n">
-        <v>15.92194653396948</v>
+        <v>15.92194751018082</v>
       </c>
       <c r="D657" t="n">
-        <v>15.45763745299108</v>
+        <v>15.45763840073457</v>
       </c>
       <c r="E657" t="n">
-        <v>15.92194653396948</v>
+        <v>15.92194751018082</v>
       </c>
       <c r="F657" t="n">
         <v>1431100</v>
@@ -13572,16 +13572,16 @@
         <v>45061</v>
       </c>
       <c r="B658" t="n">
-        <v>15.9799861907959</v>
+        <v>15.97998714447021</v>
       </c>
       <c r="C658" t="n">
-        <v>16.13475588094887</v>
+        <v>16.13475684385973</v>
       </c>
       <c r="D658" t="n">
-        <v>15.45763710277945</v>
+        <v>15.45763802528034</v>
       </c>
       <c r="E658" t="n">
-        <v>15.6897916380089</v>
+        <v>15.68979257436461</v>
       </c>
       <c r="F658" t="n">
         <v>995650</v>
@@ -13612,16 +13612,16 @@
         <v>45063</v>
       </c>
       <c r="B660" t="n">
-        <v>16.2121410369873</v>
+        <v>16.21214294433594</v>
       </c>
       <c r="C660" t="n">
-        <v>16.2121410369873</v>
+        <v>16.21214294433594</v>
       </c>
       <c r="D660" t="n">
-        <v>15.41894497598903</v>
+        <v>15.41894679001862</v>
       </c>
       <c r="E660" t="n">
-        <v>15.41894497598903</v>
+        <v>15.41894679001862</v>
       </c>
       <c r="F660" t="n">
         <v>1361350</v>
@@ -13632,16 +13632,16 @@
         <v>45064</v>
       </c>
       <c r="B661" t="n">
-        <v>16.8118724822998</v>
+        <v>16.81187438964844</v>
       </c>
       <c r="C661" t="n">
-        <v>16.96664401439827</v>
+        <v>16.96664593930611</v>
       </c>
       <c r="D661" t="n">
-        <v>16.19279373390678</v>
+        <v>16.19279557101939</v>
       </c>
       <c r="E661" t="n">
-        <v>16.23148707818144</v>
+        <v>16.23148891968391</v>
       </c>
       <c r="F661" t="n">
         <v>1963800</v>
@@ -13692,16 +13692,16 @@
         <v>45069</v>
       </c>
       <c r="B664" t="n">
-        <v>17.1407585144043</v>
+        <v>17.14076042175293</v>
       </c>
       <c r="C664" t="n">
-        <v>17.85656877788956</v>
+        <v>17.85657076489042</v>
       </c>
       <c r="D664" t="n">
-        <v>17.1407585144043</v>
+        <v>17.14076042175293</v>
       </c>
       <c r="E664" t="n">
-        <v>17.45029973334405</v>
+        <v>17.45030167513708</v>
       </c>
       <c r="F664" t="n">
         <v>1008500</v>
@@ -13792,16 +13792,16 @@
         <v>45076</v>
       </c>
       <c r="B669" t="n">
-        <v>17.27618408203125</v>
+        <v>17.27618598937988</v>
       </c>
       <c r="C669" t="n">
-        <v>17.99199437484214</v>
+        <v>17.99199636121863</v>
       </c>
       <c r="D669" t="n">
-        <v>17.1214143887208</v>
+        <v>17.12141627898234</v>
       </c>
       <c r="E669" t="n">
-        <v>17.89526285527304</v>
+        <v>17.89526483097004</v>
       </c>
       <c r="F669" t="n">
         <v>1402500</v>
@@ -13812,16 +13812,16 @@
         <v>45077</v>
       </c>
       <c r="B670" t="n">
-        <v>17.87591552734375</v>
+        <v>17.87591743469238</v>
       </c>
       <c r="C670" t="n">
-        <v>17.97264704336838</v>
+        <v>17.9726489610382</v>
       </c>
       <c r="D670" t="n">
-        <v>16.92795072930284</v>
+        <v>16.92795253550424</v>
       </c>
       <c r="E670" t="n">
-        <v>17.10206708914713</v>
+        <v>17.10206891392664</v>
       </c>
       <c r="F670" t="n">
         <v>3045450</v>
@@ -13832,16 +13832,16 @@
         <v>45078</v>
       </c>
       <c r="B671" t="n">
-        <v>18.53368759155273</v>
+        <v>18.53368949890137</v>
       </c>
       <c r="C671" t="n">
-        <v>18.55303426372559</v>
+        <v>18.55303617306524</v>
       </c>
       <c r="D671" t="n">
-        <v>17.75983915464039</v>
+        <v>17.75984098235032</v>
       </c>
       <c r="E671" t="n">
-        <v>17.99199368571409</v>
+        <v>17.99199553731563</v>
       </c>
       <c r="F671" t="n">
         <v>1437950</v>
@@ -13852,16 +13852,16 @@
         <v>45079</v>
       </c>
       <c r="B672" t="n">
-        <v>18.76584243774414</v>
+        <v>18.76584434509277</v>
       </c>
       <c r="C672" t="n">
-        <v>19.19146000769305</v>
+        <v>19.19146195830118</v>
       </c>
       <c r="D672" t="n">
-        <v>18.59172607526503</v>
+        <v>18.59172796491659</v>
       </c>
       <c r="E672" t="n">
-        <v>18.66911092025572</v>
+        <v>18.66911281777262</v>
       </c>
       <c r="F672" t="n">
         <v>1482700</v>
@@ -13892,16 +13892,16 @@
         <v>45083</v>
       </c>
       <c r="B674" t="n">
-        <v>19.67511749267578</v>
+        <v>19.67511558532715</v>
       </c>
       <c r="C674" t="n">
-        <v>19.7718490187313</v>
+        <v>19.7718471020053</v>
       </c>
       <c r="D674" t="n">
-        <v>18.92061380344323</v>
+        <v>18.92061196923783</v>
       </c>
       <c r="E674" t="n">
-        <v>18.99799865528756</v>
+        <v>18.9979968135803</v>
       </c>
       <c r="F674" t="n">
         <v>1624800</v>
@@ -13912,16 +13912,16 @@
         <v>45084</v>
       </c>
       <c r="B675" t="n">
-        <v>19.46230888366699</v>
+        <v>19.46230697631836</v>
       </c>
       <c r="C675" t="n">
-        <v>20.19746402620084</v>
+        <v>20.1974620468054</v>
       </c>
       <c r="D675" t="n">
-        <v>19.26884583878946</v>
+        <v>19.26884395040062</v>
       </c>
       <c r="E675" t="n">
-        <v>19.86857980190955</v>
+        <v>19.86857785474549</v>
       </c>
       <c r="F675" t="n">
         <v>1620300</v>
@@ -13932,16 +13932,16 @@
         <v>45086</v>
       </c>
       <c r="B676" t="n">
-        <v>19.50099945068359</v>
+        <v>19.50100135803223</v>
       </c>
       <c r="C676" t="n">
-        <v>20.10073338504996</v>
+        <v>20.10073535105722</v>
       </c>
       <c r="D676" t="n">
-        <v>19.36557643276226</v>
+        <v>19.36557832686547</v>
       </c>
       <c r="E676" t="n">
-        <v>19.61707764104492</v>
+        <v>19.61707955974689</v>
       </c>
       <c r="F676" t="n">
         <v>1125800</v>
@@ -14052,16 +14052,16 @@
         <v>45096</v>
       </c>
       <c r="B682" t="n">
-        <v>18.99799728393555</v>
+        <v>18.99799919128418</v>
       </c>
       <c r="C682" t="n">
-        <v>19.17211364926698</v>
+        <v>19.17211557409643</v>
       </c>
       <c r="D682" t="n">
-        <v>18.10807062946401</v>
+        <v>18.10807244746636</v>
       </c>
       <c r="E682" t="n">
-        <v>18.47565003294153</v>
+        <v>18.47565188784788</v>
       </c>
       <c r="F682" t="n">
         <v>1236750</v>
@@ -14092,16 +14092,16 @@
         <v>45098</v>
       </c>
       <c r="B684" t="n">
-        <v>18.92061424255371</v>
+        <v>18.92061233520508</v>
       </c>
       <c r="C684" t="n">
-        <v>18.92061424255371</v>
+        <v>18.92061233520508</v>
       </c>
       <c r="D684" t="n">
-        <v>17.9919959988703</v>
+        <v>17.99199418513378</v>
       </c>
       <c r="E684" t="n">
-        <v>18.70780635629304</v>
+        <v>18.70780447039714</v>
       </c>
       <c r="F684" t="n">
         <v>2994400</v>
@@ -14112,16 +14112,16 @@
         <v>45099</v>
       </c>
       <c r="B685" t="n">
-        <v>18.59172821044922</v>
+        <v>18.59172630310059</v>
       </c>
       <c r="C685" t="n">
-        <v>18.68845973904686</v>
+        <v>18.68845782177442</v>
       </c>
       <c r="D685" t="n">
-        <v>18.06938090802268</v>
+        <v>18.0693790542623</v>
       </c>
       <c r="E685" t="n">
-        <v>18.59172821044922</v>
+        <v>18.59172630310059</v>
       </c>
       <c r="F685" t="n">
         <v>1830800</v>
@@ -14292,16 +14292,16 @@
         <v>45112</v>
       </c>
       <c r="B694" t="n">
-        <v>17.52768707275391</v>
+        <v>17.52768516540527</v>
       </c>
       <c r="C694" t="n">
-        <v>17.60507192725832</v>
+        <v>17.60507001148873</v>
       </c>
       <c r="D694" t="n">
-        <v>17.06337610072697</v>
+        <v>17.06337424390427</v>
       </c>
       <c r="E694" t="n">
-        <v>17.1601076301076</v>
+        <v>17.16010576275866</v>
       </c>
       <c r="F694" t="n">
         <v>1649600</v>
@@ -14392,16 +14392,16 @@
         <v>45119</v>
       </c>
       <c r="B699" t="n">
-        <v>18.20480155944824</v>
+        <v>18.20480346679688</v>
       </c>
       <c r="C699" t="n">
-        <v>18.49499610727698</v>
+        <v>18.4949980450298</v>
       </c>
       <c r="D699" t="n">
-        <v>18.08872521631691</v>
+        <v>18.08872711150403</v>
       </c>
       <c r="E699" t="n">
-        <v>18.1661100600712</v>
+        <v>18.16611196336606</v>
       </c>
       <c r="F699" t="n">
         <v>1232250</v>
@@ -14552,16 +14552,16 @@
         <v>45131</v>
       </c>
       <c r="B707" t="n">
-        <v>17.97264671325684</v>
+        <v>17.97264862060547</v>
       </c>
       <c r="C707" t="n">
-        <v>18.28218608285004</v>
+        <v>18.28218802304856</v>
       </c>
       <c r="D707" t="n">
-        <v>17.8565685271593</v>
+        <v>17.85657042218912</v>
       </c>
       <c r="E707" t="n">
-        <v>18.14676306990306</v>
+        <v>18.1467649957298</v>
       </c>
       <c r="F707" t="n">
         <v>773050</v>
@@ -14592,16 +14592,16 @@
         <v>45133</v>
       </c>
       <c r="B709" t="n">
-        <v>18.10807037353516</v>
+        <v>18.10807228088379</v>
       </c>
       <c r="C709" t="n">
-        <v>18.22414856378228</v>
+        <v>18.2241504833576</v>
       </c>
       <c r="D709" t="n">
-        <v>17.66310797508836</v>
+        <v>17.66310983556847</v>
       </c>
       <c r="E709" t="n">
-        <v>18.08872554599417</v>
+        <v>18.08872745130519</v>
       </c>
       <c r="F709" t="n">
         <v>1094200</v>
@@ -14632,16 +14632,16 @@
         <v>45135</v>
       </c>
       <c r="B711" t="n">
-        <v>18.28218841552734</v>
+        <v>18.28218650817871</v>
       </c>
       <c r="C711" t="n">
-        <v>18.41761329075375</v>
+        <v>18.41761136927648</v>
       </c>
       <c r="D711" t="n">
-        <v>17.93395750280329</v>
+        <v>17.93395563178498</v>
       </c>
       <c r="E711" t="n">
-        <v>18.20480356325529</v>
+        <v>18.20480166398008</v>
       </c>
       <c r="F711" t="n">
         <v>795400</v>
@@ -14652,16 +14652,16 @@
         <v>45138</v>
       </c>
       <c r="B712" t="n">
-        <v>18.92061424255371</v>
+        <v>18.92061233520508</v>
       </c>
       <c r="C712" t="n">
-        <v>19.03669244551436</v>
+        <v>19.03669052646412</v>
       </c>
       <c r="D712" t="n">
-        <v>18.30153541343144</v>
+        <v>18.30153356849088</v>
       </c>
       <c r="E712" t="n">
-        <v>18.30153541343144</v>
+        <v>18.30153356849088</v>
       </c>
       <c r="F712" t="n">
         <v>1469350</v>
@@ -14672,16 +14672,16 @@
         <v>45139</v>
       </c>
       <c r="B713" t="n">
-        <v>19.67511749267578</v>
+        <v>19.67511558532715</v>
       </c>
       <c r="C713" t="n">
-        <v>19.86858054478681</v>
+        <v>19.86857861868345</v>
       </c>
       <c r="D713" t="n">
-        <v>18.68845924791023</v>
+        <v>18.6884574362104</v>
       </c>
       <c r="E713" t="n">
-        <v>18.76584409975457</v>
+        <v>18.76584228055287</v>
       </c>
       <c r="F713" t="n">
         <v>1967600</v>
@@ -14712,16 +14712,16 @@
         <v>45141</v>
       </c>
       <c r="B715" t="n">
-        <v>20.50700569152832</v>
+        <v>20.50700378417969</v>
       </c>
       <c r="C715" t="n">
-        <v>20.95196812095753</v>
+        <v>20.95196617222311</v>
       </c>
       <c r="D715" t="n">
-        <v>19.98465656654582</v>
+        <v>19.98465470778068</v>
       </c>
       <c r="E715" t="n">
-        <v>20.19746444431626</v>
+        <v>20.19746256575794</v>
       </c>
       <c r="F715" t="n">
         <v>3735250</v>
@@ -14732,16 +14732,16 @@
         <v>45142</v>
       </c>
       <c r="B716" t="n">
-        <v>21.22281455993652</v>
+        <v>21.22281646728516</v>
       </c>
       <c r="C716" t="n">
-        <v>21.51300726829016</v>
+        <v>21.51300920171915</v>
       </c>
       <c r="D716" t="n">
-        <v>20.35223458987537</v>
+        <v>20.35223641898275</v>
       </c>
       <c r="E716" t="n">
-        <v>20.39092608998907</v>
+        <v>20.39092792257376</v>
       </c>
       <c r="F716" t="n">
         <v>1802550</v>
@@ -14812,16 +14812,16 @@
         <v>45148</v>
       </c>
       <c r="B720" t="n">
-        <v>21.22281455993652</v>
+        <v>21.22281646728516</v>
       </c>
       <c r="C720" t="n">
-        <v>21.22281455993652</v>
+        <v>21.22281646728516</v>
       </c>
       <c r="D720" t="n">
-        <v>20.79719698868431</v>
+        <v>20.79719885778161</v>
       </c>
       <c r="E720" t="n">
-        <v>20.89392850646894</v>
+        <v>20.89393038425974</v>
       </c>
       <c r="F720" t="n">
         <v>1139450</v>
@@ -14952,16 +14952,16 @@
         <v>45159</v>
       </c>
       <c r="B727" t="n">
-        <v>19.42361640930176</v>
+        <v>19.42361450195312</v>
       </c>
       <c r="C727" t="n">
-        <v>20.13942675550606</v>
+        <v>20.13942477786671</v>
       </c>
       <c r="D727" t="n">
-        <v>19.42361640930176</v>
+        <v>19.42361450195312</v>
       </c>
       <c r="E727" t="n">
-        <v>19.92661887258059</v>
+        <v>19.92661691583842</v>
       </c>
       <c r="F727" t="n">
         <v>897550</v>
@@ -14992,16 +14992,16 @@
         <v>45161</v>
       </c>
       <c r="B729" t="n">
-        <v>20.66177368164062</v>
+        <v>20.66177558898926</v>
       </c>
       <c r="C729" t="n">
-        <v>20.83589004221628</v>
+        <v>20.8358919656381</v>
       </c>
       <c r="D729" t="n">
-        <v>20.08138642805517</v>
+        <v>20.08138828182657</v>
       </c>
       <c r="E729" t="n">
-        <v>20.42961914920649</v>
+        <v>20.42962103512426</v>
       </c>
       <c r="F729" t="n">
         <v>1158100</v>
@@ -15352,16 +15352,16 @@
         <v>45188</v>
       </c>
       <c r="B747" t="n">
-        <v>17.81787872314453</v>
+        <v>17.8178768157959</v>
       </c>
       <c r="C747" t="n">
-        <v>18.10807144848877</v>
+        <v>18.1080695100759</v>
       </c>
       <c r="D747" t="n">
-        <v>17.72114719969634</v>
+        <v>17.72114530270251</v>
       </c>
       <c r="E747" t="n">
-        <v>17.89526357290302</v>
+        <v>17.89526165727057</v>
       </c>
       <c r="F747" t="n">
         <v>1342600</v>
@@ -15372,16 +15372,16 @@
         <v>45189</v>
       </c>
       <c r="B748" t="n">
-        <v>18.03068733215332</v>
+        <v>18.03068542480469</v>
       </c>
       <c r="C748" t="n">
-        <v>18.41761344168485</v>
+        <v>18.41761149340584</v>
       </c>
       <c r="D748" t="n">
-        <v>17.93395764977086</v>
+        <v>17.93395575265463</v>
       </c>
       <c r="E748" t="n">
-        <v>17.9533024792471</v>
+        <v>17.95330058008451</v>
       </c>
       <c r="F748" t="n">
         <v>1770700</v>
@@ -15432,16 +15432,16 @@
         <v>45194</v>
       </c>
       <c r="B751" t="n">
-        <v>16.88925933837891</v>
+        <v>16.88925743103027</v>
       </c>
       <c r="C751" t="n">
-        <v>17.08272239280495</v>
+        <v>17.08272046360803</v>
       </c>
       <c r="D751" t="n">
-        <v>16.5603750978553</v>
+        <v>16.56037322764844</v>
       </c>
       <c r="E751" t="n">
-        <v>17.08272239280495</v>
+        <v>17.08272046360803</v>
       </c>
       <c r="F751" t="n">
         <v>2075200</v>
@@ -15512,16 +15512,16 @@
         <v>45198</v>
       </c>
       <c r="B755" t="n">
-        <v>17.10206985473633</v>
+        <v>17.1020679473877</v>
       </c>
       <c r="C755" t="n">
-        <v>17.17945471106995</v>
+        <v>17.1794527950908</v>
       </c>
       <c r="D755" t="n">
-        <v>16.94730014206907</v>
+        <v>16.9472982519815</v>
       </c>
       <c r="E755" t="n">
-        <v>17.0246849984027</v>
+        <v>17.0246830996846</v>
       </c>
       <c r="F755" t="n">
         <v>1545500</v>
@@ -15532,16 +15532,16 @@
         <v>45201</v>
       </c>
       <c r="B756" t="n">
-        <v>16.46364212036133</v>
+        <v>16.46364402770996</v>
       </c>
       <c r="C756" t="n">
-        <v>17.14075906120447</v>
+        <v>17.14076104699856</v>
       </c>
       <c r="D756" t="n">
-        <v>16.36691060166938</v>
+        <v>16.36691249781145</v>
       </c>
       <c r="E756" t="n">
-        <v>17.14075906120447</v>
+        <v>17.14076104699856</v>
       </c>
       <c r="F756" t="n">
         <v>2150300</v>
@@ -15592,16 +15592,16 @@
         <v>45204</v>
       </c>
       <c r="B759" t="n">
-        <v>15.76717758178711</v>
+        <v>15.76717662811279</v>
       </c>
       <c r="C759" t="n">
-        <v>15.8639091061233</v>
+        <v>15.8639081465982</v>
       </c>
       <c r="D759" t="n">
-        <v>15.39960000331002</v>
+        <v>15.39959907186856</v>
       </c>
       <c r="E759" t="n">
-        <v>15.65110122858397</v>
+        <v>15.65110028193051</v>
       </c>
       <c r="F759" t="n">
         <v>1526350</v>
@@ -15612,16 +15612,16 @@
         <v>45205</v>
       </c>
       <c r="B760" t="n">
-        <v>15.51567840576172</v>
+        <v>15.5156774520874</v>
       </c>
       <c r="C760" t="n">
-        <v>15.63175476049288</v>
+        <v>15.63175379968391</v>
       </c>
       <c r="D760" t="n">
-        <v>15.05136837433608</v>
+        <v>15.05136744920068</v>
       </c>
       <c r="E760" t="n">
-        <v>15.38025353190817</v>
+        <v>15.38025258655777</v>
       </c>
       <c r="F760" t="n">
         <v>2332450</v>
@@ -15632,16 +15632,16 @@
         <v>45208</v>
       </c>
       <c r="B761" t="n">
-        <v>15.76717758178711</v>
+        <v>15.76717662811279</v>
       </c>
       <c r="C761" t="n">
-        <v>15.90260245385793</v>
+        <v>15.90260149199247</v>
       </c>
       <c r="D761" t="n">
-        <v>15.16744545190338</v>
+        <v>15.16744453450374</v>
       </c>
       <c r="E761" t="n">
-        <v>15.36090757807558</v>
+        <v>15.36090664897442</v>
       </c>
       <c r="F761" t="n">
         <v>1413450</v>
@@ -15652,16 +15652,16 @@
         <v>45209</v>
       </c>
       <c r="B762" t="n">
-        <v>15.99933433532715</v>
+        <v>15.99933338165283</v>
       </c>
       <c r="C762" t="n">
-        <v>16.40560342560713</v>
+        <v>16.40560244771628</v>
       </c>
       <c r="D762" t="n">
-        <v>15.767177933738</v>
+        <v>15.76717699390186</v>
       </c>
       <c r="E762" t="n">
-        <v>15.767177933738</v>
+        <v>15.76717699390186</v>
       </c>
       <c r="F762" t="n">
         <v>2287650</v>
@@ -15672,16 +15672,16 @@
         <v>45210</v>
       </c>
       <c r="B763" t="n">
-        <v>15.63175487518311</v>
+        <v>15.63175392150879</v>
       </c>
       <c r="C763" t="n">
-        <v>16.25083369162587</v>
+        <v>16.25083270018231</v>
       </c>
       <c r="D763" t="n">
-        <v>15.5737166973917</v>
+        <v>15.57371574725822</v>
       </c>
       <c r="E763" t="n">
-        <v>16.25083369162587</v>
+        <v>16.25083270018231</v>
       </c>
       <c r="F763" t="n">
         <v>1774000</v>
@@ -15732,16 +15732,16 @@
         <v>45216</v>
       </c>
       <c r="B766" t="n">
-        <v>14.66444301605225</v>
+        <v>14.66444206237793</v>
       </c>
       <c r="C766" t="n">
-        <v>15.01267576601139</v>
+        <v>15.01267478969041</v>
       </c>
       <c r="D766" t="n">
-        <v>14.66444301605225</v>
+        <v>14.66444206237793</v>
       </c>
       <c r="E766" t="n">
-        <v>14.85790514241834</v>
+        <v>14.85790417616257</v>
       </c>
       <c r="F766" t="n">
         <v>1172700</v>
@@ -15752,16 +15752,16 @@
         <v>45217</v>
       </c>
       <c r="B767" t="n">
-        <v>13.81320762634277</v>
+        <v>13.81320858001709</v>
       </c>
       <c r="C767" t="n">
-        <v>14.6257494142159</v>
+        <v>14.62575042398871</v>
       </c>
       <c r="D767" t="n">
-        <v>13.81320762634277</v>
+        <v>13.81320858001709</v>
       </c>
       <c r="E767" t="n">
-        <v>14.60640366438564</v>
+        <v>14.60640467282281</v>
       </c>
       <c r="F767" t="n">
         <v>3548700</v>
@@ -15812,16 +15812,16 @@
         <v>45222</v>
       </c>
       <c r="B770" t="n">
-        <v>13.81320762634277</v>
+        <v>13.81320858001709</v>
       </c>
       <c r="C770" t="n">
-        <v>14.10340125379748</v>
+        <v>14.10340222750698</v>
       </c>
       <c r="D770" t="n">
-        <v>13.52301399888807</v>
+        <v>13.5230149325272</v>
       </c>
       <c r="E770" t="n">
-        <v>13.60039976570942</v>
+        <v>13.60040070469132</v>
       </c>
       <c r="F770" t="n">
         <v>2055750</v>
@@ -15832,16 +15832,16 @@
         <v>45223</v>
       </c>
       <c r="B771" t="n">
-        <v>13.85190105438232</v>
+        <v>13.85190010070801</v>
       </c>
       <c r="C771" t="n">
-        <v>14.12274895167485</v>
+        <v>14.12274797935322</v>
       </c>
       <c r="D771" t="n">
-        <v>13.54236165461965</v>
+        <v>13.54236072225647</v>
       </c>
       <c r="E771" t="n">
-        <v>13.92928590432299</v>
+        <v>13.92928494532089</v>
       </c>
       <c r="F771" t="n">
         <v>1706300</v>
@@ -15852,16 +15852,16 @@
         <v>45224</v>
       </c>
       <c r="B772" t="n">
-        <v>13.34889888763428</v>
+        <v>13.34889984130859</v>
       </c>
       <c r="C772" t="n">
-        <v>13.87124706085692</v>
+        <v>13.87124805184892</v>
       </c>
       <c r="D772" t="n">
-        <v>13.19412919519796</v>
+        <v>13.19413013781519</v>
       </c>
       <c r="E772" t="n">
-        <v>13.87124706085692</v>
+        <v>13.87124805184892</v>
       </c>
       <c r="F772" t="n">
         <v>2334300</v>
@@ -15892,16 +15892,16 @@
         <v>45226</v>
       </c>
       <c r="B774" t="n">
-        <v>13.34889888763428</v>
+        <v>13.34889984130859</v>
       </c>
       <c r="C774" t="n">
-        <v>14.16144069542508</v>
+        <v>14.16144170714915</v>
       </c>
       <c r="D774" t="n">
-        <v>13.34889888763428</v>
+        <v>13.34889984130859</v>
       </c>
       <c r="E774" t="n">
-        <v>14.00667008048863</v>
+        <v>14.00667108115555</v>
       </c>
       <c r="F774" t="n">
         <v>1736750</v>
@@ -15912,16 +15912,16 @@
         <v>45229</v>
       </c>
       <c r="B775" t="n">
-        <v>13.19412994384766</v>
+        <v>13.19412899017334</v>
       </c>
       <c r="C775" t="n">
-        <v>13.67778572140439</v>
+        <v>13.67778473277133</v>
       </c>
       <c r="D775" t="n">
-        <v>13.13609084464077</v>
+        <v>13.13608989516153</v>
       </c>
       <c r="E775" t="n">
-        <v>13.44563024707701</v>
+        <v>13.44562927522421</v>
       </c>
       <c r="F775" t="n">
         <v>1606200</v>
@@ -16012,16 +16012,16 @@
         <v>45237</v>
       </c>
       <c r="B780" t="n">
-        <v>15.30286884307861</v>
+        <v>15.3028678894043</v>
       </c>
       <c r="C780" t="n">
-        <v>15.47698522202648</v>
+        <v>15.47698425750123</v>
       </c>
       <c r="D780" t="n">
-        <v>14.45163454516713</v>
+        <v>14.45163364454171</v>
       </c>
       <c r="E780" t="n">
-        <v>14.52902031997745</v>
+        <v>14.52901941452935</v>
       </c>
       <c r="F780" t="n">
         <v>3016050</v>
@@ -16032,16 +16032,16 @@
         <v>45238</v>
       </c>
       <c r="B781" t="n">
-        <v>15.12875270843506</v>
+        <v>15.12875175476074</v>
       </c>
       <c r="C781" t="n">
-        <v>15.67044757282283</v>
+        <v>15.67044658500158</v>
       </c>
       <c r="D781" t="n">
-        <v>14.99332876171307</v>
+        <v>14.99332781657551</v>
       </c>
       <c r="E781" t="n">
-        <v>15.39959967937886</v>
+        <v>15.39959870863111</v>
       </c>
       <c r="F781" t="n">
         <v>2428450</v>
@@ -16052,16 +16052,16 @@
         <v>45239</v>
       </c>
       <c r="B782" t="n">
-        <v>14.43228816986084</v>
+        <v>14.43228721618652</v>
       </c>
       <c r="C782" t="n">
-        <v>15.07071363508924</v>
+        <v>15.07071263922827</v>
       </c>
       <c r="D782" t="n">
-        <v>14.43228816986084</v>
+        <v>14.43228721618652</v>
       </c>
       <c r="E782" t="n">
-        <v>15.07071363508924</v>
+        <v>15.07071263922827</v>
       </c>
       <c r="F782" t="n">
         <v>2913950</v>
@@ -16092,16 +16092,16 @@
         <v>45243</v>
       </c>
       <c r="B784" t="n">
-        <v>14.7418270111084</v>
+        <v>14.74182796478271</v>
       </c>
       <c r="C784" t="n">
-        <v>15.03202064506725</v>
+        <v>15.0320216175147</v>
       </c>
       <c r="D784" t="n">
-        <v>14.70313458808056</v>
+        <v>14.7031355392518</v>
       </c>
       <c r="E784" t="n">
-        <v>14.95463579901157</v>
+        <v>14.95463676645286</v>
       </c>
       <c r="F784" t="n">
         <v>860600</v>
@@ -16112,16 +16112,16 @@
         <v>45244</v>
       </c>
       <c r="B785" t="n">
-        <v>15.63175487518311</v>
+        <v>15.63175392150879</v>
       </c>
       <c r="C785" t="n">
-        <v>15.92194760914055</v>
+        <v>15.92194663776193</v>
       </c>
       <c r="D785" t="n">
-        <v>14.76117482831036</v>
+        <v>14.76117392774907</v>
       </c>
       <c r="E785" t="n">
-        <v>14.76117482831036</v>
+        <v>14.76117392774907</v>
       </c>
       <c r="F785" t="n">
         <v>2729450</v>
@@ -16132,16 +16132,16 @@
         <v>45246</v>
       </c>
       <c r="B786" t="n">
-        <v>15.63175487518311</v>
+        <v>15.63175392150879</v>
       </c>
       <c r="C786" t="n">
-        <v>15.94129428340449</v>
+        <v>15.94129331084555</v>
       </c>
       <c r="D786" t="n">
-        <v>15.53502334886382</v>
+        <v>15.53502240109098</v>
       </c>
       <c r="E786" t="n">
-        <v>15.74783307576633</v>
+        <v>15.74783211501022</v>
       </c>
       <c r="F786" t="n">
         <v>2085150</v>
@@ -16152,16 +16152,16 @@
         <v>45247</v>
       </c>
       <c r="B787" t="n">
-        <v>15.5350227355957</v>
+        <v>15.53502178192139</v>
       </c>
       <c r="C787" t="n">
-        <v>15.92194698059802</v>
+        <v>15.92194600317094</v>
       </c>
       <c r="D787" t="n">
-        <v>15.49633123359564</v>
+        <v>15.49633028229654</v>
       </c>
       <c r="E787" t="n">
-        <v>15.72848578059703</v>
+        <v>15.72848481504628</v>
       </c>
       <c r="F787" t="n">
         <v>2256600</v>
@@ -16212,16 +16212,16 @@
         <v>45252</v>
       </c>
       <c r="B790" t="n">
-        <v>15.99933433532715</v>
+        <v>15.99933338165283</v>
       </c>
       <c r="C790" t="n">
-        <v>16.5216816264017</v>
+        <v>16.52168064159176</v>
       </c>
       <c r="D790" t="n">
-        <v>15.8252179566355</v>
+        <v>15.82521701333976</v>
       </c>
       <c r="E790" t="n">
-        <v>15.84456278593425</v>
+        <v>15.84456184148542</v>
       </c>
       <c r="F790" t="n">
         <v>1763100</v>
@@ -16232,16 +16232,16 @@
         <v>45253</v>
       </c>
       <c r="B791" t="n">
-        <v>16.25083160400391</v>
+        <v>16.25083351135254</v>
       </c>
       <c r="C791" t="n">
-        <v>16.67644915813263</v>
+        <v>16.67645111543569</v>
       </c>
       <c r="D791" t="n">
-        <v>15.78652255131812</v>
+        <v>15.78652440417113</v>
       </c>
       <c r="E791" t="n">
-        <v>16.07671709299686</v>
+        <v>16.0767189799098</v>
       </c>
       <c r="F791" t="n">
         <v>2342200</v>
@@ -16272,16 +16272,16 @@
         <v>45257</v>
       </c>
       <c r="B793" t="n">
-        <v>15.9799861907959</v>
+        <v>15.97998714447021</v>
       </c>
       <c r="C793" t="n">
-        <v>16.30887224362101</v>
+        <v>16.30887321692302</v>
       </c>
       <c r="D793" t="n">
-        <v>15.82521650064293</v>
+        <v>15.8252174450807</v>
       </c>
       <c r="E793" t="n">
-        <v>16.15410255346805</v>
+        <v>16.1541035175335</v>
       </c>
       <c r="F793" t="n">
         <v>1299600</v>
@@ -16292,16 +16292,16 @@
         <v>45258</v>
       </c>
       <c r="B794" t="n">
-        <v>15.8639087677002</v>
+        <v>15.86390781402588</v>
       </c>
       <c r="C794" t="n">
-        <v>16.19279483642693</v>
+        <v>16.19279386298131</v>
       </c>
       <c r="D794" t="n">
-        <v>15.70913907006412</v>
+        <v>15.70913812569394</v>
       </c>
       <c r="E794" t="n">
-        <v>15.8639087677002</v>
+        <v>15.86390781402588</v>
       </c>
       <c r="F794" t="n">
         <v>1112300</v>
@@ -16312,16 +16312,16 @@
         <v>45259</v>
       </c>
       <c r="B795" t="n">
-        <v>16.2121410369873</v>
+        <v>16.21214294433594</v>
       </c>
       <c r="C795" t="n">
-        <v>16.50233375034019</v>
+        <v>16.50233569182982</v>
       </c>
       <c r="D795" t="n">
-        <v>16.07671801675599</v>
+        <v>16.07671990817219</v>
       </c>
       <c r="E795" t="n">
-        <v>16.19279436409704</v>
+        <v>16.19279626916955</v>
       </c>
       <c r="F795" t="n">
         <v>1523050</v>
@@ -16332,16 +16332,16 @@
         <v>45260</v>
       </c>
       <c r="B796" t="n">
-        <v>16.40560340881348</v>
+        <v>16.40560150146484</v>
       </c>
       <c r="C796" t="n">
-        <v>16.65710463944393</v>
+        <v>16.65710270285525</v>
       </c>
       <c r="D796" t="n">
-        <v>16.15410402318344</v>
+        <v>16.15410214507463</v>
       </c>
       <c r="E796" t="n">
-        <v>16.36691190525517</v>
+        <v>16.36691000240489</v>
       </c>
       <c r="F796" t="n">
         <v>2105800</v>
@@ -16392,16 +16392,16 @@
         <v>45265</v>
       </c>
       <c r="B799" t="n">
-        <v>16.8118724822998</v>
+        <v>16.81187438964844</v>
       </c>
       <c r="C799" t="n">
-        <v>17.06337368508452</v>
+        <v>17.06337562096659</v>
       </c>
       <c r="D799" t="n">
-        <v>16.54102645237796</v>
+        <v>16.54102832899844</v>
       </c>
       <c r="E799" t="n">
-        <v>16.56037312451529</v>
+        <v>16.5603750033307</v>
       </c>
       <c r="F799" t="n">
         <v>1673400</v>
@@ -16412,16 +16412,16 @@
         <v>45266</v>
       </c>
       <c r="B800" t="n">
-        <v>16.86991500854492</v>
+        <v>16.86991310119629</v>
       </c>
       <c r="C800" t="n">
-        <v>17.14076107876208</v>
+        <v>17.14075914079101</v>
       </c>
       <c r="D800" t="n">
-        <v>16.79253015348281</v>
+        <v>16.79252825488348</v>
       </c>
       <c r="E800" t="n">
-        <v>16.86991500854492</v>
+        <v>16.86991310119629</v>
       </c>
       <c r="F800" t="n">
         <v>1160950</v>
@@ -16452,16 +16452,16 @@
         <v>45268</v>
       </c>
       <c r="B802" t="n">
-        <v>17.04402923583984</v>
+        <v>17.04403114318848</v>
       </c>
       <c r="C802" t="n">
-        <v>17.21814375393562</v>
+        <v>17.21814568076891</v>
       </c>
       <c r="D802" t="n">
-        <v>16.65710316451525</v>
+        <v>16.65710502856409</v>
       </c>
       <c r="E802" t="n">
-        <v>17.14075890867075</v>
+        <v>17.14076082684412</v>
       </c>
       <c r="F802" t="n">
         <v>1314900</v>
@@ -16472,16 +16472,16 @@
         <v>45271</v>
       </c>
       <c r="B803" t="n">
-        <v>16.96664619445801</v>
+        <v>16.96664428710938</v>
       </c>
       <c r="C803" t="n">
-        <v>17.10206922681956</v>
+        <v>17.102067304247</v>
       </c>
       <c r="D803" t="n">
-        <v>16.83122131709602</v>
+        <v>16.83121942497151</v>
       </c>
       <c r="E803" t="n">
-        <v>17.06337587757315</v>
+        <v>17.0633739593504</v>
       </c>
       <c r="F803" t="n">
         <v>1129450</v>
@@ -16532,16 +16532,16 @@
         <v>45274</v>
       </c>
       <c r="B806" t="n">
-        <v>18.18545532226562</v>
+        <v>18.18545722961426</v>
       </c>
       <c r="C806" t="n">
-        <v>19.11407531453039</v>
+        <v>19.11407731927565</v>
       </c>
       <c r="D806" t="n">
-        <v>17.99199413075231</v>
+        <v>17.99199601781012</v>
       </c>
       <c r="E806" t="n">
-        <v>18.47564987703597</v>
+        <v>18.47565181482114</v>
       </c>
       <c r="F806" t="n">
         <v>3264550</v>
@@ -16552,16 +16552,16 @@
         <v>45275</v>
       </c>
       <c r="B807" t="n">
-        <v>18.18545532226562</v>
+        <v>18.18545722961426</v>
       </c>
       <c r="C807" t="n">
-        <v>18.41761170408201</v>
+        <v>18.41761363577994</v>
       </c>
       <c r="D807" t="n">
-        <v>18.05003230370628</v>
+        <v>18.05003419685131</v>
       </c>
       <c r="E807" t="n">
-        <v>18.32088018582522</v>
+        <v>18.32088210737765</v>
       </c>
       <c r="F807" t="n">
         <v>1249050</v>
@@ -16572,16 +16572,16 @@
         <v>45278</v>
       </c>
       <c r="B808" t="n">
-        <v>18.39826393127441</v>
+        <v>18.39826583862305</v>
       </c>
       <c r="C808" t="n">
-        <v>18.61107178271392</v>
+        <v>18.61107371212435</v>
       </c>
       <c r="D808" t="n">
-        <v>18.18545423483477</v>
+        <v>18.18545612012141</v>
       </c>
       <c r="E808" t="n">
-        <v>18.20480090632931</v>
+        <v>18.20480279362162</v>
       </c>
       <c r="F808" t="n">
         <v>1257100</v>
@@ -16592,16 +16592,16 @@
         <v>45279</v>
       </c>
       <c r="B809" t="n">
-        <v>18.20480155944824</v>
+        <v>18.20480346679688</v>
       </c>
       <c r="C809" t="n">
-        <v>18.57238095103127</v>
+        <v>18.57238289689183</v>
       </c>
       <c r="D809" t="n">
-        <v>18.14676338788258</v>
+        <v>18.14676528915045</v>
       </c>
       <c r="E809" t="n">
-        <v>18.53368760665402</v>
+        <v>18.53368954846061</v>
       </c>
       <c r="F809" t="n">
         <v>801350</v>
@@ -16632,16 +16632,16 @@
         <v>45281</v>
       </c>
       <c r="B811" t="n">
-        <v>18.30153274536133</v>
+        <v>18.30153465270996</v>
       </c>
       <c r="C811" t="n">
-        <v>18.30153274536133</v>
+        <v>18.30153465270996</v>
       </c>
       <c r="D811" t="n">
-        <v>17.7791836756892</v>
+        <v>17.77918552859967</v>
       </c>
       <c r="E811" t="n">
-        <v>17.97264670408632</v>
+        <v>17.97264857715912</v>
       </c>
       <c r="F811" t="n">
         <v>1203800</v>
@@ -16692,16 +16692,16 @@
         <v>45287</v>
       </c>
       <c r="B814" t="n">
-        <v>18.99799728393555</v>
+        <v>18.99799919128418</v>
       </c>
       <c r="C814" t="n">
-        <v>19.11407547582326</v>
+        <v>19.11407739482583</v>
       </c>
       <c r="D814" t="n">
-        <v>18.55303487919991</v>
+        <v>18.5530367418755</v>
       </c>
       <c r="E814" t="n">
-        <v>18.59172637982897</v>
+        <v>18.59172824638908</v>
       </c>
       <c r="F814" t="n">
         <v>1585900</v>
@@ -16852,16 +16852,16 @@
         <v>45301</v>
       </c>
       <c r="B822" t="n">
-        <v>17.79853248596191</v>
+        <v>17.79853057861328</v>
       </c>
       <c r="C822" t="n">
-        <v>18.14676524091565</v>
+        <v>18.14676329624926</v>
       </c>
       <c r="D822" t="n">
-        <v>17.70180096014139</v>
+        <v>17.70179906315882</v>
       </c>
       <c r="E822" t="n">
-        <v>17.74049430846976</v>
+        <v>17.74049240734069</v>
       </c>
       <c r="F822" t="n">
         <v>1471250</v>
@@ -16992,16 +16992,16 @@
         <v>45310</v>
       </c>
       <c r="B829" t="n">
-        <v>15.96063995361328</v>
+        <v>15.9606409072876</v>
       </c>
       <c r="C829" t="n">
-        <v>16.01867812775361</v>
+        <v>16.0186790848958</v>
       </c>
       <c r="D829" t="n">
-        <v>15.39959935025598</v>
+        <v>15.3996002704072</v>
       </c>
       <c r="E829" t="n">
-        <v>15.786523586192</v>
+        <v>15.78652452946258</v>
       </c>
       <c r="F829" t="n">
         <v>1462850</v>
@@ -17132,16 +17132,16 @@
         <v>45321</v>
       </c>
       <c r="B836" t="n">
-        <v>14.70313549041748</v>
+        <v>14.70313453674316</v>
       </c>
       <c r="C836" t="n">
-        <v>14.93529004283192</v>
+        <v>14.9352890740996</v>
       </c>
       <c r="D836" t="n">
-        <v>14.64509731356396</v>
+        <v>14.64509636365412</v>
       </c>
       <c r="E836" t="n">
-        <v>14.93529004283192</v>
+        <v>14.9352890740996</v>
       </c>
       <c r="F836" t="n">
         <v>1155000</v>
@@ -17172,16 +17172,16 @@
         <v>45323</v>
       </c>
       <c r="B838" t="n">
-        <v>14.70313549041748</v>
+        <v>14.70313453674316</v>
       </c>
       <c r="C838" t="n">
-        <v>15.32221521935618</v>
+        <v>15.32221422552713</v>
       </c>
       <c r="D838" t="n">
-        <v>14.64509731356396</v>
+        <v>14.64509636365412</v>
       </c>
       <c r="E838" t="n">
-        <v>15.10940641839285</v>
+        <v>15.109405438367</v>
       </c>
       <c r="F838" t="n">
         <v>1910050</v>
@@ -17192,16 +17192,16 @@
         <v>45324</v>
       </c>
       <c r="B839" t="n">
-        <v>14.54836559295654</v>
+        <v>14.54836463928223</v>
       </c>
       <c r="C839" t="n">
-        <v>14.99332894034418</v>
+        <v>14.99332795750163</v>
       </c>
       <c r="D839" t="n">
-        <v>14.37424921973959</v>
+        <v>14.37424827747894</v>
       </c>
       <c r="E839" t="n">
-        <v>14.7224819661735</v>
+        <v>14.72248100108551</v>
       </c>
       <c r="F839" t="n">
         <v>1676950</v>
@@ -17232,16 +17232,16 @@
         <v>45328</v>
       </c>
       <c r="B841" t="n">
-        <v>14.50967216491699</v>
+        <v>14.50967311859131</v>
       </c>
       <c r="C841" t="n">
-        <v>14.85790396477496</v>
+        <v>14.85790494133744</v>
       </c>
       <c r="D841" t="n">
-        <v>14.35490247609123</v>
+        <v>14.35490341959303</v>
       </c>
       <c r="E841" t="n">
-        <v>14.43228732050411</v>
+        <v>14.43228826909217</v>
       </c>
       <c r="F841" t="n">
         <v>1423950</v>
@@ -17272,16 +17272,16 @@
         <v>45330</v>
       </c>
       <c r="B843" t="n">
-        <v>14.54836559295654</v>
+        <v>14.54836463928223</v>
       </c>
       <c r="C843" t="n">
-        <v>15.01267561403504</v>
+        <v>15.01267462992427</v>
       </c>
       <c r="D843" t="n">
-        <v>14.23882619390433</v>
+        <v>14.23882526052094</v>
       </c>
       <c r="E843" t="n">
-        <v>15.01267561403504</v>
+        <v>15.01267462992427</v>
       </c>
       <c r="F843" t="n">
         <v>1518250</v>
@@ -17312,16 +17312,16 @@
         <v>45336</v>
       </c>
       <c r="B845" t="n">
-        <v>14.02601623535156</v>
+        <v>14.02601718902588</v>
       </c>
       <c r="C845" t="n">
-        <v>14.16144017248258</v>
+        <v>14.16144113536481</v>
       </c>
       <c r="D845" t="n">
-        <v>13.90993897031073</v>
+        <v>13.90993991609258</v>
       </c>
       <c r="E845" t="n">
-        <v>14.1227477508023</v>
+        <v>14.12274871105371</v>
       </c>
       <c r="F845" t="n">
         <v>825600</v>
@@ -17372,16 +17372,16 @@
         <v>45341</v>
       </c>
       <c r="B848" t="n">
-        <v>14.0453634262085</v>
+        <v>14.04536437988281</v>
       </c>
       <c r="C848" t="n">
-        <v>14.39359523419295</v>
+        <v>14.39359621151207</v>
       </c>
       <c r="D848" t="n">
-        <v>13.96797765748959</v>
+        <v>13.96797860590945</v>
       </c>
       <c r="E848" t="n">
-        <v>14.37424856138819</v>
+        <v>14.37424953739368</v>
       </c>
       <c r="F848" t="n">
         <v>1052250</v>
@@ -17392,16 +17392,16 @@
         <v>45342</v>
       </c>
       <c r="B849" t="n">
-        <v>14.8579044342041</v>
+        <v>14.85790538787842</v>
       </c>
       <c r="C849" t="n">
-        <v>14.8579044342041</v>
+        <v>14.85790538787842</v>
       </c>
       <c r="D849" t="n">
-        <v>13.85190050255226</v>
+        <v>13.85190139165488</v>
       </c>
       <c r="E849" t="n">
-        <v>14.02601686923244</v>
+        <v>14.02601776951094</v>
       </c>
       <c r="F849" t="n">
         <v>1580750</v>
@@ -17452,16 +17452,16 @@
         <v>45345</v>
       </c>
       <c r="B852" t="n">
-        <v>14.72248077392578</v>
+        <v>14.7224817276001</v>
       </c>
       <c r="C852" t="n">
-        <v>14.97398105403876</v>
+        <v>14.97398202400444</v>
       </c>
       <c r="D852" t="n">
-        <v>14.62574925830534</v>
+        <v>14.6257502057137</v>
       </c>
       <c r="E852" t="n">
-        <v>14.89659621054244</v>
+        <v>14.89659717549539</v>
       </c>
       <c r="F852" t="n">
         <v>898000</v>
@@ -17572,16 +17572,16 @@
         <v>45355</v>
       </c>
       <c r="B858" t="n">
-        <v>14.6257495880127</v>
+        <v>14.62575054168701</v>
       </c>
       <c r="C858" t="n">
-        <v>15.3609065403004</v>
+        <v>15.36090754191074</v>
       </c>
       <c r="D858" t="n">
-        <v>14.6257495880127</v>
+        <v>14.62575054168701</v>
       </c>
       <c r="E858" t="n">
-        <v>15.01267473671681</v>
+        <v>15.01267571562064</v>
       </c>
       <c r="F858" t="n">
         <v>1354250</v>
@@ -17632,16 +17632,16 @@
         <v>45358</v>
       </c>
       <c r="B861" t="n">
-        <v>14.81921291351318</v>
+        <v>14.81921195983887</v>
       </c>
       <c r="C861" t="n">
-        <v>14.89659776508504</v>
+        <v>14.8965968064307</v>
       </c>
       <c r="D861" t="n">
-        <v>14.60640503294068</v>
+        <v>14.60640409296138</v>
       </c>
       <c r="E861" t="n">
-        <v>14.79986716187032</v>
+        <v>14.79986620944098</v>
       </c>
       <c r="F861" t="n">
         <v>965200</v>
@@ -17652,16 +17652,16 @@
         <v>45359</v>
       </c>
       <c r="B862" t="n">
-        <v>14.6257495880127</v>
+        <v>14.62575054168701</v>
       </c>
       <c r="C862" t="n">
-        <v>15.18679017725854</v>
+        <v>15.1867911675156</v>
       </c>
       <c r="D862" t="n">
-        <v>14.4709798975311</v>
+        <v>14.47098084111363</v>
       </c>
       <c r="E862" t="n">
-        <v>14.72248110581375</v>
+        <v>14.72248206579546</v>
       </c>
       <c r="F862" t="n">
         <v>1363500</v>
@@ -17672,16 +17672,16 @@
         <v>45362</v>
       </c>
       <c r="B863" t="n">
-        <v>14.72248077392578</v>
+        <v>14.7224817276001</v>
       </c>
       <c r="C863" t="n">
-        <v>14.89659621054244</v>
+        <v>14.89659717549539</v>
       </c>
       <c r="D863" t="n">
-        <v>14.4709795713127</v>
+        <v>14.47098050869559</v>
       </c>
       <c r="E863" t="n">
-        <v>14.58705683655718</v>
+        <v>14.58705778145917</v>
       </c>
       <c r="F863" t="n">
         <v>1166500</v>
@@ -17712,16 +17712,16 @@
         <v>45364</v>
       </c>
       <c r="B865" t="n">
-        <v>15.32221412658691</v>
+        <v>15.32221508026123</v>
       </c>
       <c r="C865" t="n">
-        <v>15.38025229930119</v>
+        <v>15.38025325658788</v>
       </c>
       <c r="D865" t="n">
-        <v>14.83855838230071</v>
+        <v>14.83855930587167</v>
       </c>
       <c r="E865" t="n">
-        <v>15.03202049551517</v>
+        <v>15.03202143112746</v>
       </c>
       <c r="F865" t="n">
         <v>836800</v>
@@ -17772,16 +17772,16 @@
         <v>45369</v>
       </c>
       <c r="B868" t="n">
-        <v>14.7418270111084</v>
+        <v>14.74182796478271</v>
       </c>
       <c r="C868" t="n">
-        <v>15.14809791415077</v>
+        <v>15.14809889410745</v>
       </c>
       <c r="D868" t="n">
-        <v>14.72248126084454</v>
+        <v>14.72248221326735</v>
       </c>
       <c r="E868" t="n">
-        <v>14.91594337598374</v>
+        <v>14.91594434092194</v>
       </c>
       <c r="F868" t="n">
         <v>1960200</v>
@@ -17812,16 +17812,16 @@
         <v>45371</v>
       </c>
       <c r="B870" t="n">
-        <v>15.5350227355957</v>
+        <v>15.53502178192139</v>
       </c>
       <c r="C870" t="n">
-        <v>15.67044760509676</v>
+        <v>15.6704466431089</v>
       </c>
       <c r="D870" t="n">
-        <v>14.85790484559156</v>
+        <v>14.85790393348461</v>
       </c>
       <c r="E870" t="n">
-        <v>14.93528969459202</v>
+        <v>14.93528877773452</v>
       </c>
       <c r="F870" t="n">
         <v>1877500</v>
@@ -17912,16 +17912,16 @@
         <v>45378</v>
       </c>
       <c r="B875" t="n">
-        <v>13.92928504943848</v>
+        <v>13.92928600311279</v>
       </c>
       <c r="C875" t="n">
-        <v>15.14809774495188</v>
+        <v>15.14809878207271</v>
       </c>
       <c r="D875" t="n">
-        <v>13.60039991862545</v>
+        <v>13.6004008497825</v>
       </c>
       <c r="E875" t="n">
-        <v>14.74182684644741</v>
+        <v>14.74182785575274</v>
       </c>
       <c r="F875" t="n">
         <v>5512200</v>
@@ -17952,16 +17952,16 @@
         <v>45383</v>
       </c>
       <c r="B877" t="n">
-        <v>13.92928504943848</v>
+        <v>13.92928600311279</v>
       </c>
       <c r="C877" t="n">
-        <v>14.58705715606478</v>
+        <v>14.58705815477374</v>
       </c>
       <c r="D877" t="n">
-        <v>13.90993929939071</v>
+        <v>13.90994025174051</v>
       </c>
       <c r="E877" t="n">
-        <v>14.3742483705386</v>
+        <v>14.37424935467752</v>
       </c>
       <c r="F877" t="n">
         <v>1720450</v>
@@ -18012,16 +18012,16 @@
         <v>45386</v>
       </c>
       <c r="B880" t="n">
-        <v>13.75516986846924</v>
+        <v>13.75517082214355</v>
       </c>
       <c r="C880" t="n">
-        <v>14.1807865250498</v>
+        <v>14.180787508233</v>
       </c>
       <c r="D880" t="n">
-        <v>13.56170775184171</v>
+        <v>13.5617086921029</v>
       </c>
       <c r="E880" t="n">
-        <v>13.6197459255799</v>
+        <v>13.619746869865</v>
       </c>
       <c r="F880" t="n">
         <v>1938500</v>
@@ -18052,16 +18052,16 @@
         <v>45390</v>
       </c>
       <c r="B882" t="n">
-        <v>13.96797847747803</v>
+        <v>13.96797752380371</v>
       </c>
       <c r="C882" t="n">
-        <v>14.08405667612067</v>
+        <v>14.08405571452103</v>
       </c>
       <c r="D882" t="n">
-        <v>13.56170847222953</v>
+        <v>13.56170754629361</v>
       </c>
       <c r="E882" t="n">
-        <v>13.58105422366985</v>
+        <v>13.58105329641307</v>
       </c>
       <c r="F882" t="n">
         <v>1262500</v>
@@ -18072,16 +18072,16 @@
         <v>45391</v>
       </c>
       <c r="B883" t="n">
-        <v>14.54836559295654</v>
+        <v>14.54836463928223</v>
       </c>
       <c r="C883" t="n">
-        <v>14.70313529248265</v>
+        <v>14.70313432866287</v>
       </c>
       <c r="D883" t="n">
-        <v>14.08405649437823</v>
+        <v>14.0840555711403</v>
       </c>
       <c r="E883" t="n">
-        <v>14.08405649437823</v>
+        <v>14.0840555711403</v>
       </c>
       <c r="F883" t="n">
         <v>1883300</v>
@@ -18112,16 +18112,16 @@
         <v>45393</v>
       </c>
       <c r="B885" t="n">
-        <v>13.81320762634277</v>
+        <v>13.81320858001709</v>
       </c>
       <c r="C885" t="n">
-        <v>14.18078609811872</v>
+        <v>14.18078707717093</v>
       </c>
       <c r="D885" t="n">
-        <v>13.77451520418215</v>
+        <v>13.77451615518512</v>
       </c>
       <c r="E885" t="n">
-        <v>13.89059247066401</v>
+        <v>13.89059342968104</v>
       </c>
       <c r="F885" t="n">
         <v>1884250</v>
@@ -18292,16 +18292,16 @@
         <v>45406</v>
       </c>
       <c r="B894" t="n">
-        <v>11.33689212799072</v>
+        <v>11.33689117431641</v>
       </c>
       <c r="C894" t="n">
-        <v>11.89793277811738</v>
+        <v>11.89793177724758</v>
       </c>
       <c r="D894" t="n">
-        <v>11.31754545333108</v>
+        <v>11.31754450128423</v>
       </c>
       <c r="E894" t="n">
-        <v>11.83989367663866</v>
+        <v>11.83989268065119</v>
       </c>
       <c r="F894" t="n">
         <v>4655650</v>
@@ -18332,16 +18332,16 @@
         <v>45408</v>
       </c>
       <c r="B896" t="n">
-        <v>11.53035354614258</v>
+        <v>11.53035259246826</v>
       </c>
       <c r="C896" t="n">
-        <v>11.72381566822547</v>
+        <v>11.72381469854993</v>
       </c>
       <c r="D896" t="n">
-        <v>11.12408262851841</v>
+        <v>11.12408170844672</v>
       </c>
       <c r="E896" t="n">
-        <v>11.12408262851841</v>
+        <v>11.12408170844672</v>
       </c>
       <c r="F896" t="n">
         <v>4499500</v>
@@ -18512,16 +18512,16 @@
         <v>45422</v>
       </c>
       <c r="B905" t="n">
-        <v>11.91727828979492</v>
+        <v>11.91727733612061</v>
       </c>
       <c r="C905" t="n">
-        <v>12.51701135463848</v>
+        <v>12.51701035297082</v>
       </c>
       <c r="D905" t="n">
-        <v>11.85924011198759</v>
+        <v>11.85923916295775</v>
       </c>
       <c r="E905" t="n">
-        <v>12.18812619456314</v>
+        <v>12.18812521921435</v>
       </c>
       <c r="F905" t="n">
         <v>2860000</v>
@@ -18552,16 +18552,16 @@
         <v>45426</v>
       </c>
       <c r="B907" t="n">
-        <v>11.72381496429443</v>
+        <v>11.72381591796875</v>
       </c>
       <c r="C907" t="n">
-        <v>11.97531616915144</v>
+        <v>11.97531714328413</v>
       </c>
       <c r="D907" t="n">
-        <v>11.62708437031105</v>
+        <v>11.62708531611681</v>
       </c>
       <c r="E907" t="n">
-        <v>11.80119980848119</v>
+        <v>11.80120076845038</v>
       </c>
       <c r="F907" t="n">
         <v>1774250</v>
@@ -18592,16 +18592,16 @@
         <v>45428</v>
       </c>
       <c r="B909" t="n">
-        <v>12.49766540527344</v>
+        <v>12.49766445159912</v>
       </c>
       <c r="C909" t="n">
-        <v>12.51701115673661</v>
+        <v>12.51701020158606</v>
       </c>
       <c r="D909" t="n">
-        <v>12.09139447704472</v>
+        <v>12.09139355437221</v>
       </c>
       <c r="E909" t="n">
-        <v>12.38158812899383</v>
+        <v>12.38158718417716</v>
       </c>
       <c r="F909" t="n">
         <v>1367600</v>
@@ -18612,16 +18612,16 @@
         <v>45429</v>
       </c>
       <c r="B910" t="n">
-        <v>12.42027950286865</v>
+        <v>12.42028045654297</v>
       </c>
       <c r="C910" t="n">
-        <v>12.57504919147136</v>
+        <v>12.57505015702946</v>
       </c>
       <c r="D910" t="n">
-        <v>12.26550981426595</v>
+        <v>12.26551075605648</v>
       </c>
       <c r="E910" t="n">
-        <v>12.51701009699529</v>
+        <v>12.51701105809693</v>
       </c>
       <c r="F910" t="n">
         <v>1489500</v>
@@ -18672,16 +18672,16 @@
         <v>45434</v>
       </c>
       <c r="B913" t="n">
-        <v>11.95596981048584</v>
+        <v>11.95597076416016</v>
       </c>
       <c r="C913" t="n">
-        <v>12.26551011785288</v>
+        <v>12.26551109621784</v>
       </c>
       <c r="D913" t="n">
-        <v>11.93662406018172</v>
+        <v>11.93662501231292</v>
       </c>
       <c r="E913" t="n">
-        <v>12.1687785988319</v>
+        <v>12.16877956948103</v>
       </c>
       <c r="F913" t="n">
         <v>1558800</v>
@@ -18732,16 +18732,16 @@
         <v>45439</v>
       </c>
       <c r="B916" t="n">
-        <v>11.80120086669922</v>
+        <v>11.8011999130249</v>
       </c>
       <c r="C916" t="n">
-        <v>11.8785857178251</v>
+        <v>11.87858475789719</v>
       </c>
       <c r="D916" t="n">
-        <v>11.64643116444746</v>
+        <v>11.64643022328033</v>
       </c>
       <c r="E916" t="n">
-        <v>11.82054754073078</v>
+        <v>11.82054658549303</v>
       </c>
       <c r="F916" t="n">
         <v>882300</v>
@@ -18772,16 +18772,16 @@
         <v>45441</v>
       </c>
       <c r="B918" t="n">
-        <v>11.64643096923828</v>
+        <v>11.64643001556396</v>
       </c>
       <c r="C918" t="n">
-        <v>11.8205473426032</v>
+        <v>11.82054637467127</v>
       </c>
       <c r="D918" t="n">
-        <v>11.53035369449506</v>
+        <v>11.5303527503258</v>
       </c>
       <c r="E918" t="n">
-        <v>11.60773854432388</v>
+        <v>11.60773759381791</v>
       </c>
       <c r="F918" t="n">
         <v>2109650</v>
@@ -18892,16 +18892,16 @@
         <v>45450</v>
       </c>
       <c r="B924" t="n">
-        <v>11.22081470489502</v>
+        <v>11.2208137512207</v>
       </c>
       <c r="C924" t="n">
-        <v>11.68512382082161</v>
+        <v>11.68512282768494</v>
       </c>
       <c r="D924" t="n">
-        <v>11.22081470489502</v>
+        <v>11.2208137512207</v>
       </c>
       <c r="E924" t="n">
-        <v>11.60773896816717</v>
+        <v>11.60773798160757</v>
       </c>
       <c r="F924" t="n">
         <v>2327400</v>
@@ -19052,16 +19052,16 @@
         <v>45462</v>
       </c>
       <c r="B932" t="n">
-        <v>10.25350284576416</v>
+        <v>10.25350189208984</v>
       </c>
       <c r="C932" t="n">
-        <v>10.25350284576416</v>
+        <v>10.25350189208984</v>
       </c>
       <c r="D932" t="n">
-        <v>9.924616769664151</v>
+        <v>9.9246158465794</v>
       </c>
       <c r="E932" t="n">
-        <v>10.07938647076999</v>
+        <v>10.07938553329017</v>
       </c>
       <c r="F932" t="n">
         <v>739050</v>
@@ -19212,16 +19212,16 @@
         <v>45474</v>
       </c>
       <c r="B940" t="n">
-        <v>10.4082727432251</v>
+        <v>10.40827178955078</v>
       </c>
       <c r="C940" t="n">
-        <v>10.54369577299741</v>
+        <v>10.54369480691475</v>
       </c>
       <c r="D940" t="n">
-        <v>10.25350303919948</v>
+        <v>10.25350209970618</v>
       </c>
       <c r="E940" t="n">
-        <v>10.31154121695898</v>
+        <v>10.31154027214784</v>
       </c>
       <c r="F940" t="n">
         <v>1525600</v>
@@ -19252,16 +19252,16 @@
         <v>45476</v>
       </c>
       <c r="B942" t="n">
-        <v>11.33689212799072</v>
+        <v>11.33689117431641</v>
       </c>
       <c r="C942" t="n">
-        <v>11.33689212799072</v>
+        <v>11.33689117431641</v>
       </c>
       <c r="D942" t="n">
-        <v>10.4276187139922</v>
+        <v>10.42761783680716</v>
       </c>
       <c r="E942" t="n">
-        <v>10.4276187139922</v>
+        <v>10.42761783680716</v>
       </c>
       <c r="F942" t="n">
         <v>2681150</v>
@@ -19292,16 +19292,16 @@
         <v>45478</v>
       </c>
       <c r="B944" t="n">
-        <v>13.31020736694336</v>
+        <v>13.31020641326904</v>
       </c>
       <c r="C944" t="n">
-        <v>13.50366949560529</v>
+        <v>13.50366852806944</v>
       </c>
       <c r="D944" t="n">
-        <v>12.43962640421439</v>
+        <v>12.43962551291707</v>
       </c>
       <c r="E944" t="n">
-        <v>12.76851248418977</v>
+        <v>12.76851156932781</v>
       </c>
       <c r="F944" t="n">
         <v>3453400</v>
@@ -19432,16 +19432,16 @@
         <v>45489</v>
       </c>
       <c r="B951" t="n">
-        <v>13.11674404144287</v>
+        <v>13.11674499511719</v>
       </c>
       <c r="C951" t="n">
-        <v>13.36824432450511</v>
+        <v>13.36824529646517</v>
       </c>
       <c r="D951" t="n">
-        <v>13.00066585233708</v>
+        <v>13.00066679757175</v>
       </c>
       <c r="E951" t="n">
-        <v>13.05870494688998</v>
+        <v>13.05870589634447</v>
       </c>
       <c r="F951" t="n">
         <v>878950</v>
@@ -19452,16 +19452,16 @@
         <v>45490</v>
       </c>
       <c r="B952" t="n">
-        <v>13.11674404144287</v>
+        <v>13.11674499511719</v>
       </c>
       <c r="C952" t="n">
-        <v>13.29085948010133</v>
+        <v>13.29086044643499</v>
       </c>
       <c r="D952" t="n">
-        <v>13.03935827453898</v>
+        <v>13.03935922258683</v>
       </c>
       <c r="E952" t="n">
-        <v>13.19412888584666</v>
+        <v>13.19412984514736</v>
       </c>
       <c r="F952" t="n">
         <v>1096150</v>
@@ -19512,16 +19512,16 @@
         <v>45495</v>
       </c>
       <c r="B955" t="n">
-        <v>12.2268180847168</v>
+        <v>12.22681713104248</v>
       </c>
       <c r="C955" t="n">
-        <v>12.55570323037755</v>
+        <v>12.55570225105066</v>
       </c>
       <c r="D955" t="n">
-        <v>12.07204746484683</v>
+        <v>12.0720465232444</v>
       </c>
       <c r="E955" t="n">
-        <v>12.3815877820866</v>
+        <v>12.38158681634047</v>
       </c>
       <c r="F955" t="n">
         <v>1509750</v>
@@ -19532,16 +19532,16 @@
         <v>45496</v>
       </c>
       <c r="B956" t="n">
-        <v>11.83989238739014</v>
+        <v>11.83989334106445</v>
       </c>
       <c r="C956" t="n">
-        <v>12.36224055381911</v>
+        <v>12.36224154956729</v>
       </c>
       <c r="D956" t="n">
-        <v>11.80119996478429</v>
+        <v>11.80120091534203</v>
       </c>
       <c r="E956" t="n">
-        <v>12.18812511334287</v>
+        <v>12.18812609506648</v>
       </c>
       <c r="F956" t="n">
         <v>1251950</v>
@@ -19612,16 +19612,16 @@
         <v>45502</v>
       </c>
       <c r="B960" t="n">
-        <v>11.91727828979492</v>
+        <v>11.91727733612061</v>
       </c>
       <c r="C960" t="n">
-        <v>12.82655168544498</v>
+        <v>12.82655065900651</v>
       </c>
       <c r="D960" t="n">
-        <v>11.91727828979492</v>
+        <v>11.91727733612061</v>
       </c>
       <c r="E960" t="n">
-        <v>12.38158832475457</v>
+        <v>12.38158733392407</v>
       </c>
       <c r="F960" t="n">
         <v>1341100</v>
@@ -19632,16 +19632,16 @@
         <v>45503</v>
       </c>
       <c r="B961" t="n">
-        <v>11.53035354614258</v>
+        <v>11.53035259246826</v>
       </c>
       <c r="C961" t="n">
-        <v>11.89793203935016</v>
+        <v>11.89793105527347</v>
       </c>
       <c r="D961" t="n">
-        <v>11.51100687268421</v>
+        <v>11.51100592061005</v>
       </c>
       <c r="E961" t="n">
-        <v>11.89793203935016</v>
+        <v>11.89793105527347</v>
       </c>
       <c r="F961" t="n">
         <v>1370800</v>
@@ -19672,16 +19672,16 @@
         <v>45505</v>
       </c>
       <c r="B963" t="n">
-        <v>12.03335571289062</v>
+        <v>12.03335475921631</v>
       </c>
       <c r="C963" t="n">
-        <v>12.76851273897564</v>
+        <v>12.76851172703824</v>
       </c>
       <c r="D963" t="n">
-        <v>12.03335571289062</v>
+        <v>12.03335475921631</v>
       </c>
       <c r="E963" t="n">
-        <v>12.55570393195099</v>
+        <v>12.55570293687923</v>
       </c>
       <c r="F963" t="n">
         <v>1586950</v>
@@ -19692,16 +19692,16 @@
         <v>45506</v>
       </c>
       <c r="B964" t="n">
-        <v>12.65243434906006</v>
+        <v>12.65243530273438</v>
       </c>
       <c r="C964" t="n">
-        <v>12.71047344497324</v>
+        <v>12.71047440302224</v>
       </c>
       <c r="D964" t="n">
-        <v>11.91727738749385</v>
+        <v>11.91727828575588</v>
       </c>
       <c r="E964" t="n">
-        <v>12.03335465682007</v>
+        <v>12.0333555638314</v>
       </c>
       <c r="F964" t="n">
         <v>1882450</v>
@@ -19712,16 +19712,16 @@
         <v>45509</v>
       </c>
       <c r="B965" t="n">
-        <v>12.3428955078125</v>
+        <v>12.34289455413818</v>
       </c>
       <c r="C965" t="n">
-        <v>12.55570338303328</v>
+        <v>12.55570241291635</v>
       </c>
       <c r="D965" t="n">
-        <v>12.01400943565289</v>
+        <v>12.01400850738997</v>
       </c>
       <c r="E965" t="n">
-        <v>12.18812580856096</v>
+        <v>12.18812486684493</v>
       </c>
       <c r="F965" t="n">
         <v>1772600</v>
@@ -19732,16 +19732,16 @@
         <v>45510</v>
       </c>
       <c r="B966" t="n">
-        <v>11.64643096923828</v>
+        <v>11.64643001556396</v>
       </c>
       <c r="C966" t="n">
-        <v>12.6137425145986</v>
+        <v>12.61374148171546</v>
       </c>
       <c r="D966" t="n">
-        <v>11.64643096923828</v>
+        <v>11.64643001556396</v>
       </c>
       <c r="E966" t="n">
-        <v>12.40093371631928</v>
+        <v>12.4009327008621</v>
       </c>
       <c r="F966" t="n">
         <v>2298300</v>
@@ -19812,16 +19812,16 @@
         <v>45516</v>
       </c>
       <c r="B970" t="n">
-        <v>13.27151489257812</v>
+        <v>13.27151393890381</v>
       </c>
       <c r="C970" t="n">
-        <v>13.83255552489191</v>
+        <v>13.83255453090192</v>
       </c>
       <c r="D970" t="n">
-        <v>12.96197456535314</v>
+        <v>12.961973633922</v>
       </c>
       <c r="E970" t="n">
-        <v>12.96197456535314</v>
+        <v>12.961973633922</v>
       </c>
       <c r="F970" t="n">
         <v>2737250</v>
@@ -19852,16 +19852,16 @@
         <v>45518</v>
       </c>
       <c r="B972" t="n">
-        <v>12.65243434906006</v>
+        <v>12.65243530273438</v>
       </c>
       <c r="C972" t="n">
-        <v>13.07805192575634</v>
+        <v>13.07805291151149</v>
       </c>
       <c r="D972" t="n">
-        <v>12.47831798382066</v>
+        <v>12.47831892437099</v>
       </c>
       <c r="E972" t="n">
-        <v>13.02001282984317</v>
+        <v>13.02001381122363</v>
       </c>
       <c r="F972" t="n">
         <v>1762700</v>
@@ -19952,16 +19952,16 @@
         <v>45525</v>
       </c>
       <c r="B977" t="n">
-        <v>13.23282146453857</v>
+        <v>13.23282241821289</v>
       </c>
       <c r="C977" t="n">
-        <v>13.81320780443054</v>
+        <v>13.81320879993264</v>
       </c>
       <c r="D977" t="n">
-        <v>13.11674419656018</v>
+        <v>13.11674514186894</v>
       </c>
       <c r="E977" t="n">
-        <v>13.61974569113322</v>
+        <v>13.61974667269272</v>
       </c>
       <c r="F977" t="n">
         <v>1538350</v>
@@ -19972,16 +19972,16 @@
         <v>45526</v>
       </c>
       <c r="B978" t="n">
-        <v>12.53635692596436</v>
+        <v>12.53635787963867</v>
       </c>
       <c r="C978" t="n">
-        <v>13.34889872378151</v>
+        <v>13.34889973926806</v>
       </c>
       <c r="D978" t="n">
-        <v>12.53635692596436</v>
+        <v>12.53635787963867</v>
       </c>
       <c r="E978" t="n">
-        <v>13.23282145587907</v>
+        <v>13.23282246253532</v>
       </c>
       <c r="F978" t="n">
         <v>1658500</v>
@@ -20072,16 +20072,16 @@
         <v>45533</v>
       </c>
       <c r="B983" t="n">
-        <v>11.91727828979492</v>
+        <v>11.91727733612061</v>
       </c>
       <c r="C983" t="n">
-        <v>12.26551104663971</v>
+        <v>12.26551006509824</v>
       </c>
       <c r="D983" t="n">
-        <v>11.89793253802588</v>
+        <v>11.8979315858997</v>
       </c>
       <c r="E983" t="n">
-        <v>12.11074134248656</v>
+        <v>12.11074037333046</v>
       </c>
       <c r="F983" t="n">
         <v>2310450</v>
@@ -20272,16 +20272,16 @@
         <v>45547</v>
       </c>
       <c r="B993" t="n">
-        <v>11.12408256530762</v>
+        <v>11.1240816116333</v>
       </c>
       <c r="C993" t="n">
-        <v>11.58839165566821</v>
+        <v>11.58839066218839</v>
       </c>
       <c r="D993" t="n">
-        <v>11.12408256530762</v>
+        <v>11.1240816116333</v>
       </c>
       <c r="E993" t="n">
-        <v>11.51100680727478</v>
+        <v>11.51100582042921</v>
       </c>
       <c r="F993" t="n">
         <v>1254550</v>
@@ -20292,16 +20292,16 @@
         <v>45548</v>
       </c>
       <c r="B994" t="n">
-        <v>11.53035354614258</v>
+        <v>11.53035259246826</v>
       </c>
       <c r="C994" t="n">
-        <v>11.80120051705863</v>
+        <v>11.80119954098259</v>
       </c>
       <c r="D994" t="n">
-        <v>11.24015990176815</v>
+        <v>11.24015897209572</v>
       </c>
       <c r="E994" t="n">
-        <v>11.24015990176815</v>
+        <v>11.24015897209572</v>
       </c>
       <c r="F994" t="n">
         <v>1874650</v>
@@ -20432,16 +20432,16 @@
         <v>45559</v>
       </c>
       <c r="B1001" t="n">
-        <v>10.25350284576416</v>
+        <v>10.25350189208984</v>
       </c>
       <c r="C1001" t="n">
-        <v>10.52434982269939</v>
+        <v>10.5243488438337</v>
       </c>
       <c r="D1001" t="n">
-        <v>10.19546374659938</v>
+        <v>10.19546279832325</v>
       </c>
       <c r="E1001" t="n">
-        <v>10.35023344770522</v>
+        <v>10.35023248503403</v>
       </c>
       <c r="F1001" t="n">
         <v>1642200</v>
@@ -20532,16 +20532,16 @@
         <v>45566</v>
       </c>
       <c r="B1006" t="n">
-        <v>11.06604385375977</v>
+        <v>11.06604290008545</v>
       </c>
       <c r="C1006" t="n">
-        <v>11.43362235770024</v>
+        <v>11.43362137234792</v>
       </c>
       <c r="D1006" t="n">
-        <v>10.83388930048163</v>
+        <v>10.83388836681445</v>
       </c>
       <c r="E1006" t="n">
-        <v>10.93062082559762</v>
+        <v>10.93061988359409</v>
       </c>
       <c r="F1006" t="n">
         <v>4182200</v>
@@ -20652,16 +20652,16 @@
         <v>45574</v>
       </c>
       <c r="B1012" t="n">
-        <v>9.673115730285645</v>
+        <v>9.673114776611328</v>
       </c>
       <c r="C1012" t="n">
-        <v>9.963309386694254</v>
+        <v>9.963308404409689</v>
       </c>
       <c r="D1012" t="n">
-        <v>9.673115730285645</v>
+        <v>9.673114776611328</v>
       </c>
       <c r="E1012" t="n">
-        <v>9.905270286412451</v>
+        <v>9.905269309849972</v>
       </c>
       <c r="F1012" t="n">
         <v>2585700</v>
@@ -20672,16 +20672,16 @@
         <v>45575</v>
       </c>
       <c r="B1013" t="n">
-        <v>9.595730781555176</v>
+        <v>9.595729827880859</v>
       </c>
       <c r="C1013" t="n">
-        <v>9.827885335342753</v>
+        <v>9.827884358595695</v>
       </c>
       <c r="D1013" t="n">
-        <v>9.51834593029265</v>
+        <v>9.518344984309248</v>
       </c>
       <c r="E1013" t="n">
-        <v>9.69246230688343</v>
+        <v>9.692461343595424</v>
       </c>
       <c r="F1013" t="n">
         <v>2540250</v>
@@ -20772,16 +20772,16 @@
         <v>45582</v>
       </c>
       <c r="B1018" t="n">
-        <v>9.827885627746582</v>
+        <v>9.827884674072266</v>
       </c>
       <c r="C1018" t="n">
-        <v>9.905270481311499</v>
+        <v>9.905269520127943</v>
       </c>
       <c r="D1018" t="n">
-        <v>9.692462595258089</v>
+        <v>9.692461654724896</v>
       </c>
       <c r="E1018" t="n">
-        <v>9.86657805452904</v>
+        <v>9.866577097100103</v>
       </c>
       <c r="F1018" t="n">
         <v>1402900</v>
@@ -20892,16 +20892,16 @@
         <v>45590</v>
       </c>
       <c r="B1024" t="n">
-        <v>10.25350284576416</v>
+        <v>10.25350189208984</v>
       </c>
       <c r="C1024" t="n">
-        <v>10.71781194908169</v>
+        <v>10.71781095222216</v>
       </c>
       <c r="D1024" t="n">
-        <v>10.17611799521124</v>
+        <v>10.17611704873446</v>
       </c>
       <c r="E1024" t="n">
-        <v>10.56304224797585</v>
+        <v>10.56304126551139</v>
       </c>
       <c r="F1024" t="n">
         <v>1207500</v>
@@ -20912,16 +20912,16 @@
         <v>45593</v>
       </c>
       <c r="B1025" t="n">
-        <v>10.5243501663208</v>
+        <v>10.52434921264648</v>
       </c>
       <c r="C1025" t="n">
-        <v>10.73715897353966</v>
+        <v>10.73715800058147</v>
       </c>
       <c r="D1025" t="n">
-        <v>10.33088803362193</v>
+        <v>10.33088709747838</v>
       </c>
       <c r="E1025" t="n">
-        <v>10.35023378564171</v>
+        <v>10.35023284774512</v>
       </c>
       <c r="F1025" t="n">
         <v>1608400</v>
@@ -20992,16 +20992,16 @@
         <v>45597</v>
       </c>
       <c r="B1029" t="n">
-        <v>9.634422302246094</v>
+        <v>9.63442325592041</v>
       </c>
       <c r="C1029" t="n">
-        <v>10.4856565086795</v>
+        <v>10.4856575466142</v>
       </c>
       <c r="D1029" t="n">
-        <v>9.595729880249126</v>
+        <v>9.595730830093428</v>
       </c>
       <c r="E1029" t="n">
-        <v>10.40827166468556</v>
+        <v>10.40827269496024</v>
       </c>
       <c r="F1029" t="n">
         <v>1791350</v>
@@ -21012,16 +21012,16 @@
         <v>45600</v>
       </c>
       <c r="B1030" t="n">
-        <v>10.5243501663208</v>
+        <v>10.52434921264648</v>
       </c>
       <c r="C1030" t="n">
-        <v>10.56304259286057</v>
+        <v>10.56304163568011</v>
       </c>
       <c r="D1030" t="n">
-        <v>9.769847387545106</v>
+        <v>9.769846502240801</v>
       </c>
       <c r="E1030" t="n">
-        <v>9.827885566104658</v>
+        <v>9.827884675541167</v>
       </c>
       <c r="F1030" t="n">
         <v>1954700</v>
@@ -21052,16 +21052,16 @@
         <v>45602</v>
       </c>
       <c r="B1032" t="n">
-        <v>10.83388900756836</v>
+        <v>10.83388805389404</v>
       </c>
       <c r="C1032" t="n">
-        <v>11.06604355456978</v>
+        <v>11.06604258045961</v>
       </c>
       <c r="D1032" t="n">
-        <v>10.19546354206435</v>
+        <v>10.19546264458869</v>
       </c>
       <c r="E1032" t="n">
-        <v>10.33088748906527</v>
+        <v>10.33088657966865</v>
       </c>
       <c r="F1032" t="n">
         <v>2218850</v>
@@ -21072,16 +21072,16 @@
         <v>45603</v>
       </c>
       <c r="B1033" t="n">
-        <v>10.25350284576416</v>
+        <v>10.25350189208984</v>
       </c>
       <c r="C1033" t="n">
-        <v>11.02735135129338</v>
+        <v>11.02735032564371</v>
       </c>
       <c r="D1033" t="n">
-        <v>10.25350284576416</v>
+        <v>10.25350189208984</v>
       </c>
       <c r="E1033" t="n">
-        <v>10.87258165018753</v>
+        <v>10.87258063893294</v>
       </c>
       <c r="F1033" t="n">
         <v>1449250</v>
@@ -21312,16 +21312,16 @@
         <v>45623</v>
       </c>
       <c r="B1045" t="n">
-        <v>9.943963050842285</v>
+        <v>9.943962097167969</v>
       </c>
       <c r="C1045" t="n">
-        <v>10.85323647703325</v>
+        <v>10.8532354361552</v>
       </c>
       <c r="D1045" t="n">
-        <v>9.943963050842285</v>
+        <v>9.943962097167969</v>
       </c>
       <c r="E1045" t="n">
-        <v>10.71781252010049</v>
+        <v>10.71781149221026</v>
       </c>
       <c r="F1045" t="n">
         <v>1813650</v>
@@ -21352,16 +21352,16 @@
         <v>45625</v>
       </c>
       <c r="B1047" t="n">
-        <v>8.937957763671875</v>
+        <v>8.937958717346191</v>
       </c>
       <c r="C1047" t="n">
-        <v>9.092727451311198</v>
+        <v>9.09272842149934</v>
       </c>
       <c r="D1047" t="n">
-        <v>8.415609606639105</v>
+        <v>8.415610504579211</v>
       </c>
       <c r="E1047" t="n">
-        <v>9.073381701606335</v>
+        <v>9.073382669730298</v>
       </c>
       <c r="F1047" t="n">
         <v>4685450</v>
@@ -21432,16 +21432,16 @@
         <v>45631</v>
       </c>
       <c r="B1051" t="n">
-        <v>8.125415802001953</v>
+        <v>8.12541675567627</v>
       </c>
       <c r="C1051" t="n">
-        <v>8.667110619302122</v>
+        <v>8.667111636554777</v>
       </c>
       <c r="D1051" t="n">
-        <v>8.125415802001953</v>
+        <v>8.12541675567627</v>
       </c>
       <c r="E1051" t="n">
-        <v>8.415609421180612</v>
+        <v>8.41561040891475</v>
       </c>
       <c r="F1051" t="n">
         <v>2576750</v>
@@ -21452,16 +21452,16 @@
         <v>45632</v>
       </c>
       <c r="B1052" t="n">
-        <v>7.77718448638916</v>
+        <v>7.777184963226318</v>
       </c>
       <c r="C1052" t="n">
-        <v>8.280186913282558</v>
+        <v>8.280187420959956</v>
       </c>
       <c r="D1052" t="n">
-        <v>7.77718448638916</v>
+        <v>7.777184963226318</v>
       </c>
       <c r="E1052" t="n">
-        <v>8.183455393495322</v>
+        <v>8.183455895241888</v>
       </c>
       <c r="F1052" t="n">
         <v>2378500</v>
@@ -21492,16 +21492,16 @@
         <v>45636</v>
       </c>
       <c r="B1054" t="n">
-        <v>8.125415802001953</v>
+        <v>8.12541675567627</v>
       </c>
       <c r="C1054" t="n">
-        <v>8.183454894837718</v>
+        <v>8.183455855324043</v>
       </c>
       <c r="D1054" t="n">
-        <v>7.622414328259016</v>
+        <v>7.622415222896405</v>
       </c>
       <c r="E1054" t="n">
-        <v>7.641760538787591</v>
+        <v>7.641761435695631</v>
       </c>
       <c r="F1054" t="n">
         <v>2421800</v>
@@ -21532,16 +21532,16 @@
         <v>45638</v>
       </c>
       <c r="B1056" t="n">
-        <v>7.815877437591553</v>
+        <v>7.815876960754395</v>
       </c>
       <c r="C1056" t="n">
-        <v>8.260840798159894</v>
+        <v>8.260840294176061</v>
       </c>
       <c r="D1056" t="n">
-        <v>7.757839259800146</v>
+        <v>7.757838786503825</v>
       </c>
       <c r="E1056" t="n">
-        <v>8.144763520076873</v>
+        <v>8.144763023174777</v>
       </c>
       <c r="F1056" t="n">
         <v>2302150</v>
@@ -21632,16 +21632,16 @@
         <v>45645</v>
       </c>
       <c r="B1061" t="n">
-        <v>6.364910125732422</v>
+        <v>6.364909648895264</v>
       </c>
       <c r="C1061" t="n">
-        <v>6.480987404689523</v>
+        <v>6.480986919156255</v>
       </c>
       <c r="D1061" t="n">
-        <v>6.24883284677532</v>
+        <v>6.248832378634273</v>
       </c>
       <c r="E1061" t="n">
-        <v>6.461641191530006</v>
+        <v>6.46164070744609</v>
       </c>
       <c r="F1061" t="n">
         <v>3682600</v>
@@ -21652,16 +21652,16 @@
         <v>45646</v>
       </c>
       <c r="B1062" t="n">
-        <v>6.983989238739014</v>
+        <v>6.983988761901855</v>
       </c>
       <c r="C1062" t="n">
-        <v>7.351567741106881</v>
+        <v>7.351567239173022</v>
       </c>
       <c r="D1062" t="n">
-        <v>6.384256184086237</v>
+        <v>6.384255748196307</v>
       </c>
       <c r="E1062" t="n">
-        <v>6.403602396776646</v>
+        <v>6.403601959565839</v>
       </c>
       <c r="F1062" t="n">
         <v>7093050</v>
@@ -21752,16 +21752,16 @@
         <v>45659</v>
       </c>
       <c r="B1067" t="n">
-        <v>6.597064971923828</v>
+        <v>6.59706449508667</v>
       </c>
       <c r="C1067" t="n">
-        <v>6.887258161707811</v>
+        <v>6.887257663895431</v>
       </c>
       <c r="D1067" t="n">
-        <v>6.442294809455611</v>
+        <v>6.442294343805271</v>
       </c>
       <c r="E1067" t="n">
-        <v>6.790527098446483</v>
+        <v>6.790526607625844</v>
       </c>
       <c r="F1067" t="n">
         <v>1597700</v>
@@ -21772,16 +21772,16 @@
         <v>45660</v>
       </c>
       <c r="B1068" t="n">
-        <v>6.597064971923828</v>
+        <v>6.59706449508667</v>
       </c>
       <c r="C1068" t="n">
-        <v>6.771180885794218</v>
+        <v>6.771180396371927</v>
       </c>
       <c r="D1068" t="n">
-        <v>6.480987234760143</v>
+        <v>6.480986766313106</v>
       </c>
       <c r="E1068" t="n">
-        <v>6.539026333967032</v>
+        <v>6.539025861324918</v>
       </c>
       <c r="F1068" t="n">
         <v>1097250</v>
@@ -21792,16 +21792,16 @@
         <v>45663</v>
       </c>
       <c r="B1069" t="n">
-        <v>6.867911815643311</v>
+        <v>6.867911338806152</v>
       </c>
       <c r="C1069" t="n">
-        <v>6.92595045247268</v>
+        <v>6.925949971605917</v>
       </c>
       <c r="D1069" t="n">
-        <v>6.655103480602286</v>
+        <v>6.65510301854035</v>
       </c>
       <c r="E1069" t="n">
-        <v>6.6937959051552</v>
+        <v>6.69379544040686</v>
       </c>
       <c r="F1069" t="n">
         <v>1681500</v>
@@ -21812,16 +21812,16 @@
         <v>45664</v>
       </c>
       <c r="B1070" t="n">
-        <v>6.867911815643311</v>
+        <v>6.867911338806152</v>
       </c>
       <c r="C1070" t="n">
-        <v>7.100066824210875</v>
+        <v>7.100066331255261</v>
       </c>
       <c r="D1070" t="n">
-        <v>6.867911815643311</v>
+        <v>6.867911338806152</v>
       </c>
       <c r="E1070" t="n">
-        <v>6.945296664749137</v>
+        <v>6.945296182539171</v>
       </c>
       <c r="F1070" t="n">
         <v>1019600</v>
@@ -21852,16 +21852,16 @@
         <v>45666</v>
       </c>
       <c r="B1072" t="n">
-        <v>6.65510368347168</v>
+        <v>6.655103206634521</v>
       </c>
       <c r="C1072" t="n">
-        <v>6.829219599267415</v>
+        <v>6.829219109954878</v>
       </c>
       <c r="D1072" t="n">
-        <v>6.577718832006909</v>
+        <v>6.577718360714363</v>
       </c>
       <c r="E1072" t="n">
-        <v>6.674449896337872</v>
+        <v>6.674449418114562</v>
       </c>
       <c r="F1072" t="n">
         <v>1017500</v>
@@ -21892,16 +21892,16 @@
         <v>45670</v>
       </c>
       <c r="B1074" t="n">
-        <v>6.30687141418457</v>
+        <v>6.306870937347412</v>
       </c>
       <c r="C1074" t="n">
-        <v>6.539026430696018</v>
+        <v>6.539025936306553</v>
       </c>
       <c r="D1074" t="n">
-        <v>6.248832775369234</v>
+        <v>6.248832302920142</v>
       </c>
       <c r="E1074" t="n">
-        <v>6.480987330630581</v>
+        <v>6.480986840629219</v>
       </c>
       <c r="F1074" t="n">
         <v>1925650</v>
@@ -21932,16 +21932,16 @@
         <v>45672</v>
       </c>
       <c r="B1076" t="n">
-        <v>6.713142395019531</v>
+        <v>6.713141918182373</v>
       </c>
       <c r="C1076" t="n">
-        <v>6.829219673478057</v>
+        <v>6.829219188395884</v>
       </c>
       <c r="D1076" t="n">
-        <v>6.461641163775955</v>
+        <v>6.461640704803028</v>
       </c>
       <c r="E1076" t="n">
-        <v>6.519679803005218</v>
+        <v>6.519679339909785</v>
       </c>
       <c r="F1076" t="n">
         <v>3254350</v>
@@ -22032,16 +22032,16 @@
         <v>45679</v>
       </c>
       <c r="B1081" t="n">
-        <v>6.558372020721436</v>
+        <v>6.558372497558594</v>
       </c>
       <c r="C1081" t="n">
-        <v>6.597064442923328</v>
+        <v>6.597064922573682</v>
       </c>
       <c r="D1081" t="n">
-        <v>6.326217026260029</v>
+        <v>6.326217486217979</v>
       </c>
       <c r="E1081" t="n">
-        <v>6.577718231822382</v>
+        <v>6.577718710066138</v>
       </c>
       <c r="F1081" t="n">
         <v>3642400</v>
@@ -22072,16 +22072,16 @@
         <v>45681</v>
       </c>
       <c r="B1083" t="n">
-        <v>6.287525177001953</v>
+        <v>6.287524700164795</v>
       </c>
       <c r="C1083" t="n">
-        <v>6.539026405482078</v>
+        <v>6.539025909571417</v>
       </c>
       <c r="D1083" t="n">
-        <v>6.248832751274256</v>
+        <v>6.248832277371478</v>
       </c>
       <c r="E1083" t="n">
-        <v>6.461641092776587</v>
+        <v>6.46164060273472</v>
       </c>
       <c r="F1083" t="n">
         <v>3630450</v>
@@ -22092,16 +22092,16 @@
         <v>45684</v>
       </c>
       <c r="B1084" t="n">
-        <v>6.597064971923828</v>
+        <v>6.59706449508667</v>
       </c>
       <c r="C1084" t="n">
-        <v>6.732488460489686</v>
+        <v>6.732487973864091</v>
       </c>
       <c r="D1084" t="n">
-        <v>6.210140257628426</v>
+        <v>6.210139808758262</v>
       </c>
       <c r="E1084" t="n">
-        <v>6.287525108237488</v>
+        <v>6.287524653773932</v>
       </c>
       <c r="F1084" t="n">
         <v>4752900</v>
@@ -22172,16 +22172,16 @@
         <v>45688</v>
       </c>
       <c r="B1088" t="n">
-        <v>6.983989238739014</v>
+        <v>6.983988761901855</v>
       </c>
       <c r="C1088" t="n">
-        <v>7.332221528416472</v>
+        <v>7.332221027803491</v>
       </c>
       <c r="D1088" t="n">
-        <v>6.887258175286968</v>
+        <v>6.887257705054196</v>
       </c>
       <c r="E1088" t="n">
-        <v>7.042028338060335</v>
+        <v>7.042027857260513</v>
       </c>
       <c r="F1088" t="n">
         <v>3089150</v>
@@ -22232,16 +22232,16 @@
         <v>45693</v>
       </c>
       <c r="B1091" t="n">
-        <v>6.577718734741211</v>
+        <v>6.577718257904053</v>
       </c>
       <c r="C1091" t="n">
-        <v>6.771180860542385</v>
+        <v>6.771180369680619</v>
       </c>
       <c r="D1091" t="n">
-        <v>6.539026309580976</v>
+        <v>6.539025835548739</v>
       </c>
       <c r="E1091" t="n">
-        <v>6.771180860542385</v>
+        <v>6.771180369680619</v>
       </c>
       <c r="F1091" t="n">
         <v>2646500</v>
@@ -22272,16 +22272,16 @@
         <v>45695</v>
       </c>
       <c r="B1093" t="n">
-        <v>6.30687141418457</v>
+        <v>6.306870937347412</v>
       </c>
       <c r="C1093" t="n">
-        <v>6.577718856572909</v>
+        <v>6.577718359258066</v>
       </c>
       <c r="D1093" t="n">
-        <v>6.248832775369234</v>
+        <v>6.248832302920142</v>
       </c>
       <c r="E1093" t="n">
-        <v>6.500333543569027</v>
+        <v>6.500333052104975</v>
       </c>
       <c r="F1093" t="n">
         <v>3225150</v>
@@ -22372,16 +22372,16 @@
         <v>45702</v>
       </c>
       <c r="B1098" t="n">
-        <v>7.661107063293457</v>
+        <v>7.661107540130615</v>
       </c>
       <c r="C1098" t="n">
-        <v>7.815876753865021</v>
+        <v>7.815877240335245</v>
       </c>
       <c r="D1098" t="n">
-        <v>6.906603899256954</v>
+        <v>6.906604329132865</v>
       </c>
       <c r="E1098" t="n">
-        <v>6.906603899256954</v>
+        <v>6.906604329132865</v>
       </c>
       <c r="F1098" t="n">
         <v>4465400</v>
@@ -22432,16 +22432,16 @@
         <v>45707</v>
       </c>
       <c r="B1101" t="n">
-        <v>7.661107063293457</v>
+        <v>7.661107540130615</v>
       </c>
       <c r="C1101" t="n">
-        <v>7.989993117008094</v>
+        <v>7.989993614315543</v>
       </c>
       <c r="D1101" t="n">
-        <v>7.641760851972011</v>
+        <v>7.641761327605037</v>
       </c>
       <c r="E1101" t="n">
-        <v>7.931954021793696</v>
+        <v>7.931954515488718</v>
       </c>
       <c r="F1101" t="n">
         <v>2081600</v>
@@ -22472,16 +22472,16 @@
         <v>45709</v>
       </c>
       <c r="B1103" t="n">
-        <v>6.964642524719238</v>
+        <v>6.964643001556396</v>
       </c>
       <c r="C1103" t="n">
-        <v>7.235489944138903</v>
+        <v>7.235490439519743</v>
       </c>
       <c r="D1103" t="n">
-        <v>6.848565256932265</v>
+        <v>6.848565725822144</v>
       </c>
       <c r="E1103" t="n">
-        <v>7.216143732841074</v>
+        <v>7.216144226897367</v>
       </c>
       <c r="F1103" t="n">
         <v>5203300</v>
@@ -22492,16 +22492,16 @@
         <v>45712</v>
       </c>
       <c r="B1104" t="n">
-        <v>6.65510368347168</v>
+        <v>6.655103206634521</v>
       </c>
       <c r="C1104" t="n">
-        <v>7.061374614911826</v>
+        <v>7.061374108965418</v>
       </c>
       <c r="D1104" t="n">
-        <v>6.635757470605487</v>
+        <v>6.635756995154482</v>
       </c>
       <c r="E1104" t="n">
-        <v>6.964643089330764</v>
+        <v>6.964642590315155</v>
       </c>
       <c r="F1104" t="n">
         <v>3038000</v>
@@ -22512,16 +22512,16 @@
         <v>45713</v>
       </c>
       <c r="B1105" t="n">
-        <v>6.577718734741211</v>
+        <v>6.577718257904053</v>
       </c>
       <c r="C1105" t="n">
-        <v>6.80987328570262</v>
+        <v>6.809872792035932</v>
       </c>
       <c r="D1105" t="n">
-        <v>6.539026309580976</v>
+        <v>6.539025835548739</v>
       </c>
       <c r="E1105" t="n">
-        <v>6.616411159901446</v>
+        <v>6.616410680259366</v>
       </c>
       <c r="F1105" t="n">
         <v>1959150</v>
@@ -22552,16 +22552,16 @@
         <v>45715</v>
       </c>
       <c r="B1107" t="n">
-        <v>6.268178462982178</v>
+        <v>6.268178939819336</v>
       </c>
       <c r="C1107" t="n">
-        <v>6.480986787469972</v>
+        <v>6.480987280496031</v>
       </c>
       <c r="D1107" t="n">
-        <v>6.171447406396816</v>
+        <v>6.171447875875384</v>
       </c>
       <c r="E1107" t="n">
-        <v>6.345563308250466</v>
+        <v>6.345563790974498</v>
       </c>
       <c r="F1107" t="n">
         <v>2313250</v>
@@ -22592,16 +22592,16 @@
         <v>45721</v>
       </c>
       <c r="B1109" t="n">
-        <v>5.861907482147217</v>
+        <v>5.861907958984375</v>
       </c>
       <c r="C1109" t="n">
-        <v>6.055370053864155</v>
+        <v>6.055370546438536</v>
       </c>
       <c r="D1109" t="n">
-        <v>5.784522637960463</v>
+        <v>5.784523108502748</v>
       </c>
       <c r="E1109" t="n">
-        <v>6.016677170520723</v>
+        <v>6.016677659947629</v>
       </c>
       <c r="F1109" t="n">
         <v>2753500</v>
@@ -22612,16 +22612,16 @@
         <v>45722</v>
       </c>
       <c r="B1110" t="n">
-        <v>5.900600433349609</v>
+        <v>5.900599956512451</v>
       </c>
       <c r="C1110" t="n">
-        <v>6.036023922819902</v>
+        <v>6.03602343503895</v>
       </c>
       <c r="D1110" t="n">
-        <v>5.784523156660787</v>
+        <v>5.784522689204024</v>
       </c>
       <c r="E1110" t="n">
-        <v>5.881254220568139</v>
+        <v>5.88125374529438</v>
       </c>
       <c r="F1110" t="n">
         <v>2642900</v>
@@ -22652,16 +22652,16 @@
         <v>45726</v>
       </c>
       <c r="B1112" t="n">
-        <v>6.364910125732422</v>
+        <v>6.364909648895264</v>
       </c>
       <c r="C1112" t="n">
-        <v>6.597065144896729</v>
+        <v>6.597064650667317</v>
       </c>
       <c r="D1112" t="n">
-        <v>6.210140420456287</v>
+        <v>6.210139955213942</v>
       </c>
       <c r="E1112" t="n">
-        <v>6.24883284677532</v>
+        <v>6.248832378634273</v>
       </c>
       <c r="F1112" t="n">
         <v>2113300</v>
@@ -22672,16 +22672,16 @@
         <v>45727</v>
       </c>
       <c r="B1113" t="n">
-        <v>6.519679546356201</v>
+        <v>6.519679069519043</v>
       </c>
       <c r="C1113" t="n">
-        <v>6.577718644550842</v>
+        <v>6.577718163468813</v>
       </c>
       <c r="D1113" t="n">
-        <v>6.30687121089283</v>
+        <v>6.306870749620075</v>
       </c>
       <c r="E1113" t="n">
-        <v>6.364909847837386</v>
+        <v>6.364909382319794</v>
       </c>
       <c r="F1113" t="n">
         <v>2132300</v>
@@ -22732,16 +22732,16 @@
         <v>45730</v>
       </c>
       <c r="B1116" t="n">
-        <v>7.061374664306641</v>
+        <v>7.061374187469482</v>
       </c>
       <c r="C1116" t="n">
-        <v>7.254836794321849</v>
+        <v>7.254836304420672</v>
       </c>
       <c r="D1116" t="n">
-        <v>6.46164113875929</v>
+        <v>6.461640702420653</v>
       </c>
       <c r="E1116" t="n">
-        <v>6.46164113875929</v>
+        <v>6.461640702420653</v>
       </c>
       <c r="F1116" t="n">
         <v>2901850</v>
@@ -22792,16 +22792,16 @@
         <v>45735</v>
       </c>
       <c r="B1119" t="n">
-        <v>7.97064733505249</v>
+        <v>7.970646858215332</v>
       </c>
       <c r="C1119" t="n">
-        <v>8.067378863718266</v>
+        <v>8.067378381094228</v>
       </c>
       <c r="D1119" t="n">
-        <v>7.506338211457305</v>
+        <v>7.506337762397043</v>
       </c>
       <c r="E1119" t="n">
-        <v>7.854570054153694</v>
+        <v>7.854569584260759</v>
       </c>
       <c r="F1119" t="n">
         <v>2592600</v>
@@ -22812,16 +22812,16 @@
         <v>45736</v>
       </c>
       <c r="B1120" t="n">
-        <v>7.989993095397949</v>
+        <v>7.989993572235107</v>
       </c>
       <c r="C1120" t="n">
-        <v>8.086723690493493</v>
+        <v>8.086724173103466</v>
       </c>
       <c r="D1120" t="n">
-        <v>7.757838560168499</v>
+        <v>7.757839023150837</v>
       </c>
       <c r="E1120" t="n">
-        <v>7.893261577802284</v>
+        <v>7.893262048866574</v>
       </c>
       <c r="F1120" t="n">
         <v>2707250</v>
@@ -22872,16 +22872,16 @@
         <v>45741</v>
       </c>
       <c r="B1123" t="n">
-        <v>8.570379257202148</v>
+        <v>8.570380210876465</v>
       </c>
       <c r="C1123" t="n">
-        <v>8.995996818869131</v>
+        <v>8.995997819904309</v>
       </c>
       <c r="D1123" t="n">
-        <v>8.028685352807935</v>
+        <v>8.028686246204925</v>
       </c>
       <c r="E1123" t="n">
-        <v>8.028685352807935</v>
+        <v>8.028686246204925</v>
       </c>
       <c r="F1123" t="n">
         <v>4835050</v>
@@ -22892,16 +22892,16 @@
         <v>45742</v>
       </c>
       <c r="B1124" t="n">
-        <v>8.937957763671875</v>
+        <v>8.937958717346191</v>
       </c>
       <c r="C1124" t="n">
-        <v>9.073381701606335</v>
+        <v>9.073382669730298</v>
       </c>
       <c r="D1124" t="n">
-        <v>8.744495654122721</v>
+        <v>8.744496587154755</v>
       </c>
       <c r="E1124" t="n">
-        <v>8.783188076032552</v>
+        <v>8.783189013193041</v>
       </c>
       <c r="F1124" t="n">
         <v>4448600</v>
@@ -22932,16 +22932,16 @@
         <v>45744</v>
       </c>
       <c r="B1126" t="n">
-        <v>8.454301834106445</v>
+        <v>8.454302787780762</v>
       </c>
       <c r="C1126" t="n">
-        <v>9.073381492925485</v>
+        <v>9.073382516434116</v>
       </c>
       <c r="D1126" t="n">
-        <v>8.454301834106445</v>
+        <v>8.454302787780762</v>
       </c>
       <c r="E1126" t="n">
-        <v>9.03468907190555</v>
+        <v>9.034690091049542</v>
       </c>
       <c r="F1126" t="n">
         <v>4483900</v>
@@ -22972,16 +22972,16 @@
         <v>45748</v>
       </c>
       <c r="B1128" t="n">
-        <v>8.202801704406738</v>
+        <v>8.202800750732422</v>
       </c>
       <c r="C1128" t="n">
-        <v>8.4929953610957</v>
+        <v>8.492994373682881</v>
       </c>
       <c r="D1128" t="n">
-        <v>7.757839265983922</v>
+        <v>7.757838364041838</v>
       </c>
       <c r="E1128" t="n">
-        <v>7.931954721997136</v>
+        <v>7.931953799812037</v>
       </c>
       <c r="F1128" t="n">
         <v>2823650</v>
@@ -23012,16 +23012,16 @@
         <v>45750</v>
       </c>
       <c r="B1130" t="n">
-        <v>9.266843795776367</v>
+        <v>9.266844749450684</v>
       </c>
       <c r="C1130" t="n">
-        <v>9.402267733486079</v>
+        <v>9.402268701097217</v>
       </c>
       <c r="D1130" t="n">
-        <v>8.531686858209531</v>
+        <v>8.53168773622699</v>
       </c>
       <c r="E1130" t="n">
-        <v>8.551033530382393</v>
+        <v>8.551034410390866</v>
       </c>
       <c r="F1130" t="n">
         <v>5445750</v>
@@ -23032,16 +23032,16 @@
         <v>45751</v>
       </c>
       <c r="B1131" t="n">
-        <v>8.454301834106445</v>
+        <v>8.454302787780762</v>
       </c>
       <c r="C1131" t="n">
-        <v>8.937957558105671</v>
+        <v>8.937958566338017</v>
       </c>
       <c r="D1131" t="n">
-        <v>8.376916992066576</v>
+        <v>8.376917937011616</v>
       </c>
       <c r="E1131" t="n">
-        <v>8.879919387825812</v>
+        <v>8.87992038951125</v>
       </c>
       <c r="F1131" t="n">
         <v>3071650</v>
@@ -23072,16 +23072,16 @@
         <v>45755</v>
       </c>
       <c r="B1133" t="n">
-        <v>7.815877437591553</v>
+        <v>7.815876960754395</v>
       </c>
       <c r="C1133" t="n">
-        <v>8.299533224187567</v>
+        <v>8.299532717843157</v>
       </c>
       <c r="D1133" t="n">
-        <v>7.564376668411679</v>
+        <v>7.564376206918276</v>
       </c>
       <c r="E1133" t="n">
-        <v>8.299533224187567</v>
+        <v>8.299532717843157</v>
       </c>
       <c r="F1133" t="n">
         <v>3625800</v>
@@ -23192,16 +23192,16 @@
         <v>45763</v>
       </c>
       <c r="B1139" t="n">
-        <v>9.092727661132812</v>
+        <v>9.092728614807129</v>
       </c>
       <c r="C1139" t="n">
-        <v>9.479652811659818</v>
+        <v>9.479653805916081</v>
       </c>
       <c r="D1139" t="n">
-        <v>9.034689488178843</v>
+        <v>9.034690435765931</v>
       </c>
       <c r="E1139" t="n">
-        <v>9.208805852041003</v>
+        <v>9.20880681788997</v>
       </c>
       <c r="F1139" t="n">
         <v>1920850</v>
@@ -23212,16 +23212,16 @@
         <v>45764</v>
       </c>
       <c r="B1140" t="n">
-        <v>9.634422302246094</v>
+        <v>9.63442325592041</v>
       </c>
       <c r="C1140" t="n">
-        <v>9.634422302246094</v>
+        <v>9.63442325592041</v>
       </c>
       <c r="D1140" t="n">
-        <v>8.918612034052133</v>
+        <v>8.918612916871151</v>
       </c>
       <c r="E1140" t="n">
-        <v>9.208805660279445</v>
+        <v>9.208806571823612</v>
       </c>
       <c r="F1140" t="n">
         <v>2900350</v>
@@ -23272,16 +23272,16 @@
         <v>45771</v>
       </c>
       <c r="B1143" t="n">
-        <v>10.6404275894165</v>
+        <v>10.64042663574219</v>
       </c>
       <c r="C1143" t="n">
-        <v>10.93062125362791</v>
+        <v>10.93062027394428</v>
       </c>
       <c r="D1143" t="n">
-        <v>10.23415664402058</v>
+        <v>10.23415572675929</v>
       </c>
       <c r="E1143" t="n">
-        <v>10.3502339252051</v>
+        <v>10.3502329975401</v>
       </c>
       <c r="F1143" t="n">
         <v>3582850</v>
@@ -23332,16 +23332,16 @@
         <v>45776</v>
       </c>
       <c r="B1146" t="n">
-        <v>10.6404275894165</v>
+        <v>10.64042663574219</v>
       </c>
       <c r="C1146" t="n">
-        <v>10.71781244353951</v>
+        <v>10.71781148292939</v>
       </c>
       <c r="D1146" t="n">
-        <v>10.31154149814359</v>
+        <v>10.3115405739465</v>
       </c>
       <c r="E1146" t="n">
-        <v>10.50500363345112</v>
+        <v>10.50500269191451</v>
       </c>
       <c r="F1146" t="n">
         <v>2176450</v>
@@ -23352,16 +23352,16 @@
         <v>45777</v>
       </c>
       <c r="B1147" t="n">
-        <v>10.36958026885986</v>
+        <v>10.36957931518555</v>
       </c>
       <c r="C1147" t="n">
-        <v>11.00800575623833</v>
+        <v>11.008004743849</v>
       </c>
       <c r="D1147" t="n">
-        <v>10.2341563172189</v>
+        <v>10.23415537599931</v>
       </c>
       <c r="E1147" t="n">
-        <v>10.62108057547851</v>
+        <v>10.6210795986741</v>
       </c>
       <c r="F1147" t="n">
         <v>2383850</v>
@@ -29552,19 +29552,39 @@
         <v>46230</v>
       </c>
       <c r="B1457" t="n">
-        <v>7.64</v>
+        <v>7.639999866485596</v>
       </c>
       <c r="C1457" t="n">
-        <v>7.7</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="D1457" t="n">
-        <v>7.52</v>
+        <v>7.519999980926514</v>
       </c>
       <c r="E1457" t="n">
-        <v>7.52</v>
+        <v>7.519999980926514</v>
       </c>
       <c r="F1457" t="n">
         <v>1730100</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>449000</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -452,16 +452,16 @@
         <v>44092</v>
       </c>
       <c r="B2" t="n">
-        <v>13.02992820739746</v>
+        <v>13.02992725372314</v>
       </c>
       <c r="C2" t="n">
-        <v>13.73904012484181</v>
+        <v>13.73903911926684</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63548506786634</v>
+        <v>12.63548414306174</v>
       </c>
       <c r="E2" t="n">
-        <v>13.38448458878317</v>
+        <v>13.3844836091585</v>
       </c>
       <c r="F2" t="n">
         <v>539400</v>
@@ -512,16 +512,16 @@
         <v>44097</v>
       </c>
       <c r="B5" t="n">
-        <v>12.65321159362793</v>
+        <v>12.65321254730225</v>
       </c>
       <c r="C5" t="n">
-        <v>12.99447180307224</v>
+        <v>12.99447278246738</v>
       </c>
       <c r="D5" t="n">
-        <v>12.24990438076721</v>
+        <v>12.24990530404421</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41388683378818</v>
+        <v>12.41388776942456</v>
       </c>
       <c r="F5" t="n">
         <v>1967400</v>
@@ -532,16 +532,16 @@
         <v>44098</v>
       </c>
       <c r="B6" t="n">
-        <v>12.45377540588379</v>
+        <v>12.45377349853516</v>
       </c>
       <c r="C6" t="n">
-        <v>12.84378650043098</v>
+        <v>12.84378453335049</v>
       </c>
       <c r="D6" t="n">
-        <v>12.40945575198984</v>
+        <v>12.40945385142895</v>
       </c>
       <c r="E6" t="n">
-        <v>12.65321258041594</v>
+        <v>12.65321064252266</v>
       </c>
       <c r="F6" t="n">
         <v>571400</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513614654541</v>
+        <v>12.36513519287109</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366305880876</v>
+        <v>12.49366209522167</v>
       </c>
       <c r="D7" t="n">
-        <v>12.3208164924778</v>
+        <v>12.32081554222169</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377545468063</v>
+        <v>12.45377449416991</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -592,16 +592,16 @@
         <v>44103</v>
       </c>
       <c r="B9" t="n">
-        <v>11.29703712463379</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C9" t="n">
-        <v>11.83330335641843</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="D9" t="n">
-        <v>11.07987173996964</v>
+        <v>11.07987080462801</v>
       </c>
       <c r="E9" t="n">
-        <v>11.83330335641843</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="F9" t="n">
         <v>897600</v>
@@ -612,16 +612,16 @@
         <v>44104</v>
       </c>
       <c r="B10" t="n">
-        <v>11.26158142089844</v>
+        <v>11.26158046722412</v>
       </c>
       <c r="C10" t="n">
-        <v>11.49647500301699</v>
+        <v>11.49647402945097</v>
       </c>
       <c r="D10" t="n">
-        <v>11.1951023603976</v>
+        <v>11.19510141235299</v>
       </c>
       <c r="E10" t="n">
-        <v>11.28374082595634</v>
+        <v>11.28373987040548</v>
       </c>
       <c r="F10" t="n">
         <v>764200</v>
@@ -652,16 +652,16 @@
         <v>44106</v>
       </c>
       <c r="B12" t="n">
-        <v>11.29703712463379</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C12" t="n">
-        <v>11.554090115188</v>
+        <v>11.55408913981376</v>
       </c>
       <c r="D12" t="n">
-        <v>11.19953455763982</v>
+        <v>11.19953361219649</v>
       </c>
       <c r="E12" t="n">
-        <v>11.51420250929794</v>
+        <v>11.51420153729093</v>
       </c>
       <c r="F12" t="n">
         <v>878600</v>
@@ -752,16 +752,16 @@
         <v>44113</v>
       </c>
       <c r="B17" t="n">
-        <v>12.1036491394043</v>
+        <v>12.10365009307861</v>
       </c>
       <c r="C17" t="n">
-        <v>12.29422302902209</v>
+        <v>12.29422399771216</v>
       </c>
       <c r="D17" t="n">
-        <v>11.53192831587788</v>
+        <v>11.531929224505</v>
       </c>
       <c r="E17" t="n">
-        <v>11.53636036509305</v>
+        <v>11.53636127406939</v>
       </c>
       <c r="F17" t="n">
         <v>672400</v>
@@ -772,16 +772,16 @@
         <v>44117</v>
       </c>
       <c r="B18" t="n">
-        <v>12.18785762786865</v>
+        <v>12.18785858154297</v>
       </c>
       <c r="C18" t="n">
-        <v>12.44934264096545</v>
+        <v>12.44934361510042</v>
       </c>
       <c r="D18" t="n">
-        <v>12.18785762786865</v>
+        <v>12.18785858154297</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36956743760344</v>
+        <v>12.36956840549617</v>
       </c>
       <c r="F18" t="n">
         <v>440800</v>
@@ -832,16 +832,16 @@
         <v>44120</v>
       </c>
       <c r="B21" t="n">
-        <v>12.45377540588379</v>
+        <v>12.45377349853516</v>
       </c>
       <c r="C21" t="n">
-        <v>12.49366300985564</v>
+        <v>12.49366109639805</v>
       </c>
       <c r="D21" t="n">
-        <v>11.9795570534708</v>
+        <v>11.97955521875072</v>
       </c>
       <c r="E21" t="n">
-        <v>12.06376346600951</v>
+        <v>12.06376161839286</v>
       </c>
       <c r="F21" t="n">
         <v>585200</v>
@@ -852,16 +852,16 @@
         <v>44123</v>
       </c>
       <c r="B22" t="n">
-        <v>12.53798198699951</v>
+        <v>12.53798294067383</v>
       </c>
       <c r="C22" t="n">
-        <v>12.78617085195148</v>
+        <v>12.78617182450374</v>
       </c>
       <c r="D22" t="n">
-        <v>12.30752047545202</v>
+        <v>12.30752141159678</v>
       </c>
       <c r="E22" t="n">
-        <v>12.40945508217713</v>
+        <v>12.40945602607532</v>
       </c>
       <c r="F22" t="n">
         <v>521200</v>
@@ -872,16 +872,16 @@
         <v>44124</v>
       </c>
       <c r="B23" t="n">
-        <v>12.8526496887207</v>
+        <v>12.85265064239502</v>
       </c>
       <c r="C23" t="n">
-        <v>12.87037788715177</v>
+        <v>12.87037884214153</v>
       </c>
       <c r="D23" t="n">
-        <v>12.41388692147603</v>
+        <v>12.41388784259389</v>
       </c>
       <c r="E23" t="n">
-        <v>12.53798177451245</v>
+        <v>12.53798270483821</v>
       </c>
       <c r="F23" t="n">
         <v>729200</v>
@@ -892,16 +892,16 @@
         <v>44125</v>
       </c>
       <c r="B24" t="n">
-        <v>12.8526496887207</v>
+        <v>12.85265064239502</v>
       </c>
       <c r="C24" t="n">
-        <v>12.94572019450274</v>
+        <v>12.94572115508295</v>
       </c>
       <c r="D24" t="n">
-        <v>12.51138947686584</v>
+        <v>12.51139040521844</v>
       </c>
       <c r="E24" t="n">
-        <v>12.8526496887207</v>
+        <v>12.85265064239502</v>
       </c>
       <c r="F24" t="n">
         <v>501200</v>
@@ -912,16 +912,16 @@
         <v>44126</v>
       </c>
       <c r="B25" t="n">
-        <v>13.06981563568115</v>
+        <v>13.06981468200684</v>
       </c>
       <c r="C25" t="n">
-        <v>13.21163784820361</v>
+        <v>13.21163688418085</v>
       </c>
       <c r="D25" t="n">
-        <v>12.69753190514617</v>
+        <v>12.69753097863653</v>
       </c>
       <c r="E25" t="n">
-        <v>12.75071565750562</v>
+        <v>12.75071472711529</v>
       </c>
       <c r="F25" t="n">
         <v>963600</v>
@@ -932,16 +932,16 @@
         <v>44127</v>
       </c>
       <c r="B26" t="n">
-        <v>12.94128704071045</v>
+        <v>12.94128894805908</v>
       </c>
       <c r="C26" t="n">
-        <v>13.18061176618817</v>
+        <v>13.18061370880962</v>
       </c>
       <c r="D26" t="n">
-        <v>12.86151185044224</v>
+        <v>12.86151374603323</v>
       </c>
       <c r="E26" t="n">
-        <v>13.08754127442653</v>
+        <v>13.08754320333081</v>
       </c>
       <c r="F26" t="n">
         <v>543600</v>
@@ -952,16 +952,16 @@
         <v>44130</v>
       </c>
       <c r="B27" t="n">
-        <v>12.60002899169922</v>
+        <v>12.6000280380249</v>
       </c>
       <c r="C27" t="n">
-        <v>12.87480930941692</v>
+        <v>12.87480833494496</v>
       </c>
       <c r="D27" t="n">
-        <v>12.41831918133934</v>
+        <v>12.41831824141832</v>
       </c>
       <c r="E27" t="n">
-        <v>12.84821785664712</v>
+        <v>12.84821688418782</v>
       </c>
       <c r="F27" t="n">
         <v>307600</v>
@@ -972,16 +972,16 @@
         <v>44131</v>
       </c>
       <c r="B28" t="n">
-        <v>12.22774505615234</v>
+        <v>12.22774410247803</v>
       </c>
       <c r="C28" t="n">
-        <v>12.77730652723113</v>
+        <v>12.77730553069506</v>
       </c>
       <c r="D28" t="n">
-        <v>12.19228950464168</v>
+        <v>12.19228855373264</v>
       </c>
       <c r="E28" t="n">
-        <v>12.67537192230385</v>
+        <v>12.67537093371793</v>
       </c>
       <c r="F28" t="n">
         <v>652400</v>
@@ -1112,16 +1112,16 @@
         <v>44141</v>
       </c>
       <c r="B35" t="n">
-        <v>13.55732917785645</v>
+        <v>13.55733013153076</v>
       </c>
       <c r="C35" t="n">
-        <v>13.69471933097108</v>
+        <v>13.69472029430994</v>
       </c>
       <c r="D35" t="n">
-        <v>12.65764341771108</v>
+        <v>12.65764430809807</v>
       </c>
       <c r="E35" t="n">
-        <v>12.74185066750967</v>
+        <v>12.74185156382011</v>
       </c>
       <c r="F35" t="n">
         <v>948200</v>
@@ -1192,16 +1192,16 @@
         <v>44147</v>
       </c>
       <c r="B39" t="n">
-        <v>12.94128704071045</v>
+        <v>12.94128894805908</v>
       </c>
       <c r="C39" t="n">
-        <v>13.35345744821801</v>
+        <v>13.35345941631429</v>
       </c>
       <c r="D39" t="n">
-        <v>12.75071316292016</v>
+        <v>12.7507150421811</v>
       </c>
       <c r="E39" t="n">
-        <v>13.12299682062052</v>
+        <v>13.12299875475041</v>
       </c>
       <c r="F39" t="n">
         <v>656600</v>
@@ -1232,16 +1232,16 @@
         <v>44151</v>
       </c>
       <c r="B41" t="n">
-        <v>13.02106380462646</v>
+        <v>13.02106475830078</v>
       </c>
       <c r="C41" t="n">
-        <v>13.37118812799716</v>
+        <v>13.37118910731489</v>
       </c>
       <c r="D41" t="n">
-        <v>12.65321212752895</v>
+        <v>12.65321305426148</v>
       </c>
       <c r="E41" t="n">
-        <v>13.20720566805696</v>
+        <v>13.20720663536447</v>
       </c>
       <c r="F41" t="n">
         <v>631800</v>
@@ -1252,16 +1252,16 @@
         <v>44152</v>
       </c>
       <c r="B42" t="n">
-        <v>13.02106380462646</v>
+        <v>13.02106475830078</v>
       </c>
       <c r="C42" t="n">
-        <v>13.09197575551494</v>
+        <v>13.09197671438291</v>
       </c>
       <c r="D42" t="n">
-        <v>12.6975317798366</v>
+        <v>12.69753270981514</v>
       </c>
       <c r="E42" t="n">
-        <v>12.93242534533822</v>
+        <v>12.93242629252057</v>
       </c>
       <c r="F42" t="n">
         <v>784800</v>
@@ -1272,16 +1272,16 @@
         <v>44153</v>
       </c>
       <c r="B43" t="n">
-        <v>12.74185276031494</v>
+        <v>12.74185180664062</v>
       </c>
       <c r="C43" t="n">
-        <v>13.18947968916004</v>
+        <v>13.18947870198273</v>
       </c>
       <c r="D43" t="n">
-        <v>12.66207754691106</v>
+        <v>12.66207659920759</v>
       </c>
       <c r="E43" t="n">
-        <v>13.11413652598162</v>
+        <v>13.11413554444342</v>
       </c>
       <c r="F43" t="n">
         <v>532400</v>
@@ -1292,16 +1292,16 @@
         <v>44154</v>
       </c>
       <c r="B44" t="n">
-        <v>12.99447059631348</v>
+        <v>12.99447154998779</v>
       </c>
       <c r="C44" t="n">
-        <v>13.07424579062724</v>
+        <v>13.07424675015632</v>
       </c>
       <c r="D44" t="n">
-        <v>12.48036472776582</v>
+        <v>12.4803656437095</v>
       </c>
       <c r="E44" t="n">
-        <v>12.74184971120452</v>
+        <v>12.74185064633879</v>
       </c>
       <c r="F44" t="n">
         <v>711400</v>
@@ -1312,16 +1312,16 @@
         <v>44158</v>
       </c>
       <c r="B45" t="n">
-        <v>13.35345935821533</v>
+        <v>13.35346031188965</v>
       </c>
       <c r="C45" t="n">
-        <v>13.47312216073348</v>
+        <v>13.47312312295385</v>
       </c>
       <c r="D45" t="n">
-        <v>13.06981494809263</v>
+        <v>13.0698158815097</v>
       </c>
       <c r="E45" t="n">
-        <v>13.13629400104926</v>
+        <v>13.13629493921411</v>
       </c>
       <c r="F45" t="n">
         <v>731400</v>
@@ -1332,16 +1332,16 @@
         <v>44159</v>
       </c>
       <c r="B46" t="n">
-        <v>13.73903751373291</v>
+        <v>13.73904037475586</v>
       </c>
       <c r="C46" t="n">
-        <v>13.82767680356518</v>
+        <v>13.82767968304641</v>
       </c>
       <c r="D46" t="n">
-        <v>13.27368335543079</v>
+        <v>13.27368611954819</v>
       </c>
       <c r="E46" t="n">
-        <v>13.47312048956302</v>
+        <v>13.4731232952113</v>
       </c>
       <c r="F46" t="n">
         <v>798800</v>
@@ -1352,16 +1352,16 @@
         <v>44160</v>
       </c>
       <c r="B47" t="n">
-        <v>13.65040016174316</v>
+        <v>13.65039920806885</v>
       </c>
       <c r="C47" t="n">
-        <v>13.77449501605975</v>
+        <v>13.77449405371565</v>
       </c>
       <c r="D47" t="n">
-        <v>13.34016429394225</v>
+        <v>13.34016336194231</v>
       </c>
       <c r="E47" t="n">
-        <v>13.61494460984229</v>
+        <v>13.61494365864504</v>
       </c>
       <c r="F47" t="n">
         <v>724200</v>
@@ -1372,16 +1372,16 @@
         <v>44161</v>
       </c>
       <c r="B48" t="n">
-        <v>13.53073787689209</v>
+        <v>13.53073883056641</v>
       </c>
       <c r="C48" t="n">
-        <v>13.73903913363267</v>
+        <v>13.73904010198848</v>
       </c>
       <c r="D48" t="n">
-        <v>13.44653062615568</v>
+        <v>13.4465315738949</v>
       </c>
       <c r="E48" t="n">
-        <v>13.65039983334939</v>
+        <v>13.65040079545773</v>
       </c>
       <c r="F48" t="n">
         <v>209800</v>
@@ -1392,16 +1392,16 @@
         <v>44162</v>
       </c>
       <c r="B49" t="n">
-        <v>13.39334774017334</v>
+        <v>13.39334583282471</v>
       </c>
       <c r="C49" t="n">
-        <v>13.71688061533133</v>
+        <v>13.71687866190833</v>
       </c>
       <c r="D49" t="n">
-        <v>13.38891569034081</v>
+        <v>13.38891378362335</v>
       </c>
       <c r="E49" t="n">
-        <v>13.5307387490005</v>
+        <v>13.53073682208599</v>
       </c>
       <c r="F49" t="n">
         <v>510000</v>
@@ -1412,16 +1412,16 @@
         <v>44165</v>
       </c>
       <c r="B50" t="n">
-        <v>13.13629245758057</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="C50" t="n">
-        <v>13.73017350549127</v>
+        <v>13.73017450228043</v>
       </c>
       <c r="D50" t="n">
-        <v>13.13629245758057</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="E50" t="n">
-        <v>13.3889133363299</v>
+        <v>13.38891430834409</v>
       </c>
       <c r="F50" t="n">
         <v>1093200</v>
@@ -1432,16 +1432,16 @@
         <v>44166</v>
       </c>
       <c r="B51" t="n">
-        <v>14.18223285675049</v>
+        <v>14.18223476409912</v>
       </c>
       <c r="C51" t="n">
-        <v>14.40383024513721</v>
+        <v>14.40383218228817</v>
       </c>
       <c r="D51" t="n">
-        <v>13.47755309405454</v>
+        <v>13.47755490663178</v>
       </c>
       <c r="E51" t="n">
-        <v>13.73460603077007</v>
+        <v>13.73460787791799</v>
       </c>
       <c r="F51" t="n">
         <v>2351000</v>
@@ -1452,16 +1452,16 @@
         <v>44167</v>
       </c>
       <c r="B52" t="n">
-        <v>14.18223285675049</v>
+        <v>14.18223476409912</v>
       </c>
       <c r="C52" t="n">
-        <v>14.37280674601539</v>
+        <v>14.37280867899403</v>
       </c>
       <c r="D52" t="n">
-        <v>13.9340440184489</v>
+        <v>13.93404589241896</v>
       </c>
       <c r="E52" t="n">
-        <v>14.18223285675049</v>
+        <v>14.18223476409912</v>
       </c>
       <c r="F52" t="n">
         <v>767800</v>
@@ -1472,16 +1472,16 @@
         <v>44168</v>
       </c>
       <c r="B53" t="n">
-        <v>14.35951232910156</v>
+        <v>14.3595142364502</v>
       </c>
       <c r="C53" t="n">
-        <v>14.44371873324512</v>
+        <v>14.44372065177874</v>
       </c>
       <c r="D53" t="n">
-        <v>14.05813888173424</v>
+        <v>14.05814074905197</v>
       </c>
       <c r="E53" t="n">
-        <v>14.31519183429916</v>
+        <v>14.31519373576078</v>
       </c>
       <c r="F53" t="n">
         <v>1033200</v>
@@ -1492,16 +1492,16 @@
         <v>44169</v>
       </c>
       <c r="B54" t="n">
-        <v>14.07143688201904</v>
+        <v>14.07143592834473</v>
       </c>
       <c r="C54" t="n">
-        <v>14.44815183881928</v>
+        <v>14.44815085961357</v>
       </c>
       <c r="D54" t="n">
-        <v>13.94734201622206</v>
+        <v>13.94734107095812</v>
       </c>
       <c r="E54" t="n">
-        <v>14.44815183881928</v>
+        <v>14.44815085961357</v>
       </c>
       <c r="F54" t="n">
         <v>751600</v>
@@ -1512,16 +1512,16 @@
         <v>44172</v>
       </c>
       <c r="B55" t="n">
-        <v>14.25314426422119</v>
+        <v>14.25314617156982</v>
       </c>
       <c r="C55" t="n">
-        <v>14.36837416480735</v>
+        <v>14.36837608757599</v>
       </c>
       <c r="D55" t="n">
-        <v>13.82767767499762</v>
+        <v>13.82767952541053</v>
       </c>
       <c r="E55" t="n">
-        <v>14.06257037080052</v>
+        <v>14.06257225264665</v>
       </c>
       <c r="F55" t="n">
         <v>782600</v>
@@ -1532,16 +1532,16 @@
         <v>44173</v>
       </c>
       <c r="B56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="C56" t="n">
-        <v>14.53679034258752</v>
+        <v>14.53678935892345</v>
       </c>
       <c r="D56" t="n">
-        <v>13.89859038475245</v>
+        <v>13.89858944427358</v>
       </c>
       <c r="E56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="F56" t="n">
         <v>767200</v>
@@ -1552,16 +1552,16 @@
         <v>44174</v>
       </c>
       <c r="B57" t="n">
-        <v>13.88972473144531</v>
+        <v>13.88972663879395</v>
       </c>
       <c r="C57" t="n">
-        <v>14.24871311856489</v>
+        <v>14.24871507521011</v>
       </c>
       <c r="D57" t="n">
-        <v>13.65926323867578</v>
+        <v>13.65926511437724</v>
       </c>
       <c r="E57" t="n">
-        <v>14.14677767481842</v>
+        <v>14.14677961746578</v>
       </c>
       <c r="F57" t="n">
         <v>570800</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.004958152771</v>
+        <v>14.00495719909668</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10246072049168</v>
+        <v>14.10245976017788</v>
       </c>
       <c r="D58" t="n">
-        <v>13.51744362351329</v>
+        <v>13.5174427030365</v>
       </c>
       <c r="E58" t="n">
-        <v>13.88529533420892</v>
+        <v>13.8852943886831</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1592,16 +1592,16 @@
         <v>44176</v>
       </c>
       <c r="B59" t="n">
-        <v>13.82324695587158</v>
+        <v>13.82324600219727</v>
       </c>
       <c r="C59" t="n">
-        <v>13.96063711619654</v>
+        <v>13.9606361530436</v>
       </c>
       <c r="D59" t="n">
-        <v>13.40221153010944</v>
+        <v>13.40221060548261</v>
       </c>
       <c r="E59" t="n">
-        <v>13.92074951395268</v>
+        <v>13.9207485535516</v>
       </c>
       <c r="F59" t="n">
         <v>523600</v>
@@ -1612,16 +1612,16 @@
         <v>44179</v>
       </c>
       <c r="B60" t="n">
-        <v>13.7567663192749</v>
+        <v>13.75676822662354</v>
       </c>
       <c r="C60" t="n">
-        <v>14.05813805833661</v>
+        <v>14.05814000746984</v>
       </c>
       <c r="D60" t="n">
-        <v>13.61494328019492</v>
+        <v>13.61494516788007</v>
       </c>
       <c r="E60" t="n">
-        <v>13.74347017161295</v>
+        <v>13.7434720771181</v>
       </c>
       <c r="F60" t="n">
         <v>525000</v>
@@ -1672,16 +1672,16 @@
         <v>44182</v>
       </c>
       <c r="B63" t="n">
-        <v>13.73903751373291</v>
+        <v>13.73904037475586</v>
       </c>
       <c r="C63" t="n">
-        <v>14.13348057829998</v>
+        <v>14.13348352146192</v>
       </c>
       <c r="D63" t="n">
-        <v>13.67255846902217</v>
+        <v>13.67256131620149</v>
       </c>
       <c r="E63" t="n">
-        <v>13.91631524807053</v>
+        <v>13.91631814600987</v>
       </c>
       <c r="F63" t="n">
         <v>633000</v>
@@ -1692,16 +1692,16 @@
         <v>44183</v>
       </c>
       <c r="B64" t="n">
-        <v>13.40664386749268</v>
+        <v>13.40664291381836</v>
       </c>
       <c r="C64" t="n">
-        <v>13.83654255661189</v>
+        <v>13.83654157235696</v>
       </c>
       <c r="D64" t="n">
-        <v>13.28698105819358</v>
+        <v>13.28698011303142</v>
       </c>
       <c r="E64" t="n">
-        <v>13.61937718713968</v>
+        <v>13.6193762183327</v>
       </c>
       <c r="F64" t="n">
         <v>920000</v>
@@ -1712,16 +1712,16 @@
         <v>44186</v>
       </c>
       <c r="B65" t="n">
-        <v>13.14958953857422</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="C65" t="n">
-        <v>13.3401634347651</v>
+        <v>13.3401644022608</v>
       </c>
       <c r="D65" t="n">
-        <v>12.76844174619245</v>
+        <v>12.76844267222401</v>
       </c>
       <c r="E65" t="n">
-        <v>13.14958953857422</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="F65" t="n">
         <v>872000</v>
@@ -1752,16 +1752,16 @@
         <v>44188</v>
       </c>
       <c r="B67" t="n">
-        <v>14.04484462738037</v>
+        <v>14.04484272003174</v>
       </c>
       <c r="C67" t="n">
-        <v>14.15121128686777</v>
+        <v>14.1512093650741</v>
       </c>
       <c r="D67" t="n">
-        <v>13.40221177531775</v>
+        <v>13.40220995524134</v>
       </c>
       <c r="E67" t="n">
-        <v>13.45539552772498</v>
+        <v>13.45539370042599</v>
       </c>
       <c r="F67" t="n">
         <v>2040000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294269561768</v>
+        <v>15.11294364929199</v>
       </c>
       <c r="C68" t="n">
-        <v>15.13067089418624</v>
+        <v>15.13067184897926</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586759384061</v>
+        <v>14.07586848207222</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348254853438</v>
+        <v>14.13348344040167</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.19715023040771</v>
+        <v>15.19715213775635</v>
       </c>
       <c r="C69" t="n">
-        <v>15.34783653134916</v>
+        <v>15.34783845760998</v>
       </c>
       <c r="D69" t="n">
-        <v>14.74952253173429</v>
+        <v>14.74952438290252</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510322837077</v>
+        <v>15.13510512793207</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1812,16 +1812,16 @@
         <v>44195</v>
       </c>
       <c r="B70" t="n">
-        <v>15.72012138366699</v>
+        <v>15.72012233734131</v>
       </c>
       <c r="C70" t="n">
-        <v>15.9151265029923</v>
+        <v>15.91512746849676</v>
       </c>
       <c r="D70" t="n">
-        <v>15.2503342485805</v>
+        <v>15.25033517375479</v>
       </c>
       <c r="E70" t="n">
-        <v>15.37886115685711</v>
+        <v>15.37886208982859</v>
       </c>
       <c r="F70" t="n">
         <v>2946000</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884773254395</v>
+        <v>14.98884868621826</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171721175532</v>
+        <v>15.94171822605652</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952213906937</v>
+        <v>14.74952307751646</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069371156276</v>
+        <v>15.91069472389008</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.58997344970703</v>
+        <v>14.58997249603271</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135801482809</v>
+        <v>15.28135701596139</v>
       </c>
       <c r="D73" t="n">
-        <v>14.58997344970703</v>
+        <v>14.58997249603271</v>
       </c>
       <c r="E73" t="n">
-        <v>15.1395358000321</v>
+        <v>15.13953481043562</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1892,16 +1892,16 @@
         <v>44203</v>
       </c>
       <c r="B74" t="n">
-        <v>14.40513038635254</v>
+        <v>14.40513134002686</v>
       </c>
       <c r="C74" t="n">
-        <v>14.96995047062398</v>
+        <v>14.96995146169153</v>
       </c>
       <c r="D74" t="n">
-        <v>14.39623538149606</v>
+        <v>14.39623633458149</v>
       </c>
       <c r="E74" t="n">
-        <v>14.68531710141131</v>
+        <v>14.68531807363505</v>
       </c>
       <c r="F74" t="n">
         <v>1215000</v>
@@ -1932,16 +1932,16 @@
         <v>44207</v>
       </c>
       <c r="B76" t="n">
-        <v>15.83274555206299</v>
+        <v>15.83274841308594</v>
       </c>
       <c r="C76" t="n">
-        <v>15.83274555206299</v>
+        <v>15.83274841308594</v>
       </c>
       <c r="D76" t="n">
-        <v>14.80539709311043</v>
+        <v>14.80539976848854</v>
       </c>
       <c r="E76" t="n">
-        <v>14.95216043158278</v>
+        <v>14.95216313348145</v>
       </c>
       <c r="F76" t="n">
         <v>1758200</v>
@@ -1952,16 +1952,16 @@
         <v>44208</v>
       </c>
       <c r="B77" t="n">
-        <v>15.99285316467285</v>
+        <v>15.99285221099854</v>
       </c>
       <c r="C77" t="n">
-        <v>16.31306657107592</v>
+        <v>16.31306559830687</v>
       </c>
       <c r="D77" t="n">
-        <v>15.34353304306556</v>
+        <v>15.34353212811103</v>
       </c>
       <c r="E77" t="n">
-        <v>15.90390480772213</v>
+        <v>15.90390385935192</v>
       </c>
       <c r="F77" t="n">
         <v>2193200</v>
@@ -1972,16 +1972,16 @@
         <v>44209</v>
       </c>
       <c r="B78" t="n">
-        <v>15.72156143188477</v>
+        <v>15.72156238555908</v>
       </c>
       <c r="C78" t="n">
-        <v>16.7177799754675</v>
+        <v>16.71778098957271</v>
       </c>
       <c r="D78" t="n">
-        <v>15.41469138192811</v>
+        <v>15.4146923169876</v>
       </c>
       <c r="E78" t="n">
-        <v>15.9661698375192</v>
+        <v>15.96617080603153</v>
       </c>
       <c r="F78" t="n">
         <v>1238200</v>
@@ -1992,16 +1992,16 @@
         <v>44210</v>
       </c>
       <c r="B79" t="n">
-        <v>16.08624649047852</v>
+        <v>16.08624458312988</v>
       </c>
       <c r="C79" t="n">
-        <v>16.2552481813217</v>
+        <v>16.25524625393452</v>
       </c>
       <c r="D79" t="n">
-        <v>15.65929645771021</v>
+        <v>15.6592946009851</v>
       </c>
       <c r="E79" t="n">
-        <v>15.94837816337235</v>
+        <v>15.94837627237078</v>
       </c>
       <c r="F79" t="n">
         <v>1217000</v>
@@ -2012,16 +2012,16 @@
         <v>44211</v>
       </c>
       <c r="B80" t="n">
-        <v>15.88166618347168</v>
+        <v>15.88166809082031</v>
       </c>
       <c r="C80" t="n">
-        <v>16.09069454203798</v>
+        <v>16.09069647449039</v>
       </c>
       <c r="D80" t="n">
-        <v>15.61037449168528</v>
+        <v>15.61037636645245</v>
       </c>
       <c r="E80" t="n">
-        <v>16.08624619163735</v>
+        <v>16.08624812355553</v>
       </c>
       <c r="F80" t="n">
         <v>728000</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422584533691</v>
+        <v>16.38422393798828</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538419561817</v>
+        <v>16.45538227998573</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169572023429</v>
+        <v>15.92169386673051</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93503907728939</v>
+        <v>15.93503722223226</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2052,16 +2052,16 @@
         <v>44215</v>
       </c>
       <c r="B82" t="n">
-        <v>16.63327980041504</v>
+        <v>16.63328170776367</v>
       </c>
       <c r="C82" t="n">
-        <v>17.07801988388551</v>
+        <v>17.07802184223276</v>
       </c>
       <c r="D82" t="n">
-        <v>16.0951430100387</v>
+        <v>16.09514485567885</v>
       </c>
       <c r="E82" t="n">
-        <v>17.07801988388551</v>
+        <v>17.07802184223276</v>
       </c>
       <c r="F82" t="n">
         <v>1918400</v>
@@ -2072,16 +2072,16 @@
         <v>44216</v>
       </c>
       <c r="B83" t="n">
-        <v>16.25525093078613</v>
+        <v>16.2552490234375</v>
       </c>
       <c r="C83" t="n">
-        <v>16.81117607682225</v>
+        <v>16.81117410424281</v>
       </c>
       <c r="D83" t="n">
-        <v>16.01064420584002</v>
+        <v>16.0106423271929</v>
       </c>
       <c r="E83" t="n">
-        <v>16.69999104761502</v>
+        <v>16.69998908808175</v>
       </c>
       <c r="F83" t="n">
         <v>1073000</v>
@@ -2092,16 +2092,16 @@
         <v>44217</v>
       </c>
       <c r="B84" t="n">
-        <v>15.85498332977295</v>
+        <v>15.85498523712158</v>
       </c>
       <c r="C84" t="n">
-        <v>16.36643336510678</v>
+        <v>16.36643533398266</v>
       </c>
       <c r="D84" t="n">
-        <v>15.53032160299971</v>
+        <v>15.53032347129166</v>
       </c>
       <c r="E84" t="n">
-        <v>16.25969670405826</v>
+        <v>16.25969866009376</v>
       </c>
       <c r="F84" t="n">
         <v>928200</v>
@@ -2112,16 +2112,16 @@
         <v>44218</v>
       </c>
       <c r="B85" t="n">
-        <v>15.40134906768799</v>
+        <v>15.4013500213623</v>
       </c>
       <c r="C85" t="n">
-        <v>15.84164078602173</v>
+        <v>15.84164176695957</v>
       </c>
       <c r="D85" t="n">
-        <v>15.17453068238381</v>
+        <v>15.17453162201319</v>
       </c>
       <c r="E85" t="n">
-        <v>15.60592909229859</v>
+        <v>15.60593005864081</v>
       </c>
       <c r="F85" t="n">
         <v>1029200</v>
@@ -2132,16 +2132,16 @@
         <v>44222</v>
       </c>
       <c r="B86" t="n">
-        <v>14.67197608947754</v>
+        <v>14.67197704315186</v>
       </c>
       <c r="C86" t="n">
-        <v>15.525876234775</v>
+        <v>15.52587724395259</v>
       </c>
       <c r="D86" t="n">
-        <v>14.63639606848242</v>
+        <v>14.63639701984405</v>
       </c>
       <c r="E86" t="n">
-        <v>15.38355954389209</v>
+        <v>15.38356054381913</v>
       </c>
       <c r="F86" t="n">
         <v>1156000</v>
@@ -2152,16 +2152,16 @@
         <v>44223</v>
       </c>
       <c r="B87" t="n">
-        <v>15.00552940368652</v>
+        <v>15.00553035736084</v>
       </c>
       <c r="C87" t="n">
-        <v>15.5703477505178</v>
+        <v>15.57034874008907</v>
       </c>
       <c r="D87" t="n">
-        <v>14.53410435971512</v>
+        <v>14.53410528342808</v>
       </c>
       <c r="E87" t="n">
-        <v>14.74313271733759</v>
+        <v>14.74313365433532</v>
       </c>
       <c r="F87" t="n">
         <v>1909000</v>
@@ -2172,16 +2172,16 @@
         <v>44224</v>
       </c>
       <c r="B88" t="n">
-        <v>15.65929698944092</v>
+        <v>15.6592960357666</v>
       </c>
       <c r="C88" t="n">
-        <v>15.98840537788466</v>
+        <v>15.98840440416715</v>
       </c>
       <c r="D88" t="n">
-        <v>14.95216023141669</v>
+        <v>14.95215932080804</v>
       </c>
       <c r="E88" t="n">
-        <v>15.13450358680413</v>
+        <v>15.13450266509051</v>
       </c>
       <c r="F88" t="n">
         <v>3941600</v>
@@ -2212,16 +2212,16 @@
         <v>44228</v>
       </c>
       <c r="B90" t="n">
-        <v>16.76670265197754</v>
+        <v>16.76670074462891</v>
       </c>
       <c r="C90" t="n">
-        <v>17.02909938733217</v>
+        <v>17.02909745013378</v>
       </c>
       <c r="D90" t="n">
-        <v>15.65929902065404</v>
+        <v>15.65929723928157</v>
       </c>
       <c r="E90" t="n">
-        <v>16.01064411819733</v>
+        <v>16.0106422968565</v>
       </c>
       <c r="F90" t="n">
         <v>3072200</v>
@@ -2272,16 +2272,16 @@
         <v>44231</v>
       </c>
       <c r="B93" t="n">
-        <v>17.8874454498291</v>
+        <v>17.88744735717773</v>
       </c>
       <c r="C93" t="n">
-        <v>18.36331717015739</v>
+        <v>18.3633191282485</v>
       </c>
       <c r="D93" t="n">
-        <v>17.61615374642633</v>
+        <v>17.61615562484698</v>
       </c>
       <c r="E93" t="n">
-        <v>17.79404874945122</v>
+        <v>17.79405064684091</v>
       </c>
       <c r="F93" t="n">
         <v>1940600</v>
@@ -2292,16 +2292,16 @@
         <v>44232</v>
       </c>
       <c r="B94" t="n">
-        <v>18.80805969238281</v>
+        <v>18.80805778503418</v>
       </c>
       <c r="C94" t="n">
-        <v>19.56856487465802</v>
+        <v>19.56856289018561</v>
       </c>
       <c r="D94" t="n">
-        <v>17.78960443150729</v>
+        <v>17.78960262744146</v>
       </c>
       <c r="E94" t="n">
-        <v>17.99863282647314</v>
+        <v>17.99863100120949</v>
       </c>
       <c r="F94" t="n">
         <v>14342200</v>
@@ -2312,16 +2312,16 @@
         <v>44235</v>
       </c>
       <c r="B95" t="n">
-        <v>19.23056030273438</v>
+        <v>19.23056221008301</v>
       </c>
       <c r="C95" t="n">
-        <v>19.36842863096819</v>
+        <v>19.36843055199105</v>
       </c>
       <c r="D95" t="n">
-        <v>18.46560688202301</v>
+        <v>18.46560871350112</v>
       </c>
       <c r="E95" t="n">
-        <v>18.81250357441601</v>
+        <v>18.81250544030044</v>
       </c>
       <c r="F95" t="n">
         <v>1758400</v>
@@ -2352,16 +2352,16 @@
         <v>44237</v>
       </c>
       <c r="B97" t="n">
-        <v>18.55900192260742</v>
+        <v>18.55900573730469</v>
       </c>
       <c r="C97" t="n">
-        <v>18.9815053057677</v>
+        <v>18.98150920730814</v>
       </c>
       <c r="D97" t="n">
-        <v>18.24323689700658</v>
+        <v>18.24324064680014</v>
       </c>
       <c r="E97" t="n">
-        <v>18.87032029422808</v>
+        <v>18.87032417291507</v>
       </c>
       <c r="F97" t="n">
         <v>979000</v>
@@ -2372,16 +2372,16 @@
         <v>44238</v>
       </c>
       <c r="B98" t="n">
-        <v>18.63460922241211</v>
+        <v>18.63461112976074</v>
       </c>
       <c r="C98" t="n">
-        <v>19.14605927430059</v>
+        <v>19.14606123399878</v>
       </c>
       <c r="D98" t="n">
-        <v>18.4344758557824</v>
+        <v>18.43447774264635</v>
       </c>
       <c r="E98" t="n">
-        <v>18.55900252988591</v>
+        <v>18.55900442949581</v>
       </c>
       <c r="F98" t="n">
         <v>912400</v>
@@ -2412,16 +2412,16 @@
         <v>44244</v>
       </c>
       <c r="B100" t="n">
-        <v>18.52787017822266</v>
+        <v>18.52787208557129</v>
       </c>
       <c r="C100" t="n">
-        <v>18.68797686562316</v>
+        <v>18.68797878945395</v>
       </c>
       <c r="D100" t="n">
-        <v>18.20765680342165</v>
+        <v>18.20765867780597</v>
       </c>
       <c r="E100" t="n">
-        <v>18.51897517375056</v>
+        <v>18.5189770801835</v>
       </c>
       <c r="F100" t="n">
         <v>743200</v>
@@ -2452,16 +2452,16 @@
         <v>44246</v>
       </c>
       <c r="B102" t="n">
-        <v>18.27881622314453</v>
+        <v>18.2788143157959</v>
       </c>
       <c r="C102" t="n">
-        <v>18.57234460188025</v>
+        <v>18.57234266390267</v>
       </c>
       <c r="D102" t="n">
-        <v>17.92302450597225</v>
+        <v>17.92302263574959</v>
       </c>
       <c r="E102" t="n">
-        <v>18.23434289470377</v>
+        <v>18.23434099199582</v>
       </c>
       <c r="F102" t="n">
         <v>881800</v>
@@ -2472,16 +2472,16 @@
         <v>44249</v>
       </c>
       <c r="B103" t="n">
-        <v>17.81628799438477</v>
+        <v>17.81628608703613</v>
       </c>
       <c r="C103" t="n">
-        <v>18.46115974514026</v>
+        <v>18.46115776875395</v>
       </c>
       <c r="D103" t="n">
-        <v>16.95793951491647</v>
+        <v>16.95793769945958</v>
       </c>
       <c r="E103" t="n">
-        <v>17.34486290467952</v>
+        <v>17.34486104779998</v>
       </c>
       <c r="F103" t="n">
         <v>2023200</v>
@@ -2492,16 +2492,16 @@
         <v>44250</v>
       </c>
       <c r="B104" t="n">
-        <v>17.70065689086914</v>
+        <v>17.70065498352051</v>
       </c>
       <c r="C104" t="n">
-        <v>18.1009236877591</v>
+        <v>18.1009217372794</v>
       </c>
       <c r="D104" t="n">
-        <v>17.51831350485237</v>
+        <v>17.5183116171523</v>
       </c>
       <c r="E104" t="n">
-        <v>17.86076360962512</v>
+        <v>17.86076168502407</v>
       </c>
       <c r="F104" t="n">
         <v>1151400</v>
@@ -2512,16 +2512,16 @@
         <v>44251</v>
       </c>
       <c r="B105" t="n">
-        <v>17.68731498718262</v>
+        <v>17.68731307983398</v>
       </c>
       <c r="C105" t="n">
-        <v>18.09647508812474</v>
+        <v>18.09647313665348</v>
       </c>
       <c r="D105" t="n">
-        <v>17.54499828280719</v>
+        <v>17.54499639080558</v>
       </c>
       <c r="E105" t="n">
-        <v>17.70510499936678</v>
+        <v>17.70510309009973</v>
       </c>
       <c r="F105" t="n">
         <v>1411000</v>
@@ -2532,16 +2532,16 @@
         <v>44252</v>
       </c>
       <c r="B106" t="n">
-        <v>16.9445972442627</v>
+        <v>16.94459533691406</v>
       </c>
       <c r="C106" t="n">
-        <v>17.79405077305967</v>
+        <v>17.7940487700933</v>
       </c>
       <c r="D106" t="n">
-        <v>16.63772718397596</v>
+        <v>16.6377253111698</v>
       </c>
       <c r="E106" t="n">
-        <v>17.68731409841596</v>
+        <v>17.68731210746428</v>
       </c>
       <c r="F106" t="n">
         <v>1207600</v>
@@ -2552,16 +2552,16 @@
         <v>44253</v>
       </c>
       <c r="B107" t="n">
-        <v>16.69998741149902</v>
+        <v>16.69999122619629</v>
       </c>
       <c r="C107" t="n">
-        <v>17.20699076284545</v>
+        <v>17.20699469335504</v>
       </c>
       <c r="D107" t="n">
-        <v>16.40201241244574</v>
+        <v>16.40201615907802</v>
       </c>
       <c r="E107" t="n">
-        <v>17.13583242750821</v>
+        <v>17.13583634176344</v>
       </c>
       <c r="F107" t="n">
         <v>1586600</v>
@@ -2572,16 +2572,16 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>16.44648742675781</v>
+        <v>16.44649124145508</v>
       </c>
       <c r="C108" t="n">
-        <v>17.0246491728847</v>
+        <v>17.02465312168428</v>
       </c>
       <c r="D108" t="n">
-        <v>16.27748572675039</v>
+        <v>16.27748950224838</v>
       </c>
       <c r="E108" t="n">
-        <v>16.69998912849459</v>
+        <v>16.69999300199057</v>
       </c>
       <c r="F108" t="n">
         <v>1540800</v>
@@ -2612,16 +2612,16 @@
         <v>44258</v>
       </c>
       <c r="B110" t="n">
-        <v>16.19298934936523</v>
+        <v>16.1929874420166</v>
       </c>
       <c r="C110" t="n">
-        <v>16.80228290074185</v>
+        <v>16.80228092162542</v>
       </c>
       <c r="D110" t="n">
-        <v>15.61927412900413</v>
+        <v>15.61927228923258</v>
       </c>
       <c r="E110" t="n">
-        <v>16.80228290074185</v>
+        <v>16.80228092162542</v>
       </c>
       <c r="F110" t="n">
         <v>1368800</v>
@@ -2632,16 +2632,16 @@
         <v>44259</v>
       </c>
       <c r="B111" t="n">
-        <v>16.0506706237793</v>
+        <v>16.05066871643066</v>
       </c>
       <c r="C111" t="n">
-        <v>16.75780746592523</v>
+        <v>16.75780547454543</v>
       </c>
       <c r="D111" t="n">
-        <v>15.79272054586055</v>
+        <v>15.79271866916489</v>
       </c>
       <c r="E111" t="n">
-        <v>16.23301400085849</v>
+        <v>16.23301207184145</v>
       </c>
       <c r="F111" t="n">
         <v>1300400</v>
@@ -2652,16 +2652,16 @@
         <v>44260</v>
       </c>
       <c r="B112" t="n">
-        <v>16.26414108276367</v>
+        <v>16.2641429901123</v>
       </c>
       <c r="C112" t="n">
-        <v>16.35308941889308</v>
+        <v>16.35309133667297</v>
       </c>
       <c r="D112" t="n">
-        <v>15.42358278426497</v>
+        <v>15.4235845930386</v>
       </c>
       <c r="E112" t="n">
-        <v>16.23300941960064</v>
+        <v>16.23301132329836</v>
       </c>
       <c r="F112" t="n">
         <v>2305400</v>
@@ -2672,16 +2672,16 @@
         <v>44263</v>
       </c>
       <c r="B113" t="n">
-        <v>14.91213417053223</v>
+        <v>14.91213512420654</v>
       </c>
       <c r="C113" t="n">
-        <v>16.05956437827389</v>
+        <v>16.0595654053297</v>
       </c>
       <c r="D113" t="n">
-        <v>14.76537082800059</v>
+        <v>14.76537177228896</v>
       </c>
       <c r="E113" t="n">
-        <v>16.01064269858043</v>
+        <v>16.01064372250756</v>
       </c>
       <c r="F113" t="n">
         <v>3236800</v>
@@ -2692,16 +2692,16 @@
         <v>44264</v>
       </c>
       <c r="B114" t="n">
-        <v>14.76537132263184</v>
+        <v>14.76537036895752</v>
       </c>
       <c r="C114" t="n">
-        <v>15.42358645203744</v>
+        <v>15.42358545584995</v>
       </c>
       <c r="D114" t="n">
-        <v>14.55634293750244</v>
+        <v>14.55634199732897</v>
       </c>
       <c r="E114" t="n">
-        <v>15.11671640079224</v>
+        <v>15.11671542442504</v>
       </c>
       <c r="F114" t="n">
         <v>1628800</v>
@@ -2732,16 +2732,16 @@
         <v>44266</v>
       </c>
       <c r="B116" t="n">
-        <v>15.81940364837646</v>
+        <v>15.81940650939941</v>
       </c>
       <c r="C116" t="n">
-        <v>15.99285199868294</v>
+        <v>15.99285489107494</v>
       </c>
       <c r="D116" t="n">
-        <v>15.15674191533128</v>
+        <v>15.15674465650835</v>
       </c>
       <c r="E116" t="n">
-        <v>15.15674191533128</v>
+        <v>15.15674465650835</v>
       </c>
       <c r="F116" t="n">
         <v>2295400</v>
@@ -2752,16 +2752,16 @@
         <v>44267</v>
       </c>
       <c r="B117" t="n">
-        <v>15.61037635803223</v>
+        <v>15.61037445068359</v>
       </c>
       <c r="C117" t="n">
-        <v>15.96172143355023</v>
+        <v>15.96171948327262</v>
       </c>
       <c r="D117" t="n">
-        <v>15.41913798510718</v>
+        <v>15.41913610112494</v>
       </c>
       <c r="E117" t="n">
-        <v>15.96172143355023</v>
+        <v>15.96171948327262</v>
       </c>
       <c r="F117" t="n">
         <v>1034800</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708873748779</v>
+        <v>15.67708778381348</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619716243003</v>
+        <v>16.00619618873527</v>
       </c>
       <c r="D118" t="n">
-        <v>15.49474536187826</v>
+        <v>15.49474441929632</v>
       </c>
       <c r="E118" t="n">
-        <v>15.61482539409169</v>
+        <v>15.614824444205</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880424499512</v>
+        <v>16.58880615234375</v>
       </c>
       <c r="C120" t="n">
-        <v>16.7578059463568</v>
+        <v>16.75780787313692</v>
       </c>
       <c r="D120" t="n">
-        <v>16.07735418324739</v>
+        <v>16.07735603179049</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298585477987</v>
+        <v>16.19298771661808</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2852,16 +2852,16 @@
         <v>44274</v>
       </c>
       <c r="B122" t="n">
-        <v>16.32196235656738</v>
+        <v>16.32195854187012</v>
       </c>
       <c r="C122" t="n">
-        <v>16.54433241129841</v>
+        <v>16.5443285446298</v>
       </c>
       <c r="D122" t="n">
-        <v>15.89056390749354</v>
+        <v>15.89056019362082</v>
       </c>
       <c r="E122" t="n">
-        <v>16.17519730610144</v>
+        <v>16.17519352570546</v>
       </c>
       <c r="F122" t="n">
         <v>1059200</v>
@@ -2872,16 +2872,16 @@
         <v>44277</v>
       </c>
       <c r="B123" t="n">
-        <v>16.54433250427246</v>
+        <v>16.54433059692383</v>
       </c>
       <c r="C123" t="n">
-        <v>16.58435918221094</v>
+        <v>16.58435727024774</v>
       </c>
       <c r="D123" t="n">
-        <v>15.921695668907</v>
+        <v>15.92169383334038</v>
       </c>
       <c r="E123" t="n">
-        <v>16.26414575870311</v>
+        <v>16.26414388365641</v>
       </c>
       <c r="F123" t="n">
         <v>938000</v>
@@ -2932,16 +2932,16 @@
         <v>44280</v>
       </c>
       <c r="B126" t="n">
-        <v>16.06846046447754</v>
+        <v>16.06845855712891</v>
       </c>
       <c r="C126" t="n">
-        <v>16.22411882256725</v>
+        <v>16.22411689674175</v>
       </c>
       <c r="D126" t="n">
-        <v>15.07224188305681</v>
+        <v>15.07224009396071</v>
       </c>
       <c r="E126" t="n">
-        <v>15.38800695035243</v>
+        <v>15.38800512377458</v>
       </c>
       <c r="F126" t="n">
         <v>1320600</v>
@@ -2952,16 +2952,16 @@
         <v>44281</v>
       </c>
       <c r="B127" t="n">
-        <v>15.85498332977295</v>
+        <v>15.85498523712158</v>
       </c>
       <c r="C127" t="n">
-        <v>16.41535504164929</v>
+        <v>16.41535701641043</v>
       </c>
       <c r="D127" t="n">
-        <v>15.67263997864547</v>
+        <v>15.67264186405827</v>
       </c>
       <c r="E127" t="n">
-        <v>16.1040366699186</v>
+        <v>16.10403860722825</v>
       </c>
       <c r="F127" t="n">
         <v>1078200</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.58369445800781</v>
+        <v>15.58369064331055</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174956665047</v>
+        <v>16.00174564961845</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245606766462</v>
+        <v>15.39245229978017</v>
       </c>
       <c r="E128" t="n">
-        <v>15.74380117518341</v>
+        <v>15.74379732129399</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514236450195</v>
+        <v>16.09514045715332</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23745904978063</v>
+        <v>16.23745712556681</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48584894961834</v>
+        <v>15.48584711447378</v>
       </c>
       <c r="E129" t="n">
-        <v>15.58813896112809</v>
+        <v>15.5881371138617</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3052,16 +3052,16 @@
         <v>44291</v>
       </c>
       <c r="B132" t="n">
-        <v>16.86454582214355</v>
+        <v>16.86454391479492</v>
       </c>
       <c r="C132" t="n">
-        <v>17.01131088727931</v>
+        <v>17.01130896333182</v>
       </c>
       <c r="D132" t="n">
-        <v>16.60215076002032</v>
+        <v>16.60214888234808</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90012584880036</v>
+        <v>16.90012393742769</v>
       </c>
       <c r="F132" t="n">
         <v>838600</v>
@@ -3092,16 +3092,16 @@
         <v>44293</v>
       </c>
       <c r="B134" t="n">
-        <v>17.37154579162598</v>
+        <v>17.37155151367188</v>
       </c>
       <c r="C134" t="n">
-        <v>17.63838912500147</v>
+        <v>17.63839493494339</v>
       </c>
       <c r="D134" t="n">
-        <v>17.1135957656876</v>
+        <v>17.11360140276686</v>
       </c>
       <c r="E134" t="n">
-        <v>17.47828244635676</v>
+        <v>17.47828820356084</v>
       </c>
       <c r="F134" t="n">
         <v>869400</v>
@@ -3112,16 +3112,16 @@
         <v>44294</v>
       </c>
       <c r="B135" t="n">
-        <v>17.60725975036621</v>
+        <v>17.60725784301758</v>
       </c>
       <c r="C135" t="n">
-        <v>17.90968313903537</v>
+        <v>17.909681198926</v>
       </c>
       <c r="D135" t="n">
-        <v>17.2737046919707</v>
+        <v>17.27370282075522</v>
       </c>
       <c r="E135" t="n">
-        <v>17.38044305713872</v>
+        <v>17.38044117436055</v>
       </c>
       <c r="F135" t="n">
         <v>710000</v>
@@ -3172,16 +3172,16 @@
         <v>44299</v>
       </c>
       <c r="B138" t="n">
-        <v>17.40712547302246</v>
+        <v>17.40712738037109</v>
       </c>
       <c r="C138" t="n">
-        <v>17.74068051411476</v>
+        <v>17.74068245801198</v>
       </c>
       <c r="D138" t="n">
-        <v>17.20254545499086</v>
+        <v>17.20254733992308</v>
       </c>
       <c r="E138" t="n">
-        <v>17.74068051411476</v>
+        <v>17.74068245801198</v>
       </c>
       <c r="F138" t="n">
         <v>699800</v>
@@ -3272,16 +3272,16 @@
         <v>44306</v>
       </c>
       <c r="B143" t="n">
-        <v>17.81184005737305</v>
+        <v>17.81184387207031</v>
       </c>
       <c r="C143" t="n">
-        <v>18.40779183888181</v>
+        <v>18.40779578121191</v>
       </c>
       <c r="D143" t="n">
-        <v>17.62949669046246</v>
+        <v>17.62950046610791</v>
       </c>
       <c r="E143" t="n">
-        <v>18.01642008921442</v>
+        <v>18.01642394772585</v>
       </c>
       <c r="F143" t="n">
         <v>1050400</v>
@@ -3292,16 +3292,16 @@
         <v>44308</v>
       </c>
       <c r="B144" t="n">
-        <v>17.32707214355469</v>
+        <v>17.32707595825195</v>
       </c>
       <c r="C144" t="n">
-        <v>17.97639221698004</v>
+        <v>17.97639617463046</v>
       </c>
       <c r="D144" t="n">
-        <v>17.26925715789328</v>
+        <v>17.26926095986211</v>
       </c>
       <c r="E144" t="n">
-        <v>17.94970889945899</v>
+        <v>17.94971285123485</v>
       </c>
       <c r="F144" t="n">
         <v>1084000</v>
@@ -3372,16 +3372,16 @@
         <v>44314</v>
       </c>
       <c r="B148" t="n">
-        <v>18.56789779663086</v>
+        <v>18.56789970397949</v>
       </c>
       <c r="C148" t="n">
-        <v>18.63905613948654</v>
+        <v>18.63905805414477</v>
       </c>
       <c r="D148" t="n">
-        <v>17.32707260257054</v>
+        <v>17.32707438245799</v>
       </c>
       <c r="E148" t="n">
-        <v>17.33596760749609</v>
+        <v>17.33596938829726</v>
       </c>
       <c r="F148" t="n">
         <v>2195600</v>
@@ -3392,16 +3392,16 @@
         <v>44315</v>
       </c>
       <c r="B149" t="n">
-        <v>18.93703269958496</v>
+        <v>18.93703460693359</v>
       </c>
       <c r="C149" t="n">
-        <v>19.07045437919426</v>
+        <v>19.0704562999812</v>
       </c>
       <c r="D149" t="n">
-        <v>18.13205257468259</v>
+        <v>18.13205440095317</v>
       </c>
       <c r="E149" t="n">
-        <v>18.57234428704813</v>
+        <v>18.57234615766514</v>
       </c>
       <c r="F149" t="n">
         <v>2301200</v>
@@ -3472,16 +3472,16 @@
         <v>44321</v>
       </c>
       <c r="B153" t="n">
-        <v>20.46219635009766</v>
+        <v>20.46219825744629</v>
       </c>
       <c r="C153" t="n">
-        <v>21.00761702468171</v>
+        <v>21.00761898287081</v>
       </c>
       <c r="D153" t="n">
-        <v>19.8944227326284</v>
+        <v>19.89442458705298</v>
       </c>
       <c r="E153" t="n">
-        <v>20.09113101760648</v>
+        <v>20.09113289036689</v>
       </c>
       <c r="F153" t="n">
         <v>1994000</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.8332633972168</v>
+        <v>20.83325958251953</v>
       </c>
       <c r="C155" t="n">
-        <v>20.87797099574675</v>
+        <v>20.87796717286325</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384469788557</v>
+        <v>20.36384096914172</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902947604076</v>
+        <v>20.86902565479451</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3532,16 +3532,16 @@
         <v>44326</v>
       </c>
       <c r="B156" t="n">
-        <v>20.36384201049805</v>
+        <v>20.36384010314941</v>
       </c>
       <c r="C156" t="n">
-        <v>20.94502707132523</v>
+        <v>20.94502510954077</v>
       </c>
       <c r="D156" t="n">
-        <v>20.25207558705358</v>
+        <v>20.25207369017338</v>
       </c>
       <c r="E156" t="n">
-        <v>20.83326064788076</v>
+        <v>20.83325869656473</v>
       </c>
       <c r="F156" t="n">
         <v>979800</v>
@@ -3552,16 +3552,16 @@
         <v>44327</v>
       </c>
       <c r="B157" t="n">
-        <v>20.60078811645508</v>
+        <v>20.60078620910645</v>
       </c>
       <c r="C157" t="n">
-        <v>20.60972792961658</v>
+        <v>20.60972602144025</v>
       </c>
       <c r="D157" t="n">
-        <v>19.7826570731339</v>
+        <v>19.78265524153291</v>
       </c>
       <c r="E157" t="n">
-        <v>20.25207571344624</v>
+        <v>20.25207383838357</v>
       </c>
       <c r="F157" t="n">
         <v>1012800</v>
@@ -3632,16 +3632,16 @@
         <v>44333</v>
       </c>
       <c r="B161" t="n">
-        <v>20.98526000976562</v>
+        <v>20.98526382446289</v>
       </c>
       <c r="C161" t="n">
-        <v>21.13279248592639</v>
+        <v>21.13279632744209</v>
       </c>
       <c r="D161" t="n">
-        <v>20.03748135387293</v>
+        <v>20.03748499628314</v>
       </c>
       <c r="E161" t="n">
-        <v>20.16265918424931</v>
+        <v>20.16266284941433</v>
       </c>
       <c r="F161" t="n">
         <v>1096800</v>
@@ -3692,16 +3692,16 @@
         <v>44336</v>
       </c>
       <c r="B164" t="n">
-        <v>21.86151313781738</v>
+        <v>21.86151504516602</v>
       </c>
       <c r="C164" t="n">
-        <v>21.93751348726187</v>
+        <v>21.9375154012413</v>
       </c>
       <c r="D164" t="n">
-        <v>21.37868136927493</v>
+        <v>21.378683234498</v>
       </c>
       <c r="E164" t="n">
-        <v>21.49044779287232</v>
+        <v>21.49044966784666</v>
       </c>
       <c r="F164" t="n">
         <v>917400</v>
@@ -3712,16 +3712,16 @@
         <v>44337</v>
       </c>
       <c r="B165" t="n">
-        <v>21.94645500183105</v>
+        <v>21.94645690917969</v>
       </c>
       <c r="C165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04034030384297</v>
       </c>
       <c r="D165" t="n">
-        <v>21.50385921408051</v>
+        <v>21.5038610829635</v>
       </c>
       <c r="E165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04034030384297</v>
       </c>
       <c r="F165" t="n">
         <v>653400</v>
@@ -3732,16 +3732,16 @@
         <v>44340</v>
       </c>
       <c r="B166" t="n">
-        <v>21.87045288085938</v>
+        <v>21.87045478820801</v>
       </c>
       <c r="C166" t="n">
-        <v>22.12081028286665</v>
+        <v>22.12081221204925</v>
       </c>
       <c r="D166" t="n">
-        <v>21.50385914906818</v>
+        <v>21.50386102444573</v>
       </c>
       <c r="E166" t="n">
-        <v>21.67821620187448</v>
+        <v>21.67821809245792</v>
       </c>
       <c r="F166" t="n">
         <v>900600</v>
@@ -3752,16 +3752,16 @@
         <v>44341</v>
       </c>
       <c r="B167" t="n">
-        <v>22.17892837524414</v>
+        <v>22.17893028259277</v>
       </c>
       <c r="C167" t="n">
-        <v>22.36222523349326</v>
+        <v>22.3622271566051</v>
       </c>
       <c r="D167" t="n">
-        <v>21.77209867984146</v>
+        <v>21.77210055220345</v>
       </c>
       <c r="E167" t="n">
-        <v>21.98221838708007</v>
+        <v>21.98222027751199</v>
       </c>
       <c r="F167" t="n">
         <v>773000</v>
@@ -3772,16 +3772,16 @@
         <v>44342</v>
       </c>
       <c r="B168" t="n">
-        <v>22.17445755004883</v>
+        <v>22.1744556427002</v>
       </c>
       <c r="C168" t="n">
-        <v>22.42481495049289</v>
+        <v>22.42481302160963</v>
       </c>
       <c r="D168" t="n">
-        <v>21.53515347667831</v>
+        <v>21.53515162431978</v>
       </c>
       <c r="E168" t="n">
-        <v>22.17445755004883</v>
+        <v>22.1744556427002</v>
       </c>
       <c r="F168" t="n">
         <v>837000</v>
@@ -3832,16 +3832,16 @@
         <v>44347</v>
       </c>
       <c r="B171" t="n">
-        <v>23.22953224182129</v>
+        <v>23.22953414916992</v>
       </c>
       <c r="C171" t="n">
-        <v>23.22953224182129</v>
+        <v>23.22953414916992</v>
       </c>
       <c r="D171" t="n">
-        <v>22.24151750179612</v>
+        <v>22.24151932802007</v>
       </c>
       <c r="E171" t="n">
-        <v>22.24151750179612</v>
+        <v>22.24151932802007</v>
       </c>
       <c r="F171" t="n">
         <v>1311400</v>
@@ -4052,16 +4052,16 @@
         <v>44363</v>
       </c>
       <c r="B182" t="n">
-        <v>24.49920082092285</v>
+        <v>24.49919891357422</v>
       </c>
       <c r="C182" t="n">
-        <v>24.58414439817256</v>
+        <v>24.58414248421078</v>
       </c>
       <c r="D182" t="n">
-        <v>23.90013269509492</v>
+        <v>23.90013083438584</v>
       </c>
       <c r="E182" t="n">
-        <v>24.36508144761637</v>
+        <v>24.36507955070941</v>
       </c>
       <c r="F182" t="n">
         <v>781400</v>
@@ -4092,16 +4092,16 @@
         <v>44365</v>
       </c>
       <c r="B184" t="n">
-        <v>24.89709091186523</v>
+        <v>24.89708709716797</v>
       </c>
       <c r="C184" t="n">
-        <v>25.19215423756184</v>
+        <v>25.19215037765539</v>
       </c>
       <c r="D184" t="n">
-        <v>24.25778675528583</v>
+        <v>24.25778303854185</v>
       </c>
       <c r="E184" t="n">
-        <v>24.6780296502074</v>
+        <v>24.6780258690744</v>
       </c>
       <c r="F184" t="n">
         <v>1737600</v>
@@ -4112,16 +4112,16 @@
         <v>44368</v>
       </c>
       <c r="B185" t="n">
-        <v>25.23685836791992</v>
+        <v>25.23685646057129</v>
       </c>
       <c r="C185" t="n">
-        <v>25.64815798128789</v>
+        <v>25.6481560428541</v>
       </c>
       <c r="D185" t="n">
-        <v>24.69590929604326</v>
+        <v>24.69590742957842</v>
       </c>
       <c r="E185" t="n">
-        <v>25.25026979279315</v>
+        <v>25.25026788443091</v>
       </c>
       <c r="F185" t="n">
         <v>748400</v>
@@ -4152,16 +4152,16 @@
         <v>44370</v>
       </c>
       <c r="B187" t="n">
-        <v>24.72273254394531</v>
+        <v>24.72273445129395</v>
       </c>
       <c r="C187" t="n">
-        <v>24.87920656014071</v>
+        <v>24.87920847956124</v>
       </c>
       <c r="D187" t="n">
-        <v>24.28013846179841</v>
+        <v>24.28014033500109</v>
       </c>
       <c r="E187" t="n">
-        <v>24.71379102541241</v>
+        <v>24.71379293207121</v>
       </c>
       <c r="F187" t="n">
         <v>1264600</v>
@@ -4172,16 +4172,16 @@
         <v>44371</v>
       </c>
       <c r="B188" t="n">
-        <v>24.58414268493652</v>
+        <v>24.58414459228516</v>
       </c>
       <c r="C188" t="n">
-        <v>25.05803121795611</v>
+        <v>25.05803316207115</v>
       </c>
       <c r="D188" t="n">
-        <v>23.98060298898671</v>
+        <v>23.98060484951002</v>
       </c>
       <c r="E188" t="n">
-        <v>25.05356131150621</v>
+        <v>25.05356325527446</v>
       </c>
       <c r="F188" t="n">
         <v>1450200</v>
@@ -4192,16 +4192,16 @@
         <v>44372</v>
       </c>
       <c r="B189" t="n">
-        <v>24.3516674041748</v>
+        <v>24.35167121887207</v>
       </c>
       <c r="C189" t="n">
-        <v>24.58861166172607</v>
+        <v>24.58861551354074</v>
       </c>
       <c r="D189" t="n">
-        <v>24.00295502455915</v>
+        <v>24.0029587846305</v>
       </c>
       <c r="E189" t="n">
-        <v>24.27119544775736</v>
+        <v>24.27119924984866</v>
       </c>
       <c r="F189" t="n">
         <v>926400</v>
@@ -4232,16 +4232,16 @@
         <v>44376</v>
       </c>
       <c r="B191" t="n">
-        <v>24.49920082092285</v>
+        <v>24.49919891357422</v>
       </c>
       <c r="C191" t="n">
-        <v>24.70485064035414</v>
+        <v>24.70484871699495</v>
       </c>
       <c r="D191" t="n">
-        <v>23.49330296299373</v>
+        <v>23.49330113395778</v>
       </c>
       <c r="E191" t="n">
-        <v>24.46790635733202</v>
+        <v>24.46790445241977</v>
       </c>
       <c r="F191" t="n">
         <v>1326200</v>
@@ -4272,16 +4272,16 @@
         <v>44378</v>
       </c>
       <c r="B193" t="n">
-        <v>24.92838287353516</v>
+        <v>24.92838096618652</v>
       </c>
       <c r="C193" t="n">
-        <v>25.96557687450705</v>
+        <v>25.96557488779945</v>
       </c>
       <c r="D193" t="n">
-        <v>24.91050154151692</v>
+        <v>24.91049963553645</v>
       </c>
       <c r="E193" t="n">
-        <v>25.2592122444671</v>
+        <v>25.25921031180567</v>
       </c>
       <c r="F193" t="n">
         <v>1991200</v>
@@ -4292,16 +4292,16 @@
         <v>44379</v>
       </c>
       <c r="B194" t="n">
-        <v>26.42605400085449</v>
+        <v>26.42605209350586</v>
       </c>
       <c r="C194" t="n">
-        <v>26.7702947971231</v>
+        <v>26.77029286492826</v>
       </c>
       <c r="D194" t="n">
-        <v>25.41568455613461</v>
+        <v>25.41568272171123</v>
       </c>
       <c r="E194" t="n">
-        <v>25.41568455613461</v>
+        <v>25.41568272171123</v>
       </c>
       <c r="F194" t="n">
         <v>2268600</v>
@@ -4352,16 +4352,16 @@
         <v>44384</v>
       </c>
       <c r="B197" t="n">
-        <v>26.5244083404541</v>
+        <v>26.52440643310547</v>
       </c>
       <c r="C197" t="n">
-        <v>26.9357079587326</v>
+        <v>26.93570602180775</v>
       </c>
       <c r="D197" t="n">
-        <v>26.10863711021764</v>
+        <v>26.10863523276678</v>
       </c>
       <c r="E197" t="n">
-        <v>26.19804888433364</v>
+        <v>26.19804700045325</v>
       </c>
       <c r="F197" t="n">
         <v>915800</v>
@@ -4372,16 +4372,16 @@
         <v>44385</v>
       </c>
       <c r="B198" t="n">
-        <v>26.5244083404541</v>
+        <v>26.52440643310547</v>
       </c>
       <c r="C198" t="n">
-        <v>26.5244083404541</v>
+        <v>26.52440643310547</v>
       </c>
       <c r="D198" t="n">
-        <v>25.82251363461749</v>
+        <v>25.82251177774154</v>
       </c>
       <c r="E198" t="n">
-        <v>26.23828486485395</v>
+        <v>26.23828297808023</v>
       </c>
       <c r="F198" t="n">
         <v>1041800</v>
@@ -4392,16 +4392,16 @@
         <v>44389</v>
       </c>
       <c r="B199" t="n">
-        <v>27.5437183380127</v>
+        <v>27.54371643066406</v>
       </c>
       <c r="C199" t="n">
-        <v>27.57501280090645</v>
+        <v>27.57501089139074</v>
       </c>
       <c r="D199" t="n">
-        <v>26.56911496538337</v>
+        <v>26.56911312552412</v>
       </c>
       <c r="E199" t="n">
-        <v>26.81500076187162</v>
+        <v>26.81499890498525</v>
       </c>
       <c r="F199" t="n">
         <v>886400</v>
@@ -4432,16 +4432,16 @@
         <v>44391</v>
       </c>
       <c r="B201" t="n">
-        <v>28.17407989501953</v>
+        <v>28.17408180236816</v>
       </c>
       <c r="C201" t="n">
-        <v>28.33502381575305</v>
+        <v>28.33502573399738</v>
       </c>
       <c r="D201" t="n">
-        <v>27.44089243871817</v>
+        <v>27.44089429643097</v>
       </c>
       <c r="E201" t="n">
-        <v>27.67336680139767</v>
+        <v>27.67336867484868</v>
       </c>
       <c r="F201" t="n">
         <v>880600</v>
@@ -4472,16 +4472,16 @@
         <v>44393</v>
       </c>
       <c r="B203" t="n">
-        <v>28.7910270690918</v>
+        <v>28.79102897644043</v>
       </c>
       <c r="C203" t="n">
-        <v>29.03244291704072</v>
+        <v>29.03244484038268</v>
       </c>
       <c r="D203" t="n">
-        <v>28.15172308586781</v>
+        <v>28.15172495086382</v>
       </c>
       <c r="E203" t="n">
-        <v>28.72843815416134</v>
+        <v>28.72844005736358</v>
       </c>
       <c r="F203" t="n">
         <v>1048600</v>
@@ -4552,16 +4552,16 @@
         <v>44399</v>
       </c>
       <c r="B207" t="n">
-        <v>30.17693328857422</v>
+        <v>30.17693519592285</v>
       </c>
       <c r="C207" t="n">
-        <v>30.65082181615548</v>
+        <v>30.65082375345648</v>
       </c>
       <c r="D207" t="n">
-        <v>29.62257280245648</v>
+        <v>29.62257467476647</v>
       </c>
       <c r="E207" t="n">
-        <v>29.69410153735533</v>
+        <v>29.69410341418633</v>
       </c>
       <c r="F207" t="n">
         <v>1168200</v>
@@ -4592,16 +4592,16 @@
         <v>44403</v>
       </c>
       <c r="B209" t="n">
-        <v>30.0875244140625</v>
+        <v>30.08752059936523</v>
       </c>
       <c r="C209" t="n">
-        <v>30.48988083464328</v>
+        <v>30.48987696893258</v>
       </c>
       <c r="D209" t="n">
-        <v>29.5644549277941</v>
+        <v>29.56445117941508</v>
       </c>
       <c r="E209" t="n">
-        <v>30.48988083464328</v>
+        <v>30.48987696893258</v>
       </c>
       <c r="F209" t="n">
         <v>1240800</v>
@@ -4612,16 +4612,16 @@
         <v>44404</v>
       </c>
       <c r="B210" t="n">
-        <v>29.40797996520996</v>
+        <v>29.40798187255859</v>
       </c>
       <c r="C210" t="n">
-        <v>30.1992881310479</v>
+        <v>30.19929008971936</v>
       </c>
       <c r="D210" t="n">
-        <v>29.30068515675142</v>
+        <v>29.3006870571411</v>
       </c>
       <c r="E210" t="n">
-        <v>29.98916671513793</v>
+        <v>29.98916866018129</v>
       </c>
       <c r="F210" t="n">
         <v>1032400</v>
@@ -4632,16 +4632,16 @@
         <v>44405</v>
       </c>
       <c r="B211" t="n">
-        <v>29.43927192687988</v>
+        <v>29.43927383422852</v>
       </c>
       <c r="C211" t="n">
-        <v>30.57034745860774</v>
+        <v>30.57034943923792</v>
       </c>
       <c r="D211" t="n">
-        <v>28.7329073919184</v>
+        <v>28.7329092535022</v>
       </c>
       <c r="E211" t="n">
-        <v>29.52868710203713</v>
+        <v>29.52868901517891</v>
       </c>
       <c r="F211" t="n">
         <v>1257400</v>
@@ -4672,16 +4672,16 @@
         <v>44407</v>
       </c>
       <c r="B213" t="n">
-        <v>31.13812637329102</v>
+        <v>31.13812828063965</v>
       </c>
       <c r="C213" t="n">
-        <v>31.58072045679423</v>
+        <v>31.58072239125372</v>
       </c>
       <c r="D213" t="n">
-        <v>30.41387871868892</v>
+        <v>30.41388058167417</v>
       </c>
       <c r="E213" t="n">
-        <v>30.80282710167089</v>
+        <v>30.80282898848094</v>
       </c>
       <c r="F213" t="n">
         <v>1548200</v>
@@ -4732,16 +4732,16 @@
         <v>44412</v>
       </c>
       <c r="B216" t="n">
-        <v>29.78798675537109</v>
+        <v>29.78798484802246</v>
       </c>
       <c r="C216" t="n">
-        <v>30.84753370622673</v>
+        <v>30.84753173103446</v>
       </c>
       <c r="D216" t="n">
-        <v>29.7566922923926</v>
+        <v>29.75669038704778</v>
       </c>
       <c r="E216" t="n">
-        <v>30.62400085328306</v>
+        <v>30.62399889240378</v>
       </c>
       <c r="F216" t="n">
         <v>1263400</v>
@@ -4792,16 +4792,16 @@
         <v>44417</v>
       </c>
       <c r="B219" t="n">
-        <v>30.23952102661133</v>
+        <v>30.23952484130859</v>
       </c>
       <c r="C219" t="n">
-        <v>30.40493654902606</v>
+        <v>30.4049403845904</v>
       </c>
       <c r="D219" t="n">
-        <v>29.54209968716381</v>
+        <v>29.54210341388179</v>
       </c>
       <c r="E219" t="n">
-        <v>29.85951589706211</v>
+        <v>29.85951966382196</v>
       </c>
       <c r="F219" t="n">
         <v>1023000</v>
@@ -4812,16 +4812,16 @@
         <v>44418</v>
       </c>
       <c r="B220" t="n">
-        <v>29.59574699401855</v>
+        <v>29.59574890136719</v>
       </c>
       <c r="C220" t="n">
-        <v>30.78494335377824</v>
+        <v>30.78494533776667</v>
       </c>
       <c r="D220" t="n">
-        <v>29.59574699401855</v>
+        <v>29.59574890136719</v>
       </c>
       <c r="E220" t="n">
-        <v>30.4898783643616</v>
+        <v>30.48988032933406</v>
       </c>
       <c r="F220" t="n">
         <v>1186200</v>
@@ -4832,16 +4832,16 @@
         <v>44419</v>
       </c>
       <c r="B221" t="n">
-        <v>29.1129207611084</v>
+        <v>29.11291694641113</v>
       </c>
       <c r="C221" t="n">
-        <v>30.38258576202377</v>
+        <v>30.38258178096093</v>
       </c>
       <c r="D221" t="n">
-        <v>28.14725717378623</v>
+        <v>28.14725348562089</v>
       </c>
       <c r="E221" t="n">
-        <v>29.68516433396269</v>
+        <v>29.68516044428373</v>
       </c>
       <c r="F221" t="n">
         <v>1237750</v>
@@ -4852,16 +4852,16 @@
         <v>44420</v>
       </c>
       <c r="B222" t="n">
-        <v>29.32750511169434</v>
+        <v>29.3275089263916</v>
       </c>
       <c r="C222" t="n">
-        <v>31.18729979924009</v>
+        <v>31.1873038558452</v>
       </c>
       <c r="D222" t="n">
-        <v>28.46913990706097</v>
+        <v>28.46914361010866</v>
       </c>
       <c r="E222" t="n">
-        <v>28.48702294184585</v>
+        <v>28.48702664721963</v>
       </c>
       <c r="F222" t="n">
         <v>1567750</v>
@@ -4892,16 +4892,16 @@
         <v>44424</v>
       </c>
       <c r="B224" t="n">
-        <v>25.64369010925293</v>
+        <v>25.6436882019043</v>
       </c>
       <c r="C224" t="n">
-        <v>28.14725747247807</v>
+        <v>28.14725537891694</v>
       </c>
       <c r="D224" t="n">
-        <v>24.26672686568483</v>
+        <v>24.26672506075316</v>
       </c>
       <c r="E224" t="n">
-        <v>28.14725747247807</v>
+        <v>28.14725537891694</v>
       </c>
       <c r="F224" t="n">
         <v>6674400</v>
@@ -4912,16 +4912,16 @@
         <v>44425</v>
       </c>
       <c r="B225" t="n">
-        <v>25.66156959533691</v>
+        <v>25.66157150268555</v>
       </c>
       <c r="C225" t="n">
-        <v>25.66156959533691</v>
+        <v>25.66157150268555</v>
       </c>
       <c r="D225" t="n">
-        <v>23.42624129279607</v>
+        <v>23.42624303399936</v>
       </c>
       <c r="E225" t="n">
-        <v>24.67802480113491</v>
+        <v>24.67802663537957</v>
       </c>
       <c r="F225" t="n">
         <v>4282800</v>
@@ -5012,16 +5012,16 @@
         <v>44432</v>
       </c>
       <c r="B230" t="n">
-        <v>27.48559951782227</v>
+        <v>27.48559761047363</v>
       </c>
       <c r="C230" t="n">
-        <v>27.84325174306836</v>
+        <v>27.84324981090064</v>
       </c>
       <c r="D230" t="n">
-        <v>27.00276944009512</v>
+        <v>27.00276756625223</v>
       </c>
       <c r="E230" t="n">
-        <v>27.64654344553809</v>
+        <v>27.64654152702084</v>
       </c>
       <c r="F230" t="n">
         <v>835550</v>
@@ -5032,16 +5032,16 @@
         <v>44433</v>
       </c>
       <c r="B231" t="n">
-        <v>27.89690017700195</v>
+        <v>27.89690208435059</v>
       </c>
       <c r="C231" t="n">
-        <v>28.41549631734295</v>
+        <v>28.4154982601487</v>
       </c>
       <c r="D231" t="n">
-        <v>27.27100751898821</v>
+        <v>27.27100938354371</v>
       </c>
       <c r="E231" t="n">
-        <v>27.48559884891342</v>
+        <v>27.48560072814082</v>
       </c>
       <c r="F231" t="n">
         <v>1098800</v>
@@ -5052,16 +5052,16 @@
         <v>44434</v>
       </c>
       <c r="B232" t="n">
-        <v>27.19947624206543</v>
+        <v>27.19947814941406</v>
       </c>
       <c r="C232" t="n">
-        <v>28.21878545432528</v>
+        <v>28.21878743315242</v>
       </c>
       <c r="D232" t="n">
-        <v>26.93123751423502</v>
+        <v>26.93123940277355</v>
       </c>
       <c r="E232" t="n">
-        <v>27.80748584426262</v>
+        <v>27.8074877942476</v>
       </c>
       <c r="F232" t="n">
         <v>1359900</v>
@@ -5132,16 +5132,16 @@
         <v>44440</v>
       </c>
       <c r="B236" t="n">
-        <v>26.59146499633789</v>
+        <v>26.59146690368652</v>
       </c>
       <c r="C236" t="n">
-        <v>27.25312196212229</v>
+        <v>27.25312391693015</v>
       </c>
       <c r="D236" t="n">
-        <v>25.71521672046829</v>
+        <v>25.71521856496552</v>
       </c>
       <c r="E236" t="n">
-        <v>26.55570063070043</v>
+        <v>26.55570253548375</v>
       </c>
       <c r="F236" t="n">
         <v>1751800</v>
@@ -5192,16 +5192,16 @@
         <v>44445</v>
       </c>
       <c r="B239" t="n">
-        <v>25.76886749267578</v>
+        <v>25.76886558532715</v>
       </c>
       <c r="C239" t="n">
-        <v>25.89404534691268</v>
+        <v>25.89404343029868</v>
       </c>
       <c r="D239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="E239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="F239" t="n">
         <v>528250</v>
@@ -5212,16 +5212,16 @@
         <v>44447</v>
       </c>
       <c r="B240" t="n">
-        <v>24.48131561279297</v>
+        <v>24.4813175201416</v>
       </c>
       <c r="C240" t="n">
-        <v>26.10863610235777</v>
+        <v>26.10863813649156</v>
       </c>
       <c r="D240" t="n">
-        <v>24.32037340234477</v>
+        <v>24.32037529715434</v>
       </c>
       <c r="E240" t="n">
-        <v>25.59003998757081</v>
+        <v>25.59004198130058</v>
       </c>
       <c r="F240" t="n">
         <v>1259500</v>
@@ -5252,16 +5252,16 @@
         <v>44449</v>
       </c>
       <c r="B242" t="n">
-        <v>25.19662284851074</v>
+        <v>25.19662475585938</v>
       </c>
       <c r="C242" t="n">
-        <v>26.19804905049173</v>
+        <v>26.19805103364691</v>
       </c>
       <c r="D242" t="n">
-        <v>24.64226063620605</v>
+        <v>24.64226250159025</v>
       </c>
       <c r="E242" t="n">
-        <v>26.00134075860054</v>
+        <v>26.00134272686518</v>
       </c>
       <c r="F242" t="n">
         <v>1514650</v>
@@ -5352,16 +5352,16 @@
         <v>44456</v>
       </c>
       <c r="B247" t="n">
-        <v>24.98203277587891</v>
+        <v>24.98203086853027</v>
       </c>
       <c r="C247" t="n">
-        <v>26.00134206622641</v>
+        <v>26.00134008105472</v>
       </c>
       <c r="D247" t="n">
-        <v>24.98203277587891</v>
+        <v>24.98203086853027</v>
       </c>
       <c r="E247" t="n">
-        <v>25.64368983324662</v>
+        <v>25.64368787538125</v>
       </c>
       <c r="F247" t="n">
         <v>2806100</v>
@@ -5392,16 +5392,16 @@
         <v>44460</v>
       </c>
       <c r="B249" t="n">
-        <v>25.07144546508789</v>
+        <v>25.07144355773926</v>
       </c>
       <c r="C249" t="n">
-        <v>25.19662331630446</v>
+        <v>25.19662139943273</v>
       </c>
       <c r="D249" t="n">
-        <v>24.05213450165763</v>
+        <v>24.05213267185464</v>
       </c>
       <c r="E249" t="n">
-        <v>24.57073064938097</v>
+        <v>24.57072878012499</v>
       </c>
       <c r="F249" t="n">
         <v>662000</v>
@@ -5412,16 +5412,16 @@
         <v>44461</v>
       </c>
       <c r="B250" t="n">
-        <v>25.48274230957031</v>
+        <v>25.48274421691895</v>
       </c>
       <c r="C250" t="n">
-        <v>26.37687361867804</v>
+        <v>26.37687559295119</v>
       </c>
       <c r="D250" t="n">
-        <v>25.2323849290689</v>
+        <v>25.23238681767862</v>
       </c>
       <c r="E250" t="n">
-        <v>25.92980796412418</v>
+        <v>25.92980990493507</v>
       </c>
       <c r="F250" t="n">
         <v>900000</v>
@@ -5432,16 +5432,16 @@
         <v>44462</v>
       </c>
       <c r="B251" t="n">
-        <v>26.2874641418457</v>
+        <v>26.28746223449707</v>
       </c>
       <c r="C251" t="n">
-        <v>26.6987654933632</v>
+        <v>26.69876355617164</v>
       </c>
       <c r="D251" t="n">
-        <v>25.3218022494651</v>
+        <v>25.32180041218233</v>
       </c>
       <c r="E251" t="n">
-        <v>25.3218022494651</v>
+        <v>25.32180041218233</v>
       </c>
       <c r="F251" t="n">
         <v>1394250</v>
@@ -5492,16 +5492,16 @@
         <v>44467</v>
       </c>
       <c r="B254" t="n">
-        <v>24.83896827697754</v>
+        <v>24.83897018432617</v>
       </c>
       <c r="C254" t="n">
-        <v>25.80463001855441</v>
+        <v>25.80463200005482</v>
       </c>
       <c r="D254" t="n">
-        <v>24.44555002509952</v>
+        <v>24.44555190223813</v>
       </c>
       <c r="E254" t="n">
-        <v>25.75098091233005</v>
+        <v>25.75098288971082</v>
       </c>
       <c r="F254" t="n">
         <v>1020250</v>
@@ -5512,16 +5512,16 @@
         <v>44468</v>
       </c>
       <c r="B255" t="n">
-        <v>24.67802810668945</v>
+        <v>24.67802619934082</v>
       </c>
       <c r="C255" t="n">
-        <v>25.39333257714754</v>
+        <v>25.39333061451349</v>
       </c>
       <c r="D255" t="n">
-        <v>24.46343676555203</v>
+        <v>24.46343487478902</v>
       </c>
       <c r="E255" t="n">
-        <v>25.10721078896431</v>
+        <v>25.10720884844443</v>
       </c>
       <c r="F255" t="n">
         <v>580300</v>
@@ -5532,16 +5532,16 @@
         <v>44469</v>
       </c>
       <c r="B256" t="n">
-        <v>24.44555473327637</v>
+        <v>24.44555282592773</v>
       </c>
       <c r="C256" t="n">
-        <v>24.89262047206281</v>
+        <v>24.89261852983216</v>
       </c>
       <c r="D256" t="n">
-        <v>24.07001944447894</v>
+        <v>24.0700175664312</v>
       </c>
       <c r="E256" t="n">
-        <v>24.85685439435808</v>
+        <v>24.85685245491806</v>
       </c>
       <c r="F256" t="n">
         <v>989250</v>
@@ -5572,16 +5572,16 @@
         <v>44473</v>
       </c>
       <c r="B258" t="n">
-        <v>23.8733081817627</v>
+        <v>23.87331008911133</v>
       </c>
       <c r="C258" t="n">
-        <v>25.10720871787369</v>
+        <v>25.10721072380433</v>
       </c>
       <c r="D258" t="n">
-        <v>23.8733081817627</v>
+        <v>23.87331008911133</v>
       </c>
       <c r="E258" t="n">
-        <v>25.01779524008704</v>
+        <v>25.01779723887402</v>
       </c>
       <c r="F258" t="n">
         <v>576500</v>
@@ -5632,16 +5632,16 @@
         <v>44476</v>
       </c>
       <c r="B261" t="n">
-        <v>23.62294960021973</v>
+        <v>23.62295150756836</v>
       </c>
       <c r="C261" t="n">
-        <v>24.26672353823827</v>
+        <v>24.26672549756607</v>
       </c>
       <c r="D261" t="n">
-        <v>23.42624132329132</v>
+        <v>23.42624321475746</v>
       </c>
       <c r="E261" t="n">
-        <v>24.15942873461192</v>
+        <v>24.1594306852766</v>
       </c>
       <c r="F261" t="n">
         <v>699850</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35613822937012</v>
+        <v>24.35613632202148</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991219957796</v>
+        <v>24.99991024181488</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848602369909</v>
+        <v>23.99848414435849</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307734710171</v>
+        <v>24.21307545095629</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5732,16 +5732,16 @@
         <v>44484</v>
       </c>
       <c r="B266" t="n">
-        <v>26.16228675842285</v>
+        <v>26.16228294372559</v>
       </c>
       <c r="C266" t="n">
-        <v>26.59146945048253</v>
+        <v>26.59146557320656</v>
       </c>
       <c r="D266" t="n">
-        <v>24.44555428476369</v>
+        <v>24.44555072038149</v>
       </c>
       <c r="E266" t="n">
-        <v>24.76744215651866</v>
+        <v>24.76743854520231</v>
       </c>
       <c r="F266" t="n">
         <v>2075800</v>
@@ -5752,16 +5752,16 @@
         <v>44487</v>
       </c>
       <c r="B267" t="n">
-        <v>26.2874641418457</v>
+        <v>26.28746223449707</v>
       </c>
       <c r="C267" t="n">
-        <v>27.37830559621184</v>
+        <v>27.37830360971465</v>
       </c>
       <c r="D267" t="n">
-        <v>25.69733752458091</v>
+        <v>25.6973356600503</v>
       </c>
       <c r="E267" t="n">
-        <v>26.60935200777937</v>
+        <v>26.6093500770754</v>
       </c>
       <c r="F267" t="n">
         <v>1715900</v>
@@ -5792,16 +5792,16 @@
         <v>44489</v>
       </c>
       <c r="B269" t="n">
-        <v>23.89118957519531</v>
+        <v>23.89119148254395</v>
       </c>
       <c r="C269" t="n">
-        <v>24.94626486390061</v>
+        <v>24.94626685548099</v>
       </c>
       <c r="D269" t="n">
-        <v>23.19376819856792</v>
+        <v>23.19377005023805</v>
       </c>
       <c r="E269" t="n">
-        <v>24.85685138588114</v>
+        <v>24.8568533703232</v>
       </c>
       <c r="F269" t="n">
         <v>1327650</v>
@@ -5852,16 +5852,16 @@
         <v>44494</v>
       </c>
       <c r="B272" t="n">
-        <v>21.62009811401367</v>
+        <v>21.62009620666504</v>
       </c>
       <c r="C272" t="n">
-        <v>22.28175516339335</v>
+        <v>22.28175319767261</v>
       </c>
       <c r="D272" t="n">
-        <v>20.79749713538103</v>
+        <v>20.79749530060315</v>
       </c>
       <c r="E272" t="n">
-        <v>20.83326150553705</v>
+        <v>20.833259667604</v>
       </c>
       <c r="F272" t="n">
         <v>1833600</v>
@@ -5892,16 +5892,16 @@
         <v>44496</v>
       </c>
       <c r="B274" t="n">
-        <v>20.49348831176758</v>
+        <v>20.49349021911621</v>
       </c>
       <c r="C274" t="n">
-        <v>21.10149783444344</v>
+        <v>21.1014997983801</v>
       </c>
       <c r="D274" t="n">
-        <v>20.31466137965585</v>
+        <v>20.31466327036089</v>
       </c>
       <c r="E274" t="n">
-        <v>20.42195788000689</v>
+        <v>20.42195978069811</v>
       </c>
       <c r="F274" t="n">
         <v>1013650</v>
@@ -5992,16 +5992,16 @@
         <v>44504</v>
       </c>
       <c r="B279" t="n">
-        <v>19.97489356994629</v>
+        <v>19.97489547729492</v>
       </c>
       <c r="C279" t="n">
-        <v>21.31609053280524</v>
+        <v>21.31609256822115</v>
       </c>
       <c r="D279" t="n">
-        <v>19.58147531665669</v>
+        <v>19.58147718643888</v>
       </c>
       <c r="E279" t="n">
-        <v>20.04642400641529</v>
+        <v>20.04642592059417</v>
       </c>
       <c r="F279" t="n">
         <v>1953350</v>
@@ -6012,16 +6012,16 @@
         <v>44505</v>
       </c>
       <c r="B280" t="n">
-        <v>20.42196273803711</v>
+        <v>20.42196083068848</v>
       </c>
       <c r="C280" t="n">
-        <v>20.94055891802213</v>
+        <v>20.94055696223821</v>
       </c>
       <c r="D280" t="n">
-        <v>19.99278004537787</v>
+        <v>19.99277817811358</v>
       </c>
       <c r="E280" t="n">
-        <v>20.20737139170749</v>
+        <v>20.20736950440103</v>
       </c>
       <c r="F280" t="n">
         <v>901950</v>
@@ -6032,16 +6032,16 @@
         <v>44508</v>
       </c>
       <c r="B281" t="n">
-        <v>20.13583755493164</v>
+        <v>20.13583946228027</v>
       </c>
       <c r="C281" t="n">
-        <v>20.86902495788224</v>
+        <v>20.86902693468137</v>
       </c>
       <c r="D281" t="n">
-        <v>19.86759713808767</v>
+        <v>19.86759902002748</v>
       </c>
       <c r="E281" t="n">
-        <v>20.86902495788224</v>
+        <v>20.86902693468137</v>
       </c>
       <c r="F281" t="n">
         <v>919700</v>
@@ -6092,16 +6092,16 @@
         <v>44511</v>
       </c>
       <c r="B284" t="n">
-        <v>21.94198417663574</v>
+        <v>21.94198608398438</v>
       </c>
       <c r="C284" t="n">
-        <v>22.99705773847886</v>
+        <v>22.99705973754176</v>
       </c>
       <c r="D284" t="n">
-        <v>21.78104026055555</v>
+        <v>21.78104215391382</v>
       </c>
       <c r="E284" t="n">
-        <v>21.95986550754004</v>
+        <v>21.95986741644305</v>
       </c>
       <c r="F284" t="n">
         <v>2031350</v>
@@ -6212,16 +6212,16 @@
         <v>44522</v>
       </c>
       <c r="B290" t="n">
-        <v>20.18948554992676</v>
+        <v>20.18948745727539</v>
       </c>
       <c r="C290" t="n">
-        <v>21.44126908242115</v>
+        <v>21.44127110802875</v>
       </c>
       <c r="D290" t="n">
-        <v>19.97489423339231</v>
+        <v>19.97489612046799</v>
       </c>
       <c r="E290" t="n">
-        <v>20.86902557166261</v>
+        <v>20.869027543209</v>
       </c>
       <c r="F290" t="n">
         <v>852100</v>
@@ -6232,16 +6232,16 @@
         <v>44523</v>
       </c>
       <c r="B291" t="n">
-        <v>19.24170684814453</v>
+        <v>19.24170875549316</v>
       </c>
       <c r="C291" t="n">
-        <v>20.45772431098796</v>
+        <v>20.45772633887523</v>
       </c>
       <c r="D291" t="n">
-        <v>19.02711553117216</v>
+        <v>19.02711741724927</v>
       </c>
       <c r="E291" t="n">
-        <v>20.20736862723029</v>
+        <v>20.20737063030087</v>
       </c>
       <c r="F291" t="n">
         <v>1896750</v>
@@ -6252,16 +6252,16 @@
         <v>44524</v>
       </c>
       <c r="B292" t="n">
-        <v>19.58147621154785</v>
+        <v>19.58147811889648</v>
       </c>
       <c r="C292" t="n">
-        <v>20.33254668150708</v>
+        <v>20.3325486620143</v>
       </c>
       <c r="D292" t="n">
-        <v>19.02711572993332</v>
+        <v>19.02711758328404</v>
       </c>
       <c r="E292" t="n">
-        <v>19.04499706080266</v>
+        <v>19.04499891589514</v>
       </c>
       <c r="F292" t="n">
         <v>1594900</v>
@@ -6312,16 +6312,16 @@
         <v>44529</v>
       </c>
       <c r="B295" t="n">
-        <v>19.20594024658203</v>
+        <v>19.20594215393066</v>
       </c>
       <c r="C295" t="n">
-        <v>20.33254590870044</v>
+        <v>20.33254792793267</v>
       </c>
       <c r="D295" t="n">
-        <v>19.06287937254352</v>
+        <v>19.06288126568472</v>
       </c>
       <c r="E295" t="n">
-        <v>20.33254590870044</v>
+        <v>20.33254792793267</v>
       </c>
       <c r="F295" t="n">
         <v>830750</v>
@@ -6352,16 +6352,16 @@
         <v>44531</v>
       </c>
       <c r="B297" t="n">
-        <v>17.95415687561035</v>
+        <v>17.95415878295898</v>
       </c>
       <c r="C297" t="n">
-        <v>19.67088908188234</v>
+        <v>19.67089117160695</v>
       </c>
       <c r="D297" t="n">
-        <v>17.93627383987144</v>
+        <v>17.93627574532028</v>
       </c>
       <c r="E297" t="n">
-        <v>18.99134907258508</v>
+        <v>18.99135109011918</v>
       </c>
       <c r="F297" t="n">
         <v>1102200</v>
@@ -6412,16 +6412,16 @@
         <v>44536</v>
       </c>
       <c r="B300" t="n">
-        <v>19.97489356994629</v>
+        <v>19.97489547729492</v>
       </c>
       <c r="C300" t="n">
-        <v>20.38619315328804</v>
+        <v>20.38619509991056</v>
       </c>
       <c r="D300" t="n">
-        <v>19.56359228118441</v>
+        <v>19.56359414925899</v>
       </c>
       <c r="E300" t="n">
-        <v>20.08218837193973</v>
+        <v>20.08219028953366</v>
       </c>
       <c r="F300" t="n">
         <v>963750</v>
@@ -6492,16 +6492,16 @@
         <v>44540</v>
       </c>
       <c r="B304" t="n">
-        <v>21.81680297851562</v>
+        <v>21.81680488586426</v>
       </c>
       <c r="C304" t="n">
-        <v>22.19233818584029</v>
+        <v>22.19234012602034</v>
       </c>
       <c r="D304" t="n">
-        <v>21.06573256386629</v>
+        <v>21.06573440555209</v>
       </c>
       <c r="E304" t="n">
-        <v>22.1386907863425</v>
+        <v>22.1386927218324</v>
       </c>
       <c r="F304" t="n">
         <v>899500</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78104019165039</v>
+        <v>21.78103828430176</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422762443386</v>
+        <v>22.51422565288058</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550495712469</v>
+        <v>21.40550308266138</v>
       </c>
       <c r="E305" t="n">
-        <v>22.13869238990815</v>
+        <v>22.1386904512402</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6532,16 +6532,16 @@
         <v>44544</v>
       </c>
       <c r="B306" t="n">
-        <v>21.49492263793945</v>
+        <v>21.49491882324219</v>
       </c>
       <c r="C306" t="n">
-        <v>22.06716626709573</v>
+        <v>22.06716235084257</v>
       </c>
       <c r="D306" t="n">
-        <v>21.22668215770705</v>
+        <v>21.22667839061434</v>
       </c>
       <c r="E306" t="n">
-        <v>21.95986973391866</v>
+        <v>21.95986583670738</v>
       </c>
       <c r="F306" t="n">
         <v>979700</v>
@@ -6552,16 +6552,16 @@
         <v>44545</v>
       </c>
       <c r="B307" t="n">
-        <v>22.03139877319336</v>
+        <v>22.03139686584473</v>
       </c>
       <c r="C307" t="n">
-        <v>22.37116968525772</v>
+        <v>22.37116774849373</v>
       </c>
       <c r="D307" t="n">
-        <v>21.11938597412999</v>
+        <v>21.11938414573805</v>
       </c>
       <c r="E307" t="n">
-        <v>21.45915518077393</v>
+        <v>21.45915332296677</v>
       </c>
       <c r="F307" t="n">
         <v>1028800</v>
@@ -6572,16 +6572,16 @@
         <v>44546</v>
       </c>
       <c r="B308" t="n">
-        <v>21.94198417663574</v>
+        <v>21.94198608398438</v>
       </c>
       <c r="C308" t="n">
-        <v>22.97917640757456</v>
+        <v>22.97917840508309</v>
       </c>
       <c r="D308" t="n">
-        <v>21.53068286827299</v>
+        <v>21.53068473986848</v>
       </c>
       <c r="E308" t="n">
-        <v>22.53211073198299</v>
+        <v>22.5321126906295</v>
       </c>
       <c r="F308" t="n">
         <v>888550</v>
@@ -6692,16 +6692,16 @@
         <v>44557</v>
       </c>
       <c r="B314" t="n">
-        <v>20.92362594604492</v>
+        <v>20.92362403869629</v>
       </c>
       <c r="C314" t="n">
-        <v>21.35652812474094</v>
+        <v>21.35652617792996</v>
       </c>
       <c r="D314" t="n">
-        <v>20.58091043109365</v>
+        <v>20.58090855498616</v>
       </c>
       <c r="E314" t="n">
-        <v>21.08596297290567</v>
+        <v>21.08596105075877</v>
       </c>
       <c r="F314" t="n">
         <v>929800</v>
@@ -6712,16 +6712,16 @@
         <v>44558</v>
       </c>
       <c r="B315" t="n">
-        <v>20.76128768920898</v>
+        <v>20.76128959655762</v>
       </c>
       <c r="C315" t="n">
-        <v>21.24830222169153</v>
+        <v>21.2483041737824</v>
       </c>
       <c r="D315" t="n">
-        <v>20.58091091705966</v>
+        <v>20.58091280783701</v>
       </c>
       <c r="E315" t="n">
-        <v>20.90558841884829</v>
+        <v>20.90559033945389</v>
       </c>
       <c r="F315" t="n">
         <v>793100</v>
@@ -6752,16 +6752,16 @@
         <v>44560</v>
       </c>
       <c r="B317" t="n">
-        <v>21.06792449951172</v>
+        <v>21.06792640686035</v>
       </c>
       <c r="C317" t="n">
-        <v>21.15811115395539</v>
+        <v>21.15811306946891</v>
       </c>
       <c r="D317" t="n">
-        <v>19.93155510747982</v>
+        <v>19.93155691194919</v>
       </c>
       <c r="E317" t="n">
-        <v>20.29230688585499</v>
+        <v>20.2923087229844</v>
       </c>
       <c r="F317" t="n">
         <v>1399700</v>
@@ -6772,16 +6772,16 @@
         <v>44564</v>
       </c>
       <c r="B318" t="n">
-        <v>20.05781936645508</v>
+        <v>20.05782127380371</v>
       </c>
       <c r="C318" t="n">
-        <v>21.32045154948475</v>
+        <v>21.32045357690026</v>
       </c>
       <c r="D318" t="n">
-        <v>19.87744432327959</v>
+        <v>19.8774462134759</v>
       </c>
       <c r="E318" t="n">
-        <v>21.26633920855213</v>
+        <v>21.26634123082196</v>
       </c>
       <c r="F318" t="n">
         <v>905200</v>
@@ -6852,16 +6852,16 @@
         <v>44568</v>
       </c>
       <c r="B322" t="n">
-        <v>17.28002738952637</v>
+        <v>17.280029296875</v>
       </c>
       <c r="C322" t="n">
-        <v>17.53255450710743</v>
+        <v>17.5325564423297</v>
       </c>
       <c r="D322" t="n">
-        <v>16.9012375732549</v>
+        <v>16.90123943879317</v>
       </c>
       <c r="E322" t="n">
-        <v>17.47844044749704</v>
+        <v>17.47844237674627</v>
       </c>
       <c r="F322" t="n">
         <v>932550</v>
@@ -6872,16 +6872,16 @@
         <v>44571</v>
       </c>
       <c r="B323" t="n">
-        <v>16.360107421875</v>
+        <v>16.36010932922363</v>
       </c>
       <c r="C323" t="n">
-        <v>17.13572499859104</v>
+        <v>17.13572699636531</v>
       </c>
       <c r="D323" t="n">
-        <v>16.10758204913961</v>
+        <v>16.10758392704749</v>
       </c>
       <c r="E323" t="n">
-        <v>17.11768698048135</v>
+        <v>17.11768897615265</v>
       </c>
       <c r="F323" t="n">
         <v>1820150</v>
@@ -6912,16 +6912,16 @@
         <v>44573</v>
       </c>
       <c r="B325" t="n">
-        <v>17.53255653381348</v>
+        <v>17.53255462646484</v>
       </c>
       <c r="C325" t="n">
-        <v>17.69489529100997</v>
+        <v>17.69489336600067</v>
       </c>
       <c r="D325" t="n">
-        <v>16.7028264460762</v>
+        <v>16.70282462899304</v>
       </c>
       <c r="E325" t="n">
-        <v>16.86516520327269</v>
+        <v>16.86516336852887</v>
       </c>
       <c r="F325" t="n">
         <v>1172500</v>
@@ -6932,16 +6932,16 @@
         <v>44574</v>
       </c>
       <c r="B326" t="n">
-        <v>16.64871406555176</v>
+        <v>16.64871215820312</v>
       </c>
       <c r="C326" t="n">
-        <v>17.62274670733157</v>
+        <v>17.62274468839355</v>
       </c>
       <c r="D326" t="n">
-        <v>16.5765636906274</v>
+        <v>16.57656179154462</v>
       </c>
       <c r="E326" t="n">
-        <v>17.58667065976908</v>
+        <v>17.58666864496408</v>
       </c>
       <c r="F326" t="n">
         <v>921200</v>
@@ -6992,16 +6992,16 @@
         <v>44579</v>
       </c>
       <c r="B329" t="n">
-        <v>16.30599784851074</v>
+        <v>16.30599594116211</v>
       </c>
       <c r="C329" t="n">
-        <v>16.79301409872861</v>
+        <v>16.79301213441261</v>
       </c>
       <c r="D329" t="n">
-        <v>16.07150873398366</v>
+        <v>16.07150685406374</v>
       </c>
       <c r="E329" t="n">
-        <v>16.73890003523749</v>
+        <v>16.73889807725132</v>
       </c>
       <c r="F329" t="n">
         <v>670850</v>
@@ -7012,16 +7012,16 @@
         <v>44580</v>
       </c>
       <c r="B330" t="n">
-        <v>16.41422653198242</v>
+        <v>16.41422462463379</v>
       </c>
       <c r="C330" t="n">
-        <v>16.72086605349554</v>
+        <v>16.72086411051511</v>
       </c>
       <c r="D330" t="n">
-        <v>16.19777368839618</v>
+        <v>16.19777180619957</v>
       </c>
       <c r="E330" t="n">
-        <v>16.41422653198242</v>
+        <v>16.41422462463379</v>
       </c>
       <c r="F330" t="n">
         <v>847250</v>
@@ -7132,16 +7132,16 @@
         <v>44588</v>
       </c>
       <c r="B336" t="n">
-        <v>19.3363151550293</v>
+        <v>19.33631706237793</v>
       </c>
       <c r="C336" t="n">
-        <v>19.91351802765098</v>
+        <v>19.91351999193534</v>
       </c>
       <c r="D336" t="n">
-        <v>19.08378803815718</v>
+        <v>19.08378992059635</v>
       </c>
       <c r="E336" t="n">
-        <v>19.64295461115963</v>
+        <v>19.64295654875541</v>
       </c>
       <c r="F336" t="n">
         <v>815000</v>
@@ -7152,16 +7152,16 @@
         <v>44589</v>
       </c>
       <c r="B337" t="n">
-        <v>19.67903137207031</v>
+        <v>19.67902946472168</v>
       </c>
       <c r="C337" t="n">
-        <v>19.67903137207031</v>
+        <v>19.67902946472168</v>
       </c>
       <c r="D337" t="n">
-        <v>18.84930127963634</v>
+        <v>18.84929945270756</v>
       </c>
       <c r="E337" t="n">
-        <v>19.30024150986784</v>
+        <v>19.30023963923261</v>
       </c>
       <c r="F337" t="n">
         <v>645650</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96763038635254</v>
+        <v>19.96762847900391</v>
       </c>
       <c r="C338" t="n">
-        <v>20.27426984278146</v>
+        <v>20.274267906142</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44453985247972</v>
+        <v>19.44453799509775</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706696959773</v>
+        <v>19.69706508809386</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7192,16 +7192,16 @@
         <v>44593</v>
       </c>
       <c r="B339" t="n">
-        <v>20.05781936645508</v>
+        <v>20.05782127380371</v>
       </c>
       <c r="C339" t="n">
-        <v>20.38249685245139</v>
+        <v>20.38249879067443</v>
       </c>
       <c r="D339" t="n">
-        <v>19.75117990083641</v>
+        <v>19.75118177902592</v>
       </c>
       <c r="E339" t="n">
-        <v>20.29230847076349</v>
+        <v>20.29231040041029</v>
       </c>
       <c r="F339" t="n">
         <v>629350</v>
@@ -7212,16 +7212,16 @@
         <v>44594</v>
       </c>
       <c r="B340" t="n">
-        <v>20.22015762329102</v>
+        <v>20.22015953063965</v>
       </c>
       <c r="C340" t="n">
-        <v>20.86951085947065</v>
+        <v>20.86951282807217</v>
       </c>
       <c r="D340" t="n">
-        <v>19.85940582541344</v>
+        <v>19.85940769873269</v>
       </c>
       <c r="E340" t="n">
-        <v>20.25623194297864</v>
+        <v>20.25623385373013</v>
       </c>
       <c r="F340" t="n">
         <v>1270900</v>
@@ -7292,16 +7292,16 @@
         <v>44600</v>
       </c>
       <c r="B344" t="n">
-        <v>19.46257972717285</v>
+        <v>19.46257781982422</v>
       </c>
       <c r="C344" t="n">
-        <v>20.03978265536617</v>
+        <v>20.03978069145118</v>
       </c>
       <c r="D344" t="n">
-        <v>19.40846738270483</v>
+        <v>19.40846548065925</v>
       </c>
       <c r="E344" t="n">
-        <v>19.6609928036892</v>
+        <v>19.66099087689592</v>
       </c>
       <c r="F344" t="n">
         <v>697700</v>
@@ -7312,16 +7312,16 @@
         <v>44601</v>
       </c>
       <c r="B345" t="n">
-        <v>19.91351890563965</v>
+        <v>19.91352081298828</v>
       </c>
       <c r="C345" t="n">
-        <v>20.18408233406016</v>
+        <v>20.18408426732379</v>
       </c>
       <c r="D345" t="n">
-        <v>19.42650439044265</v>
+        <v>19.42650625114426</v>
       </c>
       <c r="E345" t="n">
-        <v>19.48061673208669</v>
+        <v>19.48061859797126</v>
       </c>
       <c r="F345" t="n">
         <v>427500</v>
@@ -7372,16 +7372,16 @@
         <v>44606</v>
       </c>
       <c r="B348" t="n">
-        <v>20.00370788574219</v>
+        <v>20.00370597839355</v>
       </c>
       <c r="C348" t="n">
-        <v>20.14800861456807</v>
+        <v>20.1480066934604</v>
       </c>
       <c r="D348" t="n">
-        <v>19.26416622045944</v>
+        <v>19.26416438362593</v>
       </c>
       <c r="E348" t="n">
-        <v>19.26416622045944</v>
+        <v>19.26416438362593</v>
       </c>
       <c r="F348" t="n">
         <v>683300</v>
@@ -7392,16 +7392,16 @@
         <v>44607</v>
       </c>
       <c r="B349" t="n">
-        <v>20.52680015563965</v>
+        <v>20.52679824829102</v>
       </c>
       <c r="C349" t="n">
-        <v>20.70717522149135</v>
+        <v>20.70717329738229</v>
       </c>
       <c r="D349" t="n">
-        <v>20.11193423579974</v>
+        <v>20.11193236700041</v>
       </c>
       <c r="E349" t="n">
-        <v>20.20212262882585</v>
+        <v>20.20212075164623</v>
       </c>
       <c r="F349" t="n">
         <v>560950</v>
@@ -7412,16 +7412,16 @@
         <v>44608</v>
       </c>
       <c r="B350" t="n">
-        <v>20.74324798583984</v>
+        <v>20.74324989318848</v>
       </c>
       <c r="C350" t="n">
-        <v>20.76128600563211</v>
+        <v>20.76128791463935</v>
       </c>
       <c r="D350" t="n">
-        <v>20.27426979244236</v>
+        <v>20.27427165666829</v>
       </c>
       <c r="E350" t="n">
-        <v>20.74324798583984</v>
+        <v>20.74324989318848</v>
       </c>
       <c r="F350" t="n">
         <v>576900</v>
@@ -7432,16 +7432,16 @@
         <v>44609</v>
       </c>
       <c r="B351" t="n">
-        <v>20.05781936645508</v>
+        <v>20.05782127380371</v>
       </c>
       <c r="C351" t="n">
-        <v>20.72521063862504</v>
+        <v>20.72521260943759</v>
       </c>
       <c r="D351" t="n">
-        <v>20.05781936645508</v>
+        <v>20.05782127380371</v>
       </c>
       <c r="E351" t="n">
-        <v>20.72521063862504</v>
+        <v>20.72521260943759</v>
       </c>
       <c r="F351" t="n">
         <v>544250</v>
@@ -7452,16 +7452,16 @@
         <v>44610</v>
       </c>
       <c r="B352" t="n">
-        <v>19.93155670166016</v>
+        <v>19.93155860900879</v>
       </c>
       <c r="C352" t="n">
-        <v>20.50875959322669</v>
+        <v>20.5087615558107</v>
       </c>
       <c r="D352" t="n">
-        <v>19.64295525587689</v>
+        <v>19.64295713560783</v>
       </c>
       <c r="E352" t="n">
-        <v>20.47268527260393</v>
+        <v>20.47268723173582</v>
       </c>
       <c r="F352" t="n">
         <v>904300</v>
@@ -7472,16 +7472,16 @@
         <v>44613</v>
       </c>
       <c r="B353" t="n">
-        <v>18.66892242431641</v>
+        <v>18.66892433166504</v>
       </c>
       <c r="C353" t="n">
-        <v>19.94959248662468</v>
+        <v>19.94959452481559</v>
       </c>
       <c r="D353" t="n">
-        <v>18.66892242431641</v>
+        <v>18.66892433166504</v>
       </c>
       <c r="E353" t="n">
-        <v>19.85940411487337</v>
+        <v>19.85940614385</v>
       </c>
       <c r="F353" t="n">
         <v>728950</v>
@@ -7512,16 +7512,16 @@
         <v>44615</v>
       </c>
       <c r="B355" t="n">
-        <v>19.66098976135254</v>
+        <v>19.6609935760498</v>
       </c>
       <c r="C355" t="n">
-        <v>20.49071970233843</v>
+        <v>20.49072367802294</v>
       </c>
       <c r="D355" t="n">
-        <v>19.55276508916316</v>
+        <v>19.55276888286228</v>
       </c>
       <c r="E355" t="n">
-        <v>19.85940452736665</v>
+        <v>19.85940838056108</v>
       </c>
       <c r="F355" t="n">
         <v>1327750</v>
@@ -7532,16 +7532,16 @@
         <v>44616</v>
       </c>
       <c r="B356" t="n">
-        <v>19.3363151550293</v>
+        <v>19.33631706237793</v>
       </c>
       <c r="C356" t="n">
-        <v>19.4265035339265</v>
+        <v>19.42650545017138</v>
       </c>
       <c r="D356" t="n">
-        <v>18.27209606848287</v>
+        <v>18.27209787085614</v>
       </c>
       <c r="E356" t="n">
-        <v>18.52462318535499</v>
+        <v>18.52462501263771</v>
       </c>
       <c r="F356" t="n">
         <v>1831750</v>
@@ -7572,16 +7572,16 @@
         <v>44622</v>
       </c>
       <c r="B358" t="n">
-        <v>18.83126258850098</v>
+        <v>18.83126068115234</v>
       </c>
       <c r="C358" t="n">
-        <v>18.90341295396648</v>
+        <v>18.90341103931001</v>
       </c>
       <c r="D358" t="n">
-        <v>18.23602164336046</v>
+        <v>18.23601979630157</v>
       </c>
       <c r="E358" t="n">
-        <v>18.74107592181939</v>
+        <v>18.74107402360544</v>
       </c>
       <c r="F358" t="n">
         <v>1044650</v>
@@ -7592,16 +7592,16 @@
         <v>44623</v>
       </c>
       <c r="B359" t="n">
-        <v>18.5787353515625</v>
+        <v>18.57873344421387</v>
       </c>
       <c r="C359" t="n">
-        <v>19.46257767208202</v>
+        <v>19.46257567399548</v>
       </c>
       <c r="D359" t="n">
-        <v>18.54265931225955</v>
+        <v>18.54265740861459</v>
       </c>
       <c r="E359" t="n">
-        <v>18.72303606837384</v>
+        <v>18.72303414621086</v>
       </c>
       <c r="F359" t="n">
         <v>930450</v>
@@ -7672,16 +7672,16 @@
         <v>44629</v>
       </c>
       <c r="B363" t="n">
-        <v>18.23602104187012</v>
+        <v>18.23602294921875</v>
       </c>
       <c r="C363" t="n">
-        <v>18.36228546742039</v>
+        <v>18.36228738797532</v>
       </c>
       <c r="D363" t="n">
-        <v>17.51451741101287</v>
+        <v>17.51451924289774</v>
       </c>
       <c r="E363" t="n">
-        <v>17.53255543183439</v>
+        <v>17.5325572656059</v>
       </c>
       <c r="F363" t="n">
         <v>713800</v>
@@ -7712,16 +7712,16 @@
         <v>44631</v>
       </c>
       <c r="B365" t="n">
-        <v>17.22591781616211</v>
+        <v>17.22591590881348</v>
       </c>
       <c r="C365" t="n">
-        <v>18.45247412088051</v>
+        <v>18.4524720777208</v>
       </c>
       <c r="D365" t="n">
-        <v>17.02750300613079</v>
+        <v>17.02750112075174</v>
       </c>
       <c r="E365" t="n">
-        <v>18.30817337914893</v>
+        <v>18.30817135196699</v>
       </c>
       <c r="F365" t="n">
         <v>837400</v>
@@ -7732,16 +7732,16 @@
         <v>44634</v>
       </c>
       <c r="B366" t="n">
-        <v>17.31610488891602</v>
+        <v>17.31610679626465</v>
       </c>
       <c r="C366" t="n">
-        <v>17.67685671572668</v>
+        <v>17.67685866281171</v>
       </c>
       <c r="D366" t="n">
-        <v>16.88320097654281</v>
+        <v>16.88320283620759</v>
       </c>
       <c r="E366" t="n">
-        <v>17.35217921149688</v>
+        <v>17.35218112281906</v>
       </c>
       <c r="F366" t="n">
         <v>989600</v>
@@ -7752,16 +7752,16 @@
         <v>44635</v>
       </c>
       <c r="B367" t="n">
-        <v>17.46040725708008</v>
+        <v>17.46040534973145</v>
       </c>
       <c r="C367" t="n">
-        <v>17.56863195517241</v>
+        <v>17.56863003600147</v>
       </c>
       <c r="D367" t="n">
-        <v>16.93731662909899</v>
+        <v>16.93731477889199</v>
       </c>
       <c r="E367" t="n">
-        <v>17.04554132719132</v>
+        <v>17.04553946516202</v>
       </c>
       <c r="F367" t="n">
         <v>763850</v>
@@ -7772,16 +7772,16 @@
         <v>44636</v>
       </c>
       <c r="B368" t="n">
-        <v>17.53255653381348</v>
+        <v>17.53255462646484</v>
       </c>
       <c r="C368" t="n">
-        <v>18.10975947477838</v>
+        <v>18.10975750463644</v>
       </c>
       <c r="D368" t="n">
-        <v>17.15376667375514</v>
+        <v>17.15376480761467</v>
       </c>
       <c r="E368" t="n">
-        <v>17.58666887947882</v>
+        <v>17.58666696624336</v>
       </c>
       <c r="F368" t="n">
         <v>1212700</v>
@@ -7792,16 +7792,16 @@
         <v>44637</v>
       </c>
       <c r="B369" t="n">
-        <v>18.16387176513672</v>
+        <v>18.16387367248535</v>
       </c>
       <c r="C369" t="n">
-        <v>18.30817249993856</v>
+        <v>18.3081744224399</v>
       </c>
       <c r="D369" t="n">
-        <v>17.17180464342414</v>
+        <v>17.17180644659796</v>
       </c>
       <c r="E369" t="n">
-        <v>17.56863080402899</v>
+        <v>17.56863264887267</v>
       </c>
       <c r="F369" t="n">
         <v>935650</v>
@@ -7932,16 +7932,16 @@
         <v>44648</v>
       </c>
       <c r="B376" t="n">
-        <v>21.3384895324707</v>
+        <v>21.33849143981934</v>
       </c>
       <c r="C376" t="n">
-        <v>22.11410720534708</v>
+        <v>22.11410918202458</v>
       </c>
       <c r="D376" t="n">
-        <v>21.08596240822715</v>
+        <v>21.08596429300356</v>
       </c>
       <c r="E376" t="n">
-        <v>21.55494061602219</v>
+        <v>21.55494254271838</v>
       </c>
       <c r="F376" t="n">
         <v>980450</v>
@@ -7952,16 +7952,16 @@
         <v>44649</v>
       </c>
       <c r="B377" t="n">
-        <v>21.91569137573242</v>
+        <v>21.91569328308105</v>
       </c>
       <c r="C377" t="n">
-        <v>22.36663154165449</v>
+        <v>22.36663348824898</v>
       </c>
       <c r="D377" t="n">
-        <v>21.6631659837442</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="E377" t="n">
-        <v>21.6631659837442</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="F377" t="n">
         <v>1103500</v>
@@ -7972,16 +7972,16 @@
         <v>44650</v>
       </c>
       <c r="B378" t="n">
-        <v>21.41064071655273</v>
+        <v>21.4106388092041</v>
       </c>
       <c r="C378" t="n">
-        <v>22.02391967028623</v>
+        <v>22.02391770830417</v>
       </c>
       <c r="D378" t="n">
-        <v>21.28437800967832</v>
+        <v>21.28437611357769</v>
       </c>
       <c r="E378" t="n">
-        <v>21.93373128529007</v>
+        <v>21.93372933134236</v>
       </c>
       <c r="F378" t="n">
         <v>851150</v>
@@ -8012,16 +8012,16 @@
         <v>44652</v>
       </c>
       <c r="B380" t="n">
-        <v>21.7894287109375</v>
+        <v>21.78943061828613</v>
       </c>
       <c r="C380" t="n">
-        <v>21.84354104926957</v>
+        <v>21.84354296135495</v>
       </c>
       <c r="D380" t="n">
-        <v>21.17614980917333</v>
+        <v>21.17615166283828</v>
       </c>
       <c r="E380" t="n">
-        <v>21.42867692172335</v>
+        <v>21.42867879749339</v>
       </c>
       <c r="F380" t="n">
         <v>746250</v>
@@ -8032,16 +8032,16 @@
         <v>44655</v>
       </c>
       <c r="B381" t="n">
-        <v>21.89765739440918</v>
+        <v>21.89765930175781</v>
       </c>
       <c r="C381" t="n">
-        <v>21.91569369560312</v>
+        <v>21.91569560452276</v>
       </c>
       <c r="D381" t="n">
-        <v>21.32045275119318</v>
+        <v>21.32045460826564</v>
       </c>
       <c r="E381" t="n">
-        <v>21.78943098624356</v>
+        <v>21.78943288416536</v>
       </c>
       <c r="F381" t="n">
         <v>503500</v>
@@ -8092,16 +8092,16 @@
         <v>44658</v>
       </c>
       <c r="B384" t="n">
-        <v>19.66098976135254</v>
+        <v>19.6609935760498</v>
       </c>
       <c r="C384" t="n">
-        <v>20.00370523708592</v>
+        <v>20.0037091182781</v>
       </c>
       <c r="D384" t="n">
-        <v>19.55276508916316</v>
+        <v>19.55276888286228</v>
       </c>
       <c r="E384" t="n">
-        <v>19.85940452736665</v>
+        <v>19.85940838056108</v>
       </c>
       <c r="F384" t="n">
         <v>978600</v>
@@ -8112,16 +8112,16 @@
         <v>44659</v>
       </c>
       <c r="B385" t="n">
-        <v>19.39042854309082</v>
+        <v>19.39042663574219</v>
       </c>
       <c r="C385" t="n">
-        <v>19.60687963203151</v>
+        <v>19.60687770339157</v>
       </c>
       <c r="D385" t="n">
-        <v>19.01163870739452</v>
+        <v>19.01163683730573</v>
       </c>
       <c r="E385" t="n">
-        <v>19.57080531064157</v>
+        <v>19.57080338555009</v>
       </c>
       <c r="F385" t="n">
         <v>914050</v>
@@ -8232,16 +8232,16 @@
         <v>44670</v>
       </c>
       <c r="B391" t="n">
-        <v>20.32838249206543</v>
+        <v>20.32838439941406</v>
       </c>
       <c r="C391" t="n">
-        <v>20.34641879045101</v>
+        <v>20.34642069949194</v>
       </c>
       <c r="D391" t="n">
-        <v>19.01163637871046</v>
+        <v>19.01163816251292</v>
       </c>
       <c r="E391" t="n">
-        <v>19.55276489488099</v>
+        <v>19.55276672945585</v>
       </c>
       <c r="F391" t="n">
         <v>1459950</v>
@@ -8292,16 +8292,16 @@
         <v>44676</v>
       </c>
       <c r="B394" t="n">
-        <v>19.30023956298828</v>
+        <v>19.30024147033691</v>
       </c>
       <c r="C394" t="n">
-        <v>19.57080470595465</v>
+        <v>19.57080664004192</v>
       </c>
       <c r="D394" t="n">
-        <v>18.61481027575389</v>
+        <v>18.61481211536489</v>
       </c>
       <c r="E394" t="n">
-        <v>19.28220154275046</v>
+        <v>19.28220344831649</v>
       </c>
       <c r="F394" t="n">
         <v>1378800</v>
@@ -8352,16 +8352,16 @@
         <v>44679</v>
       </c>
       <c r="B397" t="n">
-        <v>21.04988861083984</v>
+        <v>21.04989051818848</v>
       </c>
       <c r="C397" t="n">
-        <v>21.10400095302237</v>
+        <v>21.10400286527417</v>
       </c>
       <c r="D397" t="n">
-        <v>19.30024015840165</v>
+        <v>19.30024190721312</v>
       </c>
       <c r="E397" t="n">
-        <v>19.84136874082794</v>
+        <v>19.84137053867153</v>
       </c>
       <c r="F397" t="n">
         <v>1501350</v>
@@ -8372,16 +8372,16 @@
         <v>44680</v>
       </c>
       <c r="B398" t="n">
-        <v>21.04988861083984</v>
+        <v>21.04989051818848</v>
       </c>
       <c r="C398" t="n">
-        <v>21.60905349386008</v>
+        <v>21.60905545187512</v>
       </c>
       <c r="D398" t="n">
-        <v>20.90558788488621</v>
+        <v>20.90558977915963</v>
       </c>
       <c r="E398" t="n">
-        <v>21.60905349386008</v>
+        <v>21.60905545187512</v>
       </c>
       <c r="F398" t="n">
         <v>1651000</v>
@@ -8432,16 +8432,16 @@
         <v>44685</v>
       </c>
       <c r="B401" t="n">
-        <v>20.47268486022949</v>
+        <v>20.47268676757812</v>
       </c>
       <c r="C401" t="n">
-        <v>20.56287152006993</v>
+        <v>20.56287343582085</v>
       </c>
       <c r="D401" t="n">
-        <v>19.17397666016394</v>
+        <v>19.17397844651773</v>
       </c>
       <c r="E401" t="n">
-        <v>19.84136792014478</v>
+        <v>19.84136976867643</v>
       </c>
       <c r="F401" t="n">
         <v>1413100</v>
@@ -8452,16 +8452,16 @@
         <v>44686</v>
       </c>
       <c r="B402" t="n">
-        <v>20.09389305114746</v>
+        <v>20.09389495849609</v>
       </c>
       <c r="C402" t="n">
-        <v>20.47268283366227</v>
+        <v>20.47268477696631</v>
       </c>
       <c r="D402" t="n">
-        <v>19.73313956669518</v>
+        <v>19.73314143980044</v>
       </c>
       <c r="E402" t="n">
-        <v>20.41856877887437</v>
+        <v>20.41857071704181</v>
       </c>
       <c r="F402" t="n">
         <v>1134600</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.5190315246582</v>
+        <v>19.51902961730957</v>
       </c>
       <c r="C403" t="n">
-        <v>19.9347326068735</v>
+        <v>19.93473065890365</v>
       </c>
       <c r="D403" t="n">
-        <v>18.81989895121317</v>
+        <v>18.81989711218194</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019522691586</v>
+        <v>19.67019330479591</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8492,16 +8492,16 @@
         <v>44690</v>
       </c>
       <c r="B404" t="n">
-        <v>18.78210830688477</v>
+        <v>18.7821102142334</v>
       </c>
       <c r="C404" t="n">
-        <v>19.53792866776176</v>
+        <v>19.53793065186498</v>
       </c>
       <c r="D404" t="n">
-        <v>18.38530311297808</v>
+        <v>18.38530498003061</v>
       </c>
       <c r="E404" t="n">
-        <v>19.25449535667779</v>
+        <v>19.25449731199797</v>
       </c>
       <c r="F404" t="n">
         <v>2367350</v>
@@ -8512,16 +8512,16 @@
         <v>44691</v>
       </c>
       <c r="B405" t="n">
-        <v>19.1600170135498</v>
+        <v>19.16001892089844</v>
       </c>
       <c r="C405" t="n">
-        <v>19.38676255310495</v>
+        <v>19.38676448302573</v>
       </c>
       <c r="D405" t="n">
-        <v>18.6120481757882</v>
+        <v>18.61205002858743</v>
       </c>
       <c r="E405" t="n">
-        <v>19.04664334276555</v>
+        <v>19.04664523882802</v>
       </c>
       <c r="F405" t="n">
         <v>1243050</v>
@@ -8552,16 +8552,16 @@
         <v>44693</v>
       </c>
       <c r="B407" t="n">
-        <v>19.33007431030273</v>
+        <v>19.33007621765137</v>
       </c>
       <c r="C407" t="n">
-        <v>19.7079853350076</v>
+        <v>19.7079872796457</v>
       </c>
       <c r="D407" t="n">
-        <v>18.81989731017247</v>
+        <v>18.81989916718061</v>
       </c>
       <c r="E407" t="n">
-        <v>18.93327097798659</v>
+        <v>18.93327284618161</v>
       </c>
       <c r="F407" t="n">
         <v>1412250</v>
@@ -8632,16 +8632,16 @@
         <v>44699</v>
       </c>
       <c r="B411" t="n">
-        <v>20.36932754516602</v>
+        <v>20.36932563781738</v>
       </c>
       <c r="C411" t="n">
-        <v>20.76613270912441</v>
+        <v>20.76613076461962</v>
       </c>
       <c r="D411" t="n">
-        <v>20.10479197053606</v>
+        <v>20.10479008795808</v>
       </c>
       <c r="E411" t="n">
-        <v>20.44490939534792</v>
+        <v>20.44490748092194</v>
       </c>
       <c r="F411" t="n">
         <v>1338150</v>
@@ -8692,16 +8692,16 @@
         <v>44704</v>
       </c>
       <c r="B414" t="n">
-        <v>20.82282257080078</v>
+        <v>20.82282066345215</v>
       </c>
       <c r="C414" t="n">
-        <v>21.1629400302818</v>
+        <v>21.16293809177876</v>
       </c>
       <c r="D414" t="n">
-        <v>20.61497111010355</v>
+        <v>20.61496922179389</v>
       </c>
       <c r="E414" t="n">
-        <v>20.78503074085087</v>
+        <v>20.78502883696393</v>
       </c>
       <c r="F414" t="n">
         <v>1655200</v>
@@ -8712,16 +8712,16 @@
         <v>44705</v>
       </c>
       <c r="B415" t="n">
-        <v>20.38822364807129</v>
+        <v>20.38822555541992</v>
       </c>
       <c r="C415" t="n">
-        <v>20.78502881572475</v>
+        <v>20.7850307601951</v>
       </c>
       <c r="D415" t="n">
-        <v>19.93473254275689</v>
+        <v>19.93473440768075</v>
       </c>
       <c r="E415" t="n">
-        <v>20.59607328750369</v>
+        <v>20.59607521429696</v>
       </c>
       <c r="F415" t="n">
         <v>1381900</v>
@@ -8892,16 +8892,16 @@
         <v>44718</v>
       </c>
       <c r="B424" t="n">
-        <v>22.03212738037109</v>
+        <v>22.03212928771973</v>
       </c>
       <c r="C424" t="n">
-        <v>22.63678210852805</v>
+        <v>22.63678406822239</v>
       </c>
       <c r="D424" t="n">
-        <v>21.52195040399197</v>
+        <v>21.52195226717395</v>
       </c>
       <c r="E424" t="n">
-        <v>22.52341024800523</v>
+        <v>22.52341219788483</v>
       </c>
       <c r="F424" t="n">
         <v>1535250</v>
@@ -8912,16 +8912,16 @@
         <v>44719</v>
       </c>
       <c r="B425" t="n">
-        <v>21.5975341796875</v>
+        <v>21.59753608703613</v>
       </c>
       <c r="C425" t="n">
-        <v>21.93765159373639</v>
+        <v>21.93765353112191</v>
       </c>
       <c r="D425" t="n">
-        <v>21.25741496362521</v>
+        <v>21.25741684093681</v>
       </c>
       <c r="E425" t="n">
-        <v>21.72980196281688</v>
+        <v>21.72980388184651</v>
       </c>
       <c r="F425" t="n">
         <v>1412350</v>
@@ -8992,16 +8992,16 @@
         <v>44725</v>
       </c>
       <c r="B429" t="n">
-        <v>19.25449562072754</v>
+        <v>19.25449371337891</v>
       </c>
       <c r="C429" t="n">
-        <v>20.0103159919696</v>
+        <v>20.01031400974947</v>
       </c>
       <c r="D429" t="n">
-        <v>18.98996002250438</v>
+        <v>18.98995814136063</v>
       </c>
       <c r="E429" t="n">
-        <v>19.95363004978087</v>
+        <v>19.95362807317604</v>
       </c>
       <c r="F429" t="n">
         <v>2646600</v>
@@ -9012,16 +9012,16 @@
         <v>44726</v>
       </c>
       <c r="B430" t="n">
-        <v>19.12222480773926</v>
+        <v>19.12222671508789</v>
       </c>
       <c r="C430" t="n">
-        <v>19.51902994454667</v>
+        <v>19.51903189147468</v>
       </c>
       <c r="D430" t="n">
-        <v>18.89547927270836</v>
+        <v>18.89548115744023</v>
       </c>
       <c r="E430" t="n">
-        <v>19.51902994454667</v>
+        <v>19.51903189147468</v>
       </c>
       <c r="F430" t="n">
         <v>1027150</v>
@@ -9172,16 +9172,16 @@
         <v>44739</v>
       </c>
       <c r="B438" t="n">
-        <v>18.55536079406738</v>
+        <v>18.55536270141602</v>
       </c>
       <c r="C438" t="n">
-        <v>18.70652448999358</v>
+        <v>18.70652641288067</v>
       </c>
       <c r="D438" t="n">
-        <v>18.38530118564707</v>
+        <v>18.38530307551488</v>
       </c>
       <c r="E438" t="n">
-        <v>18.57425670656151</v>
+        <v>18.57425861585249</v>
       </c>
       <c r="F438" t="n">
         <v>799000</v>
@@ -9352,16 +9352,16 @@
         <v>44750</v>
       </c>
       <c r="B447" t="n">
-        <v>17.72396087646484</v>
+        <v>17.72396278381348</v>
       </c>
       <c r="C447" t="n">
-        <v>18.12076603795336</v>
+        <v>18.12076798800384</v>
       </c>
       <c r="D447" t="n">
-        <v>17.64837902675339</v>
+        <v>17.64838092596834</v>
       </c>
       <c r="E447" t="n">
-        <v>17.81843863910753</v>
+        <v>17.8184405566233</v>
       </c>
       <c r="F447" t="n">
         <v>701700</v>
@@ -9412,16 +9412,16 @@
         <v>44755</v>
       </c>
       <c r="B450" t="n">
-        <v>16.87366485595703</v>
+        <v>16.87366676330566</v>
       </c>
       <c r="C450" t="n">
-        <v>17.02482855752328</v>
+        <v>17.024830481959</v>
       </c>
       <c r="D450" t="n">
-        <v>16.3445900984617</v>
+        <v>16.3445919460053</v>
       </c>
       <c r="E450" t="n">
-        <v>16.51464971322709</v>
+        <v>16.51465157999372</v>
       </c>
       <c r="F450" t="n">
         <v>919750</v>
@@ -9472,16 +9472,16 @@
         <v>44760</v>
       </c>
       <c r="B453" t="n">
-        <v>16.94924736022949</v>
+        <v>16.94924926757812</v>
       </c>
       <c r="C453" t="n">
-        <v>17.34605254264335</v>
+        <v>17.34605449464563</v>
       </c>
       <c r="D453" t="n">
-        <v>16.74139591105195</v>
+        <v>16.74139779501045</v>
       </c>
       <c r="E453" t="n">
-        <v>16.74139591105195</v>
+        <v>16.74139779501045</v>
       </c>
       <c r="F453" t="n">
         <v>809650</v>
@@ -9512,16 +9512,16 @@
         <v>44762</v>
       </c>
       <c r="B455" t="n">
-        <v>17.96960258483887</v>
+        <v>17.9696044921875</v>
       </c>
       <c r="C455" t="n">
-        <v>18.02628852239609</v>
+        <v>18.02629043576155</v>
       </c>
       <c r="D455" t="n">
-        <v>17.23267818854108</v>
+        <v>17.2326800176703</v>
       </c>
       <c r="E455" t="n">
-        <v>17.25157410173131</v>
+        <v>17.2515759328662</v>
       </c>
       <c r="F455" t="n">
         <v>812650</v>
@@ -9532,16 +9532,16 @@
         <v>44763</v>
       </c>
       <c r="B456" t="n">
-        <v>18.02628707885742</v>
+        <v>18.02628898620605</v>
       </c>
       <c r="C456" t="n">
-        <v>18.23413670126503</v>
+        <v>18.23413863060609</v>
       </c>
       <c r="D456" t="n">
-        <v>17.66727376706003</v>
+        <v>17.66727563642172</v>
       </c>
       <c r="E456" t="n">
-        <v>18.04518299053447</v>
+        <v>18.04518489988247</v>
       </c>
       <c r="F456" t="n">
         <v>845300</v>
@@ -9592,16 +9592,16 @@
         <v>44768</v>
       </c>
       <c r="B459" t="n">
-        <v>17.40273857116699</v>
+        <v>17.40273666381836</v>
       </c>
       <c r="C459" t="n">
-        <v>18.158557111994</v>
+        <v>18.15855512180728</v>
       </c>
       <c r="D459" t="n">
-        <v>17.25157486300159</v>
+        <v>17.25157297222058</v>
       </c>
       <c r="E459" t="n">
-        <v>18.04518523187672</v>
+        <v>18.04518325411562</v>
       </c>
       <c r="F459" t="n">
         <v>578050</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.5190315246582</v>
+        <v>19.51902961730957</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65129931363029</v>
+        <v>19.65129739335679</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431710008434</v>
+        <v>18.74431526843877</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658488905642</v>
+        <v>18.87658304448599</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9672,16 +9672,16 @@
         <v>44774</v>
       </c>
       <c r="B463" t="n">
-        <v>19.12222480773926</v>
+        <v>19.12222671508789</v>
       </c>
       <c r="C463" t="n">
-        <v>19.74577547957757</v>
+        <v>19.74577744912234</v>
       </c>
       <c r="D463" t="n">
-        <v>19.04664296272896</v>
+        <v>19.04664486253867</v>
       </c>
       <c r="E463" t="n">
-        <v>19.50013403279076</v>
+        <v>19.50013597783399</v>
       </c>
       <c r="F463" t="n">
         <v>811600</v>
@@ -9712,16 +9712,16 @@
         <v>44776</v>
       </c>
       <c r="B465" t="n">
-        <v>19.6890926361084</v>
+        <v>19.68909072875977</v>
       </c>
       <c r="C465" t="n">
-        <v>19.74577857825845</v>
+        <v>19.74577666541846</v>
       </c>
       <c r="D465" t="n">
-        <v>19.02775003697459</v>
+        <v>19.02774819369244</v>
       </c>
       <c r="E465" t="n">
-        <v>19.08443778113825</v>
+        <v>19.08443593236457</v>
       </c>
       <c r="F465" t="n">
         <v>1095050</v>
@@ -9732,16 +9732,16 @@
         <v>44777</v>
       </c>
       <c r="B466" t="n">
-        <v>21.31410217285156</v>
+        <v>21.3141040802002</v>
       </c>
       <c r="C466" t="n">
-        <v>21.46526587746648</v>
+        <v>21.46526779834239</v>
       </c>
       <c r="D466" t="n">
-        <v>19.78356921312217</v>
+        <v>19.78357098350703</v>
       </c>
       <c r="E466" t="n">
-        <v>19.89694109057661</v>
+        <v>19.89694287110684</v>
       </c>
       <c r="F466" t="n">
         <v>1697500</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75015640258789</v>
+        <v>22.75015830993652</v>
       </c>
       <c r="C474" t="n">
-        <v>23.1280656181764</v>
+        <v>23.12806755720854</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341087323478</v>
+        <v>22.52341276157331</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027559762419</v>
+        <v>23.09027753348805</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9912,16 +9912,16 @@
         <v>44790</v>
       </c>
       <c r="B475" t="n">
-        <v>22.80684661865234</v>
+        <v>22.80684471130371</v>
       </c>
       <c r="C475" t="n">
-        <v>23.09027993509618</v>
+        <v>23.09027800404387</v>
       </c>
       <c r="D475" t="n">
-        <v>22.2399835897919</v>
+        <v>22.23998172985033</v>
       </c>
       <c r="E475" t="n">
-        <v>22.4856232745575</v>
+        <v>22.48562139407294</v>
       </c>
       <c r="F475" t="n">
         <v>781800</v>
@@ -9932,16 +9932,16 @@
         <v>44791</v>
       </c>
       <c r="B476" t="n">
-        <v>22.25887680053711</v>
+        <v>22.25887489318848</v>
       </c>
       <c r="C476" t="n">
-        <v>23.14696493951494</v>
+        <v>23.14696295606662</v>
       </c>
       <c r="D476" t="n">
-        <v>21.84317750315476</v>
+        <v>21.84317563142713</v>
       </c>
       <c r="E476" t="n">
-        <v>22.99580123100981</v>
+        <v>22.9957992605146</v>
       </c>
       <c r="F476" t="n">
         <v>1546750</v>
@@ -9992,16 +9992,16 @@
         <v>44796</v>
       </c>
       <c r="B479" t="n">
-        <v>20.76613235473633</v>
+        <v>20.76613426208496</v>
       </c>
       <c r="C479" t="n">
-        <v>20.97398379069955</v>
+        <v>20.97398571713913</v>
       </c>
       <c r="D479" t="n">
-        <v>20.29374534865763</v>
+        <v>20.29374721261799</v>
       </c>
       <c r="E479" t="n">
-        <v>20.80392418018906</v>
+        <v>20.80392609100884</v>
       </c>
       <c r="F479" t="n">
         <v>1768900</v>
@@ -10052,16 +10052,16 @@
         <v>44799</v>
       </c>
       <c r="B482" t="n">
-        <v>20.46380615234375</v>
+        <v>20.46380805969238</v>
       </c>
       <c r="C482" t="n">
-        <v>21.10625280639183</v>
+        <v>21.10625477362032</v>
       </c>
       <c r="D482" t="n">
-        <v>20.27485061808954</v>
+        <v>20.2748525078264</v>
       </c>
       <c r="E482" t="n">
-        <v>20.97398501362199</v>
+        <v>20.97398696852234</v>
       </c>
       <c r="F482" t="n">
         <v>564750</v>
@@ -10212,16 +10212,16 @@
         <v>44812</v>
       </c>
       <c r="B490" t="n">
-        <v>19.76467514038086</v>
+        <v>19.76467323303223</v>
       </c>
       <c r="C490" t="n">
-        <v>20.7283451985652</v>
+        <v>20.72834319821961</v>
       </c>
       <c r="D490" t="n">
-        <v>19.63240733702705</v>
+        <v>19.63240544244264</v>
       </c>
       <c r="E490" t="n">
-        <v>20.7283451985652</v>
+        <v>20.72834319821961</v>
       </c>
       <c r="F490" t="n">
         <v>1701700</v>
@@ -10292,16 +10292,16 @@
         <v>44818</v>
       </c>
       <c r="B494" t="n">
-        <v>20.4260139465332</v>
+        <v>20.42601585388184</v>
       </c>
       <c r="C494" t="n">
-        <v>20.5204899015629</v>
+        <v>20.52049181773355</v>
       </c>
       <c r="D494" t="n">
-        <v>19.51903000173875</v>
+        <v>19.51903182439467</v>
       </c>
       <c r="E494" t="n">
-        <v>19.70798551582482</v>
+        <v>19.7079873561251</v>
       </c>
       <c r="F494" t="n">
         <v>1153500</v>
@@ -10352,16 +10352,16 @@
         <v>44823</v>
       </c>
       <c r="B497" t="n">
-        <v>20.36932754516602</v>
+        <v>20.36932563781738</v>
       </c>
       <c r="C497" t="n">
-        <v>20.52049124552984</v>
+        <v>20.5204893240265</v>
       </c>
       <c r="D497" t="n">
-        <v>19.85915050694149</v>
+        <v>19.85914864736495</v>
       </c>
       <c r="E497" t="n">
-        <v>19.93473235712339</v>
+        <v>19.93473049046951</v>
       </c>
       <c r="F497" t="n">
         <v>718850</v>
@@ -10392,16 +10392,16 @@
         <v>44825</v>
       </c>
       <c r="B499" t="n">
-        <v>19.12222480773926</v>
+        <v>19.12222671508789</v>
       </c>
       <c r="C499" t="n">
-        <v>20.08589468313058</v>
+        <v>20.08589668660058</v>
       </c>
       <c r="D499" t="n">
-        <v>19.04664296272896</v>
+        <v>19.04664486253867</v>
       </c>
       <c r="E499" t="n">
-        <v>19.84025323634378</v>
+        <v>19.84025521531224</v>
       </c>
       <c r="F499" t="n">
         <v>1245900</v>
@@ -10432,16 +10432,16 @@
         <v>44827</v>
       </c>
       <c r="B501" t="n">
-        <v>19.57571601867676</v>
+        <v>19.57571792602539</v>
       </c>
       <c r="C501" t="n">
-        <v>19.68908968801476</v>
+        <v>19.68909160640989</v>
       </c>
       <c r="D501" t="n">
-        <v>19.21670270279754</v>
+        <v>19.21670457516592</v>
       </c>
       <c r="E501" t="n">
-        <v>19.34897048201409</v>
+        <v>19.3489723672699</v>
       </c>
       <c r="F501" t="n">
         <v>673550</v>
@@ -10512,16 +10512,16 @@
         <v>44833</v>
       </c>
       <c r="B505" t="n">
-        <v>18.21524429321289</v>
+        <v>18.21524238586426</v>
       </c>
       <c r="C505" t="n">
-        <v>18.30972025639716</v>
+        <v>18.30971833915579</v>
       </c>
       <c r="D505" t="n">
-        <v>17.8562291458641</v>
+        <v>17.85622727610854</v>
       </c>
       <c r="E505" t="n">
-        <v>18.2908261449684</v>
+        <v>18.29082422970546</v>
       </c>
       <c r="F505" t="n">
         <v>1182750</v>
@@ -10532,16 +10532,16 @@
         <v>44834</v>
       </c>
       <c r="B506" t="n">
-        <v>18.2530345916748</v>
+        <v>18.25303649902344</v>
       </c>
       <c r="C506" t="n">
-        <v>18.51757197779093</v>
+        <v>18.51757391278236</v>
       </c>
       <c r="D506" t="n">
-        <v>17.95070718012124</v>
+        <v>17.95070905587821</v>
       </c>
       <c r="E506" t="n">
-        <v>18.21524456623737</v>
+        <v>18.21524646963713</v>
       </c>
       <c r="F506" t="n">
         <v>981200</v>
@@ -10712,16 +10712,16 @@
         <v>44848</v>
       </c>
       <c r="B515" t="n">
-        <v>19.1600170135498</v>
+        <v>19.16001892089844</v>
       </c>
       <c r="C515" t="n">
-        <v>19.84025363221523</v>
+        <v>19.84025560728032</v>
       </c>
       <c r="D515" t="n">
-        <v>18.97106149624717</v>
+        <v>18.97106338478559</v>
       </c>
       <c r="E515" t="n">
-        <v>19.84025363221523</v>
+        <v>19.84025560728032</v>
       </c>
       <c r="F515" t="n">
         <v>919650</v>
@@ -10872,16 +10872,16 @@
         <v>44860</v>
       </c>
       <c r="B523" t="n">
-        <v>18.38530349731445</v>
+        <v>18.38530158996582</v>
       </c>
       <c r="C523" t="n">
-        <v>19.31118350379421</v>
+        <v>19.3111815003919</v>
       </c>
       <c r="D523" t="n">
-        <v>18.06408195459271</v>
+        <v>18.06408008056859</v>
       </c>
       <c r="E523" t="n">
-        <v>18.98996015905884</v>
+        <v>18.98995818898124</v>
       </c>
       <c r="F523" t="n">
         <v>1458850</v>
@@ -10912,16 +10912,16 @@
         <v>44862</v>
       </c>
       <c r="B525" t="n">
-        <v>19.40565872192383</v>
+        <v>19.40566062927246</v>
       </c>
       <c r="C525" t="n">
-        <v>19.74577613474872</v>
+        <v>19.7457780755269</v>
       </c>
       <c r="D525" t="n">
-        <v>18.87658398728353</v>
+        <v>18.87658584263032</v>
       </c>
       <c r="E525" t="n">
-        <v>19.29228504963994</v>
+        <v>19.29228694584527</v>
       </c>
       <c r="F525" t="n">
         <v>1190600</v>
@@ -10932,16 +10932,16 @@
         <v>44865</v>
       </c>
       <c r="B526" t="n">
-        <v>20.46380615234375</v>
+        <v>20.46380805969238</v>
       </c>
       <c r="C526" t="n">
-        <v>20.50159798</v>
+        <v>20.50159989087106</v>
       </c>
       <c r="D526" t="n">
-        <v>18.76321355210998</v>
+        <v>18.76321530095325</v>
       </c>
       <c r="E526" t="n">
-        <v>18.78210766392458</v>
+        <v>18.78210941452889</v>
       </c>
       <c r="F526" t="n">
         <v>2299050</v>
@@ -11052,16 +11052,16 @@
         <v>44874</v>
       </c>
       <c r="B532" t="n">
-        <v>18.78210830688477</v>
+        <v>18.7821102142334</v>
       </c>
       <c r="C532" t="n">
-        <v>20.06700165896615</v>
+        <v>20.06700369679745</v>
       </c>
       <c r="D532" t="n">
-        <v>18.61205048265069</v>
+        <v>18.61205237272972</v>
       </c>
       <c r="E532" t="n">
-        <v>19.85915200578211</v>
+        <v>19.85915402250599</v>
       </c>
       <c r="F532" t="n">
         <v>1714900</v>
@@ -11072,16 +11072,16 @@
         <v>44875</v>
       </c>
       <c r="B533" t="n">
-        <v>16.94924736022949</v>
+        <v>16.94924926757812</v>
       </c>
       <c r="C533" t="n">
-        <v>18.51757217595721</v>
+        <v>18.51757425979405</v>
       </c>
       <c r="D533" t="n">
-        <v>16.25011476302671</v>
+        <v>16.2501165916999</v>
       </c>
       <c r="E533" t="n">
-        <v>18.51757217595721</v>
+        <v>18.51757425979405</v>
       </c>
       <c r="F533" t="n">
         <v>6247350</v>
@@ -11112,16 +11112,16 @@
         <v>44879</v>
       </c>
       <c r="B535" t="n">
-        <v>15.45650577545166</v>
+        <v>15.45650386810303</v>
       </c>
       <c r="C535" t="n">
-        <v>16.26901032459178</v>
+        <v>16.26900831697925</v>
       </c>
       <c r="D535" t="n">
-        <v>14.88964092120513</v>
+        <v>14.8896390838082</v>
       </c>
       <c r="E535" t="n">
-        <v>15.96668288286395</v>
+        <v>15.96668091255894</v>
       </c>
       <c r="F535" t="n">
         <v>3328550</v>
@@ -11172,16 +11172,16 @@
         <v>44883</v>
       </c>
       <c r="B538" t="n">
-        <v>13.83149242401123</v>
+        <v>13.83149147033691</v>
       </c>
       <c r="C538" t="n">
-        <v>14.88963925247558</v>
+        <v>14.88963822584258</v>
       </c>
       <c r="D538" t="n">
-        <v>13.73701465855629</v>
+        <v>13.73701371139616</v>
       </c>
       <c r="E538" t="n">
-        <v>14.26608852329183</v>
+        <v>14.26608753965234</v>
       </c>
       <c r="F538" t="n">
         <v>3266800</v>
@@ -11192,16 +11192,16 @@
         <v>44886</v>
       </c>
       <c r="B539" t="n">
-        <v>14.51172828674316</v>
+        <v>14.51172924041748</v>
       </c>
       <c r="C539" t="n">
-        <v>14.60620604695773</v>
+        <v>14.60620700684089</v>
       </c>
       <c r="D539" t="n">
-        <v>13.79370073293793</v>
+        <v>13.79370163942528</v>
       </c>
       <c r="E539" t="n">
-        <v>14.1338190478983</v>
+        <v>14.13381997673737</v>
       </c>
       <c r="F539" t="n">
         <v>1946900</v>
@@ -11212,16 +11212,16 @@
         <v>44887</v>
       </c>
       <c r="B540" t="n">
-        <v>14.09602928161621</v>
+        <v>14.09602832794189</v>
       </c>
       <c r="C540" t="n">
-        <v>14.71958002742118</v>
+        <v>14.71957903156021</v>
       </c>
       <c r="D540" t="n">
-        <v>13.88817873267896</v>
+        <v>13.88817779306689</v>
       </c>
       <c r="E540" t="n">
-        <v>14.60620724645726</v>
+        <v>14.60620625826658</v>
       </c>
       <c r="F540" t="n">
         <v>2112800</v>
@@ -11272,16 +11272,16 @@
         <v>44890</v>
       </c>
       <c r="B543" t="n">
-        <v>14.11492443084717</v>
+        <v>14.11492538452148</v>
       </c>
       <c r="C543" t="n">
-        <v>14.90853480626151</v>
+        <v>14.90853581355609</v>
       </c>
       <c r="D543" t="n">
-        <v>13.94486570826322</v>
+        <v>13.94486665044753</v>
       </c>
       <c r="E543" t="n">
-        <v>14.90853480626151</v>
+        <v>14.90853581355609</v>
       </c>
       <c r="F543" t="n">
         <v>1492900</v>
@@ -11352,16 +11352,16 @@
         <v>44896</v>
       </c>
       <c r="B547" t="n">
-        <v>14.15271472930908</v>
+        <v>14.1527156829834</v>
       </c>
       <c r="C547" t="n">
-        <v>14.51172897371034</v>
+        <v>14.51172995157667</v>
       </c>
       <c r="D547" t="n">
-        <v>14.0393419522887</v>
+        <v>14.03934289832344</v>
       </c>
       <c r="E547" t="n">
-        <v>14.30387933300967</v>
+        <v>14.30388029687014</v>
       </c>
       <c r="F547" t="n">
         <v>1145350</v>
@@ -11372,16 +11372,16 @@
         <v>44897</v>
       </c>
       <c r="B548" t="n">
-        <v>14.28498268127441</v>
+        <v>14.28498363494873</v>
       </c>
       <c r="C548" t="n">
-        <v>14.58731007103471</v>
+        <v>14.58731104489259</v>
       </c>
       <c r="D548" t="n">
-        <v>14.05823713895419</v>
+        <v>14.05823807749083</v>
       </c>
       <c r="E548" t="n">
-        <v>14.1716099101143</v>
+        <v>14.17161085621978</v>
       </c>
       <c r="F548" t="n">
         <v>1219600</v>
@@ -11412,16 +11412,16 @@
         <v>44901</v>
       </c>
       <c r="B550" t="n">
-        <v>13.15125465393066</v>
+        <v>13.15125370025635</v>
       </c>
       <c r="C550" t="n">
-        <v>13.66143259735872</v>
+        <v>13.66143160668842</v>
       </c>
       <c r="D550" t="n">
-        <v>12.67886763590444</v>
+        <v>12.67886671648566</v>
       </c>
       <c r="E550" t="n">
-        <v>13.54805982115323</v>
+        <v>13.54805883870426</v>
       </c>
       <c r="F550" t="n">
         <v>4313950</v>
@@ -11532,16 +11532,16 @@
         <v>44909</v>
       </c>
       <c r="B556" t="n">
-        <v>11.50734901428223</v>
+        <v>11.50734806060791</v>
       </c>
       <c r="C556" t="n">
-        <v>11.62072180001323</v>
+        <v>11.62072083694312</v>
       </c>
       <c r="D556" t="n">
-        <v>11.0727528851433</v>
+        <v>11.07275196748624</v>
       </c>
       <c r="E556" t="n">
-        <v>11.50734901428223</v>
+        <v>11.50734806060791</v>
       </c>
       <c r="F556" t="n">
         <v>4449300</v>
@@ -11552,16 +11552,16 @@
         <v>44910</v>
       </c>
       <c r="B557" t="n">
-        <v>11.5640344619751</v>
+        <v>11.56403541564941</v>
       </c>
       <c r="C557" t="n">
-        <v>11.9041537056258</v>
+        <v>11.90415468734941</v>
       </c>
       <c r="D557" t="n">
-        <v>11.2617070462916</v>
+        <v>11.26170797503327</v>
       </c>
       <c r="E557" t="n">
-        <v>11.41287075413335</v>
+        <v>11.41287169534134</v>
       </c>
       <c r="F557" t="n">
         <v>3167400</v>
@@ -11732,16 +11732,16 @@
         <v>44923</v>
       </c>
       <c r="B566" t="n">
-        <v>13.10084915161133</v>
+        <v>13.10085010528564</v>
       </c>
       <c r="C566" t="n">
-        <v>13.1201439219793</v>
+        <v>13.12014487705818</v>
       </c>
       <c r="D566" t="n">
-        <v>12.29048719666213</v>
+        <v>12.29048809134627</v>
       </c>
       <c r="E566" t="n">
-        <v>12.46413644987275</v>
+        <v>12.46413735719766</v>
       </c>
       <c r="F566" t="n">
         <v>2129050</v>
@@ -11772,16 +11772,16 @@
         <v>44928</v>
       </c>
       <c r="B568" t="n">
-        <v>12.21331024169922</v>
+        <v>12.21331119537354</v>
       </c>
       <c r="C568" t="n">
-        <v>12.83072910757643</v>
+        <v>12.83073010946179</v>
       </c>
       <c r="D568" t="n">
-        <v>11.98177851200476</v>
+        <v>11.98177944759996</v>
       </c>
       <c r="E568" t="n">
-        <v>12.83072910757643</v>
+        <v>12.83073010946179</v>
       </c>
       <c r="F568" t="n">
         <v>1499800</v>
@@ -11792,16 +11792,16 @@
         <v>44929</v>
       </c>
       <c r="B569" t="n">
-        <v>11.65377521514893</v>
+        <v>11.65377616882324</v>
       </c>
       <c r="C569" t="n">
-        <v>12.21331071004653</v>
+        <v>12.21331170950984</v>
       </c>
       <c r="D569" t="n">
-        <v>11.59589274051833</v>
+        <v>11.5958936894559</v>
       </c>
       <c r="E569" t="n">
-        <v>12.21331071004653</v>
+        <v>12.21331170950984</v>
       </c>
       <c r="F569" t="n">
         <v>2015100</v>
@@ -11852,16 +11852,16 @@
         <v>44932</v>
       </c>
       <c r="B572" t="n">
-        <v>13.08155727386475</v>
+        <v>13.08155632019043</v>
       </c>
       <c r="C572" t="n">
-        <v>13.13943975364632</v>
+        <v>13.13943879575224</v>
       </c>
       <c r="D572" t="n">
-        <v>12.44484355608945</v>
+        <v>12.44484264883297</v>
       </c>
       <c r="E572" t="n">
-        <v>12.7342587150736</v>
+        <v>12.73425778671811</v>
       </c>
       <c r="F572" t="n">
         <v>1382000</v>
@@ -11892,16 +11892,16 @@
         <v>44936</v>
       </c>
       <c r="B574" t="n">
-        <v>13.85332870483398</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C574" t="n">
-        <v>14.0076841187254</v>
+        <v>14.00768508302567</v>
       </c>
       <c r="D574" t="n">
-        <v>13.04296761203716</v>
+        <v>13.04296850992557</v>
       </c>
       <c r="E574" t="n">
-        <v>13.17802733415729</v>
+        <v>13.17802824134331</v>
       </c>
       <c r="F574" t="n">
         <v>2939000</v>
@@ -11952,16 +11952,16 @@
         <v>44939</v>
       </c>
       <c r="B577" t="n">
-        <v>13.33238124847412</v>
+        <v>13.33238220214844</v>
       </c>
       <c r="C577" t="n">
-        <v>13.4867357356305</v>
+        <v>13.4867367003459</v>
       </c>
       <c r="D577" t="n">
-        <v>13.13943813952864</v>
+        <v>13.13943907940161</v>
       </c>
       <c r="E577" t="n">
-        <v>13.42885326295952</v>
+        <v>13.42885422353454</v>
       </c>
       <c r="F577" t="n">
         <v>1373850</v>
@@ -12052,16 +12052,16 @@
         <v>44946</v>
       </c>
       <c r="B582" t="n">
-        <v>14.06556606292725</v>
+        <v>14.06556701660156</v>
       </c>
       <c r="C582" t="n">
-        <v>14.12344945595456</v>
+        <v>14.12345041355349</v>
       </c>
       <c r="D582" t="n">
-        <v>13.50603058377296</v>
+        <v>13.50603149950962</v>
       </c>
       <c r="E582" t="n">
-        <v>13.73756231583157</v>
+        <v>13.73756324726655</v>
       </c>
       <c r="F582" t="n">
         <v>2454200</v>
@@ -12152,16 +12152,16 @@
         <v>44953</v>
       </c>
       <c r="B587" t="n">
-        <v>14.35498237609863</v>
+        <v>14.35498142242432</v>
       </c>
       <c r="C587" t="n">
-        <v>14.6443975251379</v>
+        <v>14.64439655223626</v>
       </c>
       <c r="D587" t="n">
-        <v>14.29709897828062</v>
+        <v>14.29709802845179</v>
       </c>
       <c r="E587" t="n">
-        <v>14.56722027473081</v>
+        <v>14.56721930695646</v>
       </c>
       <c r="F587" t="n">
         <v>1566450</v>
@@ -12172,16 +12172,16 @@
         <v>44956</v>
       </c>
       <c r="B588" t="n">
-        <v>14.39357089996338</v>
+        <v>14.39356994628906</v>
       </c>
       <c r="C588" t="n">
-        <v>14.66369127448637</v>
+        <v>14.6636903029147</v>
       </c>
       <c r="D588" t="n">
-        <v>14.31639365009966</v>
+        <v>14.31639270153888</v>
       </c>
       <c r="E588" t="n">
-        <v>14.37427612748476</v>
+        <v>14.37427517508885</v>
       </c>
       <c r="F588" t="n">
         <v>1160300</v>
@@ -12192,16 +12192,16 @@
         <v>44957</v>
       </c>
       <c r="B589" t="n">
-        <v>14.99169445037842</v>
+        <v>14.99169540405273</v>
       </c>
       <c r="C589" t="n">
-        <v>15.04957784548756</v>
+        <v>15.04957880284405</v>
       </c>
       <c r="D589" t="n">
-        <v>14.39357032770223</v>
+        <v>14.39357124332777</v>
       </c>
       <c r="E589" t="n">
-        <v>14.41286417938838</v>
+        <v>14.41286509624127</v>
       </c>
       <c r="F589" t="n">
         <v>1759050</v>
@@ -12212,16 +12212,16 @@
         <v>44958</v>
       </c>
       <c r="B590" t="n">
-        <v>14.99169445037842</v>
+        <v>14.99169540405273</v>
       </c>
       <c r="C590" t="n">
-        <v>15.1653437156805</v>
+        <v>15.16534468040126</v>
       </c>
       <c r="D590" t="n">
-        <v>14.74086793828104</v>
+        <v>14.7408688759994</v>
       </c>
       <c r="E590" t="n">
-        <v>14.97240059869227</v>
+        <v>14.97240155113924</v>
       </c>
       <c r="F590" t="n">
         <v>1831550</v>
@@ -12372,16 +12372,16 @@
         <v>44970</v>
       </c>
       <c r="B598" t="n">
-        <v>14.12345027923584</v>
+        <v>14.12344932556152</v>
       </c>
       <c r="C598" t="n">
-        <v>14.62510239460502</v>
+        <v>14.62510140705705</v>
       </c>
       <c r="D598" t="n">
-        <v>13.9690948621738</v>
+        <v>13.9690939189222</v>
       </c>
       <c r="E598" t="n">
-        <v>14.04627303071751</v>
+        <v>14.04627208225452</v>
       </c>
       <c r="F598" t="n">
         <v>1583800</v>
@@ -12392,16 +12392,16 @@
         <v>44971</v>
       </c>
       <c r="B599" t="n">
-        <v>13.96909523010254</v>
+        <v>13.96909427642822</v>
       </c>
       <c r="C599" t="n">
-        <v>14.50933690398556</v>
+        <v>14.50933591342878</v>
       </c>
       <c r="D599" t="n">
-        <v>13.69897485317373</v>
+        <v>13.69897391794061</v>
       </c>
       <c r="E599" t="n">
-        <v>14.35498240288338</v>
+        <v>14.35498142286443</v>
       </c>
       <c r="F599" t="n">
         <v>2796000</v>
@@ -12412,16 +12412,16 @@
         <v>44972</v>
       </c>
       <c r="B600" t="n">
-        <v>14.83734035491943</v>
+        <v>14.83734130859375</v>
       </c>
       <c r="C600" t="n">
-        <v>15.04957824931416</v>
+        <v>15.04957921663013</v>
       </c>
       <c r="D600" t="n">
-        <v>13.73756317853808</v>
+        <v>13.7375640615239</v>
       </c>
       <c r="E600" t="n">
-        <v>14.00768446959514</v>
+        <v>14.00768536994309</v>
       </c>
       <c r="F600" t="n">
         <v>2808050</v>
@@ -12492,16 +12492,16 @@
         <v>44980</v>
       </c>
       <c r="B604" t="n">
-        <v>14.41286468505859</v>
+        <v>14.41286563873291</v>
       </c>
       <c r="C604" t="n">
-        <v>14.91451772685366</v>
+        <v>14.91451871372149</v>
       </c>
       <c r="D604" t="n">
-        <v>14.27780495844099</v>
+        <v>14.27780590317863</v>
       </c>
       <c r="E604" t="n">
-        <v>14.66369120595613</v>
+        <v>14.6636921762272</v>
       </c>
       <c r="F604" t="n">
         <v>1540800</v>
@@ -12552,16 +12552,16 @@
         <v>44985</v>
       </c>
       <c r="B607" t="n">
-        <v>13.85332870483398</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C607" t="n">
-        <v>14.0076841187254</v>
+        <v>14.00768508302567</v>
       </c>
       <c r="D607" t="n">
-        <v>13.48673632188941</v>
+        <v>13.48673725032721</v>
       </c>
       <c r="E607" t="n">
-        <v>13.71826898271386</v>
+        <v>13.71826992709055</v>
       </c>
       <c r="F607" t="n">
         <v>1742300</v>
@@ -12572,16 +12572,16 @@
         <v>44986</v>
       </c>
       <c r="B608" t="n">
-        <v>13.48673629760742</v>
+        <v>13.48673725128174</v>
       </c>
       <c r="C608" t="n">
-        <v>13.85332867989197</v>
+        <v>13.85332965948877</v>
       </c>
       <c r="D608" t="n">
-        <v>13.21661593382815</v>
+        <v>13.21661686840171</v>
       </c>
       <c r="E608" t="n">
-        <v>13.85332867989197</v>
+        <v>13.85332965948877</v>
       </c>
       <c r="F608" t="n">
         <v>2358750</v>
@@ -12632,16 +12632,16 @@
         <v>44991</v>
       </c>
       <c r="B611" t="n">
-        <v>14.12345027923584</v>
+        <v>14.12344932556152</v>
       </c>
       <c r="C611" t="n">
-        <v>14.25851000413024</v>
+        <v>14.25850904133613</v>
       </c>
       <c r="D611" t="n">
-        <v>13.35167687402712</v>
+        <v>13.35167597246616</v>
       </c>
       <c r="E611" t="n">
-        <v>13.35167687402712</v>
+        <v>13.35167597246616</v>
       </c>
       <c r="F611" t="n">
         <v>2062900</v>
@@ -12672,16 +12672,16 @@
         <v>44993</v>
       </c>
       <c r="B613" t="n">
-        <v>15.85993957519531</v>
+        <v>15.85994148254395</v>
       </c>
       <c r="C613" t="n">
-        <v>15.85993957519531</v>
+        <v>15.85994148254395</v>
       </c>
       <c r="D613" t="n">
-        <v>14.16203833580244</v>
+        <v>14.16204003895802</v>
       </c>
       <c r="E613" t="n">
-        <v>14.68298520243147</v>
+        <v>14.68298696823717</v>
       </c>
       <c r="F613" t="n">
         <v>5225650</v>
@@ -12752,16 +12752,16 @@
         <v>44999</v>
       </c>
       <c r="B617" t="n">
-        <v>14.9724006652832</v>
+        <v>14.97240161895752</v>
       </c>
       <c r="C617" t="n">
-        <v>15.89852763094573</v>
+        <v>15.89852864361015</v>
       </c>
       <c r="D617" t="n">
-        <v>14.77945662741149</v>
+        <v>14.77945756879614</v>
       </c>
       <c r="E617" t="n">
-        <v>15.53193616705032</v>
+        <v>15.53193715636452</v>
       </c>
       <c r="F617" t="n">
         <v>2100150</v>
@@ -12772,16 +12772,16 @@
         <v>45000</v>
       </c>
       <c r="B618" t="n">
-        <v>15.31969928741455</v>
+        <v>15.31969833374023</v>
       </c>
       <c r="C618" t="n">
-        <v>15.47405471189345</v>
+        <v>15.47405374861028</v>
       </c>
       <c r="D618" t="n">
-        <v>14.4514538198256</v>
+        <v>14.45145292020087</v>
       </c>
       <c r="E618" t="n">
-        <v>14.64439787041787</v>
+        <v>14.64439695878208</v>
       </c>
       <c r="F618" t="n">
         <v>2068400</v>
@@ -12832,16 +12832,16 @@
         <v>45005</v>
       </c>
       <c r="B621" t="n">
-        <v>13.96909523010254</v>
+        <v>13.96909427642822</v>
       </c>
       <c r="C621" t="n">
-        <v>15.33899280742245</v>
+        <v>15.33899176022482</v>
       </c>
       <c r="D621" t="n">
-        <v>13.94980137747747</v>
+        <v>13.94980042512035</v>
       </c>
       <c r="E621" t="n">
-        <v>15.1653444536952</v>
+        <v>15.16534341835259</v>
       </c>
       <c r="F621" t="n">
         <v>2781400</v>
@@ -12972,16 +12972,16 @@
         <v>45014</v>
       </c>
       <c r="B628" t="n">
-        <v>14.14274406433105</v>
+        <v>14.14274501800537</v>
       </c>
       <c r="C628" t="n">
-        <v>14.41286443286514</v>
+        <v>14.41286540475423</v>
       </c>
       <c r="D628" t="n">
-        <v>13.75685782356807</v>
+        <v>13.75685875122129</v>
       </c>
       <c r="E628" t="n">
-        <v>14.41286443286514</v>
+        <v>14.41286540475423</v>
       </c>
       <c r="F628" t="n">
         <v>1398800</v>
@@ -13032,16 +13032,16 @@
         <v>45019</v>
       </c>
       <c r="B631" t="n">
-        <v>13.83403587341309</v>
+        <v>13.83403491973877</v>
       </c>
       <c r="C631" t="n">
-        <v>14.49004344075163</v>
+        <v>14.49004244185425</v>
       </c>
       <c r="D631" t="n">
-        <v>13.62179796868142</v>
+        <v>13.62179702963811</v>
       </c>
       <c r="E631" t="n">
-        <v>14.39357141495758</v>
+        <v>14.39357042271067</v>
       </c>
       <c r="F631" t="n">
         <v>1766300</v>
@@ -13072,16 +13072,16 @@
         <v>45021</v>
       </c>
       <c r="B633" t="n">
-        <v>13.85332870483398</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C633" t="n">
-        <v>14.29709833471159</v>
+        <v>14.29709931893536</v>
       </c>
       <c r="D633" t="n">
-        <v>13.66038558750141</v>
+        <v>13.66038652789336</v>
       </c>
       <c r="E633" t="n">
-        <v>14.18133246431204</v>
+        <v>14.1813334405664</v>
       </c>
       <c r="F633" t="n">
         <v>2634950</v>
@@ -13092,16 +13092,16 @@
         <v>45022</v>
       </c>
       <c r="B634" t="n">
-        <v>14.14274406433105</v>
+        <v>14.14274501800537</v>
       </c>
       <c r="C634" t="n">
-        <v>14.29709856063625</v>
+        <v>14.297099524719</v>
       </c>
       <c r="D634" t="n">
-        <v>13.77615167559354</v>
+        <v>13.77615260454778</v>
       </c>
       <c r="E634" t="n">
-        <v>13.85332892374614</v>
+        <v>13.85332985790459</v>
       </c>
       <c r="F634" t="n">
         <v>1739850</v>
@@ -13112,16 +13112,16 @@
         <v>45026</v>
       </c>
       <c r="B635" t="n">
-        <v>13.96909523010254</v>
+        <v>13.96909427642822</v>
       </c>
       <c r="C635" t="n">
-        <v>14.2006279017812</v>
+        <v>14.20062693230008</v>
       </c>
       <c r="D635" t="n">
-        <v>13.89191797955145</v>
+        <v>13.89191703114605</v>
       </c>
       <c r="E635" t="n">
-        <v>13.94980137747747</v>
+        <v>13.94980042512035</v>
       </c>
       <c r="F635" t="n">
         <v>1451200</v>
@@ -13152,16 +13152,16 @@
         <v>45028</v>
       </c>
       <c r="B637" t="n">
-        <v>15.45475959777832</v>
+        <v>15.454758644104</v>
       </c>
       <c r="C637" t="n">
-        <v>15.7827633725165</v>
+        <v>15.78276239860189</v>
       </c>
       <c r="D637" t="n">
-        <v>15.14604967565836</v>
+        <v>15.14604874103375</v>
       </c>
       <c r="E637" t="n">
-        <v>15.31969894934925</v>
+        <v>15.31969800400918</v>
       </c>
       <c r="F637" t="n">
         <v>3667400</v>
@@ -13192,16 +13192,16 @@
         <v>45030</v>
       </c>
       <c r="B639" t="n">
-        <v>15.6091136932373</v>
+        <v>15.60911273956299</v>
       </c>
       <c r="C639" t="n">
-        <v>15.91782268731036</v>
+        <v>15.91782171477476</v>
       </c>
       <c r="D639" t="n">
-        <v>15.12675542998548</v>
+        <v>15.12675450578194</v>
       </c>
       <c r="E639" t="n">
-        <v>15.68629094175557</v>
+        <v>15.68628998336593</v>
       </c>
       <c r="F639" t="n">
         <v>1580050</v>
@@ -13212,16 +13212,16 @@
         <v>45033</v>
       </c>
       <c r="B640" t="n">
-        <v>15.5319356918335</v>
+        <v>15.53193664550781</v>
       </c>
       <c r="C640" t="n">
-        <v>15.76346742616516</v>
+        <v>15.76346839405572</v>
       </c>
       <c r="D640" t="n">
-        <v>15.49334614941956</v>
+        <v>15.49334710072444</v>
       </c>
       <c r="E640" t="n">
-        <v>15.60911293661072</v>
+        <v>15.60911389502378</v>
       </c>
       <c r="F640" t="n">
         <v>1212550</v>
@@ -13232,16 +13232,16 @@
         <v>45034</v>
       </c>
       <c r="B641" t="n">
-        <v>15.06887245178223</v>
+        <v>15.06887149810791</v>
       </c>
       <c r="C641" t="n">
-        <v>15.74417385507098</v>
+        <v>15.74417285865839</v>
       </c>
       <c r="D641" t="n">
-        <v>14.87592932513193</v>
+        <v>14.87592838366854</v>
       </c>
       <c r="E641" t="n">
-        <v>15.6284088991062</v>
+        <v>15.62840791002011</v>
       </c>
       <c r="F641" t="n">
         <v>1695600</v>
@@ -13272,16 +13272,16 @@
         <v>45036</v>
       </c>
       <c r="B643" t="n">
-        <v>14.93381214141846</v>
+        <v>14.93381118774414</v>
       </c>
       <c r="C643" t="n">
-        <v>14.93381214141846</v>
+        <v>14.93381118774414</v>
       </c>
       <c r="D643" t="n">
-        <v>14.29709934903595</v>
+        <v>14.29709843602215</v>
       </c>
       <c r="E643" t="n">
-        <v>14.43216000076346</v>
+        <v>14.43215907912469</v>
       </c>
       <c r="F643" t="n">
         <v>1458900</v>
@@ -29572,7 +29572,7 @@
         <v>46231</v>
       </c>
       <c r="B1458" t="n">
-        <v>7.72</v>
+        <v>8</v>
       </c>
       <c r="C1458" t="n">
         <v>8.119999999999999</v>
@@ -29584,7 +29584,7 @@
         <v>8.08</v>
       </c>
       <c r="F1458" t="n">
-        <v>449000</v>
+        <v>2146900</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1458"/>
+  <dimension ref="A1:F1459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44095</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59559631347656</v>
+        <v>12.5955982208252</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80832961567333</v>
+        <v>12.80833155523612</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45377411201205</v>
+        <v>12.45377599788458</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46706941506998</v>
+        <v>12.46707130295581</v>
       </c>
       <c r="F3" t="n">
         <v>1323800</v>
@@ -492,16 +492,16 @@
         <v>44096</v>
       </c>
       <c r="B4" t="n">
-        <v>12.58673286437988</v>
+        <v>12.5867338180542</v>
       </c>
       <c r="C4" t="n">
-        <v>12.77287472474392</v>
+        <v>12.77287569252187</v>
       </c>
       <c r="D4" t="n">
-        <v>12.43161450652202</v>
+        <v>12.43161544844329</v>
       </c>
       <c r="E4" t="n">
-        <v>12.44491065559339</v>
+        <v>12.44491159852209</v>
       </c>
       <c r="F4" t="n">
         <v>1698000</v>
@@ -572,16 +572,16 @@
         <v>44102</v>
       </c>
       <c r="B8" t="n">
-        <v>11.58067989349365</v>
+        <v>11.58068084716797</v>
       </c>
       <c r="C8" t="n">
-        <v>12.51138915392602</v>
+        <v>12.51139018424467</v>
       </c>
       <c r="D8" t="n">
-        <v>11.58067989349365</v>
+        <v>11.58068084716797</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43161395369939</v>
+        <v>12.43161497744851</v>
       </c>
       <c r="F8" t="n">
         <v>1524000</v>
@@ -732,16 +732,16 @@
         <v>44112</v>
       </c>
       <c r="B16" t="n">
-        <v>11.52306461334229</v>
+        <v>11.5230655670166</v>
       </c>
       <c r="C16" t="n">
-        <v>11.90421240567286</v>
+        <v>11.90421339089181</v>
       </c>
       <c r="D16" t="n">
-        <v>11.39010651362682</v>
+        <v>11.39010745629723</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68261500926243</v>
+        <v>11.68261597614149</v>
       </c>
       <c r="F16" t="n">
         <v>595200</v>
@@ -772,16 +772,16 @@
         <v>44117</v>
       </c>
       <c r="B18" t="n">
-        <v>12.18785762786865</v>
+        <v>12.18785667419434</v>
       </c>
       <c r="C18" t="n">
-        <v>12.44934264096545</v>
+        <v>12.44934166683048</v>
       </c>
       <c r="D18" t="n">
-        <v>12.18785762786865</v>
+        <v>12.18785667419434</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36956743760344</v>
+        <v>12.36956646971071</v>
       </c>
       <c r="F18" t="n">
         <v>440800</v>
@@ -792,16 +792,16 @@
         <v>44118</v>
       </c>
       <c r="B19" t="n">
-        <v>12.13024234771729</v>
+        <v>12.1302433013916</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63105211214986</v>
+        <v>12.63105310519763</v>
       </c>
       <c r="D19" t="n">
-        <v>12.00614749633282</v>
+        <v>12.00614844025086</v>
       </c>
       <c r="E19" t="n">
-        <v>12.18785730119724</v>
+        <v>12.18785825940122</v>
       </c>
       <c r="F19" t="n">
         <v>441800</v>
@@ -912,16 +912,16 @@
         <v>44126</v>
       </c>
       <c r="B25" t="n">
-        <v>13.06981468200684</v>
+        <v>13.06981658935547</v>
       </c>
       <c r="C25" t="n">
-        <v>13.21163688418085</v>
+        <v>13.21163881222637</v>
       </c>
       <c r="D25" t="n">
-        <v>12.69753097863653</v>
+        <v>12.6975328316558</v>
       </c>
       <c r="E25" t="n">
-        <v>12.75071472711529</v>
+        <v>12.75071658789595</v>
       </c>
       <c r="F25" t="n">
         <v>963600</v>
@@ -952,16 +952,16 @@
         <v>44130</v>
       </c>
       <c r="B27" t="n">
-        <v>12.6000280380249</v>
+        <v>12.60002899169922</v>
       </c>
       <c r="C27" t="n">
-        <v>12.87480833494496</v>
+        <v>12.87480930941692</v>
       </c>
       <c r="D27" t="n">
-        <v>12.41831824141832</v>
+        <v>12.41831918133934</v>
       </c>
       <c r="E27" t="n">
-        <v>12.84821688418782</v>
+        <v>12.84821785664712</v>
       </c>
       <c r="F27" t="n">
         <v>307600</v>
@@ -972,16 +972,16 @@
         <v>44131</v>
       </c>
       <c r="B28" t="n">
-        <v>12.22774314880371</v>
+        <v>12.22774505615234</v>
       </c>
       <c r="C28" t="n">
-        <v>12.77730453415898</v>
+        <v>12.77730652723113</v>
       </c>
       <c r="D28" t="n">
-        <v>12.19228760282359</v>
+        <v>12.19228950464168</v>
       </c>
       <c r="E28" t="n">
-        <v>12.675369945132</v>
+        <v>12.67537192230385</v>
       </c>
       <c r="F28" t="n">
         <v>652400</v>
@@ -1012,16 +1012,16 @@
         <v>44133</v>
       </c>
       <c r="B30" t="n">
-        <v>11.70477390289307</v>
+        <v>11.70477485656738</v>
       </c>
       <c r="C30" t="n">
-        <v>11.87761959408865</v>
+        <v>11.87762056184598</v>
       </c>
       <c r="D30" t="n">
-        <v>11.00895824360864</v>
+        <v>11.00895914058972</v>
       </c>
       <c r="E30" t="n">
-        <v>11.3945372232491</v>
+        <v>11.39453815164614</v>
       </c>
       <c r="F30" t="n">
         <v>683400</v>
@@ -1032,16 +1032,16 @@
         <v>44134</v>
       </c>
       <c r="B31" t="n">
-        <v>11.38567543029785</v>
+        <v>11.38567447662354</v>
       </c>
       <c r="C31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.81114107243664</v>
       </c>
       <c r="D31" t="n">
-        <v>11.00895965537159</v>
+        <v>11.00895873325132</v>
       </c>
       <c r="E31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.81114107243664</v>
       </c>
       <c r="F31" t="n">
         <v>907200</v>
@@ -1092,16 +1092,16 @@
         <v>44140</v>
       </c>
       <c r="B34" t="n">
-        <v>12.79503536224365</v>
+        <v>12.79503440856934</v>
       </c>
       <c r="C34" t="n">
-        <v>13.02992808569082</v>
+        <v>13.02992711450884</v>
       </c>
       <c r="D34" t="n">
-        <v>12.63991699966924</v>
+        <v>12.63991605755662</v>
       </c>
       <c r="E34" t="n">
-        <v>12.78617126259321</v>
+        <v>12.78617030957958</v>
       </c>
       <c r="F34" t="n">
         <v>682600</v>
@@ -1112,16 +1112,16 @@
         <v>44141</v>
       </c>
       <c r="B35" t="n">
-        <v>13.55732822418213</v>
+        <v>13.55732917785645</v>
       </c>
       <c r="C35" t="n">
-        <v>13.69471836763221</v>
+        <v>13.69471933097108</v>
       </c>
       <c r="D35" t="n">
-        <v>12.6576425273241</v>
+        <v>12.65764341771108</v>
       </c>
       <c r="E35" t="n">
-        <v>12.74184977119922</v>
+        <v>12.74185066750967</v>
       </c>
       <c r="F35" t="n">
         <v>948200</v>
@@ -1132,16 +1132,16 @@
         <v>44144</v>
       </c>
       <c r="B36" t="n">
-        <v>13.29584407806396</v>
+        <v>13.2958459854126</v>
       </c>
       <c r="C36" t="n">
-        <v>13.96950038089769</v>
+        <v>13.96950238488535</v>
       </c>
       <c r="D36" t="n">
-        <v>13.12299837555377</v>
+        <v>13.12300025810691</v>
       </c>
       <c r="E36" t="n">
-        <v>13.7390388806661</v>
+        <v>13.73904085159302</v>
       </c>
       <c r="F36" t="n">
         <v>650800</v>
@@ -1152,16 +1152,16 @@
         <v>44145</v>
       </c>
       <c r="B37" t="n">
-        <v>13.15845489501953</v>
+        <v>13.15845394134521</v>
       </c>
       <c r="C37" t="n">
-        <v>13.57948948130297</v>
+        <v>13.57948849711368</v>
       </c>
       <c r="D37" t="n">
-        <v>13.07867968942368</v>
+        <v>13.07867874153117</v>
       </c>
       <c r="E37" t="n">
-        <v>13.07867968942368</v>
+        <v>13.07867874153117</v>
       </c>
       <c r="F37" t="n">
         <v>489600</v>
@@ -1172,16 +1172,16 @@
         <v>44146</v>
       </c>
       <c r="B38" t="n">
-        <v>13.29584407806396</v>
+        <v>13.2958459854126</v>
       </c>
       <c r="C38" t="n">
-        <v>13.41993892711028</v>
+        <v>13.41994085226088</v>
       </c>
       <c r="D38" t="n">
-        <v>12.89696892478745</v>
+        <v>12.89697077491564</v>
       </c>
       <c r="E38" t="n">
-        <v>13.25152442873835</v>
+        <v>13.25152632972913</v>
       </c>
       <c r="F38" t="n">
         <v>586400</v>
@@ -1212,16 +1212,16 @@
         <v>44148</v>
       </c>
       <c r="B40" t="n">
-        <v>13.10970401763916</v>
+        <v>13.10970211029053</v>
       </c>
       <c r="C40" t="n">
-        <v>13.53073947574565</v>
+        <v>13.53073750714</v>
       </c>
       <c r="D40" t="n">
-        <v>12.84378693069438</v>
+        <v>12.84378506203439</v>
       </c>
       <c r="E40" t="n">
-        <v>13.29584589396779</v>
+        <v>13.29584395953713</v>
       </c>
       <c r="F40" t="n">
         <v>720400</v>
@@ -1232,16 +1232,16 @@
         <v>44151</v>
       </c>
       <c r="B41" t="n">
-        <v>13.02106475830078</v>
+        <v>13.02106285095215</v>
       </c>
       <c r="C41" t="n">
-        <v>13.37118910731489</v>
+        <v>13.37118714867942</v>
       </c>
       <c r="D41" t="n">
-        <v>12.65321305426148</v>
+        <v>12.65321120079642</v>
       </c>
       <c r="E41" t="n">
-        <v>13.20720663536447</v>
+        <v>13.20720470074945</v>
       </c>
       <c r="F41" t="n">
         <v>631800</v>
@@ -1252,16 +1252,16 @@
         <v>44152</v>
       </c>
       <c r="B42" t="n">
-        <v>13.02106475830078</v>
+        <v>13.02106285095215</v>
       </c>
       <c r="C42" t="n">
-        <v>13.09197671438291</v>
+        <v>13.09197479664697</v>
       </c>
       <c r="D42" t="n">
-        <v>12.69753270981514</v>
+        <v>12.69753084985806</v>
       </c>
       <c r="E42" t="n">
-        <v>12.93242629252057</v>
+        <v>12.93242439815586</v>
       </c>
       <c r="F42" t="n">
         <v>784800</v>
@@ -1272,16 +1272,16 @@
         <v>44153</v>
       </c>
       <c r="B43" t="n">
-        <v>12.74185180664062</v>
+        <v>12.74184989929199</v>
       </c>
       <c r="C43" t="n">
-        <v>13.18947870198273</v>
+        <v>13.18947672762809</v>
       </c>
       <c r="D43" t="n">
-        <v>12.66207659920759</v>
+        <v>12.66207470380063</v>
       </c>
       <c r="E43" t="n">
-        <v>13.11413554444342</v>
+        <v>13.11413358136703</v>
       </c>
       <c r="F43" t="n">
         <v>532400</v>
@@ -1352,16 +1352,16 @@
         <v>44160</v>
       </c>
       <c r="B47" t="n">
-        <v>13.65039920806885</v>
+        <v>13.65040016174316</v>
       </c>
       <c r="C47" t="n">
-        <v>13.77449405371565</v>
+        <v>13.77449501605975</v>
       </c>
       <c r="D47" t="n">
-        <v>13.34016336194231</v>
+        <v>13.34016429394225</v>
       </c>
       <c r="E47" t="n">
-        <v>13.61494365864504</v>
+        <v>13.61494460984229</v>
       </c>
       <c r="F47" t="n">
         <v>724200</v>
@@ -1372,16 +1372,16 @@
         <v>44161</v>
       </c>
       <c r="B48" t="n">
-        <v>13.53073883056641</v>
+        <v>13.53073978424072</v>
       </c>
       <c r="C48" t="n">
-        <v>13.73904010198848</v>
+        <v>13.7390410703443</v>
       </c>
       <c r="D48" t="n">
-        <v>13.4465315738949</v>
+        <v>13.44653252163411</v>
       </c>
       <c r="E48" t="n">
-        <v>13.65040079545773</v>
+        <v>13.65040175756607</v>
       </c>
       <c r="F48" t="n">
         <v>209800</v>
@@ -1392,16 +1392,16 @@
         <v>44162</v>
       </c>
       <c r="B49" t="n">
-        <v>13.39334583282471</v>
+        <v>13.39334678649902</v>
       </c>
       <c r="C49" t="n">
-        <v>13.71687866190833</v>
+        <v>13.71687963861983</v>
       </c>
       <c r="D49" t="n">
-        <v>13.38891378362335</v>
+        <v>13.38891473698208</v>
       </c>
       <c r="E49" t="n">
-        <v>13.53073682208599</v>
+        <v>13.53073778554325</v>
       </c>
       <c r="F49" t="n">
         <v>510000</v>
@@ -1412,16 +1412,16 @@
         <v>44165</v>
       </c>
       <c r="B50" t="n">
-        <v>13.1362943649292</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="C50" t="n">
-        <v>13.73017549906958</v>
+        <v>13.73017450228043</v>
       </c>
       <c r="D50" t="n">
-        <v>13.1362943649292</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="E50" t="n">
-        <v>13.38891528035829</v>
+        <v>13.38891430834409</v>
       </c>
       <c r="F50" t="n">
         <v>1093200</v>
@@ -1432,16 +1432,16 @@
         <v>44166</v>
       </c>
       <c r="B51" t="n">
-        <v>14.18223476409912</v>
+        <v>14.1822338104248</v>
       </c>
       <c r="C51" t="n">
-        <v>14.40383218228817</v>
+        <v>14.40383121371269</v>
       </c>
       <c r="D51" t="n">
-        <v>13.47755490663178</v>
+        <v>13.47755400034316</v>
       </c>
       <c r="E51" t="n">
-        <v>13.73460787791799</v>
+        <v>13.73460695434403</v>
       </c>
       <c r="F51" t="n">
         <v>2351000</v>
@@ -1452,16 +1452,16 @@
         <v>44167</v>
       </c>
       <c r="B52" t="n">
-        <v>14.18223476409912</v>
+        <v>14.1822338104248</v>
       </c>
       <c r="C52" t="n">
-        <v>14.37280867899403</v>
+        <v>14.37280771250471</v>
       </c>
       <c r="D52" t="n">
-        <v>13.93404589241896</v>
+        <v>13.93404495543393</v>
       </c>
       <c r="E52" t="n">
-        <v>14.18223476409912</v>
+        <v>14.1822338104248</v>
       </c>
       <c r="F52" t="n">
         <v>767800</v>
@@ -1472,16 +1472,16 @@
         <v>44168</v>
       </c>
       <c r="B53" t="n">
-        <v>14.3595142364502</v>
+        <v>14.35951328277588</v>
       </c>
       <c r="C53" t="n">
-        <v>14.44372065177874</v>
+        <v>14.44371969251193</v>
       </c>
       <c r="D53" t="n">
-        <v>14.05814074905197</v>
+        <v>14.0581398153931</v>
       </c>
       <c r="E53" t="n">
-        <v>14.31519373576078</v>
+        <v>14.31519278502997</v>
       </c>
       <c r="F53" t="n">
         <v>1033200</v>
@@ -1512,16 +1512,16 @@
         <v>44172</v>
       </c>
       <c r="B55" t="n">
-        <v>14.25314521789551</v>
+        <v>14.25314426422119</v>
       </c>
       <c r="C55" t="n">
-        <v>14.36837512619167</v>
+        <v>14.36837416480735</v>
       </c>
       <c r="D55" t="n">
-        <v>13.82767860020407</v>
+        <v>13.82767767499762</v>
       </c>
       <c r="E55" t="n">
-        <v>14.06257131172358</v>
+        <v>14.06257037080052</v>
       </c>
       <c r="F55" t="n">
         <v>782600</v>
@@ -1552,16 +1552,16 @@
         <v>44174</v>
       </c>
       <c r="B57" t="n">
-        <v>13.88972568511963</v>
+        <v>13.889723777771</v>
       </c>
       <c r="C57" t="n">
-        <v>14.2487140968875</v>
+        <v>14.24871214024228</v>
       </c>
       <c r="D57" t="n">
-        <v>13.65926417652651</v>
+        <v>13.65926230082504</v>
       </c>
       <c r="E57" t="n">
-        <v>14.1467786461421</v>
+        <v>14.14677670349474</v>
       </c>
       <c r="F57" t="n">
         <v>570800</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.00495719909668</v>
+        <v>14.00495624542236</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10245976017788</v>
+        <v>14.10245879986408</v>
       </c>
       <c r="D58" t="n">
-        <v>13.5174427030365</v>
+        <v>13.51744178255972</v>
       </c>
       <c r="E58" t="n">
-        <v>13.8852943886831</v>
+        <v>13.88529344315728</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1632,16 +1632,16 @@
         <v>44180</v>
       </c>
       <c r="B61" t="n">
-        <v>14.08473110198975</v>
+        <v>14.08473205566406</v>
       </c>
       <c r="C61" t="n">
-        <v>14.1246187017679</v>
+        <v>14.124619658143</v>
       </c>
       <c r="D61" t="n">
-        <v>13.57062519965683</v>
+        <v>13.57062611852114</v>
       </c>
       <c r="E61" t="n">
-        <v>13.75676705017923</v>
+        <v>13.75676798164717</v>
       </c>
       <c r="F61" t="n">
         <v>732800</v>
@@ -1652,16 +1652,16 @@
         <v>44181</v>
       </c>
       <c r="B62" t="n">
-        <v>13.9163179397583</v>
+        <v>13.91631698608398</v>
       </c>
       <c r="C62" t="n">
-        <v>14.1778029654802</v>
+        <v>14.17780199388652</v>
       </c>
       <c r="D62" t="n">
-        <v>13.71688076705103</v>
+        <v>13.71687982704398</v>
       </c>
       <c r="E62" t="n">
-        <v>14.13791536187333</v>
+        <v>14.13791439301312</v>
       </c>
       <c r="F62" t="n">
         <v>564600</v>
@@ -1732,16 +1732,16 @@
         <v>44187</v>
       </c>
       <c r="B66" t="n">
-        <v>13.00776767730713</v>
+        <v>13.00776958465576</v>
       </c>
       <c r="C66" t="n">
-        <v>13.60608083227121</v>
+        <v>13.60608282735141</v>
       </c>
       <c r="D66" t="n">
-        <v>12.94571982987305</v>
+        <v>12.94572172812351</v>
       </c>
       <c r="E66" t="n">
-        <v>13.22493303000889</v>
+        <v>13.22493496920081</v>
       </c>
       <c r="F66" t="n">
         <v>911600</v>
@@ -1752,16 +1752,16 @@
         <v>44188</v>
       </c>
       <c r="B67" t="n">
-        <v>14.04484367370605</v>
+        <v>14.04484272003174</v>
       </c>
       <c r="C67" t="n">
-        <v>14.15121032597093</v>
+        <v>14.1512093650741</v>
       </c>
       <c r="D67" t="n">
-        <v>13.40221086527954</v>
+        <v>13.40220995524134</v>
       </c>
       <c r="E67" t="n">
-        <v>13.45539461407549</v>
+        <v>13.45539370042599</v>
       </c>
       <c r="F67" t="n">
         <v>2040000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294269561768</v>
+        <v>15.11294364929199</v>
       </c>
       <c r="C68" t="n">
-        <v>15.13067089418624</v>
+        <v>15.13067184897926</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586759384061</v>
+        <v>14.07586848207222</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348254853438</v>
+        <v>14.13348344040167</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.19715023040771</v>
+        <v>15.19715118408203</v>
       </c>
       <c r="C69" t="n">
-        <v>15.34783653134916</v>
+        <v>15.34783749447957</v>
       </c>
       <c r="D69" t="n">
-        <v>14.74952253173429</v>
+        <v>14.7495234573184</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510322837077</v>
+        <v>15.13510417815142</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884773254395</v>
+        <v>14.98884677886963</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171721175532</v>
+        <v>15.94171619745412</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952213906937</v>
+        <v>14.74952120062229</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069371156276</v>
+        <v>15.91069269923545</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1852,16 +1852,16 @@
         <v>44201</v>
       </c>
       <c r="B72" t="n">
-        <v>15.13953685760498</v>
+        <v>15.13953495025635</v>
       </c>
       <c r="C72" t="n">
-        <v>15.45863770851384</v>
+        <v>15.45863576096341</v>
       </c>
       <c r="D72" t="n">
-        <v>14.36394582659929</v>
+        <v>14.36394401696318</v>
       </c>
       <c r="E72" t="n">
-        <v>14.84702830782329</v>
+        <v>14.84702643732623</v>
       </c>
       <c r="F72" t="n">
         <v>1878200</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.58997249603271</v>
+        <v>14.5899715423584</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135701596139</v>
+        <v>15.28135601709469</v>
       </c>
       <c r="D73" t="n">
-        <v>14.58997249603271</v>
+        <v>14.5899715423584</v>
       </c>
       <c r="E73" t="n">
-        <v>15.13953481043562</v>
+        <v>15.13953382083913</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1892,16 +1892,16 @@
         <v>44203</v>
       </c>
       <c r="B74" t="n">
-        <v>14.40513229370117</v>
+        <v>14.40512943267822</v>
       </c>
       <c r="C74" t="n">
-        <v>14.96995245275908</v>
+        <v>14.96994947955643</v>
       </c>
       <c r="D74" t="n">
-        <v>14.39623728766692</v>
+        <v>14.39623442841062</v>
       </c>
       <c r="E74" t="n">
-        <v>14.6853190458588</v>
+        <v>14.68531612918757</v>
       </c>
       <c r="F74" t="n">
         <v>1215000</v>
@@ -1912,16 +1912,16 @@
         <v>44204</v>
       </c>
       <c r="B75" t="n">
-        <v>15.06334495544434</v>
+        <v>15.06334686279297</v>
       </c>
       <c r="C75" t="n">
-        <v>15.27237332096537</v>
+        <v>15.27237525478156</v>
       </c>
       <c r="D75" t="n">
-        <v>14.38733987868677</v>
+        <v>14.38734170043839</v>
       </c>
       <c r="E75" t="n">
-        <v>14.38733987868677</v>
+        <v>14.38734170043839</v>
       </c>
       <c r="F75" t="n">
         <v>1077600</v>
@@ -1932,16 +1932,16 @@
         <v>44207</v>
       </c>
       <c r="B76" t="n">
-        <v>15.8327465057373</v>
+        <v>15.83274555206299</v>
       </c>
       <c r="C76" t="n">
-        <v>15.8327465057373</v>
+        <v>15.83274555206299</v>
       </c>
       <c r="D76" t="n">
-        <v>14.80539798490314</v>
+        <v>14.80539709311043</v>
       </c>
       <c r="E76" t="n">
-        <v>14.95216133221568</v>
+        <v>14.95216043158278</v>
       </c>
       <c r="F76" t="n">
         <v>1758200</v>
@@ -1972,16 +1972,16 @@
         <v>44209</v>
       </c>
       <c r="B78" t="n">
-        <v>15.72156238555908</v>
+        <v>15.72156047821045</v>
       </c>
       <c r="C78" t="n">
-        <v>16.71778098957271</v>
+        <v>16.71777896136228</v>
       </c>
       <c r="D78" t="n">
-        <v>15.4146923169876</v>
+        <v>15.41469044686861</v>
       </c>
       <c r="E78" t="n">
-        <v>15.96617080603153</v>
+        <v>15.96616886900687</v>
       </c>
       <c r="F78" t="n">
         <v>1238200</v>
@@ -1992,16 +1992,16 @@
         <v>44210</v>
       </c>
       <c r="B79" t="n">
-        <v>16.08624458312988</v>
+        <v>16.08624649047852</v>
       </c>
       <c r="C79" t="n">
-        <v>16.25524625393452</v>
+        <v>16.2552481813217</v>
       </c>
       <c r="D79" t="n">
-        <v>15.6592946009851</v>
+        <v>15.65929645771021</v>
       </c>
       <c r="E79" t="n">
-        <v>15.94837627237078</v>
+        <v>15.94837816337235</v>
       </c>
       <c r="F79" t="n">
         <v>1217000</v>
@@ -2012,16 +2012,16 @@
         <v>44211</v>
       </c>
       <c r="B80" t="n">
-        <v>15.88166809082031</v>
+        <v>15.881667137146</v>
       </c>
       <c r="C80" t="n">
-        <v>16.09069647449039</v>
+        <v>16.09069550826418</v>
       </c>
       <c r="D80" t="n">
-        <v>15.61037636645245</v>
+        <v>15.61037542906886</v>
       </c>
       <c r="E80" t="n">
-        <v>16.08624812355553</v>
+        <v>16.08624715759644</v>
       </c>
       <c r="F80" t="n">
         <v>728000</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422203063965</v>
+        <v>16.38422584533691</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538036435329</v>
+        <v>16.45538419561817</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169201322673</v>
+        <v>15.92169572023429</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93503536717513</v>
+        <v>15.93503907728939</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2092,16 +2092,16 @@
         <v>44217</v>
       </c>
       <c r="B84" t="n">
-        <v>15.85498523712158</v>
+        <v>15.85498142242432</v>
       </c>
       <c r="C84" t="n">
-        <v>16.36643533398266</v>
+        <v>16.3664313962309</v>
       </c>
       <c r="D84" t="n">
-        <v>15.53032347129166</v>
+        <v>15.53031973470776</v>
       </c>
       <c r="E84" t="n">
-        <v>16.25969866009376</v>
+        <v>16.25969474802276</v>
       </c>
       <c r="F84" t="n">
         <v>928200</v>
@@ -2132,16 +2132,16 @@
         <v>44222</v>
       </c>
       <c r="B86" t="n">
-        <v>14.67197608947754</v>
+        <v>14.67197704315186</v>
       </c>
       <c r="C86" t="n">
-        <v>15.525876234775</v>
+        <v>15.52587724395259</v>
       </c>
       <c r="D86" t="n">
-        <v>14.63639606848242</v>
+        <v>14.63639701984405</v>
       </c>
       <c r="E86" t="n">
-        <v>15.38355954389209</v>
+        <v>15.38356054381913</v>
       </c>
       <c r="F86" t="n">
         <v>1156000</v>
@@ -2152,16 +2152,16 @@
         <v>44223</v>
       </c>
       <c r="B87" t="n">
-        <v>15.00553035736084</v>
+        <v>15.00553131103516</v>
       </c>
       <c r="C87" t="n">
-        <v>15.57034874008907</v>
+        <v>15.57034972966033</v>
       </c>
       <c r="D87" t="n">
-        <v>14.53410528342808</v>
+        <v>14.53410620714105</v>
       </c>
       <c r="E87" t="n">
-        <v>14.74313365433532</v>
+        <v>14.74313459133305</v>
       </c>
       <c r="F87" t="n">
         <v>1909000</v>
@@ -2192,16 +2192,16 @@
         <v>44225</v>
       </c>
       <c r="B89" t="n">
-        <v>15.74379920959473</v>
+        <v>15.74379634857178</v>
       </c>
       <c r="C89" t="n">
-        <v>16.55322600399441</v>
+        <v>16.55322299587936</v>
       </c>
       <c r="D89" t="n">
-        <v>15.38800579515856</v>
+        <v>15.38800299879174</v>
       </c>
       <c r="E89" t="n">
-        <v>16.01064257387312</v>
+        <v>16.01063966435838</v>
       </c>
       <c r="F89" t="n">
         <v>3936400</v>
@@ -2372,16 +2372,16 @@
         <v>44238</v>
       </c>
       <c r="B98" t="n">
-        <v>18.63461112976074</v>
+        <v>18.63461303710938</v>
       </c>
       <c r="C98" t="n">
-        <v>19.14606123399878</v>
+        <v>19.14606319369697</v>
       </c>
       <c r="D98" t="n">
-        <v>18.43447774264635</v>
+        <v>18.4344796295103</v>
       </c>
       <c r="E98" t="n">
-        <v>18.55900442949581</v>
+        <v>18.5590063291057</v>
       </c>
       <c r="F98" t="n">
         <v>912400</v>
@@ -2392,16 +2392,16 @@
         <v>44239</v>
       </c>
       <c r="B99" t="n">
-        <v>18.51897811889648</v>
+        <v>18.51897621154785</v>
       </c>
       <c r="C99" t="n">
-        <v>18.72355816464402</v>
+        <v>18.72355623622481</v>
       </c>
       <c r="D99" t="n">
-        <v>18.16318636617275</v>
+        <v>18.16318449546863</v>
       </c>
       <c r="E99" t="n">
-        <v>18.58124146355452</v>
+        <v>18.58123954979312</v>
       </c>
       <c r="F99" t="n">
         <v>849600</v>
@@ -2412,16 +2412,16 @@
         <v>44244</v>
       </c>
       <c r="B100" t="n">
-        <v>18.52787208557129</v>
+        <v>18.52787017822266</v>
       </c>
       <c r="C100" t="n">
-        <v>18.68797878945395</v>
+        <v>18.68797686562316</v>
       </c>
       <c r="D100" t="n">
-        <v>18.20765867780597</v>
+        <v>18.20765680342165</v>
       </c>
       <c r="E100" t="n">
-        <v>18.5189770801835</v>
+        <v>18.51897517375056</v>
       </c>
       <c r="F100" t="n">
         <v>743200</v>
@@ -2432,16 +2432,16 @@
         <v>44245</v>
       </c>
       <c r="B101" t="n">
-        <v>18.24324035644531</v>
+        <v>18.24323654174805</v>
       </c>
       <c r="C101" t="n">
-        <v>19.03487724582877</v>
+        <v>19.03487326559868</v>
       </c>
       <c r="D101" t="n">
-        <v>17.90523690720254</v>
+        <v>17.90523316318246</v>
       </c>
       <c r="E101" t="n">
-        <v>18.6924271417626</v>
+        <v>18.6924232331395</v>
       </c>
       <c r="F101" t="n">
         <v>1007600</v>
@@ -2452,16 +2452,16 @@
         <v>44246</v>
       </c>
       <c r="B102" t="n">
-        <v>18.27881622314453</v>
+        <v>18.27881813049316</v>
       </c>
       <c r="C102" t="n">
-        <v>18.57234460188025</v>
+        <v>18.57234653985784</v>
       </c>
       <c r="D102" t="n">
-        <v>17.92302450597225</v>
+        <v>17.92302637619491</v>
       </c>
       <c r="E102" t="n">
-        <v>18.23434289470377</v>
+        <v>18.23434479741172</v>
       </c>
       <c r="F102" t="n">
         <v>881800</v>
@@ -2472,16 +2472,16 @@
         <v>44249</v>
       </c>
       <c r="B103" t="n">
-        <v>17.81628608703613</v>
+        <v>17.81628799438477</v>
       </c>
       <c r="C103" t="n">
-        <v>18.46115776875395</v>
+        <v>18.46115974514026</v>
       </c>
       <c r="D103" t="n">
-        <v>16.95793769945958</v>
+        <v>16.95793951491647</v>
       </c>
       <c r="E103" t="n">
-        <v>17.34486104779998</v>
+        <v>17.34486290467952</v>
       </c>
       <c r="F103" t="n">
         <v>2023200</v>
@@ -2492,16 +2492,16 @@
         <v>44250</v>
       </c>
       <c r="B104" t="n">
-        <v>17.70065498352051</v>
+        <v>17.70065116882324</v>
       </c>
       <c r="C104" t="n">
-        <v>18.1009217372794</v>
+        <v>18.10091783631999</v>
       </c>
       <c r="D104" t="n">
-        <v>17.5183116171523</v>
+        <v>17.51830784175215</v>
       </c>
       <c r="E104" t="n">
-        <v>17.86076168502407</v>
+        <v>17.86075783582194</v>
       </c>
       <c r="F104" t="n">
         <v>1151400</v>
@@ -2532,16 +2532,16 @@
         <v>44252</v>
       </c>
       <c r="B106" t="n">
-        <v>16.94459533691406</v>
+        <v>16.9445972442627</v>
       </c>
       <c r="C106" t="n">
-        <v>17.7940487700933</v>
+        <v>17.79405077305967</v>
       </c>
       <c r="D106" t="n">
-        <v>16.6377253111698</v>
+        <v>16.63772718397596</v>
       </c>
       <c r="E106" t="n">
-        <v>17.68731210746428</v>
+        <v>17.68731409841596</v>
       </c>
       <c r="F106" t="n">
         <v>1207600</v>
@@ -2592,16 +2592,16 @@
         <v>44257</v>
       </c>
       <c r="B109" t="n">
-        <v>16.65551567077637</v>
+        <v>16.655517578125</v>
       </c>
       <c r="C109" t="n">
-        <v>16.90456901984825</v>
+        <v>16.90457095571786</v>
       </c>
       <c r="D109" t="n">
-        <v>15.75269219074469</v>
+        <v>15.7526939947042</v>
       </c>
       <c r="E109" t="n">
-        <v>16.17964393988693</v>
+        <v>16.1796457927399</v>
       </c>
       <c r="F109" t="n">
         <v>1243600</v>
@@ -2672,16 +2672,16 @@
         <v>44263</v>
       </c>
       <c r="B113" t="n">
-        <v>14.91213607788086</v>
+        <v>14.91213226318359</v>
       </c>
       <c r="C113" t="n">
-        <v>16.05956643238552</v>
+        <v>16.05956232416226</v>
       </c>
       <c r="D113" t="n">
-        <v>14.76537271657734</v>
+        <v>14.76536893942384</v>
       </c>
       <c r="E113" t="n">
-        <v>16.01064474643469</v>
+        <v>16.01064065072617</v>
       </c>
       <c r="F113" t="n">
         <v>3236800</v>
@@ -2692,16 +2692,16 @@
         <v>44264</v>
       </c>
       <c r="B114" t="n">
-        <v>14.7653694152832</v>
+        <v>14.76537227630615</v>
       </c>
       <c r="C114" t="n">
-        <v>15.42358445966246</v>
+        <v>15.42358744822494</v>
       </c>
       <c r="D114" t="n">
-        <v>14.5563410571555</v>
+        <v>14.55634387767591</v>
       </c>
       <c r="E114" t="n">
-        <v>15.11671444805785</v>
+        <v>15.11671737715943</v>
       </c>
       <c r="F114" t="n">
         <v>1628800</v>
@@ -2732,16 +2732,16 @@
         <v>44266</v>
       </c>
       <c r="B116" t="n">
-        <v>15.81940460205078</v>
+        <v>15.81940650939941</v>
       </c>
       <c r="C116" t="n">
-        <v>15.99285296281361</v>
+        <v>15.99285489107494</v>
       </c>
       <c r="D116" t="n">
-        <v>15.15674282905697</v>
+        <v>15.15674465650835</v>
       </c>
       <c r="E116" t="n">
-        <v>15.15674282905697</v>
+        <v>15.15674465650835</v>
       </c>
       <c r="F116" t="n">
         <v>2295400</v>
@@ -2752,16 +2752,16 @@
         <v>44267</v>
       </c>
       <c r="B117" t="n">
-        <v>15.61037445068359</v>
+        <v>15.61037635803223</v>
       </c>
       <c r="C117" t="n">
-        <v>15.96171948327262</v>
+        <v>15.96172143355023</v>
       </c>
       <c r="D117" t="n">
-        <v>15.41913610112494</v>
+        <v>15.41913798510718</v>
       </c>
       <c r="E117" t="n">
-        <v>15.96171948327262</v>
+        <v>15.96172143355023</v>
       </c>
       <c r="F117" t="n">
         <v>1034800</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708969116211</v>
+        <v>15.67708778381348</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619813612479</v>
+        <v>16.00619618873527</v>
       </c>
       <c r="D118" t="n">
-        <v>15.4947463044602</v>
+        <v>15.49474441929632</v>
       </c>
       <c r="E118" t="n">
-        <v>15.61482634397838</v>
+        <v>15.614824444205</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2792,16 +2792,16 @@
         <v>44271</v>
       </c>
       <c r="B119" t="n">
-        <v>16.46872520446777</v>
+        <v>16.46872901916504</v>
       </c>
       <c r="C119" t="n">
-        <v>16.83786029832273</v>
+        <v>16.8378641985238</v>
       </c>
       <c r="D119" t="n">
-        <v>15.6815350313212</v>
+        <v>15.68153866367939</v>
       </c>
       <c r="E119" t="n">
-        <v>15.68598338234651</v>
+        <v>15.68598701573508</v>
       </c>
       <c r="F119" t="n">
         <v>1963400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880615234375</v>
+        <v>16.58880424499512</v>
       </c>
       <c r="C120" t="n">
-        <v>16.75780787313692</v>
+        <v>16.7578059463568</v>
       </c>
       <c r="D120" t="n">
-        <v>16.07735603179049</v>
+        <v>16.07735418324739</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298771661808</v>
+        <v>16.19298585477987</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2852,16 +2852,16 @@
         <v>44274</v>
       </c>
       <c r="B122" t="n">
-        <v>16.32196044921875</v>
+        <v>16.32196235656738</v>
       </c>
       <c r="C122" t="n">
-        <v>16.54433047796411</v>
+        <v>16.54433241129841</v>
       </c>
       <c r="D122" t="n">
-        <v>15.89056205055718</v>
+        <v>15.89056390749354</v>
       </c>
       <c r="E122" t="n">
-        <v>16.17519541590345</v>
+        <v>16.17519730610144</v>
       </c>
       <c r="F122" t="n">
         <v>1059200</v>
@@ -2892,16 +2892,16 @@
         <v>44278</v>
       </c>
       <c r="B124" t="n">
-        <v>16.0995922088623</v>
+        <v>16.09959411621094</v>
       </c>
       <c r="C124" t="n">
-        <v>16.49985728713733</v>
+        <v>16.49985924190611</v>
       </c>
       <c r="D124" t="n">
-        <v>15.87277380427914</v>
+        <v>15.87277568475618</v>
       </c>
       <c r="E124" t="n">
-        <v>16.4553839550675</v>
+        <v>16.45538590456745</v>
       </c>
       <c r="F124" t="n">
         <v>855200</v>
@@ -2952,16 +2952,16 @@
         <v>44281</v>
       </c>
       <c r="B127" t="n">
-        <v>15.85498523712158</v>
+        <v>15.85498142242432</v>
       </c>
       <c r="C127" t="n">
-        <v>16.41535701641043</v>
+        <v>16.41535306688814</v>
       </c>
       <c r="D127" t="n">
-        <v>15.67264186405827</v>
+        <v>15.67263809323268</v>
       </c>
       <c r="E127" t="n">
-        <v>16.10403860722825</v>
+        <v>16.10403473260894</v>
       </c>
       <c r="F127" t="n">
         <v>1078200</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.58369064331055</v>
+        <v>15.58369159698486</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174564961845</v>
+        <v>16.00174662887645</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245229978017</v>
+        <v>15.39245324175128</v>
       </c>
       <c r="E128" t="n">
-        <v>15.74379732129399</v>
+        <v>15.74379828476634</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -3012,16 +3012,16 @@
         <v>44286</v>
       </c>
       <c r="B130" t="n">
-        <v>16.61548805236816</v>
+        <v>16.6154899597168</v>
       </c>
       <c r="C130" t="n">
-        <v>16.71777805728372</v>
+        <v>16.71777997637457</v>
       </c>
       <c r="D130" t="n">
-        <v>15.94392964648752</v>
+        <v>15.94393147674567</v>
       </c>
       <c r="E130" t="n">
-        <v>16.10848468167865</v>
+        <v>16.10848653082663</v>
       </c>
       <c r="F130" t="n">
         <v>1491400</v>
@@ -3032,16 +3032,16 @@
         <v>44287</v>
       </c>
       <c r="B131" t="n">
-        <v>16.59325408935547</v>
+        <v>16.59325218200684</v>
       </c>
       <c r="C131" t="n">
-        <v>17.04244085328361</v>
+        <v>17.0424388943022</v>
       </c>
       <c r="D131" t="n">
-        <v>16.48651571663801</v>
+        <v>16.48651382155865</v>
       </c>
       <c r="E131" t="n">
-        <v>17.03799419867195</v>
+        <v>17.03799224020167</v>
       </c>
       <c r="F131" t="n">
         <v>1225400</v>
@@ -3052,16 +3052,16 @@
         <v>44291</v>
       </c>
       <c r="B132" t="n">
-        <v>16.86454391479492</v>
+        <v>16.86454200744629</v>
       </c>
       <c r="C132" t="n">
-        <v>17.01130896333182</v>
+        <v>17.01130703938433</v>
       </c>
       <c r="D132" t="n">
-        <v>16.60214888234808</v>
+        <v>16.60214700467584</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90012393742769</v>
+        <v>16.90012202605503</v>
       </c>
       <c r="F132" t="n">
         <v>838600</v>
@@ -3092,16 +3092,16 @@
         <v>44293</v>
       </c>
       <c r="B134" t="n">
-        <v>17.37155151367188</v>
+        <v>17.37154769897461</v>
       </c>
       <c r="C134" t="n">
-        <v>17.63839493494339</v>
+        <v>17.63839106164878</v>
       </c>
       <c r="D134" t="n">
-        <v>17.11360140276686</v>
+        <v>17.11359764471402</v>
       </c>
       <c r="E134" t="n">
-        <v>17.47828820356084</v>
+        <v>17.47828436542479</v>
       </c>
       <c r="F134" t="n">
         <v>869400</v>
@@ -3112,16 +3112,16 @@
         <v>44294</v>
       </c>
       <c r="B135" t="n">
-        <v>17.60725975036621</v>
+        <v>17.60726165771484</v>
       </c>
       <c r="C135" t="n">
-        <v>17.90968313903537</v>
+        <v>17.90968507914474</v>
       </c>
       <c r="D135" t="n">
-        <v>17.2737046919707</v>
+        <v>17.27370656318618</v>
       </c>
       <c r="E135" t="n">
-        <v>17.38044305713872</v>
+        <v>17.38044493991689</v>
       </c>
       <c r="F135" t="n">
         <v>710000</v>
@@ -3132,16 +3132,16 @@
         <v>44295</v>
       </c>
       <c r="B136" t="n">
-        <v>18.03420829772949</v>
+        <v>18.03421020507812</v>
       </c>
       <c r="C136" t="n">
-        <v>18.25657831791493</v>
+        <v>18.25658024878204</v>
       </c>
       <c r="D136" t="n">
-        <v>17.41157325913943</v>
+        <v>17.41157510063643</v>
       </c>
       <c r="E136" t="n">
-        <v>17.6428365871695</v>
+        <v>17.64283845312556</v>
       </c>
       <c r="F136" t="n">
         <v>1023600</v>
@@ -3152,16 +3152,16 @@
         <v>44298</v>
       </c>
       <c r="B137" t="n">
-        <v>17.7451286315918</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="C137" t="n">
-        <v>18.05644530861555</v>
+        <v>18.05644724942629</v>
       </c>
       <c r="D137" t="n">
-        <v>17.58946859653127</v>
+        <v>17.58947048714867</v>
       </c>
       <c r="E137" t="n">
-        <v>18.05644530861555</v>
+        <v>18.05644724942629</v>
       </c>
       <c r="F137" t="n">
         <v>810600</v>
@@ -3192,16 +3192,16 @@
         <v>44300</v>
       </c>
       <c r="B139" t="n">
-        <v>17.16251945495605</v>
+        <v>17.16252136230469</v>
       </c>
       <c r="C139" t="n">
-        <v>17.71399789099429</v>
+        <v>17.71399985963123</v>
       </c>
       <c r="D139" t="n">
-        <v>17.07801945199119</v>
+        <v>17.07802134994895</v>
       </c>
       <c r="E139" t="n">
-        <v>17.37154783179656</v>
+        <v>17.37154976237547</v>
       </c>
       <c r="F139" t="n">
         <v>861200</v>
@@ -3232,16 +3232,16 @@
         <v>44302</v>
       </c>
       <c r="B141" t="n">
-        <v>17.7451286315918</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="C141" t="n">
-        <v>17.7451286315918</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="D141" t="n">
-        <v>17.12249188444699</v>
+        <v>17.12249372487104</v>
       </c>
       <c r="E141" t="n">
-        <v>17.38488858118748</v>
+        <v>17.38489044981543</v>
       </c>
       <c r="F141" t="n">
         <v>774600</v>
@@ -3272,16 +3272,16 @@
         <v>44306</v>
       </c>
       <c r="B143" t="n">
-        <v>17.81184196472168</v>
+        <v>17.81183815002441</v>
       </c>
       <c r="C143" t="n">
-        <v>18.40779381004686</v>
+        <v>18.40778986771676</v>
       </c>
       <c r="D143" t="n">
-        <v>17.62949857828519</v>
+        <v>17.62949480263974</v>
       </c>
       <c r="E143" t="n">
-        <v>18.01642201847014</v>
+        <v>18.01641815995871</v>
       </c>
       <c r="F143" t="n">
         <v>1050400</v>
@@ -3292,16 +3292,16 @@
         <v>44308</v>
       </c>
       <c r="B144" t="n">
-        <v>17.32707595825195</v>
+        <v>17.32707214355469</v>
       </c>
       <c r="C144" t="n">
-        <v>17.97639617463046</v>
+        <v>17.97639221698004</v>
       </c>
       <c r="D144" t="n">
-        <v>17.26926095986211</v>
+        <v>17.26925715789328</v>
       </c>
       <c r="E144" t="n">
-        <v>17.94971285123485</v>
+        <v>17.94970889945899</v>
       </c>
       <c r="F144" t="n">
         <v>1084000</v>
@@ -3312,16 +3312,16 @@
         <v>44309</v>
       </c>
       <c r="B145" t="n">
-        <v>17.21144104003906</v>
+        <v>17.2114429473877</v>
       </c>
       <c r="C145" t="n">
-        <v>17.57167941077477</v>
+        <v>17.57168135804453</v>
       </c>
       <c r="D145" t="n">
-        <v>16.88233264191577</v>
+        <v>16.88233451279305</v>
       </c>
       <c r="E145" t="n">
-        <v>17.52275942819921</v>
+        <v>17.52276137004772</v>
       </c>
       <c r="F145" t="n">
         <v>903000</v>
@@ -3332,16 +3332,16 @@
         <v>44312</v>
       </c>
       <c r="B146" t="n">
-        <v>17.0869140625</v>
+        <v>17.08691024780273</v>
       </c>
       <c r="C146" t="n">
-        <v>17.31817912126438</v>
+        <v>17.3181752549366</v>
       </c>
       <c r="D146" t="n">
-        <v>16.90012403227619</v>
+        <v>16.90012025928028</v>
       </c>
       <c r="E146" t="n">
-        <v>17.31817912126438</v>
+        <v>17.3181752549366</v>
       </c>
       <c r="F146" t="n">
         <v>836400</v>
@@ -3372,16 +3372,16 @@
         <v>44314</v>
       </c>
       <c r="B148" t="n">
-        <v>18.56789779663086</v>
+        <v>18.56789970397949</v>
       </c>
       <c r="C148" t="n">
-        <v>18.63905613948654</v>
+        <v>18.63905805414477</v>
       </c>
       <c r="D148" t="n">
-        <v>17.32707260257054</v>
+        <v>17.32707438245799</v>
       </c>
       <c r="E148" t="n">
-        <v>17.33596760749609</v>
+        <v>17.33596938829726</v>
       </c>
       <c r="F148" t="n">
         <v>2195600</v>
@@ -3432,16 +3432,16 @@
         <v>44319</v>
       </c>
       <c r="B151" t="n">
-        <v>19.44736099243164</v>
+        <v>19.44735527038574</v>
       </c>
       <c r="C151" t="n">
-        <v>19.67089387740212</v>
+        <v>19.67088808958558</v>
       </c>
       <c r="D151" t="n">
-        <v>18.83935127244465</v>
+        <v>18.83934572929498</v>
       </c>
       <c r="E151" t="n">
-        <v>19.62618798257625</v>
+        <v>19.62618220791364</v>
       </c>
       <c r="F151" t="n">
         <v>2225200</v>
@@ -3472,16 +3472,16 @@
         <v>44321</v>
       </c>
       <c r="B153" t="n">
-        <v>20.46219825744629</v>
+        <v>20.46219635009766</v>
       </c>
       <c r="C153" t="n">
-        <v>21.00761898287081</v>
+        <v>21.00761702468171</v>
       </c>
       <c r="D153" t="n">
-        <v>19.89442458705298</v>
+        <v>19.8944227326284</v>
       </c>
       <c r="E153" t="n">
-        <v>20.09113289036689</v>
+        <v>20.09113101760648</v>
       </c>
       <c r="F153" t="n">
         <v>1994000</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.83325958251953</v>
+        <v>20.83326148986816</v>
       </c>
       <c r="C155" t="n">
-        <v>20.87796717286325</v>
+        <v>20.877969084305</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384096914172</v>
+        <v>20.36384283351365</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902565479451</v>
+        <v>20.86902756541763</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3532,16 +3532,16 @@
         <v>44326</v>
       </c>
       <c r="B156" t="n">
-        <v>20.36384010314941</v>
+        <v>20.36384201049805</v>
       </c>
       <c r="C156" t="n">
-        <v>20.94502510954077</v>
+        <v>20.94502707132523</v>
       </c>
       <c r="D156" t="n">
-        <v>20.25207369017338</v>
+        <v>20.25207558705358</v>
       </c>
       <c r="E156" t="n">
-        <v>20.83325869656473</v>
+        <v>20.83326064788076</v>
       </c>
       <c r="F156" t="n">
         <v>979800</v>
@@ -3552,16 +3552,16 @@
         <v>44327</v>
       </c>
       <c r="B157" t="n">
-        <v>20.60078620910645</v>
+        <v>20.60078811645508</v>
       </c>
       <c r="C157" t="n">
-        <v>20.60972602144025</v>
+        <v>20.60972792961658</v>
       </c>
       <c r="D157" t="n">
-        <v>19.78265524153291</v>
+        <v>19.7826570731339</v>
       </c>
       <c r="E157" t="n">
-        <v>20.25207383838357</v>
+        <v>20.25207571344624</v>
       </c>
       <c r="F157" t="n">
         <v>1012800</v>
@@ -3572,16 +3572,16 @@
         <v>44328</v>
       </c>
       <c r="B158" t="n">
-        <v>20.1581916809082</v>
+        <v>20.15819358825684</v>
       </c>
       <c r="C158" t="n">
-        <v>20.59631584486362</v>
+        <v>20.59631779366714</v>
       </c>
       <c r="D158" t="n">
-        <v>19.57253502320829</v>
+        <v>19.57253687514265</v>
       </c>
       <c r="E158" t="n">
-        <v>20.59631584486362</v>
+        <v>20.59631779366714</v>
       </c>
       <c r="F158" t="n">
         <v>1344400</v>
@@ -3592,16 +3592,16 @@
         <v>44329</v>
       </c>
       <c r="B159" t="n">
-        <v>20.90478897094727</v>
+        <v>20.9047908782959</v>
       </c>
       <c r="C159" t="n">
-        <v>20.9718495003822</v>
+        <v>20.97185141384942</v>
       </c>
       <c r="D159" t="n">
-        <v>20.1581901566442</v>
+        <v>20.15819199587331</v>
       </c>
       <c r="E159" t="n">
-        <v>20.25654514503674</v>
+        <v>20.25654699323974</v>
       </c>
       <c r="F159" t="n">
         <v>1469200</v>
@@ -3632,16 +3632,16 @@
         <v>44333</v>
       </c>
       <c r="B161" t="n">
-        <v>20.98526382446289</v>
+        <v>20.98526191711426</v>
       </c>
       <c r="C161" t="n">
-        <v>21.13279632744209</v>
+        <v>21.13279440668424</v>
       </c>
       <c r="D161" t="n">
-        <v>20.03748499628314</v>
+        <v>20.03748317507803</v>
       </c>
       <c r="E161" t="n">
-        <v>20.16266284941433</v>
+        <v>20.16266101683182</v>
       </c>
       <c r="F161" t="n">
         <v>1096800</v>
@@ -3712,16 +3712,16 @@
         <v>44337</v>
       </c>
       <c r="B165" t="n">
-        <v>21.94645690917969</v>
+        <v>21.94645500183105</v>
       </c>
       <c r="C165" t="n">
-        <v>22.04034030384297</v>
+        <v>22.04033838833501</v>
       </c>
       <c r="D165" t="n">
-        <v>21.5038610829635</v>
+        <v>21.50385921408051</v>
       </c>
       <c r="E165" t="n">
-        <v>22.04034030384297</v>
+        <v>22.04033838833501</v>
       </c>
       <c r="F165" t="n">
         <v>653400</v>
@@ -3732,16 +3732,16 @@
         <v>44340</v>
       </c>
       <c r="B166" t="n">
-        <v>21.87045288085938</v>
+        <v>21.87045478820801</v>
       </c>
       <c r="C166" t="n">
-        <v>22.12081028286665</v>
+        <v>22.12081221204925</v>
       </c>
       <c r="D166" t="n">
-        <v>21.50385914906818</v>
+        <v>21.50386102444573</v>
       </c>
       <c r="E166" t="n">
-        <v>21.67821620187448</v>
+        <v>21.67821809245792</v>
       </c>
       <c r="F166" t="n">
         <v>900600</v>
@@ -3752,16 +3752,16 @@
         <v>44341</v>
       </c>
       <c r="B167" t="n">
-        <v>22.17893218994141</v>
+        <v>22.17892837524414</v>
       </c>
       <c r="C167" t="n">
-        <v>22.36222907971693</v>
+        <v>22.36222523349326</v>
       </c>
       <c r="D167" t="n">
-        <v>21.77210242456545</v>
+        <v>21.77209867984146</v>
       </c>
       <c r="E167" t="n">
-        <v>21.98222216794391</v>
+        <v>21.98221838708007</v>
       </c>
       <c r="F167" t="n">
         <v>773000</v>
@@ -3792,16 +3792,16 @@
         <v>44343</v>
       </c>
       <c r="B169" t="n">
-        <v>22.3443431854248</v>
+        <v>22.34434127807617</v>
       </c>
       <c r="C169" t="n">
-        <v>22.3443431854248</v>
+        <v>22.34434127807617</v>
       </c>
       <c r="D169" t="n">
-        <v>21.80339410488992</v>
+        <v>21.80339224371756</v>
       </c>
       <c r="E169" t="n">
-        <v>22.27281274258895</v>
+        <v>22.27281084134627</v>
       </c>
       <c r="F169" t="n">
         <v>1342400</v>
@@ -3812,16 +3812,16 @@
         <v>44344</v>
       </c>
       <c r="B170" t="n">
-        <v>22.21469497680664</v>
+        <v>22.21469306945801</v>
       </c>
       <c r="C170" t="n">
-        <v>22.54552435945486</v>
+        <v>22.54552242370129</v>
       </c>
       <c r="D170" t="n">
-        <v>21.94198632060221</v>
+        <v>21.94198443666828</v>
       </c>
       <c r="E170" t="n">
-        <v>22.29516694270971</v>
+        <v>22.29516502845177</v>
       </c>
       <c r="F170" t="n">
         <v>840600</v>
@@ -3852,16 +3852,16 @@
         <v>44348</v>
       </c>
       <c r="B172" t="n">
-        <v>23.69448471069336</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C172" t="n">
-        <v>24.09237295466603</v>
+        <v>24.09236907591068</v>
       </c>
       <c r="D172" t="n">
-        <v>23.10435805810596</v>
+        <v>23.10435433841622</v>
       </c>
       <c r="E172" t="n">
-        <v>23.32341932020708</v>
+        <v>23.32341556524954</v>
       </c>
       <c r="F172" t="n">
         <v>1770600</v>
@@ -3872,16 +3872,16 @@
         <v>44349</v>
       </c>
       <c r="B173" t="n">
-        <v>23.69448471069336</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C173" t="n">
-        <v>24.03872554227276</v>
+        <v>24.03872167215439</v>
       </c>
       <c r="D173" t="n">
-        <v>23.47095183606418</v>
+        <v>23.47094805735462</v>
       </c>
       <c r="E173" t="n">
-        <v>24.03872554227276</v>
+        <v>24.03872167215439</v>
       </c>
       <c r="F173" t="n">
         <v>823800</v>
@@ -3892,16 +3892,16 @@
         <v>44351</v>
       </c>
       <c r="B174" t="n">
-        <v>23.69448471069336</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C174" t="n">
-        <v>23.91801758532254</v>
+        <v>23.91801373463757</v>
       </c>
       <c r="D174" t="n">
-        <v>23.39942138439966</v>
+        <v>23.39941761720616</v>
       </c>
       <c r="E174" t="n">
-        <v>23.69448471069336</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="F174" t="n">
         <v>902800</v>
@@ -3932,16 +3932,16 @@
         <v>44355</v>
       </c>
       <c r="B176" t="n">
-        <v>23.40389060974121</v>
+        <v>23.40388870239258</v>
       </c>
       <c r="C176" t="n">
-        <v>23.68107259410971</v>
+        <v>23.68107066417156</v>
       </c>
       <c r="D176" t="n">
-        <v>22.95235496652872</v>
+        <v>22.95235309597892</v>
       </c>
       <c r="E176" t="n">
-        <v>23.47095115234466</v>
+        <v>23.47094923953079</v>
       </c>
       <c r="F176" t="n">
         <v>1006800</v>
@@ -3972,16 +3972,16 @@
         <v>44357</v>
       </c>
       <c r="B178" t="n">
-        <v>23.69448471069336</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C178" t="n">
-        <v>23.89119302641566</v>
+        <v>23.89118918004931</v>
       </c>
       <c r="D178" t="n">
-        <v>23.44859888968536</v>
+        <v>23.44859511457452</v>
       </c>
       <c r="E178" t="n">
-        <v>23.69448471069336</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="F178" t="n">
         <v>946600</v>
@@ -3992,16 +3992,16 @@
         <v>44358</v>
       </c>
       <c r="B179" t="n">
-        <v>23.30553436279297</v>
+        <v>23.3055362701416</v>
       </c>
       <c r="C179" t="n">
-        <v>23.56483157022843</v>
+        <v>23.5648334987982</v>
       </c>
       <c r="D179" t="n">
-        <v>22.55893379079491</v>
+        <v>22.55893563704099</v>
       </c>
       <c r="E179" t="n">
-        <v>23.56483157022843</v>
+        <v>23.5648334987982</v>
       </c>
       <c r="F179" t="n">
         <v>855400</v>
@@ -4012,16 +4012,16 @@
         <v>44361</v>
       </c>
       <c r="B180" t="n">
-        <v>24.58860969543457</v>
+        <v>24.5886116027832</v>
       </c>
       <c r="C180" t="n">
-        <v>24.76743662993302</v>
+        <v>24.76743855115333</v>
       </c>
       <c r="D180" t="n">
-        <v>23.26082422614669</v>
+        <v>23.26082603049845</v>
       </c>
       <c r="E180" t="n">
-        <v>23.45753419517899</v>
+        <v>23.45753601478963</v>
       </c>
       <c r="F180" t="n">
         <v>1774600</v>
@@ -4072,16 +4072,16 @@
         <v>44364</v>
       </c>
       <c r="B183" t="n">
-        <v>24.58860969543457</v>
+        <v>24.5886116027832</v>
       </c>
       <c r="C183" t="n">
-        <v>24.71378752633146</v>
+        <v>24.71378944339019</v>
       </c>
       <c r="D183" t="n">
-        <v>23.96718874145352</v>
+        <v>23.96719060059827</v>
       </c>
       <c r="E183" t="n">
-        <v>24.63331557634916</v>
+        <v>24.63331748716565</v>
       </c>
       <c r="F183" t="n">
         <v>897400</v>
@@ -4112,16 +4112,16 @@
         <v>44368</v>
       </c>
       <c r="B185" t="n">
-        <v>25.23685646057129</v>
+        <v>25.23685836791992</v>
       </c>
       <c r="C185" t="n">
-        <v>25.6481560428541</v>
+        <v>25.64815798128789</v>
       </c>
       <c r="D185" t="n">
-        <v>24.69590742957842</v>
+        <v>24.69590929604326</v>
       </c>
       <c r="E185" t="n">
-        <v>25.25026788443091</v>
+        <v>25.25026979279315</v>
       </c>
       <c r="F185" t="n">
         <v>748400</v>
@@ -4132,16 +4132,16 @@
         <v>44369</v>
       </c>
       <c r="B186" t="n">
-        <v>24.58860969543457</v>
+        <v>24.5886116027832</v>
       </c>
       <c r="C186" t="n">
-        <v>25.26814965894062</v>
+        <v>25.26815161900145</v>
       </c>
       <c r="D186" t="n">
-        <v>24.54390381451998</v>
+        <v>24.54390571840076</v>
       </c>
       <c r="E186" t="n">
-        <v>25.23238358987291</v>
+        <v>25.23238554715936</v>
       </c>
       <c r="F186" t="n">
         <v>871000</v>
@@ -4152,16 +4152,16 @@
         <v>44370</v>
       </c>
       <c r="B187" t="n">
-        <v>24.72273254394531</v>
+        <v>24.72273445129395</v>
       </c>
       <c r="C187" t="n">
-        <v>24.87920656014071</v>
+        <v>24.87920847956124</v>
       </c>
       <c r="D187" t="n">
-        <v>24.28013846179841</v>
+        <v>24.28014033500109</v>
       </c>
       <c r="E187" t="n">
-        <v>24.71379102541241</v>
+        <v>24.71379293207121</v>
       </c>
       <c r="F187" t="n">
         <v>1264600</v>
@@ -4172,16 +4172,16 @@
         <v>44371</v>
       </c>
       <c r="B188" t="n">
-        <v>24.58414268493652</v>
+        <v>24.58414459228516</v>
       </c>
       <c r="C188" t="n">
-        <v>25.05803121795611</v>
+        <v>25.05803316207115</v>
       </c>
       <c r="D188" t="n">
-        <v>23.98060298898671</v>
+        <v>23.98060484951002</v>
       </c>
       <c r="E188" t="n">
-        <v>25.05356131150621</v>
+        <v>25.05356325527446</v>
       </c>
       <c r="F188" t="n">
         <v>1450200</v>
@@ -4192,16 +4192,16 @@
         <v>44372</v>
       </c>
       <c r="B189" t="n">
-        <v>24.35167121887207</v>
+        <v>24.3516674041748</v>
       </c>
       <c r="C189" t="n">
-        <v>24.58861551354074</v>
+        <v>24.58861166172607</v>
       </c>
       <c r="D189" t="n">
-        <v>24.0029587846305</v>
+        <v>24.00295502455915</v>
       </c>
       <c r="E189" t="n">
-        <v>24.27119924984866</v>
+        <v>24.27119544775736</v>
       </c>
       <c r="F189" t="n">
         <v>926400</v>
@@ -4212,16 +4212,16 @@
         <v>44375</v>
       </c>
       <c r="B190" t="n">
-        <v>24.48578834533691</v>
+        <v>24.48578643798828</v>
       </c>
       <c r="C190" t="n">
-        <v>25.01332600242071</v>
+        <v>25.01332405397893</v>
       </c>
       <c r="D190" t="n">
-        <v>24.06107559355992</v>
+        <v>24.06107371929478</v>
       </c>
       <c r="E190" t="n">
-        <v>24.06107559355992</v>
+        <v>24.06107371929478</v>
       </c>
       <c r="F190" t="n">
         <v>1351800</v>
@@ -4252,16 +4252,16 @@
         <v>44377</v>
       </c>
       <c r="B192" t="n">
-        <v>24.86579132080078</v>
+        <v>24.86579322814941</v>
       </c>
       <c r="C192" t="n">
-        <v>24.86579132080078</v>
+        <v>24.86579322814941</v>
       </c>
       <c r="D192" t="n">
-        <v>24.12813401130879</v>
+        <v>24.12813586207488</v>
       </c>
       <c r="E192" t="n">
-        <v>24.16836998858436</v>
+        <v>24.16837184243678</v>
       </c>
       <c r="F192" t="n">
         <v>1430400</v>
@@ -4292,16 +4292,16 @@
         <v>44379</v>
       </c>
       <c r="B194" t="n">
-        <v>26.42605400085449</v>
+        <v>26.42605209350586</v>
       </c>
       <c r="C194" t="n">
-        <v>26.7702947971231</v>
+        <v>26.77029286492826</v>
       </c>
       <c r="D194" t="n">
-        <v>25.41568455613461</v>
+        <v>25.41568272171123</v>
       </c>
       <c r="E194" t="n">
-        <v>25.41568455613461</v>
+        <v>25.41568272171123</v>
       </c>
       <c r="F194" t="n">
         <v>2268600</v>
@@ -4352,16 +4352,16 @@
         <v>44384</v>
       </c>
       <c r="B197" t="n">
-        <v>26.52440643310547</v>
+        <v>26.52441024780273</v>
       </c>
       <c r="C197" t="n">
-        <v>26.93570602180775</v>
+        <v>26.93570989565746</v>
       </c>
       <c r="D197" t="n">
-        <v>26.10863523276678</v>
+        <v>26.1086389876685</v>
       </c>
       <c r="E197" t="n">
-        <v>26.19804700045325</v>
+        <v>26.19805076821403</v>
       </c>
       <c r="F197" t="n">
         <v>915800</v>
@@ -4372,16 +4372,16 @@
         <v>44385</v>
       </c>
       <c r="B198" t="n">
-        <v>26.52440643310547</v>
+        <v>26.52441024780273</v>
       </c>
       <c r="C198" t="n">
-        <v>26.52440643310547</v>
+        <v>26.52441024780273</v>
       </c>
       <c r="D198" t="n">
-        <v>25.82251177774154</v>
+        <v>25.82251549149344</v>
       </c>
       <c r="E198" t="n">
-        <v>26.23828297808023</v>
+        <v>26.23828675162768</v>
       </c>
       <c r="F198" t="n">
         <v>1041800</v>
@@ -4392,16 +4392,16 @@
         <v>44389</v>
       </c>
       <c r="B199" t="n">
-        <v>27.54371643066406</v>
+        <v>27.5437183380127</v>
       </c>
       <c r="C199" t="n">
-        <v>27.57501089139074</v>
+        <v>27.57501280090645</v>
       </c>
       <c r="D199" t="n">
-        <v>26.56911312552412</v>
+        <v>26.56911496538337</v>
       </c>
       <c r="E199" t="n">
-        <v>26.81499890498525</v>
+        <v>26.81500076187162</v>
       </c>
       <c r="F199" t="n">
         <v>886400</v>
@@ -4432,16 +4432,16 @@
         <v>44391</v>
       </c>
       <c r="B201" t="n">
-        <v>28.1740837097168</v>
+        <v>28.1740779876709</v>
       </c>
       <c r="C201" t="n">
-        <v>28.33502765224171</v>
+        <v>28.33502189750872</v>
       </c>
       <c r="D201" t="n">
-        <v>27.44089615414376</v>
+        <v>27.44089058100538</v>
       </c>
       <c r="E201" t="n">
-        <v>27.67337054829968</v>
+        <v>27.67336492794666</v>
       </c>
       <c r="F201" t="n">
         <v>880600</v>
@@ -4452,16 +4452,16 @@
         <v>44392</v>
       </c>
       <c r="B202" t="n">
-        <v>28.47808456420898</v>
+        <v>28.47808647155762</v>
       </c>
       <c r="C202" t="n">
-        <v>28.76420462521192</v>
+        <v>28.76420655172373</v>
       </c>
       <c r="D202" t="n">
-        <v>27.81195594110106</v>
+        <v>27.81195780383505</v>
       </c>
       <c r="E202" t="n">
-        <v>28.21431574102132</v>
+        <v>28.21431763070376</v>
       </c>
       <c r="F202" t="n">
         <v>1015800</v>
@@ -4472,16 +4472,16 @@
         <v>44393</v>
       </c>
       <c r="B203" t="n">
-        <v>28.79102897644043</v>
+        <v>28.79103088378906</v>
       </c>
       <c r="C203" t="n">
-        <v>29.03244484038268</v>
+        <v>29.03244676372463</v>
       </c>
       <c r="D203" t="n">
-        <v>28.15172495086382</v>
+        <v>28.15172681585982</v>
       </c>
       <c r="E203" t="n">
-        <v>28.72844005736358</v>
+        <v>28.72844196056582</v>
       </c>
       <c r="F203" t="n">
         <v>1048600</v>
@@ -4492,16 +4492,16 @@
         <v>44396</v>
       </c>
       <c r="B204" t="n">
-        <v>28.77314758300781</v>
+        <v>28.77314567565918</v>
       </c>
       <c r="C204" t="n">
-        <v>29.12185826943477</v>
+        <v>29.12185633897039</v>
       </c>
       <c r="D204" t="n">
-        <v>28.02207710038034</v>
+        <v>28.02207524281956</v>
       </c>
       <c r="E204" t="n">
-        <v>28.3842009169608</v>
+        <v>28.38419903539513</v>
       </c>
       <c r="F204" t="n">
         <v>866800</v>
@@ -4512,16 +4512,16 @@
         <v>44397</v>
       </c>
       <c r="B205" t="n">
-        <v>29.39903831481934</v>
+        <v>29.39904022216797</v>
       </c>
       <c r="C205" t="n">
-        <v>29.60468810602794</v>
+        <v>29.60469002671871</v>
       </c>
       <c r="D205" t="n">
-        <v>28.661379304737</v>
+        <v>28.66138116422784</v>
       </c>
       <c r="E205" t="n">
-        <v>28.8402062482176</v>
+        <v>28.84020811931037</v>
       </c>
       <c r="F205" t="n">
         <v>665800</v>
@@ -4552,16 +4552,16 @@
         <v>44399</v>
       </c>
       <c r="B207" t="n">
-        <v>30.17693328857422</v>
+        <v>30.17693519592285</v>
       </c>
       <c r="C207" t="n">
-        <v>30.65082181615548</v>
+        <v>30.65082375345648</v>
       </c>
       <c r="D207" t="n">
-        <v>29.62257280245648</v>
+        <v>29.62257467476647</v>
       </c>
       <c r="E207" t="n">
-        <v>29.69410153735533</v>
+        <v>29.69410341418633</v>
       </c>
       <c r="F207" t="n">
         <v>1168200</v>
@@ -4592,16 +4592,16 @@
         <v>44403</v>
       </c>
       <c r="B209" t="n">
-        <v>30.0875186920166</v>
+        <v>30.08752250671387</v>
       </c>
       <c r="C209" t="n">
-        <v>30.48987503607723</v>
+        <v>30.48987890178793</v>
       </c>
       <c r="D209" t="n">
-        <v>29.56444930522557</v>
+        <v>29.56445305360459</v>
       </c>
       <c r="E209" t="n">
-        <v>30.48987503607723</v>
+        <v>30.48987890178793</v>
       </c>
       <c r="F209" t="n">
         <v>1240800</v>
@@ -4612,16 +4612,16 @@
         <v>44404</v>
       </c>
       <c r="B210" t="n">
-        <v>29.40797996520996</v>
+        <v>29.40798187255859</v>
       </c>
       <c r="C210" t="n">
-        <v>30.1992881310479</v>
+        <v>30.19929008971936</v>
       </c>
       <c r="D210" t="n">
-        <v>29.30068515675142</v>
+        <v>29.3006870571411</v>
       </c>
       <c r="E210" t="n">
-        <v>29.98916671513793</v>
+        <v>29.98916866018129</v>
       </c>
       <c r="F210" t="n">
         <v>1032400</v>
@@ -4632,16 +4632,16 @@
         <v>44405</v>
       </c>
       <c r="B211" t="n">
-        <v>29.43927383422852</v>
+        <v>29.43927574157715</v>
       </c>
       <c r="C211" t="n">
-        <v>30.57034943923792</v>
+        <v>30.57035141986809</v>
       </c>
       <c r="D211" t="n">
-        <v>28.7329092535022</v>
+        <v>28.73291111508599</v>
       </c>
       <c r="E211" t="n">
-        <v>29.52868901517891</v>
+        <v>29.52869092832068</v>
       </c>
       <c r="F211" t="n">
         <v>1257400</v>
@@ -4652,16 +4652,16 @@
         <v>44406</v>
       </c>
       <c r="B212" t="n">
-        <v>30.84753227233887</v>
+        <v>30.8475341796875</v>
       </c>
       <c r="C212" t="n">
-        <v>31.51365918811201</v>
+        <v>31.51366113664825</v>
       </c>
       <c r="D212" t="n">
-        <v>29.56445252818104</v>
+        <v>29.56445435619494</v>
       </c>
       <c r="E212" t="n">
-        <v>29.56445252818104</v>
+        <v>29.56445435619494</v>
       </c>
       <c r="F212" t="n">
         <v>1386000</v>
@@ -4672,16 +4672,16 @@
         <v>44407</v>
       </c>
       <c r="B213" t="n">
-        <v>31.13812828063965</v>
+        <v>31.13812446594238</v>
       </c>
       <c r="C213" t="n">
-        <v>31.58072239125372</v>
+        <v>31.58071852233474</v>
       </c>
       <c r="D213" t="n">
-        <v>30.41388058167417</v>
+        <v>30.41387685570368</v>
       </c>
       <c r="E213" t="n">
-        <v>30.80282898848094</v>
+        <v>30.80282521486082</v>
       </c>
       <c r="F213" t="n">
         <v>1548200</v>
@@ -4692,16 +4692,16 @@
         <v>44410</v>
       </c>
       <c r="B214" t="n">
-        <v>31.24989318847656</v>
+        <v>31.24989128112793</v>
       </c>
       <c r="C214" t="n">
-        <v>31.98755227744596</v>
+        <v>31.98755032507403</v>
       </c>
       <c r="D214" t="n">
-        <v>31.03977176322897</v>
+        <v>31.03976986870518</v>
       </c>
       <c r="E214" t="n">
-        <v>31.58072085224903</v>
+        <v>31.58071892470821</v>
       </c>
       <c r="F214" t="n">
         <v>1185600</v>
@@ -4712,16 +4712,16 @@
         <v>44411</v>
       </c>
       <c r="B215" t="n">
-        <v>30.62399673461914</v>
+        <v>30.62400245666504</v>
       </c>
       <c r="C215" t="n">
-        <v>31.14259452090504</v>
+        <v>31.14260033985012</v>
       </c>
       <c r="D215" t="n">
-        <v>30.20375393613507</v>
+        <v>30.20375957965926</v>
       </c>
       <c r="E215" t="n">
-        <v>31.13812290941217</v>
+        <v>31.13812872752174</v>
       </c>
       <c r="F215" t="n">
         <v>1467200</v>
@@ -4732,16 +4732,16 @@
         <v>44412</v>
       </c>
       <c r="B216" t="n">
-        <v>29.78798484802246</v>
+        <v>29.78798675537109</v>
       </c>
       <c r="C216" t="n">
-        <v>30.84753173103446</v>
+        <v>30.84753370622673</v>
       </c>
       <c r="D216" t="n">
-        <v>29.75669038704778</v>
+        <v>29.7566922923926</v>
       </c>
       <c r="E216" t="n">
-        <v>30.62399889240378</v>
+        <v>30.62400085328306</v>
       </c>
       <c r="F216" t="n">
         <v>1263400</v>
@@ -4752,16 +4752,16 @@
         <v>44413</v>
       </c>
       <c r="B217" t="n">
-        <v>29.48398399353027</v>
+        <v>29.48397827148438</v>
       </c>
       <c r="C217" t="n">
-        <v>30.38705869242438</v>
+        <v>30.38705279511604</v>
       </c>
       <c r="D217" t="n">
-        <v>29.13974487677855</v>
+        <v>29.13973922154018</v>
       </c>
       <c r="E217" t="n">
-        <v>29.82375490871703</v>
+        <v>29.82374912073076</v>
       </c>
       <c r="F217" t="n">
         <v>1197200</v>
@@ -4772,16 +4772,16 @@
         <v>44414</v>
       </c>
       <c r="B218" t="n">
-        <v>29.46162796020508</v>
+        <v>29.46163177490234</v>
       </c>
       <c r="C218" t="n">
-        <v>29.99810539304109</v>
+        <v>29.99810927720156</v>
       </c>
       <c r="D218" t="n">
-        <v>29.10397406442085</v>
+        <v>29.10397783280902</v>
       </c>
       <c r="E218" t="n">
-        <v>29.97575415632978</v>
+        <v>29.97575803759621</v>
       </c>
       <c r="F218" t="n">
         <v>684400</v>
@@ -4812,16 +4812,16 @@
         <v>44418</v>
       </c>
       <c r="B220" t="n">
-        <v>29.59574890136719</v>
+        <v>29.59574699401855</v>
       </c>
       <c r="C220" t="n">
-        <v>30.78494533776667</v>
+        <v>30.78494335377824</v>
       </c>
       <c r="D220" t="n">
-        <v>29.59574890136719</v>
+        <v>29.59574699401855</v>
       </c>
       <c r="E220" t="n">
-        <v>30.48988032933406</v>
+        <v>30.4898783643616</v>
       </c>
       <c r="F220" t="n">
         <v>1186200</v>
@@ -4852,16 +4852,16 @@
         <v>44420</v>
       </c>
       <c r="B222" t="n">
-        <v>29.32750511169434</v>
+        <v>29.32751083374023</v>
       </c>
       <c r="C222" t="n">
-        <v>31.18729979924009</v>
+        <v>31.18730588414776</v>
       </c>
       <c r="D222" t="n">
-        <v>28.46913990706097</v>
+        <v>28.46914546163251</v>
       </c>
       <c r="E222" t="n">
-        <v>28.48702294184585</v>
+        <v>28.48702849990652</v>
       </c>
       <c r="F222" t="n">
         <v>1567750</v>
@@ -4872,16 +4872,16 @@
         <v>44421</v>
       </c>
       <c r="B223" t="n">
-        <v>28.34396553039551</v>
+        <v>28.34396362304688</v>
       </c>
       <c r="C223" t="n">
-        <v>29.59574742040596</v>
+        <v>29.59574542882125</v>
       </c>
       <c r="D223" t="n">
-        <v>27.18159370895106</v>
+        <v>27.18159187982183</v>
       </c>
       <c r="E223" t="n">
-        <v>29.50633564641969</v>
+        <v>29.50633366085176</v>
       </c>
       <c r="F223" t="n">
         <v>1962050</v>
@@ -4932,16 +4932,16 @@
         <v>44426</v>
       </c>
       <c r="B226" t="n">
-        <v>25.7509822845459</v>
+        <v>25.75098419189453</v>
       </c>
       <c r="C226" t="n">
-        <v>26.43052231748461</v>
+        <v>26.43052427516607</v>
       </c>
       <c r="D226" t="n">
-        <v>24.89261700425713</v>
+        <v>24.89261884802754</v>
       </c>
       <c r="E226" t="n">
-        <v>25.39333008442558</v>
+        <v>25.39333196528328</v>
       </c>
       <c r="F226" t="n">
         <v>2048900</v>
@@ -4952,16 +4952,16 @@
         <v>44427</v>
       </c>
       <c r="B227" t="n">
-        <v>26.4662914276123</v>
+        <v>26.46628761291504</v>
       </c>
       <c r="C227" t="n">
-        <v>26.73453018213193</v>
+        <v>26.73452632877229</v>
       </c>
       <c r="D227" t="n">
-        <v>24.30249323678068</v>
+        <v>24.3024897339607</v>
       </c>
       <c r="E227" t="n">
-        <v>24.85685378423334</v>
+        <v>24.85685020151106</v>
       </c>
       <c r="F227" t="n">
         <v>1738450</v>
@@ -4972,16 +4972,16 @@
         <v>44428</v>
       </c>
       <c r="B228" t="n">
-        <v>26.64511489868164</v>
+        <v>26.64511299133301</v>
       </c>
       <c r="C228" t="n">
-        <v>26.87758926611801</v>
+        <v>26.87758734212807</v>
       </c>
       <c r="D228" t="n">
-        <v>25.73310217156392</v>
+        <v>25.73310032950029</v>
       </c>
       <c r="E228" t="n">
-        <v>26.34111008783564</v>
+        <v>26.34110820224871</v>
       </c>
       <c r="F228" t="n">
         <v>1186050</v>
@@ -4992,16 +4992,16 @@
         <v>44431</v>
       </c>
       <c r="B229" t="n">
-        <v>26.85970878601074</v>
+        <v>26.85970687866211</v>
       </c>
       <c r="C229" t="n">
-        <v>27.41406931365822</v>
+        <v>27.41406736694361</v>
       </c>
       <c r="D229" t="n">
-        <v>26.28746351516839</v>
+        <v>26.28746164845576</v>
       </c>
       <c r="E229" t="n">
-        <v>26.71664618923489</v>
+        <v>26.71664429204535</v>
       </c>
       <c r="F229" t="n">
         <v>1094150</v>
@@ -5012,16 +5012,16 @@
         <v>44432</v>
       </c>
       <c r="B230" t="n">
-        <v>27.48559761047363</v>
+        <v>27.48559951782227</v>
       </c>
       <c r="C230" t="n">
-        <v>27.84324981090064</v>
+        <v>27.84325174306836</v>
       </c>
       <c r="D230" t="n">
-        <v>27.00276756625223</v>
+        <v>27.00276944009512</v>
       </c>
       <c r="E230" t="n">
-        <v>27.64654152702084</v>
+        <v>27.64654344553809</v>
       </c>
       <c r="F230" t="n">
         <v>835550</v>
@@ -5072,16 +5072,16 @@
         <v>44435</v>
       </c>
       <c r="B233" t="n">
-        <v>28.96985816955566</v>
+        <v>28.9698600769043</v>
       </c>
       <c r="C233" t="n">
-        <v>29.11291905438238</v>
+        <v>29.11292097115001</v>
       </c>
       <c r="D233" t="n">
-        <v>27.00276844505784</v>
+        <v>27.00277022289511</v>
       </c>
       <c r="E233" t="n">
-        <v>27.44983413649641</v>
+        <v>27.44983594376807</v>
       </c>
       <c r="F233" t="n">
         <v>1634000</v>
@@ -5092,16 +5092,16 @@
         <v>44438</v>
       </c>
       <c r="B234" t="n">
-        <v>27.68230628967285</v>
+        <v>27.68230819702148</v>
       </c>
       <c r="C234" t="n">
-        <v>29.68516205150646</v>
+        <v>29.68516409685458</v>
       </c>
       <c r="D234" t="n">
-        <v>27.55712844409084</v>
+        <v>27.55713034281455</v>
       </c>
       <c r="E234" t="n">
-        <v>28.96985764043749</v>
+        <v>28.96985963650016</v>
       </c>
       <c r="F234" t="n">
         <v>1402700</v>
@@ -5112,16 +5112,16 @@
         <v>44439</v>
       </c>
       <c r="B235" t="n">
-        <v>26.55570030212402</v>
+        <v>26.55570411682129</v>
       </c>
       <c r="C235" t="n">
-        <v>27.86113118201179</v>
+        <v>27.86113518423277</v>
       </c>
       <c r="D235" t="n">
-        <v>25.87616030921885</v>
+        <v>25.87616402630093</v>
       </c>
       <c r="E235" t="n">
-        <v>27.6823042397767</v>
+        <v>27.68230821630939</v>
       </c>
       <c r="F235" t="n">
         <v>1705500</v>
@@ -5132,16 +5132,16 @@
         <v>44440</v>
       </c>
       <c r="B236" t="n">
-        <v>26.59146499633789</v>
+        <v>26.59146690368652</v>
       </c>
       <c r="C236" t="n">
-        <v>27.25312196212229</v>
+        <v>27.25312391693015</v>
       </c>
       <c r="D236" t="n">
-        <v>25.71521672046829</v>
+        <v>25.71521856496552</v>
       </c>
       <c r="E236" t="n">
-        <v>26.55570063070043</v>
+        <v>26.55570253548375</v>
       </c>
       <c r="F236" t="n">
         <v>1751800</v>
@@ -5192,16 +5192,16 @@
         <v>44445</v>
       </c>
       <c r="B239" t="n">
-        <v>25.76886558532715</v>
+        <v>25.76886749267578</v>
       </c>
       <c r="C239" t="n">
-        <v>25.89404343029868</v>
+        <v>25.89404534691268</v>
       </c>
       <c r="D239" t="n">
-        <v>24.87473422314136</v>
+        <v>24.87473606430857</v>
       </c>
       <c r="E239" t="n">
-        <v>24.87473422314136</v>
+        <v>24.87473606430857</v>
       </c>
       <c r="F239" t="n">
         <v>528250</v>
@@ -5272,16 +5272,16 @@
         <v>44452</v>
       </c>
       <c r="B243" t="n">
-        <v>26.48417472839355</v>
+        <v>26.48417091369629</v>
       </c>
       <c r="C243" t="n">
-        <v>26.82394393451239</v>
+        <v>26.82394007087584</v>
       </c>
       <c r="D243" t="n">
-        <v>25.16085886483809</v>
+        <v>25.16085524074708</v>
       </c>
       <c r="E243" t="n">
-        <v>25.37545021166373</v>
+        <v>25.37544655666366</v>
       </c>
       <c r="F243" t="n">
         <v>1238850</v>
@@ -5292,16 +5292,16 @@
         <v>44453</v>
       </c>
       <c r="B244" t="n">
-        <v>26.34111022949219</v>
+        <v>26.34110832214355</v>
       </c>
       <c r="C244" t="n">
-        <v>27.02065029824824</v>
+        <v>27.0206483416944</v>
       </c>
       <c r="D244" t="n">
-        <v>25.84039712293205</v>
+        <v>25.84039525183984</v>
       </c>
       <c r="E244" t="n">
-        <v>26.60935067278606</v>
+        <v>26.60934874601425</v>
       </c>
       <c r="F244" t="n">
         <v>937200</v>
@@ -5312,16 +5312,16 @@
         <v>44454</v>
       </c>
       <c r="B245" t="n">
-        <v>26.32322883605957</v>
+        <v>26.32322692871094</v>
       </c>
       <c r="C245" t="n">
-        <v>26.53782016694073</v>
+        <v>26.53781824404307</v>
       </c>
       <c r="D245" t="n">
-        <v>25.66157180615427</v>
+        <v>25.66156994674848</v>
       </c>
       <c r="E245" t="n">
-        <v>26.30534579879773</v>
+        <v>26.30534389274488</v>
       </c>
       <c r="F245" t="n">
         <v>552000</v>
@@ -5332,16 +5332,16 @@
         <v>44455</v>
       </c>
       <c r="B246" t="n">
-        <v>25.7509822845459</v>
+        <v>25.75098419189453</v>
       </c>
       <c r="C246" t="n">
-        <v>26.66299667391787</v>
+        <v>26.66299864881847</v>
       </c>
       <c r="D246" t="n">
-        <v>25.73310095360504</v>
+        <v>25.73310285962922</v>
       </c>
       <c r="E246" t="n">
-        <v>26.16228359374943</v>
+        <v>26.16228553156272</v>
       </c>
       <c r="F246" t="n">
         <v>615650</v>
@@ -5372,16 +5372,16 @@
         <v>44459</v>
       </c>
       <c r="B248" t="n">
-        <v>24.17731475830078</v>
+        <v>24.17731094360352</v>
       </c>
       <c r="C248" t="n">
-        <v>24.58861439873235</v>
+        <v>24.58861051914021</v>
       </c>
       <c r="D248" t="n">
-        <v>23.71236600400568</v>
+        <v>23.71236226266804</v>
       </c>
       <c r="E248" t="n">
-        <v>24.37402305953931</v>
+        <v>24.3740192138054</v>
       </c>
       <c r="F248" t="n">
         <v>1148950</v>
@@ -5412,16 +5412,16 @@
         <v>44461</v>
       </c>
       <c r="B250" t="n">
-        <v>25.48274230957031</v>
+        <v>25.48274612426758</v>
       </c>
       <c r="C250" t="n">
-        <v>26.37687361867804</v>
+        <v>26.37687756722434</v>
       </c>
       <c r="D250" t="n">
-        <v>25.2323849290689</v>
+        <v>25.23238870628835</v>
       </c>
       <c r="E250" t="n">
-        <v>25.92980796412418</v>
+        <v>25.92981184574596</v>
       </c>
       <c r="F250" t="n">
         <v>900000</v>
@@ -5472,16 +5472,16 @@
         <v>44466</v>
       </c>
       <c r="B253" t="n">
-        <v>26.01922035217285</v>
+        <v>26.01922416687012</v>
       </c>
       <c r="C253" t="n">
-        <v>26.34110645035635</v>
+        <v>26.34111031224558</v>
       </c>
       <c r="D253" t="n">
-        <v>25.57215471624349</v>
+        <v>25.57215846539613</v>
       </c>
       <c r="E253" t="n">
-        <v>26.21592861803055</v>
+        <v>26.21593246156736</v>
       </c>
       <c r="F253" t="n">
         <v>663500</v>
@@ -5512,16 +5512,16 @@
         <v>44468</v>
       </c>
       <c r="B255" t="n">
-        <v>24.67802429199219</v>
+        <v>24.67802619934082</v>
       </c>
       <c r="C255" t="n">
-        <v>25.39332865187945</v>
+        <v>25.39333061451349</v>
       </c>
       <c r="D255" t="n">
-        <v>24.46343298402601</v>
+        <v>24.46343487478902</v>
       </c>
       <c r="E255" t="n">
-        <v>25.10720690792455</v>
+        <v>25.10720884844443</v>
       </c>
       <c r="F255" t="n">
         <v>580300</v>
@@ -5532,16 +5532,16 @@
         <v>44469</v>
       </c>
       <c r="B256" t="n">
-        <v>24.44555282592773</v>
+        <v>24.4455509185791</v>
       </c>
       <c r="C256" t="n">
-        <v>24.89261852983216</v>
+        <v>24.89261658760151</v>
       </c>
       <c r="D256" t="n">
-        <v>24.0700175664312</v>
+        <v>24.07001568838347</v>
       </c>
       <c r="E256" t="n">
-        <v>24.85685245491806</v>
+        <v>24.85685051547803</v>
       </c>
       <c r="F256" t="n">
         <v>989250</v>
@@ -5592,16 +5592,16 @@
         <v>44474</v>
       </c>
       <c r="B259" t="n">
-        <v>23.40836143493652</v>
+        <v>23.40835952758789</v>
       </c>
       <c r="C259" t="n">
-        <v>23.98060501233891</v>
+        <v>23.98060305836301</v>
       </c>
       <c r="D259" t="n">
-        <v>23.08647356993749</v>
+        <v>23.08647168881676</v>
       </c>
       <c r="E259" t="n">
-        <v>23.90907456516361</v>
+        <v>23.90907261701612</v>
       </c>
       <c r="F259" t="n">
         <v>1237200</v>
@@ -5612,16 +5612,16 @@
         <v>44475</v>
       </c>
       <c r="B260" t="n">
-        <v>23.60506820678711</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="C260" t="n">
-        <v>23.60506820678711</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="D260" t="n">
-        <v>22.37116764671513</v>
+        <v>22.37116583906875</v>
       </c>
       <c r="E260" t="n">
-        <v>22.97917726096693</v>
+        <v>22.97917540419186</v>
       </c>
       <c r="F260" t="n">
         <v>1199850</v>
@@ -5632,16 +5632,16 @@
         <v>44476</v>
       </c>
       <c r="B261" t="n">
-        <v>23.62295341491699</v>
+        <v>23.62295150756836</v>
       </c>
       <c r="C261" t="n">
-        <v>24.26672745689388</v>
+        <v>24.26672549756607</v>
       </c>
       <c r="D261" t="n">
-        <v>23.42624510622361</v>
+        <v>23.42624321475746</v>
       </c>
       <c r="E261" t="n">
-        <v>24.15943263594128</v>
+        <v>24.1594306852766</v>
       </c>
       <c r="F261" t="n">
         <v>699850</v>
@@ -5652,16 +5652,16 @@
         <v>44477</v>
       </c>
       <c r="B262" t="n">
-        <v>24.0521354675293</v>
+        <v>24.05213165283203</v>
       </c>
       <c r="C262" t="n">
-        <v>24.53496726518875</v>
+        <v>24.53496337391379</v>
       </c>
       <c r="D262" t="n">
-        <v>23.69448323153362</v>
+        <v>23.69447947356042</v>
       </c>
       <c r="E262" t="n">
-        <v>23.81966108777701</v>
+        <v>23.81965730995046</v>
       </c>
       <c r="F262" t="n">
         <v>982950</v>
@@ -5672,16 +5672,16 @@
         <v>44480</v>
       </c>
       <c r="B263" t="n">
-        <v>24.0879020690918</v>
+        <v>24.08790016174316</v>
       </c>
       <c r="C263" t="n">
-        <v>24.60649824894896</v>
+        <v>24.60649630053641</v>
       </c>
       <c r="D263" t="n">
-        <v>23.73024982529728</v>
+        <v>23.73024794626857</v>
       </c>
       <c r="E263" t="n">
-        <v>24.0342529534573</v>
+        <v>24.03425105035676</v>
       </c>
       <c r="F263" t="n">
         <v>770500</v>
@@ -5712,16 +5712,16 @@
         <v>44483</v>
       </c>
       <c r="B265" t="n">
-        <v>24.37402153015137</v>
+        <v>24.37401962280273</v>
       </c>
       <c r="C265" t="n">
-        <v>24.91050069718188</v>
+        <v>24.91049874785196</v>
       </c>
       <c r="D265" t="n">
-        <v>23.92695584186265</v>
+        <v>23.9269539694984</v>
       </c>
       <c r="E265" t="n">
-        <v>24.51708241397014</v>
+        <v>24.51708049542651</v>
       </c>
       <c r="F265" t="n">
         <v>635500</v>
@@ -5732,16 +5732,16 @@
         <v>44484</v>
       </c>
       <c r="B266" t="n">
-        <v>26.16228294372559</v>
+        <v>26.16228675842285</v>
       </c>
       <c r="C266" t="n">
-        <v>26.59146557320656</v>
+        <v>26.59146945048253</v>
       </c>
       <c r="D266" t="n">
-        <v>24.44555072038149</v>
+        <v>24.44555428476369</v>
       </c>
       <c r="E266" t="n">
-        <v>24.76743854520231</v>
+        <v>24.76744215651866</v>
       </c>
       <c r="F266" t="n">
         <v>2075800</v>
@@ -5772,16 +5772,16 @@
         <v>44488</v>
       </c>
       <c r="B268" t="n">
-        <v>24.60649490356445</v>
+        <v>24.60649681091309</v>
       </c>
       <c r="C268" t="n">
-        <v>26.46628802386757</v>
+        <v>26.46629007537627</v>
       </c>
       <c r="D268" t="n">
-        <v>24.12366316102009</v>
+        <v>24.12366503094249</v>
       </c>
       <c r="E268" t="n">
-        <v>26.4305219516405</v>
+        <v>26.43052400037682</v>
       </c>
       <c r="F268" t="n">
         <v>1499450</v>
@@ -5832,16 +5832,16 @@
         <v>44491</v>
       </c>
       <c r="B271" t="n">
-        <v>21.08361625671387</v>
+        <v>21.0836181640625</v>
       </c>
       <c r="C271" t="n">
-        <v>21.99563060373434</v>
+        <v>21.99563259358919</v>
       </c>
       <c r="D271" t="n">
-        <v>19.81394972618147</v>
+        <v>19.81395151866856</v>
       </c>
       <c r="E271" t="n">
-        <v>21.99563060373434</v>
+        <v>21.99563259358919</v>
       </c>
       <c r="F271" t="n">
         <v>3185950</v>
@@ -5852,16 +5852,16 @@
         <v>44494</v>
       </c>
       <c r="B272" t="n">
-        <v>21.62009620666504</v>
+        <v>21.62009811401367</v>
       </c>
       <c r="C272" t="n">
-        <v>22.28175319767261</v>
+        <v>22.28175516339335</v>
       </c>
       <c r="D272" t="n">
-        <v>20.79749530060315</v>
+        <v>20.79749713538103</v>
       </c>
       <c r="E272" t="n">
-        <v>20.833259667604</v>
+        <v>20.83326150553705</v>
       </c>
       <c r="F272" t="n">
         <v>1833600</v>
@@ -5892,16 +5892,16 @@
         <v>44496</v>
       </c>
       <c r="B274" t="n">
-        <v>20.49348831176758</v>
+        <v>20.49349212646484</v>
       </c>
       <c r="C274" t="n">
-        <v>21.10149783444344</v>
+        <v>21.10150176231677</v>
       </c>
       <c r="D274" t="n">
-        <v>20.31466137965585</v>
+        <v>20.31466516106592</v>
       </c>
       <c r="E274" t="n">
-        <v>20.42195788000689</v>
+        <v>20.42196168138934</v>
       </c>
       <c r="F274" t="n">
         <v>1013650</v>
@@ -5932,16 +5932,16 @@
         <v>44498</v>
       </c>
       <c r="B276" t="n">
-        <v>18.32969284057617</v>
+        <v>18.32969093322754</v>
       </c>
       <c r="C276" t="n">
-        <v>20.52925516284361</v>
+        <v>20.52925302661322</v>
       </c>
       <c r="D276" t="n">
-        <v>18.09721848282576</v>
+        <v>18.09721659966791</v>
       </c>
       <c r="E276" t="n">
-        <v>20.24313340112624</v>
+        <v>20.24313129466907</v>
       </c>
       <c r="F276" t="n">
         <v>3577000</v>
@@ -5952,16 +5952,16 @@
         <v>44501</v>
       </c>
       <c r="B277" t="n">
-        <v>18.77675819396973</v>
+        <v>18.77676010131836</v>
       </c>
       <c r="C277" t="n">
-        <v>19.40265081593679</v>
+        <v>19.40265278686379</v>
       </c>
       <c r="D277" t="n">
-        <v>18.68734471862869</v>
+        <v>18.68734661689468</v>
       </c>
       <c r="E277" t="n">
-        <v>18.77675819396973</v>
+        <v>18.77676010131836</v>
       </c>
       <c r="F277" t="n">
         <v>1843300</v>
@@ -6032,16 +6032,16 @@
         <v>44508</v>
       </c>
       <c r="B281" t="n">
-        <v>20.13583755493164</v>
+        <v>20.13583946228027</v>
       </c>
       <c r="C281" t="n">
-        <v>20.86902495788224</v>
+        <v>20.86902693468137</v>
       </c>
       <c r="D281" t="n">
-        <v>19.86759713808767</v>
+        <v>19.86759902002748</v>
       </c>
       <c r="E281" t="n">
-        <v>20.86902495788224</v>
+        <v>20.86902693468137</v>
       </c>
       <c r="F281" t="n">
         <v>919700</v>
@@ -6052,16 +6052,16 @@
         <v>44509</v>
       </c>
       <c r="B282" t="n">
-        <v>20.67231559753418</v>
+        <v>20.67231941223145</v>
       </c>
       <c r="C282" t="n">
-        <v>21.36973689277714</v>
+        <v>21.36974083617073</v>
       </c>
       <c r="D282" t="n">
-        <v>20.29678039801103</v>
+        <v>20.29678414341015</v>
       </c>
       <c r="E282" t="n">
-        <v>20.29678039801103</v>
+        <v>20.29678414341015</v>
       </c>
       <c r="F282" t="n">
         <v>912150</v>
@@ -6072,16 +6072,16 @@
         <v>44510</v>
       </c>
       <c r="B283" t="n">
-        <v>21.08361625671387</v>
+        <v>21.0836181640625</v>
       </c>
       <c r="C283" t="n">
-        <v>21.65585975033293</v>
+        <v>21.65586170945009</v>
       </c>
       <c r="D283" t="n">
-        <v>20.49348972756417</v>
+        <v>20.49349158152647</v>
       </c>
       <c r="E283" t="n">
-        <v>20.88690798213735</v>
+        <v>20.88690987169059</v>
       </c>
       <c r="F283" t="n">
         <v>1309800</v>
@@ -6112,16 +6112,16 @@
         <v>44512</v>
       </c>
       <c r="B285" t="n">
-        <v>21.08361625671387</v>
+        <v>21.0836181640625</v>
       </c>
       <c r="C285" t="n">
-        <v>22.12080844160848</v>
+        <v>22.12081044278765</v>
       </c>
       <c r="D285" t="n">
-        <v>21.08361625671387</v>
+        <v>21.0836181640625</v>
       </c>
       <c r="E285" t="n">
-        <v>21.76315625809657</v>
+        <v>21.76315822692041</v>
       </c>
       <c r="F285" t="n">
         <v>1307150</v>
@@ -6132,16 +6132,16 @@
         <v>44516</v>
       </c>
       <c r="B286" t="n">
-        <v>20.63654899597168</v>
+        <v>20.63655090332031</v>
       </c>
       <c r="C286" t="n">
-        <v>21.87044935947683</v>
+        <v>21.87045138086964</v>
       </c>
       <c r="D286" t="n">
-        <v>19.77818382230201</v>
+        <v>19.77818565031559</v>
       </c>
       <c r="E286" t="n">
-        <v>21.76315456547812</v>
+        <v>21.76315657695413</v>
       </c>
       <c r="F286" t="n">
         <v>1709550</v>
@@ -6152,16 +6152,16 @@
         <v>44517</v>
       </c>
       <c r="B287" t="n">
-        <v>19.99277877807617</v>
+        <v>19.99277687072754</v>
       </c>
       <c r="C287" t="n">
-        <v>20.92267455322699</v>
+        <v>20.92267255716455</v>
       </c>
       <c r="D287" t="n">
-        <v>19.59936048203298</v>
+        <v>19.59935861221719</v>
       </c>
       <c r="E287" t="n">
-        <v>20.40407840611472</v>
+        <v>20.40407645952734</v>
       </c>
       <c r="F287" t="n">
         <v>1179650</v>
@@ -6172,16 +6172,16 @@
         <v>44518</v>
       </c>
       <c r="B288" t="n">
-        <v>20.33254623413086</v>
+        <v>20.33254814147949</v>
       </c>
       <c r="C288" t="n">
-        <v>20.70808146084758</v>
+        <v>20.7080834034243</v>
       </c>
       <c r="D288" t="n">
-        <v>19.68877229065369</v>
+        <v>19.68877413761139</v>
       </c>
       <c r="E288" t="n">
-        <v>19.68877229065369</v>
+        <v>19.68877413761139</v>
       </c>
       <c r="F288" t="n">
         <v>766850</v>
@@ -6212,16 +6212,16 @@
         <v>44522</v>
       </c>
       <c r="B290" t="n">
-        <v>20.18948745727539</v>
+        <v>20.18948554992676</v>
       </c>
       <c r="C290" t="n">
-        <v>21.44127110802875</v>
+        <v>21.44126908242115</v>
       </c>
       <c r="D290" t="n">
-        <v>19.97489612046799</v>
+        <v>19.97489423339231</v>
       </c>
       <c r="E290" t="n">
-        <v>20.869027543209</v>
+        <v>20.86902557166261</v>
       </c>
       <c r="F290" t="n">
         <v>852100</v>
@@ -6232,16 +6232,16 @@
         <v>44523</v>
       </c>
       <c r="B291" t="n">
-        <v>19.24170875549316</v>
+        <v>19.24170684814453</v>
       </c>
       <c r="C291" t="n">
-        <v>20.45772633887523</v>
+        <v>20.45772431098796</v>
       </c>
       <c r="D291" t="n">
-        <v>19.02711741724927</v>
+        <v>19.02711553117216</v>
       </c>
       <c r="E291" t="n">
-        <v>20.20737063030087</v>
+        <v>20.20736862723029</v>
       </c>
       <c r="F291" t="n">
         <v>1896750</v>
@@ -6252,16 +6252,16 @@
         <v>44524</v>
       </c>
       <c r="B292" t="n">
-        <v>19.58147811889648</v>
+        <v>19.58147621154785</v>
       </c>
       <c r="C292" t="n">
-        <v>20.3325486620143</v>
+        <v>20.33254668150708</v>
       </c>
       <c r="D292" t="n">
-        <v>19.02711758328404</v>
+        <v>19.02711572993332</v>
       </c>
       <c r="E292" t="n">
-        <v>19.04499891589514</v>
+        <v>19.04499706080266</v>
       </c>
       <c r="F292" t="n">
         <v>1594900</v>
@@ -6312,16 +6312,16 @@
         <v>44529</v>
       </c>
       <c r="B295" t="n">
-        <v>19.20594215393066</v>
+        <v>19.2059440612793</v>
       </c>
       <c r="C295" t="n">
-        <v>20.33254792793267</v>
+        <v>20.33254994716491</v>
       </c>
       <c r="D295" t="n">
-        <v>19.06288126568472</v>
+        <v>19.06288315882593</v>
       </c>
       <c r="E295" t="n">
-        <v>20.33254792793267</v>
+        <v>20.33254994716491</v>
       </c>
       <c r="F295" t="n">
         <v>830750</v>
@@ -6332,16 +6332,16 @@
         <v>44530</v>
       </c>
       <c r="B296" t="n">
-        <v>18.83040618896484</v>
+        <v>18.83040809631348</v>
       </c>
       <c r="C296" t="n">
-        <v>19.25959054300976</v>
+        <v>19.25959249383086</v>
       </c>
       <c r="D296" t="n">
-        <v>18.06145436986738</v>
+        <v>18.06145619932819</v>
       </c>
       <c r="E296" t="n">
-        <v>19.04499751327718</v>
+        <v>19.04499944236196</v>
       </c>
       <c r="F296" t="n">
         <v>1327800</v>
@@ -6372,16 +6372,16 @@
         <v>44532</v>
       </c>
       <c r="B298" t="n">
-        <v>18.59793281555176</v>
+        <v>18.59793090820312</v>
       </c>
       <c r="C298" t="n">
-        <v>18.86617326425185</v>
+        <v>18.86617132939327</v>
       </c>
       <c r="D298" t="n">
-        <v>18.11510273656414</v>
+        <v>18.11510087873313</v>
       </c>
       <c r="E298" t="n">
-        <v>18.22239755170791</v>
+        <v>18.22239568287305</v>
       </c>
       <c r="F298" t="n">
         <v>961350</v>
@@ -6432,16 +6432,16 @@
         <v>44537</v>
       </c>
       <c r="B301" t="n">
-        <v>19.93912887573242</v>
+        <v>19.93913078308105</v>
       </c>
       <c r="C301" t="n">
-        <v>20.72596543664007</v>
+        <v>20.72596741925636</v>
       </c>
       <c r="D301" t="n">
-        <v>19.90336450773857</v>
+        <v>19.90336641166604</v>
       </c>
       <c r="E301" t="n">
-        <v>20.35043019289329</v>
+        <v>20.35043213958642</v>
       </c>
       <c r="F301" t="n">
         <v>881500</v>
@@ -6452,16 +6452,16 @@
         <v>44538</v>
       </c>
       <c r="B302" t="n">
-        <v>21.42338562011719</v>
+        <v>21.42338752746582</v>
       </c>
       <c r="C302" t="n">
-        <v>21.51279909324929</v>
+        <v>21.51280100855851</v>
       </c>
       <c r="D302" t="n">
-        <v>19.86759732713109</v>
+        <v>19.86759909596611</v>
       </c>
       <c r="E302" t="n">
-        <v>20.18948514823861</v>
+        <v>20.18948694573167</v>
       </c>
       <c r="F302" t="n">
         <v>984450</v>
@@ -6472,16 +6472,16 @@
         <v>44539</v>
       </c>
       <c r="B303" t="n">
-        <v>20.90478897094727</v>
+        <v>20.9047908782959</v>
       </c>
       <c r="C303" t="n">
-        <v>21.36973765463187</v>
+        <v>21.36973960440232</v>
       </c>
       <c r="D303" t="n">
-        <v>20.72596373482095</v>
+        <v>20.72596562585361</v>
       </c>
       <c r="E303" t="n">
-        <v>21.24455981880144</v>
+        <v>21.24456175715069</v>
       </c>
       <c r="F303" t="n">
         <v>669550</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78103828430176</v>
+        <v>21.78104019165039</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422565288058</v>
+        <v>22.51422762443386</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550308266138</v>
+        <v>21.40550495712469</v>
       </c>
       <c r="E305" t="n">
-        <v>22.1386904512402</v>
+        <v>22.13869238990815</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6532,16 +6532,16 @@
         <v>44544</v>
       </c>
       <c r="B306" t="n">
-        <v>21.49491691589355</v>
+        <v>21.49492073059082</v>
       </c>
       <c r="C306" t="n">
-        <v>22.06716039271598</v>
+        <v>22.06716430896915</v>
       </c>
       <c r="D306" t="n">
-        <v>21.22667650706798</v>
+        <v>21.22668027416069</v>
       </c>
       <c r="E306" t="n">
-        <v>21.95986388810174</v>
+        <v>21.95986778531302</v>
       </c>
       <c r="F306" t="n">
         <v>979700</v>
@@ -6552,16 +6552,16 @@
         <v>44545</v>
       </c>
       <c r="B307" t="n">
-        <v>22.03139495849609</v>
+        <v>22.03139877319336</v>
       </c>
       <c r="C307" t="n">
-        <v>22.37116581172973</v>
+        <v>22.37116968525772</v>
       </c>
       <c r="D307" t="n">
-        <v>21.11938231734611</v>
+        <v>21.11938597412999</v>
       </c>
       <c r="E307" t="n">
-        <v>21.45915146515961</v>
+        <v>21.45915518077393</v>
       </c>
       <c r="F307" t="n">
         <v>1028800</v>
@@ -6632,16 +6632,16 @@
         <v>44551</v>
       </c>
       <c r="B311" t="n">
-        <v>21.38762283325195</v>
+        <v>21.38762092590332</v>
       </c>
       <c r="C311" t="n">
-        <v>22.19234074001621</v>
+        <v>22.19233876090282</v>
       </c>
       <c r="D311" t="n">
-        <v>21.38762283325195</v>
+        <v>21.38762092590332</v>
       </c>
       <c r="E311" t="n">
-        <v>22.0313968175793</v>
+        <v>22.0313948528189</v>
       </c>
       <c r="F311" t="n">
         <v>785250</v>
@@ -6652,16 +6652,16 @@
         <v>44552</v>
       </c>
       <c r="B312" t="n">
-        <v>21.45915222167969</v>
+        <v>21.45915412902832</v>
       </c>
       <c r="C312" t="n">
-        <v>21.78104005073934</v>
+        <v>21.78104198669826</v>
       </c>
       <c r="D312" t="n">
-        <v>20.65443435445074</v>
+        <v>20.65443619027383</v>
       </c>
       <c r="E312" t="n">
-        <v>21.42338614937519</v>
+        <v>21.42338805354484</v>
       </c>
       <c r="F312" t="n">
         <v>1154200</v>
@@ -6692,16 +6692,16 @@
         <v>44557</v>
       </c>
       <c r="B314" t="n">
-        <v>20.92362403869629</v>
+        <v>20.92362594604492</v>
       </c>
       <c r="C314" t="n">
-        <v>21.35652617792996</v>
+        <v>21.35652812474094</v>
       </c>
       <c r="D314" t="n">
-        <v>20.58090855498616</v>
+        <v>20.58091043109365</v>
       </c>
       <c r="E314" t="n">
-        <v>21.08596105075877</v>
+        <v>21.08596297290567</v>
       </c>
       <c r="F314" t="n">
         <v>929800</v>
@@ -6712,16 +6712,16 @@
         <v>44558</v>
       </c>
       <c r="B315" t="n">
-        <v>20.76128959655762</v>
+        <v>20.76128768920898</v>
       </c>
       <c r="C315" t="n">
-        <v>21.2483041737824</v>
+        <v>21.24830222169153</v>
       </c>
       <c r="D315" t="n">
-        <v>20.58091280783701</v>
+        <v>20.58091091705966</v>
       </c>
       <c r="E315" t="n">
-        <v>20.90559033945389</v>
+        <v>20.90558841884829</v>
       </c>
       <c r="F315" t="n">
         <v>793100</v>
@@ -6732,16 +6732,16 @@
         <v>44559</v>
       </c>
       <c r="B316" t="n">
-        <v>20.29231071472168</v>
+        <v>20.29230690002441</v>
       </c>
       <c r="C316" t="n">
-        <v>20.90558971377646</v>
+        <v>20.90558578379051</v>
       </c>
       <c r="D316" t="n">
-        <v>20.05782158448306</v>
+        <v>20.05781781386678</v>
       </c>
       <c r="E316" t="n">
-        <v>20.70717490808197</v>
+        <v>20.7071710153955</v>
       </c>
       <c r="F316" t="n">
         <v>541350</v>
@@ -6752,16 +6752,16 @@
         <v>44560</v>
       </c>
       <c r="B317" t="n">
-        <v>21.06792640686035</v>
+        <v>21.06792831420898</v>
       </c>
       <c r="C317" t="n">
-        <v>21.15811306946891</v>
+        <v>21.15811498498244</v>
       </c>
       <c r="D317" t="n">
-        <v>19.93155691194919</v>
+        <v>19.93155871641855</v>
       </c>
       <c r="E317" t="n">
-        <v>20.2923087229844</v>
+        <v>20.29231056011382</v>
       </c>
       <c r="F317" t="n">
         <v>1399700</v>
@@ -6772,16 +6772,16 @@
         <v>44564</v>
       </c>
       <c r="B318" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C318" t="n">
-        <v>21.32045357690026</v>
+        <v>21.32045154948475</v>
       </c>
       <c r="D318" t="n">
-        <v>19.8774462134759</v>
+        <v>19.87744432327959</v>
       </c>
       <c r="E318" t="n">
-        <v>21.26634123082196</v>
+        <v>21.26633920855213</v>
       </c>
       <c r="F318" t="n">
         <v>905200</v>
@@ -6792,16 +6792,16 @@
         <v>44565</v>
       </c>
       <c r="B319" t="n">
-        <v>18.99360084533691</v>
+        <v>18.99359893798828</v>
       </c>
       <c r="C319" t="n">
-        <v>20.23819676739794</v>
+        <v>20.23819473506625</v>
       </c>
       <c r="D319" t="n">
-        <v>18.84930011817047</v>
+        <v>18.8492982253126</v>
       </c>
       <c r="E319" t="n">
-        <v>20.0758580192856</v>
+        <v>20.07585600325606</v>
       </c>
       <c r="F319" t="n">
         <v>1398150</v>
@@ -6812,16 +6812,16 @@
         <v>44566</v>
       </c>
       <c r="B320" t="n">
-        <v>17.78508186340332</v>
+        <v>17.78507995605469</v>
       </c>
       <c r="C320" t="n">
-        <v>18.88537711386832</v>
+        <v>18.8853750885193</v>
       </c>
       <c r="D320" t="n">
-        <v>17.55059273986488</v>
+        <v>17.55059085766387</v>
       </c>
       <c r="E320" t="n">
-        <v>18.77715070292733</v>
+        <v>18.77714868918498</v>
       </c>
       <c r="F320" t="n">
         <v>2337000</v>
@@ -6872,16 +6872,16 @@
         <v>44571</v>
       </c>
       <c r="B323" t="n">
-        <v>16.36010932922363</v>
+        <v>16.36011123657227</v>
       </c>
       <c r="C323" t="n">
-        <v>17.13572699636531</v>
+        <v>17.13572899413958</v>
       </c>
       <c r="D323" t="n">
-        <v>16.10758392704749</v>
+        <v>16.10758580495536</v>
       </c>
       <c r="E323" t="n">
-        <v>17.11768897615265</v>
+        <v>17.11769097182395</v>
       </c>
       <c r="F323" t="n">
         <v>1820150</v>
@@ -6912,16 +6912,16 @@
         <v>44573</v>
       </c>
       <c r="B325" t="n">
-        <v>17.53255462646484</v>
+        <v>17.53255653381348</v>
       </c>
       <c r="C325" t="n">
-        <v>17.69489336600067</v>
+        <v>17.69489529100997</v>
       </c>
       <c r="D325" t="n">
-        <v>16.70282462899304</v>
+        <v>16.7028264460762</v>
       </c>
       <c r="E325" t="n">
-        <v>16.86516336852887</v>
+        <v>16.86516520327269</v>
       </c>
       <c r="F325" t="n">
         <v>1172500</v>
@@ -6932,16 +6932,16 @@
         <v>44574</v>
       </c>
       <c r="B326" t="n">
-        <v>16.64871215820312</v>
+        <v>16.64871025085449</v>
       </c>
       <c r="C326" t="n">
-        <v>17.62274468839355</v>
+        <v>17.62274266945553</v>
       </c>
       <c r="D326" t="n">
-        <v>16.57656179154462</v>
+        <v>16.57655989246185</v>
       </c>
       <c r="E326" t="n">
-        <v>17.58666864496408</v>
+        <v>17.58666663015909</v>
       </c>
       <c r="F326" t="n">
         <v>921200</v>
@@ -6952,16 +6952,16 @@
         <v>44575</v>
       </c>
       <c r="B327" t="n">
-        <v>17.00946617126465</v>
+        <v>17.00946235656738</v>
       </c>
       <c r="C327" t="n">
-        <v>17.02750247326626</v>
+        <v>17.02749865452401</v>
       </c>
       <c r="D327" t="n">
-        <v>16.17973607217368</v>
+        <v>16.17973244355922</v>
       </c>
       <c r="E327" t="n">
-        <v>16.55852593741522</v>
+        <v>16.5585222238499</v>
       </c>
       <c r="F327" t="n">
         <v>789200</v>
@@ -7032,16 +7032,16 @@
         <v>44581</v>
       </c>
       <c r="B331" t="n">
-        <v>17.4243278503418</v>
+        <v>17.42432594299316</v>
       </c>
       <c r="C331" t="n">
-        <v>18.12779513306872</v>
+        <v>18.12779314871526</v>
       </c>
       <c r="D331" t="n">
-        <v>16.48637319357279</v>
+        <v>16.48637138889707</v>
       </c>
       <c r="E331" t="n">
-        <v>16.48637319357279</v>
+        <v>16.48637138889707</v>
       </c>
       <c r="F331" t="n">
         <v>2219300</v>
@@ -7092,16 +7092,16 @@
         <v>44586</v>
       </c>
       <c r="B334" t="n">
-        <v>18.72303581237793</v>
+        <v>18.72303771972656</v>
       </c>
       <c r="C334" t="n">
-        <v>18.75911013098741</v>
+        <v>18.759112042011</v>
       </c>
       <c r="D334" t="n">
-        <v>17.65881675029495</v>
+        <v>17.65881854922971</v>
       </c>
       <c r="E334" t="n">
-        <v>17.71292908830928</v>
+        <v>17.71293089275656</v>
       </c>
       <c r="F334" t="n">
         <v>1122500</v>
@@ -7112,16 +7112,16 @@
         <v>44587</v>
       </c>
       <c r="B335" t="n">
-        <v>19.35435485839844</v>
+        <v>19.3543529510498</v>
       </c>
       <c r="C335" t="n">
-        <v>19.80529511198872</v>
+        <v>19.80529316020046</v>
       </c>
       <c r="D335" t="n">
-        <v>18.84930225603348</v>
+        <v>18.84930039845718</v>
       </c>
       <c r="E335" t="n">
-        <v>18.9214526277999</v>
+        <v>18.92145076311327</v>
       </c>
       <c r="F335" t="n">
         <v>1494250</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96762847900391</v>
+        <v>19.96763038635254</v>
       </c>
       <c r="C338" t="n">
-        <v>20.274267906142</v>
+        <v>20.27426984278146</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44453799509775</v>
+        <v>19.44453985247972</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706508809386</v>
+        <v>19.69706696959773</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7192,16 +7192,16 @@
         <v>44593</v>
       </c>
       <c r="B339" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C339" t="n">
-        <v>20.38249879067443</v>
+        <v>20.38249685245139</v>
       </c>
       <c r="D339" t="n">
-        <v>19.75118177902592</v>
+        <v>19.75117990083641</v>
       </c>
       <c r="E339" t="n">
-        <v>20.29231040041029</v>
+        <v>20.29230847076349</v>
       </c>
       <c r="F339" t="n">
         <v>629350</v>
@@ -7232,16 +7232,16 @@
         <v>44595</v>
       </c>
       <c r="B341" t="n">
-        <v>20.12997055053711</v>
+        <v>20.12997245788574</v>
       </c>
       <c r="C341" t="n">
-        <v>20.67109914258173</v>
+        <v>20.67110110120321</v>
       </c>
       <c r="D341" t="n">
-        <v>19.93155747887424</v>
+        <v>19.9315593674229</v>
       </c>
       <c r="E341" t="n">
-        <v>20.43661002868905</v>
+        <v>20.43661196509229</v>
       </c>
       <c r="F341" t="n">
         <v>747450</v>
@@ -7292,16 +7292,16 @@
         <v>44600</v>
       </c>
       <c r="B344" t="n">
-        <v>19.46257781982422</v>
+        <v>19.46257972717285</v>
       </c>
       <c r="C344" t="n">
-        <v>20.03978069145118</v>
+        <v>20.03978265536617</v>
       </c>
       <c r="D344" t="n">
-        <v>19.40846548065925</v>
+        <v>19.40846738270483</v>
       </c>
       <c r="E344" t="n">
-        <v>19.66099087689592</v>
+        <v>19.6609928036892</v>
       </c>
       <c r="F344" t="n">
         <v>697700</v>
@@ -7352,16 +7352,16 @@
         <v>44603</v>
       </c>
       <c r="B347" t="n">
-        <v>19.44454193115234</v>
+        <v>19.44454002380371</v>
       </c>
       <c r="C347" t="n">
-        <v>20.47268680917258</v>
+        <v>20.47268480097144</v>
       </c>
       <c r="D347" t="n">
-        <v>19.13790244194285</v>
+        <v>19.13790056467302</v>
       </c>
       <c r="E347" t="n">
-        <v>20.09389695310205</v>
+        <v>20.09389498205707</v>
       </c>
       <c r="F347" t="n">
         <v>1043600</v>
@@ -7372,16 +7372,16 @@
         <v>44606</v>
       </c>
       <c r="B348" t="n">
-        <v>20.00370597839355</v>
+        <v>20.00370788574219</v>
       </c>
       <c r="C348" t="n">
-        <v>20.1480066934604</v>
+        <v>20.14800861456807</v>
       </c>
       <c r="D348" t="n">
-        <v>19.26416438362593</v>
+        <v>19.26416622045944</v>
       </c>
       <c r="E348" t="n">
-        <v>19.26416438362593</v>
+        <v>19.26416622045944</v>
       </c>
       <c r="F348" t="n">
         <v>683300</v>
@@ -7392,16 +7392,16 @@
         <v>44607</v>
       </c>
       <c r="B349" t="n">
-        <v>20.52679824829102</v>
+        <v>20.52679634094238</v>
       </c>
       <c r="C349" t="n">
-        <v>20.70717329738229</v>
+        <v>20.70717137327322</v>
       </c>
       <c r="D349" t="n">
-        <v>20.11193236700041</v>
+        <v>20.11193049820109</v>
       </c>
       <c r="E349" t="n">
-        <v>20.20212075164623</v>
+        <v>20.2021188744666</v>
       </c>
       <c r="F349" t="n">
         <v>560950</v>
@@ -7432,16 +7432,16 @@
         <v>44609</v>
       </c>
       <c r="B351" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C351" t="n">
-        <v>20.72521260943759</v>
+        <v>20.72521063862504</v>
       </c>
       <c r="D351" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="E351" t="n">
-        <v>20.72521260943759</v>
+        <v>20.72521063862504</v>
       </c>
       <c r="F351" t="n">
         <v>544250</v>
@@ -7472,16 +7472,16 @@
         <v>44613</v>
       </c>
       <c r="B353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892623901367</v>
       </c>
       <c r="C353" t="n">
-        <v>19.94959452481559</v>
+        <v>19.9495965630065</v>
       </c>
       <c r="D353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892623901367</v>
       </c>
       <c r="E353" t="n">
-        <v>19.85940614385</v>
+        <v>19.85940817282663</v>
       </c>
       <c r="F353" t="n">
         <v>728950</v>
@@ -7512,16 +7512,16 @@
         <v>44615</v>
       </c>
       <c r="B355" t="n">
-        <v>19.6609935760498</v>
+        <v>19.66099166870117</v>
       </c>
       <c r="C355" t="n">
-        <v>20.49072367802294</v>
+        <v>20.49072169018069</v>
       </c>
       <c r="D355" t="n">
-        <v>19.55276888286228</v>
+        <v>19.55276698601272</v>
       </c>
       <c r="E355" t="n">
-        <v>19.85940838056108</v>
+        <v>19.85940645396386</v>
       </c>
       <c r="F355" t="n">
         <v>1327750</v>
@@ -7552,16 +7552,16 @@
         <v>44617</v>
       </c>
       <c r="B357" t="n">
-        <v>19.02967643737793</v>
+        <v>19.02967834472656</v>
       </c>
       <c r="C357" t="n">
-        <v>19.62491735291844</v>
+        <v>19.62491931992821</v>
       </c>
       <c r="D357" t="n">
-        <v>18.6508866074703</v>
+        <v>18.65088847685275</v>
       </c>
       <c r="E357" t="n">
-        <v>19.28220184384947</v>
+        <v>19.28220377650878</v>
       </c>
       <c r="F357" t="n">
         <v>1262850</v>
@@ -7592,16 +7592,16 @@
         <v>44623</v>
       </c>
       <c r="B359" t="n">
-        <v>18.57873344421387</v>
+        <v>18.57873725891113</v>
       </c>
       <c r="C359" t="n">
-        <v>19.46257567399548</v>
+        <v>19.46257967016855</v>
       </c>
       <c r="D359" t="n">
-        <v>18.54265740861459</v>
+        <v>18.54266121590451</v>
       </c>
       <c r="E359" t="n">
-        <v>18.72303414621086</v>
+        <v>18.72303799053682</v>
       </c>
       <c r="F359" t="n">
         <v>930450</v>
@@ -7612,16 +7612,16 @@
         <v>44624</v>
       </c>
       <c r="B360" t="n">
-        <v>17.91134452819824</v>
+        <v>17.91134643554688</v>
       </c>
       <c r="C360" t="n">
-        <v>18.75911082938567</v>
+        <v>18.7591128270115</v>
       </c>
       <c r="D360" t="n">
-        <v>17.55059100747137</v>
+        <v>17.55059287640398</v>
       </c>
       <c r="E360" t="n">
-        <v>18.57873578922251</v>
+        <v>18.5787377676405</v>
       </c>
       <c r="F360" t="n">
         <v>1669200</v>
@@ -7672,16 +7672,16 @@
         <v>44629</v>
       </c>
       <c r="B363" t="n">
-        <v>18.23602294921875</v>
+        <v>18.23602104187012</v>
       </c>
       <c r="C363" t="n">
-        <v>18.36228738797532</v>
+        <v>18.36228546742039</v>
       </c>
       <c r="D363" t="n">
-        <v>17.51451924289774</v>
+        <v>17.51451741101287</v>
       </c>
       <c r="E363" t="n">
-        <v>17.5325572656059</v>
+        <v>17.53255543183439</v>
       </c>
       <c r="F363" t="n">
         <v>713800</v>
@@ -7732,16 +7732,16 @@
         <v>44634</v>
       </c>
       <c r="B366" t="n">
-        <v>17.31610679626465</v>
+        <v>17.31610488891602</v>
       </c>
       <c r="C366" t="n">
-        <v>17.67685866281171</v>
+        <v>17.67685671572668</v>
       </c>
       <c r="D366" t="n">
-        <v>16.88320283620759</v>
+        <v>16.88320097654281</v>
       </c>
       <c r="E366" t="n">
-        <v>17.35218112281906</v>
+        <v>17.35217921149688</v>
       </c>
       <c r="F366" t="n">
         <v>989600</v>
@@ -7752,16 +7752,16 @@
         <v>44635</v>
       </c>
       <c r="B367" t="n">
-        <v>17.46040534973145</v>
+        <v>17.46040725708008</v>
       </c>
       <c r="C367" t="n">
-        <v>17.56863003600147</v>
+        <v>17.56863195517241</v>
       </c>
       <c r="D367" t="n">
-        <v>16.93731477889199</v>
+        <v>16.93731662909899</v>
       </c>
       <c r="E367" t="n">
-        <v>17.04553946516202</v>
+        <v>17.04554132719132</v>
       </c>
       <c r="F367" t="n">
         <v>763850</v>
@@ -7772,16 +7772,16 @@
         <v>44636</v>
       </c>
       <c r="B368" t="n">
-        <v>17.53255462646484</v>
+        <v>17.53255653381348</v>
       </c>
       <c r="C368" t="n">
-        <v>18.10975750463644</v>
+        <v>18.10975947477838</v>
       </c>
       <c r="D368" t="n">
-        <v>17.15376480761467</v>
+        <v>17.15376667375514</v>
       </c>
       <c r="E368" t="n">
-        <v>17.58666696624336</v>
+        <v>17.58666887947882</v>
       </c>
       <c r="F368" t="n">
         <v>1212700</v>
@@ -7792,16 +7792,16 @@
         <v>44637</v>
       </c>
       <c r="B369" t="n">
-        <v>18.16387367248535</v>
+        <v>18.16387176513672</v>
       </c>
       <c r="C369" t="n">
-        <v>18.3081744224399</v>
+        <v>18.30817249993856</v>
       </c>
       <c r="D369" t="n">
-        <v>17.17180644659796</v>
+        <v>17.17180464342414</v>
       </c>
       <c r="E369" t="n">
-        <v>17.56863264887267</v>
+        <v>17.56863080402899</v>
       </c>
       <c r="F369" t="n">
         <v>935650</v>
@@ -7812,16 +7812,16 @@
         <v>44638</v>
       </c>
       <c r="B370" t="n">
-        <v>18.43443489074707</v>
+        <v>18.4344367980957</v>
       </c>
       <c r="C370" t="n">
-        <v>18.90341136679641</v>
+        <v>18.90341332266845</v>
       </c>
       <c r="D370" t="n">
-        <v>18.01956903400312</v>
+        <v>18.01957089842698</v>
       </c>
       <c r="E370" t="n">
-        <v>18.16386975281834</v>
+        <v>18.16387163217251</v>
       </c>
       <c r="F370" t="n">
         <v>2000150</v>
@@ -7892,16 +7892,16 @@
         <v>44644</v>
       </c>
       <c r="B374" t="n">
-        <v>20.79736137390137</v>
+        <v>20.79736328125</v>
       </c>
       <c r="C374" t="n">
-        <v>20.79736137390137</v>
+        <v>20.79736328125</v>
       </c>
       <c r="D374" t="n">
-        <v>19.49865484696414</v>
+        <v>19.49865663520698</v>
       </c>
       <c r="E374" t="n">
-        <v>19.71510593478701</v>
+        <v>19.71510774288082</v>
       </c>
       <c r="F374" t="n">
         <v>1624000</v>
@@ -7912,16 +7912,16 @@
         <v>44645</v>
       </c>
       <c r="B375" t="n">
-        <v>21.19418907165527</v>
+        <v>21.19418716430664</v>
       </c>
       <c r="C375" t="n">
-        <v>21.4467161990152</v>
+        <v>21.44671426894065</v>
       </c>
       <c r="D375" t="n">
-        <v>20.81539924071555</v>
+        <v>20.81539736745571</v>
       </c>
       <c r="E375" t="n">
-        <v>20.92362564392704</v>
+        <v>20.92362376092747</v>
       </c>
       <c r="F375" t="n">
         <v>911550</v>
@@ -7972,16 +7972,16 @@
         <v>44650</v>
       </c>
       <c r="B378" t="n">
-        <v>21.4106388092041</v>
+        <v>21.41064071655273</v>
       </c>
       <c r="C378" t="n">
-        <v>22.02391770830417</v>
+        <v>22.02391967028623</v>
       </c>
       <c r="D378" t="n">
-        <v>21.28437611357769</v>
+        <v>21.28437800967832</v>
       </c>
       <c r="E378" t="n">
-        <v>21.93372933134236</v>
+        <v>21.93373128529007</v>
       </c>
       <c r="F378" t="n">
         <v>851150</v>
@@ -8012,16 +8012,16 @@
         <v>44652</v>
       </c>
       <c r="B380" t="n">
-        <v>21.78943061828613</v>
+        <v>21.7894287109375</v>
       </c>
       <c r="C380" t="n">
-        <v>21.84354296135495</v>
+        <v>21.84354104926957</v>
       </c>
       <c r="D380" t="n">
-        <v>21.17615166283828</v>
+        <v>21.17614980917333</v>
       </c>
       <c r="E380" t="n">
-        <v>21.42867879749339</v>
+        <v>21.42867692172335</v>
       </c>
       <c r="F380" t="n">
         <v>746250</v>
@@ -8032,16 +8032,16 @@
         <v>44655</v>
       </c>
       <c r="B381" t="n">
-        <v>21.89765930175781</v>
+        <v>21.89765739440918</v>
       </c>
       <c r="C381" t="n">
-        <v>21.91569560452276</v>
+        <v>21.91569369560312</v>
       </c>
       <c r="D381" t="n">
-        <v>21.32045460826564</v>
+        <v>21.32045275119318</v>
       </c>
       <c r="E381" t="n">
-        <v>21.78943288416536</v>
+        <v>21.78943098624356</v>
       </c>
       <c r="F381" t="n">
         <v>503500</v>
@@ -8072,16 +8072,16 @@
         <v>44657</v>
       </c>
       <c r="B383" t="n">
-        <v>20.0217456817627</v>
+        <v>20.02174377441406</v>
       </c>
       <c r="C383" t="n">
-        <v>20.58091056962541</v>
+        <v>20.58090860900858</v>
       </c>
       <c r="D383" t="n">
-        <v>19.58884177995242</v>
+        <v>19.58883991384388</v>
       </c>
       <c r="E383" t="n">
-        <v>20.58091056962541</v>
+        <v>20.58090860900858</v>
       </c>
       <c r="F383" t="n">
         <v>1237700</v>
@@ -8092,16 +8092,16 @@
         <v>44658</v>
       </c>
       <c r="B384" t="n">
-        <v>19.6609935760498</v>
+        <v>19.66099166870117</v>
       </c>
       <c r="C384" t="n">
-        <v>20.0037091182781</v>
+        <v>20.00370717768201</v>
       </c>
       <c r="D384" t="n">
-        <v>19.55276888286228</v>
+        <v>19.55276698601272</v>
       </c>
       <c r="E384" t="n">
-        <v>19.85940838056108</v>
+        <v>19.85940645396386</v>
       </c>
       <c r="F384" t="n">
         <v>978600</v>
@@ -8152,16 +8152,16 @@
         <v>44663</v>
       </c>
       <c r="B387" t="n">
-        <v>19.13789939880371</v>
+        <v>19.13790130615234</v>
       </c>
       <c r="C387" t="n">
-        <v>19.84136665398996</v>
+        <v>19.84136863144855</v>
       </c>
       <c r="D387" t="n">
-        <v>18.99359868802707</v>
+        <v>18.9936005809942</v>
       </c>
       <c r="E387" t="n">
-        <v>19.33631416627171</v>
+        <v>19.33631609339504</v>
       </c>
       <c r="F387" t="n">
         <v>1155250</v>
@@ -8192,16 +8192,16 @@
         <v>44665</v>
       </c>
       <c r="B389" t="n">
-        <v>19.57080459594727</v>
+        <v>19.5708065032959</v>
       </c>
       <c r="C389" t="n">
-        <v>19.67902927636525</v>
+        <v>19.67903119426134</v>
       </c>
       <c r="D389" t="n">
-        <v>19.01163801312008</v>
+        <v>19.01163986597297</v>
       </c>
       <c r="E389" t="n">
-        <v>19.17397675394734</v>
+        <v>19.17397862262157</v>
       </c>
       <c r="F389" t="n">
         <v>760550</v>
@@ -8212,16 +8212,16 @@
         <v>44669</v>
       </c>
       <c r="B390" t="n">
-        <v>19.55276870727539</v>
+        <v>19.55276679992676</v>
       </c>
       <c r="C390" t="n">
-        <v>20.0037089386417</v>
+        <v>20.0037069873044</v>
       </c>
       <c r="D390" t="n">
-        <v>19.49865636116756</v>
+        <v>19.49865445909752</v>
       </c>
       <c r="E390" t="n">
-        <v>19.67903142159381</v>
+        <v>19.6790295019284</v>
       </c>
       <c r="F390" t="n">
         <v>1023750</v>
@@ -8232,16 +8232,16 @@
         <v>44670</v>
       </c>
       <c r="B391" t="n">
-        <v>20.32838439941406</v>
+        <v>20.32838249206543</v>
       </c>
       <c r="C391" t="n">
-        <v>20.34642069949194</v>
+        <v>20.34641879045101</v>
       </c>
       <c r="D391" t="n">
-        <v>19.01163816251292</v>
+        <v>19.01163637871046</v>
       </c>
       <c r="E391" t="n">
-        <v>19.55276672945585</v>
+        <v>19.55276489488099</v>
       </c>
       <c r="F391" t="n">
         <v>1459950</v>
@@ -8272,16 +8272,16 @@
         <v>44673</v>
       </c>
       <c r="B393" t="n">
-        <v>19.55276870727539</v>
+        <v>19.55276679992676</v>
       </c>
       <c r="C393" t="n">
-        <v>20.49072349401308</v>
+        <v>20.4907214951681</v>
       </c>
       <c r="D393" t="n">
-        <v>19.35435390454591</v>
+        <v>19.3543520165524</v>
       </c>
       <c r="E393" t="n">
-        <v>20.09389732895506</v>
+        <v>20.09389536881999</v>
       </c>
       <c r="F393" t="n">
         <v>931750</v>
@@ -8292,16 +8292,16 @@
         <v>44676</v>
       </c>
       <c r="B394" t="n">
-        <v>19.30024147033691</v>
+        <v>19.30023956298828</v>
       </c>
       <c r="C394" t="n">
-        <v>19.57080664004192</v>
+        <v>19.57080470595465</v>
       </c>
       <c r="D394" t="n">
-        <v>18.61481211536489</v>
+        <v>18.61481027575389</v>
       </c>
       <c r="E394" t="n">
-        <v>19.28220344831649</v>
+        <v>19.28220154275046</v>
       </c>
       <c r="F394" t="n">
         <v>1378800</v>
@@ -8332,16 +8332,16 @@
         <v>44678</v>
       </c>
       <c r="B396" t="n">
-        <v>19.49865341186523</v>
+        <v>19.49865531921387</v>
       </c>
       <c r="C396" t="n">
-        <v>19.55276574978821</v>
+        <v>19.55276766243008</v>
       </c>
       <c r="D396" t="n">
-        <v>19.10182558662962</v>
+        <v>19.10182745516075</v>
       </c>
       <c r="E396" t="n">
-        <v>19.46257737311645</v>
+        <v>19.46257927693614</v>
       </c>
       <c r="F396" t="n">
         <v>619300</v>
@@ -8352,16 +8352,16 @@
         <v>44679</v>
       </c>
       <c r="B397" t="n">
-        <v>21.04989051818848</v>
+        <v>21.04988861083984</v>
       </c>
       <c r="C397" t="n">
-        <v>21.10400286527417</v>
+        <v>21.10400095302237</v>
       </c>
       <c r="D397" t="n">
-        <v>19.30024190721312</v>
+        <v>19.30024015840165</v>
       </c>
       <c r="E397" t="n">
-        <v>19.84137053867153</v>
+        <v>19.84136874082794</v>
       </c>
       <c r="F397" t="n">
         <v>1501350</v>
@@ -8372,16 +8372,16 @@
         <v>44680</v>
       </c>
       <c r="B398" t="n">
-        <v>21.04989051818848</v>
+        <v>21.04988861083984</v>
       </c>
       <c r="C398" t="n">
-        <v>21.60905545187512</v>
+        <v>21.60905349386008</v>
       </c>
       <c r="D398" t="n">
-        <v>20.90558977915963</v>
+        <v>20.90558788488621</v>
       </c>
       <c r="E398" t="n">
-        <v>21.60905545187512</v>
+        <v>21.60905349386008</v>
       </c>
       <c r="F398" t="n">
         <v>1651000</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.51902961730957</v>
+        <v>19.5190315246582</v>
       </c>
       <c r="C403" t="n">
-        <v>19.93473065890365</v>
+        <v>19.9347326068735</v>
       </c>
       <c r="D403" t="n">
-        <v>18.81989711218194</v>
+        <v>18.81989895121317</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019330479591</v>
+        <v>19.67019522691586</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8492,16 +8492,16 @@
         <v>44690</v>
       </c>
       <c r="B404" t="n">
-        <v>18.7821102142334</v>
+        <v>18.78210830688477</v>
       </c>
       <c r="C404" t="n">
-        <v>19.53793065186498</v>
+        <v>19.53792866776176</v>
       </c>
       <c r="D404" t="n">
-        <v>18.38530498003061</v>
+        <v>18.38530311297808</v>
       </c>
       <c r="E404" t="n">
-        <v>19.25449731199797</v>
+        <v>19.25449535667779</v>
       </c>
       <c r="F404" t="n">
         <v>2367350</v>
@@ -8512,16 +8512,16 @@
         <v>44691</v>
       </c>
       <c r="B405" t="n">
-        <v>19.16001892089844</v>
+        <v>19.1600170135498</v>
       </c>
       <c r="C405" t="n">
-        <v>19.38676448302573</v>
+        <v>19.38676255310495</v>
       </c>
       <c r="D405" t="n">
-        <v>18.61205002858743</v>
+        <v>18.6120481757882</v>
       </c>
       <c r="E405" t="n">
-        <v>19.04664523882802</v>
+        <v>19.04664334276555</v>
       </c>
       <c r="F405" t="n">
         <v>1243050</v>
@@ -8532,16 +8532,16 @@
         <v>44692</v>
       </c>
       <c r="B406" t="n">
-        <v>19.10333251953125</v>
+        <v>19.10333061218262</v>
       </c>
       <c r="C406" t="n">
-        <v>19.57571959095203</v>
+        <v>19.57571763643849</v>
       </c>
       <c r="D406" t="n">
-        <v>18.93327468751125</v>
+        <v>18.93327279714184</v>
       </c>
       <c r="E406" t="n">
-        <v>19.14112435021147</v>
+        <v>19.14112243908956</v>
       </c>
       <c r="F406" t="n">
         <v>1048200</v>
@@ -8552,16 +8552,16 @@
         <v>44693</v>
       </c>
       <c r="B407" t="n">
-        <v>19.33007621765137</v>
+        <v>19.330078125</v>
       </c>
       <c r="C407" t="n">
-        <v>19.7079872796457</v>
+        <v>19.70798922428379</v>
       </c>
       <c r="D407" t="n">
-        <v>18.81989916718061</v>
+        <v>18.81990102418875</v>
       </c>
       <c r="E407" t="n">
-        <v>18.93327284618161</v>
+        <v>18.93327471437663</v>
       </c>
       <c r="F407" t="n">
         <v>1412250</v>
@@ -8632,16 +8632,16 @@
         <v>44699</v>
       </c>
       <c r="B411" t="n">
-        <v>20.36932563781738</v>
+        <v>20.36932945251465</v>
       </c>
       <c r="C411" t="n">
-        <v>20.76613076461962</v>
+        <v>20.76613465362919</v>
       </c>
       <c r="D411" t="n">
-        <v>20.10479008795808</v>
+        <v>20.10479385311404</v>
       </c>
       <c r="E411" t="n">
-        <v>20.44490748092194</v>
+        <v>20.44491130977391</v>
       </c>
       <c r="F411" t="n">
         <v>1338150</v>
@@ -8672,16 +8672,16 @@
         <v>44701</v>
       </c>
       <c r="B413" t="n">
-        <v>20.65276336669922</v>
+        <v>20.65275955200195</v>
       </c>
       <c r="C413" t="n">
-        <v>21.08735860801926</v>
+        <v>21.08735471304948</v>
       </c>
       <c r="D413" t="n">
-        <v>20.25595815409612</v>
+        <v>20.25595441269131</v>
       </c>
       <c r="E413" t="n">
-        <v>21.03067266393701</v>
+        <v>21.03066877943749</v>
       </c>
       <c r="F413" t="n">
         <v>1756800</v>
@@ -8692,16 +8692,16 @@
         <v>44704</v>
       </c>
       <c r="B414" t="n">
-        <v>20.82282066345215</v>
+        <v>20.82282257080078</v>
       </c>
       <c r="C414" t="n">
-        <v>21.16293809177876</v>
+        <v>21.1629400302818</v>
       </c>
       <c r="D414" t="n">
-        <v>20.61496922179389</v>
+        <v>20.61497111010355</v>
       </c>
       <c r="E414" t="n">
-        <v>20.78502883696393</v>
+        <v>20.78503074085087</v>
       </c>
       <c r="F414" t="n">
         <v>1655200</v>
@@ -8712,16 +8712,16 @@
         <v>44705</v>
       </c>
       <c r="B415" t="n">
-        <v>20.38822555541992</v>
+        <v>20.38822364807129</v>
       </c>
       <c r="C415" t="n">
-        <v>20.7850307601951</v>
+        <v>20.78502881572475</v>
       </c>
       <c r="D415" t="n">
-        <v>19.93473440768075</v>
+        <v>19.93473254275689</v>
       </c>
       <c r="E415" t="n">
-        <v>20.59607521429696</v>
+        <v>20.59607328750369</v>
       </c>
       <c r="F415" t="n">
         <v>1381900</v>
@@ -8752,16 +8752,16 @@
         <v>44707</v>
       </c>
       <c r="B417" t="n">
-        <v>21.18183517456055</v>
+        <v>21.18183326721191</v>
       </c>
       <c r="C417" t="n">
-        <v>21.27631294398413</v>
+        <v>21.27631102812812</v>
       </c>
       <c r="D417" t="n">
-        <v>20.67165630088131</v>
+        <v>20.67165443947247</v>
       </c>
       <c r="E417" t="n">
-        <v>20.8228218131672</v>
+        <v>20.82281993814643</v>
       </c>
       <c r="F417" t="n">
         <v>1373550</v>
@@ -8792,16 +8792,16 @@
         <v>44711</v>
       </c>
       <c r="B419" t="n">
-        <v>22.14550590515137</v>
+        <v>22.14550399780273</v>
       </c>
       <c r="C419" t="n">
-        <v>23.22254782665845</v>
+        <v>23.22254582654633</v>
       </c>
       <c r="D419" t="n">
-        <v>22.14550590515137</v>
+        <v>22.14550399780273</v>
       </c>
       <c r="E419" t="n">
-        <v>22.97690633890859</v>
+        <v>22.97690435995308</v>
       </c>
       <c r="F419" t="n">
         <v>1234700</v>
@@ -8812,16 +8812,16 @@
         <v>44712</v>
       </c>
       <c r="B420" t="n">
-        <v>22.52341461181641</v>
+        <v>22.52341270446777</v>
       </c>
       <c r="C420" t="n">
-        <v>22.76905609322542</v>
+        <v>22.76905416507515</v>
       </c>
       <c r="D420" t="n">
-        <v>21.99434162217354</v>
+        <v>21.99433975962836</v>
       </c>
       <c r="E420" t="n">
-        <v>22.23998310358255</v>
+        <v>22.23998122023573</v>
       </c>
       <c r="F420" t="n">
         <v>1969900</v>
@@ -8912,16 +8912,16 @@
         <v>44719</v>
       </c>
       <c r="B425" t="n">
-        <v>21.59753608703613</v>
+        <v>21.5975341796875</v>
       </c>
       <c r="C425" t="n">
-        <v>21.93765353112191</v>
+        <v>21.93765159373639</v>
       </c>
       <c r="D425" t="n">
-        <v>21.25741684093681</v>
+        <v>21.25741496362521</v>
       </c>
       <c r="E425" t="n">
-        <v>21.72980388184651</v>
+        <v>21.72980196281688</v>
       </c>
       <c r="F425" t="n">
         <v>1412350</v>
@@ -8932,16 +8932,16 @@
         <v>44720</v>
       </c>
       <c r="B426" t="n">
-        <v>21.20072937011719</v>
+        <v>21.20073127746582</v>
       </c>
       <c r="C426" t="n">
-        <v>21.82428007494298</v>
+        <v>21.82428203839009</v>
       </c>
       <c r="D426" t="n">
-        <v>21.03066975934408</v>
+        <v>21.0306716513931</v>
       </c>
       <c r="E426" t="n">
-        <v>21.48416085339676</v>
+        <v>21.48416278624464</v>
       </c>
       <c r="F426" t="n">
         <v>863650</v>
@@ -8952,16 +8952,16 @@
         <v>44721</v>
       </c>
       <c r="B427" t="n">
-        <v>21.54084777832031</v>
+        <v>21.54084968566895</v>
       </c>
       <c r="C427" t="n">
-        <v>21.72980331052155</v>
+        <v>21.72980523460138</v>
       </c>
       <c r="D427" t="n">
-        <v>20.8984029332658</v>
+        <v>20.89840478372873</v>
       </c>
       <c r="E427" t="n">
-        <v>21.20073034317699</v>
+        <v>21.20073222040969</v>
       </c>
       <c r="F427" t="n">
         <v>1117750</v>
@@ -8992,16 +8992,16 @@
         <v>44725</v>
       </c>
       <c r="B429" t="n">
-        <v>19.25449371337891</v>
+        <v>19.25449562072754</v>
       </c>
       <c r="C429" t="n">
-        <v>20.01031400974947</v>
+        <v>20.0103159919696</v>
       </c>
       <c r="D429" t="n">
-        <v>18.98995814136063</v>
+        <v>18.98996002250438</v>
       </c>
       <c r="E429" t="n">
-        <v>19.95362807317604</v>
+        <v>19.95363004978087</v>
       </c>
       <c r="F429" t="n">
         <v>2646600</v>
@@ -9032,16 +9032,16 @@
         <v>44727</v>
       </c>
       <c r="B431" t="n">
-        <v>19.65130043029785</v>
+        <v>19.65130233764648</v>
       </c>
       <c r="C431" t="n">
-        <v>19.82136005550457</v>
+        <v>19.82136197935914</v>
       </c>
       <c r="D431" t="n">
-        <v>19.17891338339633</v>
+        <v>19.17891524489523</v>
       </c>
       <c r="E431" t="n">
-        <v>19.44345077838607</v>
+        <v>19.44345266556088</v>
       </c>
       <c r="F431" t="n">
         <v>990050</v>
@@ -9052,16 +9052,16 @@
         <v>44729</v>
       </c>
       <c r="B432" t="n">
-        <v>19.19780731201172</v>
+        <v>19.19780921936035</v>
       </c>
       <c r="C432" t="n">
-        <v>19.51903061483979</v>
+        <v>19.51903255410274</v>
       </c>
       <c r="D432" t="n">
-        <v>18.68763029117579</v>
+        <v>18.6876321478371</v>
       </c>
       <c r="E432" t="n">
-        <v>19.17891139960691</v>
+        <v>19.17891330507819</v>
       </c>
       <c r="F432" t="n">
         <v>2517400</v>
@@ -9132,16 +9132,16 @@
         <v>44735</v>
       </c>
       <c r="B436" t="n">
-        <v>18.81989860534668</v>
+        <v>18.81990051269531</v>
       </c>
       <c r="C436" t="n">
-        <v>18.89548045508649</v>
+        <v>18.89548237009515</v>
       </c>
       <c r="D436" t="n">
-        <v>18.49867529344914</v>
+        <v>18.4986771682426</v>
       </c>
       <c r="E436" t="n">
-        <v>18.72542084266856</v>
+        <v>18.72542274044211</v>
       </c>
       <c r="F436" t="n">
         <v>1280500</v>
@@ -9152,16 +9152,16 @@
         <v>44736</v>
       </c>
       <c r="B437" t="n">
-        <v>18.47978019714355</v>
+        <v>18.47978210449219</v>
       </c>
       <c r="C437" t="n">
-        <v>18.95216722939579</v>
+        <v>18.95216918550078</v>
       </c>
       <c r="D437" t="n">
-        <v>18.23413872413077</v>
+        <v>18.23414060612608</v>
       </c>
       <c r="E437" t="n">
-        <v>18.95216722939579</v>
+        <v>18.95216918550078</v>
       </c>
       <c r="F437" t="n">
         <v>1255000</v>
@@ -9172,16 +9172,16 @@
         <v>44739</v>
       </c>
       <c r="B438" t="n">
-        <v>18.55536270141602</v>
+        <v>18.55536079406738</v>
       </c>
       <c r="C438" t="n">
-        <v>18.70652641288067</v>
+        <v>18.70652448999358</v>
       </c>
       <c r="D438" t="n">
-        <v>18.38530307551488</v>
+        <v>18.38530118564707</v>
       </c>
       <c r="E438" t="n">
-        <v>18.57425861585249</v>
+        <v>18.57425670656151</v>
       </c>
       <c r="F438" t="n">
         <v>799000</v>
@@ -9252,16 +9252,16 @@
         <v>44743</v>
       </c>
       <c r="B442" t="n">
-        <v>17.59169387817383</v>
+        <v>17.5916919708252</v>
       </c>
       <c r="C442" t="n">
-        <v>17.72396167059182</v>
+        <v>17.72395974890228</v>
       </c>
       <c r="D442" t="n">
-        <v>17.06261910447483</v>
+        <v>17.06261725449021</v>
       </c>
       <c r="E442" t="n">
-        <v>17.2515746382264</v>
+        <v>17.25157276775461</v>
       </c>
       <c r="F442" t="n">
         <v>2016600</v>
@@ -9272,16 +9272,16 @@
         <v>44746</v>
       </c>
       <c r="B443" t="n">
-        <v>17.28936576843262</v>
+        <v>17.28936386108398</v>
       </c>
       <c r="C443" t="n">
-        <v>17.64838094509635</v>
+        <v>17.64837899814145</v>
       </c>
       <c r="D443" t="n">
-        <v>17.25157574047591</v>
+        <v>17.25157383729624</v>
       </c>
       <c r="E443" t="n">
-        <v>17.44052948428672</v>
+        <v>17.44052756026183</v>
       </c>
       <c r="F443" t="n">
         <v>903450</v>
@@ -9292,16 +9292,16 @@
         <v>44747</v>
       </c>
       <c r="B444" t="n">
-        <v>17.10041236877441</v>
+        <v>17.10041046142578</v>
       </c>
       <c r="C444" t="n">
-        <v>17.25157608767075</v>
+        <v>17.25157416346159</v>
       </c>
       <c r="D444" t="n">
-        <v>16.57133935263724</v>
+        <v>16.57133750430044</v>
       </c>
       <c r="E444" t="n">
-        <v>17.15709831285712</v>
+        <v>17.15709639918584</v>
       </c>
       <c r="F444" t="n">
         <v>2077700</v>
@@ -9332,16 +9332,16 @@
         <v>44749</v>
       </c>
       <c r="B446" t="n">
-        <v>17.66727447509766</v>
+        <v>17.66727638244629</v>
       </c>
       <c r="C446" t="n">
-        <v>18.13966147387552</v>
+        <v>18.13966343222278</v>
       </c>
       <c r="D446" t="n">
-        <v>17.49721486721548</v>
+        <v>17.49721675620458</v>
       </c>
       <c r="E446" t="n">
-        <v>17.51611077964981</v>
+        <v>17.5161126706789</v>
       </c>
       <c r="F446" t="n">
         <v>1515500</v>
@@ -9412,16 +9412,16 @@
         <v>44755</v>
       </c>
       <c r="B450" t="n">
-        <v>16.87366676330566</v>
+        <v>16.87366485595703</v>
       </c>
       <c r="C450" t="n">
-        <v>17.024830481959</v>
+        <v>17.02482855752328</v>
       </c>
       <c r="D450" t="n">
-        <v>16.3445919460053</v>
+        <v>16.3445900984617</v>
       </c>
       <c r="E450" t="n">
-        <v>16.51465157999372</v>
+        <v>16.51464971322709</v>
       </c>
       <c r="F450" t="n">
         <v>919750</v>
@@ -9452,16 +9452,16 @@
         <v>44757</v>
       </c>
       <c r="B452" t="n">
-        <v>16.59023284912109</v>
+        <v>16.59023094177246</v>
       </c>
       <c r="C452" t="n">
-        <v>17.15709767491168</v>
+        <v>17.15709570239164</v>
       </c>
       <c r="D452" t="n">
-        <v>16.59023284912109</v>
+        <v>16.59023094177246</v>
       </c>
       <c r="E452" t="n">
-        <v>17.06261990361098</v>
+        <v>17.06261794195288</v>
       </c>
       <c r="F452" t="n">
         <v>1098550</v>
@@ -9472,16 +9472,16 @@
         <v>44760</v>
       </c>
       <c r="B453" t="n">
-        <v>16.94924926757812</v>
+        <v>16.94924736022949</v>
       </c>
       <c r="C453" t="n">
-        <v>17.34605449464563</v>
+        <v>17.34605254264335</v>
       </c>
       <c r="D453" t="n">
-        <v>16.74139779501045</v>
+        <v>16.74139591105195</v>
       </c>
       <c r="E453" t="n">
-        <v>16.74139779501045</v>
+        <v>16.74139591105195</v>
       </c>
       <c r="F453" t="n">
         <v>809650</v>
@@ -9492,16 +9492,16 @@
         <v>44761</v>
       </c>
       <c r="B454" t="n">
-        <v>17.28936576843262</v>
+        <v>17.28936386108398</v>
       </c>
       <c r="C454" t="n">
-        <v>17.51611314422741</v>
+        <v>17.51611121186419</v>
       </c>
       <c r="D454" t="n">
-        <v>17.1004120246218</v>
+        <v>17.10041013811839</v>
       </c>
       <c r="E454" t="n">
-        <v>17.1004120246218</v>
+        <v>17.10041013811839</v>
       </c>
       <c r="F454" t="n">
         <v>816100</v>
@@ -9512,16 +9512,16 @@
         <v>44762</v>
       </c>
       <c r="B455" t="n">
-        <v>17.9696044921875</v>
+        <v>17.96960067749023</v>
       </c>
       <c r="C455" t="n">
-        <v>18.02629043576155</v>
+        <v>18.02628660903064</v>
       </c>
       <c r="D455" t="n">
-        <v>17.2326800176703</v>
+        <v>17.23267635941185</v>
       </c>
       <c r="E455" t="n">
-        <v>17.2515759328662</v>
+        <v>17.25157227059641</v>
       </c>
       <c r="F455" t="n">
         <v>812650</v>
@@ -9592,16 +9592,16 @@
         <v>44768</v>
       </c>
       <c r="B459" t="n">
-        <v>17.40273666381836</v>
+        <v>17.40273857116699</v>
       </c>
       <c r="C459" t="n">
-        <v>18.15855512180728</v>
+        <v>18.158557111994</v>
       </c>
       <c r="D459" t="n">
-        <v>17.25157297222058</v>
+        <v>17.25157486300159</v>
       </c>
       <c r="E459" t="n">
-        <v>18.04518325411562</v>
+        <v>18.04518523187672</v>
       </c>
       <c r="F459" t="n">
         <v>578050</v>
@@ -9612,16 +9612,16 @@
         <v>44769</v>
       </c>
       <c r="B460" t="n">
-        <v>18.23413848876953</v>
+        <v>18.23414039611816</v>
       </c>
       <c r="C460" t="n">
-        <v>18.38530219297798</v>
+        <v>18.38530411613882</v>
       </c>
       <c r="D460" t="n">
-        <v>17.34605217704824</v>
+        <v>17.34605399150023</v>
       </c>
       <c r="E460" t="n">
-        <v>17.4405281406684</v>
+        <v>17.44052996500288</v>
       </c>
       <c r="F460" t="n">
         <v>704800</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.51902961730957</v>
+        <v>19.5190315246582</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65129739335679</v>
+        <v>19.65129931363029</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431526843877</v>
+        <v>18.74431710008434</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658304448599</v>
+        <v>18.87658488905642</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9692,16 +9692,16 @@
         <v>44775</v>
       </c>
       <c r="B464" t="n">
-        <v>19.08443832397461</v>
+        <v>19.08443641662598</v>
       </c>
       <c r="C464" t="n">
-        <v>19.38676576005906</v>
+        <v>19.38676382249504</v>
       </c>
       <c r="D464" t="n">
-        <v>18.895482775415</v>
+        <v>18.89548088695107</v>
       </c>
       <c r="E464" t="n">
-        <v>19.12222835247834</v>
+        <v>19.12222644135287</v>
       </c>
       <c r="F464" t="n">
         <v>867500</v>
@@ -9732,16 +9732,16 @@
         <v>44777</v>
       </c>
       <c r="B466" t="n">
-        <v>21.3141040802002</v>
+        <v>21.31410217285156</v>
       </c>
       <c r="C466" t="n">
-        <v>21.46526779834239</v>
+        <v>21.46526587746648</v>
       </c>
       <c r="D466" t="n">
-        <v>19.78357098350703</v>
+        <v>19.78356921312217</v>
       </c>
       <c r="E466" t="n">
-        <v>19.89694287110684</v>
+        <v>19.89694109057661</v>
       </c>
       <c r="F466" t="n">
         <v>1697500</v>
@@ -9772,16 +9772,16 @@
         <v>44781</v>
       </c>
       <c r="B468" t="n">
-        <v>21.54084777832031</v>
+        <v>21.54084968566895</v>
       </c>
       <c r="C468" t="n">
-        <v>21.843176990245</v>
+        <v>21.84317892436357</v>
       </c>
       <c r="D468" t="n">
-        <v>21.01177481097574</v>
+        <v>21.01177667147726</v>
       </c>
       <c r="E468" t="n">
-        <v>21.21962445478631</v>
+        <v>21.21962633369201</v>
       </c>
       <c r="F468" t="n">
         <v>1786950</v>
@@ -9792,16 +9792,16 @@
         <v>44782</v>
       </c>
       <c r="B469" t="n">
-        <v>20.8795051574707</v>
+        <v>20.87950706481934</v>
       </c>
       <c r="C469" t="n">
-        <v>21.84317504212628</v>
+        <v>21.84317703750642</v>
       </c>
       <c r="D469" t="n">
-        <v>20.72834146599689</v>
+        <v>20.72834335953668</v>
       </c>
       <c r="E469" t="n">
-        <v>21.7486972844518</v>
+        <v>21.74869927120138</v>
       </c>
       <c r="F469" t="n">
         <v>1406900</v>
@@ -9812,16 +9812,16 @@
         <v>44783</v>
       </c>
       <c r="B470" t="n">
-        <v>21.82428359985352</v>
+        <v>21.82427978515625</v>
       </c>
       <c r="C470" t="n">
-        <v>22.12661104471852</v>
+        <v>22.12660717717701</v>
       </c>
       <c r="D470" t="n">
-        <v>21.08735910148479</v>
+        <v>21.08735541559559</v>
       </c>
       <c r="E470" t="n">
-        <v>21.16294096270104</v>
+        <v>21.16293726360078</v>
       </c>
       <c r="F470" t="n">
         <v>1851300</v>
@@ -9832,16 +9832,16 @@
         <v>44784</v>
       </c>
       <c r="B471" t="n">
-        <v>22.01323699951172</v>
+        <v>22.01323509216309</v>
       </c>
       <c r="C471" t="n">
-        <v>22.0888188595181</v>
+        <v>22.08881694562063</v>
       </c>
       <c r="D471" t="n">
-        <v>21.54084992396843</v>
+        <v>21.54084805755003</v>
       </c>
       <c r="E471" t="n">
-        <v>21.82428325050261</v>
+        <v>21.82428135952598</v>
       </c>
       <c r="F471" t="n">
         <v>1242750</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75015830993652</v>
+        <v>22.75016021728516</v>
       </c>
       <c r="C474" t="n">
-        <v>23.12806755720854</v>
+        <v>23.12806949624067</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341276157331</v>
+        <v>22.52341464991185</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027753348805</v>
+        <v>23.09027946935192</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9912,16 +9912,16 @@
         <v>44790</v>
       </c>
       <c r="B475" t="n">
-        <v>22.80684471130371</v>
+        <v>22.80684661865234</v>
       </c>
       <c r="C475" t="n">
-        <v>23.09027800404387</v>
+        <v>23.09027993509618</v>
       </c>
       <c r="D475" t="n">
-        <v>22.23998172985033</v>
+        <v>22.2399835897919</v>
       </c>
       <c r="E475" t="n">
-        <v>22.48562139407294</v>
+        <v>22.4856232745575</v>
       </c>
       <c r="F475" t="n">
         <v>781800</v>
@@ -9932,16 +9932,16 @@
         <v>44791</v>
       </c>
       <c r="B476" t="n">
-        <v>22.25887489318848</v>
+        <v>22.25887680053711</v>
       </c>
       <c r="C476" t="n">
-        <v>23.14696295606662</v>
+        <v>23.14696493951494</v>
       </c>
       <c r="D476" t="n">
-        <v>21.84317563142713</v>
+        <v>21.84317750315476</v>
       </c>
       <c r="E476" t="n">
-        <v>22.9957992605146</v>
+        <v>22.99580123100981</v>
       </c>
       <c r="F476" t="n">
         <v>1546750</v>
@@ -10032,16 +10032,16 @@
         <v>44798</v>
       </c>
       <c r="B481" t="n">
-        <v>20.8795051574707</v>
+        <v>20.87950706481934</v>
       </c>
       <c r="C481" t="n">
-        <v>21.21962256228011</v>
+        <v>21.21962450069856</v>
       </c>
       <c r="D481" t="n">
-        <v>20.57717777452308</v>
+        <v>20.57717965425402</v>
       </c>
       <c r="E481" t="n">
-        <v>20.91729517933248</v>
+        <v>20.91729709013325</v>
       </c>
       <c r="F481" t="n">
         <v>1364800</v>
@@ -10052,16 +10052,16 @@
         <v>44799</v>
       </c>
       <c r="B482" t="n">
-        <v>20.46380805969238</v>
+        <v>20.46380615234375</v>
       </c>
       <c r="C482" t="n">
-        <v>21.10625477362032</v>
+        <v>21.10625280639183</v>
       </c>
       <c r="D482" t="n">
-        <v>20.2748525078264</v>
+        <v>20.27485061808954</v>
       </c>
       <c r="E482" t="n">
-        <v>20.97398696852234</v>
+        <v>20.97398501362199</v>
       </c>
       <c r="F482" t="n">
         <v>564750</v>
@@ -10152,16 +10152,16 @@
         <v>44806</v>
       </c>
       <c r="B487" t="n">
-        <v>20.97398567199707</v>
+        <v>20.97398376464844</v>
       </c>
       <c r="C487" t="n">
-        <v>21.20073123901156</v>
+        <v>21.20072931104297</v>
       </c>
       <c r="D487" t="n">
-        <v>20.55828456479703</v>
+        <v>20.55828269525176</v>
       </c>
       <c r="E487" t="n">
-        <v>20.8795079019043</v>
+        <v>20.87950600314736</v>
       </c>
       <c r="F487" t="n">
         <v>1001300</v>
@@ -10172,16 +10172,16 @@
         <v>44809</v>
       </c>
       <c r="B488" t="n">
-        <v>21.72980117797852</v>
+        <v>21.72980308532715</v>
       </c>
       <c r="C488" t="n">
-        <v>21.84317484657557</v>
+        <v>21.84317676387566</v>
       </c>
       <c r="D488" t="n">
-        <v>20.87950497054724</v>
+        <v>20.87950680326052</v>
       </c>
       <c r="E488" t="n">
-        <v>21.01177274889936</v>
+        <v>21.01177459322254</v>
       </c>
       <c r="F488" t="n">
         <v>878600</v>
@@ -10192,16 +10192,16 @@
         <v>44810</v>
       </c>
       <c r="B489" t="n">
-        <v>20.55828285217285</v>
+        <v>20.55828475952148</v>
       </c>
       <c r="C489" t="n">
-        <v>21.67311648196554</v>
+        <v>21.67311849274579</v>
       </c>
       <c r="D489" t="n">
-        <v>20.3504332168947</v>
+        <v>20.35043510495954</v>
       </c>
       <c r="E489" t="n">
-        <v>21.55974280689618</v>
+        <v>21.55974480715789</v>
       </c>
       <c r="F489" t="n">
         <v>1564950</v>
@@ -10252,16 +10252,16 @@
         <v>44816</v>
       </c>
       <c r="B492" t="n">
-        <v>20.65276336669922</v>
+        <v>20.65275955200195</v>
       </c>
       <c r="C492" t="n">
-        <v>21.12515043874988</v>
+        <v>21.1251465367997</v>
       </c>
       <c r="D492" t="n">
-        <v>20.42601778835654</v>
+        <v>20.42601401554063</v>
       </c>
       <c r="E492" t="n">
-        <v>20.44491190170818</v>
+        <v>20.44490812540241</v>
       </c>
       <c r="F492" t="n">
         <v>1299050</v>
@@ -10292,16 +10292,16 @@
         <v>44818</v>
       </c>
       <c r="B494" t="n">
-        <v>20.42601585388184</v>
+        <v>20.4260139465332</v>
       </c>
       <c r="C494" t="n">
-        <v>20.52049181773355</v>
+        <v>20.5204899015629</v>
       </c>
       <c r="D494" t="n">
-        <v>19.51903182439467</v>
+        <v>19.51903000173875</v>
       </c>
       <c r="E494" t="n">
-        <v>19.7079873561251</v>
+        <v>19.70798551582482</v>
       </c>
       <c r="F494" t="n">
         <v>1153500</v>
@@ -10332,16 +10332,16 @@
         <v>44820</v>
       </c>
       <c r="B496" t="n">
-        <v>20.02920913696289</v>
+        <v>20.02921104431152</v>
       </c>
       <c r="C496" t="n">
-        <v>20.27484878648363</v>
+        <v>20.27485071722412</v>
       </c>
       <c r="D496" t="n">
-        <v>19.55682214601578</v>
+        <v>19.55682400837977</v>
       </c>
       <c r="E496" t="n">
-        <v>20.27484878648363</v>
+        <v>20.27485071722412</v>
       </c>
       <c r="F496" t="n">
         <v>1629800</v>
@@ -10352,16 +10352,16 @@
         <v>44823</v>
       </c>
       <c r="B497" t="n">
-        <v>20.36932563781738</v>
+        <v>20.36932945251465</v>
       </c>
       <c r="C497" t="n">
-        <v>20.5204893240265</v>
+        <v>20.52049316703318</v>
       </c>
       <c r="D497" t="n">
-        <v>19.85914864736495</v>
+        <v>19.85915236651802</v>
       </c>
       <c r="E497" t="n">
-        <v>19.93473049046951</v>
+        <v>19.93473422377729</v>
       </c>
       <c r="F497" t="n">
         <v>718850</v>
@@ -10412,16 +10412,16 @@
         <v>44826</v>
       </c>
       <c r="B500" t="n">
-        <v>19.93473434448242</v>
+        <v>19.93473243713379</v>
       </c>
       <c r="C500" t="n">
-        <v>19.97252437233406</v>
+        <v>19.97252246136969</v>
       </c>
       <c r="D500" t="n">
-        <v>18.81990059164773</v>
+        <v>18.81989879096601</v>
       </c>
       <c r="E500" t="n">
-        <v>19.34897359566612</v>
+        <v>19.34897174436288</v>
       </c>
       <c r="F500" t="n">
         <v>1035500</v>
@@ -10472,16 +10472,16 @@
         <v>44831</v>
       </c>
       <c r="B503" t="n">
-        <v>18.30972099304199</v>
+        <v>18.30972290039062</v>
       </c>
       <c r="C503" t="n">
-        <v>19.00885540242521</v>
+        <v>19.00885738260363</v>
       </c>
       <c r="D503" t="n">
-        <v>18.25303505244812</v>
+        <v>18.2530369538917</v>
       </c>
       <c r="E503" t="n">
-        <v>18.97106357402025</v>
+        <v>18.97106555026184</v>
       </c>
       <c r="F503" t="n">
         <v>994450</v>
@@ -10512,16 +10512,16 @@
         <v>44833</v>
       </c>
       <c r="B505" t="n">
-        <v>18.21524238586426</v>
+        <v>18.21524429321289</v>
       </c>
       <c r="C505" t="n">
-        <v>18.30971833915579</v>
+        <v>18.30972025639716</v>
       </c>
       <c r="D505" t="n">
-        <v>17.85622727610854</v>
+        <v>17.8562291458641</v>
       </c>
       <c r="E505" t="n">
-        <v>18.29082422970546</v>
+        <v>18.2908261449684</v>
       </c>
       <c r="F505" t="n">
         <v>1182750</v>
@@ -10532,16 +10532,16 @@
         <v>44834</v>
       </c>
       <c r="B506" t="n">
-        <v>18.25303649902344</v>
+        <v>18.2530345916748</v>
       </c>
       <c r="C506" t="n">
-        <v>18.51757391278236</v>
+        <v>18.51757197779093</v>
       </c>
       <c r="D506" t="n">
-        <v>17.95070905587821</v>
+        <v>17.95070718012124</v>
       </c>
       <c r="E506" t="n">
-        <v>18.21524646963713</v>
+        <v>18.21524456623737</v>
       </c>
       <c r="F506" t="n">
         <v>981200</v>
@@ -10552,16 +10552,16 @@
         <v>44837</v>
       </c>
       <c r="B507" t="n">
-        <v>19.27338981628418</v>
+        <v>19.27339172363281</v>
       </c>
       <c r="C507" t="n">
-        <v>19.27338981628418</v>
+        <v>19.27339172363281</v>
       </c>
       <c r="D507" t="n">
-        <v>18.76321277806593</v>
+        <v>18.76321463492602</v>
       </c>
       <c r="E507" t="n">
-        <v>18.89548056537928</v>
+        <v>18.89548243532896</v>
       </c>
       <c r="F507" t="n">
         <v>1581550</v>
@@ -10592,16 +10592,16 @@
         <v>44839</v>
       </c>
       <c r="B509" t="n">
-        <v>19.63240814208984</v>
+        <v>19.63240432739258</v>
       </c>
       <c r="C509" t="n">
-        <v>19.8402578133139</v>
+        <v>19.84025395823017</v>
       </c>
       <c r="D509" t="n">
-        <v>19.38676663863574</v>
+        <v>19.38676287166812</v>
       </c>
       <c r="E509" t="n">
-        <v>19.72688411863749</v>
+        <v>19.72688028558296</v>
       </c>
       <c r="F509" t="n">
         <v>721150</v>
@@ -10632,16 +10632,16 @@
         <v>44841</v>
       </c>
       <c r="B511" t="n">
-        <v>19.63240814208984</v>
+        <v>19.63240432739258</v>
       </c>
       <c r="C511" t="n">
-        <v>20.38822676655345</v>
+        <v>20.38822280499599</v>
       </c>
       <c r="D511" t="n">
-        <v>19.55682627964348</v>
+        <v>19.55682247963224</v>
       </c>
       <c r="E511" t="n">
-        <v>20.38822676655345</v>
+        <v>20.38822280499599</v>
       </c>
       <c r="F511" t="n">
         <v>673950</v>
@@ -10652,16 +10652,16 @@
         <v>44844</v>
       </c>
       <c r="B512" t="n">
-        <v>19.55682373046875</v>
+        <v>19.55682182312012</v>
       </c>
       <c r="C512" t="n">
-        <v>19.74577746094821</v>
+        <v>19.7457755351712</v>
       </c>
       <c r="D512" t="n">
-        <v>19.29228634538129</v>
+        <v>19.2922844638326</v>
       </c>
       <c r="E512" t="n">
-        <v>19.68909152200573</v>
+        <v>19.68908960175721</v>
       </c>
       <c r="F512" t="n">
         <v>555250</v>
@@ -10712,16 +10712,16 @@
         <v>44848</v>
       </c>
       <c r="B515" t="n">
-        <v>19.16001892089844</v>
+        <v>19.1600170135498</v>
       </c>
       <c r="C515" t="n">
-        <v>19.84025560728032</v>
+        <v>19.84025363221523</v>
       </c>
       <c r="D515" t="n">
-        <v>18.97106338478559</v>
+        <v>18.97106149624717</v>
       </c>
       <c r="E515" t="n">
-        <v>19.84025560728032</v>
+        <v>19.84025363221523</v>
       </c>
       <c r="F515" t="n">
         <v>919650</v>
@@ -10752,16 +10752,16 @@
         <v>44852</v>
       </c>
       <c r="B517" t="n">
-        <v>19.53792762756348</v>
+        <v>19.53792953491211</v>
       </c>
       <c r="C517" t="n">
-        <v>19.78356909661954</v>
+        <v>19.7835710279484</v>
       </c>
       <c r="D517" t="n">
-        <v>19.23560022011401</v>
+        <v>19.23560209794857</v>
       </c>
       <c r="E517" t="n">
-        <v>19.55682354103244</v>
+        <v>19.55682545022575</v>
       </c>
       <c r="F517" t="n">
         <v>665900</v>
@@ -10792,16 +10792,16 @@
         <v>44854</v>
       </c>
       <c r="B519" t="n">
-        <v>19.48124313354492</v>
+        <v>19.48124122619629</v>
       </c>
       <c r="C519" t="n">
-        <v>19.84025650600569</v>
+        <v>19.84025456350717</v>
       </c>
       <c r="D519" t="n">
-        <v>19.19780981653667</v>
+        <v>19.19780793693812</v>
       </c>
       <c r="E519" t="n">
-        <v>19.84025650600569</v>
+        <v>19.84025456350717</v>
       </c>
       <c r="F519" t="n">
         <v>1274100</v>
@@ -10832,16 +10832,16 @@
         <v>44858</v>
       </c>
       <c r="B521" t="n">
-        <v>19.55682373046875</v>
+        <v>19.55682182312012</v>
       </c>
       <c r="C521" t="n">
-        <v>19.8591511408467</v>
+        <v>19.85914920401251</v>
       </c>
       <c r="D521" t="n">
-        <v>19.33007637067178</v>
+        <v>19.33007448543749</v>
       </c>
       <c r="E521" t="n">
-        <v>19.74577746094821</v>
+        <v>19.7457755351712</v>
       </c>
       <c r="F521" t="n">
         <v>947100</v>
@@ -10872,16 +10872,16 @@
         <v>44860</v>
       </c>
       <c r="B523" t="n">
-        <v>18.38530158996582</v>
+        <v>18.38530349731445</v>
       </c>
       <c r="C523" t="n">
-        <v>19.3111815003919</v>
+        <v>19.31118350379421</v>
       </c>
       <c r="D523" t="n">
-        <v>18.06408008056859</v>
+        <v>18.06408195459271</v>
       </c>
       <c r="E523" t="n">
-        <v>18.98995818898124</v>
+        <v>18.98996015905884</v>
       </c>
       <c r="F523" t="n">
         <v>1458850</v>
@@ -10892,16 +10892,16 @@
         <v>44861</v>
       </c>
       <c r="B524" t="n">
-        <v>19.50013542175293</v>
+        <v>19.50013732910156</v>
       </c>
       <c r="C524" t="n">
-        <v>19.74577688603637</v>
+        <v>19.7457788174117</v>
       </c>
       <c r="D524" t="n">
-        <v>18.40419769003509</v>
+        <v>18.40419949018779</v>
       </c>
       <c r="E524" t="n">
-        <v>18.49867545353079</v>
+        <v>18.49867726292455</v>
       </c>
       <c r="F524" t="n">
         <v>1150900</v>
@@ -10912,16 +10912,16 @@
         <v>44862</v>
       </c>
       <c r="B525" t="n">
-        <v>19.40566062927246</v>
+        <v>19.40565872192383</v>
       </c>
       <c r="C525" t="n">
-        <v>19.7457780755269</v>
+        <v>19.74577613474872</v>
       </c>
       <c r="D525" t="n">
-        <v>18.87658584263032</v>
+        <v>18.87658398728353</v>
       </c>
       <c r="E525" t="n">
-        <v>19.29228694584527</v>
+        <v>19.29228504963994</v>
       </c>
       <c r="F525" t="n">
         <v>1190600</v>
@@ -10932,16 +10932,16 @@
         <v>44865</v>
       </c>
       <c r="B526" t="n">
-        <v>20.46380805969238</v>
+        <v>20.46380615234375</v>
       </c>
       <c r="C526" t="n">
-        <v>20.50159989087106</v>
+        <v>20.50159798</v>
       </c>
       <c r="D526" t="n">
-        <v>18.76321530095325</v>
+        <v>18.76321355210998</v>
       </c>
       <c r="E526" t="n">
-        <v>18.78210941452889</v>
+        <v>18.78210766392458</v>
       </c>
       <c r="F526" t="n">
         <v>2299050</v>
@@ -10952,16 +10952,16 @@
         <v>44866</v>
       </c>
       <c r="B527" t="n">
-        <v>20.48270225524902</v>
+        <v>20.48270034790039</v>
       </c>
       <c r="C527" t="n">
-        <v>20.84171561122987</v>
+        <v>20.84171367044992</v>
       </c>
       <c r="D527" t="n">
-        <v>19.95362927727227</v>
+        <v>19.95362741919089</v>
       </c>
       <c r="E527" t="n">
-        <v>20.274850805248</v>
+        <v>20.27484891725449</v>
       </c>
       <c r="F527" t="n">
         <v>1462800</v>
@@ -10992,16 +10992,16 @@
         <v>44869</v>
       </c>
       <c r="B529" t="n">
-        <v>21.38968276977539</v>
+        <v>21.38968467712402</v>
       </c>
       <c r="C529" t="n">
-        <v>21.74869789867495</v>
+        <v>21.74869983803748</v>
       </c>
       <c r="D529" t="n">
-        <v>21.011773530418</v>
+        <v>21.01177540406793</v>
       </c>
       <c r="E529" t="n">
-        <v>21.40857868224661</v>
+        <v>21.40858059128022</v>
       </c>
       <c r="F529" t="n">
         <v>1653450</v>
@@ -11012,16 +11012,16 @@
         <v>44872</v>
       </c>
       <c r="B530" t="n">
-        <v>20.44491004943848</v>
+        <v>20.44491195678711</v>
       </c>
       <c r="C530" t="n">
-        <v>21.52195370150519</v>
+        <v>21.52195570933349</v>
       </c>
       <c r="D530" t="n">
-        <v>20.23706040529189</v>
+        <v>20.23706229324979</v>
       </c>
       <c r="E530" t="n">
-        <v>21.29520814370522</v>
+        <v>21.29521013037995</v>
       </c>
       <c r="F530" t="n">
         <v>1164150</v>
@@ -11032,16 +11032,16 @@
         <v>44873</v>
       </c>
       <c r="B531" t="n">
-        <v>19.9536304473877</v>
+        <v>19.95362854003906</v>
       </c>
       <c r="C531" t="n">
-        <v>20.35043565464299</v>
+        <v>20.35043370936413</v>
       </c>
       <c r="D531" t="n">
-        <v>19.25449600440303</v>
+        <v>19.254494163884</v>
       </c>
       <c r="E531" t="n">
-        <v>20.35043565464299</v>
+        <v>20.35043370936413</v>
       </c>
       <c r="F531" t="n">
         <v>2602700</v>
@@ -11052,16 +11052,16 @@
         <v>44874</v>
       </c>
       <c r="B532" t="n">
-        <v>18.7821102142334</v>
+        <v>18.78210830688477</v>
       </c>
       <c r="C532" t="n">
-        <v>20.06700369679745</v>
+        <v>20.06700165896615</v>
       </c>
       <c r="D532" t="n">
-        <v>18.61205237272972</v>
+        <v>18.61205048265069</v>
       </c>
       <c r="E532" t="n">
-        <v>19.85915402250599</v>
+        <v>19.85915200578211</v>
       </c>
       <c r="F532" t="n">
         <v>1714900</v>
@@ -11072,16 +11072,16 @@
         <v>44875</v>
       </c>
       <c r="B533" t="n">
-        <v>16.94924926757812</v>
+        <v>16.94924736022949</v>
       </c>
       <c r="C533" t="n">
-        <v>18.51757425979405</v>
+        <v>18.51757217595721</v>
       </c>
       <c r="D533" t="n">
-        <v>16.2501165916999</v>
+        <v>16.25011476302671</v>
       </c>
       <c r="E533" t="n">
-        <v>18.51757425979405</v>
+        <v>18.51757217595721</v>
       </c>
       <c r="F533" t="n">
         <v>6247350</v>
@@ -11092,16 +11092,16 @@
         <v>44876</v>
       </c>
       <c r="B534" t="n">
-        <v>15.5131893157959</v>
+        <v>15.51319122314453</v>
       </c>
       <c r="C534" t="n">
-        <v>16.96814035410347</v>
+        <v>16.96814244033852</v>
       </c>
       <c r="D534" t="n">
-        <v>15.05969732248658</v>
+        <v>15.05969917407831</v>
       </c>
       <c r="E534" t="n">
-        <v>16.94924624343426</v>
+        <v>16.94924832734628</v>
       </c>
       <c r="F534" t="n">
         <v>6426800</v>
@@ -11132,16 +11132,16 @@
         <v>44881</v>
       </c>
       <c r="B536" t="n">
-        <v>14.47393798828125</v>
+        <v>14.47393894195557</v>
       </c>
       <c r="C536" t="n">
-        <v>15.64545758032868</v>
+        <v>15.64545861119334</v>
       </c>
       <c r="D536" t="n">
-        <v>14.41725205050845</v>
+        <v>14.41725300044779</v>
       </c>
       <c r="E536" t="n">
-        <v>15.49429387825891</v>
+        <v>15.49429489916353</v>
       </c>
       <c r="F536" t="n">
         <v>3432000</v>
@@ -11172,16 +11172,16 @@
         <v>44883</v>
       </c>
       <c r="B538" t="n">
-        <v>13.83149147033691</v>
+        <v>13.83149242401123</v>
       </c>
       <c r="C538" t="n">
-        <v>14.88963822584258</v>
+        <v>14.88963925247558</v>
       </c>
       <c r="D538" t="n">
-        <v>13.73701371139616</v>
+        <v>13.73701465855629</v>
       </c>
       <c r="E538" t="n">
-        <v>14.26608753965234</v>
+        <v>14.26608852329183</v>
       </c>
       <c r="F538" t="n">
         <v>3266800</v>
@@ -11192,16 +11192,16 @@
         <v>44886</v>
       </c>
       <c r="B539" t="n">
-        <v>14.51172924041748</v>
+        <v>14.5117301940918</v>
       </c>
       <c r="C539" t="n">
-        <v>14.60620700684089</v>
+        <v>14.60620796672404</v>
       </c>
       <c r="D539" t="n">
-        <v>13.79370163942528</v>
+        <v>13.79370254591263</v>
       </c>
       <c r="E539" t="n">
-        <v>14.13381997673737</v>
+        <v>14.13382090557644</v>
       </c>
       <c r="F539" t="n">
         <v>1946900</v>
@@ -11212,16 +11212,16 @@
         <v>44887</v>
       </c>
       <c r="B540" t="n">
-        <v>14.09602832794189</v>
+        <v>14.09602928161621</v>
       </c>
       <c r="C540" t="n">
-        <v>14.71957903156021</v>
+        <v>14.71958002742118</v>
       </c>
       <c r="D540" t="n">
-        <v>13.88817779306689</v>
+        <v>13.88817873267896</v>
       </c>
       <c r="E540" t="n">
-        <v>14.60620625826658</v>
+        <v>14.60620724645726</v>
       </c>
       <c r="F540" t="n">
         <v>2112800</v>
@@ -11272,16 +11272,16 @@
         <v>44890</v>
       </c>
       <c r="B543" t="n">
-        <v>14.11492538452148</v>
+        <v>14.11492443084717</v>
       </c>
       <c r="C543" t="n">
-        <v>14.90853581355609</v>
+        <v>14.90853480626151</v>
       </c>
       <c r="D543" t="n">
-        <v>13.94486665044753</v>
+        <v>13.94486570826322</v>
       </c>
       <c r="E543" t="n">
-        <v>14.90853581355609</v>
+        <v>14.90853480626151</v>
       </c>
       <c r="F543" t="n">
         <v>1492900</v>
@@ -11292,16 +11292,16 @@
         <v>44893</v>
       </c>
       <c r="B544" t="n">
-        <v>13.98265647888184</v>
+        <v>13.98265552520752</v>
       </c>
       <c r="C544" t="n">
-        <v>14.28498389431492</v>
+        <v>14.28498292002064</v>
       </c>
       <c r="D544" t="n">
-        <v>13.90707462502356</v>
+        <v>13.90707367650424</v>
       </c>
       <c r="E544" t="n">
-        <v>14.13382018659838</v>
+        <v>14.13381922261408</v>
       </c>
       <c r="F544" t="n">
         <v>1713550</v>
@@ -11332,16 +11332,16 @@
         <v>44895</v>
       </c>
       <c r="B546" t="n">
-        <v>14.41725254058838</v>
+        <v>14.41725158691406</v>
       </c>
       <c r="C546" t="n">
-        <v>14.60620717459865</v>
+        <v>14.60620620842533</v>
       </c>
       <c r="D546" t="n">
-        <v>13.83149272465316</v>
+        <v>13.83149180972576</v>
       </c>
       <c r="E546" t="n">
-        <v>14.41725254058838</v>
+        <v>14.41725158691406</v>
       </c>
       <c r="F546" t="n">
         <v>1926400</v>
@@ -11372,16 +11372,16 @@
         <v>44897</v>
       </c>
       <c r="B548" t="n">
-        <v>14.28498363494873</v>
+        <v>14.28498458862305</v>
       </c>
       <c r="C548" t="n">
-        <v>14.58731104489259</v>
+        <v>14.58731201875047</v>
       </c>
       <c r="D548" t="n">
-        <v>14.05823807749083</v>
+        <v>14.05823901602748</v>
       </c>
       <c r="E548" t="n">
-        <v>14.17161085621978</v>
+        <v>14.17161180232526</v>
       </c>
       <c r="F548" t="n">
         <v>1219600</v>
@@ -11392,16 +11392,16 @@
         <v>44900</v>
       </c>
       <c r="B549" t="n">
-        <v>13.41579055786133</v>
+        <v>13.41579151153564</v>
       </c>
       <c r="C549" t="n">
-        <v>14.22829677075448</v>
+        <v>14.22829778218658</v>
       </c>
       <c r="D549" t="n">
-        <v>13.30241778650555</v>
+        <v>13.30241873212065</v>
       </c>
       <c r="E549" t="n">
-        <v>14.22829677075448</v>
+        <v>14.22829778218658</v>
       </c>
       <c r="F549" t="n">
         <v>1514950</v>
@@ -11412,16 +11412,16 @@
         <v>44901</v>
       </c>
       <c r="B550" t="n">
-        <v>13.15125370025635</v>
+        <v>13.15125465393066</v>
       </c>
       <c r="C550" t="n">
-        <v>13.66143160668842</v>
+        <v>13.66143259735872</v>
       </c>
       <c r="D550" t="n">
-        <v>12.67886671648566</v>
+        <v>12.67886763590444</v>
       </c>
       <c r="E550" t="n">
-        <v>13.54805883870426</v>
+        <v>13.54805982115323</v>
       </c>
       <c r="F550" t="n">
         <v>4313950</v>
@@ -11452,16 +11452,16 @@
         <v>44903</v>
       </c>
       <c r="B552" t="n">
-        <v>12.376540184021</v>
+        <v>12.37653923034668</v>
       </c>
       <c r="C552" t="n">
-        <v>13.09456776383221</v>
+        <v>13.09456675483028</v>
       </c>
       <c r="D552" t="n">
-        <v>12.16868964462491</v>
+        <v>12.16868870696652</v>
       </c>
       <c r="E552" t="n">
-        <v>13.03788182645574</v>
+        <v>13.03788082182175</v>
       </c>
       <c r="F552" t="n">
         <v>3031100</v>
@@ -11492,16 +11492,16 @@
         <v>44907</v>
       </c>
       <c r="B554" t="n">
-        <v>11.90415382385254</v>
+        <v>11.90415287017822</v>
       </c>
       <c r="C554" t="n">
-        <v>12.35764495188166</v>
+        <v>12.35764396187693</v>
       </c>
       <c r="D554" t="n">
-        <v>11.58293049099519</v>
+        <v>11.58292956305495</v>
       </c>
       <c r="E554" t="n">
-        <v>12.18758532836735</v>
+        <v>12.18758435198656</v>
       </c>
       <c r="F554" t="n">
         <v>2931550</v>
@@ -11512,16 +11512,16 @@
         <v>44908</v>
       </c>
       <c r="B555" t="n">
-        <v>11.58293056488037</v>
+        <v>11.58292961120605</v>
       </c>
       <c r="C555" t="n">
-        <v>12.22537633368632</v>
+        <v>12.22537532711658</v>
       </c>
       <c r="D555" t="n">
-        <v>11.48845279543493</v>
+        <v>11.48845184953939</v>
       </c>
       <c r="E555" t="n">
-        <v>11.97973575494038</v>
+        <v>11.97973476859532</v>
       </c>
       <c r="F555" t="n">
         <v>2082000</v>
@@ -11572,16 +11572,16 @@
         <v>44911</v>
       </c>
       <c r="B558" t="n">
-        <v>11.31839275360107</v>
+        <v>11.31839370727539</v>
       </c>
       <c r="C558" t="n">
-        <v>11.71519792903348</v>
+        <v>11.71519891614213</v>
       </c>
       <c r="D558" t="n">
-        <v>11.09164719649877</v>
+        <v>11.09164813106777</v>
       </c>
       <c r="E558" t="n">
-        <v>11.63961607666605</v>
+        <v>11.63961705740626</v>
       </c>
       <c r="F558" t="n">
         <v>4251600</v>
@@ -11612,16 +11612,16 @@
         <v>44915</v>
       </c>
       <c r="B560" t="n">
-        <v>12.56549549102783</v>
+        <v>12.56549453735352</v>
       </c>
       <c r="C560" t="n">
-        <v>12.86782290943231</v>
+        <v>12.86782193281247</v>
       </c>
       <c r="D560" t="n">
-        <v>11.6774073479545</v>
+        <v>11.67740646168276</v>
       </c>
       <c r="E560" t="n">
-        <v>11.79078012985618</v>
+        <v>11.79077923497987</v>
       </c>
       <c r="F560" t="n">
         <v>2603950</v>
@@ -11672,16 +11672,16 @@
         <v>44918</v>
       </c>
       <c r="B563" t="n">
-        <v>13.39689636230469</v>
+        <v>13.39689540863037</v>
       </c>
       <c r="C563" t="n">
-        <v>13.66143284491103</v>
+        <v>13.66143187240536</v>
       </c>
       <c r="D563" t="n">
-        <v>12.88671840963194</v>
+        <v>12.88671749227526</v>
       </c>
       <c r="E563" t="n">
-        <v>12.90561342217188</v>
+        <v>12.90561250347013</v>
       </c>
       <c r="F563" t="n">
         <v>1442850</v>
@@ -11692,16 +11692,16 @@
         <v>44921</v>
       </c>
       <c r="B564" t="n">
-        <v>13.17015075683594</v>
+        <v>13.17014980316162</v>
       </c>
       <c r="C564" t="n">
-        <v>13.49137409985749</v>
+        <v>13.49137312292281</v>
       </c>
       <c r="D564" t="n">
-        <v>12.83003240005202</v>
+        <v>12.83003147100628</v>
       </c>
       <c r="E564" t="n">
-        <v>13.4157922427944</v>
+        <v>13.41579127133274</v>
       </c>
       <c r="F564" t="n">
         <v>1094200</v>
@@ -11732,16 +11732,16 @@
         <v>44923</v>
       </c>
       <c r="B566" t="n">
-        <v>13.10085010528564</v>
+        <v>13.10084915161133</v>
       </c>
       <c r="C566" t="n">
-        <v>13.12014487705818</v>
+        <v>13.1201439219793</v>
       </c>
       <c r="D566" t="n">
-        <v>12.29048809134627</v>
+        <v>12.29048719666213</v>
       </c>
       <c r="E566" t="n">
-        <v>12.46413735719766</v>
+        <v>12.46413644987275</v>
       </c>
       <c r="F566" t="n">
         <v>2129050</v>
@@ -11772,16 +11772,16 @@
         <v>44928</v>
       </c>
       <c r="B568" t="n">
-        <v>12.21331119537354</v>
+        <v>12.21331024169922</v>
       </c>
       <c r="C568" t="n">
-        <v>12.83073010946179</v>
+        <v>12.83072910757643</v>
       </c>
       <c r="D568" t="n">
-        <v>11.98177944759996</v>
+        <v>11.98177851200476</v>
       </c>
       <c r="E568" t="n">
-        <v>12.83073010946179</v>
+        <v>12.83072910757643</v>
       </c>
       <c r="F568" t="n">
         <v>1499800</v>
@@ -11792,16 +11792,16 @@
         <v>44929</v>
       </c>
       <c r="B569" t="n">
-        <v>11.65377616882324</v>
+        <v>11.65377521514893</v>
       </c>
       <c r="C569" t="n">
-        <v>12.21331170950984</v>
+        <v>12.21331071004653</v>
       </c>
       <c r="D569" t="n">
-        <v>11.5958936894559</v>
+        <v>11.59589274051833</v>
       </c>
       <c r="E569" t="n">
-        <v>12.21331170950984</v>
+        <v>12.21331071004653</v>
       </c>
       <c r="F569" t="n">
         <v>2015100</v>
@@ -11852,16 +11852,16 @@
         <v>44932</v>
       </c>
       <c r="B572" t="n">
-        <v>13.08155632019043</v>
+        <v>13.08155727386475</v>
       </c>
       <c r="C572" t="n">
-        <v>13.13943879575224</v>
+        <v>13.13943975364632</v>
       </c>
       <c r="D572" t="n">
-        <v>12.44484264883297</v>
+        <v>12.44484355608945</v>
       </c>
       <c r="E572" t="n">
-        <v>12.73425778671811</v>
+        <v>12.7342587150736</v>
       </c>
       <c r="F572" t="n">
         <v>1382000</v>
@@ -11892,16 +11892,16 @@
         <v>44936</v>
       </c>
       <c r="B574" t="n">
-        <v>13.8533296585083</v>
+        <v>13.85332870483398</v>
       </c>
       <c r="C574" t="n">
-        <v>14.00768508302567</v>
+        <v>14.0076841187254</v>
       </c>
       <c r="D574" t="n">
-        <v>13.04296850992557</v>
+        <v>13.04296761203716</v>
       </c>
       <c r="E574" t="n">
-        <v>13.17802824134331</v>
+        <v>13.17802733415729</v>
       </c>
       <c r="F574" t="n">
         <v>2939000</v>
@@ -11952,16 +11952,16 @@
         <v>44939</v>
       </c>
       <c r="B577" t="n">
-        <v>13.33238220214844</v>
+        <v>13.33238124847412</v>
       </c>
       <c r="C577" t="n">
-        <v>13.4867367003459</v>
+        <v>13.4867357356305</v>
       </c>
       <c r="D577" t="n">
-        <v>13.13943907940161</v>
+        <v>13.13943813952864</v>
       </c>
       <c r="E577" t="n">
-        <v>13.42885422353454</v>
+        <v>13.42885326295952</v>
       </c>
       <c r="F577" t="n">
         <v>1373850</v>
@@ -12052,16 +12052,16 @@
         <v>44946</v>
       </c>
       <c r="B582" t="n">
-        <v>14.06556701660156</v>
+        <v>14.06556606292725</v>
       </c>
       <c r="C582" t="n">
-        <v>14.12345041355349</v>
+        <v>14.12344945595456</v>
       </c>
       <c r="D582" t="n">
-        <v>13.50603149950962</v>
+        <v>13.50603058377296</v>
       </c>
       <c r="E582" t="n">
-        <v>13.73756324726655</v>
+        <v>13.73756231583157</v>
       </c>
       <c r="F582" t="n">
         <v>2454200</v>
@@ -12152,16 +12152,16 @@
         <v>44953</v>
       </c>
       <c r="B587" t="n">
-        <v>14.35498142242432</v>
+        <v>14.35498237609863</v>
       </c>
       <c r="C587" t="n">
-        <v>14.64439655223626</v>
+        <v>14.6443975251379</v>
       </c>
       <c r="D587" t="n">
-        <v>14.29709802845179</v>
+        <v>14.29709897828062</v>
       </c>
       <c r="E587" t="n">
-        <v>14.56721930695646</v>
+        <v>14.56722027473081</v>
       </c>
       <c r="F587" t="n">
         <v>1566450</v>
@@ -12172,16 +12172,16 @@
         <v>44956</v>
       </c>
       <c r="B588" t="n">
-        <v>14.39356994628906</v>
+        <v>14.39357089996338</v>
       </c>
       <c r="C588" t="n">
-        <v>14.6636903029147</v>
+        <v>14.66369127448637</v>
       </c>
       <c r="D588" t="n">
-        <v>14.31639270153888</v>
+        <v>14.31639365009966</v>
       </c>
       <c r="E588" t="n">
-        <v>14.37427517508885</v>
+        <v>14.37427612748476</v>
       </c>
       <c r="F588" t="n">
         <v>1160300</v>
@@ -12192,16 +12192,16 @@
         <v>44957</v>
       </c>
       <c r="B589" t="n">
-        <v>14.99169540405273</v>
+        <v>14.99169445037842</v>
       </c>
       <c r="C589" t="n">
-        <v>15.04957880284405</v>
+        <v>15.04957784548756</v>
       </c>
       <c r="D589" t="n">
-        <v>14.39357124332777</v>
+        <v>14.39357032770223</v>
       </c>
       <c r="E589" t="n">
-        <v>14.41286509624127</v>
+        <v>14.41286417938838</v>
       </c>
       <c r="F589" t="n">
         <v>1759050</v>
@@ -12212,16 +12212,16 @@
         <v>44958</v>
       </c>
       <c r="B590" t="n">
-        <v>14.99169540405273</v>
+        <v>14.99169445037842</v>
       </c>
       <c r="C590" t="n">
-        <v>15.16534468040126</v>
+        <v>15.1653437156805</v>
       </c>
       <c r="D590" t="n">
-        <v>14.7408688759994</v>
+        <v>14.74086793828104</v>
       </c>
       <c r="E590" t="n">
-        <v>14.97240155113924</v>
+        <v>14.97240059869227</v>
       </c>
       <c r="F590" t="n">
         <v>1831550</v>
@@ -12372,16 +12372,16 @@
         <v>44970</v>
       </c>
       <c r="B598" t="n">
-        <v>14.12344932556152</v>
+        <v>14.12345027923584</v>
       </c>
       <c r="C598" t="n">
-        <v>14.62510140705705</v>
+        <v>14.62510239460502</v>
       </c>
       <c r="D598" t="n">
-        <v>13.9690939189222</v>
+        <v>13.9690948621738</v>
       </c>
       <c r="E598" t="n">
-        <v>14.04627208225452</v>
+        <v>14.04627303071751</v>
       </c>
       <c r="F598" t="n">
         <v>1583800</v>
@@ -12392,16 +12392,16 @@
         <v>44971</v>
       </c>
       <c r="B599" t="n">
-        <v>13.96909427642822</v>
+        <v>13.96909523010254</v>
       </c>
       <c r="C599" t="n">
-        <v>14.50933591342878</v>
+        <v>14.50933690398556</v>
       </c>
       <c r="D599" t="n">
-        <v>13.69897391794061</v>
+        <v>13.69897485317373</v>
       </c>
       <c r="E599" t="n">
-        <v>14.35498142286443</v>
+        <v>14.35498240288338</v>
       </c>
       <c r="F599" t="n">
         <v>2796000</v>
@@ -12412,16 +12412,16 @@
         <v>44972</v>
       </c>
       <c r="B600" t="n">
-        <v>14.83734130859375</v>
+        <v>14.83734035491943</v>
       </c>
       <c r="C600" t="n">
-        <v>15.04957921663013</v>
+        <v>15.04957824931416</v>
       </c>
       <c r="D600" t="n">
-        <v>13.7375640615239</v>
+        <v>13.73756317853808</v>
       </c>
       <c r="E600" t="n">
-        <v>14.00768536994309</v>
+        <v>14.00768446959514</v>
       </c>
       <c r="F600" t="n">
         <v>2808050</v>
@@ -12492,16 +12492,16 @@
         <v>44980</v>
       </c>
       <c r="B604" t="n">
-        <v>14.41286563873291</v>
+        <v>14.41286468505859</v>
       </c>
       <c r="C604" t="n">
-        <v>14.91451871372149</v>
+        <v>14.91451772685366</v>
       </c>
       <c r="D604" t="n">
-        <v>14.27780590317863</v>
+        <v>14.27780495844099</v>
       </c>
       <c r="E604" t="n">
-        <v>14.6636921762272</v>
+        <v>14.66369120595613</v>
       </c>
       <c r="F604" t="n">
         <v>1540800</v>
@@ -12552,16 +12552,16 @@
         <v>44985</v>
       </c>
       <c r="B607" t="n">
-        <v>13.8533296585083</v>
+        <v>13.85332870483398</v>
       </c>
       <c r="C607" t="n">
-        <v>14.00768508302567</v>
+        <v>14.0076841187254</v>
       </c>
       <c r="D607" t="n">
-        <v>13.48673725032721</v>
+        <v>13.48673632188941</v>
       </c>
       <c r="E607" t="n">
-        <v>13.71826992709055</v>
+        <v>13.71826898271386</v>
       </c>
       <c r="F607" t="n">
         <v>1742300</v>
@@ -12572,16 +12572,16 @@
         <v>44986</v>
       </c>
       <c r="B608" t="n">
-        <v>13.48673725128174</v>
+        <v>13.48673629760742</v>
       </c>
       <c r="C608" t="n">
-        <v>13.85332965948877</v>
+        <v>13.85332867989197</v>
       </c>
       <c r="D608" t="n">
-        <v>13.21661686840171</v>
+        <v>13.21661593382815</v>
       </c>
       <c r="E608" t="n">
-        <v>13.85332965948877</v>
+        <v>13.85332867989197</v>
       </c>
       <c r="F608" t="n">
         <v>2358750</v>
@@ -12632,16 +12632,16 @@
         <v>44991</v>
       </c>
       <c r="B611" t="n">
-        <v>14.12344932556152</v>
+        <v>14.12345027923584</v>
       </c>
       <c r="C611" t="n">
-        <v>14.25850904133613</v>
+        <v>14.25851000413024</v>
       </c>
       <c r="D611" t="n">
-        <v>13.35167597246616</v>
+        <v>13.35167687402712</v>
       </c>
       <c r="E611" t="n">
-        <v>13.35167597246616</v>
+        <v>13.35167687402712</v>
       </c>
       <c r="F611" t="n">
         <v>2062900</v>
@@ -12672,16 +12672,16 @@
         <v>44993</v>
       </c>
       <c r="B613" t="n">
-        <v>15.85994148254395</v>
+        <v>15.85993957519531</v>
       </c>
       <c r="C613" t="n">
-        <v>15.85994148254395</v>
+        <v>15.85993957519531</v>
       </c>
       <c r="D613" t="n">
-        <v>14.16204003895802</v>
+        <v>14.16203833580244</v>
       </c>
       <c r="E613" t="n">
-        <v>14.68298696823717</v>
+        <v>14.68298520243147</v>
       </c>
       <c r="F613" t="n">
         <v>5225650</v>
@@ -12752,16 +12752,16 @@
         <v>44999</v>
       </c>
       <c r="B617" t="n">
-        <v>14.97240161895752</v>
+        <v>14.9724006652832</v>
       </c>
       <c r="C617" t="n">
-        <v>15.89852864361015</v>
+        <v>15.89852763094573</v>
       </c>
       <c r="D617" t="n">
-        <v>14.77945756879614</v>
+        <v>14.77945662741149</v>
       </c>
       <c r="E617" t="n">
-        <v>15.53193715636452</v>
+        <v>15.53193616705032</v>
       </c>
       <c r="F617" t="n">
         <v>2100150</v>
@@ -12772,16 +12772,16 @@
         <v>45000</v>
       </c>
       <c r="B618" t="n">
-        <v>15.31969833374023</v>
+        <v>15.31969928741455</v>
       </c>
       <c r="C618" t="n">
-        <v>15.47405374861028</v>
+        <v>15.47405471189345</v>
       </c>
       <c r="D618" t="n">
-        <v>14.45145292020087</v>
+        <v>14.4514538198256</v>
       </c>
       <c r="E618" t="n">
-        <v>14.64439695878208</v>
+        <v>14.64439787041787</v>
       </c>
       <c r="F618" t="n">
         <v>2068400</v>
@@ -12832,16 +12832,16 @@
         <v>45005</v>
       </c>
       <c r="B621" t="n">
-        <v>13.96909427642822</v>
+        <v>13.96909523010254</v>
       </c>
       <c r="C621" t="n">
-        <v>15.33899176022482</v>
+        <v>15.33899280742245</v>
       </c>
       <c r="D621" t="n">
-        <v>13.94980042512035</v>
+        <v>13.94980137747747</v>
       </c>
       <c r="E621" t="n">
-        <v>15.16534341835259</v>
+        <v>15.1653444536952</v>
       </c>
       <c r="F621" t="n">
         <v>2781400</v>
@@ -12972,16 +12972,16 @@
         <v>45014</v>
       </c>
       <c r="B628" t="n">
-        <v>14.14274501800537</v>
+        <v>14.14274406433105</v>
       </c>
       <c r="C628" t="n">
-        <v>14.41286540475423</v>
+        <v>14.41286443286514</v>
       </c>
       <c r="D628" t="n">
-        <v>13.75685875122129</v>
+        <v>13.75685782356807</v>
       </c>
       <c r="E628" t="n">
-        <v>14.41286540475423</v>
+        <v>14.41286443286514</v>
       </c>
       <c r="F628" t="n">
         <v>1398800</v>
@@ -13032,16 +13032,16 @@
         <v>45019</v>
       </c>
       <c r="B631" t="n">
-        <v>13.83403491973877</v>
+        <v>13.83403587341309</v>
       </c>
       <c r="C631" t="n">
-        <v>14.49004244185425</v>
+        <v>14.49004344075163</v>
       </c>
       <c r="D631" t="n">
-        <v>13.62179702963811</v>
+        <v>13.62179796868142</v>
       </c>
       <c r="E631" t="n">
-        <v>14.39357042271067</v>
+        <v>14.39357141495758</v>
       </c>
       <c r="F631" t="n">
         <v>1766300</v>
@@ -13072,16 +13072,16 @@
         <v>45021</v>
       </c>
       <c r="B633" t="n">
-        <v>13.8533296585083</v>
+        <v>13.85332870483398</v>
       </c>
       <c r="C633" t="n">
-        <v>14.29709931893536</v>
+        <v>14.29709833471159</v>
       </c>
       <c r="D633" t="n">
-        <v>13.66038652789336</v>
+        <v>13.66038558750141</v>
       </c>
       <c r="E633" t="n">
-        <v>14.1813334405664</v>
+        <v>14.18133246431204</v>
       </c>
       <c r="F633" t="n">
         <v>2634950</v>
@@ -13092,16 +13092,16 @@
         <v>45022</v>
       </c>
       <c r="B634" t="n">
-        <v>14.14274501800537</v>
+        <v>14.14274406433105</v>
       </c>
       <c r="C634" t="n">
-        <v>14.297099524719</v>
+        <v>14.29709856063625</v>
       </c>
       <c r="D634" t="n">
-        <v>13.77615260454778</v>
+        <v>13.77615167559354</v>
       </c>
       <c r="E634" t="n">
-        <v>13.85332985790459</v>
+        <v>13.85332892374614</v>
       </c>
       <c r="F634" t="n">
         <v>1739850</v>
@@ -13112,16 +13112,16 @@
         <v>45026</v>
       </c>
       <c r="B635" t="n">
-        <v>13.96909427642822</v>
+        <v>13.96909523010254</v>
       </c>
       <c r="C635" t="n">
-        <v>14.20062693230008</v>
+        <v>14.2006279017812</v>
       </c>
       <c r="D635" t="n">
-        <v>13.89191703114605</v>
+        <v>13.89191797955145</v>
       </c>
       <c r="E635" t="n">
-        <v>13.94980042512035</v>
+        <v>13.94980137747747</v>
       </c>
       <c r="F635" t="n">
         <v>1451200</v>
@@ -13152,16 +13152,16 @@
         <v>45028</v>
       </c>
       <c r="B637" t="n">
-        <v>15.454758644104</v>
+        <v>15.45475959777832</v>
       </c>
       <c r="C637" t="n">
-        <v>15.78276239860189</v>
+        <v>15.7827633725165</v>
       </c>
       <c r="D637" t="n">
-        <v>15.14604874103375</v>
+        <v>15.14604967565836</v>
       </c>
       <c r="E637" t="n">
-        <v>15.31969800400918</v>
+        <v>15.31969894934925</v>
       </c>
       <c r="F637" t="n">
         <v>3667400</v>
@@ -13192,16 +13192,16 @@
         <v>45030</v>
       </c>
       <c r="B639" t="n">
-        <v>15.60911273956299</v>
+        <v>15.6091136932373</v>
       </c>
       <c r="C639" t="n">
-        <v>15.91782171477476</v>
+        <v>15.91782268731036</v>
       </c>
       <c r="D639" t="n">
-        <v>15.12675450578194</v>
+        <v>15.12675542998548</v>
       </c>
       <c r="E639" t="n">
-        <v>15.68628998336593</v>
+        <v>15.68629094175557</v>
       </c>
       <c r="F639" t="n">
         <v>1580050</v>
@@ -13212,16 +13212,16 @@
         <v>45033</v>
       </c>
       <c r="B640" t="n">
-        <v>15.53193664550781</v>
+        <v>15.5319356918335</v>
       </c>
       <c r="C640" t="n">
-        <v>15.76346839405572</v>
+        <v>15.76346742616516</v>
       </c>
       <c r="D640" t="n">
-        <v>15.49334710072444</v>
+        <v>15.49334614941956</v>
       </c>
       <c r="E640" t="n">
-        <v>15.60911389502378</v>
+        <v>15.60911293661072</v>
       </c>
       <c r="F640" t="n">
         <v>1212550</v>
@@ -13232,16 +13232,16 @@
         <v>45034</v>
       </c>
       <c r="B641" t="n">
-        <v>15.06887149810791</v>
+        <v>15.06887245178223</v>
       </c>
       <c r="C641" t="n">
-        <v>15.74417285865839</v>
+        <v>15.74417385507098</v>
       </c>
       <c r="D641" t="n">
-        <v>14.87592838366854</v>
+        <v>14.87592932513193</v>
       </c>
       <c r="E641" t="n">
-        <v>15.62840791002011</v>
+        <v>15.6284088991062</v>
       </c>
       <c r="F641" t="n">
         <v>1695600</v>
@@ -13272,16 +13272,16 @@
         <v>45036</v>
       </c>
       <c r="B643" t="n">
-        <v>14.93381118774414</v>
+        <v>14.93381214141846</v>
       </c>
       <c r="C643" t="n">
-        <v>14.93381118774414</v>
+        <v>14.93381214141846</v>
       </c>
       <c r="D643" t="n">
-        <v>14.29709843602215</v>
+        <v>14.29709934903595</v>
       </c>
       <c r="E643" t="n">
-        <v>14.43215907912469</v>
+        <v>14.43216000076346</v>
       </c>
       <c r="F643" t="n">
         <v>1458900</v>
@@ -29585,6 +29585,26 @@
       </c>
       <c r="F1458" t="n">
         <v>2866400</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>1889700</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -472,16 +472,16 @@
         <v>44095</v>
       </c>
       <c r="B3" t="n">
-        <v>12.5955982208252</v>
+        <v>12.59559726715088</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80833155523612</v>
+        <v>12.80833058545472</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45377599788458</v>
+        <v>12.45377505494831</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46707130295581</v>
+        <v>12.46707035901289</v>
       </c>
       <c r="F3" t="n">
         <v>1323800</v>
@@ -492,16 +492,16 @@
         <v>44096</v>
       </c>
       <c r="B4" t="n">
-        <v>12.5867338180542</v>
+        <v>12.58673191070557</v>
       </c>
       <c r="C4" t="n">
-        <v>12.77287569252187</v>
+        <v>12.77287375696596</v>
       </c>
       <c r="D4" t="n">
-        <v>12.43161544844329</v>
+        <v>12.43161356460074</v>
       </c>
       <c r="E4" t="n">
-        <v>12.44491159852209</v>
+        <v>12.44490971266469</v>
       </c>
       <c r="F4" t="n">
         <v>1698000</v>
@@ -512,16 +512,16 @@
         <v>44097</v>
       </c>
       <c r="B5" t="n">
-        <v>12.65321254730225</v>
+        <v>12.65321159362793</v>
       </c>
       <c r="C5" t="n">
-        <v>12.99447278246738</v>
+        <v>12.99447180307224</v>
       </c>
       <c r="D5" t="n">
-        <v>12.24990530404421</v>
+        <v>12.24990438076721</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41388776942456</v>
+        <v>12.41388683378818</v>
       </c>
       <c r="F5" t="n">
         <v>1967400</v>
@@ -532,16 +532,16 @@
         <v>44098</v>
       </c>
       <c r="B6" t="n">
-        <v>12.45377349853516</v>
+        <v>12.45377445220947</v>
       </c>
       <c r="C6" t="n">
-        <v>12.84378453335049</v>
+        <v>12.84378551689074</v>
       </c>
       <c r="D6" t="n">
-        <v>12.40945385142895</v>
+        <v>12.40945480170939</v>
       </c>
       <c r="E6" t="n">
-        <v>12.65321064252266</v>
+        <v>12.6532116114693</v>
       </c>
       <c r="F6" t="n">
         <v>571400</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513519287109</v>
+        <v>12.36513614654541</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366209522167</v>
+        <v>12.49366305880876</v>
       </c>
       <c r="D7" t="n">
-        <v>12.32081554222169</v>
+        <v>12.3208164924778</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377449416991</v>
+        <v>12.45377545468063</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -572,16 +572,16 @@
         <v>44102</v>
       </c>
       <c r="B8" t="n">
-        <v>11.58068084716797</v>
+        <v>11.58067989349365</v>
       </c>
       <c r="C8" t="n">
-        <v>12.51139018424467</v>
+        <v>12.51138915392602</v>
       </c>
       <c r="D8" t="n">
-        <v>11.58068084716797</v>
+        <v>11.58067989349365</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43161497744851</v>
+        <v>12.43161395369939</v>
       </c>
       <c r="F8" t="n">
         <v>1524000</v>
@@ -592,16 +592,16 @@
         <v>44103</v>
       </c>
       <c r="B9" t="n">
-        <v>11.29703617095947</v>
+        <v>11.29703521728516</v>
       </c>
       <c r="C9" t="n">
-        <v>11.83330235747354</v>
+        <v>11.83330135852865</v>
       </c>
       <c r="D9" t="n">
-        <v>11.07987080462801</v>
+        <v>11.07986986928638</v>
       </c>
       <c r="E9" t="n">
-        <v>11.83330235747354</v>
+        <v>11.83330135852865</v>
       </c>
       <c r="F9" t="n">
         <v>897600</v>
@@ -632,16 +632,16 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>11.68261528015137</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="C11" t="n">
-        <v>11.68261528015137</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="D11" t="n">
-        <v>10.92918377675503</v>
+        <v>10.92918466892529</v>
       </c>
       <c r="E11" t="n">
-        <v>11.22612432864335</v>
+        <v>11.22612524505344</v>
       </c>
       <c r="F11" t="n">
         <v>1726600</v>
@@ -652,16 +652,16 @@
         <v>44106</v>
       </c>
       <c r="B12" t="n">
-        <v>11.29703617095947</v>
+        <v>11.29703521728516</v>
       </c>
       <c r="C12" t="n">
-        <v>11.55408913981376</v>
+        <v>11.55408816443952</v>
       </c>
       <c r="D12" t="n">
-        <v>11.19953361219649</v>
+        <v>11.19953266675315</v>
       </c>
       <c r="E12" t="n">
-        <v>11.51420153729093</v>
+        <v>11.51420056528393</v>
       </c>
       <c r="F12" t="n">
         <v>878600</v>
@@ -692,16 +692,16 @@
         <v>44110</v>
       </c>
       <c r="B14" t="n">
-        <v>11.43885898590088</v>
+        <v>11.43885803222656</v>
       </c>
       <c r="C14" t="n">
-        <v>12.05490040998342</v>
+        <v>12.05489940494884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.38124402661904</v>
+        <v>11.38124307774816</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5895453044252</v>
+        <v>11.58954433818795</v>
       </c>
       <c r="F14" t="n">
         <v>472800</v>
@@ -712,16 +712,16 @@
         <v>44111</v>
       </c>
       <c r="B15" t="n">
-        <v>11.68261528015137</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82443748189021</v>
+        <v>11.82443844714174</v>
       </c>
       <c r="D15" t="n">
-        <v>11.35465122729855</v>
+        <v>11.35465215420053</v>
       </c>
       <c r="E15" t="n">
-        <v>11.6294315318358</v>
+        <v>11.62943248116863</v>
       </c>
       <c r="F15" t="n">
         <v>437200</v>
@@ -752,16 +752,16 @@
         <v>44113</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10365009307861</v>
+        <v>12.10365104675293</v>
       </c>
       <c r="C17" t="n">
-        <v>12.29422399771216</v>
+        <v>12.29422496640223</v>
       </c>
       <c r="D17" t="n">
-        <v>11.531929224505</v>
+        <v>11.53193013313212</v>
       </c>
       <c r="E17" t="n">
-        <v>11.53636127406939</v>
+        <v>11.53636218304571</v>
       </c>
       <c r="F17" t="n">
         <v>672400</v>
@@ -772,16 +772,16 @@
         <v>44117</v>
       </c>
       <c r="B18" t="n">
-        <v>12.18785667419434</v>
+        <v>12.18785762786865</v>
       </c>
       <c r="C18" t="n">
-        <v>12.44934166683048</v>
+        <v>12.44934264096545</v>
       </c>
       <c r="D18" t="n">
-        <v>12.18785667419434</v>
+        <v>12.18785762786865</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36956646971071</v>
+        <v>12.36956743760344</v>
       </c>
       <c r="F18" t="n">
         <v>440800</v>
@@ -792,16 +792,16 @@
         <v>44118</v>
       </c>
       <c r="B19" t="n">
-        <v>12.1302433013916</v>
+        <v>12.13024234771729</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63105310519763</v>
+        <v>12.63105211214986</v>
       </c>
       <c r="D19" t="n">
-        <v>12.00614844025086</v>
+        <v>12.00614749633282</v>
       </c>
       <c r="E19" t="n">
-        <v>12.18785825940122</v>
+        <v>12.18785730119724</v>
       </c>
       <c r="F19" t="n">
         <v>441800</v>
@@ -832,16 +832,16 @@
         <v>44120</v>
       </c>
       <c r="B21" t="n">
-        <v>12.45377349853516</v>
+        <v>12.45377445220947</v>
       </c>
       <c r="C21" t="n">
-        <v>12.49366109639805</v>
+        <v>12.49366205312684</v>
       </c>
       <c r="D21" t="n">
-        <v>11.97955521875072</v>
+        <v>11.97955613611076</v>
       </c>
       <c r="E21" t="n">
-        <v>12.06376161839286</v>
+        <v>12.06376254220119</v>
       </c>
       <c r="F21" t="n">
         <v>585200</v>
@@ -912,16 +912,16 @@
         <v>44126</v>
       </c>
       <c r="B25" t="n">
-        <v>13.06981658935547</v>
+        <v>13.06981372833252</v>
       </c>
       <c r="C25" t="n">
-        <v>13.21163881222637</v>
+        <v>13.2116359201581</v>
       </c>
       <c r="D25" t="n">
-        <v>12.6975328316558</v>
+        <v>12.6975300521269</v>
       </c>
       <c r="E25" t="n">
-        <v>12.75071658789595</v>
+        <v>12.75071379672497</v>
       </c>
       <c r="F25" t="n">
         <v>963600</v>
@@ -952,16 +952,16 @@
         <v>44130</v>
       </c>
       <c r="B27" t="n">
-        <v>12.60002899169922</v>
+        <v>12.60002994537354</v>
       </c>
       <c r="C27" t="n">
-        <v>12.87480930941692</v>
+        <v>12.87481028388888</v>
       </c>
       <c r="D27" t="n">
-        <v>12.41831918133934</v>
+        <v>12.41832012126036</v>
       </c>
       <c r="E27" t="n">
-        <v>12.84821785664712</v>
+        <v>12.84821882910642</v>
       </c>
       <c r="F27" t="n">
         <v>307600</v>
@@ -972,16 +972,16 @@
         <v>44131</v>
       </c>
       <c r="B28" t="n">
-        <v>12.22774505615234</v>
+        <v>12.22774600982666</v>
       </c>
       <c r="C28" t="n">
-        <v>12.77730652723113</v>
+        <v>12.77730752376721</v>
       </c>
       <c r="D28" t="n">
-        <v>12.19228950464168</v>
+        <v>12.19229045555073</v>
       </c>
       <c r="E28" t="n">
-        <v>12.67537192230385</v>
+        <v>12.67537291088978</v>
       </c>
       <c r="F28" t="n">
         <v>652400</v>
@@ -992,16 +992,16 @@
         <v>44132</v>
       </c>
       <c r="B29" t="n">
-        <v>11.43885898590088</v>
+        <v>11.43885803222656</v>
       </c>
       <c r="C29" t="n">
-        <v>11.9263734961074</v>
+        <v>11.92637250178829</v>
       </c>
       <c r="D29" t="n">
-        <v>11.30146881736179</v>
+        <v>11.3014678751419</v>
       </c>
       <c r="E29" t="n">
-        <v>11.9263734961074</v>
+        <v>11.92637250178829</v>
       </c>
       <c r="F29" t="n">
         <v>860400</v>
@@ -1032,16 +1032,16 @@
         <v>44134</v>
       </c>
       <c r="B31" t="n">
-        <v>11.38567447662354</v>
+        <v>11.38567543029785</v>
       </c>
       <c r="C31" t="n">
-        <v>11.81114107243664</v>
+        <v>11.81114206174842</v>
       </c>
       <c r="D31" t="n">
-        <v>11.00895873325132</v>
+        <v>11.00895965537159</v>
       </c>
       <c r="E31" t="n">
-        <v>11.81114107243664</v>
+        <v>11.81114206174842</v>
       </c>
       <c r="F31" t="n">
         <v>907200</v>
@@ -1052,16 +1052,16 @@
         <v>44138</v>
       </c>
       <c r="B32" t="n">
-        <v>11.85546207427979</v>
+        <v>11.8554630279541</v>
       </c>
       <c r="C32" t="n">
-        <v>11.96626078525436</v>
+        <v>11.96626174784152</v>
       </c>
       <c r="D32" t="n">
-        <v>11.51863389147782</v>
+        <v>11.51863481805708</v>
       </c>
       <c r="E32" t="n">
-        <v>11.70034370984996</v>
+        <v>11.70034465104628</v>
       </c>
       <c r="F32" t="n">
         <v>1038200</v>
@@ -1112,16 +1112,16 @@
         <v>44141</v>
       </c>
       <c r="B35" t="n">
-        <v>13.55732917785645</v>
+        <v>13.55733013153076</v>
       </c>
       <c r="C35" t="n">
-        <v>13.69471933097108</v>
+        <v>13.69472029430994</v>
       </c>
       <c r="D35" t="n">
-        <v>12.65764341771108</v>
+        <v>12.65764430809807</v>
       </c>
       <c r="E35" t="n">
-        <v>12.74185066750967</v>
+        <v>12.74185156382011</v>
       </c>
       <c r="F35" t="n">
         <v>948200</v>
@@ -1132,16 +1132,16 @@
         <v>44144</v>
       </c>
       <c r="B36" t="n">
-        <v>13.2958459854126</v>
+        <v>13.29584407806396</v>
       </c>
       <c r="C36" t="n">
-        <v>13.96950238488535</v>
+        <v>13.96950038089769</v>
       </c>
       <c r="D36" t="n">
-        <v>13.12300025810691</v>
+        <v>13.12299837555377</v>
       </c>
       <c r="E36" t="n">
-        <v>13.73904085159302</v>
+        <v>13.7390388806661</v>
       </c>
       <c r="F36" t="n">
         <v>650800</v>
@@ -1152,16 +1152,16 @@
         <v>44145</v>
       </c>
       <c r="B37" t="n">
-        <v>13.15845394134521</v>
+        <v>13.15845489501953</v>
       </c>
       <c r="C37" t="n">
-        <v>13.57948849711368</v>
+        <v>13.57948948130297</v>
       </c>
       <c r="D37" t="n">
-        <v>13.07867874153117</v>
+        <v>13.07867968942368</v>
       </c>
       <c r="E37" t="n">
-        <v>13.07867874153117</v>
+        <v>13.07867968942368</v>
       </c>
       <c r="F37" t="n">
         <v>489600</v>
@@ -1172,16 +1172,16 @@
         <v>44146</v>
       </c>
       <c r="B38" t="n">
-        <v>13.2958459854126</v>
+        <v>13.29584407806396</v>
       </c>
       <c r="C38" t="n">
-        <v>13.41994085226088</v>
+        <v>13.41993892711028</v>
       </c>
       <c r="D38" t="n">
-        <v>12.89697077491564</v>
+        <v>12.89696892478745</v>
       </c>
       <c r="E38" t="n">
-        <v>13.25152632972913</v>
+        <v>13.25152442873835</v>
       </c>
       <c r="F38" t="n">
         <v>586400</v>
@@ -1212,16 +1212,16 @@
         <v>44148</v>
       </c>
       <c r="B40" t="n">
-        <v>13.10970211029053</v>
+        <v>13.10970306396484</v>
       </c>
       <c r="C40" t="n">
-        <v>13.53073750714</v>
+        <v>13.53073849144283</v>
       </c>
       <c r="D40" t="n">
-        <v>12.84378506203439</v>
+        <v>12.84378599636438</v>
       </c>
       <c r="E40" t="n">
-        <v>13.29584395953713</v>
+        <v>13.29584492675246</v>
       </c>
       <c r="F40" t="n">
         <v>720400</v>
@@ -1232,16 +1232,16 @@
         <v>44151</v>
       </c>
       <c r="B41" t="n">
-        <v>13.02106285095215</v>
+        <v>13.02106380462646</v>
       </c>
       <c r="C41" t="n">
-        <v>13.37118714867942</v>
+        <v>13.37118812799716</v>
       </c>
       <c r="D41" t="n">
-        <v>12.65321120079642</v>
+        <v>12.65321212752895</v>
       </c>
       <c r="E41" t="n">
-        <v>13.20720470074945</v>
+        <v>13.20720566805696</v>
       </c>
       <c r="F41" t="n">
         <v>631800</v>
@@ -1252,16 +1252,16 @@
         <v>44152</v>
       </c>
       <c r="B42" t="n">
-        <v>13.02106285095215</v>
+        <v>13.02106380462646</v>
       </c>
       <c r="C42" t="n">
-        <v>13.09197479664697</v>
+        <v>13.09197575551494</v>
       </c>
       <c r="D42" t="n">
-        <v>12.69753084985806</v>
+        <v>12.6975317798366</v>
       </c>
       <c r="E42" t="n">
-        <v>12.93242439815586</v>
+        <v>12.93242534533822</v>
       </c>
       <c r="F42" t="n">
         <v>784800</v>
@@ -1332,16 +1332,16 @@
         <v>44159</v>
       </c>
       <c r="B46" t="n">
-        <v>13.73904037475586</v>
+        <v>13.73903942108154</v>
       </c>
       <c r="C46" t="n">
-        <v>13.82767968304641</v>
+        <v>13.82767872321933</v>
       </c>
       <c r="D46" t="n">
-        <v>13.27368611954819</v>
+        <v>13.27368519817572</v>
       </c>
       <c r="E46" t="n">
-        <v>13.4731232952113</v>
+        <v>13.4731223599952</v>
       </c>
       <c r="F46" t="n">
         <v>798800</v>
@@ -1392,16 +1392,16 @@
         <v>44162</v>
       </c>
       <c r="B49" t="n">
-        <v>13.39334678649902</v>
+        <v>13.39334583282471</v>
       </c>
       <c r="C49" t="n">
-        <v>13.71687963861983</v>
+        <v>13.71687866190833</v>
       </c>
       <c r="D49" t="n">
-        <v>13.38891473698208</v>
+        <v>13.38891378362335</v>
       </c>
       <c r="E49" t="n">
-        <v>13.53073778554325</v>
+        <v>13.53073682208599</v>
       </c>
       <c r="F49" t="n">
         <v>510000</v>
@@ -1472,16 +1472,16 @@
         <v>44168</v>
       </c>
       <c r="B53" t="n">
-        <v>14.35951328277588</v>
+        <v>14.35951232910156</v>
       </c>
       <c r="C53" t="n">
-        <v>14.44371969251193</v>
+        <v>14.44371873324512</v>
       </c>
       <c r="D53" t="n">
-        <v>14.0581398153931</v>
+        <v>14.05813888173424</v>
       </c>
       <c r="E53" t="n">
-        <v>14.31519278502997</v>
+        <v>14.31519183429916</v>
       </c>
       <c r="F53" t="n">
         <v>1033200</v>
@@ -1512,16 +1512,16 @@
         <v>44172</v>
       </c>
       <c r="B55" t="n">
-        <v>14.25314426422119</v>
+        <v>14.25314617156982</v>
       </c>
       <c r="C55" t="n">
-        <v>14.36837416480735</v>
+        <v>14.36837608757599</v>
       </c>
       <c r="D55" t="n">
-        <v>13.82767767499762</v>
+        <v>13.82767952541053</v>
       </c>
       <c r="E55" t="n">
-        <v>14.06257037080052</v>
+        <v>14.06257225264665</v>
       </c>
       <c r="F55" t="n">
         <v>782600</v>
@@ -1532,16 +1532,16 @@
         <v>44173</v>
       </c>
       <c r="B56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="C56" t="n">
-        <v>14.53679034258752</v>
+        <v>14.53678935892345</v>
       </c>
       <c r="D56" t="n">
-        <v>13.89859038475245</v>
+        <v>13.89858944427358</v>
       </c>
       <c r="E56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="F56" t="n">
         <v>767200</v>
@@ -1552,16 +1552,16 @@
         <v>44174</v>
       </c>
       <c r="B57" t="n">
-        <v>13.889723777771</v>
+        <v>13.88972568511963</v>
       </c>
       <c r="C57" t="n">
-        <v>14.24871214024228</v>
+        <v>14.2487140968875</v>
       </c>
       <c r="D57" t="n">
-        <v>13.65926230082504</v>
+        <v>13.65926417652651</v>
       </c>
       <c r="E57" t="n">
-        <v>14.14677670349474</v>
+        <v>14.1467786461421</v>
       </c>
       <c r="F57" t="n">
         <v>570800</v>
@@ -1592,16 +1592,16 @@
         <v>44176</v>
       </c>
       <c r="B59" t="n">
-        <v>13.82324695587158</v>
+        <v>13.8232479095459</v>
       </c>
       <c r="C59" t="n">
-        <v>13.96063711619654</v>
+        <v>13.96063807934949</v>
       </c>
       <c r="D59" t="n">
-        <v>13.40221153010944</v>
+        <v>13.40221245473626</v>
       </c>
       <c r="E59" t="n">
-        <v>13.92074951395268</v>
+        <v>13.92075047435375</v>
       </c>
       <c r="F59" t="n">
         <v>523600</v>
@@ -1612,16 +1612,16 @@
         <v>44179</v>
       </c>
       <c r="B60" t="n">
-        <v>13.75676822662354</v>
+        <v>13.75676727294922</v>
       </c>
       <c r="C60" t="n">
-        <v>14.05814000746984</v>
+        <v>14.05813903290322</v>
       </c>
       <c r="D60" t="n">
-        <v>13.61494516788007</v>
+        <v>13.61494422403749</v>
       </c>
       <c r="E60" t="n">
-        <v>13.7434720771181</v>
+        <v>13.74347112436552</v>
       </c>
       <c r="F60" t="n">
         <v>525000</v>
@@ -1632,16 +1632,16 @@
         <v>44180</v>
       </c>
       <c r="B61" t="n">
-        <v>14.08473205566406</v>
+        <v>14.08473300933838</v>
       </c>
       <c r="C61" t="n">
-        <v>14.124619658143</v>
+        <v>14.1246206145181</v>
       </c>
       <c r="D61" t="n">
-        <v>13.57062611852114</v>
+        <v>13.57062703738544</v>
       </c>
       <c r="E61" t="n">
-        <v>13.75676798164717</v>
+        <v>13.7567689131151</v>
       </c>
       <c r="F61" t="n">
         <v>732800</v>
@@ -1672,16 +1672,16 @@
         <v>44182</v>
       </c>
       <c r="B63" t="n">
-        <v>13.73904037475586</v>
+        <v>13.73903942108154</v>
       </c>
       <c r="C63" t="n">
-        <v>14.13348352146192</v>
+        <v>14.13348254040794</v>
       </c>
       <c r="D63" t="n">
-        <v>13.67256131620149</v>
+        <v>13.67256036714172</v>
       </c>
       <c r="E63" t="n">
-        <v>13.91631814600987</v>
+        <v>13.91631718003009</v>
       </c>
       <c r="F63" t="n">
         <v>633000</v>
@@ -1692,16 +1692,16 @@
         <v>44183</v>
       </c>
       <c r="B64" t="n">
-        <v>13.40664386749268</v>
+        <v>13.40664196014404</v>
       </c>
       <c r="C64" t="n">
-        <v>13.83654255661189</v>
+        <v>13.83654058810204</v>
       </c>
       <c r="D64" t="n">
-        <v>13.28698105819358</v>
+        <v>13.28697916786925</v>
       </c>
       <c r="E64" t="n">
-        <v>13.61937718713968</v>
+        <v>13.61937524952571</v>
       </c>
       <c r="F64" t="n">
         <v>920000</v>
@@ -1712,16 +1712,16 @@
         <v>44186</v>
       </c>
       <c r="B65" t="n">
-        <v>13.14958953857422</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="C65" t="n">
-        <v>13.3401634347651</v>
+        <v>13.3401644022608</v>
       </c>
       <c r="D65" t="n">
-        <v>12.76844174619245</v>
+        <v>12.76844267222401</v>
       </c>
       <c r="E65" t="n">
-        <v>13.14958953857422</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="F65" t="n">
         <v>872000</v>
@@ -1732,16 +1732,16 @@
         <v>44187</v>
       </c>
       <c r="B66" t="n">
-        <v>13.00776958465576</v>
+        <v>13.00776863098145</v>
       </c>
       <c r="C66" t="n">
-        <v>13.60608282735141</v>
+        <v>13.60608182981131</v>
       </c>
       <c r="D66" t="n">
-        <v>12.94572172812351</v>
+        <v>12.94572077899828</v>
       </c>
       <c r="E66" t="n">
-        <v>13.22493496920081</v>
+        <v>13.22493399960485</v>
       </c>
       <c r="F66" t="n">
         <v>911600</v>
@@ -1752,16 +1752,16 @@
         <v>44188</v>
       </c>
       <c r="B67" t="n">
-        <v>14.04484272003174</v>
+        <v>14.04484558105469</v>
       </c>
       <c r="C67" t="n">
-        <v>14.1512093650741</v>
+        <v>14.1512122477646</v>
       </c>
       <c r="D67" t="n">
-        <v>13.40220995524134</v>
+        <v>13.40221268535595</v>
       </c>
       <c r="E67" t="n">
-        <v>13.45539370042599</v>
+        <v>13.45539644137447</v>
       </c>
       <c r="F67" t="n">
         <v>2040000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294364929199</v>
+        <v>15.11294269561768</v>
       </c>
       <c r="C68" t="n">
-        <v>15.13067184897926</v>
+        <v>15.13067089418624</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586848207222</v>
+        <v>14.07586759384061</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348344040167</v>
+        <v>14.13348254853438</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.19715118408203</v>
+        <v>15.19715213775635</v>
       </c>
       <c r="C69" t="n">
-        <v>15.34783749447957</v>
+        <v>15.34783845760998</v>
       </c>
       <c r="D69" t="n">
-        <v>14.7495234573184</v>
+        <v>14.74952438290252</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510417815142</v>
+        <v>15.13510512793207</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884677886963</v>
+        <v>14.98884773254395</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171619745412</v>
+        <v>15.94171721175532</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952120062229</v>
+        <v>14.74952213906937</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069269923545</v>
+        <v>15.91069371156276</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1852,16 +1852,16 @@
         <v>44201</v>
       </c>
       <c r="B72" t="n">
-        <v>15.13953495025635</v>
+        <v>15.13953399658203</v>
       </c>
       <c r="C72" t="n">
-        <v>15.45863576096341</v>
+        <v>15.45863478718819</v>
       </c>
       <c r="D72" t="n">
-        <v>14.36394401696318</v>
+        <v>14.36394311214514</v>
       </c>
       <c r="E72" t="n">
-        <v>14.84702643732623</v>
+        <v>14.8470255020777</v>
       </c>
       <c r="F72" t="n">
         <v>1878200</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.5899715423584</v>
+        <v>14.58997249603271</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135601709469</v>
+        <v>15.28135701596139</v>
       </c>
       <c r="D73" t="n">
-        <v>14.5899715423584</v>
+        <v>14.58997249603271</v>
       </c>
       <c r="E73" t="n">
-        <v>15.13953382083913</v>
+        <v>15.13953481043562</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1892,16 +1892,16 @@
         <v>44203</v>
       </c>
       <c r="B74" t="n">
-        <v>14.40512943267822</v>
+        <v>14.40513038635254</v>
       </c>
       <c r="C74" t="n">
-        <v>14.96994947955643</v>
+        <v>14.96995047062398</v>
       </c>
       <c r="D74" t="n">
-        <v>14.39623442841062</v>
+        <v>14.39623538149606</v>
       </c>
       <c r="E74" t="n">
-        <v>14.68531612918757</v>
+        <v>14.68531710141131</v>
       </c>
       <c r="F74" t="n">
         <v>1215000</v>
@@ -1912,16 +1912,16 @@
         <v>44204</v>
       </c>
       <c r="B75" t="n">
-        <v>15.06334686279297</v>
+        <v>15.06334495544434</v>
       </c>
       <c r="C75" t="n">
-        <v>15.27237525478156</v>
+        <v>15.27237332096537</v>
       </c>
       <c r="D75" t="n">
-        <v>14.38734170043839</v>
+        <v>14.38733987868677</v>
       </c>
       <c r="E75" t="n">
-        <v>14.38734170043839</v>
+        <v>14.38733987868677</v>
       </c>
       <c r="F75" t="n">
         <v>1077600</v>
@@ -1932,16 +1932,16 @@
         <v>44207</v>
       </c>
       <c r="B76" t="n">
-        <v>15.83274555206299</v>
+        <v>15.8327465057373</v>
       </c>
       <c r="C76" t="n">
-        <v>15.83274555206299</v>
+        <v>15.8327465057373</v>
       </c>
       <c r="D76" t="n">
-        <v>14.80539709311043</v>
+        <v>14.80539798490314</v>
       </c>
       <c r="E76" t="n">
-        <v>14.95216043158278</v>
+        <v>14.95216133221568</v>
       </c>
       <c r="F76" t="n">
         <v>1758200</v>
@@ -1952,16 +1952,16 @@
         <v>44208</v>
       </c>
       <c r="B77" t="n">
-        <v>15.99285221099854</v>
+        <v>15.99285125732422</v>
       </c>
       <c r="C77" t="n">
-        <v>16.31306559830687</v>
+        <v>16.31306462553782</v>
       </c>
       <c r="D77" t="n">
-        <v>15.34353212811103</v>
+        <v>15.3435312131565</v>
       </c>
       <c r="E77" t="n">
-        <v>15.90390385935192</v>
+        <v>15.90390291098171</v>
       </c>
       <c r="F77" t="n">
         <v>2193200</v>
@@ -1972,16 +1972,16 @@
         <v>44209</v>
       </c>
       <c r="B78" t="n">
-        <v>15.72156047821045</v>
+        <v>15.72156238555908</v>
       </c>
       <c r="C78" t="n">
-        <v>16.71777896136228</v>
+        <v>16.71778098957271</v>
       </c>
       <c r="D78" t="n">
-        <v>15.41469044686861</v>
+        <v>15.4146923169876</v>
       </c>
       <c r="E78" t="n">
-        <v>15.96616886900687</v>
+        <v>15.96617080603153</v>
       </c>
       <c r="F78" t="n">
         <v>1238200</v>
@@ -1992,16 +1992,16 @@
         <v>44210</v>
       </c>
       <c r="B79" t="n">
-        <v>16.08624649047852</v>
+        <v>16.08625030517578</v>
       </c>
       <c r="C79" t="n">
-        <v>16.2552481813217</v>
+        <v>16.25525203609608</v>
       </c>
       <c r="D79" t="n">
-        <v>15.65929645771021</v>
+        <v>15.65930017116042</v>
       </c>
       <c r="E79" t="n">
-        <v>15.94837816337235</v>
+        <v>15.94838194537548</v>
       </c>
       <c r="F79" t="n">
         <v>1217000</v>
@@ -2012,16 +2012,16 @@
         <v>44211</v>
       </c>
       <c r="B80" t="n">
-        <v>15.881667137146</v>
+        <v>15.88166904449463</v>
       </c>
       <c r="C80" t="n">
-        <v>16.09069550826418</v>
+        <v>16.0906974407166</v>
       </c>
       <c r="D80" t="n">
-        <v>15.61037542906886</v>
+        <v>15.61037730383604</v>
       </c>
       <c r="E80" t="n">
-        <v>16.08624715759644</v>
+        <v>16.08624908951462</v>
       </c>
       <c r="F80" t="n">
         <v>728000</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422584533691</v>
+        <v>16.38422775268555</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538419561817</v>
+        <v>16.45538611125061</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169572023429</v>
+        <v>15.92169757373807</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93503907728939</v>
+        <v>15.93504093234652</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2052,16 +2052,16 @@
         <v>44215</v>
       </c>
       <c r="B82" t="n">
-        <v>16.63327980041504</v>
+        <v>16.63328170776367</v>
       </c>
       <c r="C82" t="n">
-        <v>17.07801988388551</v>
+        <v>17.07802184223276</v>
       </c>
       <c r="D82" t="n">
-        <v>16.0951430100387</v>
+        <v>16.09514485567885</v>
       </c>
       <c r="E82" t="n">
-        <v>17.07801988388551</v>
+        <v>17.07802184223276</v>
       </c>
       <c r="F82" t="n">
         <v>1918400</v>
@@ -2072,16 +2072,16 @@
         <v>44216</v>
       </c>
       <c r="B83" t="n">
-        <v>16.25525093078613</v>
+        <v>16.2552490234375</v>
       </c>
       <c r="C83" t="n">
-        <v>16.81117607682225</v>
+        <v>16.81117410424281</v>
       </c>
       <c r="D83" t="n">
-        <v>16.01064420584002</v>
+        <v>16.0106423271929</v>
       </c>
       <c r="E83" t="n">
-        <v>16.69999104761502</v>
+        <v>16.69998908808175</v>
       </c>
       <c r="F83" t="n">
         <v>1073000</v>
@@ -2092,16 +2092,16 @@
         <v>44217</v>
       </c>
       <c r="B84" t="n">
-        <v>15.85498142242432</v>
+        <v>15.85498523712158</v>
       </c>
       <c r="C84" t="n">
-        <v>16.3664313962309</v>
+        <v>16.36643533398266</v>
       </c>
       <c r="D84" t="n">
-        <v>15.53031973470776</v>
+        <v>15.53032347129166</v>
       </c>
       <c r="E84" t="n">
-        <v>16.25969474802276</v>
+        <v>16.25969866009376</v>
       </c>
       <c r="F84" t="n">
         <v>928200</v>
@@ -2112,16 +2112,16 @@
         <v>44218</v>
       </c>
       <c r="B85" t="n">
-        <v>15.4013500213623</v>
+        <v>15.40135192871094</v>
       </c>
       <c r="C85" t="n">
-        <v>15.84164176695957</v>
+        <v>15.84164372883523</v>
       </c>
       <c r="D85" t="n">
-        <v>15.17453162201319</v>
+        <v>15.17453350127197</v>
       </c>
       <c r="E85" t="n">
-        <v>15.60593005864081</v>
+        <v>15.60593199132524</v>
       </c>
       <c r="F85" t="n">
         <v>1029200</v>
@@ -2152,16 +2152,16 @@
         <v>44223</v>
       </c>
       <c r="B87" t="n">
-        <v>15.00553131103516</v>
+        <v>15.00552940368652</v>
       </c>
       <c r="C87" t="n">
-        <v>15.57034972966033</v>
+        <v>15.5703477505178</v>
       </c>
       <c r="D87" t="n">
-        <v>14.53410620714105</v>
+        <v>14.53410435971512</v>
       </c>
       <c r="E87" t="n">
-        <v>14.74313459133305</v>
+        <v>14.74313271733759</v>
       </c>
       <c r="F87" t="n">
         <v>1909000</v>
@@ -2172,16 +2172,16 @@
         <v>44224</v>
       </c>
       <c r="B88" t="n">
-        <v>15.65929794311523</v>
+        <v>15.65929985046387</v>
       </c>
       <c r="C88" t="n">
-        <v>15.98840635160216</v>
+        <v>15.98840829903717</v>
       </c>
       <c r="D88" t="n">
-        <v>14.95216114202533</v>
+        <v>14.95216296324262</v>
       </c>
       <c r="E88" t="n">
-        <v>15.13450450851776</v>
+        <v>15.134506351945</v>
       </c>
       <c r="F88" t="n">
         <v>3941600</v>
@@ -2192,16 +2192,16 @@
         <v>44225</v>
       </c>
       <c r="B89" t="n">
-        <v>15.74379634857178</v>
+        <v>15.74380111694336</v>
       </c>
       <c r="C89" t="n">
-        <v>16.55322299587936</v>
+        <v>16.55322800940445</v>
       </c>
       <c r="D89" t="n">
-        <v>15.38800299879174</v>
+        <v>15.38800765940311</v>
       </c>
       <c r="E89" t="n">
-        <v>16.01063966435838</v>
+        <v>16.01064451354961</v>
       </c>
       <c r="F89" t="n">
         <v>3936400</v>
@@ -2232,16 +2232,16 @@
         <v>44229</v>
       </c>
       <c r="B91" t="n">
-        <v>17.08246803283691</v>
+        <v>17.08246612548828</v>
       </c>
       <c r="C91" t="n">
-        <v>17.32262810609502</v>
+        <v>17.32262617193124</v>
       </c>
       <c r="D91" t="n">
-        <v>16.76670295311732</v>
+        <v>16.76670108102554</v>
       </c>
       <c r="E91" t="n">
-        <v>16.76670295311732</v>
+        <v>16.76670108102554</v>
       </c>
       <c r="F91" t="n">
         <v>2620800</v>
@@ -2252,16 +2252,16 @@
         <v>44230</v>
       </c>
       <c r="B92" t="n">
-        <v>17.6117057800293</v>
+        <v>17.61170387268066</v>
       </c>
       <c r="C92" t="n">
-        <v>17.78960248348361</v>
+        <v>17.78960055686876</v>
       </c>
       <c r="D92" t="n">
-        <v>16.94014903275922</v>
+        <v>16.94014719814022</v>
       </c>
       <c r="E92" t="n">
-        <v>17.08246571690319</v>
+        <v>17.08246386687129</v>
       </c>
       <c r="F92" t="n">
         <v>1128200</v>
@@ -2292,16 +2292,16 @@
         <v>44232</v>
       </c>
       <c r="B94" t="n">
-        <v>18.80805778503418</v>
+        <v>18.80805969238281</v>
       </c>
       <c r="C94" t="n">
-        <v>19.56856289018561</v>
+        <v>19.56856487465802</v>
       </c>
       <c r="D94" t="n">
-        <v>17.78960262744146</v>
+        <v>17.78960443150729</v>
       </c>
       <c r="E94" t="n">
-        <v>17.99863100120949</v>
+        <v>17.99863282647314</v>
       </c>
       <c r="F94" t="n">
         <v>14342200</v>
@@ -2312,16 +2312,16 @@
         <v>44235</v>
       </c>
       <c r="B95" t="n">
-        <v>19.23056221008301</v>
+        <v>19.23056411743164</v>
       </c>
       <c r="C95" t="n">
-        <v>19.36843055199105</v>
+        <v>19.3684324730139</v>
       </c>
       <c r="D95" t="n">
-        <v>18.46560871350112</v>
+        <v>18.46561054497921</v>
       </c>
       <c r="E95" t="n">
-        <v>18.81250544030044</v>
+        <v>18.81250730618486</v>
       </c>
       <c r="F95" t="n">
         <v>1758400</v>
@@ -2332,16 +2332,16 @@
         <v>44236</v>
       </c>
       <c r="B96" t="n">
-        <v>18.84808540344238</v>
+        <v>18.84808349609375</v>
       </c>
       <c r="C96" t="n">
-        <v>19.4529321945371</v>
+        <v>19.45293022598046</v>
       </c>
       <c r="D96" t="n">
-        <v>18.82584873835336</v>
+        <v>18.82584683325499</v>
       </c>
       <c r="E96" t="n">
-        <v>19.4529321945371</v>
+        <v>19.45293022598046</v>
       </c>
       <c r="F96" t="n">
         <v>1201800</v>
@@ -2372,16 +2372,16 @@
         <v>44238</v>
       </c>
       <c r="B98" t="n">
-        <v>18.63461303710938</v>
+        <v>18.63461112976074</v>
       </c>
       <c r="C98" t="n">
-        <v>19.14606319369697</v>
+        <v>19.14606123399878</v>
       </c>
       <c r="D98" t="n">
-        <v>18.4344796295103</v>
+        <v>18.43447774264635</v>
       </c>
       <c r="E98" t="n">
-        <v>18.5590063291057</v>
+        <v>18.55900442949581</v>
       </c>
       <c r="F98" t="n">
         <v>912400</v>
@@ -2412,16 +2412,16 @@
         <v>44244</v>
       </c>
       <c r="B100" t="n">
-        <v>18.52787017822266</v>
+        <v>18.52787208557129</v>
       </c>
       <c r="C100" t="n">
-        <v>18.68797686562316</v>
+        <v>18.68797878945395</v>
       </c>
       <c r="D100" t="n">
-        <v>18.20765680342165</v>
+        <v>18.20765867780597</v>
       </c>
       <c r="E100" t="n">
-        <v>18.51897517375056</v>
+        <v>18.5189770801835</v>
       </c>
       <c r="F100" t="n">
         <v>743200</v>
@@ -2432,16 +2432,16 @@
         <v>44245</v>
       </c>
       <c r="B101" t="n">
-        <v>18.24323654174805</v>
+        <v>18.24323844909668</v>
       </c>
       <c r="C101" t="n">
-        <v>19.03487326559868</v>
+        <v>19.03487525571373</v>
       </c>
       <c r="D101" t="n">
-        <v>17.90523316318246</v>
+        <v>17.9052350351925</v>
       </c>
       <c r="E101" t="n">
-        <v>18.6924232331395</v>
+        <v>18.69242518745105</v>
       </c>
       <c r="F101" t="n">
         <v>1007600</v>
@@ -2452,16 +2452,16 @@
         <v>44246</v>
       </c>
       <c r="B102" t="n">
-        <v>18.27881813049316</v>
+        <v>18.2788200378418</v>
       </c>
       <c r="C102" t="n">
-        <v>18.57234653985784</v>
+        <v>18.57234847783542</v>
       </c>
       <c r="D102" t="n">
-        <v>17.92302637619491</v>
+        <v>17.92302824641757</v>
       </c>
       <c r="E102" t="n">
-        <v>18.23434479741172</v>
+        <v>18.23434670011968</v>
       </c>
       <c r="F102" t="n">
         <v>881800</v>
@@ -2492,16 +2492,16 @@
         <v>44250</v>
       </c>
       <c r="B104" t="n">
-        <v>17.70065116882324</v>
+        <v>17.70065498352051</v>
       </c>
       <c r="C104" t="n">
-        <v>18.10091783631999</v>
+        <v>18.1009217372794</v>
       </c>
       <c r="D104" t="n">
-        <v>17.51830784175215</v>
+        <v>17.5183116171523</v>
       </c>
       <c r="E104" t="n">
-        <v>17.86075783582194</v>
+        <v>17.86076168502407</v>
       </c>
       <c r="F104" t="n">
         <v>1151400</v>
@@ -2512,16 +2512,16 @@
         <v>44251</v>
       </c>
       <c r="B105" t="n">
-        <v>17.68731498718262</v>
+        <v>17.68731307983398</v>
       </c>
       <c r="C105" t="n">
-        <v>18.09647508812474</v>
+        <v>18.09647313665348</v>
       </c>
       <c r="D105" t="n">
-        <v>17.54499828280719</v>
+        <v>17.54499639080558</v>
       </c>
       <c r="E105" t="n">
-        <v>17.70510499936678</v>
+        <v>17.70510309009973</v>
       </c>
       <c r="F105" t="n">
         <v>1411000</v>
@@ -2572,16 +2572,16 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>16.44648933410645</v>
+        <v>16.44648742675781</v>
       </c>
       <c r="C108" t="n">
-        <v>17.02465114728449</v>
+        <v>17.0246491728847</v>
       </c>
       <c r="D108" t="n">
-        <v>16.27748761449939</v>
+        <v>16.27748572675039</v>
       </c>
       <c r="E108" t="n">
-        <v>16.69999106524258</v>
+        <v>16.69998912849459</v>
       </c>
       <c r="F108" t="n">
         <v>1540800</v>
@@ -2592,16 +2592,16 @@
         <v>44257</v>
       </c>
       <c r="B109" t="n">
-        <v>16.655517578125</v>
+        <v>16.65551567077637</v>
       </c>
       <c r="C109" t="n">
-        <v>16.90457095571786</v>
+        <v>16.90456901984825</v>
       </c>
       <c r="D109" t="n">
-        <v>15.7526939947042</v>
+        <v>15.75269219074469</v>
       </c>
       <c r="E109" t="n">
-        <v>16.1796457927399</v>
+        <v>16.17964393988693</v>
       </c>
       <c r="F109" t="n">
         <v>1243600</v>
@@ -2612,16 +2612,16 @@
         <v>44258</v>
       </c>
       <c r="B110" t="n">
-        <v>16.1929874420166</v>
+        <v>16.19298553466797</v>
       </c>
       <c r="C110" t="n">
-        <v>16.80228092162542</v>
+        <v>16.80227894250898</v>
       </c>
       <c r="D110" t="n">
-        <v>15.61927228923258</v>
+        <v>15.61927044946103</v>
       </c>
       <c r="E110" t="n">
-        <v>16.80228092162542</v>
+        <v>16.80227894250898</v>
       </c>
       <c r="F110" t="n">
         <v>1368800</v>
@@ -2632,16 +2632,16 @@
         <v>44259</v>
       </c>
       <c r="B111" t="n">
-        <v>16.05066871643066</v>
+        <v>16.0506706237793</v>
       </c>
       <c r="C111" t="n">
-        <v>16.75780547454543</v>
+        <v>16.75780746592523</v>
       </c>
       <c r="D111" t="n">
-        <v>15.79271866916489</v>
+        <v>15.79272054586055</v>
       </c>
       <c r="E111" t="n">
-        <v>16.23301207184145</v>
+        <v>16.23301400085849</v>
       </c>
       <c r="F111" t="n">
         <v>1300400</v>
@@ -2672,16 +2672,16 @@
         <v>44263</v>
       </c>
       <c r="B113" t="n">
-        <v>14.91213226318359</v>
+        <v>14.91213512420654</v>
       </c>
       <c r="C113" t="n">
-        <v>16.05956232416226</v>
+        <v>16.0595654053297</v>
       </c>
       <c r="D113" t="n">
-        <v>14.76536893942384</v>
+        <v>14.76537177228896</v>
       </c>
       <c r="E113" t="n">
-        <v>16.01064065072617</v>
+        <v>16.01064372250756</v>
       </c>
       <c r="F113" t="n">
         <v>3236800</v>
@@ -2712,16 +2712,16 @@
         <v>44265</v>
       </c>
       <c r="B115" t="n">
-        <v>14.64529132843018</v>
+        <v>14.64529228210449</v>
       </c>
       <c r="C115" t="n">
-        <v>15.05445139769713</v>
+        <v>15.05445237801519</v>
       </c>
       <c r="D115" t="n">
-        <v>14.28505124405912</v>
+        <v>14.28505217427527</v>
       </c>
       <c r="E115" t="n">
-        <v>15.05445139769713</v>
+        <v>15.05445237801519</v>
       </c>
       <c r="F115" t="n">
         <v>3352600</v>
@@ -2732,16 +2732,16 @@
         <v>44266</v>
       </c>
       <c r="B116" t="n">
-        <v>15.81940650939941</v>
+        <v>15.81940460205078</v>
       </c>
       <c r="C116" t="n">
-        <v>15.99285489107494</v>
+        <v>15.99285296281361</v>
       </c>
       <c r="D116" t="n">
-        <v>15.15674465650835</v>
+        <v>15.15674282905697</v>
       </c>
       <c r="E116" t="n">
-        <v>15.15674465650835</v>
+        <v>15.15674282905697</v>
       </c>
       <c r="F116" t="n">
         <v>2295400</v>
@@ -2752,16 +2752,16 @@
         <v>44267</v>
       </c>
       <c r="B117" t="n">
-        <v>15.61037635803223</v>
+        <v>15.61037826538086</v>
       </c>
       <c r="C117" t="n">
-        <v>15.96172143355023</v>
+        <v>15.96172338382784</v>
       </c>
       <c r="D117" t="n">
-        <v>15.41913798510718</v>
+        <v>15.41913986908941</v>
       </c>
       <c r="E117" t="n">
-        <v>15.96172143355023</v>
+        <v>15.96172338382784</v>
       </c>
       <c r="F117" t="n">
         <v>1034800</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708778381348</v>
+        <v>15.67708683013916</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619618873527</v>
+        <v>16.00619521504051</v>
       </c>
       <c r="D118" t="n">
-        <v>15.49474441929632</v>
+        <v>15.49474347671438</v>
       </c>
       <c r="E118" t="n">
-        <v>15.614824444205</v>
+        <v>15.61482349431831</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2792,16 +2792,16 @@
         <v>44271</v>
       </c>
       <c r="B119" t="n">
-        <v>16.46872901916504</v>
+        <v>16.46872520446777</v>
       </c>
       <c r="C119" t="n">
-        <v>16.8378641985238</v>
+        <v>16.83786029832273</v>
       </c>
       <c r="D119" t="n">
-        <v>15.68153866367939</v>
+        <v>15.6815350313212</v>
       </c>
       <c r="E119" t="n">
-        <v>15.68598701573508</v>
+        <v>15.68598338234651</v>
       </c>
       <c r="F119" t="n">
         <v>1963400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880424499512</v>
+        <v>16.58880615234375</v>
       </c>
       <c r="C120" t="n">
-        <v>16.7578059463568</v>
+        <v>16.75780787313692</v>
       </c>
       <c r="D120" t="n">
-        <v>16.07735418324739</v>
+        <v>16.07735603179049</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298585477987</v>
+        <v>16.19298771661808</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2832,16 +2832,16 @@
         <v>44273</v>
       </c>
       <c r="B121" t="n">
-        <v>16.21967315673828</v>
+        <v>16.21967124938965</v>
       </c>
       <c r="C121" t="n">
-        <v>17.29149680698328</v>
+        <v>17.2914947735938</v>
       </c>
       <c r="D121" t="n">
-        <v>16.07735645022393</v>
+        <v>16.077354559611</v>
       </c>
       <c r="E121" t="n">
-        <v>16.58880658408833</v>
+        <v>16.58880463333153</v>
       </c>
       <c r="F121" t="n">
         <v>1568800</v>
@@ -2852,16 +2852,16 @@
         <v>44274</v>
       </c>
       <c r="B122" t="n">
-        <v>16.32196235656738</v>
+        <v>16.32196044921875</v>
       </c>
       <c r="C122" t="n">
-        <v>16.54433241129841</v>
+        <v>16.54433047796411</v>
       </c>
       <c r="D122" t="n">
-        <v>15.89056390749354</v>
+        <v>15.89056205055718</v>
       </c>
       <c r="E122" t="n">
-        <v>16.17519730610144</v>
+        <v>16.17519541590345</v>
       </c>
       <c r="F122" t="n">
         <v>1059200</v>
@@ -2892,16 +2892,16 @@
         <v>44278</v>
       </c>
       <c r="B124" t="n">
-        <v>16.09959411621094</v>
+        <v>16.0995922088623</v>
       </c>
       <c r="C124" t="n">
-        <v>16.49985924190611</v>
+        <v>16.49985728713733</v>
       </c>
       <c r="D124" t="n">
-        <v>15.87277568475618</v>
+        <v>15.87277380427914</v>
       </c>
       <c r="E124" t="n">
-        <v>16.45538590456745</v>
+        <v>16.4553839550675</v>
       </c>
       <c r="F124" t="n">
         <v>855200</v>
@@ -2932,16 +2932,16 @@
         <v>44280</v>
       </c>
       <c r="B126" t="n">
-        <v>16.06845855712891</v>
+        <v>16.06846046447754</v>
       </c>
       <c r="C126" t="n">
-        <v>16.22411689674175</v>
+        <v>16.22411882256725</v>
       </c>
       <c r="D126" t="n">
-        <v>15.07224009396071</v>
+        <v>15.07224188305681</v>
       </c>
       <c r="E126" t="n">
-        <v>15.38800512377458</v>
+        <v>15.38800695035243</v>
       </c>
       <c r="F126" t="n">
         <v>1320600</v>
@@ -2952,16 +2952,16 @@
         <v>44281</v>
       </c>
       <c r="B127" t="n">
-        <v>15.85498142242432</v>
+        <v>15.85498523712158</v>
       </c>
       <c r="C127" t="n">
-        <v>16.41535306688814</v>
+        <v>16.41535701641043</v>
       </c>
       <c r="D127" t="n">
-        <v>15.67263809323268</v>
+        <v>15.67264186405827</v>
       </c>
       <c r="E127" t="n">
-        <v>16.10403473260894</v>
+        <v>16.10403860722825</v>
       </c>
       <c r="F127" t="n">
         <v>1078200</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.58369159698486</v>
+        <v>15.58368968963623</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174662887645</v>
+        <v>16.00174467036044</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245324175128</v>
+        <v>15.39245135780905</v>
       </c>
       <c r="E128" t="n">
-        <v>15.74379828476634</v>
+        <v>15.74379635782163</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514045715332</v>
+        <v>16.09514236450195</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23745712556681</v>
+        <v>16.23745904978063</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48584711447378</v>
+        <v>15.48584894961834</v>
       </c>
       <c r="E129" t="n">
-        <v>15.5881371138617</v>
+        <v>15.58813896112809</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3032,16 +3032,16 @@
         <v>44287</v>
       </c>
       <c r="B131" t="n">
-        <v>16.59325218200684</v>
+        <v>16.5932559967041</v>
       </c>
       <c r="C131" t="n">
-        <v>17.0424388943022</v>
+        <v>17.04244281226502</v>
       </c>
       <c r="D131" t="n">
-        <v>16.48651382155865</v>
+        <v>16.48651761171736</v>
       </c>
       <c r="E131" t="n">
-        <v>17.03799224020167</v>
+        <v>17.03799615714222</v>
       </c>
       <c r="F131" t="n">
         <v>1225400</v>
@@ -3092,16 +3092,16 @@
         <v>44293</v>
       </c>
       <c r="B134" t="n">
-        <v>17.37154769897461</v>
+        <v>17.37154960632324</v>
       </c>
       <c r="C134" t="n">
-        <v>17.63839106164878</v>
+        <v>17.63839299829608</v>
       </c>
       <c r="D134" t="n">
-        <v>17.11359764471402</v>
+        <v>17.11359952374044</v>
       </c>
       <c r="E134" t="n">
-        <v>17.47828436542479</v>
+        <v>17.47828628449281</v>
       </c>
       <c r="F134" t="n">
         <v>869400</v>
@@ -3112,16 +3112,16 @@
         <v>44294</v>
       </c>
       <c r="B135" t="n">
-        <v>17.60726165771484</v>
+        <v>17.60725975036621</v>
       </c>
       <c r="C135" t="n">
-        <v>17.90968507914474</v>
+        <v>17.90968313903537</v>
       </c>
       <c r="D135" t="n">
-        <v>17.27370656318618</v>
+        <v>17.2737046919707</v>
       </c>
       <c r="E135" t="n">
-        <v>17.38044493991689</v>
+        <v>17.38044305713872</v>
       </c>
       <c r="F135" t="n">
         <v>710000</v>
@@ -3152,16 +3152,16 @@
         <v>44298</v>
       </c>
       <c r="B137" t="n">
-        <v>17.74513053894043</v>
+        <v>17.7451286315918</v>
       </c>
       <c r="C137" t="n">
-        <v>18.05644724942629</v>
+        <v>18.05644530861555</v>
       </c>
       <c r="D137" t="n">
-        <v>17.58947048714867</v>
+        <v>17.58946859653127</v>
       </c>
       <c r="E137" t="n">
-        <v>18.05644724942629</v>
+        <v>18.05644530861555</v>
       </c>
       <c r="F137" t="n">
         <v>810600</v>
@@ -3232,16 +3232,16 @@
         <v>44302</v>
       </c>
       <c r="B141" t="n">
-        <v>17.74513053894043</v>
+        <v>17.7451286315918</v>
       </c>
       <c r="C141" t="n">
-        <v>17.74513053894043</v>
+        <v>17.7451286315918</v>
       </c>
       <c r="D141" t="n">
-        <v>17.12249372487104</v>
+        <v>17.12249188444699</v>
       </c>
       <c r="E141" t="n">
-        <v>17.38489044981543</v>
+        <v>17.38488858118748</v>
       </c>
       <c r="F141" t="n">
         <v>774600</v>
@@ -3252,16 +3252,16 @@
         <v>44305</v>
       </c>
       <c r="B142" t="n">
-        <v>18.01197242736816</v>
+        <v>18.0119743347168</v>
       </c>
       <c r="C142" t="n">
-        <v>18.17652577451049</v>
+        <v>18.17652769928423</v>
       </c>
       <c r="D142" t="n">
-        <v>17.70065404610391</v>
+        <v>17.70065592048599</v>
       </c>
       <c r="E142" t="n">
-        <v>17.70065404610391</v>
+        <v>17.70065592048599</v>
       </c>
       <c r="F142" t="n">
         <v>952400</v>
@@ -3272,16 +3272,16 @@
         <v>44306</v>
       </c>
       <c r="B143" t="n">
-        <v>17.81183815002441</v>
+        <v>17.81184196472168</v>
       </c>
       <c r="C143" t="n">
-        <v>18.40778986771676</v>
+        <v>18.40779381004686</v>
       </c>
       <c r="D143" t="n">
-        <v>17.62949480263974</v>
+        <v>17.62949857828519</v>
       </c>
       <c r="E143" t="n">
-        <v>18.01641815995871</v>
+        <v>18.01642201847014</v>
       </c>
       <c r="F143" t="n">
         <v>1050400</v>
@@ -3292,16 +3292,16 @@
         <v>44308</v>
       </c>
       <c r="B144" t="n">
-        <v>17.32707214355469</v>
+        <v>17.32707405090332</v>
       </c>
       <c r="C144" t="n">
-        <v>17.97639221698004</v>
+        <v>17.97639419580525</v>
       </c>
       <c r="D144" t="n">
-        <v>17.26925715789328</v>
+        <v>17.26925905887769</v>
       </c>
       <c r="E144" t="n">
-        <v>17.94970889945899</v>
+        <v>17.94971087534692</v>
       </c>
       <c r="F144" t="n">
         <v>1084000</v>
@@ -3312,16 +3312,16 @@
         <v>44309</v>
       </c>
       <c r="B145" t="n">
-        <v>17.2114429473877</v>
+        <v>17.21144485473633</v>
       </c>
       <c r="C145" t="n">
-        <v>17.57168135804453</v>
+        <v>17.57168330531429</v>
       </c>
       <c r="D145" t="n">
-        <v>16.88233451279305</v>
+        <v>16.88233638367034</v>
       </c>
       <c r="E145" t="n">
-        <v>17.52276137004772</v>
+        <v>17.52276331189624</v>
       </c>
       <c r="F145" t="n">
         <v>903000</v>
@@ -3332,16 +3332,16 @@
         <v>44312</v>
       </c>
       <c r="B146" t="n">
-        <v>17.08691024780273</v>
+        <v>17.0869140625</v>
       </c>
       <c r="C146" t="n">
-        <v>17.3181752549366</v>
+        <v>17.31817912126438</v>
       </c>
       <c r="D146" t="n">
-        <v>16.90012025928028</v>
+        <v>16.90012403227619</v>
       </c>
       <c r="E146" t="n">
-        <v>17.3181752549366</v>
+        <v>17.31817912126438</v>
       </c>
       <c r="F146" t="n">
         <v>836400</v>
@@ -3372,16 +3372,16 @@
         <v>44314</v>
       </c>
       <c r="B148" t="n">
-        <v>18.56789970397949</v>
+        <v>18.56789779663086</v>
       </c>
       <c r="C148" t="n">
-        <v>18.63905805414477</v>
+        <v>18.63905613948654</v>
       </c>
       <c r="D148" t="n">
-        <v>17.32707438245799</v>
+        <v>17.32707260257054</v>
       </c>
       <c r="E148" t="n">
-        <v>17.33596938829726</v>
+        <v>17.33596760749609</v>
       </c>
       <c r="F148" t="n">
         <v>2195600</v>
@@ -3392,16 +3392,16 @@
         <v>44315</v>
       </c>
       <c r="B149" t="n">
-        <v>18.93703460693359</v>
+        <v>18.93703269958496</v>
       </c>
       <c r="C149" t="n">
-        <v>19.0704562999812</v>
+        <v>19.07045437919426</v>
       </c>
       <c r="D149" t="n">
-        <v>18.13205440095317</v>
+        <v>18.13205257468259</v>
       </c>
       <c r="E149" t="n">
-        <v>18.57234615766514</v>
+        <v>18.57234428704813</v>
       </c>
       <c r="F149" t="n">
         <v>2301200</v>
@@ -3412,16 +3412,16 @@
         <v>44316</v>
       </c>
       <c r="B150" t="n">
-        <v>19.34006118774414</v>
+        <v>19.34005928039551</v>
       </c>
       <c r="C150" t="n">
-        <v>19.34006118774414</v>
+        <v>19.34005928039551</v>
       </c>
       <c r="D150" t="n">
-        <v>18.38334087467527</v>
+        <v>18.38333906167997</v>
       </c>
       <c r="E150" t="n">
-        <v>18.86617264318869</v>
+        <v>18.86617078257573</v>
       </c>
       <c r="F150" t="n">
         <v>2355400</v>
@@ -3432,16 +3432,16 @@
         <v>44319</v>
       </c>
       <c r="B151" t="n">
-        <v>19.44735527038574</v>
+        <v>19.44735717773438</v>
       </c>
       <c r="C151" t="n">
-        <v>19.67088808958558</v>
+        <v>19.67089001885776</v>
       </c>
       <c r="D151" t="n">
-        <v>18.83934572929498</v>
+        <v>18.83934757701153</v>
       </c>
       <c r="E151" t="n">
-        <v>19.62618220791364</v>
+        <v>19.62618413280117</v>
       </c>
       <c r="F151" t="n">
         <v>2225200</v>
@@ -3452,16 +3452,16 @@
         <v>44320</v>
       </c>
       <c r="B152" t="n">
-        <v>19.79606628417969</v>
+        <v>19.79606819152832</v>
       </c>
       <c r="C152" t="n">
-        <v>20.00618768379984</v>
+        <v>20.00618961139364</v>
       </c>
       <c r="D152" t="n">
-        <v>19.25958887263734</v>
+        <v>19.25959072829643</v>
       </c>
       <c r="E152" t="n">
-        <v>19.45182553167395</v>
+        <v>19.45182740585503</v>
       </c>
       <c r="F152" t="n">
         <v>1635200</v>
@@ -3492,16 +3492,16 @@
         <v>44322</v>
       </c>
       <c r="B154" t="n">
-        <v>20.43090057373047</v>
+        <v>20.4309024810791</v>
       </c>
       <c r="C154" t="n">
-        <v>20.65443339903295</v>
+        <v>20.65443532724973</v>
       </c>
       <c r="D154" t="n">
-        <v>20.16266016011543</v>
+        <v>20.16266204242219</v>
       </c>
       <c r="E154" t="n">
-        <v>20.46219503283921</v>
+        <v>20.46219694310937</v>
       </c>
       <c r="F154" t="n">
         <v>1030200</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.83326148986816</v>
+        <v>20.8332633972168</v>
       </c>
       <c r="C155" t="n">
-        <v>20.877969084305</v>
+        <v>20.87797099574675</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384283351365</v>
+        <v>20.36384469788557</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902756541763</v>
+        <v>20.86902947604076</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3532,16 +3532,16 @@
         <v>44326</v>
       </c>
       <c r="B156" t="n">
-        <v>20.36384201049805</v>
+        <v>20.36384010314941</v>
       </c>
       <c r="C156" t="n">
-        <v>20.94502707132523</v>
+        <v>20.94502510954077</v>
       </c>
       <c r="D156" t="n">
-        <v>20.25207558705358</v>
+        <v>20.25207369017338</v>
       </c>
       <c r="E156" t="n">
-        <v>20.83326064788076</v>
+        <v>20.83325869656473</v>
       </c>
       <c r="F156" t="n">
         <v>979800</v>
@@ -3552,16 +3552,16 @@
         <v>44327</v>
       </c>
       <c r="B157" t="n">
-        <v>20.60078811645508</v>
+        <v>20.60078620910645</v>
       </c>
       <c r="C157" t="n">
-        <v>20.60972792961658</v>
+        <v>20.60972602144025</v>
       </c>
       <c r="D157" t="n">
-        <v>19.7826570731339</v>
+        <v>19.78265524153291</v>
       </c>
       <c r="E157" t="n">
-        <v>20.25207571344624</v>
+        <v>20.25207383838357</v>
       </c>
       <c r="F157" t="n">
         <v>1012800</v>
@@ -3572,16 +3572,16 @@
         <v>44328</v>
       </c>
       <c r="B158" t="n">
-        <v>20.15819358825684</v>
+        <v>20.1581916809082</v>
       </c>
       <c r="C158" t="n">
-        <v>20.59631779366714</v>
+        <v>20.59631584486362</v>
       </c>
       <c r="D158" t="n">
-        <v>19.57253687514265</v>
+        <v>19.57253502320829</v>
       </c>
       <c r="E158" t="n">
-        <v>20.59631779366714</v>
+        <v>20.59631584486362</v>
       </c>
       <c r="F158" t="n">
         <v>1344400</v>
@@ -3592,16 +3592,16 @@
         <v>44329</v>
       </c>
       <c r="B159" t="n">
-        <v>20.9047908782959</v>
+        <v>20.90478897094727</v>
       </c>
       <c r="C159" t="n">
-        <v>20.97185141384942</v>
+        <v>20.9718495003822</v>
       </c>
       <c r="D159" t="n">
-        <v>20.15819199587331</v>
+        <v>20.1581901566442</v>
       </c>
       <c r="E159" t="n">
-        <v>20.25654699323974</v>
+        <v>20.25654514503674</v>
       </c>
       <c r="F159" t="n">
         <v>1469200</v>
@@ -3612,16 +3612,16 @@
         <v>44330</v>
       </c>
       <c r="B160" t="n">
-        <v>20.29678344726562</v>
+        <v>20.29678153991699</v>
       </c>
       <c r="C160" t="n">
-        <v>21.23562073440818</v>
+        <v>21.23561873883424</v>
       </c>
       <c r="D160" t="n">
-        <v>20.22972291014674</v>
+        <v>20.22972100909998</v>
       </c>
       <c r="E160" t="n">
-        <v>21.01655779118409</v>
+        <v>21.01655581619614</v>
       </c>
       <c r="F160" t="n">
         <v>1009800</v>
@@ -3652,16 +3652,16 @@
         <v>44334</v>
       </c>
       <c r="B162" t="n">
-        <v>21.12385368347168</v>
+        <v>21.12385559082031</v>
       </c>
       <c r="C162" t="n">
-        <v>21.74080480825265</v>
+        <v>21.74080677130802</v>
       </c>
       <c r="D162" t="n">
-        <v>20.88243780350257</v>
+        <v>20.8824396890529</v>
       </c>
       <c r="E162" t="n">
-        <v>21.15067823860833</v>
+        <v>21.15068014837905</v>
       </c>
       <c r="F162" t="n">
         <v>1192600</v>
@@ -3712,16 +3712,16 @@
         <v>44337</v>
       </c>
       <c r="B165" t="n">
-        <v>21.94645500183105</v>
+        <v>21.94645309448242</v>
       </c>
       <c r="C165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04033647282705</v>
       </c>
       <c r="D165" t="n">
-        <v>21.50385921408051</v>
+        <v>21.50385734519752</v>
       </c>
       <c r="E165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04033647282705</v>
       </c>
       <c r="F165" t="n">
         <v>653400</v>
@@ -3772,16 +3772,16 @@
         <v>44342</v>
       </c>
       <c r="B168" t="n">
-        <v>22.1744556427002</v>
+        <v>22.17445755004883</v>
       </c>
       <c r="C168" t="n">
-        <v>22.42481302160963</v>
+        <v>22.42481495049289</v>
       </c>
       <c r="D168" t="n">
-        <v>21.53515162431978</v>
+        <v>21.53515347667831</v>
       </c>
       <c r="E168" t="n">
-        <v>22.1744556427002</v>
+        <v>22.17445755004883</v>
       </c>
       <c r="F168" t="n">
         <v>837000</v>
@@ -3812,16 +3812,16 @@
         <v>44344</v>
       </c>
       <c r="B170" t="n">
-        <v>22.21469306945801</v>
+        <v>22.21469497680664</v>
       </c>
       <c r="C170" t="n">
-        <v>22.54552242370129</v>
+        <v>22.54552435945486</v>
       </c>
       <c r="D170" t="n">
-        <v>21.94198443666828</v>
+        <v>21.94198632060221</v>
       </c>
       <c r="E170" t="n">
-        <v>22.29516502845177</v>
+        <v>22.29516694270971</v>
       </c>
       <c r="F170" t="n">
         <v>840600</v>
@@ -3832,16 +3832,16 @@
         <v>44347</v>
       </c>
       <c r="B171" t="n">
-        <v>23.22953414916992</v>
+        <v>23.22953224182129</v>
       </c>
       <c r="C171" t="n">
-        <v>23.22953414916992</v>
+        <v>23.22953224182129</v>
       </c>
       <c r="D171" t="n">
-        <v>22.24151932802007</v>
+        <v>22.24151750179612</v>
       </c>
       <c r="E171" t="n">
-        <v>22.24151932802007</v>
+        <v>22.24151750179612</v>
       </c>
       <c r="F171" t="n">
         <v>1311400</v>
@@ -3852,16 +3852,16 @@
         <v>44348</v>
       </c>
       <c r="B172" t="n">
-        <v>23.69448089599609</v>
+        <v>23.69448280334473</v>
       </c>
       <c r="C172" t="n">
-        <v>24.09236907591068</v>
+        <v>24.09237101528835</v>
       </c>
       <c r="D172" t="n">
-        <v>23.10435433841622</v>
+        <v>23.10435619826109</v>
       </c>
       <c r="E172" t="n">
-        <v>23.32341556524954</v>
+        <v>23.32341744272831</v>
       </c>
       <c r="F172" t="n">
         <v>1770600</v>
@@ -3872,16 +3872,16 @@
         <v>44349</v>
       </c>
       <c r="B173" t="n">
-        <v>23.69448089599609</v>
+        <v>23.69448280334473</v>
       </c>
       <c r="C173" t="n">
-        <v>24.03872167215439</v>
+        <v>24.03872360721357</v>
       </c>
       <c r="D173" t="n">
-        <v>23.47094805735462</v>
+        <v>23.4709499467094</v>
       </c>
       <c r="E173" t="n">
-        <v>24.03872167215439</v>
+        <v>24.03872360721357</v>
       </c>
       <c r="F173" t="n">
         <v>823800</v>
@@ -3892,16 +3892,16 @@
         <v>44351</v>
       </c>
       <c r="B174" t="n">
-        <v>23.69448089599609</v>
+        <v>23.69448280334473</v>
       </c>
       <c r="C174" t="n">
-        <v>23.91801373463757</v>
+        <v>23.91801565998005</v>
       </c>
       <c r="D174" t="n">
-        <v>23.39941761720616</v>
+        <v>23.39941950080291</v>
       </c>
       <c r="E174" t="n">
-        <v>23.69448089599609</v>
+        <v>23.69448280334473</v>
       </c>
       <c r="F174" t="n">
         <v>902800</v>
@@ -3972,16 +3972,16 @@
         <v>44357</v>
       </c>
       <c r="B178" t="n">
-        <v>23.69448089599609</v>
+        <v>23.69448280334473</v>
       </c>
       <c r="C178" t="n">
-        <v>23.89118918004931</v>
+        <v>23.89119110323249</v>
       </c>
       <c r="D178" t="n">
-        <v>23.44859511457452</v>
+        <v>23.44859700212994</v>
       </c>
       <c r="E178" t="n">
-        <v>23.69448089599609</v>
+        <v>23.69448280334473</v>
       </c>
       <c r="F178" t="n">
         <v>946600</v>
@@ -3992,16 +3992,16 @@
         <v>44358</v>
       </c>
       <c r="B179" t="n">
-        <v>23.3055362701416</v>
+        <v>23.30553436279297</v>
       </c>
       <c r="C179" t="n">
-        <v>23.5648334987982</v>
+        <v>23.56483157022843</v>
       </c>
       <c r="D179" t="n">
-        <v>22.55893563704099</v>
+        <v>22.55893379079491</v>
       </c>
       <c r="E179" t="n">
-        <v>23.5648334987982</v>
+        <v>23.56483157022843</v>
       </c>
       <c r="F179" t="n">
         <v>855400</v>
@@ -4012,16 +4012,16 @@
         <v>44361</v>
       </c>
       <c r="B180" t="n">
-        <v>24.5886116027832</v>
+        <v>24.58861351013184</v>
       </c>
       <c r="C180" t="n">
-        <v>24.76743855115333</v>
+        <v>24.76744047237364</v>
       </c>
       <c r="D180" t="n">
-        <v>23.26082603049845</v>
+        <v>23.26082783485022</v>
       </c>
       <c r="E180" t="n">
-        <v>23.45753601478963</v>
+        <v>23.45753783440027</v>
       </c>
       <c r="F180" t="n">
         <v>1774600</v>
@@ -4072,16 +4072,16 @@
         <v>44364</v>
       </c>
       <c r="B183" t="n">
-        <v>24.5886116027832</v>
+        <v>24.58861351013184</v>
       </c>
       <c r="C183" t="n">
-        <v>24.71378944339019</v>
+        <v>24.71379136044892</v>
       </c>
       <c r="D183" t="n">
-        <v>23.96719060059827</v>
+        <v>23.96719245974302</v>
       </c>
       <c r="E183" t="n">
-        <v>24.63331748716565</v>
+        <v>24.63331939798214</v>
       </c>
       <c r="F183" t="n">
         <v>897400</v>
@@ -4132,16 +4132,16 @@
         <v>44369</v>
       </c>
       <c r="B186" t="n">
-        <v>24.5886116027832</v>
+        <v>24.58861351013184</v>
       </c>
       <c r="C186" t="n">
-        <v>25.26815161900145</v>
+        <v>25.26815357906228</v>
       </c>
       <c r="D186" t="n">
-        <v>24.54390571840076</v>
+        <v>24.54390762228154</v>
       </c>
       <c r="E186" t="n">
-        <v>25.23238554715936</v>
+        <v>25.2323875044458</v>
       </c>
       <c r="F186" t="n">
         <v>871000</v>
@@ -4152,16 +4152,16 @@
         <v>44370</v>
       </c>
       <c r="B187" t="n">
-        <v>24.72273445129395</v>
+        <v>24.72273254394531</v>
       </c>
       <c r="C187" t="n">
-        <v>24.87920847956124</v>
+        <v>24.87920656014071</v>
       </c>
       <c r="D187" t="n">
-        <v>24.28014033500109</v>
+        <v>24.28013846179841</v>
       </c>
       <c r="E187" t="n">
-        <v>24.71379293207121</v>
+        <v>24.71379102541241</v>
       </c>
       <c r="F187" t="n">
         <v>1264600</v>
@@ -4172,16 +4172,16 @@
         <v>44371</v>
       </c>
       <c r="B188" t="n">
-        <v>24.58414459228516</v>
+        <v>24.58414268493652</v>
       </c>
       <c r="C188" t="n">
-        <v>25.05803316207115</v>
+        <v>25.05803121795611</v>
       </c>
       <c r="D188" t="n">
-        <v>23.98060484951002</v>
+        <v>23.98060298898671</v>
       </c>
       <c r="E188" t="n">
-        <v>25.05356325527446</v>
+        <v>25.05356131150621</v>
       </c>
       <c r="F188" t="n">
         <v>1450200</v>
@@ -4192,16 +4192,16 @@
         <v>44372</v>
       </c>
       <c r="B189" t="n">
-        <v>24.3516674041748</v>
+        <v>24.35166931152344</v>
       </c>
       <c r="C189" t="n">
-        <v>24.58861166172607</v>
+        <v>24.5886135876334</v>
       </c>
       <c r="D189" t="n">
-        <v>24.00295502455915</v>
+        <v>24.00295690459483</v>
       </c>
       <c r="E189" t="n">
-        <v>24.27119544775736</v>
+        <v>24.27119734880301</v>
       </c>
       <c r="F189" t="n">
         <v>926400</v>
@@ -4212,16 +4212,16 @@
         <v>44375</v>
       </c>
       <c r="B190" t="n">
-        <v>24.48578643798828</v>
+        <v>24.48578834533691</v>
       </c>
       <c r="C190" t="n">
-        <v>25.01332405397893</v>
+        <v>25.01332600242071</v>
       </c>
       <c r="D190" t="n">
-        <v>24.06107371929478</v>
+        <v>24.06107559355992</v>
       </c>
       <c r="E190" t="n">
-        <v>24.06107371929478</v>
+        <v>24.06107559355992</v>
       </c>
       <c r="F190" t="n">
         <v>1351800</v>
@@ -4272,16 +4272,16 @@
         <v>44378</v>
       </c>
       <c r="B193" t="n">
-        <v>24.92838096618652</v>
+        <v>24.92838287353516</v>
       </c>
       <c r="C193" t="n">
-        <v>25.96557488779945</v>
+        <v>25.96557687450705</v>
       </c>
       <c r="D193" t="n">
-        <v>24.91049963553645</v>
+        <v>24.91050154151692</v>
       </c>
       <c r="E193" t="n">
-        <v>25.25921031180567</v>
+        <v>25.2592122444671</v>
       </c>
       <c r="F193" t="n">
         <v>1991200</v>
@@ -4332,16 +4332,16 @@
         <v>44383</v>
       </c>
       <c r="B196" t="n">
-        <v>26.19804954528809</v>
+        <v>26.19804763793945</v>
       </c>
       <c r="C196" t="n">
-        <v>26.53334882294324</v>
+        <v>26.53334689118315</v>
       </c>
       <c r="D196" t="n">
-        <v>25.66157206537609</v>
+        <v>25.66157019708569</v>
       </c>
       <c r="E196" t="n">
-        <v>26.53334882294324</v>
+        <v>26.53334689118315</v>
       </c>
       <c r="F196" t="n">
         <v>905000</v>
@@ -4392,16 +4392,16 @@
         <v>44389</v>
       </c>
       <c r="B199" t="n">
-        <v>27.5437183380127</v>
+        <v>27.54371643066406</v>
       </c>
       <c r="C199" t="n">
-        <v>27.57501280090645</v>
+        <v>27.57501089139074</v>
       </c>
       <c r="D199" t="n">
-        <v>26.56911496538337</v>
+        <v>26.56911312552412</v>
       </c>
       <c r="E199" t="n">
-        <v>26.81500076187162</v>
+        <v>26.81499890498525</v>
       </c>
       <c r="F199" t="n">
         <v>886400</v>
@@ -4432,16 +4432,16 @@
         <v>44391</v>
       </c>
       <c r="B201" t="n">
-        <v>28.1740779876709</v>
+        <v>28.1740837097168</v>
       </c>
       <c r="C201" t="n">
-        <v>28.33502189750872</v>
+        <v>28.33502765224171</v>
       </c>
       <c r="D201" t="n">
-        <v>27.44089058100538</v>
+        <v>27.44089615414376</v>
       </c>
       <c r="E201" t="n">
-        <v>27.67336492794666</v>
+        <v>27.67337054829968</v>
       </c>
       <c r="F201" t="n">
         <v>880600</v>
@@ -4452,16 +4452,16 @@
         <v>44392</v>
       </c>
       <c r="B202" t="n">
-        <v>28.47808647155762</v>
+        <v>28.47808456420898</v>
       </c>
       <c r="C202" t="n">
-        <v>28.76420655172373</v>
+        <v>28.76420462521192</v>
       </c>
       <c r="D202" t="n">
-        <v>27.81195780383505</v>
+        <v>27.81195594110106</v>
       </c>
       <c r="E202" t="n">
-        <v>28.21431763070376</v>
+        <v>28.21431574102132</v>
       </c>
       <c r="F202" t="n">
         <v>1015800</v>
@@ -4472,16 +4472,16 @@
         <v>44393</v>
       </c>
       <c r="B203" t="n">
-        <v>28.79103088378906</v>
+        <v>28.79102897644043</v>
       </c>
       <c r="C203" t="n">
-        <v>29.03244676372463</v>
+        <v>29.03244484038268</v>
       </c>
       <c r="D203" t="n">
-        <v>28.15172681585982</v>
+        <v>28.15172495086382</v>
       </c>
       <c r="E203" t="n">
-        <v>28.72844196056582</v>
+        <v>28.72844005736358</v>
       </c>
       <c r="F203" t="n">
         <v>1048600</v>
@@ -4492,16 +4492,16 @@
         <v>44396</v>
       </c>
       <c r="B204" t="n">
-        <v>28.77314567565918</v>
+        <v>28.77314758300781</v>
       </c>
       <c r="C204" t="n">
-        <v>29.12185633897039</v>
+        <v>29.12185826943477</v>
       </c>
       <c r="D204" t="n">
-        <v>28.02207524281956</v>
+        <v>28.02207710038034</v>
       </c>
       <c r="E204" t="n">
-        <v>28.38419903539513</v>
+        <v>28.3842009169608</v>
       </c>
       <c r="F204" t="n">
         <v>866800</v>
@@ -4532,16 +4532,16 @@
         <v>44398</v>
       </c>
       <c r="B206" t="n">
-        <v>29.60468864440918</v>
+        <v>29.60469055175781</v>
       </c>
       <c r="C206" t="n">
-        <v>29.78351559114187</v>
+        <v>29.78351751001183</v>
       </c>
       <c r="D206" t="n">
-        <v>29.0592679917526</v>
+        <v>29.05926986396128</v>
       </c>
       <c r="E206" t="n">
-        <v>29.52868830057088</v>
+        <v>29.52869020302303</v>
       </c>
       <c r="F206" t="n">
         <v>1050200</v>
@@ -4592,16 +4592,16 @@
         <v>44403</v>
       </c>
       <c r="B209" t="n">
-        <v>30.08752250671387</v>
+        <v>30.08752059936523</v>
       </c>
       <c r="C209" t="n">
-        <v>30.48987890178793</v>
+        <v>30.48987696893258</v>
       </c>
       <c r="D209" t="n">
-        <v>29.56445305360459</v>
+        <v>29.56445117941508</v>
       </c>
       <c r="E209" t="n">
-        <v>30.48987890178793</v>
+        <v>30.48987696893258</v>
       </c>
       <c r="F209" t="n">
         <v>1240800</v>
@@ -4632,16 +4632,16 @@
         <v>44405</v>
       </c>
       <c r="B211" t="n">
-        <v>29.43927574157715</v>
+        <v>29.43927383422852</v>
       </c>
       <c r="C211" t="n">
-        <v>30.57035141986809</v>
+        <v>30.57034943923792</v>
       </c>
       <c r="D211" t="n">
-        <v>28.73291111508599</v>
+        <v>28.7329092535022</v>
       </c>
       <c r="E211" t="n">
-        <v>29.52869092832068</v>
+        <v>29.52868901517891</v>
       </c>
       <c r="F211" t="n">
         <v>1257400</v>
@@ -4672,16 +4672,16 @@
         <v>44407</v>
       </c>
       <c r="B213" t="n">
-        <v>31.13812446594238</v>
+        <v>31.13812255859375</v>
       </c>
       <c r="C213" t="n">
-        <v>31.58071852233474</v>
+        <v>31.58071658787525</v>
       </c>
       <c r="D213" t="n">
-        <v>30.41387685570368</v>
+        <v>30.41387499271843</v>
       </c>
       <c r="E213" t="n">
-        <v>30.80282521486082</v>
+        <v>30.80282332805076</v>
       </c>
       <c r="F213" t="n">
         <v>1548200</v>
@@ -4692,16 +4692,16 @@
         <v>44410</v>
       </c>
       <c r="B214" t="n">
-        <v>31.24989128112793</v>
+        <v>31.24988746643066</v>
       </c>
       <c r="C214" t="n">
-        <v>31.98755032507403</v>
+        <v>31.98754642033019</v>
       </c>
       <c r="D214" t="n">
-        <v>31.03976986870518</v>
+        <v>31.03976607965759</v>
       </c>
       <c r="E214" t="n">
-        <v>31.58071892470821</v>
+        <v>31.58071506962657</v>
       </c>
       <c r="F214" t="n">
         <v>1185600</v>
@@ -4712,16 +4712,16 @@
         <v>44411</v>
       </c>
       <c r="B215" t="n">
-        <v>30.62400245666504</v>
+        <v>30.62400054931641</v>
       </c>
       <c r="C215" t="n">
-        <v>31.14260033985012</v>
+        <v>31.14259840020176</v>
       </c>
       <c r="D215" t="n">
-        <v>30.20375957965926</v>
+        <v>30.20375769848453</v>
       </c>
       <c r="E215" t="n">
-        <v>31.13812872752174</v>
+        <v>31.13812678815189</v>
       </c>
       <c r="F215" t="n">
         <v>1467200</v>
@@ -4732,16 +4732,16 @@
         <v>44412</v>
       </c>
       <c r="B216" t="n">
-        <v>29.78798675537109</v>
+        <v>29.78798484802246</v>
       </c>
       <c r="C216" t="n">
-        <v>30.84753370622673</v>
+        <v>30.84753173103446</v>
       </c>
       <c r="D216" t="n">
-        <v>29.7566922923926</v>
+        <v>29.75669038704778</v>
       </c>
       <c r="E216" t="n">
-        <v>30.62400085328306</v>
+        <v>30.62399889240378</v>
       </c>
       <c r="F216" t="n">
         <v>1263400</v>
@@ -4752,16 +4752,16 @@
         <v>44413</v>
       </c>
       <c r="B217" t="n">
-        <v>29.48397827148438</v>
+        <v>29.48398017883301</v>
       </c>
       <c r="C217" t="n">
-        <v>30.38705279511604</v>
+        <v>30.38705476088549</v>
       </c>
       <c r="D217" t="n">
-        <v>29.13973922154018</v>
+        <v>29.13974110661963</v>
       </c>
       <c r="E217" t="n">
-        <v>29.82374912073076</v>
+        <v>29.82375105005952</v>
       </c>
       <c r="F217" t="n">
         <v>1197200</v>
@@ -4772,16 +4772,16 @@
         <v>44414</v>
       </c>
       <c r="B218" t="n">
-        <v>29.46163177490234</v>
+        <v>29.46162986755371</v>
       </c>
       <c r="C218" t="n">
-        <v>29.99810927720156</v>
+        <v>29.99810733512132</v>
       </c>
       <c r="D218" t="n">
-        <v>29.10397783280902</v>
+        <v>29.10397594861493</v>
       </c>
       <c r="E218" t="n">
-        <v>29.97575803759621</v>
+        <v>29.975756096963</v>
       </c>
       <c r="F218" t="n">
         <v>684400</v>
@@ -4792,16 +4792,16 @@
         <v>44417</v>
       </c>
       <c r="B219" t="n">
-        <v>30.23952484130859</v>
+        <v>30.2395191192627</v>
       </c>
       <c r="C219" t="n">
-        <v>30.4049403845904</v>
+        <v>30.4049346312439</v>
       </c>
       <c r="D219" t="n">
-        <v>29.54210341388179</v>
+        <v>29.54209782380482</v>
       </c>
       <c r="E219" t="n">
-        <v>29.85951966382196</v>
+        <v>29.85951401368219</v>
       </c>
       <c r="F219" t="n">
         <v>1023000</v>
@@ -4832,16 +4832,16 @@
         <v>44419</v>
       </c>
       <c r="B221" t="n">
-        <v>29.11291694641113</v>
+        <v>29.11291885375977</v>
       </c>
       <c r="C221" t="n">
-        <v>30.38258178096093</v>
+        <v>30.38258377149235</v>
       </c>
       <c r="D221" t="n">
-        <v>28.14725348562089</v>
+        <v>28.14725532970356</v>
       </c>
       <c r="E221" t="n">
-        <v>29.68516044428373</v>
+        <v>29.68516238912321</v>
       </c>
       <c r="F221" t="n">
         <v>1237750</v>
@@ -4872,16 +4872,16 @@
         <v>44421</v>
       </c>
       <c r="B223" t="n">
-        <v>28.34396362304688</v>
+        <v>28.34396553039551</v>
       </c>
       <c r="C223" t="n">
-        <v>29.59574542882125</v>
+        <v>29.59574742040596</v>
       </c>
       <c r="D223" t="n">
-        <v>27.18159187982183</v>
+        <v>27.18159370895106</v>
       </c>
       <c r="E223" t="n">
-        <v>29.50633366085176</v>
+        <v>29.50633564641969</v>
       </c>
       <c r="F223" t="n">
         <v>1962050</v>
@@ -4972,16 +4972,16 @@
         <v>44428</v>
       </c>
       <c r="B228" t="n">
-        <v>26.64511299133301</v>
+        <v>26.64511680603027</v>
       </c>
       <c r="C228" t="n">
-        <v>26.87758734212807</v>
+        <v>26.87759119010796</v>
       </c>
       <c r="D228" t="n">
-        <v>25.73310032950029</v>
+        <v>25.73310401362756</v>
       </c>
       <c r="E228" t="n">
-        <v>26.34110820224871</v>
+        <v>26.34111197342256</v>
       </c>
       <c r="F228" t="n">
         <v>1186050</v>
@@ -4992,16 +4992,16 @@
         <v>44431</v>
       </c>
       <c r="B229" t="n">
-        <v>26.85970687866211</v>
+        <v>26.85970878601074</v>
       </c>
       <c r="C229" t="n">
-        <v>27.41406736694361</v>
+        <v>27.41406931365822</v>
       </c>
       <c r="D229" t="n">
-        <v>26.28746164845576</v>
+        <v>26.28746351516839</v>
       </c>
       <c r="E229" t="n">
-        <v>26.71664429204535</v>
+        <v>26.71664618923489</v>
       </c>
       <c r="F229" t="n">
         <v>1094150</v>
@@ -5012,16 +5012,16 @@
         <v>44432</v>
       </c>
       <c r="B230" t="n">
-        <v>27.48559951782227</v>
+        <v>27.48559761047363</v>
       </c>
       <c r="C230" t="n">
-        <v>27.84325174306836</v>
+        <v>27.84324981090064</v>
       </c>
       <c r="D230" t="n">
-        <v>27.00276944009512</v>
+        <v>27.00276756625223</v>
       </c>
       <c r="E230" t="n">
-        <v>27.64654344553809</v>
+        <v>27.64654152702084</v>
       </c>
       <c r="F230" t="n">
         <v>835550</v>
@@ -5032,16 +5032,16 @@
         <v>44433</v>
       </c>
       <c r="B231" t="n">
-        <v>27.89690208435059</v>
+        <v>27.89689636230469</v>
       </c>
       <c r="C231" t="n">
-        <v>28.4154982601487</v>
+        <v>28.41549243173145</v>
       </c>
       <c r="D231" t="n">
-        <v>27.27100938354371</v>
+        <v>27.27100378987718</v>
       </c>
       <c r="E231" t="n">
-        <v>27.48560072814082</v>
+        <v>27.4855950904586</v>
       </c>
       <c r="F231" t="n">
         <v>1098800</v>
@@ -5092,16 +5092,16 @@
         <v>44438</v>
       </c>
       <c r="B234" t="n">
-        <v>27.68230819702148</v>
+        <v>27.68230628967285</v>
       </c>
       <c r="C234" t="n">
-        <v>29.68516409685458</v>
+        <v>29.68516205150646</v>
       </c>
       <c r="D234" t="n">
-        <v>27.55713034281455</v>
+        <v>27.55712844409084</v>
       </c>
       <c r="E234" t="n">
-        <v>28.96985963650016</v>
+        <v>28.96985764043749</v>
       </c>
       <c r="F234" t="n">
         <v>1402700</v>
@@ -5112,16 +5112,16 @@
         <v>44439</v>
       </c>
       <c r="B235" t="n">
-        <v>26.55570411682129</v>
+        <v>26.55570220947266</v>
       </c>
       <c r="C235" t="n">
-        <v>27.86113518423277</v>
+        <v>27.86113318312228</v>
       </c>
       <c r="D235" t="n">
-        <v>25.87616402630093</v>
+        <v>25.87616216775989</v>
       </c>
       <c r="E235" t="n">
-        <v>27.68230821630939</v>
+        <v>27.68230622804304</v>
       </c>
       <c r="F235" t="n">
         <v>1705500</v>
@@ -5152,16 +5152,16 @@
         <v>44441</v>
       </c>
       <c r="B237" t="n">
-        <v>25.35756683349609</v>
+        <v>25.35756492614746</v>
       </c>
       <c r="C237" t="n">
-        <v>26.6629978477622</v>
+        <v>26.66299584222149</v>
       </c>
       <c r="D237" t="n">
-        <v>25.10720942967972</v>
+        <v>25.10720754116251</v>
       </c>
       <c r="E237" t="n">
-        <v>26.59146740458899</v>
+        <v>26.59146540442867</v>
       </c>
       <c r="F237" t="n">
         <v>1706000</v>
@@ -5192,16 +5192,16 @@
         <v>44445</v>
       </c>
       <c r="B239" t="n">
-        <v>25.76886749267578</v>
+        <v>25.76886558532715</v>
       </c>
       <c r="C239" t="n">
-        <v>25.89404534691268</v>
+        <v>25.89404343029868</v>
       </c>
       <c r="D239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="E239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="F239" t="n">
         <v>528250</v>
@@ -5252,16 +5252,16 @@
         <v>44449</v>
       </c>
       <c r="B242" t="n">
-        <v>25.19662284851074</v>
+        <v>25.19662094116211</v>
       </c>
       <c r="C242" t="n">
-        <v>26.19804905049173</v>
+        <v>26.19804706733655</v>
       </c>
       <c r="D242" t="n">
-        <v>24.64226063620605</v>
+        <v>24.64225877082185</v>
       </c>
       <c r="E242" t="n">
-        <v>26.00134075860054</v>
+        <v>26.0013387903359</v>
       </c>
       <c r="F242" t="n">
         <v>1514650</v>
@@ -5292,16 +5292,16 @@
         <v>44453</v>
       </c>
       <c r="B244" t="n">
-        <v>26.34110832214355</v>
+        <v>26.34111022949219</v>
       </c>
       <c r="C244" t="n">
-        <v>27.0206483416944</v>
+        <v>27.02065029824824</v>
       </c>
       <c r="D244" t="n">
-        <v>25.84039525183984</v>
+        <v>25.84039712293205</v>
       </c>
       <c r="E244" t="n">
-        <v>26.60934874601425</v>
+        <v>26.60935067278606</v>
       </c>
       <c r="F244" t="n">
         <v>937200</v>
@@ -5392,16 +5392,16 @@
         <v>44460</v>
       </c>
       <c r="B249" t="n">
-        <v>25.07144355773926</v>
+        <v>25.07144546508789</v>
       </c>
       <c r="C249" t="n">
-        <v>25.19662139943273</v>
+        <v>25.19662331630446</v>
       </c>
       <c r="D249" t="n">
-        <v>24.05213267185464</v>
+        <v>24.05213450165763</v>
       </c>
       <c r="E249" t="n">
-        <v>24.57072878012499</v>
+        <v>24.57073064938097</v>
       </c>
       <c r="F249" t="n">
         <v>662000</v>
@@ -5412,16 +5412,16 @@
         <v>44461</v>
       </c>
       <c r="B250" t="n">
-        <v>25.48274612426758</v>
+        <v>25.48274421691895</v>
       </c>
       <c r="C250" t="n">
-        <v>26.37687756722434</v>
+        <v>26.37687559295119</v>
       </c>
       <c r="D250" t="n">
-        <v>25.23238870628835</v>
+        <v>25.23238681767862</v>
       </c>
       <c r="E250" t="n">
-        <v>25.92981184574596</v>
+        <v>25.92980990493507</v>
       </c>
       <c r="F250" t="n">
         <v>900000</v>
@@ -5492,16 +5492,16 @@
         <v>44467</v>
       </c>
       <c r="B254" t="n">
-        <v>24.83896827697754</v>
+        <v>24.83897018432617</v>
       </c>
       <c r="C254" t="n">
-        <v>25.80463001855441</v>
+        <v>25.80463200005482</v>
       </c>
       <c r="D254" t="n">
-        <v>24.44555002509952</v>
+        <v>24.44555190223813</v>
       </c>
       <c r="E254" t="n">
-        <v>25.75098091233005</v>
+        <v>25.75098288971082</v>
       </c>
       <c r="F254" t="n">
         <v>1020250</v>
@@ -5512,16 +5512,16 @@
         <v>44468</v>
       </c>
       <c r="B255" t="n">
-        <v>24.67802619934082</v>
+        <v>24.67802810668945</v>
       </c>
       <c r="C255" t="n">
-        <v>25.39333061451349</v>
+        <v>25.39333257714754</v>
       </c>
       <c r="D255" t="n">
-        <v>24.46343487478902</v>
+        <v>24.46343676555203</v>
       </c>
       <c r="E255" t="n">
-        <v>25.10720884844443</v>
+        <v>25.10721078896431</v>
       </c>
       <c r="F255" t="n">
         <v>580300</v>
@@ -5612,16 +5612,16 @@
         <v>44475</v>
       </c>
       <c r="B260" t="n">
-        <v>23.60506629943848</v>
+        <v>23.60506820678711</v>
       </c>
       <c r="C260" t="n">
-        <v>23.60506629943848</v>
+        <v>23.60506820678711</v>
       </c>
       <c r="D260" t="n">
-        <v>22.37116583906875</v>
+        <v>22.37116764671513</v>
       </c>
       <c r="E260" t="n">
-        <v>22.97917540419186</v>
+        <v>22.97917726096693</v>
       </c>
       <c r="F260" t="n">
         <v>1199850</v>
@@ -5652,16 +5652,16 @@
         <v>44477</v>
       </c>
       <c r="B262" t="n">
-        <v>24.05213165283203</v>
+        <v>24.05213356018066</v>
       </c>
       <c r="C262" t="n">
-        <v>24.53496337391379</v>
+        <v>24.53496531955127</v>
       </c>
       <c r="D262" t="n">
-        <v>23.69447947356042</v>
+        <v>23.69448135254702</v>
       </c>
       <c r="E262" t="n">
-        <v>23.81965730995046</v>
+        <v>23.81965919886374</v>
       </c>
       <c r="F262" t="n">
         <v>982950</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35613822937012</v>
+        <v>24.35613632202148</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991219957796</v>
+        <v>24.99991024181488</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848602369909</v>
+        <v>23.99848414435849</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307734710171</v>
+        <v>24.21307545095629</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5712,16 +5712,16 @@
         <v>44483</v>
       </c>
       <c r="B265" t="n">
-        <v>24.37401962280273</v>
+        <v>24.37402153015137</v>
       </c>
       <c r="C265" t="n">
-        <v>24.91049874785196</v>
+        <v>24.91050069718188</v>
       </c>
       <c r="D265" t="n">
-        <v>23.9269539694984</v>
+        <v>23.92695584186265</v>
       </c>
       <c r="E265" t="n">
-        <v>24.51708049542651</v>
+        <v>24.51708241397014</v>
       </c>
       <c r="F265" t="n">
         <v>635500</v>
@@ -5732,16 +5732,16 @@
         <v>44484</v>
       </c>
       <c r="B266" t="n">
-        <v>26.16228675842285</v>
+        <v>26.16228485107422</v>
       </c>
       <c r="C266" t="n">
-        <v>26.59146945048253</v>
+        <v>26.59146751184455</v>
       </c>
       <c r="D266" t="n">
-        <v>24.44555428476369</v>
+        <v>24.44555250257259</v>
       </c>
       <c r="E266" t="n">
-        <v>24.76744215651866</v>
+        <v>24.76744035086049</v>
       </c>
       <c r="F266" t="n">
         <v>2075800</v>
@@ -5772,16 +5772,16 @@
         <v>44488</v>
       </c>
       <c r="B268" t="n">
-        <v>24.60649681091309</v>
+        <v>24.60649299621582</v>
       </c>
       <c r="C268" t="n">
-        <v>26.46629007537627</v>
+        <v>26.46628597235887</v>
       </c>
       <c r="D268" t="n">
-        <v>24.12366503094249</v>
+        <v>24.12366129109769</v>
       </c>
       <c r="E268" t="n">
-        <v>26.43052400037682</v>
+        <v>26.43051990290417</v>
       </c>
       <c r="F268" t="n">
         <v>1499450</v>
@@ -5832,16 +5832,16 @@
         <v>44491</v>
       </c>
       <c r="B271" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="C271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563060373434</v>
       </c>
       <c r="D271" t="n">
-        <v>19.81395151866856</v>
+        <v>19.81394972618147</v>
       </c>
       <c r="E271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563060373434</v>
       </c>
       <c r="F271" t="n">
         <v>3185950</v>
@@ -5872,16 +5872,16 @@
         <v>44495</v>
       </c>
       <c r="B273" t="n">
-        <v>20.29678344726562</v>
+        <v>20.29678153991699</v>
       </c>
       <c r="C273" t="n">
-        <v>21.53068402797473</v>
+        <v>21.53068200467281</v>
       </c>
       <c r="D273" t="n">
-        <v>20.17160389167173</v>
+        <v>20.17160199608659</v>
       </c>
       <c r="E273" t="n">
-        <v>21.45915358424406</v>
+        <v>21.45915156766407</v>
       </c>
       <c r="F273" t="n">
         <v>1532000</v>
@@ -5892,16 +5892,16 @@
         <v>44496</v>
       </c>
       <c r="B274" t="n">
-        <v>20.49349212646484</v>
+        <v>20.49349021911621</v>
       </c>
       <c r="C274" t="n">
-        <v>21.10150176231677</v>
+        <v>21.1014997983801</v>
       </c>
       <c r="D274" t="n">
-        <v>20.31466516106592</v>
+        <v>20.31466327036089</v>
       </c>
       <c r="E274" t="n">
-        <v>20.42196168138934</v>
+        <v>20.42195978069811</v>
       </c>
       <c r="F274" t="n">
         <v>1013650</v>
@@ -5932,16 +5932,16 @@
         <v>44498</v>
       </c>
       <c r="B276" t="n">
-        <v>18.32969093322754</v>
+        <v>18.3296947479248</v>
       </c>
       <c r="C276" t="n">
-        <v>20.52925302661322</v>
+        <v>20.52925729907399</v>
       </c>
       <c r="D276" t="n">
-        <v>18.09721659966791</v>
+        <v>18.0972203659836</v>
       </c>
       <c r="E276" t="n">
-        <v>20.24313129466907</v>
+        <v>20.2431355075834</v>
       </c>
       <c r="F276" t="n">
         <v>3577000</v>
@@ -5952,16 +5952,16 @@
         <v>44501</v>
       </c>
       <c r="B277" t="n">
-        <v>18.77676010131836</v>
+        <v>18.77675819396973</v>
       </c>
       <c r="C277" t="n">
-        <v>19.40265278686379</v>
+        <v>19.40265081593679</v>
       </c>
       <c r="D277" t="n">
-        <v>18.68734661689468</v>
+        <v>18.68734471862869</v>
       </c>
       <c r="E277" t="n">
-        <v>18.77676010131836</v>
+        <v>18.77675819396973</v>
       </c>
       <c r="F277" t="n">
         <v>1843300</v>
@@ -5972,16 +5972,16 @@
         <v>44503</v>
       </c>
       <c r="B278" t="n">
-        <v>20.11795425415039</v>
+        <v>20.11795616149902</v>
       </c>
       <c r="C278" t="n">
-        <v>20.36831163215328</v>
+        <v>20.36831356323787</v>
       </c>
       <c r="D278" t="n">
-        <v>18.41910512488394</v>
+        <v>18.41910687116761</v>
       </c>
       <c r="E278" t="n">
-        <v>18.47275252537737</v>
+        <v>18.47275427674726</v>
       </c>
       <c r="F278" t="n">
         <v>1851600</v>
@@ -6032,16 +6032,16 @@
         <v>44508</v>
       </c>
       <c r="B281" t="n">
-        <v>20.13583946228027</v>
+        <v>20.13583564758301</v>
       </c>
       <c r="C281" t="n">
-        <v>20.86902693468137</v>
+        <v>20.8690229810831</v>
       </c>
       <c r="D281" t="n">
-        <v>19.86759902002748</v>
+        <v>19.86759525614787</v>
       </c>
       <c r="E281" t="n">
-        <v>20.86902693468137</v>
+        <v>20.8690229810831</v>
       </c>
       <c r="F281" t="n">
         <v>919700</v>
@@ -6072,16 +6072,16 @@
         <v>44510</v>
       </c>
       <c r="B283" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="C283" t="n">
-        <v>21.65586170945009</v>
+        <v>21.65585975033293</v>
       </c>
       <c r="D283" t="n">
-        <v>20.49349158152647</v>
+        <v>20.49348972756417</v>
       </c>
       <c r="E283" t="n">
-        <v>20.88690987169059</v>
+        <v>20.88690798213735</v>
       </c>
       <c r="F283" t="n">
         <v>1309800</v>
@@ -6092,16 +6092,16 @@
         <v>44511</v>
       </c>
       <c r="B284" t="n">
-        <v>21.94198608398438</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C284" t="n">
-        <v>22.99705973754176</v>
+        <v>22.99705773847886</v>
       </c>
       <c r="D284" t="n">
-        <v>21.78104215391382</v>
+        <v>21.78104026055555</v>
       </c>
       <c r="E284" t="n">
-        <v>21.95986741644305</v>
+        <v>21.95986550754004</v>
       </c>
       <c r="F284" t="n">
         <v>2031350</v>
@@ -6112,16 +6112,16 @@
         <v>44512</v>
       </c>
       <c r="B285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="C285" t="n">
-        <v>22.12081044278765</v>
+        <v>22.12080844160848</v>
       </c>
       <c r="D285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="E285" t="n">
-        <v>21.76315822692041</v>
+        <v>21.76315625809657</v>
       </c>
       <c r="F285" t="n">
         <v>1307150</v>
@@ -6132,16 +6132,16 @@
         <v>44516</v>
       </c>
       <c r="B286" t="n">
-        <v>20.63655090332031</v>
+        <v>20.63655281066895</v>
       </c>
       <c r="C286" t="n">
-        <v>21.87045138086964</v>
+        <v>21.87045340226245</v>
       </c>
       <c r="D286" t="n">
-        <v>19.77818565031559</v>
+        <v>19.77818747832918</v>
       </c>
       <c r="E286" t="n">
-        <v>21.76315657695413</v>
+        <v>21.76315858843013</v>
       </c>
       <c r="F286" t="n">
         <v>1709550</v>
@@ -6152,16 +6152,16 @@
         <v>44517</v>
       </c>
       <c r="B287" t="n">
-        <v>19.99277687072754</v>
+        <v>19.99277877807617</v>
       </c>
       <c r="C287" t="n">
-        <v>20.92267255716455</v>
+        <v>20.92267455322699</v>
       </c>
       <c r="D287" t="n">
-        <v>19.59935861221719</v>
+        <v>19.59936048203298</v>
       </c>
       <c r="E287" t="n">
-        <v>20.40407645952734</v>
+        <v>20.40407840611472</v>
       </c>
       <c r="F287" t="n">
         <v>1179650</v>
@@ -6192,16 +6192,16 @@
         <v>44519</v>
       </c>
       <c r="B289" t="n">
-        <v>20.99420356750488</v>
+        <v>20.99420547485352</v>
       </c>
       <c r="C289" t="n">
-        <v>21.24456095801091</v>
+        <v>21.24456288810481</v>
       </c>
       <c r="D289" t="n">
-        <v>20.11795525886409</v>
+        <v>20.11795708660452</v>
       </c>
       <c r="E289" t="n">
-        <v>20.31466354077727</v>
+        <v>20.31466538638888</v>
       </c>
       <c r="F289" t="n">
         <v>767750</v>
@@ -6232,16 +6232,16 @@
         <v>44523</v>
       </c>
       <c r="B291" t="n">
-        <v>19.24170684814453</v>
+        <v>19.24170875549316</v>
       </c>
       <c r="C291" t="n">
-        <v>20.45772431098796</v>
+        <v>20.45772633887523</v>
       </c>
       <c r="D291" t="n">
-        <v>19.02711553117216</v>
+        <v>19.02711741724927</v>
       </c>
       <c r="E291" t="n">
-        <v>20.20736862723029</v>
+        <v>20.20737063030087</v>
       </c>
       <c r="F291" t="n">
         <v>1896750</v>
@@ -6252,16 +6252,16 @@
         <v>44524</v>
       </c>
       <c r="B292" t="n">
-        <v>19.58147621154785</v>
+        <v>19.58147811889648</v>
       </c>
       <c r="C292" t="n">
-        <v>20.33254668150708</v>
+        <v>20.3325486620143</v>
       </c>
       <c r="D292" t="n">
-        <v>19.02711572993332</v>
+        <v>19.02711758328404</v>
       </c>
       <c r="E292" t="n">
-        <v>19.04499706080266</v>
+        <v>19.04499891589514</v>
       </c>
       <c r="F292" t="n">
         <v>1594900</v>
@@ -6272,16 +6272,16 @@
         <v>44525</v>
       </c>
       <c r="B293" t="n">
-        <v>20.29678344726562</v>
+        <v>20.29678153991699</v>
       </c>
       <c r="C293" t="n">
-        <v>20.43984433472696</v>
+        <v>20.43984241393447</v>
       </c>
       <c r="D293" t="n">
-        <v>19.65300774826931</v>
+        <v>19.65300590141818</v>
       </c>
       <c r="E293" t="n">
-        <v>19.65300774826931</v>
+        <v>19.65300590141818</v>
       </c>
       <c r="F293" t="n">
         <v>787900</v>
@@ -6292,16 +6292,16 @@
         <v>44526</v>
       </c>
       <c r="B294" t="n">
-        <v>19.76030540466309</v>
+        <v>19.76030349731445</v>
       </c>
       <c r="C294" t="n">
-        <v>19.90336630036396</v>
+        <v>19.90336437920648</v>
       </c>
       <c r="D294" t="n">
-        <v>19.18806011643918</v>
+        <v>19.18805826432609</v>
       </c>
       <c r="E294" t="n">
-        <v>19.65300888017723</v>
+        <v>19.65300698318531</v>
       </c>
       <c r="F294" t="n">
         <v>1033400</v>
@@ -6312,16 +6312,16 @@
         <v>44529</v>
       </c>
       <c r="B295" t="n">
-        <v>19.2059440612793</v>
+        <v>19.20594215393066</v>
       </c>
       <c r="C295" t="n">
-        <v>20.33254994716491</v>
+        <v>20.33254792793267</v>
       </c>
       <c r="D295" t="n">
-        <v>19.06288315882593</v>
+        <v>19.06288126568472</v>
       </c>
       <c r="E295" t="n">
-        <v>20.33254994716491</v>
+        <v>20.33254792793267</v>
       </c>
       <c r="F295" t="n">
         <v>830750</v>
@@ -6352,16 +6352,16 @@
         <v>44531</v>
       </c>
       <c r="B297" t="n">
-        <v>17.95415878295898</v>
+        <v>17.95415687561035</v>
       </c>
       <c r="C297" t="n">
-        <v>19.67089117160695</v>
+        <v>19.67088908188234</v>
       </c>
       <c r="D297" t="n">
-        <v>17.93627574532028</v>
+        <v>17.93627383987144</v>
       </c>
       <c r="E297" t="n">
-        <v>18.99135109011918</v>
+        <v>18.99134907258508</v>
       </c>
       <c r="F297" t="n">
         <v>1102200</v>
@@ -6392,16 +6392,16 @@
         <v>44533</v>
       </c>
       <c r="B299" t="n">
-        <v>19.76030540466309</v>
+        <v>19.76030349731445</v>
       </c>
       <c r="C299" t="n">
-        <v>20.20737113008343</v>
+        <v>20.20736917958211</v>
       </c>
       <c r="D299" t="n">
-        <v>18.77676046765426</v>
+        <v>18.77675865524156</v>
       </c>
       <c r="E299" t="n">
-        <v>18.77676046765426</v>
+        <v>18.77675865524156</v>
       </c>
       <c r="F299" t="n">
         <v>1496100</v>
@@ -6432,16 +6432,16 @@
         <v>44537</v>
       </c>
       <c r="B301" t="n">
-        <v>19.93913078308105</v>
+        <v>19.93912887573242</v>
       </c>
       <c r="C301" t="n">
-        <v>20.72596741925636</v>
+        <v>20.72596543664007</v>
       </c>
       <c r="D301" t="n">
-        <v>19.90336641166604</v>
+        <v>19.90336450773857</v>
       </c>
       <c r="E301" t="n">
-        <v>20.35043213958642</v>
+        <v>20.35043019289329</v>
       </c>
       <c r="F301" t="n">
         <v>881500</v>
@@ -6472,16 +6472,16 @@
         <v>44539</v>
       </c>
       <c r="B303" t="n">
-        <v>20.9047908782959</v>
+        <v>20.90478897094727</v>
       </c>
       <c r="C303" t="n">
-        <v>21.36973960440232</v>
+        <v>21.36973765463187</v>
       </c>
       <c r="D303" t="n">
-        <v>20.72596562585361</v>
+        <v>20.72596373482095</v>
       </c>
       <c r="E303" t="n">
-        <v>21.24456175715069</v>
+        <v>21.24455981880144</v>
       </c>
       <c r="F303" t="n">
         <v>669550</v>
@@ -6492,16 +6492,16 @@
         <v>44540</v>
       </c>
       <c r="B304" t="n">
-        <v>21.81680488586426</v>
+        <v>21.81680679321289</v>
       </c>
       <c r="C304" t="n">
-        <v>22.19234012602034</v>
+        <v>22.19234206620039</v>
       </c>
       <c r="D304" t="n">
-        <v>21.06573440555209</v>
+        <v>21.06573624723789</v>
       </c>
       <c r="E304" t="n">
-        <v>22.1386927218324</v>
+        <v>22.13869465732228</v>
       </c>
       <c r="F304" t="n">
         <v>899500</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78104019165039</v>
+        <v>21.78104209899902</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422762443386</v>
+        <v>22.51422959598714</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550495712469</v>
+        <v>21.40550683158799</v>
       </c>
       <c r="E305" t="n">
-        <v>22.13869238990815</v>
+        <v>22.13869432857611</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6532,16 +6532,16 @@
         <v>44544</v>
       </c>
       <c r="B306" t="n">
-        <v>21.49492073059082</v>
+        <v>21.49491691589355</v>
       </c>
       <c r="C306" t="n">
-        <v>22.06716430896915</v>
+        <v>22.06716039271598</v>
       </c>
       <c r="D306" t="n">
-        <v>21.22668027416069</v>
+        <v>21.22667650706798</v>
       </c>
       <c r="E306" t="n">
-        <v>21.95986778531302</v>
+        <v>21.95986388810174</v>
       </c>
       <c r="F306" t="n">
         <v>979700</v>
@@ -6552,16 +6552,16 @@
         <v>44545</v>
       </c>
       <c r="B307" t="n">
-        <v>22.03139877319336</v>
+        <v>22.03139686584473</v>
       </c>
       <c r="C307" t="n">
-        <v>22.37116968525772</v>
+        <v>22.37116774849373</v>
       </c>
       <c r="D307" t="n">
-        <v>21.11938597412999</v>
+        <v>21.11938414573805</v>
       </c>
       <c r="E307" t="n">
-        <v>21.45915518077393</v>
+        <v>21.45915332296677</v>
       </c>
       <c r="F307" t="n">
         <v>1028800</v>
@@ -6572,16 +6572,16 @@
         <v>44546</v>
       </c>
       <c r="B308" t="n">
-        <v>21.94198608398438</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C308" t="n">
-        <v>22.97917840508309</v>
+        <v>22.97917640757456</v>
       </c>
       <c r="D308" t="n">
-        <v>21.53068473986848</v>
+        <v>21.53068286827299</v>
       </c>
       <c r="E308" t="n">
-        <v>22.5321126906295</v>
+        <v>22.53211073198299</v>
       </c>
       <c r="F308" t="n">
         <v>888550</v>
@@ -6592,16 +6592,16 @@
         <v>44547</v>
       </c>
       <c r="B309" t="n">
-        <v>22.37116622924805</v>
+        <v>22.37116813659668</v>
       </c>
       <c r="C309" t="n">
-        <v>22.72881841925829</v>
+        <v>22.72882035710008</v>
       </c>
       <c r="D309" t="n">
-        <v>21.42338579394568</v>
+        <v>21.42338762048728</v>
       </c>
       <c r="E309" t="n">
-        <v>21.56644837536995</v>
+        <v>21.56645021410895</v>
       </c>
       <c r="F309" t="n">
         <v>2194100</v>
@@ -6612,16 +6612,16 @@
         <v>44550</v>
       </c>
       <c r="B310" t="n">
-        <v>22.01351547241211</v>
+        <v>22.01351356506348</v>
       </c>
       <c r="C310" t="n">
-        <v>22.42481509134622</v>
+        <v>22.42481314836077</v>
       </c>
       <c r="D310" t="n">
-        <v>21.13726541806416</v>
+        <v>21.13726358663772</v>
       </c>
       <c r="E310" t="n">
-        <v>22.35328464868723</v>
+        <v>22.35328271189949</v>
       </c>
       <c r="F310" t="n">
         <v>1565700</v>
@@ -6632,16 +6632,16 @@
         <v>44551</v>
       </c>
       <c r="B311" t="n">
-        <v>21.38762092590332</v>
+        <v>21.38762283325195</v>
       </c>
       <c r="C311" t="n">
-        <v>22.19233876090282</v>
+        <v>22.19234074001621</v>
       </c>
       <c r="D311" t="n">
-        <v>21.38762092590332</v>
+        <v>21.38762283325195</v>
       </c>
       <c r="E311" t="n">
-        <v>22.0313948528189</v>
+        <v>22.0313968175793</v>
       </c>
       <c r="F311" t="n">
         <v>785250</v>
@@ -6672,16 +6672,16 @@
         <v>44553</v>
       </c>
       <c r="B313" t="n">
-        <v>21.17614936828613</v>
+        <v>21.17615127563477</v>
       </c>
       <c r="C313" t="n">
-        <v>21.69923988180597</v>
+        <v>21.69924183626969</v>
       </c>
       <c r="D313" t="n">
-        <v>20.79735956744761</v>
+        <v>20.79736144067842</v>
       </c>
       <c r="E313" t="n">
-        <v>21.69923988180597</v>
+        <v>21.69924183626969</v>
       </c>
       <c r="F313" t="n">
         <v>605250</v>
@@ -6732,16 +6732,16 @@
         <v>44559</v>
       </c>
       <c r="B316" t="n">
-        <v>20.29230690002441</v>
+        <v>20.29230880737305</v>
       </c>
       <c r="C316" t="n">
-        <v>20.90558578379051</v>
+        <v>20.90558774878349</v>
       </c>
       <c r="D316" t="n">
-        <v>20.05781781386678</v>
+        <v>20.05781969917492</v>
       </c>
       <c r="E316" t="n">
-        <v>20.7071710153955</v>
+        <v>20.70717296173873</v>
       </c>
       <c r="F316" t="n">
         <v>541350</v>
@@ -6752,16 +6752,16 @@
         <v>44560</v>
       </c>
       <c r="B317" t="n">
-        <v>21.06792831420898</v>
+        <v>21.06792640686035</v>
       </c>
       <c r="C317" t="n">
-        <v>21.15811498498244</v>
+        <v>21.15811306946891</v>
       </c>
       <c r="D317" t="n">
-        <v>19.93155871641855</v>
+        <v>19.93155691194919</v>
       </c>
       <c r="E317" t="n">
-        <v>20.29231056011382</v>
+        <v>20.2923087229844</v>
       </c>
       <c r="F317" t="n">
         <v>1399700</v>
@@ -6792,16 +6792,16 @@
         <v>44565</v>
       </c>
       <c r="B319" t="n">
-        <v>18.99359893798828</v>
+        <v>18.99360084533691</v>
       </c>
       <c r="C319" t="n">
-        <v>20.23819473506625</v>
+        <v>20.23819676739794</v>
       </c>
       <c r="D319" t="n">
-        <v>18.8492982253126</v>
+        <v>18.84930011817047</v>
       </c>
       <c r="E319" t="n">
-        <v>20.07585600325606</v>
+        <v>20.0758580192856</v>
       </c>
       <c r="F319" t="n">
         <v>1398150</v>
@@ -6812,16 +6812,16 @@
         <v>44566</v>
       </c>
       <c r="B320" t="n">
-        <v>17.78507995605469</v>
+        <v>17.78508186340332</v>
       </c>
       <c r="C320" t="n">
-        <v>18.8853750885193</v>
+        <v>18.88537711386832</v>
       </c>
       <c r="D320" t="n">
-        <v>17.55059085766387</v>
+        <v>17.55059273986488</v>
       </c>
       <c r="E320" t="n">
-        <v>18.77714868918498</v>
+        <v>18.77715070292733</v>
       </c>
       <c r="F320" t="n">
         <v>2337000</v>
@@ -6872,16 +6872,16 @@
         <v>44571</v>
       </c>
       <c r="B323" t="n">
-        <v>16.36011123657227</v>
+        <v>16.36010932922363</v>
       </c>
       <c r="C323" t="n">
-        <v>17.13572899413958</v>
+        <v>17.13572699636531</v>
       </c>
       <c r="D323" t="n">
-        <v>16.10758580495536</v>
+        <v>16.10758392704749</v>
       </c>
       <c r="E323" t="n">
-        <v>17.11769097182395</v>
+        <v>17.11768897615265</v>
       </c>
       <c r="F323" t="n">
         <v>1820150</v>
@@ -6892,16 +6892,16 @@
         <v>44572</v>
       </c>
       <c r="B324" t="n">
-        <v>16.77497673034668</v>
+        <v>16.77497291564941</v>
       </c>
       <c r="C324" t="n">
-        <v>17.04554017752951</v>
+        <v>17.04553630130503</v>
       </c>
       <c r="D324" t="n">
-        <v>16.1797357703841</v>
+        <v>16.17973209104702</v>
       </c>
       <c r="E324" t="n">
-        <v>16.19777207204929</v>
+        <v>16.19776838861069</v>
       </c>
       <c r="F324" t="n">
         <v>629400</v>
@@ -6912,16 +6912,16 @@
         <v>44573</v>
       </c>
       <c r="B325" t="n">
-        <v>17.53255653381348</v>
+        <v>17.53255462646484</v>
       </c>
       <c r="C325" t="n">
-        <v>17.69489529100997</v>
+        <v>17.69489336600067</v>
       </c>
       <c r="D325" t="n">
-        <v>16.7028264460762</v>
+        <v>16.70282462899304</v>
       </c>
       <c r="E325" t="n">
-        <v>16.86516520327269</v>
+        <v>16.86516336852887</v>
       </c>
       <c r="F325" t="n">
         <v>1172500</v>
@@ -6932,16 +6932,16 @@
         <v>44574</v>
       </c>
       <c r="B326" t="n">
-        <v>16.64871025085449</v>
+        <v>16.64871406555176</v>
       </c>
       <c r="C326" t="n">
-        <v>17.62274266945553</v>
+        <v>17.62274670733157</v>
       </c>
       <c r="D326" t="n">
-        <v>16.57655989246185</v>
+        <v>16.5765636906274</v>
       </c>
       <c r="E326" t="n">
-        <v>17.58666663015909</v>
+        <v>17.58667065976908</v>
       </c>
       <c r="F326" t="n">
         <v>921200</v>
@@ -6992,16 +6992,16 @@
         <v>44579</v>
       </c>
       <c r="B329" t="n">
-        <v>16.30599594116211</v>
+        <v>16.30599784851074</v>
       </c>
       <c r="C329" t="n">
-        <v>16.79301213441261</v>
+        <v>16.79301409872861</v>
       </c>
       <c r="D329" t="n">
-        <v>16.07150685406374</v>
+        <v>16.07150873398366</v>
       </c>
       <c r="E329" t="n">
-        <v>16.73889807725132</v>
+        <v>16.73890003523749</v>
       </c>
       <c r="F329" t="n">
         <v>670850</v>
@@ -7012,16 +7012,16 @@
         <v>44580</v>
       </c>
       <c r="B330" t="n">
-        <v>16.41422462463379</v>
+        <v>16.41422271728516</v>
       </c>
       <c r="C330" t="n">
-        <v>16.72086411051511</v>
+        <v>16.72086216753467</v>
       </c>
       <c r="D330" t="n">
-        <v>16.19777180619957</v>
+        <v>16.19776992400296</v>
       </c>
       <c r="E330" t="n">
-        <v>16.41422462463379</v>
+        <v>16.41422271728516</v>
       </c>
       <c r="F330" t="n">
         <v>847250</v>
@@ -7032,16 +7032,16 @@
         <v>44581</v>
       </c>
       <c r="B331" t="n">
-        <v>17.42432594299316</v>
+        <v>17.42432975769043</v>
       </c>
       <c r="C331" t="n">
-        <v>18.12779314871526</v>
+        <v>18.12779711742218</v>
       </c>
       <c r="D331" t="n">
-        <v>16.48637138889707</v>
+        <v>16.48637499824851</v>
       </c>
       <c r="E331" t="n">
-        <v>16.48637138889707</v>
+        <v>16.48637499824851</v>
       </c>
       <c r="F331" t="n">
         <v>2219300</v>
@@ -7072,16 +7072,16 @@
         <v>44585</v>
       </c>
       <c r="B333" t="n">
-        <v>17.85723114013672</v>
+        <v>17.85722923278809</v>
       </c>
       <c r="C333" t="n">
-        <v>18.09172024935553</v>
+        <v>18.09171831696088</v>
       </c>
       <c r="D333" t="n">
-        <v>17.47844130527562</v>
+        <v>17.47843943838591</v>
       </c>
       <c r="E333" t="n">
-        <v>18.09172024935553</v>
+        <v>18.09171831696088</v>
       </c>
       <c r="F333" t="n">
         <v>692150</v>
@@ -7112,16 +7112,16 @@
         <v>44587</v>
       </c>
       <c r="B335" t="n">
-        <v>19.3543529510498</v>
+        <v>19.35435485839844</v>
       </c>
       <c r="C335" t="n">
-        <v>19.80529316020046</v>
+        <v>19.80529511198872</v>
       </c>
       <c r="D335" t="n">
-        <v>18.84930039845718</v>
+        <v>18.84930225603348</v>
       </c>
       <c r="E335" t="n">
-        <v>18.92145076311327</v>
+        <v>18.9214526277999</v>
       </c>
       <c r="F335" t="n">
         <v>1494250</v>
@@ -7132,16 +7132,16 @@
         <v>44588</v>
       </c>
       <c r="B336" t="n">
-        <v>19.33631706237793</v>
+        <v>19.3363151550293</v>
       </c>
       <c r="C336" t="n">
-        <v>19.91351999193534</v>
+        <v>19.91351802765098</v>
       </c>
       <c r="D336" t="n">
-        <v>19.08378992059635</v>
+        <v>19.08378803815718</v>
       </c>
       <c r="E336" t="n">
-        <v>19.64295654875541</v>
+        <v>19.64295461115963</v>
       </c>
       <c r="F336" t="n">
         <v>815000</v>
@@ -7152,16 +7152,16 @@
         <v>44589</v>
       </c>
       <c r="B337" t="n">
-        <v>19.67902946472168</v>
+        <v>19.67903137207031</v>
       </c>
       <c r="C337" t="n">
-        <v>19.67902946472168</v>
+        <v>19.67903137207031</v>
       </c>
       <c r="D337" t="n">
-        <v>18.84929945270756</v>
+        <v>18.84930127963634</v>
       </c>
       <c r="E337" t="n">
-        <v>19.30023963923261</v>
+        <v>19.30024150986784</v>
       </c>
       <c r="F337" t="n">
         <v>645650</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96763038635254</v>
+        <v>19.96763229370117</v>
       </c>
       <c r="C338" t="n">
-        <v>20.27426984278146</v>
+        <v>20.27427177942092</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44453985247972</v>
+        <v>19.44454170986168</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706696959773</v>
+        <v>19.69706885110159</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7232,16 +7232,16 @@
         <v>44595</v>
       </c>
       <c r="B341" t="n">
-        <v>20.12997245788574</v>
+        <v>20.12997055053711</v>
       </c>
       <c r="C341" t="n">
-        <v>20.67110110120321</v>
+        <v>20.67109914258173</v>
       </c>
       <c r="D341" t="n">
-        <v>19.9315593674229</v>
+        <v>19.93155747887424</v>
       </c>
       <c r="E341" t="n">
-        <v>20.43661196509229</v>
+        <v>20.43661002868905</v>
       </c>
       <c r="F341" t="n">
         <v>747450</v>
@@ -7252,16 +7252,16 @@
         <v>44596</v>
       </c>
       <c r="B342" t="n">
-        <v>19.40846633911133</v>
+        <v>19.40846824645996</v>
       </c>
       <c r="C342" t="n">
-        <v>20.18408230211611</v>
+        <v>20.18408428568767</v>
       </c>
       <c r="D342" t="n">
-        <v>19.26416561482205</v>
+        <v>19.26416750798967</v>
       </c>
       <c r="E342" t="n">
-        <v>20.18408230211611</v>
+        <v>20.18408428568767</v>
       </c>
       <c r="F342" t="n">
         <v>774000</v>
@@ -7272,16 +7272,16 @@
         <v>44599</v>
       </c>
       <c r="B343" t="n">
-        <v>19.73314094543457</v>
+        <v>19.73314476013184</v>
       </c>
       <c r="C343" t="n">
-        <v>19.94959373930937</v>
+        <v>19.94959759585004</v>
       </c>
       <c r="D343" t="n">
-        <v>19.0657497048879</v>
+        <v>19.06575339056894</v>
       </c>
       <c r="E343" t="n">
-        <v>19.31827681760835</v>
+        <v>19.31828055210647</v>
       </c>
       <c r="F343" t="n">
         <v>708000</v>
@@ -7372,16 +7372,16 @@
         <v>44606</v>
       </c>
       <c r="B348" t="n">
-        <v>20.00370788574219</v>
+        <v>20.00370597839355</v>
       </c>
       <c r="C348" t="n">
-        <v>20.14800861456807</v>
+        <v>20.1480066934604</v>
       </c>
       <c r="D348" t="n">
-        <v>19.26416622045944</v>
+        <v>19.26416438362593</v>
       </c>
       <c r="E348" t="n">
-        <v>19.26416622045944</v>
+        <v>19.26416438362593</v>
       </c>
       <c r="F348" t="n">
         <v>683300</v>
@@ -7392,16 +7392,16 @@
         <v>44607</v>
       </c>
       <c r="B349" t="n">
-        <v>20.52679634094238</v>
+        <v>20.52680015563965</v>
       </c>
       <c r="C349" t="n">
-        <v>20.70717137327322</v>
+        <v>20.70717522149135</v>
       </c>
       <c r="D349" t="n">
-        <v>20.11193049820109</v>
+        <v>20.11193423579974</v>
       </c>
       <c r="E349" t="n">
-        <v>20.2021188744666</v>
+        <v>20.20212262882585</v>
       </c>
       <c r="F349" t="n">
         <v>560950</v>
@@ -7452,16 +7452,16 @@
         <v>44610</v>
       </c>
       <c r="B352" t="n">
-        <v>19.93155860900879</v>
+        <v>19.93155670166016</v>
       </c>
       <c r="C352" t="n">
-        <v>20.5087615558107</v>
+        <v>20.50875959322669</v>
       </c>
       <c r="D352" t="n">
-        <v>19.64295713560783</v>
+        <v>19.64295525587689</v>
       </c>
       <c r="E352" t="n">
-        <v>20.47268723173582</v>
+        <v>20.47268527260393</v>
       </c>
       <c r="F352" t="n">
         <v>904300</v>
@@ -7472,16 +7472,16 @@
         <v>44613</v>
       </c>
       <c r="B353" t="n">
-        <v>18.66892623901367</v>
+        <v>18.66892433166504</v>
       </c>
       <c r="C353" t="n">
-        <v>19.9495965630065</v>
+        <v>19.94959452481559</v>
       </c>
       <c r="D353" t="n">
-        <v>18.66892623901367</v>
+        <v>18.66892433166504</v>
       </c>
       <c r="E353" t="n">
-        <v>19.85940817282663</v>
+        <v>19.85940614385</v>
       </c>
       <c r="F353" t="n">
         <v>728950</v>
@@ -7512,16 +7512,16 @@
         <v>44615</v>
       </c>
       <c r="B355" t="n">
-        <v>19.66099166870117</v>
+        <v>19.6609935760498</v>
       </c>
       <c r="C355" t="n">
-        <v>20.49072169018069</v>
+        <v>20.49072367802294</v>
       </c>
       <c r="D355" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276888286228</v>
       </c>
       <c r="E355" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940838056108</v>
       </c>
       <c r="F355" t="n">
         <v>1327750</v>
@@ -7532,16 +7532,16 @@
         <v>44616</v>
       </c>
       <c r="B356" t="n">
-        <v>19.33631706237793</v>
+        <v>19.3363151550293</v>
       </c>
       <c r="C356" t="n">
-        <v>19.42650545017138</v>
+        <v>19.4265035339265</v>
       </c>
       <c r="D356" t="n">
-        <v>18.27209787085614</v>
+        <v>18.27209606848287</v>
       </c>
       <c r="E356" t="n">
-        <v>18.52462501263771</v>
+        <v>18.52462318535499</v>
       </c>
       <c r="F356" t="n">
         <v>1831750</v>
@@ -7552,16 +7552,16 @@
         <v>44617</v>
       </c>
       <c r="B357" t="n">
-        <v>19.02967834472656</v>
+        <v>19.0296745300293</v>
       </c>
       <c r="C357" t="n">
-        <v>19.62491931992821</v>
+        <v>19.62491538590869</v>
       </c>
       <c r="D357" t="n">
-        <v>18.65088847685275</v>
+        <v>18.65088473808786</v>
       </c>
       <c r="E357" t="n">
-        <v>19.28220377650878</v>
+        <v>19.28219991119016</v>
       </c>
       <c r="F357" t="n">
         <v>1262850</v>
@@ -7572,16 +7572,16 @@
         <v>44622</v>
       </c>
       <c r="B358" t="n">
-        <v>18.83126068115234</v>
+        <v>18.83126449584961</v>
       </c>
       <c r="C358" t="n">
-        <v>18.90341103931001</v>
+        <v>18.90341486862296</v>
       </c>
       <c r="D358" t="n">
-        <v>18.23601979630157</v>
+        <v>18.23602349041934</v>
       </c>
       <c r="E358" t="n">
-        <v>18.74107402360544</v>
+        <v>18.74107782003336</v>
       </c>
       <c r="F358" t="n">
         <v>1044650</v>
@@ -7612,16 +7612,16 @@
         <v>44624</v>
       </c>
       <c r="B360" t="n">
-        <v>17.91134643554688</v>
+        <v>17.91134452819824</v>
       </c>
       <c r="C360" t="n">
-        <v>18.7591128270115</v>
+        <v>18.75911082938567</v>
       </c>
       <c r="D360" t="n">
-        <v>17.55059287640398</v>
+        <v>17.55059100747137</v>
       </c>
       <c r="E360" t="n">
-        <v>18.5787377676405</v>
+        <v>18.57873578922251</v>
       </c>
       <c r="F360" t="n">
         <v>1669200</v>
@@ -7632,16 +7632,16 @@
         <v>44627</v>
       </c>
       <c r="B361" t="n">
-        <v>16.77497673034668</v>
+        <v>16.77497291564941</v>
       </c>
       <c r="C361" t="n">
-        <v>18.00153297380269</v>
+        <v>18.00152888018159</v>
       </c>
       <c r="D361" t="n">
-        <v>16.77497673034668</v>
+        <v>16.77497291564941</v>
       </c>
       <c r="E361" t="n">
-        <v>17.60470681396126</v>
+        <v>17.60470281058003</v>
       </c>
       <c r="F361" t="n">
         <v>1173850</v>
@@ -7732,16 +7732,16 @@
         <v>44634</v>
       </c>
       <c r="B366" t="n">
-        <v>17.31610488891602</v>
+        <v>17.31610298156738</v>
       </c>
       <c r="C366" t="n">
-        <v>17.67685671572668</v>
+        <v>17.67685476864166</v>
       </c>
       <c r="D366" t="n">
-        <v>16.88320097654281</v>
+        <v>16.88319911687804</v>
       </c>
       <c r="E366" t="n">
-        <v>17.35217921149688</v>
+        <v>17.35217730017471</v>
       </c>
       <c r="F366" t="n">
         <v>989600</v>
@@ -7752,16 +7752,16 @@
         <v>44635</v>
       </c>
       <c r="B367" t="n">
-        <v>17.46040725708008</v>
+        <v>17.46040534973145</v>
       </c>
       <c r="C367" t="n">
-        <v>17.56863195517241</v>
+        <v>17.56863003600147</v>
       </c>
       <c r="D367" t="n">
-        <v>16.93731662909899</v>
+        <v>16.93731477889199</v>
       </c>
       <c r="E367" t="n">
-        <v>17.04554132719132</v>
+        <v>17.04553946516202</v>
       </c>
       <c r="F367" t="n">
         <v>763850</v>
@@ -7772,16 +7772,16 @@
         <v>44636</v>
       </c>
       <c r="B368" t="n">
-        <v>17.53255653381348</v>
+        <v>17.53255462646484</v>
       </c>
       <c r="C368" t="n">
-        <v>18.10975947477838</v>
+        <v>18.10975750463644</v>
       </c>
       <c r="D368" t="n">
-        <v>17.15376667375514</v>
+        <v>17.15376480761467</v>
       </c>
       <c r="E368" t="n">
-        <v>17.58666887947882</v>
+        <v>17.58666696624336</v>
       </c>
       <c r="F368" t="n">
         <v>1212700</v>
@@ -7792,16 +7792,16 @@
         <v>44637</v>
       </c>
       <c r="B369" t="n">
-        <v>18.16387176513672</v>
+        <v>18.16386985778809</v>
       </c>
       <c r="C369" t="n">
-        <v>18.30817249993856</v>
+        <v>18.30817057743722</v>
       </c>
       <c r="D369" t="n">
-        <v>17.17180464342414</v>
+        <v>17.17180284025032</v>
       </c>
       <c r="E369" t="n">
-        <v>17.56863080402899</v>
+        <v>17.56862895918532</v>
       </c>
       <c r="F369" t="n">
         <v>935650</v>
@@ -7812,16 +7812,16 @@
         <v>44638</v>
       </c>
       <c r="B370" t="n">
-        <v>18.4344367980957</v>
+        <v>18.43443489074707</v>
       </c>
       <c r="C370" t="n">
-        <v>18.90341332266845</v>
+        <v>18.90341136679641</v>
       </c>
       <c r="D370" t="n">
-        <v>18.01957089842698</v>
+        <v>18.01956903400312</v>
       </c>
       <c r="E370" t="n">
-        <v>18.16387163217251</v>
+        <v>18.16386975281834</v>
       </c>
       <c r="F370" t="n">
         <v>2000150</v>
@@ -7832,16 +7832,16 @@
         <v>44641</v>
       </c>
       <c r="B371" t="n">
-        <v>18.56069755554199</v>
+        <v>18.56069946289062</v>
       </c>
       <c r="C371" t="n">
-        <v>18.86733701251073</v>
+        <v>18.86733895137048</v>
       </c>
       <c r="D371" t="n">
-        <v>18.23602007870444</v>
+        <v>18.23602195268832</v>
       </c>
       <c r="E371" t="n">
-        <v>18.65088593468579</v>
+        <v>18.65088785130242</v>
       </c>
       <c r="F371" t="n">
         <v>689900</v>
@@ -7852,16 +7852,16 @@
         <v>44642</v>
       </c>
       <c r="B372" t="n">
-        <v>19.40846633911133</v>
+        <v>19.40846824645996</v>
       </c>
       <c r="C372" t="n">
-        <v>19.46257868066973</v>
+        <v>19.4625805933362</v>
       </c>
       <c r="D372" t="n">
-        <v>18.68696099746462</v>
+        <v>18.686962833908</v>
       </c>
       <c r="E372" t="n">
-        <v>18.70499901805086</v>
+        <v>18.70500085626691</v>
       </c>
       <c r="F372" t="n">
         <v>868000</v>
@@ -7872,16 +7872,16 @@
         <v>44643</v>
       </c>
       <c r="B373" t="n">
-        <v>19.60687828063965</v>
+        <v>19.60688018798828</v>
       </c>
       <c r="C373" t="n">
-        <v>19.8052913351097</v>
+        <v>19.80529326175987</v>
       </c>
       <c r="D373" t="n">
-        <v>18.92144901947007</v>
+        <v>18.92145086014044</v>
       </c>
       <c r="E373" t="n">
-        <v>19.48061558417691</v>
+        <v>19.48061747924276</v>
       </c>
       <c r="F373" t="n">
         <v>823600</v>
@@ -7912,16 +7912,16 @@
         <v>44645</v>
       </c>
       <c r="B375" t="n">
-        <v>21.19418716430664</v>
+        <v>21.19418907165527</v>
       </c>
       <c r="C375" t="n">
-        <v>21.44671426894065</v>
+        <v>21.4467161990152</v>
       </c>
       <c r="D375" t="n">
-        <v>20.81539736745571</v>
+        <v>20.81539924071555</v>
       </c>
       <c r="E375" t="n">
-        <v>20.92362376092747</v>
+        <v>20.92362564392704</v>
       </c>
       <c r="F375" t="n">
         <v>911550</v>
@@ -7932,16 +7932,16 @@
         <v>44648</v>
       </c>
       <c r="B376" t="n">
-        <v>21.33849143981934</v>
+        <v>21.3384895324707</v>
       </c>
       <c r="C376" t="n">
-        <v>22.11410918202458</v>
+        <v>22.11410720534708</v>
       </c>
       <c r="D376" t="n">
-        <v>21.08596429300356</v>
+        <v>21.08596240822715</v>
       </c>
       <c r="E376" t="n">
-        <v>21.55494254271838</v>
+        <v>21.55494061602219</v>
       </c>
       <c r="F376" t="n">
         <v>980450</v>
@@ -7952,16 +7952,16 @@
         <v>44649</v>
       </c>
       <c r="B377" t="n">
-        <v>21.91569328308105</v>
+        <v>21.91569519042969</v>
       </c>
       <c r="C377" t="n">
-        <v>22.36663348824898</v>
+        <v>22.36663543484347</v>
       </c>
       <c r="D377" t="n">
-        <v>21.66316786911525</v>
+        <v>21.6631697544863</v>
       </c>
       <c r="E377" t="n">
-        <v>21.66316786911525</v>
+        <v>21.6631697544863</v>
       </c>
       <c r="F377" t="n">
         <v>1103500</v>
@@ -7992,16 +7992,16 @@
         <v>44651</v>
       </c>
       <c r="B379" t="n">
-        <v>21.17614936828613</v>
+        <v>21.17615127563477</v>
       </c>
       <c r="C379" t="n">
-        <v>21.77139023814663</v>
+        <v>21.77139219910897</v>
       </c>
       <c r="D379" t="n">
-        <v>21.04988667474002</v>
+        <v>21.0498885707161</v>
       </c>
       <c r="E379" t="n">
-        <v>21.6090515063301</v>
+        <v>21.60905345267049</v>
       </c>
       <c r="F379" t="n">
         <v>849150</v>
@@ -8012,16 +8012,16 @@
         <v>44652</v>
       </c>
       <c r="B380" t="n">
-        <v>21.7894287109375</v>
+        <v>21.78943061828613</v>
       </c>
       <c r="C380" t="n">
-        <v>21.84354104926957</v>
+        <v>21.84354296135495</v>
       </c>
       <c r="D380" t="n">
-        <v>21.17614980917333</v>
+        <v>21.17615166283828</v>
       </c>
       <c r="E380" t="n">
-        <v>21.42867692172335</v>
+        <v>21.42867879749339</v>
       </c>
       <c r="F380" t="n">
         <v>746250</v>
@@ -8032,16 +8032,16 @@
         <v>44655</v>
       </c>
       <c r="B381" t="n">
-        <v>21.89765739440918</v>
+        <v>21.89765548706055</v>
       </c>
       <c r="C381" t="n">
-        <v>21.91569369560312</v>
+        <v>21.91569178668347</v>
       </c>
       <c r="D381" t="n">
-        <v>21.32045275119318</v>
+        <v>21.32045089412073</v>
       </c>
       <c r="E381" t="n">
-        <v>21.78943098624356</v>
+        <v>21.78942908832175</v>
       </c>
       <c r="F381" t="n">
         <v>503500</v>
@@ -8052,16 +8052,16 @@
         <v>44656</v>
       </c>
       <c r="B382" t="n">
-        <v>20.70717239379883</v>
+        <v>20.70717430114746</v>
       </c>
       <c r="C382" t="n">
-        <v>21.87961790263256</v>
+        <v>21.87961991797578</v>
       </c>
       <c r="D382" t="n">
-        <v>20.59894771310666</v>
+        <v>20.59894961048666</v>
       </c>
       <c r="E382" t="n">
-        <v>21.78942952192223</v>
+        <v>21.78943152895814</v>
       </c>
       <c r="F382" t="n">
         <v>1118400</v>
@@ -8092,16 +8092,16 @@
         <v>44658</v>
       </c>
       <c r="B384" t="n">
-        <v>19.66099166870117</v>
+        <v>19.6609935760498</v>
       </c>
       <c r="C384" t="n">
-        <v>20.00370717768201</v>
+        <v>20.0037091182781</v>
       </c>
       <c r="D384" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276888286228</v>
       </c>
       <c r="E384" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940838056108</v>
       </c>
       <c r="F384" t="n">
         <v>978600</v>
@@ -8132,16 +8132,16 @@
         <v>44662</v>
       </c>
       <c r="B386" t="n">
-        <v>18.93948745727539</v>
+        <v>18.93948936462402</v>
       </c>
       <c r="C386" t="n">
-        <v>19.37238961487934</v>
+        <v>19.37239156582447</v>
       </c>
       <c r="D386" t="n">
-        <v>18.86733709767473</v>
+        <v>18.86733899775728</v>
       </c>
       <c r="E386" t="n">
-        <v>19.24612691562825</v>
+        <v>19.24612885385778</v>
       </c>
       <c r="F386" t="n">
         <v>1033000</v>
@@ -8152,16 +8152,16 @@
         <v>44663</v>
       </c>
       <c r="B387" t="n">
-        <v>19.13790130615234</v>
+        <v>19.13789939880371</v>
       </c>
       <c r="C387" t="n">
-        <v>19.84136863144855</v>
+        <v>19.84136665398996</v>
       </c>
       <c r="D387" t="n">
-        <v>18.9936005809942</v>
+        <v>18.99359868802707</v>
       </c>
       <c r="E387" t="n">
-        <v>19.33631609339504</v>
+        <v>19.33631416627171</v>
       </c>
       <c r="F387" t="n">
         <v>1155250</v>
@@ -8232,16 +8232,16 @@
         <v>44670</v>
       </c>
       <c r="B391" t="n">
-        <v>20.32838249206543</v>
+        <v>20.32838439941406</v>
       </c>
       <c r="C391" t="n">
-        <v>20.34641879045101</v>
+        <v>20.34642069949194</v>
       </c>
       <c r="D391" t="n">
-        <v>19.01163637871046</v>
+        <v>19.01163816251292</v>
       </c>
       <c r="E391" t="n">
-        <v>19.55276489488099</v>
+        <v>19.55276672945585</v>
       </c>
       <c r="F391" t="n">
         <v>1459950</v>
@@ -8252,16 +8252,16 @@
         <v>44671</v>
       </c>
       <c r="B392" t="n">
-        <v>20.61698722839355</v>
+        <v>20.61698532104492</v>
       </c>
       <c r="C392" t="n">
-        <v>20.79736228269439</v>
+        <v>20.79736035865864</v>
       </c>
       <c r="D392" t="n">
-        <v>20.11193294787024</v>
+        <v>20.11193108724592</v>
       </c>
       <c r="E392" t="n">
-        <v>20.34642206664169</v>
+        <v>20.34642018432397</v>
       </c>
       <c r="F392" t="n">
         <v>1230400</v>
@@ -8312,16 +8312,16 @@
         <v>44677</v>
       </c>
       <c r="B395" t="n">
-        <v>19.06575202941895</v>
+        <v>19.06575012207031</v>
       </c>
       <c r="C395" t="n">
-        <v>19.39042953961619</v>
+        <v>19.39042759978664</v>
       </c>
       <c r="D395" t="n">
-        <v>18.68696217425563</v>
+        <v>18.68696030480135</v>
       </c>
       <c r="E395" t="n">
-        <v>19.19201646127367</v>
+        <v>19.19201454129347</v>
       </c>
       <c r="F395" t="n">
         <v>972150</v>
@@ -8352,16 +8352,16 @@
         <v>44679</v>
       </c>
       <c r="B397" t="n">
-        <v>21.04988861083984</v>
+        <v>21.04988670349121</v>
       </c>
       <c r="C397" t="n">
-        <v>21.10400095302237</v>
+        <v>21.10399904077057</v>
       </c>
       <c r="D397" t="n">
-        <v>19.30024015840165</v>
+        <v>19.30023840959018</v>
       </c>
       <c r="E397" t="n">
-        <v>19.84136874082794</v>
+        <v>19.84136694298433</v>
       </c>
       <c r="F397" t="n">
         <v>1501350</v>
@@ -8372,16 +8372,16 @@
         <v>44680</v>
       </c>
       <c r="B398" t="n">
-        <v>21.04988861083984</v>
+        <v>21.04988670349121</v>
       </c>
       <c r="C398" t="n">
-        <v>21.60905349386008</v>
+        <v>21.60905153584503</v>
       </c>
       <c r="D398" t="n">
-        <v>20.90558788488621</v>
+        <v>20.90558599061279</v>
       </c>
       <c r="E398" t="n">
-        <v>21.60905349386008</v>
+        <v>21.60905153584503</v>
       </c>
       <c r="F398" t="n">
         <v>1651000</v>
@@ -8412,16 +8412,16 @@
         <v>44684</v>
       </c>
       <c r="B400" t="n">
-        <v>19.84136772155762</v>
+        <v>19.84136962890625</v>
       </c>
       <c r="C400" t="n">
-        <v>20.63502167353181</v>
+        <v>20.63502365717432</v>
       </c>
       <c r="D400" t="n">
-        <v>19.75117934241958</v>
+        <v>19.75118124109841</v>
       </c>
       <c r="E400" t="n">
-        <v>20.47268465532364</v>
+        <v>20.4726866233607</v>
       </c>
       <c r="F400" t="n">
         <v>1374100</v>
@@ -8452,16 +8452,16 @@
         <v>44686</v>
       </c>
       <c r="B402" t="n">
-        <v>20.09389495849609</v>
+        <v>20.09389305114746</v>
       </c>
       <c r="C402" t="n">
-        <v>20.47268477696631</v>
+        <v>20.47268283366227</v>
       </c>
       <c r="D402" t="n">
-        <v>19.73314143980044</v>
+        <v>19.73313956669518</v>
       </c>
       <c r="E402" t="n">
-        <v>20.41857071704181</v>
+        <v>20.41856877887437</v>
       </c>
       <c r="F402" t="n">
         <v>1134600</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.5190315246582</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C403" t="n">
-        <v>19.9347326068735</v>
+        <v>19.93473455484336</v>
       </c>
       <c r="D403" t="n">
-        <v>18.81989895121317</v>
+        <v>18.8199007902444</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019522691586</v>
+        <v>19.67019714903581</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8512,16 +8512,16 @@
         <v>44691</v>
       </c>
       <c r="B405" t="n">
-        <v>19.1600170135498</v>
+        <v>19.16001892089844</v>
       </c>
       <c r="C405" t="n">
-        <v>19.38676255310495</v>
+        <v>19.38676448302573</v>
       </c>
       <c r="D405" t="n">
-        <v>18.6120481757882</v>
+        <v>18.61205002858743</v>
       </c>
       <c r="E405" t="n">
-        <v>19.04664334276555</v>
+        <v>19.04664523882802</v>
       </c>
       <c r="F405" t="n">
         <v>1243050</v>
@@ -8632,16 +8632,16 @@
         <v>44699</v>
       </c>
       <c r="B411" t="n">
-        <v>20.36932945251465</v>
+        <v>20.36932754516602</v>
       </c>
       <c r="C411" t="n">
-        <v>20.76613465362919</v>
+        <v>20.76613270912441</v>
       </c>
       <c r="D411" t="n">
-        <v>20.10479385311404</v>
+        <v>20.10479197053606</v>
       </c>
       <c r="E411" t="n">
-        <v>20.44491130977391</v>
+        <v>20.44490939534792</v>
       </c>
       <c r="F411" t="n">
         <v>1338150</v>
@@ -8672,16 +8672,16 @@
         <v>44701</v>
       </c>
       <c r="B413" t="n">
-        <v>20.65275955200195</v>
+        <v>20.65276145935059</v>
       </c>
       <c r="C413" t="n">
-        <v>21.08735471304948</v>
+        <v>21.08735666053437</v>
       </c>
       <c r="D413" t="n">
-        <v>20.25595441269131</v>
+        <v>20.25595628339371</v>
       </c>
       <c r="E413" t="n">
-        <v>21.03066877943749</v>
+        <v>21.03067072168725</v>
       </c>
       <c r="F413" t="n">
         <v>1756800</v>
@@ -8692,16 +8692,16 @@
         <v>44704</v>
       </c>
       <c r="B414" t="n">
-        <v>20.82282257080078</v>
+        <v>20.82282066345215</v>
       </c>
       <c r="C414" t="n">
-        <v>21.1629400302818</v>
+        <v>21.16293809177876</v>
       </c>
       <c r="D414" t="n">
-        <v>20.61497111010355</v>
+        <v>20.61496922179389</v>
       </c>
       <c r="E414" t="n">
-        <v>20.78503074085087</v>
+        <v>20.78502883696393</v>
       </c>
       <c r="F414" t="n">
         <v>1655200</v>
@@ -8712,16 +8712,16 @@
         <v>44705</v>
       </c>
       <c r="B415" t="n">
-        <v>20.38822364807129</v>
+        <v>20.38822555541992</v>
       </c>
       <c r="C415" t="n">
-        <v>20.78502881572475</v>
+        <v>20.7850307601951</v>
       </c>
       <c r="D415" t="n">
-        <v>19.93473254275689</v>
+        <v>19.93473440768075</v>
       </c>
       <c r="E415" t="n">
-        <v>20.59607328750369</v>
+        <v>20.59607521429696</v>
       </c>
       <c r="F415" t="n">
         <v>1381900</v>
@@ -8752,16 +8752,16 @@
         <v>44707</v>
       </c>
       <c r="B417" t="n">
-        <v>21.18183326721191</v>
+        <v>21.18183517456055</v>
       </c>
       <c r="C417" t="n">
-        <v>21.27631102812812</v>
+        <v>21.27631294398413</v>
       </c>
       <c r="D417" t="n">
-        <v>20.67165443947247</v>
+        <v>20.67165630088131</v>
       </c>
       <c r="E417" t="n">
-        <v>20.82281993814643</v>
+        <v>20.8228218131672</v>
       </c>
       <c r="F417" t="n">
         <v>1373550</v>
@@ -8772,16 +8772,16 @@
         <v>44708</v>
       </c>
       <c r="B418" t="n">
-        <v>22.78795051574707</v>
+        <v>22.7879524230957</v>
       </c>
       <c r="C418" t="n">
-        <v>22.86353236646209</v>
+        <v>22.86353428013691</v>
       </c>
       <c r="D418" t="n">
-        <v>21.35189355014821</v>
+        <v>21.35189533729906</v>
       </c>
       <c r="E418" t="n">
-        <v>21.59753501547539</v>
+        <v>21.5975368231864</v>
       </c>
       <c r="F418" t="n">
         <v>2973300</v>
@@ -8812,16 +8812,16 @@
         <v>44712</v>
       </c>
       <c r="B420" t="n">
-        <v>22.52341270446777</v>
+        <v>22.52341461181641</v>
       </c>
       <c r="C420" t="n">
-        <v>22.76905416507515</v>
+        <v>22.76905609322542</v>
       </c>
       <c r="D420" t="n">
-        <v>21.99433975962836</v>
+        <v>21.99434162217354</v>
       </c>
       <c r="E420" t="n">
-        <v>22.23998122023573</v>
+        <v>22.23998310358255</v>
       </c>
       <c r="F420" t="n">
         <v>1969900</v>
@@ -8852,16 +8852,16 @@
         <v>44714</v>
       </c>
       <c r="B422" t="n">
-        <v>23.37371063232422</v>
+        <v>23.37370872497559</v>
       </c>
       <c r="C422" t="n">
-        <v>24.31848471674483</v>
+        <v>24.31848273230045</v>
       </c>
       <c r="D422" t="n">
-        <v>23.24144283714967</v>
+        <v>23.24144094059439</v>
       </c>
       <c r="E422" t="n">
-        <v>23.43039657282566</v>
+        <v>23.43039466085132</v>
       </c>
       <c r="F422" t="n">
         <v>1968350</v>
@@ -8892,16 +8892,16 @@
         <v>44718</v>
       </c>
       <c r="B424" t="n">
-        <v>22.03212928771973</v>
+        <v>22.03213119506836</v>
       </c>
       <c r="C424" t="n">
-        <v>22.63678406822239</v>
+        <v>22.63678602791673</v>
       </c>
       <c r="D424" t="n">
-        <v>21.52195226717395</v>
+        <v>21.52195413035593</v>
       </c>
       <c r="E424" t="n">
-        <v>22.52341219788483</v>
+        <v>22.52341414776443</v>
       </c>
       <c r="F424" t="n">
         <v>1535250</v>
@@ -8932,16 +8932,16 @@
         <v>44720</v>
       </c>
       <c r="B426" t="n">
-        <v>21.20073127746582</v>
+        <v>21.20072937011719</v>
       </c>
       <c r="C426" t="n">
-        <v>21.82428203839009</v>
+        <v>21.82428007494298</v>
       </c>
       <c r="D426" t="n">
-        <v>21.0306716513931</v>
+        <v>21.03066975934408</v>
       </c>
       <c r="E426" t="n">
-        <v>21.48416278624464</v>
+        <v>21.48416085339676</v>
       </c>
       <c r="F426" t="n">
         <v>863650</v>
@@ -8952,16 +8952,16 @@
         <v>44721</v>
       </c>
       <c r="B427" t="n">
-        <v>21.54084968566895</v>
+        <v>21.54084777832031</v>
       </c>
       <c r="C427" t="n">
-        <v>21.72980523460138</v>
+        <v>21.72980331052155</v>
       </c>
       <c r="D427" t="n">
-        <v>20.89840478372873</v>
+        <v>20.8984029332658</v>
       </c>
       <c r="E427" t="n">
-        <v>21.20073222040969</v>
+        <v>21.20073034317699</v>
       </c>
       <c r="F427" t="n">
         <v>1117750</v>
@@ -9032,16 +9032,16 @@
         <v>44727</v>
       </c>
       <c r="B431" t="n">
-        <v>19.65130233764648</v>
+        <v>19.65130043029785</v>
       </c>
       <c r="C431" t="n">
-        <v>19.82136197935914</v>
+        <v>19.82136005550457</v>
       </c>
       <c r="D431" t="n">
-        <v>19.17891524489523</v>
+        <v>19.17891338339633</v>
       </c>
       <c r="E431" t="n">
-        <v>19.44345266556088</v>
+        <v>19.44345077838607</v>
       </c>
       <c r="F431" t="n">
         <v>990050</v>
@@ -9072,16 +9072,16 @@
         <v>44732</v>
       </c>
       <c r="B433" t="n">
-        <v>18.6120491027832</v>
+        <v>18.61205101013184</v>
       </c>
       <c r="C433" t="n">
-        <v>19.4812412820424</v>
+        <v>19.48124327846519</v>
       </c>
       <c r="D433" t="n">
-        <v>18.51757133942631</v>
+        <v>18.51757323709293</v>
       </c>
       <c r="E433" t="n">
-        <v>19.14112205476297</v>
+        <v>19.14112401633059</v>
       </c>
       <c r="F433" t="n">
         <v>828950</v>
@@ -9112,16 +9112,16 @@
         <v>44734</v>
       </c>
       <c r="B435" t="n">
-        <v>18.6120491027832</v>
+        <v>18.61205101013184</v>
       </c>
       <c r="C435" t="n">
-        <v>18.83879465363167</v>
+        <v>18.83879658421702</v>
       </c>
       <c r="D435" t="n">
-        <v>18.15855619907281</v>
+        <v>18.15855805994783</v>
       </c>
       <c r="E435" t="n">
-        <v>18.38530174992128</v>
+        <v>18.38530363403301</v>
       </c>
       <c r="F435" t="n">
         <v>1143850</v>
@@ -9132,16 +9132,16 @@
         <v>44735</v>
       </c>
       <c r="B436" t="n">
-        <v>18.81990051269531</v>
+        <v>18.81989860534668</v>
       </c>
       <c r="C436" t="n">
-        <v>18.89548237009515</v>
+        <v>18.89548045508649</v>
       </c>
       <c r="D436" t="n">
-        <v>18.4986771682426</v>
+        <v>18.49867529344914</v>
       </c>
       <c r="E436" t="n">
-        <v>18.72542274044211</v>
+        <v>18.72542084266856</v>
       </c>
       <c r="F436" t="n">
         <v>1280500</v>
@@ -9152,16 +9152,16 @@
         <v>44736</v>
       </c>
       <c r="B437" t="n">
-        <v>18.47978210449219</v>
+        <v>18.47978019714355</v>
       </c>
       <c r="C437" t="n">
-        <v>18.95216918550078</v>
+        <v>18.95216722939579</v>
       </c>
       <c r="D437" t="n">
-        <v>18.23414060612608</v>
+        <v>18.23413872413077</v>
       </c>
       <c r="E437" t="n">
-        <v>18.95216918550078</v>
+        <v>18.95216722939579</v>
       </c>
       <c r="F437" t="n">
         <v>1255000</v>
@@ -9172,16 +9172,16 @@
         <v>44739</v>
       </c>
       <c r="B438" t="n">
-        <v>18.55536079406738</v>
+        <v>18.55536460876465</v>
       </c>
       <c r="C438" t="n">
-        <v>18.70652448999358</v>
+        <v>18.70652833576777</v>
       </c>
       <c r="D438" t="n">
-        <v>18.38530118564707</v>
+        <v>18.38530496538269</v>
       </c>
       <c r="E438" t="n">
-        <v>18.57425670656151</v>
+        <v>18.57426052514348</v>
       </c>
       <c r="F438" t="n">
         <v>799000</v>
@@ -9212,16 +9212,16 @@
         <v>44741</v>
       </c>
       <c r="B440" t="n">
-        <v>17.81843948364258</v>
+        <v>17.81843757629395</v>
       </c>
       <c r="C440" t="n">
-        <v>18.13966281064456</v>
+        <v>18.13966086891105</v>
       </c>
       <c r="D440" t="n">
-        <v>17.51611207046742</v>
+        <v>17.51611019548098</v>
       </c>
       <c r="E440" t="n">
-        <v>18.13966281064456</v>
+        <v>18.13966086891105</v>
       </c>
       <c r="F440" t="n">
         <v>939650</v>
@@ -9272,16 +9272,16 @@
         <v>44746</v>
       </c>
       <c r="B443" t="n">
-        <v>17.28936386108398</v>
+        <v>17.28936576843262</v>
       </c>
       <c r="C443" t="n">
-        <v>17.64837899814145</v>
+        <v>17.64838094509635</v>
       </c>
       <c r="D443" t="n">
-        <v>17.25157383729624</v>
+        <v>17.25157574047591</v>
       </c>
       <c r="E443" t="n">
-        <v>17.44052756026183</v>
+        <v>17.44052948428672</v>
       </c>
       <c r="F443" t="n">
         <v>903450</v>
@@ -9292,16 +9292,16 @@
         <v>44747</v>
       </c>
       <c r="B444" t="n">
-        <v>17.10041046142578</v>
+        <v>17.10041236877441</v>
       </c>
       <c r="C444" t="n">
-        <v>17.25157416346159</v>
+        <v>17.25157608767075</v>
       </c>
       <c r="D444" t="n">
-        <v>16.57133750430044</v>
+        <v>16.57133935263724</v>
       </c>
       <c r="E444" t="n">
-        <v>17.15709639918584</v>
+        <v>17.15709831285712</v>
       </c>
       <c r="F444" t="n">
         <v>2077700</v>
@@ -9332,16 +9332,16 @@
         <v>44749</v>
       </c>
       <c r="B446" t="n">
-        <v>17.66727638244629</v>
+        <v>17.66727447509766</v>
       </c>
       <c r="C446" t="n">
-        <v>18.13966343222278</v>
+        <v>18.13966147387552</v>
       </c>
       <c r="D446" t="n">
-        <v>17.49721675620458</v>
+        <v>17.49721486721548</v>
       </c>
       <c r="E446" t="n">
-        <v>17.5161126706789</v>
+        <v>17.51611077964981</v>
       </c>
       <c r="F446" t="n">
         <v>1515500</v>
@@ -9352,16 +9352,16 @@
         <v>44750</v>
       </c>
       <c r="B447" t="n">
-        <v>17.72396278381348</v>
+        <v>17.72396087646484</v>
       </c>
       <c r="C447" t="n">
-        <v>18.12076798800384</v>
+        <v>18.12076603795336</v>
       </c>
       <c r="D447" t="n">
-        <v>17.64838092596834</v>
+        <v>17.64837902675339</v>
       </c>
       <c r="E447" t="n">
-        <v>17.8184405566233</v>
+        <v>17.81843863910753</v>
       </c>
       <c r="F447" t="n">
         <v>701700</v>
@@ -9372,16 +9372,16 @@
         <v>44753</v>
       </c>
       <c r="B448" t="n">
-        <v>16.76029205322266</v>
+        <v>16.76029014587402</v>
       </c>
       <c r="C448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61058636528556</v>
       </c>
       <c r="D448" t="n">
-        <v>16.62802425795465</v>
+        <v>16.62802236565831</v>
       </c>
       <c r="E448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61058636528556</v>
       </c>
       <c r="F448" t="n">
         <v>1587350</v>
@@ -9392,16 +9392,16 @@
         <v>44754</v>
       </c>
       <c r="B449" t="n">
-        <v>16.60912895202637</v>
+        <v>16.60912704467773</v>
       </c>
       <c r="C449" t="n">
-        <v>16.87366635426378</v>
+        <v>16.87366441653637</v>
       </c>
       <c r="D449" t="n">
-        <v>16.19342783480004</v>
+        <v>16.19342597518942</v>
       </c>
       <c r="E449" t="n">
-        <v>16.79808449676932</v>
+        <v>16.79808256772154</v>
       </c>
       <c r="F449" t="n">
         <v>1842850</v>
@@ -9432,16 +9432,16 @@
         <v>44756</v>
       </c>
       <c r="B451" t="n">
-        <v>17.02482986450195</v>
+        <v>17.02482795715332</v>
       </c>
       <c r="C451" t="n">
-        <v>17.13820174837335</v>
+        <v>17.13819982832328</v>
       </c>
       <c r="D451" t="n">
-        <v>16.53354689568962</v>
+        <v>16.53354504338107</v>
       </c>
       <c r="E451" t="n">
-        <v>16.70360652351032</v>
+        <v>16.70360465214942</v>
       </c>
       <c r="F451" t="n">
         <v>750250</v>
@@ -9492,16 +9492,16 @@
         <v>44761</v>
       </c>
       <c r="B454" t="n">
-        <v>17.28936386108398</v>
+        <v>17.28936576843262</v>
       </c>
       <c r="C454" t="n">
-        <v>17.51611121186419</v>
+        <v>17.51611314422741</v>
       </c>
       <c r="D454" t="n">
-        <v>17.10041013811839</v>
+        <v>17.1004120246218</v>
       </c>
       <c r="E454" t="n">
-        <v>17.10041013811839</v>
+        <v>17.1004120246218</v>
       </c>
       <c r="F454" t="n">
         <v>816100</v>
@@ -9512,16 +9512,16 @@
         <v>44762</v>
       </c>
       <c r="B455" t="n">
-        <v>17.96960067749023</v>
+        <v>17.96960258483887</v>
       </c>
       <c r="C455" t="n">
-        <v>18.02628660903064</v>
+        <v>18.02628852239609</v>
       </c>
       <c r="D455" t="n">
-        <v>17.23267635941185</v>
+        <v>17.23267818854108</v>
       </c>
       <c r="E455" t="n">
-        <v>17.25157227059641</v>
+        <v>17.25157410173131</v>
       </c>
       <c r="F455" t="n">
         <v>812650</v>
@@ -9572,16 +9572,16 @@
         <v>44767</v>
       </c>
       <c r="B458" t="n">
-        <v>17.95070838928223</v>
+        <v>17.95070648193359</v>
       </c>
       <c r="C458" t="n">
-        <v>18.30972176418187</v>
+        <v>18.30971981868635</v>
       </c>
       <c r="D458" t="n">
-        <v>17.87512653130264</v>
+        <v>17.87512463198494</v>
       </c>
       <c r="E458" t="n">
-        <v>18.177453963221</v>
+        <v>18.17745203177956</v>
       </c>
       <c r="F458" t="n">
         <v>615900</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.5190315246582</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65129931363029</v>
+        <v>19.65130123390378</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431710008434</v>
+        <v>18.74431893172991</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658488905642</v>
+        <v>18.87658673362685</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9712,16 +9712,16 @@
         <v>44776</v>
       </c>
       <c r="B465" t="n">
-        <v>19.68909072875977</v>
+        <v>19.6890926361084</v>
       </c>
       <c r="C465" t="n">
-        <v>19.74577666541846</v>
+        <v>19.74577857825845</v>
       </c>
       <c r="D465" t="n">
-        <v>19.02774819369244</v>
+        <v>19.02775003697459</v>
       </c>
       <c r="E465" t="n">
-        <v>19.08443593236457</v>
+        <v>19.08443778113825</v>
       </c>
       <c r="F465" t="n">
         <v>1095050</v>
@@ -9772,16 +9772,16 @@
         <v>44781</v>
       </c>
       <c r="B468" t="n">
-        <v>21.54084968566895</v>
+        <v>21.54084777832031</v>
       </c>
       <c r="C468" t="n">
-        <v>21.84317892436357</v>
+        <v>21.843176990245</v>
       </c>
       <c r="D468" t="n">
-        <v>21.01177667147726</v>
+        <v>21.01177481097574</v>
       </c>
       <c r="E468" t="n">
-        <v>21.21962633369201</v>
+        <v>21.21962445478631</v>
       </c>
       <c r="F468" t="n">
         <v>1786950</v>
@@ -9812,16 +9812,16 @@
         <v>44783</v>
       </c>
       <c r="B470" t="n">
-        <v>21.82427978515625</v>
+        <v>21.82428169250488</v>
       </c>
       <c r="C470" t="n">
-        <v>22.12660717717701</v>
+        <v>22.12660911094776</v>
       </c>
       <c r="D470" t="n">
-        <v>21.08735541559559</v>
+        <v>21.08735725854019</v>
       </c>
       <c r="E470" t="n">
-        <v>21.16293726360078</v>
+        <v>21.16293911315091</v>
       </c>
       <c r="F470" t="n">
         <v>1851300</v>
@@ -9832,16 +9832,16 @@
         <v>44784</v>
       </c>
       <c r="B471" t="n">
-        <v>22.01323509216309</v>
+        <v>22.01323699951172</v>
       </c>
       <c r="C471" t="n">
-        <v>22.08881694562063</v>
+        <v>22.0888188595181</v>
       </c>
       <c r="D471" t="n">
-        <v>21.54084805755003</v>
+        <v>21.54084992396843</v>
       </c>
       <c r="E471" t="n">
-        <v>21.82428135952598</v>
+        <v>21.82428325050261</v>
       </c>
       <c r="F471" t="n">
         <v>1242750</v>
@@ -9952,16 +9952,16 @@
         <v>44792</v>
       </c>
       <c r="B477" t="n">
-        <v>21.16293907165527</v>
+        <v>21.16293716430664</v>
       </c>
       <c r="C477" t="n">
-        <v>22.16439909378708</v>
+        <v>22.16439709618003</v>
       </c>
       <c r="D477" t="n">
-        <v>20.97398533650574</v>
+        <v>20.97398344618691</v>
       </c>
       <c r="E477" t="n">
-        <v>22.16439909378708</v>
+        <v>22.16439709618003</v>
       </c>
       <c r="F477" t="n">
         <v>1251050</v>
@@ -10012,16 +10012,16 @@
         <v>44797</v>
       </c>
       <c r="B480" t="n">
-        <v>20.80392456054688</v>
+        <v>20.80392646789551</v>
       </c>
       <c r="C480" t="n">
-        <v>21.16293789884462</v>
+        <v>21.16293983910836</v>
       </c>
       <c r="D480" t="n">
-        <v>20.48270124637937</v>
+        <v>20.48270312427755</v>
       </c>
       <c r="E480" t="n">
-        <v>20.76613273440319</v>
+        <v>20.76613463828699</v>
       </c>
       <c r="F480" t="n">
         <v>1050450</v>
@@ -10172,16 +10172,16 @@
         <v>44809</v>
       </c>
       <c r="B488" t="n">
-        <v>21.72980308532715</v>
+        <v>21.72980499267578</v>
       </c>
       <c r="C488" t="n">
-        <v>21.84317676387566</v>
+        <v>21.84317868117574</v>
       </c>
       <c r="D488" t="n">
-        <v>20.87950680326052</v>
+        <v>20.8795086359738</v>
       </c>
       <c r="E488" t="n">
-        <v>21.01177459322254</v>
+        <v>21.01177643754573</v>
       </c>
       <c r="F488" t="n">
         <v>878600</v>
@@ -10232,16 +10232,16 @@
         <v>44813</v>
       </c>
       <c r="B491" t="n">
-        <v>20.25595664978027</v>
+        <v>20.25595474243164</v>
       </c>
       <c r="C491" t="n">
-        <v>20.29374667569073</v>
+        <v>20.2937447647837</v>
       </c>
       <c r="D491" t="n">
-        <v>19.42455445558783</v>
+        <v>19.42455262652599</v>
       </c>
       <c r="E491" t="n">
-        <v>19.9158374065185</v>
+        <v>19.9158355311963</v>
       </c>
       <c r="F491" t="n">
         <v>1292000</v>
@@ -10252,16 +10252,16 @@
         <v>44816</v>
       </c>
       <c r="B492" t="n">
-        <v>20.65275955200195</v>
+        <v>20.65276145935059</v>
       </c>
       <c r="C492" t="n">
-        <v>21.1251465367997</v>
+        <v>21.12514848777479</v>
       </c>
       <c r="D492" t="n">
-        <v>20.42601401554063</v>
+        <v>20.42601590194859</v>
       </c>
       <c r="E492" t="n">
-        <v>20.44490812540241</v>
+        <v>20.44491001355529</v>
       </c>
       <c r="F492" t="n">
         <v>1299050</v>
@@ -10272,16 +10272,16 @@
         <v>44817</v>
       </c>
       <c r="B493" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577903747559</v>
       </c>
       <c r="C493" t="n">
-        <v>20.27485008942426</v>
+        <v>20.27485204787884</v>
       </c>
       <c r="D493" t="n">
-        <v>19.57571751413516</v>
+        <v>19.57571940505684</v>
       </c>
       <c r="E493" t="n">
-        <v>20.12368638676789</v>
+        <v>20.12368833062077</v>
       </c>
       <c r="F493" t="n">
         <v>1035100</v>
@@ -10292,16 +10292,16 @@
         <v>44818</v>
       </c>
       <c r="B494" t="n">
-        <v>20.4260139465332</v>
+        <v>20.42601585388184</v>
       </c>
       <c r="C494" t="n">
-        <v>20.5204899015629</v>
+        <v>20.52049181773355</v>
       </c>
       <c r="D494" t="n">
-        <v>19.51903000173875</v>
+        <v>19.51903182439467</v>
       </c>
       <c r="E494" t="n">
-        <v>19.70798551582482</v>
+        <v>19.7079873561251</v>
       </c>
       <c r="F494" t="n">
         <v>1153500</v>
@@ -10312,16 +10312,16 @@
         <v>44819</v>
       </c>
       <c r="B495" t="n">
-        <v>20.4071216583252</v>
+        <v>20.40711975097656</v>
       </c>
       <c r="C495" t="n">
-        <v>20.61497131911616</v>
+        <v>20.61496939234089</v>
       </c>
       <c r="D495" t="n">
-        <v>19.99142053472962</v>
+        <v>19.99141866623443</v>
       </c>
       <c r="E495" t="n">
-        <v>20.44491168664462</v>
+        <v>20.44490977576395</v>
       </c>
       <c r="F495" t="n">
         <v>753500</v>
@@ -10332,16 +10332,16 @@
         <v>44820</v>
       </c>
       <c r="B496" t="n">
-        <v>20.02921104431152</v>
+        <v>20.02920913696289</v>
       </c>
       <c r="C496" t="n">
-        <v>20.27485071722412</v>
+        <v>20.27484878648363</v>
       </c>
       <c r="D496" t="n">
-        <v>19.55682400837977</v>
+        <v>19.55682214601578</v>
       </c>
       <c r="E496" t="n">
-        <v>20.27485071722412</v>
+        <v>20.27484878648363</v>
       </c>
       <c r="F496" t="n">
         <v>1629800</v>
@@ -10352,16 +10352,16 @@
         <v>44823</v>
       </c>
       <c r="B497" t="n">
-        <v>20.36932945251465</v>
+        <v>20.36932754516602</v>
       </c>
       <c r="C497" t="n">
-        <v>20.52049316703318</v>
+        <v>20.52049124552984</v>
       </c>
       <c r="D497" t="n">
-        <v>19.85915236651802</v>
+        <v>19.85915050694149</v>
       </c>
       <c r="E497" t="n">
-        <v>19.93473422377729</v>
+        <v>19.93473235712339</v>
       </c>
       <c r="F497" t="n">
         <v>718850</v>
@@ -10372,16 +10372,16 @@
         <v>44824</v>
       </c>
       <c r="B498" t="n">
-        <v>19.84025382995605</v>
+        <v>19.84025573730469</v>
       </c>
       <c r="C498" t="n">
-        <v>20.63386412731537</v>
+        <v>20.63386611095796</v>
       </c>
       <c r="D498" t="n">
-        <v>19.74577607036311</v>
+        <v>19.7457779686291</v>
       </c>
       <c r="E498" t="n">
-        <v>20.3693267608578</v>
+        <v>20.36932871906902</v>
       </c>
       <c r="F498" t="n">
         <v>1041050</v>
@@ -10412,16 +10412,16 @@
         <v>44826</v>
       </c>
       <c r="B500" t="n">
-        <v>19.93473243713379</v>
+        <v>19.93473052978516</v>
       </c>
       <c r="C500" t="n">
-        <v>19.97252246136969</v>
+        <v>19.97252055040532</v>
       </c>
       <c r="D500" t="n">
-        <v>18.81989879096601</v>
+        <v>18.81989699028429</v>
       </c>
       <c r="E500" t="n">
-        <v>19.34897174436288</v>
+        <v>19.34896989305964</v>
       </c>
       <c r="F500" t="n">
         <v>1035500</v>
@@ -10432,16 +10432,16 @@
         <v>44827</v>
       </c>
       <c r="B501" t="n">
-        <v>19.57571792602539</v>
+        <v>19.57571983337402</v>
       </c>
       <c r="C501" t="n">
-        <v>19.68909160640989</v>
+        <v>19.68909352480502</v>
       </c>
       <c r="D501" t="n">
-        <v>19.21670457516592</v>
+        <v>19.21670644753429</v>
       </c>
       <c r="E501" t="n">
-        <v>19.3489723672699</v>
+        <v>19.34897425252572</v>
       </c>
       <c r="F501" t="n">
         <v>673550</v>
@@ -10452,16 +10452,16 @@
         <v>44830</v>
       </c>
       <c r="B502" t="n">
-        <v>18.7065258026123</v>
+        <v>18.70652389526367</v>
       </c>
       <c r="C502" t="n">
-        <v>19.48124205111187</v>
+        <v>19.48124006477188</v>
       </c>
       <c r="D502" t="n">
-        <v>18.6309439493457</v>
+        <v>18.63094204970352</v>
       </c>
       <c r="E502" t="n">
-        <v>19.34897245638518</v>
+        <v>19.34897048353161</v>
       </c>
       <c r="F502" t="n">
         <v>1198500</v>
@@ -10472,16 +10472,16 @@
         <v>44831</v>
       </c>
       <c r="B503" t="n">
-        <v>18.30972290039062</v>
+        <v>18.30972099304199</v>
       </c>
       <c r="C503" t="n">
-        <v>19.00885738260363</v>
+        <v>19.00885540242521</v>
       </c>
       <c r="D503" t="n">
-        <v>18.2530369538917</v>
+        <v>18.25303505244812</v>
       </c>
       <c r="E503" t="n">
-        <v>18.97106555026184</v>
+        <v>18.97106357402025</v>
       </c>
       <c r="F503" t="n">
         <v>994450</v>
@@ -10492,16 +10492,16 @@
         <v>44832</v>
       </c>
       <c r="B504" t="n">
-        <v>18.44198989868164</v>
+        <v>18.44199180603027</v>
       </c>
       <c r="C504" t="n">
-        <v>18.66873545456541</v>
+        <v>18.66873738536503</v>
       </c>
       <c r="D504" t="n">
-        <v>18.15855660231681</v>
+        <v>18.15855848035157</v>
       </c>
       <c r="E504" t="n">
-        <v>18.49867583714921</v>
+        <v>18.49867775036054</v>
       </c>
       <c r="F504" t="n">
         <v>784750</v>
@@ -10572,16 +10572,16 @@
         <v>44838</v>
       </c>
       <c r="B508" t="n">
-        <v>19.72688102722168</v>
+        <v>19.72688484191895</v>
       </c>
       <c r="C508" t="n">
-        <v>20.08589616909064</v>
+        <v>20.08590005321267</v>
       </c>
       <c r="D508" t="n">
-        <v>19.46234545112188</v>
+        <v>19.46234921466442</v>
       </c>
       <c r="E508" t="n">
-        <v>19.63240506547944</v>
+        <v>19.63240886190736</v>
       </c>
       <c r="F508" t="n">
         <v>1320250</v>
@@ -10592,16 +10592,16 @@
         <v>44839</v>
       </c>
       <c r="B509" t="n">
-        <v>19.63240432739258</v>
+        <v>19.63240623474121</v>
       </c>
       <c r="C509" t="n">
-        <v>19.84025395823017</v>
+        <v>19.84025588577203</v>
       </c>
       <c r="D509" t="n">
-        <v>19.38676287166812</v>
+        <v>19.38676475515193</v>
       </c>
       <c r="E509" t="n">
-        <v>19.72688028558296</v>
+        <v>19.72688220211023</v>
       </c>
       <c r="F509" t="n">
         <v>721150</v>
@@ -10632,16 +10632,16 @@
         <v>44841</v>
       </c>
       <c r="B511" t="n">
-        <v>19.63240432739258</v>
+        <v>19.63240623474121</v>
       </c>
       <c r="C511" t="n">
-        <v>20.38822280499599</v>
+        <v>20.38822478577472</v>
       </c>
       <c r="D511" t="n">
-        <v>19.55682247963224</v>
+        <v>19.55682437963786</v>
       </c>
       <c r="E511" t="n">
-        <v>20.38822280499599</v>
+        <v>20.38822478577472</v>
       </c>
       <c r="F511" t="n">
         <v>673950</v>
@@ -10652,16 +10652,16 @@
         <v>44844</v>
       </c>
       <c r="B512" t="n">
-        <v>19.55682182312012</v>
+        <v>19.55682373046875</v>
       </c>
       <c r="C512" t="n">
-        <v>19.7457755351712</v>
+        <v>19.74577746094821</v>
       </c>
       <c r="D512" t="n">
-        <v>19.2922844638326</v>
+        <v>19.29228634538129</v>
       </c>
       <c r="E512" t="n">
-        <v>19.68908960175721</v>
+        <v>19.68909152200573</v>
       </c>
       <c r="F512" t="n">
         <v>555250</v>
@@ -10692,16 +10692,16 @@
         <v>44847</v>
       </c>
       <c r="B514" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577903747559</v>
       </c>
       <c r="C514" t="n">
-        <v>19.99141859744693</v>
+        <v>19.99142052852337</v>
       </c>
       <c r="D514" t="n">
-        <v>19.10333049283063</v>
+        <v>19.10333233812196</v>
       </c>
       <c r="E514" t="n">
-        <v>19.3489719601506</v>
+        <v>19.34897382916973</v>
       </c>
       <c r="F514" t="n">
         <v>1432800</v>
@@ -10712,16 +10712,16 @@
         <v>44848</v>
       </c>
       <c r="B515" t="n">
-        <v>19.1600170135498</v>
+        <v>19.16001892089844</v>
       </c>
       <c r="C515" t="n">
-        <v>19.84025363221523</v>
+        <v>19.84025560728032</v>
       </c>
       <c r="D515" t="n">
-        <v>18.97106149624717</v>
+        <v>18.97106338478559</v>
       </c>
       <c r="E515" t="n">
-        <v>19.84025363221523</v>
+        <v>19.84025560728032</v>
       </c>
       <c r="F515" t="n">
         <v>919650</v>
@@ -10752,16 +10752,16 @@
         <v>44852</v>
       </c>
       <c r="B517" t="n">
-        <v>19.53792953491211</v>
+        <v>19.53792762756348</v>
       </c>
       <c r="C517" t="n">
-        <v>19.7835710279484</v>
+        <v>19.78356909661954</v>
       </c>
       <c r="D517" t="n">
-        <v>19.23560209794857</v>
+        <v>19.23560022011401</v>
       </c>
       <c r="E517" t="n">
-        <v>19.55682545022575</v>
+        <v>19.55682354103244</v>
       </c>
       <c r="F517" t="n">
         <v>665900</v>
@@ -10772,16 +10772,16 @@
         <v>44853</v>
       </c>
       <c r="B518" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577903747559</v>
       </c>
       <c r="C518" t="n">
-        <v>19.76467304346237</v>
+        <v>19.76467495263626</v>
       </c>
       <c r="D518" t="n">
-        <v>19.27339010882242</v>
+        <v>19.2733919705407</v>
       </c>
       <c r="E518" t="n">
-        <v>19.46234563814962</v>
+        <v>19.46234751812012</v>
       </c>
       <c r="F518" t="n">
         <v>599800</v>
@@ -10812,16 +10812,16 @@
         <v>44855</v>
       </c>
       <c r="B520" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577903747559</v>
       </c>
       <c r="C520" t="n">
-        <v>19.93473265945416</v>
+        <v>19.934734585055</v>
       </c>
       <c r="D520" t="n">
-        <v>19.17891234415881</v>
+        <v>19.17891419675099</v>
       </c>
       <c r="E520" t="n">
-        <v>19.33007604681519</v>
+        <v>19.33007791400906</v>
       </c>
       <c r="F520" t="n">
         <v>2036950</v>
@@ -10832,16 +10832,16 @@
         <v>44858</v>
       </c>
       <c r="B521" t="n">
-        <v>19.55682182312012</v>
+        <v>19.55682373046875</v>
       </c>
       <c r="C521" t="n">
-        <v>19.85914920401251</v>
+        <v>19.8591511408467</v>
       </c>
       <c r="D521" t="n">
-        <v>19.33007448543749</v>
+        <v>19.33007637067178</v>
       </c>
       <c r="E521" t="n">
-        <v>19.7457755351712</v>
+        <v>19.74577746094821</v>
       </c>
       <c r="F521" t="n">
         <v>947100</v>
@@ -10872,16 +10872,16 @@
         <v>44860</v>
       </c>
       <c r="B523" t="n">
-        <v>18.38530349731445</v>
+        <v>18.38530540466309</v>
       </c>
       <c r="C523" t="n">
-        <v>19.31118350379421</v>
+        <v>19.31118550719652</v>
       </c>
       <c r="D523" t="n">
-        <v>18.06408195459271</v>
+        <v>18.06408382861681</v>
       </c>
       <c r="E523" t="n">
-        <v>18.98996015905884</v>
+        <v>18.98996212913643</v>
       </c>
       <c r="F523" t="n">
         <v>1458850</v>
@@ -10912,16 +10912,16 @@
         <v>44862</v>
       </c>
       <c r="B525" t="n">
-        <v>19.40565872192383</v>
+        <v>19.40566062927246</v>
       </c>
       <c r="C525" t="n">
-        <v>19.74577613474872</v>
+        <v>19.7457780755269</v>
       </c>
       <c r="D525" t="n">
-        <v>18.87658398728353</v>
+        <v>18.87658584263032</v>
       </c>
       <c r="E525" t="n">
-        <v>19.29228504963994</v>
+        <v>19.29228694584527</v>
       </c>
       <c r="F525" t="n">
         <v>1190600</v>
@@ -10952,16 +10952,16 @@
         <v>44866</v>
       </c>
       <c r="B527" t="n">
-        <v>20.48270034790039</v>
+        <v>20.48270225524902</v>
       </c>
       <c r="C527" t="n">
-        <v>20.84171367044992</v>
+        <v>20.84171561122987</v>
       </c>
       <c r="D527" t="n">
-        <v>19.95362741919089</v>
+        <v>19.95362927727227</v>
       </c>
       <c r="E527" t="n">
-        <v>20.27484891725449</v>
+        <v>20.274850805248</v>
       </c>
       <c r="F527" t="n">
         <v>1462800</v>
@@ -10992,16 +10992,16 @@
         <v>44869</v>
       </c>
       <c r="B529" t="n">
-        <v>21.38968467712402</v>
+        <v>21.38968276977539</v>
       </c>
       <c r="C529" t="n">
-        <v>21.74869983803748</v>
+        <v>21.74869789867495</v>
       </c>
       <c r="D529" t="n">
-        <v>21.01177540406793</v>
+        <v>21.011773530418</v>
       </c>
       <c r="E529" t="n">
-        <v>21.40858059128022</v>
+        <v>21.40857868224661</v>
       </c>
       <c r="F529" t="n">
         <v>1653450</v>
@@ -11092,16 +11092,16 @@
         <v>44876</v>
       </c>
       <c r="B534" t="n">
-        <v>15.51319122314453</v>
+        <v>15.51319026947021</v>
       </c>
       <c r="C534" t="n">
-        <v>16.96814244033852</v>
+        <v>16.96814139722099</v>
       </c>
       <c r="D534" t="n">
-        <v>15.05969917407831</v>
+        <v>15.05969824828244</v>
       </c>
       <c r="E534" t="n">
-        <v>16.94924832734628</v>
+        <v>16.94924728539026</v>
       </c>
       <c r="F534" t="n">
         <v>6426800</v>
@@ -11132,16 +11132,16 @@
         <v>44881</v>
       </c>
       <c r="B536" t="n">
-        <v>14.47393894195557</v>
+        <v>14.47393798828125</v>
       </c>
       <c r="C536" t="n">
-        <v>15.64545861119334</v>
+        <v>15.64545758032868</v>
       </c>
       <c r="D536" t="n">
-        <v>14.41725300044779</v>
+        <v>14.41725205050845</v>
       </c>
       <c r="E536" t="n">
-        <v>15.49429489916353</v>
+        <v>15.49429387825891</v>
       </c>
       <c r="F536" t="n">
         <v>3432000</v>
@@ -11152,16 +11152,16 @@
         <v>44882</v>
       </c>
       <c r="B537" t="n">
-        <v>13.88817882537842</v>
+        <v>13.8881778717041</v>
       </c>
       <c r="C537" t="n">
-        <v>14.26608899878738</v>
+        <v>14.2660880191627</v>
       </c>
       <c r="D537" t="n">
-        <v>13.07567343921034</v>
+        <v>13.07567254132919</v>
       </c>
       <c r="E537" t="n">
-        <v>14.26608899878738</v>
+        <v>14.2660880191627</v>
       </c>
       <c r="F537" t="n">
         <v>5220400</v>
@@ -11192,16 +11192,16 @@
         <v>44886</v>
       </c>
       <c r="B539" t="n">
-        <v>14.5117301940918</v>
+        <v>14.51172924041748</v>
       </c>
       <c r="C539" t="n">
-        <v>14.60620796672404</v>
+        <v>14.60620700684089</v>
       </c>
       <c r="D539" t="n">
-        <v>13.79370254591263</v>
+        <v>13.79370163942528</v>
       </c>
       <c r="E539" t="n">
-        <v>14.13382090557644</v>
+        <v>14.13381997673737</v>
       </c>
       <c r="F539" t="n">
         <v>1946900</v>
@@ -11212,16 +11212,16 @@
         <v>44887</v>
       </c>
       <c r="B540" t="n">
-        <v>14.09602928161621</v>
+        <v>14.09602832794189</v>
       </c>
       <c r="C540" t="n">
-        <v>14.71958002742118</v>
+        <v>14.71957903156021</v>
       </c>
       <c r="D540" t="n">
-        <v>13.88817873267896</v>
+        <v>13.88817779306689</v>
       </c>
       <c r="E540" t="n">
-        <v>14.60620724645726</v>
+        <v>14.60620625826658</v>
       </c>
       <c r="F540" t="n">
         <v>2112800</v>
@@ -11232,16 +11232,16 @@
         <v>44888</v>
       </c>
       <c r="B541" t="n">
-        <v>14.02044773101807</v>
+        <v>14.02044677734375</v>
       </c>
       <c r="C541" t="n">
-        <v>14.07713367222323</v>
+        <v>14.07713271469312</v>
       </c>
       <c r="D541" t="n">
-        <v>13.62364253855478</v>
+        <v>13.62364161187125</v>
       </c>
       <c r="E541" t="n">
-        <v>14.05823865882377</v>
+        <v>14.05823770257891</v>
       </c>
       <c r="F541" t="n">
         <v>1795300</v>
@@ -11252,16 +11252,16 @@
         <v>44889</v>
       </c>
       <c r="B542" t="n">
-        <v>14.94632530212402</v>
+        <v>14.94632625579834</v>
       </c>
       <c r="C542" t="n">
-        <v>15.11638492080524</v>
+        <v>15.11638588533049</v>
       </c>
       <c r="D542" t="n">
-        <v>14.22829770315091</v>
+        <v>14.22829861101032</v>
       </c>
       <c r="E542" t="n">
-        <v>14.30387955567439</v>
+        <v>14.30388046835643</v>
       </c>
       <c r="F542" t="n">
         <v>1608000</v>
@@ -11352,16 +11352,16 @@
         <v>44896</v>
       </c>
       <c r="B547" t="n">
-        <v>14.1527156829834</v>
+        <v>14.15271472930908</v>
       </c>
       <c r="C547" t="n">
-        <v>14.51172995157667</v>
+        <v>14.51172897371034</v>
       </c>
       <c r="D547" t="n">
-        <v>14.03934289832344</v>
+        <v>14.0393419522887</v>
       </c>
       <c r="E547" t="n">
-        <v>14.30388029687014</v>
+        <v>14.30387933300967</v>
       </c>
       <c r="F547" t="n">
         <v>1145350</v>
@@ -11372,16 +11372,16 @@
         <v>44897</v>
       </c>
       <c r="B548" t="n">
-        <v>14.28498458862305</v>
+        <v>14.28498363494873</v>
       </c>
       <c r="C548" t="n">
-        <v>14.58731201875047</v>
+        <v>14.58731104489259</v>
       </c>
       <c r="D548" t="n">
-        <v>14.05823901602748</v>
+        <v>14.05823807749083</v>
       </c>
       <c r="E548" t="n">
-        <v>14.17161180232526</v>
+        <v>14.17161085621978</v>
       </c>
       <c r="F548" t="n">
         <v>1219600</v>
@@ -11412,16 +11412,16 @@
         <v>44901</v>
       </c>
       <c r="B550" t="n">
-        <v>13.15125465393066</v>
+        <v>13.15125560760498</v>
       </c>
       <c r="C550" t="n">
-        <v>13.66143259735872</v>
+        <v>13.66143358802902</v>
       </c>
       <c r="D550" t="n">
-        <v>12.67886763590444</v>
+        <v>12.67886855532321</v>
       </c>
       <c r="E550" t="n">
-        <v>13.54805982115323</v>
+        <v>13.54806080360221</v>
       </c>
       <c r="F550" t="n">
         <v>4313950</v>
@@ -11452,16 +11452,16 @@
         <v>44903</v>
       </c>
       <c r="B552" t="n">
-        <v>12.37653923034668</v>
+        <v>12.376540184021</v>
       </c>
       <c r="C552" t="n">
-        <v>13.09456675483028</v>
+        <v>13.09456776383221</v>
       </c>
       <c r="D552" t="n">
-        <v>12.16868870696652</v>
+        <v>12.16868964462491</v>
       </c>
       <c r="E552" t="n">
-        <v>13.03788082182175</v>
+        <v>13.03788182645574</v>
       </c>
       <c r="F552" t="n">
         <v>3031100</v>
@@ -11492,16 +11492,16 @@
         <v>44907</v>
       </c>
       <c r="B554" t="n">
-        <v>11.90415287017822</v>
+        <v>11.90415382385254</v>
       </c>
       <c r="C554" t="n">
-        <v>12.35764396187693</v>
+        <v>12.35764495188166</v>
       </c>
       <c r="D554" t="n">
-        <v>11.58292956305495</v>
+        <v>11.58293049099519</v>
       </c>
       <c r="E554" t="n">
-        <v>12.18758435198656</v>
+        <v>12.18758532836735</v>
       </c>
       <c r="F554" t="n">
         <v>2931550</v>
@@ -11512,16 +11512,16 @@
         <v>44908</v>
       </c>
       <c r="B555" t="n">
-        <v>11.58292961120605</v>
+        <v>11.58293056488037</v>
       </c>
       <c r="C555" t="n">
-        <v>12.22537532711658</v>
+        <v>12.22537633368632</v>
       </c>
       <c r="D555" t="n">
-        <v>11.48845184953939</v>
+        <v>11.48845279543493</v>
       </c>
       <c r="E555" t="n">
-        <v>11.97973476859532</v>
+        <v>11.97973575494038</v>
       </c>
       <c r="F555" t="n">
         <v>2082000</v>
@@ -11532,16 +11532,16 @@
         <v>44909</v>
       </c>
       <c r="B556" t="n">
-        <v>11.50734806060791</v>
+        <v>11.50734901428223</v>
       </c>
       <c r="C556" t="n">
-        <v>11.62072083694312</v>
+        <v>11.62072180001323</v>
       </c>
       <c r="D556" t="n">
-        <v>11.07275196748624</v>
+        <v>11.0727528851433</v>
       </c>
       <c r="E556" t="n">
-        <v>11.50734806060791</v>
+        <v>11.50734901428223</v>
       </c>
       <c r="F556" t="n">
         <v>4449300</v>
@@ -11612,16 +11612,16 @@
         <v>44915</v>
       </c>
       <c r="B560" t="n">
-        <v>12.56549453735352</v>
+        <v>12.56549549102783</v>
       </c>
       <c r="C560" t="n">
-        <v>12.86782193281247</v>
+        <v>12.86782290943231</v>
       </c>
       <c r="D560" t="n">
-        <v>11.67740646168276</v>
+        <v>11.6774073479545</v>
       </c>
       <c r="E560" t="n">
-        <v>11.79077923497987</v>
+        <v>11.79078012985618</v>
       </c>
       <c r="F560" t="n">
         <v>2603950</v>
@@ -11632,16 +11632,16 @@
         <v>44916</v>
       </c>
       <c r="B561" t="n">
-        <v>12.65997219085693</v>
+        <v>12.65997314453125</v>
       </c>
       <c r="C561" t="n">
-        <v>12.81113679906094</v>
+        <v>12.81113776412247</v>
       </c>
       <c r="D561" t="n">
-        <v>12.22537608216148</v>
+        <v>12.22537700309772</v>
       </c>
       <c r="E561" t="n">
-        <v>12.62218126405762</v>
+        <v>12.62218221488515</v>
       </c>
       <c r="F561" t="n">
         <v>1430400</v>
@@ -11692,16 +11692,16 @@
         <v>44921</v>
       </c>
       <c r="B564" t="n">
-        <v>13.17014980316162</v>
+        <v>13.17015075683594</v>
       </c>
       <c r="C564" t="n">
-        <v>13.49137312292281</v>
+        <v>13.49137409985749</v>
       </c>
       <c r="D564" t="n">
-        <v>12.83003147100628</v>
+        <v>12.83003240005202</v>
       </c>
       <c r="E564" t="n">
-        <v>13.41579127133274</v>
+        <v>13.4157922427944</v>
       </c>
       <c r="F564" t="n">
         <v>1094200</v>
@@ -11712,16 +11712,16 @@
         <v>44922</v>
       </c>
       <c r="B565" t="n">
-        <v>12.35764503479004</v>
+        <v>12.35764408111572</v>
       </c>
       <c r="C565" t="n">
-        <v>13.24573318464882</v>
+        <v>13.24573216243824</v>
       </c>
       <c r="D565" t="n">
-        <v>12.22537633772409</v>
+        <v>12.22537539425732</v>
       </c>
       <c r="E565" t="n">
-        <v>13.24573318464882</v>
+        <v>13.24573216243824</v>
       </c>
       <c r="F565" t="n">
         <v>2491300</v>
@@ -11732,16 +11732,16 @@
         <v>44923</v>
       </c>
       <c r="B566" t="n">
-        <v>13.10084915161133</v>
+        <v>13.10085010528564</v>
       </c>
       <c r="C566" t="n">
-        <v>13.1201439219793</v>
+        <v>13.12014487705818</v>
       </c>
       <c r="D566" t="n">
-        <v>12.29048719666213</v>
+        <v>12.29048809134627</v>
       </c>
       <c r="E566" t="n">
-        <v>12.46413644987275</v>
+        <v>12.46413735719766</v>
       </c>
       <c r="F566" t="n">
         <v>2129050</v>
@@ -11772,16 +11772,16 @@
         <v>44928</v>
       </c>
       <c r="B568" t="n">
-        <v>12.21331024169922</v>
+        <v>12.21331214904785</v>
       </c>
       <c r="C568" t="n">
-        <v>12.83072910757643</v>
+        <v>12.83073111134716</v>
       </c>
       <c r="D568" t="n">
-        <v>11.98177851200476</v>
+        <v>11.98178038319516</v>
       </c>
       <c r="E568" t="n">
-        <v>12.83072910757643</v>
+        <v>12.83073111134716</v>
       </c>
       <c r="F568" t="n">
         <v>1499800</v>
@@ -11792,16 +11792,16 @@
         <v>44929</v>
       </c>
       <c r="B569" t="n">
-        <v>11.65377521514893</v>
+        <v>11.65377616882324</v>
       </c>
       <c r="C569" t="n">
-        <v>12.21331071004653</v>
+        <v>12.21331170950984</v>
       </c>
       <c r="D569" t="n">
-        <v>11.59589274051833</v>
+        <v>11.5958936894559</v>
       </c>
       <c r="E569" t="n">
-        <v>12.21331071004653</v>
+        <v>12.21331170950984</v>
       </c>
       <c r="F569" t="n">
         <v>2015100</v>
@@ -11892,16 +11892,16 @@
         <v>44936</v>
       </c>
       <c r="B574" t="n">
-        <v>13.85332870483398</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C574" t="n">
-        <v>14.0076841187254</v>
+        <v>14.00768508302567</v>
       </c>
       <c r="D574" t="n">
-        <v>13.04296761203716</v>
+        <v>13.04296850992557</v>
       </c>
       <c r="E574" t="n">
-        <v>13.17802733415729</v>
+        <v>13.17802824134331</v>
       </c>
       <c r="F574" t="n">
         <v>2939000</v>
@@ -11952,16 +11952,16 @@
         <v>44939</v>
       </c>
       <c r="B577" t="n">
-        <v>13.33238124847412</v>
+        <v>13.33238220214844</v>
       </c>
       <c r="C577" t="n">
-        <v>13.4867357356305</v>
+        <v>13.4867367003459</v>
       </c>
       <c r="D577" t="n">
-        <v>13.13943813952864</v>
+        <v>13.13943907940161</v>
       </c>
       <c r="E577" t="n">
-        <v>13.42885326295952</v>
+        <v>13.42885422353454</v>
       </c>
       <c r="F577" t="n">
         <v>1373850</v>
@@ -11992,16 +11992,16 @@
         <v>44943</v>
       </c>
       <c r="B579" t="n">
-        <v>13.06226253509521</v>
+        <v>13.0622615814209</v>
       </c>
       <c r="C579" t="n">
-        <v>13.29379429488402</v>
+        <v>13.2937933243056</v>
       </c>
       <c r="D579" t="n">
-        <v>12.86931940193787</v>
+        <v>12.86931846235032</v>
       </c>
       <c r="E579" t="n">
-        <v>13.0043791351353</v>
+        <v>13.00437818568704</v>
       </c>
       <c r="F579" t="n">
         <v>1398800</v>
@@ -12052,16 +12052,16 @@
         <v>44946</v>
       </c>
       <c r="B582" t="n">
-        <v>14.06556606292725</v>
+        <v>14.06556701660156</v>
       </c>
       <c r="C582" t="n">
-        <v>14.12344945595456</v>
+        <v>14.12345041355349</v>
       </c>
       <c r="D582" t="n">
-        <v>13.50603058377296</v>
+        <v>13.50603149950962</v>
       </c>
       <c r="E582" t="n">
-        <v>13.73756231583157</v>
+        <v>13.73756324726655</v>
       </c>
       <c r="F582" t="n">
         <v>2454200</v>
@@ -12132,16 +12132,16 @@
         <v>44952</v>
       </c>
       <c r="B586" t="n">
-        <v>14.56722068786621</v>
+        <v>14.56721973419189</v>
       </c>
       <c r="C586" t="n">
-        <v>14.68298656676003</v>
+        <v>14.68298560550685</v>
       </c>
       <c r="D586" t="n">
-        <v>14.20062827802307</v>
+        <v>14.20062734834852</v>
       </c>
       <c r="E586" t="n">
-        <v>14.49004343527033</v>
+        <v>14.49004248664859</v>
       </c>
       <c r="F586" t="n">
         <v>1715850</v>
@@ -12172,16 +12172,16 @@
         <v>44956</v>
       </c>
       <c r="B588" t="n">
-        <v>14.39357089996338</v>
+        <v>14.39356994628906</v>
       </c>
       <c r="C588" t="n">
-        <v>14.66369127448637</v>
+        <v>14.6636903029147</v>
       </c>
       <c r="D588" t="n">
-        <v>14.31639365009966</v>
+        <v>14.31639270153888</v>
       </c>
       <c r="E588" t="n">
-        <v>14.37427612748476</v>
+        <v>14.37427517508885</v>
       </c>
       <c r="F588" t="n">
         <v>1160300</v>
@@ -12192,16 +12192,16 @@
         <v>44957</v>
       </c>
       <c r="B589" t="n">
-        <v>14.99169445037842</v>
+        <v>14.99169540405273</v>
       </c>
       <c r="C589" t="n">
-        <v>15.04957784548756</v>
+        <v>15.04957880284405</v>
       </c>
       <c r="D589" t="n">
-        <v>14.39357032770223</v>
+        <v>14.39357124332777</v>
       </c>
       <c r="E589" t="n">
-        <v>14.41286417938838</v>
+        <v>14.41286509624127</v>
       </c>
       <c r="F589" t="n">
         <v>1759050</v>
@@ -12212,16 +12212,16 @@
         <v>44958</v>
       </c>
       <c r="B590" t="n">
-        <v>14.99169445037842</v>
+        <v>14.99169540405273</v>
       </c>
       <c r="C590" t="n">
-        <v>15.1653437156805</v>
+        <v>15.16534468040126</v>
       </c>
       <c r="D590" t="n">
-        <v>14.74086793828104</v>
+        <v>14.7408688759994</v>
       </c>
       <c r="E590" t="n">
-        <v>14.97240059869227</v>
+        <v>14.97240155113924</v>
       </c>
       <c r="F590" t="n">
         <v>1831550</v>
@@ -12252,16 +12252,16 @@
         <v>44960</v>
       </c>
       <c r="B592" t="n">
-        <v>14.27780532836914</v>
+        <v>14.27780437469482</v>
       </c>
       <c r="C592" t="n">
-        <v>14.58651433437969</v>
+        <v>14.58651336008541</v>
       </c>
       <c r="D592" t="n">
-        <v>14.12345082536386</v>
+        <v>14.12344988199953</v>
       </c>
       <c r="E592" t="n">
-        <v>14.56722048151674</v>
+        <v>14.56721950851117</v>
       </c>
       <c r="F592" t="n">
         <v>1563350</v>
@@ -12272,16 +12272,16 @@
         <v>44963</v>
       </c>
       <c r="B593" t="n">
-        <v>14.27780532836914</v>
+        <v>14.27780437469482</v>
       </c>
       <c r="C593" t="n">
-        <v>14.35498257987178</v>
+        <v>14.35498162104247</v>
       </c>
       <c r="D593" t="n">
-        <v>13.91121292371891</v>
+        <v>13.91121199453083</v>
       </c>
       <c r="E593" t="n">
-        <v>14.18133330397814</v>
+        <v>14.18133235674759</v>
       </c>
       <c r="F593" t="n">
         <v>1305850</v>
@@ -12312,16 +12312,16 @@
         <v>44965</v>
       </c>
       <c r="B595" t="n">
-        <v>14.74086856842041</v>
+        <v>14.74086761474609</v>
       </c>
       <c r="C595" t="n">
-        <v>14.81804581851486</v>
+        <v>14.81804485984749</v>
       </c>
       <c r="D595" t="n">
-        <v>14.25851029531742</v>
+        <v>14.25850937284972</v>
       </c>
       <c r="E595" t="n">
-        <v>14.35498231794817</v>
+        <v>14.35498138923913</v>
       </c>
       <c r="F595" t="n">
         <v>1645600</v>
@@ -12332,16 +12332,16 @@
         <v>44966</v>
       </c>
       <c r="B596" t="n">
-        <v>13.64109230041504</v>
+        <v>13.64109134674072</v>
       </c>
       <c r="C596" t="n">
-        <v>14.74086857474552</v>
+        <v>14.74086754418378</v>
       </c>
       <c r="D596" t="n">
-        <v>13.64109230041504</v>
+        <v>13.64109134674072</v>
       </c>
       <c r="E596" t="n">
-        <v>14.74086857474552</v>
+        <v>14.74086754418378</v>
       </c>
       <c r="F596" t="n">
         <v>2708250</v>
@@ -12392,16 +12392,16 @@
         <v>44971</v>
       </c>
       <c r="B599" t="n">
-        <v>13.96909523010254</v>
+        <v>13.96909427642822</v>
       </c>
       <c r="C599" t="n">
-        <v>14.50933690398556</v>
+        <v>14.50933591342878</v>
       </c>
       <c r="D599" t="n">
-        <v>13.69897485317373</v>
+        <v>13.69897391794061</v>
       </c>
       <c r="E599" t="n">
-        <v>14.35498240288338</v>
+        <v>14.35498142286443</v>
       </c>
       <c r="F599" t="n">
         <v>2796000</v>
@@ -12432,16 +12432,16 @@
         <v>44973</v>
       </c>
       <c r="B601" t="n">
-        <v>14.79875183105469</v>
+        <v>14.79875087738037</v>
       </c>
       <c r="C601" t="n">
-        <v>14.99169495453137</v>
+        <v>14.99169398842324</v>
       </c>
       <c r="D601" t="n">
-        <v>14.58651393521765</v>
+        <v>14.58651299522056</v>
       </c>
       <c r="E601" t="n">
-        <v>14.81804568338966</v>
+        <v>14.818044728472</v>
       </c>
       <c r="F601" t="n">
         <v>1393950</v>
@@ -12492,16 +12492,16 @@
         <v>44980</v>
       </c>
       <c r="B604" t="n">
-        <v>14.41286468505859</v>
+        <v>14.41286563873291</v>
       </c>
       <c r="C604" t="n">
-        <v>14.91451772685366</v>
+        <v>14.91451871372149</v>
       </c>
       <c r="D604" t="n">
-        <v>14.27780495844099</v>
+        <v>14.27780590317863</v>
       </c>
       <c r="E604" t="n">
-        <v>14.66369120595613</v>
+        <v>14.6636921762272</v>
       </c>
       <c r="F604" t="n">
         <v>1540800</v>
@@ -12532,16 +12532,16 @@
         <v>44984</v>
       </c>
       <c r="B606" t="n">
-        <v>13.64109230041504</v>
+        <v>13.64109134674072</v>
       </c>
       <c r="C606" t="n">
-        <v>13.81474065318936</v>
+        <v>13.81473968737496</v>
       </c>
       <c r="D606" t="n">
-        <v>13.25520512975183</v>
+        <v>13.25520420305561</v>
       </c>
       <c r="E606" t="n">
-        <v>13.79544680067017</v>
+        <v>13.79544583620464</v>
       </c>
       <c r="F606" t="n">
         <v>2165600</v>
@@ -12552,16 +12552,16 @@
         <v>44985</v>
       </c>
       <c r="B607" t="n">
-        <v>13.85332870483398</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C607" t="n">
-        <v>14.0076841187254</v>
+        <v>14.00768508302567</v>
       </c>
       <c r="D607" t="n">
-        <v>13.48673632188941</v>
+        <v>13.48673725032721</v>
       </c>
       <c r="E607" t="n">
-        <v>13.71826898271386</v>
+        <v>13.71826992709055</v>
       </c>
       <c r="F607" t="n">
         <v>1742300</v>
@@ -12572,16 +12572,16 @@
         <v>44986</v>
       </c>
       <c r="B608" t="n">
-        <v>13.48673629760742</v>
+        <v>13.48673725128174</v>
       </c>
       <c r="C608" t="n">
-        <v>13.85332867989197</v>
+        <v>13.85332965948877</v>
       </c>
       <c r="D608" t="n">
-        <v>13.21661593382815</v>
+        <v>13.21661686840171</v>
       </c>
       <c r="E608" t="n">
-        <v>13.85332867989197</v>
+        <v>13.85332965948877</v>
       </c>
       <c r="F608" t="n">
         <v>2358750</v>
@@ -12592,16 +12592,16 @@
         <v>44987</v>
       </c>
       <c r="B609" t="n">
-        <v>13.29379367828369</v>
+        <v>13.29379272460938</v>
       </c>
       <c r="C609" t="n">
-        <v>13.69897469913348</v>
+        <v>13.69897371639216</v>
       </c>
       <c r="D609" t="n">
-        <v>13.23591120103394</v>
+        <v>13.23591025151202</v>
       </c>
       <c r="E609" t="n">
-        <v>13.48673680249183</v>
+        <v>13.4867358349761</v>
       </c>
       <c r="F609" t="n">
         <v>2574150</v>
@@ -12672,16 +12672,16 @@
         <v>44993</v>
       </c>
       <c r="B613" t="n">
-        <v>15.85993957519531</v>
+        <v>15.85994148254395</v>
       </c>
       <c r="C613" t="n">
-        <v>15.85993957519531</v>
+        <v>15.85994148254395</v>
       </c>
       <c r="D613" t="n">
-        <v>14.16203833580244</v>
+        <v>14.16204003895802</v>
       </c>
       <c r="E613" t="n">
-        <v>14.68298520243147</v>
+        <v>14.68298696823717</v>
       </c>
       <c r="F613" t="n">
         <v>5225650</v>
@@ -12712,16 +12712,16 @@
         <v>44995</v>
       </c>
       <c r="B615" t="n">
-        <v>15.43546485900879</v>
+        <v>15.43546390533447</v>
       </c>
       <c r="C615" t="n">
-        <v>15.97570561385987</v>
+        <v>15.97570462680699</v>
       </c>
       <c r="D615" t="n">
-        <v>15.33899283562982</v>
+        <v>15.33899188791599</v>
       </c>
       <c r="E615" t="n">
-        <v>15.97570561385987</v>
+        <v>15.97570462680699</v>
       </c>
       <c r="F615" t="n">
         <v>1980300</v>
@@ -12772,16 +12772,16 @@
         <v>45000</v>
       </c>
       <c r="B618" t="n">
-        <v>15.31969928741455</v>
+        <v>15.31969833374023</v>
       </c>
       <c r="C618" t="n">
-        <v>15.47405471189345</v>
+        <v>15.47405374861028</v>
       </c>
       <c r="D618" t="n">
-        <v>14.4514538198256</v>
+        <v>14.45145292020087</v>
       </c>
       <c r="E618" t="n">
-        <v>14.64439787041787</v>
+        <v>14.64439695878208</v>
       </c>
       <c r="F618" t="n">
         <v>2068400</v>
@@ -12792,16 +12792,16 @@
         <v>45001</v>
       </c>
       <c r="B619" t="n">
-        <v>15.76346874237061</v>
+        <v>15.76346778869629</v>
       </c>
       <c r="C619" t="n">
-        <v>15.91782324481321</v>
+        <v>15.9178222818006</v>
       </c>
       <c r="D619" t="n">
-        <v>15.20393321100345</v>
+        <v>15.20393229118048</v>
       </c>
       <c r="E619" t="n">
-        <v>15.28111046222475</v>
+        <v>15.28110953773264</v>
       </c>
       <c r="F619" t="n">
         <v>2813350</v>
@@ -12812,16 +12812,16 @@
         <v>45002</v>
       </c>
       <c r="B620" t="n">
-        <v>15.24252223968506</v>
+        <v>15.24252128601074</v>
       </c>
       <c r="C620" t="n">
-        <v>15.80205686582306</v>
+        <v>15.80205587714051</v>
       </c>
       <c r="D620" t="n">
-        <v>15.14605021309463</v>
+        <v>15.14604926545625</v>
       </c>
       <c r="E620" t="n">
-        <v>15.80205686582306</v>
+        <v>15.80205587714051</v>
       </c>
       <c r="F620" t="n">
         <v>4012850</v>
@@ -12832,16 +12832,16 @@
         <v>45005</v>
       </c>
       <c r="B621" t="n">
-        <v>13.96909523010254</v>
+        <v>13.96909427642822</v>
       </c>
       <c r="C621" t="n">
-        <v>15.33899280742245</v>
+        <v>15.33899176022482</v>
       </c>
       <c r="D621" t="n">
-        <v>13.94980137747747</v>
+        <v>13.94980042512035</v>
       </c>
       <c r="E621" t="n">
-        <v>15.1653444536952</v>
+        <v>15.16534341835259</v>
       </c>
       <c r="F621" t="n">
         <v>2781400</v>
@@ -12872,16 +12872,16 @@
         <v>45007</v>
       </c>
       <c r="B623" t="n">
-        <v>14.37427616119385</v>
+        <v>14.37427520751953</v>
       </c>
       <c r="C623" t="n">
-        <v>14.85663443398593</v>
+        <v>14.85663344830912</v>
       </c>
       <c r="D623" t="n">
-        <v>13.83403541088094</v>
+        <v>13.83403449304938</v>
       </c>
       <c r="E623" t="n">
-        <v>13.85332926337942</v>
+        <v>13.85332834426779</v>
       </c>
       <c r="F623" t="n">
         <v>2838400</v>
@@ -12932,16 +12932,16 @@
         <v>45012</v>
       </c>
       <c r="B626" t="n">
-        <v>13.98839092254639</v>
+        <v>13.98838996887207</v>
       </c>
       <c r="C626" t="n">
-        <v>14.12345157990428</v>
+        <v>14.12345061702205</v>
       </c>
       <c r="D626" t="n">
-        <v>13.56391601660446</v>
+        <v>13.5639150918692</v>
       </c>
       <c r="E626" t="n">
-        <v>13.83403641129478</v>
+        <v>13.83403546814375</v>
       </c>
       <c r="F626" t="n">
         <v>1142000</v>
@@ -13032,16 +13032,16 @@
         <v>45019</v>
       </c>
       <c r="B631" t="n">
-        <v>13.83403587341309</v>
+        <v>13.83403491973877</v>
       </c>
       <c r="C631" t="n">
-        <v>14.49004344075163</v>
+        <v>14.49004244185425</v>
       </c>
       <c r="D631" t="n">
-        <v>13.62179796868142</v>
+        <v>13.62179702963811</v>
       </c>
       <c r="E631" t="n">
-        <v>14.39357141495758</v>
+        <v>14.39357042271067</v>
       </c>
       <c r="F631" t="n">
         <v>1766300</v>
@@ -13072,16 +13072,16 @@
         <v>45021</v>
       </c>
       <c r="B633" t="n">
-        <v>13.85332870483398</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C633" t="n">
-        <v>14.29709833471159</v>
+        <v>14.29709931893536</v>
       </c>
       <c r="D633" t="n">
-        <v>13.66038558750141</v>
+        <v>13.66038652789336</v>
       </c>
       <c r="E633" t="n">
-        <v>14.18133246431204</v>
+        <v>14.1813334405664</v>
       </c>
       <c r="F633" t="n">
         <v>2634950</v>
@@ -13112,16 +13112,16 @@
         <v>45026</v>
       </c>
       <c r="B635" t="n">
-        <v>13.96909523010254</v>
+        <v>13.96909427642822</v>
       </c>
       <c r="C635" t="n">
-        <v>14.2006279017812</v>
+        <v>14.20062693230008</v>
       </c>
       <c r="D635" t="n">
-        <v>13.89191797955145</v>
+        <v>13.89191703114605</v>
       </c>
       <c r="E635" t="n">
-        <v>13.94980137747747</v>
+        <v>13.94980042512035</v>
       </c>
       <c r="F635" t="n">
         <v>1451200</v>
@@ -13172,16 +13172,16 @@
         <v>45029</v>
       </c>
       <c r="B638" t="n">
-        <v>15.70558643341064</v>
+        <v>15.70558547973633</v>
       </c>
       <c r="C638" t="n">
-        <v>15.93711818957249</v>
+        <v>15.93711722183911</v>
       </c>
       <c r="D638" t="n">
-        <v>15.10746134995442</v>
+        <v>15.10746043259944</v>
       </c>
       <c r="E638" t="n">
-        <v>15.49334761022416</v>
+        <v>15.49334666943741</v>
       </c>
       <c r="F638" t="n">
         <v>2173500</v>
@@ -13192,16 +13192,16 @@
         <v>45030</v>
       </c>
       <c r="B639" t="n">
-        <v>15.6091136932373</v>
+        <v>15.60911273956299</v>
       </c>
       <c r="C639" t="n">
-        <v>15.91782268731036</v>
+        <v>15.91782171477476</v>
       </c>
       <c r="D639" t="n">
-        <v>15.12675542998548</v>
+        <v>15.12675450578194</v>
       </c>
       <c r="E639" t="n">
-        <v>15.68629094175557</v>
+        <v>15.68628998336593</v>
       </c>
       <c r="F639" t="n">
         <v>1580050</v>
@@ -13212,16 +13212,16 @@
         <v>45033</v>
       </c>
       <c r="B640" t="n">
-        <v>15.5319356918335</v>
+        <v>15.53193664550781</v>
       </c>
       <c r="C640" t="n">
-        <v>15.76346742616516</v>
+        <v>15.76346839405572</v>
       </c>
       <c r="D640" t="n">
-        <v>15.49334614941956</v>
+        <v>15.49334710072444</v>
       </c>
       <c r="E640" t="n">
-        <v>15.60911293661072</v>
+        <v>15.60911389502378</v>
       </c>
       <c r="F640" t="n">
         <v>1212550</v>
@@ -13232,16 +13232,16 @@
         <v>45034</v>
       </c>
       <c r="B641" t="n">
-        <v>15.06887245178223</v>
+        <v>15.06887149810791</v>
       </c>
       <c r="C641" t="n">
-        <v>15.74417385507098</v>
+        <v>15.74417285865839</v>
       </c>
       <c r="D641" t="n">
-        <v>14.87592932513193</v>
+        <v>14.87592838366854</v>
       </c>
       <c r="E641" t="n">
-        <v>15.6284088991062</v>
+        <v>15.62840791002011</v>
       </c>
       <c r="F641" t="n">
         <v>1695600</v>
@@ -13272,16 +13272,16 @@
         <v>45036</v>
       </c>
       <c r="B643" t="n">
-        <v>14.93381214141846</v>
+        <v>14.93381118774414</v>
       </c>
       <c r="C643" t="n">
-        <v>14.93381214141846</v>
+        <v>14.93381118774414</v>
       </c>
       <c r="D643" t="n">
-        <v>14.29709934903595</v>
+        <v>14.29709843602215</v>
       </c>
       <c r="E643" t="n">
-        <v>14.43216000076346</v>
+        <v>14.43215907912469</v>
       </c>
       <c r="F643" t="n">
         <v>1458900</v>
@@ -13292,16 +13292,16 @@
         <v>45040</v>
       </c>
       <c r="B644" t="n">
-        <v>14.74086856842041</v>
+        <v>14.74086761474609</v>
       </c>
       <c r="C644" t="n">
-        <v>15.08816711387082</v>
+        <v>15.0881661377277</v>
       </c>
       <c r="D644" t="n">
-        <v>14.62510269327874</v>
+        <v>14.62510174709401</v>
       </c>
       <c r="E644" t="n">
-        <v>14.93381169365653</v>
+        <v>14.93381072749958</v>
       </c>
       <c r="F644" t="n">
         <v>897550</v>
@@ -13372,16 +13372,16 @@
         <v>45044</v>
       </c>
       <c r="B648" t="n">
-        <v>14.79875183105469</v>
+        <v>14.79875087738037</v>
       </c>
       <c r="C648" t="n">
-        <v>14.856634308085</v>
+        <v>14.85663335068057</v>
       </c>
       <c r="D648" t="n">
-        <v>14.33568741468527</v>
+        <v>14.33568649085217</v>
       </c>
       <c r="E648" t="n">
-        <v>14.83734045575002</v>
+        <v>14.83733949958894</v>
       </c>
       <c r="F648" t="n">
         <v>3490000</v>
@@ -13412,16 +13412,16 @@
         <v>45049</v>
       </c>
       <c r="B650" t="n">
-        <v>14.74086856842041</v>
+        <v>14.74086761474609</v>
       </c>
       <c r="C650" t="n">
-        <v>14.81804581851486</v>
+        <v>14.81804485984749</v>
       </c>
       <c r="D650" t="n">
-        <v>14.21992167027019</v>
+        <v>14.21992075029902</v>
       </c>
       <c r="E650" t="n">
-        <v>14.43215956804262</v>
+        <v>14.43215863434052</v>
       </c>
       <c r="F650" t="n">
         <v>2516550</v>
@@ -29592,7 +29592,7 @@
         <v>46232</v>
       </c>
       <c r="B1459" t="n">
-        <v>7.5</v>
+        <v>7.54</v>
       </c>
       <c r="C1459" t="n">
         <v>7.84</v>
@@ -29604,7 +29604,7 @@
         <v>7.83</v>
       </c>
       <c r="F1459" t="n">
-        <v>1889700</v>
+        <v>2553000</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1461"/>
+  <dimension ref="A1:F1462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44095</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59559726715088</v>
+        <v>12.59559631347656</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80833058545472</v>
+        <v>12.80832961567333</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45377505494831</v>
+        <v>12.45377411201205</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46707035901289</v>
+        <v>12.46706941506998</v>
       </c>
       <c r="F3" t="n">
         <v>1323800</v>
@@ -512,16 +512,16 @@
         <v>44097</v>
       </c>
       <c r="B5" t="n">
-        <v>12.65321063995361</v>
+        <v>12.65321159362793</v>
       </c>
       <c r="C5" t="n">
-        <v>12.99447082367709</v>
+        <v>12.99447180307224</v>
       </c>
       <c r="D5" t="n">
-        <v>12.24990345749021</v>
+        <v>12.24990438076721</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41388589815181</v>
+        <v>12.41388683378818</v>
       </c>
       <c r="F5" t="n">
         <v>1967400</v>
@@ -532,16 +532,16 @@
         <v>44098</v>
       </c>
       <c r="B6" t="n">
-        <v>12.45377445220947</v>
+        <v>12.45377254486084</v>
       </c>
       <c r="C6" t="n">
-        <v>12.84378551689074</v>
+        <v>12.84378354981024</v>
       </c>
       <c r="D6" t="n">
-        <v>12.40945480170939</v>
+        <v>12.4094529011485</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6532116114693</v>
+        <v>12.65320967357602</v>
       </c>
       <c r="F6" t="n">
         <v>571400</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513519287109</v>
+        <v>12.36513614654541</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366209522167</v>
+        <v>12.49366305880876</v>
       </c>
       <c r="D7" t="n">
-        <v>12.32081554222169</v>
+        <v>12.3208164924778</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377449416991</v>
+        <v>12.45377545468063</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -572,16 +572,16 @@
         <v>44102</v>
       </c>
       <c r="B8" t="n">
-        <v>11.58068084716797</v>
+        <v>11.58067893981934</v>
       </c>
       <c r="C8" t="n">
-        <v>12.51139018424467</v>
+        <v>12.51138812360737</v>
       </c>
       <c r="D8" t="n">
-        <v>11.58068084716797</v>
+        <v>11.58067893981934</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43161497744851</v>
+        <v>12.43161292995026</v>
       </c>
       <c r="F8" t="n">
         <v>1524000</v>
@@ -592,16 +592,16 @@
         <v>44103</v>
       </c>
       <c r="B9" t="n">
-        <v>11.29703712463379</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C9" t="n">
-        <v>11.83330335641843</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="D9" t="n">
-        <v>11.07987173996964</v>
+        <v>11.07987080462801</v>
       </c>
       <c r="E9" t="n">
-        <v>11.83330335641843</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="F9" t="n">
         <v>897600</v>
@@ -632,16 +632,16 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>11.68261623382568</v>
+        <v>11.68261432647705</v>
       </c>
       <c r="C11" t="n">
-        <v>11.68261623382568</v>
+        <v>11.68261432647705</v>
       </c>
       <c r="D11" t="n">
-        <v>10.92918466892529</v>
+        <v>10.92918288458478</v>
       </c>
       <c r="E11" t="n">
-        <v>11.22612524505344</v>
+        <v>11.22612341223327</v>
       </c>
       <c r="F11" t="n">
         <v>1726600</v>
@@ -652,16 +652,16 @@
         <v>44106</v>
       </c>
       <c r="B12" t="n">
-        <v>11.29703712463379</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C12" t="n">
-        <v>11.554090115188</v>
+        <v>11.55408913981376</v>
       </c>
       <c r="D12" t="n">
-        <v>11.19953455763982</v>
+        <v>11.19953361219649</v>
       </c>
       <c r="E12" t="n">
-        <v>11.51420250929794</v>
+        <v>11.51420153729093</v>
       </c>
       <c r="F12" t="n">
         <v>878600</v>
@@ -692,16 +692,16 @@
         <v>44110</v>
       </c>
       <c r="B14" t="n">
-        <v>11.43885803222656</v>
+        <v>11.43885707855225</v>
       </c>
       <c r="C14" t="n">
-        <v>12.05489940494884</v>
+        <v>12.05489839991425</v>
       </c>
       <c r="D14" t="n">
-        <v>11.38124307774816</v>
+        <v>11.38124212887729</v>
       </c>
       <c r="E14" t="n">
-        <v>11.58954433818795</v>
+        <v>11.5895433719507</v>
       </c>
       <c r="F14" t="n">
         <v>472800</v>
@@ -712,16 +712,16 @@
         <v>44111</v>
       </c>
       <c r="B15" t="n">
-        <v>11.68261623382568</v>
+        <v>11.68261432647705</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82443844714174</v>
+        <v>11.82443651663867</v>
       </c>
       <c r="D15" t="n">
-        <v>11.35465215420053</v>
+        <v>11.35465030039657</v>
       </c>
       <c r="E15" t="n">
-        <v>11.62943248116863</v>
+        <v>11.62943058250298</v>
       </c>
       <c r="F15" t="n">
         <v>437200</v>
@@ -732,16 +732,16 @@
         <v>44112</v>
       </c>
       <c r="B16" t="n">
-        <v>11.52306365966797</v>
+        <v>11.52306461334229</v>
       </c>
       <c r="C16" t="n">
-        <v>11.90421142045391</v>
+        <v>11.90421240567286</v>
       </c>
       <c r="D16" t="n">
-        <v>11.39010557095641</v>
+        <v>11.39010651362682</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68261404238337</v>
+        <v>11.68261500926243</v>
       </c>
       <c r="F16" t="n">
         <v>595200</v>
@@ -752,16 +752,16 @@
         <v>44113</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10365009307861</v>
+        <v>12.10365200042725</v>
       </c>
       <c r="C17" t="n">
-        <v>12.29422399771216</v>
+        <v>12.2942259350923</v>
       </c>
       <c r="D17" t="n">
-        <v>11.531929224505</v>
+        <v>11.53193104175924</v>
       </c>
       <c r="E17" t="n">
-        <v>11.53636127406939</v>
+        <v>11.53636309202205</v>
       </c>
       <c r="F17" t="n">
         <v>672400</v>
@@ -772,16 +772,16 @@
         <v>44117</v>
       </c>
       <c r="B18" t="n">
-        <v>12.18785858154297</v>
+        <v>12.18785762786865</v>
       </c>
       <c r="C18" t="n">
-        <v>12.44934361510042</v>
+        <v>12.44934264096545</v>
       </c>
       <c r="D18" t="n">
-        <v>12.18785858154297</v>
+        <v>12.18785762786865</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36956840549617</v>
+        <v>12.36956743760344</v>
       </c>
       <c r="F18" t="n">
         <v>440800</v>
@@ -792,16 +792,16 @@
         <v>44118</v>
       </c>
       <c r="B19" t="n">
-        <v>12.13024234771729</v>
+        <v>12.13024139404297</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63105211214986</v>
+        <v>12.63105111910211</v>
       </c>
       <c r="D19" t="n">
-        <v>12.00614749633282</v>
+        <v>12.00614655241479</v>
       </c>
       <c r="E19" t="n">
-        <v>12.18785730119724</v>
+        <v>12.18785634299326</v>
       </c>
       <c r="F19" t="n">
         <v>441800</v>
@@ -832,16 +832,16 @@
         <v>44120</v>
       </c>
       <c r="B21" t="n">
-        <v>12.45377445220947</v>
+        <v>12.45377254486084</v>
       </c>
       <c r="C21" t="n">
-        <v>12.49366205312684</v>
+        <v>12.49366013966925</v>
       </c>
       <c r="D21" t="n">
-        <v>11.97955613611076</v>
+        <v>11.97955430139068</v>
       </c>
       <c r="E21" t="n">
-        <v>12.06376254220119</v>
+        <v>12.06376069458454</v>
       </c>
       <c r="F21" t="n">
         <v>585200</v>
@@ -852,16 +852,16 @@
         <v>44123</v>
       </c>
       <c r="B22" t="n">
-        <v>12.53798294067383</v>
+        <v>12.53798198699951</v>
       </c>
       <c r="C22" t="n">
-        <v>12.78617182450374</v>
+        <v>12.78617085195148</v>
       </c>
       <c r="D22" t="n">
-        <v>12.30752141159678</v>
+        <v>12.30752047545202</v>
       </c>
       <c r="E22" t="n">
-        <v>12.40945602607532</v>
+        <v>12.40945508217713</v>
       </c>
       <c r="F22" t="n">
         <v>521200</v>
@@ -872,16 +872,16 @@
         <v>44124</v>
       </c>
       <c r="B23" t="n">
-        <v>12.85264778137207</v>
+        <v>12.85264873504639</v>
       </c>
       <c r="C23" t="n">
-        <v>12.87037597717226</v>
+        <v>12.87037693216201</v>
       </c>
       <c r="D23" t="n">
-        <v>12.41388507924032</v>
+        <v>12.41388600035818</v>
       </c>
       <c r="E23" t="n">
-        <v>12.53797991386091</v>
+        <v>12.53798084418668</v>
       </c>
       <c r="F23" t="n">
         <v>729200</v>
@@ -892,16 +892,16 @@
         <v>44125</v>
       </c>
       <c r="B24" t="n">
-        <v>12.85264778137207</v>
+        <v>12.85264873504639</v>
       </c>
       <c r="C24" t="n">
-        <v>12.94571827334233</v>
+        <v>12.94571923392254</v>
       </c>
       <c r="D24" t="n">
-        <v>12.51138762016063</v>
+        <v>12.51138854851324</v>
       </c>
       <c r="E24" t="n">
-        <v>12.85264778137207</v>
+        <v>12.85264873504639</v>
       </c>
       <c r="F24" t="n">
         <v>501200</v>
@@ -932,16 +932,16 @@
         <v>44127</v>
       </c>
       <c r="B26" t="n">
-        <v>12.94128894805908</v>
+        <v>12.9412899017334</v>
       </c>
       <c r="C26" t="n">
-        <v>13.18061370880962</v>
+        <v>13.18061468012035</v>
       </c>
       <c r="D26" t="n">
-        <v>12.86151374603323</v>
+        <v>12.86151469382872</v>
       </c>
       <c r="E26" t="n">
-        <v>13.08754320333081</v>
+        <v>13.08754416778295</v>
       </c>
       <c r="F26" t="n">
         <v>543600</v>
@@ -992,16 +992,16 @@
         <v>44132</v>
       </c>
       <c r="B29" t="n">
-        <v>11.43885803222656</v>
+        <v>11.43885707855225</v>
       </c>
       <c r="C29" t="n">
-        <v>11.92637250178829</v>
+        <v>11.92637150746918</v>
       </c>
       <c r="D29" t="n">
-        <v>11.3014678751419</v>
+        <v>11.301466932922</v>
       </c>
       <c r="E29" t="n">
-        <v>11.92637250178829</v>
+        <v>11.92637150746918</v>
       </c>
       <c r="F29" t="n">
         <v>860400</v>
@@ -1012,16 +1012,16 @@
         <v>44133</v>
       </c>
       <c r="B30" t="n">
-        <v>11.70477485656738</v>
+        <v>11.7047758102417</v>
       </c>
       <c r="C30" t="n">
-        <v>11.87762056184598</v>
+        <v>11.87762152960331</v>
       </c>
       <c r="D30" t="n">
-        <v>11.00895914058972</v>
+        <v>11.0089600375708</v>
       </c>
       <c r="E30" t="n">
-        <v>11.39453815164614</v>
+        <v>11.39453908004318</v>
       </c>
       <c r="F30" t="n">
         <v>683400</v>
@@ -1052,16 +1052,16 @@
         <v>44138</v>
       </c>
       <c r="B32" t="n">
-        <v>11.85546207427979</v>
+        <v>11.85546112060547</v>
       </c>
       <c r="C32" t="n">
-        <v>11.96626078525436</v>
+        <v>11.9662598226672</v>
       </c>
       <c r="D32" t="n">
-        <v>11.51863389147782</v>
+        <v>11.51863296489856</v>
       </c>
       <c r="E32" t="n">
-        <v>11.70034370984996</v>
+        <v>11.70034276865364</v>
       </c>
       <c r="F32" t="n">
         <v>1038200</v>
@@ -1072,16 +1072,16 @@
         <v>44139</v>
       </c>
       <c r="B33" t="n">
-        <v>12.5778694152832</v>
+        <v>12.57786846160889</v>
       </c>
       <c r="C33" t="n">
-        <v>12.78173948494929</v>
+        <v>12.78173851581722</v>
       </c>
       <c r="D33" t="n">
-        <v>11.90421388871892</v>
+        <v>11.90421298612225</v>
       </c>
       <c r="E33" t="n">
-        <v>11.96626089693912</v>
+        <v>11.96625998963795</v>
       </c>
       <c r="F33" t="n">
         <v>620400</v>
@@ -1092,16 +1092,16 @@
         <v>44140</v>
       </c>
       <c r="B34" t="n">
-        <v>12.79503345489502</v>
+        <v>12.79503440856934</v>
       </c>
       <c r="C34" t="n">
-        <v>13.02992614332686</v>
+        <v>13.02992711450884</v>
       </c>
       <c r="D34" t="n">
-        <v>12.63991511544401</v>
+        <v>12.63991605755662</v>
       </c>
       <c r="E34" t="n">
-        <v>12.78616935656595</v>
+        <v>12.78617030957958</v>
       </c>
       <c r="F34" t="n">
         <v>682600</v>
@@ -1152,16 +1152,16 @@
         <v>44145</v>
       </c>
       <c r="B37" t="n">
-        <v>13.15845489501953</v>
+        <v>13.15845394134521</v>
       </c>
       <c r="C37" t="n">
-        <v>13.57948948130297</v>
+        <v>13.57948849711368</v>
       </c>
       <c r="D37" t="n">
-        <v>13.07867968942368</v>
+        <v>13.07867874153117</v>
       </c>
       <c r="E37" t="n">
-        <v>13.07867968942368</v>
+        <v>13.07867874153117</v>
       </c>
       <c r="F37" t="n">
         <v>489600</v>
@@ -1192,16 +1192,16 @@
         <v>44147</v>
       </c>
       <c r="B39" t="n">
-        <v>12.94128894805908</v>
+        <v>12.9412899017334</v>
       </c>
       <c r="C39" t="n">
-        <v>13.35345941631429</v>
+        <v>13.35346040036243</v>
       </c>
       <c r="D39" t="n">
-        <v>12.7507150421811</v>
+        <v>12.75071598181158</v>
       </c>
       <c r="E39" t="n">
-        <v>13.12299875475041</v>
+        <v>13.12299972181535</v>
       </c>
       <c r="F39" t="n">
         <v>656600</v>
@@ -1212,16 +1212,16 @@
         <v>44148</v>
       </c>
       <c r="B40" t="n">
-        <v>13.10970306396484</v>
+        <v>13.10970115661621</v>
       </c>
       <c r="C40" t="n">
-        <v>13.53073849144283</v>
+        <v>13.53073652283718</v>
       </c>
       <c r="D40" t="n">
-        <v>12.84378599636438</v>
+        <v>12.84378412770439</v>
       </c>
       <c r="E40" t="n">
-        <v>13.29584492675246</v>
+        <v>13.29584299232179</v>
       </c>
       <c r="F40" t="n">
         <v>720400</v>
@@ -1312,16 +1312,16 @@
         <v>44158</v>
       </c>
       <c r="B45" t="n">
-        <v>13.35346031188965</v>
+        <v>13.35345840454102</v>
       </c>
       <c r="C45" t="n">
-        <v>13.47312312295385</v>
+        <v>13.47312119851311</v>
       </c>
       <c r="D45" t="n">
-        <v>13.0698158815097</v>
+        <v>13.06981401467557</v>
       </c>
       <c r="E45" t="n">
-        <v>13.13629493921411</v>
+        <v>13.13629306288441</v>
       </c>
       <c r="F45" t="n">
         <v>731400</v>
@@ -1332,16 +1332,16 @@
         <v>44159</v>
       </c>
       <c r="B46" t="n">
-        <v>13.73903942108154</v>
+        <v>13.73903846740723</v>
       </c>
       <c r="C46" t="n">
-        <v>13.82767872321933</v>
+        <v>13.82767776339226</v>
       </c>
       <c r="D46" t="n">
-        <v>13.27368519817572</v>
+        <v>13.27368427680326</v>
       </c>
       <c r="E46" t="n">
-        <v>13.4731223599952</v>
+        <v>13.47312142477911</v>
       </c>
       <c r="F46" t="n">
         <v>798800</v>
@@ -1352,16 +1352,16 @@
         <v>44160</v>
       </c>
       <c r="B47" t="n">
-        <v>13.65040111541748</v>
+        <v>13.65040016174316</v>
       </c>
       <c r="C47" t="n">
-        <v>13.77449597840386</v>
+        <v>13.77449501605975</v>
       </c>
       <c r="D47" t="n">
-        <v>13.34016522594218</v>
+        <v>13.34016429394225</v>
       </c>
       <c r="E47" t="n">
-        <v>13.61494556103953</v>
+        <v>13.61494460984229</v>
       </c>
       <c r="F47" t="n">
         <v>724200</v>
@@ -1392,16 +1392,16 @@
         <v>44162</v>
       </c>
       <c r="B49" t="n">
-        <v>13.39334678649902</v>
+        <v>13.39334774017334</v>
       </c>
       <c r="C49" t="n">
-        <v>13.71687963861983</v>
+        <v>13.71688061533133</v>
       </c>
       <c r="D49" t="n">
-        <v>13.38891473698208</v>
+        <v>13.38891569034081</v>
       </c>
       <c r="E49" t="n">
-        <v>13.53073778554325</v>
+        <v>13.5307387490005</v>
       </c>
       <c r="F49" t="n">
         <v>510000</v>
@@ -1412,16 +1412,16 @@
         <v>44165</v>
       </c>
       <c r="B50" t="n">
-        <v>13.13629341125488</v>
+        <v>13.13629531860352</v>
       </c>
       <c r="C50" t="n">
-        <v>13.73017450228043</v>
+        <v>13.73017649585873</v>
       </c>
       <c r="D50" t="n">
-        <v>13.13629341125488</v>
+        <v>13.13629531860352</v>
       </c>
       <c r="E50" t="n">
-        <v>13.38891430834409</v>
+        <v>13.38891625237249</v>
       </c>
       <c r="F50" t="n">
         <v>1093200</v>
@@ -1432,16 +1432,16 @@
         <v>44166</v>
       </c>
       <c r="B51" t="n">
-        <v>14.18223285675049</v>
+        <v>14.18223476409912</v>
       </c>
       <c r="C51" t="n">
-        <v>14.40383024513721</v>
+        <v>14.40383218228817</v>
       </c>
       <c r="D51" t="n">
-        <v>13.47755309405454</v>
+        <v>13.47755490663178</v>
       </c>
       <c r="E51" t="n">
-        <v>13.73460603077007</v>
+        <v>13.73460787791799</v>
       </c>
       <c r="F51" t="n">
         <v>2351000</v>
@@ -1452,16 +1452,16 @@
         <v>44167</v>
       </c>
       <c r="B52" t="n">
-        <v>14.18223285675049</v>
+        <v>14.18223476409912</v>
       </c>
       <c r="C52" t="n">
-        <v>14.37280674601539</v>
+        <v>14.37280867899403</v>
       </c>
       <c r="D52" t="n">
-        <v>13.9340440184489</v>
+        <v>13.93404589241896</v>
       </c>
       <c r="E52" t="n">
-        <v>14.18223285675049</v>
+        <v>14.18223476409912</v>
       </c>
       <c r="F52" t="n">
         <v>767800</v>
@@ -1472,16 +1472,16 @@
         <v>44168</v>
       </c>
       <c r="B53" t="n">
-        <v>14.35951328277588</v>
+        <v>14.35951232910156</v>
       </c>
       <c r="C53" t="n">
-        <v>14.44371969251193</v>
+        <v>14.44371873324512</v>
       </c>
       <c r="D53" t="n">
-        <v>14.0581398153931</v>
+        <v>14.05813888173424</v>
       </c>
       <c r="E53" t="n">
-        <v>14.31519278502997</v>
+        <v>14.31519183429916</v>
       </c>
       <c r="F53" t="n">
         <v>1033200</v>
@@ -1532,16 +1532,16 @@
         <v>44173</v>
       </c>
       <c r="B56" t="n">
-        <v>14.09359645843506</v>
+        <v>14.09359550476074</v>
       </c>
       <c r="C56" t="n">
-        <v>14.5367913262516</v>
+        <v>14.53679034258752</v>
       </c>
       <c r="D56" t="n">
-        <v>13.89859132523131</v>
+        <v>13.89859038475245</v>
       </c>
       <c r="E56" t="n">
-        <v>14.09359645843506</v>
+        <v>14.09359550476074</v>
       </c>
       <c r="F56" t="n">
         <v>767200</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.00495719909668</v>
+        <v>14.004958152771</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10245976017788</v>
+        <v>14.10246072049168</v>
       </c>
       <c r="D58" t="n">
-        <v>13.5174427030365</v>
+        <v>13.51744362351329</v>
       </c>
       <c r="E58" t="n">
-        <v>13.8852943886831</v>
+        <v>13.88529533420892</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1632,16 +1632,16 @@
         <v>44180</v>
       </c>
       <c r="B61" t="n">
-        <v>14.08473110198975</v>
+        <v>14.08473205566406</v>
       </c>
       <c r="C61" t="n">
-        <v>14.1246187017679</v>
+        <v>14.124619658143</v>
       </c>
       <c r="D61" t="n">
-        <v>13.57062519965683</v>
+        <v>13.57062611852114</v>
       </c>
       <c r="E61" t="n">
-        <v>13.75676705017923</v>
+        <v>13.75676798164717</v>
       </c>
       <c r="F61" t="n">
         <v>732800</v>
@@ -1652,16 +1652,16 @@
         <v>44181</v>
       </c>
       <c r="B62" t="n">
-        <v>13.9163179397583</v>
+        <v>13.91631698608398</v>
       </c>
       <c r="C62" t="n">
-        <v>14.1778029654802</v>
+        <v>14.17780199388652</v>
       </c>
       <c r="D62" t="n">
-        <v>13.71688076705103</v>
+        <v>13.71687982704398</v>
       </c>
       <c r="E62" t="n">
-        <v>14.13791536187333</v>
+        <v>14.13791439301312</v>
       </c>
       <c r="F62" t="n">
         <v>564600</v>
@@ -1672,16 +1672,16 @@
         <v>44182</v>
       </c>
       <c r="B63" t="n">
-        <v>13.73903942108154</v>
+        <v>13.73903846740723</v>
       </c>
       <c r="C63" t="n">
-        <v>14.13348254040794</v>
+        <v>14.13348155935396</v>
       </c>
       <c r="D63" t="n">
-        <v>13.67256036714172</v>
+        <v>13.67255941808194</v>
       </c>
       <c r="E63" t="n">
-        <v>13.91631718003009</v>
+        <v>13.91631621405031</v>
       </c>
       <c r="F63" t="n">
         <v>633000</v>
@@ -1692,16 +1692,16 @@
         <v>44183</v>
       </c>
       <c r="B64" t="n">
-        <v>13.40664291381836</v>
+        <v>13.40664386749268</v>
       </c>
       <c r="C64" t="n">
-        <v>13.83654157235696</v>
+        <v>13.83654255661189</v>
       </c>
       <c r="D64" t="n">
-        <v>13.28698011303142</v>
+        <v>13.28698105819358</v>
       </c>
       <c r="E64" t="n">
-        <v>13.6193762183327</v>
+        <v>13.61937718713968</v>
       </c>
       <c r="F64" t="n">
         <v>920000</v>
@@ -1712,16 +1712,16 @@
         <v>44186</v>
       </c>
       <c r="B65" t="n">
-        <v>13.14959144592285</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="C65" t="n">
-        <v>13.34016536975649</v>
+        <v>13.3401644022608</v>
       </c>
       <c r="D65" t="n">
-        <v>12.76844359825558</v>
+        <v>12.76844267222401</v>
       </c>
       <c r="E65" t="n">
-        <v>13.14959144592285</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="F65" t="n">
         <v>872000</v>
@@ -1752,16 +1752,16 @@
         <v>44188</v>
       </c>
       <c r="B67" t="n">
-        <v>14.04484272003174</v>
+        <v>14.04484367370605</v>
       </c>
       <c r="C67" t="n">
-        <v>14.1512093650741</v>
+        <v>14.15121032597093</v>
       </c>
       <c r="D67" t="n">
-        <v>13.40220995524134</v>
+        <v>13.40221086527954</v>
       </c>
       <c r="E67" t="n">
-        <v>13.45539370042599</v>
+        <v>13.45539461407549</v>
       </c>
       <c r="F67" t="n">
         <v>2040000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294269561768</v>
+        <v>15.11294364929199</v>
       </c>
       <c r="C68" t="n">
-        <v>15.13067089418624</v>
+        <v>15.13067184897926</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586759384061</v>
+        <v>14.07586848207222</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348254853438</v>
+        <v>14.13348344040167</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.19715213775635</v>
+        <v>15.19715118408203</v>
       </c>
       <c r="C69" t="n">
-        <v>15.34783845760998</v>
+        <v>15.34783749447957</v>
       </c>
       <c r="D69" t="n">
-        <v>14.74952438290252</v>
+        <v>14.7495234573184</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510512793207</v>
+        <v>15.13510417815142</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1812,16 +1812,16 @@
         <v>44195</v>
       </c>
       <c r="B70" t="n">
-        <v>15.72011852264404</v>
+        <v>15.72011947631836</v>
       </c>
       <c r="C70" t="n">
-        <v>15.9151236064789</v>
+        <v>15.91512457198337</v>
       </c>
       <c r="D70" t="n">
-        <v>15.25033147305764</v>
+        <v>15.25033239823193</v>
       </c>
       <c r="E70" t="n">
-        <v>15.37885835794267</v>
+        <v>15.37885929091415</v>
       </c>
       <c r="F70" t="n">
         <v>2946000</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884677886963</v>
+        <v>14.98885059356689</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171619745412</v>
+        <v>15.94172025465893</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952120062229</v>
+        <v>14.74952495441062</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069269923545</v>
+        <v>15.9106967485447</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.58997058868408</v>
+        <v>14.58997344970703</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135501822799</v>
+        <v>15.28135801482809</v>
       </c>
       <c r="D73" t="n">
-        <v>14.58997058868408</v>
+        <v>14.58997344970703</v>
       </c>
       <c r="E73" t="n">
-        <v>15.13953283124265</v>
+        <v>15.1395358000321</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1892,16 +1892,16 @@
         <v>44203</v>
       </c>
       <c r="B74" t="n">
-        <v>14.40513038635254</v>
+        <v>14.40513134002686</v>
       </c>
       <c r="C74" t="n">
-        <v>14.96995047062398</v>
+        <v>14.96995146169153</v>
       </c>
       <c r="D74" t="n">
-        <v>14.39623538149606</v>
+        <v>14.39623633458149</v>
       </c>
       <c r="E74" t="n">
-        <v>14.68531710141131</v>
+        <v>14.68531807363505</v>
       </c>
       <c r="F74" t="n">
         <v>1215000</v>
@@ -1952,16 +1952,16 @@
         <v>44208</v>
       </c>
       <c r="B77" t="n">
-        <v>15.99285316467285</v>
+        <v>15.99285221099854</v>
       </c>
       <c r="C77" t="n">
-        <v>16.31306657107592</v>
+        <v>16.31306559830687</v>
       </c>
       <c r="D77" t="n">
-        <v>15.34353304306556</v>
+        <v>15.34353212811103</v>
       </c>
       <c r="E77" t="n">
-        <v>15.90390480772213</v>
+        <v>15.90390385935192</v>
       </c>
       <c r="F77" t="n">
         <v>2193200</v>
@@ -1972,16 +1972,16 @@
         <v>44209</v>
       </c>
       <c r="B78" t="n">
-        <v>15.72156047821045</v>
+        <v>15.72155952453613</v>
       </c>
       <c r="C78" t="n">
-        <v>16.71777896136228</v>
+        <v>16.71777794725707</v>
       </c>
       <c r="D78" t="n">
-        <v>15.41469044686861</v>
+        <v>15.41468951180912</v>
       </c>
       <c r="E78" t="n">
-        <v>15.96616886900687</v>
+        <v>15.96616790049454</v>
       </c>
       <c r="F78" t="n">
         <v>1238200</v>
@@ -1992,16 +1992,16 @@
         <v>44210</v>
       </c>
       <c r="B79" t="n">
-        <v>16.08624839782715</v>
+        <v>16.08624649047852</v>
       </c>
       <c r="C79" t="n">
-        <v>16.25525010870889</v>
+        <v>16.2552481813217</v>
       </c>
       <c r="D79" t="n">
-        <v>15.65929831443531</v>
+        <v>15.65929645771021</v>
       </c>
       <c r="E79" t="n">
-        <v>15.94838005437391</v>
+        <v>15.94837816337235</v>
       </c>
       <c r="F79" t="n">
         <v>1217000</v>
@@ -2052,16 +2052,16 @@
         <v>44215</v>
       </c>
       <c r="B82" t="n">
-        <v>16.63328170776367</v>
+        <v>16.63327789306641</v>
       </c>
       <c r="C82" t="n">
-        <v>17.07802184223276</v>
+        <v>17.07801792553825</v>
       </c>
       <c r="D82" t="n">
-        <v>16.09514485567885</v>
+        <v>16.09514116439855</v>
       </c>
       <c r="E82" t="n">
-        <v>17.07802184223276</v>
+        <v>17.07801792553825</v>
       </c>
       <c r="F82" t="n">
         <v>1918400</v>
@@ -2072,16 +2072,16 @@
         <v>44216</v>
       </c>
       <c r="B83" t="n">
-        <v>16.25525283813477</v>
+        <v>16.2552490234375</v>
       </c>
       <c r="C83" t="n">
-        <v>16.81117804940168</v>
+        <v>16.81117410424281</v>
       </c>
       <c r="D83" t="n">
-        <v>16.01064608448715</v>
+        <v>16.0106423271929</v>
       </c>
       <c r="E83" t="n">
-        <v>16.6999930071483</v>
+        <v>16.69998908808175</v>
       </c>
       <c r="F83" t="n">
         <v>1073000</v>
@@ -2092,16 +2092,16 @@
         <v>44217</v>
       </c>
       <c r="B84" t="n">
-        <v>15.85498332977295</v>
+        <v>15.85498428344727</v>
       </c>
       <c r="C84" t="n">
-        <v>16.36643336510678</v>
+        <v>16.36643434954472</v>
       </c>
       <c r="D84" t="n">
-        <v>15.53032160299971</v>
+        <v>15.53032253714568</v>
       </c>
       <c r="E84" t="n">
-        <v>16.25969670405826</v>
+        <v>16.25969768207601</v>
       </c>
       <c r="F84" t="n">
         <v>928200</v>
@@ -2152,16 +2152,16 @@
         <v>44223</v>
       </c>
       <c r="B87" t="n">
-        <v>15.00552940368652</v>
+        <v>15.00553035736084</v>
       </c>
       <c r="C87" t="n">
-        <v>15.5703477505178</v>
+        <v>15.57034874008907</v>
       </c>
       <c r="D87" t="n">
-        <v>14.53410435971512</v>
+        <v>14.53410528342808</v>
       </c>
       <c r="E87" t="n">
-        <v>14.74313271733759</v>
+        <v>14.74313365433532</v>
       </c>
       <c r="F87" t="n">
         <v>1909000</v>
@@ -2172,16 +2172,16 @@
         <v>44224</v>
       </c>
       <c r="B88" t="n">
-        <v>15.6592960357666</v>
+        <v>15.65930080413818</v>
       </c>
       <c r="C88" t="n">
-        <v>15.98840440416715</v>
+        <v>15.98840927275467</v>
       </c>
       <c r="D88" t="n">
-        <v>14.95215932080804</v>
+        <v>14.95216387385126</v>
       </c>
       <c r="E88" t="n">
-        <v>15.13450266509051</v>
+        <v>15.13450727365862</v>
       </c>
       <c r="F88" t="n">
         <v>3941600</v>
@@ -2192,16 +2192,16 @@
         <v>44225</v>
       </c>
       <c r="B89" t="n">
-        <v>15.74379920959473</v>
+        <v>15.74380111694336</v>
       </c>
       <c r="C89" t="n">
-        <v>16.55322600399441</v>
+        <v>16.55322800940445</v>
       </c>
       <c r="D89" t="n">
-        <v>15.38800579515856</v>
+        <v>15.38800765940311</v>
       </c>
       <c r="E89" t="n">
-        <v>16.01064257387312</v>
+        <v>16.01064451354961</v>
       </c>
       <c r="F89" t="n">
         <v>3936400</v>
@@ -2212,16 +2212,16 @@
         <v>44228</v>
       </c>
       <c r="B90" t="n">
-        <v>16.76670265197754</v>
+        <v>16.76670074462891</v>
       </c>
       <c r="C90" t="n">
-        <v>17.02909938733217</v>
+        <v>17.02909745013378</v>
       </c>
       <c r="D90" t="n">
-        <v>15.65929902065404</v>
+        <v>15.65929723928157</v>
       </c>
       <c r="E90" t="n">
-        <v>16.01064411819733</v>
+        <v>16.0106422968565</v>
       </c>
       <c r="F90" t="n">
         <v>3072200</v>
@@ -2232,16 +2232,16 @@
         <v>44229</v>
       </c>
       <c r="B91" t="n">
-        <v>17.08246803283691</v>
+        <v>17.08246612548828</v>
       </c>
       <c r="C91" t="n">
-        <v>17.32262810609502</v>
+        <v>17.32262617193124</v>
       </c>
       <c r="D91" t="n">
-        <v>16.76670295311732</v>
+        <v>16.76670108102554</v>
       </c>
       <c r="E91" t="n">
-        <v>16.76670295311732</v>
+        <v>16.76670108102554</v>
       </c>
       <c r="F91" t="n">
         <v>2620800</v>
@@ -2312,16 +2312,16 @@
         <v>44235</v>
       </c>
       <c r="B95" t="n">
-        <v>19.23056411743164</v>
+        <v>19.23056221008301</v>
       </c>
       <c r="C95" t="n">
-        <v>19.3684324730139</v>
+        <v>19.36843055199105</v>
       </c>
       <c r="D95" t="n">
-        <v>18.46561054497921</v>
+        <v>18.46560871350112</v>
       </c>
       <c r="E95" t="n">
-        <v>18.81250730618486</v>
+        <v>18.81250544030044</v>
       </c>
       <c r="F95" t="n">
         <v>1758400</v>
@@ -2352,16 +2352,16 @@
         <v>44237</v>
       </c>
       <c r="B97" t="n">
-        <v>18.55900192260742</v>
+        <v>18.55900001525879</v>
       </c>
       <c r="C97" t="n">
-        <v>18.9815053057677</v>
+        <v>18.98150335499749</v>
       </c>
       <c r="D97" t="n">
-        <v>18.24323689700658</v>
+        <v>18.2432350221098</v>
       </c>
       <c r="E97" t="n">
-        <v>18.87032029422808</v>
+        <v>18.87031835488459</v>
       </c>
       <c r="F97" t="n">
         <v>979000</v>
@@ -2372,16 +2372,16 @@
         <v>44238</v>
       </c>
       <c r="B98" t="n">
-        <v>18.63460922241211</v>
+        <v>18.63461112976074</v>
       </c>
       <c r="C98" t="n">
-        <v>19.14605927430059</v>
+        <v>19.14606123399878</v>
       </c>
       <c r="D98" t="n">
-        <v>18.4344758557824</v>
+        <v>18.43447774264635</v>
       </c>
       <c r="E98" t="n">
-        <v>18.55900252988591</v>
+        <v>18.55900442949581</v>
       </c>
       <c r="F98" t="n">
         <v>912400</v>
@@ -2392,16 +2392,16 @@
         <v>44239</v>
       </c>
       <c r="B99" t="n">
-        <v>18.51897430419922</v>
+        <v>18.51897811889648</v>
       </c>
       <c r="C99" t="n">
-        <v>18.72355430780561</v>
+        <v>18.72355816464402</v>
       </c>
       <c r="D99" t="n">
-        <v>18.16318262476451</v>
+        <v>18.16318636617275</v>
       </c>
       <c r="E99" t="n">
-        <v>18.58123763603172</v>
+        <v>18.58124146355452</v>
       </c>
       <c r="F99" t="n">
         <v>849600</v>
@@ -2412,16 +2412,16 @@
         <v>44244</v>
       </c>
       <c r="B100" t="n">
-        <v>18.52787399291992</v>
+        <v>18.52787208557129</v>
       </c>
       <c r="C100" t="n">
-        <v>18.68798071328474</v>
+        <v>18.68797878945395</v>
       </c>
       <c r="D100" t="n">
-        <v>18.20766055219028</v>
+        <v>18.20765867780597</v>
       </c>
       <c r="E100" t="n">
-        <v>18.51897898661644</v>
+        <v>18.5189770801835</v>
       </c>
       <c r="F100" t="n">
         <v>743200</v>
@@ -2452,16 +2452,16 @@
         <v>44246</v>
       </c>
       <c r="B102" t="n">
-        <v>18.27881813049316</v>
+        <v>18.27881622314453</v>
       </c>
       <c r="C102" t="n">
-        <v>18.57234653985784</v>
+        <v>18.57234460188025</v>
       </c>
       <c r="D102" t="n">
-        <v>17.92302637619491</v>
+        <v>17.92302450597225</v>
       </c>
       <c r="E102" t="n">
-        <v>18.23434479741172</v>
+        <v>18.23434289470377</v>
       </c>
       <c r="F102" t="n">
         <v>881800</v>
@@ -2472,16 +2472,16 @@
         <v>44249</v>
       </c>
       <c r="B103" t="n">
-        <v>17.81628608703613</v>
+        <v>17.81628799438477</v>
       </c>
       <c r="C103" t="n">
-        <v>18.46115776875395</v>
+        <v>18.46115974514026</v>
       </c>
       <c r="D103" t="n">
-        <v>16.95793769945958</v>
+        <v>16.95793951491647</v>
       </c>
       <c r="E103" t="n">
-        <v>17.34486104779998</v>
+        <v>17.34486290467952</v>
       </c>
       <c r="F103" t="n">
         <v>2023200</v>
@@ -2492,16 +2492,16 @@
         <v>44250</v>
       </c>
       <c r="B104" t="n">
-        <v>17.70065116882324</v>
+        <v>17.70065498352051</v>
       </c>
       <c r="C104" t="n">
-        <v>18.10091783631999</v>
+        <v>18.1009217372794</v>
       </c>
       <c r="D104" t="n">
-        <v>17.51830784175215</v>
+        <v>17.5183116171523</v>
       </c>
       <c r="E104" t="n">
-        <v>17.86075783582194</v>
+        <v>17.86076168502407</v>
       </c>
       <c r="F104" t="n">
         <v>1151400</v>
@@ -2512,16 +2512,16 @@
         <v>44251</v>
       </c>
       <c r="B105" t="n">
-        <v>17.68731498718262</v>
+        <v>17.68731307983398</v>
       </c>
       <c r="C105" t="n">
-        <v>18.09647508812474</v>
+        <v>18.09647313665348</v>
       </c>
       <c r="D105" t="n">
-        <v>17.54499828280719</v>
+        <v>17.54499639080558</v>
       </c>
       <c r="E105" t="n">
-        <v>17.70510499936678</v>
+        <v>17.70510309009973</v>
       </c>
       <c r="F105" t="n">
         <v>1411000</v>
@@ -2552,16 +2552,16 @@
         <v>44253</v>
       </c>
       <c r="B107" t="n">
-        <v>16.69999122619629</v>
+        <v>16.69998741149902</v>
       </c>
       <c r="C107" t="n">
-        <v>17.20699469335504</v>
+        <v>17.20699076284545</v>
       </c>
       <c r="D107" t="n">
-        <v>16.40201615907802</v>
+        <v>16.40201241244574</v>
       </c>
       <c r="E107" t="n">
-        <v>17.13583634176344</v>
+        <v>17.13583242750821</v>
       </c>
       <c r="F107" t="n">
         <v>1586600</v>
@@ -2592,16 +2592,16 @@
         <v>44257</v>
       </c>
       <c r="B109" t="n">
-        <v>16.655517578125</v>
+        <v>16.65551567077637</v>
       </c>
       <c r="C109" t="n">
-        <v>16.90457095571786</v>
+        <v>16.90456901984825</v>
       </c>
       <c r="D109" t="n">
-        <v>15.7526939947042</v>
+        <v>15.75269219074469</v>
       </c>
       <c r="E109" t="n">
-        <v>16.1796457927399</v>
+        <v>16.17964393988693</v>
       </c>
       <c r="F109" t="n">
         <v>1243600</v>
@@ -2612,16 +2612,16 @@
         <v>44258</v>
       </c>
       <c r="B110" t="n">
-        <v>16.19298553466797</v>
+        <v>16.19298362731934</v>
       </c>
       <c r="C110" t="n">
-        <v>16.80227894250898</v>
+        <v>16.80227696339255</v>
       </c>
       <c r="D110" t="n">
-        <v>15.61927044946103</v>
+        <v>15.61926860968948</v>
       </c>
       <c r="E110" t="n">
-        <v>16.80227894250898</v>
+        <v>16.80227696339255</v>
       </c>
       <c r="F110" t="n">
         <v>1368800</v>
@@ -2672,16 +2672,16 @@
         <v>44263</v>
       </c>
       <c r="B113" t="n">
-        <v>14.91213417053223</v>
+        <v>14.91213512420654</v>
       </c>
       <c r="C113" t="n">
-        <v>16.05956437827389</v>
+        <v>16.0595654053297</v>
       </c>
       <c r="D113" t="n">
-        <v>14.76537082800059</v>
+        <v>14.76537177228896</v>
       </c>
       <c r="E113" t="n">
-        <v>16.01064269858043</v>
+        <v>16.01064372250756</v>
       </c>
       <c r="F113" t="n">
         <v>3236800</v>
@@ -2692,16 +2692,16 @@
         <v>44264</v>
       </c>
       <c r="B114" t="n">
-        <v>14.76537227630615</v>
+        <v>14.7653694152832</v>
       </c>
       <c r="C114" t="n">
-        <v>15.42358744822494</v>
+        <v>15.42358445966246</v>
       </c>
       <c r="D114" t="n">
-        <v>14.55634387767591</v>
+        <v>14.5563410571555</v>
       </c>
       <c r="E114" t="n">
-        <v>15.11671737715943</v>
+        <v>15.11671444805785</v>
       </c>
       <c r="F114" t="n">
         <v>1628800</v>
@@ -2732,16 +2732,16 @@
         <v>44266</v>
       </c>
       <c r="B116" t="n">
-        <v>15.81940650939941</v>
+        <v>15.81940269470215</v>
       </c>
       <c r="C116" t="n">
-        <v>15.99285489107494</v>
+        <v>15.99285103455227</v>
       </c>
       <c r="D116" t="n">
-        <v>15.15674465650835</v>
+        <v>15.15674100160559</v>
       </c>
       <c r="E116" t="n">
-        <v>15.15674465650835</v>
+        <v>15.15674100160559</v>
       </c>
       <c r="F116" t="n">
         <v>2295400</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708873748779</v>
+        <v>15.67708587646484</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619716243003</v>
+        <v>16.00619424134576</v>
       </c>
       <c r="D118" t="n">
-        <v>15.49474536187826</v>
+        <v>15.49474253413244</v>
       </c>
       <c r="E118" t="n">
-        <v>15.61482539409169</v>
+        <v>15.61482254443162</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2792,16 +2792,16 @@
         <v>44271</v>
       </c>
       <c r="B119" t="n">
-        <v>16.46872329711914</v>
+        <v>16.46872520446777</v>
       </c>
       <c r="C119" t="n">
-        <v>16.8378583482222</v>
+        <v>16.83786029832273</v>
       </c>
       <c r="D119" t="n">
-        <v>15.68153321514211</v>
+        <v>15.6815350313212</v>
       </c>
       <c r="E119" t="n">
-        <v>15.68598156565223</v>
+        <v>15.68598338234651</v>
       </c>
       <c r="F119" t="n">
         <v>1963400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880805969238</v>
+        <v>16.58880615234375</v>
       </c>
       <c r="C120" t="n">
-        <v>16.75780979991704</v>
+        <v>16.75780787313692</v>
       </c>
       <c r="D120" t="n">
-        <v>16.07735788033358</v>
+        <v>16.07735603179049</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298957845627</v>
+        <v>16.19298771661808</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2832,16 +2832,16 @@
         <v>44273</v>
       </c>
       <c r="B121" t="n">
-        <v>16.21967124938965</v>
+        <v>16.21966934204102</v>
       </c>
       <c r="C121" t="n">
-        <v>17.2914947735938</v>
+        <v>17.29149274020432</v>
       </c>
       <c r="D121" t="n">
-        <v>16.077354559611</v>
+        <v>16.07735266899806</v>
       </c>
       <c r="E121" t="n">
-        <v>16.58880463333153</v>
+        <v>16.58880268257474</v>
       </c>
       <c r="F121" t="n">
         <v>1568800</v>
@@ -2852,16 +2852,16 @@
         <v>44274</v>
       </c>
       <c r="B122" t="n">
-        <v>16.32195854187012</v>
+        <v>16.32196426391602</v>
       </c>
       <c r="C122" t="n">
-        <v>16.5443285446298</v>
+        <v>16.54433434463272</v>
       </c>
       <c r="D122" t="n">
-        <v>15.89056019362082</v>
+        <v>15.8905657644299</v>
       </c>
       <c r="E122" t="n">
-        <v>16.17519352570546</v>
+        <v>16.17519919629943</v>
       </c>
       <c r="F122" t="n">
         <v>1059200</v>
@@ -2872,16 +2872,16 @@
         <v>44277</v>
       </c>
       <c r="B123" t="n">
-        <v>16.54433059692383</v>
+        <v>16.54433250427246</v>
       </c>
       <c r="C123" t="n">
-        <v>16.58435727024774</v>
+        <v>16.58435918221094</v>
       </c>
       <c r="D123" t="n">
-        <v>15.92169383334038</v>
+        <v>15.921695668907</v>
       </c>
       <c r="E123" t="n">
-        <v>16.26414388365641</v>
+        <v>16.26414575870311</v>
       </c>
       <c r="F123" t="n">
         <v>938000</v>
@@ -2892,16 +2892,16 @@
         <v>44278</v>
       </c>
       <c r="B124" t="n">
-        <v>16.0995922088623</v>
+        <v>16.09959030151367</v>
       </c>
       <c r="C124" t="n">
-        <v>16.49985728713733</v>
+        <v>16.49985533236855</v>
       </c>
       <c r="D124" t="n">
-        <v>15.87277380427914</v>
+        <v>15.87277192380211</v>
       </c>
       <c r="E124" t="n">
-        <v>16.4553839550675</v>
+        <v>16.45538200556756</v>
       </c>
       <c r="F124" t="n">
         <v>855200</v>
@@ -2912,16 +2912,16 @@
         <v>44279</v>
       </c>
       <c r="B125" t="n">
-        <v>15.41024303436279</v>
+        <v>15.41024589538574</v>
       </c>
       <c r="C125" t="n">
-        <v>16.2107747654813</v>
+        <v>16.21077777512874</v>
       </c>
       <c r="D125" t="n">
-        <v>15.21455633135589</v>
+        <v>15.21455915604819</v>
       </c>
       <c r="E125" t="n">
-        <v>16.05066807994787</v>
+        <v>16.05067105987036</v>
       </c>
       <c r="F125" t="n">
         <v>1010400</v>
@@ -2952,16 +2952,16 @@
         <v>44281</v>
       </c>
       <c r="B127" t="n">
-        <v>15.85498332977295</v>
+        <v>15.85498428344727</v>
       </c>
       <c r="C127" t="n">
-        <v>16.41535504164929</v>
+        <v>16.41535602902986</v>
       </c>
       <c r="D127" t="n">
-        <v>15.67263997864547</v>
+        <v>15.67264092135187</v>
       </c>
       <c r="E127" t="n">
-        <v>16.1040366699186</v>
+        <v>16.10403763857342</v>
       </c>
       <c r="F127" t="n">
         <v>1078200</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.58369159698486</v>
+        <v>15.5836935043335</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174662887645</v>
+        <v>16.00174858739247</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245324175128</v>
+        <v>15.39245512569351</v>
       </c>
       <c r="E128" t="n">
-        <v>15.74379828476634</v>
+        <v>15.74380021171105</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514236450195</v>
+        <v>16.09514427185059</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23745904978063</v>
+        <v>16.23746097399444</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48584894961834</v>
+        <v>15.48585078476289</v>
       </c>
       <c r="E129" t="n">
-        <v>15.58813896112809</v>
+        <v>15.58814080839448</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3012,16 +3012,16 @@
         <v>44286</v>
       </c>
       <c r="B130" t="n">
-        <v>16.6154899597168</v>
+        <v>16.61548805236816</v>
       </c>
       <c r="C130" t="n">
-        <v>16.71777997637457</v>
+        <v>16.71777805728372</v>
       </c>
       <c r="D130" t="n">
-        <v>15.94393147674567</v>
+        <v>15.94392964648752</v>
       </c>
       <c r="E130" t="n">
-        <v>16.10848653082663</v>
+        <v>16.10848468167865</v>
       </c>
       <c r="F130" t="n">
         <v>1491400</v>
@@ -3032,16 +3032,16 @@
         <v>44287</v>
       </c>
       <c r="B131" t="n">
-        <v>16.59325408935547</v>
+        <v>16.59325218200684</v>
       </c>
       <c r="C131" t="n">
-        <v>17.04244085328361</v>
+        <v>17.0424388943022</v>
       </c>
       <c r="D131" t="n">
-        <v>16.48651571663801</v>
+        <v>16.48651382155865</v>
       </c>
       <c r="E131" t="n">
-        <v>17.03799419867195</v>
+        <v>17.03799224020167</v>
       </c>
       <c r="F131" t="n">
         <v>1225400</v>
@@ -3072,16 +3072,16 @@
         <v>44292</v>
       </c>
       <c r="B133" t="n">
-        <v>17.52275848388672</v>
+        <v>17.52276039123535</v>
       </c>
       <c r="C133" t="n">
-        <v>17.56723180984916</v>
+        <v>17.5672337220387</v>
       </c>
       <c r="D133" t="n">
-        <v>16.82896340165162</v>
+        <v>16.8289652334808</v>
       </c>
       <c r="E133" t="n">
-        <v>16.8912267366185</v>
+        <v>16.89122857522503</v>
       </c>
       <c r="F133" t="n">
         <v>1684600</v>
@@ -3132,16 +3132,16 @@
         <v>44295</v>
       </c>
       <c r="B136" t="n">
-        <v>18.03420829772949</v>
+        <v>18.03421020507812</v>
       </c>
       <c r="C136" t="n">
-        <v>18.25657831791493</v>
+        <v>18.25658024878204</v>
       </c>
       <c r="D136" t="n">
-        <v>17.41157325913943</v>
+        <v>17.41157510063643</v>
       </c>
       <c r="E136" t="n">
-        <v>17.6428365871695</v>
+        <v>17.64283845312556</v>
       </c>
       <c r="F136" t="n">
         <v>1023600</v>
@@ -3212,16 +3212,16 @@
         <v>44301</v>
       </c>
       <c r="B140" t="n">
-        <v>17.38044166564941</v>
+        <v>17.38044357299805</v>
       </c>
       <c r="C140" t="n">
-        <v>17.60281168677666</v>
+        <v>17.60281361852843</v>
       </c>
       <c r="D140" t="n">
-        <v>17.17141330289424</v>
+        <v>17.17141518730387</v>
       </c>
       <c r="E140" t="n">
-        <v>17.17141330289424</v>
+        <v>17.17141518730387</v>
       </c>
       <c r="F140" t="n">
         <v>924800</v>
@@ -3272,16 +3272,16 @@
         <v>44306</v>
       </c>
       <c r="B143" t="n">
-        <v>17.81184005737305</v>
+        <v>17.81183815002441</v>
       </c>
       <c r="C143" t="n">
-        <v>18.40779183888181</v>
+        <v>18.40778986771676</v>
       </c>
       <c r="D143" t="n">
-        <v>17.62949669046246</v>
+        <v>17.62949480263974</v>
       </c>
       <c r="E143" t="n">
-        <v>18.01642008921442</v>
+        <v>18.01641815995871</v>
       </c>
       <c r="F143" t="n">
         <v>1050400</v>
@@ -3312,16 +3312,16 @@
         <v>44309</v>
       </c>
       <c r="B145" t="n">
-        <v>17.21144104003906</v>
+        <v>17.21143913269043</v>
       </c>
       <c r="C145" t="n">
-        <v>17.57167941077477</v>
+        <v>17.57167746350501</v>
       </c>
       <c r="D145" t="n">
-        <v>16.88233264191577</v>
+        <v>16.88233077103849</v>
       </c>
       <c r="E145" t="n">
-        <v>17.52275942819921</v>
+        <v>17.5227574863507</v>
       </c>
       <c r="F145" t="n">
         <v>903000</v>
@@ -3352,16 +3352,16 @@
         <v>44313</v>
       </c>
       <c r="B147" t="n">
-        <v>17.33596801757812</v>
+        <v>17.33596992492676</v>
       </c>
       <c r="C147" t="n">
-        <v>17.78070809508361</v>
+        <v>17.78071005136372</v>
       </c>
       <c r="D147" t="n">
-        <v>17.01130796458497</v>
+        <v>17.01130983621365</v>
       </c>
       <c r="E147" t="n">
-        <v>17.04688798512881</v>
+        <v>17.0468898606721</v>
       </c>
       <c r="F147" t="n">
         <v>1372600</v>
@@ -3372,16 +3372,16 @@
         <v>44314</v>
       </c>
       <c r="B148" t="n">
-        <v>18.56789970397949</v>
+        <v>18.56789779663086</v>
       </c>
       <c r="C148" t="n">
-        <v>18.63905805414477</v>
+        <v>18.63905613948654</v>
       </c>
       <c r="D148" t="n">
-        <v>17.32707438245799</v>
+        <v>17.32707260257054</v>
       </c>
       <c r="E148" t="n">
-        <v>17.33596938829726</v>
+        <v>17.33596760749609</v>
       </c>
       <c r="F148" t="n">
         <v>2195600</v>
@@ -3392,16 +3392,16 @@
         <v>44315</v>
       </c>
       <c r="B149" t="n">
-        <v>18.93703651428223</v>
+        <v>18.93703460693359</v>
       </c>
       <c r="C149" t="n">
-        <v>19.07045822076813</v>
+        <v>19.0704562999812</v>
       </c>
       <c r="D149" t="n">
-        <v>18.13205622722375</v>
+        <v>18.13205440095317</v>
       </c>
       <c r="E149" t="n">
-        <v>18.57234802828215</v>
+        <v>18.57234615766514</v>
       </c>
       <c r="F149" t="n">
         <v>2301200</v>
@@ -3412,16 +3412,16 @@
         <v>44316</v>
       </c>
       <c r="B150" t="n">
-        <v>19.34006118774414</v>
+        <v>19.34005928039551</v>
       </c>
       <c r="C150" t="n">
-        <v>19.34006118774414</v>
+        <v>19.34005928039551</v>
       </c>
       <c r="D150" t="n">
-        <v>18.38334087467527</v>
+        <v>18.38333906167997</v>
       </c>
       <c r="E150" t="n">
-        <v>18.86617264318869</v>
+        <v>18.86617078257573</v>
       </c>
       <c r="F150" t="n">
         <v>2355400</v>
@@ -3432,16 +3432,16 @@
         <v>44319</v>
       </c>
       <c r="B151" t="n">
-        <v>19.44735717773438</v>
+        <v>19.44735908508301</v>
       </c>
       <c r="C151" t="n">
-        <v>19.67089001885776</v>
+        <v>19.67089194812994</v>
       </c>
       <c r="D151" t="n">
-        <v>18.83934757701153</v>
+        <v>18.83934942472809</v>
       </c>
       <c r="E151" t="n">
-        <v>19.62618413280117</v>
+        <v>19.62618605768871</v>
       </c>
       <c r="F151" t="n">
         <v>2225200</v>
@@ -3452,16 +3452,16 @@
         <v>44320</v>
       </c>
       <c r="B152" t="n">
-        <v>19.79607009887695</v>
+        <v>19.79606819152832</v>
       </c>
       <c r="C152" t="n">
-        <v>20.00619153898745</v>
+        <v>20.00618961139364</v>
       </c>
       <c r="D152" t="n">
-        <v>19.25959258395553</v>
+        <v>19.25959072829643</v>
       </c>
       <c r="E152" t="n">
-        <v>19.4518292800361</v>
+        <v>19.45182740585503</v>
       </c>
       <c r="F152" t="n">
         <v>1635200</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.83326148986816</v>
+        <v>20.83325958251953</v>
       </c>
       <c r="C155" t="n">
-        <v>20.877969084305</v>
+        <v>20.87796717286325</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384283351365</v>
+        <v>20.36384096914172</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902756541763</v>
+        <v>20.86902565479451</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3552,16 +3552,16 @@
         <v>44327</v>
       </c>
       <c r="B157" t="n">
-        <v>20.60078811645508</v>
+        <v>20.60078620910645</v>
       </c>
       <c r="C157" t="n">
-        <v>20.60972792961658</v>
+        <v>20.60972602144025</v>
       </c>
       <c r="D157" t="n">
-        <v>19.7826570731339</v>
+        <v>19.78265524153291</v>
       </c>
       <c r="E157" t="n">
-        <v>20.25207571344624</v>
+        <v>20.25207383838357</v>
       </c>
       <c r="F157" t="n">
         <v>1012800</v>
@@ -3652,16 +3652,16 @@
         <v>44334</v>
       </c>
       <c r="B162" t="n">
-        <v>21.12385559082031</v>
+        <v>21.12385368347168</v>
       </c>
       <c r="C162" t="n">
-        <v>21.74080677130802</v>
+        <v>21.74080480825265</v>
       </c>
       <c r="D162" t="n">
-        <v>20.8824396890529</v>
+        <v>20.88243780350257</v>
       </c>
       <c r="E162" t="n">
-        <v>21.15068014837905</v>
+        <v>21.15067823860833</v>
       </c>
       <c r="F162" t="n">
         <v>1192600</v>
@@ -3672,16 +3672,16 @@
         <v>44335</v>
       </c>
       <c r="B163" t="n">
-        <v>21.3697395324707</v>
+        <v>21.36974143981934</v>
       </c>
       <c r="C163" t="n">
-        <v>21.49044747280858</v>
+        <v>21.49044939093096</v>
       </c>
       <c r="D163" t="n">
-        <v>20.88690947653946</v>
+        <v>20.88691134079327</v>
       </c>
       <c r="E163" t="n">
-        <v>21.2043257055278</v>
+        <v>21.20432759811249</v>
       </c>
       <c r="F163" t="n">
         <v>1135200</v>
@@ -3712,16 +3712,16 @@
         <v>44337</v>
       </c>
       <c r="B165" t="n">
-        <v>21.94645500183105</v>
+        <v>21.94645690917969</v>
       </c>
       <c r="C165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04034030384297</v>
       </c>
       <c r="D165" t="n">
-        <v>21.50385921408051</v>
+        <v>21.5038610829635</v>
       </c>
       <c r="E165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04034030384297</v>
       </c>
       <c r="F165" t="n">
         <v>653400</v>
@@ -3752,16 +3752,16 @@
         <v>44341</v>
       </c>
       <c r="B167" t="n">
-        <v>22.17892646789551</v>
+        <v>22.17892837524414</v>
       </c>
       <c r="C167" t="n">
-        <v>22.36222331038142</v>
+        <v>22.36222523349326</v>
       </c>
       <c r="D167" t="n">
-        <v>21.77209680747946</v>
+        <v>21.77209867984146</v>
       </c>
       <c r="E167" t="n">
-        <v>21.98221649664815</v>
+        <v>21.98221838708007</v>
       </c>
       <c r="F167" t="n">
         <v>773000</v>
@@ -3772,16 +3772,16 @@
         <v>44342</v>
       </c>
       <c r="B168" t="n">
-        <v>22.1744556427002</v>
+        <v>22.17445755004883</v>
       </c>
       <c r="C168" t="n">
-        <v>22.42481302160963</v>
+        <v>22.42481495049289</v>
       </c>
       <c r="D168" t="n">
-        <v>21.53515162431978</v>
+        <v>21.53515347667831</v>
       </c>
       <c r="E168" t="n">
-        <v>22.1744556427002</v>
+        <v>22.17445755004883</v>
       </c>
       <c r="F168" t="n">
         <v>837000</v>
@@ -3792,16 +3792,16 @@
         <v>44343</v>
       </c>
       <c r="B169" t="n">
-        <v>22.34434509277344</v>
+        <v>22.3443431854248</v>
       </c>
       <c r="C169" t="n">
-        <v>22.34434509277344</v>
+        <v>22.3443431854248</v>
       </c>
       <c r="D169" t="n">
-        <v>21.80339596606228</v>
+        <v>21.80339410488992</v>
       </c>
       <c r="E169" t="n">
-        <v>22.27281464383163</v>
+        <v>22.27281274258895</v>
       </c>
       <c r="F169" t="n">
         <v>1342400</v>
@@ -3932,16 +3932,16 @@
         <v>44355</v>
       </c>
       <c r="B176" t="n">
-        <v>23.40389060974121</v>
+        <v>23.40388679504395</v>
       </c>
       <c r="C176" t="n">
-        <v>23.68107259410971</v>
+        <v>23.68106873423341</v>
       </c>
       <c r="D176" t="n">
-        <v>22.95235496652872</v>
+        <v>22.95235122542912</v>
       </c>
       <c r="E176" t="n">
-        <v>23.47095115234466</v>
+        <v>23.47094732671691</v>
       </c>
       <c r="F176" t="n">
         <v>1006800</v>
@@ -4012,16 +4012,16 @@
         <v>44361</v>
       </c>
       <c r="B180" t="n">
-        <v>24.58861351013184</v>
+        <v>24.58860969543457</v>
       </c>
       <c r="C180" t="n">
-        <v>24.76744047237364</v>
+        <v>24.76743662993302</v>
       </c>
       <c r="D180" t="n">
-        <v>23.26082783485022</v>
+        <v>23.26082422614669</v>
       </c>
       <c r="E180" t="n">
-        <v>23.45753783440027</v>
+        <v>23.45753419517899</v>
       </c>
       <c r="F180" t="n">
         <v>1774600</v>
@@ -4032,16 +4032,16 @@
         <v>44362</v>
       </c>
       <c r="B181" t="n">
-        <v>24.32037544250488</v>
+        <v>24.32037353515625</v>
       </c>
       <c r="C181" t="n">
-        <v>24.97756088020314</v>
+        <v>24.97755892131411</v>
       </c>
       <c r="D181" t="n">
-        <v>23.85989659893767</v>
+        <v>23.85989472770252</v>
       </c>
       <c r="E181" t="n">
-        <v>24.60649722564159</v>
+        <v>24.60649529585358</v>
       </c>
       <c r="F181" t="n">
         <v>1629200</v>
@@ -4072,16 +4072,16 @@
         <v>44364</v>
       </c>
       <c r="B183" t="n">
-        <v>24.58861351013184</v>
+        <v>24.58860969543457</v>
       </c>
       <c r="C183" t="n">
-        <v>24.71379136044892</v>
+        <v>24.71378752633146</v>
       </c>
       <c r="D183" t="n">
-        <v>23.96719245974302</v>
+        <v>23.96718874145352</v>
       </c>
       <c r="E183" t="n">
-        <v>24.63331939798214</v>
+        <v>24.63331557634916</v>
       </c>
       <c r="F183" t="n">
         <v>897400</v>
@@ -4092,16 +4092,16 @@
         <v>44365</v>
       </c>
       <c r="B184" t="n">
-        <v>24.89708518981934</v>
+        <v>24.8970890045166</v>
       </c>
       <c r="C184" t="n">
-        <v>25.19214844770217</v>
+        <v>25.19215230760862</v>
       </c>
       <c r="D184" t="n">
-        <v>24.25778118016986</v>
+        <v>24.25778489691384</v>
       </c>
       <c r="E184" t="n">
-        <v>24.67802397850789</v>
+        <v>24.6780277596409</v>
       </c>
       <c r="F184" t="n">
         <v>1737600</v>
@@ -4112,16 +4112,16 @@
         <v>44368</v>
       </c>
       <c r="B185" t="n">
-        <v>25.23685646057129</v>
+        <v>25.23686027526855</v>
       </c>
       <c r="C185" t="n">
-        <v>25.6481560428541</v>
+        <v>25.64815991972168</v>
       </c>
       <c r="D185" t="n">
-        <v>24.69590742957842</v>
+        <v>24.6959111625081</v>
       </c>
       <c r="E185" t="n">
-        <v>25.25026788443091</v>
+        <v>25.25027170115539</v>
       </c>
       <c r="F185" t="n">
         <v>748400</v>
@@ -4132,16 +4132,16 @@
         <v>44369</v>
       </c>
       <c r="B186" t="n">
-        <v>24.58861351013184</v>
+        <v>24.58860969543457</v>
       </c>
       <c r="C186" t="n">
-        <v>25.26815357906228</v>
+        <v>25.26814965894062</v>
       </c>
       <c r="D186" t="n">
-        <v>24.54390762228154</v>
+        <v>24.54390381451998</v>
       </c>
       <c r="E186" t="n">
-        <v>25.2323875044458</v>
+        <v>25.23238358987291</v>
       </c>
       <c r="F186" t="n">
         <v>871000</v>
@@ -4252,16 +4252,16 @@
         <v>44377</v>
       </c>
       <c r="B192" t="n">
-        <v>24.86579513549805</v>
+        <v>24.86579322814941</v>
       </c>
       <c r="C192" t="n">
-        <v>24.86579513549805</v>
+        <v>24.86579322814941</v>
       </c>
       <c r="D192" t="n">
-        <v>24.12813771284097</v>
+        <v>24.12813586207488</v>
       </c>
       <c r="E192" t="n">
-        <v>24.16837369628921</v>
+        <v>24.16837184243678</v>
       </c>
       <c r="F192" t="n">
         <v>1430400</v>
@@ -4272,16 +4272,16 @@
         <v>44378</v>
       </c>
       <c r="B193" t="n">
-        <v>24.92838287353516</v>
+        <v>24.92838096618652</v>
       </c>
       <c r="C193" t="n">
-        <v>25.96557687450705</v>
+        <v>25.96557488779945</v>
       </c>
       <c r="D193" t="n">
-        <v>24.91050154151692</v>
+        <v>24.91049963553645</v>
       </c>
       <c r="E193" t="n">
-        <v>25.2592122444671</v>
+        <v>25.25921031180567</v>
       </c>
       <c r="F193" t="n">
         <v>1991200</v>
@@ -4312,16 +4312,16 @@
         <v>44382</v>
       </c>
       <c r="B195" t="n">
-        <v>26.53334808349609</v>
+        <v>26.53334617614746</v>
       </c>
       <c r="C195" t="n">
-        <v>26.77923557792692</v>
+        <v>26.77923365290268</v>
       </c>
       <c r="D195" t="n">
-        <v>26.17122596518936</v>
+        <v>26.17122408387186</v>
       </c>
       <c r="E195" t="n">
-        <v>26.3813456803117</v>
+        <v>26.38134378388976</v>
       </c>
       <c r="F195" t="n">
         <v>581600</v>
@@ -4332,16 +4332,16 @@
         <v>44383</v>
       </c>
       <c r="B196" t="n">
-        <v>26.19804763793945</v>
+        <v>26.19804954528809</v>
       </c>
       <c r="C196" t="n">
-        <v>26.53334689118315</v>
+        <v>26.53334882294324</v>
       </c>
       <c r="D196" t="n">
-        <v>25.66157019708569</v>
+        <v>25.66157206537609</v>
       </c>
       <c r="E196" t="n">
-        <v>26.53334689118315</v>
+        <v>26.53334882294324</v>
       </c>
       <c r="F196" t="n">
         <v>905000</v>
@@ -4352,16 +4352,16 @@
         <v>44384</v>
       </c>
       <c r="B197" t="n">
-        <v>26.52441215515137</v>
+        <v>26.52440452575684</v>
       </c>
       <c r="C197" t="n">
-        <v>26.93571183258231</v>
+        <v>26.93570408488289</v>
       </c>
       <c r="D197" t="n">
-        <v>26.10864086511936</v>
+        <v>26.10863335531591</v>
       </c>
       <c r="E197" t="n">
-        <v>26.19805265209442</v>
+        <v>26.19804511657286</v>
       </c>
       <c r="F197" t="n">
         <v>915800</v>
@@ -4372,16 +4372,16 @@
         <v>44385</v>
       </c>
       <c r="B198" t="n">
-        <v>26.52441215515137</v>
+        <v>26.52440452575684</v>
       </c>
       <c r="C198" t="n">
-        <v>26.52441215515137</v>
+        <v>26.52440452575684</v>
       </c>
       <c r="D198" t="n">
-        <v>25.8225173483694</v>
+        <v>25.82250992086558</v>
       </c>
       <c r="E198" t="n">
-        <v>26.23828863840141</v>
+        <v>26.2382810913065</v>
       </c>
       <c r="F198" t="n">
         <v>1041800</v>
@@ -4472,16 +4472,16 @@
         <v>44393</v>
       </c>
       <c r="B203" t="n">
-        <v>28.79102897644043</v>
+        <v>28.79103088378906</v>
       </c>
       <c r="C203" t="n">
-        <v>29.03244484038268</v>
+        <v>29.03244676372463</v>
       </c>
       <c r="D203" t="n">
-        <v>28.15172495086382</v>
+        <v>28.15172681585982</v>
       </c>
       <c r="E203" t="n">
-        <v>28.72844005736358</v>
+        <v>28.72844196056582</v>
       </c>
       <c r="F203" t="n">
         <v>1048600</v>
@@ -4492,16 +4492,16 @@
         <v>44396</v>
       </c>
       <c r="B204" t="n">
-        <v>28.77314949035645</v>
+        <v>28.77314758300781</v>
       </c>
       <c r="C204" t="n">
-        <v>29.12186019989915</v>
+        <v>29.12185826943477</v>
       </c>
       <c r="D204" t="n">
-        <v>28.02207895794112</v>
+        <v>28.02207710038034</v>
       </c>
       <c r="E204" t="n">
-        <v>28.38420279852648</v>
+        <v>28.3842009169608</v>
       </c>
       <c r="F204" t="n">
         <v>866800</v>
@@ -4532,16 +4532,16 @@
         <v>44398</v>
       </c>
       <c r="B206" t="n">
-        <v>29.60469245910645</v>
+        <v>29.60468673706055</v>
       </c>
       <c r="C206" t="n">
-        <v>29.7835194288818</v>
+        <v>29.78351367227192</v>
       </c>
       <c r="D206" t="n">
-        <v>29.05927173616996</v>
+        <v>29.05926611954392</v>
       </c>
       <c r="E206" t="n">
-        <v>29.52869210547517</v>
+        <v>29.52868639811875</v>
       </c>
       <c r="F206" t="n">
         <v>1050200</v>
@@ -4592,16 +4592,16 @@
         <v>44403</v>
       </c>
       <c r="B209" t="n">
-        <v>30.0875186920166</v>
+        <v>30.08752059936523</v>
       </c>
       <c r="C209" t="n">
-        <v>30.48987503607723</v>
+        <v>30.48987696893258</v>
       </c>
       <c r="D209" t="n">
-        <v>29.56444930522557</v>
+        <v>29.56445117941508</v>
       </c>
       <c r="E209" t="n">
-        <v>30.48987503607723</v>
+        <v>30.48987696893258</v>
       </c>
       <c r="F209" t="n">
         <v>1240800</v>
@@ -4612,16 +4612,16 @@
         <v>44404</v>
       </c>
       <c r="B210" t="n">
-        <v>29.40797996520996</v>
+        <v>29.40797805786133</v>
       </c>
       <c r="C210" t="n">
-        <v>30.1992881310479</v>
+        <v>30.19928617237645</v>
       </c>
       <c r="D210" t="n">
-        <v>29.30068515675142</v>
+        <v>29.30068325636174</v>
       </c>
       <c r="E210" t="n">
-        <v>29.98916671513793</v>
+        <v>29.98916477009458</v>
       </c>
       <c r="F210" t="n">
         <v>1032400</v>
@@ -4632,16 +4632,16 @@
         <v>44405</v>
       </c>
       <c r="B211" t="n">
-        <v>29.43927574157715</v>
+        <v>29.43927383422852</v>
       </c>
       <c r="C211" t="n">
-        <v>30.57035141986809</v>
+        <v>30.57034943923792</v>
       </c>
       <c r="D211" t="n">
-        <v>28.73291111508599</v>
+        <v>28.7329092535022</v>
       </c>
       <c r="E211" t="n">
-        <v>29.52869092832068</v>
+        <v>29.52868901517891</v>
       </c>
       <c r="F211" t="n">
         <v>1257400</v>
@@ -4652,16 +4652,16 @@
         <v>44406</v>
       </c>
       <c r="B212" t="n">
-        <v>30.8475341796875</v>
+        <v>30.84753227233887</v>
       </c>
       <c r="C212" t="n">
-        <v>31.51366113664825</v>
+        <v>31.51365918811201</v>
       </c>
       <c r="D212" t="n">
-        <v>29.56445435619494</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="E212" t="n">
-        <v>29.56445435619494</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="F212" t="n">
         <v>1386000</v>
@@ -4692,16 +4692,16 @@
         <v>44410</v>
       </c>
       <c r="B214" t="n">
-        <v>31.24988746643066</v>
+        <v>31.2498893737793</v>
       </c>
       <c r="C214" t="n">
-        <v>31.98754642033019</v>
+        <v>31.98754837270211</v>
       </c>
       <c r="D214" t="n">
-        <v>31.03976607965759</v>
+        <v>31.03976797418139</v>
       </c>
       <c r="E214" t="n">
-        <v>31.58071506962657</v>
+        <v>31.5807169971674</v>
       </c>
       <c r="F214" t="n">
         <v>1185600</v>
@@ -4712,16 +4712,16 @@
         <v>44411</v>
       </c>
       <c r="B215" t="n">
-        <v>30.62400054931641</v>
+        <v>30.62399673461914</v>
       </c>
       <c r="C215" t="n">
-        <v>31.14259840020176</v>
+        <v>31.14259452090504</v>
       </c>
       <c r="D215" t="n">
-        <v>30.20375769848453</v>
+        <v>30.20375393613507</v>
       </c>
       <c r="E215" t="n">
-        <v>31.13812678815189</v>
+        <v>31.13812290941217</v>
       </c>
       <c r="F215" t="n">
         <v>1467200</v>
@@ -4752,16 +4752,16 @@
         <v>44413</v>
       </c>
       <c r="B217" t="n">
-        <v>29.48398017883301</v>
+        <v>29.48398208618164</v>
       </c>
       <c r="C217" t="n">
-        <v>30.38705476088549</v>
+        <v>30.38705672665493</v>
       </c>
       <c r="D217" t="n">
-        <v>29.13974110661963</v>
+        <v>29.13974299169909</v>
       </c>
       <c r="E217" t="n">
-        <v>29.82375105005952</v>
+        <v>29.82375297938827</v>
       </c>
       <c r="F217" t="n">
         <v>1197200</v>
@@ -4792,16 +4792,16 @@
         <v>44417</v>
       </c>
       <c r="B219" t="n">
-        <v>30.2395191192627</v>
+        <v>30.23952293395996</v>
       </c>
       <c r="C219" t="n">
-        <v>30.4049346312439</v>
+        <v>30.40493846680823</v>
       </c>
       <c r="D219" t="n">
-        <v>29.54209782380482</v>
+        <v>29.5421015505228</v>
       </c>
       <c r="E219" t="n">
-        <v>29.85951401368219</v>
+        <v>29.85951778044203</v>
       </c>
       <c r="F219" t="n">
         <v>1023000</v>
@@ -4832,16 +4832,16 @@
         <v>44419</v>
       </c>
       <c r="B221" t="n">
-        <v>29.11291694641113</v>
+        <v>29.11291885375977</v>
       </c>
       <c r="C221" t="n">
-        <v>30.38258178096093</v>
+        <v>30.38258377149235</v>
       </c>
       <c r="D221" t="n">
-        <v>28.14725348562089</v>
+        <v>28.14725532970356</v>
       </c>
       <c r="E221" t="n">
-        <v>29.68516044428373</v>
+        <v>29.68516238912321</v>
       </c>
       <c r="F221" t="n">
         <v>1237750</v>
@@ -4852,16 +4852,16 @@
         <v>44420</v>
       </c>
       <c r="B222" t="n">
-        <v>29.3275089263916</v>
+        <v>29.32750701904297</v>
       </c>
       <c r="C222" t="n">
-        <v>31.1873038558452</v>
+        <v>31.18730182754265</v>
       </c>
       <c r="D222" t="n">
-        <v>28.46914361010866</v>
+        <v>28.46914175858482</v>
       </c>
       <c r="E222" t="n">
-        <v>28.48702664721963</v>
+        <v>28.48702479453274</v>
       </c>
       <c r="F222" t="n">
         <v>1567750</v>
@@ -4892,16 +4892,16 @@
         <v>44424</v>
       </c>
       <c r="B224" t="n">
-        <v>25.64369010925293</v>
+        <v>25.6436882019043</v>
       </c>
       <c r="C224" t="n">
-        <v>28.14725747247807</v>
+        <v>28.14725537891694</v>
       </c>
       <c r="D224" t="n">
-        <v>24.26672686568483</v>
+        <v>24.26672506075316</v>
       </c>
       <c r="E224" t="n">
-        <v>28.14725747247807</v>
+        <v>28.14725537891694</v>
       </c>
       <c r="F224" t="n">
         <v>6674400</v>
@@ -4912,16 +4912,16 @@
         <v>44425</v>
       </c>
       <c r="B225" t="n">
-        <v>25.66157341003418</v>
+        <v>25.66157150268555</v>
       </c>
       <c r="C225" t="n">
-        <v>25.66157341003418</v>
+        <v>25.66157150268555</v>
       </c>
       <c r="D225" t="n">
-        <v>23.42624477520264</v>
+        <v>23.42624303399936</v>
       </c>
       <c r="E225" t="n">
-        <v>24.67802846962422</v>
+        <v>24.67802663537957</v>
       </c>
       <c r="F225" t="n">
         <v>4282800</v>
@@ -4952,16 +4952,16 @@
         <v>44427</v>
       </c>
       <c r="B227" t="n">
-        <v>26.46628761291504</v>
+        <v>26.46628952026367</v>
       </c>
       <c r="C227" t="n">
-        <v>26.73452632877229</v>
+        <v>26.73452825545211</v>
       </c>
       <c r="D227" t="n">
-        <v>24.3024897339607</v>
+        <v>24.30249148537069</v>
       </c>
       <c r="E227" t="n">
-        <v>24.85685020151106</v>
+        <v>24.8568519928722</v>
       </c>
       <c r="F227" t="n">
         <v>1738450</v>
@@ -5012,16 +5012,16 @@
         <v>44432</v>
       </c>
       <c r="B230" t="n">
-        <v>27.48559761047363</v>
+        <v>27.48559951782227</v>
       </c>
       <c r="C230" t="n">
-        <v>27.84324981090064</v>
+        <v>27.84325174306836</v>
       </c>
       <c r="D230" t="n">
-        <v>27.00276756625223</v>
+        <v>27.00276944009512</v>
       </c>
       <c r="E230" t="n">
-        <v>27.64654152702084</v>
+        <v>27.64654344553809</v>
       </c>
       <c r="F230" t="n">
         <v>835550</v>
@@ -5032,16 +5032,16 @@
         <v>44433</v>
       </c>
       <c r="B231" t="n">
-        <v>27.89689826965332</v>
+        <v>27.89690208435059</v>
       </c>
       <c r="C231" t="n">
-        <v>28.4154943745372</v>
+        <v>28.4154982601487</v>
       </c>
       <c r="D231" t="n">
-        <v>27.2710056544327</v>
+        <v>27.27100938354371</v>
       </c>
       <c r="E231" t="n">
-        <v>27.48559696968601</v>
+        <v>27.48560072814082</v>
       </c>
       <c r="F231" t="n">
         <v>1098800</v>
@@ -5072,16 +5072,16 @@
         <v>44435</v>
       </c>
       <c r="B233" t="n">
-        <v>28.9698600769043</v>
+        <v>28.96985816955566</v>
       </c>
       <c r="C233" t="n">
-        <v>29.11292097115001</v>
+        <v>29.11291905438238</v>
       </c>
       <c r="D233" t="n">
-        <v>27.00277022289511</v>
+        <v>27.00276844505784</v>
       </c>
       <c r="E233" t="n">
-        <v>27.44983594376807</v>
+        <v>27.44983413649641</v>
       </c>
       <c r="F233" t="n">
         <v>1634000</v>
@@ -5112,16 +5112,16 @@
         <v>44439</v>
       </c>
       <c r="B235" t="n">
-        <v>26.55570220947266</v>
+        <v>26.55570030212402</v>
       </c>
       <c r="C235" t="n">
-        <v>27.86113318312228</v>
+        <v>27.86113118201179</v>
       </c>
       <c r="D235" t="n">
-        <v>25.87616216775989</v>
+        <v>25.87616030921885</v>
       </c>
       <c r="E235" t="n">
-        <v>27.68230622804304</v>
+        <v>27.6823042397767</v>
       </c>
       <c r="F235" t="n">
         <v>1705500</v>
@@ -5152,16 +5152,16 @@
         <v>44441</v>
       </c>
       <c r="B237" t="n">
-        <v>25.35756492614746</v>
+        <v>25.35756683349609</v>
       </c>
       <c r="C237" t="n">
-        <v>26.66299584222149</v>
+        <v>26.6629978477622</v>
       </c>
       <c r="D237" t="n">
-        <v>25.10720754116251</v>
+        <v>25.10720942967972</v>
       </c>
       <c r="E237" t="n">
-        <v>26.59146540442867</v>
+        <v>26.59146740458899</v>
       </c>
       <c r="F237" t="n">
         <v>1706000</v>
@@ -5172,16 +5172,16 @@
         <v>44442</v>
       </c>
       <c r="B238" t="n">
-        <v>25.03567886352539</v>
+        <v>25.03568077087402</v>
       </c>
       <c r="C238" t="n">
-        <v>25.84039677162608</v>
+        <v>25.84039874028232</v>
       </c>
       <c r="D238" t="n">
-        <v>24.80320449799936</v>
+        <v>24.80320638763689</v>
       </c>
       <c r="E238" t="n">
-        <v>25.57215803739928</v>
+        <v>25.57215998561969</v>
       </c>
       <c r="F238" t="n">
         <v>2369000</v>
@@ -5192,16 +5192,16 @@
         <v>44445</v>
       </c>
       <c r="B239" t="n">
-        <v>25.76886558532715</v>
+        <v>25.76886367797852</v>
       </c>
       <c r="C239" t="n">
-        <v>25.89404343029868</v>
+        <v>25.89404151368469</v>
       </c>
       <c r="D239" t="n">
-        <v>24.87473422314136</v>
+        <v>24.87473238197415</v>
       </c>
       <c r="E239" t="n">
-        <v>24.87473422314136</v>
+        <v>24.87473238197415</v>
       </c>
       <c r="F239" t="n">
         <v>528250</v>
@@ -5212,16 +5212,16 @@
         <v>44447</v>
       </c>
       <c r="B240" t="n">
-        <v>24.4813175201416</v>
+        <v>24.48131561279297</v>
       </c>
       <c r="C240" t="n">
-        <v>26.10863813649156</v>
+        <v>26.10863610235777</v>
       </c>
       <c r="D240" t="n">
-        <v>24.32037529715434</v>
+        <v>24.32037340234477</v>
       </c>
       <c r="E240" t="n">
-        <v>25.59004198130058</v>
+        <v>25.59003998757081</v>
       </c>
       <c r="F240" t="n">
         <v>1259500</v>
@@ -5232,16 +5232,16 @@
         <v>44448</v>
       </c>
       <c r="B241" t="n">
-        <v>25.03567886352539</v>
+        <v>25.03568077087402</v>
       </c>
       <c r="C241" t="n">
-        <v>25.75098329174372</v>
+        <v>25.75098525358797</v>
       </c>
       <c r="D241" t="n">
-        <v>23.8017782984937</v>
+        <v>23.80178011183736</v>
       </c>
       <c r="E241" t="n">
-        <v>23.99848658989868</v>
+        <v>23.99848841822859</v>
       </c>
       <c r="F241" t="n">
         <v>1540350</v>
@@ -5252,16 +5252,16 @@
         <v>44449</v>
       </c>
       <c r="B242" t="n">
-        <v>25.19662284851074</v>
+        <v>25.19662094116211</v>
       </c>
       <c r="C242" t="n">
-        <v>26.19804905049173</v>
+        <v>26.19804706733655</v>
       </c>
       <c r="D242" t="n">
-        <v>24.64226063620605</v>
+        <v>24.64225877082185</v>
       </c>
       <c r="E242" t="n">
-        <v>26.00134075860054</v>
+        <v>26.0013387903359</v>
       </c>
       <c r="F242" t="n">
         <v>1514650</v>
@@ -5312,16 +5312,16 @@
         <v>44454</v>
       </c>
       <c r="B245" t="n">
-        <v>26.32322692871094</v>
+        <v>26.3232307434082</v>
       </c>
       <c r="C245" t="n">
-        <v>26.53781824404307</v>
+        <v>26.53782208983838</v>
       </c>
       <c r="D245" t="n">
-        <v>25.66156994674848</v>
+        <v>25.66157366556005</v>
       </c>
       <c r="E245" t="n">
-        <v>26.30534389274488</v>
+        <v>26.30534770485058</v>
       </c>
       <c r="F245" t="n">
         <v>552000</v>
@@ -5392,16 +5392,16 @@
         <v>44460</v>
       </c>
       <c r="B249" t="n">
-        <v>25.07144546508789</v>
+        <v>25.07144355773926</v>
       </c>
       <c r="C249" t="n">
-        <v>25.19662331630446</v>
+        <v>25.19662139943273</v>
       </c>
       <c r="D249" t="n">
-        <v>24.05213450165763</v>
+        <v>24.05213267185464</v>
       </c>
       <c r="E249" t="n">
-        <v>24.57073064938097</v>
+        <v>24.57072878012499</v>
       </c>
       <c r="F249" t="n">
         <v>662000</v>
@@ -5412,16 +5412,16 @@
         <v>44461</v>
       </c>
       <c r="B250" t="n">
-        <v>25.48274421691895</v>
+        <v>25.48274612426758</v>
       </c>
       <c r="C250" t="n">
-        <v>26.37687559295119</v>
+        <v>26.37687756722434</v>
       </c>
       <c r="D250" t="n">
-        <v>25.23238681767862</v>
+        <v>25.23238870628835</v>
       </c>
       <c r="E250" t="n">
-        <v>25.92980990493507</v>
+        <v>25.92981184574596</v>
       </c>
       <c r="F250" t="n">
         <v>900000</v>
@@ -5432,16 +5432,16 @@
         <v>44462</v>
       </c>
       <c r="B251" t="n">
-        <v>26.28746223449707</v>
+        <v>26.28746032714844</v>
       </c>
       <c r="C251" t="n">
-        <v>26.69876355617164</v>
+        <v>26.69876161898007</v>
       </c>
       <c r="D251" t="n">
-        <v>25.32180041218233</v>
+        <v>25.32179857489956</v>
       </c>
       <c r="E251" t="n">
-        <v>25.32180041218233</v>
+        <v>25.32179857489956</v>
       </c>
       <c r="F251" t="n">
         <v>1394250</v>
@@ -5452,16 +5452,16 @@
         <v>44463</v>
       </c>
       <c r="B252" t="n">
-        <v>25.89404296875</v>
+        <v>25.89404487609863</v>
       </c>
       <c r="C252" t="n">
-        <v>26.19804776290805</v>
+        <v>26.1980496926496</v>
       </c>
       <c r="D252" t="n">
-        <v>25.39332989236859</v>
+        <v>25.39333176283482</v>
       </c>
       <c r="E252" t="n">
-        <v>26.19804776290805</v>
+        <v>26.1980496926496</v>
       </c>
       <c r="F252" t="n">
         <v>1097400</v>
@@ -5472,16 +5472,16 @@
         <v>44466</v>
       </c>
       <c r="B253" t="n">
-        <v>26.01922607421875</v>
+        <v>26.01922416687012</v>
       </c>
       <c r="C253" t="n">
-        <v>26.34111224319019</v>
+        <v>26.34111031224558</v>
       </c>
       <c r="D253" t="n">
-        <v>25.57216033997245</v>
+        <v>25.57215846539613</v>
       </c>
       <c r="E253" t="n">
-        <v>26.21593438333576</v>
+        <v>26.21593246156736</v>
       </c>
       <c r="F253" t="n">
         <v>663500</v>
@@ -5512,16 +5512,16 @@
         <v>44468</v>
       </c>
       <c r="B255" t="n">
-        <v>24.67802810668945</v>
+        <v>24.67802429199219</v>
       </c>
       <c r="C255" t="n">
-        <v>25.39333257714754</v>
+        <v>25.39332865187945</v>
       </c>
       <c r="D255" t="n">
-        <v>24.46343676555203</v>
+        <v>24.46343298402601</v>
       </c>
       <c r="E255" t="n">
-        <v>25.10721078896431</v>
+        <v>25.10720690792455</v>
       </c>
       <c r="F255" t="n">
         <v>580300</v>
@@ -5532,16 +5532,16 @@
         <v>44469</v>
       </c>
       <c r="B256" t="n">
-        <v>24.4455509185791</v>
+        <v>24.44555282592773</v>
       </c>
       <c r="C256" t="n">
-        <v>24.89261658760151</v>
+        <v>24.89261852983216</v>
       </c>
       <c r="D256" t="n">
-        <v>24.07001568838347</v>
+        <v>24.0700175664312</v>
       </c>
       <c r="E256" t="n">
-        <v>24.85685051547803</v>
+        <v>24.85685245491806</v>
       </c>
       <c r="F256" t="n">
         <v>989250</v>
@@ -5552,16 +5552,16 @@
         <v>44470</v>
       </c>
       <c r="B257" t="n">
-        <v>25.03567886352539</v>
+        <v>25.03568077087402</v>
       </c>
       <c r="C257" t="n">
-        <v>25.10720930634723</v>
+        <v>25.10721121914542</v>
       </c>
       <c r="D257" t="n">
-        <v>24.2309609554247</v>
+        <v>24.23096280146573</v>
       </c>
       <c r="E257" t="n">
-        <v>24.74955709223806</v>
+        <v>24.74955897778844</v>
       </c>
       <c r="F257" t="n">
         <v>904400</v>
@@ -5572,16 +5572,16 @@
         <v>44473</v>
       </c>
       <c r="B258" t="n">
-        <v>23.8733081817627</v>
+        <v>23.87330627441406</v>
       </c>
       <c r="C258" t="n">
-        <v>25.10720871787369</v>
+        <v>25.10720671194305</v>
       </c>
       <c r="D258" t="n">
-        <v>23.8733081817627</v>
+        <v>23.87330627441406</v>
       </c>
       <c r="E258" t="n">
-        <v>25.01779524008704</v>
+        <v>25.01779324130006</v>
       </c>
       <c r="F258" t="n">
         <v>576500</v>
@@ -5612,16 +5612,16 @@
         <v>44475</v>
       </c>
       <c r="B260" t="n">
-        <v>23.60506629943848</v>
+        <v>23.60506820678711</v>
       </c>
       <c r="C260" t="n">
-        <v>23.60506629943848</v>
+        <v>23.60506820678711</v>
       </c>
       <c r="D260" t="n">
-        <v>22.37116583906875</v>
+        <v>22.37116764671513</v>
       </c>
       <c r="E260" t="n">
-        <v>22.97917540419186</v>
+        <v>22.97917726096693</v>
       </c>
       <c r="F260" t="n">
         <v>1199850</v>
@@ -5632,16 +5632,16 @@
         <v>44476</v>
       </c>
       <c r="B261" t="n">
-        <v>23.62295150756836</v>
+        <v>23.62294960021973</v>
       </c>
       <c r="C261" t="n">
-        <v>24.26672549756607</v>
+        <v>24.26672353823827</v>
       </c>
       <c r="D261" t="n">
-        <v>23.42624321475746</v>
+        <v>23.42624132329132</v>
       </c>
       <c r="E261" t="n">
-        <v>24.1594306852766</v>
+        <v>24.15942873461192</v>
       </c>
       <c r="F261" t="n">
         <v>699850</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35614013671875</v>
+        <v>24.35613632202148</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991415734105</v>
+        <v>24.99991024181488</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848790303969</v>
+        <v>23.99848414435849</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307924324713</v>
+        <v>24.21307545095629</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5712,16 +5712,16 @@
         <v>44483</v>
       </c>
       <c r="B265" t="n">
-        <v>24.37401962280273</v>
+        <v>24.37402153015137</v>
       </c>
       <c r="C265" t="n">
-        <v>24.91049874785196</v>
+        <v>24.91050069718188</v>
       </c>
       <c r="D265" t="n">
-        <v>23.9269539694984</v>
+        <v>23.92695584186265</v>
       </c>
       <c r="E265" t="n">
-        <v>24.51708049542651</v>
+        <v>24.51708241397014</v>
       </c>
       <c r="F265" t="n">
         <v>635500</v>
@@ -5732,16 +5732,16 @@
         <v>44484</v>
       </c>
       <c r="B266" t="n">
-        <v>26.16228485107422</v>
+        <v>26.16228294372559</v>
       </c>
       <c r="C266" t="n">
-        <v>26.59146751184455</v>
+        <v>26.59146557320656</v>
       </c>
       <c r="D266" t="n">
-        <v>24.44555250257259</v>
+        <v>24.44555072038149</v>
       </c>
       <c r="E266" t="n">
-        <v>24.76744035086049</v>
+        <v>24.76743854520231</v>
       </c>
       <c r="F266" t="n">
         <v>2075800</v>
@@ -5752,16 +5752,16 @@
         <v>44487</v>
       </c>
       <c r="B267" t="n">
-        <v>26.28746223449707</v>
+        <v>26.28746032714844</v>
       </c>
       <c r="C267" t="n">
-        <v>27.37830360971465</v>
+        <v>27.37830162321745</v>
       </c>
       <c r="D267" t="n">
-        <v>25.6973356600503</v>
+        <v>25.69733379551969</v>
       </c>
       <c r="E267" t="n">
-        <v>26.6093500770754</v>
+        <v>26.60934814637144</v>
       </c>
       <c r="F267" t="n">
         <v>1715900</v>
@@ -5772,16 +5772,16 @@
         <v>44488</v>
       </c>
       <c r="B268" t="n">
-        <v>24.60649299621582</v>
+        <v>24.60649490356445</v>
       </c>
       <c r="C268" t="n">
-        <v>26.46628597235887</v>
+        <v>26.46628802386757</v>
       </c>
       <c r="D268" t="n">
-        <v>24.12366129109769</v>
+        <v>24.12366316102009</v>
       </c>
       <c r="E268" t="n">
-        <v>26.43051990290417</v>
+        <v>26.4305219516405</v>
       </c>
       <c r="F268" t="n">
         <v>1499450</v>
@@ -5812,16 +5812,16 @@
         <v>44490</v>
       </c>
       <c r="B270" t="n">
-        <v>22.44269752502441</v>
+        <v>22.44269943237305</v>
       </c>
       <c r="C270" t="n">
-        <v>23.46200673186731</v>
+        <v>23.46200872584448</v>
       </c>
       <c r="D270" t="n">
-        <v>21.67374400804736</v>
+        <v>21.67374585004456</v>
       </c>
       <c r="E270" t="n">
-        <v>22.8897632059794</v>
+        <v>22.88976515132303</v>
       </c>
       <c r="F270" t="n">
         <v>1908000</v>
@@ -5852,16 +5852,16 @@
         <v>44494</v>
       </c>
       <c r="B272" t="n">
-        <v>21.62009811401367</v>
+        <v>21.62009620666504</v>
       </c>
       <c r="C272" t="n">
-        <v>22.28175516339335</v>
+        <v>22.28175319767261</v>
       </c>
       <c r="D272" t="n">
-        <v>20.79749713538103</v>
+        <v>20.79749530060315</v>
       </c>
       <c r="E272" t="n">
-        <v>20.83326150553705</v>
+        <v>20.833259667604</v>
       </c>
       <c r="F272" t="n">
         <v>1833600</v>
@@ -5892,16 +5892,16 @@
         <v>44496</v>
       </c>
       <c r="B274" t="n">
-        <v>20.49349212646484</v>
+        <v>20.49349403381348</v>
       </c>
       <c r="C274" t="n">
-        <v>21.10150176231677</v>
+        <v>21.10150372625343</v>
       </c>
       <c r="D274" t="n">
-        <v>20.31466516106592</v>
+        <v>20.31466705177096</v>
       </c>
       <c r="E274" t="n">
-        <v>20.42196168138934</v>
+        <v>20.42196358208057</v>
       </c>
       <c r="F274" t="n">
         <v>1013650</v>
@@ -5912,16 +5912,16 @@
         <v>44497</v>
       </c>
       <c r="B275" t="n">
-        <v>19.29535484313965</v>
+        <v>19.29535675048828</v>
       </c>
       <c r="C275" t="n">
-        <v>20.76172974015886</v>
+        <v>20.76173179245886</v>
       </c>
       <c r="D275" t="n">
-        <v>19.29535484313965</v>
+        <v>19.29535675048828</v>
       </c>
       <c r="E275" t="n">
-        <v>20.74384840892759</v>
+        <v>20.74385045946002</v>
       </c>
       <c r="F275" t="n">
         <v>1280700</v>
@@ -5972,16 +5972,16 @@
         <v>44503</v>
       </c>
       <c r="B278" t="n">
-        <v>20.11795425415039</v>
+        <v>20.11795616149902</v>
       </c>
       <c r="C278" t="n">
-        <v>20.36831163215328</v>
+        <v>20.36831356323787</v>
       </c>
       <c r="D278" t="n">
-        <v>18.41910512488394</v>
+        <v>18.41910687116761</v>
       </c>
       <c r="E278" t="n">
-        <v>18.47275252537737</v>
+        <v>18.47275427674726</v>
       </c>
       <c r="F278" t="n">
         <v>1851600</v>
@@ -6012,16 +6012,16 @@
         <v>44505</v>
       </c>
       <c r="B280" t="n">
-        <v>20.42196273803711</v>
+        <v>20.42196083068848</v>
       </c>
       <c r="C280" t="n">
-        <v>20.94055891802213</v>
+        <v>20.94055696223821</v>
       </c>
       <c r="D280" t="n">
-        <v>19.99278004537787</v>
+        <v>19.99277817811358</v>
       </c>
       <c r="E280" t="n">
-        <v>20.20737139170749</v>
+        <v>20.20736950440103</v>
       </c>
       <c r="F280" t="n">
         <v>901950</v>
@@ -6172,16 +6172,16 @@
         <v>44518</v>
       </c>
       <c r="B288" t="n">
-        <v>20.33254623413086</v>
+        <v>20.33254814147949</v>
       </c>
       <c r="C288" t="n">
-        <v>20.70808146084758</v>
+        <v>20.7080834034243</v>
       </c>
       <c r="D288" t="n">
-        <v>19.68877229065369</v>
+        <v>19.68877413761139</v>
       </c>
       <c r="E288" t="n">
-        <v>19.68877229065369</v>
+        <v>19.68877413761139</v>
       </c>
       <c r="F288" t="n">
         <v>766850</v>
@@ -6192,16 +6192,16 @@
         <v>44519</v>
       </c>
       <c r="B289" t="n">
-        <v>20.99420547485352</v>
+        <v>20.99420356750488</v>
       </c>
       <c r="C289" t="n">
-        <v>21.24456288810481</v>
+        <v>21.24456095801091</v>
       </c>
       <c r="D289" t="n">
-        <v>20.11795708660452</v>
+        <v>20.11795525886409</v>
       </c>
       <c r="E289" t="n">
-        <v>20.31466538638888</v>
+        <v>20.31466354077727</v>
       </c>
       <c r="F289" t="n">
         <v>767750</v>
@@ -6212,16 +6212,16 @@
         <v>44522</v>
       </c>
       <c r="B290" t="n">
-        <v>20.18948554992676</v>
+        <v>20.18948745727539</v>
       </c>
       <c r="C290" t="n">
-        <v>21.44126908242115</v>
+        <v>21.44127110802875</v>
       </c>
       <c r="D290" t="n">
-        <v>19.97489423339231</v>
+        <v>19.97489612046799</v>
       </c>
       <c r="E290" t="n">
-        <v>20.86902557166261</v>
+        <v>20.869027543209</v>
       </c>
       <c r="F290" t="n">
         <v>852100</v>
@@ -6232,16 +6232,16 @@
         <v>44523</v>
       </c>
       <c r="B291" t="n">
-        <v>19.24170684814453</v>
+        <v>19.2417049407959</v>
       </c>
       <c r="C291" t="n">
-        <v>20.45772431098796</v>
+        <v>20.45772228310068</v>
       </c>
       <c r="D291" t="n">
-        <v>19.02711553117216</v>
+        <v>19.02711364509506</v>
       </c>
       <c r="E291" t="n">
-        <v>20.20736862723029</v>
+        <v>20.20736662415971</v>
       </c>
       <c r="F291" t="n">
         <v>1896750</v>
@@ -6252,16 +6252,16 @@
         <v>44524</v>
       </c>
       <c r="B292" t="n">
-        <v>19.58147811889648</v>
+        <v>19.58147621154785</v>
       </c>
       <c r="C292" t="n">
-        <v>20.3325486620143</v>
+        <v>20.33254668150708</v>
       </c>
       <c r="D292" t="n">
-        <v>19.02711758328404</v>
+        <v>19.02711572993332</v>
       </c>
       <c r="E292" t="n">
-        <v>19.04499891589514</v>
+        <v>19.04499706080266</v>
       </c>
       <c r="F292" t="n">
         <v>1594900</v>
@@ -6292,16 +6292,16 @@
         <v>44526</v>
       </c>
       <c r="B294" t="n">
-        <v>19.76030349731445</v>
+        <v>19.76030540466309</v>
       </c>
       <c r="C294" t="n">
-        <v>19.90336437920648</v>
+        <v>19.90336630036396</v>
       </c>
       <c r="D294" t="n">
-        <v>19.18805826432609</v>
+        <v>19.18806011643918</v>
       </c>
       <c r="E294" t="n">
-        <v>19.65300698318531</v>
+        <v>19.65300888017723</v>
       </c>
       <c r="F294" t="n">
         <v>1033400</v>
@@ -6332,16 +6332,16 @@
         <v>44530</v>
       </c>
       <c r="B296" t="n">
-        <v>18.83040809631348</v>
+        <v>18.83040428161621</v>
       </c>
       <c r="C296" t="n">
-        <v>19.25959249383086</v>
+        <v>19.25958859218866</v>
       </c>
       <c r="D296" t="n">
-        <v>18.06145619932819</v>
+        <v>18.06145254040656</v>
       </c>
       <c r="E296" t="n">
-        <v>19.04499944236196</v>
+        <v>19.0449955841924</v>
       </c>
       <c r="F296" t="n">
         <v>1327800</v>
@@ -6352,16 +6352,16 @@
         <v>44531</v>
       </c>
       <c r="B297" t="n">
-        <v>17.95415687561035</v>
+        <v>17.95415878295898</v>
       </c>
       <c r="C297" t="n">
-        <v>19.67088908188234</v>
+        <v>19.67089117160695</v>
       </c>
       <c r="D297" t="n">
-        <v>17.93627383987144</v>
+        <v>17.93627574532028</v>
       </c>
       <c r="E297" t="n">
-        <v>18.99134907258508</v>
+        <v>18.99135109011918</v>
       </c>
       <c r="F297" t="n">
         <v>1102200</v>
@@ -6392,16 +6392,16 @@
         <v>44533</v>
       </c>
       <c r="B299" t="n">
-        <v>19.76030349731445</v>
+        <v>19.76030540466309</v>
       </c>
       <c r="C299" t="n">
-        <v>20.20736917958211</v>
+        <v>20.20737113008343</v>
       </c>
       <c r="D299" t="n">
-        <v>18.77675865524156</v>
+        <v>18.77676046765426</v>
       </c>
       <c r="E299" t="n">
-        <v>18.77675865524156</v>
+        <v>18.77676046765426</v>
       </c>
       <c r="F299" t="n">
         <v>1496100</v>
@@ -6452,16 +6452,16 @@
         <v>44538</v>
       </c>
       <c r="B302" t="n">
-        <v>21.42338752746582</v>
+        <v>21.42338562011719</v>
       </c>
       <c r="C302" t="n">
-        <v>21.51280100855851</v>
+        <v>21.51279909324929</v>
       </c>
       <c r="D302" t="n">
-        <v>19.86759909596611</v>
+        <v>19.86759732713109</v>
       </c>
       <c r="E302" t="n">
-        <v>20.18948694573167</v>
+        <v>20.18948514823861</v>
       </c>
       <c r="F302" t="n">
         <v>984450</v>
@@ -6492,16 +6492,16 @@
         <v>44540</v>
       </c>
       <c r="B304" t="n">
-        <v>21.81680679321289</v>
+        <v>21.81680488586426</v>
       </c>
       <c r="C304" t="n">
-        <v>22.19234206620039</v>
+        <v>22.19234012602034</v>
       </c>
       <c r="D304" t="n">
-        <v>21.06573624723789</v>
+        <v>21.06573440555209</v>
       </c>
       <c r="E304" t="n">
-        <v>22.13869465732228</v>
+        <v>22.1386927218324</v>
       </c>
       <c r="F304" t="n">
         <v>899500</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78104209899902</v>
+        <v>21.78104019165039</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422959598714</v>
+        <v>22.51422762443386</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550683158799</v>
+        <v>21.40550495712469</v>
       </c>
       <c r="E305" t="n">
-        <v>22.13869432857611</v>
+        <v>22.13869238990815</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6532,16 +6532,16 @@
         <v>44544</v>
       </c>
       <c r="B306" t="n">
-        <v>21.49492073059082</v>
+        <v>21.49491882324219</v>
       </c>
       <c r="C306" t="n">
-        <v>22.06716430896915</v>
+        <v>22.06716235084257</v>
       </c>
       <c r="D306" t="n">
-        <v>21.22668027416069</v>
+        <v>21.22667839061434</v>
       </c>
       <c r="E306" t="n">
-        <v>21.95986778531302</v>
+        <v>21.95986583670738</v>
       </c>
       <c r="F306" t="n">
         <v>979700</v>
@@ -6612,16 +6612,16 @@
         <v>44550</v>
       </c>
       <c r="B310" t="n">
-        <v>22.01351737976074</v>
+        <v>22.01351547241211</v>
       </c>
       <c r="C310" t="n">
-        <v>22.42481703433168</v>
+        <v>22.42481509134622</v>
       </c>
       <c r="D310" t="n">
-        <v>21.1372672494906</v>
+        <v>21.13726541806416</v>
       </c>
       <c r="E310" t="n">
-        <v>22.35328658547498</v>
+        <v>22.35328464868723</v>
       </c>
       <c r="F310" t="n">
         <v>1565700</v>
@@ -6652,16 +6652,16 @@
         <v>44552</v>
       </c>
       <c r="B312" t="n">
-        <v>21.45915412902832</v>
+        <v>21.45915603637695</v>
       </c>
       <c r="C312" t="n">
-        <v>21.78104198669826</v>
+        <v>21.78104392265717</v>
       </c>
       <c r="D312" t="n">
-        <v>20.65443619027383</v>
+        <v>20.65443802609692</v>
       </c>
       <c r="E312" t="n">
-        <v>21.42338805354484</v>
+        <v>21.42338995771449</v>
       </c>
       <c r="F312" t="n">
         <v>1154200</v>
@@ -6712,16 +6712,16 @@
         <v>44558</v>
       </c>
       <c r="B315" t="n">
-        <v>20.76128959655762</v>
+        <v>20.76128768920898</v>
       </c>
       <c r="C315" t="n">
-        <v>21.2483041737824</v>
+        <v>21.24830222169153</v>
       </c>
       <c r="D315" t="n">
-        <v>20.58091280783701</v>
+        <v>20.58091091705966</v>
       </c>
       <c r="E315" t="n">
-        <v>20.90559033945389</v>
+        <v>20.90558841884829</v>
       </c>
       <c r="F315" t="n">
         <v>793100</v>
@@ -6752,16 +6752,16 @@
         <v>44560</v>
       </c>
       <c r="B317" t="n">
-        <v>21.06792640686035</v>
+        <v>21.06793022155762</v>
       </c>
       <c r="C317" t="n">
-        <v>21.15811306946891</v>
+        <v>21.15811690049597</v>
       </c>
       <c r="D317" t="n">
-        <v>19.93155691194919</v>
+        <v>19.93156052088792</v>
       </c>
       <c r="E317" t="n">
-        <v>20.2923087229844</v>
+        <v>20.29231239724323</v>
       </c>
       <c r="F317" t="n">
         <v>1399700</v>
@@ -6872,16 +6872,16 @@
         <v>44571</v>
       </c>
       <c r="B323" t="n">
-        <v>16.360107421875</v>
+        <v>16.36010932922363</v>
       </c>
       <c r="C323" t="n">
-        <v>17.13572499859104</v>
+        <v>17.13572699636531</v>
       </c>
       <c r="D323" t="n">
-        <v>16.10758204913961</v>
+        <v>16.10758392704749</v>
       </c>
       <c r="E323" t="n">
-        <v>17.11768698048135</v>
+        <v>17.11768897615265</v>
       </c>
       <c r="F323" t="n">
         <v>1820150</v>
@@ -6892,16 +6892,16 @@
         <v>44572</v>
       </c>
       <c r="B324" t="n">
-        <v>16.77497482299805</v>
+        <v>16.77497673034668</v>
       </c>
       <c r="C324" t="n">
-        <v>17.04553823941727</v>
+        <v>17.04554017752951</v>
       </c>
       <c r="D324" t="n">
-        <v>16.17973393071556</v>
+        <v>16.1797357703841</v>
       </c>
       <c r="E324" t="n">
-        <v>16.19777023032999</v>
+        <v>16.19777207204929</v>
       </c>
       <c r="F324" t="n">
         <v>629400</v>
@@ -6932,16 +6932,16 @@
         <v>44574</v>
       </c>
       <c r="B326" t="n">
-        <v>16.64871215820312</v>
+        <v>16.64871025085449</v>
       </c>
       <c r="C326" t="n">
-        <v>17.62274468839355</v>
+        <v>17.62274266945553</v>
       </c>
       <c r="D326" t="n">
-        <v>16.57656179154462</v>
+        <v>16.57655989246185</v>
       </c>
       <c r="E326" t="n">
-        <v>17.58666864496408</v>
+        <v>17.58666663015909</v>
       </c>
       <c r="F326" t="n">
         <v>921200</v>
@@ -6992,16 +6992,16 @@
         <v>44579</v>
       </c>
       <c r="B329" t="n">
-        <v>16.30599784851074</v>
+        <v>16.30599594116211</v>
       </c>
       <c r="C329" t="n">
-        <v>16.79301409872861</v>
+        <v>16.79301213441261</v>
       </c>
       <c r="D329" t="n">
-        <v>16.07150873398366</v>
+        <v>16.07150685406374</v>
       </c>
       <c r="E329" t="n">
-        <v>16.73890003523749</v>
+        <v>16.73889807725132</v>
       </c>
       <c r="F329" t="n">
         <v>670850</v>
@@ -7032,16 +7032,16 @@
         <v>44581</v>
       </c>
       <c r="B331" t="n">
-        <v>17.42433166503906</v>
+        <v>17.4243278503418</v>
       </c>
       <c r="C331" t="n">
-        <v>18.12779910177564</v>
+        <v>18.12779513306872</v>
       </c>
       <c r="D331" t="n">
-        <v>16.48637680292423</v>
+        <v>16.48637319357279</v>
       </c>
       <c r="E331" t="n">
-        <v>16.48637680292423</v>
+        <v>16.48637319357279</v>
       </c>
       <c r="F331" t="n">
         <v>2219300</v>
@@ -7072,16 +7072,16 @@
         <v>44585</v>
       </c>
       <c r="B333" t="n">
-        <v>17.85723114013672</v>
+        <v>17.85723304748535</v>
       </c>
       <c r="C333" t="n">
-        <v>18.09172024935553</v>
+        <v>18.09172218175017</v>
       </c>
       <c r="D333" t="n">
-        <v>17.47844130527562</v>
+        <v>17.47844317216533</v>
       </c>
       <c r="E333" t="n">
-        <v>18.09172024935553</v>
+        <v>18.09172218175017</v>
       </c>
       <c r="F333" t="n">
         <v>692150</v>
@@ -7112,16 +7112,16 @@
         <v>44587</v>
       </c>
       <c r="B335" t="n">
-        <v>19.3543529510498</v>
+        <v>19.35435485839844</v>
       </c>
       <c r="C335" t="n">
-        <v>19.80529316020046</v>
+        <v>19.80529511198872</v>
       </c>
       <c r="D335" t="n">
-        <v>18.84930039845718</v>
+        <v>18.84930225603348</v>
       </c>
       <c r="E335" t="n">
-        <v>18.92145076311327</v>
+        <v>18.9214526277999</v>
       </c>
       <c r="F335" t="n">
         <v>1494250</v>
@@ -7232,16 +7232,16 @@
         <v>44595</v>
       </c>
       <c r="B341" t="n">
-        <v>20.12997055053711</v>
+        <v>20.12996864318848</v>
       </c>
       <c r="C341" t="n">
-        <v>20.67109914258173</v>
+        <v>20.67109718396025</v>
       </c>
       <c r="D341" t="n">
-        <v>19.93155747887424</v>
+        <v>19.93155559032558</v>
       </c>
       <c r="E341" t="n">
-        <v>20.43661002868905</v>
+        <v>20.43660809228581</v>
       </c>
       <c r="F341" t="n">
         <v>747450</v>
@@ -7252,16 +7252,16 @@
         <v>44596</v>
       </c>
       <c r="B342" t="n">
-        <v>19.40846824645996</v>
+        <v>19.4084644317627</v>
       </c>
       <c r="C342" t="n">
-        <v>20.18408428568767</v>
+        <v>20.18408031854456</v>
       </c>
       <c r="D342" t="n">
-        <v>19.26416750798967</v>
+        <v>19.26416372165443</v>
       </c>
       <c r="E342" t="n">
-        <v>20.18408428568767</v>
+        <v>20.18408031854456</v>
       </c>
       <c r="F342" t="n">
         <v>774000</v>
@@ -7272,16 +7272,16 @@
         <v>44599</v>
       </c>
       <c r="B343" t="n">
-        <v>19.73314476013184</v>
+        <v>19.73314094543457</v>
       </c>
       <c r="C343" t="n">
-        <v>19.94959759585004</v>
+        <v>19.94959373930937</v>
       </c>
       <c r="D343" t="n">
-        <v>19.06575339056894</v>
+        <v>19.0657497048879</v>
       </c>
       <c r="E343" t="n">
-        <v>19.31828055210647</v>
+        <v>19.31827681760835</v>
       </c>
       <c r="F343" t="n">
         <v>708000</v>
@@ -7332,16 +7332,16 @@
         <v>44602</v>
       </c>
       <c r="B346" t="n">
-        <v>19.98567008972168</v>
+        <v>19.98566818237305</v>
       </c>
       <c r="C346" t="n">
-        <v>20.59894905424028</v>
+        <v>20.59894708836287</v>
       </c>
       <c r="D346" t="n">
-        <v>19.82333133791377</v>
+        <v>19.82332944605806</v>
       </c>
       <c r="E346" t="n">
-        <v>20.18408316404224</v>
+        <v>20.18408123775789</v>
       </c>
       <c r="F346" t="n">
         <v>563100</v>
@@ -7352,16 +7352,16 @@
         <v>44603</v>
       </c>
       <c r="B347" t="n">
-        <v>19.44453811645508</v>
+        <v>19.44454193115234</v>
       </c>
       <c r="C347" t="n">
-        <v>20.4726827927703</v>
+        <v>20.47268680917258</v>
       </c>
       <c r="D347" t="n">
-        <v>19.13789868740318</v>
+        <v>19.13790244194285</v>
       </c>
       <c r="E347" t="n">
-        <v>20.09389301101209</v>
+        <v>20.09389695310205</v>
       </c>
       <c r="F347" t="n">
         <v>1043600</v>
@@ -7372,16 +7372,16 @@
         <v>44606</v>
       </c>
       <c r="B348" t="n">
-        <v>20.00370788574219</v>
+        <v>20.00370597839355</v>
       </c>
       <c r="C348" t="n">
-        <v>20.14800861456807</v>
+        <v>20.1480066934604</v>
       </c>
       <c r="D348" t="n">
-        <v>19.26416622045944</v>
+        <v>19.26416438362593</v>
       </c>
       <c r="E348" t="n">
-        <v>19.26416622045944</v>
+        <v>19.26416438362593</v>
       </c>
       <c r="F348" t="n">
         <v>683300</v>
@@ -7392,16 +7392,16 @@
         <v>44607</v>
       </c>
       <c r="B349" t="n">
-        <v>20.52680015563965</v>
+        <v>20.52679634094238</v>
       </c>
       <c r="C349" t="n">
-        <v>20.70717522149135</v>
+        <v>20.70717137327322</v>
       </c>
       <c r="D349" t="n">
-        <v>20.11193423579974</v>
+        <v>20.11193049820109</v>
       </c>
       <c r="E349" t="n">
-        <v>20.20212262882585</v>
+        <v>20.2021188744666</v>
       </c>
       <c r="F349" t="n">
         <v>560950</v>
@@ -7412,16 +7412,16 @@
         <v>44608</v>
       </c>
       <c r="B350" t="n">
-        <v>20.74324607849121</v>
+        <v>20.74324989318848</v>
       </c>
       <c r="C350" t="n">
-        <v>20.76128409662488</v>
+        <v>20.76128791463935</v>
       </c>
       <c r="D350" t="n">
-        <v>20.27426792821643</v>
+        <v>20.27427165666829</v>
       </c>
       <c r="E350" t="n">
-        <v>20.74324607849121</v>
+        <v>20.74324989318848</v>
       </c>
       <c r="F350" t="n">
         <v>576900</v>
@@ -7452,16 +7452,16 @@
         <v>44610</v>
       </c>
       <c r="B352" t="n">
-        <v>19.93155479431152</v>
+        <v>19.93155860900879</v>
       </c>
       <c r="C352" t="n">
-        <v>20.50875763064267</v>
+        <v>20.5087615558107</v>
       </c>
       <c r="D352" t="n">
-        <v>19.64295337614595</v>
+        <v>19.64295713560783</v>
       </c>
       <c r="E352" t="n">
-        <v>20.47268331347204</v>
+        <v>20.47268723173582</v>
       </c>
       <c r="F352" t="n">
         <v>904300</v>
@@ -7512,16 +7512,16 @@
         <v>44615</v>
       </c>
       <c r="B355" t="n">
-        <v>19.66099166870117</v>
+        <v>19.6609935760498</v>
       </c>
       <c r="C355" t="n">
-        <v>20.49072169018069</v>
+        <v>20.49072367802294</v>
       </c>
       <c r="D355" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276888286228</v>
       </c>
       <c r="E355" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940838056108</v>
       </c>
       <c r="F355" t="n">
         <v>1327750</v>
@@ -7552,16 +7552,16 @@
         <v>44617</v>
       </c>
       <c r="B357" t="n">
-        <v>19.02967834472656</v>
+        <v>19.02967643737793</v>
       </c>
       <c r="C357" t="n">
-        <v>19.62491931992821</v>
+        <v>19.62491735291844</v>
       </c>
       <c r="D357" t="n">
-        <v>18.65088847685275</v>
+        <v>18.6508866074703</v>
       </c>
       <c r="E357" t="n">
-        <v>19.28220377650878</v>
+        <v>19.28220184384947</v>
       </c>
       <c r="F357" t="n">
         <v>1262850</v>
@@ -7572,16 +7572,16 @@
         <v>44622</v>
       </c>
       <c r="B358" t="n">
-        <v>18.83126068115234</v>
+        <v>18.83126258850098</v>
       </c>
       <c r="C358" t="n">
-        <v>18.90341103931001</v>
+        <v>18.90341295396648</v>
       </c>
       <c r="D358" t="n">
-        <v>18.23601979630157</v>
+        <v>18.23602164336046</v>
       </c>
       <c r="E358" t="n">
-        <v>18.74107402360544</v>
+        <v>18.74107592181939</v>
       </c>
       <c r="F358" t="n">
         <v>1044650</v>
@@ -7612,16 +7612,16 @@
         <v>44624</v>
       </c>
       <c r="B360" t="n">
-        <v>17.91134643554688</v>
+        <v>17.91134452819824</v>
       </c>
       <c r="C360" t="n">
-        <v>18.7591128270115</v>
+        <v>18.75911082938567</v>
       </c>
       <c r="D360" t="n">
-        <v>17.55059287640398</v>
+        <v>17.55059100747137</v>
       </c>
       <c r="E360" t="n">
-        <v>18.5787377676405</v>
+        <v>18.57873578922251</v>
       </c>
       <c r="F360" t="n">
         <v>1669200</v>
@@ -7632,16 +7632,16 @@
         <v>44627</v>
       </c>
       <c r="B361" t="n">
-        <v>16.77497482299805</v>
+        <v>16.77497673034668</v>
       </c>
       <c r="C361" t="n">
-        <v>18.00153092699214</v>
+        <v>18.00153297380269</v>
       </c>
       <c r="D361" t="n">
-        <v>16.77497482299805</v>
+        <v>16.77497673034668</v>
       </c>
       <c r="E361" t="n">
-        <v>17.60470481227065</v>
+        <v>17.60470681396126</v>
       </c>
       <c r="F361" t="n">
         <v>1173850</v>
@@ -7652,16 +7652,16 @@
         <v>44628</v>
       </c>
       <c r="B362" t="n">
-        <v>17.38825225830078</v>
+        <v>17.38825416564941</v>
       </c>
       <c r="C362" t="n">
-        <v>17.58666529881019</v>
+        <v>17.58666722792311</v>
       </c>
       <c r="D362" t="n">
-        <v>16.54048432121493</v>
+        <v>16.54048613557037</v>
       </c>
       <c r="E362" t="n">
-        <v>16.84712375122045</v>
+        <v>16.84712559921172</v>
       </c>
       <c r="F362" t="n">
         <v>1040800</v>
@@ -7672,16 +7672,16 @@
         <v>44629</v>
       </c>
       <c r="B363" t="n">
-        <v>18.23602294921875</v>
+        <v>18.23602104187012</v>
       </c>
       <c r="C363" t="n">
-        <v>18.36228738797532</v>
+        <v>18.36228546742039</v>
       </c>
       <c r="D363" t="n">
-        <v>17.51451924289774</v>
+        <v>17.51451741101287</v>
       </c>
       <c r="E363" t="n">
-        <v>17.5325572656059</v>
+        <v>17.53255543183439</v>
       </c>
       <c r="F363" t="n">
         <v>713800</v>
@@ -7732,16 +7732,16 @@
         <v>44634</v>
       </c>
       <c r="B366" t="n">
-        <v>17.31610488891602</v>
+        <v>17.31610298156738</v>
       </c>
       <c r="C366" t="n">
-        <v>17.67685671572668</v>
+        <v>17.67685476864166</v>
       </c>
       <c r="D366" t="n">
-        <v>16.88320097654281</v>
+        <v>16.88319911687804</v>
       </c>
       <c r="E366" t="n">
-        <v>17.35217921149688</v>
+        <v>17.35217730017471</v>
       </c>
       <c r="F366" t="n">
         <v>989600</v>
@@ -7792,16 +7792,16 @@
         <v>44637</v>
       </c>
       <c r="B369" t="n">
-        <v>18.16386985778809</v>
+        <v>18.16387176513672</v>
       </c>
       <c r="C369" t="n">
-        <v>18.30817057743722</v>
+        <v>18.30817249993856</v>
       </c>
       <c r="D369" t="n">
-        <v>17.17180284025032</v>
+        <v>17.17180464342414</v>
       </c>
       <c r="E369" t="n">
-        <v>17.56862895918532</v>
+        <v>17.56863080402899</v>
       </c>
       <c r="F369" t="n">
         <v>935650</v>
@@ -7812,16 +7812,16 @@
         <v>44638</v>
       </c>
       <c r="B370" t="n">
-        <v>18.43443870544434</v>
+        <v>18.4344367980957</v>
       </c>
       <c r="C370" t="n">
-        <v>18.90341527854049</v>
+        <v>18.90341332266845</v>
       </c>
       <c r="D370" t="n">
-        <v>18.01957276285085</v>
+        <v>18.01957089842698</v>
       </c>
       <c r="E370" t="n">
-        <v>18.16387351152668</v>
+        <v>18.16387163217251</v>
       </c>
       <c r="F370" t="n">
         <v>2000150</v>
@@ -7852,16 +7852,16 @@
         <v>44642</v>
       </c>
       <c r="B372" t="n">
-        <v>19.40846824645996</v>
+        <v>19.4084644317627</v>
       </c>
       <c r="C372" t="n">
-        <v>19.4625805933362</v>
+        <v>19.46257676800326</v>
       </c>
       <c r="D372" t="n">
-        <v>18.686962833908</v>
+        <v>18.68695916102124</v>
       </c>
       <c r="E372" t="n">
-        <v>18.70500085626691</v>
+        <v>18.70499717983481</v>
       </c>
       <c r="F372" t="n">
         <v>868000</v>
@@ -7872,16 +7872,16 @@
         <v>44643</v>
       </c>
       <c r="B373" t="n">
-        <v>19.60688018798828</v>
+        <v>19.60687828063965</v>
       </c>
       <c r="C373" t="n">
-        <v>19.80529326175987</v>
+        <v>19.8052913351097</v>
       </c>
       <c r="D373" t="n">
-        <v>18.92145086014044</v>
+        <v>18.92144901947007</v>
       </c>
       <c r="E373" t="n">
-        <v>19.48061747924276</v>
+        <v>19.48061558417691</v>
       </c>
       <c r="F373" t="n">
         <v>823600</v>
@@ -7952,16 +7952,16 @@
         <v>44649</v>
       </c>
       <c r="B377" t="n">
-        <v>21.91569137573242</v>
+        <v>21.91569519042969</v>
       </c>
       <c r="C377" t="n">
-        <v>22.36663154165449</v>
+        <v>22.36663543484347</v>
       </c>
       <c r="D377" t="n">
-        <v>21.6631659837442</v>
+        <v>21.6631697544863</v>
       </c>
       <c r="E377" t="n">
-        <v>21.6631659837442</v>
+        <v>21.6631697544863</v>
       </c>
       <c r="F377" t="n">
         <v>1103500</v>
@@ -8012,16 +8012,16 @@
         <v>44652</v>
       </c>
       <c r="B380" t="n">
-        <v>21.78943252563477</v>
+        <v>21.78943061828613</v>
       </c>
       <c r="C380" t="n">
-        <v>21.84354487344034</v>
+        <v>21.84354296135495</v>
       </c>
       <c r="D380" t="n">
-        <v>21.17615351650324</v>
+        <v>21.17615166283828</v>
       </c>
       <c r="E380" t="n">
-        <v>21.42868067326343</v>
+        <v>21.42867879749339</v>
       </c>
       <c r="F380" t="n">
         <v>746250</v>
@@ -8032,16 +8032,16 @@
         <v>44655</v>
       </c>
       <c r="B381" t="n">
-        <v>21.89765548706055</v>
+        <v>21.89765739440918</v>
       </c>
       <c r="C381" t="n">
-        <v>21.91569178668347</v>
+        <v>21.91569369560312</v>
       </c>
       <c r="D381" t="n">
-        <v>21.32045089412073</v>
+        <v>21.32045275119318</v>
       </c>
       <c r="E381" t="n">
-        <v>21.78942908832175</v>
+        <v>21.78943098624356</v>
       </c>
       <c r="F381" t="n">
         <v>503500</v>
@@ -8072,16 +8072,16 @@
         <v>44657</v>
       </c>
       <c r="B383" t="n">
-        <v>20.0217456817627</v>
+        <v>20.02174377441406</v>
       </c>
       <c r="C383" t="n">
-        <v>20.58091056962541</v>
+        <v>20.58090860900858</v>
       </c>
       <c r="D383" t="n">
-        <v>19.58884177995242</v>
+        <v>19.58883991384388</v>
       </c>
       <c r="E383" t="n">
-        <v>20.58091056962541</v>
+        <v>20.58090860900858</v>
       </c>
       <c r="F383" t="n">
         <v>1237700</v>
@@ -8092,16 +8092,16 @@
         <v>44658</v>
       </c>
       <c r="B384" t="n">
-        <v>19.66099166870117</v>
+        <v>19.6609935760498</v>
       </c>
       <c r="C384" t="n">
-        <v>20.00370717768201</v>
+        <v>20.0037091182781</v>
       </c>
       <c r="D384" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276888286228</v>
       </c>
       <c r="E384" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940838056108</v>
       </c>
       <c r="F384" t="n">
         <v>978600</v>
@@ -8112,16 +8112,16 @@
         <v>44659</v>
       </c>
       <c r="B385" t="n">
-        <v>19.39042854309082</v>
+        <v>19.39042663574219</v>
       </c>
       <c r="C385" t="n">
-        <v>19.60687963203151</v>
+        <v>19.60687770339157</v>
       </c>
       <c r="D385" t="n">
-        <v>19.01163870739452</v>
+        <v>19.01163683730573</v>
       </c>
       <c r="E385" t="n">
-        <v>19.57080531064157</v>
+        <v>19.57080338555009</v>
       </c>
       <c r="F385" t="n">
         <v>914050</v>
@@ -8152,16 +8152,16 @@
         <v>44663</v>
       </c>
       <c r="B387" t="n">
-        <v>19.13789939880371</v>
+        <v>19.13790130615234</v>
       </c>
       <c r="C387" t="n">
-        <v>19.84136665398996</v>
+        <v>19.84136863144855</v>
       </c>
       <c r="D387" t="n">
-        <v>18.99359868802707</v>
+        <v>18.9936005809942</v>
       </c>
       <c r="E387" t="n">
-        <v>19.33631416627171</v>
+        <v>19.33631609339504</v>
       </c>
       <c r="F387" t="n">
         <v>1155250</v>
@@ -8192,16 +8192,16 @@
         <v>44665</v>
       </c>
       <c r="B389" t="n">
-        <v>19.5708065032959</v>
+        <v>19.57080841064453</v>
       </c>
       <c r="C389" t="n">
-        <v>19.67903119426134</v>
+        <v>19.67903311215743</v>
       </c>
       <c r="D389" t="n">
-        <v>19.01163986597297</v>
+        <v>19.01164171882585</v>
       </c>
       <c r="E389" t="n">
-        <v>19.17397862262157</v>
+        <v>19.17398049129581</v>
       </c>
       <c r="F389" t="n">
         <v>760550</v>
@@ -8252,16 +8252,16 @@
         <v>44671</v>
       </c>
       <c r="B392" t="n">
-        <v>20.61698722839355</v>
+        <v>20.61698532104492</v>
       </c>
       <c r="C392" t="n">
-        <v>20.79736228269439</v>
+        <v>20.79736035865864</v>
       </c>
       <c r="D392" t="n">
-        <v>20.11193294787024</v>
+        <v>20.11193108724592</v>
       </c>
       <c r="E392" t="n">
-        <v>20.34642206664169</v>
+        <v>20.34642018432397</v>
       </c>
       <c r="F392" t="n">
         <v>1230400</v>
@@ -8292,16 +8292,16 @@
         <v>44676</v>
       </c>
       <c r="B394" t="n">
-        <v>19.30023956298828</v>
+        <v>19.30023765563965</v>
       </c>
       <c r="C394" t="n">
-        <v>19.57080470595465</v>
+        <v>19.57080277186738</v>
       </c>
       <c r="D394" t="n">
-        <v>18.61481027575389</v>
+        <v>18.6148084361429</v>
       </c>
       <c r="E394" t="n">
-        <v>19.28220154275046</v>
+        <v>19.28219963718444</v>
       </c>
       <c r="F394" t="n">
         <v>1378800</v>
@@ -8312,16 +8312,16 @@
         <v>44677</v>
       </c>
       <c r="B395" t="n">
-        <v>19.06575012207031</v>
+        <v>19.06575393676758</v>
       </c>
       <c r="C395" t="n">
-        <v>19.39042759978664</v>
+        <v>19.39043147944575</v>
       </c>
       <c r="D395" t="n">
-        <v>18.68696030480135</v>
+        <v>18.68696404370992</v>
       </c>
       <c r="E395" t="n">
-        <v>19.19201454129347</v>
+        <v>19.19201838125387</v>
       </c>
       <c r="F395" t="n">
         <v>972150</v>
@@ -8332,16 +8332,16 @@
         <v>44678</v>
       </c>
       <c r="B396" t="n">
-        <v>19.49865531921387</v>
+        <v>19.49865341186523</v>
       </c>
       <c r="C396" t="n">
-        <v>19.55276766243008</v>
+        <v>19.55276574978821</v>
       </c>
       <c r="D396" t="n">
-        <v>19.10182745516075</v>
+        <v>19.10182558662962</v>
       </c>
       <c r="E396" t="n">
-        <v>19.46257927693614</v>
+        <v>19.46257737311645</v>
       </c>
       <c r="F396" t="n">
         <v>619300</v>
@@ -8352,16 +8352,16 @@
         <v>44679</v>
       </c>
       <c r="B397" t="n">
-        <v>21.04988670349121</v>
+        <v>21.04989051818848</v>
       </c>
       <c r="C397" t="n">
-        <v>21.10399904077057</v>
+        <v>21.10400286527417</v>
       </c>
       <c r="D397" t="n">
-        <v>19.30023840959018</v>
+        <v>19.30024190721312</v>
       </c>
       <c r="E397" t="n">
-        <v>19.84136694298433</v>
+        <v>19.84137053867153</v>
       </c>
       <c r="F397" t="n">
         <v>1501350</v>
@@ -8372,16 +8372,16 @@
         <v>44680</v>
       </c>
       <c r="B398" t="n">
-        <v>21.04988670349121</v>
+        <v>21.04989051818848</v>
       </c>
       <c r="C398" t="n">
-        <v>21.60905153584503</v>
+        <v>21.60905545187512</v>
       </c>
       <c r="D398" t="n">
-        <v>20.90558599061279</v>
+        <v>20.90558977915963</v>
       </c>
       <c r="E398" t="n">
-        <v>21.60905153584503</v>
+        <v>21.60905545187512</v>
       </c>
       <c r="F398" t="n">
         <v>1651000</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.51902961730957</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C403" t="n">
-        <v>19.93473065890365</v>
+        <v>19.93473455484336</v>
       </c>
       <c r="D403" t="n">
-        <v>18.81989711218194</v>
+        <v>18.8199007902444</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019330479591</v>
+        <v>19.67019714903581</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8492,16 +8492,16 @@
         <v>44690</v>
       </c>
       <c r="B404" t="n">
-        <v>18.7821102142334</v>
+        <v>18.78210830688477</v>
       </c>
       <c r="C404" t="n">
-        <v>19.53793065186498</v>
+        <v>19.53792866776176</v>
       </c>
       <c r="D404" t="n">
-        <v>18.38530498003061</v>
+        <v>18.38530311297808</v>
       </c>
       <c r="E404" t="n">
-        <v>19.25449731199797</v>
+        <v>19.25449535667779</v>
       </c>
       <c r="F404" t="n">
         <v>2367350</v>
@@ -8512,16 +8512,16 @@
         <v>44691</v>
       </c>
       <c r="B405" t="n">
-        <v>19.16001892089844</v>
+        <v>19.1600170135498</v>
       </c>
       <c r="C405" t="n">
-        <v>19.38676448302573</v>
+        <v>19.38676255310495</v>
       </c>
       <c r="D405" t="n">
-        <v>18.61205002858743</v>
+        <v>18.6120481757882</v>
       </c>
       <c r="E405" t="n">
-        <v>19.04664523882802</v>
+        <v>19.04664334276555</v>
       </c>
       <c r="F405" t="n">
         <v>1243050</v>
@@ -8632,16 +8632,16 @@
         <v>44699</v>
       </c>
       <c r="B411" t="n">
-        <v>20.36932563781738</v>
+        <v>20.36932945251465</v>
       </c>
       <c r="C411" t="n">
-        <v>20.76613076461962</v>
+        <v>20.76613465362919</v>
       </c>
       <c r="D411" t="n">
-        <v>20.10479008795808</v>
+        <v>20.10479385311404</v>
       </c>
       <c r="E411" t="n">
-        <v>20.44490748092194</v>
+        <v>20.44491130977391</v>
       </c>
       <c r="F411" t="n">
         <v>1338150</v>
@@ -8692,16 +8692,16 @@
         <v>44704</v>
       </c>
       <c r="B414" t="n">
-        <v>20.82282066345215</v>
+        <v>20.82282257080078</v>
       </c>
       <c r="C414" t="n">
-        <v>21.16293809177876</v>
+        <v>21.1629400302818</v>
       </c>
       <c r="D414" t="n">
-        <v>20.61496922179389</v>
+        <v>20.61497111010355</v>
       </c>
       <c r="E414" t="n">
-        <v>20.78502883696393</v>
+        <v>20.78503074085087</v>
       </c>
       <c r="F414" t="n">
         <v>1655200</v>
@@ -8712,16 +8712,16 @@
         <v>44705</v>
       </c>
       <c r="B415" t="n">
-        <v>20.38822555541992</v>
+        <v>20.38822364807129</v>
       </c>
       <c r="C415" t="n">
-        <v>20.7850307601951</v>
+        <v>20.78502881572475</v>
       </c>
       <c r="D415" t="n">
-        <v>19.93473440768075</v>
+        <v>19.93473254275689</v>
       </c>
       <c r="E415" t="n">
-        <v>20.59607521429696</v>
+        <v>20.59607328750369</v>
       </c>
       <c r="F415" t="n">
         <v>1381900</v>
@@ -8752,16 +8752,16 @@
         <v>44707</v>
       </c>
       <c r="B417" t="n">
-        <v>21.18183517456055</v>
+        <v>21.18183326721191</v>
       </c>
       <c r="C417" t="n">
-        <v>21.27631294398413</v>
+        <v>21.27631102812812</v>
       </c>
       <c r="D417" t="n">
-        <v>20.67165630088131</v>
+        <v>20.67165443947247</v>
       </c>
       <c r="E417" t="n">
-        <v>20.8228218131672</v>
+        <v>20.82281993814643</v>
       </c>
       <c r="F417" t="n">
         <v>1373550</v>
@@ -8792,16 +8792,16 @@
         <v>44711</v>
       </c>
       <c r="B419" t="n">
-        <v>22.14550590515137</v>
+        <v>22.14550399780273</v>
       </c>
       <c r="C419" t="n">
-        <v>23.22254782665845</v>
+        <v>23.22254582654633</v>
       </c>
       <c r="D419" t="n">
-        <v>22.14550590515137</v>
+        <v>22.14550399780273</v>
       </c>
       <c r="E419" t="n">
-        <v>22.97690633890859</v>
+        <v>22.97690435995308</v>
       </c>
       <c r="F419" t="n">
         <v>1234700</v>
@@ -8852,16 +8852,16 @@
         <v>44714</v>
       </c>
       <c r="B422" t="n">
-        <v>23.37371063232422</v>
+        <v>23.37370872497559</v>
       </c>
       <c r="C422" t="n">
-        <v>24.31848471674483</v>
+        <v>24.31848273230045</v>
       </c>
       <c r="D422" t="n">
-        <v>23.24144283714967</v>
+        <v>23.24144094059439</v>
       </c>
       <c r="E422" t="n">
-        <v>23.43039657282566</v>
+        <v>23.43039466085132</v>
       </c>
       <c r="F422" t="n">
         <v>1968350</v>
@@ -8912,16 +8912,16 @@
         <v>44719</v>
       </c>
       <c r="B425" t="n">
-        <v>21.59753608703613</v>
+        <v>21.5975341796875</v>
       </c>
       <c r="C425" t="n">
-        <v>21.93765353112191</v>
+        <v>21.93765159373639</v>
       </c>
       <c r="D425" t="n">
-        <v>21.25741684093681</v>
+        <v>21.25741496362521</v>
       </c>
       <c r="E425" t="n">
-        <v>21.72980388184651</v>
+        <v>21.72980196281688</v>
       </c>
       <c r="F425" t="n">
         <v>1412350</v>
@@ -8932,16 +8932,16 @@
         <v>44720</v>
       </c>
       <c r="B426" t="n">
-        <v>21.20072937011719</v>
+        <v>21.20073127746582</v>
       </c>
       <c r="C426" t="n">
-        <v>21.82428007494298</v>
+        <v>21.82428203839009</v>
       </c>
       <c r="D426" t="n">
-        <v>21.03066975934408</v>
+        <v>21.0306716513931</v>
       </c>
       <c r="E426" t="n">
-        <v>21.48416085339676</v>
+        <v>21.48416278624464</v>
       </c>
       <c r="F426" t="n">
         <v>863650</v>
@@ -8952,16 +8952,16 @@
         <v>44721</v>
       </c>
       <c r="B427" t="n">
-        <v>21.54084777832031</v>
+        <v>21.54084968566895</v>
       </c>
       <c r="C427" t="n">
-        <v>21.72980331052155</v>
+        <v>21.72980523460138</v>
       </c>
       <c r="D427" t="n">
-        <v>20.8984029332658</v>
+        <v>20.89840478372873</v>
       </c>
       <c r="E427" t="n">
-        <v>21.20073034317699</v>
+        <v>21.20073222040969</v>
       </c>
       <c r="F427" t="n">
         <v>1117750</v>
@@ -8992,16 +8992,16 @@
         <v>44725</v>
       </c>
       <c r="B429" t="n">
-        <v>19.25449371337891</v>
+        <v>19.25449752807617</v>
       </c>
       <c r="C429" t="n">
-        <v>20.01031400974947</v>
+        <v>20.01031797418974</v>
       </c>
       <c r="D429" t="n">
-        <v>18.98995814136063</v>
+        <v>18.98996190364815</v>
       </c>
       <c r="E429" t="n">
-        <v>19.95362807317604</v>
+        <v>19.9536320263857</v>
       </c>
       <c r="F429" t="n">
         <v>2646600</v>
@@ -9012,16 +9012,16 @@
         <v>44726</v>
       </c>
       <c r="B430" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C430" t="n">
-        <v>19.51903189147468</v>
+        <v>19.51902994454667</v>
       </c>
       <c r="D430" t="n">
-        <v>18.89548115744023</v>
+        <v>18.89547927270836</v>
       </c>
       <c r="E430" t="n">
-        <v>19.51903189147468</v>
+        <v>19.51902994454667</v>
       </c>
       <c r="F430" t="n">
         <v>1027150</v>
@@ -9052,16 +9052,16 @@
         <v>44729</v>
       </c>
       <c r="B432" t="n">
-        <v>19.19780731201172</v>
+        <v>19.19780921936035</v>
       </c>
       <c r="C432" t="n">
-        <v>19.51903061483979</v>
+        <v>19.51903255410274</v>
       </c>
       <c r="D432" t="n">
-        <v>18.68763029117579</v>
+        <v>18.6876321478371</v>
       </c>
       <c r="E432" t="n">
-        <v>19.17891139960691</v>
+        <v>19.17891330507819</v>
       </c>
       <c r="F432" t="n">
         <v>2517400</v>
@@ -9132,16 +9132,16 @@
         <v>44735</v>
       </c>
       <c r="B436" t="n">
-        <v>18.81989860534668</v>
+        <v>18.81990051269531</v>
       </c>
       <c r="C436" t="n">
-        <v>18.89548045508649</v>
+        <v>18.89548237009515</v>
       </c>
       <c r="D436" t="n">
-        <v>18.49867529344914</v>
+        <v>18.4986771682426</v>
       </c>
       <c r="E436" t="n">
-        <v>18.72542084266856</v>
+        <v>18.72542274044211</v>
       </c>
       <c r="F436" t="n">
         <v>1280500</v>
@@ -9172,16 +9172,16 @@
         <v>44739</v>
       </c>
       <c r="B438" t="n">
-        <v>18.55536270141602</v>
+        <v>18.55536079406738</v>
       </c>
       <c r="C438" t="n">
-        <v>18.70652641288067</v>
+        <v>18.70652448999358</v>
       </c>
       <c r="D438" t="n">
-        <v>18.38530307551488</v>
+        <v>18.38530118564707</v>
       </c>
       <c r="E438" t="n">
-        <v>18.57425861585249</v>
+        <v>18.57425670656151</v>
       </c>
       <c r="F438" t="n">
         <v>799000</v>
@@ -9272,16 +9272,16 @@
         <v>44746</v>
       </c>
       <c r="B443" t="n">
-        <v>17.28936576843262</v>
+        <v>17.28936386108398</v>
       </c>
       <c r="C443" t="n">
-        <v>17.64838094509635</v>
+        <v>17.64837899814145</v>
       </c>
       <c r="D443" t="n">
-        <v>17.25157574047591</v>
+        <v>17.25157383729624</v>
       </c>
       <c r="E443" t="n">
-        <v>17.44052948428672</v>
+        <v>17.44052756026183</v>
       </c>
       <c r="F443" t="n">
         <v>903450</v>
@@ -9292,16 +9292,16 @@
         <v>44747</v>
       </c>
       <c r="B444" t="n">
-        <v>17.10041236877441</v>
+        <v>17.10041046142578</v>
       </c>
       <c r="C444" t="n">
-        <v>17.25157608767075</v>
+        <v>17.25157416346159</v>
       </c>
       <c r="D444" t="n">
-        <v>16.57133935263724</v>
+        <v>16.57133750430044</v>
       </c>
       <c r="E444" t="n">
-        <v>17.15709831285712</v>
+        <v>17.15709639918584</v>
       </c>
       <c r="F444" t="n">
         <v>2077700</v>
@@ -9332,16 +9332,16 @@
         <v>44749</v>
       </c>
       <c r="B446" t="n">
-        <v>17.66727447509766</v>
+        <v>17.66727638244629</v>
       </c>
       <c r="C446" t="n">
-        <v>18.13966147387552</v>
+        <v>18.13966343222278</v>
       </c>
       <c r="D446" t="n">
-        <v>17.49721486721548</v>
+        <v>17.49721675620458</v>
       </c>
       <c r="E446" t="n">
-        <v>17.51611077964981</v>
+        <v>17.5161126706789</v>
       </c>
       <c r="F446" t="n">
         <v>1515500</v>
@@ -9352,16 +9352,16 @@
         <v>44750</v>
       </c>
       <c r="B447" t="n">
-        <v>17.72396278381348</v>
+        <v>17.72396087646484</v>
       </c>
       <c r="C447" t="n">
-        <v>18.12076798800384</v>
+        <v>18.12076603795336</v>
       </c>
       <c r="D447" t="n">
-        <v>17.64838092596834</v>
+        <v>17.64837902675339</v>
       </c>
       <c r="E447" t="n">
-        <v>17.8184405566233</v>
+        <v>17.81843863910753</v>
       </c>
       <c r="F447" t="n">
         <v>701700</v>
@@ -9412,16 +9412,16 @@
         <v>44755</v>
       </c>
       <c r="B450" t="n">
-        <v>16.87366676330566</v>
+        <v>16.87366485595703</v>
       </c>
       <c r="C450" t="n">
-        <v>17.024830481959</v>
+        <v>17.02482855752328</v>
       </c>
       <c r="D450" t="n">
-        <v>16.3445919460053</v>
+        <v>16.3445900984617</v>
       </c>
       <c r="E450" t="n">
-        <v>16.51465157999372</v>
+        <v>16.51464971322709</v>
       </c>
       <c r="F450" t="n">
         <v>919750</v>
@@ -9452,16 +9452,16 @@
         <v>44757</v>
       </c>
       <c r="B452" t="n">
-        <v>16.59023284912109</v>
+        <v>16.59023094177246</v>
       </c>
       <c r="C452" t="n">
-        <v>17.15709767491168</v>
+        <v>17.15709570239164</v>
       </c>
       <c r="D452" t="n">
-        <v>16.59023284912109</v>
+        <v>16.59023094177246</v>
       </c>
       <c r="E452" t="n">
-        <v>17.06261990361098</v>
+        <v>17.06261794195288</v>
       </c>
       <c r="F452" t="n">
         <v>1098550</v>
@@ -9472,16 +9472,16 @@
         <v>44760</v>
       </c>
       <c r="B453" t="n">
-        <v>16.94924926757812</v>
+        <v>16.94924736022949</v>
       </c>
       <c r="C453" t="n">
-        <v>17.34605449464563</v>
+        <v>17.34605254264335</v>
       </c>
       <c r="D453" t="n">
-        <v>16.74139779501045</v>
+        <v>16.74139591105195</v>
       </c>
       <c r="E453" t="n">
-        <v>16.74139779501045</v>
+        <v>16.74139591105195</v>
       </c>
       <c r="F453" t="n">
         <v>809650</v>
@@ -9492,16 +9492,16 @@
         <v>44761</v>
       </c>
       <c r="B454" t="n">
-        <v>17.28936576843262</v>
+        <v>17.28936386108398</v>
       </c>
       <c r="C454" t="n">
-        <v>17.51611314422741</v>
+        <v>17.51611121186419</v>
       </c>
       <c r="D454" t="n">
-        <v>17.1004120246218</v>
+        <v>17.10041013811839</v>
       </c>
       <c r="E454" t="n">
-        <v>17.1004120246218</v>
+        <v>17.10041013811839</v>
       </c>
       <c r="F454" t="n">
         <v>816100</v>
@@ -9512,16 +9512,16 @@
         <v>44762</v>
       </c>
       <c r="B455" t="n">
-        <v>17.9696044921875</v>
+        <v>17.96960067749023</v>
       </c>
       <c r="C455" t="n">
-        <v>18.02629043576155</v>
+        <v>18.02628660903064</v>
       </c>
       <c r="D455" t="n">
-        <v>17.2326800176703</v>
+        <v>17.23267635941185</v>
       </c>
       <c r="E455" t="n">
-        <v>17.2515759328662</v>
+        <v>17.25157227059641</v>
       </c>
       <c r="F455" t="n">
         <v>812650</v>
@@ -9592,16 +9592,16 @@
         <v>44768</v>
       </c>
       <c r="B459" t="n">
-        <v>17.40273666381836</v>
+        <v>17.40273857116699</v>
       </c>
       <c r="C459" t="n">
-        <v>18.15855512180728</v>
+        <v>18.158557111994</v>
       </c>
       <c r="D459" t="n">
-        <v>17.25157297222058</v>
+        <v>17.25157486300159</v>
       </c>
       <c r="E459" t="n">
-        <v>18.04518325411562</v>
+        <v>18.04518523187672</v>
       </c>
       <c r="F459" t="n">
         <v>578050</v>
@@ -9612,16 +9612,16 @@
         <v>44769</v>
       </c>
       <c r="B460" t="n">
-        <v>18.23413848876953</v>
+        <v>18.23414039611816</v>
       </c>
       <c r="C460" t="n">
-        <v>18.38530219297798</v>
+        <v>18.38530411613882</v>
       </c>
       <c r="D460" t="n">
-        <v>17.34605217704824</v>
+        <v>17.34605399150023</v>
       </c>
       <c r="E460" t="n">
-        <v>17.4405281406684</v>
+        <v>17.44052996500288</v>
       </c>
       <c r="F460" t="n">
         <v>704800</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.51902961730957</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65129739335679</v>
+        <v>19.65130123390378</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431526843877</v>
+        <v>18.74431893172991</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658304448599</v>
+        <v>18.87658673362685</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9672,16 +9672,16 @@
         <v>44774</v>
       </c>
       <c r="B463" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C463" t="n">
-        <v>19.74577744912234</v>
+        <v>19.74577547957757</v>
       </c>
       <c r="D463" t="n">
-        <v>19.04664486253867</v>
+        <v>19.04664296272896</v>
       </c>
       <c r="E463" t="n">
-        <v>19.50013597783399</v>
+        <v>19.50013403279076</v>
       </c>
       <c r="F463" t="n">
         <v>811600</v>
@@ -9712,16 +9712,16 @@
         <v>44776</v>
       </c>
       <c r="B465" t="n">
-        <v>19.68909072875977</v>
+        <v>19.6890926361084</v>
       </c>
       <c r="C465" t="n">
-        <v>19.74577666541846</v>
+        <v>19.74577857825845</v>
       </c>
       <c r="D465" t="n">
-        <v>19.02774819369244</v>
+        <v>19.02775003697459</v>
       </c>
       <c r="E465" t="n">
-        <v>19.08443593236457</v>
+        <v>19.08443778113825</v>
       </c>
       <c r="F465" t="n">
         <v>1095050</v>
@@ -9732,16 +9732,16 @@
         <v>44777</v>
       </c>
       <c r="B466" t="n">
-        <v>21.3141040802002</v>
+        <v>21.31410026550293</v>
       </c>
       <c r="C466" t="n">
-        <v>21.46526779834239</v>
+        <v>21.46526395659056</v>
       </c>
       <c r="D466" t="n">
-        <v>19.78357098350703</v>
+        <v>19.78356744273731</v>
       </c>
       <c r="E466" t="n">
-        <v>19.89694287110684</v>
+        <v>19.89693931004637</v>
       </c>
       <c r="F466" t="n">
         <v>1697500</v>
@@ -9752,16 +9752,16 @@
         <v>44778</v>
       </c>
       <c r="B467" t="n">
-        <v>21.06846046447754</v>
+        <v>21.06846237182617</v>
       </c>
       <c r="C467" t="n">
-        <v>21.38968378366087</v>
+        <v>21.38968572009017</v>
       </c>
       <c r="D467" t="n">
-        <v>20.40711971475746</v>
+        <v>20.40712156223426</v>
       </c>
       <c r="E467" t="n">
-        <v>20.93619267493622</v>
+        <v>20.93619457031052</v>
       </c>
       <c r="F467" t="n">
         <v>1243500</v>
@@ -9772,16 +9772,16 @@
         <v>44781</v>
       </c>
       <c r="B468" t="n">
-        <v>21.54084777832031</v>
+        <v>21.54084968566895</v>
       </c>
       <c r="C468" t="n">
-        <v>21.843176990245</v>
+        <v>21.84317892436357</v>
       </c>
       <c r="D468" t="n">
-        <v>21.01177481097574</v>
+        <v>21.01177667147726</v>
       </c>
       <c r="E468" t="n">
-        <v>21.21962445478631</v>
+        <v>21.21962633369201</v>
       </c>
       <c r="F468" t="n">
         <v>1786950</v>
@@ -9832,16 +9832,16 @@
         <v>44784</v>
       </c>
       <c r="B471" t="n">
-        <v>22.01323699951172</v>
+        <v>22.01323509216309</v>
       </c>
       <c r="C471" t="n">
-        <v>22.0888188595181</v>
+        <v>22.08881694562063</v>
       </c>
       <c r="D471" t="n">
-        <v>21.54084992396843</v>
+        <v>21.54084805755003</v>
       </c>
       <c r="E471" t="n">
-        <v>21.82428325050261</v>
+        <v>21.82428135952598</v>
       </c>
       <c r="F471" t="n">
         <v>1242750</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75015830993652</v>
+        <v>22.75015640258789</v>
       </c>
       <c r="C474" t="n">
-        <v>23.12806755720854</v>
+        <v>23.1280656181764</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341276157331</v>
+        <v>22.52341087323478</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027753348805</v>
+        <v>23.09027559762419</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9932,16 +9932,16 @@
         <v>44791</v>
       </c>
       <c r="B476" t="n">
-        <v>22.25887489318848</v>
+        <v>22.25887680053711</v>
       </c>
       <c r="C476" t="n">
-        <v>23.14696295606662</v>
+        <v>23.14696493951494</v>
       </c>
       <c r="D476" t="n">
-        <v>21.84317563142713</v>
+        <v>21.84317750315476</v>
       </c>
       <c r="E476" t="n">
-        <v>22.9957992605146</v>
+        <v>22.99580123100981</v>
       </c>
       <c r="F476" t="n">
         <v>1546750</v>
@@ -9952,16 +9952,16 @@
         <v>44792</v>
       </c>
       <c r="B477" t="n">
-        <v>21.16293907165527</v>
+        <v>21.16293716430664</v>
       </c>
       <c r="C477" t="n">
-        <v>22.16439909378708</v>
+        <v>22.16439709618003</v>
       </c>
       <c r="D477" t="n">
-        <v>20.97398533650574</v>
+        <v>20.97398344618691</v>
       </c>
       <c r="E477" t="n">
-        <v>22.16439909378708</v>
+        <v>22.16439709618003</v>
       </c>
       <c r="F477" t="n">
         <v>1251050</v>
@@ -9972,16 +9972,16 @@
         <v>44795</v>
       </c>
       <c r="B478" t="n">
-        <v>20.67165756225586</v>
+        <v>20.67165565490723</v>
       </c>
       <c r="C478" t="n">
-        <v>20.86061311263301</v>
+        <v>20.86061118784968</v>
       </c>
       <c r="D478" t="n">
-        <v>20.46380789845194</v>
+        <v>20.46380601028133</v>
       </c>
       <c r="E478" t="n">
-        <v>20.80392716832534</v>
+        <v>20.80392524877235</v>
       </c>
       <c r="F478" t="n">
         <v>1246950</v>
@@ -9992,16 +9992,16 @@
         <v>44796</v>
       </c>
       <c r="B479" t="n">
-        <v>20.76613426208496</v>
+        <v>20.76613235473633</v>
       </c>
       <c r="C479" t="n">
-        <v>20.97398571713913</v>
+        <v>20.97398379069955</v>
       </c>
       <c r="D479" t="n">
-        <v>20.29374721261799</v>
+        <v>20.29374534865763</v>
       </c>
       <c r="E479" t="n">
-        <v>20.80392609100884</v>
+        <v>20.80392418018906</v>
       </c>
       <c r="F479" t="n">
         <v>1768900</v>
@@ -10052,16 +10052,16 @@
         <v>44799</v>
       </c>
       <c r="B482" t="n">
-        <v>20.46380805969238</v>
+        <v>20.46380424499512</v>
       </c>
       <c r="C482" t="n">
-        <v>21.10625477362032</v>
+        <v>21.10625083916334</v>
       </c>
       <c r="D482" t="n">
-        <v>20.2748525078264</v>
+        <v>20.27484872835269</v>
       </c>
       <c r="E482" t="n">
-        <v>20.97398696852234</v>
+        <v>20.97398305872166</v>
       </c>
       <c r="F482" t="n">
         <v>564750</v>
@@ -10192,16 +10192,16 @@
         <v>44810</v>
       </c>
       <c r="B489" t="n">
-        <v>20.55828285217285</v>
+        <v>20.55828475952148</v>
       </c>
       <c r="C489" t="n">
-        <v>21.67311648196554</v>
+        <v>21.67311849274579</v>
       </c>
       <c r="D489" t="n">
-        <v>20.3504332168947</v>
+        <v>20.35043510495954</v>
       </c>
       <c r="E489" t="n">
-        <v>21.55974280689618</v>
+        <v>21.55974480715789</v>
       </c>
       <c r="F489" t="n">
         <v>1564950</v>
@@ -10292,16 +10292,16 @@
         <v>44818</v>
       </c>
       <c r="B494" t="n">
-        <v>20.42601585388184</v>
+        <v>20.4260139465332</v>
       </c>
       <c r="C494" t="n">
-        <v>20.52049181773355</v>
+        <v>20.5204899015629</v>
       </c>
       <c r="D494" t="n">
-        <v>19.51903182439467</v>
+        <v>19.51903000173875</v>
       </c>
       <c r="E494" t="n">
-        <v>19.7079873561251</v>
+        <v>19.70798551582482</v>
       </c>
       <c r="F494" t="n">
         <v>1153500</v>
@@ -10332,16 +10332,16 @@
         <v>44820</v>
       </c>
       <c r="B496" t="n">
-        <v>20.02920913696289</v>
+        <v>20.02921104431152</v>
       </c>
       <c r="C496" t="n">
-        <v>20.27484878648363</v>
+        <v>20.27485071722412</v>
       </c>
       <c r="D496" t="n">
-        <v>19.55682214601578</v>
+        <v>19.55682400837977</v>
       </c>
       <c r="E496" t="n">
-        <v>20.27484878648363</v>
+        <v>20.27485071722412</v>
       </c>
       <c r="F496" t="n">
         <v>1629800</v>
@@ -10352,16 +10352,16 @@
         <v>44823</v>
       </c>
       <c r="B497" t="n">
-        <v>20.36932563781738</v>
+        <v>20.36932945251465</v>
       </c>
       <c r="C497" t="n">
-        <v>20.5204893240265</v>
+        <v>20.52049316703318</v>
       </c>
       <c r="D497" t="n">
-        <v>19.85914864736495</v>
+        <v>19.85915236651802</v>
       </c>
       <c r="E497" t="n">
-        <v>19.93473049046951</v>
+        <v>19.93473422377729</v>
       </c>
       <c r="F497" t="n">
         <v>718850</v>
@@ -10392,16 +10392,16 @@
         <v>44825</v>
       </c>
       <c r="B499" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C499" t="n">
-        <v>20.08589668660058</v>
+        <v>20.08589468313058</v>
       </c>
       <c r="D499" t="n">
-        <v>19.04664486253867</v>
+        <v>19.04664296272896</v>
       </c>
       <c r="E499" t="n">
-        <v>19.84025521531224</v>
+        <v>19.84025323634378</v>
       </c>
       <c r="F499" t="n">
         <v>1245900</v>
@@ -10432,16 +10432,16 @@
         <v>44827</v>
       </c>
       <c r="B501" t="n">
-        <v>19.57571792602539</v>
+        <v>19.57571601867676</v>
       </c>
       <c r="C501" t="n">
-        <v>19.68909160640989</v>
+        <v>19.68908968801476</v>
       </c>
       <c r="D501" t="n">
-        <v>19.21670457516592</v>
+        <v>19.21670270279754</v>
       </c>
       <c r="E501" t="n">
-        <v>19.3489723672699</v>
+        <v>19.34897048201409</v>
       </c>
       <c r="F501" t="n">
         <v>673550</v>
@@ -10472,16 +10472,16 @@
         <v>44831</v>
       </c>
       <c r="B503" t="n">
-        <v>18.30972099304199</v>
+        <v>18.30971908569336</v>
       </c>
       <c r="C503" t="n">
-        <v>19.00885540242521</v>
+        <v>19.00885342224679</v>
       </c>
       <c r="D503" t="n">
-        <v>18.25303505244812</v>
+        <v>18.25303315100454</v>
       </c>
       <c r="E503" t="n">
-        <v>18.97106357402025</v>
+        <v>18.97106159777866</v>
       </c>
       <c r="F503" t="n">
         <v>994450</v>
@@ -10512,16 +10512,16 @@
         <v>44833</v>
       </c>
       <c r="B505" t="n">
-        <v>18.21524238586426</v>
+        <v>18.21524620056152</v>
       </c>
       <c r="C505" t="n">
-        <v>18.30971833915579</v>
+        <v>18.30972217363853</v>
       </c>
       <c r="D505" t="n">
-        <v>17.85622727610854</v>
+        <v>17.85623101561966</v>
       </c>
       <c r="E505" t="n">
-        <v>18.29082422970546</v>
+        <v>18.29082806023133</v>
       </c>
       <c r="F505" t="n">
         <v>1182750</v>
@@ -10532,16 +10532,16 @@
         <v>44834</v>
       </c>
       <c r="B506" t="n">
-        <v>18.25303649902344</v>
+        <v>18.25303268432617</v>
       </c>
       <c r="C506" t="n">
-        <v>18.51757391278236</v>
+        <v>18.51757004279949</v>
       </c>
       <c r="D506" t="n">
-        <v>17.95070905587821</v>
+        <v>17.95070530436427</v>
       </c>
       <c r="E506" t="n">
-        <v>18.21524646963713</v>
+        <v>18.2152426628376</v>
       </c>
       <c r="F506" t="n">
         <v>981200</v>
@@ -10592,16 +10592,16 @@
         <v>44839</v>
       </c>
       <c r="B509" t="n">
-        <v>19.63240814208984</v>
+        <v>19.63240623474121</v>
       </c>
       <c r="C509" t="n">
-        <v>19.8402578133139</v>
+        <v>19.84025588577203</v>
       </c>
       <c r="D509" t="n">
-        <v>19.38676663863574</v>
+        <v>19.38676475515193</v>
       </c>
       <c r="E509" t="n">
-        <v>19.72688411863749</v>
+        <v>19.72688220211023</v>
       </c>
       <c r="F509" t="n">
         <v>721150</v>
@@ -10632,16 +10632,16 @@
         <v>44841</v>
       </c>
       <c r="B511" t="n">
-        <v>19.63240814208984</v>
+        <v>19.63240623474121</v>
       </c>
       <c r="C511" t="n">
-        <v>20.38822676655345</v>
+        <v>20.38822478577472</v>
       </c>
       <c r="D511" t="n">
-        <v>19.55682627964348</v>
+        <v>19.55682437963786</v>
       </c>
       <c r="E511" t="n">
-        <v>20.38822676655345</v>
+        <v>20.38822478577472</v>
       </c>
       <c r="F511" t="n">
         <v>673950</v>
@@ -10652,16 +10652,16 @@
         <v>44844</v>
       </c>
       <c r="B512" t="n">
-        <v>19.55682373046875</v>
+        <v>19.55682182312012</v>
       </c>
       <c r="C512" t="n">
-        <v>19.74577746094821</v>
+        <v>19.7457755351712</v>
       </c>
       <c r="D512" t="n">
-        <v>19.29228634538129</v>
+        <v>19.2922844638326</v>
       </c>
       <c r="E512" t="n">
-        <v>19.68909152200573</v>
+        <v>19.68908960175721</v>
       </c>
       <c r="F512" t="n">
         <v>555250</v>
@@ -10712,16 +10712,16 @@
         <v>44848</v>
       </c>
       <c r="B515" t="n">
-        <v>19.16001892089844</v>
+        <v>19.1600170135498</v>
       </c>
       <c r="C515" t="n">
-        <v>19.84025560728032</v>
+        <v>19.84025363221523</v>
       </c>
       <c r="D515" t="n">
-        <v>18.97106338478559</v>
+        <v>18.97106149624717</v>
       </c>
       <c r="E515" t="n">
-        <v>19.84025560728032</v>
+        <v>19.84025363221523</v>
       </c>
       <c r="F515" t="n">
         <v>919650</v>
@@ -10752,16 +10752,16 @@
         <v>44852</v>
       </c>
       <c r="B517" t="n">
-        <v>19.53792762756348</v>
+        <v>19.53792953491211</v>
       </c>
       <c r="C517" t="n">
-        <v>19.78356909661954</v>
+        <v>19.7835710279484</v>
       </c>
       <c r="D517" t="n">
-        <v>19.23560022011401</v>
+        <v>19.23560209794857</v>
       </c>
       <c r="E517" t="n">
-        <v>19.55682354103244</v>
+        <v>19.55682545022575</v>
       </c>
       <c r="F517" t="n">
         <v>665900</v>
@@ -10792,16 +10792,16 @@
         <v>44854</v>
       </c>
       <c r="B519" t="n">
-        <v>19.48124313354492</v>
+        <v>19.48124122619629</v>
       </c>
       <c r="C519" t="n">
-        <v>19.84025650600569</v>
+        <v>19.84025456350717</v>
       </c>
       <c r="D519" t="n">
-        <v>19.19780981653667</v>
+        <v>19.19780793693812</v>
       </c>
       <c r="E519" t="n">
-        <v>19.84025650600569</v>
+        <v>19.84025456350717</v>
       </c>
       <c r="F519" t="n">
         <v>1274100</v>
@@ -10832,16 +10832,16 @@
         <v>44858</v>
       </c>
       <c r="B521" t="n">
-        <v>19.55682373046875</v>
+        <v>19.55682182312012</v>
       </c>
       <c r="C521" t="n">
-        <v>19.8591511408467</v>
+        <v>19.85914920401251</v>
       </c>
       <c r="D521" t="n">
-        <v>19.33007637067178</v>
+        <v>19.33007448543749</v>
       </c>
       <c r="E521" t="n">
-        <v>19.74577746094821</v>
+        <v>19.7457755351712</v>
       </c>
       <c r="F521" t="n">
         <v>947100</v>
@@ -10872,16 +10872,16 @@
         <v>44860</v>
       </c>
       <c r="B523" t="n">
-        <v>18.38530158996582</v>
+        <v>18.38530349731445</v>
       </c>
       <c r="C523" t="n">
-        <v>19.3111815003919</v>
+        <v>19.31118350379421</v>
       </c>
       <c r="D523" t="n">
-        <v>18.06408008056859</v>
+        <v>18.06408195459271</v>
       </c>
       <c r="E523" t="n">
-        <v>18.98995818898124</v>
+        <v>18.98996015905884</v>
       </c>
       <c r="F523" t="n">
         <v>1458850</v>
@@ -10912,16 +10912,16 @@
         <v>44862</v>
       </c>
       <c r="B525" t="n">
-        <v>19.40566062927246</v>
+        <v>19.40565872192383</v>
       </c>
       <c r="C525" t="n">
-        <v>19.7457780755269</v>
+        <v>19.74577613474872</v>
       </c>
       <c r="D525" t="n">
-        <v>18.87658584263032</v>
+        <v>18.87658398728353</v>
       </c>
       <c r="E525" t="n">
-        <v>19.29228694584527</v>
+        <v>19.29228504963994</v>
       </c>
       <c r="F525" t="n">
         <v>1190600</v>
@@ -10932,16 +10932,16 @@
         <v>44865</v>
       </c>
       <c r="B526" t="n">
-        <v>20.46380805969238</v>
+        <v>20.46380424499512</v>
       </c>
       <c r="C526" t="n">
-        <v>20.50159989087106</v>
+        <v>20.50159606912895</v>
       </c>
       <c r="D526" t="n">
-        <v>18.76321530095325</v>
+        <v>18.76321180326671</v>
       </c>
       <c r="E526" t="n">
-        <v>18.78210941452889</v>
+        <v>18.78210591332026</v>
       </c>
       <c r="F526" t="n">
         <v>2299050</v>
@@ -10972,16 +10972,16 @@
         <v>44868</v>
       </c>
       <c r="B528" t="n">
-        <v>21.06846046447754</v>
+        <v>21.06846237182617</v>
       </c>
       <c r="C528" t="n">
-        <v>21.20073005603234</v>
+        <v>21.20073197535547</v>
       </c>
       <c r="D528" t="n">
-        <v>19.97252271738623</v>
+        <v>19.97252452551853</v>
       </c>
       <c r="E528" t="n">
-        <v>20.18037416039514</v>
+        <v>20.18037598734444</v>
       </c>
       <c r="F528" t="n">
         <v>1731950</v>
@@ -10992,16 +10992,16 @@
         <v>44869</v>
       </c>
       <c r="B529" t="n">
-        <v>21.38968276977539</v>
+        <v>21.38968467712402</v>
       </c>
       <c r="C529" t="n">
-        <v>21.74869789867495</v>
+        <v>21.74869983803748</v>
       </c>
       <c r="D529" t="n">
-        <v>21.011773530418</v>
+        <v>21.01177540406793</v>
       </c>
       <c r="E529" t="n">
-        <v>21.40857868224661</v>
+        <v>21.40858059128022</v>
       </c>
       <c r="F529" t="n">
         <v>1653450</v>
@@ -11052,16 +11052,16 @@
         <v>44874</v>
       </c>
       <c r="B532" t="n">
-        <v>18.7821102142334</v>
+        <v>18.78210830688477</v>
       </c>
       <c r="C532" t="n">
-        <v>20.06700369679745</v>
+        <v>20.06700165896615</v>
       </c>
       <c r="D532" t="n">
-        <v>18.61205237272972</v>
+        <v>18.61205048265069</v>
       </c>
       <c r="E532" t="n">
-        <v>19.85915402250599</v>
+        <v>19.85915200578211</v>
       </c>
       <c r="F532" t="n">
         <v>1714900</v>
@@ -11072,16 +11072,16 @@
         <v>44875</v>
       </c>
       <c r="B533" t="n">
-        <v>16.94924926757812</v>
+        <v>16.94924736022949</v>
       </c>
       <c r="C533" t="n">
-        <v>18.51757425979405</v>
+        <v>18.51757217595721</v>
       </c>
       <c r="D533" t="n">
-        <v>16.2501165916999</v>
+        <v>16.25011476302671</v>
       </c>
       <c r="E533" t="n">
-        <v>18.51757425979405</v>
+        <v>18.51757217595721</v>
       </c>
       <c r="F533" t="n">
         <v>6247350</v>
@@ -11092,16 +11092,16 @@
         <v>44876</v>
       </c>
       <c r="B534" t="n">
-        <v>15.5131893157959</v>
+        <v>15.51319026947021</v>
       </c>
       <c r="C534" t="n">
-        <v>16.96814035410347</v>
+        <v>16.96814139722099</v>
       </c>
       <c r="D534" t="n">
-        <v>15.05969732248658</v>
+        <v>15.05969824828244</v>
       </c>
       <c r="E534" t="n">
-        <v>16.94924624343426</v>
+        <v>16.94924728539026</v>
       </c>
       <c r="F534" t="n">
         <v>6426800</v>
@@ -11112,16 +11112,16 @@
         <v>44879</v>
       </c>
       <c r="B535" t="n">
-        <v>15.45650386810303</v>
+        <v>15.45650577545166</v>
       </c>
       <c r="C535" t="n">
-        <v>16.26900831697925</v>
+        <v>16.26901032459178</v>
       </c>
       <c r="D535" t="n">
-        <v>14.8896390838082</v>
+        <v>14.88964092120513</v>
       </c>
       <c r="E535" t="n">
-        <v>15.96668091255894</v>
+        <v>15.96668288286395</v>
       </c>
       <c r="F535" t="n">
         <v>3328550</v>
@@ -11172,16 +11172,16 @@
         <v>44883</v>
       </c>
       <c r="B538" t="n">
-        <v>13.83149147033691</v>
+        <v>13.83149242401123</v>
       </c>
       <c r="C538" t="n">
-        <v>14.88963822584258</v>
+        <v>14.88963925247558</v>
       </c>
       <c r="D538" t="n">
-        <v>13.73701371139616</v>
+        <v>13.73701465855629</v>
       </c>
       <c r="E538" t="n">
-        <v>14.26608753965234</v>
+        <v>14.26608852329183</v>
       </c>
       <c r="F538" t="n">
         <v>3266800</v>
@@ -11212,16 +11212,16 @@
         <v>44887</v>
       </c>
       <c r="B540" t="n">
-        <v>14.09602832794189</v>
+        <v>14.09603023529053</v>
       </c>
       <c r="C540" t="n">
-        <v>14.71957903156021</v>
+        <v>14.71958102328215</v>
       </c>
       <c r="D540" t="n">
-        <v>13.88817779306689</v>
+        <v>13.88817967229104</v>
       </c>
       <c r="E540" t="n">
-        <v>14.60620625826658</v>
+        <v>14.60620823464794</v>
       </c>
       <c r="F540" t="n">
         <v>2112800</v>
@@ -11272,16 +11272,16 @@
         <v>44890</v>
       </c>
       <c r="B543" t="n">
-        <v>14.11492538452148</v>
+        <v>14.11492347717285</v>
       </c>
       <c r="C543" t="n">
-        <v>14.90853581355609</v>
+        <v>14.90853379896694</v>
       </c>
       <c r="D543" t="n">
-        <v>13.94486665044753</v>
+        <v>13.94486476607892</v>
       </c>
       <c r="E543" t="n">
-        <v>14.90853581355609</v>
+        <v>14.90853379896694</v>
       </c>
       <c r="F543" t="n">
         <v>1492900</v>
@@ -11352,16 +11352,16 @@
         <v>44896</v>
       </c>
       <c r="B547" t="n">
-        <v>14.1527156829834</v>
+        <v>14.15271472930908</v>
       </c>
       <c r="C547" t="n">
-        <v>14.51172995157667</v>
+        <v>14.51172897371034</v>
       </c>
       <c r="D547" t="n">
-        <v>14.03934289832344</v>
+        <v>14.0393419522887</v>
       </c>
       <c r="E547" t="n">
-        <v>14.30388029687014</v>
+        <v>14.30387933300967</v>
       </c>
       <c r="F547" t="n">
         <v>1145350</v>
@@ -11372,16 +11372,16 @@
         <v>44897</v>
       </c>
       <c r="B548" t="n">
-        <v>14.28498363494873</v>
+        <v>14.28498268127441</v>
       </c>
       <c r="C548" t="n">
-        <v>14.58731104489259</v>
+        <v>14.58731007103471</v>
       </c>
       <c r="D548" t="n">
-        <v>14.05823807749083</v>
+        <v>14.05823713895419</v>
       </c>
       <c r="E548" t="n">
-        <v>14.17161085621978</v>
+        <v>14.1716099101143</v>
       </c>
       <c r="F548" t="n">
         <v>1219600</v>
@@ -11412,16 +11412,16 @@
         <v>44901</v>
       </c>
       <c r="B550" t="n">
-        <v>13.15125370025635</v>
+        <v>13.15125560760498</v>
       </c>
       <c r="C550" t="n">
-        <v>13.66143160668842</v>
+        <v>13.66143358802902</v>
       </c>
       <c r="D550" t="n">
-        <v>12.67886671648566</v>
+        <v>12.67886855532321</v>
       </c>
       <c r="E550" t="n">
-        <v>13.54805883870426</v>
+        <v>13.54806080360221</v>
       </c>
       <c r="F550" t="n">
         <v>4313950</v>
@@ -11512,16 +11512,16 @@
         <v>44908</v>
       </c>
       <c r="B555" t="n">
-        <v>11.58293056488037</v>
+        <v>11.58292961120605</v>
       </c>
       <c r="C555" t="n">
-        <v>12.22537633368632</v>
+        <v>12.22537532711658</v>
       </c>
       <c r="D555" t="n">
-        <v>11.48845279543493</v>
+        <v>11.48845184953939</v>
       </c>
       <c r="E555" t="n">
-        <v>11.97973575494038</v>
+        <v>11.97973476859532</v>
       </c>
       <c r="F555" t="n">
         <v>2082000</v>
@@ -11552,16 +11552,16 @@
         <v>44910</v>
       </c>
       <c r="B557" t="n">
-        <v>11.56403541564941</v>
+        <v>11.5640344619751</v>
       </c>
       <c r="C557" t="n">
-        <v>11.90415468734941</v>
+        <v>11.9041537056258</v>
       </c>
       <c r="D557" t="n">
-        <v>11.26170797503327</v>
+        <v>11.2617070462916</v>
       </c>
       <c r="E557" t="n">
-        <v>11.41287169534134</v>
+        <v>11.41287075413335</v>
       </c>
       <c r="F557" t="n">
         <v>3167400</v>
@@ -11692,16 +11692,16 @@
         <v>44921</v>
       </c>
       <c r="B564" t="n">
-        <v>13.17015075683594</v>
+        <v>13.17014980316162</v>
       </c>
       <c r="C564" t="n">
-        <v>13.49137409985749</v>
+        <v>13.49137312292281</v>
       </c>
       <c r="D564" t="n">
-        <v>12.83003240005202</v>
+        <v>12.83003147100628</v>
       </c>
       <c r="E564" t="n">
-        <v>13.4157922427944</v>
+        <v>13.41579127133274</v>
       </c>
       <c r="F564" t="n">
         <v>1094200</v>
@@ -11732,16 +11732,16 @@
         <v>44923</v>
       </c>
       <c r="B566" t="n">
-        <v>13.10085010528564</v>
+        <v>13.10084915161133</v>
       </c>
       <c r="C566" t="n">
-        <v>13.12014487705818</v>
+        <v>13.1201439219793</v>
       </c>
       <c r="D566" t="n">
-        <v>12.29048809134627</v>
+        <v>12.29048719666213</v>
       </c>
       <c r="E566" t="n">
-        <v>12.46413735719766</v>
+        <v>12.46413644987275</v>
       </c>
       <c r="F566" t="n">
         <v>2129050</v>
@@ -11772,16 +11772,16 @@
         <v>44928</v>
       </c>
       <c r="B568" t="n">
-        <v>12.21331119537354</v>
+        <v>12.21331024169922</v>
       </c>
       <c r="C568" t="n">
-        <v>12.83073010946179</v>
+        <v>12.83072910757643</v>
       </c>
       <c r="D568" t="n">
-        <v>11.98177944759996</v>
+        <v>11.98177851200476</v>
       </c>
       <c r="E568" t="n">
-        <v>12.83073010946179</v>
+        <v>12.83072910757643</v>
       </c>
       <c r="F568" t="n">
         <v>1499800</v>
@@ -11792,16 +11792,16 @@
         <v>44929</v>
       </c>
       <c r="B569" t="n">
-        <v>11.65377616882324</v>
+        <v>11.65377521514893</v>
       </c>
       <c r="C569" t="n">
-        <v>12.21331170950984</v>
+        <v>12.21331071004653</v>
       </c>
       <c r="D569" t="n">
-        <v>11.5958936894559</v>
+        <v>11.59589274051833</v>
       </c>
       <c r="E569" t="n">
-        <v>12.21331170950984</v>
+        <v>12.21331071004653</v>
       </c>
       <c r="F569" t="n">
         <v>2015100</v>
@@ -11852,16 +11852,16 @@
         <v>44932</v>
       </c>
       <c r="B572" t="n">
-        <v>13.08155632019043</v>
+        <v>13.08155727386475</v>
       </c>
       <c r="C572" t="n">
-        <v>13.13943879575224</v>
+        <v>13.13943975364632</v>
       </c>
       <c r="D572" t="n">
-        <v>12.44484264883297</v>
+        <v>12.44484355608945</v>
       </c>
       <c r="E572" t="n">
-        <v>12.73425778671811</v>
+        <v>12.7342587150736</v>
       </c>
       <c r="F572" t="n">
         <v>1382000</v>
@@ -11892,16 +11892,16 @@
         <v>44936</v>
       </c>
       <c r="B574" t="n">
-        <v>13.8533296585083</v>
+        <v>13.85332870483398</v>
       </c>
       <c r="C574" t="n">
-        <v>14.00768508302567</v>
+        <v>14.0076841187254</v>
       </c>
       <c r="D574" t="n">
-        <v>13.04296850992557</v>
+        <v>13.04296761203716</v>
       </c>
       <c r="E574" t="n">
-        <v>13.17802824134331</v>
+        <v>13.17802733415729</v>
       </c>
       <c r="F574" t="n">
         <v>2939000</v>
@@ -11952,16 +11952,16 @@
         <v>44939</v>
       </c>
       <c r="B577" t="n">
-        <v>13.33238220214844</v>
+        <v>13.33238124847412</v>
       </c>
       <c r="C577" t="n">
-        <v>13.4867367003459</v>
+        <v>13.4867357356305</v>
       </c>
       <c r="D577" t="n">
-        <v>13.13943907940161</v>
+        <v>13.13943813952864</v>
       </c>
       <c r="E577" t="n">
-        <v>13.42885422353454</v>
+        <v>13.42885326295952</v>
       </c>
       <c r="F577" t="n">
         <v>1373850</v>
@@ -12052,16 +12052,16 @@
         <v>44946</v>
       </c>
       <c r="B582" t="n">
-        <v>14.06556701660156</v>
+        <v>14.06556606292725</v>
       </c>
       <c r="C582" t="n">
-        <v>14.12345041355349</v>
+        <v>14.12344945595456</v>
       </c>
       <c r="D582" t="n">
-        <v>13.50603149950962</v>
+        <v>13.50603058377296</v>
       </c>
       <c r="E582" t="n">
-        <v>13.73756324726655</v>
+        <v>13.73756231583157</v>
       </c>
       <c r="F582" t="n">
         <v>2454200</v>
@@ -12152,16 +12152,16 @@
         <v>44953</v>
       </c>
       <c r="B587" t="n">
-        <v>14.35498142242432</v>
+        <v>14.35498237609863</v>
       </c>
       <c r="C587" t="n">
-        <v>14.64439655223626</v>
+        <v>14.6443975251379</v>
       </c>
       <c r="D587" t="n">
-        <v>14.29709802845179</v>
+        <v>14.29709897828062</v>
       </c>
       <c r="E587" t="n">
-        <v>14.56721930695646</v>
+        <v>14.56722027473081</v>
       </c>
       <c r="F587" t="n">
         <v>1566450</v>
@@ -12172,16 +12172,16 @@
         <v>44956</v>
       </c>
       <c r="B588" t="n">
-        <v>14.39356994628906</v>
+        <v>14.39357089996338</v>
       </c>
       <c r="C588" t="n">
-        <v>14.6636903029147</v>
+        <v>14.66369127448637</v>
       </c>
       <c r="D588" t="n">
-        <v>14.31639270153888</v>
+        <v>14.31639365009966</v>
       </c>
       <c r="E588" t="n">
-        <v>14.37427517508885</v>
+        <v>14.37427612748476</v>
       </c>
       <c r="F588" t="n">
         <v>1160300</v>
@@ -12192,16 +12192,16 @@
         <v>44957</v>
       </c>
       <c r="B589" t="n">
-        <v>14.99169540405273</v>
+        <v>14.99169445037842</v>
       </c>
       <c r="C589" t="n">
-        <v>15.04957880284405</v>
+        <v>15.04957784548756</v>
       </c>
       <c r="D589" t="n">
-        <v>14.39357124332777</v>
+        <v>14.39357032770223</v>
       </c>
       <c r="E589" t="n">
-        <v>14.41286509624127</v>
+        <v>14.41286417938838</v>
       </c>
       <c r="F589" t="n">
         <v>1759050</v>
@@ -12212,16 +12212,16 @@
         <v>44958</v>
       </c>
       <c r="B590" t="n">
-        <v>14.99169540405273</v>
+        <v>14.99169445037842</v>
       </c>
       <c r="C590" t="n">
-        <v>15.16534468040126</v>
+        <v>15.1653437156805</v>
       </c>
       <c r="D590" t="n">
-        <v>14.7408688759994</v>
+        <v>14.74086793828104</v>
       </c>
       <c r="E590" t="n">
-        <v>14.97240155113924</v>
+        <v>14.97240059869227</v>
       </c>
       <c r="F590" t="n">
         <v>1831550</v>
@@ -12372,16 +12372,16 @@
         <v>44970</v>
       </c>
       <c r="B598" t="n">
-        <v>14.12344932556152</v>
+        <v>14.12345027923584</v>
       </c>
       <c r="C598" t="n">
-        <v>14.62510140705705</v>
+        <v>14.62510239460502</v>
       </c>
       <c r="D598" t="n">
-        <v>13.9690939189222</v>
+        <v>13.9690948621738</v>
       </c>
       <c r="E598" t="n">
-        <v>14.04627208225452</v>
+        <v>14.04627303071751</v>
       </c>
       <c r="F598" t="n">
         <v>1583800</v>
@@ -12392,16 +12392,16 @@
         <v>44971</v>
       </c>
       <c r="B599" t="n">
-        <v>13.96909427642822</v>
+        <v>13.96909523010254</v>
       </c>
       <c r="C599" t="n">
-        <v>14.50933591342878</v>
+        <v>14.50933690398556</v>
       </c>
       <c r="D599" t="n">
-        <v>13.69897391794061</v>
+        <v>13.69897485317373</v>
       </c>
       <c r="E599" t="n">
-        <v>14.35498142286443</v>
+        <v>14.35498240288338</v>
       </c>
       <c r="F599" t="n">
         <v>2796000</v>
@@ -12412,16 +12412,16 @@
         <v>44972</v>
       </c>
       <c r="B600" t="n">
-        <v>14.83734130859375</v>
+        <v>14.83734035491943</v>
       </c>
       <c r="C600" t="n">
-        <v>15.04957921663013</v>
+        <v>15.04957824931416</v>
       </c>
       <c r="D600" t="n">
-        <v>13.7375640615239</v>
+        <v>13.73756317853808</v>
       </c>
       <c r="E600" t="n">
-        <v>14.00768536994309</v>
+        <v>14.00768446959514</v>
       </c>
       <c r="F600" t="n">
         <v>2808050</v>
@@ -12492,16 +12492,16 @@
         <v>44980</v>
       </c>
       <c r="B604" t="n">
-        <v>14.41286563873291</v>
+        <v>14.41286468505859</v>
       </c>
       <c r="C604" t="n">
-        <v>14.91451871372149</v>
+        <v>14.91451772685366</v>
       </c>
       <c r="D604" t="n">
-        <v>14.27780590317863</v>
+        <v>14.27780495844099</v>
       </c>
       <c r="E604" t="n">
-        <v>14.6636921762272</v>
+        <v>14.66369120595613</v>
       </c>
       <c r="F604" t="n">
         <v>1540800</v>
@@ -12552,16 +12552,16 @@
         <v>44985</v>
       </c>
       <c r="B607" t="n">
-        <v>13.8533296585083</v>
+        <v>13.85332870483398</v>
       </c>
       <c r="C607" t="n">
-        <v>14.00768508302567</v>
+        <v>14.0076841187254</v>
       </c>
       <c r="D607" t="n">
-        <v>13.48673725032721</v>
+        <v>13.48673632188941</v>
       </c>
       <c r="E607" t="n">
-        <v>13.71826992709055</v>
+        <v>13.71826898271386</v>
       </c>
       <c r="F607" t="n">
         <v>1742300</v>
@@ -12572,16 +12572,16 @@
         <v>44986</v>
       </c>
       <c r="B608" t="n">
-        <v>13.48673725128174</v>
+        <v>13.48673629760742</v>
       </c>
       <c r="C608" t="n">
-        <v>13.85332965948877</v>
+        <v>13.85332867989197</v>
       </c>
       <c r="D608" t="n">
-        <v>13.21661686840171</v>
+        <v>13.21661593382815</v>
       </c>
       <c r="E608" t="n">
-        <v>13.85332965948877</v>
+        <v>13.85332867989197</v>
       </c>
       <c r="F608" t="n">
         <v>2358750</v>
@@ -12632,16 +12632,16 @@
         <v>44991</v>
       </c>
       <c r="B611" t="n">
-        <v>14.12344932556152</v>
+        <v>14.12345027923584</v>
       </c>
       <c r="C611" t="n">
-        <v>14.25850904133613</v>
+        <v>14.25851000413024</v>
       </c>
       <c r="D611" t="n">
-        <v>13.35167597246616</v>
+        <v>13.35167687402712</v>
       </c>
       <c r="E611" t="n">
-        <v>13.35167597246616</v>
+        <v>13.35167687402712</v>
       </c>
       <c r="F611" t="n">
         <v>2062900</v>
@@ -12672,16 +12672,16 @@
         <v>44993</v>
       </c>
       <c r="B613" t="n">
-        <v>15.85994148254395</v>
+        <v>15.85993957519531</v>
       </c>
       <c r="C613" t="n">
-        <v>15.85994148254395</v>
+        <v>15.85993957519531</v>
       </c>
       <c r="D613" t="n">
-        <v>14.16204003895802</v>
+        <v>14.16203833580244</v>
       </c>
       <c r="E613" t="n">
-        <v>14.68298696823717</v>
+        <v>14.68298520243147</v>
       </c>
       <c r="F613" t="n">
         <v>5225650</v>
@@ -12752,16 +12752,16 @@
         <v>44999</v>
       </c>
       <c r="B617" t="n">
-        <v>14.97240161895752</v>
+        <v>14.9724006652832</v>
       </c>
       <c r="C617" t="n">
-        <v>15.89852864361015</v>
+        <v>15.89852763094573</v>
       </c>
       <c r="D617" t="n">
-        <v>14.77945756879614</v>
+        <v>14.77945662741149</v>
       </c>
       <c r="E617" t="n">
-        <v>15.53193715636452</v>
+        <v>15.53193616705032</v>
       </c>
       <c r="F617" t="n">
         <v>2100150</v>
@@ -12772,16 +12772,16 @@
         <v>45000</v>
       </c>
       <c r="B618" t="n">
-        <v>15.31969833374023</v>
+        <v>15.31969928741455</v>
       </c>
       <c r="C618" t="n">
-        <v>15.47405374861028</v>
+        <v>15.47405471189345</v>
       </c>
       <c r="D618" t="n">
-        <v>14.45145292020087</v>
+        <v>14.4514538198256</v>
       </c>
       <c r="E618" t="n">
-        <v>14.64439695878208</v>
+        <v>14.64439787041787</v>
       </c>
       <c r="F618" t="n">
         <v>2068400</v>
@@ -12832,16 +12832,16 @@
         <v>45005</v>
       </c>
       <c r="B621" t="n">
-        <v>13.96909427642822</v>
+        <v>13.96909523010254</v>
       </c>
       <c r="C621" t="n">
-        <v>15.33899176022482</v>
+        <v>15.33899280742245</v>
       </c>
       <c r="D621" t="n">
-        <v>13.94980042512035</v>
+        <v>13.94980137747747</v>
       </c>
       <c r="E621" t="n">
-        <v>15.16534341835259</v>
+        <v>15.1653444536952</v>
       </c>
       <c r="F621" t="n">
         <v>2781400</v>
@@ -12972,16 +12972,16 @@
         <v>45014</v>
       </c>
       <c r="B628" t="n">
-        <v>14.14274501800537</v>
+        <v>14.14274406433105</v>
       </c>
       <c r="C628" t="n">
-        <v>14.41286540475423</v>
+        <v>14.41286443286514</v>
       </c>
       <c r="D628" t="n">
-        <v>13.75685875122129</v>
+        <v>13.75685782356807</v>
       </c>
       <c r="E628" t="n">
-        <v>14.41286540475423</v>
+        <v>14.41286443286514</v>
       </c>
       <c r="F628" t="n">
         <v>1398800</v>
@@ -13032,16 +13032,16 @@
         <v>45019</v>
       </c>
       <c r="B631" t="n">
-        <v>13.83403491973877</v>
+        <v>13.83403587341309</v>
       </c>
       <c r="C631" t="n">
-        <v>14.49004244185425</v>
+        <v>14.49004344075163</v>
       </c>
       <c r="D631" t="n">
-        <v>13.62179702963811</v>
+        <v>13.62179796868142</v>
       </c>
       <c r="E631" t="n">
-        <v>14.39357042271067</v>
+        <v>14.39357141495758</v>
       </c>
       <c r="F631" t="n">
         <v>1766300</v>
@@ -13072,16 +13072,16 @@
         <v>45021</v>
       </c>
       <c r="B633" t="n">
-        <v>13.8533296585083</v>
+        <v>13.85332870483398</v>
       </c>
       <c r="C633" t="n">
-        <v>14.29709931893536</v>
+        <v>14.29709833471159</v>
       </c>
       <c r="D633" t="n">
-        <v>13.66038652789336</v>
+        <v>13.66038558750141</v>
       </c>
       <c r="E633" t="n">
-        <v>14.1813334405664</v>
+        <v>14.18133246431204</v>
       </c>
       <c r="F633" t="n">
         <v>2634950</v>
@@ -13092,16 +13092,16 @@
         <v>45022</v>
       </c>
       <c r="B634" t="n">
-        <v>14.14274501800537</v>
+        <v>14.14274406433105</v>
       </c>
       <c r="C634" t="n">
-        <v>14.297099524719</v>
+        <v>14.29709856063625</v>
       </c>
       <c r="D634" t="n">
-        <v>13.77615260454778</v>
+        <v>13.77615167559354</v>
       </c>
       <c r="E634" t="n">
-        <v>13.85332985790459</v>
+        <v>13.85332892374614</v>
       </c>
       <c r="F634" t="n">
         <v>1739850</v>
@@ -13112,16 +13112,16 @@
         <v>45026</v>
       </c>
       <c r="B635" t="n">
-        <v>13.96909427642822</v>
+        <v>13.96909523010254</v>
       </c>
       <c r="C635" t="n">
-        <v>14.20062693230008</v>
+        <v>14.2006279017812</v>
       </c>
       <c r="D635" t="n">
-        <v>13.89191703114605</v>
+        <v>13.89191797955145</v>
       </c>
       <c r="E635" t="n">
-        <v>13.94980042512035</v>
+        <v>13.94980137747747</v>
       </c>
       <c r="F635" t="n">
         <v>1451200</v>
@@ -13152,16 +13152,16 @@
         <v>45028</v>
       </c>
       <c r="B637" t="n">
-        <v>15.454758644104</v>
+        <v>15.45475959777832</v>
       </c>
       <c r="C637" t="n">
-        <v>15.78276239860189</v>
+        <v>15.7827633725165</v>
       </c>
       <c r="D637" t="n">
-        <v>15.14604874103375</v>
+        <v>15.14604967565836</v>
       </c>
       <c r="E637" t="n">
-        <v>15.31969800400918</v>
+        <v>15.31969894934925</v>
       </c>
       <c r="F637" t="n">
         <v>3667400</v>
@@ -13192,16 +13192,16 @@
         <v>45030</v>
       </c>
       <c r="B639" t="n">
-        <v>15.60911273956299</v>
+        <v>15.6091136932373</v>
       </c>
       <c r="C639" t="n">
-        <v>15.91782171477476</v>
+        <v>15.91782268731036</v>
       </c>
       <c r="D639" t="n">
-        <v>15.12675450578194</v>
+        <v>15.12675542998548</v>
       </c>
       <c r="E639" t="n">
-        <v>15.68628998336593</v>
+        <v>15.68629094175557</v>
       </c>
       <c r="F639" t="n">
         <v>1580050</v>
@@ -13212,16 +13212,16 @@
         <v>45033</v>
       </c>
       <c r="B640" t="n">
-        <v>15.53193664550781</v>
+        <v>15.5319356918335</v>
       </c>
       <c r="C640" t="n">
-        <v>15.76346839405572</v>
+        <v>15.76346742616516</v>
       </c>
       <c r="D640" t="n">
-        <v>15.49334710072444</v>
+        <v>15.49334614941956</v>
       </c>
       <c r="E640" t="n">
-        <v>15.60911389502378</v>
+        <v>15.60911293661072</v>
       </c>
       <c r="F640" t="n">
         <v>1212550</v>
@@ -13232,16 +13232,16 @@
         <v>45034</v>
       </c>
       <c r="B641" t="n">
-        <v>15.06887149810791</v>
+        <v>15.06887245178223</v>
       </c>
       <c r="C641" t="n">
-        <v>15.74417285865839</v>
+        <v>15.74417385507098</v>
       </c>
       <c r="D641" t="n">
-        <v>14.87592838366854</v>
+        <v>14.87592932513193</v>
       </c>
       <c r="E641" t="n">
-        <v>15.62840791002011</v>
+        <v>15.6284088991062</v>
       </c>
       <c r="F641" t="n">
         <v>1695600</v>
@@ -13272,16 +13272,16 @@
         <v>45036</v>
       </c>
       <c r="B643" t="n">
-        <v>14.93381118774414</v>
+        <v>14.93381214141846</v>
       </c>
       <c r="C643" t="n">
-        <v>14.93381118774414</v>
+        <v>14.93381214141846</v>
       </c>
       <c r="D643" t="n">
-        <v>14.29709843602215</v>
+        <v>14.29709934903595</v>
       </c>
       <c r="E643" t="n">
-        <v>14.43215907912469</v>
+        <v>14.43216000076346</v>
       </c>
       <c r="F643" t="n">
         <v>1458900</v>
@@ -29632,19 +29632,39 @@
         <v>46234</v>
       </c>
       <c r="B1461" t="n">
-        <v>7.71</v>
+        <v>7.710000038146973</v>
       </c>
       <c r="C1461" t="n">
-        <v>7.76</v>
+        <v>7.760000228881836</v>
       </c>
       <c r="D1461" t="n">
-        <v>7.58</v>
+        <v>7.579999923706055</v>
       </c>
       <c r="E1461" t="n">
-        <v>7.73</v>
+        <v>7.730000019073486</v>
       </c>
       <c r="F1461" t="n">
         <v>1129300</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>2238200</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -452,16 +452,16 @@
         <v>44092</v>
       </c>
       <c r="B2" t="n">
-        <v>13.02992725372314</v>
+        <v>13.02992820739746</v>
       </c>
       <c r="C2" t="n">
-        <v>13.73903911926684</v>
+        <v>13.73904012484181</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63548414306174</v>
+        <v>12.63548506786634</v>
       </c>
       <c r="E2" t="n">
-        <v>13.3844836091585</v>
+        <v>13.38448458878317</v>
       </c>
       <c r="F2" t="n">
         <v>539400</v>
@@ -472,16 +472,16 @@
         <v>44095</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59559631347656</v>
+        <v>12.59559726715088</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80832961567333</v>
+        <v>12.80833058545472</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45377411201205</v>
+        <v>12.45377505494831</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46706941506998</v>
+        <v>12.46707035901289</v>
       </c>
       <c r="F3" t="n">
         <v>1323800</v>
@@ -532,16 +532,16 @@
         <v>44098</v>
       </c>
       <c r="B6" t="n">
-        <v>12.45377254486084</v>
+        <v>12.45377445220947</v>
       </c>
       <c r="C6" t="n">
-        <v>12.84378354981024</v>
+        <v>12.84378551689074</v>
       </c>
       <c r="D6" t="n">
-        <v>12.4094529011485</v>
+        <v>12.40945480170939</v>
       </c>
       <c r="E6" t="n">
-        <v>12.65320967357602</v>
+        <v>12.6532116114693</v>
       </c>
       <c r="F6" t="n">
         <v>571400</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513614654541</v>
+        <v>12.36513519287109</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366305880876</v>
+        <v>12.49366209522167</v>
       </c>
       <c r="D7" t="n">
-        <v>12.3208164924778</v>
+        <v>12.32081554222169</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377545468063</v>
+        <v>12.45377449416991</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -572,16 +572,16 @@
         <v>44102</v>
       </c>
       <c r="B8" t="n">
-        <v>11.58067893981934</v>
+        <v>11.58067989349365</v>
       </c>
       <c r="C8" t="n">
-        <v>12.51138812360737</v>
+        <v>12.51138915392602</v>
       </c>
       <c r="D8" t="n">
-        <v>11.58067893981934</v>
+        <v>11.58067989349365</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43161292995026</v>
+        <v>12.43161395369939</v>
       </c>
       <c r="F8" t="n">
         <v>1524000</v>
@@ -612,16 +612,16 @@
         <v>44104</v>
       </c>
       <c r="B10" t="n">
-        <v>11.26158046722412</v>
+        <v>11.26158142089844</v>
       </c>
       <c r="C10" t="n">
-        <v>11.49647402945097</v>
+        <v>11.49647500301699</v>
       </c>
       <c r="D10" t="n">
-        <v>11.19510141235299</v>
+        <v>11.1951023603976</v>
       </c>
       <c r="E10" t="n">
-        <v>11.28373987040548</v>
+        <v>11.28374082595634</v>
       </c>
       <c r="F10" t="n">
         <v>764200</v>
@@ -632,16 +632,16 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>11.68261432647705</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="C11" t="n">
-        <v>11.68261432647705</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="D11" t="n">
-        <v>10.92918288458478</v>
+        <v>10.92918466892529</v>
       </c>
       <c r="E11" t="n">
-        <v>11.22612341223327</v>
+        <v>11.22612524505344</v>
       </c>
       <c r="F11" t="n">
         <v>1726600</v>
@@ -712,16 +712,16 @@
         <v>44111</v>
       </c>
       <c r="B15" t="n">
-        <v>11.68261432647705</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82443651663867</v>
+        <v>11.82443844714174</v>
       </c>
       <c r="D15" t="n">
-        <v>11.35465030039657</v>
+        <v>11.35465215420053</v>
       </c>
       <c r="E15" t="n">
-        <v>11.62943058250298</v>
+        <v>11.62943248116863</v>
       </c>
       <c r="F15" t="n">
         <v>437200</v>
@@ -732,16 +732,16 @@
         <v>44112</v>
       </c>
       <c r="B16" t="n">
-        <v>11.52306461334229</v>
+        <v>11.5230655670166</v>
       </c>
       <c r="C16" t="n">
-        <v>11.90421240567286</v>
+        <v>11.90421339089181</v>
       </c>
       <c r="D16" t="n">
-        <v>11.39010651362682</v>
+        <v>11.39010745629723</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68261500926243</v>
+        <v>11.68261597614149</v>
       </c>
       <c r="F16" t="n">
         <v>595200</v>
@@ -752,16 +752,16 @@
         <v>44113</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10365200042725</v>
+        <v>12.10365009307861</v>
       </c>
       <c r="C17" t="n">
-        <v>12.2942259350923</v>
+        <v>12.29422399771216</v>
       </c>
       <c r="D17" t="n">
-        <v>11.53193104175924</v>
+        <v>11.531929224505</v>
       </c>
       <c r="E17" t="n">
-        <v>11.53636309202205</v>
+        <v>11.53636127406939</v>
       </c>
       <c r="F17" t="n">
         <v>672400</v>
@@ -792,16 +792,16 @@
         <v>44118</v>
       </c>
       <c r="B19" t="n">
-        <v>12.13024139404297</v>
+        <v>12.13024234771729</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63105111910211</v>
+        <v>12.63105211214986</v>
       </c>
       <c r="D19" t="n">
-        <v>12.00614655241479</v>
+        <v>12.00614749633282</v>
       </c>
       <c r="E19" t="n">
-        <v>12.18785634299326</v>
+        <v>12.18785730119724</v>
       </c>
       <c r="F19" t="n">
         <v>441800</v>
@@ -812,16 +812,16 @@
         <v>44119</v>
       </c>
       <c r="B20" t="n">
-        <v>11.9795560836792</v>
+        <v>11.97955703735352</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39615859870633</v>
+        <v>12.39615958554575</v>
       </c>
       <c r="D20" t="n">
-        <v>11.78011807996524</v>
+        <v>11.7801190177626</v>
       </c>
       <c r="E20" t="n">
-        <v>12.0283069382216</v>
+        <v>12.02830789577689</v>
       </c>
       <c r="F20" t="n">
         <v>483400</v>
@@ -832,16 +832,16 @@
         <v>44120</v>
       </c>
       <c r="B21" t="n">
-        <v>12.45377254486084</v>
+        <v>12.45377445220947</v>
       </c>
       <c r="C21" t="n">
-        <v>12.49366013966925</v>
+        <v>12.49366205312684</v>
       </c>
       <c r="D21" t="n">
-        <v>11.97955430139068</v>
+        <v>11.97955613611076</v>
       </c>
       <c r="E21" t="n">
-        <v>12.06376069458454</v>
+        <v>12.06376254220119</v>
       </c>
       <c r="F21" t="n">
         <v>585200</v>
@@ -912,16 +912,16 @@
         <v>44126</v>
       </c>
       <c r="B25" t="n">
-        <v>13.06981468200684</v>
+        <v>13.06981372833252</v>
       </c>
       <c r="C25" t="n">
-        <v>13.21163688418085</v>
+        <v>13.2116359201581</v>
       </c>
       <c r="D25" t="n">
-        <v>12.69753097863653</v>
+        <v>12.6975300521269</v>
       </c>
       <c r="E25" t="n">
-        <v>12.75071472711529</v>
+        <v>12.75071379672497</v>
       </c>
       <c r="F25" t="n">
         <v>963600</v>
@@ -1012,16 +1012,16 @@
         <v>44133</v>
       </c>
       <c r="B30" t="n">
-        <v>11.7047758102417</v>
+        <v>11.70477485656738</v>
       </c>
       <c r="C30" t="n">
-        <v>11.87762152960331</v>
+        <v>11.87762056184598</v>
       </c>
       <c r="D30" t="n">
-        <v>11.0089600375708</v>
+        <v>11.00895914058972</v>
       </c>
       <c r="E30" t="n">
-        <v>11.39453908004318</v>
+        <v>11.39453815164614</v>
       </c>
       <c r="F30" t="n">
         <v>683400</v>
@@ -1032,16 +1032,16 @@
         <v>44134</v>
       </c>
       <c r="B31" t="n">
-        <v>11.38567543029785</v>
+        <v>11.38567733764648</v>
       </c>
       <c r="C31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.81114404037198</v>
       </c>
       <c r="D31" t="n">
-        <v>11.00895965537159</v>
+        <v>11.00896149961212</v>
       </c>
       <c r="E31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.81114404037198</v>
       </c>
       <c r="F31" t="n">
         <v>907200</v>
@@ -1052,16 +1052,16 @@
         <v>44138</v>
       </c>
       <c r="B32" t="n">
-        <v>11.85546112060547</v>
+        <v>11.85546207427979</v>
       </c>
       <c r="C32" t="n">
-        <v>11.9662598226672</v>
+        <v>11.96626078525436</v>
       </c>
       <c r="D32" t="n">
-        <v>11.51863296489856</v>
+        <v>11.51863389147782</v>
       </c>
       <c r="E32" t="n">
-        <v>11.70034276865364</v>
+        <v>11.70034370984996</v>
       </c>
       <c r="F32" t="n">
         <v>1038200</v>
@@ -1092,16 +1092,16 @@
         <v>44140</v>
       </c>
       <c r="B34" t="n">
-        <v>12.79503440856934</v>
+        <v>12.79503536224365</v>
       </c>
       <c r="C34" t="n">
-        <v>13.02992711450884</v>
+        <v>13.02992808569082</v>
       </c>
       <c r="D34" t="n">
-        <v>12.63991605755662</v>
+        <v>12.63991699966924</v>
       </c>
       <c r="E34" t="n">
-        <v>12.78617030957958</v>
+        <v>12.78617126259321</v>
       </c>
       <c r="F34" t="n">
         <v>682600</v>
@@ -1112,16 +1112,16 @@
         <v>44141</v>
       </c>
       <c r="B35" t="n">
-        <v>13.55733013153076</v>
+        <v>13.55733108520508</v>
       </c>
       <c r="C35" t="n">
-        <v>13.69472029430994</v>
+        <v>13.6947212576488</v>
       </c>
       <c r="D35" t="n">
-        <v>12.65764430809807</v>
+        <v>12.65764519848505</v>
       </c>
       <c r="E35" t="n">
-        <v>12.74185156382011</v>
+        <v>12.74185246013055</v>
       </c>
       <c r="F35" t="n">
         <v>948200</v>
@@ -1132,16 +1132,16 @@
         <v>44144</v>
       </c>
       <c r="B36" t="n">
-        <v>13.29584407806396</v>
+        <v>13.29584503173828</v>
       </c>
       <c r="C36" t="n">
-        <v>13.96950038089769</v>
+        <v>13.96950138289152</v>
       </c>
       <c r="D36" t="n">
-        <v>13.12299837555377</v>
+        <v>13.12299931683034</v>
       </c>
       <c r="E36" t="n">
-        <v>13.7390388806661</v>
+        <v>13.73903986612956</v>
       </c>
       <c r="F36" t="n">
         <v>650800</v>
@@ -1172,16 +1172,16 @@
         <v>44146</v>
       </c>
       <c r="B38" t="n">
-        <v>13.29584407806396</v>
+        <v>13.29584503173828</v>
       </c>
       <c r="C38" t="n">
-        <v>13.41993892711028</v>
+        <v>13.41993988968558</v>
       </c>
       <c r="D38" t="n">
-        <v>12.89696892478745</v>
+        <v>12.89696984985155</v>
       </c>
       <c r="E38" t="n">
-        <v>13.25152442873835</v>
+        <v>13.25152537923374</v>
       </c>
       <c r="F38" t="n">
         <v>586400</v>
@@ -1212,16 +1212,16 @@
         <v>44148</v>
       </c>
       <c r="B40" t="n">
-        <v>13.10970115661621</v>
+        <v>13.10970306396484</v>
       </c>
       <c r="C40" t="n">
-        <v>13.53073652283718</v>
+        <v>13.53073849144283</v>
       </c>
       <c r="D40" t="n">
-        <v>12.84378412770439</v>
+        <v>12.84378599636438</v>
       </c>
       <c r="E40" t="n">
-        <v>13.29584299232179</v>
+        <v>13.29584492675246</v>
       </c>
       <c r="F40" t="n">
         <v>720400</v>
@@ -1232,16 +1232,16 @@
         <v>44151</v>
       </c>
       <c r="B41" t="n">
-        <v>13.02106380462646</v>
+        <v>13.02106285095215</v>
       </c>
       <c r="C41" t="n">
-        <v>13.37118812799716</v>
+        <v>13.37118714867942</v>
       </c>
       <c r="D41" t="n">
-        <v>12.65321212752895</v>
+        <v>12.65321120079642</v>
       </c>
       <c r="E41" t="n">
-        <v>13.20720566805696</v>
+        <v>13.20720470074945</v>
       </c>
       <c r="F41" t="n">
         <v>631800</v>
@@ -1252,16 +1252,16 @@
         <v>44152</v>
       </c>
       <c r="B42" t="n">
-        <v>13.02106380462646</v>
+        <v>13.02106285095215</v>
       </c>
       <c r="C42" t="n">
-        <v>13.09197575551494</v>
+        <v>13.09197479664697</v>
       </c>
       <c r="D42" t="n">
-        <v>12.6975317798366</v>
+        <v>12.69753084985806</v>
       </c>
       <c r="E42" t="n">
-        <v>12.93242534533822</v>
+        <v>12.93242439815586</v>
       </c>
       <c r="F42" t="n">
         <v>784800</v>
@@ -1292,16 +1292,16 @@
         <v>44154</v>
       </c>
       <c r="B44" t="n">
-        <v>12.99447250366211</v>
+        <v>12.99447154998779</v>
       </c>
       <c r="C44" t="n">
-        <v>13.0742477096854</v>
+        <v>13.07424675015632</v>
       </c>
       <c r="D44" t="n">
-        <v>12.48036655965319</v>
+        <v>12.4803656437095</v>
       </c>
       <c r="E44" t="n">
-        <v>12.74185158147306</v>
+        <v>12.74185064633879</v>
       </c>
       <c r="F44" t="n">
         <v>711400</v>
@@ -1312,16 +1312,16 @@
         <v>44158</v>
       </c>
       <c r="B45" t="n">
-        <v>13.35345840454102</v>
+        <v>13.35346031188965</v>
       </c>
       <c r="C45" t="n">
-        <v>13.47312119851311</v>
+        <v>13.47312312295385</v>
       </c>
       <c r="D45" t="n">
-        <v>13.06981401467557</v>
+        <v>13.0698158815097</v>
       </c>
       <c r="E45" t="n">
-        <v>13.13629306288441</v>
+        <v>13.13629493921411</v>
       </c>
       <c r="F45" t="n">
         <v>731400</v>
@@ -1332,16 +1332,16 @@
         <v>44159</v>
       </c>
       <c r="B46" t="n">
-        <v>13.73903846740723</v>
+        <v>13.73904037475586</v>
       </c>
       <c r="C46" t="n">
-        <v>13.82767776339226</v>
+        <v>13.82767968304641</v>
       </c>
       <c r="D46" t="n">
-        <v>13.27368427680326</v>
+        <v>13.27368611954819</v>
       </c>
       <c r="E46" t="n">
-        <v>13.47312142477911</v>
+        <v>13.4731232952113</v>
       </c>
       <c r="F46" t="n">
         <v>798800</v>
@@ -1392,16 +1392,16 @@
         <v>44162</v>
       </c>
       <c r="B49" t="n">
-        <v>13.39334774017334</v>
+        <v>13.39334678649902</v>
       </c>
       <c r="C49" t="n">
-        <v>13.71688061533133</v>
+        <v>13.71687963861983</v>
       </c>
       <c r="D49" t="n">
-        <v>13.38891569034081</v>
+        <v>13.38891473698208</v>
       </c>
       <c r="E49" t="n">
-        <v>13.5307387490005</v>
+        <v>13.53073778554325</v>
       </c>
       <c r="F49" t="n">
         <v>510000</v>
@@ -1412,16 +1412,16 @@
         <v>44165</v>
       </c>
       <c r="B50" t="n">
-        <v>13.13629531860352</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="C50" t="n">
-        <v>13.73017649585873</v>
+        <v>13.73017450228043</v>
       </c>
       <c r="D50" t="n">
-        <v>13.13629531860352</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="E50" t="n">
-        <v>13.38891625237249</v>
+        <v>13.38891430834409</v>
       </c>
       <c r="F50" t="n">
         <v>1093200</v>
@@ -1432,16 +1432,16 @@
         <v>44166</v>
       </c>
       <c r="B51" t="n">
-        <v>14.18223476409912</v>
+        <v>14.1822338104248</v>
       </c>
       <c r="C51" t="n">
-        <v>14.40383218228817</v>
+        <v>14.40383121371269</v>
       </c>
       <c r="D51" t="n">
-        <v>13.47755490663178</v>
+        <v>13.47755400034316</v>
       </c>
       <c r="E51" t="n">
-        <v>13.73460787791799</v>
+        <v>13.73460695434403</v>
       </c>
       <c r="F51" t="n">
         <v>2351000</v>
@@ -1452,16 +1452,16 @@
         <v>44167</v>
       </c>
       <c r="B52" t="n">
-        <v>14.18223476409912</v>
+        <v>14.1822338104248</v>
       </c>
       <c r="C52" t="n">
-        <v>14.37280867899403</v>
+        <v>14.37280771250471</v>
       </c>
       <c r="D52" t="n">
-        <v>13.93404589241896</v>
+        <v>13.93404495543393</v>
       </c>
       <c r="E52" t="n">
-        <v>14.18223476409912</v>
+        <v>14.1822338104248</v>
       </c>
       <c r="F52" t="n">
         <v>767800</v>
@@ -1512,16 +1512,16 @@
         <v>44172</v>
       </c>
       <c r="B55" t="n">
-        <v>14.25314426422119</v>
+        <v>14.25314617156982</v>
       </c>
       <c r="C55" t="n">
-        <v>14.36837416480735</v>
+        <v>14.36837608757599</v>
       </c>
       <c r="D55" t="n">
-        <v>13.82767767499762</v>
+        <v>13.82767952541053</v>
       </c>
       <c r="E55" t="n">
-        <v>14.06257037080052</v>
+        <v>14.06257225264665</v>
       </c>
       <c r="F55" t="n">
         <v>782600</v>
@@ -1532,16 +1532,16 @@
         <v>44173</v>
       </c>
       <c r="B56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="C56" t="n">
-        <v>14.53679034258752</v>
+        <v>14.53678935892345</v>
       </c>
       <c r="D56" t="n">
-        <v>13.89859038475245</v>
+        <v>13.89858944427358</v>
       </c>
       <c r="E56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="F56" t="n">
         <v>767200</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.004958152771</v>
+        <v>14.00495719909668</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10246072049168</v>
+        <v>14.10245976017788</v>
       </c>
       <c r="D58" t="n">
-        <v>13.51744362351329</v>
+        <v>13.5174427030365</v>
       </c>
       <c r="E58" t="n">
-        <v>13.88529533420892</v>
+        <v>13.8852943886831</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1592,16 +1592,16 @@
         <v>44176</v>
       </c>
       <c r="B59" t="n">
-        <v>13.82324695587158</v>
+        <v>13.8232479095459</v>
       </c>
       <c r="C59" t="n">
-        <v>13.96063711619654</v>
+        <v>13.96063807934949</v>
       </c>
       <c r="D59" t="n">
-        <v>13.40221153010944</v>
+        <v>13.40221245473626</v>
       </c>
       <c r="E59" t="n">
-        <v>13.92074951395268</v>
+        <v>13.92075047435375</v>
       </c>
       <c r="F59" t="n">
         <v>523600</v>
@@ -1632,16 +1632,16 @@
         <v>44180</v>
       </c>
       <c r="B61" t="n">
-        <v>14.08473205566406</v>
+        <v>14.08473300933838</v>
       </c>
       <c r="C61" t="n">
-        <v>14.124619658143</v>
+        <v>14.1246206145181</v>
       </c>
       <c r="D61" t="n">
-        <v>13.57062611852114</v>
+        <v>13.57062703738544</v>
       </c>
       <c r="E61" t="n">
-        <v>13.75676798164717</v>
+        <v>13.7567689131151</v>
       </c>
       <c r="F61" t="n">
         <v>732800</v>
@@ -1672,16 +1672,16 @@
         <v>44182</v>
       </c>
       <c r="B63" t="n">
-        <v>13.73903846740723</v>
+        <v>13.73904037475586</v>
       </c>
       <c r="C63" t="n">
-        <v>14.13348155935396</v>
+        <v>14.13348352146192</v>
       </c>
       <c r="D63" t="n">
-        <v>13.67255941808194</v>
+        <v>13.67256131620149</v>
       </c>
       <c r="E63" t="n">
-        <v>13.91631621405031</v>
+        <v>13.91631814600987</v>
       </c>
       <c r="F63" t="n">
         <v>633000</v>
@@ -1692,16 +1692,16 @@
         <v>44183</v>
       </c>
       <c r="B64" t="n">
-        <v>13.40664386749268</v>
+        <v>13.40664196014404</v>
       </c>
       <c r="C64" t="n">
-        <v>13.83654255661189</v>
+        <v>13.83654058810204</v>
       </c>
       <c r="D64" t="n">
-        <v>13.28698105819358</v>
+        <v>13.28697916786925</v>
       </c>
       <c r="E64" t="n">
-        <v>13.61937718713968</v>
+        <v>13.61937524952571</v>
       </c>
       <c r="F64" t="n">
         <v>920000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294364929199</v>
+        <v>15.11294174194336</v>
       </c>
       <c r="C68" t="n">
-        <v>15.13067184897926</v>
+        <v>15.13066993939322</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586848207222</v>
+        <v>14.075866705609</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348344040167</v>
+        <v>14.13348165666709</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.19715118408203</v>
+        <v>15.19715023040771</v>
       </c>
       <c r="C69" t="n">
-        <v>15.34783749447957</v>
+        <v>15.34783653134916</v>
       </c>
       <c r="D69" t="n">
-        <v>14.7495234573184</v>
+        <v>14.74952253173429</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510417815142</v>
+        <v>15.13510322837077</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1812,16 +1812,16 @@
         <v>44195</v>
       </c>
       <c r="B70" t="n">
-        <v>15.72011947631836</v>
+        <v>15.72012042999268</v>
       </c>
       <c r="C70" t="n">
-        <v>15.91512457198337</v>
+        <v>15.91512553748784</v>
       </c>
       <c r="D70" t="n">
-        <v>15.25033239823193</v>
+        <v>15.25033332340621</v>
       </c>
       <c r="E70" t="n">
-        <v>15.37885929091415</v>
+        <v>15.37886022388563</v>
       </c>
       <c r="F70" t="n">
         <v>2946000</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98885059356689</v>
+        <v>14.98884963989258</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94172025465893</v>
+        <v>15.94171924035773</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952495441062</v>
+        <v>14.74952401596354</v>
       </c>
       <c r="E71" t="n">
-        <v>15.9106967485447</v>
+        <v>15.91069573621739</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.58997344970703</v>
+        <v>14.58997249603271</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135801482809</v>
+        <v>15.28135701596139</v>
       </c>
       <c r="D73" t="n">
-        <v>14.58997344970703</v>
+        <v>14.58997249603271</v>
       </c>
       <c r="E73" t="n">
-        <v>15.1395358000321</v>
+        <v>15.13953481043562</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1912,16 +1912,16 @@
         <v>44204</v>
       </c>
       <c r="B75" t="n">
-        <v>15.06334686279297</v>
+        <v>15.06334590911865</v>
       </c>
       <c r="C75" t="n">
-        <v>15.27237525478156</v>
+        <v>15.27237428787347</v>
       </c>
       <c r="D75" t="n">
-        <v>14.38734170043839</v>
+        <v>14.38734078956258</v>
       </c>
       <c r="E75" t="n">
-        <v>14.38734170043839</v>
+        <v>14.38734078956258</v>
       </c>
       <c r="F75" t="n">
         <v>1077600</v>
@@ -1952,16 +1952,16 @@
         <v>44208</v>
       </c>
       <c r="B77" t="n">
-        <v>15.99285221099854</v>
+        <v>15.99285316467285</v>
       </c>
       <c r="C77" t="n">
-        <v>16.31306559830687</v>
+        <v>16.31306657107592</v>
       </c>
       <c r="D77" t="n">
-        <v>15.34353212811103</v>
+        <v>15.34353304306556</v>
       </c>
       <c r="E77" t="n">
-        <v>15.90390385935192</v>
+        <v>15.90390480772213</v>
       </c>
       <c r="F77" t="n">
         <v>2193200</v>
@@ -1972,16 +1972,16 @@
         <v>44209</v>
       </c>
       <c r="B78" t="n">
-        <v>15.72155952453613</v>
+        <v>15.72156238555908</v>
       </c>
       <c r="C78" t="n">
-        <v>16.71777794725707</v>
+        <v>16.71778098957271</v>
       </c>
       <c r="D78" t="n">
-        <v>15.41468951180912</v>
+        <v>15.4146923169876</v>
       </c>
       <c r="E78" t="n">
-        <v>15.96616790049454</v>
+        <v>15.96617080603153</v>
       </c>
       <c r="F78" t="n">
         <v>1238200</v>
@@ -1992,16 +1992,16 @@
         <v>44210</v>
       </c>
       <c r="B79" t="n">
-        <v>16.08624649047852</v>
+        <v>16.08625030517578</v>
       </c>
       <c r="C79" t="n">
-        <v>16.2552481813217</v>
+        <v>16.25525203609608</v>
       </c>
       <c r="D79" t="n">
-        <v>15.65929645771021</v>
+        <v>15.65930017116042</v>
       </c>
       <c r="E79" t="n">
-        <v>15.94837816337235</v>
+        <v>15.94838194537548</v>
       </c>
       <c r="F79" t="n">
         <v>1217000</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422584533691</v>
+        <v>16.38422393798828</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538419561817</v>
+        <v>16.45538227998573</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169572023429</v>
+        <v>15.92169386673051</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93503907728939</v>
+        <v>15.93503722223226</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2052,16 +2052,16 @@
         <v>44215</v>
       </c>
       <c r="B82" t="n">
-        <v>16.63327789306641</v>
+        <v>16.63327980041504</v>
       </c>
       <c r="C82" t="n">
-        <v>17.07801792553825</v>
+        <v>17.07801988388551</v>
       </c>
       <c r="D82" t="n">
-        <v>16.09514116439855</v>
+        <v>16.0951430100387</v>
       </c>
       <c r="E82" t="n">
-        <v>17.07801792553825</v>
+        <v>17.07801988388551</v>
       </c>
       <c r="F82" t="n">
         <v>1918400</v>
@@ -2072,16 +2072,16 @@
         <v>44216</v>
       </c>
       <c r="B83" t="n">
-        <v>16.2552490234375</v>
+        <v>16.25525093078613</v>
       </c>
       <c r="C83" t="n">
-        <v>16.81117410424281</v>
+        <v>16.81117607682225</v>
       </c>
       <c r="D83" t="n">
-        <v>16.0106423271929</v>
+        <v>16.01064420584002</v>
       </c>
       <c r="E83" t="n">
-        <v>16.69998908808175</v>
+        <v>16.69999104761502</v>
       </c>
       <c r="F83" t="n">
         <v>1073000</v>
@@ -2092,16 +2092,16 @@
         <v>44217</v>
       </c>
       <c r="B84" t="n">
-        <v>15.85498428344727</v>
+        <v>15.85498332977295</v>
       </c>
       <c r="C84" t="n">
-        <v>16.36643434954472</v>
+        <v>16.36643336510678</v>
       </c>
       <c r="D84" t="n">
-        <v>15.53032253714568</v>
+        <v>15.53032160299971</v>
       </c>
       <c r="E84" t="n">
-        <v>16.25969768207601</v>
+        <v>16.25969670405826</v>
       </c>
       <c r="F84" t="n">
         <v>928200</v>
@@ -2112,16 +2112,16 @@
         <v>44218</v>
       </c>
       <c r="B85" t="n">
-        <v>15.4013500213623</v>
+        <v>15.40134811401367</v>
       </c>
       <c r="C85" t="n">
-        <v>15.84164176695957</v>
+        <v>15.8416398050839</v>
       </c>
       <c r="D85" t="n">
-        <v>15.17453162201319</v>
+        <v>15.17452974275442</v>
       </c>
       <c r="E85" t="n">
-        <v>15.60593005864081</v>
+        <v>15.60592812595638</v>
       </c>
       <c r="F85" t="n">
         <v>1029200</v>
@@ -2152,16 +2152,16 @@
         <v>44223</v>
       </c>
       <c r="B87" t="n">
-        <v>15.00553035736084</v>
+        <v>15.00552940368652</v>
       </c>
       <c r="C87" t="n">
-        <v>15.57034874008907</v>
+        <v>15.5703477505178</v>
       </c>
       <c r="D87" t="n">
-        <v>14.53410528342808</v>
+        <v>14.53410435971512</v>
       </c>
       <c r="E87" t="n">
-        <v>14.74313365433532</v>
+        <v>14.74313271733759</v>
       </c>
       <c r="F87" t="n">
         <v>1909000</v>
@@ -2172,16 +2172,16 @@
         <v>44224</v>
       </c>
       <c r="B88" t="n">
-        <v>15.65930080413818</v>
+        <v>15.65929794311523</v>
       </c>
       <c r="C88" t="n">
-        <v>15.98840927275467</v>
+        <v>15.98840635160216</v>
       </c>
       <c r="D88" t="n">
-        <v>14.95216387385126</v>
+        <v>14.95216114202533</v>
       </c>
       <c r="E88" t="n">
-        <v>15.13450727365862</v>
+        <v>15.13450450851776</v>
       </c>
       <c r="F88" t="n">
         <v>3941600</v>
@@ -2212,16 +2212,16 @@
         <v>44228</v>
       </c>
       <c r="B90" t="n">
-        <v>16.76670074462891</v>
+        <v>16.76670265197754</v>
       </c>
       <c r="C90" t="n">
-        <v>17.02909745013378</v>
+        <v>17.02909938733217</v>
       </c>
       <c r="D90" t="n">
-        <v>15.65929723928157</v>
+        <v>15.65929902065404</v>
       </c>
       <c r="E90" t="n">
-        <v>16.0106422968565</v>
+        <v>16.01064411819733</v>
       </c>
       <c r="F90" t="n">
         <v>3072200</v>
@@ -2232,16 +2232,16 @@
         <v>44229</v>
       </c>
       <c r="B91" t="n">
-        <v>17.08246612548828</v>
+        <v>17.08246803283691</v>
       </c>
       <c r="C91" t="n">
-        <v>17.32262617193124</v>
+        <v>17.32262810609502</v>
       </c>
       <c r="D91" t="n">
-        <v>16.76670108102554</v>
+        <v>16.76670295311732</v>
       </c>
       <c r="E91" t="n">
-        <v>16.76670108102554</v>
+        <v>16.76670295311732</v>
       </c>
       <c r="F91" t="n">
         <v>2620800</v>
@@ -2252,16 +2252,16 @@
         <v>44230</v>
       </c>
       <c r="B92" t="n">
-        <v>17.61170768737793</v>
+        <v>17.6117057800293</v>
       </c>
       <c r="C92" t="n">
-        <v>17.78960441009847</v>
+        <v>17.78960248348361</v>
       </c>
       <c r="D92" t="n">
-        <v>16.94015086737822</v>
+        <v>16.94014903275922</v>
       </c>
       <c r="E92" t="n">
-        <v>17.0824675669351</v>
+        <v>17.08246571690319</v>
       </c>
       <c r="F92" t="n">
         <v>1128200</v>
@@ -2292,16 +2292,16 @@
         <v>44232</v>
       </c>
       <c r="B94" t="n">
-        <v>18.80805969238281</v>
+        <v>18.80805778503418</v>
       </c>
       <c r="C94" t="n">
-        <v>19.56856487465802</v>
+        <v>19.56856289018561</v>
       </c>
       <c r="D94" t="n">
-        <v>17.78960443150729</v>
+        <v>17.78960262744146</v>
       </c>
       <c r="E94" t="n">
-        <v>17.99863282647314</v>
+        <v>17.99863100120949</v>
       </c>
       <c r="F94" t="n">
         <v>14342200</v>
@@ -2312,16 +2312,16 @@
         <v>44235</v>
       </c>
       <c r="B95" t="n">
-        <v>19.23056221008301</v>
+        <v>19.23056030273438</v>
       </c>
       <c r="C95" t="n">
-        <v>19.36843055199105</v>
+        <v>19.36842863096819</v>
       </c>
       <c r="D95" t="n">
-        <v>18.46560871350112</v>
+        <v>18.46560688202301</v>
       </c>
       <c r="E95" t="n">
-        <v>18.81250544030044</v>
+        <v>18.81250357441601</v>
       </c>
       <c r="F95" t="n">
         <v>1758400</v>
@@ -2332,16 +2332,16 @@
         <v>44236</v>
       </c>
       <c r="B96" t="n">
-        <v>18.84808349609375</v>
+        <v>18.84808540344238</v>
       </c>
       <c r="C96" t="n">
-        <v>19.45293022598046</v>
+        <v>19.4529321945371</v>
       </c>
       <c r="D96" t="n">
-        <v>18.82584683325499</v>
+        <v>18.82584873835336</v>
       </c>
       <c r="E96" t="n">
-        <v>19.45293022598046</v>
+        <v>19.4529321945371</v>
       </c>
       <c r="F96" t="n">
         <v>1201800</v>
@@ -2352,16 +2352,16 @@
         <v>44237</v>
       </c>
       <c r="B97" t="n">
-        <v>18.55900001525879</v>
+        <v>18.55900192260742</v>
       </c>
       <c r="C97" t="n">
-        <v>18.98150335499749</v>
+        <v>18.9815053057677</v>
       </c>
       <c r="D97" t="n">
-        <v>18.2432350221098</v>
+        <v>18.24323689700658</v>
       </c>
       <c r="E97" t="n">
-        <v>18.87031835488459</v>
+        <v>18.87032029422808</v>
       </c>
       <c r="F97" t="n">
         <v>979000</v>
@@ -2372,16 +2372,16 @@
         <v>44238</v>
       </c>
       <c r="B98" t="n">
-        <v>18.63461112976074</v>
+        <v>18.63460922241211</v>
       </c>
       <c r="C98" t="n">
-        <v>19.14606123399878</v>
+        <v>19.14605927430059</v>
       </c>
       <c r="D98" t="n">
-        <v>18.43447774264635</v>
+        <v>18.4344758557824</v>
       </c>
       <c r="E98" t="n">
-        <v>18.55900442949581</v>
+        <v>18.55900252988591</v>
       </c>
       <c r="F98" t="n">
         <v>912400</v>
@@ -2392,16 +2392,16 @@
         <v>44239</v>
       </c>
       <c r="B99" t="n">
-        <v>18.51897811889648</v>
+        <v>18.51897430419922</v>
       </c>
       <c r="C99" t="n">
-        <v>18.72355816464402</v>
+        <v>18.72355430780561</v>
       </c>
       <c r="D99" t="n">
-        <v>18.16318636617275</v>
+        <v>18.16318262476451</v>
       </c>
       <c r="E99" t="n">
-        <v>18.58124146355452</v>
+        <v>18.58123763603172</v>
       </c>
       <c r="F99" t="n">
         <v>849600</v>
@@ -2432,16 +2432,16 @@
         <v>44245</v>
       </c>
       <c r="B101" t="n">
-        <v>18.24323844909668</v>
+        <v>18.24324035644531</v>
       </c>
       <c r="C101" t="n">
-        <v>19.03487525571373</v>
+        <v>19.03487724582877</v>
       </c>
       <c r="D101" t="n">
-        <v>17.9052350351925</v>
+        <v>17.90523690720254</v>
       </c>
       <c r="E101" t="n">
-        <v>18.69242518745105</v>
+        <v>18.6924271417626</v>
       </c>
       <c r="F101" t="n">
         <v>1007600</v>
@@ -2452,16 +2452,16 @@
         <v>44246</v>
       </c>
       <c r="B102" t="n">
-        <v>18.27881622314453</v>
+        <v>18.27881813049316</v>
       </c>
       <c r="C102" t="n">
-        <v>18.57234460188025</v>
+        <v>18.57234653985784</v>
       </c>
       <c r="D102" t="n">
-        <v>17.92302450597225</v>
+        <v>17.92302637619491</v>
       </c>
       <c r="E102" t="n">
-        <v>18.23434289470377</v>
+        <v>18.23434479741172</v>
       </c>
       <c r="F102" t="n">
         <v>881800</v>
@@ -2492,16 +2492,16 @@
         <v>44250</v>
       </c>
       <c r="B104" t="n">
-        <v>17.70065498352051</v>
+        <v>17.70065307617188</v>
       </c>
       <c r="C104" t="n">
-        <v>18.1009217372794</v>
+        <v>18.10091978679969</v>
       </c>
       <c r="D104" t="n">
-        <v>17.5183116171523</v>
+        <v>17.51830972945222</v>
       </c>
       <c r="E104" t="n">
-        <v>17.86076168502407</v>
+        <v>17.860759760423</v>
       </c>
       <c r="F104" t="n">
         <v>1151400</v>
@@ -2512,16 +2512,16 @@
         <v>44251</v>
       </c>
       <c r="B105" t="n">
-        <v>17.68731307983398</v>
+        <v>17.68731498718262</v>
       </c>
       <c r="C105" t="n">
-        <v>18.09647313665348</v>
+        <v>18.09647508812474</v>
       </c>
       <c r="D105" t="n">
-        <v>17.54499639080558</v>
+        <v>17.54499828280719</v>
       </c>
       <c r="E105" t="n">
-        <v>17.70510309009973</v>
+        <v>17.70510499936678</v>
       </c>
       <c r="F105" t="n">
         <v>1411000</v>
@@ -2552,16 +2552,16 @@
         <v>44253</v>
       </c>
       <c r="B107" t="n">
-        <v>16.69998741149902</v>
+        <v>16.69998931884766</v>
       </c>
       <c r="C107" t="n">
-        <v>17.20699076284545</v>
+        <v>17.20699272810024</v>
       </c>
       <c r="D107" t="n">
-        <v>16.40201241244574</v>
+        <v>16.40201428576187</v>
       </c>
       <c r="E107" t="n">
-        <v>17.13583242750821</v>
+        <v>17.13583438463582</v>
       </c>
       <c r="F107" t="n">
         <v>1586600</v>
@@ -2612,16 +2612,16 @@
         <v>44258</v>
       </c>
       <c r="B110" t="n">
-        <v>16.19298362731934</v>
+        <v>16.1929874420166</v>
       </c>
       <c r="C110" t="n">
-        <v>16.80227696339255</v>
+        <v>16.80228092162542</v>
       </c>
       <c r="D110" t="n">
-        <v>15.61926860968948</v>
+        <v>15.61927228923258</v>
       </c>
       <c r="E110" t="n">
-        <v>16.80227696339255</v>
+        <v>16.80228092162542</v>
       </c>
       <c r="F110" t="n">
         <v>1368800</v>
@@ -2632,16 +2632,16 @@
         <v>44259</v>
       </c>
       <c r="B111" t="n">
-        <v>16.05066871643066</v>
+        <v>16.0506706237793</v>
       </c>
       <c r="C111" t="n">
-        <v>16.75780547454543</v>
+        <v>16.75780746592523</v>
       </c>
       <c r="D111" t="n">
-        <v>15.79271866916489</v>
+        <v>15.79272054586055</v>
       </c>
       <c r="E111" t="n">
-        <v>16.23301207184145</v>
+        <v>16.23301400085849</v>
       </c>
       <c r="F111" t="n">
         <v>1300400</v>
@@ -2672,16 +2672,16 @@
         <v>44263</v>
       </c>
       <c r="B113" t="n">
-        <v>14.91213512420654</v>
+        <v>14.91213417053223</v>
       </c>
       <c r="C113" t="n">
-        <v>16.0595654053297</v>
+        <v>16.05956437827389</v>
       </c>
       <c r="D113" t="n">
-        <v>14.76537177228896</v>
+        <v>14.76537082800059</v>
       </c>
       <c r="E113" t="n">
-        <v>16.01064372250756</v>
+        <v>16.01064269858043</v>
       </c>
       <c r="F113" t="n">
         <v>3236800</v>
@@ -2692,16 +2692,16 @@
         <v>44264</v>
       </c>
       <c r="B114" t="n">
-        <v>14.7653694152832</v>
+        <v>14.76537036895752</v>
       </c>
       <c r="C114" t="n">
-        <v>15.42358445966246</v>
+        <v>15.42358545584995</v>
       </c>
       <c r="D114" t="n">
-        <v>14.5563410571555</v>
+        <v>14.55634199732897</v>
       </c>
       <c r="E114" t="n">
-        <v>15.11671444805785</v>
+        <v>15.11671542442504</v>
       </c>
       <c r="F114" t="n">
         <v>1628800</v>
@@ -2712,16 +2712,16 @@
         <v>44265</v>
       </c>
       <c r="B115" t="n">
-        <v>14.64529132843018</v>
+        <v>14.64529037475586</v>
       </c>
       <c r="C115" t="n">
-        <v>15.05445139769713</v>
+        <v>15.05445041737906</v>
       </c>
       <c r="D115" t="n">
-        <v>14.28505124405912</v>
+        <v>14.28505031384297</v>
       </c>
       <c r="E115" t="n">
-        <v>15.05445139769713</v>
+        <v>15.05445041737906</v>
       </c>
       <c r="F115" t="n">
         <v>3352600</v>
@@ -2732,16 +2732,16 @@
         <v>44266</v>
       </c>
       <c r="B116" t="n">
-        <v>15.81940269470215</v>
+        <v>15.81940460205078</v>
       </c>
       <c r="C116" t="n">
-        <v>15.99285103455227</v>
+        <v>15.99285296281361</v>
       </c>
       <c r="D116" t="n">
-        <v>15.15674100160559</v>
+        <v>15.15674282905697</v>
       </c>
       <c r="E116" t="n">
-        <v>15.15674100160559</v>
+        <v>15.15674282905697</v>
       </c>
       <c r="F116" t="n">
         <v>2295400</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708587646484</v>
+        <v>15.67708683013916</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619424134576</v>
+        <v>16.00619521504051</v>
       </c>
       <c r="D118" t="n">
-        <v>15.49474253413244</v>
+        <v>15.49474347671438</v>
       </c>
       <c r="E118" t="n">
-        <v>15.61482254443162</v>
+        <v>15.61482349431831</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880615234375</v>
+        <v>16.58880805969238</v>
       </c>
       <c r="C120" t="n">
-        <v>16.75780787313692</v>
+        <v>16.75780979991704</v>
       </c>
       <c r="D120" t="n">
-        <v>16.07735603179049</v>
+        <v>16.07735788033358</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298771661808</v>
+        <v>16.19298957845627</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2832,16 +2832,16 @@
         <v>44273</v>
       </c>
       <c r="B121" t="n">
-        <v>16.21966934204102</v>
+        <v>16.21967124938965</v>
       </c>
       <c r="C121" t="n">
-        <v>17.29149274020432</v>
+        <v>17.2914947735938</v>
       </c>
       <c r="D121" t="n">
-        <v>16.07735266899806</v>
+        <v>16.077354559611</v>
       </c>
       <c r="E121" t="n">
-        <v>16.58880268257474</v>
+        <v>16.58880463333153</v>
       </c>
       <c r="F121" t="n">
         <v>1568800</v>
@@ -2852,16 +2852,16 @@
         <v>44274</v>
       </c>
       <c r="B122" t="n">
-        <v>16.32196426391602</v>
+        <v>16.32196044921875</v>
       </c>
       <c r="C122" t="n">
-        <v>16.54433434463272</v>
+        <v>16.54433047796411</v>
       </c>
       <c r="D122" t="n">
-        <v>15.8905657644299</v>
+        <v>15.89056205055718</v>
       </c>
       <c r="E122" t="n">
-        <v>16.17519919629943</v>
+        <v>16.17519541590345</v>
       </c>
       <c r="F122" t="n">
         <v>1059200</v>
@@ -2912,16 +2912,16 @@
         <v>44279</v>
       </c>
       <c r="B125" t="n">
-        <v>15.41024589538574</v>
+        <v>15.41024303436279</v>
       </c>
       <c r="C125" t="n">
-        <v>16.21077777512874</v>
+        <v>16.2107747654813</v>
       </c>
       <c r="D125" t="n">
-        <v>15.21455915604819</v>
+        <v>15.21455633135589</v>
       </c>
       <c r="E125" t="n">
-        <v>16.05067105987036</v>
+        <v>16.05066807994787</v>
       </c>
       <c r="F125" t="n">
         <v>1010400</v>
@@ -2932,16 +2932,16 @@
         <v>44280</v>
       </c>
       <c r="B126" t="n">
-        <v>16.06846046447754</v>
+        <v>16.06846237182617</v>
       </c>
       <c r="C126" t="n">
-        <v>16.22411882256725</v>
+        <v>16.22412074839275</v>
       </c>
       <c r="D126" t="n">
-        <v>15.07224188305681</v>
+        <v>15.07224367215291</v>
       </c>
       <c r="E126" t="n">
-        <v>15.38800695035243</v>
+        <v>15.38800877693028</v>
       </c>
       <c r="F126" t="n">
         <v>1320600</v>
@@ -2952,16 +2952,16 @@
         <v>44281</v>
       </c>
       <c r="B127" t="n">
-        <v>15.85498428344727</v>
+        <v>15.85498332977295</v>
       </c>
       <c r="C127" t="n">
-        <v>16.41535602902986</v>
+        <v>16.41535504164929</v>
       </c>
       <c r="D127" t="n">
-        <v>15.67264092135187</v>
+        <v>15.67263997864547</v>
       </c>
       <c r="E127" t="n">
-        <v>16.10403763857342</v>
+        <v>16.1040366699186</v>
       </c>
       <c r="F127" t="n">
         <v>1078200</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.5836935043335</v>
+        <v>15.58369541168213</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174858739247</v>
+        <v>16.00175054590848</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245512569351</v>
+        <v>15.39245700963573</v>
       </c>
       <c r="E128" t="n">
-        <v>15.74380021171105</v>
+        <v>15.74380213865577</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514427185059</v>
+        <v>16.09514236450195</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23746097399444</v>
+        <v>16.23745904978063</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48585078476289</v>
+        <v>15.48584894961834</v>
       </c>
       <c r="E129" t="n">
-        <v>15.58814080839448</v>
+        <v>15.58813896112809</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3012,16 +3012,16 @@
         <v>44286</v>
       </c>
       <c r="B130" t="n">
-        <v>16.61548805236816</v>
+        <v>16.6154899597168</v>
       </c>
       <c r="C130" t="n">
-        <v>16.71777805728372</v>
+        <v>16.71777997637457</v>
       </c>
       <c r="D130" t="n">
-        <v>15.94392964648752</v>
+        <v>15.94393147674567</v>
       </c>
       <c r="E130" t="n">
-        <v>16.10848468167865</v>
+        <v>16.10848653082663</v>
       </c>
       <c r="F130" t="n">
         <v>1491400</v>
@@ -3112,16 +3112,16 @@
         <v>44294</v>
       </c>
       <c r="B135" t="n">
-        <v>17.60726165771484</v>
+        <v>17.60725975036621</v>
       </c>
       <c r="C135" t="n">
-        <v>17.90968507914474</v>
+        <v>17.90968313903537</v>
       </c>
       <c r="D135" t="n">
-        <v>17.27370656318618</v>
+        <v>17.2737046919707</v>
       </c>
       <c r="E135" t="n">
-        <v>17.38044493991689</v>
+        <v>17.38044305713872</v>
       </c>
       <c r="F135" t="n">
         <v>710000</v>
@@ -3152,16 +3152,16 @@
         <v>44298</v>
       </c>
       <c r="B137" t="n">
-        <v>17.7451286315918</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="C137" t="n">
-        <v>18.05644530861555</v>
+        <v>18.05644724942629</v>
       </c>
       <c r="D137" t="n">
-        <v>17.58946859653127</v>
+        <v>17.58947048714867</v>
       </c>
       <c r="E137" t="n">
-        <v>18.05644530861555</v>
+        <v>18.05644724942629</v>
       </c>
       <c r="F137" t="n">
         <v>810600</v>
@@ -3192,16 +3192,16 @@
         <v>44300</v>
       </c>
       <c r="B139" t="n">
-        <v>17.16251945495605</v>
+        <v>17.16252136230469</v>
       </c>
       <c r="C139" t="n">
-        <v>17.71399789099429</v>
+        <v>17.71399985963123</v>
       </c>
       <c r="D139" t="n">
-        <v>17.07801945199119</v>
+        <v>17.07802134994895</v>
       </c>
       <c r="E139" t="n">
-        <v>17.37154783179656</v>
+        <v>17.37154976237547</v>
       </c>
       <c r="F139" t="n">
         <v>861200</v>
@@ -3232,16 +3232,16 @@
         <v>44302</v>
       </c>
       <c r="B141" t="n">
-        <v>17.7451286315918</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="C141" t="n">
-        <v>17.7451286315918</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="D141" t="n">
-        <v>17.12249188444699</v>
+        <v>17.12249372487104</v>
       </c>
       <c r="E141" t="n">
-        <v>17.38488858118748</v>
+        <v>17.38489044981543</v>
       </c>
       <c r="F141" t="n">
         <v>774600</v>
@@ -3252,16 +3252,16 @@
         <v>44305</v>
       </c>
       <c r="B142" t="n">
-        <v>18.01197242736816</v>
+        <v>18.0119743347168</v>
       </c>
       <c r="C142" t="n">
-        <v>18.17652577451049</v>
+        <v>18.17652769928423</v>
       </c>
       <c r="D142" t="n">
-        <v>17.70065404610391</v>
+        <v>17.70065592048599</v>
       </c>
       <c r="E142" t="n">
-        <v>17.70065404610391</v>
+        <v>17.70065592048599</v>
       </c>
       <c r="F142" t="n">
         <v>952400</v>
@@ -3312,16 +3312,16 @@
         <v>44309</v>
       </c>
       <c r="B145" t="n">
-        <v>17.21143913269043</v>
+        <v>17.21144104003906</v>
       </c>
       <c r="C145" t="n">
-        <v>17.57167746350501</v>
+        <v>17.57167941077477</v>
       </c>
       <c r="D145" t="n">
-        <v>16.88233077103849</v>
+        <v>16.88233264191577</v>
       </c>
       <c r="E145" t="n">
-        <v>17.5227574863507</v>
+        <v>17.52275942819921</v>
       </c>
       <c r="F145" t="n">
         <v>903000</v>
@@ -3332,16 +3332,16 @@
         <v>44312</v>
       </c>
       <c r="B146" t="n">
-        <v>17.08691215515137</v>
+        <v>17.0869140625</v>
       </c>
       <c r="C146" t="n">
-        <v>17.31817718810049</v>
+        <v>17.31817912126438</v>
       </c>
       <c r="D146" t="n">
-        <v>16.90012214577824</v>
+        <v>16.90012403227619</v>
       </c>
       <c r="E146" t="n">
-        <v>17.31817718810049</v>
+        <v>17.31817912126438</v>
       </c>
       <c r="F146" t="n">
         <v>836400</v>
@@ -3352,16 +3352,16 @@
         <v>44313</v>
       </c>
       <c r="B147" t="n">
-        <v>17.33596992492676</v>
+        <v>17.33596611022949</v>
       </c>
       <c r="C147" t="n">
-        <v>17.78071005136372</v>
+        <v>17.78070613880351</v>
       </c>
       <c r="D147" t="n">
-        <v>17.01130983621365</v>
+        <v>17.01130609295629</v>
       </c>
       <c r="E147" t="n">
-        <v>17.0468898606721</v>
+        <v>17.04688610958552</v>
       </c>
       <c r="F147" t="n">
         <v>1372600</v>
@@ -3432,16 +3432,16 @@
         <v>44319</v>
       </c>
       <c r="B151" t="n">
-        <v>19.44735908508301</v>
+        <v>19.44735717773438</v>
       </c>
       <c r="C151" t="n">
-        <v>19.67089194812994</v>
+        <v>19.67089001885776</v>
       </c>
       <c r="D151" t="n">
-        <v>18.83934942472809</v>
+        <v>18.83934757701153</v>
       </c>
       <c r="E151" t="n">
-        <v>19.62618605768871</v>
+        <v>19.62618413280117</v>
       </c>
       <c r="F151" t="n">
         <v>2225200</v>
@@ -3452,16 +3452,16 @@
         <v>44320</v>
       </c>
       <c r="B152" t="n">
-        <v>19.79606819152832</v>
+        <v>19.79606628417969</v>
       </c>
       <c r="C152" t="n">
-        <v>20.00618961139364</v>
+        <v>20.00618768379984</v>
       </c>
       <c r="D152" t="n">
-        <v>19.25959072829643</v>
+        <v>19.25958887263734</v>
       </c>
       <c r="E152" t="n">
-        <v>19.45182740585503</v>
+        <v>19.45182553167395</v>
       </c>
       <c r="F152" t="n">
         <v>1635200</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.83325958251953</v>
+        <v>20.83326148986816</v>
       </c>
       <c r="C155" t="n">
-        <v>20.87796717286325</v>
+        <v>20.877969084305</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384096914172</v>
+        <v>20.36384283351365</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902565479451</v>
+        <v>20.86902756541763</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3612,16 +3612,16 @@
         <v>44330</v>
       </c>
       <c r="B160" t="n">
-        <v>20.29678344726562</v>
+        <v>20.29677963256836</v>
       </c>
       <c r="C160" t="n">
-        <v>21.23562073440818</v>
+        <v>21.23561674326029</v>
       </c>
       <c r="D160" t="n">
-        <v>20.22972291014674</v>
+        <v>20.22971910805323</v>
       </c>
       <c r="E160" t="n">
-        <v>21.01655779118409</v>
+        <v>21.01655384120819</v>
       </c>
       <c r="F160" t="n">
         <v>1009800</v>
@@ -3652,16 +3652,16 @@
         <v>44334</v>
       </c>
       <c r="B162" t="n">
-        <v>21.12385368347168</v>
+        <v>21.12385177612305</v>
       </c>
       <c r="C162" t="n">
-        <v>21.74080480825265</v>
+        <v>21.74080284519728</v>
       </c>
       <c r="D162" t="n">
-        <v>20.88243780350257</v>
+        <v>20.88243591795225</v>
       </c>
       <c r="E162" t="n">
-        <v>21.15067823860833</v>
+        <v>21.15067632883762</v>
       </c>
       <c r="F162" t="n">
         <v>1192600</v>
@@ -3672,16 +3672,16 @@
         <v>44335</v>
       </c>
       <c r="B163" t="n">
-        <v>21.36974143981934</v>
+        <v>21.3697395324707</v>
       </c>
       <c r="C163" t="n">
-        <v>21.49044939093096</v>
+        <v>21.49044747280858</v>
       </c>
       <c r="D163" t="n">
-        <v>20.88691134079327</v>
+        <v>20.88690947653946</v>
       </c>
       <c r="E163" t="n">
-        <v>21.20432759811249</v>
+        <v>21.2043257055278</v>
       </c>
       <c r="F163" t="n">
         <v>1135200</v>
@@ -3692,16 +3692,16 @@
         <v>44336</v>
       </c>
       <c r="B164" t="n">
-        <v>21.86151313781738</v>
+        <v>21.86151123046875</v>
       </c>
       <c r="C164" t="n">
-        <v>21.93751348726187</v>
+        <v>21.93751157328245</v>
       </c>
       <c r="D164" t="n">
-        <v>21.37868136927493</v>
+        <v>21.37867950405186</v>
       </c>
       <c r="E164" t="n">
-        <v>21.49044779287232</v>
+        <v>21.49044591789798</v>
       </c>
       <c r="F164" t="n">
         <v>917400</v>
@@ -3712,16 +3712,16 @@
         <v>44337</v>
       </c>
       <c r="B165" t="n">
-        <v>21.94645690917969</v>
+        <v>21.94645309448242</v>
       </c>
       <c r="C165" t="n">
-        <v>22.04034030384297</v>
+        <v>22.04033647282705</v>
       </c>
       <c r="D165" t="n">
-        <v>21.5038610829635</v>
+        <v>21.50385734519752</v>
       </c>
       <c r="E165" t="n">
-        <v>22.04034030384297</v>
+        <v>22.04033647282705</v>
       </c>
       <c r="F165" t="n">
         <v>653400</v>
@@ -3772,16 +3772,16 @@
         <v>44342</v>
       </c>
       <c r="B168" t="n">
-        <v>22.17445755004883</v>
+        <v>22.17445945739746</v>
       </c>
       <c r="C168" t="n">
-        <v>22.42481495049289</v>
+        <v>22.42481687937616</v>
       </c>
       <c r="D168" t="n">
-        <v>21.53515347667831</v>
+        <v>21.53515532903684</v>
       </c>
       <c r="E168" t="n">
-        <v>22.17445755004883</v>
+        <v>22.17445945739746</v>
       </c>
       <c r="F168" t="n">
         <v>837000</v>
@@ -3792,16 +3792,16 @@
         <v>44343</v>
       </c>
       <c r="B169" t="n">
-        <v>22.3443431854248</v>
+        <v>22.34434509277344</v>
       </c>
       <c r="C169" t="n">
-        <v>22.3443431854248</v>
+        <v>22.34434509277344</v>
       </c>
       <c r="D169" t="n">
-        <v>21.80339410488992</v>
+        <v>21.80339596606228</v>
       </c>
       <c r="E169" t="n">
-        <v>22.27281274258895</v>
+        <v>22.27281464383163</v>
       </c>
       <c r="F169" t="n">
         <v>1342400</v>
@@ -3812,16 +3812,16 @@
         <v>44344</v>
       </c>
       <c r="B170" t="n">
-        <v>22.21469306945801</v>
+        <v>22.21469497680664</v>
       </c>
       <c r="C170" t="n">
-        <v>22.54552242370129</v>
+        <v>22.54552435945486</v>
       </c>
       <c r="D170" t="n">
-        <v>21.94198443666828</v>
+        <v>21.94198632060221</v>
       </c>
       <c r="E170" t="n">
-        <v>22.29516502845177</v>
+        <v>22.29516694270971</v>
       </c>
       <c r="F170" t="n">
         <v>840600</v>
@@ -3852,16 +3852,16 @@
         <v>44348</v>
       </c>
       <c r="B172" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C172" t="n">
-        <v>24.09237101528835</v>
+        <v>24.09236907591068</v>
       </c>
       <c r="D172" t="n">
-        <v>23.10435619826109</v>
+        <v>23.10435433841622</v>
       </c>
       <c r="E172" t="n">
-        <v>23.32341744272831</v>
+        <v>23.32341556524954</v>
       </c>
       <c r="F172" t="n">
         <v>1770600</v>
@@ -3872,16 +3872,16 @@
         <v>44349</v>
       </c>
       <c r="B173" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C173" t="n">
-        <v>24.03872360721357</v>
+        <v>24.03872167215439</v>
       </c>
       <c r="D173" t="n">
-        <v>23.4709499467094</v>
+        <v>23.47094805735462</v>
       </c>
       <c r="E173" t="n">
-        <v>24.03872360721357</v>
+        <v>24.03872167215439</v>
       </c>
       <c r="F173" t="n">
         <v>823800</v>
@@ -3892,16 +3892,16 @@
         <v>44351</v>
       </c>
       <c r="B174" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C174" t="n">
-        <v>23.91801565998005</v>
+        <v>23.91801373463757</v>
       </c>
       <c r="D174" t="n">
-        <v>23.39941950080291</v>
+        <v>23.39941761720616</v>
       </c>
       <c r="E174" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="F174" t="n">
         <v>902800</v>
@@ -3912,16 +3912,16 @@
         <v>44354</v>
       </c>
       <c r="B175" t="n">
-        <v>23.51565361022949</v>
+        <v>23.51565551757812</v>
       </c>
       <c r="C175" t="n">
-        <v>23.95377946853823</v>
+        <v>23.95378141142314</v>
       </c>
       <c r="D175" t="n">
-        <v>23.24741488982269</v>
+        <v>23.24741677541455</v>
       </c>
       <c r="E175" t="n">
-        <v>23.56483110690212</v>
+        <v>23.56483301823953</v>
       </c>
       <c r="F175" t="n">
         <v>1060000</v>
@@ -3932,16 +3932,16 @@
         <v>44355</v>
       </c>
       <c r="B176" t="n">
-        <v>23.40388679504395</v>
+        <v>23.40388870239258</v>
       </c>
       <c r="C176" t="n">
-        <v>23.68106873423341</v>
+        <v>23.68107066417156</v>
       </c>
       <c r="D176" t="n">
-        <v>22.95235122542912</v>
+        <v>22.95235309597892</v>
       </c>
       <c r="E176" t="n">
-        <v>23.47094732671691</v>
+        <v>23.47094923953079</v>
       </c>
       <c r="F176" t="n">
         <v>1006800</v>
@@ -3952,16 +3952,16 @@
         <v>44356</v>
       </c>
       <c r="B177" t="n">
-        <v>23.51565361022949</v>
+        <v>23.51565551757812</v>
       </c>
       <c r="C177" t="n">
-        <v>23.60059717918046</v>
+        <v>23.60059909341884</v>
       </c>
       <c r="D177" t="n">
-        <v>23.1803543570109</v>
+        <v>23.18035623716349</v>
       </c>
       <c r="E177" t="n">
-        <v>23.444123171093</v>
+        <v>23.44412507263982</v>
       </c>
       <c r="F177" t="n">
         <v>621600</v>
@@ -3972,16 +3972,16 @@
         <v>44357</v>
       </c>
       <c r="B178" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C178" t="n">
-        <v>23.89119110323249</v>
+        <v>23.89118918004931</v>
       </c>
       <c r="D178" t="n">
-        <v>23.44859700212994</v>
+        <v>23.44859511457452</v>
       </c>
       <c r="E178" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="F178" t="n">
         <v>946600</v>
@@ -4012,16 +4012,16 @@
         <v>44361</v>
       </c>
       <c r="B180" t="n">
-        <v>24.58860969543457</v>
+        <v>24.58861351013184</v>
       </c>
       <c r="C180" t="n">
-        <v>24.76743662993302</v>
+        <v>24.76744047237364</v>
       </c>
       <c r="D180" t="n">
-        <v>23.26082422614669</v>
+        <v>23.26082783485022</v>
       </c>
       <c r="E180" t="n">
-        <v>23.45753419517899</v>
+        <v>23.45753783440027</v>
       </c>
       <c r="F180" t="n">
         <v>1774600</v>
@@ -4052,16 +4052,16 @@
         <v>44363</v>
       </c>
       <c r="B182" t="n">
-        <v>24.49920082092285</v>
+        <v>24.49919891357422</v>
       </c>
       <c r="C182" t="n">
-        <v>24.58414439817256</v>
+        <v>24.58414248421078</v>
       </c>
       <c r="D182" t="n">
-        <v>23.90013269509492</v>
+        <v>23.90013083438584</v>
       </c>
       <c r="E182" t="n">
-        <v>24.36508144761637</v>
+        <v>24.36507955070941</v>
       </c>
       <c r="F182" t="n">
         <v>781400</v>
@@ -4072,16 +4072,16 @@
         <v>44364</v>
       </c>
       <c r="B183" t="n">
-        <v>24.58860969543457</v>
+        <v>24.58861351013184</v>
       </c>
       <c r="C183" t="n">
-        <v>24.71378752633146</v>
+        <v>24.71379136044892</v>
       </c>
       <c r="D183" t="n">
-        <v>23.96718874145352</v>
+        <v>23.96719245974302</v>
       </c>
       <c r="E183" t="n">
-        <v>24.63331557634916</v>
+        <v>24.63331939798214</v>
       </c>
       <c r="F183" t="n">
         <v>897400</v>
@@ -4092,16 +4092,16 @@
         <v>44365</v>
       </c>
       <c r="B184" t="n">
-        <v>24.8970890045166</v>
+        <v>24.89708518981934</v>
       </c>
       <c r="C184" t="n">
-        <v>25.19215230760862</v>
+        <v>25.19214844770217</v>
       </c>
       <c r="D184" t="n">
-        <v>24.25778489691384</v>
+        <v>24.25778118016986</v>
       </c>
       <c r="E184" t="n">
-        <v>24.6780277596409</v>
+        <v>24.67802397850789</v>
       </c>
       <c r="F184" t="n">
         <v>1737600</v>
@@ -4112,16 +4112,16 @@
         <v>44368</v>
       </c>
       <c r="B185" t="n">
-        <v>25.23686027526855</v>
+        <v>25.23685836791992</v>
       </c>
       <c r="C185" t="n">
-        <v>25.64815991972168</v>
+        <v>25.64815798128789</v>
       </c>
       <c r="D185" t="n">
-        <v>24.6959111625081</v>
+        <v>24.69590929604326</v>
       </c>
       <c r="E185" t="n">
-        <v>25.25027170115539</v>
+        <v>25.25026979279315</v>
       </c>
       <c r="F185" t="n">
         <v>748400</v>
@@ -4132,16 +4132,16 @@
         <v>44369</v>
       </c>
       <c r="B186" t="n">
-        <v>24.58860969543457</v>
+        <v>24.58861351013184</v>
       </c>
       <c r="C186" t="n">
-        <v>25.26814965894062</v>
+        <v>25.26815357906228</v>
       </c>
       <c r="D186" t="n">
-        <v>24.54390381451998</v>
+        <v>24.54390762228154</v>
       </c>
       <c r="E186" t="n">
-        <v>25.23238358987291</v>
+        <v>25.2323875044458</v>
       </c>
       <c r="F186" t="n">
         <v>871000</v>
@@ -4152,16 +4152,16 @@
         <v>44370</v>
       </c>
       <c r="B187" t="n">
-        <v>24.72273445129395</v>
+        <v>24.72273063659668</v>
       </c>
       <c r="C187" t="n">
-        <v>24.87920847956124</v>
+        <v>24.87920464072016</v>
       </c>
       <c r="D187" t="n">
-        <v>24.28014033500109</v>
+        <v>24.28013658859573</v>
       </c>
       <c r="E187" t="n">
-        <v>24.71379293207121</v>
+        <v>24.71378911875361</v>
       </c>
       <c r="F187" t="n">
         <v>1264600</v>
@@ -4172,16 +4172,16 @@
         <v>44371</v>
       </c>
       <c r="B188" t="n">
-        <v>24.58414268493652</v>
+        <v>24.58414459228516</v>
       </c>
       <c r="C188" t="n">
-        <v>25.05803121795611</v>
+        <v>25.05803316207115</v>
       </c>
       <c r="D188" t="n">
-        <v>23.98060298898671</v>
+        <v>23.98060484951002</v>
       </c>
       <c r="E188" t="n">
-        <v>25.05356131150621</v>
+        <v>25.05356325527446</v>
       </c>
       <c r="F188" t="n">
         <v>1450200</v>
@@ -4232,16 +4232,16 @@
         <v>44376</v>
       </c>
       <c r="B191" t="n">
-        <v>24.49920082092285</v>
+        <v>24.49919891357422</v>
       </c>
       <c r="C191" t="n">
-        <v>24.70485064035414</v>
+        <v>24.70484871699495</v>
       </c>
       <c r="D191" t="n">
-        <v>23.49330296299373</v>
+        <v>23.49330113395778</v>
       </c>
       <c r="E191" t="n">
-        <v>24.46790635733202</v>
+        <v>24.46790445241977</v>
       </c>
       <c r="F191" t="n">
         <v>1326200</v>
@@ -4292,16 +4292,16 @@
         <v>44379</v>
       </c>
       <c r="B194" t="n">
-        <v>26.42605209350586</v>
+        <v>26.42605400085449</v>
       </c>
       <c r="C194" t="n">
-        <v>26.77029286492826</v>
+        <v>26.7702947971231</v>
       </c>
       <c r="D194" t="n">
-        <v>25.41568272171123</v>
+        <v>25.41568455613461</v>
       </c>
       <c r="E194" t="n">
-        <v>25.41568272171123</v>
+        <v>25.41568455613461</v>
       </c>
       <c r="F194" t="n">
         <v>2268600</v>
@@ -4312,16 +4312,16 @@
         <v>44382</v>
       </c>
       <c r="B195" t="n">
-        <v>26.53334617614746</v>
+        <v>26.53334808349609</v>
       </c>
       <c r="C195" t="n">
-        <v>26.77923365290268</v>
+        <v>26.77923557792692</v>
       </c>
       <c r="D195" t="n">
-        <v>26.17122408387186</v>
+        <v>26.17122596518936</v>
       </c>
       <c r="E195" t="n">
-        <v>26.38134378388976</v>
+        <v>26.3813456803117</v>
       </c>
       <c r="F195" t="n">
         <v>581600</v>
@@ -4332,16 +4332,16 @@
         <v>44383</v>
       </c>
       <c r="B196" t="n">
-        <v>26.19804954528809</v>
+        <v>26.19804763793945</v>
       </c>
       <c r="C196" t="n">
-        <v>26.53334882294324</v>
+        <v>26.53334689118315</v>
       </c>
       <c r="D196" t="n">
-        <v>25.66157206537609</v>
+        <v>25.66157019708569</v>
       </c>
       <c r="E196" t="n">
-        <v>26.53334882294324</v>
+        <v>26.53334689118315</v>
       </c>
       <c r="F196" t="n">
         <v>905000</v>
@@ -4352,16 +4352,16 @@
         <v>44384</v>
       </c>
       <c r="B197" t="n">
-        <v>26.52440452575684</v>
+        <v>26.5244083404541</v>
       </c>
       <c r="C197" t="n">
-        <v>26.93570408488289</v>
+        <v>26.9357079587326</v>
       </c>
       <c r="D197" t="n">
-        <v>26.10863335531591</v>
+        <v>26.10863711021764</v>
       </c>
       <c r="E197" t="n">
-        <v>26.19804511657286</v>
+        <v>26.19804888433364</v>
       </c>
       <c r="F197" t="n">
         <v>915800</v>
@@ -4372,16 +4372,16 @@
         <v>44385</v>
       </c>
       <c r="B198" t="n">
-        <v>26.52440452575684</v>
+        <v>26.5244083404541</v>
       </c>
       <c r="C198" t="n">
-        <v>26.52440452575684</v>
+        <v>26.5244083404541</v>
       </c>
       <c r="D198" t="n">
-        <v>25.82250992086558</v>
+        <v>25.82251363461749</v>
       </c>
       <c r="E198" t="n">
-        <v>26.2382810913065</v>
+        <v>26.23828486485395</v>
       </c>
       <c r="F198" t="n">
         <v>1041800</v>
@@ -4412,16 +4412,16 @@
         <v>44390</v>
       </c>
       <c r="B200" t="n">
-        <v>27.66442680358887</v>
+        <v>27.66442489624023</v>
       </c>
       <c r="C200" t="n">
-        <v>27.70466278598387</v>
+        <v>27.70466087586113</v>
       </c>
       <c r="D200" t="n">
-        <v>27.1681835891906</v>
+        <v>27.1681817160559</v>
       </c>
       <c r="E200" t="n">
-        <v>27.33806903768288</v>
+        <v>27.33806715283528</v>
       </c>
       <c r="F200" t="n">
         <v>796200</v>
@@ -4432,16 +4432,16 @@
         <v>44391</v>
       </c>
       <c r="B201" t="n">
-        <v>28.17408180236816</v>
+        <v>28.17407989501953</v>
       </c>
       <c r="C201" t="n">
-        <v>28.33502573399738</v>
+        <v>28.33502381575305</v>
       </c>
       <c r="D201" t="n">
-        <v>27.44089429643097</v>
+        <v>27.44089243871817</v>
       </c>
       <c r="E201" t="n">
-        <v>27.67336867484868</v>
+        <v>27.67336680139767</v>
       </c>
       <c r="F201" t="n">
         <v>880600</v>
@@ -4532,16 +4532,16 @@
         <v>44398</v>
       </c>
       <c r="B206" t="n">
-        <v>29.60468673706055</v>
+        <v>29.60468864440918</v>
       </c>
       <c r="C206" t="n">
-        <v>29.78351367227192</v>
+        <v>29.78351559114187</v>
       </c>
       <c r="D206" t="n">
-        <v>29.05926611954392</v>
+        <v>29.0592679917526</v>
       </c>
       <c r="E206" t="n">
-        <v>29.52868639811875</v>
+        <v>29.52868830057088</v>
       </c>
       <c r="F206" t="n">
         <v>1050200</v>
@@ -4572,16 +4572,16 @@
         <v>44400</v>
       </c>
       <c r="B208" t="n">
-        <v>30.31105613708496</v>
+        <v>30.31105804443359</v>
       </c>
       <c r="C208" t="n">
-        <v>30.62400076597767</v>
+        <v>30.62400269301861</v>
       </c>
       <c r="D208" t="n">
-        <v>29.97128524654384</v>
+        <v>29.97128713251211</v>
       </c>
       <c r="E208" t="n">
-        <v>30.2395239871434</v>
+        <v>30.23952588999082</v>
       </c>
       <c r="F208" t="n">
         <v>819000</v>
@@ -4592,16 +4592,16 @@
         <v>44403</v>
       </c>
       <c r="B209" t="n">
-        <v>30.08752059936523</v>
+        <v>30.0875244140625</v>
       </c>
       <c r="C209" t="n">
-        <v>30.48987696893258</v>
+        <v>30.48988083464328</v>
       </c>
       <c r="D209" t="n">
-        <v>29.56445117941508</v>
+        <v>29.5644549277941</v>
       </c>
       <c r="E209" t="n">
-        <v>30.48987696893258</v>
+        <v>30.48988083464328</v>
       </c>
       <c r="F209" t="n">
         <v>1240800</v>
@@ -4652,16 +4652,16 @@
         <v>44406</v>
       </c>
       <c r="B212" t="n">
-        <v>30.84753227233887</v>
+        <v>30.8475341796875</v>
       </c>
       <c r="C212" t="n">
-        <v>31.51365918811201</v>
+        <v>31.51366113664825</v>
       </c>
       <c r="D212" t="n">
-        <v>29.56445252818104</v>
+        <v>29.56445435619494</v>
       </c>
       <c r="E212" t="n">
-        <v>29.56445252818104</v>
+        <v>29.56445435619494</v>
       </c>
       <c r="F212" t="n">
         <v>1386000</v>
@@ -4692,16 +4692,16 @@
         <v>44410</v>
       </c>
       <c r="B214" t="n">
-        <v>31.2498893737793</v>
+        <v>31.24988746643066</v>
       </c>
       <c r="C214" t="n">
-        <v>31.98754837270211</v>
+        <v>31.98754642033019</v>
       </c>
       <c r="D214" t="n">
-        <v>31.03976797418139</v>
+        <v>31.03976607965759</v>
       </c>
       <c r="E214" t="n">
-        <v>31.5807169971674</v>
+        <v>31.58071506962657</v>
       </c>
       <c r="F214" t="n">
         <v>1185600</v>
@@ -4712,16 +4712,16 @@
         <v>44411</v>
       </c>
       <c r="B215" t="n">
-        <v>30.62399673461914</v>
+        <v>30.62400054931641</v>
       </c>
       <c r="C215" t="n">
-        <v>31.14259452090504</v>
+        <v>31.14259840020176</v>
       </c>
       <c r="D215" t="n">
-        <v>30.20375393613507</v>
+        <v>30.20375769848453</v>
       </c>
       <c r="E215" t="n">
-        <v>31.13812290941217</v>
+        <v>31.13812678815189</v>
       </c>
       <c r="F215" t="n">
         <v>1467200</v>
@@ -4732,16 +4732,16 @@
         <v>44412</v>
       </c>
       <c r="B216" t="n">
-        <v>29.78798675537109</v>
+        <v>29.78798294067383</v>
       </c>
       <c r="C216" t="n">
-        <v>30.84753370622673</v>
+        <v>30.84752975584219</v>
       </c>
       <c r="D216" t="n">
-        <v>29.7566922923926</v>
+        <v>29.75668848170296</v>
       </c>
       <c r="E216" t="n">
-        <v>30.62400085328306</v>
+        <v>30.62399693152449</v>
       </c>
       <c r="F216" t="n">
         <v>1263400</v>
@@ -4752,16 +4752,16 @@
         <v>44413</v>
       </c>
       <c r="B217" t="n">
-        <v>29.48398208618164</v>
+        <v>29.48397827148438</v>
       </c>
       <c r="C217" t="n">
-        <v>30.38705672665493</v>
+        <v>30.38705279511604</v>
       </c>
       <c r="D217" t="n">
-        <v>29.13974299169909</v>
+        <v>29.13973922154018</v>
       </c>
       <c r="E217" t="n">
-        <v>29.82375297938827</v>
+        <v>29.82374912073076</v>
       </c>
       <c r="F217" t="n">
         <v>1197200</v>
@@ -4812,16 +4812,16 @@
         <v>44418</v>
       </c>
       <c r="B220" t="n">
-        <v>29.59574699401855</v>
+        <v>29.59574317932129</v>
       </c>
       <c r="C220" t="n">
-        <v>30.78494335377824</v>
+        <v>30.78493938580138</v>
       </c>
       <c r="D220" t="n">
-        <v>29.59574699401855</v>
+        <v>29.59574317932129</v>
       </c>
       <c r="E220" t="n">
-        <v>30.4898783643616</v>
+        <v>30.48987443441668</v>
       </c>
       <c r="F220" t="n">
         <v>1186200</v>
@@ -4852,16 +4852,16 @@
         <v>44420</v>
       </c>
       <c r="B222" t="n">
-        <v>29.32750701904297</v>
+        <v>29.3275089263916</v>
       </c>
       <c r="C222" t="n">
-        <v>31.18730182754265</v>
+        <v>31.1873038558452</v>
       </c>
       <c r="D222" t="n">
-        <v>28.46914175858482</v>
+        <v>28.46914361010866</v>
       </c>
       <c r="E222" t="n">
-        <v>28.48702479453274</v>
+        <v>28.48702664721963</v>
       </c>
       <c r="F222" t="n">
         <v>1567750</v>
@@ -4892,16 +4892,16 @@
         <v>44424</v>
       </c>
       <c r="B224" t="n">
-        <v>25.6436882019043</v>
+        <v>25.64369010925293</v>
       </c>
       <c r="C224" t="n">
-        <v>28.14725537891694</v>
+        <v>28.14725747247807</v>
       </c>
       <c r="D224" t="n">
-        <v>24.26672506075316</v>
+        <v>24.26672686568483</v>
       </c>
       <c r="E224" t="n">
-        <v>28.14725537891694</v>
+        <v>28.14725747247807</v>
       </c>
       <c r="F224" t="n">
         <v>6674400</v>
@@ -4912,16 +4912,16 @@
         <v>44425</v>
       </c>
       <c r="B225" t="n">
-        <v>25.66157150268555</v>
+        <v>25.66156959533691</v>
       </c>
       <c r="C225" t="n">
-        <v>25.66157150268555</v>
+        <v>25.66156959533691</v>
       </c>
       <c r="D225" t="n">
-        <v>23.42624303399936</v>
+        <v>23.42624129279607</v>
       </c>
       <c r="E225" t="n">
-        <v>24.67802663537957</v>
+        <v>24.67802480113491</v>
       </c>
       <c r="F225" t="n">
         <v>4282800</v>
@@ -4992,16 +4992,16 @@
         <v>44431</v>
       </c>
       <c r="B229" t="n">
-        <v>26.85970687866211</v>
+        <v>26.85970878601074</v>
       </c>
       <c r="C229" t="n">
-        <v>27.41406736694361</v>
+        <v>27.41406931365822</v>
       </c>
       <c r="D229" t="n">
-        <v>26.28746164845576</v>
+        <v>26.28746351516839</v>
       </c>
       <c r="E229" t="n">
-        <v>26.71664429204535</v>
+        <v>26.71664618923489</v>
       </c>
       <c r="F229" t="n">
         <v>1094150</v>
@@ -5012,16 +5012,16 @@
         <v>44432</v>
       </c>
       <c r="B230" t="n">
-        <v>27.48559951782227</v>
+        <v>27.48559761047363</v>
       </c>
       <c r="C230" t="n">
-        <v>27.84325174306836</v>
+        <v>27.84324981090064</v>
       </c>
       <c r="D230" t="n">
-        <v>27.00276944009512</v>
+        <v>27.00276756625223</v>
       </c>
       <c r="E230" t="n">
-        <v>27.64654344553809</v>
+        <v>27.64654152702084</v>
       </c>
       <c r="F230" t="n">
         <v>835550</v>
@@ -5052,16 +5052,16 @@
         <v>44434</v>
       </c>
       <c r="B232" t="n">
-        <v>27.19947624206543</v>
+        <v>27.19947814941406</v>
       </c>
       <c r="C232" t="n">
-        <v>28.21878545432528</v>
+        <v>28.21878743315242</v>
       </c>
       <c r="D232" t="n">
-        <v>26.93123751423502</v>
+        <v>26.93123940277355</v>
       </c>
       <c r="E232" t="n">
-        <v>27.80748584426262</v>
+        <v>27.8074877942476</v>
       </c>
       <c r="F232" t="n">
         <v>1359900</v>
@@ -5072,16 +5072,16 @@
         <v>44435</v>
       </c>
       <c r="B233" t="n">
-        <v>28.96985816955566</v>
+        <v>28.9698600769043</v>
       </c>
       <c r="C233" t="n">
-        <v>29.11291905438238</v>
+        <v>29.11292097115001</v>
       </c>
       <c r="D233" t="n">
-        <v>27.00276844505784</v>
+        <v>27.00277022289511</v>
       </c>
       <c r="E233" t="n">
-        <v>27.44983413649641</v>
+        <v>27.44983594376807</v>
       </c>
       <c r="F233" t="n">
         <v>1634000</v>
@@ -5112,16 +5112,16 @@
         <v>44439</v>
       </c>
       <c r="B235" t="n">
-        <v>26.55570030212402</v>
+        <v>26.55570411682129</v>
       </c>
       <c r="C235" t="n">
-        <v>27.86113118201179</v>
+        <v>27.86113518423277</v>
       </c>
       <c r="D235" t="n">
-        <v>25.87616030921885</v>
+        <v>25.87616402630093</v>
       </c>
       <c r="E235" t="n">
-        <v>27.6823042397767</v>
+        <v>27.68230821630939</v>
       </c>
       <c r="F235" t="n">
         <v>1705500</v>
@@ -5152,16 +5152,16 @@
         <v>44441</v>
       </c>
       <c r="B237" t="n">
-        <v>25.35756683349609</v>
+        <v>25.35756492614746</v>
       </c>
       <c r="C237" t="n">
-        <v>26.6629978477622</v>
+        <v>26.66299584222149</v>
       </c>
       <c r="D237" t="n">
-        <v>25.10720942967972</v>
+        <v>25.10720754116251</v>
       </c>
       <c r="E237" t="n">
-        <v>26.59146740458899</v>
+        <v>26.59146540442867</v>
       </c>
       <c r="F237" t="n">
         <v>1706000</v>
@@ -5172,16 +5172,16 @@
         <v>44442</v>
       </c>
       <c r="B238" t="n">
-        <v>25.03568077087402</v>
+        <v>25.03567886352539</v>
       </c>
       <c r="C238" t="n">
-        <v>25.84039874028232</v>
+        <v>25.84039677162608</v>
       </c>
       <c r="D238" t="n">
-        <v>24.80320638763689</v>
+        <v>24.80320449799936</v>
       </c>
       <c r="E238" t="n">
-        <v>25.57215998561969</v>
+        <v>25.57215803739928</v>
       </c>
       <c r="F238" t="n">
         <v>2369000</v>
@@ -5192,16 +5192,16 @@
         <v>44445</v>
       </c>
       <c r="B239" t="n">
-        <v>25.76886367797852</v>
+        <v>25.76886558532715</v>
       </c>
       <c r="C239" t="n">
-        <v>25.89404151368469</v>
+        <v>25.89404343029868</v>
       </c>
       <c r="D239" t="n">
-        <v>24.87473238197415</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="E239" t="n">
-        <v>24.87473238197415</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="F239" t="n">
         <v>528250</v>
@@ -5212,16 +5212,16 @@
         <v>44447</v>
       </c>
       <c r="B240" t="n">
-        <v>24.48131561279297</v>
+        <v>24.4813175201416</v>
       </c>
       <c r="C240" t="n">
-        <v>26.10863610235777</v>
+        <v>26.10863813649156</v>
       </c>
       <c r="D240" t="n">
-        <v>24.32037340234477</v>
+        <v>24.32037529715434</v>
       </c>
       <c r="E240" t="n">
-        <v>25.59003998757081</v>
+        <v>25.59004198130058</v>
       </c>
       <c r="F240" t="n">
         <v>1259500</v>
@@ -5232,16 +5232,16 @@
         <v>44448</v>
       </c>
       <c r="B241" t="n">
-        <v>25.03568077087402</v>
+        <v>25.03567886352539</v>
       </c>
       <c r="C241" t="n">
-        <v>25.75098525358797</v>
+        <v>25.75098329174372</v>
       </c>
       <c r="D241" t="n">
-        <v>23.80178011183736</v>
+        <v>23.8017782984937</v>
       </c>
       <c r="E241" t="n">
-        <v>23.99848841822859</v>
+        <v>23.99848658989868</v>
       </c>
       <c r="F241" t="n">
         <v>1540350</v>
@@ -5312,16 +5312,16 @@
         <v>44454</v>
       </c>
       <c r="B245" t="n">
-        <v>26.3232307434082</v>
+        <v>26.32322692871094</v>
       </c>
       <c r="C245" t="n">
-        <v>26.53782208983838</v>
+        <v>26.53781824404307</v>
       </c>
       <c r="D245" t="n">
-        <v>25.66157366556005</v>
+        <v>25.66156994674848</v>
       </c>
       <c r="E245" t="n">
-        <v>26.30534770485058</v>
+        <v>26.30534389274488</v>
       </c>
       <c r="F245" t="n">
         <v>552000</v>
@@ -5392,16 +5392,16 @@
         <v>44460</v>
       </c>
       <c r="B249" t="n">
-        <v>25.07144355773926</v>
+        <v>25.07144546508789</v>
       </c>
       <c r="C249" t="n">
-        <v>25.19662139943273</v>
+        <v>25.19662331630446</v>
       </c>
       <c r="D249" t="n">
-        <v>24.05213267185464</v>
+        <v>24.05213450165763</v>
       </c>
       <c r="E249" t="n">
-        <v>24.57072878012499</v>
+        <v>24.57073064938097</v>
       </c>
       <c r="F249" t="n">
         <v>662000</v>
@@ -5432,16 +5432,16 @@
         <v>44462</v>
       </c>
       <c r="B251" t="n">
-        <v>26.28746032714844</v>
+        <v>26.28746223449707</v>
       </c>
       <c r="C251" t="n">
-        <v>26.69876161898007</v>
+        <v>26.69876355617164</v>
       </c>
       <c r="D251" t="n">
-        <v>25.32179857489956</v>
+        <v>25.32180041218233</v>
       </c>
       <c r="E251" t="n">
-        <v>25.32179857489956</v>
+        <v>25.32180041218233</v>
       </c>
       <c r="F251" t="n">
         <v>1394250</v>
@@ -5472,16 +5472,16 @@
         <v>44466</v>
       </c>
       <c r="B253" t="n">
-        <v>26.01922416687012</v>
+        <v>26.01922225952148</v>
       </c>
       <c r="C253" t="n">
-        <v>26.34111031224558</v>
+        <v>26.34110838130097</v>
       </c>
       <c r="D253" t="n">
-        <v>25.57215846539613</v>
+        <v>25.57215659081981</v>
       </c>
       <c r="E253" t="n">
-        <v>26.21593246156736</v>
+        <v>26.21593053979895</v>
       </c>
       <c r="F253" t="n">
         <v>663500</v>
@@ -5512,16 +5512,16 @@
         <v>44468</v>
       </c>
       <c r="B255" t="n">
-        <v>24.67802429199219</v>
+        <v>24.67802810668945</v>
       </c>
       <c r="C255" t="n">
-        <v>25.39332865187945</v>
+        <v>25.39333257714754</v>
       </c>
       <c r="D255" t="n">
-        <v>24.46343298402601</v>
+        <v>24.46343676555203</v>
       </c>
       <c r="E255" t="n">
-        <v>25.10720690792455</v>
+        <v>25.10721078896431</v>
       </c>
       <c r="F255" t="n">
         <v>580300</v>
@@ -5532,16 +5532,16 @@
         <v>44469</v>
       </c>
       <c r="B256" t="n">
-        <v>24.44555282592773</v>
+        <v>24.4455509185791</v>
       </c>
       <c r="C256" t="n">
-        <v>24.89261852983216</v>
+        <v>24.89261658760151</v>
       </c>
       <c r="D256" t="n">
-        <v>24.0700175664312</v>
+        <v>24.07001568838347</v>
       </c>
       <c r="E256" t="n">
-        <v>24.85685245491806</v>
+        <v>24.85685051547803</v>
       </c>
       <c r="F256" t="n">
         <v>989250</v>
@@ -5552,16 +5552,16 @@
         <v>44470</v>
       </c>
       <c r="B257" t="n">
-        <v>25.03568077087402</v>
+        <v>25.03567886352539</v>
       </c>
       <c r="C257" t="n">
-        <v>25.10721121914542</v>
+        <v>25.10720930634723</v>
       </c>
       <c r="D257" t="n">
-        <v>24.23096280146573</v>
+        <v>24.2309609554247</v>
       </c>
       <c r="E257" t="n">
-        <v>24.74955897778844</v>
+        <v>24.74955709223806</v>
       </c>
       <c r="F257" t="n">
         <v>904400</v>
@@ -5572,16 +5572,16 @@
         <v>44473</v>
       </c>
       <c r="B258" t="n">
-        <v>23.87330627441406</v>
+        <v>23.8733081817627</v>
       </c>
       <c r="C258" t="n">
-        <v>25.10720671194305</v>
+        <v>25.10720871787369</v>
       </c>
       <c r="D258" t="n">
-        <v>23.87330627441406</v>
+        <v>23.8733081817627</v>
       </c>
       <c r="E258" t="n">
-        <v>25.01779324130006</v>
+        <v>25.01779524008704</v>
       </c>
       <c r="F258" t="n">
         <v>576500</v>
@@ -5612,16 +5612,16 @@
         <v>44475</v>
       </c>
       <c r="B260" t="n">
-        <v>23.60506820678711</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="C260" t="n">
-        <v>23.60506820678711</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="D260" t="n">
-        <v>22.37116764671513</v>
+        <v>22.37116583906875</v>
       </c>
       <c r="E260" t="n">
-        <v>22.97917726096693</v>
+        <v>22.97917540419186</v>
       </c>
       <c r="F260" t="n">
         <v>1199850</v>
@@ -5672,16 +5672,16 @@
         <v>44480</v>
       </c>
       <c r="B263" t="n">
-        <v>24.08789825439453</v>
+        <v>24.0879020690918</v>
       </c>
       <c r="C263" t="n">
-        <v>24.60649435212385</v>
+        <v>24.60649824894896</v>
       </c>
       <c r="D263" t="n">
-        <v>23.73024606723985</v>
+        <v>23.73024982529728</v>
       </c>
       <c r="E263" t="n">
-        <v>24.03424914725622</v>
+        <v>24.0342529534573</v>
       </c>
       <c r="F263" t="n">
         <v>770500</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35613632202148</v>
+        <v>24.35614013671875</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991024181488</v>
+        <v>24.99991415734105</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848414435849</v>
+        <v>23.99848790303969</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307545095629</v>
+        <v>24.21307924324713</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5752,16 +5752,16 @@
         <v>44487</v>
       </c>
       <c r="B267" t="n">
-        <v>26.28746032714844</v>
+        <v>26.28746223449707</v>
       </c>
       <c r="C267" t="n">
-        <v>27.37830162321745</v>
+        <v>27.37830360971465</v>
       </c>
       <c r="D267" t="n">
-        <v>25.69733379551969</v>
+        <v>25.6973356600503</v>
       </c>
       <c r="E267" t="n">
-        <v>26.60934814637144</v>
+        <v>26.6093500770754</v>
       </c>
       <c r="F267" t="n">
         <v>1715900</v>
@@ -5772,16 +5772,16 @@
         <v>44488</v>
       </c>
       <c r="B268" t="n">
-        <v>24.60649490356445</v>
+        <v>24.60649299621582</v>
       </c>
       <c r="C268" t="n">
-        <v>26.46628802386757</v>
+        <v>26.46628597235887</v>
       </c>
       <c r="D268" t="n">
-        <v>24.12366316102009</v>
+        <v>24.12366129109769</v>
       </c>
       <c r="E268" t="n">
-        <v>26.4305219516405</v>
+        <v>26.43051990290417</v>
       </c>
       <c r="F268" t="n">
         <v>1499450</v>
@@ -5832,16 +5832,16 @@
         <v>44491</v>
       </c>
       <c r="B271" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08362007141113</v>
       </c>
       <c r="C271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563458344404</v>
       </c>
       <c r="D271" t="n">
-        <v>19.81395151866856</v>
+        <v>19.81395331115565</v>
       </c>
       <c r="E271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563458344404</v>
       </c>
       <c r="F271" t="n">
         <v>3185950</v>
@@ -5872,16 +5872,16 @@
         <v>44495</v>
       </c>
       <c r="B273" t="n">
-        <v>20.29678344726562</v>
+        <v>20.29677963256836</v>
       </c>
       <c r="C273" t="n">
-        <v>21.53068402797473</v>
+        <v>21.5306799813709</v>
       </c>
       <c r="D273" t="n">
-        <v>20.17160389167173</v>
+        <v>20.17160010050145</v>
       </c>
       <c r="E273" t="n">
-        <v>21.45915358424406</v>
+        <v>21.45914955108409</v>
       </c>
       <c r="F273" t="n">
         <v>1532000</v>
@@ -5892,16 +5892,16 @@
         <v>44496</v>
       </c>
       <c r="B274" t="n">
-        <v>20.49349403381348</v>
+        <v>20.49349021911621</v>
       </c>
       <c r="C274" t="n">
-        <v>21.10150372625343</v>
+        <v>21.1014997983801</v>
       </c>
       <c r="D274" t="n">
-        <v>20.31466705177096</v>
+        <v>20.31466327036089</v>
       </c>
       <c r="E274" t="n">
-        <v>20.42196358208057</v>
+        <v>20.42195978069811</v>
       </c>
       <c r="F274" t="n">
         <v>1013650</v>
@@ -5912,16 +5912,16 @@
         <v>44497</v>
       </c>
       <c r="B275" t="n">
-        <v>19.29535675048828</v>
+        <v>19.29535484313965</v>
       </c>
       <c r="C275" t="n">
-        <v>20.76173179245886</v>
+        <v>20.76172974015886</v>
       </c>
       <c r="D275" t="n">
-        <v>19.29535675048828</v>
+        <v>19.29535484313965</v>
       </c>
       <c r="E275" t="n">
-        <v>20.74385045946002</v>
+        <v>20.74384840892759</v>
       </c>
       <c r="F275" t="n">
         <v>1280700</v>
@@ -6052,16 +6052,16 @@
         <v>44509</v>
       </c>
       <c r="B282" t="n">
-        <v>20.67231941223145</v>
+        <v>20.67232131958008</v>
       </c>
       <c r="C282" t="n">
-        <v>21.36974083617073</v>
+        <v>21.36974280786753</v>
       </c>
       <c r="D282" t="n">
-        <v>20.29678414341015</v>
+        <v>20.29678601610971</v>
       </c>
       <c r="E282" t="n">
-        <v>20.29678414341015</v>
+        <v>20.29678601610971</v>
       </c>
       <c r="F282" t="n">
         <v>912150</v>
@@ -6072,16 +6072,16 @@
         <v>44510</v>
       </c>
       <c r="B283" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08362007141113</v>
       </c>
       <c r="C283" t="n">
-        <v>21.65586170945009</v>
+        <v>21.65586366856726</v>
       </c>
       <c r="D283" t="n">
-        <v>20.49349158152647</v>
+        <v>20.49349343548877</v>
       </c>
       <c r="E283" t="n">
-        <v>20.88690987169059</v>
+        <v>20.88691176124383</v>
       </c>
       <c r="F283" t="n">
         <v>1309800</v>
@@ -6092,16 +6092,16 @@
         <v>44511</v>
       </c>
       <c r="B284" t="n">
-        <v>21.94198608398438</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C284" t="n">
-        <v>22.99705973754176</v>
+        <v>22.99705773847886</v>
       </c>
       <c r="D284" t="n">
-        <v>21.78104215391382</v>
+        <v>21.78104026055555</v>
       </c>
       <c r="E284" t="n">
-        <v>21.95986741644305</v>
+        <v>21.95986550754004</v>
       </c>
       <c r="F284" t="n">
         <v>2031350</v>
@@ -6112,16 +6112,16 @@
         <v>44512</v>
       </c>
       <c r="B285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08362007141113</v>
       </c>
       <c r="C285" t="n">
-        <v>22.12081044278765</v>
+        <v>22.12081244396683</v>
       </c>
       <c r="D285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08362007141113</v>
       </c>
       <c r="E285" t="n">
-        <v>21.76315822692041</v>
+        <v>21.76316019574425</v>
       </c>
       <c r="F285" t="n">
         <v>1307150</v>
@@ -6132,16 +6132,16 @@
         <v>44516</v>
       </c>
       <c r="B286" t="n">
-        <v>20.63655090332031</v>
+        <v>20.63655281066895</v>
       </c>
       <c r="C286" t="n">
-        <v>21.87045138086964</v>
+        <v>21.87045340226245</v>
       </c>
       <c r="D286" t="n">
-        <v>19.77818565031559</v>
+        <v>19.77818747832918</v>
       </c>
       <c r="E286" t="n">
-        <v>21.76315657695413</v>
+        <v>21.76315858843013</v>
       </c>
       <c r="F286" t="n">
         <v>1709550</v>
@@ -6172,16 +6172,16 @@
         <v>44518</v>
       </c>
       <c r="B288" t="n">
-        <v>20.33254814147949</v>
+        <v>20.33254623413086</v>
       </c>
       <c r="C288" t="n">
-        <v>20.7080834034243</v>
+        <v>20.70808146084758</v>
       </c>
       <c r="D288" t="n">
-        <v>19.68877413761139</v>
+        <v>19.68877229065369</v>
       </c>
       <c r="E288" t="n">
-        <v>19.68877413761139</v>
+        <v>19.68877229065369</v>
       </c>
       <c r="F288" t="n">
         <v>766850</v>
@@ -6212,16 +6212,16 @@
         <v>44522</v>
       </c>
       <c r="B290" t="n">
-        <v>20.18948745727539</v>
+        <v>20.18948554992676</v>
       </c>
       <c r="C290" t="n">
-        <v>21.44127110802875</v>
+        <v>21.44126908242115</v>
       </c>
       <c r="D290" t="n">
-        <v>19.97489612046799</v>
+        <v>19.97489423339231</v>
       </c>
       <c r="E290" t="n">
-        <v>20.869027543209</v>
+        <v>20.86902557166261</v>
       </c>
       <c r="F290" t="n">
         <v>852100</v>
@@ -6232,16 +6232,16 @@
         <v>44523</v>
       </c>
       <c r="B291" t="n">
-        <v>19.2417049407959</v>
+        <v>19.24170684814453</v>
       </c>
       <c r="C291" t="n">
-        <v>20.45772228310068</v>
+        <v>20.45772431098796</v>
       </c>
       <c r="D291" t="n">
-        <v>19.02711364509506</v>
+        <v>19.02711553117216</v>
       </c>
       <c r="E291" t="n">
-        <v>20.20736662415971</v>
+        <v>20.20736862723029</v>
       </c>
       <c r="F291" t="n">
         <v>1896750</v>
@@ -6252,16 +6252,16 @@
         <v>44524</v>
       </c>
       <c r="B292" t="n">
-        <v>19.58147621154785</v>
+        <v>19.58147811889648</v>
       </c>
       <c r="C292" t="n">
-        <v>20.33254668150708</v>
+        <v>20.3325486620143</v>
       </c>
       <c r="D292" t="n">
-        <v>19.02711572993332</v>
+        <v>19.02711758328404</v>
       </c>
       <c r="E292" t="n">
-        <v>19.04499706080266</v>
+        <v>19.04499891589514</v>
       </c>
       <c r="F292" t="n">
         <v>1594900</v>
@@ -6272,16 +6272,16 @@
         <v>44525</v>
       </c>
       <c r="B293" t="n">
-        <v>20.29678344726562</v>
+        <v>20.29677963256836</v>
       </c>
       <c r="C293" t="n">
-        <v>20.43984433472696</v>
+        <v>20.43984049314199</v>
       </c>
       <c r="D293" t="n">
-        <v>19.65300774826931</v>
+        <v>19.65300405456705</v>
       </c>
       <c r="E293" t="n">
-        <v>19.65300774826931</v>
+        <v>19.65300405456705</v>
       </c>
       <c r="F293" t="n">
         <v>787900</v>
@@ -6292,16 +6292,16 @@
         <v>44526</v>
       </c>
       <c r="B294" t="n">
-        <v>19.76030540466309</v>
+        <v>19.76030349731445</v>
       </c>
       <c r="C294" t="n">
-        <v>19.90336630036396</v>
+        <v>19.90336437920648</v>
       </c>
       <c r="D294" t="n">
-        <v>19.18806011643918</v>
+        <v>19.18805826432609</v>
       </c>
       <c r="E294" t="n">
-        <v>19.65300888017723</v>
+        <v>19.65300698318531</v>
       </c>
       <c r="F294" t="n">
         <v>1033400</v>
@@ -6312,16 +6312,16 @@
         <v>44529</v>
       </c>
       <c r="B295" t="n">
-        <v>19.2059440612793</v>
+        <v>19.20594024658203</v>
       </c>
       <c r="C295" t="n">
-        <v>20.33254994716491</v>
+        <v>20.33254590870044</v>
       </c>
       <c r="D295" t="n">
-        <v>19.06288315882593</v>
+        <v>19.06287937254352</v>
       </c>
       <c r="E295" t="n">
-        <v>20.33254994716491</v>
+        <v>20.33254590870044</v>
       </c>
       <c r="F295" t="n">
         <v>830750</v>
@@ -6332,16 +6332,16 @@
         <v>44530</v>
       </c>
       <c r="B296" t="n">
-        <v>18.83040428161621</v>
+        <v>18.83040618896484</v>
       </c>
       <c r="C296" t="n">
-        <v>19.25958859218866</v>
+        <v>19.25959054300976</v>
       </c>
       <c r="D296" t="n">
-        <v>18.06145254040656</v>
+        <v>18.06145436986738</v>
       </c>
       <c r="E296" t="n">
-        <v>19.0449955841924</v>
+        <v>19.04499751327718</v>
       </c>
       <c r="F296" t="n">
         <v>1327800</v>
@@ -6392,16 +6392,16 @@
         <v>44533</v>
       </c>
       <c r="B299" t="n">
-        <v>19.76030540466309</v>
+        <v>19.76030349731445</v>
       </c>
       <c r="C299" t="n">
-        <v>20.20737113008343</v>
+        <v>20.20736917958211</v>
       </c>
       <c r="D299" t="n">
-        <v>18.77676046765426</v>
+        <v>18.77675865524156</v>
       </c>
       <c r="E299" t="n">
-        <v>18.77676046765426</v>
+        <v>18.77675865524156</v>
       </c>
       <c r="F299" t="n">
         <v>1496100</v>
@@ -6452,16 +6452,16 @@
         <v>44538</v>
       </c>
       <c r="B302" t="n">
-        <v>21.42338562011719</v>
+        <v>21.42338752746582</v>
       </c>
       <c r="C302" t="n">
-        <v>21.51279909324929</v>
+        <v>21.51280100855851</v>
       </c>
       <c r="D302" t="n">
-        <v>19.86759732713109</v>
+        <v>19.86759909596611</v>
       </c>
       <c r="E302" t="n">
-        <v>20.18948514823861</v>
+        <v>20.18948694573167</v>
       </c>
       <c r="F302" t="n">
         <v>984450</v>
@@ -6492,16 +6492,16 @@
         <v>44540</v>
       </c>
       <c r="B304" t="n">
-        <v>21.81680488586426</v>
+        <v>21.81680297851562</v>
       </c>
       <c r="C304" t="n">
-        <v>22.19234012602034</v>
+        <v>22.19233818584029</v>
       </c>
       <c r="D304" t="n">
-        <v>21.06573440555209</v>
+        <v>21.06573256386629</v>
       </c>
       <c r="E304" t="n">
-        <v>22.1386927218324</v>
+        <v>22.1386907863425</v>
       </c>
       <c r="F304" t="n">
         <v>899500</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78104019165039</v>
+        <v>21.78104209899902</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422762443386</v>
+        <v>22.51422959598714</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550495712469</v>
+        <v>21.40550683158799</v>
       </c>
       <c r="E305" t="n">
-        <v>22.13869238990815</v>
+        <v>22.13869432857611</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6552,16 +6552,16 @@
         <v>44545</v>
       </c>
       <c r="B307" t="n">
-        <v>22.03139686584473</v>
+        <v>22.03139877319336</v>
       </c>
       <c r="C307" t="n">
-        <v>22.37116774849373</v>
+        <v>22.37116968525772</v>
       </c>
       <c r="D307" t="n">
-        <v>21.11938414573805</v>
+        <v>21.11938597412999</v>
       </c>
       <c r="E307" t="n">
-        <v>21.45915332296677</v>
+        <v>21.45915518077393</v>
       </c>
       <c r="F307" t="n">
         <v>1028800</v>
@@ -6572,16 +6572,16 @@
         <v>44546</v>
       </c>
       <c r="B308" t="n">
-        <v>21.94198608398438</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C308" t="n">
-        <v>22.97917840508309</v>
+        <v>22.97917640757456</v>
       </c>
       <c r="D308" t="n">
-        <v>21.53068473986848</v>
+        <v>21.53068286827299</v>
       </c>
       <c r="E308" t="n">
-        <v>22.5321126906295</v>
+        <v>22.53211073198299</v>
       </c>
       <c r="F308" t="n">
         <v>888550</v>
@@ -6592,16 +6592,16 @@
         <v>44547</v>
       </c>
       <c r="B309" t="n">
-        <v>22.37116813659668</v>
+        <v>22.37116622924805</v>
       </c>
       <c r="C309" t="n">
-        <v>22.72882035710008</v>
+        <v>22.72881841925829</v>
       </c>
       <c r="D309" t="n">
-        <v>21.42338762048728</v>
+        <v>21.42338579394568</v>
       </c>
       <c r="E309" t="n">
-        <v>21.56645021410895</v>
+        <v>21.56644837536995</v>
       </c>
       <c r="F309" t="n">
         <v>2194100</v>
@@ -6632,16 +6632,16 @@
         <v>44551</v>
       </c>
       <c r="B311" t="n">
-        <v>21.38762283325195</v>
+        <v>21.38762474060059</v>
       </c>
       <c r="C311" t="n">
-        <v>22.19234074001621</v>
+        <v>22.1923427191296</v>
       </c>
       <c r="D311" t="n">
-        <v>21.38762283325195</v>
+        <v>21.38762474060059</v>
       </c>
       <c r="E311" t="n">
-        <v>22.0313968175793</v>
+        <v>22.03139878233971</v>
       </c>
       <c r="F311" t="n">
         <v>785250</v>
@@ -6652,16 +6652,16 @@
         <v>44552</v>
       </c>
       <c r="B312" t="n">
-        <v>21.45915603637695</v>
+        <v>21.45915222167969</v>
       </c>
       <c r="C312" t="n">
-        <v>21.78104392265717</v>
+        <v>21.78104005073934</v>
       </c>
       <c r="D312" t="n">
-        <v>20.65443802609692</v>
+        <v>20.65443435445074</v>
       </c>
       <c r="E312" t="n">
-        <v>21.42338995771449</v>
+        <v>21.42338614937519</v>
       </c>
       <c r="F312" t="n">
         <v>1154200</v>
@@ -6672,16 +6672,16 @@
         <v>44553</v>
       </c>
       <c r="B313" t="n">
-        <v>21.17615127563477</v>
+        <v>21.17614936828613</v>
       </c>
       <c r="C313" t="n">
-        <v>21.69924183626969</v>
+        <v>21.69923988180597</v>
       </c>
       <c r="D313" t="n">
-        <v>20.79736144067842</v>
+        <v>20.79735956744761</v>
       </c>
       <c r="E313" t="n">
-        <v>21.69924183626969</v>
+        <v>21.69923988180597</v>
       </c>
       <c r="F313" t="n">
         <v>605250</v>
@@ -6732,16 +6732,16 @@
         <v>44559</v>
       </c>
       <c r="B316" t="n">
-        <v>20.29230880737305</v>
+        <v>20.29231071472168</v>
       </c>
       <c r="C316" t="n">
-        <v>20.90558774878349</v>
+        <v>20.90558971377646</v>
       </c>
       <c r="D316" t="n">
-        <v>20.05781969917492</v>
+        <v>20.05782158448306</v>
       </c>
       <c r="E316" t="n">
-        <v>20.70717296173873</v>
+        <v>20.70717490808197</v>
       </c>
       <c r="F316" t="n">
         <v>541350</v>
@@ -6752,16 +6752,16 @@
         <v>44560</v>
       </c>
       <c r="B317" t="n">
-        <v>21.06793022155762</v>
+        <v>21.06792640686035</v>
       </c>
       <c r="C317" t="n">
-        <v>21.15811690049597</v>
+        <v>21.15811306946891</v>
       </c>
       <c r="D317" t="n">
-        <v>19.93156052088792</v>
+        <v>19.93155691194919</v>
       </c>
       <c r="E317" t="n">
-        <v>20.29231239724323</v>
+        <v>20.2923087229844</v>
       </c>
       <c r="F317" t="n">
         <v>1399700</v>
@@ -6772,16 +6772,16 @@
         <v>44564</v>
       </c>
       <c r="B318" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C318" t="n">
-        <v>21.32045357690026</v>
+        <v>21.32045154948475</v>
       </c>
       <c r="D318" t="n">
-        <v>19.8774462134759</v>
+        <v>19.87744432327959</v>
       </c>
       <c r="E318" t="n">
-        <v>21.26634123082196</v>
+        <v>21.26633920855213</v>
       </c>
       <c r="F318" t="n">
         <v>905200</v>
@@ -6892,16 +6892,16 @@
         <v>44572</v>
       </c>
       <c r="B324" t="n">
-        <v>16.77497673034668</v>
+        <v>16.77497482299805</v>
       </c>
       <c r="C324" t="n">
-        <v>17.04554017752951</v>
+        <v>17.04553823941727</v>
       </c>
       <c r="D324" t="n">
-        <v>16.1797357703841</v>
+        <v>16.17973393071556</v>
       </c>
       <c r="E324" t="n">
-        <v>16.19777207204929</v>
+        <v>16.19777023032999</v>
       </c>
       <c r="F324" t="n">
         <v>629400</v>
@@ -6912,16 +6912,16 @@
         <v>44573</v>
       </c>
       <c r="B325" t="n">
-        <v>17.53255462646484</v>
+        <v>17.53255653381348</v>
       </c>
       <c r="C325" t="n">
-        <v>17.69489336600067</v>
+        <v>17.69489529100997</v>
       </c>
       <c r="D325" t="n">
-        <v>16.70282462899304</v>
+        <v>16.7028264460762</v>
       </c>
       <c r="E325" t="n">
-        <v>16.86516336852887</v>
+        <v>16.86516520327269</v>
       </c>
       <c r="F325" t="n">
         <v>1172500</v>
@@ -6972,16 +6972,16 @@
         <v>44578</v>
       </c>
       <c r="B328" t="n">
-        <v>16.88320159912109</v>
+        <v>16.88319969177246</v>
       </c>
       <c r="C328" t="n">
-        <v>17.11769072524505</v>
+        <v>17.11768879140545</v>
       </c>
       <c r="D328" t="n">
-        <v>16.6306761711418</v>
+        <v>16.63067429232176</v>
       </c>
       <c r="E328" t="n">
-        <v>16.86516529726576</v>
+        <v>16.86516339195475</v>
       </c>
       <c r="F328" t="n">
         <v>496050</v>
@@ -6992,16 +6992,16 @@
         <v>44579</v>
       </c>
       <c r="B329" t="n">
-        <v>16.30599594116211</v>
+        <v>16.30599784851074</v>
       </c>
       <c r="C329" t="n">
-        <v>16.79301213441261</v>
+        <v>16.79301409872861</v>
       </c>
       <c r="D329" t="n">
-        <v>16.07150685406374</v>
+        <v>16.07150873398366</v>
       </c>
       <c r="E329" t="n">
-        <v>16.73889807725132</v>
+        <v>16.73890003523749</v>
       </c>
       <c r="F329" t="n">
         <v>670850</v>
@@ -7012,16 +7012,16 @@
         <v>44580</v>
       </c>
       <c r="B330" t="n">
-        <v>16.41422462463379</v>
+        <v>16.41422653198242</v>
       </c>
       <c r="C330" t="n">
-        <v>16.72086411051511</v>
+        <v>16.72086605349554</v>
       </c>
       <c r="D330" t="n">
-        <v>16.19777180619957</v>
+        <v>16.19777368839618</v>
       </c>
       <c r="E330" t="n">
-        <v>16.41422462463379</v>
+        <v>16.41422653198242</v>
       </c>
       <c r="F330" t="n">
         <v>847250</v>
@@ -7032,16 +7032,16 @@
         <v>44581</v>
       </c>
       <c r="B331" t="n">
-        <v>17.4243278503418</v>
+        <v>17.42432975769043</v>
       </c>
       <c r="C331" t="n">
-        <v>18.12779513306872</v>
+        <v>18.12779711742218</v>
       </c>
       <c r="D331" t="n">
-        <v>16.48637319357279</v>
+        <v>16.48637499824851</v>
       </c>
       <c r="E331" t="n">
-        <v>16.48637319357279</v>
+        <v>16.48637499824851</v>
       </c>
       <c r="F331" t="n">
         <v>2219300</v>
@@ -7072,16 +7072,16 @@
         <v>44585</v>
       </c>
       <c r="B333" t="n">
-        <v>17.85723304748535</v>
+        <v>17.85722923278809</v>
       </c>
       <c r="C333" t="n">
-        <v>18.09172218175017</v>
+        <v>18.09171831696088</v>
       </c>
       <c r="D333" t="n">
-        <v>17.47844317216533</v>
+        <v>17.47843943838591</v>
       </c>
       <c r="E333" t="n">
-        <v>18.09172218175017</v>
+        <v>18.09171831696088</v>
       </c>
       <c r="F333" t="n">
         <v>692150</v>
@@ -7112,16 +7112,16 @@
         <v>44587</v>
       </c>
       <c r="B335" t="n">
-        <v>19.35435485839844</v>
+        <v>19.35435104370117</v>
       </c>
       <c r="C335" t="n">
-        <v>19.80529511198872</v>
+        <v>19.8052912084122</v>
       </c>
       <c r="D335" t="n">
-        <v>18.84930225603348</v>
+        <v>18.84929854088088</v>
       </c>
       <c r="E335" t="n">
-        <v>18.9214526277999</v>
+        <v>18.92144889842664</v>
       </c>
       <c r="F335" t="n">
         <v>1494250</v>
@@ -7132,16 +7132,16 @@
         <v>44588</v>
       </c>
       <c r="B336" t="n">
-        <v>19.33631706237793</v>
+        <v>19.33631896972656</v>
       </c>
       <c r="C336" t="n">
-        <v>19.91351999193534</v>
+        <v>19.9135219562197</v>
       </c>
       <c r="D336" t="n">
-        <v>19.08378992059635</v>
+        <v>19.08379180303552</v>
       </c>
       <c r="E336" t="n">
-        <v>19.64295654875541</v>
+        <v>19.64295848635119</v>
       </c>
       <c r="F336" t="n">
         <v>815000</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96763229370117</v>
+        <v>19.96763038635254</v>
       </c>
       <c r="C338" t="n">
-        <v>20.27427177942092</v>
+        <v>20.27426984278146</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44454170986168</v>
+        <v>19.44453985247972</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706885110159</v>
+        <v>19.69706696959773</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7192,16 +7192,16 @@
         <v>44593</v>
       </c>
       <c r="B339" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C339" t="n">
-        <v>20.38249879067443</v>
+        <v>20.38249685245139</v>
       </c>
       <c r="D339" t="n">
-        <v>19.75118177902592</v>
+        <v>19.75117990083641</v>
       </c>
       <c r="E339" t="n">
-        <v>20.29231040041029</v>
+        <v>20.29230847076349</v>
       </c>
       <c r="F339" t="n">
         <v>629350</v>
@@ -7212,16 +7212,16 @@
         <v>44594</v>
       </c>
       <c r="B340" t="n">
-        <v>20.22015953063965</v>
+        <v>20.22015762329102</v>
       </c>
       <c r="C340" t="n">
-        <v>20.86951282807217</v>
+        <v>20.86951085947065</v>
       </c>
       <c r="D340" t="n">
-        <v>19.85940769873269</v>
+        <v>19.85940582541344</v>
       </c>
       <c r="E340" t="n">
-        <v>20.25623385373013</v>
+        <v>20.25623194297864</v>
       </c>
       <c r="F340" t="n">
         <v>1270900</v>
@@ -7232,16 +7232,16 @@
         <v>44595</v>
       </c>
       <c r="B341" t="n">
-        <v>20.12996864318848</v>
+        <v>20.12997245788574</v>
       </c>
       <c r="C341" t="n">
-        <v>20.67109718396025</v>
+        <v>20.67110110120321</v>
       </c>
       <c r="D341" t="n">
-        <v>19.93155559032558</v>
+        <v>19.9315593674229</v>
       </c>
       <c r="E341" t="n">
-        <v>20.43660809228581</v>
+        <v>20.43661196509229</v>
       </c>
       <c r="F341" t="n">
         <v>747450</v>
@@ -7252,16 +7252,16 @@
         <v>44596</v>
       </c>
       <c r="B342" t="n">
-        <v>19.4084644317627</v>
+        <v>19.40846633911133</v>
       </c>
       <c r="C342" t="n">
-        <v>20.18408031854456</v>
+        <v>20.18408230211611</v>
       </c>
       <c r="D342" t="n">
-        <v>19.26416372165443</v>
+        <v>19.26416561482205</v>
       </c>
       <c r="E342" t="n">
-        <v>20.18408031854456</v>
+        <v>20.18408230211611</v>
       </c>
       <c r="F342" t="n">
         <v>774000</v>
@@ -7272,16 +7272,16 @@
         <v>44599</v>
       </c>
       <c r="B343" t="n">
-        <v>19.73314094543457</v>
+        <v>19.73314476013184</v>
       </c>
       <c r="C343" t="n">
-        <v>19.94959373930937</v>
+        <v>19.94959759585004</v>
       </c>
       <c r="D343" t="n">
-        <v>19.0657497048879</v>
+        <v>19.06575339056894</v>
       </c>
       <c r="E343" t="n">
-        <v>19.31827681760835</v>
+        <v>19.31828055210647</v>
       </c>
       <c r="F343" t="n">
         <v>708000</v>
@@ -7292,16 +7292,16 @@
         <v>44600</v>
       </c>
       <c r="B344" t="n">
-        <v>19.46257972717285</v>
+        <v>19.46257781982422</v>
       </c>
       <c r="C344" t="n">
-        <v>20.03978265536617</v>
+        <v>20.03978069145118</v>
       </c>
       <c r="D344" t="n">
-        <v>19.40846738270483</v>
+        <v>19.40846548065925</v>
       </c>
       <c r="E344" t="n">
-        <v>19.6609928036892</v>
+        <v>19.66099087689592</v>
       </c>
       <c r="F344" t="n">
         <v>697700</v>
@@ -7312,16 +7312,16 @@
         <v>44601</v>
       </c>
       <c r="B345" t="n">
-        <v>19.91351890563965</v>
+        <v>19.91351699829102</v>
       </c>
       <c r="C345" t="n">
-        <v>20.18408233406016</v>
+        <v>20.18408040079654</v>
       </c>
       <c r="D345" t="n">
-        <v>19.42650439044265</v>
+        <v>19.42650252974105</v>
       </c>
       <c r="E345" t="n">
-        <v>19.48061673208669</v>
+        <v>19.48061486620212</v>
       </c>
       <c r="F345" t="n">
         <v>427500</v>
@@ -7332,16 +7332,16 @@
         <v>44602</v>
       </c>
       <c r="B346" t="n">
-        <v>19.98566818237305</v>
+        <v>19.98567008972168</v>
       </c>
       <c r="C346" t="n">
-        <v>20.59894708836287</v>
+        <v>20.59894905424028</v>
       </c>
       <c r="D346" t="n">
-        <v>19.82332944605806</v>
+        <v>19.82333133791377</v>
       </c>
       <c r="E346" t="n">
-        <v>20.18408123775789</v>
+        <v>20.18408316404224</v>
       </c>
       <c r="F346" t="n">
         <v>563100</v>
@@ -7372,16 +7372,16 @@
         <v>44606</v>
       </c>
       <c r="B348" t="n">
-        <v>20.00370597839355</v>
+        <v>20.00370788574219</v>
       </c>
       <c r="C348" t="n">
-        <v>20.1480066934604</v>
+        <v>20.14800861456807</v>
       </c>
       <c r="D348" t="n">
-        <v>19.26416438362593</v>
+        <v>19.26416622045944</v>
       </c>
       <c r="E348" t="n">
-        <v>19.26416438362593</v>
+        <v>19.26416622045944</v>
       </c>
       <c r="F348" t="n">
         <v>683300</v>
@@ -7392,16 +7392,16 @@
         <v>44607</v>
       </c>
       <c r="B349" t="n">
-        <v>20.52679634094238</v>
+        <v>20.52679824829102</v>
       </c>
       <c r="C349" t="n">
-        <v>20.70717137327322</v>
+        <v>20.70717329738229</v>
       </c>
       <c r="D349" t="n">
-        <v>20.11193049820109</v>
+        <v>20.11193236700041</v>
       </c>
       <c r="E349" t="n">
-        <v>20.2021188744666</v>
+        <v>20.20212075164623</v>
       </c>
       <c r="F349" t="n">
         <v>560950</v>
@@ -7412,16 +7412,16 @@
         <v>44608</v>
       </c>
       <c r="B350" t="n">
-        <v>20.74324989318848</v>
+        <v>20.74324798583984</v>
       </c>
       <c r="C350" t="n">
-        <v>20.76128791463935</v>
+        <v>20.76128600563211</v>
       </c>
       <c r="D350" t="n">
-        <v>20.27427165666829</v>
+        <v>20.27426979244236</v>
       </c>
       <c r="E350" t="n">
-        <v>20.74324989318848</v>
+        <v>20.74324798583984</v>
       </c>
       <c r="F350" t="n">
         <v>576900</v>
@@ -7432,16 +7432,16 @@
         <v>44609</v>
       </c>
       <c r="B351" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C351" t="n">
-        <v>20.72521260943759</v>
+        <v>20.72521063862504</v>
       </c>
       <c r="D351" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="E351" t="n">
-        <v>20.72521260943759</v>
+        <v>20.72521063862504</v>
       </c>
       <c r="F351" t="n">
         <v>544250</v>
@@ -7452,16 +7452,16 @@
         <v>44610</v>
       </c>
       <c r="B352" t="n">
-        <v>19.93155860900879</v>
+        <v>19.93155670166016</v>
       </c>
       <c r="C352" t="n">
-        <v>20.5087615558107</v>
+        <v>20.50875959322669</v>
       </c>
       <c r="D352" t="n">
-        <v>19.64295713560783</v>
+        <v>19.64295525587689</v>
       </c>
       <c r="E352" t="n">
-        <v>20.47268723173582</v>
+        <v>20.47268527260393</v>
       </c>
       <c r="F352" t="n">
         <v>904300</v>
@@ -7472,16 +7472,16 @@
         <v>44613</v>
       </c>
       <c r="B353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892242431641</v>
       </c>
       <c r="C353" t="n">
-        <v>19.94959452481559</v>
+        <v>19.94959248662468</v>
       </c>
       <c r="D353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892242431641</v>
       </c>
       <c r="E353" t="n">
-        <v>19.85940614385</v>
+        <v>19.85940411487337</v>
       </c>
       <c r="F353" t="n">
         <v>728950</v>
@@ -7512,16 +7512,16 @@
         <v>44615</v>
       </c>
       <c r="B355" t="n">
-        <v>19.6609935760498</v>
+        <v>19.66098976135254</v>
       </c>
       <c r="C355" t="n">
-        <v>20.49072367802294</v>
+        <v>20.49071970233843</v>
       </c>
       <c r="D355" t="n">
-        <v>19.55276888286228</v>
+        <v>19.55276508916316</v>
       </c>
       <c r="E355" t="n">
-        <v>19.85940838056108</v>
+        <v>19.85940452736665</v>
       </c>
       <c r="F355" t="n">
         <v>1327750</v>
@@ -7532,16 +7532,16 @@
         <v>44616</v>
       </c>
       <c r="B356" t="n">
-        <v>19.33631706237793</v>
+        <v>19.33631896972656</v>
       </c>
       <c r="C356" t="n">
-        <v>19.42650545017138</v>
+        <v>19.42650736641626</v>
       </c>
       <c r="D356" t="n">
-        <v>18.27209787085614</v>
+        <v>18.2720996732294</v>
       </c>
       <c r="E356" t="n">
-        <v>18.52462501263771</v>
+        <v>18.52462683992044</v>
       </c>
       <c r="F356" t="n">
         <v>1831750</v>
@@ -7552,16 +7552,16 @@
         <v>44617</v>
       </c>
       <c r="B357" t="n">
-        <v>19.02967643737793</v>
+        <v>19.02967834472656</v>
       </c>
       <c r="C357" t="n">
-        <v>19.62491735291844</v>
+        <v>19.62491931992821</v>
       </c>
       <c r="D357" t="n">
-        <v>18.6508866074703</v>
+        <v>18.65088847685275</v>
       </c>
       <c r="E357" t="n">
-        <v>19.28220184384947</v>
+        <v>19.28220377650878</v>
       </c>
       <c r="F357" t="n">
         <v>1262850</v>
@@ -7572,16 +7572,16 @@
         <v>44622</v>
       </c>
       <c r="B358" t="n">
-        <v>18.83126258850098</v>
+        <v>18.83126068115234</v>
       </c>
       <c r="C358" t="n">
-        <v>18.90341295396648</v>
+        <v>18.90341103931001</v>
       </c>
       <c r="D358" t="n">
-        <v>18.23602164336046</v>
+        <v>18.23601979630157</v>
       </c>
       <c r="E358" t="n">
-        <v>18.74107592181939</v>
+        <v>18.74107402360544</v>
       </c>
       <c r="F358" t="n">
         <v>1044650</v>
@@ -7592,16 +7592,16 @@
         <v>44623</v>
       </c>
       <c r="B359" t="n">
-        <v>18.57873725891113</v>
+        <v>18.5787353515625</v>
       </c>
       <c r="C359" t="n">
-        <v>19.46257967016855</v>
+        <v>19.46257767208202</v>
       </c>
       <c r="D359" t="n">
-        <v>18.54266121590451</v>
+        <v>18.54265931225955</v>
       </c>
       <c r="E359" t="n">
-        <v>18.72303799053682</v>
+        <v>18.72303606837384</v>
       </c>
       <c r="F359" t="n">
         <v>930450</v>
@@ -7612,16 +7612,16 @@
         <v>44624</v>
       </c>
       <c r="B360" t="n">
-        <v>17.91134452819824</v>
+        <v>17.91134643554688</v>
       </c>
       <c r="C360" t="n">
-        <v>18.75911082938567</v>
+        <v>18.7591128270115</v>
       </c>
       <c r="D360" t="n">
-        <v>17.55059100747137</v>
+        <v>17.55059287640398</v>
       </c>
       <c r="E360" t="n">
-        <v>18.57873578922251</v>
+        <v>18.5787377676405</v>
       </c>
       <c r="F360" t="n">
         <v>1669200</v>
@@ -7632,16 +7632,16 @@
         <v>44627</v>
       </c>
       <c r="B361" t="n">
-        <v>16.77497673034668</v>
+        <v>16.77497482299805</v>
       </c>
       <c r="C361" t="n">
-        <v>18.00153297380269</v>
+        <v>18.00153092699214</v>
       </c>
       <c r="D361" t="n">
-        <v>16.77497673034668</v>
+        <v>16.77497482299805</v>
       </c>
       <c r="E361" t="n">
-        <v>17.60470681396126</v>
+        <v>17.60470481227065</v>
       </c>
       <c r="F361" t="n">
         <v>1173850</v>
@@ -7652,16 +7652,16 @@
         <v>44628</v>
       </c>
       <c r="B362" t="n">
-        <v>17.38825416564941</v>
+        <v>17.38825607299805</v>
       </c>
       <c r="C362" t="n">
-        <v>17.58666722792311</v>
+        <v>17.58666915703602</v>
       </c>
       <c r="D362" t="n">
-        <v>16.54048613557037</v>
+        <v>16.54048794992582</v>
       </c>
       <c r="E362" t="n">
-        <v>16.84712559921172</v>
+        <v>16.847127447203</v>
       </c>
       <c r="F362" t="n">
         <v>1040800</v>
@@ -7672,16 +7672,16 @@
         <v>44629</v>
       </c>
       <c r="B363" t="n">
-        <v>18.23602104187012</v>
+        <v>18.23602294921875</v>
       </c>
       <c r="C363" t="n">
-        <v>18.36228546742039</v>
+        <v>18.36228738797532</v>
       </c>
       <c r="D363" t="n">
-        <v>17.51451741101287</v>
+        <v>17.51451924289774</v>
       </c>
       <c r="E363" t="n">
-        <v>17.53255543183439</v>
+        <v>17.5325572656059</v>
       </c>
       <c r="F363" t="n">
         <v>713800</v>
@@ -7712,16 +7712,16 @@
         <v>44631</v>
       </c>
       <c r="B365" t="n">
-        <v>17.22591590881348</v>
+        <v>17.22591781616211</v>
       </c>
       <c r="C365" t="n">
-        <v>18.4524720777208</v>
+        <v>18.45247412088051</v>
       </c>
       <c r="D365" t="n">
-        <v>17.02750112075174</v>
+        <v>17.02750300613079</v>
       </c>
       <c r="E365" t="n">
-        <v>18.30817135196699</v>
+        <v>18.30817337914893</v>
       </c>
       <c r="F365" t="n">
         <v>837400</v>
@@ -7752,16 +7752,16 @@
         <v>44635</v>
       </c>
       <c r="B367" t="n">
-        <v>17.46040534973145</v>
+        <v>17.46040344238281</v>
       </c>
       <c r="C367" t="n">
-        <v>17.56863003600147</v>
+        <v>17.56862811683053</v>
       </c>
       <c r="D367" t="n">
-        <v>16.93731477889199</v>
+        <v>16.93731292868499</v>
       </c>
       <c r="E367" t="n">
-        <v>17.04553946516202</v>
+        <v>17.04553760313271</v>
       </c>
       <c r="F367" t="n">
         <v>763850</v>
@@ -7772,16 +7772,16 @@
         <v>44636</v>
       </c>
       <c r="B368" t="n">
-        <v>17.53255462646484</v>
+        <v>17.53255653381348</v>
       </c>
       <c r="C368" t="n">
-        <v>18.10975750463644</v>
+        <v>18.10975947477838</v>
       </c>
       <c r="D368" t="n">
-        <v>17.15376480761467</v>
+        <v>17.15376667375514</v>
       </c>
       <c r="E368" t="n">
-        <v>17.58666696624336</v>
+        <v>17.58666887947882</v>
       </c>
       <c r="F368" t="n">
         <v>1212700</v>
@@ -7792,16 +7792,16 @@
         <v>44637</v>
       </c>
       <c r="B369" t="n">
-        <v>18.16387176513672</v>
+        <v>18.16386985778809</v>
       </c>
       <c r="C369" t="n">
-        <v>18.30817249993856</v>
+        <v>18.30817057743722</v>
       </c>
       <c r="D369" t="n">
-        <v>17.17180464342414</v>
+        <v>17.17180284025032</v>
       </c>
       <c r="E369" t="n">
-        <v>17.56863080402899</v>
+        <v>17.56862895918532</v>
       </c>
       <c r="F369" t="n">
         <v>935650</v>
@@ -7812,16 +7812,16 @@
         <v>44638</v>
       </c>
       <c r="B370" t="n">
-        <v>18.4344367980957</v>
+        <v>18.43443489074707</v>
       </c>
       <c r="C370" t="n">
-        <v>18.90341332266845</v>
+        <v>18.90341136679641</v>
       </c>
       <c r="D370" t="n">
-        <v>18.01957089842698</v>
+        <v>18.01956903400312</v>
       </c>
       <c r="E370" t="n">
-        <v>18.16387163217251</v>
+        <v>18.16386975281834</v>
       </c>
       <c r="F370" t="n">
         <v>2000150</v>
@@ -7852,16 +7852,16 @@
         <v>44642</v>
       </c>
       <c r="B372" t="n">
-        <v>19.4084644317627</v>
+        <v>19.40846633911133</v>
       </c>
       <c r="C372" t="n">
-        <v>19.46257676800326</v>
+        <v>19.46257868066973</v>
       </c>
       <c r="D372" t="n">
-        <v>18.68695916102124</v>
+        <v>18.68696099746462</v>
       </c>
       <c r="E372" t="n">
-        <v>18.70499717983481</v>
+        <v>18.70499901805086</v>
       </c>
       <c r="F372" t="n">
         <v>868000</v>
@@ -7872,16 +7872,16 @@
         <v>44643</v>
       </c>
       <c r="B373" t="n">
-        <v>19.60687828063965</v>
+        <v>19.60688018798828</v>
       </c>
       <c r="C373" t="n">
-        <v>19.8052913351097</v>
+        <v>19.80529326175987</v>
       </c>
       <c r="D373" t="n">
-        <v>18.92144901947007</v>
+        <v>18.92145086014044</v>
       </c>
       <c r="E373" t="n">
-        <v>19.48061558417691</v>
+        <v>19.48061747924276</v>
       </c>
       <c r="F373" t="n">
         <v>823600</v>
@@ -7932,16 +7932,16 @@
         <v>44648</v>
       </c>
       <c r="B376" t="n">
-        <v>21.33849143981934</v>
+        <v>21.3384895324707</v>
       </c>
       <c r="C376" t="n">
-        <v>22.11410918202458</v>
+        <v>22.11410720534708</v>
       </c>
       <c r="D376" t="n">
-        <v>21.08596429300356</v>
+        <v>21.08596240822715</v>
       </c>
       <c r="E376" t="n">
-        <v>21.55494254271838</v>
+        <v>21.55494061602219</v>
       </c>
       <c r="F376" t="n">
         <v>980450</v>
@@ -7952,16 +7952,16 @@
         <v>44649</v>
       </c>
       <c r="B377" t="n">
-        <v>21.91569519042969</v>
+        <v>21.91569328308105</v>
       </c>
       <c r="C377" t="n">
-        <v>22.36663543484347</v>
+        <v>22.36663348824898</v>
       </c>
       <c r="D377" t="n">
-        <v>21.6631697544863</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="E377" t="n">
-        <v>21.6631697544863</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="F377" t="n">
         <v>1103500</v>
@@ -7972,16 +7972,16 @@
         <v>44650</v>
       </c>
       <c r="B378" t="n">
-        <v>21.4106388092041</v>
+        <v>21.41064262390137</v>
       </c>
       <c r="C378" t="n">
-        <v>22.02391770830417</v>
+        <v>22.0239216322683</v>
       </c>
       <c r="D378" t="n">
-        <v>21.28437611357769</v>
+        <v>21.28437990577894</v>
       </c>
       <c r="E378" t="n">
-        <v>21.93372933134236</v>
+        <v>21.93373323923777</v>
       </c>
       <c r="F378" t="n">
         <v>851150</v>
@@ -7992,16 +7992,16 @@
         <v>44651</v>
       </c>
       <c r="B379" t="n">
-        <v>21.17615127563477</v>
+        <v>21.17614936828613</v>
       </c>
       <c r="C379" t="n">
-        <v>21.77139219910897</v>
+        <v>21.77139023814663</v>
       </c>
       <c r="D379" t="n">
-        <v>21.0498885707161</v>
+        <v>21.04988667474002</v>
       </c>
       <c r="E379" t="n">
-        <v>21.60905345267049</v>
+        <v>21.6090515063301</v>
       </c>
       <c r="F379" t="n">
         <v>849150</v>
@@ -8032,16 +8032,16 @@
         <v>44655</v>
       </c>
       <c r="B381" t="n">
-        <v>21.89765739440918</v>
+        <v>21.89765548706055</v>
       </c>
       <c r="C381" t="n">
-        <v>21.91569369560312</v>
+        <v>21.91569178668347</v>
       </c>
       <c r="D381" t="n">
-        <v>21.32045275119318</v>
+        <v>21.32045089412073</v>
       </c>
       <c r="E381" t="n">
-        <v>21.78943098624356</v>
+        <v>21.78942908832175</v>
       </c>
       <c r="F381" t="n">
         <v>503500</v>
@@ -8052,16 +8052,16 @@
         <v>44656</v>
       </c>
       <c r="B382" t="n">
-        <v>20.70717239379883</v>
+        <v>20.70717430114746</v>
       </c>
       <c r="C382" t="n">
-        <v>21.87961790263256</v>
+        <v>21.87961991797578</v>
       </c>
       <c r="D382" t="n">
-        <v>20.59894771310666</v>
+        <v>20.59894961048666</v>
       </c>
       <c r="E382" t="n">
-        <v>21.78942952192223</v>
+        <v>21.78943152895814</v>
       </c>
       <c r="F382" t="n">
         <v>1118400</v>
@@ -8072,16 +8072,16 @@
         <v>44657</v>
       </c>
       <c r="B383" t="n">
-        <v>20.02174377441406</v>
+        <v>20.0217456817627</v>
       </c>
       <c r="C383" t="n">
-        <v>20.58090860900858</v>
+        <v>20.58091056962541</v>
       </c>
       <c r="D383" t="n">
-        <v>19.58883991384388</v>
+        <v>19.58884177995242</v>
       </c>
       <c r="E383" t="n">
-        <v>20.58090860900858</v>
+        <v>20.58091056962541</v>
       </c>
       <c r="F383" t="n">
         <v>1237700</v>
@@ -8092,16 +8092,16 @@
         <v>44658</v>
       </c>
       <c r="B384" t="n">
-        <v>19.6609935760498</v>
+        <v>19.66098976135254</v>
       </c>
       <c r="C384" t="n">
-        <v>20.0037091182781</v>
+        <v>20.00370523708592</v>
       </c>
       <c r="D384" t="n">
-        <v>19.55276888286228</v>
+        <v>19.55276508916316</v>
       </c>
       <c r="E384" t="n">
-        <v>19.85940838056108</v>
+        <v>19.85940452736665</v>
       </c>
       <c r="F384" t="n">
         <v>978600</v>
@@ -8132,16 +8132,16 @@
         <v>44662</v>
       </c>
       <c r="B386" t="n">
-        <v>18.93948745727539</v>
+        <v>18.93948936462402</v>
       </c>
       <c r="C386" t="n">
-        <v>19.37238961487934</v>
+        <v>19.37239156582447</v>
       </c>
       <c r="D386" t="n">
-        <v>18.86733709767473</v>
+        <v>18.86733899775728</v>
       </c>
       <c r="E386" t="n">
-        <v>19.24612691562825</v>
+        <v>19.24612885385778</v>
       </c>
       <c r="F386" t="n">
         <v>1033000</v>
@@ -8192,16 +8192,16 @@
         <v>44665</v>
       </c>
       <c r="B389" t="n">
-        <v>19.57080841064453</v>
+        <v>19.5708065032959</v>
       </c>
       <c r="C389" t="n">
-        <v>19.67903311215743</v>
+        <v>19.67903119426134</v>
       </c>
       <c r="D389" t="n">
-        <v>19.01164171882585</v>
+        <v>19.01163986597297</v>
       </c>
       <c r="E389" t="n">
-        <v>19.17398049129581</v>
+        <v>19.17397862262157</v>
       </c>
       <c r="F389" t="n">
         <v>760550</v>
@@ -8232,16 +8232,16 @@
         <v>44670</v>
       </c>
       <c r="B391" t="n">
-        <v>20.3283863067627</v>
+        <v>20.32838249206543</v>
       </c>
       <c r="C391" t="n">
-        <v>20.34642260853286</v>
+        <v>20.34641879045101</v>
       </c>
       <c r="D391" t="n">
-        <v>19.01163994631538</v>
+        <v>19.01163637871046</v>
       </c>
       <c r="E391" t="n">
-        <v>19.55276856403071</v>
+        <v>19.55276489488099</v>
       </c>
       <c r="F391" t="n">
         <v>1459950</v>
@@ -8292,16 +8292,16 @@
         <v>44676</v>
       </c>
       <c r="B394" t="n">
-        <v>19.30023765563965</v>
+        <v>19.30023956298828</v>
       </c>
       <c r="C394" t="n">
-        <v>19.57080277186738</v>
+        <v>19.57080470595465</v>
       </c>
       <c r="D394" t="n">
-        <v>18.6148084361429</v>
+        <v>18.61481027575389</v>
       </c>
       <c r="E394" t="n">
-        <v>19.28219963718444</v>
+        <v>19.28220154275046</v>
       </c>
       <c r="F394" t="n">
         <v>1378800</v>
@@ -8312,16 +8312,16 @@
         <v>44677</v>
       </c>
       <c r="B395" t="n">
-        <v>19.06575393676758</v>
+        <v>19.06575202941895</v>
       </c>
       <c r="C395" t="n">
-        <v>19.39043147944575</v>
+        <v>19.39042953961619</v>
       </c>
       <c r="D395" t="n">
-        <v>18.68696404370992</v>
+        <v>18.68696217425563</v>
       </c>
       <c r="E395" t="n">
-        <v>19.19201838125387</v>
+        <v>19.19201646127367</v>
       </c>
       <c r="F395" t="n">
         <v>972150</v>
@@ -8352,16 +8352,16 @@
         <v>44679</v>
       </c>
       <c r="B397" t="n">
-        <v>21.04989051818848</v>
+        <v>21.04988861083984</v>
       </c>
       <c r="C397" t="n">
-        <v>21.10400286527417</v>
+        <v>21.10400095302237</v>
       </c>
       <c r="D397" t="n">
-        <v>19.30024190721312</v>
+        <v>19.30024015840165</v>
       </c>
       <c r="E397" t="n">
-        <v>19.84137053867153</v>
+        <v>19.84136874082794</v>
       </c>
       <c r="F397" t="n">
         <v>1501350</v>
@@ -8372,16 +8372,16 @@
         <v>44680</v>
       </c>
       <c r="B398" t="n">
-        <v>21.04989051818848</v>
+        <v>21.04988861083984</v>
       </c>
       <c r="C398" t="n">
-        <v>21.60905545187512</v>
+        <v>21.60905349386008</v>
       </c>
       <c r="D398" t="n">
-        <v>20.90558977915963</v>
+        <v>20.90558788488621</v>
       </c>
       <c r="E398" t="n">
-        <v>21.60905545187512</v>
+        <v>21.60905349386008</v>
       </c>
       <c r="F398" t="n">
         <v>1651000</v>
@@ -8392,16 +8392,16 @@
         <v>44683</v>
       </c>
       <c r="B399" t="n">
-        <v>20.38249588012695</v>
+        <v>20.38249778747559</v>
       </c>
       <c r="C399" t="n">
-        <v>21.41063890980178</v>
+        <v>21.41064091336175</v>
       </c>
       <c r="D399" t="n">
-        <v>20.02174409078493</v>
+        <v>20.02174596437521</v>
       </c>
       <c r="E399" t="n">
-        <v>21.28437621358212</v>
+        <v>21.28437820532671</v>
       </c>
       <c r="F399" t="n">
         <v>1653550</v>
@@ -8432,16 +8432,16 @@
         <v>44685</v>
       </c>
       <c r="B401" t="n">
-        <v>20.47268676757812</v>
+        <v>20.47268295288086</v>
       </c>
       <c r="C401" t="n">
-        <v>20.56287343582085</v>
+        <v>20.56286960431901</v>
       </c>
       <c r="D401" t="n">
-        <v>19.17397844651773</v>
+        <v>19.17397487381015</v>
       </c>
       <c r="E401" t="n">
-        <v>19.84136976867643</v>
+        <v>19.84136607161312</v>
       </c>
       <c r="F401" t="n">
         <v>1413100</v>
@@ -8672,16 +8672,16 @@
         <v>44701</v>
       </c>
       <c r="B413" t="n">
-        <v>20.65276336669922</v>
+        <v>20.65276145935059</v>
       </c>
       <c r="C413" t="n">
-        <v>21.08735860801926</v>
+        <v>21.08735666053437</v>
       </c>
       <c r="D413" t="n">
-        <v>20.25595815409612</v>
+        <v>20.25595628339371</v>
       </c>
       <c r="E413" t="n">
-        <v>21.03067266393701</v>
+        <v>21.03067072168725</v>
       </c>
       <c r="F413" t="n">
         <v>1756800</v>
@@ -8812,16 +8812,16 @@
         <v>44712</v>
       </c>
       <c r="B420" t="n">
-        <v>22.52341461181641</v>
+        <v>22.52341270446777</v>
       </c>
       <c r="C420" t="n">
-        <v>22.76905609322542</v>
+        <v>22.76905416507515</v>
       </c>
       <c r="D420" t="n">
-        <v>21.99434162217354</v>
+        <v>21.99433975962836</v>
       </c>
       <c r="E420" t="n">
-        <v>22.23998310358255</v>
+        <v>22.23998122023573</v>
       </c>
       <c r="F420" t="n">
         <v>1969900</v>
@@ -8992,16 +8992,16 @@
         <v>44725</v>
       </c>
       <c r="B429" t="n">
-        <v>19.25449752807617</v>
+        <v>19.25449562072754</v>
       </c>
       <c r="C429" t="n">
-        <v>20.01031797418974</v>
+        <v>20.0103159919696</v>
       </c>
       <c r="D429" t="n">
-        <v>18.98996190364815</v>
+        <v>18.98996002250438</v>
       </c>
       <c r="E429" t="n">
-        <v>19.9536320263857</v>
+        <v>19.95363004978087</v>
       </c>
       <c r="F429" t="n">
         <v>2646600</v>
@@ -9192,16 +9192,16 @@
         <v>44740</v>
       </c>
       <c r="B439" t="n">
-        <v>18.04518508911133</v>
+        <v>18.04518699645996</v>
       </c>
       <c r="C439" t="n">
-        <v>18.7254217704739</v>
+        <v>18.72542374972252</v>
       </c>
       <c r="D439" t="n">
-        <v>17.8751254682673</v>
+        <v>17.87512735764089</v>
       </c>
       <c r="E439" t="n">
-        <v>18.70652585659934</v>
+        <v>18.70652783385068</v>
       </c>
       <c r="F439" t="n">
         <v>1533000</v>
@@ -9232,16 +9232,16 @@
         <v>44742</v>
       </c>
       <c r="B441" t="n">
-        <v>17.53500556945801</v>
+        <v>17.53500366210938</v>
       </c>
       <c r="C441" t="n">
-        <v>17.74285701026197</v>
+        <v>17.74285508030455</v>
       </c>
       <c r="D441" t="n">
-        <v>17.30826001750107</v>
+        <v>17.3082581348164</v>
       </c>
       <c r="E441" t="n">
-        <v>17.55390148262445</v>
+        <v>17.55389957322044</v>
       </c>
       <c r="F441" t="n">
         <v>1152750</v>
@@ -9292,16 +9292,16 @@
         <v>44747</v>
       </c>
       <c r="B444" t="n">
-        <v>17.10041046142578</v>
+        <v>17.10040855407715</v>
       </c>
       <c r="C444" t="n">
-        <v>17.25157416346159</v>
+        <v>17.25157223925244</v>
       </c>
       <c r="D444" t="n">
-        <v>16.57133750430044</v>
+        <v>16.57133565596364</v>
       </c>
       <c r="E444" t="n">
-        <v>17.15709639918584</v>
+        <v>17.15709448551456</v>
       </c>
       <c r="F444" t="n">
         <v>2077700</v>
@@ -9312,16 +9312,16 @@
         <v>44748</v>
       </c>
       <c r="B445" t="n">
-        <v>17.23267936706543</v>
+        <v>17.2326774597168</v>
       </c>
       <c r="C445" t="n">
-        <v>17.47832084929718</v>
+        <v>17.47831891476044</v>
       </c>
       <c r="D445" t="n">
-        <v>16.83587417300084</v>
+        <v>16.83587230957143</v>
       </c>
       <c r="E445" t="n">
-        <v>17.19488934011402</v>
+        <v>17.19488743694806</v>
       </c>
       <c r="F445" t="n">
         <v>1639900</v>
@@ -9352,16 +9352,16 @@
         <v>44750</v>
       </c>
       <c r="B447" t="n">
-        <v>17.72396087646484</v>
+        <v>17.72396278381348</v>
       </c>
       <c r="C447" t="n">
-        <v>18.12076603795336</v>
+        <v>18.12076798800384</v>
       </c>
       <c r="D447" t="n">
-        <v>17.64837902675339</v>
+        <v>17.64838092596834</v>
       </c>
       <c r="E447" t="n">
-        <v>17.81843863910753</v>
+        <v>17.8184405566233</v>
       </c>
       <c r="F447" t="n">
         <v>701700</v>
@@ -9372,16 +9372,16 @@
         <v>44753</v>
       </c>
       <c r="B448" t="n">
-        <v>16.76029205322266</v>
+        <v>16.76029396057129</v>
       </c>
       <c r="C448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61059037351305</v>
       </c>
       <c r="D448" t="n">
-        <v>16.62802425795465</v>
+        <v>16.62802615025099</v>
       </c>
       <c r="E448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61059037351305</v>
       </c>
       <c r="F448" t="n">
         <v>1587350</v>
@@ -9412,16 +9412,16 @@
         <v>44755</v>
       </c>
       <c r="B450" t="n">
-        <v>16.87366485595703</v>
+        <v>16.87366676330566</v>
       </c>
       <c r="C450" t="n">
-        <v>17.02482855752328</v>
+        <v>17.024830481959</v>
       </c>
       <c r="D450" t="n">
-        <v>16.3445900984617</v>
+        <v>16.3445919460053</v>
       </c>
       <c r="E450" t="n">
-        <v>16.51464971322709</v>
+        <v>16.51465157999372</v>
       </c>
       <c r="F450" t="n">
         <v>919750</v>
@@ -9552,16 +9552,16 @@
         <v>44764</v>
       </c>
       <c r="B457" t="n">
-        <v>18.04518508911133</v>
+        <v>18.04518699645996</v>
       </c>
       <c r="C457" t="n">
-        <v>18.23413882181639</v>
+        <v>18.23414074913714</v>
       </c>
       <c r="D457" t="n">
-        <v>17.76175178703344</v>
+        <v>17.7617536644236</v>
       </c>
       <c r="E457" t="n">
-        <v>18.12076694259606</v>
+        <v>18.12076885793358</v>
       </c>
       <c r="F457" t="n">
         <v>543750</v>
@@ -9572,16 +9572,16 @@
         <v>44767</v>
       </c>
       <c r="B458" t="n">
-        <v>17.95070838928223</v>
+        <v>17.95070648193359</v>
       </c>
       <c r="C458" t="n">
-        <v>18.30972176418187</v>
+        <v>18.30971981868635</v>
       </c>
       <c r="D458" t="n">
-        <v>17.87512653130264</v>
+        <v>17.87512463198494</v>
       </c>
       <c r="E458" t="n">
-        <v>18.177453963221</v>
+        <v>18.17745203177956</v>
       </c>
       <c r="F458" t="n">
         <v>615900</v>
@@ -9732,16 +9732,16 @@
         <v>44777</v>
       </c>
       <c r="B466" t="n">
-        <v>21.31410026550293</v>
+        <v>21.31410217285156</v>
       </c>
       <c r="C466" t="n">
-        <v>21.46526395659056</v>
+        <v>21.46526587746648</v>
       </c>
       <c r="D466" t="n">
-        <v>19.78356744273731</v>
+        <v>19.78356921312217</v>
       </c>
       <c r="E466" t="n">
-        <v>19.89693931004637</v>
+        <v>19.89694109057661</v>
       </c>
       <c r="F466" t="n">
         <v>1697500</v>
@@ -9752,16 +9752,16 @@
         <v>44778</v>
       </c>
       <c r="B467" t="n">
-        <v>21.06846237182617</v>
+        <v>21.06846046447754</v>
       </c>
       <c r="C467" t="n">
-        <v>21.38968572009017</v>
+        <v>21.38968378366087</v>
       </c>
       <c r="D467" t="n">
-        <v>20.40712156223426</v>
+        <v>20.40711971475746</v>
       </c>
       <c r="E467" t="n">
-        <v>20.93619457031052</v>
+        <v>20.93619267493622</v>
       </c>
       <c r="F467" t="n">
         <v>1243500</v>
@@ -9792,16 +9792,16 @@
         <v>44782</v>
       </c>
       <c r="B469" t="n">
-        <v>20.8795051574707</v>
+        <v>20.87950706481934</v>
       </c>
       <c r="C469" t="n">
-        <v>21.84317504212628</v>
+        <v>21.84317703750642</v>
       </c>
       <c r="D469" t="n">
-        <v>20.72834146599689</v>
+        <v>20.72834335953668</v>
       </c>
       <c r="E469" t="n">
-        <v>21.7486972844518</v>
+        <v>21.74869927120138</v>
       </c>
       <c r="F469" t="n">
         <v>1406900</v>
@@ -9812,16 +9812,16 @@
         <v>44783</v>
       </c>
       <c r="B470" t="n">
-        <v>21.82428359985352</v>
+        <v>21.82428169250488</v>
       </c>
       <c r="C470" t="n">
-        <v>22.12661104471852</v>
+        <v>22.12660911094776</v>
       </c>
       <c r="D470" t="n">
-        <v>21.08735910148479</v>
+        <v>21.08735725854019</v>
       </c>
       <c r="E470" t="n">
-        <v>21.16294096270104</v>
+        <v>21.16293911315091</v>
       </c>
       <c r="F470" t="n">
         <v>1851300</v>
@@ -9852,16 +9852,16 @@
         <v>44785</v>
       </c>
       <c r="B472" t="n">
-        <v>22.92021942138672</v>
+        <v>22.92021751403809</v>
       </c>
       <c r="C472" t="n">
-        <v>22.99580127578646</v>
+        <v>22.99579936214814</v>
       </c>
       <c r="D472" t="n">
-        <v>21.748699777184</v>
+        <v>21.74869796732555</v>
       </c>
       <c r="E472" t="n">
-        <v>21.748699777184</v>
+        <v>21.74869796732555</v>
       </c>
       <c r="F472" t="n">
         <v>1189950</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75015640258789</v>
+        <v>22.75015830993652</v>
       </c>
       <c r="C474" t="n">
-        <v>23.1280656181764</v>
+        <v>23.12806755720854</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341087323478</v>
+        <v>22.52341276157331</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027559762419</v>
+        <v>23.09027753348805</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9912,16 +9912,16 @@
         <v>44790</v>
       </c>
       <c r="B475" t="n">
-        <v>22.80684471130371</v>
+        <v>22.80684661865234</v>
       </c>
       <c r="C475" t="n">
-        <v>23.09027800404387</v>
+        <v>23.09027993509618</v>
       </c>
       <c r="D475" t="n">
-        <v>22.23998172985033</v>
+        <v>22.2399835897919</v>
       </c>
       <c r="E475" t="n">
-        <v>22.48562139407294</v>
+        <v>22.4856232745575</v>
       </c>
       <c r="F475" t="n">
         <v>781800</v>
@@ -9972,16 +9972,16 @@
         <v>44795</v>
       </c>
       <c r="B478" t="n">
-        <v>20.67165565490723</v>
+        <v>20.67165756225586</v>
       </c>
       <c r="C478" t="n">
-        <v>20.86061118784968</v>
+        <v>20.86061311263301</v>
       </c>
       <c r="D478" t="n">
-        <v>20.46380601028133</v>
+        <v>20.46380789845194</v>
       </c>
       <c r="E478" t="n">
-        <v>20.80392524877235</v>
+        <v>20.80392716832534</v>
       </c>
       <c r="F478" t="n">
         <v>1246950</v>
@@ -9992,16 +9992,16 @@
         <v>44796</v>
       </c>
       <c r="B479" t="n">
-        <v>20.76613235473633</v>
+        <v>20.76613426208496</v>
       </c>
       <c r="C479" t="n">
-        <v>20.97398379069955</v>
+        <v>20.97398571713913</v>
       </c>
       <c r="D479" t="n">
-        <v>20.29374534865763</v>
+        <v>20.29374721261799</v>
       </c>
       <c r="E479" t="n">
-        <v>20.80392418018906</v>
+        <v>20.80392609100884</v>
       </c>
       <c r="F479" t="n">
         <v>1768900</v>
@@ -10032,16 +10032,16 @@
         <v>44798</v>
       </c>
       <c r="B481" t="n">
-        <v>20.8795051574707</v>
+        <v>20.87950706481934</v>
       </c>
       <c r="C481" t="n">
-        <v>21.21962256228011</v>
+        <v>21.21962450069856</v>
       </c>
       <c r="D481" t="n">
-        <v>20.57717777452308</v>
+        <v>20.57717965425402</v>
       </c>
       <c r="E481" t="n">
-        <v>20.91729517933248</v>
+        <v>20.91729709013325</v>
       </c>
       <c r="F481" t="n">
         <v>1364800</v>
@@ -10052,16 +10052,16 @@
         <v>44799</v>
       </c>
       <c r="B482" t="n">
-        <v>20.46380424499512</v>
+        <v>20.46380615234375</v>
       </c>
       <c r="C482" t="n">
-        <v>21.10625083916334</v>
+        <v>21.10625280639183</v>
       </c>
       <c r="D482" t="n">
-        <v>20.27484872835269</v>
+        <v>20.27485061808954</v>
       </c>
       <c r="E482" t="n">
-        <v>20.97398305872166</v>
+        <v>20.97398501362199</v>
       </c>
       <c r="F482" t="n">
         <v>564750</v>
@@ -10072,16 +10072,16 @@
         <v>44802</v>
       </c>
       <c r="B483" t="n">
-        <v>20.91729736328125</v>
+        <v>20.91729545593262</v>
       </c>
       <c r="C483" t="n">
-        <v>21.12514881226926</v>
+        <v>21.12514688596765</v>
       </c>
       <c r="D483" t="n">
-        <v>20.10479288728027</v>
+        <v>20.10479105402004</v>
       </c>
       <c r="E483" t="n">
-        <v>20.40712030179352</v>
+        <v>20.4071184409655</v>
       </c>
       <c r="F483" t="n">
         <v>1048850</v>
@@ -10172,16 +10172,16 @@
         <v>44809</v>
       </c>
       <c r="B488" t="n">
-        <v>21.72980117797852</v>
+        <v>21.72980308532715</v>
       </c>
       <c r="C488" t="n">
-        <v>21.84317484657557</v>
+        <v>21.84317676387566</v>
       </c>
       <c r="D488" t="n">
-        <v>20.87950497054724</v>
+        <v>20.87950680326052</v>
       </c>
       <c r="E488" t="n">
-        <v>21.01177274889936</v>
+        <v>21.01177459322254</v>
       </c>
       <c r="F488" t="n">
         <v>878600</v>
@@ -10232,16 +10232,16 @@
         <v>44813</v>
       </c>
       <c r="B491" t="n">
-        <v>20.25595664978027</v>
+        <v>20.25595855712891</v>
       </c>
       <c r="C491" t="n">
-        <v>20.29374667569073</v>
+        <v>20.29374858659776</v>
       </c>
       <c r="D491" t="n">
-        <v>19.42455445558783</v>
+        <v>19.42455628464968</v>
       </c>
       <c r="E491" t="n">
-        <v>19.9158374065185</v>
+        <v>19.9158392818407</v>
       </c>
       <c r="F491" t="n">
         <v>1292000</v>
@@ -10252,16 +10252,16 @@
         <v>44816</v>
       </c>
       <c r="B492" t="n">
-        <v>20.65276336669922</v>
+        <v>20.65276145935059</v>
       </c>
       <c r="C492" t="n">
-        <v>21.12515043874988</v>
+        <v>21.12514848777479</v>
       </c>
       <c r="D492" t="n">
-        <v>20.42601778835654</v>
+        <v>20.42601590194859</v>
       </c>
       <c r="E492" t="n">
-        <v>20.44491190170818</v>
+        <v>20.44491001355529</v>
       </c>
       <c r="F492" t="n">
         <v>1299050</v>
@@ -10272,16 +10272,16 @@
         <v>44817</v>
       </c>
       <c r="B493" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577522277832</v>
       </c>
       <c r="C493" t="n">
-        <v>20.27485008942426</v>
+        <v>20.27484813096968</v>
       </c>
       <c r="D493" t="n">
-        <v>19.57571751413516</v>
+        <v>19.57571562321348</v>
       </c>
       <c r="E493" t="n">
-        <v>20.12368638676789</v>
+        <v>20.12368444291501</v>
       </c>
       <c r="F493" t="n">
         <v>1035100</v>
@@ -10372,16 +10372,16 @@
         <v>44824</v>
       </c>
       <c r="B498" t="n">
-        <v>19.84025382995605</v>
+        <v>19.84025573730469</v>
       </c>
       <c r="C498" t="n">
-        <v>20.63386412731537</v>
+        <v>20.63386611095796</v>
       </c>
       <c r="D498" t="n">
-        <v>19.74577607036311</v>
+        <v>19.7457779686291</v>
       </c>
       <c r="E498" t="n">
-        <v>20.3693267608578</v>
+        <v>20.36932871906902</v>
       </c>
       <c r="F498" t="n">
         <v>1041050</v>
@@ -10452,16 +10452,16 @@
         <v>44830</v>
       </c>
       <c r="B502" t="n">
-        <v>18.7065258026123</v>
+        <v>18.70652389526367</v>
       </c>
       <c r="C502" t="n">
-        <v>19.48124205111187</v>
+        <v>19.48124006477188</v>
       </c>
       <c r="D502" t="n">
-        <v>18.6309439493457</v>
+        <v>18.63094204970352</v>
       </c>
       <c r="E502" t="n">
-        <v>19.34897245638518</v>
+        <v>19.34897048353161</v>
       </c>
       <c r="F502" t="n">
         <v>1198500</v>
@@ -10472,16 +10472,16 @@
         <v>44831</v>
       </c>
       <c r="B503" t="n">
-        <v>18.30971908569336</v>
+        <v>18.30972099304199</v>
       </c>
       <c r="C503" t="n">
-        <v>19.00885342224679</v>
+        <v>19.00885540242521</v>
       </c>
       <c r="D503" t="n">
-        <v>18.25303315100454</v>
+        <v>18.25303505244812</v>
       </c>
       <c r="E503" t="n">
-        <v>18.97106159777866</v>
+        <v>18.97106357402025</v>
       </c>
       <c r="F503" t="n">
         <v>994450</v>
@@ -10532,16 +10532,16 @@
         <v>44834</v>
       </c>
       <c r="B506" t="n">
-        <v>18.25303268432617</v>
+        <v>18.2530345916748</v>
       </c>
       <c r="C506" t="n">
-        <v>18.51757004279949</v>
+        <v>18.51757197779093</v>
       </c>
       <c r="D506" t="n">
-        <v>17.95070530436427</v>
+        <v>17.95070718012124</v>
       </c>
       <c r="E506" t="n">
-        <v>18.2152426628376</v>
+        <v>18.21524456623737</v>
       </c>
       <c r="F506" t="n">
         <v>981200</v>
@@ -10692,16 +10692,16 @@
         <v>44847</v>
       </c>
       <c r="B514" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577522277832</v>
       </c>
       <c r="C514" t="n">
-        <v>19.99141859744693</v>
+        <v>19.99141666637049</v>
       </c>
       <c r="D514" t="n">
-        <v>19.10333049283063</v>
+        <v>19.1033286475393</v>
       </c>
       <c r="E514" t="n">
-        <v>19.3489719601506</v>
+        <v>19.34897009113147</v>
       </c>
       <c r="F514" t="n">
         <v>1432800</v>
@@ -10772,16 +10772,16 @@
         <v>44853</v>
       </c>
       <c r="B518" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577522277832</v>
       </c>
       <c r="C518" t="n">
-        <v>19.76467304346237</v>
+        <v>19.76467113428848</v>
       </c>
       <c r="D518" t="n">
-        <v>19.27339010882242</v>
+        <v>19.27338824710413</v>
       </c>
       <c r="E518" t="n">
-        <v>19.46234563814962</v>
+        <v>19.46234375817913</v>
       </c>
       <c r="F518" t="n">
         <v>599800</v>
@@ -10812,16 +10812,16 @@
         <v>44855</v>
       </c>
       <c r="B520" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577522277832</v>
       </c>
       <c r="C520" t="n">
-        <v>19.93473265945416</v>
+        <v>19.93473073385331</v>
       </c>
       <c r="D520" t="n">
-        <v>19.17891234415881</v>
+        <v>19.17891049156664</v>
       </c>
       <c r="E520" t="n">
-        <v>19.33007604681519</v>
+        <v>19.33007417962131</v>
       </c>
       <c r="F520" t="n">
         <v>2036950</v>
@@ -10892,16 +10892,16 @@
         <v>44861</v>
       </c>
       <c r="B524" t="n">
-        <v>19.50013542175293</v>
+        <v>19.50013732910156</v>
       </c>
       <c r="C524" t="n">
-        <v>19.74577688603637</v>
+        <v>19.7457788174117</v>
       </c>
       <c r="D524" t="n">
-        <v>18.40419769003509</v>
+        <v>18.40419949018779</v>
       </c>
       <c r="E524" t="n">
-        <v>18.49867545353079</v>
+        <v>18.49867726292455</v>
       </c>
       <c r="F524" t="n">
         <v>1150900</v>
@@ -10932,16 +10932,16 @@
         <v>44865</v>
       </c>
       <c r="B526" t="n">
-        <v>20.46380424499512</v>
+        <v>20.46380615234375</v>
       </c>
       <c r="C526" t="n">
-        <v>20.50159606912895</v>
+        <v>20.50159798</v>
       </c>
       <c r="D526" t="n">
-        <v>18.76321180326671</v>
+        <v>18.76321355210998</v>
       </c>
       <c r="E526" t="n">
-        <v>18.78210591332026</v>
+        <v>18.78210766392458</v>
       </c>
       <c r="F526" t="n">
         <v>2299050</v>
@@ -10972,16 +10972,16 @@
         <v>44868</v>
       </c>
       <c r="B528" t="n">
-        <v>21.06846237182617</v>
+        <v>21.06846046447754</v>
       </c>
       <c r="C528" t="n">
-        <v>21.20073197535547</v>
+        <v>21.20073005603234</v>
       </c>
       <c r="D528" t="n">
-        <v>19.97252452551853</v>
+        <v>19.97252271738623</v>
       </c>
       <c r="E528" t="n">
-        <v>20.18037598734444</v>
+        <v>20.18037416039514</v>
       </c>
       <c r="F528" t="n">
         <v>1731950</v>
@@ -11032,16 +11032,16 @@
         <v>44873</v>
       </c>
       <c r="B531" t="n">
-        <v>19.9536304473877</v>
+        <v>19.95362854003906</v>
       </c>
       <c r="C531" t="n">
-        <v>20.35043565464299</v>
+        <v>20.35043370936413</v>
       </c>
       <c r="D531" t="n">
-        <v>19.25449600440303</v>
+        <v>19.254494163884</v>
       </c>
       <c r="E531" t="n">
-        <v>20.35043565464299</v>
+        <v>20.35043370936413</v>
       </c>
       <c r="F531" t="n">
         <v>2602700</v>
@@ -11092,16 +11092,16 @@
         <v>44876</v>
       </c>
       <c r="B534" t="n">
-        <v>15.51319026947021</v>
+        <v>15.5131893157959</v>
       </c>
       <c r="C534" t="n">
-        <v>16.96814139722099</v>
+        <v>16.96814035410347</v>
       </c>
       <c r="D534" t="n">
-        <v>15.05969824828244</v>
+        <v>15.05969732248658</v>
       </c>
       <c r="E534" t="n">
-        <v>16.94924728539026</v>
+        <v>16.94924624343426</v>
       </c>
       <c r="F534" t="n">
         <v>6426800</v>
@@ -11112,16 +11112,16 @@
         <v>44879</v>
       </c>
       <c r="B535" t="n">
-        <v>15.45650577545166</v>
+        <v>15.45650482177734</v>
       </c>
       <c r="C535" t="n">
-        <v>16.26901032459178</v>
+        <v>16.26900932078551</v>
       </c>
       <c r="D535" t="n">
-        <v>14.88964092120513</v>
+        <v>14.88964000250667</v>
       </c>
       <c r="E535" t="n">
-        <v>15.96668288286395</v>
+        <v>15.96668189771144</v>
       </c>
       <c r="F535" t="n">
         <v>3328550</v>
@@ -11132,16 +11132,16 @@
         <v>44881</v>
       </c>
       <c r="B536" t="n">
-        <v>14.47393798828125</v>
+        <v>14.47393894195557</v>
       </c>
       <c r="C536" t="n">
-        <v>15.64545758032868</v>
+        <v>15.64545861119334</v>
       </c>
       <c r="D536" t="n">
-        <v>14.41725205050845</v>
+        <v>14.41725300044779</v>
       </c>
       <c r="E536" t="n">
-        <v>15.49429387825891</v>
+        <v>15.49429489916353</v>
       </c>
       <c r="F536" t="n">
         <v>3432000</v>
@@ -11172,16 +11172,16 @@
         <v>44883</v>
       </c>
       <c r="B538" t="n">
-        <v>13.83149242401123</v>
+        <v>13.83149337768555</v>
       </c>
       <c r="C538" t="n">
-        <v>14.88963925247558</v>
+        <v>14.88964027910857</v>
       </c>
       <c r="D538" t="n">
-        <v>13.73701465855629</v>
+        <v>13.73701560571641</v>
       </c>
       <c r="E538" t="n">
-        <v>14.26608852329183</v>
+        <v>14.26608950693133</v>
       </c>
       <c r="F538" t="n">
         <v>3266800</v>
@@ -11212,16 +11212,16 @@
         <v>44887</v>
       </c>
       <c r="B540" t="n">
-        <v>14.09603023529053</v>
+        <v>14.09602928161621</v>
       </c>
       <c r="C540" t="n">
-        <v>14.71958102328215</v>
+        <v>14.71958002742118</v>
       </c>
       <c r="D540" t="n">
-        <v>13.88817967229104</v>
+        <v>13.88817873267896</v>
       </c>
       <c r="E540" t="n">
-        <v>14.60620823464794</v>
+        <v>14.60620724645726</v>
       </c>
       <c r="F540" t="n">
         <v>2112800</v>
@@ -11352,16 +11352,16 @@
         <v>44896</v>
       </c>
       <c r="B547" t="n">
-        <v>14.15271472930908</v>
+        <v>14.1527156829834</v>
       </c>
       <c r="C547" t="n">
-        <v>14.51172897371034</v>
+        <v>14.51172995157667</v>
       </c>
       <c r="D547" t="n">
-        <v>14.0393419522887</v>
+        <v>14.03934289832344</v>
       </c>
       <c r="E547" t="n">
-        <v>14.30387933300967</v>
+        <v>14.30388029687014</v>
       </c>
       <c r="F547" t="n">
         <v>1145350</v>
@@ -11372,16 +11372,16 @@
         <v>44897</v>
       </c>
       <c r="B548" t="n">
-        <v>14.28498268127441</v>
+        <v>14.28498363494873</v>
       </c>
       <c r="C548" t="n">
-        <v>14.58731007103471</v>
+        <v>14.58731104489259</v>
       </c>
       <c r="D548" t="n">
-        <v>14.05823713895419</v>
+        <v>14.05823807749083</v>
       </c>
       <c r="E548" t="n">
-        <v>14.1716099101143</v>
+        <v>14.17161085621978</v>
       </c>
       <c r="F548" t="n">
         <v>1219600</v>
@@ -11392,16 +11392,16 @@
         <v>44900</v>
       </c>
       <c r="B549" t="n">
-        <v>13.41579055786133</v>
+        <v>13.41579151153564</v>
       </c>
       <c r="C549" t="n">
-        <v>14.22829677075448</v>
+        <v>14.22829778218658</v>
       </c>
       <c r="D549" t="n">
-        <v>13.30241778650555</v>
+        <v>13.30241873212065</v>
       </c>
       <c r="E549" t="n">
-        <v>14.22829677075448</v>
+        <v>14.22829778218658</v>
       </c>
       <c r="F549" t="n">
         <v>1514950</v>
@@ -11492,16 +11492,16 @@
         <v>44907</v>
       </c>
       <c r="B554" t="n">
-        <v>11.90415382385254</v>
+        <v>11.90415287017822</v>
       </c>
       <c r="C554" t="n">
-        <v>12.35764495188166</v>
+        <v>12.35764396187693</v>
       </c>
       <c r="D554" t="n">
-        <v>11.58293049099519</v>
+        <v>11.58292956305495</v>
       </c>
       <c r="E554" t="n">
-        <v>12.18758532836735</v>
+        <v>12.18758435198656</v>
       </c>
       <c r="F554" t="n">
         <v>2931550</v>
@@ -11532,16 +11532,16 @@
         <v>44909</v>
       </c>
       <c r="B556" t="n">
-        <v>11.50734806060791</v>
+        <v>11.50734901428223</v>
       </c>
       <c r="C556" t="n">
-        <v>11.62072083694312</v>
+        <v>11.62072180001323</v>
       </c>
       <c r="D556" t="n">
-        <v>11.07275196748624</v>
+        <v>11.0727528851433</v>
       </c>
       <c r="E556" t="n">
-        <v>11.50734806060791</v>
+        <v>11.50734901428223</v>
       </c>
       <c r="F556" t="n">
         <v>4449300</v>
@@ -11552,16 +11552,16 @@
         <v>44910</v>
       </c>
       <c r="B557" t="n">
-        <v>11.5640344619751</v>
+        <v>11.56403541564941</v>
       </c>
       <c r="C557" t="n">
-        <v>11.9041537056258</v>
+        <v>11.90415468734941</v>
       </c>
       <c r="D557" t="n">
-        <v>11.2617070462916</v>
+        <v>11.26170797503327</v>
       </c>
       <c r="E557" t="n">
-        <v>11.41287075413335</v>
+        <v>11.41287169534134</v>
       </c>
       <c r="F557" t="n">
         <v>3167400</v>
@@ -29629,42 +29629,42 @@
     </row>
     <row r="1461">
       <c r="A1461" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1461" t="n">
-        <v>7.710000038146973</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="C1461" t="n">
-        <v>7.760000228881836</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="D1461" t="n">
-        <v>7.579999923706055</v>
+        <v>7.429999828338623</v>
       </c>
       <c r="E1461" t="n">
-        <v>7.730000019073486</v>
+        <v>7.769999980926514</v>
       </c>
       <c r="F1461" t="n">
-        <v>1129300</v>
+        <v>2238200</v>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1462" t="n">
-        <v>7.55</v>
+        <v>7.56</v>
       </c>
       <c r="C1462" t="n">
-        <v>7.9</v>
+        <v>7.85</v>
       </c>
       <c r="D1462" t="n">
-        <v>7.43</v>
+        <v>7.47</v>
       </c>
       <c r="E1462" t="n">
-        <v>7.77</v>
+        <v>7.66</v>
       </c>
       <c r="F1462" t="n">
-        <v>2238200</v>
+        <v>2511600</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1464"/>
+  <dimension ref="A1:F1465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44092</v>
       </c>
       <c r="B2" t="n">
-        <v>13.02992725372314</v>
+        <v>13.02992820739746</v>
       </c>
       <c r="C2" t="n">
-        <v>13.73903911926684</v>
+        <v>13.73904012484181</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63548414306174</v>
+        <v>12.63548506786634</v>
       </c>
       <c r="E2" t="n">
-        <v>13.3844836091585</v>
+        <v>13.38448458878317</v>
       </c>
       <c r="F2" t="n">
         <v>539400</v>
@@ -492,16 +492,16 @@
         <v>44096</v>
       </c>
       <c r="B4" t="n">
-        <v>12.58673286437988</v>
+        <v>12.58673191070557</v>
       </c>
       <c r="C4" t="n">
-        <v>12.77287472474392</v>
+        <v>12.77287375696596</v>
       </c>
       <c r="D4" t="n">
-        <v>12.43161450652202</v>
+        <v>12.43161356460074</v>
       </c>
       <c r="E4" t="n">
-        <v>12.44491065559339</v>
+        <v>12.44490971266469</v>
       </c>
       <c r="F4" t="n">
         <v>1698000</v>
@@ -512,16 +512,16 @@
         <v>44097</v>
       </c>
       <c r="B5" t="n">
-        <v>12.65321254730225</v>
+        <v>12.65321159362793</v>
       </c>
       <c r="C5" t="n">
-        <v>12.99447278246738</v>
+        <v>12.99447180307224</v>
       </c>
       <c r="D5" t="n">
-        <v>12.24990530404421</v>
+        <v>12.24990438076721</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41388776942456</v>
+        <v>12.41388683378818</v>
       </c>
       <c r="F5" t="n">
         <v>1967400</v>
@@ -532,16 +532,16 @@
         <v>44098</v>
       </c>
       <c r="B6" t="n">
-        <v>12.45377445220947</v>
+        <v>12.45377540588379</v>
       </c>
       <c r="C6" t="n">
-        <v>12.84378551689074</v>
+        <v>12.84378650043098</v>
       </c>
       <c r="D6" t="n">
-        <v>12.40945480170939</v>
+        <v>12.40945575198984</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6532116114693</v>
+        <v>12.65321258041594</v>
       </c>
       <c r="F6" t="n">
         <v>571400</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513614654541</v>
+        <v>12.36513423919678</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366305880876</v>
+        <v>12.49366113163458</v>
       </c>
       <c r="D7" t="n">
-        <v>12.3208164924778</v>
+        <v>12.32081459196557</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377545468063</v>
+        <v>12.45377353365919</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -592,16 +592,16 @@
         <v>44103</v>
       </c>
       <c r="B9" t="n">
-        <v>11.29703521728516</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C9" t="n">
-        <v>11.83330135852865</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="D9" t="n">
-        <v>11.07986986928638</v>
+        <v>11.07987080462801</v>
       </c>
       <c r="E9" t="n">
-        <v>11.83330135852865</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="F9" t="n">
         <v>897600</v>
@@ -632,16 +632,16 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>11.68261432647705</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="C11" t="n">
-        <v>11.68261432647705</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="D11" t="n">
-        <v>10.92918288458478</v>
+        <v>10.92918466892529</v>
       </c>
       <c r="E11" t="n">
-        <v>11.22612341223327</v>
+        <v>11.22612524505344</v>
       </c>
       <c r="F11" t="n">
         <v>1726600</v>
@@ -652,16 +652,16 @@
         <v>44106</v>
       </c>
       <c r="B12" t="n">
-        <v>11.29703521728516</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C12" t="n">
-        <v>11.55408816443952</v>
+        <v>11.55408913981376</v>
       </c>
       <c r="D12" t="n">
-        <v>11.19953266675315</v>
+        <v>11.19953361219649</v>
       </c>
       <c r="E12" t="n">
-        <v>11.51420056528393</v>
+        <v>11.51420153729093</v>
       </c>
       <c r="F12" t="n">
         <v>878600</v>
@@ -672,16 +672,16 @@
         <v>44109</v>
       </c>
       <c r="B13" t="n">
-        <v>11.6560230255127</v>
+        <v>11.65602397918701</v>
       </c>
       <c r="C13" t="n">
-        <v>11.6560230255127</v>
+        <v>11.65602397918701</v>
       </c>
       <c r="D13" t="n">
-        <v>11.12862181655362</v>
+        <v>11.12862272707694</v>
       </c>
       <c r="E13" t="n">
-        <v>11.43442562316206</v>
+        <v>11.43442655870568</v>
       </c>
       <c r="F13" t="n">
         <v>595400</v>
@@ -692,16 +692,16 @@
         <v>44110</v>
       </c>
       <c r="B14" t="n">
-        <v>11.43885707855225</v>
+        <v>11.43885803222656</v>
       </c>
       <c r="C14" t="n">
-        <v>12.05489839991425</v>
+        <v>12.05489940494884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.38124212887729</v>
+        <v>11.38124307774816</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5895433719507</v>
+        <v>11.58954433818795</v>
       </c>
       <c r="F14" t="n">
         <v>472800</v>
@@ -712,16 +712,16 @@
         <v>44111</v>
       </c>
       <c r="B15" t="n">
-        <v>11.68261432647705</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82443651663867</v>
+        <v>11.82443844714174</v>
       </c>
       <c r="D15" t="n">
-        <v>11.35465030039657</v>
+        <v>11.35465215420053</v>
       </c>
       <c r="E15" t="n">
-        <v>11.62943058250298</v>
+        <v>11.62943248116863</v>
       </c>
       <c r="F15" t="n">
         <v>437200</v>
@@ -732,16 +732,16 @@
         <v>44112</v>
       </c>
       <c r="B16" t="n">
-        <v>11.52306461334229</v>
+        <v>11.5230655670166</v>
       </c>
       <c r="C16" t="n">
-        <v>11.90421240567286</v>
+        <v>11.90421339089181</v>
       </c>
       <c r="D16" t="n">
-        <v>11.39010651362682</v>
+        <v>11.39010745629723</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68261500926243</v>
+        <v>11.68261597614149</v>
       </c>
       <c r="F16" t="n">
         <v>595200</v>
@@ -752,16 +752,16 @@
         <v>44113</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10365104675293</v>
+        <v>12.1036491394043</v>
       </c>
       <c r="C17" t="n">
-        <v>12.29422496640223</v>
+        <v>12.29422302902209</v>
       </c>
       <c r="D17" t="n">
-        <v>11.53193013313212</v>
+        <v>11.53192831587788</v>
       </c>
       <c r="E17" t="n">
-        <v>11.53636218304571</v>
+        <v>11.53636036509305</v>
       </c>
       <c r="F17" t="n">
         <v>672400</v>
@@ -812,16 +812,16 @@
         <v>44119</v>
       </c>
       <c r="B20" t="n">
-        <v>11.97955799102783</v>
+        <v>11.97955513000488</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39616057238516</v>
+        <v>12.39615761186692</v>
       </c>
       <c r="D20" t="n">
-        <v>11.78011995555996</v>
+        <v>11.78011714216788</v>
       </c>
       <c r="E20" t="n">
-        <v>12.02830885333219</v>
+        <v>12.0283059806663</v>
       </c>
       <c r="F20" t="n">
         <v>483400</v>
@@ -832,16 +832,16 @@
         <v>44120</v>
       </c>
       <c r="B21" t="n">
-        <v>12.45377445220947</v>
+        <v>12.45377540588379</v>
       </c>
       <c r="C21" t="n">
-        <v>12.49366205312684</v>
+        <v>12.49366300985564</v>
       </c>
       <c r="D21" t="n">
-        <v>11.97955613611076</v>
+        <v>11.9795570534708</v>
       </c>
       <c r="E21" t="n">
-        <v>12.06376254220119</v>
+        <v>12.06376346600951</v>
       </c>
       <c r="F21" t="n">
         <v>585200</v>
@@ -932,16 +932,16 @@
         <v>44127</v>
       </c>
       <c r="B26" t="n">
-        <v>12.94128799438477</v>
+        <v>12.94128894805908</v>
       </c>
       <c r="C26" t="n">
-        <v>13.18061273749889</v>
+        <v>13.18061370880962</v>
       </c>
       <c r="D26" t="n">
-        <v>12.86151279823773</v>
+        <v>12.86151374603323</v>
       </c>
       <c r="E26" t="n">
-        <v>13.08754223887867</v>
+        <v>13.08754320333081</v>
       </c>
       <c r="F26" t="n">
         <v>543600</v>
@@ -992,16 +992,16 @@
         <v>44132</v>
       </c>
       <c r="B29" t="n">
-        <v>11.43885707855225</v>
+        <v>11.43885803222656</v>
       </c>
       <c r="C29" t="n">
-        <v>11.92637150746918</v>
+        <v>11.92637250178829</v>
       </c>
       <c r="D29" t="n">
-        <v>11.301466932922</v>
+        <v>11.3014678751419</v>
       </c>
       <c r="E29" t="n">
-        <v>11.92637150746918</v>
+        <v>11.92637250178829</v>
       </c>
       <c r="F29" t="n">
         <v>860400</v>
@@ -1012,16 +1012,16 @@
         <v>44133</v>
       </c>
       <c r="B30" t="n">
-        <v>11.70477390289307</v>
+        <v>11.70477485656738</v>
       </c>
       <c r="C30" t="n">
-        <v>11.87761959408865</v>
+        <v>11.87762056184598</v>
       </c>
       <c r="D30" t="n">
-        <v>11.00895824360864</v>
+        <v>11.00895914058972</v>
       </c>
       <c r="E30" t="n">
-        <v>11.3945372232491</v>
+        <v>11.39453815164614</v>
       </c>
       <c r="F30" t="n">
         <v>683400</v>
@@ -1072,16 +1072,16 @@
         <v>44139</v>
       </c>
       <c r="B33" t="n">
-        <v>12.5778694152832</v>
+        <v>12.57786750793457</v>
       </c>
       <c r="C33" t="n">
-        <v>12.78173948494929</v>
+        <v>12.78173754668514</v>
       </c>
       <c r="D33" t="n">
-        <v>11.90421388871892</v>
+        <v>11.90421208352558</v>
       </c>
       <c r="E33" t="n">
-        <v>11.96626089693912</v>
+        <v>11.96625908233677</v>
       </c>
       <c r="F33" t="n">
         <v>620400</v>
@@ -1092,16 +1092,16 @@
         <v>44140</v>
       </c>
       <c r="B34" t="n">
-        <v>12.79503536224365</v>
+        <v>12.79503345489502</v>
       </c>
       <c r="C34" t="n">
-        <v>13.02992808569082</v>
+        <v>13.02992614332686</v>
       </c>
       <c r="D34" t="n">
-        <v>12.63991699966924</v>
+        <v>12.63991511544401</v>
       </c>
       <c r="E34" t="n">
-        <v>12.78617126259321</v>
+        <v>12.78616935656595</v>
       </c>
       <c r="F34" t="n">
         <v>682600</v>
@@ -1112,16 +1112,16 @@
         <v>44141</v>
       </c>
       <c r="B35" t="n">
-        <v>13.55732917785645</v>
+        <v>13.55733013153076</v>
       </c>
       <c r="C35" t="n">
-        <v>13.69471933097108</v>
+        <v>13.69472029430994</v>
       </c>
       <c r="D35" t="n">
-        <v>12.65764341771108</v>
+        <v>12.65764430809807</v>
       </c>
       <c r="E35" t="n">
-        <v>12.74185066750967</v>
+        <v>12.74185156382011</v>
       </c>
       <c r="F35" t="n">
         <v>948200</v>
@@ -1152,16 +1152,16 @@
         <v>44145</v>
       </c>
       <c r="B37" t="n">
-        <v>13.15845394134521</v>
+        <v>13.15845489501953</v>
       </c>
       <c r="C37" t="n">
-        <v>13.57948849711368</v>
+        <v>13.57948948130297</v>
       </c>
       <c r="D37" t="n">
-        <v>13.07867874153117</v>
+        <v>13.07867968942368</v>
       </c>
       <c r="E37" t="n">
-        <v>13.07867874153117</v>
+        <v>13.07867968942368</v>
       </c>
       <c r="F37" t="n">
         <v>489600</v>
@@ -1192,16 +1192,16 @@
         <v>44147</v>
       </c>
       <c r="B39" t="n">
-        <v>12.94128799438477</v>
+        <v>12.94128894805908</v>
       </c>
       <c r="C39" t="n">
-        <v>13.35345843226615</v>
+        <v>13.35345941631429</v>
       </c>
       <c r="D39" t="n">
-        <v>12.75071410255063</v>
+        <v>12.7507150421811</v>
       </c>
       <c r="E39" t="n">
-        <v>13.12299778768546</v>
+        <v>13.12299875475041</v>
       </c>
       <c r="F39" t="n">
         <v>656600</v>
@@ -1212,16 +1212,16 @@
         <v>44148</v>
       </c>
       <c r="B40" t="n">
-        <v>13.10970401763916</v>
+        <v>13.10970211029053</v>
       </c>
       <c r="C40" t="n">
-        <v>13.53073947574565</v>
+        <v>13.53073750714</v>
       </c>
       <c r="D40" t="n">
-        <v>12.84378693069438</v>
+        <v>12.84378506203439</v>
       </c>
       <c r="E40" t="n">
-        <v>13.29584589396779</v>
+        <v>13.29584395953713</v>
       </c>
       <c r="F40" t="n">
         <v>720400</v>
@@ -1272,16 +1272,16 @@
         <v>44153</v>
       </c>
       <c r="B43" t="n">
-        <v>12.74185085296631</v>
+        <v>12.74185180664062</v>
       </c>
       <c r="C43" t="n">
-        <v>13.18947771480541</v>
+        <v>13.18947870198273</v>
       </c>
       <c r="D43" t="n">
-        <v>12.66207565150411</v>
+        <v>12.66207659920759</v>
       </c>
       <c r="E43" t="n">
-        <v>13.11413456290522</v>
+        <v>13.11413554444342</v>
       </c>
       <c r="F43" t="n">
         <v>532400</v>
@@ -1292,16 +1292,16 @@
         <v>44154</v>
       </c>
       <c r="B44" t="n">
-        <v>12.99447154998779</v>
+        <v>12.99447059631348</v>
       </c>
       <c r="C44" t="n">
-        <v>13.07424675015632</v>
+        <v>13.07424579062724</v>
       </c>
       <c r="D44" t="n">
-        <v>12.4803656437095</v>
+        <v>12.48036472776582</v>
       </c>
       <c r="E44" t="n">
-        <v>12.74185064633879</v>
+        <v>12.74184971120452</v>
       </c>
       <c r="F44" t="n">
         <v>711400</v>
@@ -1312,16 +1312,16 @@
         <v>44158</v>
       </c>
       <c r="B45" t="n">
-        <v>13.35346031188965</v>
+        <v>13.35345935821533</v>
       </c>
       <c r="C45" t="n">
-        <v>13.47312312295385</v>
+        <v>13.47312216073348</v>
       </c>
       <c r="D45" t="n">
-        <v>13.0698158815097</v>
+        <v>13.06981494809263</v>
       </c>
       <c r="E45" t="n">
-        <v>13.13629493921411</v>
+        <v>13.13629400104926</v>
       </c>
       <c r="F45" t="n">
         <v>731400</v>
@@ -1332,16 +1332,16 @@
         <v>44159</v>
       </c>
       <c r="B46" t="n">
-        <v>13.73904037475586</v>
+        <v>13.73903846740723</v>
       </c>
       <c r="C46" t="n">
-        <v>13.82767968304641</v>
+        <v>13.82767776339226</v>
       </c>
       <c r="D46" t="n">
-        <v>13.27368611954819</v>
+        <v>13.27368427680326</v>
       </c>
       <c r="E46" t="n">
-        <v>13.4731232952113</v>
+        <v>13.47312142477911</v>
       </c>
       <c r="F46" t="n">
         <v>798800</v>
@@ -1352,16 +1352,16 @@
         <v>44160</v>
       </c>
       <c r="B47" t="n">
-        <v>13.65040016174316</v>
+        <v>13.65040111541748</v>
       </c>
       <c r="C47" t="n">
-        <v>13.77449501605975</v>
+        <v>13.77449597840386</v>
       </c>
       <c r="D47" t="n">
-        <v>13.34016429394225</v>
+        <v>13.34016522594218</v>
       </c>
       <c r="E47" t="n">
-        <v>13.61494460984229</v>
+        <v>13.61494556103953</v>
       </c>
       <c r="F47" t="n">
         <v>724200</v>
@@ -1372,16 +1372,16 @@
         <v>44161</v>
       </c>
       <c r="B48" t="n">
-        <v>13.53073883056641</v>
+        <v>13.53073787689209</v>
       </c>
       <c r="C48" t="n">
-        <v>13.73904010198848</v>
+        <v>13.73903913363267</v>
       </c>
       <c r="D48" t="n">
-        <v>13.4465315738949</v>
+        <v>13.44653062615568</v>
       </c>
       <c r="E48" t="n">
-        <v>13.65040079545773</v>
+        <v>13.65039983334939</v>
       </c>
       <c r="F48" t="n">
         <v>209800</v>
@@ -1392,16 +1392,16 @@
         <v>44162</v>
       </c>
       <c r="B49" t="n">
-        <v>13.39334678649902</v>
+        <v>13.39334774017334</v>
       </c>
       <c r="C49" t="n">
-        <v>13.71687963861983</v>
+        <v>13.71688061533133</v>
       </c>
       <c r="D49" t="n">
-        <v>13.38891473698208</v>
+        <v>13.38891569034081</v>
       </c>
       <c r="E49" t="n">
-        <v>13.53073778554325</v>
+        <v>13.5307387490005</v>
       </c>
       <c r="F49" t="n">
         <v>510000</v>
@@ -1412,16 +1412,16 @@
         <v>44165</v>
       </c>
       <c r="B50" t="n">
-        <v>13.1362943649292</v>
+        <v>13.13629245758057</v>
       </c>
       <c r="C50" t="n">
-        <v>13.73017549906958</v>
+        <v>13.73017350549127</v>
       </c>
       <c r="D50" t="n">
-        <v>13.1362943649292</v>
+        <v>13.13629245758057</v>
       </c>
       <c r="E50" t="n">
-        <v>13.38891528035829</v>
+        <v>13.3889133363299</v>
       </c>
       <c r="F50" t="n">
         <v>1093200</v>
@@ -1472,16 +1472,16 @@
         <v>44168</v>
       </c>
       <c r="B53" t="n">
-        <v>14.35951328277588</v>
+        <v>14.3595142364502</v>
       </c>
       <c r="C53" t="n">
-        <v>14.44371969251193</v>
+        <v>14.44372065177874</v>
       </c>
       <c r="D53" t="n">
-        <v>14.0581398153931</v>
+        <v>14.05814074905197</v>
       </c>
       <c r="E53" t="n">
-        <v>14.31519278502997</v>
+        <v>14.31519373576078</v>
       </c>
       <c r="F53" t="n">
         <v>1033200</v>
@@ -1492,16 +1492,16 @@
         <v>44169</v>
       </c>
       <c r="B54" t="n">
-        <v>14.07143688201904</v>
+        <v>14.07143592834473</v>
       </c>
       <c r="C54" t="n">
-        <v>14.44815183881928</v>
+        <v>14.44815085961357</v>
       </c>
       <c r="D54" t="n">
-        <v>13.94734201622206</v>
+        <v>13.94734107095812</v>
       </c>
       <c r="E54" t="n">
-        <v>14.44815183881928</v>
+        <v>14.44815085961357</v>
       </c>
       <c r="F54" t="n">
         <v>751600</v>
@@ -1512,16 +1512,16 @@
         <v>44172</v>
       </c>
       <c r="B55" t="n">
-        <v>14.25314426422119</v>
+        <v>14.25314617156982</v>
       </c>
       <c r="C55" t="n">
-        <v>14.36837416480735</v>
+        <v>14.36837608757599</v>
       </c>
       <c r="D55" t="n">
-        <v>13.82767767499762</v>
+        <v>13.82767952541053</v>
       </c>
       <c r="E55" t="n">
-        <v>14.06257037080052</v>
+        <v>14.06257225264665</v>
       </c>
       <c r="F55" t="n">
         <v>782600</v>
@@ -1552,16 +1552,16 @@
         <v>44174</v>
       </c>
       <c r="B57" t="n">
-        <v>13.88972663879395</v>
+        <v>13.88972473144531</v>
       </c>
       <c r="C57" t="n">
-        <v>14.24871507521011</v>
+        <v>14.24871311856489</v>
       </c>
       <c r="D57" t="n">
-        <v>13.65926511437724</v>
+        <v>13.65926323867578</v>
       </c>
       <c r="E57" t="n">
-        <v>14.14677961746578</v>
+        <v>14.14677767481842</v>
       </c>
       <c r="F57" t="n">
         <v>570800</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.00495719909668</v>
+        <v>14.00495529174805</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10245976017788</v>
+        <v>14.10245783955028</v>
       </c>
       <c r="D58" t="n">
-        <v>13.5174427030365</v>
+        <v>13.51744086208294</v>
       </c>
       <c r="E58" t="n">
-        <v>13.8852943886831</v>
+        <v>13.88529249763146</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1592,16 +1592,16 @@
         <v>44176</v>
       </c>
       <c r="B59" t="n">
-        <v>13.82324600219727</v>
+        <v>13.82324695587158</v>
       </c>
       <c r="C59" t="n">
-        <v>13.9606361530436</v>
+        <v>13.96063711619654</v>
       </c>
       <c r="D59" t="n">
-        <v>13.40221060548261</v>
+        <v>13.40221153010944</v>
       </c>
       <c r="E59" t="n">
-        <v>13.9207485535516</v>
+        <v>13.92074951395268</v>
       </c>
       <c r="F59" t="n">
         <v>523600</v>
@@ -1672,16 +1672,16 @@
         <v>44182</v>
       </c>
       <c r="B63" t="n">
-        <v>13.73904037475586</v>
+        <v>13.73903846740723</v>
       </c>
       <c r="C63" t="n">
-        <v>14.13348352146192</v>
+        <v>14.13348155935396</v>
       </c>
       <c r="D63" t="n">
-        <v>13.67256131620149</v>
+        <v>13.67255941808194</v>
       </c>
       <c r="E63" t="n">
-        <v>13.91631814600987</v>
+        <v>13.91631621405031</v>
       </c>
       <c r="F63" t="n">
         <v>633000</v>
@@ -1692,16 +1692,16 @@
         <v>44183</v>
       </c>
       <c r="B64" t="n">
-        <v>13.40664291381836</v>
+        <v>13.40664386749268</v>
       </c>
       <c r="C64" t="n">
-        <v>13.83654157235696</v>
+        <v>13.83654255661189</v>
       </c>
       <c r="D64" t="n">
-        <v>13.28698011303142</v>
+        <v>13.28698105819358</v>
       </c>
       <c r="E64" t="n">
-        <v>13.6193762183327</v>
+        <v>13.61937718713968</v>
       </c>
       <c r="F64" t="n">
         <v>920000</v>
@@ -1712,16 +1712,16 @@
         <v>44186</v>
       </c>
       <c r="B65" t="n">
-        <v>13.14958953857422</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="C65" t="n">
-        <v>13.3401634347651</v>
+        <v>13.3401644022608</v>
       </c>
       <c r="D65" t="n">
-        <v>12.76844174619245</v>
+        <v>12.76844267222401</v>
       </c>
       <c r="E65" t="n">
-        <v>13.14958953857422</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="F65" t="n">
         <v>872000</v>
@@ -1732,16 +1732,16 @@
         <v>44187</v>
       </c>
       <c r="B66" t="n">
-        <v>13.0077657699585</v>
+        <v>13.00776767730713</v>
       </c>
       <c r="C66" t="n">
-        <v>13.60607883719102</v>
+        <v>13.60608083227121</v>
       </c>
       <c r="D66" t="n">
-        <v>12.94571793162259</v>
+        <v>12.94571982987305</v>
       </c>
       <c r="E66" t="n">
-        <v>13.22493109081698</v>
+        <v>13.22493303000889</v>
       </c>
       <c r="F66" t="n">
         <v>911600</v>
@@ -1752,16 +1752,16 @@
         <v>44188</v>
       </c>
       <c r="B67" t="n">
-        <v>14.04484462738037</v>
+        <v>14.04484367370605</v>
       </c>
       <c r="C67" t="n">
-        <v>14.15121128686777</v>
+        <v>14.15121032597093</v>
       </c>
       <c r="D67" t="n">
-        <v>13.40221177531775</v>
+        <v>13.40221086527954</v>
       </c>
       <c r="E67" t="n">
-        <v>13.45539552772498</v>
+        <v>13.45539461407549</v>
       </c>
       <c r="F67" t="n">
         <v>2040000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294364929199</v>
+        <v>15.11294269561768</v>
       </c>
       <c r="C68" t="n">
-        <v>15.13067184897926</v>
+        <v>15.13067089418624</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586848207222</v>
+        <v>14.07586759384061</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348344040167</v>
+        <v>14.13348254853438</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.19715023040771</v>
+        <v>15.1971492767334</v>
       </c>
       <c r="C69" t="n">
-        <v>15.34783653134916</v>
+        <v>15.34783556821876</v>
       </c>
       <c r="D69" t="n">
-        <v>14.74952253173429</v>
+        <v>14.74952160615018</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510322837077</v>
+        <v>15.13510227859012</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1812,16 +1812,16 @@
         <v>44195</v>
       </c>
       <c r="B70" t="n">
-        <v>15.72011947631836</v>
+        <v>15.72012042999268</v>
       </c>
       <c r="C70" t="n">
-        <v>15.91512457198337</v>
+        <v>15.91512553748784</v>
       </c>
       <c r="D70" t="n">
-        <v>15.25033239823193</v>
+        <v>15.25033332340621</v>
       </c>
       <c r="E70" t="n">
-        <v>15.37885929091415</v>
+        <v>15.37886022388563</v>
       </c>
       <c r="F70" t="n">
         <v>2946000</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884963989258</v>
+        <v>14.98884868621826</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171924035773</v>
+        <v>15.94171822605652</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952401596354</v>
+        <v>14.74952307751646</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069573621739</v>
+        <v>15.91069472389008</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1852,16 +1852,16 @@
         <v>44201</v>
       </c>
       <c r="B72" t="n">
-        <v>15.13953685760498</v>
+        <v>15.13953590393066</v>
       </c>
       <c r="C72" t="n">
-        <v>15.45863770851384</v>
+        <v>15.45863673473862</v>
       </c>
       <c r="D72" t="n">
-        <v>14.36394582659929</v>
+        <v>14.36394492178124</v>
       </c>
       <c r="E72" t="n">
-        <v>14.84702830782329</v>
+        <v>14.84702737257476</v>
       </c>
       <c r="F72" t="n">
         <v>1878200</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.58997344970703</v>
+        <v>14.5899715423584</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135801482809</v>
+        <v>15.28135601709469</v>
       </c>
       <c r="D73" t="n">
-        <v>14.58997344970703</v>
+        <v>14.5899715423584</v>
       </c>
       <c r="E73" t="n">
-        <v>15.1395358000321</v>
+        <v>15.13953382083913</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1892,16 +1892,16 @@
         <v>44203</v>
       </c>
       <c r="B74" t="n">
-        <v>14.40513038635254</v>
+        <v>14.40513134002686</v>
       </c>
       <c r="C74" t="n">
-        <v>14.96995047062398</v>
+        <v>14.96995146169153</v>
       </c>
       <c r="D74" t="n">
-        <v>14.39623538149606</v>
+        <v>14.39623633458149</v>
       </c>
       <c r="E74" t="n">
-        <v>14.68531710141131</v>
+        <v>14.68531807363505</v>
       </c>
       <c r="F74" t="n">
         <v>1215000</v>
@@ -1972,16 +1972,16 @@
         <v>44209</v>
       </c>
       <c r="B78" t="n">
-        <v>15.7215633392334</v>
+        <v>15.72156143188477</v>
       </c>
       <c r="C78" t="n">
-        <v>16.71778200367792</v>
+        <v>16.7177799754675</v>
       </c>
       <c r="D78" t="n">
-        <v>15.41469325204709</v>
+        <v>15.41469138192811</v>
       </c>
       <c r="E78" t="n">
-        <v>15.96617177454386</v>
+        <v>15.9661698375192</v>
       </c>
       <c r="F78" t="n">
         <v>1238200</v>
@@ -2012,16 +2012,16 @@
         <v>44211</v>
       </c>
       <c r="B80" t="n">
-        <v>15.881667137146</v>
+        <v>15.88166809082031</v>
       </c>
       <c r="C80" t="n">
-        <v>16.09069550826418</v>
+        <v>16.09069647449039</v>
       </c>
       <c r="D80" t="n">
-        <v>15.61037542906886</v>
+        <v>15.61037636645245</v>
       </c>
       <c r="E80" t="n">
-        <v>16.08624715759644</v>
+        <v>16.08624812355553</v>
       </c>
       <c r="F80" t="n">
         <v>728000</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422584533691</v>
+        <v>16.38422393798828</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538419561817</v>
+        <v>16.45538227998573</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169572023429</v>
+        <v>15.92169386673051</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93503907728939</v>
+        <v>15.93503722223226</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2072,16 +2072,16 @@
         <v>44216</v>
       </c>
       <c r="B83" t="n">
-        <v>16.2552490234375</v>
+        <v>16.25524711608887</v>
       </c>
       <c r="C83" t="n">
-        <v>16.81117410424281</v>
+        <v>16.81117213166337</v>
       </c>
       <c r="D83" t="n">
-        <v>16.0106423271929</v>
+        <v>16.01064044854579</v>
       </c>
       <c r="E83" t="n">
-        <v>16.69998908808175</v>
+        <v>16.69998712854847</v>
       </c>
       <c r="F83" t="n">
         <v>1073000</v>
@@ -2112,16 +2112,16 @@
         <v>44218</v>
       </c>
       <c r="B85" t="n">
-        <v>15.40135097503662</v>
+        <v>15.4013500213623</v>
       </c>
       <c r="C85" t="n">
-        <v>15.8416427478974</v>
+        <v>15.84164176695957</v>
       </c>
       <c r="D85" t="n">
-        <v>15.17453256164258</v>
+        <v>15.17453162201319</v>
       </c>
       <c r="E85" t="n">
-        <v>15.60593102498302</v>
+        <v>15.60593005864081</v>
       </c>
       <c r="F85" t="n">
         <v>1029200</v>
@@ -2152,16 +2152,16 @@
         <v>44223</v>
       </c>
       <c r="B87" t="n">
-        <v>15.00552940368652</v>
+        <v>15.00553131103516</v>
       </c>
       <c r="C87" t="n">
-        <v>15.5703477505178</v>
+        <v>15.57034972966033</v>
       </c>
       <c r="D87" t="n">
-        <v>14.53410435971512</v>
+        <v>14.53410620714105</v>
       </c>
       <c r="E87" t="n">
-        <v>14.74313271733759</v>
+        <v>14.74313459133305</v>
       </c>
       <c r="F87" t="n">
         <v>1909000</v>
@@ -2192,16 +2192,16 @@
         <v>44225</v>
       </c>
       <c r="B89" t="n">
-        <v>15.74380111694336</v>
+        <v>15.74379825592041</v>
       </c>
       <c r="C89" t="n">
-        <v>16.55322800940445</v>
+        <v>16.55322500128939</v>
       </c>
       <c r="D89" t="n">
-        <v>15.38800765940311</v>
+        <v>15.38800486303628</v>
       </c>
       <c r="E89" t="n">
-        <v>16.01064451354961</v>
+        <v>16.01064160403487</v>
       </c>
       <c r="F89" t="n">
         <v>3936400</v>
@@ -2252,16 +2252,16 @@
         <v>44230</v>
       </c>
       <c r="B92" t="n">
-        <v>17.61170768737793</v>
+        <v>17.6117057800293</v>
       </c>
       <c r="C92" t="n">
-        <v>17.78960441009847</v>
+        <v>17.78960248348361</v>
       </c>
       <c r="D92" t="n">
-        <v>16.94015086737822</v>
+        <v>16.94014903275922</v>
       </c>
       <c r="E92" t="n">
-        <v>17.0824675669351</v>
+        <v>17.08246571690319</v>
       </c>
       <c r="F92" t="n">
         <v>1128200</v>
@@ -2292,16 +2292,16 @@
         <v>44232</v>
       </c>
       <c r="B94" t="n">
-        <v>18.80805969238281</v>
+        <v>18.80805778503418</v>
       </c>
       <c r="C94" t="n">
-        <v>19.56856487465802</v>
+        <v>19.56856289018561</v>
       </c>
       <c r="D94" t="n">
-        <v>17.78960443150729</v>
+        <v>17.78960262744146</v>
       </c>
       <c r="E94" t="n">
-        <v>17.99863282647314</v>
+        <v>17.99863100120949</v>
       </c>
       <c r="F94" t="n">
         <v>14342200</v>
@@ -2312,16 +2312,16 @@
         <v>44235</v>
       </c>
       <c r="B95" t="n">
-        <v>19.23056221008301</v>
+        <v>19.23056602478027</v>
       </c>
       <c r="C95" t="n">
-        <v>19.36843055199105</v>
+        <v>19.36843439403676</v>
       </c>
       <c r="D95" t="n">
-        <v>18.46560871350112</v>
+        <v>18.46561237645731</v>
       </c>
       <c r="E95" t="n">
-        <v>18.81250544030044</v>
+        <v>18.81250917206929</v>
       </c>
       <c r="F95" t="n">
         <v>1758400</v>
@@ -2372,16 +2372,16 @@
         <v>44238</v>
       </c>
       <c r="B98" t="n">
-        <v>18.63461112976074</v>
+        <v>18.63460922241211</v>
       </c>
       <c r="C98" t="n">
-        <v>19.14606123399878</v>
+        <v>19.14605927430059</v>
       </c>
       <c r="D98" t="n">
-        <v>18.43447774264635</v>
+        <v>18.4344758557824</v>
       </c>
       <c r="E98" t="n">
-        <v>18.55900442949581</v>
+        <v>18.55900252988591</v>
       </c>
       <c r="F98" t="n">
         <v>912400</v>
@@ -2392,16 +2392,16 @@
         <v>44239</v>
       </c>
       <c r="B99" t="n">
-        <v>18.51897430419922</v>
+        <v>18.51897621154785</v>
       </c>
       <c r="C99" t="n">
-        <v>18.72355430780561</v>
+        <v>18.72355623622481</v>
       </c>
       <c r="D99" t="n">
-        <v>18.16318262476451</v>
+        <v>18.16318449546863</v>
       </c>
       <c r="E99" t="n">
-        <v>18.58123763603172</v>
+        <v>18.58123954979312</v>
       </c>
       <c r="F99" t="n">
         <v>849600</v>
@@ -2492,16 +2492,16 @@
         <v>44250</v>
       </c>
       <c r="B104" t="n">
-        <v>17.70065498352051</v>
+        <v>17.70065307617188</v>
       </c>
       <c r="C104" t="n">
-        <v>18.1009217372794</v>
+        <v>18.10091978679969</v>
       </c>
       <c r="D104" t="n">
-        <v>17.5183116171523</v>
+        <v>17.51830972945222</v>
       </c>
       <c r="E104" t="n">
-        <v>17.86076168502407</v>
+        <v>17.860759760423</v>
       </c>
       <c r="F104" t="n">
         <v>1151400</v>
@@ -2512,16 +2512,16 @@
         <v>44251</v>
       </c>
       <c r="B105" t="n">
-        <v>17.68731307983398</v>
+        <v>17.68731117248535</v>
       </c>
       <c r="C105" t="n">
-        <v>18.09647313665348</v>
+        <v>18.09647118518221</v>
       </c>
       <c r="D105" t="n">
-        <v>17.54499639080558</v>
+        <v>17.54499449880396</v>
       </c>
       <c r="E105" t="n">
-        <v>17.70510309009973</v>
+        <v>17.70510118083267</v>
       </c>
       <c r="F105" t="n">
         <v>1411000</v>
@@ -2572,16 +2572,16 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>16.44648742675781</v>
+        <v>16.44648933410645</v>
       </c>
       <c r="C108" t="n">
-        <v>17.0246491728847</v>
+        <v>17.02465114728449</v>
       </c>
       <c r="D108" t="n">
-        <v>16.27748572675039</v>
+        <v>16.27748761449939</v>
       </c>
       <c r="E108" t="n">
-        <v>16.69998912849459</v>
+        <v>16.69999106524258</v>
       </c>
       <c r="F108" t="n">
         <v>1540800</v>
@@ -2592,16 +2592,16 @@
         <v>44257</v>
       </c>
       <c r="B109" t="n">
-        <v>16.655517578125</v>
+        <v>16.65551567077637</v>
       </c>
       <c r="C109" t="n">
-        <v>16.90457095571786</v>
+        <v>16.90456901984825</v>
       </c>
       <c r="D109" t="n">
-        <v>15.7526939947042</v>
+        <v>15.75269219074469</v>
       </c>
       <c r="E109" t="n">
-        <v>16.1796457927399</v>
+        <v>16.17964393988693</v>
       </c>
       <c r="F109" t="n">
         <v>1243600</v>
@@ -2672,16 +2672,16 @@
         <v>44263</v>
       </c>
       <c r="B113" t="n">
-        <v>14.91213417053223</v>
+        <v>14.91213512420654</v>
       </c>
       <c r="C113" t="n">
-        <v>16.05956437827389</v>
+        <v>16.0595654053297</v>
       </c>
       <c r="D113" t="n">
-        <v>14.76537082800059</v>
+        <v>14.76537177228896</v>
       </c>
       <c r="E113" t="n">
-        <v>16.01064269858043</v>
+        <v>16.01064372250756</v>
       </c>
       <c r="F113" t="n">
         <v>3236800</v>
@@ -2692,16 +2692,16 @@
         <v>44264</v>
       </c>
       <c r="B114" t="n">
-        <v>14.76537036895752</v>
+        <v>14.76537227630615</v>
       </c>
       <c r="C114" t="n">
-        <v>15.42358545584995</v>
+        <v>15.42358744822494</v>
       </c>
       <c r="D114" t="n">
-        <v>14.55634199732897</v>
+        <v>14.55634387767591</v>
       </c>
       <c r="E114" t="n">
-        <v>15.11671542442504</v>
+        <v>15.11671737715943</v>
       </c>
       <c r="F114" t="n">
         <v>1628800</v>
@@ -2712,16 +2712,16 @@
         <v>44265</v>
       </c>
       <c r="B115" t="n">
-        <v>14.64529228210449</v>
+        <v>14.64529132843018</v>
       </c>
       <c r="C115" t="n">
-        <v>15.05445237801519</v>
+        <v>15.05445139769713</v>
       </c>
       <c r="D115" t="n">
-        <v>14.28505217427527</v>
+        <v>14.28505124405912</v>
       </c>
       <c r="E115" t="n">
-        <v>15.05445237801519</v>
+        <v>15.05445139769713</v>
       </c>
       <c r="F115" t="n">
         <v>3352600</v>
@@ -2732,16 +2732,16 @@
         <v>44266</v>
       </c>
       <c r="B116" t="n">
-        <v>15.81940650939941</v>
+        <v>15.81940460205078</v>
       </c>
       <c r="C116" t="n">
-        <v>15.99285489107494</v>
+        <v>15.99285296281361</v>
       </c>
       <c r="D116" t="n">
-        <v>15.15674465650835</v>
+        <v>15.15674282905697</v>
       </c>
       <c r="E116" t="n">
-        <v>15.15674465650835</v>
+        <v>15.15674282905697</v>
       </c>
       <c r="F116" t="n">
         <v>2295400</v>
@@ -2752,16 +2752,16 @@
         <v>44267</v>
       </c>
       <c r="B117" t="n">
-        <v>15.61037826538086</v>
+        <v>15.61037635803223</v>
       </c>
       <c r="C117" t="n">
-        <v>15.96172338382784</v>
+        <v>15.96172143355023</v>
       </c>
       <c r="D117" t="n">
-        <v>15.41913986908941</v>
+        <v>15.41913798510718</v>
       </c>
       <c r="E117" t="n">
-        <v>15.96172338382784</v>
+        <v>15.96172143355023</v>
       </c>
       <c r="F117" t="n">
         <v>1034800</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708873748779</v>
+        <v>15.67708778381348</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619716243003</v>
+        <v>16.00619618873527</v>
       </c>
       <c r="D118" t="n">
-        <v>15.49474536187826</v>
+        <v>15.49474441929632</v>
       </c>
       <c r="E118" t="n">
-        <v>15.61482539409169</v>
+        <v>15.614824444205</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2792,16 +2792,16 @@
         <v>44271</v>
       </c>
       <c r="B119" t="n">
-        <v>16.46872138977051</v>
+        <v>16.46872520446777</v>
       </c>
       <c r="C119" t="n">
-        <v>16.83785639812166</v>
+        <v>16.83786029832273</v>
       </c>
       <c r="D119" t="n">
-        <v>15.68153139896302</v>
+        <v>15.6815350313212</v>
       </c>
       <c r="E119" t="n">
-        <v>15.68597974895794</v>
+        <v>15.68598338234651</v>
       </c>
       <c r="F119" t="n">
         <v>1963400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880805969238</v>
+        <v>16.58880615234375</v>
       </c>
       <c r="C120" t="n">
-        <v>16.75780979991704</v>
+        <v>16.75780787313692</v>
       </c>
       <c r="D120" t="n">
-        <v>16.07735788033358</v>
+        <v>16.07735603179049</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298957845627</v>
+        <v>16.19298771661808</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2832,16 +2832,16 @@
         <v>44273</v>
       </c>
       <c r="B121" t="n">
-        <v>16.21966934204102</v>
+        <v>16.21967124938965</v>
       </c>
       <c r="C121" t="n">
-        <v>17.29149274020432</v>
+        <v>17.2914947735938</v>
       </c>
       <c r="D121" t="n">
-        <v>16.07735266899806</v>
+        <v>16.077354559611</v>
       </c>
       <c r="E121" t="n">
-        <v>16.58880268257474</v>
+        <v>16.58880463333153</v>
       </c>
       <c r="F121" t="n">
         <v>1568800</v>
@@ -2852,16 +2852,16 @@
         <v>44274</v>
       </c>
       <c r="B122" t="n">
-        <v>16.32196044921875</v>
+        <v>16.32196235656738</v>
       </c>
       <c r="C122" t="n">
-        <v>16.54433047796411</v>
+        <v>16.54433241129841</v>
       </c>
       <c r="D122" t="n">
-        <v>15.89056205055718</v>
+        <v>15.89056390749354</v>
       </c>
       <c r="E122" t="n">
-        <v>16.17519541590345</v>
+        <v>16.17519730610144</v>
       </c>
       <c r="F122" t="n">
         <v>1059200</v>
@@ -2892,16 +2892,16 @@
         <v>44278</v>
       </c>
       <c r="B124" t="n">
-        <v>16.0995922088623</v>
+        <v>16.09959411621094</v>
       </c>
       <c r="C124" t="n">
-        <v>16.49985728713733</v>
+        <v>16.49985924190611</v>
       </c>
       <c r="D124" t="n">
-        <v>15.87277380427914</v>
+        <v>15.87277568475618</v>
       </c>
       <c r="E124" t="n">
-        <v>16.4553839550675</v>
+        <v>16.45538590456745</v>
       </c>
       <c r="F124" t="n">
         <v>855200</v>
@@ -2932,16 +2932,16 @@
         <v>44280</v>
       </c>
       <c r="B126" t="n">
-        <v>16.06845855712891</v>
+        <v>16.06846046447754</v>
       </c>
       <c r="C126" t="n">
-        <v>16.22411689674175</v>
+        <v>16.22411882256725</v>
       </c>
       <c r="D126" t="n">
-        <v>15.07224009396071</v>
+        <v>15.07224188305681</v>
       </c>
       <c r="E126" t="n">
-        <v>15.38800512377458</v>
+        <v>15.38800695035243</v>
       </c>
       <c r="F126" t="n">
         <v>1320600</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.58369255065918</v>
+        <v>15.58369159698486</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174760813446</v>
+        <v>16.00174662887645</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245418372239</v>
+        <v>15.39245324175128</v>
       </c>
       <c r="E128" t="n">
-        <v>15.7437992482387</v>
+        <v>15.74379828476634</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514427185059</v>
+        <v>16.09514236450195</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23746097399444</v>
+        <v>16.23745904978063</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48585078476289</v>
+        <v>15.48584894961834</v>
       </c>
       <c r="E129" t="n">
-        <v>15.58814080839448</v>
+        <v>15.58813896112809</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3032,16 +3032,16 @@
         <v>44287</v>
       </c>
       <c r="B131" t="n">
-        <v>16.59325408935547</v>
+        <v>16.59325218200684</v>
       </c>
       <c r="C131" t="n">
-        <v>17.04244085328361</v>
+        <v>17.0424388943022</v>
       </c>
       <c r="D131" t="n">
-        <v>16.48651571663801</v>
+        <v>16.48651382155865</v>
       </c>
       <c r="E131" t="n">
-        <v>17.03799419867195</v>
+        <v>17.03799224020167</v>
       </c>
       <c r="F131" t="n">
         <v>1225400</v>
@@ -3072,16 +3072,16 @@
         <v>44292</v>
       </c>
       <c r="B133" t="n">
-        <v>17.52276229858398</v>
+        <v>17.52276039123535</v>
       </c>
       <c r="C133" t="n">
-        <v>17.56723563422825</v>
+        <v>17.5672337220387</v>
       </c>
       <c r="D133" t="n">
-        <v>16.82896706530999</v>
+        <v>16.8289652334808</v>
       </c>
       <c r="E133" t="n">
-        <v>16.89123041383156</v>
+        <v>16.89122857522503</v>
       </c>
       <c r="F133" t="n">
         <v>1684600</v>
@@ -3112,16 +3112,16 @@
         <v>44294</v>
       </c>
       <c r="B135" t="n">
-        <v>17.60725975036621</v>
+        <v>17.60725784301758</v>
       </c>
       <c r="C135" t="n">
-        <v>17.90968313903537</v>
+        <v>17.909681198926</v>
       </c>
       <c r="D135" t="n">
-        <v>17.2737046919707</v>
+        <v>17.27370282075522</v>
       </c>
       <c r="E135" t="n">
-        <v>17.38044305713872</v>
+        <v>17.38044117436055</v>
       </c>
       <c r="F135" t="n">
         <v>710000</v>
@@ -3172,16 +3172,16 @@
         <v>44299</v>
       </c>
       <c r="B138" t="n">
-        <v>17.40712547302246</v>
+        <v>17.40712738037109</v>
       </c>
       <c r="C138" t="n">
-        <v>17.74068051411476</v>
+        <v>17.74068245801198</v>
       </c>
       <c r="D138" t="n">
-        <v>17.20254545499086</v>
+        <v>17.20254733992308</v>
       </c>
       <c r="E138" t="n">
-        <v>17.74068051411476</v>
+        <v>17.74068245801198</v>
       </c>
       <c r="F138" t="n">
         <v>699800</v>
@@ -3212,16 +3212,16 @@
         <v>44301</v>
       </c>
       <c r="B140" t="n">
-        <v>17.38044166564941</v>
+        <v>17.38044357299805</v>
       </c>
       <c r="C140" t="n">
-        <v>17.60281168677666</v>
+        <v>17.60281361852843</v>
       </c>
       <c r="D140" t="n">
-        <v>17.17141330289424</v>
+        <v>17.17141518730387</v>
       </c>
       <c r="E140" t="n">
-        <v>17.17141330289424</v>
+        <v>17.17141518730387</v>
       </c>
       <c r="F140" t="n">
         <v>924800</v>
@@ -3292,16 +3292,16 @@
         <v>44308</v>
       </c>
       <c r="B144" t="n">
-        <v>17.32707214355469</v>
+        <v>17.32707023620605</v>
       </c>
       <c r="C144" t="n">
-        <v>17.97639221698004</v>
+        <v>17.97639023815483</v>
       </c>
       <c r="D144" t="n">
-        <v>17.26925715789328</v>
+        <v>17.26925525690887</v>
       </c>
       <c r="E144" t="n">
-        <v>17.94970889945899</v>
+        <v>17.94970692357105</v>
       </c>
       <c r="F144" t="n">
         <v>1084000</v>
@@ -3312,16 +3312,16 @@
         <v>44309</v>
       </c>
       <c r="B145" t="n">
-        <v>17.2114429473877</v>
+        <v>17.21144104003906</v>
       </c>
       <c r="C145" t="n">
-        <v>17.57168135804453</v>
+        <v>17.57167941077477</v>
       </c>
       <c r="D145" t="n">
-        <v>16.88233451279305</v>
+        <v>16.88233264191577</v>
       </c>
       <c r="E145" t="n">
-        <v>17.52276137004772</v>
+        <v>17.52275942819921</v>
       </c>
       <c r="F145" t="n">
         <v>903000</v>
@@ -3352,16 +3352,16 @@
         <v>44313</v>
       </c>
       <c r="B147" t="n">
-        <v>17.33596992492676</v>
+        <v>17.33596801757812</v>
       </c>
       <c r="C147" t="n">
-        <v>17.78071005136372</v>
+        <v>17.78070809508361</v>
       </c>
       <c r="D147" t="n">
-        <v>17.01130983621365</v>
+        <v>17.01130796458497</v>
       </c>
       <c r="E147" t="n">
-        <v>17.0468898606721</v>
+        <v>17.04688798512881</v>
       </c>
       <c r="F147" t="n">
         <v>1372600</v>
@@ -3372,16 +3372,16 @@
         <v>44314</v>
       </c>
       <c r="B148" t="n">
-        <v>18.56789970397949</v>
+        <v>18.56789779663086</v>
       </c>
       <c r="C148" t="n">
-        <v>18.63905805414477</v>
+        <v>18.63905613948654</v>
       </c>
       <c r="D148" t="n">
-        <v>17.32707438245799</v>
+        <v>17.32707260257054</v>
       </c>
       <c r="E148" t="n">
-        <v>17.33596938829726</v>
+        <v>17.33596760749609</v>
       </c>
       <c r="F148" t="n">
         <v>2195600</v>
@@ -3392,16 +3392,16 @@
         <v>44315</v>
       </c>
       <c r="B149" t="n">
-        <v>18.93703460693359</v>
+        <v>18.93703269958496</v>
       </c>
       <c r="C149" t="n">
-        <v>19.0704562999812</v>
+        <v>19.07045437919426</v>
       </c>
       <c r="D149" t="n">
-        <v>18.13205440095317</v>
+        <v>18.13205257468259</v>
       </c>
       <c r="E149" t="n">
-        <v>18.57234615766514</v>
+        <v>18.57234428704813</v>
       </c>
       <c r="F149" t="n">
         <v>2301200</v>
@@ -3412,16 +3412,16 @@
         <v>44316</v>
       </c>
       <c r="B150" t="n">
-        <v>19.34006118774414</v>
+        <v>19.34005928039551</v>
       </c>
       <c r="C150" t="n">
-        <v>19.34006118774414</v>
+        <v>19.34005928039551</v>
       </c>
       <c r="D150" t="n">
-        <v>18.38334087467527</v>
+        <v>18.38333906167997</v>
       </c>
       <c r="E150" t="n">
-        <v>18.86617264318869</v>
+        <v>18.86617078257573</v>
       </c>
       <c r="F150" t="n">
         <v>2355400</v>
@@ -3452,16 +3452,16 @@
         <v>44320</v>
       </c>
       <c r="B152" t="n">
-        <v>19.79607009887695</v>
+        <v>19.79606819152832</v>
       </c>
       <c r="C152" t="n">
-        <v>20.00619153898745</v>
+        <v>20.00618961139364</v>
       </c>
       <c r="D152" t="n">
-        <v>19.25959258395553</v>
+        <v>19.25959072829643</v>
       </c>
       <c r="E152" t="n">
-        <v>19.4518292800361</v>
+        <v>19.45182740585503</v>
       </c>
       <c r="F152" t="n">
         <v>1635200</v>
@@ -3472,16 +3472,16 @@
         <v>44321</v>
       </c>
       <c r="B153" t="n">
-        <v>20.46219825744629</v>
+        <v>20.46219635009766</v>
       </c>
       <c r="C153" t="n">
-        <v>21.00761898287081</v>
+        <v>21.00761702468171</v>
       </c>
       <c r="D153" t="n">
-        <v>19.89442458705298</v>
+        <v>19.8944227326284</v>
       </c>
       <c r="E153" t="n">
-        <v>20.09113289036689</v>
+        <v>20.09113101760648</v>
       </c>
       <c r="F153" t="n">
         <v>1994000</v>
@@ -3492,16 +3492,16 @@
         <v>44322</v>
       </c>
       <c r="B154" t="n">
-        <v>20.4309024810791</v>
+        <v>20.43090057373047</v>
       </c>
       <c r="C154" t="n">
-        <v>20.65443532724973</v>
+        <v>20.65443339903295</v>
       </c>
       <c r="D154" t="n">
-        <v>20.16266204242219</v>
+        <v>20.16266016011543</v>
       </c>
       <c r="E154" t="n">
-        <v>20.46219694310937</v>
+        <v>20.46219503283921</v>
       </c>
       <c r="F154" t="n">
         <v>1030200</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.8332633972168</v>
+        <v>20.83326148986816</v>
       </c>
       <c r="C155" t="n">
-        <v>20.87797099574675</v>
+        <v>20.877969084305</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384469788557</v>
+        <v>20.36384283351365</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902947604076</v>
+        <v>20.86902756541763</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3532,16 +3532,16 @@
         <v>44326</v>
       </c>
       <c r="B156" t="n">
-        <v>20.36384010314941</v>
+        <v>20.36384201049805</v>
       </c>
       <c r="C156" t="n">
-        <v>20.94502510954077</v>
+        <v>20.94502707132523</v>
       </c>
       <c r="D156" t="n">
-        <v>20.25207369017338</v>
+        <v>20.25207558705358</v>
       </c>
       <c r="E156" t="n">
-        <v>20.83325869656473</v>
+        <v>20.83326064788076</v>
       </c>
       <c r="F156" t="n">
         <v>979800</v>
@@ -3552,16 +3552,16 @@
         <v>44327</v>
       </c>
       <c r="B157" t="n">
-        <v>20.60078811645508</v>
+        <v>20.60078620910645</v>
       </c>
       <c r="C157" t="n">
-        <v>20.60972792961658</v>
+        <v>20.60972602144025</v>
       </c>
       <c r="D157" t="n">
-        <v>19.7826570731339</v>
+        <v>19.78265524153291</v>
       </c>
       <c r="E157" t="n">
-        <v>20.25207571344624</v>
+        <v>20.25207383838357</v>
       </c>
       <c r="F157" t="n">
         <v>1012800</v>
@@ -3572,16 +3572,16 @@
         <v>44328</v>
       </c>
       <c r="B158" t="n">
-        <v>20.15818977355957</v>
+        <v>20.1581916809082</v>
       </c>
       <c r="C158" t="n">
-        <v>20.5963138960601</v>
+        <v>20.59631584486362</v>
       </c>
       <c r="D158" t="n">
-        <v>19.57253317127392</v>
+        <v>19.57253502320829</v>
       </c>
       <c r="E158" t="n">
-        <v>20.5963138960601</v>
+        <v>20.59631584486362</v>
       </c>
       <c r="F158" t="n">
         <v>1344400</v>
@@ -3592,16 +3592,16 @@
         <v>44329</v>
       </c>
       <c r="B159" t="n">
-        <v>20.90479278564453</v>
+        <v>20.9047908782959</v>
       </c>
       <c r="C159" t="n">
-        <v>20.97185332731664</v>
+        <v>20.97185141384942</v>
       </c>
       <c r="D159" t="n">
-        <v>20.15819383510242</v>
+        <v>20.15819199587331</v>
       </c>
       <c r="E159" t="n">
-        <v>20.25654884144274</v>
+        <v>20.25654699323974</v>
       </c>
       <c r="F159" t="n">
         <v>1469200</v>
@@ -3612,16 +3612,16 @@
         <v>44330</v>
       </c>
       <c r="B160" t="n">
-        <v>20.29678153991699</v>
+        <v>20.29677963256836</v>
       </c>
       <c r="C160" t="n">
-        <v>21.23561873883424</v>
+        <v>21.23561674326029</v>
       </c>
       <c r="D160" t="n">
-        <v>20.22972100909998</v>
+        <v>20.22971910805323</v>
       </c>
       <c r="E160" t="n">
-        <v>21.01655581619614</v>
+        <v>21.01655384120819</v>
       </c>
       <c r="F160" t="n">
         <v>1009800</v>
@@ -3632,16 +3632,16 @@
         <v>44333</v>
       </c>
       <c r="B161" t="n">
-        <v>20.98526382446289</v>
+        <v>20.98526191711426</v>
       </c>
       <c r="C161" t="n">
-        <v>21.13279632744209</v>
+        <v>21.13279440668424</v>
       </c>
       <c r="D161" t="n">
-        <v>20.03748499628314</v>
+        <v>20.03748317507803</v>
       </c>
       <c r="E161" t="n">
-        <v>20.16266284941433</v>
+        <v>20.16266101683182</v>
       </c>
       <c r="F161" t="n">
         <v>1096800</v>
@@ -3652,16 +3652,16 @@
         <v>44334</v>
       </c>
       <c r="B162" t="n">
-        <v>21.12385177612305</v>
+        <v>21.12385368347168</v>
       </c>
       <c r="C162" t="n">
-        <v>21.74080284519728</v>
+        <v>21.74080480825265</v>
       </c>
       <c r="D162" t="n">
-        <v>20.88243591795225</v>
+        <v>20.88243780350257</v>
       </c>
       <c r="E162" t="n">
-        <v>21.15067632883762</v>
+        <v>21.15067823860833</v>
       </c>
       <c r="F162" t="n">
         <v>1192600</v>
@@ -3692,16 +3692,16 @@
         <v>44336</v>
       </c>
       <c r="B164" t="n">
-        <v>21.86151313781738</v>
+        <v>21.86151123046875</v>
       </c>
       <c r="C164" t="n">
-        <v>21.93751348726187</v>
+        <v>21.93751157328245</v>
       </c>
       <c r="D164" t="n">
-        <v>21.37868136927493</v>
+        <v>21.37867950405186</v>
       </c>
       <c r="E164" t="n">
-        <v>21.49044779287232</v>
+        <v>21.49044591789798</v>
       </c>
       <c r="F164" t="n">
         <v>917400</v>
@@ -3752,16 +3752,16 @@
         <v>44341</v>
       </c>
       <c r="B167" t="n">
-        <v>22.17892646789551</v>
+        <v>22.17893028259277</v>
       </c>
       <c r="C167" t="n">
-        <v>22.36222331038142</v>
+        <v>22.3622271566051</v>
       </c>
       <c r="D167" t="n">
-        <v>21.77209680747946</v>
+        <v>21.77210055220345</v>
       </c>
       <c r="E167" t="n">
-        <v>21.98221649664815</v>
+        <v>21.98222027751199</v>
       </c>
       <c r="F167" t="n">
         <v>773000</v>
@@ -3772,16 +3772,16 @@
         <v>44342</v>
       </c>
       <c r="B168" t="n">
-        <v>22.17445755004883</v>
+        <v>22.17445945739746</v>
       </c>
       <c r="C168" t="n">
-        <v>22.42481495049289</v>
+        <v>22.42481687937616</v>
       </c>
       <c r="D168" t="n">
-        <v>21.53515347667831</v>
+        <v>21.53515532903684</v>
       </c>
       <c r="E168" t="n">
-        <v>22.17445755004883</v>
+        <v>22.17445945739746</v>
       </c>
       <c r="F168" t="n">
         <v>837000</v>
@@ -3792,16 +3792,16 @@
         <v>44343</v>
       </c>
       <c r="B169" t="n">
-        <v>22.3443431854248</v>
+        <v>22.34434509277344</v>
       </c>
       <c r="C169" t="n">
-        <v>22.3443431854248</v>
+        <v>22.34434509277344</v>
       </c>
       <c r="D169" t="n">
-        <v>21.80339410488992</v>
+        <v>21.80339596606228</v>
       </c>
       <c r="E169" t="n">
-        <v>22.27281274258895</v>
+        <v>22.27281464383163</v>
       </c>
       <c r="F169" t="n">
         <v>1342400</v>
@@ -3852,16 +3852,16 @@
         <v>44348</v>
       </c>
       <c r="B172" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69447898864746</v>
       </c>
       <c r="C172" t="n">
-        <v>24.09237101528835</v>
+        <v>24.09236713653301</v>
       </c>
       <c r="D172" t="n">
-        <v>23.10435619826109</v>
+        <v>23.10435247857136</v>
       </c>
       <c r="E172" t="n">
-        <v>23.32341744272831</v>
+        <v>23.32341368777078</v>
       </c>
       <c r="F172" t="n">
         <v>1770600</v>
@@ -3872,16 +3872,16 @@
         <v>44349</v>
       </c>
       <c r="B173" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69447898864746</v>
       </c>
       <c r="C173" t="n">
-        <v>24.03872360721357</v>
+        <v>24.0387197370952</v>
       </c>
       <c r="D173" t="n">
-        <v>23.4709499467094</v>
+        <v>23.47094616799984</v>
       </c>
       <c r="E173" t="n">
-        <v>24.03872360721357</v>
+        <v>24.0387197370952</v>
       </c>
       <c r="F173" t="n">
         <v>823800</v>
@@ -3892,16 +3892,16 @@
         <v>44351</v>
       </c>
       <c r="B174" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69447898864746</v>
       </c>
       <c r="C174" t="n">
-        <v>23.91801565998005</v>
+        <v>23.91801180929508</v>
       </c>
       <c r="D174" t="n">
-        <v>23.39941950080291</v>
+        <v>23.39941573360941</v>
       </c>
       <c r="E174" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69447898864746</v>
       </c>
       <c r="F174" t="n">
         <v>902800</v>
@@ -3912,16 +3912,16 @@
         <v>44354</v>
       </c>
       <c r="B175" t="n">
-        <v>23.51565551757812</v>
+        <v>23.51565361022949</v>
       </c>
       <c r="C175" t="n">
-        <v>23.95378141142314</v>
+        <v>23.95377946853823</v>
       </c>
       <c r="D175" t="n">
-        <v>23.24741677541455</v>
+        <v>23.24741488982269</v>
       </c>
       <c r="E175" t="n">
-        <v>23.56483301823953</v>
+        <v>23.56483110690212</v>
       </c>
       <c r="F175" t="n">
         <v>1060000</v>
@@ -3932,16 +3932,16 @@
         <v>44355</v>
       </c>
       <c r="B176" t="n">
-        <v>23.40388679504395</v>
+        <v>23.40388870239258</v>
       </c>
       <c r="C176" t="n">
-        <v>23.68106873423341</v>
+        <v>23.68107066417156</v>
       </c>
       <c r="D176" t="n">
-        <v>22.95235122542912</v>
+        <v>22.95235309597892</v>
       </c>
       <c r="E176" t="n">
-        <v>23.47094732671691</v>
+        <v>23.47094923953079</v>
       </c>
       <c r="F176" t="n">
         <v>1006800</v>
@@ -3952,16 +3952,16 @@
         <v>44356</v>
       </c>
       <c r="B177" t="n">
-        <v>23.51565551757812</v>
+        <v>23.51565361022949</v>
       </c>
       <c r="C177" t="n">
-        <v>23.60059909341884</v>
+        <v>23.60059717918046</v>
       </c>
       <c r="D177" t="n">
-        <v>23.18035623716349</v>
+        <v>23.1803543570109</v>
       </c>
       <c r="E177" t="n">
-        <v>23.44412507263982</v>
+        <v>23.444123171093</v>
       </c>
       <c r="F177" t="n">
         <v>621600</v>
@@ -3972,16 +3972,16 @@
         <v>44357</v>
       </c>
       <c r="B178" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69447898864746</v>
       </c>
       <c r="C178" t="n">
-        <v>23.89119110323249</v>
+        <v>23.89118725686614</v>
       </c>
       <c r="D178" t="n">
-        <v>23.44859700212994</v>
+        <v>23.4485932270191</v>
       </c>
       <c r="E178" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69447898864746</v>
       </c>
       <c r="F178" t="n">
         <v>946600</v>
@@ -4012,16 +4012,16 @@
         <v>44361</v>
       </c>
       <c r="B180" t="n">
-        <v>24.58861351013184</v>
+        <v>24.5886116027832</v>
       </c>
       <c r="C180" t="n">
-        <v>24.76744047237364</v>
+        <v>24.76743855115333</v>
       </c>
       <c r="D180" t="n">
-        <v>23.26082783485022</v>
+        <v>23.26082603049845</v>
       </c>
       <c r="E180" t="n">
-        <v>23.45753783440027</v>
+        <v>23.45753601478963</v>
       </c>
       <c r="F180" t="n">
         <v>1774600</v>
@@ -4072,16 +4072,16 @@
         <v>44364</v>
       </c>
       <c r="B183" t="n">
-        <v>24.58861351013184</v>
+        <v>24.5886116027832</v>
       </c>
       <c r="C183" t="n">
-        <v>24.71379136044892</v>
+        <v>24.71378944339019</v>
       </c>
       <c r="D183" t="n">
-        <v>23.96719245974302</v>
+        <v>23.96719060059827</v>
       </c>
       <c r="E183" t="n">
-        <v>24.63331939798214</v>
+        <v>24.63331748716565</v>
       </c>
       <c r="F183" t="n">
         <v>897400</v>
@@ -4092,16 +4092,16 @@
         <v>44365</v>
       </c>
       <c r="B184" t="n">
-        <v>24.8970890045166</v>
+        <v>24.89708518981934</v>
       </c>
       <c r="C184" t="n">
-        <v>25.19215230760862</v>
+        <v>25.19214844770217</v>
       </c>
       <c r="D184" t="n">
-        <v>24.25778489691384</v>
+        <v>24.25778118016986</v>
       </c>
       <c r="E184" t="n">
-        <v>24.6780277596409</v>
+        <v>24.67802397850789</v>
       </c>
       <c r="F184" t="n">
         <v>1737600</v>
@@ -4112,16 +4112,16 @@
         <v>44368</v>
       </c>
       <c r="B185" t="n">
-        <v>25.23685836791992</v>
+        <v>25.23686027526855</v>
       </c>
       <c r="C185" t="n">
-        <v>25.64815798128789</v>
+        <v>25.64815991972168</v>
       </c>
       <c r="D185" t="n">
-        <v>24.69590929604326</v>
+        <v>24.6959111625081</v>
       </c>
       <c r="E185" t="n">
-        <v>25.25026979279315</v>
+        <v>25.25027170115539</v>
       </c>
       <c r="F185" t="n">
         <v>748400</v>
@@ -4132,16 +4132,16 @@
         <v>44369</v>
       </c>
       <c r="B186" t="n">
-        <v>24.58861351013184</v>
+        <v>24.5886116027832</v>
       </c>
       <c r="C186" t="n">
-        <v>25.26815357906228</v>
+        <v>25.26815161900145</v>
       </c>
       <c r="D186" t="n">
-        <v>24.54390762228154</v>
+        <v>24.54390571840076</v>
       </c>
       <c r="E186" t="n">
-        <v>25.2323875044458</v>
+        <v>25.23238554715936</v>
       </c>
       <c r="F186" t="n">
         <v>871000</v>
@@ -4212,16 +4212,16 @@
         <v>44375</v>
       </c>
       <c r="B190" t="n">
-        <v>24.48578453063965</v>
+        <v>24.48578834533691</v>
       </c>
       <c r="C190" t="n">
-        <v>25.01332210553714</v>
+        <v>25.01332600242071</v>
       </c>
       <c r="D190" t="n">
-        <v>24.06107184502963</v>
+        <v>24.06107559355992</v>
       </c>
       <c r="E190" t="n">
-        <v>24.06107184502963</v>
+        <v>24.06107559355992</v>
       </c>
       <c r="F190" t="n">
         <v>1351800</v>
@@ -4252,16 +4252,16 @@
         <v>44377</v>
       </c>
       <c r="B192" t="n">
-        <v>24.86579132080078</v>
+        <v>24.86579322814941</v>
       </c>
       <c r="C192" t="n">
-        <v>24.86579132080078</v>
+        <v>24.86579322814941</v>
       </c>
       <c r="D192" t="n">
-        <v>24.12813401130879</v>
+        <v>24.12813586207488</v>
       </c>
       <c r="E192" t="n">
-        <v>24.16836998858436</v>
+        <v>24.16837184243678</v>
       </c>
       <c r="F192" t="n">
         <v>1430400</v>
@@ -4272,16 +4272,16 @@
         <v>44378</v>
       </c>
       <c r="B193" t="n">
-        <v>24.92838287353516</v>
+        <v>24.92838096618652</v>
       </c>
       <c r="C193" t="n">
-        <v>25.96557687450705</v>
+        <v>25.96557488779945</v>
       </c>
       <c r="D193" t="n">
-        <v>24.91050154151692</v>
+        <v>24.91049963553645</v>
       </c>
       <c r="E193" t="n">
-        <v>25.2592122444671</v>
+        <v>25.25921031180567</v>
       </c>
       <c r="F193" t="n">
         <v>1991200</v>
@@ -4292,16 +4292,16 @@
         <v>44379</v>
       </c>
       <c r="B194" t="n">
-        <v>26.42605209350586</v>
+        <v>26.42605400085449</v>
       </c>
       <c r="C194" t="n">
-        <v>26.77029286492826</v>
+        <v>26.7702947971231</v>
       </c>
       <c r="D194" t="n">
-        <v>25.41568272171123</v>
+        <v>25.41568455613461</v>
       </c>
       <c r="E194" t="n">
-        <v>25.41568272171123</v>
+        <v>25.41568455613461</v>
       </c>
       <c r="F194" t="n">
         <v>2268600</v>
@@ -4312,16 +4312,16 @@
         <v>44382</v>
       </c>
       <c r="B195" t="n">
-        <v>26.53334808349609</v>
+        <v>26.53334617614746</v>
       </c>
       <c r="C195" t="n">
-        <v>26.77923557792692</v>
+        <v>26.77923365290268</v>
       </c>
       <c r="D195" t="n">
-        <v>26.17122596518936</v>
+        <v>26.17122408387186</v>
       </c>
       <c r="E195" t="n">
-        <v>26.3813456803117</v>
+        <v>26.38134378388976</v>
       </c>
       <c r="F195" t="n">
         <v>581600</v>
@@ -4392,16 +4392,16 @@
         <v>44389</v>
       </c>
       <c r="B199" t="n">
-        <v>27.54371643066406</v>
+        <v>27.5437183380127</v>
       </c>
       <c r="C199" t="n">
-        <v>27.57501089139074</v>
+        <v>27.57501280090645</v>
       </c>
       <c r="D199" t="n">
-        <v>26.56911312552412</v>
+        <v>26.56911496538337</v>
       </c>
       <c r="E199" t="n">
-        <v>26.81499890498525</v>
+        <v>26.81500076187162</v>
       </c>
       <c r="F199" t="n">
         <v>886400</v>
@@ -4412,16 +4412,16 @@
         <v>44390</v>
       </c>
       <c r="B200" t="n">
-        <v>27.6644229888916</v>
+        <v>27.66442680358887</v>
       </c>
       <c r="C200" t="n">
-        <v>27.70465896573839</v>
+        <v>27.70466278598387</v>
       </c>
       <c r="D200" t="n">
-        <v>27.16817984292119</v>
+        <v>27.1681835891906</v>
       </c>
       <c r="E200" t="n">
-        <v>27.33806526798767</v>
+        <v>27.33806903768288</v>
       </c>
       <c r="F200" t="n">
         <v>796200</v>
@@ -4432,16 +4432,16 @@
         <v>44391</v>
       </c>
       <c r="B201" t="n">
-        <v>28.17408180236816</v>
+        <v>28.17407989501953</v>
       </c>
       <c r="C201" t="n">
-        <v>28.33502573399738</v>
+        <v>28.33502381575305</v>
       </c>
       <c r="D201" t="n">
-        <v>27.44089429643097</v>
+        <v>27.44089243871817</v>
       </c>
       <c r="E201" t="n">
-        <v>27.67336867484868</v>
+        <v>27.67336680139767</v>
       </c>
       <c r="F201" t="n">
         <v>880600</v>
@@ -4452,16 +4452,16 @@
         <v>44392</v>
       </c>
       <c r="B202" t="n">
-        <v>28.47808647155762</v>
+        <v>28.47808456420898</v>
       </c>
       <c r="C202" t="n">
-        <v>28.76420655172373</v>
+        <v>28.76420462521192</v>
       </c>
       <c r="D202" t="n">
-        <v>27.81195780383505</v>
+        <v>27.81195594110106</v>
       </c>
       <c r="E202" t="n">
-        <v>28.21431763070376</v>
+        <v>28.21431574102132</v>
       </c>
       <c r="F202" t="n">
         <v>1015800</v>
@@ -4472,16 +4472,16 @@
         <v>44393</v>
       </c>
       <c r="B203" t="n">
-        <v>28.79103088378906</v>
+        <v>28.79102897644043</v>
       </c>
       <c r="C203" t="n">
-        <v>29.03244676372463</v>
+        <v>29.03244484038268</v>
       </c>
       <c r="D203" t="n">
-        <v>28.15172681585982</v>
+        <v>28.15172495086382</v>
       </c>
       <c r="E203" t="n">
-        <v>28.72844196056582</v>
+        <v>28.72844005736358</v>
       </c>
       <c r="F203" t="n">
         <v>1048600</v>
@@ -4552,16 +4552,16 @@
         <v>44399</v>
       </c>
       <c r="B207" t="n">
-        <v>30.17693328857422</v>
+        <v>30.17693138122559</v>
       </c>
       <c r="C207" t="n">
-        <v>30.65082181615548</v>
+        <v>30.65081987885448</v>
       </c>
       <c r="D207" t="n">
-        <v>29.62257280245648</v>
+        <v>29.62257093014648</v>
       </c>
       <c r="E207" t="n">
-        <v>29.69410153735533</v>
+        <v>29.69409966052432</v>
       </c>
       <c r="F207" t="n">
         <v>1168200</v>
@@ -4612,16 +4612,16 @@
         <v>44404</v>
       </c>
       <c r="B210" t="n">
-        <v>29.40798187255859</v>
+        <v>29.40797996520996</v>
       </c>
       <c r="C210" t="n">
-        <v>30.19929008971936</v>
+        <v>30.1992881310479</v>
       </c>
       <c r="D210" t="n">
-        <v>29.3006870571411</v>
+        <v>29.30068515675142</v>
       </c>
       <c r="E210" t="n">
-        <v>29.98916866018129</v>
+        <v>29.98916671513793</v>
       </c>
       <c r="F210" t="n">
         <v>1032400</v>
@@ -4632,16 +4632,16 @@
         <v>44405</v>
       </c>
       <c r="B211" t="n">
-        <v>29.43927192687988</v>
+        <v>29.43927383422852</v>
       </c>
       <c r="C211" t="n">
-        <v>30.57034745860774</v>
+        <v>30.57034943923792</v>
       </c>
       <c r="D211" t="n">
-        <v>28.7329073919184</v>
+        <v>28.7329092535022</v>
       </c>
       <c r="E211" t="n">
-        <v>29.52868710203713</v>
+        <v>29.52868901517891</v>
       </c>
       <c r="F211" t="n">
         <v>1257400</v>
@@ -4652,16 +4652,16 @@
         <v>44406</v>
       </c>
       <c r="B212" t="n">
-        <v>30.84753036499023</v>
+        <v>30.84753227233887</v>
       </c>
       <c r="C212" t="n">
-        <v>31.51365723957576</v>
+        <v>31.51365918811201</v>
       </c>
       <c r="D212" t="n">
-        <v>29.56445070016713</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="E212" t="n">
-        <v>29.56445070016713</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="F212" t="n">
         <v>1386000</v>
@@ -4672,16 +4672,16 @@
         <v>44407</v>
       </c>
       <c r="B213" t="n">
-        <v>31.13812828063965</v>
+        <v>31.13812637329102</v>
       </c>
       <c r="C213" t="n">
-        <v>31.58072239125372</v>
+        <v>31.58072045679423</v>
       </c>
       <c r="D213" t="n">
-        <v>30.41388058167417</v>
+        <v>30.41387871868892</v>
       </c>
       <c r="E213" t="n">
-        <v>30.80282898848094</v>
+        <v>30.80282710167089</v>
       </c>
       <c r="F213" t="n">
         <v>1548200</v>
@@ -4692,16 +4692,16 @@
         <v>44410</v>
       </c>
       <c r="B214" t="n">
-        <v>31.24989318847656</v>
+        <v>31.24989128112793</v>
       </c>
       <c r="C214" t="n">
-        <v>31.98755227744596</v>
+        <v>31.98755032507403</v>
       </c>
       <c r="D214" t="n">
-        <v>31.03977176322897</v>
+        <v>31.03976986870518</v>
       </c>
       <c r="E214" t="n">
-        <v>31.58072085224903</v>
+        <v>31.58071892470821</v>
       </c>
       <c r="F214" t="n">
         <v>1185600</v>
@@ -4752,16 +4752,16 @@
         <v>44413</v>
       </c>
       <c r="B217" t="n">
-        <v>29.48398017883301</v>
+        <v>29.48398208618164</v>
       </c>
       <c r="C217" t="n">
-        <v>30.38705476088549</v>
+        <v>30.38705672665493</v>
       </c>
       <c r="D217" t="n">
-        <v>29.13974110661963</v>
+        <v>29.13974299169909</v>
       </c>
       <c r="E217" t="n">
-        <v>29.82375105005952</v>
+        <v>29.82375297938827</v>
       </c>
       <c r="F217" t="n">
         <v>1197200</v>
@@ -4792,16 +4792,16 @@
         <v>44417</v>
       </c>
       <c r="B219" t="n">
-        <v>30.2395191192627</v>
+        <v>30.23952102661133</v>
       </c>
       <c r="C219" t="n">
-        <v>30.4049346312439</v>
+        <v>30.40493654902606</v>
       </c>
       <c r="D219" t="n">
-        <v>29.54209782380482</v>
+        <v>29.54209968716381</v>
       </c>
       <c r="E219" t="n">
-        <v>29.85951401368219</v>
+        <v>29.85951589706211</v>
       </c>
       <c r="F219" t="n">
         <v>1023000</v>
@@ -4852,16 +4852,16 @@
         <v>44420</v>
       </c>
       <c r="B222" t="n">
-        <v>29.32751083374023</v>
+        <v>29.32750701904297</v>
       </c>
       <c r="C222" t="n">
-        <v>31.18730588414776</v>
+        <v>31.18730182754265</v>
       </c>
       <c r="D222" t="n">
-        <v>28.46914546163251</v>
+        <v>28.46914175858482</v>
       </c>
       <c r="E222" t="n">
-        <v>28.48702849990652</v>
+        <v>28.48702479453274</v>
       </c>
       <c r="F222" t="n">
         <v>1567750</v>
@@ -4872,16 +4872,16 @@
         <v>44421</v>
       </c>
       <c r="B223" t="n">
-        <v>28.34396171569824</v>
+        <v>28.34396362304688</v>
       </c>
       <c r="C223" t="n">
-        <v>29.59574343723654</v>
+        <v>29.59574542882125</v>
       </c>
       <c r="D223" t="n">
-        <v>27.18159005069261</v>
+        <v>27.18159187982183</v>
       </c>
       <c r="E223" t="n">
-        <v>29.50633167528383</v>
+        <v>29.50633366085176</v>
       </c>
       <c r="F223" t="n">
         <v>1962050</v>
@@ -4952,16 +4952,16 @@
         <v>44427</v>
       </c>
       <c r="B227" t="n">
-        <v>26.46628952026367</v>
+        <v>26.4662914276123</v>
       </c>
       <c r="C227" t="n">
-        <v>26.73452825545211</v>
+        <v>26.73453018213193</v>
       </c>
       <c r="D227" t="n">
-        <v>24.30249148537069</v>
+        <v>24.30249323678068</v>
       </c>
       <c r="E227" t="n">
-        <v>24.8568519928722</v>
+        <v>24.85685378423334</v>
       </c>
       <c r="F227" t="n">
         <v>1738450</v>
@@ -5012,16 +5012,16 @@
         <v>44432</v>
       </c>
       <c r="B230" t="n">
-        <v>27.48559761047363</v>
+        <v>27.48559951782227</v>
       </c>
       <c r="C230" t="n">
-        <v>27.84324981090064</v>
+        <v>27.84325174306836</v>
       </c>
       <c r="D230" t="n">
-        <v>27.00276756625223</v>
+        <v>27.00276944009512</v>
       </c>
       <c r="E230" t="n">
-        <v>27.64654152702084</v>
+        <v>27.64654344553809</v>
       </c>
       <c r="F230" t="n">
         <v>835550</v>
@@ -5072,16 +5072,16 @@
         <v>44435</v>
       </c>
       <c r="B233" t="n">
-        <v>28.96985816955566</v>
+        <v>28.9698600769043</v>
       </c>
       <c r="C233" t="n">
-        <v>29.11291905438238</v>
+        <v>29.11292097115001</v>
       </c>
       <c r="D233" t="n">
-        <v>27.00276844505784</v>
+        <v>27.00277022289511</v>
       </c>
       <c r="E233" t="n">
-        <v>27.44983413649641</v>
+        <v>27.44983594376807</v>
       </c>
       <c r="F233" t="n">
         <v>1634000</v>
@@ -5092,16 +5092,16 @@
         <v>44438</v>
       </c>
       <c r="B234" t="n">
-        <v>27.68230628967285</v>
+        <v>27.68230819702148</v>
       </c>
       <c r="C234" t="n">
-        <v>29.68516205150646</v>
+        <v>29.68516409685458</v>
       </c>
       <c r="D234" t="n">
-        <v>27.55712844409084</v>
+        <v>27.55713034281455</v>
       </c>
       <c r="E234" t="n">
-        <v>28.96985764043749</v>
+        <v>28.96985963650016</v>
       </c>
       <c r="F234" t="n">
         <v>1402700</v>
@@ -5112,16 +5112,16 @@
         <v>44439</v>
       </c>
       <c r="B235" t="n">
-        <v>26.55570220947266</v>
+        <v>26.55570030212402</v>
       </c>
       <c r="C235" t="n">
-        <v>27.86113318312228</v>
+        <v>27.86113118201179</v>
       </c>
       <c r="D235" t="n">
-        <v>25.87616216775989</v>
+        <v>25.87616030921885</v>
       </c>
       <c r="E235" t="n">
-        <v>27.68230622804304</v>
+        <v>27.6823042397767</v>
       </c>
       <c r="F235" t="n">
         <v>1705500</v>
@@ -5132,16 +5132,16 @@
         <v>44440</v>
       </c>
       <c r="B236" t="n">
-        <v>26.59146690368652</v>
+        <v>26.59147071838379</v>
       </c>
       <c r="C236" t="n">
-        <v>27.25312391693015</v>
+        <v>27.25312782654588</v>
       </c>
       <c r="D236" t="n">
-        <v>25.71521856496552</v>
+        <v>25.71522225395998</v>
       </c>
       <c r="E236" t="n">
-        <v>26.55570253548375</v>
+        <v>26.55570634505042</v>
       </c>
       <c r="F236" t="n">
         <v>1751800</v>
@@ -5152,16 +5152,16 @@
         <v>44441</v>
       </c>
       <c r="B237" t="n">
-        <v>25.35756492614746</v>
+        <v>25.35756874084473</v>
       </c>
       <c r="C237" t="n">
-        <v>26.66299584222149</v>
+        <v>26.6629998533029</v>
       </c>
       <c r="D237" t="n">
-        <v>25.10720754116251</v>
+        <v>25.10721131819694</v>
       </c>
       <c r="E237" t="n">
-        <v>26.59146540442867</v>
+        <v>26.59146940474931</v>
       </c>
       <c r="F237" t="n">
         <v>1706000</v>
@@ -5172,16 +5172,16 @@
         <v>44442</v>
       </c>
       <c r="B238" t="n">
-        <v>25.03567695617676</v>
+        <v>25.03567886352539</v>
       </c>
       <c r="C238" t="n">
-        <v>25.84039480296984</v>
+        <v>25.84039677162608</v>
       </c>
       <c r="D238" t="n">
-        <v>24.80320260836184</v>
+        <v>24.80320449799936</v>
       </c>
       <c r="E238" t="n">
-        <v>25.57215608917886</v>
+        <v>25.57215803739928</v>
       </c>
       <c r="F238" t="n">
         <v>2369000</v>
@@ -5192,16 +5192,16 @@
         <v>44445</v>
       </c>
       <c r="B239" t="n">
-        <v>25.76886749267578</v>
+        <v>25.76886558532715</v>
       </c>
       <c r="C239" t="n">
-        <v>25.89404534691268</v>
+        <v>25.89404343029868</v>
       </c>
       <c r="D239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="E239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="F239" t="n">
         <v>528250</v>
@@ -5232,16 +5232,16 @@
         <v>44448</v>
       </c>
       <c r="B241" t="n">
-        <v>25.03567695617676</v>
+        <v>25.03567886352539</v>
       </c>
       <c r="C241" t="n">
-        <v>25.75098132989946</v>
+        <v>25.75098329174372</v>
       </c>
       <c r="D241" t="n">
-        <v>23.80177648515005</v>
+        <v>23.8017782984937</v>
       </c>
       <c r="E241" t="n">
-        <v>23.99848476156876</v>
+        <v>23.99848658989868</v>
       </c>
       <c r="F241" t="n">
         <v>1540350</v>
@@ -5252,16 +5252,16 @@
         <v>44449</v>
       </c>
       <c r="B242" t="n">
-        <v>25.19662094116211</v>
+        <v>25.19662284851074</v>
       </c>
       <c r="C242" t="n">
-        <v>26.19804706733655</v>
+        <v>26.19804905049173</v>
       </c>
       <c r="D242" t="n">
-        <v>24.64225877082185</v>
+        <v>24.64226063620605</v>
       </c>
       <c r="E242" t="n">
-        <v>26.0013387903359</v>
+        <v>26.00134075860054</v>
       </c>
       <c r="F242" t="n">
         <v>1514650</v>
@@ -5272,16 +5272,16 @@
         <v>44452</v>
       </c>
       <c r="B243" t="n">
-        <v>26.48416900634766</v>
+        <v>26.48417282104492</v>
       </c>
       <c r="C243" t="n">
-        <v>26.82393813905756</v>
+        <v>26.82394200269411</v>
       </c>
       <c r="D243" t="n">
-        <v>25.16085342870158</v>
+        <v>25.16085705279258</v>
       </c>
       <c r="E243" t="n">
-        <v>25.37544472916363</v>
+        <v>25.3754483841637</v>
       </c>
       <c r="F243" t="n">
         <v>1238850</v>
@@ -5372,16 +5372,16 @@
         <v>44459</v>
       </c>
       <c r="B248" t="n">
-        <v>24.17731285095215</v>
+        <v>24.17731475830078</v>
       </c>
       <c r="C248" t="n">
-        <v>24.58861245893628</v>
+        <v>24.58861439873235</v>
       </c>
       <c r="D248" t="n">
-        <v>23.71236413333686</v>
+        <v>23.71236600400568</v>
       </c>
       <c r="E248" t="n">
-        <v>24.37402113667235</v>
+        <v>24.37402305953931</v>
       </c>
       <c r="F248" t="n">
         <v>1148950</v>
@@ -5432,16 +5432,16 @@
         <v>44462</v>
       </c>
       <c r="B251" t="n">
-        <v>26.28746223449707</v>
+        <v>26.2874641418457</v>
       </c>
       <c r="C251" t="n">
-        <v>26.69876355617164</v>
+        <v>26.6987654933632</v>
       </c>
       <c r="D251" t="n">
-        <v>25.32180041218233</v>
+        <v>25.3218022494651</v>
       </c>
       <c r="E251" t="n">
-        <v>25.32180041218233</v>
+        <v>25.3218022494651</v>
       </c>
       <c r="F251" t="n">
         <v>1394250</v>
@@ -5452,16 +5452,16 @@
         <v>44463</v>
       </c>
       <c r="B252" t="n">
-        <v>25.89404487609863</v>
+        <v>25.89404678344727</v>
       </c>
       <c r="C252" t="n">
-        <v>26.1980496926496</v>
+        <v>26.19805162239115</v>
       </c>
       <c r="D252" t="n">
-        <v>25.39333176283482</v>
+        <v>25.39333363330106</v>
       </c>
       <c r="E252" t="n">
-        <v>26.1980496926496</v>
+        <v>26.19805162239115</v>
       </c>
       <c r="F252" t="n">
         <v>1097400</v>
@@ -5472,16 +5472,16 @@
         <v>44466</v>
       </c>
       <c r="B253" t="n">
-        <v>26.01922607421875</v>
+        <v>26.01922225952148</v>
       </c>
       <c r="C253" t="n">
-        <v>26.34111224319019</v>
+        <v>26.34110838130097</v>
       </c>
       <c r="D253" t="n">
-        <v>25.57216033997245</v>
+        <v>25.57215659081981</v>
       </c>
       <c r="E253" t="n">
-        <v>26.21593438333576</v>
+        <v>26.21593053979895</v>
       </c>
       <c r="F253" t="n">
         <v>663500</v>
@@ -5532,16 +5532,16 @@
         <v>44469</v>
       </c>
       <c r="B256" t="n">
-        <v>24.4455509185791</v>
+        <v>24.44555282592773</v>
       </c>
       <c r="C256" t="n">
-        <v>24.89261658760151</v>
+        <v>24.89261852983216</v>
       </c>
       <c r="D256" t="n">
-        <v>24.07001568838347</v>
+        <v>24.0700175664312</v>
       </c>
       <c r="E256" t="n">
-        <v>24.85685051547803</v>
+        <v>24.85685245491806</v>
       </c>
       <c r="F256" t="n">
         <v>989250</v>
@@ -5552,16 +5552,16 @@
         <v>44470</v>
       </c>
       <c r="B257" t="n">
-        <v>25.03567695617676</v>
+        <v>25.03567886352539</v>
       </c>
       <c r="C257" t="n">
-        <v>25.10720739354903</v>
+        <v>25.10720930634723</v>
       </c>
       <c r="D257" t="n">
-        <v>24.23095910938368</v>
+        <v>24.2309609554247</v>
       </c>
       <c r="E257" t="n">
-        <v>24.74955520668767</v>
+        <v>24.74955709223806</v>
       </c>
       <c r="F257" t="n">
         <v>904400</v>
@@ -5592,16 +5592,16 @@
         <v>44474</v>
       </c>
       <c r="B259" t="n">
-        <v>23.40835762023926</v>
+        <v>23.40835952758789</v>
       </c>
       <c r="C259" t="n">
-        <v>23.9806011043871</v>
+        <v>23.98060305836301</v>
       </c>
       <c r="D259" t="n">
-        <v>23.08646980769604</v>
+        <v>23.08647168881676</v>
       </c>
       <c r="E259" t="n">
-        <v>23.90907066886862</v>
+        <v>23.90907261701612</v>
       </c>
       <c r="F259" t="n">
         <v>1237200</v>
@@ -5612,16 +5612,16 @@
         <v>44475</v>
       </c>
       <c r="B260" t="n">
-        <v>23.60507011413574</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="C260" t="n">
-        <v>23.60507011413574</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="D260" t="n">
-        <v>22.37116945436151</v>
+        <v>22.37116583906875</v>
       </c>
       <c r="E260" t="n">
-        <v>22.97917911774201</v>
+        <v>22.97917540419186</v>
       </c>
       <c r="F260" t="n">
         <v>1199850</v>
@@ -5632,16 +5632,16 @@
         <v>44476</v>
       </c>
       <c r="B261" t="n">
-        <v>23.62295150756836</v>
+        <v>23.62294960021973</v>
       </c>
       <c r="C261" t="n">
-        <v>24.26672549756607</v>
+        <v>24.26672353823827</v>
       </c>
       <c r="D261" t="n">
-        <v>23.42624321475746</v>
+        <v>23.42624132329132</v>
       </c>
       <c r="E261" t="n">
-        <v>24.1594306852766</v>
+        <v>24.15942873461192</v>
       </c>
       <c r="F261" t="n">
         <v>699850</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35613632202148</v>
+        <v>24.35613822937012</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991024181488</v>
+        <v>24.99991219957796</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848414435849</v>
+        <v>23.99848602369909</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307545095629</v>
+        <v>24.21307734710171</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5712,16 +5712,16 @@
         <v>44483</v>
       </c>
       <c r="B265" t="n">
-        <v>24.37402153015137</v>
+        <v>24.3740234375</v>
       </c>
       <c r="C265" t="n">
-        <v>24.91050069718188</v>
+        <v>24.9105026465118</v>
       </c>
       <c r="D265" t="n">
-        <v>23.92695584186265</v>
+        <v>23.9269577142269</v>
       </c>
       <c r="E265" t="n">
-        <v>24.51708241397014</v>
+        <v>24.51708433251376</v>
       </c>
       <c r="F265" t="n">
         <v>635500</v>
@@ -5732,16 +5732,16 @@
         <v>44484</v>
       </c>
       <c r="B266" t="n">
-        <v>26.16228485107422</v>
+        <v>26.16228294372559</v>
       </c>
       <c r="C266" t="n">
-        <v>26.59146751184455</v>
+        <v>26.59146557320656</v>
       </c>
       <c r="D266" t="n">
-        <v>24.44555250257259</v>
+        <v>24.44555072038149</v>
       </c>
       <c r="E266" t="n">
-        <v>24.76744035086049</v>
+        <v>24.76743854520231</v>
       </c>
       <c r="F266" t="n">
         <v>2075800</v>
@@ -5752,16 +5752,16 @@
         <v>44487</v>
       </c>
       <c r="B267" t="n">
-        <v>26.28746223449707</v>
+        <v>26.2874641418457</v>
       </c>
       <c r="C267" t="n">
-        <v>27.37830360971465</v>
+        <v>27.37830559621184</v>
       </c>
       <c r="D267" t="n">
-        <v>25.6973356600503</v>
+        <v>25.69733752458091</v>
       </c>
       <c r="E267" t="n">
-        <v>26.6093500770754</v>
+        <v>26.60935200777937</v>
       </c>
       <c r="F267" t="n">
         <v>1715900</v>
@@ -5812,16 +5812,16 @@
         <v>44490</v>
       </c>
       <c r="B270" t="n">
-        <v>22.44269561767578</v>
+        <v>22.44269752502441</v>
       </c>
       <c r="C270" t="n">
-        <v>23.46200473789014</v>
+        <v>23.46200673186731</v>
       </c>
       <c r="D270" t="n">
-        <v>21.67374216605016</v>
+        <v>21.67374400804736</v>
       </c>
       <c r="E270" t="n">
-        <v>22.88976126063578</v>
+        <v>22.8897632059794</v>
       </c>
       <c r="F270" t="n">
         <v>1908000</v>
@@ -5872,16 +5872,16 @@
         <v>44495</v>
       </c>
       <c r="B273" t="n">
-        <v>20.29678153991699</v>
+        <v>20.29677963256836</v>
       </c>
       <c r="C273" t="n">
-        <v>21.53068200467281</v>
+        <v>21.5306799813709</v>
       </c>
       <c r="D273" t="n">
-        <v>20.17160199608659</v>
+        <v>20.17160010050145</v>
       </c>
       <c r="E273" t="n">
-        <v>21.45915156766407</v>
+        <v>21.45914955108409</v>
       </c>
       <c r="F273" t="n">
         <v>1532000</v>
@@ -5952,16 +5952,16 @@
         <v>44501</v>
       </c>
       <c r="B277" t="n">
-        <v>18.77675819396973</v>
+        <v>18.77676200866699</v>
       </c>
       <c r="C277" t="n">
-        <v>19.40265081593679</v>
+        <v>19.40265475779077</v>
       </c>
       <c r="D277" t="n">
-        <v>18.68734471862869</v>
+        <v>18.68734851516066</v>
       </c>
       <c r="E277" t="n">
-        <v>18.77675819396973</v>
+        <v>18.77676200866699</v>
       </c>
       <c r="F277" t="n">
         <v>1843300</v>
@@ -5992,16 +5992,16 @@
         <v>44504</v>
       </c>
       <c r="B279" t="n">
-        <v>19.97489356994629</v>
+        <v>19.97489547729492</v>
       </c>
       <c r="C279" t="n">
-        <v>21.31609053280524</v>
+        <v>21.31609256822115</v>
       </c>
       <c r="D279" t="n">
-        <v>19.58147531665669</v>
+        <v>19.58147718643888</v>
       </c>
       <c r="E279" t="n">
-        <v>20.04642400641529</v>
+        <v>20.04642592059417</v>
       </c>
       <c r="F279" t="n">
         <v>1953350</v>
@@ -6032,16 +6032,16 @@
         <v>44508</v>
       </c>
       <c r="B281" t="n">
-        <v>20.13583946228027</v>
+        <v>20.13584136962891</v>
       </c>
       <c r="C281" t="n">
-        <v>20.86902693468137</v>
+        <v>20.8690289114805</v>
       </c>
       <c r="D281" t="n">
-        <v>19.86759902002748</v>
+        <v>19.86760090196729</v>
       </c>
       <c r="E281" t="n">
-        <v>20.86902693468137</v>
+        <v>20.8690289114805</v>
       </c>
       <c r="F281" t="n">
         <v>919700</v>
@@ -6092,16 +6092,16 @@
         <v>44511</v>
       </c>
       <c r="B284" t="n">
-        <v>21.94198226928711</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C284" t="n">
-        <v>22.99705573941596</v>
+        <v>22.99705773847886</v>
       </c>
       <c r="D284" t="n">
-        <v>21.78103836719727</v>
+        <v>21.78104026055555</v>
       </c>
       <c r="E284" t="n">
-        <v>21.95986359863704</v>
+        <v>21.95986550754004</v>
       </c>
       <c r="F284" t="n">
         <v>2031350</v>
@@ -6172,16 +6172,16 @@
         <v>44518</v>
       </c>
       <c r="B288" t="n">
-        <v>20.33254623413086</v>
+        <v>20.33254814147949</v>
       </c>
       <c r="C288" t="n">
-        <v>20.70808146084758</v>
+        <v>20.7080834034243</v>
       </c>
       <c r="D288" t="n">
-        <v>19.68877229065369</v>
+        <v>19.68877413761139</v>
       </c>
       <c r="E288" t="n">
-        <v>19.68877229065369</v>
+        <v>19.68877413761139</v>
       </c>
       <c r="F288" t="n">
         <v>766850</v>
@@ -6192,16 +6192,16 @@
         <v>44519</v>
       </c>
       <c r="B289" t="n">
-        <v>20.99420547485352</v>
+        <v>20.99420166015625</v>
       </c>
       <c r="C289" t="n">
-        <v>21.24456288810481</v>
+        <v>21.24455902791701</v>
       </c>
       <c r="D289" t="n">
-        <v>20.11795708660452</v>
+        <v>20.11795343112367</v>
       </c>
       <c r="E289" t="n">
-        <v>20.31466538638888</v>
+        <v>20.31466169516567</v>
       </c>
       <c r="F289" t="n">
         <v>767750</v>
@@ -6212,16 +6212,16 @@
         <v>44522</v>
       </c>
       <c r="B290" t="n">
-        <v>20.18948745727539</v>
+        <v>20.18948554992676</v>
       </c>
       <c r="C290" t="n">
-        <v>21.44127110802875</v>
+        <v>21.44126908242115</v>
       </c>
       <c r="D290" t="n">
-        <v>19.97489612046799</v>
+        <v>19.97489423339231</v>
       </c>
       <c r="E290" t="n">
-        <v>20.869027543209</v>
+        <v>20.86902557166261</v>
       </c>
       <c r="F290" t="n">
         <v>852100</v>
@@ -6232,16 +6232,16 @@
         <v>44523</v>
       </c>
       <c r="B291" t="n">
-        <v>19.2417049407959</v>
+        <v>19.24170684814453</v>
       </c>
       <c r="C291" t="n">
-        <v>20.45772228310068</v>
+        <v>20.45772431098796</v>
       </c>
       <c r="D291" t="n">
-        <v>19.02711364509506</v>
+        <v>19.02711553117216</v>
       </c>
       <c r="E291" t="n">
-        <v>20.20736662415971</v>
+        <v>20.20736862723029</v>
       </c>
       <c r="F291" t="n">
         <v>1896750</v>
@@ -6272,16 +6272,16 @@
         <v>44525</v>
       </c>
       <c r="B293" t="n">
-        <v>20.29678153991699</v>
+        <v>20.29677963256836</v>
       </c>
       <c r="C293" t="n">
-        <v>20.43984241393447</v>
+        <v>20.43984049314199</v>
       </c>
       <c r="D293" t="n">
-        <v>19.65300590141818</v>
+        <v>19.65300405456705</v>
       </c>
       <c r="E293" t="n">
-        <v>19.65300590141818</v>
+        <v>19.65300405456705</v>
       </c>
       <c r="F293" t="n">
         <v>787900</v>
@@ -6312,16 +6312,16 @@
         <v>44529</v>
       </c>
       <c r="B295" t="n">
-        <v>19.20594215393066</v>
+        <v>19.20594024658203</v>
       </c>
       <c r="C295" t="n">
-        <v>20.33254792793267</v>
+        <v>20.33254590870044</v>
       </c>
       <c r="D295" t="n">
-        <v>19.06288126568472</v>
+        <v>19.06287937254352</v>
       </c>
       <c r="E295" t="n">
-        <v>20.33254792793267</v>
+        <v>20.33254590870044</v>
       </c>
       <c r="F295" t="n">
         <v>830750</v>
@@ -6332,16 +6332,16 @@
         <v>44530</v>
       </c>
       <c r="B296" t="n">
-        <v>18.83040809631348</v>
+        <v>18.83040618896484</v>
       </c>
       <c r="C296" t="n">
-        <v>19.25959249383086</v>
+        <v>19.25959054300976</v>
       </c>
       <c r="D296" t="n">
-        <v>18.06145619932819</v>
+        <v>18.06145436986738</v>
       </c>
       <c r="E296" t="n">
-        <v>19.04499944236196</v>
+        <v>19.04499751327718</v>
       </c>
       <c r="F296" t="n">
         <v>1327800</v>
@@ -6372,16 +6372,16 @@
         <v>44532</v>
       </c>
       <c r="B298" t="n">
-        <v>18.59793281555176</v>
+        <v>18.59793090820312</v>
       </c>
       <c r="C298" t="n">
-        <v>18.86617326425185</v>
+        <v>18.86617132939327</v>
       </c>
       <c r="D298" t="n">
-        <v>18.11510273656414</v>
+        <v>18.11510087873313</v>
       </c>
       <c r="E298" t="n">
-        <v>18.22239755170791</v>
+        <v>18.22239568287305</v>
       </c>
       <c r="F298" t="n">
         <v>961350</v>
@@ -6412,16 +6412,16 @@
         <v>44536</v>
       </c>
       <c r="B300" t="n">
-        <v>19.97489356994629</v>
+        <v>19.97489547729492</v>
       </c>
       <c r="C300" t="n">
-        <v>20.38619315328804</v>
+        <v>20.38619509991056</v>
       </c>
       <c r="D300" t="n">
-        <v>19.56359228118441</v>
+        <v>19.56359414925899</v>
       </c>
       <c r="E300" t="n">
-        <v>20.08218837193973</v>
+        <v>20.08219028953366</v>
       </c>
       <c r="F300" t="n">
         <v>963750</v>
@@ -6472,16 +6472,16 @@
         <v>44539</v>
       </c>
       <c r="B303" t="n">
-        <v>20.90479278564453</v>
+        <v>20.9047908782959</v>
       </c>
       <c r="C303" t="n">
-        <v>21.36974155417278</v>
+        <v>21.36973960440232</v>
       </c>
       <c r="D303" t="n">
-        <v>20.72596751688626</v>
+        <v>20.72596562585361</v>
       </c>
       <c r="E303" t="n">
-        <v>21.24456369549995</v>
+        <v>21.24456175715069</v>
       </c>
       <c r="F303" t="n">
         <v>669550</v>
@@ -6492,16 +6492,16 @@
         <v>44540</v>
       </c>
       <c r="B304" t="n">
-        <v>21.81680679321289</v>
+        <v>21.81680488586426</v>
       </c>
       <c r="C304" t="n">
-        <v>22.19234206620039</v>
+        <v>22.19234012602034</v>
       </c>
       <c r="D304" t="n">
-        <v>21.06573624723789</v>
+        <v>21.06573440555209</v>
       </c>
       <c r="E304" t="n">
-        <v>22.13869465732228</v>
+        <v>22.1386927218324</v>
       </c>
       <c r="F304" t="n">
         <v>899500</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78104019165039</v>
+        <v>21.78104209899902</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422762443386</v>
+        <v>22.51422959598714</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550495712469</v>
+        <v>21.40550683158799</v>
       </c>
       <c r="E305" t="n">
-        <v>22.13869238990815</v>
+        <v>22.13869432857611</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6572,16 +6572,16 @@
         <v>44546</v>
       </c>
       <c r="B308" t="n">
-        <v>21.94198226928711</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C308" t="n">
-        <v>22.97917441006602</v>
+        <v>22.97917640757456</v>
       </c>
       <c r="D308" t="n">
-        <v>21.53068099667751</v>
+        <v>21.53068286827299</v>
       </c>
       <c r="E308" t="n">
-        <v>22.53210877333649</v>
+        <v>22.53211073198299</v>
       </c>
       <c r="F308" t="n">
         <v>888550</v>
@@ -6612,16 +6612,16 @@
         <v>44550</v>
       </c>
       <c r="B310" t="n">
-        <v>22.01351356506348</v>
+        <v>22.01351547241211</v>
       </c>
       <c r="C310" t="n">
-        <v>22.42481314836077</v>
+        <v>22.42481509134622</v>
       </c>
       <c r="D310" t="n">
-        <v>21.13726358663772</v>
+        <v>21.13726541806416</v>
       </c>
       <c r="E310" t="n">
-        <v>22.35328271189949</v>
+        <v>22.35328464868723</v>
       </c>
       <c r="F310" t="n">
         <v>1565700</v>
@@ -6632,16 +6632,16 @@
         <v>44551</v>
       </c>
       <c r="B311" t="n">
-        <v>21.38762092590332</v>
+        <v>21.38762474060059</v>
       </c>
       <c r="C311" t="n">
-        <v>22.19233876090282</v>
+        <v>22.1923427191296</v>
       </c>
       <c r="D311" t="n">
-        <v>21.38762092590332</v>
+        <v>21.38762474060059</v>
       </c>
       <c r="E311" t="n">
-        <v>22.0313948528189</v>
+        <v>22.03139878233971</v>
       </c>
       <c r="F311" t="n">
         <v>785250</v>
@@ -6672,16 +6672,16 @@
         <v>44553</v>
       </c>
       <c r="B313" t="n">
-        <v>21.17614936828613</v>
+        <v>21.1761474609375</v>
       </c>
       <c r="C313" t="n">
-        <v>21.69923988180597</v>
+        <v>21.69923792734226</v>
       </c>
       <c r="D313" t="n">
-        <v>20.79735956744761</v>
+        <v>20.79735769421681</v>
       </c>
       <c r="E313" t="n">
-        <v>21.69923988180597</v>
+        <v>21.69923792734226</v>
       </c>
       <c r="F313" t="n">
         <v>605250</v>
@@ -6692,16 +6692,16 @@
         <v>44557</v>
       </c>
       <c r="B314" t="n">
-        <v>20.92362403869629</v>
+        <v>20.92362594604492</v>
       </c>
       <c r="C314" t="n">
-        <v>21.35652617792996</v>
+        <v>21.35652812474094</v>
       </c>
       <c r="D314" t="n">
-        <v>20.58090855498616</v>
+        <v>20.58091043109365</v>
       </c>
       <c r="E314" t="n">
-        <v>21.08596105075877</v>
+        <v>21.08596297290567</v>
       </c>
       <c r="F314" t="n">
         <v>929800</v>
@@ -6732,16 +6732,16 @@
         <v>44559</v>
       </c>
       <c r="B316" t="n">
-        <v>20.29230880737305</v>
+        <v>20.29230690002441</v>
       </c>
       <c r="C316" t="n">
-        <v>20.90558774878349</v>
+        <v>20.90558578379051</v>
       </c>
       <c r="D316" t="n">
-        <v>20.05781969917492</v>
+        <v>20.05781781386678</v>
       </c>
       <c r="E316" t="n">
-        <v>20.70717296173873</v>
+        <v>20.7071710153955</v>
       </c>
       <c r="F316" t="n">
         <v>541350</v>
@@ -6872,16 +6872,16 @@
         <v>44571</v>
       </c>
       <c r="B323" t="n">
-        <v>16.36011123657227</v>
+        <v>16.36010932922363</v>
       </c>
       <c r="C323" t="n">
-        <v>17.13572899413958</v>
+        <v>17.13572699636531</v>
       </c>
       <c r="D323" t="n">
-        <v>16.10758580495536</v>
+        <v>16.10758392704749</v>
       </c>
       <c r="E323" t="n">
-        <v>17.11769097182395</v>
+        <v>17.11768897615265</v>
       </c>
       <c r="F323" t="n">
         <v>1820150</v>
@@ -6932,16 +6932,16 @@
         <v>44574</v>
       </c>
       <c r="B326" t="n">
-        <v>16.64871215820312</v>
+        <v>16.64871025085449</v>
       </c>
       <c r="C326" t="n">
-        <v>17.62274468839355</v>
+        <v>17.62274266945553</v>
       </c>
       <c r="D326" t="n">
-        <v>16.57656179154462</v>
+        <v>16.57655989246185</v>
       </c>
       <c r="E326" t="n">
-        <v>17.58666864496408</v>
+        <v>17.58666663015909</v>
       </c>
       <c r="F326" t="n">
         <v>921200</v>
@@ -6972,16 +6972,16 @@
         <v>44578</v>
       </c>
       <c r="B328" t="n">
-        <v>16.88320350646973</v>
+        <v>16.88320159912109</v>
       </c>
       <c r="C328" t="n">
-        <v>17.11769265908467</v>
+        <v>17.11769072524505</v>
       </c>
       <c r="D328" t="n">
-        <v>16.63067804996184</v>
+        <v>16.6306761711418</v>
       </c>
       <c r="E328" t="n">
-        <v>16.86516720257677</v>
+        <v>16.86516529726576</v>
       </c>
       <c r="F328" t="n">
         <v>496050</v>
@@ -7012,16 +7012,16 @@
         <v>44580</v>
       </c>
       <c r="B330" t="n">
-        <v>16.41422271728516</v>
+        <v>16.41422462463379</v>
       </c>
       <c r="C330" t="n">
-        <v>16.72086216753467</v>
+        <v>16.72086411051511</v>
       </c>
       <c r="D330" t="n">
-        <v>16.19776992400296</v>
+        <v>16.19777180619957</v>
       </c>
       <c r="E330" t="n">
-        <v>16.41422271728516</v>
+        <v>16.41422462463379</v>
       </c>
       <c r="F330" t="n">
         <v>847250</v>
@@ -7072,16 +7072,16 @@
         <v>44585</v>
       </c>
       <c r="B333" t="n">
-        <v>17.85723304748535</v>
+        <v>17.85723114013672</v>
       </c>
       <c r="C333" t="n">
-        <v>18.09172218175017</v>
+        <v>18.09172024935553</v>
       </c>
       <c r="D333" t="n">
-        <v>17.47844317216533</v>
+        <v>17.47844130527562</v>
       </c>
       <c r="E333" t="n">
-        <v>18.09172218175017</v>
+        <v>18.09172024935553</v>
       </c>
       <c r="F333" t="n">
         <v>692150</v>
@@ -7092,16 +7092,16 @@
         <v>44586</v>
       </c>
       <c r="B334" t="n">
-        <v>18.7230396270752</v>
+        <v>18.72303771972656</v>
       </c>
       <c r="C334" t="n">
-        <v>18.75911395303459</v>
+        <v>18.759112042011</v>
       </c>
       <c r="D334" t="n">
-        <v>17.65882034816448</v>
+        <v>17.65881854922971</v>
       </c>
       <c r="E334" t="n">
-        <v>17.71293269720384</v>
+        <v>17.71293089275656</v>
       </c>
       <c r="F334" t="n">
         <v>1122500</v>
@@ -7132,16 +7132,16 @@
         <v>44588</v>
       </c>
       <c r="B336" t="n">
-        <v>19.33631324768066</v>
+        <v>19.33631706237793</v>
       </c>
       <c r="C336" t="n">
-        <v>19.91351606336663</v>
+        <v>19.91351999193534</v>
       </c>
       <c r="D336" t="n">
-        <v>19.08378615571801</v>
+        <v>19.08378992059635</v>
       </c>
       <c r="E336" t="n">
-        <v>19.64295267356385</v>
+        <v>19.64295654875541</v>
       </c>
       <c r="F336" t="n">
         <v>815000</v>
@@ -7152,16 +7152,16 @@
         <v>44589</v>
       </c>
       <c r="B337" t="n">
-        <v>19.67903137207031</v>
+        <v>19.67902946472168</v>
       </c>
       <c r="C337" t="n">
-        <v>19.67903137207031</v>
+        <v>19.67902946472168</v>
       </c>
       <c r="D337" t="n">
-        <v>18.84930127963634</v>
+        <v>18.84929945270756</v>
       </c>
       <c r="E337" t="n">
-        <v>19.30024150986784</v>
+        <v>19.30023963923261</v>
       </c>
       <c r="F337" t="n">
         <v>645650</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96763229370117</v>
+        <v>19.96763038635254</v>
       </c>
       <c r="C338" t="n">
-        <v>20.27427177942092</v>
+        <v>20.27426984278146</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44454170986168</v>
+        <v>19.44453985247972</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706885110159</v>
+        <v>19.69706696959773</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7332,16 +7332,16 @@
         <v>44602</v>
       </c>
       <c r="B346" t="n">
-        <v>19.98567008972168</v>
+        <v>19.98566818237305</v>
       </c>
       <c r="C346" t="n">
-        <v>20.59894905424028</v>
+        <v>20.59894708836287</v>
       </c>
       <c r="D346" t="n">
-        <v>19.82333133791377</v>
+        <v>19.82332944605806</v>
       </c>
       <c r="E346" t="n">
-        <v>20.18408316404224</v>
+        <v>20.18408123775789</v>
       </c>
       <c r="F346" t="n">
         <v>563100</v>
@@ -7352,16 +7352,16 @@
         <v>44603</v>
       </c>
       <c r="B347" t="n">
-        <v>19.44454002380371</v>
+        <v>19.44454193115234</v>
       </c>
       <c r="C347" t="n">
-        <v>20.47268480097144</v>
+        <v>20.47268680917258</v>
       </c>
       <c r="D347" t="n">
-        <v>19.13790056467302</v>
+        <v>19.13790244194285</v>
       </c>
       <c r="E347" t="n">
-        <v>20.09389498205707</v>
+        <v>20.09389695310205</v>
       </c>
       <c r="F347" t="n">
         <v>1043600</v>
@@ -7392,16 +7392,16 @@
         <v>44607</v>
       </c>
       <c r="B349" t="n">
-        <v>20.52679634094238</v>
+        <v>20.52679824829102</v>
       </c>
       <c r="C349" t="n">
-        <v>20.70717137327322</v>
+        <v>20.70717329738229</v>
       </c>
       <c r="D349" t="n">
-        <v>20.11193049820109</v>
+        <v>20.11193236700041</v>
       </c>
       <c r="E349" t="n">
-        <v>20.2021188744666</v>
+        <v>20.20212075164623</v>
       </c>
       <c r="F349" t="n">
         <v>560950</v>
@@ -7472,16 +7472,16 @@
         <v>44613</v>
       </c>
       <c r="B353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892242431641</v>
       </c>
       <c r="C353" t="n">
-        <v>19.94959452481559</v>
+        <v>19.94959248662468</v>
       </c>
       <c r="D353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892242431641</v>
       </c>
       <c r="E353" t="n">
-        <v>19.85940614385</v>
+        <v>19.85940411487337</v>
       </c>
       <c r="F353" t="n">
         <v>728950</v>
@@ -7512,16 +7512,16 @@
         <v>44615</v>
       </c>
       <c r="B355" t="n">
-        <v>19.66099166870117</v>
+        <v>19.66098976135254</v>
       </c>
       <c r="C355" t="n">
-        <v>20.49072169018069</v>
+        <v>20.49071970233843</v>
       </c>
       <c r="D355" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276508916316</v>
       </c>
       <c r="E355" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940452736665</v>
       </c>
       <c r="F355" t="n">
         <v>1327750</v>
@@ -7532,16 +7532,16 @@
         <v>44616</v>
       </c>
       <c r="B356" t="n">
-        <v>19.33631324768066</v>
+        <v>19.33631706237793</v>
       </c>
       <c r="C356" t="n">
-        <v>19.42650161768162</v>
+        <v>19.42650545017138</v>
       </c>
       <c r="D356" t="n">
-        <v>18.27209426610961</v>
+        <v>18.27209787085614</v>
       </c>
       <c r="E356" t="n">
-        <v>18.52462135807226</v>
+        <v>18.52462501263771</v>
       </c>
       <c r="F356" t="n">
         <v>1831750</v>
@@ -7552,16 +7552,16 @@
         <v>44617</v>
       </c>
       <c r="B357" t="n">
-        <v>19.02967643737793</v>
+        <v>19.02967834472656</v>
       </c>
       <c r="C357" t="n">
-        <v>19.62491735291844</v>
+        <v>19.62491931992821</v>
       </c>
       <c r="D357" t="n">
-        <v>18.6508866074703</v>
+        <v>18.65088847685275</v>
       </c>
       <c r="E357" t="n">
-        <v>19.28220184384947</v>
+        <v>19.28220377650878</v>
       </c>
       <c r="F357" t="n">
         <v>1262850</v>
@@ -7612,16 +7612,16 @@
         <v>44624</v>
       </c>
       <c r="B360" t="n">
-        <v>17.91134262084961</v>
+        <v>17.91134452819824</v>
       </c>
       <c r="C360" t="n">
-        <v>18.75910883175985</v>
+        <v>18.75911082938567</v>
       </c>
       <c r="D360" t="n">
-        <v>17.55058913853877</v>
+        <v>17.55059100747137</v>
       </c>
       <c r="E360" t="n">
-        <v>18.57873381080452</v>
+        <v>18.57873578922251</v>
       </c>
       <c r="F360" t="n">
         <v>1669200</v>
@@ -7652,16 +7652,16 @@
         <v>44628</v>
       </c>
       <c r="B362" t="n">
-        <v>17.38825225830078</v>
+        <v>17.38825416564941</v>
       </c>
       <c r="C362" t="n">
-        <v>17.58666529881019</v>
+        <v>17.58666722792311</v>
       </c>
       <c r="D362" t="n">
-        <v>16.54048432121493</v>
+        <v>16.54048613557037</v>
       </c>
       <c r="E362" t="n">
-        <v>16.84712375122045</v>
+        <v>16.84712559921172</v>
       </c>
       <c r="F362" t="n">
         <v>1040800</v>
@@ -7712,16 +7712,16 @@
         <v>44631</v>
       </c>
       <c r="B365" t="n">
-        <v>17.22591400146484</v>
+        <v>17.22591590881348</v>
       </c>
       <c r="C365" t="n">
-        <v>18.45247003456108</v>
+        <v>18.4524720777208</v>
       </c>
       <c r="D365" t="n">
-        <v>17.02749923537269</v>
+        <v>17.02750112075174</v>
       </c>
       <c r="E365" t="n">
-        <v>18.30816932478506</v>
+        <v>18.30817135196699</v>
       </c>
       <c r="F365" t="n">
         <v>837400</v>
@@ -7732,16 +7732,16 @@
         <v>44634</v>
       </c>
       <c r="B366" t="n">
-        <v>17.31610298156738</v>
+        <v>17.31610488891602</v>
       </c>
       <c r="C366" t="n">
-        <v>17.67685476864166</v>
+        <v>17.67685671572668</v>
       </c>
       <c r="D366" t="n">
-        <v>16.88319911687804</v>
+        <v>16.88320097654281</v>
       </c>
       <c r="E366" t="n">
-        <v>17.35217730017471</v>
+        <v>17.35217921149688</v>
       </c>
       <c r="F366" t="n">
         <v>989600</v>
@@ -7752,16 +7752,16 @@
         <v>44635</v>
       </c>
       <c r="B367" t="n">
-        <v>17.46040344238281</v>
+        <v>17.46040534973145</v>
       </c>
       <c r="C367" t="n">
-        <v>17.56862811683053</v>
+        <v>17.56863003600147</v>
       </c>
       <c r="D367" t="n">
-        <v>16.93731292868499</v>
+        <v>16.93731477889199</v>
       </c>
       <c r="E367" t="n">
-        <v>17.04553760313271</v>
+        <v>17.04553946516202</v>
       </c>
       <c r="F367" t="n">
         <v>763850</v>
@@ -7792,16 +7792,16 @@
         <v>44637</v>
       </c>
       <c r="B369" t="n">
-        <v>18.16387367248535</v>
+        <v>18.16387176513672</v>
       </c>
       <c r="C369" t="n">
-        <v>18.3081744224399</v>
+        <v>18.30817249993856</v>
       </c>
       <c r="D369" t="n">
-        <v>17.17180644659796</v>
+        <v>17.17180464342414</v>
       </c>
       <c r="E369" t="n">
-        <v>17.56863264887267</v>
+        <v>17.56863080402899</v>
       </c>
       <c r="F369" t="n">
         <v>935650</v>
@@ -7832,16 +7832,16 @@
         <v>44641</v>
       </c>
       <c r="B371" t="n">
-        <v>18.56069946289062</v>
+        <v>18.56069755554199</v>
       </c>
       <c r="C371" t="n">
-        <v>18.86733895137048</v>
+        <v>18.86733701251073</v>
       </c>
       <c r="D371" t="n">
-        <v>18.23602195268832</v>
+        <v>18.23602007870444</v>
       </c>
       <c r="E371" t="n">
-        <v>18.65088785130242</v>
+        <v>18.65088593468579</v>
       </c>
       <c r="F371" t="n">
         <v>689900</v>
@@ -7952,16 +7952,16 @@
         <v>44649</v>
       </c>
       <c r="B377" t="n">
-        <v>21.91569328308105</v>
+        <v>21.91569137573242</v>
       </c>
       <c r="C377" t="n">
-        <v>22.36663348824898</v>
+        <v>22.36663154165449</v>
       </c>
       <c r="D377" t="n">
-        <v>21.66316786911525</v>
+        <v>21.6631659837442</v>
       </c>
       <c r="E377" t="n">
-        <v>21.66316786911525</v>
+        <v>21.6631659837442</v>
       </c>
       <c r="F377" t="n">
         <v>1103500</v>
@@ -7992,16 +7992,16 @@
         <v>44651</v>
       </c>
       <c r="B379" t="n">
-        <v>21.17614936828613</v>
+        <v>21.1761474609375</v>
       </c>
       <c r="C379" t="n">
-        <v>21.77139023814663</v>
+        <v>21.77138827718429</v>
       </c>
       <c r="D379" t="n">
-        <v>21.04988667474002</v>
+        <v>21.04988477876395</v>
       </c>
       <c r="E379" t="n">
-        <v>21.6090515063301</v>
+        <v>21.60904955998971</v>
       </c>
       <c r="F379" t="n">
         <v>849150</v>
@@ -8072,16 +8072,16 @@
         <v>44657</v>
       </c>
       <c r="B383" t="n">
-        <v>20.0217456817627</v>
+        <v>20.02174758911133</v>
       </c>
       <c r="C383" t="n">
-        <v>20.58091056962541</v>
+        <v>20.58091253024225</v>
       </c>
       <c r="D383" t="n">
-        <v>19.58884177995242</v>
+        <v>19.58884364606096</v>
       </c>
       <c r="E383" t="n">
-        <v>20.58091056962541</v>
+        <v>20.58091253024225</v>
       </c>
       <c r="F383" t="n">
         <v>1237700</v>
@@ -8092,16 +8092,16 @@
         <v>44658</v>
       </c>
       <c r="B384" t="n">
-        <v>19.66099166870117</v>
+        <v>19.66098976135254</v>
       </c>
       <c r="C384" t="n">
-        <v>20.00370717768201</v>
+        <v>20.00370523708592</v>
       </c>
       <c r="D384" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276508916316</v>
       </c>
       <c r="E384" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940452736665</v>
       </c>
       <c r="F384" t="n">
         <v>978600</v>
@@ -8132,16 +8132,16 @@
         <v>44662</v>
       </c>
       <c r="B386" t="n">
-        <v>18.93948745727539</v>
+        <v>18.93949127197266</v>
       </c>
       <c r="C386" t="n">
-        <v>19.37238961487934</v>
+        <v>19.3723935167696</v>
       </c>
       <c r="D386" t="n">
-        <v>18.86733709767473</v>
+        <v>18.86734089783983</v>
       </c>
       <c r="E386" t="n">
-        <v>19.24612691562825</v>
+        <v>19.24613079208731</v>
       </c>
       <c r="F386" t="n">
         <v>1033000</v>
@@ -8152,16 +8152,16 @@
         <v>44663</v>
       </c>
       <c r="B387" t="n">
-        <v>19.13790130615234</v>
+        <v>19.13790321350098</v>
       </c>
       <c r="C387" t="n">
-        <v>19.84136863144855</v>
+        <v>19.84137060890714</v>
       </c>
       <c r="D387" t="n">
-        <v>18.9936005809942</v>
+        <v>18.99360247396133</v>
       </c>
       <c r="E387" t="n">
-        <v>19.33631609339504</v>
+        <v>19.33631802051837</v>
       </c>
       <c r="F387" t="n">
         <v>1155250</v>
@@ -8212,16 +8212,16 @@
         <v>44669</v>
       </c>
       <c r="B390" t="n">
-        <v>19.55276489257812</v>
+        <v>19.55276679992676</v>
       </c>
       <c r="C390" t="n">
-        <v>20.0037050359671</v>
+        <v>20.0037069873044</v>
       </c>
       <c r="D390" t="n">
-        <v>19.49865255702748</v>
+        <v>19.49865445909752</v>
       </c>
       <c r="E390" t="n">
-        <v>19.679027582263</v>
+        <v>19.6790295019284</v>
       </c>
       <c r="F390" t="n">
         <v>1023750</v>
@@ -8252,16 +8252,16 @@
         <v>44671</v>
       </c>
       <c r="B392" t="n">
-        <v>20.61698341369629</v>
+        <v>20.61698532104492</v>
       </c>
       <c r="C392" t="n">
-        <v>20.79735843462289</v>
+        <v>20.79736035865864</v>
       </c>
       <c r="D392" t="n">
-        <v>20.1119292266216</v>
+        <v>20.11193108724592</v>
       </c>
       <c r="E392" t="n">
-        <v>20.34641830200626</v>
+        <v>20.34642018432397</v>
       </c>
       <c r="F392" t="n">
         <v>1230400</v>
@@ -8272,16 +8272,16 @@
         <v>44673</v>
       </c>
       <c r="B393" t="n">
-        <v>19.55276489257812</v>
+        <v>19.55276679992676</v>
       </c>
       <c r="C393" t="n">
-        <v>20.49071949632313</v>
+        <v>20.4907214951681</v>
       </c>
       <c r="D393" t="n">
-        <v>19.35435012855889</v>
+        <v>19.3543520165524</v>
       </c>
       <c r="E393" t="n">
-        <v>20.09389340868493</v>
+        <v>20.09389536881999</v>
       </c>
       <c r="F393" t="n">
         <v>931750</v>
@@ -8392,16 +8392,16 @@
         <v>44683</v>
       </c>
       <c r="B399" t="n">
-        <v>20.38249778747559</v>
+        <v>20.38249588012695</v>
       </c>
       <c r="C399" t="n">
-        <v>21.41064091336175</v>
+        <v>21.41063890980178</v>
       </c>
       <c r="D399" t="n">
-        <v>20.02174596437521</v>
+        <v>20.02174409078493</v>
       </c>
       <c r="E399" t="n">
-        <v>21.28437820532671</v>
+        <v>21.28437621358212</v>
       </c>
       <c r="F399" t="n">
         <v>1653550</v>
@@ -8452,16 +8452,16 @@
         <v>44686</v>
       </c>
       <c r="B402" t="n">
-        <v>20.09389495849609</v>
+        <v>20.09389305114746</v>
       </c>
       <c r="C402" t="n">
-        <v>20.47268477696631</v>
+        <v>20.47268283366227</v>
       </c>
       <c r="D402" t="n">
-        <v>19.73314143980044</v>
+        <v>19.73313956669518</v>
       </c>
       <c r="E402" t="n">
-        <v>20.41857071704181</v>
+        <v>20.41856877887437</v>
       </c>
       <c r="F402" t="n">
         <v>1134600</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.5190315246582</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C403" t="n">
-        <v>19.9347326068735</v>
+        <v>19.93473455484336</v>
       </c>
       <c r="D403" t="n">
-        <v>18.81989895121317</v>
+        <v>18.8199007902444</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019522691586</v>
+        <v>19.67019714903581</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8552,16 +8552,16 @@
         <v>44693</v>
       </c>
       <c r="B407" t="n">
-        <v>19.330078125</v>
+        <v>19.33007621765137</v>
       </c>
       <c r="C407" t="n">
-        <v>19.70798922428379</v>
+        <v>19.7079872796457</v>
       </c>
       <c r="D407" t="n">
-        <v>18.81990102418875</v>
+        <v>18.81989916718061</v>
       </c>
       <c r="E407" t="n">
-        <v>18.93327471437663</v>
+        <v>18.93327284618161</v>
       </c>
       <c r="F407" t="n">
         <v>1412250</v>
@@ -8612,16 +8612,16 @@
         <v>44698</v>
       </c>
       <c r="B410" t="n">
-        <v>20.57717895507812</v>
+        <v>20.57718086242676</v>
       </c>
       <c r="C410" t="n">
-        <v>20.74723676623272</v>
+        <v>20.74723868934442</v>
       </c>
       <c r="D410" t="n">
-        <v>20.23705972874203</v>
+        <v>20.23706160456419</v>
       </c>
       <c r="E410" t="n">
-        <v>20.46380527896161</v>
+        <v>20.46380717580136</v>
       </c>
       <c r="F410" t="n">
         <v>1148200</v>
@@ -8632,16 +8632,16 @@
         <v>44699</v>
       </c>
       <c r="B411" t="n">
-        <v>20.36932754516602</v>
+        <v>20.36932945251465</v>
       </c>
       <c r="C411" t="n">
-        <v>20.76613270912441</v>
+        <v>20.76613465362919</v>
       </c>
       <c r="D411" t="n">
-        <v>20.10479197053606</v>
+        <v>20.10479385311404</v>
       </c>
       <c r="E411" t="n">
-        <v>20.44490939534792</v>
+        <v>20.44491130977391</v>
       </c>
       <c r="F411" t="n">
         <v>1338150</v>
@@ -8672,16 +8672,16 @@
         <v>44701</v>
       </c>
       <c r="B413" t="n">
-        <v>20.65276145935059</v>
+        <v>20.65276336669922</v>
       </c>
       <c r="C413" t="n">
-        <v>21.08735666053437</v>
+        <v>21.08735860801926</v>
       </c>
       <c r="D413" t="n">
-        <v>20.25595628339371</v>
+        <v>20.25595815409612</v>
       </c>
       <c r="E413" t="n">
-        <v>21.03067072168725</v>
+        <v>21.03067266393701</v>
       </c>
       <c r="F413" t="n">
         <v>1756800</v>
@@ -8792,16 +8792,16 @@
         <v>44711</v>
       </c>
       <c r="B419" t="n">
-        <v>22.14550399780273</v>
+        <v>22.14550590515137</v>
       </c>
       <c r="C419" t="n">
-        <v>23.22254582654633</v>
+        <v>23.22254782665845</v>
       </c>
       <c r="D419" t="n">
-        <v>22.14550399780273</v>
+        <v>22.14550590515137</v>
       </c>
       <c r="E419" t="n">
-        <v>22.97690435995308</v>
+        <v>22.97690633890859</v>
       </c>
       <c r="F419" t="n">
         <v>1234700</v>
@@ -8832,16 +8832,16 @@
         <v>44713</v>
       </c>
       <c r="B421" t="n">
-        <v>23.43039512634277</v>
+        <v>23.43039703369141</v>
       </c>
       <c r="C421" t="n">
-        <v>23.61935065236709</v>
+        <v>23.61935257509763</v>
       </c>
       <c r="D421" t="n">
-        <v>22.31556328924234</v>
+        <v>22.31556510583822</v>
       </c>
       <c r="E421" t="n">
-        <v>22.78795030228968</v>
+        <v>22.78795215734017</v>
       </c>
       <c r="F421" t="n">
         <v>2603350</v>
@@ -8912,16 +8912,16 @@
         <v>44719</v>
       </c>
       <c r="B425" t="n">
-        <v>21.5975341796875</v>
+        <v>21.59753608703613</v>
       </c>
       <c r="C425" t="n">
-        <v>21.93765159373639</v>
+        <v>21.93765353112191</v>
       </c>
       <c r="D425" t="n">
-        <v>21.25741496362521</v>
+        <v>21.25741684093681</v>
       </c>
       <c r="E425" t="n">
-        <v>21.72980196281688</v>
+        <v>21.72980388184651</v>
       </c>
       <c r="F425" t="n">
         <v>1412350</v>
@@ -8952,16 +8952,16 @@
         <v>44721</v>
       </c>
       <c r="B427" t="n">
-        <v>21.54084777832031</v>
+        <v>21.54084968566895</v>
       </c>
       <c r="C427" t="n">
-        <v>21.72980331052155</v>
+        <v>21.72980523460138</v>
       </c>
       <c r="D427" t="n">
-        <v>20.8984029332658</v>
+        <v>20.89840478372873</v>
       </c>
       <c r="E427" t="n">
-        <v>21.20073034317699</v>
+        <v>21.20073222040969</v>
       </c>
       <c r="F427" t="n">
         <v>1117750</v>
@@ -9012,16 +9012,16 @@
         <v>44726</v>
       </c>
       <c r="B430" t="n">
-        <v>19.12222862243652</v>
+        <v>19.12222671508789</v>
       </c>
       <c r="C430" t="n">
-        <v>19.51903383840268</v>
+        <v>19.51903189147468</v>
       </c>
       <c r="D430" t="n">
-        <v>18.8954830421721</v>
+        <v>18.89548115744023</v>
       </c>
       <c r="E430" t="n">
-        <v>19.51903383840268</v>
+        <v>19.51903189147468</v>
       </c>
       <c r="F430" t="n">
         <v>1027150</v>
@@ -9032,16 +9032,16 @@
         <v>44727</v>
       </c>
       <c r="B431" t="n">
-        <v>19.65130233764648</v>
+        <v>19.65130043029785</v>
       </c>
       <c r="C431" t="n">
-        <v>19.82136197935914</v>
+        <v>19.82136005550457</v>
       </c>
       <c r="D431" t="n">
-        <v>19.17891524489523</v>
+        <v>19.17891338339633</v>
       </c>
       <c r="E431" t="n">
-        <v>19.44345266556088</v>
+        <v>19.44345077838607</v>
       </c>
       <c r="F431" t="n">
         <v>990050</v>
@@ -9072,16 +9072,16 @@
         <v>44732</v>
       </c>
       <c r="B433" t="n">
-        <v>18.6120491027832</v>
+        <v>18.61205101013184</v>
       </c>
       <c r="C433" t="n">
-        <v>19.4812412820424</v>
+        <v>19.48124327846519</v>
       </c>
       <c r="D433" t="n">
-        <v>18.51757133942631</v>
+        <v>18.51757323709293</v>
       </c>
       <c r="E433" t="n">
-        <v>19.14112205476297</v>
+        <v>19.14112401633059</v>
       </c>
       <c r="F433" t="n">
         <v>828950</v>
@@ -9112,16 +9112,16 @@
         <v>44734</v>
       </c>
       <c r="B435" t="n">
-        <v>18.6120491027832</v>
+        <v>18.61205101013184</v>
       </c>
       <c r="C435" t="n">
-        <v>18.83879465363167</v>
+        <v>18.83879658421702</v>
       </c>
       <c r="D435" t="n">
-        <v>18.15855619907281</v>
+        <v>18.15855805994783</v>
       </c>
       <c r="E435" t="n">
-        <v>18.38530174992128</v>
+        <v>18.38530363403301</v>
       </c>
       <c r="F435" t="n">
         <v>1143850</v>
@@ -9132,16 +9132,16 @@
         <v>44735</v>
       </c>
       <c r="B436" t="n">
-        <v>18.81989860534668</v>
+        <v>18.81990051269531</v>
       </c>
       <c r="C436" t="n">
-        <v>18.89548045508649</v>
+        <v>18.89548237009515</v>
       </c>
       <c r="D436" t="n">
-        <v>18.49867529344914</v>
+        <v>18.4986771682426</v>
       </c>
       <c r="E436" t="n">
-        <v>18.72542084266856</v>
+        <v>18.72542274044211</v>
       </c>
       <c r="F436" t="n">
         <v>1280500</v>
@@ -9152,16 +9152,16 @@
         <v>44736</v>
       </c>
       <c r="B437" t="n">
-        <v>18.47978019714355</v>
+        <v>18.47977828979492</v>
       </c>
       <c r="C437" t="n">
-        <v>18.95216722939579</v>
+        <v>18.9521652732908</v>
       </c>
       <c r="D437" t="n">
-        <v>18.23413872413077</v>
+        <v>18.23413684213547</v>
       </c>
       <c r="E437" t="n">
-        <v>18.95216722939579</v>
+        <v>18.9521652732908</v>
       </c>
       <c r="F437" t="n">
         <v>1255000</v>
@@ -9192,16 +9192,16 @@
         <v>44740</v>
       </c>
       <c r="B439" t="n">
-        <v>18.0451831817627</v>
+        <v>18.04518508911133</v>
       </c>
       <c r="C439" t="n">
-        <v>18.72541979122529</v>
+        <v>18.7254217704739</v>
       </c>
       <c r="D439" t="n">
-        <v>17.87512357889371</v>
+        <v>17.8751254682673</v>
       </c>
       <c r="E439" t="n">
-        <v>18.70652387934799</v>
+        <v>18.70652585659934</v>
       </c>
       <c r="F439" t="n">
         <v>1533000</v>
@@ -9232,16 +9232,16 @@
         <v>44742</v>
       </c>
       <c r="B441" t="n">
-        <v>17.53500556945801</v>
+        <v>17.53500366210938</v>
       </c>
       <c r="C441" t="n">
-        <v>17.74285701026197</v>
+        <v>17.74285508030455</v>
       </c>
       <c r="D441" t="n">
-        <v>17.30826001750107</v>
+        <v>17.3082581348164</v>
       </c>
       <c r="E441" t="n">
-        <v>17.55390148262445</v>
+        <v>17.55389957322044</v>
       </c>
       <c r="F441" t="n">
         <v>1152750</v>
@@ -9252,16 +9252,16 @@
         <v>44743</v>
       </c>
       <c r="B442" t="n">
-        <v>17.5916919708252</v>
+        <v>17.59169387817383</v>
       </c>
       <c r="C442" t="n">
-        <v>17.72395974890228</v>
+        <v>17.72396167059182</v>
       </c>
       <c r="D442" t="n">
-        <v>17.06261725449021</v>
+        <v>17.06261910447483</v>
       </c>
       <c r="E442" t="n">
-        <v>17.25157276775461</v>
+        <v>17.2515746382264</v>
       </c>
       <c r="F442" t="n">
         <v>2016600</v>
@@ -9292,16 +9292,16 @@
         <v>44747</v>
       </c>
       <c r="B444" t="n">
-        <v>17.10041046142578</v>
+        <v>17.10040855407715</v>
       </c>
       <c r="C444" t="n">
-        <v>17.25157416346159</v>
+        <v>17.25157223925244</v>
       </c>
       <c r="D444" t="n">
-        <v>16.57133750430044</v>
+        <v>16.57133565596364</v>
       </c>
       <c r="E444" t="n">
-        <v>17.15709639918584</v>
+        <v>17.15709448551456</v>
       </c>
       <c r="F444" t="n">
         <v>2077700</v>
@@ -9312,16 +9312,16 @@
         <v>44748</v>
       </c>
       <c r="B445" t="n">
-        <v>17.23267936706543</v>
+        <v>17.2326774597168</v>
       </c>
       <c r="C445" t="n">
-        <v>17.47832084929718</v>
+        <v>17.47831891476044</v>
       </c>
       <c r="D445" t="n">
-        <v>16.83587417300084</v>
+        <v>16.83587230957143</v>
       </c>
       <c r="E445" t="n">
-        <v>17.19488934011402</v>
+        <v>17.19488743694806</v>
       </c>
       <c r="F445" t="n">
         <v>1639900</v>
@@ -9372,16 +9372,16 @@
         <v>44753</v>
       </c>
       <c r="B448" t="n">
-        <v>16.76029205322266</v>
+        <v>16.76029396057129</v>
       </c>
       <c r="C448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61059037351305</v>
       </c>
       <c r="D448" t="n">
-        <v>16.62802425795465</v>
+        <v>16.62802615025099</v>
       </c>
       <c r="E448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61059037351305</v>
       </c>
       <c r="F448" t="n">
         <v>1587350</v>
@@ -9412,16 +9412,16 @@
         <v>44755</v>
       </c>
       <c r="B450" t="n">
-        <v>16.87366485595703</v>
+        <v>16.87366676330566</v>
       </c>
       <c r="C450" t="n">
-        <v>17.02482855752328</v>
+        <v>17.024830481959</v>
       </c>
       <c r="D450" t="n">
-        <v>16.3445900984617</v>
+        <v>16.3445919460053</v>
       </c>
       <c r="E450" t="n">
-        <v>16.51464971322709</v>
+        <v>16.51465157999372</v>
       </c>
       <c r="F450" t="n">
         <v>919750</v>
@@ -9472,16 +9472,16 @@
         <v>44760</v>
       </c>
       <c r="B453" t="n">
-        <v>16.94924545288086</v>
+        <v>16.94924736022949</v>
       </c>
       <c r="C453" t="n">
-        <v>17.34605059064106</v>
+        <v>17.34605254264335</v>
       </c>
       <c r="D453" t="n">
-        <v>16.74139402709346</v>
+        <v>16.74139591105195</v>
       </c>
       <c r="E453" t="n">
-        <v>16.74139402709346</v>
+        <v>16.74139591105195</v>
       </c>
       <c r="F453" t="n">
         <v>809650</v>
@@ -9512,16 +9512,16 @@
         <v>44762</v>
       </c>
       <c r="B455" t="n">
-        <v>17.96960258483887</v>
+        <v>17.96960067749023</v>
       </c>
       <c r="C455" t="n">
-        <v>18.02628852239609</v>
+        <v>18.02628660903064</v>
       </c>
       <c r="D455" t="n">
-        <v>17.23267818854108</v>
+        <v>17.23267635941185</v>
       </c>
       <c r="E455" t="n">
-        <v>17.25157410173131</v>
+        <v>17.25157227059641</v>
       </c>
       <c r="F455" t="n">
         <v>812650</v>
@@ -9532,16 +9532,16 @@
         <v>44763</v>
       </c>
       <c r="B456" t="n">
-        <v>18.02628707885742</v>
+        <v>18.02628898620605</v>
       </c>
       <c r="C456" t="n">
-        <v>18.23413670126503</v>
+        <v>18.23413863060609</v>
       </c>
       <c r="D456" t="n">
-        <v>17.66727376706003</v>
+        <v>17.66727563642172</v>
       </c>
       <c r="E456" t="n">
-        <v>18.04518299053447</v>
+        <v>18.04518489988247</v>
       </c>
       <c r="F456" t="n">
         <v>845300</v>
@@ -9552,16 +9552,16 @@
         <v>44764</v>
       </c>
       <c r="B457" t="n">
-        <v>18.0451831817627</v>
+        <v>18.04518508911133</v>
       </c>
       <c r="C457" t="n">
-        <v>18.23413689449563</v>
+        <v>18.23413882181639</v>
       </c>
       <c r="D457" t="n">
-        <v>17.76174990964328</v>
+        <v>17.76175178703344</v>
       </c>
       <c r="E457" t="n">
-        <v>18.12076502725854</v>
+        <v>18.12076694259606</v>
       </c>
       <c r="F457" t="n">
         <v>543750</v>
@@ -9572,16 +9572,16 @@
         <v>44767</v>
       </c>
       <c r="B458" t="n">
-        <v>17.95070838928223</v>
+        <v>17.95070457458496</v>
       </c>
       <c r="C458" t="n">
-        <v>18.30972176418187</v>
+        <v>18.30971787319083</v>
       </c>
       <c r="D458" t="n">
-        <v>17.87512653130264</v>
+        <v>17.87512273266724</v>
       </c>
       <c r="E458" t="n">
-        <v>18.177453963221</v>
+        <v>18.17745010033813</v>
       </c>
       <c r="F458" t="n">
         <v>615900</v>
@@ -9612,16 +9612,16 @@
         <v>44769</v>
       </c>
       <c r="B460" t="n">
-        <v>18.23413848876953</v>
+        <v>18.23414039611816</v>
       </c>
       <c r="C460" t="n">
-        <v>18.38530219297798</v>
+        <v>18.38530411613882</v>
       </c>
       <c r="D460" t="n">
-        <v>17.34605217704824</v>
+        <v>17.34605399150023</v>
       </c>
       <c r="E460" t="n">
-        <v>17.4405281406684</v>
+        <v>17.44052996500288</v>
       </c>
       <c r="F460" t="n">
         <v>704800</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.5190315246582</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65129931363029</v>
+        <v>19.65130123390378</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431710008434</v>
+        <v>18.74431893172991</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658488905642</v>
+        <v>18.87658673362685</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9672,16 +9672,16 @@
         <v>44774</v>
       </c>
       <c r="B463" t="n">
-        <v>19.12222862243652</v>
+        <v>19.12222671508789</v>
       </c>
       <c r="C463" t="n">
-        <v>19.74577941866711</v>
+        <v>19.74577744912234</v>
       </c>
       <c r="D463" t="n">
-        <v>19.04664676234838</v>
+        <v>19.04664486253867</v>
       </c>
       <c r="E463" t="n">
-        <v>19.50013792287723</v>
+        <v>19.50013597783399</v>
       </c>
       <c r="F463" t="n">
         <v>811600</v>
@@ -9692,16 +9692,16 @@
         <v>44775</v>
       </c>
       <c r="B464" t="n">
-        <v>19.08443450927734</v>
+        <v>19.08443641662598</v>
       </c>
       <c r="C464" t="n">
-        <v>19.38676188493101</v>
+        <v>19.38676382249504</v>
       </c>
       <c r="D464" t="n">
-        <v>18.89547899848715</v>
+        <v>18.89548088695107</v>
       </c>
       <c r="E464" t="n">
-        <v>19.1222245302274</v>
+        <v>19.12222644135287</v>
       </c>
       <c r="F464" t="n">
         <v>867500</v>
@@ -9732,16 +9732,16 @@
         <v>44777</v>
       </c>
       <c r="B466" t="n">
-        <v>21.3141040802002</v>
+        <v>21.31410217285156</v>
       </c>
       <c r="C466" t="n">
-        <v>21.46526779834239</v>
+        <v>21.46526587746648</v>
       </c>
       <c r="D466" t="n">
-        <v>19.78357098350703</v>
+        <v>19.78356921312217</v>
       </c>
       <c r="E466" t="n">
-        <v>19.89694287110684</v>
+        <v>19.89694109057661</v>
       </c>
       <c r="F466" t="n">
         <v>1697500</v>
@@ -9772,16 +9772,16 @@
         <v>44781</v>
       </c>
       <c r="B468" t="n">
-        <v>21.54084777832031</v>
+        <v>21.54084968566895</v>
       </c>
       <c r="C468" t="n">
-        <v>21.843176990245</v>
+        <v>21.84317892436357</v>
       </c>
       <c r="D468" t="n">
-        <v>21.01177481097574</v>
+        <v>21.01177667147726</v>
       </c>
       <c r="E468" t="n">
-        <v>21.21962445478631</v>
+        <v>21.21962633369201</v>
       </c>
       <c r="F468" t="n">
         <v>1786950</v>
@@ -9812,16 +9812,16 @@
         <v>44783</v>
       </c>
       <c r="B470" t="n">
-        <v>21.82427978515625</v>
+        <v>21.82428169250488</v>
       </c>
       <c r="C470" t="n">
-        <v>22.12660717717701</v>
+        <v>22.12660911094776</v>
       </c>
       <c r="D470" t="n">
-        <v>21.08735541559559</v>
+        <v>21.08735725854019</v>
       </c>
       <c r="E470" t="n">
-        <v>21.16293726360078</v>
+        <v>21.16293911315091</v>
       </c>
       <c r="F470" t="n">
         <v>1851300</v>
@@ -9852,16 +9852,16 @@
         <v>44785</v>
       </c>
       <c r="B472" t="n">
-        <v>22.92021942138672</v>
+        <v>22.92021751403809</v>
       </c>
       <c r="C472" t="n">
-        <v>22.99580127578646</v>
+        <v>22.99579936214814</v>
       </c>
       <c r="D472" t="n">
-        <v>21.748699777184</v>
+        <v>21.74869796732555</v>
       </c>
       <c r="E472" t="n">
-        <v>21.748699777184</v>
+        <v>21.74869796732555</v>
       </c>
       <c r="F472" t="n">
         <v>1189950</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75016021728516</v>
+        <v>22.75015830993652</v>
       </c>
       <c r="C474" t="n">
-        <v>23.12806949624067</v>
+        <v>23.12806755720854</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341464991185</v>
+        <v>22.52341276157331</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027946935192</v>
+        <v>23.09027753348805</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9912,16 +9912,16 @@
         <v>44790</v>
       </c>
       <c r="B475" t="n">
-        <v>22.80684661865234</v>
+        <v>22.80684471130371</v>
       </c>
       <c r="C475" t="n">
-        <v>23.09027993509618</v>
+        <v>23.09027800404387</v>
       </c>
       <c r="D475" t="n">
-        <v>22.2399835897919</v>
+        <v>22.23998172985033</v>
       </c>
       <c r="E475" t="n">
-        <v>22.4856232745575</v>
+        <v>22.48562139407294</v>
       </c>
       <c r="F475" t="n">
         <v>781800</v>
@@ -9952,16 +9952,16 @@
         <v>44792</v>
       </c>
       <c r="B477" t="n">
-        <v>21.16294097900391</v>
+        <v>21.16293907165527</v>
       </c>
       <c r="C477" t="n">
-        <v>22.16440109139413</v>
+        <v>22.16439909378708</v>
       </c>
       <c r="D477" t="n">
-        <v>20.97398722682458</v>
+        <v>20.97398533650574</v>
       </c>
       <c r="E477" t="n">
-        <v>22.16440109139413</v>
+        <v>22.16439909378708</v>
       </c>
       <c r="F477" t="n">
         <v>1251050</v>
@@ -10072,16 +10072,16 @@
         <v>44802</v>
       </c>
       <c r="B483" t="n">
-        <v>20.91729736328125</v>
+        <v>20.91729545593262</v>
       </c>
       <c r="C483" t="n">
-        <v>21.12514881226926</v>
+        <v>21.12514688596765</v>
       </c>
       <c r="D483" t="n">
-        <v>20.10479288728027</v>
+        <v>20.10479105402004</v>
       </c>
       <c r="E483" t="n">
-        <v>20.40712030179352</v>
+        <v>20.4071184409655</v>
       </c>
       <c r="F483" t="n">
         <v>1048850</v>
@@ -10152,16 +10152,16 @@
         <v>44806</v>
       </c>
       <c r="B487" t="n">
-        <v>20.97398376464844</v>
+        <v>20.97398567199707</v>
       </c>
       <c r="C487" t="n">
-        <v>21.20072931104297</v>
+        <v>21.20073123901156</v>
       </c>
       <c r="D487" t="n">
-        <v>20.55828269525176</v>
+        <v>20.55828456479703</v>
       </c>
       <c r="E487" t="n">
-        <v>20.87950600314736</v>
+        <v>20.8795079019043</v>
       </c>
       <c r="F487" t="n">
         <v>1001300</v>
@@ -10192,16 +10192,16 @@
         <v>44810</v>
       </c>
       <c r="B489" t="n">
-        <v>20.55828475952148</v>
+        <v>20.55828666687012</v>
       </c>
       <c r="C489" t="n">
-        <v>21.67311849274579</v>
+        <v>21.67312050352603</v>
       </c>
       <c r="D489" t="n">
-        <v>20.35043510495954</v>
+        <v>20.35043699302438</v>
       </c>
       <c r="E489" t="n">
-        <v>21.55974480715789</v>
+        <v>21.5597468074196</v>
       </c>
       <c r="F489" t="n">
         <v>1564950</v>
@@ -10232,16 +10232,16 @@
         <v>44813</v>
       </c>
       <c r="B491" t="n">
-        <v>20.25595474243164</v>
+        <v>20.25595855712891</v>
       </c>
       <c r="C491" t="n">
-        <v>20.2937447647837</v>
+        <v>20.29374858659776</v>
       </c>
       <c r="D491" t="n">
-        <v>19.42455262652599</v>
+        <v>19.42455628464968</v>
       </c>
       <c r="E491" t="n">
-        <v>19.9158355311963</v>
+        <v>19.9158392818407</v>
       </c>
       <c r="F491" t="n">
         <v>1292000</v>
@@ -10252,16 +10252,16 @@
         <v>44816</v>
       </c>
       <c r="B492" t="n">
-        <v>20.65276145935059</v>
+        <v>20.65276336669922</v>
       </c>
       <c r="C492" t="n">
-        <v>21.12514848777479</v>
+        <v>21.12515043874988</v>
       </c>
       <c r="D492" t="n">
-        <v>20.42601590194859</v>
+        <v>20.42601778835654</v>
       </c>
       <c r="E492" t="n">
-        <v>20.44491001355529</v>
+        <v>20.44491190170818</v>
       </c>
       <c r="F492" t="n">
         <v>1299050</v>
@@ -10352,16 +10352,16 @@
         <v>44823</v>
       </c>
       <c r="B497" t="n">
-        <v>20.36932754516602</v>
+        <v>20.36932945251465</v>
       </c>
       <c r="C497" t="n">
-        <v>20.52049124552984</v>
+        <v>20.52049316703318</v>
       </c>
       <c r="D497" t="n">
-        <v>19.85915050694149</v>
+        <v>19.85915236651802</v>
       </c>
       <c r="E497" t="n">
-        <v>19.93473235712339</v>
+        <v>19.93473422377729</v>
       </c>
       <c r="F497" t="n">
         <v>718850</v>
@@ -10372,16 +10372,16 @@
         <v>44824</v>
       </c>
       <c r="B498" t="n">
-        <v>19.84025382995605</v>
+        <v>19.84025764465332</v>
       </c>
       <c r="C498" t="n">
-        <v>20.63386412731537</v>
+        <v>20.63386809460055</v>
       </c>
       <c r="D498" t="n">
-        <v>19.74577607036311</v>
+        <v>19.74577986689508</v>
       </c>
       <c r="E498" t="n">
-        <v>20.3693267608578</v>
+        <v>20.36933067728023</v>
       </c>
       <c r="F498" t="n">
         <v>1041050</v>
@@ -10392,16 +10392,16 @@
         <v>44825</v>
       </c>
       <c r="B499" t="n">
-        <v>19.12222862243652</v>
+        <v>19.12222671508789</v>
       </c>
       <c r="C499" t="n">
-        <v>20.08589869007059</v>
+        <v>20.08589668660058</v>
       </c>
       <c r="D499" t="n">
-        <v>19.04664676234838</v>
+        <v>19.04664486253867</v>
       </c>
       <c r="E499" t="n">
-        <v>19.84025719428071</v>
+        <v>19.84025521531224</v>
       </c>
       <c r="F499" t="n">
         <v>1245900</v>
@@ -10412,16 +10412,16 @@
         <v>44826</v>
       </c>
       <c r="B500" t="n">
-        <v>19.93473243713379</v>
+        <v>19.93473434448242</v>
       </c>
       <c r="C500" t="n">
-        <v>19.97252246136969</v>
+        <v>19.97252437233406</v>
       </c>
       <c r="D500" t="n">
-        <v>18.81989879096601</v>
+        <v>18.81990059164773</v>
       </c>
       <c r="E500" t="n">
-        <v>19.34897174436288</v>
+        <v>19.34897359566612</v>
       </c>
       <c r="F500" t="n">
         <v>1035500</v>
@@ -10432,16 +10432,16 @@
         <v>44827</v>
       </c>
       <c r="B501" t="n">
-        <v>19.57571983337402</v>
+        <v>19.57571792602539</v>
       </c>
       <c r="C501" t="n">
-        <v>19.68909352480502</v>
+        <v>19.68909160640989</v>
       </c>
       <c r="D501" t="n">
-        <v>19.21670644753429</v>
+        <v>19.21670457516592</v>
       </c>
       <c r="E501" t="n">
-        <v>19.34897425252572</v>
+        <v>19.3489723672699</v>
       </c>
       <c r="F501" t="n">
         <v>673550</v>
@@ -10452,16 +10452,16 @@
         <v>44830</v>
       </c>
       <c r="B502" t="n">
-        <v>18.70652770996094</v>
+        <v>18.7065258026123</v>
       </c>
       <c r="C502" t="n">
-        <v>19.48124403745187</v>
+        <v>19.48124205111187</v>
       </c>
       <c r="D502" t="n">
-        <v>18.63094584898788</v>
+        <v>18.6309439493457</v>
       </c>
       <c r="E502" t="n">
-        <v>19.34897442923874</v>
+        <v>19.34897245638518</v>
       </c>
       <c r="F502" t="n">
         <v>1198500</v>
@@ -10492,16 +10492,16 @@
         <v>44832</v>
       </c>
       <c r="B504" t="n">
-        <v>18.44198799133301</v>
+        <v>18.44198989868164</v>
       </c>
       <c r="C504" t="n">
-        <v>18.66873352376579</v>
+        <v>18.66873545456541</v>
       </c>
       <c r="D504" t="n">
-        <v>18.15855472428204</v>
+        <v>18.15855660231681</v>
       </c>
       <c r="E504" t="n">
-        <v>18.49867392393788</v>
+        <v>18.49867583714921</v>
       </c>
       <c r="F504" t="n">
         <v>784750</v>
@@ -10512,16 +10512,16 @@
         <v>44833</v>
       </c>
       <c r="B505" t="n">
-        <v>18.21524429321289</v>
+        <v>18.21524620056152</v>
       </c>
       <c r="C505" t="n">
-        <v>18.30972025639716</v>
+        <v>18.30972217363853</v>
       </c>
       <c r="D505" t="n">
-        <v>17.8562291458641</v>
+        <v>17.85623101561966</v>
       </c>
       <c r="E505" t="n">
-        <v>18.2908261449684</v>
+        <v>18.29082806023133</v>
       </c>
       <c r="F505" t="n">
         <v>1182750</v>
@@ -10552,16 +10552,16 @@
         <v>44837</v>
       </c>
       <c r="B507" t="n">
-        <v>19.27339172363281</v>
+        <v>19.27338981628418</v>
       </c>
       <c r="C507" t="n">
-        <v>19.27339172363281</v>
+        <v>19.27338981628418</v>
       </c>
       <c r="D507" t="n">
-        <v>18.76321463492602</v>
+        <v>18.76321277806593</v>
       </c>
       <c r="E507" t="n">
-        <v>18.89548243532896</v>
+        <v>18.89548056537928</v>
       </c>
       <c r="F507" t="n">
         <v>1581550</v>
@@ -10592,16 +10592,16 @@
         <v>44839</v>
       </c>
       <c r="B509" t="n">
-        <v>19.63240623474121</v>
+        <v>19.63240814208984</v>
       </c>
       <c r="C509" t="n">
-        <v>19.84025588577203</v>
+        <v>19.8402578133139</v>
       </c>
       <c r="D509" t="n">
-        <v>19.38676475515193</v>
+        <v>19.38676663863574</v>
       </c>
       <c r="E509" t="n">
-        <v>19.72688220211023</v>
+        <v>19.72688411863749</v>
       </c>
       <c r="F509" t="n">
         <v>721150</v>
@@ -10632,16 +10632,16 @@
         <v>44841</v>
       </c>
       <c r="B511" t="n">
-        <v>19.63240623474121</v>
+        <v>19.63240814208984</v>
       </c>
       <c r="C511" t="n">
-        <v>20.38822478577472</v>
+        <v>20.38822676655345</v>
       </c>
       <c r="D511" t="n">
-        <v>19.55682437963786</v>
+        <v>19.55682627964348</v>
       </c>
       <c r="E511" t="n">
-        <v>20.38822478577472</v>
+        <v>20.38822676655345</v>
       </c>
       <c r="F511" t="n">
         <v>673950</v>
@@ -10652,16 +10652,16 @@
         <v>44844</v>
       </c>
       <c r="B512" t="n">
-        <v>19.55682373046875</v>
+        <v>19.55682182312012</v>
       </c>
       <c r="C512" t="n">
-        <v>19.74577746094821</v>
+        <v>19.7457755351712</v>
       </c>
       <c r="D512" t="n">
-        <v>19.29228634538129</v>
+        <v>19.2922844638326</v>
       </c>
       <c r="E512" t="n">
-        <v>19.68909152200573</v>
+        <v>19.68908960175721</v>
       </c>
       <c r="F512" t="n">
         <v>555250</v>
@@ -10672,16 +10672,16 @@
         <v>44845</v>
       </c>
       <c r="B513" t="n">
-        <v>19.5946159362793</v>
+        <v>19.59461402893066</v>
       </c>
       <c r="C513" t="n">
-        <v>19.78357148979955</v>
+        <v>19.78356956405789</v>
       </c>
       <c r="D513" t="n">
-        <v>19.16002068600192</v>
+        <v>19.16001882095698</v>
       </c>
       <c r="E513" t="n">
-        <v>19.50013815951917</v>
+        <v>19.50013626136705</v>
       </c>
       <c r="F513" t="n">
         <v>1130250</v>
@@ -10732,16 +10732,16 @@
         <v>44851</v>
       </c>
       <c r="B516" t="n">
-        <v>19.17891502380371</v>
+        <v>19.17891311645508</v>
       </c>
       <c r="C516" t="n">
-        <v>19.70798985903592</v>
+        <v>19.70798789907064</v>
       </c>
       <c r="D516" t="n">
-        <v>19.06554313197805</v>
+        <v>19.06554123590428</v>
       </c>
       <c r="E516" t="n">
-        <v>19.23560277173027</v>
+        <v>19.23560085874403</v>
       </c>
       <c r="F516" t="n">
         <v>780550</v>
@@ -10832,16 +10832,16 @@
         <v>44858</v>
       </c>
       <c r="B521" t="n">
-        <v>19.55682373046875</v>
+        <v>19.55682182312012</v>
       </c>
       <c r="C521" t="n">
-        <v>19.8591511408467</v>
+        <v>19.85914920401251</v>
       </c>
       <c r="D521" t="n">
-        <v>19.33007637067178</v>
+        <v>19.33007448543749</v>
       </c>
       <c r="E521" t="n">
-        <v>19.74577746094821</v>
+        <v>19.7457755351712</v>
       </c>
       <c r="F521" t="n">
         <v>947100</v>
@@ -10852,16 +10852,16 @@
         <v>44859</v>
       </c>
       <c r="B522" t="n">
-        <v>19.17891502380371</v>
+        <v>19.17891311645508</v>
       </c>
       <c r="C522" t="n">
-        <v>19.78357172092427</v>
+        <v>19.78356975344236</v>
       </c>
       <c r="D522" t="n">
-        <v>19.06554313197805</v>
+        <v>19.06554123590428</v>
       </c>
       <c r="E522" t="n">
-        <v>19.51903430330817</v>
+        <v>19.51903236213458</v>
       </c>
       <c r="F522" t="n">
         <v>967800</v>
@@ -10892,16 +10892,16 @@
         <v>44861</v>
       </c>
       <c r="B524" t="n">
-        <v>19.50013732910156</v>
+        <v>19.50013542175293</v>
       </c>
       <c r="C524" t="n">
-        <v>19.7457788174117</v>
+        <v>19.74577688603637</v>
       </c>
       <c r="D524" t="n">
-        <v>18.40419949018779</v>
+        <v>18.40419769003509</v>
       </c>
       <c r="E524" t="n">
-        <v>18.49867726292455</v>
+        <v>18.49867545353079</v>
       </c>
       <c r="F524" t="n">
         <v>1150900</v>
@@ -10952,16 +10952,16 @@
         <v>44866</v>
       </c>
       <c r="B527" t="n">
-        <v>20.48270034790039</v>
+        <v>20.48270225524902</v>
       </c>
       <c r="C527" t="n">
-        <v>20.84171367044992</v>
+        <v>20.84171561122987</v>
       </c>
       <c r="D527" t="n">
-        <v>19.95362741919089</v>
+        <v>19.95362927727227</v>
       </c>
       <c r="E527" t="n">
-        <v>20.27484891725449</v>
+        <v>20.274850805248</v>
       </c>
       <c r="F527" t="n">
         <v>1462800</v>
@@ -11032,16 +11032,16 @@
         <v>44873</v>
       </c>
       <c r="B531" t="n">
-        <v>19.95362663269043</v>
+        <v>19.95362854003906</v>
       </c>
       <c r="C531" t="n">
-        <v>20.35043176408526</v>
+        <v>20.35043370936413</v>
       </c>
       <c r="D531" t="n">
-        <v>19.25449232336496</v>
+        <v>19.254494163884</v>
       </c>
       <c r="E531" t="n">
-        <v>20.35043176408526</v>
+        <v>20.35043370936413</v>
       </c>
       <c r="F531" t="n">
         <v>2602700</v>
@@ -11072,16 +11072,16 @@
         <v>44875</v>
       </c>
       <c r="B533" t="n">
-        <v>16.94924545288086</v>
+        <v>16.94924736022949</v>
       </c>
       <c r="C533" t="n">
-        <v>18.51757009212037</v>
+        <v>18.51757217595721</v>
       </c>
       <c r="D533" t="n">
-        <v>16.25011293435352</v>
+        <v>16.25011476302671</v>
       </c>
       <c r="E533" t="n">
-        <v>18.51757009212037</v>
+        <v>18.51757217595721</v>
       </c>
       <c r="F533" t="n">
         <v>6247350</v>
@@ -11092,16 +11092,16 @@
         <v>44876</v>
       </c>
       <c r="B534" t="n">
-        <v>15.51319026947021</v>
+        <v>15.51318836212158</v>
       </c>
       <c r="C534" t="n">
-        <v>16.96814139722099</v>
+        <v>16.96813931098594</v>
       </c>
       <c r="D534" t="n">
-        <v>15.05969824828244</v>
+        <v>15.05969639669071</v>
       </c>
       <c r="E534" t="n">
-        <v>16.94924728539026</v>
+        <v>16.94924520147825</v>
       </c>
       <c r="F534" t="n">
         <v>6426800</v>
@@ -11112,16 +11112,16 @@
         <v>44879</v>
       </c>
       <c r="B535" t="n">
-        <v>15.45650386810303</v>
+        <v>15.45650482177734</v>
       </c>
       <c r="C535" t="n">
-        <v>16.26900831697925</v>
+        <v>16.26900932078551</v>
       </c>
       <c r="D535" t="n">
-        <v>14.8896390838082</v>
+        <v>14.88964000250667</v>
       </c>
       <c r="E535" t="n">
-        <v>15.96668091255894</v>
+        <v>15.96668189771144</v>
       </c>
       <c r="F535" t="n">
         <v>3328550</v>
@@ -11172,16 +11172,16 @@
         <v>44883</v>
       </c>
       <c r="B538" t="n">
-        <v>13.83149242401123</v>
+        <v>13.83149337768555</v>
       </c>
       <c r="C538" t="n">
-        <v>14.88963925247558</v>
+        <v>14.88964027910857</v>
       </c>
       <c r="D538" t="n">
-        <v>13.73701465855629</v>
+        <v>13.73701560571641</v>
       </c>
       <c r="E538" t="n">
-        <v>14.26608852329183</v>
+        <v>14.26608950693133</v>
       </c>
       <c r="F538" t="n">
         <v>3266800</v>
@@ -11232,16 +11232,16 @@
         <v>44888</v>
       </c>
       <c r="B541" t="n">
-        <v>14.02044773101807</v>
+        <v>14.02044677734375</v>
       </c>
       <c r="C541" t="n">
-        <v>14.07713367222323</v>
+        <v>14.07713271469312</v>
       </c>
       <c r="D541" t="n">
-        <v>13.62364253855478</v>
+        <v>13.62364161187125</v>
       </c>
       <c r="E541" t="n">
-        <v>14.05823865882377</v>
+        <v>14.05823770257891</v>
       </c>
       <c r="F541" t="n">
         <v>1795300</v>
@@ -11252,16 +11252,16 @@
         <v>44889</v>
       </c>
       <c r="B542" t="n">
-        <v>14.94632625579834</v>
+        <v>14.94632530212402</v>
       </c>
       <c r="C542" t="n">
-        <v>15.11638588533049</v>
+        <v>15.11638492080524</v>
       </c>
       <c r="D542" t="n">
-        <v>14.22829861101032</v>
+        <v>14.22829770315091</v>
       </c>
       <c r="E542" t="n">
-        <v>14.30388046835643</v>
+        <v>14.30387955567439</v>
       </c>
       <c r="F542" t="n">
         <v>1608000</v>
@@ -11272,16 +11272,16 @@
         <v>44890</v>
       </c>
       <c r="B543" t="n">
-        <v>14.11492443084717</v>
+        <v>14.11492347717285</v>
       </c>
       <c r="C543" t="n">
-        <v>14.90853480626151</v>
+        <v>14.90853379896694</v>
       </c>
       <c r="D543" t="n">
-        <v>13.94486570826322</v>
+        <v>13.94486476607892</v>
       </c>
       <c r="E543" t="n">
-        <v>14.90853480626151</v>
+        <v>14.90853379896694</v>
       </c>
       <c r="F543" t="n">
         <v>1492900</v>
@@ -11292,16 +11292,16 @@
         <v>44893</v>
       </c>
       <c r="B544" t="n">
-        <v>13.98265647888184</v>
+        <v>13.98265743255615</v>
       </c>
       <c r="C544" t="n">
-        <v>14.28498389431492</v>
+        <v>14.28498486860921</v>
       </c>
       <c r="D544" t="n">
-        <v>13.90707462502356</v>
+        <v>13.90707557354289</v>
       </c>
       <c r="E544" t="n">
-        <v>14.13382018659838</v>
+        <v>14.13382115058268</v>
       </c>
       <c r="F544" t="n">
         <v>1713550</v>
@@ -11312,16 +11312,16 @@
         <v>44894</v>
       </c>
       <c r="B545" t="n">
-        <v>14.39835643768311</v>
+        <v>14.39835739135742</v>
       </c>
       <c r="C545" t="n">
-        <v>14.6817888354814</v>
+        <v>14.68178980792885</v>
       </c>
       <c r="D545" t="n">
-        <v>13.94486532201124</v>
+        <v>13.9448662456486</v>
       </c>
       <c r="E545" t="n">
-        <v>14.07713311357882</v>
+        <v>14.07713404597693</v>
       </c>
       <c r="F545" t="n">
         <v>1730700</v>
@@ -11332,16 +11332,16 @@
         <v>44895</v>
       </c>
       <c r="B546" t="n">
-        <v>14.41725254058838</v>
+        <v>14.4172534942627</v>
       </c>
       <c r="C546" t="n">
-        <v>14.60620717459865</v>
+        <v>14.60620814077196</v>
       </c>
       <c r="D546" t="n">
-        <v>13.83149272465316</v>
+        <v>13.83149363958056</v>
       </c>
       <c r="E546" t="n">
-        <v>14.41725254058838</v>
+        <v>14.4172534942627</v>
       </c>
       <c r="F546" t="n">
         <v>1926400</v>
@@ -11372,16 +11372,16 @@
         <v>44897</v>
       </c>
       <c r="B548" t="n">
-        <v>14.28498363494873</v>
+        <v>14.28498268127441</v>
       </c>
       <c r="C548" t="n">
-        <v>14.58731104489259</v>
+        <v>14.58731007103471</v>
       </c>
       <c r="D548" t="n">
-        <v>14.05823807749083</v>
+        <v>14.05823713895419</v>
       </c>
       <c r="E548" t="n">
-        <v>14.17161085621978</v>
+        <v>14.1716099101143</v>
       </c>
       <c r="F548" t="n">
         <v>1219600</v>
@@ -11392,16 +11392,16 @@
         <v>44900</v>
       </c>
       <c r="B549" t="n">
-        <v>13.41579151153564</v>
+        <v>13.41579246520996</v>
       </c>
       <c r="C549" t="n">
-        <v>14.22829778218658</v>
+        <v>14.22829879361868</v>
       </c>
       <c r="D549" t="n">
-        <v>13.30241873212065</v>
+        <v>13.30241967773575</v>
       </c>
       <c r="E549" t="n">
-        <v>14.22829778218658</v>
+        <v>14.22829879361868</v>
       </c>
       <c r="F549" t="n">
         <v>1514950</v>
@@ -11512,16 +11512,16 @@
         <v>44908</v>
       </c>
       <c r="B555" t="n">
-        <v>11.58292961120605</v>
+        <v>11.58293056488037</v>
       </c>
       <c r="C555" t="n">
-        <v>12.22537532711658</v>
+        <v>12.22537633368632</v>
       </c>
       <c r="D555" t="n">
-        <v>11.48845184953939</v>
+        <v>11.48845279543493</v>
       </c>
       <c r="E555" t="n">
-        <v>11.97973476859532</v>
+        <v>11.97973575494038</v>
       </c>
       <c r="F555" t="n">
         <v>2082000</v>
@@ -11572,16 +11572,16 @@
         <v>44911</v>
       </c>
       <c r="B558" t="n">
-        <v>11.31839370727539</v>
+        <v>11.31839275360107</v>
       </c>
       <c r="C558" t="n">
-        <v>11.71519891614213</v>
+        <v>11.71519792903348</v>
       </c>
       <c r="D558" t="n">
-        <v>11.09164813106777</v>
+        <v>11.09164719649877</v>
       </c>
       <c r="E558" t="n">
-        <v>11.63961705740626</v>
+        <v>11.63961607666605</v>
       </c>
       <c r="F558" t="n">
         <v>4251600</v>
@@ -11612,16 +11612,16 @@
         <v>44915</v>
       </c>
       <c r="B560" t="n">
-        <v>12.56549453735352</v>
+        <v>12.56549549102783</v>
       </c>
       <c r="C560" t="n">
-        <v>12.86782193281247</v>
+        <v>12.86782290943231</v>
       </c>
       <c r="D560" t="n">
-        <v>11.67740646168276</v>
+        <v>11.6774073479545</v>
       </c>
       <c r="E560" t="n">
-        <v>11.79077923497987</v>
+        <v>11.79078012985618</v>
       </c>
       <c r="F560" t="n">
         <v>2603950</v>
@@ -11672,16 +11672,16 @@
         <v>44918</v>
       </c>
       <c r="B563" t="n">
-        <v>13.39689540863037</v>
+        <v>13.39689636230469</v>
       </c>
       <c r="C563" t="n">
-        <v>13.66143187240536</v>
+        <v>13.66143284491103</v>
       </c>
       <c r="D563" t="n">
-        <v>12.88671749227526</v>
+        <v>12.88671840963194</v>
       </c>
       <c r="E563" t="n">
-        <v>12.90561250347013</v>
+        <v>12.90561342217188</v>
       </c>
       <c r="F563" t="n">
         <v>1442850</v>
@@ -11732,16 +11732,16 @@
         <v>44923</v>
       </c>
       <c r="B566" t="n">
-        <v>13.10085010528564</v>
+        <v>13.10084915161133</v>
       </c>
       <c r="C566" t="n">
-        <v>13.12014487705818</v>
+        <v>13.1201439219793</v>
       </c>
       <c r="D566" t="n">
-        <v>12.29048809134627</v>
+        <v>12.29048719666213</v>
       </c>
       <c r="E566" t="n">
-        <v>12.46413735719766</v>
+        <v>12.46413644987275</v>
       </c>
       <c r="F566" t="n">
         <v>2129050</v>
@@ -11972,16 +11972,16 @@
         <v>44942</v>
       </c>
       <c r="B578" t="n">
-        <v>12.88861274719238</v>
+        <v>12.88861179351807</v>
       </c>
       <c r="C578" t="n">
-        <v>13.48673689641575</v>
+        <v>13.4867358984841</v>
       </c>
       <c r="D578" t="n">
-        <v>12.69566962164055</v>
+        <v>12.69566868224278</v>
       </c>
       <c r="E578" t="n">
-        <v>13.29379377086392</v>
+        <v>13.29379278720882</v>
       </c>
       <c r="F578" t="n">
         <v>1617800</v>
@@ -11992,16 +11992,16 @@
         <v>44943</v>
       </c>
       <c r="B579" t="n">
-        <v>13.0622615814209</v>
+        <v>13.06226253509521</v>
       </c>
       <c r="C579" t="n">
-        <v>13.2937933243056</v>
+        <v>13.29379429488402</v>
       </c>
       <c r="D579" t="n">
-        <v>12.86931846235032</v>
+        <v>12.86931940193787</v>
       </c>
       <c r="E579" t="n">
-        <v>13.00437818568704</v>
+        <v>13.0043791351353</v>
       </c>
       <c r="F579" t="n">
         <v>1398800</v>
@@ -12052,16 +12052,16 @@
         <v>44946</v>
       </c>
       <c r="B582" t="n">
-        <v>14.06556701660156</v>
+        <v>14.06556606292725</v>
       </c>
       <c r="C582" t="n">
-        <v>14.12345041355349</v>
+        <v>14.12344945595456</v>
       </c>
       <c r="D582" t="n">
-        <v>13.50603149950962</v>
+        <v>13.50603058377296</v>
       </c>
       <c r="E582" t="n">
-        <v>13.73756324726655</v>
+        <v>13.73756231583157</v>
       </c>
       <c r="F582" t="n">
         <v>2454200</v>
@@ -12112,16 +12112,16 @@
         <v>44951</v>
       </c>
       <c r="B585" t="n">
-        <v>14.47074699401855</v>
+        <v>14.47074794769287</v>
       </c>
       <c r="C585" t="n">
-        <v>14.62510148141737</v>
+        <v>14.6251024452642</v>
       </c>
       <c r="D585" t="n">
-        <v>14.12344939737122</v>
+        <v>14.12345032815738</v>
       </c>
       <c r="E585" t="n">
-        <v>14.47074699401855</v>
+        <v>14.47074794769287</v>
       </c>
       <c r="F585" t="n">
         <v>2168050</v>
@@ -12132,16 +12132,16 @@
         <v>44952</v>
       </c>
       <c r="B586" t="n">
-        <v>14.56721878051758</v>
+        <v>14.56721973419189</v>
       </c>
       <c r="C586" t="n">
-        <v>14.68298464425367</v>
+        <v>14.68298560550685</v>
       </c>
       <c r="D586" t="n">
-        <v>14.20062641867396</v>
+        <v>14.20062734834852</v>
       </c>
       <c r="E586" t="n">
-        <v>14.49004153802685</v>
+        <v>14.49004248664859</v>
       </c>
       <c r="F586" t="n">
         <v>1715850</v>
@@ -12152,16 +12152,16 @@
         <v>44953</v>
       </c>
       <c r="B587" t="n">
-        <v>14.35498142242432</v>
+        <v>14.35498237609863</v>
       </c>
       <c r="C587" t="n">
-        <v>14.64439655223626</v>
+        <v>14.6443975251379</v>
       </c>
       <c r="D587" t="n">
-        <v>14.29709802845179</v>
+        <v>14.29709897828062</v>
       </c>
       <c r="E587" t="n">
-        <v>14.56721930695646</v>
+        <v>14.56722027473081</v>
       </c>
       <c r="F587" t="n">
         <v>1566450</v>
@@ -12232,16 +12232,16 @@
         <v>44959</v>
       </c>
       <c r="B591" t="n">
-        <v>14.66369152069092</v>
+        <v>14.6636905670166</v>
       </c>
       <c r="C591" t="n">
-        <v>15.31969907557229</v>
+        <v>15.31969807923358</v>
       </c>
       <c r="D591" t="n">
-        <v>14.60580904233398</v>
+        <v>14.60580809242413</v>
       </c>
       <c r="E591" t="n">
-        <v>14.85663464858973</v>
+        <v>14.85663368236708</v>
       </c>
       <c r="F591" t="n">
         <v>2155450</v>
@@ -12332,16 +12332,16 @@
         <v>44966</v>
       </c>
       <c r="B596" t="n">
-        <v>13.64109134674072</v>
+        <v>13.64109230041504</v>
       </c>
       <c r="C596" t="n">
-        <v>14.74086754418378</v>
+        <v>14.74086857474552</v>
       </c>
       <c r="D596" t="n">
-        <v>13.64109134674072</v>
+        <v>13.64109230041504</v>
       </c>
       <c r="E596" t="n">
-        <v>14.74086754418378</v>
+        <v>14.74086857474552</v>
       </c>
       <c r="F596" t="n">
         <v>2708250</v>
@@ -12372,16 +12372,16 @@
         <v>44970</v>
       </c>
       <c r="B598" t="n">
-        <v>14.12345027923584</v>
+        <v>14.12345123291016</v>
       </c>
       <c r="C598" t="n">
-        <v>14.62510239460502</v>
+        <v>14.62510338215298</v>
       </c>
       <c r="D598" t="n">
-        <v>13.9690948621738</v>
+        <v>13.96909580542539</v>
       </c>
       <c r="E598" t="n">
-        <v>14.04627303071751</v>
+        <v>14.04627397918049</v>
       </c>
       <c r="F598" t="n">
         <v>1583800</v>
@@ -12432,16 +12432,16 @@
         <v>44973</v>
       </c>
       <c r="B601" t="n">
-        <v>14.79875087738037</v>
+        <v>14.79875183105469</v>
       </c>
       <c r="C601" t="n">
-        <v>14.99169398842324</v>
+        <v>14.99169495453137</v>
       </c>
       <c r="D601" t="n">
-        <v>14.58651299522056</v>
+        <v>14.58651393521765</v>
       </c>
       <c r="E601" t="n">
-        <v>14.818044728472</v>
+        <v>14.81804568338966</v>
       </c>
       <c r="F601" t="n">
         <v>1393950</v>
@@ -12452,16 +12452,16 @@
         <v>44974</v>
       </c>
       <c r="B602" t="n">
-        <v>14.54792594909668</v>
+        <v>14.54792499542236</v>
       </c>
       <c r="C602" t="n">
-        <v>14.79875248063897</v>
+        <v>14.79875151052197</v>
       </c>
       <c r="D602" t="n">
-        <v>14.47074869631835</v>
+        <v>14.47074774770331</v>
       </c>
       <c r="E602" t="n">
-        <v>14.77945770743167</v>
+        <v>14.77945673857953</v>
       </c>
       <c r="F602" t="n">
         <v>1002450</v>
@@ -12472,16 +12472,16 @@
         <v>44979</v>
       </c>
       <c r="B603" t="n">
-        <v>14.68298530578613</v>
+        <v>14.68298625946045</v>
       </c>
       <c r="C603" t="n">
-        <v>14.68298530578613</v>
+        <v>14.68298625946045</v>
       </c>
       <c r="D603" t="n">
-        <v>14.23921568145803</v>
+        <v>14.23921660630907</v>
       </c>
       <c r="E603" t="n">
-        <v>14.45145264785709</v>
+        <v>14.45145358649313</v>
       </c>
       <c r="F603" t="n">
         <v>1555500</v>
@@ -12512,16 +12512,16 @@
         <v>44981</v>
       </c>
       <c r="B605" t="n">
-        <v>13.698974609375</v>
+        <v>13.69897365570068</v>
       </c>
       <c r="C605" t="n">
-        <v>14.52863141807201</v>
+        <v>14.52863040663991</v>
       </c>
       <c r="D605" t="n">
-        <v>13.66038598478621</v>
+        <v>13.6603850337983</v>
       </c>
       <c r="E605" t="n">
-        <v>14.45145324886905</v>
+        <v>14.45145224280983</v>
       </c>
       <c r="F605" t="n">
         <v>1763600</v>
@@ -12532,16 +12532,16 @@
         <v>44984</v>
       </c>
       <c r="B606" t="n">
-        <v>13.64109134674072</v>
+        <v>13.64109230041504</v>
       </c>
       <c r="C606" t="n">
-        <v>13.81473968737496</v>
+        <v>13.81474065318936</v>
       </c>
       <c r="D606" t="n">
-        <v>13.25520420305561</v>
+        <v>13.25520512975183</v>
       </c>
       <c r="E606" t="n">
-        <v>13.79544583620464</v>
+        <v>13.79544680067017</v>
       </c>
       <c r="F606" t="n">
         <v>2165600</v>
@@ -12572,16 +12572,16 @@
         <v>44986</v>
       </c>
       <c r="B608" t="n">
-        <v>13.48673725128174</v>
+        <v>13.48673629760742</v>
       </c>
       <c r="C608" t="n">
-        <v>13.85332965948877</v>
+        <v>13.85332867989197</v>
       </c>
       <c r="D608" t="n">
-        <v>13.21661686840171</v>
+        <v>13.21661593382815</v>
       </c>
       <c r="E608" t="n">
-        <v>13.85332965948877</v>
+        <v>13.85332867989197</v>
       </c>
       <c r="F608" t="n">
         <v>2358750</v>
@@ -12592,16 +12592,16 @@
         <v>44987</v>
       </c>
       <c r="B609" t="n">
-        <v>13.29379272460938</v>
+        <v>13.29379367828369</v>
       </c>
       <c r="C609" t="n">
-        <v>13.69897371639216</v>
+        <v>13.69897469913348</v>
       </c>
       <c r="D609" t="n">
-        <v>13.23591025151202</v>
+        <v>13.23591120103394</v>
       </c>
       <c r="E609" t="n">
-        <v>13.4867358349761</v>
+        <v>13.48673680249183</v>
       </c>
       <c r="F609" t="n">
         <v>2574150</v>
@@ -12632,16 +12632,16 @@
         <v>44991</v>
       </c>
       <c r="B611" t="n">
-        <v>14.12345027923584</v>
+        <v>14.12345123291016</v>
       </c>
       <c r="C611" t="n">
-        <v>14.25851000413024</v>
+        <v>14.25851096692435</v>
       </c>
       <c r="D611" t="n">
-        <v>13.35167687402712</v>
+        <v>13.35167777558807</v>
       </c>
       <c r="E611" t="n">
-        <v>13.35167687402712</v>
+        <v>13.35167777558807</v>
       </c>
       <c r="F611" t="n">
         <v>2062900</v>
@@ -12652,16 +12652,16 @@
         <v>44992</v>
       </c>
       <c r="B612" t="n">
-        <v>14.54792594909668</v>
+        <v>14.54792499542236</v>
       </c>
       <c r="C612" t="n">
-        <v>14.6443979750823</v>
+        <v>14.64439701508386</v>
       </c>
       <c r="D612" t="n">
-        <v>13.50603211656379</v>
+        <v>13.50603123118975</v>
       </c>
       <c r="E612" t="n">
-        <v>13.79544727449524</v>
+        <v>13.79544637014889</v>
       </c>
       <c r="F612" t="n">
         <v>3753550</v>
@@ -12692,16 +12692,16 @@
         <v>44994</v>
       </c>
       <c r="B614" t="n">
-        <v>16.11076736450195</v>
+        <v>16.11076545715332</v>
       </c>
       <c r="C614" t="n">
-        <v>16.65100812545237</v>
+        <v>16.65100615414481</v>
       </c>
       <c r="D614" t="n">
-        <v>15.78276358534078</v>
+        <v>15.78276171682441</v>
       </c>
       <c r="E614" t="n">
-        <v>15.85994083690512</v>
+        <v>15.85993895925176</v>
       </c>
       <c r="F614" t="n">
         <v>3993300</v>
@@ -12772,16 +12772,16 @@
         <v>45000</v>
       </c>
       <c r="B618" t="n">
-        <v>15.31969833374023</v>
+        <v>15.31969928741455</v>
       </c>
       <c r="C618" t="n">
-        <v>15.47405374861028</v>
+        <v>15.47405471189345</v>
       </c>
       <c r="D618" t="n">
-        <v>14.45145292020087</v>
+        <v>14.4514538198256</v>
       </c>
       <c r="E618" t="n">
-        <v>14.64439695878208</v>
+        <v>14.64439787041787</v>
       </c>
       <c r="F618" t="n">
         <v>2068400</v>
@@ -12932,16 +12932,16 @@
         <v>45012</v>
       </c>
       <c r="B626" t="n">
-        <v>13.98838901519775</v>
+        <v>13.98838996887207</v>
       </c>
       <c r="C626" t="n">
-        <v>14.12344965413982</v>
+        <v>14.12345061702205</v>
       </c>
       <c r="D626" t="n">
-        <v>13.56391416713394</v>
+        <v>13.5639150918692</v>
       </c>
       <c r="E626" t="n">
-        <v>13.83403452499273</v>
+        <v>13.83403546814375</v>
       </c>
       <c r="F626" t="n">
         <v>1142000</v>
@@ -12992,16 +12992,16 @@
         <v>45015</v>
       </c>
       <c r="B629" t="n">
-        <v>14.54792594909668</v>
+        <v>14.54792499542236</v>
       </c>
       <c r="C629" t="n">
-        <v>15.03028423897396</v>
+        <v>15.03028325367914</v>
       </c>
       <c r="D629" t="n">
-        <v>14.33568804394356</v>
+        <v>14.33568710418228</v>
       </c>
       <c r="E629" t="n">
-        <v>14.58651457548584</v>
+        <v>14.58651361928189</v>
       </c>
       <c r="F629" t="n">
         <v>2623900</v>
@@ -13132,16 +13132,16 @@
         <v>45027</v>
       </c>
       <c r="B636" t="n">
-        <v>15.10746097564697</v>
+        <v>15.10746002197266</v>
       </c>
       <c r="C636" t="n">
-        <v>15.20393299833689</v>
+        <v>15.20393203857268</v>
       </c>
       <c r="D636" t="n">
-        <v>14.18133305392022</v>
+        <v>14.1813321587087</v>
       </c>
       <c r="E636" t="n">
-        <v>14.258510304062</v>
+        <v>14.25850940397859</v>
       </c>
       <c r="F636" t="n">
         <v>3158700</v>
@@ -13172,16 +13172,16 @@
         <v>45029</v>
       </c>
       <c r="B638" t="n">
-        <v>15.70558643341064</v>
+        <v>15.70558547973633</v>
       </c>
       <c r="C638" t="n">
-        <v>15.93711818957249</v>
+        <v>15.93711722183911</v>
       </c>
       <c r="D638" t="n">
-        <v>15.10746134995442</v>
+        <v>15.10746043259944</v>
       </c>
       <c r="E638" t="n">
-        <v>15.49334761022416</v>
+        <v>15.49334666943741</v>
       </c>
       <c r="F638" t="n">
         <v>2173500</v>
@@ -13192,16 +13192,16 @@
         <v>45030</v>
       </c>
       <c r="B639" t="n">
-        <v>15.6091136932373</v>
+        <v>15.60911464691162</v>
       </c>
       <c r="C639" t="n">
-        <v>15.91782268731036</v>
+        <v>15.91782365984595</v>
       </c>
       <c r="D639" t="n">
-        <v>15.12675542998548</v>
+        <v>15.12675635418902</v>
       </c>
       <c r="E639" t="n">
-        <v>15.68629094175557</v>
+        <v>15.6862919001452</v>
       </c>
       <c r="F639" t="n">
         <v>1580050</v>
@@ -13272,16 +13272,16 @@
         <v>45036</v>
       </c>
       <c r="B643" t="n">
-        <v>14.93381118774414</v>
+        <v>14.93381214141846</v>
       </c>
       <c r="C643" t="n">
-        <v>14.93381118774414</v>
+        <v>14.93381214141846</v>
       </c>
       <c r="D643" t="n">
-        <v>14.29709843602215</v>
+        <v>14.29709934903595</v>
       </c>
       <c r="E643" t="n">
-        <v>14.43215907912469</v>
+        <v>14.43216000076346</v>
       </c>
       <c r="F643" t="n">
         <v>1458900</v>
@@ -13312,16 +13312,16 @@
         <v>45041</v>
       </c>
       <c r="B645" t="n">
-        <v>14.54792594909668</v>
+        <v>14.54792499542236</v>
       </c>
       <c r="C645" t="n">
-        <v>14.77945770743167</v>
+        <v>14.77945673857953</v>
       </c>
       <c r="D645" t="n">
-        <v>14.27780556437252</v>
+        <v>14.27780462840567</v>
       </c>
       <c r="E645" t="n">
-        <v>14.70228045465334</v>
+        <v>14.70227949086047</v>
       </c>
       <c r="F645" t="n">
         <v>1083300</v>
@@ -13352,16 +13352,16 @@
         <v>45043</v>
       </c>
       <c r="B647" t="n">
-        <v>14.72157382965088</v>
+        <v>14.7215747833252</v>
       </c>
       <c r="C647" t="n">
-        <v>15.08816620554285</v>
+        <v>15.08816718296528</v>
       </c>
       <c r="D647" t="n">
-        <v>14.52863071603019</v>
+        <v>14.52863165720552</v>
       </c>
       <c r="E647" t="n">
-        <v>15.03028281144397</v>
+        <v>15.03028378511668</v>
       </c>
       <c r="F647" t="n">
         <v>2959450</v>
@@ -13372,16 +13372,16 @@
         <v>45044</v>
       </c>
       <c r="B648" t="n">
-        <v>14.79875087738037</v>
+        <v>14.79875183105469</v>
       </c>
       <c r="C648" t="n">
-        <v>14.85663335068057</v>
+        <v>14.856634308085</v>
       </c>
       <c r="D648" t="n">
-        <v>14.33568649085217</v>
+        <v>14.33568741468527</v>
       </c>
       <c r="E648" t="n">
-        <v>14.83733949958894</v>
+        <v>14.83734045575002</v>
       </c>
       <c r="F648" t="n">
         <v>3490000</v>
@@ -13392,16 +13392,16 @@
         <v>45048</v>
       </c>
       <c r="B649" t="n">
-        <v>14.31639385223389</v>
+        <v>14.31639289855957</v>
       </c>
       <c r="C649" t="n">
-        <v>14.68298625427517</v>
+        <v>14.68298527618061</v>
       </c>
       <c r="D649" t="n">
-        <v>14.14274457757607</v>
+        <v>14.14274363546925</v>
       </c>
       <c r="E649" t="n">
-        <v>14.62510285604742</v>
+        <v>14.62510188180872</v>
       </c>
       <c r="F649" t="n">
         <v>2334400</v>
@@ -29692,19 +29692,39 @@
         <v>46239</v>
       </c>
       <c r="B1464" t="n">
-        <v>7.66</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="C1464" t="n">
-        <v>7.83</v>
+        <v>7.829999923706055</v>
       </c>
       <c r="D1464" t="n">
-        <v>7.6</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="E1464" t="n">
-        <v>7.6</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="F1464" t="n">
         <v>1601500</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="C1465" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>3215300</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -472,16 +472,16 @@
         <v>44095</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59559726715088</v>
+        <v>12.59559631347656</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80833058545472</v>
+        <v>12.80832961567333</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45377505494831</v>
+        <v>12.45377411201205</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46707035901289</v>
+        <v>12.46706941506998</v>
       </c>
       <c r="F3" t="n">
         <v>1323800</v>
@@ -492,16 +492,16 @@
         <v>44096</v>
       </c>
       <c r="B4" t="n">
-        <v>12.58673286437988</v>
+        <v>12.58673191070557</v>
       </c>
       <c r="C4" t="n">
-        <v>12.77287472474392</v>
+        <v>12.77287375696596</v>
       </c>
       <c r="D4" t="n">
-        <v>12.43161450652202</v>
+        <v>12.43161356460074</v>
       </c>
       <c r="E4" t="n">
-        <v>12.44491065559339</v>
+        <v>12.44490971266469</v>
       </c>
       <c r="F4" t="n">
         <v>1698000</v>
@@ -532,16 +532,16 @@
         <v>44098</v>
       </c>
       <c r="B6" t="n">
-        <v>12.45377445220947</v>
+        <v>12.45377349853516</v>
       </c>
       <c r="C6" t="n">
-        <v>12.84378551689074</v>
+        <v>12.84378453335049</v>
       </c>
       <c r="D6" t="n">
-        <v>12.40945480170939</v>
+        <v>12.40945385142895</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6532116114693</v>
+        <v>12.65321064252266</v>
       </c>
       <c r="F6" t="n">
         <v>571400</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513519287109</v>
+        <v>12.36513423919678</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366209522167</v>
+        <v>12.49366113163458</v>
       </c>
       <c r="D7" t="n">
-        <v>12.32081554222169</v>
+        <v>12.32081459196557</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377449416991</v>
+        <v>12.45377353365919</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -572,16 +572,16 @@
         <v>44102</v>
       </c>
       <c r="B8" t="n">
-        <v>11.58068084716797</v>
+        <v>11.58067989349365</v>
       </c>
       <c r="C8" t="n">
-        <v>12.51139018424467</v>
+        <v>12.51138915392602</v>
       </c>
       <c r="D8" t="n">
-        <v>11.58068084716797</v>
+        <v>11.58067989349365</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43161497744851</v>
+        <v>12.43161395369939</v>
       </c>
       <c r="F8" t="n">
         <v>1524000</v>
@@ -592,16 +592,16 @@
         <v>44103</v>
       </c>
       <c r="B9" t="n">
-        <v>11.29703521728516</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C9" t="n">
-        <v>11.83330135852865</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="D9" t="n">
-        <v>11.07986986928638</v>
+        <v>11.07987080462801</v>
       </c>
       <c r="E9" t="n">
-        <v>11.83330135852865</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="F9" t="n">
         <v>897600</v>
@@ -632,16 +632,16 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>11.68261528015137</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="C11" t="n">
-        <v>11.68261528015137</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="D11" t="n">
-        <v>10.92918377675503</v>
+        <v>10.92918466892529</v>
       </c>
       <c r="E11" t="n">
-        <v>11.22612432864335</v>
+        <v>11.22612524505344</v>
       </c>
       <c r="F11" t="n">
         <v>1726600</v>
@@ -652,16 +652,16 @@
         <v>44106</v>
       </c>
       <c r="B12" t="n">
-        <v>11.29703521728516</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C12" t="n">
-        <v>11.55408816443952</v>
+        <v>11.55408913981376</v>
       </c>
       <c r="D12" t="n">
-        <v>11.19953266675315</v>
+        <v>11.19953361219649</v>
       </c>
       <c r="E12" t="n">
-        <v>11.51420056528393</v>
+        <v>11.51420153729093</v>
       </c>
       <c r="F12" t="n">
         <v>878600</v>
@@ -692,16 +692,16 @@
         <v>44110</v>
       </c>
       <c r="B14" t="n">
-        <v>11.43885803222656</v>
+        <v>11.43885898590088</v>
       </c>
       <c r="C14" t="n">
-        <v>12.05489940494884</v>
+        <v>12.05490040998342</v>
       </c>
       <c r="D14" t="n">
-        <v>11.38124307774816</v>
+        <v>11.38124402661904</v>
       </c>
       <c r="E14" t="n">
-        <v>11.58954433818795</v>
+        <v>11.5895453044252</v>
       </c>
       <c r="F14" t="n">
         <v>472800</v>
@@ -712,16 +712,16 @@
         <v>44111</v>
       </c>
       <c r="B15" t="n">
-        <v>11.68261528015137</v>
+        <v>11.68261623382568</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82443748189021</v>
+        <v>11.82443844714174</v>
       </c>
       <c r="D15" t="n">
-        <v>11.35465122729855</v>
+        <v>11.35465215420053</v>
       </c>
       <c r="E15" t="n">
-        <v>11.6294315318358</v>
+        <v>11.62943248116863</v>
       </c>
       <c r="F15" t="n">
         <v>437200</v>
@@ -732,16 +732,16 @@
         <v>44112</v>
       </c>
       <c r="B16" t="n">
-        <v>11.52306461334229</v>
+        <v>11.5230655670166</v>
       </c>
       <c r="C16" t="n">
-        <v>11.90421240567286</v>
+        <v>11.90421339089181</v>
       </c>
       <c r="D16" t="n">
-        <v>11.39010651362682</v>
+        <v>11.39010745629723</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68261500926243</v>
+        <v>11.68261597614149</v>
       </c>
       <c r="F16" t="n">
         <v>595200</v>
@@ -752,16 +752,16 @@
         <v>44113</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10365104675293</v>
+        <v>12.1036491394043</v>
       </c>
       <c r="C17" t="n">
-        <v>12.29422496640223</v>
+        <v>12.29422302902209</v>
       </c>
       <c r="D17" t="n">
-        <v>11.53193013313212</v>
+        <v>11.53192831587788</v>
       </c>
       <c r="E17" t="n">
-        <v>11.53636218304571</v>
+        <v>11.53636036509305</v>
       </c>
       <c r="F17" t="n">
         <v>672400</v>
@@ -772,16 +772,16 @@
         <v>44117</v>
       </c>
       <c r="B18" t="n">
-        <v>12.18785762786865</v>
+        <v>12.18785667419434</v>
       </c>
       <c r="C18" t="n">
-        <v>12.44934264096545</v>
+        <v>12.44934166683048</v>
       </c>
       <c r="D18" t="n">
-        <v>12.18785762786865</v>
+        <v>12.18785667419434</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36956743760344</v>
+        <v>12.36956646971071</v>
       </c>
       <c r="F18" t="n">
         <v>440800</v>
@@ -832,16 +832,16 @@
         <v>44120</v>
       </c>
       <c r="B21" t="n">
-        <v>12.45377445220947</v>
+        <v>12.45377349853516</v>
       </c>
       <c r="C21" t="n">
-        <v>12.49366205312684</v>
+        <v>12.49366109639805</v>
       </c>
       <c r="D21" t="n">
-        <v>11.97955613611076</v>
+        <v>11.97955521875072</v>
       </c>
       <c r="E21" t="n">
-        <v>12.06376254220119</v>
+        <v>12.06376161839286</v>
       </c>
       <c r="F21" t="n">
         <v>585200</v>
@@ -872,16 +872,16 @@
         <v>44124</v>
       </c>
       <c r="B23" t="n">
-        <v>12.85265064239502</v>
+        <v>12.8526496887207</v>
       </c>
       <c r="C23" t="n">
-        <v>12.87037884214153</v>
+        <v>12.87037788715177</v>
       </c>
       <c r="D23" t="n">
-        <v>12.41388784259389</v>
+        <v>12.41388692147603</v>
       </c>
       <c r="E23" t="n">
-        <v>12.53798270483821</v>
+        <v>12.53798177451245</v>
       </c>
       <c r="F23" t="n">
         <v>729200</v>
@@ -892,16 +892,16 @@
         <v>44125</v>
       </c>
       <c r="B24" t="n">
-        <v>12.85265064239502</v>
+        <v>12.8526496887207</v>
       </c>
       <c r="C24" t="n">
-        <v>12.94572115508295</v>
+        <v>12.94572019450274</v>
       </c>
       <c r="D24" t="n">
-        <v>12.51139040521844</v>
+        <v>12.51138947686584</v>
       </c>
       <c r="E24" t="n">
-        <v>12.85265064239502</v>
+        <v>12.8526496887207</v>
       </c>
       <c r="F24" t="n">
         <v>501200</v>
@@ -932,16 +932,16 @@
         <v>44127</v>
       </c>
       <c r="B26" t="n">
-        <v>12.94128704071045</v>
+        <v>12.94128799438477</v>
       </c>
       <c r="C26" t="n">
-        <v>13.18061176618817</v>
+        <v>13.18061273749889</v>
       </c>
       <c r="D26" t="n">
-        <v>12.86151185044224</v>
+        <v>12.86151279823773</v>
       </c>
       <c r="E26" t="n">
-        <v>13.08754127442653</v>
+        <v>13.08754223887867</v>
       </c>
       <c r="F26" t="n">
         <v>543600</v>
@@ -952,16 +952,16 @@
         <v>44130</v>
       </c>
       <c r="B27" t="n">
-        <v>12.60002899169922</v>
+        <v>12.6000280380249</v>
       </c>
       <c r="C27" t="n">
-        <v>12.87480930941692</v>
+        <v>12.87480833494496</v>
       </c>
       <c r="D27" t="n">
-        <v>12.41831918133934</v>
+        <v>12.41831824141832</v>
       </c>
       <c r="E27" t="n">
-        <v>12.84821785664712</v>
+        <v>12.84821688418782</v>
       </c>
       <c r="F27" t="n">
         <v>307600</v>
@@ -972,16 +972,16 @@
         <v>44131</v>
       </c>
       <c r="B28" t="n">
-        <v>12.22774600982666</v>
+        <v>12.22774505615234</v>
       </c>
       <c r="C28" t="n">
-        <v>12.77730752376721</v>
+        <v>12.77730652723113</v>
       </c>
       <c r="D28" t="n">
-        <v>12.19229045555073</v>
+        <v>12.19228950464168</v>
       </c>
       <c r="E28" t="n">
-        <v>12.67537291088978</v>
+        <v>12.67537192230385</v>
       </c>
       <c r="F28" t="n">
         <v>652400</v>
@@ -992,16 +992,16 @@
         <v>44132</v>
       </c>
       <c r="B29" t="n">
-        <v>11.43885803222656</v>
+        <v>11.43885898590088</v>
       </c>
       <c r="C29" t="n">
-        <v>11.92637250178829</v>
+        <v>11.9263734961074</v>
       </c>
       <c r="D29" t="n">
-        <v>11.3014678751419</v>
+        <v>11.30146881736179</v>
       </c>
       <c r="E29" t="n">
-        <v>11.92637250178829</v>
+        <v>11.9263734961074</v>
       </c>
       <c r="F29" t="n">
         <v>860400</v>
@@ -1012,16 +1012,16 @@
         <v>44133</v>
       </c>
       <c r="B30" t="n">
-        <v>11.70477485656738</v>
+        <v>11.70477390289307</v>
       </c>
       <c r="C30" t="n">
-        <v>11.87762056184598</v>
+        <v>11.87761959408865</v>
       </c>
       <c r="D30" t="n">
-        <v>11.00895914058972</v>
+        <v>11.00895824360864</v>
       </c>
       <c r="E30" t="n">
-        <v>11.39453815164614</v>
+        <v>11.3945372232491</v>
       </c>
       <c r="F30" t="n">
         <v>683400</v>
@@ -1032,16 +1032,16 @@
         <v>44134</v>
       </c>
       <c r="B31" t="n">
-        <v>11.38567543029785</v>
+        <v>11.38567447662354</v>
       </c>
       <c r="C31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.81114107243664</v>
       </c>
       <c r="D31" t="n">
-        <v>11.00895965537159</v>
+        <v>11.00895873325132</v>
       </c>
       <c r="E31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.81114107243664</v>
       </c>
       <c r="F31" t="n">
         <v>907200</v>
@@ -1052,16 +1052,16 @@
         <v>44138</v>
       </c>
       <c r="B32" t="n">
-        <v>11.85546112060547</v>
+        <v>11.85546207427979</v>
       </c>
       <c r="C32" t="n">
-        <v>11.9662598226672</v>
+        <v>11.96626078525436</v>
       </c>
       <c r="D32" t="n">
-        <v>11.51863296489856</v>
+        <v>11.51863389147782</v>
       </c>
       <c r="E32" t="n">
-        <v>11.70034276865364</v>
+        <v>11.70034370984996</v>
       </c>
       <c r="F32" t="n">
         <v>1038200</v>
@@ -1072,16 +1072,16 @@
         <v>44139</v>
       </c>
       <c r="B33" t="n">
-        <v>12.57786846160889</v>
+        <v>12.5778694152832</v>
       </c>
       <c r="C33" t="n">
-        <v>12.78173851581722</v>
+        <v>12.78173948494929</v>
       </c>
       <c r="D33" t="n">
-        <v>11.90421298612225</v>
+        <v>11.90421388871892</v>
       </c>
       <c r="E33" t="n">
-        <v>11.96625998963795</v>
+        <v>11.96626089693912</v>
       </c>
       <c r="F33" t="n">
         <v>620400</v>
@@ -1092,16 +1092,16 @@
         <v>44140</v>
       </c>
       <c r="B34" t="n">
-        <v>12.79503536224365</v>
+        <v>12.79503345489502</v>
       </c>
       <c r="C34" t="n">
-        <v>13.02992808569082</v>
+        <v>13.02992614332686</v>
       </c>
       <c r="D34" t="n">
-        <v>12.63991699966924</v>
+        <v>12.63991511544401</v>
       </c>
       <c r="E34" t="n">
-        <v>12.78617126259321</v>
+        <v>12.78616935656595</v>
       </c>
       <c r="F34" t="n">
         <v>682600</v>
@@ -1112,16 +1112,16 @@
         <v>44141</v>
       </c>
       <c r="B35" t="n">
-        <v>13.55732822418213</v>
+        <v>13.55732917785645</v>
       </c>
       <c r="C35" t="n">
-        <v>13.69471836763221</v>
+        <v>13.69471933097108</v>
       </c>
       <c r="D35" t="n">
-        <v>12.6576425273241</v>
+        <v>12.65764341771108</v>
       </c>
       <c r="E35" t="n">
-        <v>12.74184977119922</v>
+        <v>12.74185066750967</v>
       </c>
       <c r="F35" t="n">
         <v>948200</v>
@@ -1132,16 +1132,16 @@
         <v>44144</v>
       </c>
       <c r="B36" t="n">
-        <v>13.29584407806396</v>
+        <v>13.29584503173828</v>
       </c>
       <c r="C36" t="n">
-        <v>13.96950038089769</v>
+        <v>13.96950138289152</v>
       </c>
       <c r="D36" t="n">
-        <v>13.12299837555377</v>
+        <v>13.12299931683034</v>
       </c>
       <c r="E36" t="n">
-        <v>13.7390388806661</v>
+        <v>13.73903986612956</v>
       </c>
       <c r="F36" t="n">
         <v>650800</v>
@@ -1172,16 +1172,16 @@
         <v>44146</v>
       </c>
       <c r="B38" t="n">
-        <v>13.29584407806396</v>
+        <v>13.29584503173828</v>
       </c>
       <c r="C38" t="n">
-        <v>13.41993892711028</v>
+        <v>13.41993988968558</v>
       </c>
       <c r="D38" t="n">
-        <v>12.89696892478745</v>
+        <v>12.89696984985155</v>
       </c>
       <c r="E38" t="n">
-        <v>13.25152442873835</v>
+        <v>13.25152537923374</v>
       </c>
       <c r="F38" t="n">
         <v>586400</v>
@@ -1192,16 +1192,16 @@
         <v>44147</v>
       </c>
       <c r="B39" t="n">
-        <v>12.94128704071045</v>
+        <v>12.94128799438477</v>
       </c>
       <c r="C39" t="n">
-        <v>13.35345744821801</v>
+        <v>13.35345843226615</v>
       </c>
       <c r="D39" t="n">
-        <v>12.75071316292016</v>
+        <v>12.75071410255063</v>
       </c>
       <c r="E39" t="n">
-        <v>13.12299682062052</v>
+        <v>13.12299778768546</v>
       </c>
       <c r="F39" t="n">
         <v>656600</v>
@@ -1272,16 +1272,16 @@
         <v>44153</v>
       </c>
       <c r="B43" t="n">
-        <v>12.74185276031494</v>
+        <v>12.74184989929199</v>
       </c>
       <c r="C43" t="n">
-        <v>13.18947968916004</v>
+        <v>13.18947672762809</v>
       </c>
       <c r="D43" t="n">
-        <v>12.66207754691106</v>
+        <v>12.66207470380063</v>
       </c>
       <c r="E43" t="n">
-        <v>13.11413652598162</v>
+        <v>13.11413358136703</v>
       </c>
       <c r="F43" t="n">
         <v>532400</v>
@@ -1292,16 +1292,16 @@
         <v>44154</v>
       </c>
       <c r="B44" t="n">
-        <v>12.99447250366211</v>
+        <v>12.99447059631348</v>
       </c>
       <c r="C44" t="n">
-        <v>13.0742477096854</v>
+        <v>13.07424579062724</v>
       </c>
       <c r="D44" t="n">
-        <v>12.48036655965319</v>
+        <v>12.48036472776582</v>
       </c>
       <c r="E44" t="n">
-        <v>12.74185158147306</v>
+        <v>12.74184971120452</v>
       </c>
       <c r="F44" t="n">
         <v>711400</v>
@@ -1312,16 +1312,16 @@
         <v>44158</v>
       </c>
       <c r="B45" t="n">
-        <v>13.35346031188965</v>
+        <v>13.35345935821533</v>
       </c>
       <c r="C45" t="n">
-        <v>13.47312312295385</v>
+        <v>13.47312216073348</v>
       </c>
       <c r="D45" t="n">
-        <v>13.0698158815097</v>
+        <v>13.06981494809263</v>
       </c>
       <c r="E45" t="n">
-        <v>13.13629493921411</v>
+        <v>13.13629400104926</v>
       </c>
       <c r="F45" t="n">
         <v>731400</v>
@@ -1332,16 +1332,16 @@
         <v>44159</v>
       </c>
       <c r="B46" t="n">
-        <v>13.73903942108154</v>
+        <v>13.73903751373291</v>
       </c>
       <c r="C46" t="n">
-        <v>13.82767872321933</v>
+        <v>13.82767680356518</v>
       </c>
       <c r="D46" t="n">
-        <v>13.27368519817572</v>
+        <v>13.27368335543079</v>
       </c>
       <c r="E46" t="n">
-        <v>13.4731223599952</v>
+        <v>13.47312048956302</v>
       </c>
       <c r="F46" t="n">
         <v>798800</v>
@@ -1352,16 +1352,16 @@
         <v>44160</v>
       </c>
       <c r="B47" t="n">
-        <v>13.65040016174316</v>
+        <v>13.65039920806885</v>
       </c>
       <c r="C47" t="n">
-        <v>13.77449501605975</v>
+        <v>13.77449405371565</v>
       </c>
       <c r="D47" t="n">
-        <v>13.34016429394225</v>
+        <v>13.34016336194231</v>
       </c>
       <c r="E47" t="n">
-        <v>13.61494460984229</v>
+        <v>13.61494365864504</v>
       </c>
       <c r="F47" t="n">
         <v>724200</v>
@@ -1372,16 +1372,16 @@
         <v>44161</v>
       </c>
       <c r="B48" t="n">
-        <v>13.53073787689209</v>
+        <v>13.53073978424072</v>
       </c>
       <c r="C48" t="n">
-        <v>13.73903913363267</v>
+        <v>13.7390410703443</v>
       </c>
       <c r="D48" t="n">
-        <v>13.44653062615568</v>
+        <v>13.44653252163411</v>
       </c>
       <c r="E48" t="n">
-        <v>13.65039983334939</v>
+        <v>13.65040175756607</v>
       </c>
       <c r="F48" t="n">
         <v>209800</v>
@@ -1392,16 +1392,16 @@
         <v>44162</v>
       </c>
       <c r="B49" t="n">
-        <v>13.39334774017334</v>
+        <v>13.39334678649902</v>
       </c>
       <c r="C49" t="n">
-        <v>13.71688061533133</v>
+        <v>13.71687963861983</v>
       </c>
       <c r="D49" t="n">
-        <v>13.38891569034081</v>
+        <v>13.38891473698208</v>
       </c>
       <c r="E49" t="n">
-        <v>13.5307387490005</v>
+        <v>13.53073778554325</v>
       </c>
       <c r="F49" t="n">
         <v>510000</v>
@@ -1412,16 +1412,16 @@
         <v>44165</v>
       </c>
       <c r="B50" t="n">
-        <v>13.1362943649292</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="C50" t="n">
-        <v>13.73017549906958</v>
+        <v>13.73017450228043</v>
       </c>
       <c r="D50" t="n">
-        <v>13.1362943649292</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="E50" t="n">
-        <v>13.38891528035829</v>
+        <v>13.38891430834409</v>
       </c>
       <c r="F50" t="n">
         <v>1093200</v>
@@ -1432,16 +1432,16 @@
         <v>44166</v>
       </c>
       <c r="B51" t="n">
-        <v>14.1822338104248</v>
+        <v>14.18223285675049</v>
       </c>
       <c r="C51" t="n">
-        <v>14.40383121371269</v>
+        <v>14.40383024513721</v>
       </c>
       <c r="D51" t="n">
-        <v>13.47755400034316</v>
+        <v>13.47755309405454</v>
       </c>
       <c r="E51" t="n">
-        <v>13.73460695434403</v>
+        <v>13.73460603077007</v>
       </c>
       <c r="F51" t="n">
         <v>2351000</v>
@@ -1452,16 +1452,16 @@
         <v>44167</v>
       </c>
       <c r="B52" t="n">
-        <v>14.1822338104248</v>
+        <v>14.18223285675049</v>
       </c>
       <c r="C52" t="n">
-        <v>14.37280771250471</v>
+        <v>14.37280674601539</v>
       </c>
       <c r="D52" t="n">
-        <v>13.93404495543393</v>
+        <v>13.9340440184489</v>
       </c>
       <c r="E52" t="n">
-        <v>14.1822338104248</v>
+        <v>14.18223285675049</v>
       </c>
       <c r="F52" t="n">
         <v>767800</v>
@@ -1552,16 +1552,16 @@
         <v>44174</v>
       </c>
       <c r="B57" t="n">
-        <v>13.88972568511963</v>
+        <v>13.889723777771</v>
       </c>
       <c r="C57" t="n">
-        <v>14.2487140968875</v>
+        <v>14.24871214024228</v>
       </c>
       <c r="D57" t="n">
-        <v>13.65926417652651</v>
+        <v>13.65926230082504</v>
       </c>
       <c r="E57" t="n">
-        <v>14.1467786461421</v>
+        <v>14.14677670349474</v>
       </c>
       <c r="F57" t="n">
         <v>570800</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.00495624542236</v>
+        <v>14.00495719909668</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10245879986408</v>
+        <v>14.10245976017788</v>
       </c>
       <c r="D58" t="n">
-        <v>13.51744178255972</v>
+        <v>13.5174427030365</v>
       </c>
       <c r="E58" t="n">
-        <v>13.88529344315728</v>
+        <v>13.8852943886831</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1592,16 +1592,16 @@
         <v>44176</v>
       </c>
       <c r="B59" t="n">
-        <v>13.82324695587158</v>
+        <v>13.82324600219727</v>
       </c>
       <c r="C59" t="n">
-        <v>13.96063711619654</v>
+        <v>13.9606361530436</v>
       </c>
       <c r="D59" t="n">
-        <v>13.40221153010944</v>
+        <v>13.40221060548261</v>
       </c>
       <c r="E59" t="n">
-        <v>13.92074951395268</v>
+        <v>13.9207485535516</v>
       </c>
       <c r="F59" t="n">
         <v>523600</v>
@@ -1612,16 +1612,16 @@
         <v>44179</v>
       </c>
       <c r="B60" t="n">
-        <v>13.75676822662354</v>
+        <v>13.75676727294922</v>
       </c>
       <c r="C60" t="n">
-        <v>14.05814000746984</v>
+        <v>14.05813903290322</v>
       </c>
       <c r="D60" t="n">
-        <v>13.61494516788007</v>
+        <v>13.61494422403749</v>
       </c>
       <c r="E60" t="n">
-        <v>13.7434720771181</v>
+        <v>13.74347112436552</v>
       </c>
       <c r="F60" t="n">
         <v>525000</v>
@@ -1652,16 +1652,16 @@
         <v>44181</v>
       </c>
       <c r="B62" t="n">
-        <v>13.9163179397583</v>
+        <v>13.91631698608398</v>
       </c>
       <c r="C62" t="n">
-        <v>14.1778029654802</v>
+        <v>14.17780199388652</v>
       </c>
       <c r="D62" t="n">
-        <v>13.71688076705103</v>
+        <v>13.71687982704398</v>
       </c>
       <c r="E62" t="n">
-        <v>14.13791536187333</v>
+        <v>14.13791439301312</v>
       </c>
       <c r="F62" t="n">
         <v>564600</v>
@@ -1672,16 +1672,16 @@
         <v>44182</v>
       </c>
       <c r="B63" t="n">
-        <v>13.73903942108154</v>
+        <v>13.73903751373291</v>
       </c>
       <c r="C63" t="n">
-        <v>14.13348254040794</v>
+        <v>14.13348057829998</v>
       </c>
       <c r="D63" t="n">
-        <v>13.67256036714172</v>
+        <v>13.67255846902217</v>
       </c>
       <c r="E63" t="n">
-        <v>13.91631718003009</v>
+        <v>13.91631524807053</v>
       </c>
       <c r="F63" t="n">
         <v>633000</v>
@@ -1692,16 +1692,16 @@
         <v>44183</v>
       </c>
       <c r="B64" t="n">
-        <v>13.40664386749268</v>
+        <v>13.40664291381836</v>
       </c>
       <c r="C64" t="n">
-        <v>13.83654255661189</v>
+        <v>13.83654157235696</v>
       </c>
       <c r="D64" t="n">
-        <v>13.28698105819358</v>
+        <v>13.28698011303142</v>
       </c>
       <c r="E64" t="n">
-        <v>13.61937718713968</v>
+        <v>13.6193762183327</v>
       </c>
       <c r="F64" t="n">
         <v>920000</v>
@@ -1712,16 +1712,16 @@
         <v>44186</v>
       </c>
       <c r="B65" t="n">
-        <v>13.14959144592285</v>
+        <v>13.14958953857422</v>
       </c>
       <c r="C65" t="n">
-        <v>13.34016536975649</v>
+        <v>13.3401634347651</v>
       </c>
       <c r="D65" t="n">
-        <v>12.76844359825558</v>
+        <v>12.76844174619245</v>
       </c>
       <c r="E65" t="n">
-        <v>13.14959144592285</v>
+        <v>13.14958953857422</v>
       </c>
       <c r="F65" t="n">
         <v>872000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294364929199</v>
+        <v>15.11294078826904</v>
       </c>
       <c r="C68" t="n">
-        <v>15.13067184897926</v>
+        <v>15.1306689846002</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586848207222</v>
+        <v>14.07586581737739</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348344040167</v>
+        <v>14.13348076479979</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.19715023040771</v>
+        <v>15.19715118408203</v>
       </c>
       <c r="C69" t="n">
-        <v>15.34783653134916</v>
+        <v>15.34783749447957</v>
       </c>
       <c r="D69" t="n">
-        <v>14.74952253173429</v>
+        <v>14.7495234573184</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510322837077</v>
+        <v>15.13510417815142</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1812,16 +1812,16 @@
         <v>44195</v>
       </c>
       <c r="B70" t="n">
-        <v>15.72012042999268</v>
+        <v>15.72012233734131</v>
       </c>
       <c r="C70" t="n">
-        <v>15.91512553748784</v>
+        <v>15.91512746849676</v>
       </c>
       <c r="D70" t="n">
-        <v>15.25033332340621</v>
+        <v>15.25033517375479</v>
       </c>
       <c r="E70" t="n">
-        <v>15.37886022388563</v>
+        <v>15.37886208982859</v>
       </c>
       <c r="F70" t="n">
         <v>2946000</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884868621826</v>
+        <v>14.98884963989258</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171822605652</v>
+        <v>15.94171924035773</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952307751646</v>
+        <v>14.74952401596354</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069472389008</v>
+        <v>15.91069573621739</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1852,16 +1852,16 @@
         <v>44201</v>
       </c>
       <c r="B72" t="n">
-        <v>15.13953590393066</v>
+        <v>15.13953495025635</v>
       </c>
       <c r="C72" t="n">
-        <v>15.45863673473862</v>
+        <v>15.45863576096341</v>
       </c>
       <c r="D72" t="n">
-        <v>14.36394492178124</v>
+        <v>14.36394401696318</v>
       </c>
       <c r="E72" t="n">
-        <v>14.84702737257476</v>
+        <v>14.84702643732623</v>
       </c>
       <c r="F72" t="n">
         <v>1878200</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.58997440338135</v>
+        <v>14.5899715423584</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135901369479</v>
+        <v>15.28135601709469</v>
       </c>
       <c r="D73" t="n">
-        <v>14.58997440338135</v>
+        <v>14.5899715423584</v>
       </c>
       <c r="E73" t="n">
-        <v>15.13953678962859</v>
+        <v>15.13953382083913</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1892,16 +1892,16 @@
         <v>44203</v>
       </c>
       <c r="B74" t="n">
-        <v>14.40513134002686</v>
+        <v>14.40513229370117</v>
       </c>
       <c r="C74" t="n">
-        <v>14.96995146169153</v>
+        <v>14.96995245275908</v>
       </c>
       <c r="D74" t="n">
-        <v>14.39623633458149</v>
+        <v>14.39623728766692</v>
       </c>
       <c r="E74" t="n">
-        <v>14.68531807363505</v>
+        <v>14.6853190458588</v>
       </c>
       <c r="F74" t="n">
         <v>1215000</v>
@@ -1912,16 +1912,16 @@
         <v>44204</v>
       </c>
       <c r="B75" t="n">
-        <v>15.06334400177002</v>
+        <v>15.06334590911865</v>
       </c>
       <c r="C75" t="n">
-        <v>15.27237235405728</v>
+        <v>15.27237428787347</v>
       </c>
       <c r="D75" t="n">
-        <v>14.38733896781096</v>
+        <v>14.38734078956258</v>
       </c>
       <c r="E75" t="n">
-        <v>14.38733896781096</v>
+        <v>14.38734078956258</v>
       </c>
       <c r="F75" t="n">
         <v>1077600</v>
@@ -1952,16 +1952,16 @@
         <v>44208</v>
       </c>
       <c r="B77" t="n">
-        <v>15.99285221099854</v>
+        <v>15.99285411834717</v>
       </c>
       <c r="C77" t="n">
-        <v>16.31306559830687</v>
+        <v>16.31306754384497</v>
       </c>
       <c r="D77" t="n">
-        <v>15.34353212811103</v>
+        <v>15.34353395802008</v>
       </c>
       <c r="E77" t="n">
-        <v>15.90390385935192</v>
+        <v>15.90390575609234</v>
       </c>
       <c r="F77" t="n">
         <v>2193200</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422393798828</v>
+        <v>16.38422584533691</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538227998573</v>
+        <v>16.45538419561817</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169386673051</v>
+        <v>15.92169572023429</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93503722223226</v>
+        <v>15.93503907728939</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2072,16 +2072,16 @@
         <v>44216</v>
       </c>
       <c r="B83" t="n">
-        <v>16.25525283813477</v>
+        <v>16.25525093078613</v>
       </c>
       <c r="C83" t="n">
-        <v>16.81117804940168</v>
+        <v>16.81117607682225</v>
       </c>
       <c r="D83" t="n">
-        <v>16.01064608448715</v>
+        <v>16.01064420584002</v>
       </c>
       <c r="E83" t="n">
-        <v>16.6999930071483</v>
+        <v>16.69999104761502</v>
       </c>
       <c r="F83" t="n">
         <v>1073000</v>
@@ -2112,16 +2112,16 @@
         <v>44218</v>
       </c>
       <c r="B85" t="n">
-        <v>15.4013500213623</v>
+        <v>15.40134906768799</v>
       </c>
       <c r="C85" t="n">
-        <v>15.84164176695957</v>
+        <v>15.84164078602173</v>
       </c>
       <c r="D85" t="n">
-        <v>15.17453162201319</v>
+        <v>15.17453068238381</v>
       </c>
       <c r="E85" t="n">
-        <v>15.60593005864081</v>
+        <v>15.60592909229859</v>
       </c>
       <c r="F85" t="n">
         <v>1029200</v>
@@ -2132,16 +2132,16 @@
         <v>44222</v>
       </c>
       <c r="B86" t="n">
-        <v>14.67197513580322</v>
+        <v>14.67197704315186</v>
       </c>
       <c r="C86" t="n">
-        <v>15.52587522559741</v>
+        <v>15.52587724395259</v>
       </c>
       <c r="D86" t="n">
-        <v>14.6363951171208</v>
+        <v>14.63639701984405</v>
       </c>
       <c r="E86" t="n">
-        <v>15.38355854396505</v>
+        <v>15.38356054381913</v>
       </c>
       <c r="F86" t="n">
         <v>1156000</v>
@@ -2152,16 +2152,16 @@
         <v>44223</v>
       </c>
       <c r="B87" t="n">
-        <v>15.00553131103516</v>
+        <v>15.00552940368652</v>
       </c>
       <c r="C87" t="n">
-        <v>15.57034972966033</v>
+        <v>15.5703477505178</v>
       </c>
       <c r="D87" t="n">
-        <v>14.53410620714105</v>
+        <v>14.53410435971512</v>
       </c>
       <c r="E87" t="n">
-        <v>14.74313459133305</v>
+        <v>14.74313271733759</v>
       </c>
       <c r="F87" t="n">
         <v>1909000</v>
@@ -2172,16 +2172,16 @@
         <v>44224</v>
       </c>
       <c r="B88" t="n">
-        <v>15.65929698944092</v>
+        <v>15.65929889678955</v>
       </c>
       <c r="C88" t="n">
-        <v>15.98840537788466</v>
+        <v>15.98840732531967</v>
       </c>
       <c r="D88" t="n">
-        <v>14.95216023141669</v>
+        <v>14.95216205263397</v>
       </c>
       <c r="E88" t="n">
-        <v>15.13450358680413</v>
+        <v>15.13450543023138</v>
       </c>
       <c r="F88" t="n">
         <v>3941600</v>
@@ -2192,16 +2192,16 @@
         <v>44225</v>
       </c>
       <c r="B89" t="n">
-        <v>15.74379825592041</v>
+        <v>15.74380016326904</v>
       </c>
       <c r="C89" t="n">
-        <v>16.55322500128939</v>
+        <v>16.55322700669943</v>
       </c>
       <c r="D89" t="n">
-        <v>15.38800486303628</v>
+        <v>15.38800672728083</v>
       </c>
       <c r="E89" t="n">
-        <v>16.01064160403487</v>
+        <v>16.01064354371136</v>
       </c>
       <c r="F89" t="n">
         <v>3936400</v>
@@ -2212,16 +2212,16 @@
         <v>44228</v>
       </c>
       <c r="B90" t="n">
-        <v>16.76670265197754</v>
+        <v>16.76670074462891</v>
       </c>
       <c r="C90" t="n">
-        <v>17.02909938733217</v>
+        <v>17.02909745013378</v>
       </c>
       <c r="D90" t="n">
-        <v>15.65929902065404</v>
+        <v>15.65929723928157</v>
       </c>
       <c r="E90" t="n">
-        <v>16.01064411819733</v>
+        <v>16.0106422968565</v>
       </c>
       <c r="F90" t="n">
         <v>3072200</v>
@@ -2252,16 +2252,16 @@
         <v>44230</v>
       </c>
       <c r="B92" t="n">
-        <v>17.61170768737793</v>
+        <v>17.6117057800293</v>
       </c>
       <c r="C92" t="n">
-        <v>17.78960441009847</v>
+        <v>17.78960248348361</v>
       </c>
       <c r="D92" t="n">
-        <v>16.94015086737822</v>
+        <v>16.94014903275922</v>
       </c>
       <c r="E92" t="n">
-        <v>17.0824675669351</v>
+        <v>17.08246571690319</v>
       </c>
       <c r="F92" t="n">
         <v>1128200</v>
@@ -2272,16 +2272,16 @@
         <v>44231</v>
       </c>
       <c r="B93" t="n">
-        <v>17.88744735717773</v>
+        <v>17.8874454498291</v>
       </c>
       <c r="C93" t="n">
-        <v>18.3633191282485</v>
+        <v>18.36331717015739</v>
       </c>
       <c r="D93" t="n">
-        <v>17.61615562484698</v>
+        <v>17.61615374642633</v>
       </c>
       <c r="E93" t="n">
-        <v>17.79405064684091</v>
+        <v>17.79404874945122</v>
       </c>
       <c r="F93" t="n">
         <v>1940600</v>
@@ -2392,16 +2392,16 @@
         <v>44239</v>
       </c>
       <c r="B99" t="n">
-        <v>18.51897621154785</v>
+        <v>18.51897811889648</v>
       </c>
       <c r="C99" t="n">
-        <v>18.72355623622481</v>
+        <v>18.72355816464402</v>
       </c>
       <c r="D99" t="n">
-        <v>18.16318449546863</v>
+        <v>18.16318636617275</v>
       </c>
       <c r="E99" t="n">
-        <v>18.58123954979312</v>
+        <v>18.58124146355452</v>
       </c>
       <c r="F99" t="n">
         <v>849600</v>
@@ -2412,16 +2412,16 @@
         <v>44244</v>
       </c>
       <c r="B100" t="n">
-        <v>18.52787017822266</v>
+        <v>18.52787208557129</v>
       </c>
       <c r="C100" t="n">
-        <v>18.68797686562316</v>
+        <v>18.68797878945395</v>
       </c>
       <c r="D100" t="n">
-        <v>18.20765680342165</v>
+        <v>18.20765867780597</v>
       </c>
       <c r="E100" t="n">
-        <v>18.51897517375056</v>
+        <v>18.5189770801835</v>
       </c>
       <c r="F100" t="n">
         <v>743200</v>
@@ -2432,16 +2432,16 @@
         <v>44245</v>
       </c>
       <c r="B101" t="n">
-        <v>18.24323844909668</v>
+        <v>18.24324226379395</v>
       </c>
       <c r="C101" t="n">
-        <v>19.03487525571373</v>
+        <v>19.03487923594382</v>
       </c>
       <c r="D101" t="n">
-        <v>17.9052350351925</v>
+        <v>17.90523877921258</v>
       </c>
       <c r="E101" t="n">
-        <v>18.69242518745105</v>
+        <v>18.69242909607415</v>
       </c>
       <c r="F101" t="n">
         <v>1007600</v>
@@ -2452,16 +2452,16 @@
         <v>44246</v>
       </c>
       <c r="B102" t="n">
-        <v>18.27881813049316</v>
+        <v>18.27881622314453</v>
       </c>
       <c r="C102" t="n">
-        <v>18.57234653985784</v>
+        <v>18.57234460188025</v>
       </c>
       <c r="D102" t="n">
-        <v>17.92302637619491</v>
+        <v>17.92302450597225</v>
       </c>
       <c r="E102" t="n">
-        <v>18.23434479741172</v>
+        <v>18.23434289470377</v>
       </c>
       <c r="F102" t="n">
         <v>881800</v>
@@ -2512,16 +2512,16 @@
         <v>44251</v>
       </c>
       <c r="B105" t="n">
-        <v>17.68731307983398</v>
+        <v>17.68731498718262</v>
       </c>
       <c r="C105" t="n">
-        <v>18.09647313665348</v>
+        <v>18.09647508812474</v>
       </c>
       <c r="D105" t="n">
-        <v>17.54499639080558</v>
+        <v>17.54499828280719</v>
       </c>
       <c r="E105" t="n">
-        <v>17.70510309009973</v>
+        <v>17.70510499936678</v>
       </c>
       <c r="F105" t="n">
         <v>1411000</v>
@@ -2532,16 +2532,16 @@
         <v>44252</v>
       </c>
       <c r="B106" t="n">
-        <v>16.94459533691406</v>
+        <v>16.9445972442627</v>
       </c>
       <c r="C106" t="n">
-        <v>17.7940487700933</v>
+        <v>17.79405077305967</v>
       </c>
       <c r="D106" t="n">
-        <v>16.6377253111698</v>
+        <v>16.63772718397596</v>
       </c>
       <c r="E106" t="n">
-        <v>17.68731210746428</v>
+        <v>17.68731409841596</v>
       </c>
       <c r="F106" t="n">
         <v>1207600</v>
@@ -2552,16 +2552,16 @@
         <v>44253</v>
       </c>
       <c r="B107" t="n">
-        <v>16.69999122619629</v>
+        <v>16.69998931884766</v>
       </c>
       <c r="C107" t="n">
-        <v>17.20699469335504</v>
+        <v>17.20699272810024</v>
       </c>
       <c r="D107" t="n">
-        <v>16.40201615907802</v>
+        <v>16.40201428576187</v>
       </c>
       <c r="E107" t="n">
-        <v>17.13583634176344</v>
+        <v>17.13583438463582</v>
       </c>
       <c r="F107" t="n">
         <v>1586600</v>
@@ -2572,16 +2572,16 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>16.44648933410645</v>
+        <v>16.44649124145508</v>
       </c>
       <c r="C108" t="n">
-        <v>17.02465114728449</v>
+        <v>17.02465312168428</v>
       </c>
       <c r="D108" t="n">
-        <v>16.27748761449939</v>
+        <v>16.27748950224838</v>
       </c>
       <c r="E108" t="n">
-        <v>16.69999106524258</v>
+        <v>16.69999300199057</v>
       </c>
       <c r="F108" t="n">
         <v>1540800</v>
@@ -2632,16 +2632,16 @@
         <v>44259</v>
       </c>
       <c r="B111" t="n">
-        <v>16.05066680908203</v>
+        <v>16.05066871643066</v>
       </c>
       <c r="C111" t="n">
-        <v>16.75780348316564</v>
+        <v>16.75780547454543</v>
       </c>
       <c r="D111" t="n">
-        <v>15.79271679246922</v>
+        <v>15.79271866916489</v>
       </c>
       <c r="E111" t="n">
-        <v>16.23301014282442</v>
+        <v>16.23301207184145</v>
       </c>
       <c r="F111" t="n">
         <v>1300400</v>
@@ -2672,16 +2672,16 @@
         <v>44263</v>
       </c>
       <c r="B113" t="n">
-        <v>14.91213417053223</v>
+        <v>14.91213321685791</v>
       </c>
       <c r="C113" t="n">
-        <v>16.05956437827389</v>
+        <v>16.05956335121808</v>
       </c>
       <c r="D113" t="n">
-        <v>14.76537082800059</v>
+        <v>14.76536988371221</v>
       </c>
       <c r="E113" t="n">
-        <v>16.01064269858043</v>
+        <v>16.0106416746533</v>
       </c>
       <c r="F113" t="n">
         <v>3236800</v>
@@ -2692,16 +2692,16 @@
         <v>44264</v>
       </c>
       <c r="B114" t="n">
-        <v>14.76537036895752</v>
+        <v>14.76537132263184</v>
       </c>
       <c r="C114" t="n">
-        <v>15.42358545584995</v>
+        <v>15.42358645203744</v>
       </c>
       <c r="D114" t="n">
-        <v>14.55634199732897</v>
+        <v>14.55634293750244</v>
       </c>
       <c r="E114" t="n">
-        <v>15.11671542442504</v>
+        <v>15.11671640079224</v>
       </c>
       <c r="F114" t="n">
         <v>1628800</v>
@@ -2712,16 +2712,16 @@
         <v>44265</v>
       </c>
       <c r="B115" t="n">
-        <v>14.64529037475586</v>
+        <v>14.64529132843018</v>
       </c>
       <c r="C115" t="n">
-        <v>15.05445041737906</v>
+        <v>15.05445139769713</v>
       </c>
       <c r="D115" t="n">
-        <v>14.28505031384297</v>
+        <v>14.28505124405912</v>
       </c>
       <c r="E115" t="n">
-        <v>15.05445041737906</v>
+        <v>15.05445139769713</v>
       </c>
       <c r="F115" t="n">
         <v>3352600</v>
@@ -2752,16 +2752,16 @@
         <v>44267</v>
       </c>
       <c r="B117" t="n">
-        <v>15.61037635803223</v>
+        <v>15.61037445068359</v>
       </c>
       <c r="C117" t="n">
-        <v>15.96172143355023</v>
+        <v>15.96171948327262</v>
       </c>
       <c r="D117" t="n">
-        <v>15.41913798510718</v>
+        <v>15.41913610112494</v>
       </c>
       <c r="E117" t="n">
-        <v>15.96172143355023</v>
+        <v>15.96171948327262</v>
       </c>
       <c r="F117" t="n">
         <v>1034800</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708873748779</v>
+        <v>15.67708683013916</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619716243003</v>
+        <v>16.00619521504051</v>
       </c>
       <c r="D118" t="n">
-        <v>15.49474536187826</v>
+        <v>15.49474347671438</v>
       </c>
       <c r="E118" t="n">
-        <v>15.61482539409169</v>
+        <v>15.61482349431831</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2792,16 +2792,16 @@
         <v>44271</v>
       </c>
       <c r="B119" t="n">
-        <v>16.46872329711914</v>
+        <v>16.46872520446777</v>
       </c>
       <c r="C119" t="n">
-        <v>16.8378583482222</v>
+        <v>16.83786029832273</v>
       </c>
       <c r="D119" t="n">
-        <v>15.68153321514211</v>
+        <v>15.6815350313212</v>
       </c>
       <c r="E119" t="n">
-        <v>15.68598156565223</v>
+        <v>15.68598338234651</v>
       </c>
       <c r="F119" t="n">
         <v>1963400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880424499512</v>
+        <v>16.58880615234375</v>
       </c>
       <c r="C120" t="n">
-        <v>16.7578059463568</v>
+        <v>16.75780787313692</v>
       </c>
       <c r="D120" t="n">
-        <v>16.07735418324739</v>
+        <v>16.07735603179049</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298585477987</v>
+        <v>16.19298771661808</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2852,16 +2852,16 @@
         <v>44274</v>
       </c>
       <c r="B122" t="n">
-        <v>16.32196235656738</v>
+        <v>16.32196044921875</v>
       </c>
       <c r="C122" t="n">
-        <v>16.54433241129841</v>
+        <v>16.54433047796411</v>
       </c>
       <c r="D122" t="n">
-        <v>15.89056390749354</v>
+        <v>15.89056205055718</v>
       </c>
       <c r="E122" t="n">
-        <v>16.17519730610144</v>
+        <v>16.17519541590345</v>
       </c>
       <c r="F122" t="n">
         <v>1059200</v>
@@ -2872,16 +2872,16 @@
         <v>44277</v>
       </c>
       <c r="B123" t="n">
-        <v>16.54433250427246</v>
+        <v>16.54433059692383</v>
       </c>
       <c r="C123" t="n">
-        <v>16.58435918221094</v>
+        <v>16.58435727024774</v>
       </c>
       <c r="D123" t="n">
-        <v>15.921695668907</v>
+        <v>15.92169383334038</v>
       </c>
       <c r="E123" t="n">
-        <v>16.26414575870311</v>
+        <v>16.26414388365641</v>
       </c>
       <c r="F123" t="n">
         <v>938000</v>
@@ -2892,16 +2892,16 @@
         <v>44278</v>
       </c>
       <c r="B124" t="n">
-        <v>16.09959411621094</v>
+        <v>16.09959030151367</v>
       </c>
       <c r="C124" t="n">
-        <v>16.49985924190611</v>
+        <v>16.49985533236855</v>
       </c>
       <c r="D124" t="n">
-        <v>15.87277568475618</v>
+        <v>15.87277192380211</v>
       </c>
       <c r="E124" t="n">
-        <v>16.45538590456745</v>
+        <v>16.45538200556756</v>
       </c>
       <c r="F124" t="n">
         <v>855200</v>
@@ -2912,16 +2912,16 @@
         <v>44279</v>
       </c>
       <c r="B125" t="n">
-        <v>15.41024494171143</v>
+        <v>15.41024398803711</v>
       </c>
       <c r="C125" t="n">
-        <v>16.21077677191293</v>
+        <v>16.21077576869711</v>
       </c>
       <c r="D125" t="n">
-        <v>15.21455821448409</v>
+        <v>15.21455727291999</v>
       </c>
       <c r="E125" t="n">
-        <v>16.05067006656286</v>
+        <v>16.05066907325537</v>
       </c>
       <c r="F125" t="n">
         <v>1010400</v>
@@ -2932,16 +2932,16 @@
         <v>44280</v>
       </c>
       <c r="B126" t="n">
-        <v>16.06846046447754</v>
+        <v>16.06846237182617</v>
       </c>
       <c r="C126" t="n">
-        <v>16.22411882256725</v>
+        <v>16.22412074839275</v>
       </c>
       <c r="D126" t="n">
-        <v>15.07224188305681</v>
+        <v>15.07224367215291</v>
       </c>
       <c r="E126" t="n">
-        <v>15.38800695035243</v>
+        <v>15.38800877693028</v>
       </c>
       <c r="F126" t="n">
         <v>1320600</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.58369445800781</v>
+        <v>15.5836935043335</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174956665047</v>
+        <v>16.00174858739247</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245606766462</v>
+        <v>15.39245512569351</v>
       </c>
       <c r="E128" t="n">
-        <v>15.74380117518341</v>
+        <v>15.74380021171105</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514045715332</v>
+        <v>16.09514236450195</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23745712556681</v>
+        <v>16.23745904978063</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48584711447378</v>
+        <v>15.48584894961834</v>
       </c>
       <c r="E129" t="n">
-        <v>15.5881371138617</v>
+        <v>15.58813896112809</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3052,16 +3052,16 @@
         <v>44291</v>
       </c>
       <c r="B132" t="n">
-        <v>16.86454200744629</v>
+        <v>16.86454391479492</v>
       </c>
       <c r="C132" t="n">
-        <v>17.01130703938433</v>
+        <v>17.01130896333182</v>
       </c>
       <c r="D132" t="n">
-        <v>16.60214700467584</v>
+        <v>16.60214888234808</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90012202605503</v>
+        <v>16.90012393742769</v>
       </c>
       <c r="F132" t="n">
         <v>838600</v>
@@ -3072,16 +3072,16 @@
         <v>44292</v>
       </c>
       <c r="B133" t="n">
-        <v>17.52276039123535</v>
+        <v>17.52275848388672</v>
       </c>
       <c r="C133" t="n">
-        <v>17.5672337220387</v>
+        <v>17.56723180984916</v>
       </c>
       <c r="D133" t="n">
-        <v>16.8289652334808</v>
+        <v>16.82896340165162</v>
       </c>
       <c r="E133" t="n">
-        <v>16.89122857522503</v>
+        <v>16.8912267366185</v>
       </c>
       <c r="F133" t="n">
         <v>1684600</v>
@@ -3112,16 +3112,16 @@
         <v>44294</v>
       </c>
       <c r="B135" t="n">
-        <v>17.60726356506348</v>
+        <v>17.60725784301758</v>
       </c>
       <c r="C135" t="n">
-        <v>17.90968701925412</v>
+        <v>17.909681198926</v>
       </c>
       <c r="D135" t="n">
-        <v>17.27370843440167</v>
+        <v>17.27370282075522</v>
       </c>
       <c r="E135" t="n">
-        <v>17.38044682269506</v>
+        <v>17.38044117436055</v>
       </c>
       <c r="F135" t="n">
         <v>710000</v>
@@ -3212,16 +3212,16 @@
         <v>44301</v>
       </c>
       <c r="B140" t="n">
-        <v>17.38044166564941</v>
+        <v>17.38044357299805</v>
       </c>
       <c r="C140" t="n">
-        <v>17.60281168677666</v>
+        <v>17.60281361852843</v>
       </c>
       <c r="D140" t="n">
-        <v>17.17141330289424</v>
+        <v>17.17141518730387</v>
       </c>
       <c r="E140" t="n">
-        <v>17.17141330289424</v>
+        <v>17.17141518730387</v>
       </c>
       <c r="F140" t="n">
         <v>924800</v>
@@ -3292,16 +3292,16 @@
         <v>44308</v>
       </c>
       <c r="B144" t="n">
-        <v>17.32707405090332</v>
+        <v>17.32707214355469</v>
       </c>
       <c r="C144" t="n">
-        <v>17.97639419580525</v>
+        <v>17.97639221698004</v>
       </c>
       <c r="D144" t="n">
-        <v>17.26925905887769</v>
+        <v>17.26925715789328</v>
       </c>
       <c r="E144" t="n">
-        <v>17.94971087534692</v>
+        <v>17.94970889945899</v>
       </c>
       <c r="F144" t="n">
         <v>1084000</v>
@@ -3332,16 +3332,16 @@
         <v>44312</v>
       </c>
       <c r="B146" t="n">
-        <v>17.08691215515137</v>
+        <v>17.08691596984863</v>
       </c>
       <c r="C146" t="n">
-        <v>17.31817718810049</v>
+        <v>17.31818105442827</v>
       </c>
       <c r="D146" t="n">
-        <v>16.90012214577824</v>
+        <v>16.90012591877415</v>
       </c>
       <c r="E146" t="n">
-        <v>17.31817718810049</v>
+        <v>17.31818105442827</v>
       </c>
       <c r="F146" t="n">
         <v>836400</v>
@@ -3432,16 +3432,16 @@
         <v>44319</v>
       </c>
       <c r="B151" t="n">
-        <v>19.44735717773438</v>
+        <v>19.44735527038574</v>
       </c>
       <c r="C151" t="n">
-        <v>19.67089001885776</v>
+        <v>19.67088808958558</v>
       </c>
       <c r="D151" t="n">
-        <v>18.83934757701153</v>
+        <v>18.83934572929498</v>
       </c>
       <c r="E151" t="n">
-        <v>19.62618413280117</v>
+        <v>19.62618220791364</v>
       </c>
       <c r="F151" t="n">
         <v>2225200</v>
@@ -3452,16 +3452,16 @@
         <v>44320</v>
       </c>
       <c r="B152" t="n">
-        <v>19.79606819152832</v>
+        <v>19.79606628417969</v>
       </c>
       <c r="C152" t="n">
-        <v>20.00618961139364</v>
+        <v>20.00618768379984</v>
       </c>
       <c r="D152" t="n">
-        <v>19.25959072829643</v>
+        <v>19.25958887263734</v>
       </c>
       <c r="E152" t="n">
-        <v>19.45182740585503</v>
+        <v>19.45182553167395</v>
       </c>
       <c r="F152" t="n">
         <v>1635200</v>
@@ -3472,16 +3472,16 @@
         <v>44321</v>
       </c>
       <c r="B153" t="n">
-        <v>20.46219635009766</v>
+        <v>20.46219825744629</v>
       </c>
       <c r="C153" t="n">
-        <v>21.00761702468171</v>
+        <v>21.00761898287081</v>
       </c>
       <c r="D153" t="n">
-        <v>19.8944227326284</v>
+        <v>19.89442458705298</v>
       </c>
       <c r="E153" t="n">
-        <v>20.09113101760648</v>
+        <v>20.09113289036689</v>
       </c>
       <c r="F153" t="n">
         <v>1994000</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.8332633972168</v>
+        <v>20.83326148986816</v>
       </c>
       <c r="C155" t="n">
-        <v>20.87797099574675</v>
+        <v>20.877969084305</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384469788557</v>
+        <v>20.36384283351365</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902947604076</v>
+        <v>20.86902756541763</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3572,16 +3572,16 @@
         <v>44328</v>
       </c>
       <c r="B158" t="n">
-        <v>20.1581916809082</v>
+        <v>20.15819358825684</v>
       </c>
       <c r="C158" t="n">
-        <v>20.59631584486362</v>
+        <v>20.59631779366714</v>
       </c>
       <c r="D158" t="n">
-        <v>19.57253502320829</v>
+        <v>19.57253687514265</v>
       </c>
       <c r="E158" t="n">
-        <v>20.59631584486362</v>
+        <v>20.59631779366714</v>
       </c>
       <c r="F158" t="n">
         <v>1344400</v>
@@ -3592,16 +3592,16 @@
         <v>44329</v>
       </c>
       <c r="B159" t="n">
-        <v>20.90479278564453</v>
+        <v>20.9047908782959</v>
       </c>
       <c r="C159" t="n">
-        <v>20.97185332731664</v>
+        <v>20.97185141384942</v>
       </c>
       <c r="D159" t="n">
-        <v>20.15819383510242</v>
+        <v>20.15819199587331</v>
       </c>
       <c r="E159" t="n">
-        <v>20.25654884144274</v>
+        <v>20.25654699323974</v>
       </c>
       <c r="F159" t="n">
         <v>1469200</v>
@@ -3632,16 +3632,16 @@
         <v>44333</v>
       </c>
       <c r="B161" t="n">
-        <v>20.98526382446289</v>
+        <v>20.98526191711426</v>
       </c>
       <c r="C161" t="n">
-        <v>21.13279632744209</v>
+        <v>21.13279440668424</v>
       </c>
       <c r="D161" t="n">
-        <v>20.03748499628314</v>
+        <v>20.03748317507803</v>
       </c>
       <c r="E161" t="n">
-        <v>20.16266284941433</v>
+        <v>20.16266101683182</v>
       </c>
       <c r="F161" t="n">
         <v>1096800</v>
@@ -3672,16 +3672,16 @@
         <v>44335</v>
       </c>
       <c r="B163" t="n">
-        <v>21.36974143981934</v>
+        <v>21.3697395324707</v>
       </c>
       <c r="C163" t="n">
-        <v>21.49044939093096</v>
+        <v>21.49044747280858</v>
       </c>
       <c r="D163" t="n">
-        <v>20.88691134079327</v>
+        <v>20.88690947653946</v>
       </c>
       <c r="E163" t="n">
-        <v>21.20432759811249</v>
+        <v>21.2043257055278</v>
       </c>
       <c r="F163" t="n">
         <v>1135200</v>
@@ -3712,16 +3712,16 @@
         <v>44337</v>
       </c>
       <c r="B165" t="n">
-        <v>21.94645500183105</v>
+        <v>21.94645309448242</v>
       </c>
       <c r="C165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04033647282705</v>
       </c>
       <c r="D165" t="n">
-        <v>21.50385921408051</v>
+        <v>21.50385734519752</v>
       </c>
       <c r="E165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04033647282705</v>
       </c>
       <c r="F165" t="n">
         <v>653400</v>
@@ -3732,16 +3732,16 @@
         <v>44340</v>
       </c>
       <c r="B166" t="n">
-        <v>21.87045478820801</v>
+        <v>21.87045288085938</v>
       </c>
       <c r="C166" t="n">
-        <v>22.12081221204925</v>
+        <v>22.12081028286665</v>
       </c>
       <c r="D166" t="n">
-        <v>21.50386102444573</v>
+        <v>21.50385914906818</v>
       </c>
       <c r="E166" t="n">
-        <v>21.67821809245792</v>
+        <v>21.67821620187448</v>
       </c>
       <c r="F166" t="n">
         <v>900600</v>
@@ -3752,16 +3752,16 @@
         <v>44341</v>
       </c>
       <c r="B167" t="n">
-        <v>22.17893028259277</v>
+        <v>22.17893218994141</v>
       </c>
       <c r="C167" t="n">
-        <v>22.3622271566051</v>
+        <v>22.36222907971693</v>
       </c>
       <c r="D167" t="n">
-        <v>21.77210055220345</v>
+        <v>21.77210242456545</v>
       </c>
       <c r="E167" t="n">
-        <v>21.98222027751199</v>
+        <v>21.98222216794391</v>
       </c>
       <c r="F167" t="n">
         <v>773000</v>
@@ -3772,16 +3772,16 @@
         <v>44342</v>
       </c>
       <c r="B168" t="n">
-        <v>22.17445755004883</v>
+        <v>22.1744556427002</v>
       </c>
       <c r="C168" t="n">
-        <v>22.42481495049289</v>
+        <v>22.42481302160963</v>
       </c>
       <c r="D168" t="n">
-        <v>21.53515347667831</v>
+        <v>21.53515162431978</v>
       </c>
       <c r="E168" t="n">
-        <v>22.17445755004883</v>
+        <v>22.1744556427002</v>
       </c>
       <c r="F168" t="n">
         <v>837000</v>
@@ -3792,16 +3792,16 @@
         <v>44343</v>
       </c>
       <c r="B169" t="n">
-        <v>22.34434127807617</v>
+        <v>22.34434509277344</v>
       </c>
       <c r="C169" t="n">
-        <v>22.34434127807617</v>
+        <v>22.34434509277344</v>
       </c>
       <c r="D169" t="n">
-        <v>21.80339224371756</v>
+        <v>21.80339596606228</v>
       </c>
       <c r="E169" t="n">
-        <v>22.27281084134627</v>
+        <v>22.27281464383163</v>
       </c>
       <c r="F169" t="n">
         <v>1342400</v>
@@ -3832,16 +3832,16 @@
         <v>44347</v>
       </c>
       <c r="B171" t="n">
-        <v>23.22953224182129</v>
+        <v>23.22953033447266</v>
       </c>
       <c r="C171" t="n">
-        <v>23.22953224182129</v>
+        <v>23.22953033447266</v>
       </c>
       <c r="D171" t="n">
-        <v>22.24151750179612</v>
+        <v>22.24151567557218</v>
       </c>
       <c r="E171" t="n">
-        <v>22.24151750179612</v>
+        <v>22.24151567557218</v>
       </c>
       <c r="F171" t="n">
         <v>1311400</v>
@@ -3912,16 +3912,16 @@
         <v>44354</v>
       </c>
       <c r="B175" t="n">
-        <v>23.51565551757812</v>
+        <v>23.51565361022949</v>
       </c>
       <c r="C175" t="n">
-        <v>23.95378141142314</v>
+        <v>23.95377946853823</v>
       </c>
       <c r="D175" t="n">
-        <v>23.24741677541455</v>
+        <v>23.24741488982269</v>
       </c>
       <c r="E175" t="n">
-        <v>23.56483301823953</v>
+        <v>23.56483110690212</v>
       </c>
       <c r="F175" t="n">
         <v>1060000</v>
@@ -3952,16 +3952,16 @@
         <v>44356</v>
       </c>
       <c r="B177" t="n">
-        <v>23.51565551757812</v>
+        <v>23.51565361022949</v>
       </c>
       <c r="C177" t="n">
-        <v>23.60059909341884</v>
+        <v>23.60059717918046</v>
       </c>
       <c r="D177" t="n">
-        <v>23.18035623716349</v>
+        <v>23.1803543570109</v>
       </c>
       <c r="E177" t="n">
-        <v>23.44412507263982</v>
+        <v>23.444123171093</v>
       </c>
       <c r="F177" t="n">
         <v>621600</v>
@@ -3992,16 +3992,16 @@
         <v>44358</v>
       </c>
       <c r="B179" t="n">
-        <v>23.30553436279297</v>
+        <v>23.30553245544434</v>
       </c>
       <c r="C179" t="n">
-        <v>23.56483157022843</v>
+        <v>23.56482964165865</v>
       </c>
       <c r="D179" t="n">
-        <v>22.55893379079491</v>
+        <v>22.55893194454882</v>
       </c>
       <c r="E179" t="n">
-        <v>23.56483157022843</v>
+        <v>23.56482964165865</v>
       </c>
       <c r="F179" t="n">
         <v>855400</v>
@@ -4052,16 +4052,16 @@
         <v>44363</v>
       </c>
       <c r="B182" t="n">
-        <v>24.49920082092285</v>
+        <v>24.49919891357422</v>
       </c>
       <c r="C182" t="n">
-        <v>24.58414439817256</v>
+        <v>24.58414248421078</v>
       </c>
       <c r="D182" t="n">
-        <v>23.90013269509492</v>
+        <v>23.90013083438584</v>
       </c>
       <c r="E182" t="n">
-        <v>24.36508144761637</v>
+        <v>24.36507955070941</v>
       </c>
       <c r="F182" t="n">
         <v>781400</v>
@@ -4092,16 +4092,16 @@
         <v>44365</v>
       </c>
       <c r="B184" t="n">
-        <v>24.8970890045166</v>
+        <v>24.89708709716797</v>
       </c>
       <c r="C184" t="n">
-        <v>25.19215230760862</v>
+        <v>25.19215037765539</v>
       </c>
       <c r="D184" t="n">
-        <v>24.25778489691384</v>
+        <v>24.25778303854185</v>
       </c>
       <c r="E184" t="n">
-        <v>24.6780277596409</v>
+        <v>24.6780258690744</v>
       </c>
       <c r="F184" t="n">
         <v>1737600</v>
@@ -4112,16 +4112,16 @@
         <v>44368</v>
       </c>
       <c r="B185" t="n">
-        <v>25.23685646057129</v>
+        <v>25.23685836791992</v>
       </c>
       <c r="C185" t="n">
-        <v>25.6481560428541</v>
+        <v>25.64815798128789</v>
       </c>
       <c r="D185" t="n">
-        <v>24.69590742957842</v>
+        <v>24.69590929604326</v>
       </c>
       <c r="E185" t="n">
-        <v>25.25026788443091</v>
+        <v>25.25026979279315</v>
       </c>
       <c r="F185" t="n">
         <v>748400</v>
@@ -4192,16 +4192,16 @@
         <v>44372</v>
       </c>
       <c r="B189" t="n">
-        <v>24.3516674041748</v>
+        <v>24.35166931152344</v>
       </c>
       <c r="C189" t="n">
-        <v>24.58861166172607</v>
+        <v>24.5886135876334</v>
       </c>
       <c r="D189" t="n">
-        <v>24.00295502455915</v>
+        <v>24.00295690459483</v>
       </c>
       <c r="E189" t="n">
-        <v>24.27119544775736</v>
+        <v>24.27119734880301</v>
       </c>
       <c r="F189" t="n">
         <v>926400</v>
@@ -4212,16 +4212,16 @@
         <v>44375</v>
       </c>
       <c r="B190" t="n">
-        <v>24.48578643798828</v>
+        <v>24.48579025268555</v>
       </c>
       <c r="C190" t="n">
-        <v>25.01332405397893</v>
+        <v>25.0133279508625</v>
       </c>
       <c r="D190" t="n">
-        <v>24.06107371929478</v>
+        <v>24.06107746782506</v>
       </c>
       <c r="E190" t="n">
-        <v>24.06107371929478</v>
+        <v>24.06107746782506</v>
       </c>
       <c r="F190" t="n">
         <v>1351800</v>
@@ -4232,16 +4232,16 @@
         <v>44376</v>
       </c>
       <c r="B191" t="n">
-        <v>24.49920082092285</v>
+        <v>24.49919891357422</v>
       </c>
       <c r="C191" t="n">
-        <v>24.70485064035414</v>
+        <v>24.70484871699495</v>
       </c>
       <c r="D191" t="n">
-        <v>23.49330296299373</v>
+        <v>23.49330113395778</v>
       </c>
       <c r="E191" t="n">
-        <v>24.46790635733202</v>
+        <v>24.46790445241977</v>
       </c>
       <c r="F191" t="n">
         <v>1326200</v>
@@ -4352,16 +4352,16 @@
         <v>44384</v>
       </c>
       <c r="B197" t="n">
-        <v>26.52441024780273</v>
+        <v>26.5244083404541</v>
       </c>
       <c r="C197" t="n">
-        <v>26.93570989565746</v>
+        <v>26.9357079587326</v>
       </c>
       <c r="D197" t="n">
-        <v>26.1086389876685</v>
+        <v>26.10863711021764</v>
       </c>
       <c r="E197" t="n">
-        <v>26.19805076821403</v>
+        <v>26.19804888433364</v>
       </c>
       <c r="F197" t="n">
         <v>915800</v>
@@ -4372,16 +4372,16 @@
         <v>44385</v>
       </c>
       <c r="B198" t="n">
-        <v>26.52441024780273</v>
+        <v>26.5244083404541</v>
       </c>
       <c r="C198" t="n">
-        <v>26.52441024780273</v>
+        <v>26.5244083404541</v>
       </c>
       <c r="D198" t="n">
-        <v>25.82251549149344</v>
+        <v>25.82251363461749</v>
       </c>
       <c r="E198" t="n">
-        <v>26.23828675162768</v>
+        <v>26.23828486485395</v>
       </c>
       <c r="F198" t="n">
         <v>1041800</v>
@@ -4392,16 +4392,16 @@
         <v>44389</v>
       </c>
       <c r="B199" t="n">
-        <v>27.54371643066406</v>
+        <v>27.5437183380127</v>
       </c>
       <c r="C199" t="n">
-        <v>27.57501089139074</v>
+        <v>27.57501280090645</v>
       </c>
       <c r="D199" t="n">
-        <v>26.56911312552412</v>
+        <v>26.56911496538337</v>
       </c>
       <c r="E199" t="n">
-        <v>26.81499890498525</v>
+        <v>26.81500076187162</v>
       </c>
       <c r="F199" t="n">
         <v>886400</v>
@@ -4412,16 +4412,16 @@
         <v>44390</v>
       </c>
       <c r="B200" t="n">
-        <v>27.6644229888916</v>
+        <v>27.66442489624023</v>
       </c>
       <c r="C200" t="n">
-        <v>27.70465896573839</v>
+        <v>27.70466087586113</v>
       </c>
       <c r="D200" t="n">
-        <v>27.16817984292119</v>
+        <v>27.1681817160559</v>
       </c>
       <c r="E200" t="n">
-        <v>27.33806526798767</v>
+        <v>27.33806715283528</v>
       </c>
       <c r="F200" t="n">
         <v>796200</v>
@@ -4432,16 +4432,16 @@
         <v>44391</v>
       </c>
       <c r="B201" t="n">
-        <v>28.1740779876709</v>
+        <v>28.17407989501953</v>
       </c>
       <c r="C201" t="n">
-        <v>28.33502189750872</v>
+        <v>28.33502381575305</v>
       </c>
       <c r="D201" t="n">
-        <v>27.44089058100538</v>
+        <v>27.44089243871817</v>
       </c>
       <c r="E201" t="n">
-        <v>27.67336492794666</v>
+        <v>27.67336680139767</v>
       </c>
       <c r="F201" t="n">
         <v>880600</v>
@@ -4532,16 +4532,16 @@
         <v>44398</v>
       </c>
       <c r="B206" t="n">
-        <v>29.60469245910645</v>
+        <v>29.60468864440918</v>
       </c>
       <c r="C206" t="n">
-        <v>29.7835194288818</v>
+        <v>29.78351559114187</v>
       </c>
       <c r="D206" t="n">
-        <v>29.05927173616996</v>
+        <v>29.0592679917526</v>
       </c>
       <c r="E206" t="n">
-        <v>29.52869210547517</v>
+        <v>29.52868830057088</v>
       </c>
       <c r="F206" t="n">
         <v>1050200</v>
@@ -4552,16 +4552,16 @@
         <v>44399</v>
       </c>
       <c r="B207" t="n">
-        <v>30.17693710327148</v>
+        <v>30.17693328857422</v>
       </c>
       <c r="C207" t="n">
-        <v>30.65082569075749</v>
+        <v>30.65082181615548</v>
       </c>
       <c r="D207" t="n">
-        <v>29.62257654707646</v>
+        <v>29.62257280245648</v>
       </c>
       <c r="E207" t="n">
-        <v>29.69410529101733</v>
+        <v>29.69410153735533</v>
       </c>
       <c r="F207" t="n">
         <v>1168200</v>
@@ -4632,16 +4632,16 @@
         <v>44405</v>
       </c>
       <c r="B211" t="n">
-        <v>29.43927192687988</v>
+        <v>29.43927383422852</v>
       </c>
       <c r="C211" t="n">
-        <v>30.57034745860774</v>
+        <v>30.57034943923792</v>
       </c>
       <c r="D211" t="n">
-        <v>28.7329073919184</v>
+        <v>28.7329092535022</v>
       </c>
       <c r="E211" t="n">
-        <v>29.52868710203713</v>
+        <v>29.52868901517891</v>
       </c>
       <c r="F211" t="n">
         <v>1257400</v>
@@ -4652,16 +4652,16 @@
         <v>44406</v>
       </c>
       <c r="B212" t="n">
-        <v>30.8475284576416</v>
+        <v>30.84753227233887</v>
       </c>
       <c r="C212" t="n">
-        <v>31.51365529103951</v>
+        <v>31.51365918811201</v>
       </c>
       <c r="D212" t="n">
-        <v>29.56444887215321</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="E212" t="n">
-        <v>29.56444887215321</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="F212" t="n">
         <v>1386000</v>
@@ -4672,16 +4672,16 @@
         <v>44407</v>
       </c>
       <c r="B213" t="n">
-        <v>31.13812446594238</v>
+        <v>31.13812828063965</v>
       </c>
       <c r="C213" t="n">
-        <v>31.58071852233474</v>
+        <v>31.58072239125372</v>
       </c>
       <c r="D213" t="n">
-        <v>30.41387685570368</v>
+        <v>30.41388058167417</v>
       </c>
       <c r="E213" t="n">
-        <v>30.80282521486082</v>
+        <v>30.80282898848094</v>
       </c>
       <c r="F213" t="n">
         <v>1548200</v>
@@ -4732,16 +4732,16 @@
         <v>44412</v>
       </c>
       <c r="B216" t="n">
-        <v>29.78798675537109</v>
+        <v>29.78798484802246</v>
       </c>
       <c r="C216" t="n">
-        <v>30.84753370622673</v>
+        <v>30.84753173103446</v>
       </c>
       <c r="D216" t="n">
-        <v>29.7566922923926</v>
+        <v>29.75669038704778</v>
       </c>
       <c r="E216" t="n">
-        <v>30.62400085328306</v>
+        <v>30.62399889240378</v>
       </c>
       <c r="F216" t="n">
         <v>1263400</v>
@@ -4772,16 +4772,16 @@
         <v>44414</v>
       </c>
       <c r="B218" t="n">
-        <v>29.46163177490234</v>
+        <v>29.46162986755371</v>
       </c>
       <c r="C218" t="n">
-        <v>29.99810927720156</v>
+        <v>29.99810733512132</v>
       </c>
       <c r="D218" t="n">
-        <v>29.10397783280902</v>
+        <v>29.10397594861493</v>
       </c>
       <c r="E218" t="n">
-        <v>29.97575803759621</v>
+        <v>29.975756096963</v>
       </c>
       <c r="F218" t="n">
         <v>684400</v>
@@ -4812,16 +4812,16 @@
         <v>44418</v>
       </c>
       <c r="B220" t="n">
-        <v>29.59574699401855</v>
+        <v>29.59574317932129</v>
       </c>
       <c r="C220" t="n">
-        <v>30.78494335377824</v>
+        <v>30.78493938580138</v>
       </c>
       <c r="D220" t="n">
-        <v>29.59574699401855</v>
+        <v>29.59574317932129</v>
       </c>
       <c r="E220" t="n">
-        <v>30.4898783643616</v>
+        <v>30.48987443441668</v>
       </c>
       <c r="F220" t="n">
         <v>1186200</v>
@@ -4832,16 +4832,16 @@
         <v>44419</v>
       </c>
       <c r="B221" t="n">
-        <v>29.1129207611084</v>
+        <v>29.11291885375977</v>
       </c>
       <c r="C221" t="n">
-        <v>30.38258576202377</v>
+        <v>30.38258377149235</v>
       </c>
       <c r="D221" t="n">
-        <v>28.14725717378623</v>
+        <v>28.14725532970356</v>
       </c>
       <c r="E221" t="n">
-        <v>29.68516433396269</v>
+        <v>29.68516238912321</v>
       </c>
       <c r="F221" t="n">
         <v>1237750</v>
@@ -4872,16 +4872,16 @@
         <v>44421</v>
       </c>
       <c r="B223" t="n">
-        <v>28.34396743774414</v>
+        <v>28.34396553039551</v>
       </c>
       <c r="C223" t="n">
-        <v>29.59574941199067</v>
+        <v>29.59574742040596</v>
       </c>
       <c r="D223" t="n">
-        <v>27.18159553808027</v>
+        <v>27.18159370895106</v>
       </c>
       <c r="E223" t="n">
-        <v>29.50633763198762</v>
+        <v>29.50633564641969</v>
       </c>
       <c r="F223" t="n">
         <v>1962050</v>
@@ -4892,16 +4892,16 @@
         <v>44424</v>
       </c>
       <c r="B224" t="n">
-        <v>25.6436882019043</v>
+        <v>25.64369010925293</v>
       </c>
       <c r="C224" t="n">
-        <v>28.14725537891694</v>
+        <v>28.14725747247807</v>
       </c>
       <c r="D224" t="n">
-        <v>24.26672506075316</v>
+        <v>24.26672686568483</v>
       </c>
       <c r="E224" t="n">
-        <v>28.14725537891694</v>
+        <v>28.14725747247807</v>
       </c>
       <c r="F224" t="n">
         <v>6674400</v>
@@ -4972,16 +4972,16 @@
         <v>44428</v>
       </c>
       <c r="B228" t="n">
-        <v>26.64511489868164</v>
+        <v>26.64511299133301</v>
       </c>
       <c r="C228" t="n">
-        <v>26.87758926611801</v>
+        <v>26.87758734212807</v>
       </c>
       <c r="D228" t="n">
-        <v>25.73310217156392</v>
+        <v>25.73310032950029</v>
       </c>
       <c r="E228" t="n">
-        <v>26.34111008783564</v>
+        <v>26.34110820224871</v>
       </c>
       <c r="F228" t="n">
         <v>1186050</v>
@@ -4992,16 +4992,16 @@
         <v>44431</v>
       </c>
       <c r="B229" t="n">
-        <v>26.85970687866211</v>
+        <v>26.85970878601074</v>
       </c>
       <c r="C229" t="n">
-        <v>27.41406736694361</v>
+        <v>27.41406931365822</v>
       </c>
       <c r="D229" t="n">
-        <v>26.28746164845576</v>
+        <v>26.28746351516839</v>
       </c>
       <c r="E229" t="n">
-        <v>26.71664429204535</v>
+        <v>26.71664618923489</v>
       </c>
       <c r="F229" t="n">
         <v>1094150</v>
@@ -5032,16 +5032,16 @@
         <v>44433</v>
       </c>
       <c r="B231" t="n">
-        <v>27.89689636230469</v>
+        <v>27.89690017700195</v>
       </c>
       <c r="C231" t="n">
-        <v>28.41549243173145</v>
+        <v>28.41549631734295</v>
       </c>
       <c r="D231" t="n">
-        <v>27.27100378987718</v>
+        <v>27.27100751898821</v>
       </c>
       <c r="E231" t="n">
-        <v>27.4855950904586</v>
+        <v>27.48559884891342</v>
       </c>
       <c r="F231" t="n">
         <v>1098800</v>
@@ -5072,16 +5072,16 @@
         <v>44435</v>
       </c>
       <c r="B233" t="n">
-        <v>28.96985816955566</v>
+        <v>28.9698600769043</v>
       </c>
       <c r="C233" t="n">
-        <v>29.11291905438238</v>
+        <v>29.11292097115001</v>
       </c>
       <c r="D233" t="n">
-        <v>27.00276844505784</v>
+        <v>27.00277022289511</v>
       </c>
       <c r="E233" t="n">
-        <v>27.44983413649641</v>
+        <v>27.44983594376807</v>
       </c>
       <c r="F233" t="n">
         <v>1634000</v>
@@ -5112,16 +5112,16 @@
         <v>44439</v>
       </c>
       <c r="B235" t="n">
-        <v>26.55570030212402</v>
+        <v>26.55570220947266</v>
       </c>
       <c r="C235" t="n">
-        <v>27.86113118201179</v>
+        <v>27.86113318312228</v>
       </c>
       <c r="D235" t="n">
-        <v>25.87616030921885</v>
+        <v>25.87616216775989</v>
       </c>
       <c r="E235" t="n">
-        <v>27.6823042397767</v>
+        <v>27.68230622804304</v>
       </c>
       <c r="F235" t="n">
         <v>1705500</v>
@@ -5132,16 +5132,16 @@
         <v>44440</v>
       </c>
       <c r="B236" t="n">
-        <v>26.59146499633789</v>
+        <v>26.59146881103516</v>
       </c>
       <c r="C236" t="n">
-        <v>27.25312196212229</v>
+        <v>27.25312587173802</v>
       </c>
       <c r="D236" t="n">
-        <v>25.71521672046829</v>
+        <v>25.71522040946275</v>
       </c>
       <c r="E236" t="n">
-        <v>26.55570063070043</v>
+        <v>26.55570444026709</v>
       </c>
       <c r="F236" t="n">
         <v>1751800</v>
@@ -5152,16 +5152,16 @@
         <v>44441</v>
       </c>
       <c r="B237" t="n">
-        <v>25.35756492614746</v>
+        <v>25.35756683349609</v>
       </c>
       <c r="C237" t="n">
-        <v>26.66299584222149</v>
+        <v>26.6629978477622</v>
       </c>
       <c r="D237" t="n">
-        <v>25.10720754116251</v>
+        <v>25.10720942967972</v>
       </c>
       <c r="E237" t="n">
-        <v>26.59146540442867</v>
+        <v>26.59146740458899</v>
       </c>
       <c r="F237" t="n">
         <v>1706000</v>
@@ -5172,16 +5172,16 @@
         <v>44442</v>
       </c>
       <c r="B238" t="n">
-        <v>25.03567886352539</v>
+        <v>25.03567695617676</v>
       </c>
       <c r="C238" t="n">
-        <v>25.84039677162608</v>
+        <v>25.84039480296984</v>
       </c>
       <c r="D238" t="n">
-        <v>24.80320449799936</v>
+        <v>24.80320260836184</v>
       </c>
       <c r="E238" t="n">
-        <v>25.57215803739928</v>
+        <v>25.57215608917886</v>
       </c>
       <c r="F238" t="n">
         <v>2369000</v>
@@ -5192,16 +5192,16 @@
         <v>44445</v>
       </c>
       <c r="B239" t="n">
-        <v>25.76886749267578</v>
+        <v>25.76886558532715</v>
       </c>
       <c r="C239" t="n">
-        <v>25.89404534691268</v>
+        <v>25.89404343029868</v>
       </c>
       <c r="D239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="E239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="F239" t="n">
         <v>528250</v>
@@ -5232,16 +5232,16 @@
         <v>44448</v>
       </c>
       <c r="B241" t="n">
-        <v>25.03567886352539</v>
+        <v>25.03567695617676</v>
       </c>
       <c r="C241" t="n">
-        <v>25.75098329174372</v>
+        <v>25.75098132989946</v>
       </c>
       <c r="D241" t="n">
-        <v>23.8017782984937</v>
+        <v>23.80177648515005</v>
       </c>
       <c r="E241" t="n">
-        <v>23.99848658989868</v>
+        <v>23.99848476156876</v>
       </c>
       <c r="F241" t="n">
         <v>1540350</v>
@@ -5252,16 +5252,16 @@
         <v>44449</v>
       </c>
       <c r="B242" t="n">
-        <v>25.19662284851074</v>
+        <v>25.19662094116211</v>
       </c>
       <c r="C242" t="n">
-        <v>26.19804905049173</v>
+        <v>26.19804706733655</v>
       </c>
       <c r="D242" t="n">
-        <v>24.64226063620605</v>
+        <v>24.64225877082185</v>
       </c>
       <c r="E242" t="n">
-        <v>26.00134075860054</v>
+        <v>26.0013387903359</v>
       </c>
       <c r="F242" t="n">
         <v>1514650</v>
@@ -5272,16 +5272,16 @@
         <v>44452</v>
       </c>
       <c r="B243" t="n">
-        <v>26.48417091369629</v>
+        <v>26.48417282104492</v>
       </c>
       <c r="C243" t="n">
-        <v>26.82394007087584</v>
+        <v>26.82394200269411</v>
       </c>
       <c r="D243" t="n">
-        <v>25.16085524074708</v>
+        <v>25.16085705279258</v>
       </c>
       <c r="E243" t="n">
-        <v>25.37544655666366</v>
+        <v>25.3754483841637</v>
       </c>
       <c r="F243" t="n">
         <v>1238850</v>
@@ -5372,16 +5372,16 @@
         <v>44459</v>
       </c>
       <c r="B248" t="n">
-        <v>24.17731094360352</v>
+        <v>24.17731285095215</v>
       </c>
       <c r="C248" t="n">
-        <v>24.58861051914021</v>
+        <v>24.58861245893628</v>
       </c>
       <c r="D248" t="n">
-        <v>23.71236226266804</v>
+        <v>23.71236413333686</v>
       </c>
       <c r="E248" t="n">
-        <v>24.3740192138054</v>
+        <v>24.37402113667235</v>
       </c>
       <c r="F248" t="n">
         <v>1148950</v>
@@ -5392,16 +5392,16 @@
         <v>44460</v>
       </c>
       <c r="B249" t="n">
-        <v>25.07144546508789</v>
+        <v>25.07144737243652</v>
       </c>
       <c r="C249" t="n">
-        <v>25.19662331630446</v>
+        <v>25.19662523317619</v>
       </c>
       <c r="D249" t="n">
-        <v>24.05213450165763</v>
+        <v>24.05213633146062</v>
       </c>
       <c r="E249" t="n">
-        <v>24.57073064938097</v>
+        <v>24.57073251863696</v>
       </c>
       <c r="F249" t="n">
         <v>662000</v>
@@ -5412,16 +5412,16 @@
         <v>44461</v>
       </c>
       <c r="B250" t="n">
-        <v>25.48274421691895</v>
+        <v>25.48274612426758</v>
       </c>
       <c r="C250" t="n">
-        <v>26.37687559295119</v>
+        <v>26.37687756722434</v>
       </c>
       <c r="D250" t="n">
-        <v>25.23238681767862</v>
+        <v>25.23238870628835</v>
       </c>
       <c r="E250" t="n">
-        <v>25.92980990493507</v>
+        <v>25.92981184574596</v>
       </c>
       <c r="F250" t="n">
         <v>900000</v>
@@ -5492,16 +5492,16 @@
         <v>44467</v>
       </c>
       <c r="B254" t="n">
-        <v>24.83897018432617</v>
+        <v>24.83896827697754</v>
       </c>
       <c r="C254" t="n">
-        <v>25.80463200005482</v>
+        <v>25.80463001855441</v>
       </c>
       <c r="D254" t="n">
-        <v>24.44555190223813</v>
+        <v>24.44555002509952</v>
       </c>
       <c r="E254" t="n">
-        <v>25.75098288971082</v>
+        <v>25.75098091233005</v>
       </c>
       <c r="F254" t="n">
         <v>1020250</v>
@@ -5512,16 +5512,16 @@
         <v>44468</v>
       </c>
       <c r="B255" t="n">
-        <v>24.67802619934082</v>
+        <v>24.67802810668945</v>
       </c>
       <c r="C255" t="n">
-        <v>25.39333061451349</v>
+        <v>25.39333257714754</v>
       </c>
       <c r="D255" t="n">
-        <v>24.46343487478902</v>
+        <v>24.46343676555203</v>
       </c>
       <c r="E255" t="n">
-        <v>25.10720884844443</v>
+        <v>25.10721078896431</v>
       </c>
       <c r="F255" t="n">
         <v>580300</v>
@@ -5552,16 +5552,16 @@
         <v>44470</v>
       </c>
       <c r="B257" t="n">
-        <v>25.03567886352539</v>
+        <v>25.03567695617676</v>
       </c>
       <c r="C257" t="n">
-        <v>25.10720930634723</v>
+        <v>25.10720739354903</v>
       </c>
       <c r="D257" t="n">
-        <v>24.2309609554247</v>
+        <v>24.23095910938368</v>
       </c>
       <c r="E257" t="n">
-        <v>24.74955709223806</v>
+        <v>24.74955520668767</v>
       </c>
       <c r="F257" t="n">
         <v>904400</v>
@@ -5612,16 +5612,16 @@
         <v>44475</v>
       </c>
       <c r="B260" t="n">
-        <v>23.60506820678711</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="C260" t="n">
-        <v>23.60506820678711</v>
+        <v>23.60506629943848</v>
       </c>
       <c r="D260" t="n">
-        <v>22.37116764671513</v>
+        <v>22.37116583906875</v>
       </c>
       <c r="E260" t="n">
-        <v>22.97917726096693</v>
+        <v>22.97917540419186</v>
       </c>
       <c r="F260" t="n">
         <v>1199850</v>
@@ -5632,16 +5632,16 @@
         <v>44476</v>
       </c>
       <c r="B261" t="n">
-        <v>23.62294960021973</v>
+        <v>23.62295150756836</v>
       </c>
       <c r="C261" t="n">
-        <v>24.26672353823827</v>
+        <v>24.26672549756607</v>
       </c>
       <c r="D261" t="n">
-        <v>23.42624132329132</v>
+        <v>23.42624321475746</v>
       </c>
       <c r="E261" t="n">
-        <v>24.15942873461192</v>
+        <v>24.1594306852766</v>
       </c>
       <c r="F261" t="n">
         <v>699850</v>
@@ -5652,16 +5652,16 @@
         <v>44477</v>
       </c>
       <c r="B262" t="n">
-        <v>24.05213165283203</v>
+        <v>24.05213356018066</v>
       </c>
       <c r="C262" t="n">
-        <v>24.53496337391379</v>
+        <v>24.53496531955127</v>
       </c>
       <c r="D262" t="n">
-        <v>23.69447947356042</v>
+        <v>23.69448135254702</v>
       </c>
       <c r="E262" t="n">
-        <v>23.81965730995046</v>
+        <v>23.81965919886374</v>
       </c>
       <c r="F262" t="n">
         <v>982950</v>
@@ -5672,16 +5672,16 @@
         <v>44480</v>
       </c>
       <c r="B263" t="n">
-        <v>24.08789825439453</v>
+        <v>24.08790016174316</v>
       </c>
       <c r="C263" t="n">
-        <v>24.60649435212385</v>
+        <v>24.60649630053641</v>
       </c>
       <c r="D263" t="n">
-        <v>23.73024606723985</v>
+        <v>23.73024794626857</v>
       </c>
       <c r="E263" t="n">
-        <v>24.03424914725622</v>
+        <v>24.03425105035676</v>
       </c>
       <c r="F263" t="n">
         <v>770500</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35613822937012</v>
+        <v>24.35614013671875</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991219957796</v>
+        <v>24.99991415734105</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848602369909</v>
+        <v>23.99848790303969</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307734710171</v>
+        <v>24.21307924324713</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5712,16 +5712,16 @@
         <v>44483</v>
       </c>
       <c r="B265" t="n">
-        <v>24.37401962280273</v>
+        <v>24.37402153015137</v>
       </c>
       <c r="C265" t="n">
-        <v>24.91049874785196</v>
+        <v>24.91050069718188</v>
       </c>
       <c r="D265" t="n">
-        <v>23.9269539694984</v>
+        <v>23.92695584186265</v>
       </c>
       <c r="E265" t="n">
-        <v>24.51708049542651</v>
+        <v>24.51708241397014</v>
       </c>
       <c r="F265" t="n">
         <v>635500</v>
@@ -5772,16 +5772,16 @@
         <v>44488</v>
       </c>
       <c r="B268" t="n">
-        <v>24.60649681091309</v>
+        <v>24.60649490356445</v>
       </c>
       <c r="C268" t="n">
-        <v>26.46629007537627</v>
+        <v>26.46628802386757</v>
       </c>
       <c r="D268" t="n">
-        <v>24.12366503094249</v>
+        <v>24.12366316102009</v>
       </c>
       <c r="E268" t="n">
-        <v>26.43052400037682</v>
+        <v>26.4305219516405</v>
       </c>
       <c r="F268" t="n">
         <v>1499450</v>
@@ -5832,16 +5832,16 @@
         <v>44491</v>
       </c>
       <c r="B271" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08362007141113</v>
       </c>
       <c r="C271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563458344404</v>
       </c>
       <c r="D271" t="n">
-        <v>19.81395151866856</v>
+        <v>19.81395331115565</v>
       </c>
       <c r="E271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563458344404</v>
       </c>
       <c r="F271" t="n">
         <v>3185950</v>
@@ -5912,16 +5912,16 @@
         <v>44497</v>
       </c>
       <c r="B275" t="n">
-        <v>19.29535484313965</v>
+        <v>19.29535293579102</v>
       </c>
       <c r="C275" t="n">
-        <v>20.76172974015886</v>
+        <v>20.76172768785885</v>
       </c>
       <c r="D275" t="n">
-        <v>19.29535484313965</v>
+        <v>19.29535293579102</v>
       </c>
       <c r="E275" t="n">
-        <v>20.74384840892759</v>
+        <v>20.74384635839516</v>
       </c>
       <c r="F275" t="n">
         <v>1280700</v>
@@ -5932,16 +5932,16 @@
         <v>44498</v>
       </c>
       <c r="B276" t="n">
-        <v>18.3296947479248</v>
+        <v>18.32969284057617</v>
       </c>
       <c r="C276" t="n">
-        <v>20.52925729907399</v>
+        <v>20.52925516284361</v>
       </c>
       <c r="D276" t="n">
-        <v>18.0972203659836</v>
+        <v>18.09721848282576</v>
       </c>
       <c r="E276" t="n">
-        <v>20.2431355075834</v>
+        <v>20.24313340112624</v>
       </c>
       <c r="F276" t="n">
         <v>3577000</v>
@@ -5952,16 +5952,16 @@
         <v>44501</v>
       </c>
       <c r="B277" t="n">
-        <v>18.77676010131836</v>
+        <v>18.77676200866699</v>
       </c>
       <c r="C277" t="n">
-        <v>19.40265278686379</v>
+        <v>19.40265475779077</v>
       </c>
       <c r="D277" t="n">
-        <v>18.68734661689468</v>
+        <v>18.68734851516066</v>
       </c>
       <c r="E277" t="n">
-        <v>18.77676010131836</v>
+        <v>18.77676200866699</v>
       </c>
       <c r="F277" t="n">
         <v>1843300</v>
@@ -5972,16 +5972,16 @@
         <v>44503</v>
       </c>
       <c r="B278" t="n">
-        <v>20.11795425415039</v>
+        <v>20.11795616149902</v>
       </c>
       <c r="C278" t="n">
-        <v>20.36831163215328</v>
+        <v>20.36831356323787</v>
       </c>
       <c r="D278" t="n">
-        <v>18.41910512488394</v>
+        <v>18.41910687116761</v>
       </c>
       <c r="E278" t="n">
-        <v>18.47275252537737</v>
+        <v>18.47275427674726</v>
       </c>
       <c r="F278" t="n">
         <v>1851600</v>
@@ -5992,16 +5992,16 @@
         <v>44504</v>
       </c>
       <c r="B279" t="n">
-        <v>19.97489356994629</v>
+        <v>19.97489547729492</v>
       </c>
       <c r="C279" t="n">
-        <v>21.31609053280524</v>
+        <v>21.31609256822115</v>
       </c>
       <c r="D279" t="n">
-        <v>19.58147531665669</v>
+        <v>19.58147718643888</v>
       </c>
       <c r="E279" t="n">
-        <v>20.04642400641529</v>
+        <v>20.04642592059417</v>
       </c>
       <c r="F279" t="n">
         <v>1953350</v>
@@ -6012,16 +6012,16 @@
         <v>44505</v>
       </c>
       <c r="B280" t="n">
-        <v>20.42196083068848</v>
+        <v>20.42196273803711</v>
       </c>
       <c r="C280" t="n">
-        <v>20.94055696223821</v>
+        <v>20.94055891802213</v>
       </c>
       <c r="D280" t="n">
-        <v>19.99277817811358</v>
+        <v>19.99278004537787</v>
       </c>
       <c r="E280" t="n">
-        <v>20.20736950440103</v>
+        <v>20.20737139170749</v>
       </c>
       <c r="F280" t="n">
         <v>901950</v>
@@ -6032,16 +6032,16 @@
         <v>44508</v>
       </c>
       <c r="B281" t="n">
-        <v>20.13583755493164</v>
+        <v>20.13583946228027</v>
       </c>
       <c r="C281" t="n">
-        <v>20.86902495788224</v>
+        <v>20.86902693468137</v>
       </c>
       <c r="D281" t="n">
-        <v>19.86759713808767</v>
+        <v>19.86759902002748</v>
       </c>
       <c r="E281" t="n">
-        <v>20.86902495788224</v>
+        <v>20.86902693468137</v>
       </c>
       <c r="F281" t="n">
         <v>919700</v>
@@ -6052,16 +6052,16 @@
         <v>44509</v>
       </c>
       <c r="B282" t="n">
-        <v>20.67231750488281</v>
+        <v>20.67232131958008</v>
       </c>
       <c r="C282" t="n">
-        <v>21.36973886447393</v>
+        <v>21.36974280786753</v>
       </c>
       <c r="D282" t="n">
-        <v>20.29678227071059</v>
+        <v>20.29678601610971</v>
       </c>
       <c r="E282" t="n">
-        <v>20.29678227071059</v>
+        <v>20.29678601610971</v>
       </c>
       <c r="F282" t="n">
         <v>912150</v>
@@ -6072,16 +6072,16 @@
         <v>44510</v>
       </c>
       <c r="B283" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08362007141113</v>
       </c>
       <c r="C283" t="n">
-        <v>21.65586170945009</v>
+        <v>21.65586366856726</v>
       </c>
       <c r="D283" t="n">
-        <v>20.49349158152647</v>
+        <v>20.49349343548877</v>
       </c>
       <c r="E283" t="n">
-        <v>20.88690987169059</v>
+        <v>20.88691176124383</v>
       </c>
       <c r="F283" t="n">
         <v>1309800</v>
@@ -6112,16 +6112,16 @@
         <v>44512</v>
       </c>
       <c r="B285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08362007141113</v>
       </c>
       <c r="C285" t="n">
-        <v>22.12081044278765</v>
+        <v>22.12081244396683</v>
       </c>
       <c r="D285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08362007141113</v>
       </c>
       <c r="E285" t="n">
-        <v>21.76315822692041</v>
+        <v>21.76316019574425</v>
       </c>
       <c r="F285" t="n">
         <v>1307150</v>
@@ -6152,16 +6152,16 @@
         <v>44517</v>
       </c>
       <c r="B287" t="n">
-        <v>19.99277687072754</v>
+        <v>19.99277877807617</v>
       </c>
       <c r="C287" t="n">
-        <v>20.92267255716455</v>
+        <v>20.92267455322699</v>
       </c>
       <c r="D287" t="n">
-        <v>19.59935861221719</v>
+        <v>19.59936048203298</v>
       </c>
       <c r="E287" t="n">
-        <v>20.40407645952734</v>
+        <v>20.40407840611472</v>
       </c>
       <c r="F287" t="n">
         <v>1179650</v>
@@ -6192,16 +6192,16 @@
         <v>44519</v>
       </c>
       <c r="B289" t="n">
-        <v>20.99420738220215</v>
+        <v>20.99420356750488</v>
       </c>
       <c r="C289" t="n">
-        <v>21.24456481819871</v>
+        <v>21.24456095801091</v>
       </c>
       <c r="D289" t="n">
-        <v>20.11795891434494</v>
+        <v>20.11795525886409</v>
       </c>
       <c r="E289" t="n">
-        <v>20.31466723200048</v>
+        <v>20.31466354077727</v>
       </c>
       <c r="F289" t="n">
         <v>767750</v>
@@ -6252,16 +6252,16 @@
         <v>44524</v>
       </c>
       <c r="B292" t="n">
-        <v>19.58147621154785</v>
+        <v>19.58147811889648</v>
       </c>
       <c r="C292" t="n">
-        <v>20.33254668150708</v>
+        <v>20.3325486620143</v>
       </c>
       <c r="D292" t="n">
-        <v>19.02711572993332</v>
+        <v>19.02711758328404</v>
       </c>
       <c r="E292" t="n">
-        <v>19.04499706080266</v>
+        <v>19.04499891589514</v>
       </c>
       <c r="F292" t="n">
         <v>1594900</v>
@@ -6312,16 +6312,16 @@
         <v>44529</v>
       </c>
       <c r="B295" t="n">
-        <v>19.20594215393066</v>
+        <v>19.20594024658203</v>
       </c>
       <c r="C295" t="n">
-        <v>20.33254792793267</v>
+        <v>20.33254590870044</v>
       </c>
       <c r="D295" t="n">
-        <v>19.06288126568472</v>
+        <v>19.06287937254352</v>
       </c>
       <c r="E295" t="n">
-        <v>20.33254792793267</v>
+        <v>20.33254590870044</v>
       </c>
       <c r="F295" t="n">
         <v>830750</v>
@@ -6332,16 +6332,16 @@
         <v>44530</v>
       </c>
       <c r="B296" t="n">
-        <v>18.83040618896484</v>
+        <v>18.83040428161621</v>
       </c>
       <c r="C296" t="n">
-        <v>19.25959054300976</v>
+        <v>19.25958859218866</v>
       </c>
       <c r="D296" t="n">
-        <v>18.06145436986738</v>
+        <v>18.06145254040656</v>
       </c>
       <c r="E296" t="n">
-        <v>19.04499751327718</v>
+        <v>19.0449955841924</v>
       </c>
       <c r="F296" t="n">
         <v>1327800</v>
@@ -6412,16 +6412,16 @@
         <v>44536</v>
       </c>
       <c r="B300" t="n">
-        <v>19.97489356994629</v>
+        <v>19.97489547729492</v>
       </c>
       <c r="C300" t="n">
-        <v>20.38619315328804</v>
+        <v>20.38619509991056</v>
       </c>
       <c r="D300" t="n">
-        <v>19.56359228118441</v>
+        <v>19.56359414925899</v>
       </c>
       <c r="E300" t="n">
-        <v>20.08218837193973</v>
+        <v>20.08219028953366</v>
       </c>
       <c r="F300" t="n">
         <v>963750</v>
@@ -6472,16 +6472,16 @@
         <v>44539</v>
       </c>
       <c r="B303" t="n">
-        <v>20.90479278564453</v>
+        <v>20.9047908782959</v>
       </c>
       <c r="C303" t="n">
-        <v>21.36974155417278</v>
+        <v>21.36973960440232</v>
       </c>
       <c r="D303" t="n">
-        <v>20.72596751688626</v>
+        <v>20.72596562585361</v>
       </c>
       <c r="E303" t="n">
-        <v>21.24456369549995</v>
+        <v>21.24456175715069</v>
       </c>
       <c r="F303" t="n">
         <v>669550</v>
@@ -6492,16 +6492,16 @@
         <v>44540</v>
       </c>
       <c r="B304" t="n">
-        <v>21.81680679321289</v>
+        <v>21.81680488586426</v>
       </c>
       <c r="C304" t="n">
-        <v>22.19234206620039</v>
+        <v>22.19234012602034</v>
       </c>
       <c r="D304" t="n">
-        <v>21.06573624723789</v>
+        <v>21.06573440555209</v>
       </c>
       <c r="E304" t="n">
-        <v>22.13869465732228</v>
+        <v>22.1386927218324</v>
       </c>
       <c r="F304" t="n">
         <v>899500</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78104019165039</v>
+        <v>21.78104209899902</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422762443386</v>
+        <v>22.51422959598714</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550495712469</v>
+        <v>21.40550683158799</v>
       </c>
       <c r="E305" t="n">
-        <v>22.13869238990815</v>
+        <v>22.13869432857611</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6532,16 +6532,16 @@
         <v>44544</v>
       </c>
       <c r="B306" t="n">
-        <v>21.49492073059082</v>
+        <v>21.49491882324219</v>
       </c>
       <c r="C306" t="n">
-        <v>22.06716430896915</v>
+        <v>22.06716235084257</v>
       </c>
       <c r="D306" t="n">
-        <v>21.22668027416069</v>
+        <v>21.22667839061434</v>
       </c>
       <c r="E306" t="n">
-        <v>21.95986778531302</v>
+        <v>21.95986583670738</v>
       </c>
       <c r="F306" t="n">
         <v>979700</v>
@@ -6592,16 +6592,16 @@
         <v>44547</v>
       </c>
       <c r="B309" t="n">
-        <v>22.37116813659668</v>
+        <v>22.37116622924805</v>
       </c>
       <c r="C309" t="n">
-        <v>22.72882035710008</v>
+        <v>22.72881841925829</v>
       </c>
       <c r="D309" t="n">
-        <v>21.42338762048728</v>
+        <v>21.42338579394568</v>
       </c>
       <c r="E309" t="n">
-        <v>21.56645021410895</v>
+        <v>21.56644837536995</v>
       </c>
       <c r="F309" t="n">
         <v>2194100</v>
@@ -6632,16 +6632,16 @@
         <v>44551</v>
       </c>
       <c r="B311" t="n">
-        <v>21.38762283325195</v>
+        <v>21.38762474060059</v>
       </c>
       <c r="C311" t="n">
-        <v>22.19234074001621</v>
+        <v>22.1923427191296</v>
       </c>
       <c r="D311" t="n">
-        <v>21.38762283325195</v>
+        <v>21.38762474060059</v>
       </c>
       <c r="E311" t="n">
-        <v>22.0313968175793</v>
+        <v>22.03139878233971</v>
       </c>
       <c r="F311" t="n">
         <v>785250</v>
@@ -6672,16 +6672,16 @@
         <v>44553</v>
       </c>
       <c r="B313" t="n">
-        <v>21.17615127563477</v>
+        <v>21.17614936828613</v>
       </c>
       <c r="C313" t="n">
-        <v>21.69924183626969</v>
+        <v>21.69923988180597</v>
       </c>
       <c r="D313" t="n">
-        <v>20.79736144067842</v>
+        <v>20.79735956744761</v>
       </c>
       <c r="E313" t="n">
-        <v>21.69924183626969</v>
+        <v>21.69923988180597</v>
       </c>
       <c r="F313" t="n">
         <v>605250</v>
@@ -6752,16 +6752,16 @@
         <v>44560</v>
       </c>
       <c r="B317" t="n">
-        <v>21.06792640686035</v>
+        <v>21.06792831420898</v>
       </c>
       <c r="C317" t="n">
-        <v>21.15811306946891</v>
+        <v>21.15811498498244</v>
       </c>
       <c r="D317" t="n">
-        <v>19.93155691194919</v>
+        <v>19.93155871641855</v>
       </c>
       <c r="E317" t="n">
-        <v>20.2923087229844</v>
+        <v>20.29231056011382</v>
       </c>
       <c r="F317" t="n">
         <v>1399700</v>
@@ -6852,16 +6852,16 @@
         <v>44568</v>
       </c>
       <c r="B322" t="n">
-        <v>17.28003120422363</v>
+        <v>17.280029296875</v>
       </c>
       <c r="C322" t="n">
-        <v>17.53255837755198</v>
+        <v>17.5325564423297</v>
       </c>
       <c r="D322" t="n">
-        <v>16.90124130433144</v>
+        <v>16.90123943879317</v>
       </c>
       <c r="E322" t="n">
-        <v>17.47844430599549</v>
+        <v>17.47844237674627</v>
       </c>
       <c r="F322" t="n">
         <v>932550</v>
@@ -6872,16 +6872,16 @@
         <v>44571</v>
       </c>
       <c r="B323" t="n">
-        <v>16.3601131439209</v>
+        <v>16.36011123657227</v>
       </c>
       <c r="C323" t="n">
-        <v>17.13573099191385</v>
+        <v>17.13572899413958</v>
       </c>
       <c r="D323" t="n">
-        <v>16.10758768286324</v>
+        <v>16.10758580495536</v>
       </c>
       <c r="E323" t="n">
-        <v>17.11769296749525</v>
+        <v>17.11769097182395</v>
       </c>
       <c r="F323" t="n">
         <v>1820150</v>
@@ -6932,16 +6932,16 @@
         <v>44574</v>
       </c>
       <c r="B326" t="n">
-        <v>16.64871215820312</v>
+        <v>16.64871025085449</v>
       </c>
       <c r="C326" t="n">
-        <v>17.62274468839355</v>
+        <v>17.62274266945553</v>
       </c>
       <c r="D326" t="n">
-        <v>16.57656179154462</v>
+        <v>16.57655989246185</v>
       </c>
       <c r="E326" t="n">
-        <v>17.58666864496408</v>
+        <v>17.58666663015909</v>
       </c>
       <c r="F326" t="n">
         <v>921200</v>
@@ -6972,16 +6972,16 @@
         <v>44578</v>
       </c>
       <c r="B328" t="n">
-        <v>16.88320350646973</v>
+        <v>16.88320159912109</v>
       </c>
       <c r="C328" t="n">
-        <v>17.11769265908467</v>
+        <v>17.11769072524505</v>
       </c>
       <c r="D328" t="n">
-        <v>16.63067804996184</v>
+        <v>16.6306761711418</v>
       </c>
       <c r="E328" t="n">
-        <v>16.86516720257677</v>
+        <v>16.86516529726576</v>
       </c>
       <c r="F328" t="n">
         <v>496050</v>
@@ -7012,16 +7012,16 @@
         <v>44580</v>
       </c>
       <c r="B330" t="n">
-        <v>16.41422271728516</v>
+        <v>16.41422462463379</v>
       </c>
       <c r="C330" t="n">
-        <v>16.72086216753467</v>
+        <v>16.72086411051511</v>
       </c>
       <c r="D330" t="n">
-        <v>16.19776992400296</v>
+        <v>16.19777180619957</v>
       </c>
       <c r="E330" t="n">
-        <v>16.41422271728516</v>
+        <v>16.41422462463379</v>
       </c>
       <c r="F330" t="n">
         <v>847250</v>
@@ -7072,16 +7072,16 @@
         <v>44585</v>
       </c>
       <c r="B333" t="n">
-        <v>17.85723304748535</v>
+        <v>17.85723114013672</v>
       </c>
       <c r="C333" t="n">
-        <v>18.09172218175017</v>
+        <v>18.09172024935553</v>
       </c>
       <c r="D333" t="n">
-        <v>17.47844317216533</v>
+        <v>17.47844130527562</v>
       </c>
       <c r="E333" t="n">
-        <v>18.09172218175017</v>
+        <v>18.09172024935553</v>
       </c>
       <c r="F333" t="n">
         <v>692150</v>
@@ -7132,16 +7132,16 @@
         <v>44588</v>
       </c>
       <c r="B336" t="n">
-        <v>19.3363151550293</v>
+        <v>19.33631706237793</v>
       </c>
       <c r="C336" t="n">
-        <v>19.91351802765098</v>
+        <v>19.91351999193534</v>
       </c>
       <c r="D336" t="n">
-        <v>19.08378803815718</v>
+        <v>19.08378992059635</v>
       </c>
       <c r="E336" t="n">
-        <v>19.64295461115963</v>
+        <v>19.64295654875541</v>
       </c>
       <c r="F336" t="n">
         <v>815000</v>
@@ -7152,16 +7152,16 @@
         <v>44589</v>
       </c>
       <c r="B337" t="n">
-        <v>19.67903137207031</v>
+        <v>19.67902946472168</v>
       </c>
       <c r="C337" t="n">
-        <v>19.67903137207031</v>
+        <v>19.67902946472168</v>
       </c>
       <c r="D337" t="n">
-        <v>18.84930127963634</v>
+        <v>18.84929945270756</v>
       </c>
       <c r="E337" t="n">
-        <v>19.30024150986784</v>
+        <v>19.30023963923261</v>
       </c>
       <c r="F337" t="n">
         <v>645650</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96763229370117</v>
+        <v>19.96763038635254</v>
       </c>
       <c r="C338" t="n">
-        <v>20.27427177942092</v>
+        <v>20.27426984278146</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44454170986168</v>
+        <v>19.44453985247972</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706885110159</v>
+        <v>19.69706696959773</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7512,16 +7512,16 @@
         <v>44615</v>
       </c>
       <c r="B355" t="n">
-        <v>19.66099166870117</v>
+        <v>19.66098976135254</v>
       </c>
       <c r="C355" t="n">
-        <v>20.49072169018069</v>
+        <v>20.49071970233843</v>
       </c>
       <c r="D355" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276508916316</v>
       </c>
       <c r="E355" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940452736665</v>
       </c>
       <c r="F355" t="n">
         <v>1327750</v>
@@ -7532,16 +7532,16 @@
         <v>44616</v>
       </c>
       <c r="B356" t="n">
-        <v>19.3363151550293</v>
+        <v>19.33631706237793</v>
       </c>
       <c r="C356" t="n">
-        <v>19.4265035339265</v>
+        <v>19.42650545017138</v>
       </c>
       <c r="D356" t="n">
-        <v>18.27209606848287</v>
+        <v>18.27209787085614</v>
       </c>
       <c r="E356" t="n">
-        <v>18.52462318535499</v>
+        <v>18.52462501263771</v>
       </c>
       <c r="F356" t="n">
         <v>1831750</v>
@@ -7552,16 +7552,16 @@
         <v>44617</v>
       </c>
       <c r="B357" t="n">
-        <v>19.02967643737793</v>
+        <v>19.02967834472656</v>
       </c>
       <c r="C357" t="n">
-        <v>19.62491735291844</v>
+        <v>19.62491931992821</v>
       </c>
       <c r="D357" t="n">
-        <v>18.6508866074703</v>
+        <v>18.65088847685275</v>
       </c>
       <c r="E357" t="n">
-        <v>19.28220184384947</v>
+        <v>19.28220377650878</v>
       </c>
       <c r="F357" t="n">
         <v>1262850</v>
@@ -7612,16 +7612,16 @@
         <v>44624</v>
       </c>
       <c r="B360" t="n">
-        <v>17.91134262084961</v>
+        <v>17.91134452819824</v>
       </c>
       <c r="C360" t="n">
-        <v>18.75910883175985</v>
+        <v>18.75911082938567</v>
       </c>
       <c r="D360" t="n">
-        <v>17.55058913853877</v>
+        <v>17.55059100747137</v>
       </c>
       <c r="E360" t="n">
-        <v>18.57873381080452</v>
+        <v>18.57873578922251</v>
       </c>
       <c r="F360" t="n">
         <v>1669200</v>
@@ -7652,16 +7652,16 @@
         <v>44628</v>
       </c>
       <c r="B362" t="n">
-        <v>17.38825225830078</v>
+        <v>17.38825416564941</v>
       </c>
       <c r="C362" t="n">
-        <v>17.58666529881019</v>
+        <v>17.58666722792311</v>
       </c>
       <c r="D362" t="n">
-        <v>16.54048432121493</v>
+        <v>16.54048613557037</v>
       </c>
       <c r="E362" t="n">
-        <v>16.84712375122045</v>
+        <v>16.84712559921172</v>
       </c>
       <c r="F362" t="n">
         <v>1040800</v>
@@ -7672,16 +7672,16 @@
         <v>44629</v>
       </c>
       <c r="B363" t="n">
-        <v>18.23601913452148</v>
+        <v>18.23602104187012</v>
       </c>
       <c r="C363" t="n">
-        <v>18.36228354686547</v>
+        <v>18.36228546742039</v>
       </c>
       <c r="D363" t="n">
-        <v>17.51451557912802</v>
+        <v>17.51451741101287</v>
       </c>
       <c r="E363" t="n">
-        <v>17.5325535980629</v>
+        <v>17.53255543183439</v>
       </c>
       <c r="F363" t="n">
         <v>713800</v>
@@ -7712,16 +7712,16 @@
         <v>44631</v>
       </c>
       <c r="B365" t="n">
-        <v>17.22591590881348</v>
+        <v>17.22591781616211</v>
       </c>
       <c r="C365" t="n">
-        <v>18.4524720777208</v>
+        <v>18.45247412088051</v>
       </c>
       <c r="D365" t="n">
-        <v>17.02750112075174</v>
+        <v>17.02750300613079</v>
       </c>
       <c r="E365" t="n">
-        <v>18.30817135196699</v>
+        <v>18.30817337914893</v>
       </c>
       <c r="F365" t="n">
         <v>837400</v>
@@ -7732,16 +7732,16 @@
         <v>44634</v>
       </c>
       <c r="B366" t="n">
-        <v>17.31610107421875</v>
+        <v>17.31610298156738</v>
       </c>
       <c r="C366" t="n">
-        <v>17.67685282155664</v>
+        <v>17.67685476864166</v>
       </c>
       <c r="D366" t="n">
-        <v>16.88319725721326</v>
+        <v>16.88319911687804</v>
       </c>
       <c r="E366" t="n">
-        <v>17.35217538885253</v>
+        <v>17.35217730017471</v>
       </c>
       <c r="F366" t="n">
         <v>989600</v>
@@ -7792,16 +7792,16 @@
         <v>44637</v>
       </c>
       <c r="B369" t="n">
-        <v>18.16387176513672</v>
+        <v>18.16386985778809</v>
       </c>
       <c r="C369" t="n">
-        <v>18.30817249993856</v>
+        <v>18.30817057743722</v>
       </c>
       <c r="D369" t="n">
-        <v>17.17180464342414</v>
+        <v>17.17180284025032</v>
       </c>
       <c r="E369" t="n">
-        <v>17.56863080402899</v>
+        <v>17.56862895918532</v>
       </c>
       <c r="F369" t="n">
         <v>935650</v>
@@ -7832,16 +7832,16 @@
         <v>44641</v>
       </c>
       <c r="B371" t="n">
-        <v>18.56069946289062</v>
+        <v>18.56069755554199</v>
       </c>
       <c r="C371" t="n">
-        <v>18.86733895137048</v>
+        <v>18.86733701251073</v>
       </c>
       <c r="D371" t="n">
-        <v>18.23602195268832</v>
+        <v>18.23602007870444</v>
       </c>
       <c r="E371" t="n">
-        <v>18.65088785130242</v>
+        <v>18.65088593468579</v>
       </c>
       <c r="F371" t="n">
         <v>689900</v>
@@ -7892,16 +7892,16 @@
         <v>44644</v>
       </c>
       <c r="B374" t="n">
-        <v>20.79736328125</v>
+        <v>20.79736137390137</v>
       </c>
       <c r="C374" t="n">
-        <v>20.79736328125</v>
+        <v>20.79736137390137</v>
       </c>
       <c r="D374" t="n">
-        <v>19.49865663520698</v>
+        <v>19.49865484696414</v>
       </c>
       <c r="E374" t="n">
-        <v>19.71510774288082</v>
+        <v>19.71510593478701</v>
       </c>
       <c r="F374" t="n">
         <v>1624000</v>
@@ -7912,16 +7912,16 @@
         <v>44645</v>
       </c>
       <c r="B375" t="n">
-        <v>21.19418907165527</v>
+        <v>21.19418716430664</v>
       </c>
       <c r="C375" t="n">
-        <v>21.4467161990152</v>
+        <v>21.44671426894065</v>
       </c>
       <c r="D375" t="n">
-        <v>20.81539924071555</v>
+        <v>20.81539736745571</v>
       </c>
       <c r="E375" t="n">
-        <v>20.92362564392704</v>
+        <v>20.92362376092747</v>
       </c>
       <c r="F375" t="n">
         <v>911550</v>
@@ -7952,16 +7952,16 @@
         <v>44649</v>
       </c>
       <c r="B377" t="n">
-        <v>21.91569519042969</v>
+        <v>21.91569328308105</v>
       </c>
       <c r="C377" t="n">
-        <v>22.36663543484347</v>
+        <v>22.36663348824898</v>
       </c>
       <c r="D377" t="n">
-        <v>21.6631697544863</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="E377" t="n">
-        <v>21.6631697544863</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="F377" t="n">
         <v>1103500</v>
@@ -7992,16 +7992,16 @@
         <v>44651</v>
       </c>
       <c r="B379" t="n">
-        <v>21.17615127563477</v>
+        <v>21.17614936828613</v>
       </c>
       <c r="C379" t="n">
-        <v>21.77139219910897</v>
+        <v>21.77139023814663</v>
       </c>
       <c r="D379" t="n">
-        <v>21.0498885707161</v>
+        <v>21.04988667474002</v>
       </c>
       <c r="E379" t="n">
-        <v>21.60905345267049</v>
+        <v>21.6090515063301</v>
       </c>
       <c r="F379" t="n">
         <v>849150</v>
@@ -8072,16 +8072,16 @@
         <v>44657</v>
       </c>
       <c r="B383" t="n">
-        <v>20.02174377441406</v>
+        <v>20.0217456817627</v>
       </c>
       <c r="C383" t="n">
-        <v>20.58090860900858</v>
+        <v>20.58091056962541</v>
       </c>
       <c r="D383" t="n">
-        <v>19.58883991384388</v>
+        <v>19.58884177995242</v>
       </c>
       <c r="E383" t="n">
-        <v>20.58090860900858</v>
+        <v>20.58091056962541</v>
       </c>
       <c r="F383" t="n">
         <v>1237700</v>
@@ -8092,16 +8092,16 @@
         <v>44658</v>
       </c>
       <c r="B384" t="n">
-        <v>19.66099166870117</v>
+        <v>19.66098976135254</v>
       </c>
       <c r="C384" t="n">
-        <v>20.00370717768201</v>
+        <v>20.00370523708592</v>
       </c>
       <c r="D384" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276508916316</v>
       </c>
       <c r="E384" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940452736665</v>
       </c>
       <c r="F384" t="n">
         <v>978600</v>
@@ -8132,16 +8132,16 @@
         <v>44662</v>
       </c>
       <c r="B386" t="n">
-        <v>18.93948745727539</v>
+        <v>18.93948936462402</v>
       </c>
       <c r="C386" t="n">
-        <v>19.37238961487934</v>
+        <v>19.37239156582447</v>
       </c>
       <c r="D386" t="n">
-        <v>18.86733709767473</v>
+        <v>18.86733899775728</v>
       </c>
       <c r="E386" t="n">
-        <v>19.24612691562825</v>
+        <v>19.24612885385778</v>
       </c>
       <c r="F386" t="n">
         <v>1033000</v>
@@ -8212,16 +8212,16 @@
         <v>44669</v>
       </c>
       <c r="B390" t="n">
-        <v>19.55276679992676</v>
+        <v>19.55276870727539</v>
       </c>
       <c r="C390" t="n">
-        <v>20.0037069873044</v>
+        <v>20.0037089386417</v>
       </c>
       <c r="D390" t="n">
-        <v>19.49865445909752</v>
+        <v>19.49865636116756</v>
       </c>
       <c r="E390" t="n">
-        <v>19.6790295019284</v>
+        <v>19.67903142159381</v>
       </c>
       <c r="F390" t="n">
         <v>1023750</v>
@@ -8272,16 +8272,16 @@
         <v>44673</v>
       </c>
       <c r="B393" t="n">
-        <v>19.55276679992676</v>
+        <v>19.55276870727539</v>
       </c>
       <c r="C393" t="n">
-        <v>20.4907214951681</v>
+        <v>20.49072349401308</v>
       </c>
       <c r="D393" t="n">
-        <v>19.3543520165524</v>
+        <v>19.35435390454591</v>
       </c>
       <c r="E393" t="n">
-        <v>20.09389536881999</v>
+        <v>20.09389732895506</v>
       </c>
       <c r="F393" t="n">
         <v>931750</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.5190315246582</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C403" t="n">
-        <v>19.9347326068735</v>
+        <v>19.93473455484336</v>
       </c>
       <c r="D403" t="n">
-        <v>18.81989895121317</v>
+        <v>18.8199007902444</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019522691586</v>
+        <v>19.67019714903581</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8532,16 +8532,16 @@
         <v>44692</v>
       </c>
       <c r="B406" t="n">
-        <v>19.10333061218262</v>
+        <v>19.10333251953125</v>
       </c>
       <c r="C406" t="n">
-        <v>19.57571763643849</v>
+        <v>19.57571959095203</v>
       </c>
       <c r="D406" t="n">
-        <v>18.93327279714184</v>
+        <v>18.93327468751125</v>
       </c>
       <c r="E406" t="n">
-        <v>19.14112243908956</v>
+        <v>19.14112435021147</v>
       </c>
       <c r="F406" t="n">
         <v>1048200</v>
@@ -8552,16 +8552,16 @@
         <v>44693</v>
       </c>
       <c r="B407" t="n">
-        <v>19.330078125</v>
+        <v>19.33007621765137</v>
       </c>
       <c r="C407" t="n">
-        <v>19.70798922428379</v>
+        <v>19.7079872796457</v>
       </c>
       <c r="D407" t="n">
-        <v>18.81990102418875</v>
+        <v>18.81989916718061</v>
       </c>
       <c r="E407" t="n">
-        <v>18.93327471437663</v>
+        <v>18.93327284618161</v>
       </c>
       <c r="F407" t="n">
         <v>1412250</v>
@@ -8672,16 +8672,16 @@
         <v>44701</v>
       </c>
       <c r="B413" t="n">
-        <v>20.65275955200195</v>
+        <v>20.65276145935059</v>
       </c>
       <c r="C413" t="n">
-        <v>21.08735471304948</v>
+        <v>21.08735666053437</v>
       </c>
       <c r="D413" t="n">
-        <v>20.25595441269131</v>
+        <v>20.25595628339371</v>
       </c>
       <c r="E413" t="n">
-        <v>21.03066877943749</v>
+        <v>21.03067072168725</v>
       </c>
       <c r="F413" t="n">
         <v>1756800</v>
@@ -8852,16 +8852,16 @@
         <v>44714</v>
       </c>
       <c r="B422" t="n">
-        <v>23.37371063232422</v>
+        <v>23.37370872497559</v>
       </c>
       <c r="C422" t="n">
-        <v>24.31848471674483</v>
+        <v>24.31848273230045</v>
       </c>
       <c r="D422" t="n">
-        <v>23.24144283714967</v>
+        <v>23.24144094059439</v>
       </c>
       <c r="E422" t="n">
-        <v>23.43039657282566</v>
+        <v>23.43039466085132</v>
       </c>
       <c r="F422" t="n">
         <v>1968350</v>
@@ -9012,16 +9012,16 @@
         <v>44726</v>
       </c>
       <c r="B430" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C430" t="n">
-        <v>19.51903189147468</v>
+        <v>19.51902994454667</v>
       </c>
       <c r="D430" t="n">
-        <v>18.89548115744023</v>
+        <v>18.89547927270836</v>
       </c>
       <c r="E430" t="n">
-        <v>19.51903189147468</v>
+        <v>19.51902994454667</v>
       </c>
       <c r="F430" t="n">
         <v>1027150</v>
@@ -9032,16 +9032,16 @@
         <v>44727</v>
       </c>
       <c r="B431" t="n">
-        <v>19.65130233764648</v>
+        <v>19.65130043029785</v>
       </c>
       <c r="C431" t="n">
-        <v>19.82136197935914</v>
+        <v>19.82136005550457</v>
       </c>
       <c r="D431" t="n">
-        <v>19.17891524489523</v>
+        <v>19.17891338339633</v>
       </c>
       <c r="E431" t="n">
-        <v>19.44345266556088</v>
+        <v>19.44345077838607</v>
       </c>
       <c r="F431" t="n">
         <v>990050</v>
@@ -9152,16 +9152,16 @@
         <v>44736</v>
       </c>
       <c r="B437" t="n">
-        <v>18.47978210449219</v>
+        <v>18.47978019714355</v>
       </c>
       <c r="C437" t="n">
-        <v>18.95216918550078</v>
+        <v>18.95216722939579</v>
       </c>
       <c r="D437" t="n">
-        <v>18.23414060612608</v>
+        <v>18.23413872413077</v>
       </c>
       <c r="E437" t="n">
-        <v>18.95216918550078</v>
+        <v>18.95216722939579</v>
       </c>
       <c r="F437" t="n">
         <v>1255000</v>
@@ -9192,16 +9192,16 @@
         <v>44740</v>
       </c>
       <c r="B439" t="n">
-        <v>18.04518508911133</v>
+        <v>18.04518699645996</v>
       </c>
       <c r="C439" t="n">
-        <v>18.7254217704739</v>
+        <v>18.72542374972252</v>
       </c>
       <c r="D439" t="n">
-        <v>17.8751254682673</v>
+        <v>17.87512735764089</v>
       </c>
       <c r="E439" t="n">
-        <v>18.70652585659934</v>
+        <v>18.70652783385068</v>
       </c>
       <c r="F439" t="n">
         <v>1533000</v>
@@ -9232,16 +9232,16 @@
         <v>44742</v>
       </c>
       <c r="B441" t="n">
-        <v>17.53500556945801</v>
+        <v>17.53500366210938</v>
       </c>
       <c r="C441" t="n">
-        <v>17.74285701026197</v>
+        <v>17.74285508030455</v>
       </c>
       <c r="D441" t="n">
-        <v>17.30826001750107</v>
+        <v>17.3082581348164</v>
       </c>
       <c r="E441" t="n">
-        <v>17.55390148262445</v>
+        <v>17.55389957322044</v>
       </c>
       <c r="F441" t="n">
         <v>1152750</v>
@@ -9252,16 +9252,16 @@
         <v>44743</v>
       </c>
       <c r="B442" t="n">
-        <v>17.5916919708252</v>
+        <v>17.59169387817383</v>
       </c>
       <c r="C442" t="n">
-        <v>17.72395974890228</v>
+        <v>17.72396167059182</v>
       </c>
       <c r="D442" t="n">
-        <v>17.06261725449021</v>
+        <v>17.06261910447483</v>
       </c>
       <c r="E442" t="n">
-        <v>17.25157276775461</v>
+        <v>17.2515746382264</v>
       </c>
       <c r="F442" t="n">
         <v>2016600</v>
@@ -9292,16 +9292,16 @@
         <v>44747</v>
       </c>
       <c r="B444" t="n">
-        <v>17.10041046142578</v>
+        <v>17.10040855407715</v>
       </c>
       <c r="C444" t="n">
-        <v>17.25157416346159</v>
+        <v>17.25157223925244</v>
       </c>
       <c r="D444" t="n">
-        <v>16.57133750430044</v>
+        <v>16.57133565596364</v>
       </c>
       <c r="E444" t="n">
-        <v>17.15709639918584</v>
+        <v>17.15709448551456</v>
       </c>
       <c r="F444" t="n">
         <v>2077700</v>
@@ -9312,16 +9312,16 @@
         <v>44748</v>
       </c>
       <c r="B445" t="n">
-        <v>17.23267936706543</v>
+        <v>17.2326774597168</v>
       </c>
       <c r="C445" t="n">
-        <v>17.47832084929718</v>
+        <v>17.47831891476044</v>
       </c>
       <c r="D445" t="n">
-        <v>16.83587417300084</v>
+        <v>16.83587230957143</v>
       </c>
       <c r="E445" t="n">
-        <v>17.19488934011402</v>
+        <v>17.19488743694806</v>
       </c>
       <c r="F445" t="n">
         <v>1639900</v>
@@ -9372,16 +9372,16 @@
         <v>44753</v>
       </c>
       <c r="B448" t="n">
-        <v>16.76029205322266</v>
+        <v>16.76029396057129</v>
       </c>
       <c r="C448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61059037351305</v>
       </c>
       <c r="D448" t="n">
-        <v>16.62802425795465</v>
+        <v>16.62802615025099</v>
       </c>
       <c r="E448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61059037351305</v>
       </c>
       <c r="F448" t="n">
         <v>1587350</v>
@@ -9412,16 +9412,16 @@
         <v>44755</v>
       </c>
       <c r="B450" t="n">
-        <v>16.87366485595703</v>
+        <v>16.87366676330566</v>
       </c>
       <c r="C450" t="n">
-        <v>17.02482855752328</v>
+        <v>17.024830481959</v>
       </c>
       <c r="D450" t="n">
-        <v>16.3445900984617</v>
+        <v>16.3445919460053</v>
       </c>
       <c r="E450" t="n">
-        <v>16.51464971322709</v>
+        <v>16.51465157999372</v>
       </c>
       <c r="F450" t="n">
         <v>919750</v>
@@ -9552,16 +9552,16 @@
         <v>44764</v>
       </c>
       <c r="B457" t="n">
-        <v>18.04518508911133</v>
+        <v>18.04518699645996</v>
       </c>
       <c r="C457" t="n">
-        <v>18.23413882181639</v>
+        <v>18.23414074913714</v>
       </c>
       <c r="D457" t="n">
-        <v>17.76175178703344</v>
+        <v>17.7617536644236</v>
       </c>
       <c r="E457" t="n">
-        <v>18.12076694259606</v>
+        <v>18.12076885793358</v>
       </c>
       <c r="F457" t="n">
         <v>543750</v>
@@ -9572,16 +9572,16 @@
         <v>44767</v>
       </c>
       <c r="B458" t="n">
-        <v>17.95070838928223</v>
+        <v>17.95070648193359</v>
       </c>
       <c r="C458" t="n">
-        <v>18.30972176418187</v>
+        <v>18.30971981868635</v>
       </c>
       <c r="D458" t="n">
-        <v>17.87512653130264</v>
+        <v>17.87512463198494</v>
       </c>
       <c r="E458" t="n">
-        <v>18.177453963221</v>
+        <v>18.17745203177956</v>
       </c>
       <c r="F458" t="n">
         <v>615900</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.5190315246582</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65129931363029</v>
+        <v>19.65130123390378</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431710008434</v>
+        <v>18.74431893172991</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658488905642</v>
+        <v>18.87658673362685</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9672,16 +9672,16 @@
         <v>44774</v>
       </c>
       <c r="B463" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C463" t="n">
-        <v>19.74577744912234</v>
+        <v>19.74577547957757</v>
       </c>
       <c r="D463" t="n">
-        <v>19.04664486253867</v>
+        <v>19.04664296272896</v>
       </c>
       <c r="E463" t="n">
-        <v>19.50013597783399</v>
+        <v>19.50013403279076</v>
       </c>
       <c r="F463" t="n">
         <v>811600</v>
@@ -9692,16 +9692,16 @@
         <v>44775</v>
       </c>
       <c r="B464" t="n">
-        <v>19.08443641662598</v>
+        <v>19.08443832397461</v>
       </c>
       <c r="C464" t="n">
-        <v>19.38676382249504</v>
+        <v>19.38676576005906</v>
       </c>
       <c r="D464" t="n">
-        <v>18.89548088695107</v>
+        <v>18.895482775415</v>
       </c>
       <c r="E464" t="n">
-        <v>19.12222644135287</v>
+        <v>19.12222835247834</v>
       </c>
       <c r="F464" t="n">
         <v>867500</v>
@@ -9712,16 +9712,16 @@
         <v>44776</v>
       </c>
       <c r="B465" t="n">
-        <v>19.68909072875977</v>
+        <v>19.6890926361084</v>
       </c>
       <c r="C465" t="n">
-        <v>19.74577666541846</v>
+        <v>19.74577857825845</v>
       </c>
       <c r="D465" t="n">
-        <v>19.02774819369244</v>
+        <v>19.02775003697459</v>
       </c>
       <c r="E465" t="n">
-        <v>19.08443593236457</v>
+        <v>19.08443778113825</v>
       </c>
       <c r="F465" t="n">
         <v>1095050</v>
@@ -9812,16 +9812,16 @@
         <v>44783</v>
       </c>
       <c r="B470" t="n">
-        <v>21.82427978515625</v>
+        <v>21.82428169250488</v>
       </c>
       <c r="C470" t="n">
-        <v>22.12660717717701</v>
+        <v>22.12660911094776</v>
       </c>
       <c r="D470" t="n">
-        <v>21.08735541559559</v>
+        <v>21.08735725854019</v>
       </c>
       <c r="E470" t="n">
-        <v>21.16293726360078</v>
+        <v>21.16293911315091</v>
       </c>
       <c r="F470" t="n">
         <v>1851300</v>
@@ -9852,16 +9852,16 @@
         <v>44785</v>
       </c>
       <c r="B472" t="n">
-        <v>22.92021942138672</v>
+        <v>22.92021751403809</v>
       </c>
       <c r="C472" t="n">
-        <v>22.99580127578646</v>
+        <v>22.99579936214814</v>
       </c>
       <c r="D472" t="n">
-        <v>21.748699777184</v>
+        <v>21.74869796732555</v>
       </c>
       <c r="E472" t="n">
-        <v>21.748699777184</v>
+        <v>21.74869796732555</v>
       </c>
       <c r="F472" t="n">
         <v>1189950</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75016021728516</v>
+        <v>22.75015830993652</v>
       </c>
       <c r="C474" t="n">
-        <v>23.12806949624067</v>
+        <v>23.12806755720854</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341464991185</v>
+        <v>22.52341276157331</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027946935192</v>
+        <v>23.09027753348805</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9952,16 +9952,16 @@
         <v>44792</v>
       </c>
       <c r="B477" t="n">
-        <v>21.16293907165527</v>
+        <v>21.16293716430664</v>
       </c>
       <c r="C477" t="n">
-        <v>22.16439909378708</v>
+        <v>22.16439709618003</v>
       </c>
       <c r="D477" t="n">
-        <v>20.97398533650574</v>
+        <v>20.97398344618691</v>
       </c>
       <c r="E477" t="n">
-        <v>22.16439909378708</v>
+        <v>22.16439709618003</v>
       </c>
       <c r="F477" t="n">
         <v>1251050</v>
@@ -10072,16 +10072,16 @@
         <v>44802</v>
       </c>
       <c r="B483" t="n">
-        <v>20.91729736328125</v>
+        <v>20.91729545593262</v>
       </c>
       <c r="C483" t="n">
-        <v>21.12514881226926</v>
+        <v>21.12514688596765</v>
       </c>
       <c r="D483" t="n">
-        <v>20.10479288728027</v>
+        <v>20.10479105402004</v>
       </c>
       <c r="E483" t="n">
-        <v>20.40712030179352</v>
+        <v>20.4071184409655</v>
       </c>
       <c r="F483" t="n">
         <v>1048850</v>
@@ -10152,16 +10152,16 @@
         <v>44806</v>
       </c>
       <c r="B487" t="n">
-        <v>20.97398376464844</v>
+        <v>20.97398567199707</v>
       </c>
       <c r="C487" t="n">
-        <v>21.20072931104297</v>
+        <v>21.20073123901156</v>
       </c>
       <c r="D487" t="n">
-        <v>20.55828269525176</v>
+        <v>20.55828456479703</v>
       </c>
       <c r="E487" t="n">
-        <v>20.87950600314736</v>
+        <v>20.8795079019043</v>
       </c>
       <c r="F487" t="n">
         <v>1001300</v>
@@ -10232,16 +10232,16 @@
         <v>44813</v>
       </c>
       <c r="B491" t="n">
-        <v>20.25595664978027</v>
+        <v>20.25595855712891</v>
       </c>
       <c r="C491" t="n">
-        <v>20.29374667569073</v>
+        <v>20.29374858659776</v>
       </c>
       <c r="D491" t="n">
-        <v>19.42455445558783</v>
+        <v>19.42455628464968</v>
       </c>
       <c r="E491" t="n">
-        <v>19.9158374065185</v>
+        <v>19.9158392818407</v>
       </c>
       <c r="F491" t="n">
         <v>1292000</v>
@@ -10252,16 +10252,16 @@
         <v>44816</v>
       </c>
       <c r="B492" t="n">
-        <v>20.65275955200195</v>
+        <v>20.65276145935059</v>
       </c>
       <c r="C492" t="n">
-        <v>21.1251465367997</v>
+        <v>21.12514848777479</v>
       </c>
       <c r="D492" t="n">
-        <v>20.42601401554063</v>
+        <v>20.42601590194859</v>
       </c>
       <c r="E492" t="n">
-        <v>20.44490812540241</v>
+        <v>20.44491001355529</v>
       </c>
       <c r="F492" t="n">
         <v>1299050</v>
@@ -10272,16 +10272,16 @@
         <v>44817</v>
       </c>
       <c r="B493" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577522277832</v>
       </c>
       <c r="C493" t="n">
-        <v>20.27485008942426</v>
+        <v>20.27484813096968</v>
       </c>
       <c r="D493" t="n">
-        <v>19.57571751413516</v>
+        <v>19.57571562321348</v>
       </c>
       <c r="E493" t="n">
-        <v>20.12368638676789</v>
+        <v>20.12368444291501</v>
       </c>
       <c r="F493" t="n">
         <v>1035100</v>
@@ -10372,16 +10372,16 @@
         <v>44824</v>
       </c>
       <c r="B498" t="n">
-        <v>19.84025382995605</v>
+        <v>19.84025573730469</v>
       </c>
       <c r="C498" t="n">
-        <v>20.63386412731537</v>
+        <v>20.63386611095796</v>
       </c>
       <c r="D498" t="n">
-        <v>19.74577607036311</v>
+        <v>19.7457779686291</v>
       </c>
       <c r="E498" t="n">
-        <v>20.3693267608578</v>
+        <v>20.36932871906902</v>
       </c>
       <c r="F498" t="n">
         <v>1041050</v>
@@ -10392,16 +10392,16 @@
         <v>44825</v>
       </c>
       <c r="B499" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C499" t="n">
-        <v>20.08589668660058</v>
+        <v>20.08589468313058</v>
       </c>
       <c r="D499" t="n">
-        <v>19.04664486253867</v>
+        <v>19.04664296272896</v>
       </c>
       <c r="E499" t="n">
-        <v>19.84025521531224</v>
+        <v>19.84025323634378</v>
       </c>
       <c r="F499" t="n">
         <v>1245900</v>
@@ -10412,16 +10412,16 @@
         <v>44826</v>
       </c>
       <c r="B500" t="n">
-        <v>19.93473243713379</v>
+        <v>19.93473434448242</v>
       </c>
       <c r="C500" t="n">
-        <v>19.97252246136969</v>
+        <v>19.97252437233406</v>
       </c>
       <c r="D500" t="n">
-        <v>18.81989879096601</v>
+        <v>18.81990059164773</v>
       </c>
       <c r="E500" t="n">
-        <v>19.34897174436288</v>
+        <v>19.34897359566612</v>
       </c>
       <c r="F500" t="n">
         <v>1035500</v>
@@ -10432,16 +10432,16 @@
         <v>44827</v>
       </c>
       <c r="B501" t="n">
-        <v>19.57571792602539</v>
+        <v>19.57571601867676</v>
       </c>
       <c r="C501" t="n">
-        <v>19.68909160640989</v>
+        <v>19.68908968801476</v>
       </c>
       <c r="D501" t="n">
-        <v>19.21670457516592</v>
+        <v>19.21670270279754</v>
       </c>
       <c r="E501" t="n">
-        <v>19.3489723672699</v>
+        <v>19.34897048201409</v>
       </c>
       <c r="F501" t="n">
         <v>673550</v>
@@ -10452,16 +10452,16 @@
         <v>44830</v>
       </c>
       <c r="B502" t="n">
-        <v>18.7065258026123</v>
+        <v>18.70652389526367</v>
       </c>
       <c r="C502" t="n">
-        <v>19.48124205111187</v>
+        <v>19.48124006477188</v>
       </c>
       <c r="D502" t="n">
-        <v>18.6309439493457</v>
+        <v>18.63094204970352</v>
       </c>
       <c r="E502" t="n">
-        <v>19.34897245638518</v>
+        <v>19.34897048353161</v>
       </c>
       <c r="F502" t="n">
         <v>1198500</v>
@@ -10472,16 +10472,16 @@
         <v>44831</v>
       </c>
       <c r="B503" t="n">
-        <v>18.30972290039062</v>
+        <v>18.30972099304199</v>
       </c>
       <c r="C503" t="n">
-        <v>19.00885738260363</v>
+        <v>19.00885540242521</v>
       </c>
       <c r="D503" t="n">
-        <v>18.2530369538917</v>
+        <v>18.25303505244812</v>
       </c>
       <c r="E503" t="n">
-        <v>18.97106555026184</v>
+        <v>18.97106357402025</v>
       </c>
       <c r="F503" t="n">
         <v>994450</v>
@@ -10512,16 +10512,16 @@
         <v>44833</v>
       </c>
       <c r="B505" t="n">
-        <v>18.21524429321289</v>
+        <v>18.21524620056152</v>
       </c>
       <c r="C505" t="n">
-        <v>18.30972025639716</v>
+        <v>18.30972217363853</v>
       </c>
       <c r="D505" t="n">
-        <v>17.8562291458641</v>
+        <v>17.85623101561966</v>
       </c>
       <c r="E505" t="n">
-        <v>18.2908261449684</v>
+        <v>18.29082806023133</v>
       </c>
       <c r="F505" t="n">
         <v>1182750</v>
@@ -10552,16 +10552,16 @@
         <v>44837</v>
       </c>
       <c r="B507" t="n">
-        <v>19.27339172363281</v>
+        <v>19.27338981628418</v>
       </c>
       <c r="C507" t="n">
-        <v>19.27339172363281</v>
+        <v>19.27338981628418</v>
       </c>
       <c r="D507" t="n">
-        <v>18.76321463492602</v>
+        <v>18.76321277806593</v>
       </c>
       <c r="E507" t="n">
-        <v>18.89548243532896</v>
+        <v>18.89548056537928</v>
       </c>
       <c r="F507" t="n">
         <v>1581550</v>
@@ -10592,16 +10592,16 @@
         <v>44839</v>
       </c>
       <c r="B509" t="n">
-        <v>19.63240432739258</v>
+        <v>19.63240623474121</v>
       </c>
       <c r="C509" t="n">
-        <v>19.84025395823017</v>
+        <v>19.84025588577203</v>
       </c>
       <c r="D509" t="n">
-        <v>19.38676287166812</v>
+        <v>19.38676475515193</v>
       </c>
       <c r="E509" t="n">
-        <v>19.72688028558296</v>
+        <v>19.72688220211023</v>
       </c>
       <c r="F509" t="n">
         <v>721150</v>
@@ -10632,16 +10632,16 @@
         <v>44841</v>
       </c>
       <c r="B511" t="n">
-        <v>19.63240432739258</v>
+        <v>19.63240623474121</v>
       </c>
       <c r="C511" t="n">
-        <v>20.38822280499599</v>
+        <v>20.38822478577472</v>
       </c>
       <c r="D511" t="n">
-        <v>19.55682247963224</v>
+        <v>19.55682437963786</v>
       </c>
       <c r="E511" t="n">
-        <v>20.38822280499599</v>
+        <v>20.38822478577472</v>
       </c>
       <c r="F511" t="n">
         <v>673950</v>
@@ -10692,16 +10692,16 @@
         <v>44847</v>
       </c>
       <c r="B514" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577522277832</v>
       </c>
       <c r="C514" t="n">
-        <v>19.99141859744693</v>
+        <v>19.99141666637049</v>
       </c>
       <c r="D514" t="n">
-        <v>19.10333049283063</v>
+        <v>19.1033286475393</v>
       </c>
       <c r="E514" t="n">
-        <v>19.3489719601506</v>
+        <v>19.34897009113147</v>
       </c>
       <c r="F514" t="n">
         <v>1432800</v>
@@ -10772,16 +10772,16 @@
         <v>44853</v>
       </c>
       <c r="B518" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577522277832</v>
       </c>
       <c r="C518" t="n">
-        <v>19.76467304346237</v>
+        <v>19.76467113428848</v>
       </c>
       <c r="D518" t="n">
-        <v>19.27339010882242</v>
+        <v>19.27338824710413</v>
       </c>
       <c r="E518" t="n">
-        <v>19.46234563814962</v>
+        <v>19.46234375817913</v>
       </c>
       <c r="F518" t="n">
         <v>599800</v>
@@ -10812,16 +10812,16 @@
         <v>44855</v>
       </c>
       <c r="B520" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577522277832</v>
       </c>
       <c r="C520" t="n">
-        <v>19.93473265945416</v>
+        <v>19.93473073385331</v>
       </c>
       <c r="D520" t="n">
-        <v>19.17891234415881</v>
+        <v>19.17891049156664</v>
       </c>
       <c r="E520" t="n">
-        <v>19.33007604681519</v>
+        <v>19.33007417962131</v>
       </c>
       <c r="F520" t="n">
         <v>2036950</v>
@@ -10952,16 +10952,16 @@
         <v>44866</v>
       </c>
       <c r="B527" t="n">
-        <v>20.48270034790039</v>
+        <v>20.48270225524902</v>
       </c>
       <c r="C527" t="n">
-        <v>20.84171367044992</v>
+        <v>20.84171561122987</v>
       </c>
       <c r="D527" t="n">
-        <v>19.95362741919089</v>
+        <v>19.95362927727227</v>
       </c>
       <c r="E527" t="n">
-        <v>20.27484891725449</v>
+        <v>20.274850805248</v>
       </c>
       <c r="F527" t="n">
         <v>1462800</v>
@@ -11012,16 +11012,16 @@
         <v>44872</v>
       </c>
       <c r="B530" t="n">
-        <v>20.44491195678711</v>
+        <v>20.44491004943848</v>
       </c>
       <c r="C530" t="n">
-        <v>21.52195570933349</v>
+        <v>21.52195370150519</v>
       </c>
       <c r="D530" t="n">
-        <v>20.23706229324979</v>
+        <v>20.23706040529189</v>
       </c>
       <c r="E530" t="n">
-        <v>21.29521013037995</v>
+        <v>21.29520814370522</v>
       </c>
       <c r="F530" t="n">
         <v>1164150</v>
@@ -11092,16 +11092,16 @@
         <v>44876</v>
       </c>
       <c r="B534" t="n">
-        <v>15.51319122314453</v>
+        <v>15.5131893157959</v>
       </c>
       <c r="C534" t="n">
-        <v>16.96814244033852</v>
+        <v>16.96814035410347</v>
       </c>
       <c r="D534" t="n">
-        <v>15.05969917407831</v>
+        <v>15.05969732248658</v>
       </c>
       <c r="E534" t="n">
-        <v>16.94924832734628</v>
+        <v>16.94924624343426</v>
       </c>
       <c r="F534" t="n">
         <v>6426800</v>
@@ -11112,16 +11112,16 @@
         <v>44879</v>
       </c>
       <c r="B535" t="n">
-        <v>15.45650386810303</v>
+        <v>15.45650482177734</v>
       </c>
       <c r="C535" t="n">
-        <v>16.26900831697925</v>
+        <v>16.26900932078551</v>
       </c>
       <c r="D535" t="n">
-        <v>14.8896390838082</v>
+        <v>14.88964000250667</v>
       </c>
       <c r="E535" t="n">
-        <v>15.96668091255894</v>
+        <v>15.96668189771144</v>
       </c>
       <c r="F535" t="n">
         <v>3328550</v>
@@ -11172,16 +11172,16 @@
         <v>44883</v>
       </c>
       <c r="B538" t="n">
-        <v>13.83149242401123</v>
+        <v>13.83149337768555</v>
       </c>
       <c r="C538" t="n">
-        <v>14.88963925247558</v>
+        <v>14.88964027910857</v>
       </c>
       <c r="D538" t="n">
-        <v>13.73701465855629</v>
+        <v>13.73701560571641</v>
       </c>
       <c r="E538" t="n">
-        <v>14.26608852329183</v>
+        <v>14.26608950693133</v>
       </c>
       <c r="F538" t="n">
         <v>3266800</v>
@@ -11192,16 +11192,16 @@
         <v>44886</v>
       </c>
       <c r="B539" t="n">
-        <v>14.5117301940918</v>
+        <v>14.51172924041748</v>
       </c>
       <c r="C539" t="n">
-        <v>14.60620796672404</v>
+        <v>14.60620700684089</v>
       </c>
       <c r="D539" t="n">
-        <v>13.79370254591263</v>
+        <v>13.79370163942528</v>
       </c>
       <c r="E539" t="n">
-        <v>14.13382090557644</v>
+        <v>14.13381997673737</v>
       </c>
       <c r="F539" t="n">
         <v>1946900</v>
@@ -11272,16 +11272,16 @@
         <v>44890</v>
       </c>
       <c r="B543" t="n">
-        <v>14.11492443084717</v>
+        <v>14.11492347717285</v>
       </c>
       <c r="C543" t="n">
-        <v>14.90853480626151</v>
+        <v>14.90853379896694</v>
       </c>
       <c r="D543" t="n">
-        <v>13.94486570826322</v>
+        <v>13.94486476607892</v>
       </c>
       <c r="E543" t="n">
-        <v>14.90853480626151</v>
+        <v>14.90853379896694</v>
       </c>
       <c r="F543" t="n">
         <v>1492900</v>
@@ -11292,16 +11292,16 @@
         <v>44893</v>
       </c>
       <c r="B544" t="n">
-        <v>13.98265552520752</v>
+        <v>13.98265647888184</v>
       </c>
       <c r="C544" t="n">
-        <v>14.28498292002064</v>
+        <v>14.28498389431492</v>
       </c>
       <c r="D544" t="n">
-        <v>13.90707367650424</v>
+        <v>13.90707462502356</v>
       </c>
       <c r="E544" t="n">
-        <v>14.13381922261408</v>
+        <v>14.13382018659838</v>
       </c>
       <c r="F544" t="n">
         <v>1713550</v>
@@ -11332,16 +11332,16 @@
         <v>44895</v>
       </c>
       <c r="B546" t="n">
-        <v>14.41725158691406</v>
+        <v>14.41725254058838</v>
       </c>
       <c r="C546" t="n">
-        <v>14.60620620842533</v>
+        <v>14.60620717459865</v>
       </c>
       <c r="D546" t="n">
-        <v>13.83149180972576</v>
+        <v>13.83149272465316</v>
       </c>
       <c r="E546" t="n">
-        <v>14.41725158691406</v>
+        <v>14.41725254058838</v>
       </c>
       <c r="F546" t="n">
         <v>1926400</v>
@@ -11372,16 +11372,16 @@
         <v>44897</v>
       </c>
       <c r="B548" t="n">
-        <v>14.28498458862305</v>
+        <v>14.28498363494873</v>
       </c>
       <c r="C548" t="n">
-        <v>14.58731201875047</v>
+        <v>14.58731104489259</v>
       </c>
       <c r="D548" t="n">
-        <v>14.05823901602748</v>
+        <v>14.05823807749083</v>
       </c>
       <c r="E548" t="n">
-        <v>14.17161180232526</v>
+        <v>14.17161085621978</v>
       </c>
       <c r="F548" t="n">
         <v>1219600</v>
@@ -11412,16 +11412,16 @@
         <v>44901</v>
       </c>
       <c r="B550" t="n">
-        <v>13.15125465393066</v>
+        <v>13.15125560760498</v>
       </c>
       <c r="C550" t="n">
-        <v>13.66143259735872</v>
+        <v>13.66143358802902</v>
       </c>
       <c r="D550" t="n">
-        <v>12.67886763590444</v>
+        <v>12.67886855532321</v>
       </c>
       <c r="E550" t="n">
-        <v>13.54805982115323</v>
+        <v>13.54806080360221</v>
       </c>
       <c r="F550" t="n">
         <v>4313950</v>
@@ -11452,16 +11452,16 @@
         <v>44903</v>
       </c>
       <c r="B552" t="n">
-        <v>12.37653923034668</v>
+        <v>12.376540184021</v>
       </c>
       <c r="C552" t="n">
-        <v>13.09456675483028</v>
+        <v>13.09456776383221</v>
       </c>
       <c r="D552" t="n">
-        <v>12.16868870696652</v>
+        <v>12.16868964462491</v>
       </c>
       <c r="E552" t="n">
-        <v>13.03788082182175</v>
+        <v>13.03788182645574</v>
       </c>
       <c r="F552" t="n">
         <v>3031100</v>
@@ -11532,16 +11532,16 @@
         <v>44909</v>
       </c>
       <c r="B556" t="n">
-        <v>11.50734806060791</v>
+        <v>11.50734901428223</v>
       </c>
       <c r="C556" t="n">
-        <v>11.62072083694312</v>
+        <v>11.62072180001323</v>
       </c>
       <c r="D556" t="n">
-        <v>11.07275196748624</v>
+        <v>11.0727528851433</v>
       </c>
       <c r="E556" t="n">
-        <v>11.50734806060791</v>
+        <v>11.50734901428223</v>
       </c>
       <c r="F556" t="n">
         <v>4449300</v>
@@ -11572,16 +11572,16 @@
         <v>44911</v>
       </c>
       <c r="B558" t="n">
-        <v>11.31839370727539</v>
+        <v>11.31839275360107</v>
       </c>
       <c r="C558" t="n">
-        <v>11.71519891614213</v>
+        <v>11.71519792903348</v>
       </c>
       <c r="D558" t="n">
-        <v>11.09164813106777</v>
+        <v>11.09164719649877</v>
       </c>
       <c r="E558" t="n">
-        <v>11.63961705740626</v>
+        <v>11.63961607666605</v>
       </c>
       <c r="F558" t="n">
         <v>4251600</v>
@@ -11612,16 +11612,16 @@
         <v>44915</v>
       </c>
       <c r="B560" t="n">
-        <v>12.56549453735352</v>
+        <v>12.56549549102783</v>
       </c>
       <c r="C560" t="n">
-        <v>12.86782193281247</v>
+        <v>12.86782290943231</v>
       </c>
       <c r="D560" t="n">
-        <v>11.67740646168276</v>
+        <v>11.6774073479545</v>
       </c>
       <c r="E560" t="n">
-        <v>11.79077923497987</v>
+        <v>11.79078012985618</v>
       </c>
       <c r="F560" t="n">
         <v>2603950</v>
@@ -11672,16 +11672,16 @@
         <v>44918</v>
       </c>
       <c r="B563" t="n">
-        <v>13.39689540863037</v>
+        <v>13.39689636230469</v>
       </c>
       <c r="C563" t="n">
-        <v>13.66143187240536</v>
+        <v>13.66143284491103</v>
       </c>
       <c r="D563" t="n">
-        <v>12.88671749227526</v>
+        <v>12.88671840963194</v>
       </c>
       <c r="E563" t="n">
-        <v>12.90561250347013</v>
+        <v>12.90561342217188</v>
       </c>
       <c r="F563" t="n">
         <v>1442850</v>
@@ -29629,102 +29629,102 @@
     </row>
     <row r="1461">
       <c r="A1461" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1461" t="n">
-        <v>7.710000038146973</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="C1461" t="n">
-        <v>7.760000228881836</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="D1461" t="n">
-        <v>7.579999923706055</v>
+        <v>7.429999828338623</v>
       </c>
       <c r="E1461" t="n">
-        <v>7.730000019073486</v>
+        <v>7.769999980926514</v>
       </c>
       <c r="F1461" t="n">
-        <v>1129300</v>
+        <v>2238200</v>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1462" t="n">
-        <v>7.550000190734863</v>
+        <v>7.559999942779541</v>
       </c>
       <c r="C1462" t="n">
-        <v>7.900000095367432</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="D1462" t="n">
-        <v>7.429999828338623</v>
+        <v>7.46999979019165</v>
       </c>
       <c r="E1462" t="n">
-        <v>7.769999980926514</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="F1462" t="n">
-        <v>2238200</v>
+        <v>2511600</v>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1463" t="n">
-        <v>7.559999942779541</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="C1463" t="n">
-        <v>7.849999904632568</v>
+        <v>7.829999923706055</v>
       </c>
       <c r="D1463" t="n">
-        <v>7.46999979019165</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="E1463" t="n">
-        <v>7.659999847412109</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="F1463" t="n">
-        <v>2511600</v>
+        <v>1601500</v>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1464" t="n">
-        <v>7.659999847412109</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="C1464" t="n">
-        <v>7.829999923706055</v>
+        <v>7.630000114440918</v>
       </c>
       <c r="D1464" t="n">
-        <v>7.599999904632568</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="E1464" t="n">
-        <v>7.599999904632568</v>
+        <v>7.610000133514404</v>
       </c>
       <c r="F1464" t="n">
-        <v>1601500</v>
+        <v>3215300</v>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1465" t="n">
-        <v>7.14</v>
+        <v>7.04</v>
       </c>
       <c r="C1465" t="n">
-        <v>7.63</v>
+        <v>7.21</v>
       </c>
       <c r="D1465" t="n">
-        <v>7.14</v>
+        <v>6.94</v>
       </c>
       <c r="E1465" t="n">
-        <v>7.61</v>
+        <v>7.19</v>
       </c>
       <c r="F1465" t="n">
-        <v>3215300</v>
+        <v>2229400</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1468"/>
+  <dimension ref="A1:F1467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44092</v>
       </c>
       <c r="B2" t="n">
-        <v>13.02992630004883</v>
+        <v>13.02992820739746</v>
       </c>
       <c r="C2" t="n">
-        <v>13.73903811369186</v>
+        <v>13.73904012484181</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63548321825714</v>
+        <v>12.63548506786634</v>
       </c>
       <c r="E2" t="n">
-        <v>13.38448262953382</v>
+        <v>13.38448458878317</v>
       </c>
       <c r="F2" t="n">
         <v>539400</v>
@@ -512,16 +512,16 @@
         <v>44097</v>
       </c>
       <c r="B5" t="n">
-        <v>12.65321254730225</v>
+        <v>12.65321159362793</v>
       </c>
       <c r="C5" t="n">
-        <v>12.99447278246738</v>
+        <v>12.99447180307224</v>
       </c>
       <c r="D5" t="n">
-        <v>12.24990530404421</v>
+        <v>12.24990438076721</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41388776942456</v>
+        <v>12.41388683378818</v>
       </c>
       <c r="F5" t="n">
         <v>1967400</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513519287109</v>
+        <v>12.36513423919678</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366209522167</v>
+        <v>12.49366113163458</v>
       </c>
       <c r="D7" t="n">
-        <v>12.32081554222169</v>
+        <v>12.32081459196557</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377449416991</v>
+        <v>12.45377353365919</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -572,16 +572,16 @@
         <v>44102</v>
       </c>
       <c r="B8" t="n">
-        <v>11.58067989349365</v>
+        <v>11.58068084716797</v>
       </c>
       <c r="C8" t="n">
-        <v>12.51138915392602</v>
+        <v>12.51139018424467</v>
       </c>
       <c r="D8" t="n">
-        <v>11.58067989349365</v>
+        <v>11.58068084716797</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43161395369939</v>
+        <v>12.43161497744851</v>
       </c>
       <c r="F8" t="n">
         <v>1524000</v>
@@ -592,16 +592,16 @@
         <v>44103</v>
       </c>
       <c r="B9" t="n">
-        <v>11.29703521728516</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C9" t="n">
-        <v>11.83330135852865</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="D9" t="n">
-        <v>11.07986986928638</v>
+        <v>11.07987080462801</v>
       </c>
       <c r="E9" t="n">
-        <v>11.83330135852865</v>
+        <v>11.83330235747354</v>
       </c>
       <c r="F9" t="n">
         <v>897600</v>
@@ -612,16 +612,16 @@
         <v>44104</v>
       </c>
       <c r="B10" t="n">
-        <v>11.26158046722412</v>
+        <v>11.2615795135498</v>
       </c>
       <c r="C10" t="n">
-        <v>11.49647402945097</v>
+        <v>11.49647305588496</v>
       </c>
       <c r="D10" t="n">
-        <v>11.19510141235299</v>
+        <v>11.19510046430838</v>
       </c>
       <c r="E10" t="n">
-        <v>11.28373987040548</v>
+        <v>11.28373891485462</v>
       </c>
       <c r="F10" t="n">
         <v>764200</v>
@@ -632,16 +632,16 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>11.68261528015137</v>
+        <v>11.68261432647705</v>
       </c>
       <c r="C11" t="n">
-        <v>11.68261528015137</v>
+        <v>11.68261432647705</v>
       </c>
       <c r="D11" t="n">
-        <v>10.92918377675503</v>
+        <v>10.92918288458478</v>
       </c>
       <c r="E11" t="n">
-        <v>11.22612432864335</v>
+        <v>11.22612341223327</v>
       </c>
       <c r="F11" t="n">
         <v>1726600</v>
@@ -652,16 +652,16 @@
         <v>44106</v>
       </c>
       <c r="B12" t="n">
-        <v>11.29703521728516</v>
+        <v>11.29703617095947</v>
       </c>
       <c r="C12" t="n">
-        <v>11.55408816443952</v>
+        <v>11.55408913981376</v>
       </c>
       <c r="D12" t="n">
-        <v>11.19953266675315</v>
+        <v>11.19953361219649</v>
       </c>
       <c r="E12" t="n">
-        <v>11.51420056528393</v>
+        <v>11.51420153729093</v>
       </c>
       <c r="F12" t="n">
         <v>878600</v>
@@ -672,16 +672,16 @@
         <v>44109</v>
       </c>
       <c r="B13" t="n">
-        <v>11.65602207183838</v>
+        <v>11.6560230255127</v>
       </c>
       <c r="C13" t="n">
-        <v>11.65602207183838</v>
+        <v>11.6560230255127</v>
       </c>
       <c r="D13" t="n">
-        <v>11.1286209060303</v>
+        <v>11.12862181655362</v>
       </c>
       <c r="E13" t="n">
-        <v>11.43442468761843</v>
+        <v>11.43442562316206</v>
       </c>
       <c r="F13" t="n">
         <v>595400</v>
@@ -692,16 +692,16 @@
         <v>44110</v>
       </c>
       <c r="B14" t="n">
-        <v>11.4388599395752</v>
+        <v>11.43885898590088</v>
       </c>
       <c r="C14" t="n">
-        <v>12.05490141501801</v>
+        <v>12.05490040998342</v>
       </c>
       <c r="D14" t="n">
-        <v>11.38124497548991</v>
+        <v>11.38124402661904</v>
       </c>
       <c r="E14" t="n">
-        <v>11.58954627066246</v>
+        <v>11.5895453044252</v>
       </c>
       <c r="F14" t="n">
         <v>472800</v>
@@ -712,16 +712,16 @@
         <v>44111</v>
       </c>
       <c r="B15" t="n">
-        <v>11.68261528015137</v>
+        <v>11.68261432647705</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82443748189021</v>
+        <v>11.82443651663867</v>
       </c>
       <c r="D15" t="n">
-        <v>11.35465122729855</v>
+        <v>11.35465030039657</v>
       </c>
       <c r="E15" t="n">
-        <v>11.6294315318358</v>
+        <v>11.62943058250298</v>
       </c>
       <c r="F15" t="n">
         <v>437200</v>
@@ -752,16 +752,16 @@
         <v>44113</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10365009307861</v>
+        <v>12.10365104675293</v>
       </c>
       <c r="C17" t="n">
-        <v>12.29422399771216</v>
+        <v>12.29422496640223</v>
       </c>
       <c r="D17" t="n">
-        <v>11.531929224505</v>
+        <v>11.53193013313212</v>
       </c>
       <c r="E17" t="n">
-        <v>11.53636127406939</v>
+        <v>11.53636218304571</v>
       </c>
       <c r="F17" t="n">
         <v>672400</v>
@@ -792,16 +792,16 @@
         <v>44118</v>
       </c>
       <c r="B19" t="n">
-        <v>12.1302433013916</v>
+        <v>12.13024234771729</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63105310519763</v>
+        <v>12.63105211214986</v>
       </c>
       <c r="D19" t="n">
-        <v>12.00614844025086</v>
+        <v>12.00614749633282</v>
       </c>
       <c r="E19" t="n">
-        <v>12.18785825940122</v>
+        <v>12.18785730119724</v>
       </c>
       <c r="F19" t="n">
         <v>441800</v>
@@ -812,16 +812,16 @@
         <v>44119</v>
       </c>
       <c r="B20" t="n">
-        <v>11.97955513000488</v>
+        <v>11.9795560836792</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39615761186692</v>
+        <v>12.39615859870633</v>
       </c>
       <c r="D20" t="n">
-        <v>11.78011714216788</v>
+        <v>11.78011807996524</v>
       </c>
       <c r="E20" t="n">
-        <v>12.0283059806663</v>
+        <v>12.0283069382216</v>
       </c>
       <c r="F20" t="n">
         <v>483400</v>
@@ -872,16 +872,16 @@
         <v>44124</v>
       </c>
       <c r="B23" t="n">
-        <v>12.85264873504639</v>
+        <v>12.8526496887207</v>
       </c>
       <c r="C23" t="n">
-        <v>12.87037693216201</v>
+        <v>12.87037788715177</v>
       </c>
       <c r="D23" t="n">
-        <v>12.41388600035818</v>
+        <v>12.41388692147603</v>
       </c>
       <c r="E23" t="n">
-        <v>12.53798084418668</v>
+        <v>12.53798177451245</v>
       </c>
       <c r="F23" t="n">
         <v>729200</v>
@@ -892,16 +892,16 @@
         <v>44125</v>
       </c>
       <c r="B24" t="n">
-        <v>12.85264873504639</v>
+        <v>12.8526496887207</v>
       </c>
       <c r="C24" t="n">
-        <v>12.94571923392254</v>
+        <v>12.94572019450274</v>
       </c>
       <c r="D24" t="n">
-        <v>12.51138854851324</v>
+        <v>12.51138947686584</v>
       </c>
       <c r="E24" t="n">
-        <v>12.85264873504639</v>
+        <v>12.8526496887207</v>
       </c>
       <c r="F24" t="n">
         <v>501200</v>
@@ -912,16 +912,16 @@
         <v>44126</v>
       </c>
       <c r="B25" t="n">
-        <v>13.06981372833252</v>
+        <v>13.06981658935547</v>
       </c>
       <c r="C25" t="n">
-        <v>13.2116359201581</v>
+        <v>13.21163881222637</v>
       </c>
       <c r="D25" t="n">
-        <v>12.6975300521269</v>
+        <v>12.6975328316558</v>
       </c>
       <c r="E25" t="n">
-        <v>12.75071379672497</v>
+        <v>12.75071658789595</v>
       </c>
       <c r="F25" t="n">
         <v>963600</v>
@@ -932,16 +932,16 @@
         <v>44127</v>
       </c>
       <c r="B26" t="n">
-        <v>12.9412899017334</v>
+        <v>12.94128894805908</v>
       </c>
       <c r="C26" t="n">
-        <v>13.18061468012035</v>
+        <v>13.18061370880962</v>
       </c>
       <c r="D26" t="n">
-        <v>12.86151469382872</v>
+        <v>12.86151374603323</v>
       </c>
       <c r="E26" t="n">
-        <v>13.08754416778295</v>
+        <v>13.08754320333081</v>
       </c>
       <c r="F26" t="n">
         <v>543600</v>
@@ -972,16 +972,16 @@
         <v>44131</v>
       </c>
       <c r="B28" t="n">
-        <v>12.22774410247803</v>
+        <v>12.22774600982666</v>
       </c>
       <c r="C28" t="n">
-        <v>12.77730553069506</v>
+        <v>12.77730752376721</v>
       </c>
       <c r="D28" t="n">
-        <v>12.19228855373264</v>
+        <v>12.19229045555073</v>
       </c>
       <c r="E28" t="n">
-        <v>12.67537093371793</v>
+        <v>12.67537291088978</v>
       </c>
       <c r="F28" t="n">
         <v>652400</v>
@@ -992,16 +992,16 @@
         <v>44132</v>
       </c>
       <c r="B29" t="n">
-        <v>11.4388599395752</v>
+        <v>11.43885898590088</v>
       </c>
       <c r="C29" t="n">
-        <v>11.92637449042651</v>
+        <v>11.9263734961074</v>
       </c>
       <c r="D29" t="n">
-        <v>11.30146975958169</v>
+        <v>11.30146881736179</v>
       </c>
       <c r="E29" t="n">
-        <v>11.92637449042651</v>
+        <v>11.9263734961074</v>
       </c>
       <c r="F29" t="n">
         <v>860400</v>
@@ -1012,16 +1012,16 @@
         <v>44133</v>
       </c>
       <c r="B30" t="n">
-        <v>11.7047758102417</v>
+        <v>11.70477485656738</v>
       </c>
       <c r="C30" t="n">
-        <v>11.87762152960331</v>
+        <v>11.87762056184598</v>
       </c>
       <c r="D30" t="n">
-        <v>11.0089600375708</v>
+        <v>11.00895914058972</v>
       </c>
       <c r="E30" t="n">
-        <v>11.39453908004318</v>
+        <v>11.39453815164614</v>
       </c>
       <c r="F30" t="n">
         <v>683400</v>
@@ -1032,16 +1032,16 @@
         <v>44134</v>
       </c>
       <c r="B31" t="n">
-        <v>11.38567543029785</v>
+        <v>11.38567638397217</v>
       </c>
       <c r="C31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.8111430510602</v>
       </c>
       <c r="D31" t="n">
-        <v>11.00895965537159</v>
+        <v>11.00896057749186</v>
       </c>
       <c r="E31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.8111430510602</v>
       </c>
       <c r="F31" t="n">
         <v>907200</v>
@@ -1052,16 +1052,16 @@
         <v>44138</v>
       </c>
       <c r="B32" t="n">
-        <v>11.85546112060547</v>
+        <v>11.85546207427979</v>
       </c>
       <c r="C32" t="n">
-        <v>11.9662598226672</v>
+        <v>11.96626078525436</v>
       </c>
       <c r="D32" t="n">
-        <v>11.51863296489856</v>
+        <v>11.51863389147782</v>
       </c>
       <c r="E32" t="n">
-        <v>11.70034276865364</v>
+        <v>11.70034370984996</v>
       </c>
       <c r="F32" t="n">
         <v>1038200</v>
@@ -1072,16 +1072,16 @@
         <v>44139</v>
       </c>
       <c r="B33" t="n">
-        <v>12.5778694152832</v>
+        <v>12.57786846160889</v>
       </c>
       <c r="C33" t="n">
-        <v>12.78173948494929</v>
+        <v>12.78173851581722</v>
       </c>
       <c r="D33" t="n">
-        <v>11.90421388871892</v>
+        <v>11.90421298612225</v>
       </c>
       <c r="E33" t="n">
-        <v>11.96626089693912</v>
+        <v>11.96625998963795</v>
       </c>
       <c r="F33" t="n">
         <v>620400</v>
@@ -1092,16 +1092,16 @@
         <v>44140</v>
       </c>
       <c r="B34" t="n">
-        <v>12.79503440856934</v>
+        <v>12.79503536224365</v>
       </c>
       <c r="C34" t="n">
-        <v>13.02992711450884</v>
+        <v>13.02992808569082</v>
       </c>
       <c r="D34" t="n">
-        <v>12.63991605755662</v>
+        <v>12.63991699966924</v>
       </c>
       <c r="E34" t="n">
-        <v>12.78617030957958</v>
+        <v>12.78617126259321</v>
       </c>
       <c r="F34" t="n">
         <v>682600</v>
@@ -1132,16 +1132,16 @@
         <v>44144</v>
       </c>
       <c r="B36" t="n">
-        <v>13.29584503173828</v>
+        <v>13.2958459854126</v>
       </c>
       <c r="C36" t="n">
-        <v>13.96950138289152</v>
+        <v>13.96950238488535</v>
       </c>
       <c r="D36" t="n">
-        <v>13.12299931683034</v>
+        <v>13.12300025810691</v>
       </c>
       <c r="E36" t="n">
-        <v>13.73903986612956</v>
+        <v>13.73904085159302</v>
       </c>
       <c r="F36" t="n">
         <v>650800</v>
@@ -1172,16 +1172,16 @@
         <v>44146</v>
       </c>
       <c r="B38" t="n">
-        <v>13.29584503173828</v>
+        <v>13.2958459854126</v>
       </c>
       <c r="C38" t="n">
-        <v>13.41993988968558</v>
+        <v>13.41994085226088</v>
       </c>
       <c r="D38" t="n">
-        <v>12.89696984985155</v>
+        <v>12.89697077491564</v>
       </c>
       <c r="E38" t="n">
-        <v>13.25152537923374</v>
+        <v>13.25152632972913</v>
       </c>
       <c r="F38" t="n">
         <v>586400</v>
@@ -1192,16 +1192,16 @@
         <v>44147</v>
       </c>
       <c r="B39" t="n">
-        <v>12.9412899017334</v>
+        <v>12.94128894805908</v>
       </c>
       <c r="C39" t="n">
-        <v>13.35346040036243</v>
+        <v>13.35345941631429</v>
       </c>
       <c r="D39" t="n">
-        <v>12.75071598181158</v>
+        <v>12.7507150421811</v>
       </c>
       <c r="E39" t="n">
-        <v>13.12299972181535</v>
+        <v>13.12299875475041</v>
       </c>
       <c r="F39" t="n">
         <v>656600</v>
@@ -1232,16 +1232,16 @@
         <v>44151</v>
       </c>
       <c r="B41" t="n">
-        <v>13.02106094360352</v>
+        <v>13.02106380462646</v>
       </c>
       <c r="C41" t="n">
-        <v>13.37118519004395</v>
+        <v>13.37118812799716</v>
       </c>
       <c r="D41" t="n">
-        <v>12.65320934733135</v>
+        <v>12.65321212752895</v>
       </c>
       <c r="E41" t="n">
-        <v>13.20720276613442</v>
+        <v>13.20720566805696</v>
       </c>
       <c r="F41" t="n">
         <v>631800</v>
@@ -1252,16 +1252,16 @@
         <v>44152</v>
       </c>
       <c r="B42" t="n">
-        <v>13.02106094360352</v>
+        <v>13.02106380462646</v>
       </c>
       <c r="C42" t="n">
-        <v>13.09197287891103</v>
+        <v>13.09197575551494</v>
       </c>
       <c r="D42" t="n">
-        <v>12.69752898990097</v>
+        <v>12.6975317798366</v>
       </c>
       <c r="E42" t="n">
-        <v>12.93242250379115</v>
+        <v>12.93242534533822</v>
       </c>
       <c r="F42" t="n">
         <v>784800</v>
@@ -1272,16 +1272,16 @@
         <v>44153</v>
       </c>
       <c r="B43" t="n">
-        <v>12.74185085296631</v>
+        <v>12.74185180664062</v>
       </c>
       <c r="C43" t="n">
-        <v>13.18947771480541</v>
+        <v>13.18947870198273</v>
       </c>
       <c r="D43" t="n">
-        <v>12.66207565150411</v>
+        <v>12.66207659920759</v>
       </c>
       <c r="E43" t="n">
-        <v>13.11413456290522</v>
+        <v>13.11413554444342</v>
       </c>
       <c r="F43" t="n">
         <v>532400</v>
@@ -1292,16 +1292,16 @@
         <v>44154</v>
       </c>
       <c r="B44" t="n">
-        <v>12.99447345733643</v>
+        <v>12.99447250366211</v>
       </c>
       <c r="C44" t="n">
-        <v>13.07424866921448</v>
+        <v>13.0742477096854</v>
       </c>
       <c r="D44" t="n">
-        <v>12.48036747559687</v>
+        <v>12.48036655965319</v>
       </c>
       <c r="E44" t="n">
-        <v>12.74185251660733</v>
+        <v>12.74185158147306</v>
       </c>
       <c r="F44" t="n">
         <v>711400</v>
@@ -1352,16 +1352,16 @@
         <v>44160</v>
       </c>
       <c r="B47" t="n">
-        <v>13.65040111541748</v>
+        <v>13.65039920806885</v>
       </c>
       <c r="C47" t="n">
-        <v>13.77449597840386</v>
+        <v>13.77449405371565</v>
       </c>
       <c r="D47" t="n">
-        <v>13.34016522594218</v>
+        <v>13.34016336194231</v>
       </c>
       <c r="E47" t="n">
-        <v>13.61494556103953</v>
+        <v>13.61494365864504</v>
       </c>
       <c r="F47" t="n">
         <v>724200</v>
@@ -1412,16 +1412,16 @@
         <v>44165</v>
       </c>
       <c r="B50" t="n">
-        <v>13.13629531860352</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="C50" t="n">
-        <v>13.73017649585873</v>
+        <v>13.73017450228043</v>
       </c>
       <c r="D50" t="n">
-        <v>13.13629531860352</v>
+        <v>13.13629341125488</v>
       </c>
       <c r="E50" t="n">
-        <v>13.38891625237249</v>
+        <v>13.38891430834409</v>
       </c>
       <c r="F50" t="n">
         <v>1093200</v>
@@ -1492,16 +1492,16 @@
         <v>44169</v>
       </c>
       <c r="B54" t="n">
-        <v>14.07143592834473</v>
+        <v>14.07143497467041</v>
       </c>
       <c r="C54" t="n">
-        <v>14.44815085961357</v>
+        <v>14.44814988040786</v>
       </c>
       <c r="D54" t="n">
-        <v>13.94734107095812</v>
+        <v>13.94734012569418</v>
       </c>
       <c r="E54" t="n">
-        <v>14.44815085961357</v>
+        <v>14.44814988040786</v>
       </c>
       <c r="F54" t="n">
         <v>751600</v>
@@ -1512,16 +1512,16 @@
         <v>44172</v>
       </c>
       <c r="B55" t="n">
-        <v>14.25314426422119</v>
+        <v>14.25314521789551</v>
       </c>
       <c r="C55" t="n">
-        <v>14.36837416480735</v>
+        <v>14.36837512619167</v>
       </c>
       <c r="D55" t="n">
-        <v>13.82767767499762</v>
+        <v>13.82767860020407</v>
       </c>
       <c r="E55" t="n">
-        <v>14.06257037080052</v>
+        <v>14.06257131172358</v>
       </c>
       <c r="F55" t="n">
         <v>782600</v>
@@ -1532,16 +1532,16 @@
         <v>44173</v>
       </c>
       <c r="B56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="C56" t="n">
-        <v>14.53679034258752</v>
+        <v>14.53678935892345</v>
       </c>
       <c r="D56" t="n">
-        <v>13.89859038475245</v>
+        <v>13.89858944427358</v>
       </c>
       <c r="E56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="F56" t="n">
         <v>767200</v>
@@ -1552,16 +1552,16 @@
         <v>44174</v>
       </c>
       <c r="B57" t="n">
-        <v>13.88972473144531</v>
+        <v>13.88972568511963</v>
       </c>
       <c r="C57" t="n">
-        <v>14.24871311856489</v>
+        <v>14.2487140968875</v>
       </c>
       <c r="D57" t="n">
-        <v>13.65926323867578</v>
+        <v>13.65926417652651</v>
       </c>
       <c r="E57" t="n">
-        <v>14.14677767481842</v>
+        <v>14.1467786461421</v>
       </c>
       <c r="F57" t="n">
         <v>570800</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.00495529174805</v>
+        <v>14.004958152771</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10245783955028</v>
+        <v>14.10246072049168</v>
       </c>
       <c r="D58" t="n">
-        <v>13.51744086208294</v>
+        <v>13.51744362351329</v>
       </c>
       <c r="E58" t="n">
-        <v>13.88529249763146</v>
+        <v>13.88529533420892</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1612,16 +1612,16 @@
         <v>44179</v>
       </c>
       <c r="B60" t="n">
-        <v>13.7567663192749</v>
+        <v>13.75676727294922</v>
       </c>
       <c r="C60" t="n">
-        <v>14.05813805833661</v>
+        <v>14.05813903290322</v>
       </c>
       <c r="D60" t="n">
-        <v>13.61494328019492</v>
+        <v>13.61494422403749</v>
       </c>
       <c r="E60" t="n">
-        <v>13.74347017161295</v>
+        <v>13.74347112436552</v>
       </c>
       <c r="F60" t="n">
         <v>525000</v>
@@ -1692,16 +1692,16 @@
         <v>44183</v>
       </c>
       <c r="B64" t="n">
-        <v>13.40664482116699</v>
+        <v>13.40664291381836</v>
       </c>
       <c r="C64" t="n">
-        <v>13.83654354086681</v>
+        <v>13.83654157235696</v>
       </c>
       <c r="D64" t="n">
-        <v>13.28698200335575</v>
+        <v>13.28698011303142</v>
       </c>
       <c r="E64" t="n">
-        <v>13.61937815594667</v>
+        <v>13.6193762183327</v>
       </c>
       <c r="F64" t="n">
         <v>920000</v>
@@ -1732,16 +1732,16 @@
         <v>44187</v>
       </c>
       <c r="B66" t="n">
-        <v>13.00776672363281</v>
+        <v>13.00776863098145</v>
       </c>
       <c r="C66" t="n">
-        <v>13.60607983473112</v>
+        <v>13.60608182981131</v>
       </c>
       <c r="D66" t="n">
-        <v>12.94571888074782</v>
+        <v>12.94572077899828</v>
       </c>
       <c r="E66" t="n">
-        <v>13.22493206041293</v>
+        <v>13.22493399960485</v>
       </c>
       <c r="F66" t="n">
         <v>911600</v>
@@ -1752,16 +1752,16 @@
         <v>44188</v>
       </c>
       <c r="B67" t="n">
-        <v>14.04484367370605</v>
+        <v>14.04484272003174</v>
       </c>
       <c r="C67" t="n">
-        <v>14.15121032597093</v>
+        <v>14.1512093650741</v>
       </c>
       <c r="D67" t="n">
-        <v>13.40221086527954</v>
+        <v>13.40220995524134</v>
       </c>
       <c r="E67" t="n">
-        <v>13.45539461407549</v>
+        <v>13.45539370042599</v>
       </c>
       <c r="F67" t="n">
         <v>2040000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294269561768</v>
+        <v>15.11294078826904</v>
       </c>
       <c r="C68" t="n">
-        <v>15.13067089418624</v>
+        <v>15.1306689846002</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586759384061</v>
+        <v>14.07586581737739</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348254853438</v>
+        <v>14.13348076479979</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1812,16 +1812,16 @@
         <v>44195</v>
       </c>
       <c r="B70" t="n">
-        <v>15.72011852264404</v>
+        <v>15.72011947631836</v>
       </c>
       <c r="C70" t="n">
-        <v>15.9151236064789</v>
+        <v>15.91512457198337</v>
       </c>
       <c r="D70" t="n">
-        <v>15.25033147305764</v>
+        <v>15.25033239823193</v>
       </c>
       <c r="E70" t="n">
-        <v>15.37885835794267</v>
+        <v>15.37885929091415</v>
       </c>
       <c r="F70" t="n">
         <v>2946000</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884868621826</v>
+        <v>14.98884963989258</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171822605652</v>
+        <v>15.94171924035773</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952307751646</v>
+        <v>14.74952401596354</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069472389008</v>
+        <v>15.91069573621739</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1852,16 +1852,16 @@
         <v>44201</v>
       </c>
       <c r="B72" t="n">
-        <v>15.13953590393066</v>
+        <v>15.13953495025635</v>
       </c>
       <c r="C72" t="n">
-        <v>15.45863673473862</v>
+        <v>15.45863576096341</v>
       </c>
       <c r="D72" t="n">
-        <v>14.36394492178124</v>
+        <v>14.36394401696318</v>
       </c>
       <c r="E72" t="n">
-        <v>14.84702737257476</v>
+        <v>14.84702643732623</v>
       </c>
       <c r="F72" t="n">
         <v>1878200</v>
@@ -1912,16 +1912,16 @@
         <v>44204</v>
       </c>
       <c r="B75" t="n">
-        <v>15.06334590911865</v>
+        <v>15.06334781646729</v>
       </c>
       <c r="C75" t="n">
-        <v>15.27237428787347</v>
+        <v>15.27237622168966</v>
       </c>
       <c r="D75" t="n">
-        <v>14.38734078956258</v>
+        <v>14.38734261131419</v>
       </c>
       <c r="E75" t="n">
-        <v>14.38734078956258</v>
+        <v>14.38734261131419</v>
       </c>
       <c r="F75" t="n">
         <v>1077600</v>
@@ -1932,16 +1932,16 @@
         <v>44207</v>
       </c>
       <c r="B76" t="n">
-        <v>15.83274364471436</v>
+        <v>15.83274555206299</v>
       </c>
       <c r="C76" t="n">
-        <v>15.83274364471436</v>
+        <v>15.83274555206299</v>
       </c>
       <c r="D76" t="n">
-        <v>14.80539530952503</v>
+        <v>14.80539709311043</v>
       </c>
       <c r="E76" t="n">
-        <v>14.95215863031701</v>
+        <v>14.95216043158278</v>
       </c>
       <c r="F76" t="n">
         <v>1758200</v>
@@ -1952,16 +1952,16 @@
         <v>44208</v>
       </c>
       <c r="B77" t="n">
-        <v>15.99285221099854</v>
+        <v>15.99285316467285</v>
       </c>
       <c r="C77" t="n">
-        <v>16.31306559830687</v>
+        <v>16.31306657107592</v>
       </c>
       <c r="D77" t="n">
-        <v>15.34353212811103</v>
+        <v>15.34353304306556</v>
       </c>
       <c r="E77" t="n">
-        <v>15.90390385935192</v>
+        <v>15.90390480772213</v>
       </c>
       <c r="F77" t="n">
         <v>2193200</v>
@@ -1972,16 +1972,16 @@
         <v>44209</v>
       </c>
       <c r="B78" t="n">
-        <v>15.72156429290771</v>
+        <v>15.72156143188477</v>
       </c>
       <c r="C78" t="n">
-        <v>16.71778301778313</v>
+        <v>16.7177799754675</v>
       </c>
       <c r="D78" t="n">
-        <v>15.41469418710659</v>
+        <v>15.41469138192811</v>
       </c>
       <c r="E78" t="n">
-        <v>15.96617274305619</v>
+        <v>15.9661698375192</v>
       </c>
       <c r="F78" t="n">
         <v>1238200</v>
@@ -2012,16 +2012,16 @@
         <v>44211</v>
       </c>
       <c r="B80" t="n">
-        <v>15.881667137146</v>
+        <v>15.88166618347168</v>
       </c>
       <c r="C80" t="n">
-        <v>16.09069550826418</v>
+        <v>16.09069454203798</v>
       </c>
       <c r="D80" t="n">
-        <v>15.61037542906886</v>
+        <v>15.61037449168528</v>
       </c>
       <c r="E80" t="n">
-        <v>16.08624715759644</v>
+        <v>16.08624619163735</v>
       </c>
       <c r="F80" t="n">
         <v>728000</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422584533691</v>
+        <v>16.38422393798828</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538419561817</v>
+        <v>16.45538227998573</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169572023429</v>
+        <v>15.92169386673051</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93503907728939</v>
+        <v>15.93503722223226</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2052,16 +2052,16 @@
         <v>44215</v>
       </c>
       <c r="B82" t="n">
-        <v>16.63327789306641</v>
+        <v>16.63327980041504</v>
       </c>
       <c r="C82" t="n">
-        <v>17.07801792553825</v>
+        <v>17.07801988388551</v>
       </c>
       <c r="D82" t="n">
-        <v>16.09514116439855</v>
+        <v>16.0951430100387</v>
       </c>
       <c r="E82" t="n">
-        <v>17.07801792553825</v>
+        <v>17.07801988388551</v>
       </c>
       <c r="F82" t="n">
         <v>1918400</v>
@@ -2092,16 +2092,16 @@
         <v>44217</v>
       </c>
       <c r="B84" t="n">
-        <v>15.85498142242432</v>
+        <v>15.85498523712158</v>
       </c>
       <c r="C84" t="n">
-        <v>16.3664313962309</v>
+        <v>16.36643533398266</v>
       </c>
       <c r="D84" t="n">
-        <v>15.53031973470776</v>
+        <v>15.53032347129166</v>
       </c>
       <c r="E84" t="n">
-        <v>16.25969474802276</v>
+        <v>16.25969866009376</v>
       </c>
       <c r="F84" t="n">
         <v>928200</v>
@@ -2132,16 +2132,16 @@
         <v>44222</v>
       </c>
       <c r="B86" t="n">
-        <v>14.67197608947754</v>
+        <v>14.67197513580322</v>
       </c>
       <c r="C86" t="n">
-        <v>15.525876234775</v>
+        <v>15.52587522559741</v>
       </c>
       <c r="D86" t="n">
-        <v>14.63639606848242</v>
+        <v>14.6363951171208</v>
       </c>
       <c r="E86" t="n">
-        <v>15.38355954389209</v>
+        <v>15.38355854396505</v>
       </c>
       <c r="F86" t="n">
         <v>1156000</v>
@@ -2172,16 +2172,16 @@
         <v>44224</v>
       </c>
       <c r="B88" t="n">
-        <v>15.65929794311523</v>
+        <v>15.6592960357666</v>
       </c>
       <c r="C88" t="n">
-        <v>15.98840635160216</v>
+        <v>15.98840440416715</v>
       </c>
       <c r="D88" t="n">
-        <v>14.95216114202533</v>
+        <v>14.95215932080804</v>
       </c>
       <c r="E88" t="n">
-        <v>15.13450450851776</v>
+        <v>15.13450266509051</v>
       </c>
       <c r="F88" t="n">
         <v>3941600</v>
@@ -2192,16 +2192,16 @@
         <v>44225</v>
       </c>
       <c r="B89" t="n">
-        <v>15.74380016326904</v>
+        <v>15.74379920959473</v>
       </c>
       <c r="C89" t="n">
-        <v>16.55322700669943</v>
+        <v>16.55322600399441</v>
       </c>
       <c r="D89" t="n">
-        <v>15.38800672728083</v>
+        <v>15.38800579515856</v>
       </c>
       <c r="E89" t="n">
-        <v>16.01064354371136</v>
+        <v>16.01064257387312</v>
       </c>
       <c r="F89" t="n">
         <v>3936400</v>
@@ -2212,16 +2212,16 @@
         <v>44228</v>
       </c>
       <c r="B90" t="n">
-        <v>16.76670074462891</v>
+        <v>16.76670265197754</v>
       </c>
       <c r="C90" t="n">
-        <v>17.02909745013378</v>
+        <v>17.02909938733217</v>
       </c>
       <c r="D90" t="n">
-        <v>15.65929723928157</v>
+        <v>15.65929902065404</v>
       </c>
       <c r="E90" t="n">
-        <v>16.0106422968565</v>
+        <v>16.01064411819733</v>
       </c>
       <c r="F90" t="n">
         <v>3072200</v>
@@ -2292,16 +2292,16 @@
         <v>44232</v>
       </c>
       <c r="B94" t="n">
-        <v>18.80805969238281</v>
+        <v>18.80805778503418</v>
       </c>
       <c r="C94" t="n">
-        <v>19.56856487465802</v>
+        <v>19.56856289018561</v>
       </c>
       <c r="D94" t="n">
-        <v>17.78960443150729</v>
+        <v>17.78960262744146</v>
       </c>
       <c r="E94" t="n">
-        <v>17.99863282647314</v>
+        <v>17.99863100120949</v>
       </c>
       <c r="F94" t="n">
         <v>14342200</v>
@@ -2312,16 +2312,16 @@
         <v>44235</v>
       </c>
       <c r="B95" t="n">
-        <v>19.23056030273438</v>
+        <v>19.23056221008301</v>
       </c>
       <c r="C95" t="n">
-        <v>19.36842863096819</v>
+        <v>19.36843055199105</v>
       </c>
       <c r="D95" t="n">
-        <v>18.46560688202301</v>
+        <v>18.46560871350112</v>
       </c>
       <c r="E95" t="n">
-        <v>18.81250357441601</v>
+        <v>18.81250544030044</v>
       </c>
       <c r="F95" t="n">
         <v>1758400</v>
@@ -2352,16 +2352,16 @@
         <v>44237</v>
       </c>
       <c r="B97" t="n">
-        <v>18.55900001525879</v>
+        <v>18.55900382995605</v>
       </c>
       <c r="C97" t="n">
-        <v>18.98150335499749</v>
+        <v>18.98150725653792</v>
       </c>
       <c r="D97" t="n">
-        <v>18.2432350221098</v>
+        <v>18.24323877190336</v>
       </c>
       <c r="E97" t="n">
-        <v>18.87031835488459</v>
+        <v>18.87032223357157</v>
       </c>
       <c r="F97" t="n">
         <v>979000</v>
@@ -2372,16 +2372,16 @@
         <v>44238</v>
       </c>
       <c r="B98" t="n">
-        <v>18.63461112976074</v>
+        <v>18.63460922241211</v>
       </c>
       <c r="C98" t="n">
-        <v>19.14606123399878</v>
+        <v>19.14605927430059</v>
       </c>
       <c r="D98" t="n">
-        <v>18.43447774264635</v>
+        <v>18.4344758557824</v>
       </c>
       <c r="E98" t="n">
-        <v>18.55900442949581</v>
+        <v>18.55900252988591</v>
       </c>
       <c r="F98" t="n">
         <v>912400</v>
@@ -2412,16 +2412,16 @@
         <v>44244</v>
       </c>
       <c r="B100" t="n">
-        <v>18.52787399291992</v>
+        <v>18.52787208557129</v>
       </c>
       <c r="C100" t="n">
-        <v>18.68798071328474</v>
+        <v>18.68797878945395</v>
       </c>
       <c r="D100" t="n">
-        <v>18.20766055219028</v>
+        <v>18.20765867780597</v>
       </c>
       <c r="E100" t="n">
-        <v>18.51897898661644</v>
+        <v>18.5189770801835</v>
       </c>
       <c r="F100" t="n">
         <v>743200</v>
@@ -2432,16 +2432,16 @@
         <v>44245</v>
       </c>
       <c r="B101" t="n">
-        <v>18.24323844909668</v>
+        <v>18.24323654174805</v>
       </c>
       <c r="C101" t="n">
-        <v>19.03487525571373</v>
+        <v>19.03487326559868</v>
       </c>
       <c r="D101" t="n">
-        <v>17.9052350351925</v>
+        <v>17.90523316318246</v>
       </c>
       <c r="E101" t="n">
-        <v>18.69242518745105</v>
+        <v>18.6924232331395</v>
       </c>
       <c r="F101" t="n">
         <v>1007600</v>
@@ -2492,16 +2492,16 @@
         <v>44250</v>
       </c>
       <c r="B104" t="n">
-        <v>17.70065307617188</v>
+        <v>17.70065498352051</v>
       </c>
       <c r="C104" t="n">
-        <v>18.10091978679969</v>
+        <v>18.1009217372794</v>
       </c>
       <c r="D104" t="n">
-        <v>17.51830972945222</v>
+        <v>17.5183116171523</v>
       </c>
       <c r="E104" t="n">
-        <v>17.860759760423</v>
+        <v>17.86076168502407</v>
       </c>
       <c r="F104" t="n">
         <v>1151400</v>
@@ -2532,16 +2532,16 @@
         <v>44252</v>
       </c>
       <c r="B106" t="n">
-        <v>16.94459533691406</v>
+        <v>16.9445972442627</v>
       </c>
       <c r="C106" t="n">
-        <v>17.7940487700933</v>
+        <v>17.79405077305967</v>
       </c>
       <c r="D106" t="n">
-        <v>16.6377253111698</v>
+        <v>16.63772718397596</v>
       </c>
       <c r="E106" t="n">
-        <v>17.68731210746428</v>
+        <v>17.68731409841596</v>
       </c>
       <c r="F106" t="n">
         <v>1207600</v>
@@ -2552,16 +2552,16 @@
         <v>44253</v>
       </c>
       <c r="B107" t="n">
-        <v>16.69998931884766</v>
+        <v>16.69999122619629</v>
       </c>
       <c r="C107" t="n">
-        <v>17.20699272810024</v>
+        <v>17.20699469335504</v>
       </c>
       <c r="D107" t="n">
-        <v>16.40201428576187</v>
+        <v>16.40201615907802</v>
       </c>
       <c r="E107" t="n">
-        <v>17.13583438463582</v>
+        <v>17.13583634176344</v>
       </c>
       <c r="F107" t="n">
         <v>1586600</v>
@@ -2572,16 +2572,16 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>16.44648933410645</v>
+        <v>16.44648742675781</v>
       </c>
       <c r="C108" t="n">
-        <v>17.02465114728449</v>
+        <v>17.0246491728847</v>
       </c>
       <c r="D108" t="n">
-        <v>16.27748761449939</v>
+        <v>16.27748572675039</v>
       </c>
       <c r="E108" t="n">
-        <v>16.69999106524258</v>
+        <v>16.69998912849459</v>
       </c>
       <c r="F108" t="n">
         <v>1540800</v>
@@ -2612,16 +2612,16 @@
         <v>44258</v>
       </c>
       <c r="B110" t="n">
-        <v>16.19298553466797</v>
+        <v>16.19298362731934</v>
       </c>
       <c r="C110" t="n">
-        <v>16.80227894250898</v>
+        <v>16.80227696339255</v>
       </c>
       <c r="D110" t="n">
-        <v>15.61927044946103</v>
+        <v>15.61926860968948</v>
       </c>
       <c r="E110" t="n">
-        <v>16.80227894250898</v>
+        <v>16.80227696339255</v>
       </c>
       <c r="F110" t="n">
         <v>1368800</v>
@@ -2632,16 +2632,16 @@
         <v>44259</v>
       </c>
       <c r="B111" t="n">
-        <v>16.05066680908203</v>
+        <v>16.0506706237793</v>
       </c>
       <c r="C111" t="n">
-        <v>16.75780348316564</v>
+        <v>16.75780746592523</v>
       </c>
       <c r="D111" t="n">
-        <v>15.79271679246922</v>
+        <v>15.79272054586055</v>
       </c>
       <c r="E111" t="n">
-        <v>16.23301014282442</v>
+        <v>16.23301400085849</v>
       </c>
       <c r="F111" t="n">
         <v>1300400</v>
@@ -2672,16 +2672,16 @@
         <v>44263</v>
       </c>
       <c r="B113" t="n">
-        <v>14.91213417053223</v>
+        <v>14.91213321685791</v>
       </c>
       <c r="C113" t="n">
-        <v>16.05956437827389</v>
+        <v>16.05956335121808</v>
       </c>
       <c r="D113" t="n">
-        <v>14.76537082800059</v>
+        <v>14.76536988371221</v>
       </c>
       <c r="E113" t="n">
-        <v>16.01064269858043</v>
+        <v>16.0106416746533</v>
       </c>
       <c r="F113" t="n">
         <v>3236800</v>
@@ -2692,16 +2692,16 @@
         <v>44264</v>
       </c>
       <c r="B114" t="n">
-        <v>14.76537132263184</v>
+        <v>14.76537036895752</v>
       </c>
       <c r="C114" t="n">
-        <v>15.42358645203744</v>
+        <v>15.42358545584995</v>
       </c>
       <c r="D114" t="n">
-        <v>14.55634293750244</v>
+        <v>14.55634199732897</v>
       </c>
       <c r="E114" t="n">
-        <v>15.11671640079224</v>
+        <v>15.11671542442504</v>
       </c>
       <c r="F114" t="n">
         <v>1628800</v>
@@ -2712,16 +2712,16 @@
         <v>44265</v>
       </c>
       <c r="B115" t="n">
-        <v>14.64529037475586</v>
+        <v>14.64529132843018</v>
       </c>
       <c r="C115" t="n">
-        <v>15.05445041737906</v>
+        <v>15.05445139769713</v>
       </c>
       <c r="D115" t="n">
-        <v>14.28505031384297</v>
+        <v>14.28505124405912</v>
       </c>
       <c r="E115" t="n">
-        <v>15.05445041737906</v>
+        <v>15.05445139769713</v>
       </c>
       <c r="F115" t="n">
         <v>3352600</v>
@@ -2732,16 +2732,16 @@
         <v>44266</v>
       </c>
       <c r="B116" t="n">
-        <v>15.81940460205078</v>
+        <v>15.8194055557251</v>
       </c>
       <c r="C116" t="n">
-        <v>15.99285296281361</v>
+        <v>15.99285392694427</v>
       </c>
       <c r="D116" t="n">
-        <v>15.15674282905697</v>
+        <v>15.15674374278266</v>
       </c>
       <c r="E116" t="n">
-        <v>15.15674282905697</v>
+        <v>15.15674374278266</v>
       </c>
       <c r="F116" t="n">
         <v>2295400</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708778381348</v>
+        <v>15.67708683013916</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619618873527</v>
+        <v>16.00619521504051</v>
       </c>
       <c r="D118" t="n">
-        <v>15.49474441929632</v>
+        <v>15.49474347671438</v>
       </c>
       <c r="E118" t="n">
-        <v>15.614824444205</v>
+        <v>15.61482349431831</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2792,16 +2792,16 @@
         <v>44271</v>
       </c>
       <c r="B119" t="n">
-        <v>16.46872520446777</v>
+        <v>16.46872329711914</v>
       </c>
       <c r="C119" t="n">
-        <v>16.83786029832273</v>
+        <v>16.8378583482222</v>
       </c>
       <c r="D119" t="n">
-        <v>15.6815350313212</v>
+        <v>15.68153321514211</v>
       </c>
       <c r="E119" t="n">
-        <v>15.68598338234651</v>
+        <v>15.68598156565223</v>
       </c>
       <c r="F119" t="n">
         <v>1963400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880805969238</v>
+        <v>16.58880424499512</v>
       </c>
       <c r="C120" t="n">
-        <v>16.75780979991704</v>
+        <v>16.7578059463568</v>
       </c>
       <c r="D120" t="n">
-        <v>16.07735788033358</v>
+        <v>16.07735418324739</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298957845627</v>
+        <v>16.19298585477987</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2832,16 +2832,16 @@
         <v>44273</v>
       </c>
       <c r="B121" t="n">
-        <v>16.21967124938965</v>
+        <v>16.21967315673828</v>
       </c>
       <c r="C121" t="n">
-        <v>17.2914947735938</v>
+        <v>17.29149680698328</v>
       </c>
       <c r="D121" t="n">
-        <v>16.077354559611</v>
+        <v>16.07735645022393</v>
       </c>
       <c r="E121" t="n">
-        <v>16.58880463333153</v>
+        <v>16.58880658408833</v>
       </c>
       <c r="F121" t="n">
         <v>1568800</v>
@@ -2852,16 +2852,16 @@
         <v>44274</v>
       </c>
       <c r="B122" t="n">
-        <v>16.32196044921875</v>
+        <v>16.32196235656738</v>
       </c>
       <c r="C122" t="n">
-        <v>16.54433047796411</v>
+        <v>16.54433241129841</v>
       </c>
       <c r="D122" t="n">
-        <v>15.89056205055718</v>
+        <v>15.89056390749354</v>
       </c>
       <c r="E122" t="n">
-        <v>16.17519541590345</v>
+        <v>16.17519730610144</v>
       </c>
       <c r="F122" t="n">
         <v>1059200</v>
@@ -2872,16 +2872,16 @@
         <v>44277</v>
       </c>
       <c r="B123" t="n">
-        <v>16.54433250427246</v>
+        <v>16.54433059692383</v>
       </c>
       <c r="C123" t="n">
-        <v>16.58435918221094</v>
+        <v>16.58435727024774</v>
       </c>
       <c r="D123" t="n">
-        <v>15.921695668907</v>
+        <v>15.92169383334038</v>
       </c>
       <c r="E123" t="n">
-        <v>16.26414575870311</v>
+        <v>16.26414388365641</v>
       </c>
       <c r="F123" t="n">
         <v>938000</v>
@@ -2912,16 +2912,16 @@
         <v>44279</v>
       </c>
       <c r="B125" t="n">
-        <v>15.41024589538574</v>
+        <v>15.41024303436279</v>
       </c>
       <c r="C125" t="n">
-        <v>16.21077777512874</v>
+        <v>16.2107747654813</v>
       </c>
       <c r="D125" t="n">
-        <v>15.21455915604819</v>
+        <v>15.21455633135589</v>
       </c>
       <c r="E125" t="n">
-        <v>16.05067105987036</v>
+        <v>16.05066807994787</v>
       </c>
       <c r="F125" t="n">
         <v>1010400</v>
@@ -2952,16 +2952,16 @@
         <v>44281</v>
       </c>
       <c r="B127" t="n">
-        <v>15.85498142242432</v>
+        <v>15.85498523712158</v>
       </c>
       <c r="C127" t="n">
-        <v>16.41535306688814</v>
+        <v>16.41535701641043</v>
       </c>
       <c r="D127" t="n">
-        <v>15.67263809323268</v>
+        <v>15.67264186405827</v>
       </c>
       <c r="E127" t="n">
-        <v>16.10403473260894</v>
+        <v>16.10403860722825</v>
       </c>
       <c r="F127" t="n">
         <v>1078200</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.5836935043335</v>
+        <v>15.58369255065918</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174858739247</v>
+        <v>16.00174760813446</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245512569351</v>
+        <v>15.39245418372239</v>
       </c>
       <c r="E128" t="n">
-        <v>15.74380021171105</v>
+        <v>15.7437992482387</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514236450195</v>
+        <v>16.09514427185059</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23745904978063</v>
+        <v>16.23746097399444</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48584894961834</v>
+        <v>15.48585078476289</v>
       </c>
       <c r="E129" t="n">
-        <v>15.58813896112809</v>
+        <v>15.58814080839448</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3012,16 +3012,16 @@
         <v>44286</v>
       </c>
       <c r="B130" t="n">
-        <v>16.6154899597168</v>
+        <v>16.61549186706543</v>
       </c>
       <c r="C130" t="n">
-        <v>16.71777997637457</v>
+        <v>16.71778189546542</v>
       </c>
       <c r="D130" t="n">
-        <v>15.94393147674567</v>
+        <v>15.94393330700381</v>
       </c>
       <c r="E130" t="n">
-        <v>16.10848653082663</v>
+        <v>16.10848837997462</v>
       </c>
       <c r="F130" t="n">
         <v>1491400</v>
@@ -3072,16 +3072,16 @@
         <v>44292</v>
       </c>
       <c r="B133" t="n">
-        <v>17.52275848388672</v>
+        <v>17.52276039123535</v>
       </c>
       <c r="C133" t="n">
-        <v>17.56723180984916</v>
+        <v>17.5672337220387</v>
       </c>
       <c r="D133" t="n">
-        <v>16.82896340165162</v>
+        <v>16.8289652334808</v>
       </c>
       <c r="E133" t="n">
-        <v>16.8912267366185</v>
+        <v>16.89122857522503</v>
       </c>
       <c r="F133" t="n">
         <v>1684600</v>
@@ -3112,16 +3112,16 @@
         <v>44294</v>
       </c>
       <c r="B135" t="n">
-        <v>17.60726165771484</v>
+        <v>17.60725975036621</v>
       </c>
       <c r="C135" t="n">
-        <v>17.90968507914474</v>
+        <v>17.90968313903537</v>
       </c>
       <c r="D135" t="n">
-        <v>17.27370656318618</v>
+        <v>17.2737046919707</v>
       </c>
       <c r="E135" t="n">
-        <v>17.38044493991689</v>
+        <v>17.38044305713872</v>
       </c>
       <c r="F135" t="n">
         <v>710000</v>
@@ -3132,16 +3132,16 @@
         <v>44295</v>
       </c>
       <c r="B136" t="n">
-        <v>18.03420639038086</v>
+        <v>18.03421020507812</v>
       </c>
       <c r="C136" t="n">
-        <v>18.25657638704782</v>
+        <v>18.25658024878204</v>
       </c>
       <c r="D136" t="n">
-        <v>17.41157141764243</v>
+        <v>17.41157510063643</v>
       </c>
       <c r="E136" t="n">
-        <v>17.64283472121344</v>
+        <v>17.64283845312556</v>
       </c>
       <c r="F136" t="n">
         <v>1023600</v>
@@ -3152,16 +3152,16 @@
         <v>44298</v>
       </c>
       <c r="B137" t="n">
-        <v>17.7451286315918</v>
+        <v>17.74513244628906</v>
       </c>
       <c r="C137" t="n">
-        <v>18.05644530861555</v>
+        <v>18.05644919023704</v>
       </c>
       <c r="D137" t="n">
-        <v>17.58946859653127</v>
+        <v>17.58947237776606</v>
       </c>
       <c r="E137" t="n">
-        <v>18.05644530861555</v>
+        <v>18.05644919023704</v>
       </c>
       <c r="F137" t="n">
         <v>810600</v>
@@ -3172,16 +3172,16 @@
         <v>44299</v>
       </c>
       <c r="B138" t="n">
-        <v>17.40712547302246</v>
+        <v>17.40712356567383</v>
       </c>
       <c r="C138" t="n">
-        <v>17.74068051411476</v>
+        <v>17.74067857021755</v>
       </c>
       <c r="D138" t="n">
-        <v>17.20254545499086</v>
+        <v>17.20254357005865</v>
       </c>
       <c r="E138" t="n">
-        <v>17.74068051411476</v>
+        <v>17.74067857021755</v>
       </c>
       <c r="F138" t="n">
         <v>699800</v>
@@ -3192,16 +3192,16 @@
         <v>44300</v>
       </c>
       <c r="B139" t="n">
-        <v>17.16252136230469</v>
+        <v>17.16251945495605</v>
       </c>
       <c r="C139" t="n">
-        <v>17.71399985963123</v>
+        <v>17.71399789099429</v>
       </c>
       <c r="D139" t="n">
-        <v>17.07802134994895</v>
+        <v>17.07801945199119</v>
       </c>
       <c r="E139" t="n">
-        <v>17.37154976237547</v>
+        <v>17.37154783179656</v>
       </c>
       <c r="F139" t="n">
         <v>861200</v>
@@ -3232,16 +3232,16 @@
         <v>44302</v>
       </c>
       <c r="B141" t="n">
-        <v>17.7451286315918</v>
+        <v>17.74513244628906</v>
       </c>
       <c r="C141" t="n">
-        <v>17.7451286315918</v>
+        <v>17.74513244628906</v>
       </c>
       <c r="D141" t="n">
-        <v>17.12249188444699</v>
+        <v>17.12249556529509</v>
       </c>
       <c r="E141" t="n">
-        <v>17.38488858118748</v>
+        <v>17.38489231844339</v>
       </c>
       <c r="F141" t="n">
         <v>774600</v>
@@ -3252,16 +3252,16 @@
         <v>44305</v>
       </c>
       <c r="B142" t="n">
-        <v>18.0119686126709</v>
+        <v>18.0119743347168</v>
       </c>
       <c r="C142" t="n">
-        <v>18.176521924963</v>
+        <v>18.17652769928423</v>
       </c>
       <c r="D142" t="n">
-        <v>17.70065029733976</v>
+        <v>17.70065592048599</v>
       </c>
       <c r="E142" t="n">
-        <v>17.70065029733976</v>
+        <v>17.70065592048599</v>
       </c>
       <c r="F142" t="n">
         <v>952400</v>
@@ -3332,16 +3332,16 @@
         <v>44312</v>
       </c>
       <c r="B146" t="n">
-        <v>17.0869140625</v>
+        <v>17.08691215515137</v>
       </c>
       <c r="C146" t="n">
-        <v>17.31817912126438</v>
+        <v>17.31817718810049</v>
       </c>
       <c r="D146" t="n">
-        <v>16.90012403227619</v>
+        <v>16.90012214577824</v>
       </c>
       <c r="E146" t="n">
-        <v>17.31817912126438</v>
+        <v>17.31817718810049</v>
       </c>
       <c r="F146" t="n">
         <v>836400</v>
@@ -3352,16 +3352,16 @@
         <v>44313</v>
       </c>
       <c r="B147" t="n">
-        <v>17.33596801757812</v>
+        <v>17.33596992492676</v>
       </c>
       <c r="C147" t="n">
-        <v>17.78070809508361</v>
+        <v>17.78071005136372</v>
       </c>
       <c r="D147" t="n">
-        <v>17.01130796458497</v>
+        <v>17.01130983621365</v>
       </c>
       <c r="E147" t="n">
-        <v>17.04688798512881</v>
+        <v>17.0468898606721</v>
       </c>
       <c r="F147" t="n">
         <v>1372600</v>
@@ -3372,16 +3372,16 @@
         <v>44314</v>
       </c>
       <c r="B148" t="n">
-        <v>18.56789588928223</v>
+        <v>18.56789779663086</v>
       </c>
       <c r="C148" t="n">
-        <v>18.63905422482831</v>
+        <v>18.63905613948654</v>
       </c>
       <c r="D148" t="n">
-        <v>17.32707082268309</v>
+        <v>17.32707260257054</v>
       </c>
       <c r="E148" t="n">
-        <v>17.33596582669492</v>
+        <v>17.33596760749609</v>
       </c>
       <c r="F148" t="n">
         <v>2195600</v>
@@ -3432,16 +3432,16 @@
         <v>44319</v>
       </c>
       <c r="B151" t="n">
-        <v>19.44735908508301</v>
+        <v>19.44736099243164</v>
       </c>
       <c r="C151" t="n">
-        <v>19.67089194812994</v>
+        <v>19.67089387740212</v>
       </c>
       <c r="D151" t="n">
-        <v>18.83934942472809</v>
+        <v>18.83935127244465</v>
       </c>
       <c r="E151" t="n">
-        <v>19.62618605768871</v>
+        <v>19.62618798257625</v>
       </c>
       <c r="F151" t="n">
         <v>2225200</v>
@@ -3452,16 +3452,16 @@
         <v>44320</v>
       </c>
       <c r="B152" t="n">
-        <v>19.79606819152832</v>
+        <v>19.79606437683105</v>
       </c>
       <c r="C152" t="n">
-        <v>20.00618961139364</v>
+        <v>20.00618575620603</v>
       </c>
       <c r="D152" t="n">
-        <v>19.25959072829643</v>
+        <v>19.25958701697824</v>
       </c>
       <c r="E152" t="n">
-        <v>19.45182740585503</v>
+        <v>19.45182365749287</v>
       </c>
       <c r="F152" t="n">
         <v>1635200</v>
@@ -3492,16 +3492,16 @@
         <v>44322</v>
       </c>
       <c r="B154" t="n">
-        <v>20.4309024810791</v>
+        <v>20.43090057373047</v>
       </c>
       <c r="C154" t="n">
-        <v>20.65443532724973</v>
+        <v>20.65443339903295</v>
       </c>
       <c r="D154" t="n">
-        <v>20.16266204242219</v>
+        <v>20.16266016011543</v>
       </c>
       <c r="E154" t="n">
-        <v>20.46219694310937</v>
+        <v>20.46219503283921</v>
       </c>
       <c r="F154" t="n">
         <v>1030200</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.83325958251953</v>
+        <v>20.83326148986816</v>
       </c>
       <c r="C155" t="n">
-        <v>20.87796717286325</v>
+        <v>20.877969084305</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384096914172</v>
+        <v>20.36384283351365</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902565479451</v>
+        <v>20.86902756541763</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3532,16 +3532,16 @@
         <v>44326</v>
       </c>
       <c r="B156" t="n">
-        <v>20.36384010314941</v>
+        <v>20.36384201049805</v>
       </c>
       <c r="C156" t="n">
-        <v>20.94502510954077</v>
+        <v>20.94502707132523</v>
       </c>
       <c r="D156" t="n">
-        <v>20.25207369017338</v>
+        <v>20.25207558705358</v>
       </c>
       <c r="E156" t="n">
-        <v>20.83325869656473</v>
+        <v>20.83326064788076</v>
       </c>
       <c r="F156" t="n">
         <v>979800</v>
@@ -3572,16 +3572,16 @@
         <v>44328</v>
       </c>
       <c r="B158" t="n">
-        <v>20.1581916809082</v>
+        <v>20.15819358825684</v>
       </c>
       <c r="C158" t="n">
-        <v>20.59631584486362</v>
+        <v>20.59631779366714</v>
       </c>
       <c r="D158" t="n">
-        <v>19.57253502320829</v>
+        <v>19.57253687514265</v>
       </c>
       <c r="E158" t="n">
-        <v>20.59631584486362</v>
+        <v>20.59631779366714</v>
       </c>
       <c r="F158" t="n">
         <v>1344400</v>
@@ -3612,16 +3612,16 @@
         <v>44330</v>
       </c>
       <c r="B160" t="n">
-        <v>20.29678344726562</v>
+        <v>20.29678153991699</v>
       </c>
       <c r="C160" t="n">
-        <v>21.23562073440818</v>
+        <v>21.23561873883424</v>
       </c>
       <c r="D160" t="n">
-        <v>20.22972291014674</v>
+        <v>20.22972100909998</v>
       </c>
       <c r="E160" t="n">
-        <v>21.01655779118409</v>
+        <v>21.01655581619614</v>
       </c>
       <c r="F160" t="n">
         <v>1009800</v>
@@ -3632,16 +3632,16 @@
         <v>44333</v>
       </c>
       <c r="B161" t="n">
-        <v>20.98526382446289</v>
+        <v>20.98526573181152</v>
       </c>
       <c r="C161" t="n">
-        <v>21.13279632744209</v>
+        <v>21.13279824819994</v>
       </c>
       <c r="D161" t="n">
-        <v>20.03748499628314</v>
+        <v>20.03748681748824</v>
       </c>
       <c r="E161" t="n">
-        <v>20.16266284941433</v>
+        <v>20.16266468199684</v>
       </c>
       <c r="F161" t="n">
         <v>1096800</v>
@@ -3652,16 +3652,16 @@
         <v>44334</v>
       </c>
       <c r="B162" t="n">
-        <v>21.12385368347168</v>
+        <v>21.12385177612305</v>
       </c>
       <c r="C162" t="n">
-        <v>21.74080480825265</v>
+        <v>21.74080284519728</v>
       </c>
       <c r="D162" t="n">
-        <v>20.88243780350257</v>
+        <v>20.88243591795225</v>
       </c>
       <c r="E162" t="n">
-        <v>21.15067823860833</v>
+        <v>21.15067632883762</v>
       </c>
       <c r="F162" t="n">
         <v>1192600</v>
@@ -3692,16 +3692,16 @@
         <v>44336</v>
       </c>
       <c r="B164" t="n">
-        <v>21.86151123046875</v>
+        <v>21.86151313781738</v>
       </c>
       <c r="C164" t="n">
-        <v>21.93751157328245</v>
+        <v>21.93751348726187</v>
       </c>
       <c r="D164" t="n">
-        <v>21.37867950405186</v>
+        <v>21.37868136927493</v>
       </c>
       <c r="E164" t="n">
-        <v>21.49044591789798</v>
+        <v>21.49044779287232</v>
       </c>
       <c r="F164" t="n">
         <v>917400</v>
@@ -3732,16 +3732,16 @@
         <v>44340</v>
       </c>
       <c r="B166" t="n">
-        <v>21.87045288085938</v>
+        <v>21.87045478820801</v>
       </c>
       <c r="C166" t="n">
-        <v>22.12081028286665</v>
+        <v>22.12081221204925</v>
       </c>
       <c r="D166" t="n">
-        <v>21.50385914906818</v>
+        <v>21.50386102444573</v>
       </c>
       <c r="E166" t="n">
-        <v>21.67821620187448</v>
+        <v>21.67821809245792</v>
       </c>
       <c r="F166" t="n">
         <v>900600</v>
@@ -3792,16 +3792,16 @@
         <v>44343</v>
       </c>
       <c r="B169" t="n">
-        <v>22.34434127807617</v>
+        <v>22.3443431854248</v>
       </c>
       <c r="C169" t="n">
-        <v>22.34434127807617</v>
+        <v>22.3443431854248</v>
       </c>
       <c r="D169" t="n">
-        <v>21.80339224371756</v>
+        <v>21.80339410488992</v>
       </c>
       <c r="E169" t="n">
-        <v>22.27281084134627</v>
+        <v>22.27281274258895</v>
       </c>
       <c r="F169" t="n">
         <v>1342400</v>
@@ -3832,16 +3832,16 @@
         <v>44347</v>
       </c>
       <c r="B171" t="n">
-        <v>23.22953033447266</v>
+        <v>23.22953414916992</v>
       </c>
       <c r="C171" t="n">
-        <v>23.22953033447266</v>
+        <v>23.22953414916992</v>
       </c>
       <c r="D171" t="n">
-        <v>22.24151567557218</v>
+        <v>22.24151932802007</v>
       </c>
       <c r="E171" t="n">
-        <v>22.24151567557218</v>
+        <v>22.24151932802007</v>
       </c>
       <c r="F171" t="n">
         <v>1311400</v>
@@ -3912,16 +3912,16 @@
         <v>44354</v>
       </c>
       <c r="B175" t="n">
-        <v>23.51565170288086</v>
+        <v>23.51565551757812</v>
       </c>
       <c r="C175" t="n">
-        <v>23.95377752565332</v>
+        <v>23.95378141142314</v>
       </c>
       <c r="D175" t="n">
-        <v>23.24741300423083</v>
+        <v>23.24741677541455</v>
       </c>
       <c r="E175" t="n">
-        <v>23.56482919556471</v>
+        <v>23.56483301823953</v>
       </c>
       <c r="F175" t="n">
         <v>1060000</v>
@@ -3932,16 +3932,16 @@
         <v>44355</v>
       </c>
       <c r="B176" t="n">
-        <v>23.40388679504395</v>
+        <v>23.40388870239258</v>
       </c>
       <c r="C176" t="n">
-        <v>23.68106873423341</v>
+        <v>23.68107066417156</v>
       </c>
       <c r="D176" t="n">
-        <v>22.95235122542912</v>
+        <v>22.95235309597892</v>
       </c>
       <c r="E176" t="n">
-        <v>23.47094732671691</v>
+        <v>23.47094923953079</v>
       </c>
       <c r="F176" t="n">
         <v>1006800</v>
@@ -3952,16 +3952,16 @@
         <v>44356</v>
       </c>
       <c r="B177" t="n">
-        <v>23.51565170288086</v>
+        <v>23.51565551757812</v>
       </c>
       <c r="C177" t="n">
-        <v>23.60059526494208</v>
+        <v>23.60059909341884</v>
       </c>
       <c r="D177" t="n">
-        <v>23.1803524768583</v>
+        <v>23.18035623716349</v>
       </c>
       <c r="E177" t="n">
-        <v>23.44412126954618</v>
+        <v>23.44412507263982</v>
       </c>
       <c r="F177" t="n">
         <v>621600</v>
@@ -3992,16 +3992,16 @@
         <v>44358</v>
       </c>
       <c r="B179" t="n">
-        <v>23.30553436279297</v>
+        <v>23.3055362701416</v>
       </c>
       <c r="C179" t="n">
-        <v>23.56483157022843</v>
+        <v>23.5648334987982</v>
       </c>
       <c r="D179" t="n">
-        <v>22.55893379079491</v>
+        <v>22.55893563704099</v>
       </c>
       <c r="E179" t="n">
-        <v>23.56483157022843</v>
+        <v>23.5648334987982</v>
       </c>
       <c r="F179" t="n">
         <v>855400</v>
@@ -4012,16 +4012,16 @@
         <v>44361</v>
       </c>
       <c r="B180" t="n">
-        <v>24.58860969543457</v>
+        <v>24.5886116027832</v>
       </c>
       <c r="C180" t="n">
-        <v>24.76743662993302</v>
+        <v>24.76743855115333</v>
       </c>
       <c r="D180" t="n">
-        <v>23.26082422614669</v>
+        <v>23.26082603049845</v>
       </c>
       <c r="E180" t="n">
-        <v>23.45753419517899</v>
+        <v>23.45753601478963</v>
       </c>
       <c r="F180" t="n">
         <v>1774600</v>
@@ -4072,16 +4072,16 @@
         <v>44364</v>
       </c>
       <c r="B183" t="n">
-        <v>24.58860969543457</v>
+        <v>24.5886116027832</v>
       </c>
       <c r="C183" t="n">
-        <v>24.71378752633146</v>
+        <v>24.71378944339019</v>
       </c>
       <c r="D183" t="n">
-        <v>23.96718874145352</v>
+        <v>23.96719060059827</v>
       </c>
       <c r="E183" t="n">
-        <v>24.63331557634916</v>
+        <v>24.63331748716565</v>
       </c>
       <c r="F183" t="n">
         <v>897400</v>
@@ -4092,16 +4092,16 @@
         <v>44365</v>
       </c>
       <c r="B184" t="n">
-        <v>24.8970890045166</v>
+        <v>24.89708518981934</v>
       </c>
       <c r="C184" t="n">
-        <v>25.19215230760862</v>
+        <v>25.19214844770217</v>
       </c>
       <c r="D184" t="n">
-        <v>24.25778489691384</v>
+        <v>24.25778118016986</v>
       </c>
       <c r="E184" t="n">
-        <v>24.6780277596409</v>
+        <v>24.67802397850789</v>
       </c>
       <c r="F184" t="n">
         <v>1737600</v>
@@ -4132,16 +4132,16 @@
         <v>44369</v>
       </c>
       <c r="B186" t="n">
-        <v>24.58860969543457</v>
+        <v>24.5886116027832</v>
       </c>
       <c r="C186" t="n">
-        <v>25.26814965894062</v>
+        <v>25.26815161900145</v>
       </c>
       <c r="D186" t="n">
-        <v>24.54390381451998</v>
+        <v>24.54390571840076</v>
       </c>
       <c r="E186" t="n">
-        <v>25.23238358987291</v>
+        <v>25.23238554715936</v>
       </c>
       <c r="F186" t="n">
         <v>871000</v>
@@ -4192,16 +4192,16 @@
         <v>44372</v>
       </c>
       <c r="B189" t="n">
-        <v>24.3516674041748</v>
+        <v>24.35167121887207</v>
       </c>
       <c r="C189" t="n">
-        <v>24.58861166172607</v>
+        <v>24.58861551354074</v>
       </c>
       <c r="D189" t="n">
-        <v>24.00295502455915</v>
+        <v>24.0029587846305</v>
       </c>
       <c r="E189" t="n">
-        <v>24.27119544775736</v>
+        <v>24.27119924984866</v>
       </c>
       <c r="F189" t="n">
         <v>926400</v>
@@ -4252,16 +4252,16 @@
         <v>44377</v>
       </c>
       <c r="B192" t="n">
-        <v>24.86579513549805</v>
+        <v>24.86579322814941</v>
       </c>
       <c r="C192" t="n">
-        <v>24.86579513549805</v>
+        <v>24.86579322814941</v>
       </c>
       <c r="D192" t="n">
-        <v>24.12813771284097</v>
+        <v>24.12813586207488</v>
       </c>
       <c r="E192" t="n">
-        <v>24.16837369628921</v>
+        <v>24.16837184243678</v>
       </c>
       <c r="F192" t="n">
         <v>1430400</v>
@@ -4312,16 +4312,16 @@
         <v>44382</v>
       </c>
       <c r="B195" t="n">
-        <v>26.53334617614746</v>
+        <v>26.53334808349609</v>
       </c>
       <c r="C195" t="n">
-        <v>26.77923365290268</v>
+        <v>26.77923557792692</v>
       </c>
       <c r="D195" t="n">
-        <v>26.17122408387186</v>
+        <v>26.17122596518936</v>
       </c>
       <c r="E195" t="n">
-        <v>26.38134378388976</v>
+        <v>26.3813456803117</v>
       </c>
       <c r="F195" t="n">
         <v>581600</v>
@@ -4352,16 +4352,16 @@
         <v>44384</v>
       </c>
       <c r="B197" t="n">
-        <v>26.52440643310547</v>
+        <v>26.5244083404541</v>
       </c>
       <c r="C197" t="n">
-        <v>26.93570602180775</v>
+        <v>26.9357079587326</v>
       </c>
       <c r="D197" t="n">
-        <v>26.10863523276678</v>
+        <v>26.10863711021764</v>
       </c>
       <c r="E197" t="n">
-        <v>26.19804700045325</v>
+        <v>26.19804888433364</v>
       </c>
       <c r="F197" t="n">
         <v>915800</v>
@@ -4372,16 +4372,16 @@
         <v>44385</v>
       </c>
       <c r="B198" t="n">
-        <v>26.52440643310547</v>
+        <v>26.5244083404541</v>
       </c>
       <c r="C198" t="n">
-        <v>26.52440643310547</v>
+        <v>26.5244083404541</v>
       </c>
       <c r="D198" t="n">
-        <v>25.82251177774154</v>
+        <v>25.82251363461749</v>
       </c>
       <c r="E198" t="n">
-        <v>26.23828297808023</v>
+        <v>26.23828486485395</v>
       </c>
       <c r="F198" t="n">
         <v>1041800</v>
@@ -4392,16 +4392,16 @@
         <v>44389</v>
       </c>
       <c r="B199" t="n">
-        <v>27.54372024536133</v>
+        <v>27.5437183380127</v>
       </c>
       <c r="C199" t="n">
-        <v>27.57501471042217</v>
+        <v>27.57501280090645</v>
       </c>
       <c r="D199" t="n">
-        <v>26.56911680524263</v>
+        <v>26.56911496538337</v>
       </c>
       <c r="E199" t="n">
-        <v>26.81500261875798</v>
+        <v>26.81500076187162</v>
       </c>
       <c r="F199" t="n">
         <v>886400</v>
@@ -4432,16 +4432,16 @@
         <v>44391</v>
       </c>
       <c r="B201" t="n">
-        <v>28.17407989501953</v>
+        <v>28.17408180236816</v>
       </c>
       <c r="C201" t="n">
-        <v>28.33502381575305</v>
+        <v>28.33502573399738</v>
       </c>
       <c r="D201" t="n">
-        <v>27.44089243871817</v>
+        <v>27.44089429643097</v>
       </c>
       <c r="E201" t="n">
-        <v>27.67336680139767</v>
+        <v>27.67336867484868</v>
       </c>
       <c r="F201" t="n">
         <v>880600</v>
@@ -4452,16 +4452,16 @@
         <v>44392</v>
       </c>
       <c r="B202" t="n">
-        <v>28.47808647155762</v>
+        <v>28.47808456420898</v>
       </c>
       <c r="C202" t="n">
-        <v>28.76420655172373</v>
+        <v>28.76420462521192</v>
       </c>
       <c r="D202" t="n">
-        <v>27.81195780383505</v>
+        <v>27.81195594110106</v>
       </c>
       <c r="E202" t="n">
-        <v>28.21431763070376</v>
+        <v>28.21431574102132</v>
       </c>
       <c r="F202" t="n">
         <v>1015800</v>
@@ -4492,16 +4492,16 @@
         <v>44396</v>
       </c>
       <c r="B204" t="n">
-        <v>28.77314567565918</v>
+        <v>28.77314758300781</v>
       </c>
       <c r="C204" t="n">
-        <v>29.12185633897039</v>
+        <v>29.12185826943477</v>
       </c>
       <c r="D204" t="n">
-        <v>28.02207524281956</v>
+        <v>28.02207710038034</v>
       </c>
       <c r="E204" t="n">
-        <v>28.38419903539513</v>
+        <v>28.3842009169608</v>
       </c>
       <c r="F204" t="n">
         <v>866800</v>
@@ -4512,16 +4512,16 @@
         <v>44397</v>
       </c>
       <c r="B205" t="n">
-        <v>29.39904022216797</v>
+        <v>29.3990421295166</v>
       </c>
       <c r="C205" t="n">
-        <v>29.60469002671871</v>
+        <v>29.60469194740947</v>
       </c>
       <c r="D205" t="n">
-        <v>28.66138116422784</v>
+        <v>28.66138302371869</v>
       </c>
       <c r="E205" t="n">
-        <v>28.84020811931037</v>
+        <v>28.84020999040314</v>
       </c>
       <c r="F205" t="n">
         <v>665800</v>
@@ -4532,16 +4532,16 @@
         <v>44398</v>
       </c>
       <c r="B206" t="n">
-        <v>29.60468864440918</v>
+        <v>29.60469055175781</v>
       </c>
       <c r="C206" t="n">
-        <v>29.78351559114187</v>
+        <v>29.78351751001183</v>
       </c>
       <c r="D206" t="n">
-        <v>29.0592679917526</v>
+        <v>29.05926986396128</v>
       </c>
       <c r="E206" t="n">
-        <v>29.52868830057088</v>
+        <v>29.52869020302303</v>
       </c>
       <c r="F206" t="n">
         <v>1050200</v>
@@ -4552,16 +4552,16 @@
         <v>44399</v>
       </c>
       <c r="B207" t="n">
-        <v>30.17693328857422</v>
+        <v>30.17693519592285</v>
       </c>
       <c r="C207" t="n">
-        <v>30.65082181615548</v>
+        <v>30.65082375345648</v>
       </c>
       <c r="D207" t="n">
-        <v>29.62257280245648</v>
+        <v>29.62257467476647</v>
       </c>
       <c r="E207" t="n">
-        <v>29.69410153735533</v>
+        <v>29.69410341418633</v>
       </c>
       <c r="F207" t="n">
         <v>1168200</v>
@@ -4592,16 +4592,16 @@
         <v>44403</v>
       </c>
       <c r="B209" t="n">
-        <v>30.08752059936523</v>
+        <v>30.08752250671387</v>
       </c>
       <c r="C209" t="n">
-        <v>30.48987696893258</v>
+        <v>30.48987890178793</v>
       </c>
       <c r="D209" t="n">
-        <v>29.56445117941508</v>
+        <v>29.56445305360459</v>
       </c>
       <c r="E209" t="n">
-        <v>30.48987696893258</v>
+        <v>30.48987890178793</v>
       </c>
       <c r="F209" t="n">
         <v>1240800</v>
@@ -4652,16 +4652,16 @@
         <v>44406</v>
       </c>
       <c r="B212" t="n">
-        <v>30.84753227233887</v>
+        <v>30.84753608703613</v>
       </c>
       <c r="C212" t="n">
-        <v>31.51365918811201</v>
+        <v>31.5136630851845</v>
       </c>
       <c r="D212" t="n">
-        <v>29.56445252818104</v>
+        <v>29.56445618420886</v>
       </c>
       <c r="E212" t="n">
-        <v>29.56445252818104</v>
+        <v>29.56445618420886</v>
       </c>
       <c r="F212" t="n">
         <v>1386000</v>
@@ -4672,16 +4672,16 @@
         <v>44407</v>
       </c>
       <c r="B213" t="n">
-        <v>31.13812446594238</v>
+        <v>31.13812828063965</v>
       </c>
       <c r="C213" t="n">
-        <v>31.58071852233474</v>
+        <v>31.58072239125372</v>
       </c>
       <c r="D213" t="n">
-        <v>30.41387685570368</v>
+        <v>30.41388058167417</v>
       </c>
       <c r="E213" t="n">
-        <v>30.80282521486082</v>
+        <v>30.80282898848094</v>
       </c>
       <c r="F213" t="n">
         <v>1548200</v>
@@ -4692,16 +4692,16 @@
         <v>44410</v>
       </c>
       <c r="B214" t="n">
-        <v>31.2498893737793</v>
+        <v>31.24989318847656</v>
       </c>
       <c r="C214" t="n">
-        <v>31.98754837270211</v>
+        <v>31.98755227744596</v>
       </c>
       <c r="D214" t="n">
-        <v>31.03976797418139</v>
+        <v>31.03977176322897</v>
       </c>
       <c r="E214" t="n">
-        <v>31.5807169971674</v>
+        <v>31.58072085224903</v>
       </c>
       <c r="F214" t="n">
         <v>1185600</v>
@@ -4712,16 +4712,16 @@
         <v>44411</v>
       </c>
       <c r="B215" t="n">
-        <v>30.62399673461914</v>
+        <v>30.62400054931641</v>
       </c>
       <c r="C215" t="n">
-        <v>31.14259452090504</v>
+        <v>31.14259840020176</v>
       </c>
       <c r="D215" t="n">
-        <v>30.20375393613507</v>
+        <v>30.20375769848453</v>
       </c>
       <c r="E215" t="n">
-        <v>31.13812290941217</v>
+        <v>31.13812678815189</v>
       </c>
       <c r="F215" t="n">
         <v>1467200</v>
@@ -4732,16 +4732,16 @@
         <v>44412</v>
       </c>
       <c r="B216" t="n">
-        <v>29.78798675537109</v>
+        <v>29.78798484802246</v>
       </c>
       <c r="C216" t="n">
-        <v>30.84753370622673</v>
+        <v>30.84753173103446</v>
       </c>
       <c r="D216" t="n">
-        <v>29.7566922923926</v>
+        <v>29.75669038704778</v>
       </c>
       <c r="E216" t="n">
-        <v>30.62400085328306</v>
+        <v>30.62399889240378</v>
       </c>
       <c r="F216" t="n">
         <v>1263400</v>
@@ -4752,16 +4752,16 @@
         <v>44413</v>
       </c>
       <c r="B217" t="n">
-        <v>29.48398017883301</v>
+        <v>29.48398399353027</v>
       </c>
       <c r="C217" t="n">
-        <v>30.38705476088549</v>
+        <v>30.38705869242438</v>
       </c>
       <c r="D217" t="n">
-        <v>29.13974110661963</v>
+        <v>29.13974487677855</v>
       </c>
       <c r="E217" t="n">
-        <v>29.82375105005952</v>
+        <v>29.82375490871703</v>
       </c>
       <c r="F217" t="n">
         <v>1197200</v>
@@ -4772,16 +4772,16 @@
         <v>44414</v>
       </c>
       <c r="B218" t="n">
-        <v>29.46163177490234</v>
+        <v>29.46162986755371</v>
       </c>
       <c r="C218" t="n">
-        <v>29.99810927720156</v>
+        <v>29.99810733512132</v>
       </c>
       <c r="D218" t="n">
-        <v>29.10397783280902</v>
+        <v>29.10397594861493</v>
       </c>
       <c r="E218" t="n">
-        <v>29.97575803759621</v>
+        <v>29.975756096963</v>
       </c>
       <c r="F218" t="n">
         <v>684400</v>
@@ -4792,16 +4792,16 @@
         <v>44417</v>
       </c>
       <c r="B219" t="n">
-        <v>30.23952293395996</v>
+        <v>30.23952484130859</v>
       </c>
       <c r="C219" t="n">
-        <v>30.40493846680823</v>
+        <v>30.4049403845904</v>
       </c>
       <c r="D219" t="n">
-        <v>29.5421015505228</v>
+        <v>29.54210341388179</v>
       </c>
       <c r="E219" t="n">
-        <v>29.85951778044203</v>
+        <v>29.85951966382196</v>
       </c>
       <c r="F219" t="n">
         <v>1023000</v>
@@ -4832,16 +4832,16 @@
         <v>44419</v>
       </c>
       <c r="B221" t="n">
-        <v>29.1129207611084</v>
+        <v>29.11291885375977</v>
       </c>
       <c r="C221" t="n">
-        <v>30.38258576202377</v>
+        <v>30.38258377149235</v>
       </c>
       <c r="D221" t="n">
-        <v>28.14725717378623</v>
+        <v>28.14725532970356</v>
       </c>
       <c r="E221" t="n">
-        <v>29.68516433396269</v>
+        <v>29.68516238912321</v>
       </c>
       <c r="F221" t="n">
         <v>1237750</v>
@@ -4852,16 +4852,16 @@
         <v>44420</v>
       </c>
       <c r="B222" t="n">
-        <v>29.32750701904297</v>
+        <v>29.32750511169434</v>
       </c>
       <c r="C222" t="n">
-        <v>31.18730182754265</v>
+        <v>31.18729979924009</v>
       </c>
       <c r="D222" t="n">
-        <v>28.46914175858482</v>
+        <v>28.46913990706097</v>
       </c>
       <c r="E222" t="n">
-        <v>28.48702479453274</v>
+        <v>28.48702294184585</v>
       </c>
       <c r="F222" t="n">
         <v>1567750</v>
@@ -4872,16 +4872,16 @@
         <v>44421</v>
       </c>
       <c r="B223" t="n">
-        <v>28.34396362304688</v>
+        <v>28.34396553039551</v>
       </c>
       <c r="C223" t="n">
-        <v>29.59574542882125</v>
+        <v>29.59574742040596</v>
       </c>
       <c r="D223" t="n">
-        <v>27.18159187982183</v>
+        <v>27.18159370895106</v>
       </c>
       <c r="E223" t="n">
-        <v>29.50633366085176</v>
+        <v>29.50633564641969</v>
       </c>
       <c r="F223" t="n">
         <v>1962050</v>
@@ -4892,16 +4892,16 @@
         <v>44424</v>
       </c>
       <c r="B224" t="n">
-        <v>25.64369010925293</v>
+        <v>25.6436882019043</v>
       </c>
       <c r="C224" t="n">
-        <v>28.14725747247807</v>
+        <v>28.14725537891694</v>
       </c>
       <c r="D224" t="n">
-        <v>24.26672686568483</v>
+        <v>24.26672506075316</v>
       </c>
       <c r="E224" t="n">
-        <v>28.14725747247807</v>
+        <v>28.14725537891694</v>
       </c>
       <c r="F224" t="n">
         <v>6674400</v>
@@ -4912,16 +4912,16 @@
         <v>44425</v>
       </c>
       <c r="B225" t="n">
-        <v>25.66157150268555</v>
+        <v>25.66156959533691</v>
       </c>
       <c r="C225" t="n">
-        <v>25.66157150268555</v>
+        <v>25.66156959533691</v>
       </c>
       <c r="D225" t="n">
-        <v>23.42624303399936</v>
+        <v>23.42624129279607</v>
       </c>
       <c r="E225" t="n">
-        <v>24.67802663537957</v>
+        <v>24.67802480113491</v>
       </c>
       <c r="F225" t="n">
         <v>4282800</v>
@@ -4932,16 +4932,16 @@
         <v>44426</v>
       </c>
       <c r="B226" t="n">
-        <v>25.7509822845459</v>
+        <v>25.75098419189453</v>
       </c>
       <c r="C226" t="n">
-        <v>26.43052231748461</v>
+        <v>26.43052427516607</v>
       </c>
       <c r="D226" t="n">
-        <v>24.89261700425713</v>
+        <v>24.89261884802754</v>
       </c>
       <c r="E226" t="n">
-        <v>25.39333008442558</v>
+        <v>25.39333196528328</v>
       </c>
       <c r="F226" t="n">
         <v>2048900</v>
@@ -4952,16 +4952,16 @@
         <v>44427</v>
       </c>
       <c r="B227" t="n">
-        <v>26.46628952026367</v>
+        <v>26.4662914276123</v>
       </c>
       <c r="C227" t="n">
-        <v>26.73452825545211</v>
+        <v>26.73453018213193</v>
       </c>
       <c r="D227" t="n">
-        <v>24.30249148537069</v>
+        <v>24.30249323678068</v>
       </c>
       <c r="E227" t="n">
-        <v>24.8568519928722</v>
+        <v>24.85685378423334</v>
       </c>
       <c r="F227" t="n">
         <v>1738450</v>
@@ -4992,16 +4992,16 @@
         <v>44431</v>
       </c>
       <c r="B229" t="n">
-        <v>26.85970687866211</v>
+        <v>26.85970878601074</v>
       </c>
       <c r="C229" t="n">
-        <v>27.41406736694361</v>
+        <v>27.41406931365822</v>
       </c>
       <c r="D229" t="n">
-        <v>26.28746164845576</v>
+        <v>26.28746351516839</v>
       </c>
       <c r="E229" t="n">
-        <v>26.71664429204535</v>
+        <v>26.71664618923489</v>
       </c>
       <c r="F229" t="n">
         <v>1094150</v>
@@ -5012,16 +5012,16 @@
         <v>44432</v>
       </c>
       <c r="B230" t="n">
-        <v>27.48559951782227</v>
+        <v>27.48559761047363</v>
       </c>
       <c r="C230" t="n">
-        <v>27.84325174306836</v>
+        <v>27.84324981090064</v>
       </c>
       <c r="D230" t="n">
-        <v>27.00276944009512</v>
+        <v>27.00276756625223</v>
       </c>
       <c r="E230" t="n">
-        <v>27.64654344553809</v>
+        <v>27.64654152702084</v>
       </c>
       <c r="F230" t="n">
         <v>835550</v>
@@ -5032,16 +5032,16 @@
         <v>44433</v>
       </c>
       <c r="B231" t="n">
-        <v>27.89690208435059</v>
+        <v>27.89690017700195</v>
       </c>
       <c r="C231" t="n">
-        <v>28.4154982601487</v>
+        <v>28.41549631734295</v>
       </c>
       <c r="D231" t="n">
-        <v>27.27100938354371</v>
+        <v>27.27100751898821</v>
       </c>
       <c r="E231" t="n">
-        <v>27.48560072814082</v>
+        <v>27.48559884891342</v>
       </c>
       <c r="F231" t="n">
         <v>1098800</v>
@@ -5072,16 +5072,16 @@
         <v>44435</v>
       </c>
       <c r="B233" t="n">
-        <v>28.96985816955566</v>
+        <v>28.96985626220703</v>
       </c>
       <c r="C233" t="n">
-        <v>29.11291905438238</v>
+        <v>29.11291713761476</v>
       </c>
       <c r="D233" t="n">
-        <v>27.00276844505784</v>
+        <v>27.00276666722057</v>
       </c>
       <c r="E233" t="n">
-        <v>27.44983413649641</v>
+        <v>27.44983232922475</v>
       </c>
       <c r="F233" t="n">
         <v>1634000</v>
@@ -5112,16 +5112,16 @@
         <v>44439</v>
       </c>
       <c r="B235" t="n">
-        <v>26.55570030212402</v>
+        <v>26.55570220947266</v>
       </c>
       <c r="C235" t="n">
-        <v>27.86113118201179</v>
+        <v>27.86113318312228</v>
       </c>
       <c r="D235" t="n">
-        <v>25.87616030921885</v>
+        <v>25.87616216775989</v>
       </c>
       <c r="E235" t="n">
-        <v>27.6823042397767</v>
+        <v>27.68230622804304</v>
       </c>
       <c r="F235" t="n">
         <v>1705500</v>
@@ -5152,16 +5152,16 @@
         <v>44441</v>
       </c>
       <c r="B237" t="n">
-        <v>25.35756874084473</v>
+        <v>25.35756492614746</v>
       </c>
       <c r="C237" t="n">
-        <v>26.6629998533029</v>
+        <v>26.66299584222149</v>
       </c>
       <c r="D237" t="n">
-        <v>25.10721131819694</v>
+        <v>25.10720754116251</v>
       </c>
       <c r="E237" t="n">
-        <v>26.59146940474931</v>
+        <v>26.59146540442867</v>
       </c>
       <c r="F237" t="n">
         <v>1706000</v>
@@ -5212,16 +5212,16 @@
         <v>44447</v>
       </c>
       <c r="B240" t="n">
-        <v>24.48131561279297</v>
+        <v>24.4813175201416</v>
       </c>
       <c r="C240" t="n">
-        <v>26.10863610235777</v>
+        <v>26.10863813649156</v>
       </c>
       <c r="D240" t="n">
-        <v>24.32037340234477</v>
+        <v>24.32037529715434</v>
       </c>
       <c r="E240" t="n">
-        <v>25.59003998757081</v>
+        <v>25.59004198130058</v>
       </c>
       <c r="F240" t="n">
         <v>1259500</v>
@@ -5252,16 +5252,16 @@
         <v>44449</v>
       </c>
       <c r="B242" t="n">
-        <v>25.19661903381348</v>
+        <v>25.19662284851074</v>
       </c>
       <c r="C242" t="n">
-        <v>26.19804508418138</v>
+        <v>26.19804905049173</v>
       </c>
       <c r="D242" t="n">
-        <v>24.64225690543765</v>
+        <v>24.64226063620605</v>
       </c>
       <c r="E242" t="n">
-        <v>26.00133682207126</v>
+        <v>26.00134075860054</v>
       </c>
       <c r="F242" t="n">
         <v>1514650</v>
@@ -5272,16 +5272,16 @@
         <v>44452</v>
       </c>
       <c r="B243" t="n">
-        <v>26.48417282104492</v>
+        <v>26.48417472839355</v>
       </c>
       <c r="C243" t="n">
-        <v>26.82394200269411</v>
+        <v>26.82394393451239</v>
       </c>
       <c r="D243" t="n">
-        <v>25.16085705279258</v>
+        <v>25.16085886483809</v>
       </c>
       <c r="E243" t="n">
-        <v>25.3754483841637</v>
+        <v>25.37545021166373</v>
       </c>
       <c r="F243" t="n">
         <v>1238850</v>
@@ -5292,16 +5292,16 @@
         <v>44453</v>
       </c>
       <c r="B244" t="n">
-        <v>26.34111213684082</v>
+        <v>26.34111022949219</v>
       </c>
       <c r="C244" t="n">
-        <v>27.02065225480208</v>
+        <v>27.02065029824824</v>
       </c>
       <c r="D244" t="n">
-        <v>25.84039899402426</v>
+        <v>25.84039712293205</v>
       </c>
       <c r="E244" t="n">
-        <v>26.60935259955787</v>
+        <v>26.60935067278606</v>
       </c>
       <c r="F244" t="n">
         <v>937200</v>
@@ -5332,16 +5332,16 @@
         <v>44455</v>
       </c>
       <c r="B246" t="n">
-        <v>25.7509822845459</v>
+        <v>25.75098419189453</v>
       </c>
       <c r="C246" t="n">
-        <v>26.66299667391787</v>
+        <v>26.66299864881847</v>
       </c>
       <c r="D246" t="n">
-        <v>25.73310095360504</v>
+        <v>25.73310285962922</v>
       </c>
       <c r="E246" t="n">
-        <v>26.16228359374943</v>
+        <v>26.16228553156272</v>
       </c>
       <c r="F246" t="n">
         <v>615650</v>
@@ -5392,16 +5392,16 @@
         <v>44460</v>
       </c>
       <c r="B249" t="n">
-        <v>25.07144546508789</v>
+        <v>25.07144355773926</v>
       </c>
       <c r="C249" t="n">
-        <v>25.19662331630446</v>
+        <v>25.19662139943273</v>
       </c>
       <c r="D249" t="n">
-        <v>24.05213450165763</v>
+        <v>24.05213267185464</v>
       </c>
       <c r="E249" t="n">
-        <v>24.57073064938097</v>
+        <v>24.57072878012499</v>
       </c>
       <c r="F249" t="n">
         <v>662000</v>
@@ -5412,16 +5412,16 @@
         <v>44461</v>
       </c>
       <c r="B250" t="n">
-        <v>25.48274612426758</v>
+        <v>25.48274230957031</v>
       </c>
       <c r="C250" t="n">
-        <v>26.37687756722434</v>
+        <v>26.37687361867804</v>
       </c>
       <c r="D250" t="n">
-        <v>25.23238870628835</v>
+        <v>25.2323849290689</v>
       </c>
       <c r="E250" t="n">
-        <v>25.92981184574596</v>
+        <v>25.92980796412418</v>
       </c>
       <c r="F250" t="n">
         <v>900000</v>
@@ -5432,16 +5432,16 @@
         <v>44462</v>
       </c>
       <c r="B251" t="n">
-        <v>26.28746032714844</v>
+        <v>26.28746223449707</v>
       </c>
       <c r="C251" t="n">
-        <v>26.69876161898007</v>
+        <v>26.69876355617164</v>
       </c>
       <c r="D251" t="n">
-        <v>25.32179857489956</v>
+        <v>25.32180041218233</v>
       </c>
       <c r="E251" t="n">
-        <v>25.32179857489956</v>
+        <v>25.32180041218233</v>
       </c>
       <c r="F251" t="n">
         <v>1394250</v>
@@ -5452,16 +5452,16 @@
         <v>44463</v>
       </c>
       <c r="B252" t="n">
-        <v>25.89404296875</v>
+        <v>25.89404487609863</v>
       </c>
       <c r="C252" t="n">
-        <v>26.19804776290805</v>
+        <v>26.1980496926496</v>
       </c>
       <c r="D252" t="n">
-        <v>25.39332989236859</v>
+        <v>25.39333176283482</v>
       </c>
       <c r="E252" t="n">
-        <v>26.19804776290805</v>
+        <v>26.1980496926496</v>
       </c>
       <c r="F252" t="n">
         <v>1097400</v>
@@ -5492,16 +5492,16 @@
         <v>44467</v>
       </c>
       <c r="B254" t="n">
-        <v>24.83896827697754</v>
+        <v>24.83897018432617</v>
       </c>
       <c r="C254" t="n">
-        <v>25.80463001855441</v>
+        <v>25.80463200005482</v>
       </c>
       <c r="D254" t="n">
-        <v>24.44555002509952</v>
+        <v>24.44555190223813</v>
       </c>
       <c r="E254" t="n">
-        <v>25.75098091233005</v>
+        <v>25.75098288971082</v>
       </c>
       <c r="F254" t="n">
         <v>1020250</v>
@@ -5512,16 +5512,16 @@
         <v>44468</v>
       </c>
       <c r="B255" t="n">
-        <v>24.67802429199219</v>
+        <v>24.67802810668945</v>
       </c>
       <c r="C255" t="n">
-        <v>25.39332865187945</v>
+        <v>25.39333257714754</v>
       </c>
       <c r="D255" t="n">
-        <v>24.46343298402601</v>
+        <v>24.46343676555203</v>
       </c>
       <c r="E255" t="n">
-        <v>25.10720690792455</v>
+        <v>25.10721078896431</v>
       </c>
       <c r="F255" t="n">
         <v>580300</v>
@@ -5572,16 +5572,16 @@
         <v>44473</v>
       </c>
       <c r="B258" t="n">
-        <v>23.8733081817627</v>
+        <v>23.87331008911133</v>
       </c>
       <c r="C258" t="n">
-        <v>25.10720871787369</v>
+        <v>25.10721072380433</v>
       </c>
       <c r="D258" t="n">
-        <v>23.8733081817627</v>
+        <v>23.87331008911133</v>
       </c>
       <c r="E258" t="n">
-        <v>25.01779524008704</v>
+        <v>25.01779723887402</v>
       </c>
       <c r="F258" t="n">
         <v>576500</v>
@@ -5592,16 +5592,16 @@
         <v>44474</v>
       </c>
       <c r="B259" t="n">
-        <v>23.40835952758789</v>
+        <v>23.40836143493652</v>
       </c>
       <c r="C259" t="n">
-        <v>23.98060305836301</v>
+        <v>23.98060501233891</v>
       </c>
       <c r="D259" t="n">
-        <v>23.08647168881676</v>
+        <v>23.08647356993749</v>
       </c>
       <c r="E259" t="n">
-        <v>23.90907261701612</v>
+        <v>23.90907456516361</v>
       </c>
       <c r="F259" t="n">
         <v>1237200</v>
@@ -5632,16 +5632,16 @@
         <v>44476</v>
       </c>
       <c r="B261" t="n">
-        <v>23.62294960021973</v>
+        <v>23.62295150756836</v>
       </c>
       <c r="C261" t="n">
-        <v>24.26672353823827</v>
+        <v>24.26672549756607</v>
       </c>
       <c r="D261" t="n">
-        <v>23.42624132329132</v>
+        <v>23.42624321475746</v>
       </c>
       <c r="E261" t="n">
-        <v>24.15942873461192</v>
+        <v>24.1594306852766</v>
       </c>
       <c r="F261" t="n">
         <v>699850</v>
@@ -5652,16 +5652,16 @@
         <v>44477</v>
       </c>
       <c r="B262" t="n">
-        <v>24.05213165283203</v>
+        <v>24.05213356018066</v>
       </c>
       <c r="C262" t="n">
-        <v>24.53496337391379</v>
+        <v>24.53496531955127</v>
       </c>
       <c r="D262" t="n">
-        <v>23.69447947356042</v>
+        <v>23.69448135254702</v>
       </c>
       <c r="E262" t="n">
-        <v>23.81965730995046</v>
+        <v>23.81965919886374</v>
       </c>
       <c r="F262" t="n">
         <v>982950</v>
@@ -5672,16 +5672,16 @@
         <v>44480</v>
       </c>
       <c r="B263" t="n">
-        <v>24.08789825439453</v>
+        <v>24.0879020690918</v>
       </c>
       <c r="C263" t="n">
-        <v>24.60649435212385</v>
+        <v>24.60649824894896</v>
       </c>
       <c r="D263" t="n">
-        <v>23.73024606723985</v>
+        <v>23.73024982529728</v>
       </c>
       <c r="E263" t="n">
-        <v>24.03424914725622</v>
+        <v>24.0342529534573</v>
       </c>
       <c r="F263" t="n">
         <v>770500</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35613632202148</v>
+        <v>24.35613822937012</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991024181488</v>
+        <v>24.99991219957796</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848414435849</v>
+        <v>23.99848602369909</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307545095629</v>
+        <v>24.21307734710171</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5712,16 +5712,16 @@
         <v>44483</v>
       </c>
       <c r="B265" t="n">
-        <v>24.3740234375</v>
+        <v>24.37402153015137</v>
       </c>
       <c r="C265" t="n">
-        <v>24.9105026465118</v>
+        <v>24.91050069718188</v>
       </c>
       <c r="D265" t="n">
-        <v>23.9269577142269</v>
+        <v>23.92695584186265</v>
       </c>
       <c r="E265" t="n">
-        <v>24.51708433251376</v>
+        <v>24.51708241397014</v>
       </c>
       <c r="F265" t="n">
         <v>635500</v>
@@ -5752,16 +5752,16 @@
         <v>44487</v>
       </c>
       <c r="B267" t="n">
-        <v>26.28746032714844</v>
+        <v>26.28746223449707</v>
       </c>
       <c r="C267" t="n">
-        <v>27.37830162321745</v>
+        <v>27.37830360971465</v>
       </c>
       <c r="D267" t="n">
-        <v>25.69733379551969</v>
+        <v>25.6973356600503</v>
       </c>
       <c r="E267" t="n">
-        <v>26.60934814637144</v>
+        <v>26.6093500770754</v>
       </c>
       <c r="F267" t="n">
         <v>1715900</v>
@@ -5792,16 +5792,16 @@
         <v>44489</v>
       </c>
       <c r="B269" t="n">
-        <v>23.89118957519531</v>
+        <v>23.89119148254395</v>
       </c>
       <c r="C269" t="n">
-        <v>24.94626486390061</v>
+        <v>24.94626685548099</v>
       </c>
       <c r="D269" t="n">
-        <v>23.19376819856792</v>
+        <v>23.19377005023805</v>
       </c>
       <c r="E269" t="n">
-        <v>24.85685138588114</v>
+        <v>24.8568533703232</v>
       </c>
       <c r="F269" t="n">
         <v>1327650</v>
@@ -5832,16 +5832,16 @@
         <v>44491</v>
       </c>
       <c r="B271" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="C271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563060373434</v>
       </c>
       <c r="D271" t="n">
-        <v>19.81395151866856</v>
+        <v>19.81394972618147</v>
       </c>
       <c r="E271" t="n">
-        <v>21.99563259358919</v>
+        <v>21.99563060373434</v>
       </c>
       <c r="F271" t="n">
         <v>3185950</v>
@@ -5872,16 +5872,16 @@
         <v>44495</v>
       </c>
       <c r="B273" t="n">
-        <v>20.29678344726562</v>
+        <v>20.29678153991699</v>
       </c>
       <c r="C273" t="n">
-        <v>21.53068402797473</v>
+        <v>21.53068200467281</v>
       </c>
       <c r="D273" t="n">
-        <v>20.17160389167173</v>
+        <v>20.17160199608659</v>
       </c>
       <c r="E273" t="n">
-        <v>21.45915358424406</v>
+        <v>21.45915156766407</v>
       </c>
       <c r="F273" t="n">
         <v>1532000</v>
@@ -5892,16 +5892,16 @@
         <v>44496</v>
       </c>
       <c r="B274" t="n">
-        <v>20.49349212646484</v>
+        <v>20.49348831176758</v>
       </c>
       <c r="C274" t="n">
-        <v>21.10150176231677</v>
+        <v>21.10149783444344</v>
       </c>
       <c r="D274" t="n">
-        <v>20.31466516106592</v>
+        <v>20.31466137965585</v>
       </c>
       <c r="E274" t="n">
-        <v>20.42196168138934</v>
+        <v>20.42195788000689</v>
       </c>
       <c r="F274" t="n">
         <v>1013650</v>
@@ -5912,16 +5912,16 @@
         <v>44497</v>
       </c>
       <c r="B275" t="n">
-        <v>19.29535484313965</v>
+        <v>19.29535675048828</v>
       </c>
       <c r="C275" t="n">
-        <v>20.76172974015886</v>
+        <v>20.76173179245886</v>
       </c>
       <c r="D275" t="n">
-        <v>19.29535484313965</v>
+        <v>19.29535675048828</v>
       </c>
       <c r="E275" t="n">
-        <v>20.74384840892759</v>
+        <v>20.74385045946002</v>
       </c>
       <c r="F275" t="n">
         <v>1280700</v>
@@ -5932,16 +5932,16 @@
         <v>44498</v>
       </c>
       <c r="B276" t="n">
-        <v>18.3296947479248</v>
+        <v>18.32969284057617</v>
       </c>
       <c r="C276" t="n">
-        <v>20.52925729907399</v>
+        <v>20.52925516284361</v>
       </c>
       <c r="D276" t="n">
-        <v>18.0972203659836</v>
+        <v>18.09721848282576</v>
       </c>
       <c r="E276" t="n">
-        <v>20.2431355075834</v>
+        <v>20.24313340112624</v>
       </c>
       <c r="F276" t="n">
         <v>3577000</v>
@@ -6052,16 +6052,16 @@
         <v>44509</v>
       </c>
       <c r="B282" t="n">
-        <v>20.67231941223145</v>
+        <v>20.67231750488281</v>
       </c>
       <c r="C282" t="n">
-        <v>21.36974083617073</v>
+        <v>21.36973886447393</v>
       </c>
       <c r="D282" t="n">
-        <v>20.29678414341015</v>
+        <v>20.29678227071059</v>
       </c>
       <c r="E282" t="n">
-        <v>20.29678414341015</v>
+        <v>20.29678227071059</v>
       </c>
       <c r="F282" t="n">
         <v>912150</v>
@@ -6072,16 +6072,16 @@
         <v>44510</v>
       </c>
       <c r="B283" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="C283" t="n">
-        <v>21.65586170945009</v>
+        <v>21.65585975033293</v>
       </c>
       <c r="D283" t="n">
-        <v>20.49349158152647</v>
+        <v>20.49348972756417</v>
       </c>
       <c r="E283" t="n">
-        <v>20.88690987169059</v>
+        <v>20.88690798213735</v>
       </c>
       <c r="F283" t="n">
         <v>1309800</v>
@@ -6112,16 +6112,16 @@
         <v>44512</v>
       </c>
       <c r="B285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="C285" t="n">
-        <v>22.12081044278765</v>
+        <v>22.12080844160848</v>
       </c>
       <c r="D285" t="n">
-        <v>21.0836181640625</v>
+        <v>21.08361625671387</v>
       </c>
       <c r="E285" t="n">
-        <v>21.76315822692041</v>
+        <v>21.76315625809657</v>
       </c>
       <c r="F285" t="n">
         <v>1307150</v>
@@ -6132,16 +6132,16 @@
         <v>44516</v>
       </c>
       <c r="B286" t="n">
-        <v>20.63655281066895</v>
+        <v>20.63655090332031</v>
       </c>
       <c r="C286" t="n">
-        <v>21.87045340226245</v>
+        <v>21.87045138086964</v>
       </c>
       <c r="D286" t="n">
-        <v>19.77818747832918</v>
+        <v>19.77818565031559</v>
       </c>
       <c r="E286" t="n">
-        <v>21.76315858843013</v>
+        <v>21.76315657695413</v>
       </c>
       <c r="F286" t="n">
         <v>1709550</v>
@@ -6152,16 +6152,16 @@
         <v>44517</v>
       </c>
       <c r="B287" t="n">
-        <v>19.99277687072754</v>
+        <v>19.99277877807617</v>
       </c>
       <c r="C287" t="n">
-        <v>20.92267255716455</v>
+        <v>20.92267455322699</v>
       </c>
       <c r="D287" t="n">
-        <v>19.59935861221719</v>
+        <v>19.59936048203298</v>
       </c>
       <c r="E287" t="n">
-        <v>20.40407645952734</v>
+        <v>20.40407840611472</v>
       </c>
       <c r="F287" t="n">
         <v>1179650</v>
@@ -6172,16 +6172,16 @@
         <v>44518</v>
       </c>
       <c r="B288" t="n">
-        <v>20.33254814147949</v>
+        <v>20.33254623413086</v>
       </c>
       <c r="C288" t="n">
-        <v>20.7080834034243</v>
+        <v>20.70808146084758</v>
       </c>
       <c r="D288" t="n">
-        <v>19.68877413761139</v>
+        <v>19.68877229065369</v>
       </c>
       <c r="E288" t="n">
-        <v>19.68877413761139</v>
+        <v>19.68877229065369</v>
       </c>
       <c r="F288" t="n">
         <v>766850</v>
@@ -6192,16 +6192,16 @@
         <v>44519</v>
       </c>
       <c r="B289" t="n">
-        <v>20.99420547485352</v>
+        <v>20.99420356750488</v>
       </c>
       <c r="C289" t="n">
-        <v>21.24456288810481</v>
+        <v>21.24456095801091</v>
       </c>
       <c r="D289" t="n">
-        <v>20.11795708660452</v>
+        <v>20.11795525886409</v>
       </c>
       <c r="E289" t="n">
-        <v>20.31466538638888</v>
+        <v>20.31466354077727</v>
       </c>
       <c r="F289" t="n">
         <v>767750</v>
@@ -6212,16 +6212,16 @@
         <v>44522</v>
       </c>
       <c r="B290" t="n">
-        <v>20.18948554992676</v>
+        <v>20.18948745727539</v>
       </c>
       <c r="C290" t="n">
-        <v>21.44126908242115</v>
+        <v>21.44127110802875</v>
       </c>
       <c r="D290" t="n">
-        <v>19.97489423339231</v>
+        <v>19.97489612046799</v>
       </c>
       <c r="E290" t="n">
-        <v>20.86902557166261</v>
+        <v>20.869027543209</v>
       </c>
       <c r="F290" t="n">
         <v>852100</v>
@@ -6272,16 +6272,16 @@
         <v>44525</v>
       </c>
       <c r="B293" t="n">
-        <v>20.29678344726562</v>
+        <v>20.29678153991699</v>
       </c>
       <c r="C293" t="n">
-        <v>20.43984433472696</v>
+        <v>20.43984241393447</v>
       </c>
       <c r="D293" t="n">
-        <v>19.65300774826931</v>
+        <v>19.65300590141818</v>
       </c>
       <c r="E293" t="n">
-        <v>19.65300774826931</v>
+        <v>19.65300590141818</v>
       </c>
       <c r="F293" t="n">
         <v>787900</v>
@@ -6292,16 +6292,16 @@
         <v>44526</v>
       </c>
       <c r="B294" t="n">
-        <v>19.76030540466309</v>
+        <v>19.76030349731445</v>
       </c>
       <c r="C294" t="n">
-        <v>19.90336630036396</v>
+        <v>19.90336437920648</v>
       </c>
       <c r="D294" t="n">
-        <v>19.18806011643918</v>
+        <v>19.18805826432609</v>
       </c>
       <c r="E294" t="n">
-        <v>19.65300888017723</v>
+        <v>19.65300698318531</v>
       </c>
       <c r="F294" t="n">
         <v>1033400</v>
@@ -6312,16 +6312,16 @@
         <v>44529</v>
       </c>
       <c r="B295" t="n">
-        <v>19.20594215393066</v>
+        <v>19.20594024658203</v>
       </c>
       <c r="C295" t="n">
-        <v>20.33254792793267</v>
+        <v>20.33254590870044</v>
       </c>
       <c r="D295" t="n">
-        <v>19.06288126568472</v>
+        <v>19.06287937254352</v>
       </c>
       <c r="E295" t="n">
-        <v>20.33254792793267</v>
+        <v>20.33254590870044</v>
       </c>
       <c r="F295" t="n">
         <v>830750</v>
@@ -6372,16 +6372,16 @@
         <v>44532</v>
       </c>
       <c r="B298" t="n">
-        <v>18.59793090820312</v>
+        <v>18.59793281555176</v>
       </c>
       <c r="C298" t="n">
-        <v>18.86617132939327</v>
+        <v>18.86617326425185</v>
       </c>
       <c r="D298" t="n">
-        <v>18.11510087873313</v>
+        <v>18.11510273656414</v>
       </c>
       <c r="E298" t="n">
-        <v>18.22239568287305</v>
+        <v>18.22239755170791</v>
       </c>
       <c r="F298" t="n">
         <v>961350</v>
@@ -6392,16 +6392,16 @@
         <v>44533</v>
       </c>
       <c r="B299" t="n">
-        <v>19.76030540466309</v>
+        <v>19.76030349731445</v>
       </c>
       <c r="C299" t="n">
-        <v>20.20737113008343</v>
+        <v>20.20736917958211</v>
       </c>
       <c r="D299" t="n">
-        <v>18.77676046765426</v>
+        <v>18.77675865524156</v>
       </c>
       <c r="E299" t="n">
-        <v>18.77676046765426</v>
+        <v>18.77675865524156</v>
       </c>
       <c r="F299" t="n">
         <v>1496100</v>
@@ -6432,16 +6432,16 @@
         <v>44537</v>
       </c>
       <c r="B301" t="n">
-        <v>19.93913078308105</v>
+        <v>19.93912696838379</v>
       </c>
       <c r="C301" t="n">
-        <v>20.72596741925636</v>
+        <v>20.72596345402377</v>
       </c>
       <c r="D301" t="n">
-        <v>19.90336641166604</v>
+        <v>19.90336260381111</v>
       </c>
       <c r="E301" t="n">
-        <v>20.35043213958642</v>
+        <v>20.35042824620016</v>
       </c>
       <c r="F301" t="n">
         <v>881500</v>
@@ -6492,16 +6492,16 @@
         <v>44540</v>
       </c>
       <c r="B304" t="n">
-        <v>21.81680488586426</v>
+        <v>21.81680297851562</v>
       </c>
       <c r="C304" t="n">
-        <v>22.19234012602034</v>
+        <v>22.19233818584029</v>
       </c>
       <c r="D304" t="n">
-        <v>21.06573440555209</v>
+        <v>21.06573256386629</v>
       </c>
       <c r="E304" t="n">
-        <v>22.1386927218324</v>
+        <v>22.1386907863425</v>
       </c>
       <c r="F304" t="n">
         <v>899500</v>
@@ -6532,16 +6532,16 @@
         <v>44544</v>
       </c>
       <c r="B306" t="n">
-        <v>21.49492073059082</v>
+        <v>21.49491882324219</v>
       </c>
       <c r="C306" t="n">
-        <v>22.06716430896915</v>
+        <v>22.06716235084257</v>
       </c>
       <c r="D306" t="n">
-        <v>21.22668027416069</v>
+        <v>21.22667839061434</v>
       </c>
       <c r="E306" t="n">
-        <v>21.95986778531302</v>
+        <v>21.95986583670738</v>
       </c>
       <c r="F306" t="n">
         <v>979700</v>
@@ -6552,16 +6552,16 @@
         <v>44545</v>
       </c>
       <c r="B307" t="n">
-        <v>22.03139686584473</v>
+        <v>22.03139495849609</v>
       </c>
       <c r="C307" t="n">
-        <v>22.37116774849373</v>
+        <v>22.37116581172973</v>
       </c>
       <c r="D307" t="n">
-        <v>21.11938414573805</v>
+        <v>21.11938231734611</v>
       </c>
       <c r="E307" t="n">
-        <v>21.45915332296677</v>
+        <v>21.45915146515961</v>
       </c>
       <c r="F307" t="n">
         <v>1028800</v>
@@ -6592,16 +6592,16 @@
         <v>44547</v>
       </c>
       <c r="B309" t="n">
-        <v>22.37116622924805</v>
+        <v>22.37116813659668</v>
       </c>
       <c r="C309" t="n">
-        <v>22.72881841925829</v>
+        <v>22.72882035710008</v>
       </c>
       <c r="D309" t="n">
-        <v>21.42338579394568</v>
+        <v>21.42338762048728</v>
       </c>
       <c r="E309" t="n">
-        <v>21.56644837536995</v>
+        <v>21.56645021410895</v>
       </c>
       <c r="F309" t="n">
         <v>2194100</v>
@@ -6652,16 +6652,16 @@
         <v>44552</v>
       </c>
       <c r="B312" t="n">
-        <v>21.45915603637695</v>
+        <v>21.45915222167969</v>
       </c>
       <c r="C312" t="n">
-        <v>21.78104392265717</v>
+        <v>21.78104005073934</v>
       </c>
       <c r="D312" t="n">
-        <v>20.65443802609692</v>
+        <v>20.65443435445074</v>
       </c>
       <c r="E312" t="n">
-        <v>21.42338995771449</v>
+        <v>21.42338614937519</v>
       </c>
       <c r="F312" t="n">
         <v>1154200</v>
@@ -6672,16 +6672,16 @@
         <v>44553</v>
       </c>
       <c r="B313" t="n">
-        <v>21.17615127563477</v>
+        <v>21.17614936828613</v>
       </c>
       <c r="C313" t="n">
-        <v>21.69924183626969</v>
+        <v>21.69923988180597</v>
       </c>
       <c r="D313" t="n">
-        <v>20.79736144067842</v>
+        <v>20.79735956744761</v>
       </c>
       <c r="E313" t="n">
-        <v>21.69924183626969</v>
+        <v>21.69923988180597</v>
       </c>
       <c r="F313" t="n">
         <v>605250</v>
@@ -6692,16 +6692,16 @@
         <v>44557</v>
       </c>
       <c r="B314" t="n">
-        <v>20.92362594604492</v>
+        <v>20.92362403869629</v>
       </c>
       <c r="C314" t="n">
-        <v>21.35652812474094</v>
+        <v>21.35652617792996</v>
       </c>
       <c r="D314" t="n">
-        <v>20.58091043109365</v>
+        <v>20.58090855498616</v>
       </c>
       <c r="E314" t="n">
-        <v>21.08596297290567</v>
+        <v>21.08596105075877</v>
       </c>
       <c r="F314" t="n">
         <v>929800</v>
@@ -6712,16 +6712,16 @@
         <v>44558</v>
       </c>
       <c r="B315" t="n">
-        <v>20.76128768920898</v>
+        <v>20.76128959655762</v>
       </c>
       <c r="C315" t="n">
-        <v>21.24830222169153</v>
+        <v>21.2483041737824</v>
       </c>
       <c r="D315" t="n">
-        <v>20.58091091705966</v>
+        <v>20.58091280783701</v>
       </c>
       <c r="E315" t="n">
-        <v>20.90558841884829</v>
+        <v>20.90559033945389</v>
       </c>
       <c r="F315" t="n">
         <v>793100</v>
@@ -6732,16 +6732,16 @@
         <v>44559</v>
       </c>
       <c r="B316" t="n">
-        <v>20.29230880737305</v>
+        <v>20.29231071472168</v>
       </c>
       <c r="C316" t="n">
-        <v>20.90558774878349</v>
+        <v>20.90558971377646</v>
       </c>
       <c r="D316" t="n">
-        <v>20.05781969917492</v>
+        <v>20.05782158448306</v>
       </c>
       <c r="E316" t="n">
-        <v>20.70717296173873</v>
+        <v>20.70717490808197</v>
       </c>
       <c r="F316" t="n">
         <v>541350</v>
@@ -6752,16 +6752,16 @@
         <v>44560</v>
       </c>
       <c r="B317" t="n">
-        <v>21.06793022155762</v>
+        <v>21.06792640686035</v>
       </c>
       <c r="C317" t="n">
-        <v>21.15811690049597</v>
+        <v>21.15811306946891</v>
       </c>
       <c r="D317" t="n">
-        <v>19.93156052088792</v>
+        <v>19.93155691194919</v>
       </c>
       <c r="E317" t="n">
-        <v>20.29231239724323</v>
+        <v>20.2923087229844</v>
       </c>
       <c r="F317" t="n">
         <v>1399700</v>
@@ -6792,16 +6792,16 @@
         <v>44565</v>
       </c>
       <c r="B319" t="n">
-        <v>18.99359893798828</v>
+        <v>18.99360084533691</v>
       </c>
       <c r="C319" t="n">
-        <v>20.23819473506625</v>
+        <v>20.23819676739794</v>
       </c>
       <c r="D319" t="n">
-        <v>18.8492982253126</v>
+        <v>18.84930011817047</v>
       </c>
       <c r="E319" t="n">
-        <v>20.07585600325606</v>
+        <v>20.0758580192856</v>
       </c>
       <c r="F319" t="n">
         <v>1398150</v>
@@ -6832,16 +6832,16 @@
         <v>44567</v>
       </c>
       <c r="B321" t="n">
-        <v>17.58666801452637</v>
+        <v>17.58666610717773</v>
       </c>
       <c r="C321" t="n">
-        <v>18.03760822002704</v>
+        <v>18.03760626377203</v>
       </c>
       <c r="D321" t="n">
-        <v>16.86516437380543</v>
+        <v>16.86516254470693</v>
       </c>
       <c r="E321" t="n">
-        <v>18.03760822002704</v>
+        <v>18.03760626377203</v>
       </c>
       <c r="F321" t="n">
         <v>2077850</v>
@@ -6892,16 +6892,16 @@
         <v>44572</v>
       </c>
       <c r="B324" t="n">
-        <v>16.77497673034668</v>
+        <v>16.77497482299805</v>
       </c>
       <c r="C324" t="n">
-        <v>17.04554017752951</v>
+        <v>17.04553823941727</v>
       </c>
       <c r="D324" t="n">
-        <v>16.1797357703841</v>
+        <v>16.17973393071556</v>
       </c>
       <c r="E324" t="n">
-        <v>16.19777207204929</v>
+        <v>16.19777023032999</v>
       </c>
       <c r="F324" t="n">
         <v>629400</v>
@@ -6932,16 +6932,16 @@
         <v>44574</v>
       </c>
       <c r="B326" t="n">
-        <v>16.64871025085449</v>
+        <v>16.64871406555176</v>
       </c>
       <c r="C326" t="n">
-        <v>17.62274266945553</v>
+        <v>17.62274670733157</v>
       </c>
       <c r="D326" t="n">
-        <v>16.57655989246185</v>
+        <v>16.5765636906274</v>
       </c>
       <c r="E326" t="n">
-        <v>17.58666663015909</v>
+        <v>17.58667065976908</v>
       </c>
       <c r="F326" t="n">
         <v>921200</v>
@@ -6952,16 +6952,16 @@
         <v>44575</v>
       </c>
       <c r="B327" t="n">
-        <v>17.00946426391602</v>
+        <v>17.00946617126465</v>
       </c>
       <c r="C327" t="n">
-        <v>17.02750056389514</v>
+        <v>17.02750247326626</v>
       </c>
       <c r="D327" t="n">
-        <v>16.17973425786645</v>
+        <v>16.17973607217368</v>
       </c>
       <c r="E327" t="n">
-        <v>16.55852408063256</v>
+        <v>16.55852593741522</v>
       </c>
       <c r="F327" t="n">
         <v>789200</v>
@@ -6992,16 +6992,16 @@
         <v>44579</v>
       </c>
       <c r="B329" t="n">
-        <v>16.30599594116211</v>
+        <v>16.30599784851074</v>
       </c>
       <c r="C329" t="n">
-        <v>16.79301213441261</v>
+        <v>16.79301409872861</v>
       </c>
       <c r="D329" t="n">
-        <v>16.07150685406374</v>
+        <v>16.07150873398366</v>
       </c>
       <c r="E329" t="n">
-        <v>16.73889807725132</v>
+        <v>16.73890003523749</v>
       </c>
       <c r="F329" t="n">
         <v>670850</v>
@@ -7032,16 +7032,16 @@
         <v>44581</v>
       </c>
       <c r="B331" t="n">
-        <v>17.4243278503418</v>
+        <v>17.42432975769043</v>
       </c>
       <c r="C331" t="n">
-        <v>18.12779513306872</v>
+        <v>18.12779711742218</v>
       </c>
       <c r="D331" t="n">
-        <v>16.48637319357279</v>
+        <v>16.48637499824851</v>
       </c>
       <c r="E331" t="n">
-        <v>16.48637319357279</v>
+        <v>16.48637499824851</v>
       </c>
       <c r="F331" t="n">
         <v>2219300</v>
@@ -7072,16 +7072,16 @@
         <v>44585</v>
       </c>
       <c r="B333" t="n">
-        <v>17.85723304748535</v>
+        <v>17.85722923278809</v>
       </c>
       <c r="C333" t="n">
-        <v>18.09172218175017</v>
+        <v>18.09171831696088</v>
       </c>
       <c r="D333" t="n">
-        <v>17.47844317216533</v>
+        <v>17.47843943838591</v>
       </c>
       <c r="E333" t="n">
-        <v>18.09172218175017</v>
+        <v>18.09171831696088</v>
       </c>
       <c r="F333" t="n">
         <v>692150</v>
@@ -7092,16 +7092,16 @@
         <v>44586</v>
       </c>
       <c r="B334" t="n">
-        <v>18.72303771972656</v>
+        <v>18.72303581237793</v>
       </c>
       <c r="C334" t="n">
-        <v>18.759112042011</v>
+        <v>18.75911013098741</v>
       </c>
       <c r="D334" t="n">
-        <v>17.65881854922971</v>
+        <v>17.65881675029495</v>
       </c>
       <c r="E334" t="n">
-        <v>17.71293089275656</v>
+        <v>17.71292908830928</v>
       </c>
       <c r="F334" t="n">
         <v>1122500</v>
@@ -7112,16 +7112,16 @@
         <v>44587</v>
       </c>
       <c r="B335" t="n">
-        <v>19.35435485839844</v>
+        <v>19.3543529510498</v>
       </c>
       <c r="C335" t="n">
-        <v>19.80529511198872</v>
+        <v>19.80529316020046</v>
       </c>
       <c r="D335" t="n">
-        <v>18.84930225603348</v>
+        <v>18.84930039845718</v>
       </c>
       <c r="E335" t="n">
-        <v>18.9214526277999</v>
+        <v>18.92145076311327</v>
       </c>
       <c r="F335" t="n">
         <v>1494250</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96763229370117</v>
+        <v>19.96762847900391</v>
       </c>
       <c r="C338" t="n">
-        <v>20.27427177942092</v>
+        <v>20.274267906142</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44454170986168</v>
+        <v>19.44453799509775</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706885110159</v>
+        <v>19.69706508809386</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7212,16 +7212,16 @@
         <v>44594</v>
       </c>
       <c r="B340" t="n">
-        <v>20.22015953063965</v>
+        <v>20.22015762329102</v>
       </c>
       <c r="C340" t="n">
-        <v>20.86951282807217</v>
+        <v>20.86951085947065</v>
       </c>
       <c r="D340" t="n">
-        <v>19.85940769873269</v>
+        <v>19.85940582541344</v>
       </c>
       <c r="E340" t="n">
-        <v>20.25623385373013</v>
+        <v>20.25623194297864</v>
       </c>
       <c r="F340" t="n">
         <v>1270900</v>
@@ -7252,16 +7252,16 @@
         <v>44596</v>
       </c>
       <c r="B342" t="n">
-        <v>19.4084644317627</v>
+        <v>19.40846633911133</v>
       </c>
       <c r="C342" t="n">
-        <v>20.18408031854456</v>
+        <v>20.18408230211611</v>
       </c>
       <c r="D342" t="n">
-        <v>19.26416372165443</v>
+        <v>19.26416561482205</v>
       </c>
       <c r="E342" t="n">
-        <v>20.18408031854456</v>
+        <v>20.18408230211611</v>
       </c>
       <c r="F342" t="n">
         <v>774000</v>
@@ -7272,16 +7272,16 @@
         <v>44599</v>
       </c>
       <c r="B343" t="n">
-        <v>19.73314094543457</v>
+        <v>19.7331428527832</v>
       </c>
       <c r="C343" t="n">
-        <v>19.94959373930937</v>
+        <v>19.94959566757971</v>
       </c>
       <c r="D343" t="n">
-        <v>19.0657497048879</v>
+        <v>19.06575154772842</v>
       </c>
       <c r="E343" t="n">
-        <v>19.31827681760835</v>
+        <v>19.31827868485741</v>
       </c>
       <c r="F343" t="n">
         <v>708000</v>
@@ -7332,16 +7332,16 @@
         <v>44602</v>
       </c>
       <c r="B346" t="n">
-        <v>19.98566818237305</v>
+        <v>19.98567008972168</v>
       </c>
       <c r="C346" t="n">
-        <v>20.59894708836287</v>
+        <v>20.59894905424028</v>
       </c>
       <c r="D346" t="n">
-        <v>19.82332944605806</v>
+        <v>19.82333133791377</v>
       </c>
       <c r="E346" t="n">
-        <v>20.18408123775789</v>
+        <v>20.18408316404224</v>
       </c>
       <c r="F346" t="n">
         <v>563100</v>
@@ -7372,16 +7372,16 @@
         <v>44606</v>
       </c>
       <c r="B348" t="n">
-        <v>20.00370597839355</v>
+        <v>20.00370788574219</v>
       </c>
       <c r="C348" t="n">
-        <v>20.1480066934604</v>
+        <v>20.14800861456807</v>
       </c>
       <c r="D348" t="n">
-        <v>19.26416438362593</v>
+        <v>19.26416622045944</v>
       </c>
       <c r="E348" t="n">
-        <v>19.26416438362593</v>
+        <v>19.26416622045944</v>
       </c>
       <c r="F348" t="n">
         <v>683300</v>
@@ -7392,16 +7392,16 @@
         <v>44607</v>
       </c>
       <c r="B349" t="n">
-        <v>20.52679634094238</v>
+        <v>20.52680015563965</v>
       </c>
       <c r="C349" t="n">
-        <v>20.70717137327322</v>
+        <v>20.70717522149135</v>
       </c>
       <c r="D349" t="n">
-        <v>20.11193049820109</v>
+        <v>20.11193423579974</v>
       </c>
       <c r="E349" t="n">
-        <v>20.2021188744666</v>
+        <v>20.20212262882585</v>
       </c>
       <c r="F349" t="n">
         <v>560950</v>
@@ -7412,16 +7412,16 @@
         <v>44608</v>
       </c>
       <c r="B350" t="n">
-        <v>20.74324989318848</v>
+        <v>20.74324798583984</v>
       </c>
       <c r="C350" t="n">
-        <v>20.76128791463935</v>
+        <v>20.76128600563211</v>
       </c>
       <c r="D350" t="n">
-        <v>20.27427165666829</v>
+        <v>20.27426979244236</v>
       </c>
       <c r="E350" t="n">
-        <v>20.74324989318848</v>
+        <v>20.74324798583984</v>
       </c>
       <c r="F350" t="n">
         <v>576900</v>
@@ -7452,16 +7452,16 @@
         <v>44610</v>
       </c>
       <c r="B352" t="n">
-        <v>19.93155860900879</v>
+        <v>19.93155670166016</v>
       </c>
       <c r="C352" t="n">
-        <v>20.5087615558107</v>
+        <v>20.50875959322669</v>
       </c>
       <c r="D352" t="n">
-        <v>19.64295713560783</v>
+        <v>19.64295525587689</v>
       </c>
       <c r="E352" t="n">
-        <v>20.47268723173582</v>
+        <v>20.47268527260393</v>
       </c>
       <c r="F352" t="n">
         <v>904300</v>
@@ -7472,16 +7472,16 @@
         <v>44613</v>
       </c>
       <c r="B353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892242431641</v>
       </c>
       <c r="C353" t="n">
-        <v>19.94959452481559</v>
+        <v>19.94959248662468</v>
       </c>
       <c r="D353" t="n">
-        <v>18.66892433166504</v>
+        <v>18.66892242431641</v>
       </c>
       <c r="E353" t="n">
-        <v>19.85940614385</v>
+        <v>19.85940411487337</v>
       </c>
       <c r="F353" t="n">
         <v>728950</v>
@@ -7512,16 +7512,16 @@
         <v>44615</v>
       </c>
       <c r="B355" t="n">
-        <v>19.6609935760498</v>
+        <v>19.66099166870117</v>
       </c>
       <c r="C355" t="n">
-        <v>20.49072367802294</v>
+        <v>20.49072169018069</v>
       </c>
       <c r="D355" t="n">
-        <v>19.55276888286228</v>
+        <v>19.55276698601272</v>
       </c>
       <c r="E355" t="n">
-        <v>19.85940838056108</v>
+        <v>19.85940645396386</v>
       </c>
       <c r="F355" t="n">
         <v>1327750</v>
@@ -7572,16 +7572,16 @@
         <v>44622</v>
       </c>
       <c r="B358" t="n">
-        <v>18.83126258850098</v>
+        <v>18.83126068115234</v>
       </c>
       <c r="C358" t="n">
-        <v>18.90341295396648</v>
+        <v>18.90341103931001</v>
       </c>
       <c r="D358" t="n">
-        <v>18.23602164336046</v>
+        <v>18.23601979630157</v>
       </c>
       <c r="E358" t="n">
-        <v>18.74107592181939</v>
+        <v>18.74107402360544</v>
       </c>
       <c r="F358" t="n">
         <v>1044650</v>
@@ -7592,16 +7592,16 @@
         <v>44623</v>
       </c>
       <c r="B359" t="n">
-        <v>18.57873725891113</v>
+        <v>18.5787353515625</v>
       </c>
       <c r="C359" t="n">
-        <v>19.46257967016855</v>
+        <v>19.46257767208202</v>
       </c>
       <c r="D359" t="n">
-        <v>18.54266121590451</v>
+        <v>18.54265931225955</v>
       </c>
       <c r="E359" t="n">
-        <v>18.72303799053682</v>
+        <v>18.72303606837384</v>
       </c>
       <c r="F359" t="n">
         <v>930450</v>
@@ -7632,16 +7632,16 @@
         <v>44627</v>
       </c>
       <c r="B361" t="n">
-        <v>16.77497673034668</v>
+        <v>16.77497482299805</v>
       </c>
       <c r="C361" t="n">
-        <v>18.00153297380269</v>
+        <v>18.00153092699214</v>
       </c>
       <c r="D361" t="n">
-        <v>16.77497673034668</v>
+        <v>16.77497482299805</v>
       </c>
       <c r="E361" t="n">
-        <v>17.60470681396126</v>
+        <v>17.60470481227065</v>
       </c>
       <c r="F361" t="n">
         <v>1173850</v>
@@ -7712,16 +7712,16 @@
         <v>44631</v>
       </c>
       <c r="B365" t="n">
-        <v>17.22591590881348</v>
+        <v>17.22591781616211</v>
       </c>
       <c r="C365" t="n">
-        <v>18.4524720777208</v>
+        <v>18.45247412088051</v>
       </c>
       <c r="D365" t="n">
-        <v>17.02750112075174</v>
+        <v>17.02750300613079</v>
       </c>
       <c r="E365" t="n">
-        <v>18.30817135196699</v>
+        <v>18.30817337914893</v>
       </c>
       <c r="F365" t="n">
         <v>837400</v>
@@ -7732,16 +7732,16 @@
         <v>44634</v>
       </c>
       <c r="B366" t="n">
-        <v>17.31610298156738</v>
+        <v>17.31610488891602</v>
       </c>
       <c r="C366" t="n">
-        <v>17.67685476864166</v>
+        <v>17.67685671572668</v>
       </c>
       <c r="D366" t="n">
-        <v>16.88319911687804</v>
+        <v>16.88320097654281</v>
       </c>
       <c r="E366" t="n">
-        <v>17.35217730017471</v>
+        <v>17.35217921149688</v>
       </c>
       <c r="F366" t="n">
         <v>989600</v>
@@ -7752,16 +7752,16 @@
         <v>44635</v>
       </c>
       <c r="B367" t="n">
-        <v>17.46040534973145</v>
+        <v>17.46040725708008</v>
       </c>
       <c r="C367" t="n">
-        <v>17.56863003600147</v>
+        <v>17.56863195517241</v>
       </c>
       <c r="D367" t="n">
-        <v>16.93731477889199</v>
+        <v>16.93731662909899</v>
       </c>
       <c r="E367" t="n">
-        <v>17.04553946516202</v>
+        <v>17.04554132719132</v>
       </c>
       <c r="F367" t="n">
         <v>763850</v>
@@ -7812,16 +7812,16 @@
         <v>44638</v>
       </c>
       <c r="B370" t="n">
-        <v>18.4344367980957</v>
+        <v>18.43443489074707</v>
       </c>
       <c r="C370" t="n">
-        <v>18.90341332266845</v>
+        <v>18.90341136679641</v>
       </c>
       <c r="D370" t="n">
-        <v>18.01957089842698</v>
+        <v>18.01956903400312</v>
       </c>
       <c r="E370" t="n">
-        <v>18.16387163217251</v>
+        <v>18.16386975281834</v>
       </c>
       <c r="F370" t="n">
         <v>2000150</v>
@@ -7852,16 +7852,16 @@
         <v>44642</v>
       </c>
       <c r="B372" t="n">
-        <v>19.4084644317627</v>
+        <v>19.40846633911133</v>
       </c>
       <c r="C372" t="n">
-        <v>19.46257676800326</v>
+        <v>19.46257868066973</v>
       </c>
       <c r="D372" t="n">
-        <v>18.68695916102124</v>
+        <v>18.68696099746462</v>
       </c>
       <c r="E372" t="n">
-        <v>18.70499717983481</v>
+        <v>18.70499901805086</v>
       </c>
       <c r="F372" t="n">
         <v>868000</v>
@@ -7912,16 +7912,16 @@
         <v>44645</v>
       </c>
       <c r="B375" t="n">
-        <v>21.19418716430664</v>
+        <v>21.19418907165527</v>
       </c>
       <c r="C375" t="n">
-        <v>21.44671426894065</v>
+        <v>21.4467161990152</v>
       </c>
       <c r="D375" t="n">
-        <v>20.81539736745571</v>
+        <v>20.81539924071555</v>
       </c>
       <c r="E375" t="n">
-        <v>20.92362376092747</v>
+        <v>20.92362564392704</v>
       </c>
       <c r="F375" t="n">
         <v>911550</v>
@@ -7952,16 +7952,16 @@
         <v>44649</v>
       </c>
       <c r="B377" t="n">
-        <v>21.91569519042969</v>
+        <v>21.91569328308105</v>
       </c>
       <c r="C377" t="n">
-        <v>22.36663543484347</v>
+        <v>22.36663348824898</v>
       </c>
       <c r="D377" t="n">
-        <v>21.6631697544863</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="E377" t="n">
-        <v>21.6631697544863</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="F377" t="n">
         <v>1103500</v>
@@ -7992,16 +7992,16 @@
         <v>44651</v>
       </c>
       <c r="B379" t="n">
-        <v>21.17615127563477</v>
+        <v>21.17614936828613</v>
       </c>
       <c r="C379" t="n">
-        <v>21.77139219910897</v>
+        <v>21.77139023814663</v>
       </c>
       <c r="D379" t="n">
-        <v>21.0498885707161</v>
+        <v>21.04988667474002</v>
       </c>
       <c r="E379" t="n">
-        <v>21.60905345267049</v>
+        <v>21.6090515063301</v>
       </c>
       <c r="F379" t="n">
         <v>849150</v>
@@ -8052,16 +8052,16 @@
         <v>44656</v>
       </c>
       <c r="B382" t="n">
-        <v>20.70717239379883</v>
+        <v>20.7071704864502</v>
       </c>
       <c r="C382" t="n">
-        <v>21.87961790263256</v>
+        <v>21.87961588728935</v>
       </c>
       <c r="D382" t="n">
-        <v>20.59894771310666</v>
+        <v>20.59894581572666</v>
       </c>
       <c r="E382" t="n">
-        <v>21.78942952192223</v>
+        <v>21.78942751488632</v>
       </c>
       <c r="F382" t="n">
         <v>1118400</v>
@@ -8072,16 +8072,16 @@
         <v>44657</v>
       </c>
       <c r="B383" t="n">
-        <v>20.02174377441406</v>
+        <v>20.0217456817627</v>
       </c>
       <c r="C383" t="n">
-        <v>20.58090860900858</v>
+        <v>20.58091056962541</v>
       </c>
       <c r="D383" t="n">
-        <v>19.58883991384388</v>
+        <v>19.58884177995242</v>
       </c>
       <c r="E383" t="n">
-        <v>20.58090860900858</v>
+        <v>20.58091056962541</v>
       </c>
       <c r="F383" t="n">
         <v>1237700</v>
@@ -8092,16 +8092,16 @@
         <v>44658</v>
       </c>
       <c r="B384" t="n">
-        <v>19.6609935760498</v>
+        <v>19.66099166870117</v>
       </c>
       <c r="C384" t="n">
-        <v>20.0037091182781</v>
+        <v>20.00370717768201</v>
       </c>
       <c r="D384" t="n">
-        <v>19.55276888286228</v>
+        <v>19.55276698601272</v>
       </c>
       <c r="E384" t="n">
-        <v>19.85940838056108</v>
+        <v>19.85940645396386</v>
       </c>
       <c r="F384" t="n">
         <v>978600</v>
@@ -8112,16 +8112,16 @@
         <v>44659</v>
       </c>
       <c r="B385" t="n">
-        <v>19.39042663574219</v>
+        <v>19.39042854309082</v>
       </c>
       <c r="C385" t="n">
-        <v>19.60687770339157</v>
+        <v>19.60687963203151</v>
       </c>
       <c r="D385" t="n">
-        <v>19.01163683730573</v>
+        <v>19.01163870739452</v>
       </c>
       <c r="E385" t="n">
-        <v>19.57080338555009</v>
+        <v>19.57080531064157</v>
       </c>
       <c r="F385" t="n">
         <v>914050</v>
@@ -8152,16 +8152,16 @@
         <v>44663</v>
       </c>
       <c r="B387" t="n">
-        <v>19.13790130615234</v>
+        <v>19.13789939880371</v>
       </c>
       <c r="C387" t="n">
-        <v>19.84136863144855</v>
+        <v>19.84136665398996</v>
       </c>
       <c r="D387" t="n">
-        <v>18.9936005809942</v>
+        <v>18.99359868802707</v>
       </c>
       <c r="E387" t="n">
-        <v>19.33631609339504</v>
+        <v>19.33631416627171</v>
       </c>
       <c r="F387" t="n">
         <v>1155250</v>
@@ -8172,16 +8172,16 @@
         <v>44664</v>
       </c>
       <c r="B388" t="n">
-        <v>19.17397880554199</v>
+        <v>19.17397689819336</v>
       </c>
       <c r="C388" t="n">
-        <v>19.73314372799893</v>
+        <v>19.73314176502687</v>
       </c>
       <c r="D388" t="n">
-        <v>18.95752770134571</v>
+        <v>18.95752581552875</v>
       </c>
       <c r="E388" t="n">
-        <v>19.11986645954304</v>
+        <v>19.11986455757728</v>
       </c>
       <c r="F388" t="n">
         <v>1163900</v>
@@ -8192,16 +8192,16 @@
         <v>44665</v>
       </c>
       <c r="B389" t="n">
-        <v>19.57080841064453</v>
+        <v>19.57080459594727</v>
       </c>
       <c r="C389" t="n">
-        <v>19.67903311215743</v>
+        <v>19.67902927636525</v>
       </c>
       <c r="D389" t="n">
-        <v>19.01164171882585</v>
+        <v>19.01163801312008</v>
       </c>
       <c r="E389" t="n">
-        <v>19.17398049129581</v>
+        <v>19.17397675394734</v>
       </c>
       <c r="F389" t="n">
         <v>760550</v>
@@ -8212,16 +8212,16 @@
         <v>44669</v>
       </c>
       <c r="B390" t="n">
-        <v>19.55276679992676</v>
+        <v>19.55276870727539</v>
       </c>
       <c r="C390" t="n">
-        <v>20.0037069873044</v>
+        <v>20.0037089386417</v>
       </c>
       <c r="D390" t="n">
-        <v>19.49865445909752</v>
+        <v>19.49865636116756</v>
       </c>
       <c r="E390" t="n">
-        <v>19.6790295019284</v>
+        <v>19.67903142159381</v>
       </c>
       <c r="F390" t="n">
         <v>1023750</v>
@@ -8232,16 +8232,16 @@
         <v>44670</v>
       </c>
       <c r="B391" t="n">
-        <v>20.3283863067627</v>
+        <v>20.32838439941406</v>
       </c>
       <c r="C391" t="n">
-        <v>20.34642260853286</v>
+        <v>20.34642069949194</v>
       </c>
       <c r="D391" t="n">
-        <v>19.01163994631538</v>
+        <v>19.01163816251292</v>
       </c>
       <c r="E391" t="n">
-        <v>19.55276856403071</v>
+        <v>19.55276672945585</v>
       </c>
       <c r="F391" t="n">
         <v>1459950</v>
@@ -8252,16 +8252,16 @@
         <v>44671</v>
       </c>
       <c r="B392" t="n">
-        <v>20.61698532104492</v>
+        <v>20.61698722839355</v>
       </c>
       <c r="C392" t="n">
-        <v>20.79736035865864</v>
+        <v>20.79736228269439</v>
       </c>
       <c r="D392" t="n">
-        <v>20.11193108724592</v>
+        <v>20.11193294787024</v>
       </c>
       <c r="E392" t="n">
-        <v>20.34642018432397</v>
+        <v>20.34642206664169</v>
       </c>
       <c r="F392" t="n">
         <v>1230400</v>
@@ -8272,16 +8272,16 @@
         <v>44673</v>
       </c>
       <c r="B393" t="n">
-        <v>19.55276679992676</v>
+        <v>19.55276870727539</v>
       </c>
       <c r="C393" t="n">
-        <v>20.4907214951681</v>
+        <v>20.49072349401308</v>
       </c>
       <c r="D393" t="n">
-        <v>19.3543520165524</v>
+        <v>19.35435390454591</v>
       </c>
       <c r="E393" t="n">
-        <v>20.09389536881999</v>
+        <v>20.09389732895506</v>
       </c>
       <c r="F393" t="n">
         <v>931750</v>
@@ -8292,16 +8292,16 @@
         <v>44676</v>
       </c>
       <c r="B394" t="n">
-        <v>19.30023765563965</v>
+        <v>19.30024147033691</v>
       </c>
       <c r="C394" t="n">
-        <v>19.57080277186738</v>
+        <v>19.57080664004192</v>
       </c>
       <c r="D394" t="n">
-        <v>18.6148084361429</v>
+        <v>18.61481211536489</v>
       </c>
       <c r="E394" t="n">
-        <v>19.28219963718444</v>
+        <v>19.28220344831649</v>
       </c>
       <c r="F394" t="n">
         <v>1378800</v>
@@ -8312,16 +8312,16 @@
         <v>44677</v>
       </c>
       <c r="B395" t="n">
-        <v>19.06575393676758</v>
+        <v>19.06575202941895</v>
       </c>
       <c r="C395" t="n">
-        <v>19.39043147944575</v>
+        <v>19.39042953961619</v>
       </c>
       <c r="D395" t="n">
-        <v>18.68696404370992</v>
+        <v>18.68696217425563</v>
       </c>
       <c r="E395" t="n">
-        <v>19.19201838125387</v>
+        <v>19.19201646127367</v>
       </c>
       <c r="F395" t="n">
         <v>972150</v>
@@ -8332,16 +8332,16 @@
         <v>44678</v>
       </c>
       <c r="B396" t="n">
-        <v>19.49865341186523</v>
+        <v>19.49865531921387</v>
       </c>
       <c r="C396" t="n">
-        <v>19.55276574978821</v>
+        <v>19.55276766243008</v>
       </c>
       <c r="D396" t="n">
-        <v>19.10182558662962</v>
+        <v>19.10182745516075</v>
       </c>
       <c r="E396" t="n">
-        <v>19.46257737311645</v>
+        <v>19.46257927693614</v>
       </c>
       <c r="F396" t="n">
         <v>619300</v>
@@ -8352,16 +8352,16 @@
         <v>44679</v>
       </c>
       <c r="B397" t="n">
-        <v>21.04989051818848</v>
+        <v>21.04988861083984</v>
       </c>
       <c r="C397" t="n">
-        <v>21.10400286527417</v>
+        <v>21.10400095302237</v>
       </c>
       <c r="D397" t="n">
-        <v>19.30024190721312</v>
+        <v>19.30024015840165</v>
       </c>
       <c r="E397" t="n">
-        <v>19.84137053867153</v>
+        <v>19.84136874082794</v>
       </c>
       <c r="F397" t="n">
         <v>1501350</v>
@@ -8372,16 +8372,16 @@
         <v>44680</v>
       </c>
       <c r="B398" t="n">
-        <v>21.04989051818848</v>
+        <v>21.04988861083984</v>
       </c>
       <c r="C398" t="n">
-        <v>21.60905545187512</v>
+        <v>21.60905349386008</v>
       </c>
       <c r="D398" t="n">
-        <v>20.90558977915963</v>
+        <v>20.90558788488621</v>
       </c>
       <c r="E398" t="n">
-        <v>21.60905545187512</v>
+        <v>21.60905349386008</v>
       </c>
       <c r="F398" t="n">
         <v>1651000</v>
@@ -8392,16 +8392,16 @@
         <v>44683</v>
       </c>
       <c r="B399" t="n">
-        <v>20.38249588012695</v>
+        <v>20.38249778747559</v>
       </c>
       <c r="C399" t="n">
-        <v>21.41063890980178</v>
+        <v>21.41064091336175</v>
       </c>
       <c r="D399" t="n">
-        <v>20.02174409078493</v>
+        <v>20.02174596437521</v>
       </c>
       <c r="E399" t="n">
-        <v>21.28437621358212</v>
+        <v>21.28437820532671</v>
       </c>
       <c r="F399" t="n">
         <v>1653550</v>
@@ -8412,16 +8412,16 @@
         <v>44684</v>
       </c>
       <c r="B400" t="n">
-        <v>19.84136962890625</v>
+        <v>19.84136772155762</v>
       </c>
       <c r="C400" t="n">
-        <v>20.63502365717432</v>
+        <v>20.63502167353181</v>
       </c>
       <c r="D400" t="n">
-        <v>19.75118124109841</v>
+        <v>19.75117934241958</v>
       </c>
       <c r="E400" t="n">
-        <v>20.4726866233607</v>
+        <v>20.47268465532364</v>
       </c>
       <c r="F400" t="n">
         <v>1374100</v>
@@ -8432,16 +8432,16 @@
         <v>44685</v>
       </c>
       <c r="B401" t="n">
-        <v>20.47268676757812</v>
+        <v>20.47268486022949</v>
       </c>
       <c r="C401" t="n">
-        <v>20.56287343582085</v>
+        <v>20.56287152006993</v>
       </c>
       <c r="D401" t="n">
-        <v>19.17397844651773</v>
+        <v>19.17397666016394</v>
       </c>
       <c r="E401" t="n">
-        <v>19.84136976867643</v>
+        <v>19.84136792014478</v>
       </c>
       <c r="F401" t="n">
         <v>1413100</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.51903343200684</v>
+        <v>19.51902961730957</v>
       </c>
       <c r="C403" t="n">
-        <v>19.93473455484336</v>
+        <v>19.93473065890365</v>
       </c>
       <c r="D403" t="n">
-        <v>18.8199007902444</v>
+        <v>18.81989711218194</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019714903581</v>
+        <v>19.67019330479591</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8492,16 +8492,16 @@
         <v>44690</v>
       </c>
       <c r="B404" t="n">
-        <v>18.78210830688477</v>
+        <v>18.7821102142334</v>
       </c>
       <c r="C404" t="n">
-        <v>19.53792866776176</v>
+        <v>19.53793065186498</v>
       </c>
       <c r="D404" t="n">
-        <v>18.38530311297808</v>
+        <v>18.38530498003061</v>
       </c>
       <c r="E404" t="n">
-        <v>19.25449535667779</v>
+        <v>19.25449731199797</v>
       </c>
       <c r="F404" t="n">
         <v>2367350</v>
@@ -8512,16 +8512,16 @@
         <v>44691</v>
       </c>
       <c r="B405" t="n">
-        <v>19.1600170135498</v>
+        <v>19.16001892089844</v>
       </c>
       <c r="C405" t="n">
-        <v>19.38676255310495</v>
+        <v>19.38676448302573</v>
       </c>
       <c r="D405" t="n">
-        <v>18.6120481757882</v>
+        <v>18.61205002858743</v>
       </c>
       <c r="E405" t="n">
-        <v>19.04664334276555</v>
+        <v>19.04664523882802</v>
       </c>
       <c r="F405" t="n">
         <v>1243050</v>
@@ -8632,16 +8632,16 @@
         <v>44699</v>
       </c>
       <c r="B411" t="n">
-        <v>20.36932945251465</v>
+        <v>20.36932563781738</v>
       </c>
       <c r="C411" t="n">
-        <v>20.76613465362919</v>
+        <v>20.76613076461962</v>
       </c>
       <c r="D411" t="n">
-        <v>20.10479385311404</v>
+        <v>20.10479008795808</v>
       </c>
       <c r="E411" t="n">
-        <v>20.44491130977391</v>
+        <v>20.44490748092194</v>
       </c>
       <c r="F411" t="n">
         <v>1338150</v>
@@ -8692,16 +8692,16 @@
         <v>44704</v>
       </c>
       <c r="B414" t="n">
-        <v>20.82282257080078</v>
+        <v>20.82282066345215</v>
       </c>
       <c r="C414" t="n">
-        <v>21.1629400302818</v>
+        <v>21.16293809177876</v>
       </c>
       <c r="D414" t="n">
-        <v>20.61497111010355</v>
+        <v>20.61496922179389</v>
       </c>
       <c r="E414" t="n">
-        <v>20.78503074085087</v>
+        <v>20.78502883696393</v>
       </c>
       <c r="F414" t="n">
         <v>1655200</v>
@@ -8712,16 +8712,16 @@
         <v>44705</v>
       </c>
       <c r="B415" t="n">
-        <v>20.38822364807129</v>
+        <v>20.38822555541992</v>
       </c>
       <c r="C415" t="n">
-        <v>20.78502881572475</v>
+        <v>20.7850307601951</v>
       </c>
       <c r="D415" t="n">
-        <v>19.93473254275689</v>
+        <v>19.93473440768075</v>
       </c>
       <c r="E415" t="n">
-        <v>20.59607328750369</v>
+        <v>20.59607521429696</v>
       </c>
       <c r="F415" t="n">
         <v>1381900</v>
@@ -8752,16 +8752,16 @@
         <v>44707</v>
       </c>
       <c r="B417" t="n">
-        <v>21.18183326721191</v>
+        <v>21.18183517456055</v>
       </c>
       <c r="C417" t="n">
-        <v>21.27631102812812</v>
+        <v>21.27631294398413</v>
       </c>
       <c r="D417" t="n">
-        <v>20.67165443947247</v>
+        <v>20.67165630088131</v>
       </c>
       <c r="E417" t="n">
-        <v>20.82281993814643</v>
+        <v>20.8228218131672</v>
       </c>
       <c r="F417" t="n">
         <v>1373550</v>
@@ -8792,16 +8792,16 @@
         <v>44711</v>
       </c>
       <c r="B419" t="n">
-        <v>22.14550399780273</v>
+        <v>22.14550590515137</v>
       </c>
       <c r="C419" t="n">
-        <v>23.22254582654633</v>
+        <v>23.22254782665845</v>
       </c>
       <c r="D419" t="n">
-        <v>22.14550399780273</v>
+        <v>22.14550590515137</v>
       </c>
       <c r="E419" t="n">
-        <v>22.97690435995308</v>
+        <v>22.97690633890859</v>
       </c>
       <c r="F419" t="n">
         <v>1234700</v>
@@ -8852,16 +8852,16 @@
         <v>44714</v>
       </c>
       <c r="B422" t="n">
-        <v>23.37370872497559</v>
+        <v>23.37371063232422</v>
       </c>
       <c r="C422" t="n">
-        <v>24.31848273230045</v>
+        <v>24.31848471674483</v>
       </c>
       <c r="D422" t="n">
-        <v>23.24144094059439</v>
+        <v>23.24144283714967</v>
       </c>
       <c r="E422" t="n">
-        <v>23.43039466085132</v>
+        <v>23.43039657282566</v>
       </c>
       <c r="F422" t="n">
         <v>1968350</v>
@@ -8912,16 +8912,16 @@
         <v>44719</v>
       </c>
       <c r="B425" t="n">
-        <v>21.5975341796875</v>
+        <v>21.59753608703613</v>
       </c>
       <c r="C425" t="n">
-        <v>21.93765159373639</v>
+        <v>21.93765353112191</v>
       </c>
       <c r="D425" t="n">
-        <v>21.25741496362521</v>
+        <v>21.25741684093681</v>
       </c>
       <c r="E425" t="n">
-        <v>21.72980196281688</v>
+        <v>21.72980388184651</v>
       </c>
       <c r="F425" t="n">
         <v>1412350</v>
@@ -8932,16 +8932,16 @@
         <v>44720</v>
       </c>
       <c r="B426" t="n">
-        <v>21.20073127746582</v>
+        <v>21.20072937011719</v>
       </c>
       <c r="C426" t="n">
-        <v>21.82428203839009</v>
+        <v>21.82428007494298</v>
       </c>
       <c r="D426" t="n">
-        <v>21.0306716513931</v>
+        <v>21.03066975934408</v>
       </c>
       <c r="E426" t="n">
-        <v>21.48416278624464</v>
+        <v>21.48416085339676</v>
       </c>
       <c r="F426" t="n">
         <v>863650</v>
@@ -8952,16 +8952,16 @@
         <v>44721</v>
       </c>
       <c r="B427" t="n">
-        <v>21.54084968566895</v>
+        <v>21.54084777832031</v>
       </c>
       <c r="C427" t="n">
-        <v>21.72980523460138</v>
+        <v>21.72980331052155</v>
       </c>
       <c r="D427" t="n">
-        <v>20.89840478372873</v>
+        <v>20.8984029332658</v>
       </c>
       <c r="E427" t="n">
-        <v>21.20073222040969</v>
+        <v>21.20073034317699</v>
       </c>
       <c r="F427" t="n">
         <v>1117750</v>
@@ -8992,16 +8992,16 @@
         <v>44725</v>
       </c>
       <c r="B429" t="n">
-        <v>19.25449752807617</v>
+        <v>19.25449371337891</v>
       </c>
       <c r="C429" t="n">
-        <v>20.01031797418974</v>
+        <v>20.01031400974947</v>
       </c>
       <c r="D429" t="n">
-        <v>18.98996190364815</v>
+        <v>18.98995814136063</v>
       </c>
       <c r="E429" t="n">
-        <v>19.9536320263857</v>
+        <v>19.95362807317604</v>
       </c>
       <c r="F429" t="n">
         <v>2646600</v>
@@ -9012,16 +9012,16 @@
         <v>44726</v>
       </c>
       <c r="B430" t="n">
-        <v>19.12222480773926</v>
+        <v>19.12222671508789</v>
       </c>
       <c r="C430" t="n">
-        <v>19.51902994454667</v>
+        <v>19.51903189147468</v>
       </c>
       <c r="D430" t="n">
-        <v>18.89547927270836</v>
+        <v>18.89548115744023</v>
       </c>
       <c r="E430" t="n">
-        <v>19.51902994454667</v>
+        <v>19.51903189147468</v>
       </c>
       <c r="F430" t="n">
         <v>1027150</v>
@@ -9052,16 +9052,16 @@
         <v>44729</v>
       </c>
       <c r="B432" t="n">
-        <v>19.19780921936035</v>
+        <v>19.19780731201172</v>
       </c>
       <c r="C432" t="n">
-        <v>19.51903255410274</v>
+        <v>19.51903061483979</v>
       </c>
       <c r="D432" t="n">
-        <v>18.6876321478371</v>
+        <v>18.68763029117579</v>
       </c>
       <c r="E432" t="n">
-        <v>19.17891330507819</v>
+        <v>19.17891139960691</v>
       </c>
       <c r="F432" t="n">
         <v>2517400</v>
@@ -9132,16 +9132,16 @@
         <v>44735</v>
       </c>
       <c r="B436" t="n">
-        <v>18.81990051269531</v>
+        <v>18.81989860534668</v>
       </c>
       <c r="C436" t="n">
-        <v>18.89548237009515</v>
+        <v>18.89548045508649</v>
       </c>
       <c r="D436" t="n">
-        <v>18.4986771682426</v>
+        <v>18.49867529344914</v>
       </c>
       <c r="E436" t="n">
-        <v>18.72542274044211</v>
+        <v>18.72542084266856</v>
       </c>
       <c r="F436" t="n">
         <v>1280500</v>
@@ -9172,16 +9172,16 @@
         <v>44739</v>
       </c>
       <c r="B438" t="n">
-        <v>18.55536079406738</v>
+        <v>18.55536270141602</v>
       </c>
       <c r="C438" t="n">
-        <v>18.70652448999358</v>
+        <v>18.70652641288067</v>
       </c>
       <c r="D438" t="n">
-        <v>18.38530118564707</v>
+        <v>18.38530307551488</v>
       </c>
       <c r="E438" t="n">
-        <v>18.57425670656151</v>
+        <v>18.57425861585249</v>
       </c>
       <c r="F438" t="n">
         <v>799000</v>
@@ -9272,16 +9272,16 @@
         <v>44746</v>
       </c>
       <c r="B443" t="n">
-        <v>17.28936386108398</v>
+        <v>17.28936576843262</v>
       </c>
       <c r="C443" t="n">
-        <v>17.64837899814145</v>
+        <v>17.64838094509635</v>
       </c>
       <c r="D443" t="n">
-        <v>17.25157383729624</v>
+        <v>17.25157574047591</v>
       </c>
       <c r="E443" t="n">
-        <v>17.44052756026183</v>
+        <v>17.44052948428672</v>
       </c>
       <c r="F443" t="n">
         <v>903450</v>
@@ -9292,16 +9292,16 @@
         <v>44747</v>
       </c>
       <c r="B444" t="n">
-        <v>17.10041046142578</v>
+        <v>17.10041236877441</v>
       </c>
       <c r="C444" t="n">
-        <v>17.25157416346159</v>
+        <v>17.25157608767075</v>
       </c>
       <c r="D444" t="n">
-        <v>16.57133750430044</v>
+        <v>16.57133935263724</v>
       </c>
       <c r="E444" t="n">
-        <v>17.15709639918584</v>
+        <v>17.15709831285712</v>
       </c>
       <c r="F444" t="n">
         <v>2077700</v>
@@ -9332,16 +9332,16 @@
         <v>44749</v>
       </c>
       <c r="B446" t="n">
-        <v>17.66727638244629</v>
+        <v>17.66727447509766</v>
       </c>
       <c r="C446" t="n">
-        <v>18.13966343222278</v>
+        <v>18.13966147387552</v>
       </c>
       <c r="D446" t="n">
-        <v>17.49721675620458</v>
+        <v>17.49721486721548</v>
       </c>
       <c r="E446" t="n">
-        <v>17.5161126706789</v>
+        <v>17.51611077964981</v>
       </c>
       <c r="F446" t="n">
         <v>1515500</v>
@@ -9352,16 +9352,16 @@
         <v>44750</v>
       </c>
       <c r="B447" t="n">
-        <v>17.72396087646484</v>
+        <v>17.72396278381348</v>
       </c>
       <c r="C447" t="n">
-        <v>18.12076603795336</v>
+        <v>18.12076798800384</v>
       </c>
       <c r="D447" t="n">
-        <v>17.64837902675339</v>
+        <v>17.64838092596834</v>
       </c>
       <c r="E447" t="n">
-        <v>17.81843863910753</v>
+        <v>17.8184405566233</v>
       </c>
       <c r="F447" t="n">
         <v>701700</v>
@@ -9412,16 +9412,16 @@
         <v>44755</v>
       </c>
       <c r="B450" t="n">
-        <v>16.87366485595703</v>
+        <v>16.87366676330566</v>
       </c>
       <c r="C450" t="n">
-        <v>17.02482855752328</v>
+        <v>17.024830481959</v>
       </c>
       <c r="D450" t="n">
-        <v>16.3445900984617</v>
+        <v>16.3445919460053</v>
       </c>
       <c r="E450" t="n">
-        <v>16.51464971322709</v>
+        <v>16.51465157999372</v>
       </c>
       <c r="F450" t="n">
         <v>919750</v>
@@ -9452,16 +9452,16 @@
         <v>44757</v>
       </c>
       <c r="B452" t="n">
-        <v>16.59023094177246</v>
+        <v>16.59023284912109</v>
       </c>
       <c r="C452" t="n">
-        <v>17.15709570239164</v>
+        <v>17.15709767491168</v>
       </c>
       <c r="D452" t="n">
-        <v>16.59023094177246</v>
+        <v>16.59023284912109</v>
       </c>
       <c r="E452" t="n">
-        <v>17.06261794195288</v>
+        <v>17.06261990361098</v>
       </c>
       <c r="F452" t="n">
         <v>1098550</v>
@@ -9472,16 +9472,16 @@
         <v>44760</v>
       </c>
       <c r="B453" t="n">
-        <v>16.94924736022949</v>
+        <v>16.94924926757812</v>
       </c>
       <c r="C453" t="n">
-        <v>17.34605254264335</v>
+        <v>17.34605449464563</v>
       </c>
       <c r="D453" t="n">
-        <v>16.74139591105195</v>
+        <v>16.74139779501045</v>
       </c>
       <c r="E453" t="n">
-        <v>16.74139591105195</v>
+        <v>16.74139779501045</v>
       </c>
       <c r="F453" t="n">
         <v>809650</v>
@@ -9492,16 +9492,16 @@
         <v>44761</v>
       </c>
       <c r="B454" t="n">
-        <v>17.28936386108398</v>
+        <v>17.28936576843262</v>
       </c>
       <c r="C454" t="n">
-        <v>17.51611121186419</v>
+        <v>17.51611314422741</v>
       </c>
       <c r="D454" t="n">
-        <v>17.10041013811839</v>
+        <v>17.1004120246218</v>
       </c>
       <c r="E454" t="n">
-        <v>17.10041013811839</v>
+        <v>17.1004120246218</v>
       </c>
       <c r="F454" t="n">
         <v>816100</v>
@@ -9512,16 +9512,16 @@
         <v>44762</v>
       </c>
       <c r="B455" t="n">
-        <v>17.96960067749023</v>
+        <v>17.9696044921875</v>
       </c>
       <c r="C455" t="n">
-        <v>18.02628660903064</v>
+        <v>18.02629043576155</v>
       </c>
       <c r="D455" t="n">
-        <v>17.23267635941185</v>
+        <v>17.2326800176703</v>
       </c>
       <c r="E455" t="n">
-        <v>17.25157227059641</v>
+        <v>17.2515759328662</v>
       </c>
       <c r="F455" t="n">
         <v>812650</v>
@@ -9592,16 +9592,16 @@
         <v>44768</v>
       </c>
       <c r="B459" t="n">
-        <v>17.40273857116699</v>
+        <v>17.40273666381836</v>
       </c>
       <c r="C459" t="n">
-        <v>18.158557111994</v>
+        <v>18.15855512180728</v>
       </c>
       <c r="D459" t="n">
-        <v>17.25157486300159</v>
+        <v>17.25157297222058</v>
       </c>
       <c r="E459" t="n">
-        <v>18.04518523187672</v>
+        <v>18.04518325411562</v>
       </c>
       <c r="F459" t="n">
         <v>578050</v>
@@ -9612,16 +9612,16 @@
         <v>44769</v>
       </c>
       <c r="B460" t="n">
-        <v>18.23414039611816</v>
+        <v>18.23413848876953</v>
       </c>
       <c r="C460" t="n">
-        <v>18.38530411613882</v>
+        <v>18.38530219297798</v>
       </c>
       <c r="D460" t="n">
-        <v>17.34605399150023</v>
+        <v>17.34605217704824</v>
       </c>
       <c r="E460" t="n">
-        <v>17.44052996500288</v>
+        <v>17.4405281406684</v>
       </c>
       <c r="F460" t="n">
         <v>704800</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.51903343200684</v>
+        <v>19.51902961730957</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65130123390378</v>
+        <v>19.65129739335679</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431893172991</v>
+        <v>18.74431526843877</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658673362685</v>
+        <v>18.87658304448599</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9672,16 +9672,16 @@
         <v>44774</v>
       </c>
       <c r="B463" t="n">
-        <v>19.12222480773926</v>
+        <v>19.12222671508789</v>
       </c>
       <c r="C463" t="n">
-        <v>19.74577547957757</v>
+        <v>19.74577744912234</v>
       </c>
       <c r="D463" t="n">
-        <v>19.04664296272896</v>
+        <v>19.04664486253867</v>
       </c>
       <c r="E463" t="n">
-        <v>19.50013403279076</v>
+        <v>19.50013597783399</v>
       </c>
       <c r="F463" t="n">
         <v>811600</v>
@@ -9712,16 +9712,16 @@
         <v>44776</v>
       </c>
       <c r="B465" t="n">
-        <v>19.6890926361084</v>
+        <v>19.68909072875977</v>
       </c>
       <c r="C465" t="n">
-        <v>19.74577857825845</v>
+        <v>19.74577666541846</v>
       </c>
       <c r="D465" t="n">
-        <v>19.02775003697459</v>
+        <v>19.02774819369244</v>
       </c>
       <c r="E465" t="n">
-        <v>19.08443778113825</v>
+        <v>19.08443593236457</v>
       </c>
       <c r="F465" t="n">
         <v>1095050</v>
@@ -9732,16 +9732,16 @@
         <v>44777</v>
       </c>
       <c r="B466" t="n">
-        <v>21.31410026550293</v>
+        <v>21.3141040802002</v>
       </c>
       <c r="C466" t="n">
-        <v>21.46526395659056</v>
+        <v>21.46526779834239</v>
       </c>
       <c r="D466" t="n">
-        <v>19.78356744273731</v>
+        <v>19.78357098350703</v>
       </c>
       <c r="E466" t="n">
-        <v>19.89693931004637</v>
+        <v>19.89694287110684</v>
       </c>
       <c r="F466" t="n">
         <v>1697500</v>
@@ -9752,16 +9752,16 @@
         <v>44778</v>
       </c>
       <c r="B467" t="n">
-        <v>21.06846237182617</v>
+        <v>21.06846046447754</v>
       </c>
       <c r="C467" t="n">
-        <v>21.38968572009017</v>
+        <v>21.38968378366087</v>
       </c>
       <c r="D467" t="n">
-        <v>20.40712156223426</v>
+        <v>20.40711971475746</v>
       </c>
       <c r="E467" t="n">
-        <v>20.93619457031052</v>
+        <v>20.93619267493622</v>
       </c>
       <c r="F467" t="n">
         <v>1243500</v>
@@ -9772,16 +9772,16 @@
         <v>44781</v>
       </c>
       <c r="B468" t="n">
-        <v>21.54084968566895</v>
+        <v>21.54084777832031</v>
       </c>
       <c r="C468" t="n">
-        <v>21.84317892436357</v>
+        <v>21.843176990245</v>
       </c>
       <c r="D468" t="n">
-        <v>21.01177667147726</v>
+        <v>21.01177481097574</v>
       </c>
       <c r="E468" t="n">
-        <v>21.21962633369201</v>
+        <v>21.21962445478631</v>
       </c>
       <c r="F468" t="n">
         <v>1786950</v>
@@ -9832,16 +9832,16 @@
         <v>44784</v>
       </c>
       <c r="B471" t="n">
-        <v>22.01323509216309</v>
+        <v>22.01323699951172</v>
       </c>
       <c r="C471" t="n">
-        <v>22.08881694562063</v>
+        <v>22.0888188595181</v>
       </c>
       <c r="D471" t="n">
-        <v>21.54084805755003</v>
+        <v>21.54084992396843</v>
       </c>
       <c r="E471" t="n">
-        <v>21.82428135952598</v>
+        <v>21.82428325050261</v>
       </c>
       <c r="F471" t="n">
         <v>1242750</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75015640258789</v>
+        <v>22.75015830993652</v>
       </c>
       <c r="C474" t="n">
-        <v>23.1280656181764</v>
+        <v>23.12806755720854</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341087323478</v>
+        <v>22.52341276157331</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027559762419</v>
+        <v>23.09027753348805</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9932,16 +9932,16 @@
         <v>44791</v>
       </c>
       <c r="B476" t="n">
-        <v>22.25887680053711</v>
+        <v>22.25887489318848</v>
       </c>
       <c r="C476" t="n">
-        <v>23.14696493951494</v>
+        <v>23.14696295606662</v>
       </c>
       <c r="D476" t="n">
-        <v>21.84317750315476</v>
+        <v>21.84317563142713</v>
       </c>
       <c r="E476" t="n">
-        <v>22.99580123100981</v>
+        <v>22.9957992605146</v>
       </c>
       <c r="F476" t="n">
         <v>1546750</v>
@@ -9952,16 +9952,16 @@
         <v>44792</v>
       </c>
       <c r="B477" t="n">
-        <v>21.16293716430664</v>
+        <v>21.16293907165527</v>
       </c>
       <c r="C477" t="n">
-        <v>22.16439709618003</v>
+        <v>22.16439909378708</v>
       </c>
       <c r="D477" t="n">
-        <v>20.97398344618691</v>
+        <v>20.97398533650574</v>
       </c>
       <c r="E477" t="n">
-        <v>22.16439709618003</v>
+        <v>22.16439909378708</v>
       </c>
       <c r="F477" t="n">
         <v>1251050</v>
@@ -9972,16 +9972,16 @@
         <v>44795</v>
       </c>
       <c r="B478" t="n">
-        <v>20.67165565490723</v>
+        <v>20.67165756225586</v>
       </c>
       <c r="C478" t="n">
-        <v>20.86061118784968</v>
+        <v>20.86061311263301</v>
       </c>
       <c r="D478" t="n">
-        <v>20.46380601028133</v>
+        <v>20.46380789845194</v>
       </c>
       <c r="E478" t="n">
-        <v>20.80392524877235</v>
+        <v>20.80392716832534</v>
       </c>
       <c r="F478" t="n">
         <v>1246950</v>
@@ -9992,16 +9992,16 @@
         <v>44796</v>
       </c>
       <c r="B479" t="n">
-        <v>20.76613235473633</v>
+        <v>20.76613426208496</v>
       </c>
       <c r="C479" t="n">
-        <v>20.97398379069955</v>
+        <v>20.97398571713913</v>
       </c>
       <c r="D479" t="n">
-        <v>20.29374534865763</v>
+        <v>20.29374721261799</v>
       </c>
       <c r="E479" t="n">
-        <v>20.80392418018906</v>
+        <v>20.80392609100884</v>
       </c>
       <c r="F479" t="n">
         <v>1768900</v>
@@ -10052,16 +10052,16 @@
         <v>44799</v>
       </c>
       <c r="B482" t="n">
-        <v>20.46380424499512</v>
+        <v>20.46380805969238</v>
       </c>
       <c r="C482" t="n">
-        <v>21.10625083916334</v>
+        <v>21.10625477362032</v>
       </c>
       <c r="D482" t="n">
-        <v>20.27484872835269</v>
+        <v>20.2748525078264</v>
       </c>
       <c r="E482" t="n">
-        <v>20.97398305872166</v>
+        <v>20.97398696852234</v>
       </c>
       <c r="F482" t="n">
         <v>564750</v>
@@ -10192,16 +10192,16 @@
         <v>44810</v>
       </c>
       <c r="B489" t="n">
-        <v>20.55828475952148</v>
+        <v>20.55828285217285</v>
       </c>
       <c r="C489" t="n">
-        <v>21.67311849274579</v>
+        <v>21.67311648196554</v>
       </c>
       <c r="D489" t="n">
-        <v>20.35043510495954</v>
+        <v>20.3504332168947</v>
       </c>
       <c r="E489" t="n">
-        <v>21.55974480715789</v>
+        <v>21.55974280689618</v>
       </c>
       <c r="F489" t="n">
         <v>1564950</v>
@@ -10292,16 +10292,16 @@
         <v>44818</v>
       </c>
       <c r="B494" t="n">
-        <v>20.4260139465332</v>
+        <v>20.42601585388184</v>
       </c>
       <c r="C494" t="n">
-        <v>20.5204899015629</v>
+        <v>20.52049181773355</v>
       </c>
       <c r="D494" t="n">
-        <v>19.51903000173875</v>
+        <v>19.51903182439467</v>
       </c>
       <c r="E494" t="n">
-        <v>19.70798551582482</v>
+        <v>19.7079873561251</v>
       </c>
       <c r="F494" t="n">
         <v>1153500</v>
@@ -10332,16 +10332,16 @@
         <v>44820</v>
       </c>
       <c r="B496" t="n">
-        <v>20.02921104431152</v>
+        <v>20.02920913696289</v>
       </c>
       <c r="C496" t="n">
-        <v>20.27485071722412</v>
+        <v>20.27484878648363</v>
       </c>
       <c r="D496" t="n">
-        <v>19.55682400837977</v>
+        <v>19.55682214601578</v>
       </c>
       <c r="E496" t="n">
-        <v>20.27485071722412</v>
+        <v>20.27484878648363</v>
       </c>
       <c r="F496" t="n">
         <v>1629800</v>
@@ -10352,16 +10352,16 @@
         <v>44823</v>
       </c>
       <c r="B497" t="n">
-        <v>20.36932945251465</v>
+        <v>20.36932563781738</v>
       </c>
       <c r="C497" t="n">
-        <v>20.52049316703318</v>
+        <v>20.5204893240265</v>
       </c>
       <c r="D497" t="n">
-        <v>19.85915236651802</v>
+        <v>19.85914864736495</v>
       </c>
       <c r="E497" t="n">
-        <v>19.93473422377729</v>
+        <v>19.93473049046951</v>
       </c>
       <c r="F497" t="n">
         <v>718850</v>
@@ -10392,16 +10392,16 @@
         <v>44825</v>
       </c>
       <c r="B499" t="n">
-        <v>19.12222480773926</v>
+        <v>19.12222671508789</v>
       </c>
       <c r="C499" t="n">
-        <v>20.08589468313058</v>
+        <v>20.08589668660058</v>
       </c>
       <c r="D499" t="n">
-        <v>19.04664296272896</v>
+        <v>19.04664486253867</v>
       </c>
       <c r="E499" t="n">
-        <v>19.84025323634378</v>
+        <v>19.84025521531224</v>
       </c>
       <c r="F499" t="n">
         <v>1245900</v>
@@ -10432,16 +10432,16 @@
         <v>44827</v>
       </c>
       <c r="B501" t="n">
-        <v>19.57571601867676</v>
+        <v>19.57571792602539</v>
       </c>
       <c r="C501" t="n">
-        <v>19.68908968801476</v>
+        <v>19.68909160640989</v>
       </c>
       <c r="D501" t="n">
-        <v>19.21670270279754</v>
+        <v>19.21670457516592</v>
       </c>
       <c r="E501" t="n">
-        <v>19.34897048201409</v>
+        <v>19.3489723672699</v>
       </c>
       <c r="F501" t="n">
         <v>673550</v>
@@ -10472,16 +10472,16 @@
         <v>44831</v>
       </c>
       <c r="B503" t="n">
-        <v>18.30971908569336</v>
+        <v>18.30972099304199</v>
       </c>
       <c r="C503" t="n">
-        <v>19.00885342224679</v>
+        <v>19.00885540242521</v>
       </c>
       <c r="D503" t="n">
-        <v>18.25303315100454</v>
+        <v>18.25303505244812</v>
       </c>
       <c r="E503" t="n">
-        <v>18.97106159777866</v>
+        <v>18.97106357402025</v>
       </c>
       <c r="F503" t="n">
         <v>994450</v>
@@ -10512,16 +10512,16 @@
         <v>44833</v>
       </c>
       <c r="B505" t="n">
-        <v>18.21524620056152</v>
+        <v>18.21524238586426</v>
       </c>
       <c r="C505" t="n">
-        <v>18.30972217363853</v>
+        <v>18.30971833915579</v>
       </c>
       <c r="D505" t="n">
-        <v>17.85623101561966</v>
+        <v>17.85622727610854</v>
       </c>
       <c r="E505" t="n">
-        <v>18.29082806023133</v>
+        <v>18.29082422970546</v>
       </c>
       <c r="F505" t="n">
         <v>1182750</v>
@@ -10532,16 +10532,16 @@
         <v>44834</v>
       </c>
       <c r="B506" t="n">
-        <v>18.25303268432617</v>
+        <v>18.25303649902344</v>
       </c>
       <c r="C506" t="n">
-        <v>18.51757004279949</v>
+        <v>18.51757391278236</v>
       </c>
       <c r="D506" t="n">
-        <v>17.95070530436427</v>
+        <v>17.95070905587821</v>
       </c>
       <c r="E506" t="n">
-        <v>18.2152426628376</v>
+        <v>18.21524646963713</v>
       </c>
       <c r="F506" t="n">
         <v>981200</v>
@@ -10592,16 +10592,16 @@
         <v>44839</v>
       </c>
       <c r="B509" t="n">
-        <v>19.63240623474121</v>
+        <v>19.63240814208984</v>
       </c>
       <c r="C509" t="n">
-        <v>19.84025588577203</v>
+        <v>19.8402578133139</v>
       </c>
       <c r="D509" t="n">
-        <v>19.38676475515193</v>
+        <v>19.38676663863574</v>
       </c>
       <c r="E509" t="n">
-        <v>19.72688220211023</v>
+        <v>19.72688411863749</v>
       </c>
       <c r="F509" t="n">
         <v>721150</v>
@@ -10632,16 +10632,16 @@
         <v>44841</v>
       </c>
       <c r="B511" t="n">
-        <v>19.63240623474121</v>
+        <v>19.63240814208984</v>
       </c>
       <c r="C511" t="n">
-        <v>20.38822478577472</v>
+        <v>20.38822676655345</v>
       </c>
       <c r="D511" t="n">
-        <v>19.55682437963786</v>
+        <v>19.55682627964348</v>
       </c>
       <c r="E511" t="n">
-        <v>20.38822478577472</v>
+        <v>20.38822676655345</v>
       </c>
       <c r="F511" t="n">
         <v>673950</v>
@@ -10652,16 +10652,16 @@
         <v>44844</v>
       </c>
       <c r="B512" t="n">
-        <v>19.55682182312012</v>
+        <v>19.55682373046875</v>
       </c>
       <c r="C512" t="n">
-        <v>19.7457755351712</v>
+        <v>19.74577746094821</v>
       </c>
       <c r="D512" t="n">
-        <v>19.2922844638326</v>
+        <v>19.29228634538129</v>
       </c>
       <c r="E512" t="n">
-        <v>19.68908960175721</v>
+        <v>19.68909152200573</v>
       </c>
       <c r="F512" t="n">
         <v>555250</v>
@@ -10712,16 +10712,16 @@
         <v>44848</v>
       </c>
       <c r="B515" t="n">
-        <v>19.1600170135498</v>
+        <v>19.16001892089844</v>
       </c>
       <c r="C515" t="n">
-        <v>19.84025363221523</v>
+        <v>19.84025560728032</v>
       </c>
       <c r="D515" t="n">
-        <v>18.97106149624717</v>
+        <v>18.97106338478559</v>
       </c>
       <c r="E515" t="n">
-        <v>19.84025363221523</v>
+        <v>19.84025560728032</v>
       </c>
       <c r="F515" t="n">
         <v>919650</v>
@@ -10752,16 +10752,16 @@
         <v>44852</v>
       </c>
       <c r="B517" t="n">
-        <v>19.53792953491211</v>
+        <v>19.53792762756348</v>
       </c>
       <c r="C517" t="n">
-        <v>19.7835710279484</v>
+        <v>19.78356909661954</v>
       </c>
       <c r="D517" t="n">
-        <v>19.23560209794857</v>
+        <v>19.23560022011401</v>
       </c>
       <c r="E517" t="n">
-        <v>19.55682545022575</v>
+        <v>19.55682354103244</v>
       </c>
       <c r="F517" t="n">
         <v>665900</v>
@@ -10792,16 +10792,16 @@
         <v>44854</v>
       </c>
       <c r="B519" t="n">
-        <v>19.48124122619629</v>
+        <v>19.48124313354492</v>
       </c>
       <c r="C519" t="n">
-        <v>19.84025456350717</v>
+        <v>19.84025650600569</v>
       </c>
       <c r="D519" t="n">
-        <v>19.19780793693812</v>
+        <v>19.19780981653667</v>
       </c>
       <c r="E519" t="n">
-        <v>19.84025456350717</v>
+        <v>19.84025650600569</v>
       </c>
       <c r="F519" t="n">
         <v>1274100</v>
@@ -10832,16 +10832,16 @@
         <v>44858</v>
       </c>
       <c r="B521" t="n">
-        <v>19.55682182312012</v>
+        <v>19.55682373046875</v>
       </c>
       <c r="C521" t="n">
-        <v>19.85914920401251</v>
+        <v>19.8591511408467</v>
       </c>
       <c r="D521" t="n">
-        <v>19.33007448543749</v>
+        <v>19.33007637067178</v>
       </c>
       <c r="E521" t="n">
-        <v>19.7457755351712</v>
+        <v>19.74577746094821</v>
       </c>
       <c r="F521" t="n">
         <v>947100</v>
@@ -10872,16 +10872,16 @@
         <v>44860</v>
       </c>
       <c r="B523" t="n">
-        <v>18.38530349731445</v>
+        <v>18.38530158996582</v>
       </c>
       <c r="C523" t="n">
-        <v>19.31118350379421</v>
+        <v>19.3111815003919</v>
       </c>
       <c r="D523" t="n">
-        <v>18.06408195459271</v>
+        <v>18.06408008056859</v>
       </c>
       <c r="E523" t="n">
-        <v>18.98996015905884</v>
+        <v>18.98995818898124</v>
       </c>
       <c r="F523" t="n">
         <v>1458850</v>
@@ -10912,16 +10912,16 @@
         <v>44862</v>
       </c>
       <c r="B525" t="n">
-        <v>19.40565872192383</v>
+        <v>19.40566062927246</v>
       </c>
       <c r="C525" t="n">
-        <v>19.74577613474872</v>
+        <v>19.7457780755269</v>
       </c>
       <c r="D525" t="n">
-        <v>18.87658398728353</v>
+        <v>18.87658584263032</v>
       </c>
       <c r="E525" t="n">
-        <v>19.29228504963994</v>
+        <v>19.29228694584527</v>
       </c>
       <c r="F525" t="n">
         <v>1190600</v>
@@ -10932,16 +10932,16 @@
         <v>44865</v>
       </c>
       <c r="B526" t="n">
-        <v>20.46380424499512</v>
+        <v>20.46380805969238</v>
       </c>
       <c r="C526" t="n">
-        <v>20.50159606912895</v>
+        <v>20.50159989087106</v>
       </c>
       <c r="D526" t="n">
-        <v>18.76321180326671</v>
+        <v>18.76321530095325</v>
       </c>
       <c r="E526" t="n">
-        <v>18.78210591332026</v>
+        <v>18.78210941452889</v>
       </c>
       <c r="F526" t="n">
         <v>2299050</v>
@@ -10972,16 +10972,16 @@
         <v>44868</v>
       </c>
       <c r="B528" t="n">
-        <v>21.06846237182617</v>
+        <v>21.06846046447754</v>
       </c>
       <c r="C528" t="n">
-        <v>21.20073197535547</v>
+        <v>21.20073005603234</v>
       </c>
       <c r="D528" t="n">
-        <v>19.97252452551853</v>
+        <v>19.97252271738623</v>
       </c>
       <c r="E528" t="n">
-        <v>20.18037598734444</v>
+        <v>20.18037416039514</v>
       </c>
       <c r="F528" t="n">
         <v>1731950</v>
@@ -10992,16 +10992,16 @@
         <v>44869</v>
       </c>
       <c r="B529" t="n">
-        <v>21.38968467712402</v>
+        <v>21.38968276977539</v>
       </c>
       <c r="C529" t="n">
-        <v>21.74869983803748</v>
+        <v>21.74869789867495</v>
       </c>
       <c r="D529" t="n">
-        <v>21.01177540406793</v>
+        <v>21.011773530418</v>
       </c>
       <c r="E529" t="n">
-        <v>21.40858059128022</v>
+        <v>21.40857868224661</v>
       </c>
       <c r="F529" t="n">
         <v>1653450</v>
@@ -11052,16 +11052,16 @@
         <v>44874</v>
       </c>
       <c r="B532" t="n">
-        <v>18.78210830688477</v>
+        <v>18.7821102142334</v>
       </c>
       <c r="C532" t="n">
-        <v>20.06700165896615</v>
+        <v>20.06700369679745</v>
       </c>
       <c r="D532" t="n">
-        <v>18.61205048265069</v>
+        <v>18.61205237272972</v>
       </c>
       <c r="E532" t="n">
-        <v>19.85915200578211</v>
+        <v>19.85915402250599</v>
       </c>
       <c r="F532" t="n">
         <v>1714900</v>
@@ -11072,16 +11072,16 @@
         <v>44875</v>
       </c>
       <c r="B533" t="n">
-        <v>16.94924736022949</v>
+        <v>16.94924926757812</v>
       </c>
       <c r="C533" t="n">
-        <v>18.51757217595721</v>
+        <v>18.51757425979405</v>
       </c>
       <c r="D533" t="n">
-        <v>16.25011476302671</v>
+        <v>16.2501165916999</v>
       </c>
       <c r="E533" t="n">
-        <v>18.51757217595721</v>
+        <v>18.51757425979405</v>
       </c>
       <c r="F533" t="n">
         <v>6247350</v>
@@ -11092,16 +11092,16 @@
         <v>44876</v>
       </c>
       <c r="B534" t="n">
-        <v>15.51319026947021</v>
+        <v>15.5131893157959</v>
       </c>
       <c r="C534" t="n">
-        <v>16.96814139722099</v>
+        <v>16.96814035410347</v>
       </c>
       <c r="D534" t="n">
-        <v>15.05969824828244</v>
+        <v>15.05969732248658</v>
       </c>
       <c r="E534" t="n">
-        <v>16.94924728539026</v>
+        <v>16.94924624343426</v>
       </c>
       <c r="F534" t="n">
         <v>6426800</v>
@@ -11112,16 +11112,16 @@
         <v>44879</v>
       </c>
       <c r="B535" t="n">
-        <v>15.45650577545166</v>
+        <v>15.45650386810303</v>
       </c>
       <c r="C535" t="n">
-        <v>16.26901032459178</v>
+        <v>16.26900831697925</v>
       </c>
       <c r="D535" t="n">
-        <v>14.88964092120513</v>
+        <v>14.8896390838082</v>
       </c>
       <c r="E535" t="n">
-        <v>15.96668288286395</v>
+        <v>15.96668091255894</v>
       </c>
       <c r="F535" t="n">
         <v>3328550</v>
@@ -11172,16 +11172,16 @@
         <v>44883</v>
       </c>
       <c r="B538" t="n">
-        <v>13.83149242401123</v>
+        <v>13.83149147033691</v>
       </c>
       <c r="C538" t="n">
-        <v>14.88963925247558</v>
+        <v>14.88963822584258</v>
       </c>
       <c r="D538" t="n">
-        <v>13.73701465855629</v>
+        <v>13.73701371139616</v>
       </c>
       <c r="E538" t="n">
-        <v>14.26608852329183</v>
+        <v>14.26608753965234</v>
       </c>
       <c r="F538" t="n">
         <v>3266800</v>
@@ -11212,16 +11212,16 @@
         <v>44887</v>
       </c>
       <c r="B540" t="n">
-        <v>14.09603023529053</v>
+        <v>14.09602832794189</v>
       </c>
       <c r="C540" t="n">
-        <v>14.71958102328215</v>
+        <v>14.71957903156021</v>
       </c>
       <c r="D540" t="n">
-        <v>13.88817967229104</v>
+        <v>13.88817779306689</v>
       </c>
       <c r="E540" t="n">
-        <v>14.60620823464794</v>
+        <v>14.60620625826658</v>
       </c>
       <c r="F540" t="n">
         <v>2112800</v>
@@ -11272,16 +11272,16 @@
         <v>44890</v>
       </c>
       <c r="B543" t="n">
-        <v>14.11492347717285</v>
+        <v>14.11492538452148</v>
       </c>
       <c r="C543" t="n">
-        <v>14.90853379896694</v>
+        <v>14.90853581355609</v>
       </c>
       <c r="D543" t="n">
-        <v>13.94486476607892</v>
+        <v>13.94486665044753</v>
       </c>
       <c r="E543" t="n">
-        <v>14.90853379896694</v>
+        <v>14.90853581355609</v>
       </c>
       <c r="F543" t="n">
         <v>1492900</v>
@@ -11352,16 +11352,16 @@
         <v>44896</v>
       </c>
       <c r="B547" t="n">
-        <v>14.15271472930908</v>
+        <v>14.1527156829834</v>
       </c>
       <c r="C547" t="n">
-        <v>14.51172897371034</v>
+        <v>14.51172995157667</v>
       </c>
       <c r="D547" t="n">
-        <v>14.0393419522887</v>
+        <v>14.03934289832344</v>
       </c>
       <c r="E547" t="n">
-        <v>14.30387933300967</v>
+        <v>14.30388029687014</v>
       </c>
       <c r="F547" t="n">
         <v>1145350</v>
@@ -11372,16 +11372,16 @@
         <v>44897</v>
       </c>
       <c r="B548" t="n">
-        <v>14.28498268127441</v>
+        <v>14.28498363494873</v>
       </c>
       <c r="C548" t="n">
-        <v>14.58731007103471</v>
+        <v>14.58731104489259</v>
       </c>
       <c r="D548" t="n">
-        <v>14.05823713895419</v>
+        <v>14.05823807749083</v>
       </c>
       <c r="E548" t="n">
-        <v>14.1716099101143</v>
+        <v>14.17161085621978</v>
       </c>
       <c r="F548" t="n">
         <v>1219600</v>
@@ -11412,16 +11412,16 @@
         <v>44901</v>
       </c>
       <c r="B550" t="n">
-        <v>13.15125560760498</v>
+        <v>13.15125370025635</v>
       </c>
       <c r="C550" t="n">
-        <v>13.66143358802902</v>
+        <v>13.66143160668842</v>
       </c>
       <c r="D550" t="n">
-        <v>12.67886855532321</v>
+        <v>12.67886671648566</v>
       </c>
       <c r="E550" t="n">
-        <v>13.54806080360221</v>
+        <v>13.54805883870426</v>
       </c>
       <c r="F550" t="n">
         <v>4313950</v>
@@ -11512,16 +11512,16 @@
         <v>44908</v>
       </c>
       <c r="B555" t="n">
-        <v>11.58292961120605</v>
+        <v>11.58293056488037</v>
       </c>
       <c r="C555" t="n">
-        <v>12.22537532711658</v>
+        <v>12.22537633368632</v>
       </c>
       <c r="D555" t="n">
-        <v>11.48845184953939</v>
+        <v>11.48845279543493</v>
       </c>
       <c r="E555" t="n">
-        <v>11.97973476859532</v>
+        <v>11.97973575494038</v>
       </c>
       <c r="F555" t="n">
         <v>2082000</v>
@@ -11552,16 +11552,16 @@
         <v>44910</v>
       </c>
       <c r="B557" t="n">
-        <v>11.5640344619751</v>
+        <v>11.56403541564941</v>
       </c>
       <c r="C557" t="n">
-        <v>11.9041537056258</v>
+        <v>11.90415468734941</v>
       </c>
       <c r="D557" t="n">
-        <v>11.2617070462916</v>
+        <v>11.26170797503327</v>
       </c>
       <c r="E557" t="n">
-        <v>11.41287075413335</v>
+        <v>11.41287169534134</v>
       </c>
       <c r="F557" t="n">
         <v>3167400</v>
@@ -11692,16 +11692,16 @@
         <v>44921</v>
       </c>
       <c r="B564" t="n">
-        <v>13.17014980316162</v>
+        <v>13.17015075683594</v>
       </c>
       <c r="C564" t="n">
-        <v>13.49137312292281</v>
+        <v>13.49137409985749</v>
       </c>
       <c r="D564" t="n">
-        <v>12.83003147100628</v>
+        <v>12.83003240005202</v>
       </c>
       <c r="E564" t="n">
-        <v>13.41579127133274</v>
+        <v>13.4157922427944</v>
       </c>
       <c r="F564" t="n">
         <v>1094200</v>
@@ -11732,16 +11732,16 @@
         <v>44923</v>
       </c>
       <c r="B566" t="n">
-        <v>13.10084915161133</v>
+        <v>13.10085010528564</v>
       </c>
       <c r="C566" t="n">
-        <v>13.1201439219793</v>
+        <v>13.12014487705818</v>
       </c>
       <c r="D566" t="n">
-        <v>12.29048719666213</v>
+        <v>12.29048809134627</v>
       </c>
       <c r="E566" t="n">
-        <v>12.46413644987275</v>
+        <v>12.46413735719766</v>
       </c>
       <c r="F566" t="n">
         <v>2129050</v>
@@ -11772,16 +11772,16 @@
         <v>44928</v>
       </c>
       <c r="B568" t="n">
-        <v>12.21331024169922</v>
+        <v>12.21331119537354</v>
       </c>
       <c r="C568" t="n">
-        <v>12.83072910757643</v>
+        <v>12.83073010946179</v>
       </c>
       <c r="D568" t="n">
-        <v>11.98177851200476</v>
+        <v>11.98177944759996</v>
       </c>
       <c r="E568" t="n">
-        <v>12.83072910757643</v>
+        <v>12.83073010946179</v>
       </c>
       <c r="F568" t="n">
         <v>1499800</v>
@@ -11792,16 +11792,16 @@
         <v>44929</v>
       </c>
       <c r="B569" t="n">
-        <v>11.65377521514893</v>
+        <v>11.65377616882324</v>
       </c>
       <c r="C569" t="n">
-        <v>12.21331071004653</v>
+        <v>12.21331170950984</v>
       </c>
       <c r="D569" t="n">
-        <v>11.59589274051833</v>
+        <v>11.5958936894559</v>
       </c>
       <c r="E569" t="n">
-        <v>12.21331071004653</v>
+        <v>12.21331170950984</v>
       </c>
       <c r="F569" t="n">
         <v>2015100</v>
@@ -11852,16 +11852,16 @@
         <v>44932</v>
       </c>
       <c r="B572" t="n">
-        <v>13.08155727386475</v>
+        <v>13.08155632019043</v>
       </c>
       <c r="C572" t="n">
-        <v>13.13943975364632</v>
+        <v>13.13943879575224</v>
       </c>
       <c r="D572" t="n">
-        <v>12.44484355608945</v>
+        <v>12.44484264883297</v>
       </c>
       <c r="E572" t="n">
-        <v>12.7342587150736</v>
+        <v>12.73425778671811</v>
       </c>
       <c r="F572" t="n">
         <v>1382000</v>
@@ -11892,16 +11892,16 @@
         <v>44936</v>
       </c>
       <c r="B574" t="n">
-        <v>13.85332870483398</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C574" t="n">
-        <v>14.0076841187254</v>
+        <v>14.00768508302567</v>
       </c>
       <c r="D574" t="n">
-        <v>13.04296761203716</v>
+        <v>13.04296850992557</v>
       </c>
       <c r="E574" t="n">
-        <v>13.17802733415729</v>
+        <v>13.17802824134331</v>
       </c>
       <c r="F574" t="n">
         <v>2939000</v>
@@ -11952,16 +11952,16 @@
         <v>44939</v>
       </c>
       <c r="B577" t="n">
-        <v>13.33238124847412</v>
+        <v>13.33238220214844</v>
       </c>
       <c r="C577" t="n">
-        <v>13.4867357356305</v>
+        <v>13.4867367003459</v>
       </c>
       <c r="D577" t="n">
-        <v>13.13943813952864</v>
+        <v>13.13943907940161</v>
       </c>
       <c r="E577" t="n">
-        <v>13.42885326295952</v>
+        <v>13.42885422353454</v>
       </c>
       <c r="F577" t="n">
         <v>1373850</v>
@@ -12052,16 +12052,16 @@
         <v>44946</v>
       </c>
       <c r="B582" t="n">
-        <v>14.06556606292725</v>
+        <v>14.06556701660156</v>
       </c>
       <c r="C582" t="n">
-        <v>14.12344945595456</v>
+        <v>14.12345041355349</v>
       </c>
       <c r="D582" t="n">
-        <v>13.50603058377296</v>
+        <v>13.50603149950962</v>
       </c>
       <c r="E582" t="n">
-        <v>13.73756231583157</v>
+        <v>13.73756324726655</v>
       </c>
       <c r="F582" t="n">
         <v>2454200</v>
@@ -12152,16 +12152,16 @@
         <v>44953</v>
       </c>
       <c r="B587" t="n">
-        <v>14.35498237609863</v>
+        <v>14.35498142242432</v>
       </c>
       <c r="C587" t="n">
-        <v>14.6443975251379</v>
+        <v>14.64439655223626</v>
       </c>
       <c r="D587" t="n">
-        <v>14.29709897828062</v>
+        <v>14.29709802845179</v>
       </c>
       <c r="E587" t="n">
-        <v>14.56722027473081</v>
+        <v>14.56721930695646</v>
       </c>
       <c r="F587" t="n">
         <v>1566450</v>
@@ -12172,16 +12172,16 @@
         <v>44956</v>
       </c>
       <c r="B588" t="n">
-        <v>14.39357089996338</v>
+        <v>14.39356994628906</v>
       </c>
       <c r="C588" t="n">
-        <v>14.66369127448637</v>
+        <v>14.6636903029147</v>
       </c>
       <c r="D588" t="n">
-        <v>14.31639365009966</v>
+        <v>14.31639270153888</v>
       </c>
       <c r="E588" t="n">
-        <v>14.37427612748476</v>
+        <v>14.37427517508885</v>
       </c>
       <c r="F588" t="n">
         <v>1160300</v>
@@ -12192,16 +12192,16 @@
         <v>44957</v>
       </c>
       <c r="B589" t="n">
-        <v>14.99169445037842</v>
+        <v>14.99169540405273</v>
       </c>
       <c r="C589" t="n">
-        <v>15.04957784548756</v>
+        <v>15.04957880284405</v>
       </c>
       <c r="D589" t="n">
-        <v>14.39357032770223</v>
+        <v>14.39357124332777</v>
       </c>
       <c r="E589" t="n">
-        <v>14.41286417938838</v>
+        <v>14.41286509624127</v>
       </c>
       <c r="F589" t="n">
         <v>1759050</v>
@@ -12212,16 +12212,16 @@
         <v>44958</v>
       </c>
       <c r="B590" t="n">
-        <v>14.99169445037842</v>
+        <v>14.99169540405273</v>
       </c>
       <c r="C590" t="n">
-        <v>15.1653437156805</v>
+        <v>15.16534468040126</v>
       </c>
       <c r="D590" t="n">
-        <v>14.74086793828104</v>
+        <v>14.7408688759994</v>
       </c>
       <c r="E590" t="n">
-        <v>14.97240059869227</v>
+        <v>14.97240155113924</v>
       </c>
       <c r="F590" t="n">
         <v>1831550</v>
@@ -12372,16 +12372,16 @@
         <v>44970</v>
       </c>
       <c r="B598" t="n">
-        <v>14.12345027923584</v>
+        <v>14.12344932556152</v>
       </c>
       <c r="C598" t="n">
-        <v>14.62510239460502</v>
+        <v>14.62510140705705</v>
       </c>
       <c r="D598" t="n">
-        <v>13.9690948621738</v>
+        <v>13.9690939189222</v>
       </c>
       <c r="E598" t="n">
-        <v>14.04627303071751</v>
+        <v>14.04627208225452</v>
       </c>
       <c r="F598" t="n">
         <v>1583800</v>
@@ -12392,16 +12392,16 @@
         <v>44971</v>
       </c>
       <c r="B599" t="n">
-        <v>13.96909523010254</v>
+        <v>13.96909427642822</v>
       </c>
       <c r="C599" t="n">
-        <v>14.50933690398556</v>
+        <v>14.50933591342878</v>
       </c>
       <c r="D599" t="n">
-        <v>13.69897485317373</v>
+        <v>13.69897391794061</v>
       </c>
       <c r="E599" t="n">
-        <v>14.35498240288338</v>
+        <v>14.35498142286443</v>
       </c>
       <c r="F599" t="n">
         <v>2796000</v>
@@ -12412,16 +12412,16 @@
         <v>44972</v>
       </c>
       <c r="B600" t="n">
-        <v>14.83734035491943</v>
+        <v>14.83734130859375</v>
       </c>
       <c r="C600" t="n">
-        <v>15.04957824931416</v>
+        <v>15.04957921663013</v>
       </c>
       <c r="D600" t="n">
-        <v>13.73756317853808</v>
+        <v>13.7375640615239</v>
       </c>
       <c r="E600" t="n">
-        <v>14.00768446959514</v>
+        <v>14.00768536994309</v>
       </c>
       <c r="F600" t="n">
         <v>2808050</v>
@@ -12492,16 +12492,16 @@
         <v>44980</v>
       </c>
       <c r="B604" t="n">
-        <v>14.41286468505859</v>
+        <v>14.41286563873291</v>
       </c>
       <c r="C604" t="n">
-        <v>14.91451772685366</v>
+        <v>14.91451871372149</v>
       </c>
       <c r="D604" t="n">
-        <v>14.27780495844099</v>
+        <v>14.27780590317863</v>
       </c>
       <c r="E604" t="n">
-        <v>14.66369120595613</v>
+        <v>14.6636921762272</v>
       </c>
       <c r="F604" t="n">
         <v>1540800</v>
@@ -12552,16 +12552,16 @@
         <v>44985</v>
       </c>
       <c r="B607" t="n">
-        <v>13.85332870483398</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C607" t="n">
-        <v>14.0076841187254</v>
+        <v>14.00768508302567</v>
       </c>
       <c r="D607" t="n">
-        <v>13.48673632188941</v>
+        <v>13.48673725032721</v>
       </c>
       <c r="E607" t="n">
-        <v>13.71826898271386</v>
+        <v>13.71826992709055</v>
       </c>
       <c r="F607" t="n">
         <v>1742300</v>
@@ -12572,16 +12572,16 @@
         <v>44986</v>
       </c>
       <c r="B608" t="n">
-        <v>13.48673629760742</v>
+        <v>13.48673725128174</v>
       </c>
       <c r="C608" t="n">
-        <v>13.85332867989197</v>
+        <v>13.85332965948877</v>
       </c>
       <c r="D608" t="n">
-        <v>13.21661593382815</v>
+        <v>13.21661686840171</v>
       </c>
       <c r="E608" t="n">
-        <v>13.85332867989197</v>
+        <v>13.85332965948877</v>
       </c>
       <c r="F608" t="n">
         <v>2358750</v>
@@ -12632,16 +12632,16 @@
         <v>44991</v>
       </c>
       <c r="B611" t="n">
-        <v>14.12345027923584</v>
+        <v>14.12344932556152</v>
       </c>
       <c r="C611" t="n">
-        <v>14.25851000413024</v>
+        <v>14.25850904133613</v>
       </c>
       <c r="D611" t="n">
-        <v>13.35167687402712</v>
+        <v>13.35167597246616</v>
       </c>
       <c r="E611" t="n">
-        <v>13.35167687402712</v>
+        <v>13.35167597246616</v>
       </c>
       <c r="F611" t="n">
         <v>2062900</v>
@@ -12672,16 +12672,16 @@
         <v>44993</v>
       </c>
       <c r="B613" t="n">
-        <v>15.85993957519531</v>
+        <v>15.85994148254395</v>
       </c>
       <c r="C613" t="n">
-        <v>15.85993957519531</v>
+        <v>15.85994148254395</v>
       </c>
       <c r="D613" t="n">
-        <v>14.16203833580244</v>
+        <v>14.16204003895802</v>
       </c>
       <c r="E613" t="n">
-        <v>14.68298520243147</v>
+        <v>14.68298696823717</v>
       </c>
       <c r="F613" t="n">
         <v>5225650</v>
@@ -12752,16 +12752,16 @@
         <v>44999</v>
       </c>
       <c r="B617" t="n">
-        <v>14.9724006652832</v>
+        <v>14.97240161895752</v>
       </c>
       <c r="C617" t="n">
-        <v>15.89852763094573</v>
+        <v>15.89852864361015</v>
       </c>
       <c r="D617" t="n">
-        <v>14.77945662741149</v>
+        <v>14.77945756879614</v>
       </c>
       <c r="E617" t="n">
-        <v>15.53193616705032</v>
+        <v>15.53193715636452</v>
       </c>
       <c r="F617" t="n">
         <v>2100150</v>
@@ -12772,16 +12772,16 @@
         <v>45000</v>
       </c>
       <c r="B618" t="n">
-        <v>15.31969928741455</v>
+        <v>15.31969833374023</v>
       </c>
       <c r="C618" t="n">
-        <v>15.47405471189345</v>
+        <v>15.47405374861028</v>
       </c>
       <c r="D618" t="n">
-        <v>14.4514538198256</v>
+        <v>14.45145292020087</v>
       </c>
       <c r="E618" t="n">
-        <v>14.64439787041787</v>
+        <v>14.64439695878208</v>
       </c>
       <c r="F618" t="n">
         <v>2068400</v>
@@ -12832,16 +12832,16 @@
         <v>45005</v>
       </c>
       <c r="B621" t="n">
-        <v>13.96909523010254</v>
+        <v>13.96909427642822</v>
       </c>
       <c r="C621" t="n">
-        <v>15.33899280742245</v>
+        <v>15.33899176022482</v>
       </c>
       <c r="D621" t="n">
-        <v>13.94980137747747</v>
+        <v>13.94980042512035</v>
       </c>
       <c r="E621" t="n">
-        <v>15.1653444536952</v>
+        <v>15.16534341835259</v>
       </c>
       <c r="F621" t="n">
         <v>2781400</v>
@@ -12972,16 +12972,16 @@
         <v>45014</v>
       </c>
       <c r="B628" t="n">
-        <v>14.14274406433105</v>
+        <v>14.14274501800537</v>
       </c>
       <c r="C628" t="n">
-        <v>14.41286443286514</v>
+        <v>14.41286540475423</v>
       </c>
       <c r="D628" t="n">
-        <v>13.75685782356807</v>
+        <v>13.75685875122129</v>
       </c>
       <c r="E628" t="n">
-        <v>14.41286443286514</v>
+        <v>14.41286540475423</v>
       </c>
       <c r="F628" t="n">
         <v>1398800</v>
@@ -13032,16 +13032,16 @@
         <v>45019</v>
       </c>
       <c r="B631" t="n">
-        <v>13.83403587341309</v>
+        <v>13.83403491973877</v>
       </c>
       <c r="C631" t="n">
-        <v>14.49004344075163</v>
+        <v>14.49004244185425</v>
       </c>
       <c r="D631" t="n">
-        <v>13.62179796868142</v>
+        <v>13.62179702963811</v>
       </c>
       <c r="E631" t="n">
-        <v>14.39357141495758</v>
+        <v>14.39357042271067</v>
       </c>
       <c r="F631" t="n">
         <v>1766300</v>
@@ -13072,16 +13072,16 @@
         <v>45021</v>
       </c>
       <c r="B633" t="n">
-        <v>13.85332870483398</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C633" t="n">
-        <v>14.29709833471159</v>
+        <v>14.29709931893536</v>
       </c>
       <c r="D633" t="n">
-        <v>13.66038558750141</v>
+        <v>13.66038652789336</v>
       </c>
       <c r="E633" t="n">
-        <v>14.18133246431204</v>
+        <v>14.1813334405664</v>
       </c>
       <c r="F633" t="n">
         <v>2634950</v>
@@ -13092,16 +13092,16 @@
         <v>45022</v>
       </c>
       <c r="B634" t="n">
-        <v>14.14274406433105</v>
+        <v>14.14274501800537</v>
       </c>
       <c r="C634" t="n">
-        <v>14.29709856063625</v>
+        <v>14.297099524719</v>
       </c>
       <c r="D634" t="n">
-        <v>13.77615167559354</v>
+        <v>13.77615260454778</v>
       </c>
       <c r="E634" t="n">
-        <v>13.85332892374614</v>
+        <v>13.85332985790459</v>
       </c>
       <c r="F634" t="n">
         <v>1739850</v>
@@ -13112,16 +13112,16 @@
         <v>45026</v>
       </c>
       <c r="B635" t="n">
-        <v>13.96909523010254</v>
+        <v>13.96909427642822</v>
       </c>
       <c r="C635" t="n">
-        <v>14.2006279017812</v>
+        <v>14.20062693230008</v>
       </c>
       <c r="D635" t="n">
-        <v>13.89191797955145</v>
+        <v>13.89191703114605</v>
       </c>
       <c r="E635" t="n">
-        <v>13.94980137747747</v>
+        <v>13.94980042512035</v>
       </c>
       <c r="F635" t="n">
         <v>1451200</v>
@@ -13152,16 +13152,16 @@
         <v>45028</v>
       </c>
       <c r="B637" t="n">
-        <v>15.45475959777832</v>
+        <v>15.454758644104</v>
       </c>
       <c r="C637" t="n">
-        <v>15.7827633725165</v>
+        <v>15.78276239860189</v>
       </c>
       <c r="D637" t="n">
-        <v>15.14604967565836</v>
+        <v>15.14604874103375</v>
       </c>
       <c r="E637" t="n">
-        <v>15.31969894934925</v>
+        <v>15.31969800400918</v>
       </c>
       <c r="F637" t="n">
         <v>3667400</v>
@@ -13192,16 +13192,16 @@
         <v>45030</v>
       </c>
       <c r="B639" t="n">
-        <v>15.6091136932373</v>
+        <v>15.60911273956299</v>
       </c>
       <c r="C639" t="n">
-        <v>15.91782268731036</v>
+        <v>15.91782171477476</v>
       </c>
       <c r="D639" t="n">
-        <v>15.12675542998548</v>
+        <v>15.12675450578194</v>
       </c>
       <c r="E639" t="n">
-        <v>15.68629094175557</v>
+        <v>15.68628998336593</v>
       </c>
       <c r="F639" t="n">
         <v>1580050</v>
@@ -13212,16 +13212,16 @@
         <v>45033</v>
       </c>
       <c r="B640" t="n">
-        <v>15.5319356918335</v>
+        <v>15.53193664550781</v>
       </c>
       <c r="C640" t="n">
-        <v>15.76346742616516</v>
+        <v>15.76346839405572</v>
       </c>
       <c r="D640" t="n">
-        <v>15.49334614941956</v>
+        <v>15.49334710072444</v>
       </c>
       <c r="E640" t="n">
-        <v>15.60911293661072</v>
+        <v>15.60911389502378</v>
       </c>
       <c r="F640" t="n">
         <v>1212550</v>
@@ -13232,16 +13232,16 @@
         <v>45034</v>
       </c>
       <c r="B641" t="n">
-        <v>15.06887245178223</v>
+        <v>15.06887149810791</v>
       </c>
       <c r="C641" t="n">
-        <v>15.74417385507098</v>
+        <v>15.74417285865839</v>
       </c>
       <c r="D641" t="n">
-        <v>14.87592932513193</v>
+        <v>14.87592838366854</v>
       </c>
       <c r="E641" t="n">
-        <v>15.6284088991062</v>
+        <v>15.62840791002011</v>
       </c>
       <c r="F641" t="n">
         <v>1695600</v>
@@ -13272,16 +13272,16 @@
         <v>45036</v>
       </c>
       <c r="B643" t="n">
-        <v>14.93381214141846</v>
+        <v>14.93381118774414</v>
       </c>
       <c r="C643" t="n">
-        <v>14.93381214141846</v>
+        <v>14.93381118774414</v>
       </c>
       <c r="D643" t="n">
-        <v>14.29709934903595</v>
+        <v>14.29709843602215</v>
       </c>
       <c r="E643" t="n">
-        <v>14.43216000076346</v>
+        <v>14.43215907912469</v>
       </c>
       <c r="F643" t="n">
         <v>1458900</v>
@@ -29629,162 +29629,142 @@
     </row>
     <row r="1461">
       <c r="A1461" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1461" t="n">
-        <v>7.710000038146973</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="C1461" t="n">
-        <v>7.760000228881836</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="D1461" t="n">
-        <v>7.579999923706055</v>
+        <v>7.429999828338623</v>
       </c>
       <c r="E1461" t="n">
-        <v>7.730000019073486</v>
+        <v>7.769999980926514</v>
       </c>
       <c r="F1461" t="n">
-        <v>1129300</v>
+        <v>2238200</v>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1462" t="n">
-        <v>7.550000190734863</v>
+        <v>7.559999942779541</v>
       </c>
       <c r="C1462" t="n">
-        <v>7.900000095367432</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="D1462" t="n">
-        <v>7.429999828338623</v>
+        <v>7.46999979019165</v>
       </c>
       <c r="E1462" t="n">
-        <v>7.769999980926514</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="F1462" t="n">
-        <v>2238200</v>
+        <v>2511600</v>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1463" t="n">
-        <v>7.559999942779541</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="C1463" t="n">
-        <v>7.849999904632568</v>
+        <v>7.829999923706055</v>
       </c>
       <c r="D1463" t="n">
-        <v>7.46999979019165</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="E1463" t="n">
-        <v>7.659999847412109</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="F1463" t="n">
-        <v>2511600</v>
+        <v>1601500</v>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1464" t="n">
-        <v>7.659999847412109</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="C1464" t="n">
-        <v>7.829999923706055</v>
+        <v>7.630000114440918</v>
       </c>
       <c r="D1464" t="n">
-        <v>7.599999904632568</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="E1464" t="n">
-        <v>7.599999904632568</v>
+        <v>7.610000133514404</v>
       </c>
       <c r="F1464" t="n">
-        <v>1601500</v>
+        <v>3215300</v>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1465" t="n">
-        <v>7.139999866485596</v>
+        <v>7.039999961853027</v>
       </c>
       <c r="C1465" t="n">
-        <v>7.630000114440918</v>
+        <v>7.210000038146973</v>
       </c>
       <c r="D1465" t="n">
-        <v>7.139999866485596</v>
+        <v>6.940000057220459</v>
       </c>
       <c r="E1465" t="n">
-        <v>7.610000133514404</v>
+        <v>7.190000057220459</v>
       </c>
       <c r="F1465" t="n">
-        <v>3215300</v>
+        <v>2229400</v>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B1466" t="n">
-        <v>7.039999961853027</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="C1466" t="n">
-        <v>7.210000038146973</v>
+        <v>6.840000152587891</v>
       </c>
       <c r="D1466" t="n">
-        <v>6.940000057220459</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="E1466" t="n">
-        <v>7.190000057220459</v>
+        <v>6.78000020980835</v>
       </c>
       <c r="F1466" t="n">
-        <v>2229400</v>
+        <v>5571600</v>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B1467" t="n">
-        <v>6.75</v>
+        <v>6.21</v>
       </c>
       <c r="C1467" t="n">
-        <v>7.079999923706055</v>
+        <v>6.27</v>
       </c>
       <c r="D1467" t="n">
-        <v>6.71999979019165</v>
+        <v>6.08</v>
       </c>
       <c r="E1467" t="n">
-        <v>7.039999961853027</v>
+        <v>6.25</v>
       </c>
       <c r="F1467" t="n">
-        <v>1860600</v>
-      </c>
-    </row>
-    <row r="1468">
-      <c r="A1468" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B1468" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="C1468" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="D1468" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="E1468" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="F1468" t="n">
-        <v>5571600</v>
+        <v>2934800</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1467"/>
+  <dimension ref="A1:F1468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44092</v>
       </c>
       <c r="B2" t="n">
-        <v>13.02992820739746</v>
+        <v>13.02992725372314</v>
       </c>
       <c r="C2" t="n">
-        <v>13.73904012484181</v>
+        <v>13.73903911926684</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63548506786634</v>
+        <v>12.63548414306174</v>
       </c>
       <c r="E2" t="n">
-        <v>13.38448458878317</v>
+        <v>13.3844836091585</v>
       </c>
       <c r="F2" t="n">
         <v>539400</v>
@@ -472,16 +472,16 @@
         <v>44095</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59559631347656</v>
+        <v>12.59559535980225</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80832961567333</v>
+        <v>12.80832864589193</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45377411201205</v>
+        <v>12.45377316907579</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46706941506998</v>
+        <v>12.46706847112706</v>
       </c>
       <c r="F3" t="n">
         <v>1323800</v>
@@ -492,16 +492,16 @@
         <v>44096</v>
       </c>
       <c r="B4" t="n">
-        <v>12.58673286437988</v>
+        <v>12.58673191070557</v>
       </c>
       <c r="C4" t="n">
-        <v>12.77287472474392</v>
+        <v>12.77287375696596</v>
       </c>
       <c r="D4" t="n">
-        <v>12.43161450652202</v>
+        <v>12.43161356460074</v>
       </c>
       <c r="E4" t="n">
-        <v>12.44491065559339</v>
+        <v>12.44490971266469</v>
       </c>
       <c r="F4" t="n">
         <v>1698000</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513423919678</v>
+        <v>12.36513614654541</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366113163458</v>
+        <v>12.49366305880876</v>
       </c>
       <c r="D7" t="n">
-        <v>12.32081459196557</v>
+        <v>12.3208164924778</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377353365919</v>
+        <v>12.45377545468063</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -612,16 +612,16 @@
         <v>44104</v>
       </c>
       <c r="B10" t="n">
-        <v>11.2615795135498</v>
+        <v>11.26158046722412</v>
       </c>
       <c r="C10" t="n">
-        <v>11.49647305588496</v>
+        <v>11.49647402945097</v>
       </c>
       <c r="D10" t="n">
-        <v>11.19510046430838</v>
+        <v>11.19510141235299</v>
       </c>
       <c r="E10" t="n">
-        <v>11.28373891485462</v>
+        <v>11.28373987040548</v>
       </c>
       <c r="F10" t="n">
         <v>764200</v>
@@ -692,16 +692,16 @@
         <v>44110</v>
       </c>
       <c r="B14" t="n">
-        <v>11.43885898590088</v>
+        <v>11.43885803222656</v>
       </c>
       <c r="C14" t="n">
-        <v>12.05490040998342</v>
+        <v>12.05489940494884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.38124402661904</v>
+        <v>11.38124307774816</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5895453044252</v>
+        <v>11.58954433818795</v>
       </c>
       <c r="F14" t="n">
         <v>472800</v>
@@ -732,16 +732,16 @@
         <v>44112</v>
       </c>
       <c r="B16" t="n">
-        <v>11.5230655670166</v>
+        <v>11.52306365966797</v>
       </c>
       <c r="C16" t="n">
-        <v>11.90421339089181</v>
+        <v>11.90421142045391</v>
       </c>
       <c r="D16" t="n">
-        <v>11.39010745629723</v>
+        <v>11.39010557095641</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68261597614149</v>
+        <v>11.68261404238337</v>
       </c>
       <c r="F16" t="n">
         <v>595200</v>
@@ -752,16 +752,16 @@
         <v>44113</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10365104675293</v>
+        <v>12.10365009307861</v>
       </c>
       <c r="C17" t="n">
-        <v>12.29422496640223</v>
+        <v>12.29422399771216</v>
       </c>
       <c r="D17" t="n">
-        <v>11.53193013313212</v>
+        <v>11.531929224505</v>
       </c>
       <c r="E17" t="n">
-        <v>11.53636218304571</v>
+        <v>11.53636127406939</v>
       </c>
       <c r="F17" t="n">
         <v>672400</v>
@@ -772,16 +772,16 @@
         <v>44117</v>
       </c>
       <c r="B18" t="n">
-        <v>12.18785667419434</v>
+        <v>12.18785762786865</v>
       </c>
       <c r="C18" t="n">
-        <v>12.44934166683048</v>
+        <v>12.44934264096545</v>
       </c>
       <c r="D18" t="n">
-        <v>12.18785667419434</v>
+        <v>12.18785762786865</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36956646971071</v>
+        <v>12.36956743760344</v>
       </c>
       <c r="F18" t="n">
         <v>440800</v>
@@ -792,16 +792,16 @@
         <v>44118</v>
       </c>
       <c r="B19" t="n">
-        <v>12.13024234771729</v>
+        <v>12.1302433013916</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63105211214986</v>
+        <v>12.63105310519763</v>
       </c>
       <c r="D19" t="n">
-        <v>12.00614749633282</v>
+        <v>12.00614844025086</v>
       </c>
       <c r="E19" t="n">
-        <v>12.18785730119724</v>
+        <v>12.18785825940122</v>
       </c>
       <c r="F19" t="n">
         <v>441800</v>
@@ -912,16 +912,16 @@
         <v>44126</v>
       </c>
       <c r="B25" t="n">
-        <v>13.06981658935547</v>
+        <v>13.06981563568115</v>
       </c>
       <c r="C25" t="n">
-        <v>13.21163881222637</v>
+        <v>13.21163784820361</v>
       </c>
       <c r="D25" t="n">
-        <v>12.6975328316558</v>
+        <v>12.69753190514617</v>
       </c>
       <c r="E25" t="n">
-        <v>12.75071658789595</v>
+        <v>12.75071565750562</v>
       </c>
       <c r="F25" t="n">
         <v>963600</v>
@@ -992,16 +992,16 @@
         <v>44132</v>
       </c>
       <c r="B29" t="n">
-        <v>11.43885898590088</v>
+        <v>11.43885803222656</v>
       </c>
       <c r="C29" t="n">
-        <v>11.9263734961074</v>
+        <v>11.92637250178829</v>
       </c>
       <c r="D29" t="n">
-        <v>11.30146881736179</v>
+        <v>11.3014678751419</v>
       </c>
       <c r="E29" t="n">
-        <v>11.9263734961074</v>
+        <v>11.92637250178829</v>
       </c>
       <c r="F29" t="n">
         <v>860400</v>
@@ -1012,16 +1012,16 @@
         <v>44133</v>
       </c>
       <c r="B30" t="n">
-        <v>11.70477485656738</v>
+        <v>11.70477390289307</v>
       </c>
       <c r="C30" t="n">
-        <v>11.87762056184598</v>
+        <v>11.87761959408865</v>
       </c>
       <c r="D30" t="n">
-        <v>11.00895914058972</v>
+        <v>11.00895824360864</v>
       </c>
       <c r="E30" t="n">
-        <v>11.39453815164614</v>
+        <v>11.3945372232491</v>
       </c>
       <c r="F30" t="n">
         <v>683400</v>
@@ -1032,16 +1032,16 @@
         <v>44134</v>
       </c>
       <c r="B31" t="n">
-        <v>11.38567638397217</v>
+        <v>11.38567543029785</v>
       </c>
       <c r="C31" t="n">
-        <v>11.8111430510602</v>
+        <v>11.81114206174842</v>
       </c>
       <c r="D31" t="n">
-        <v>11.00896057749186</v>
+        <v>11.00895965537159</v>
       </c>
       <c r="E31" t="n">
-        <v>11.8111430510602</v>
+        <v>11.81114206174842</v>
       </c>
       <c r="F31" t="n">
         <v>907200</v>
@@ -1072,16 +1072,16 @@
         <v>44139</v>
       </c>
       <c r="B33" t="n">
-        <v>12.57786846160889</v>
+        <v>12.57786750793457</v>
       </c>
       <c r="C33" t="n">
-        <v>12.78173851581722</v>
+        <v>12.78173754668514</v>
       </c>
       <c r="D33" t="n">
-        <v>11.90421298612225</v>
+        <v>11.90421208352558</v>
       </c>
       <c r="E33" t="n">
-        <v>11.96625998963795</v>
+        <v>11.96625908233677</v>
       </c>
       <c r="F33" t="n">
         <v>620400</v>
@@ -1092,16 +1092,16 @@
         <v>44140</v>
       </c>
       <c r="B34" t="n">
-        <v>12.79503536224365</v>
+        <v>12.79503440856934</v>
       </c>
       <c r="C34" t="n">
-        <v>13.02992808569082</v>
+        <v>13.02992711450884</v>
       </c>
       <c r="D34" t="n">
-        <v>12.63991699966924</v>
+        <v>12.63991605755662</v>
       </c>
       <c r="E34" t="n">
-        <v>12.78617126259321</v>
+        <v>12.78617030957958</v>
       </c>
       <c r="F34" t="n">
         <v>682600</v>
@@ -1132,16 +1132,16 @@
         <v>44144</v>
       </c>
       <c r="B36" t="n">
-        <v>13.2958459854126</v>
+        <v>13.29584407806396</v>
       </c>
       <c r="C36" t="n">
-        <v>13.96950238488535</v>
+        <v>13.96950038089769</v>
       </c>
       <c r="D36" t="n">
-        <v>13.12300025810691</v>
+        <v>13.12299837555377</v>
       </c>
       <c r="E36" t="n">
-        <v>13.73904085159302</v>
+        <v>13.7390388806661</v>
       </c>
       <c r="F36" t="n">
         <v>650800</v>
@@ -1152,16 +1152,16 @@
         <v>44145</v>
       </c>
       <c r="B37" t="n">
-        <v>13.15845394134521</v>
+        <v>13.15845489501953</v>
       </c>
       <c r="C37" t="n">
-        <v>13.57948849711368</v>
+        <v>13.57948948130297</v>
       </c>
       <c r="D37" t="n">
-        <v>13.07867874153117</v>
+        <v>13.07867968942368</v>
       </c>
       <c r="E37" t="n">
-        <v>13.07867874153117</v>
+        <v>13.07867968942368</v>
       </c>
       <c r="F37" t="n">
         <v>489600</v>
@@ -1172,16 +1172,16 @@
         <v>44146</v>
       </c>
       <c r="B38" t="n">
-        <v>13.2958459854126</v>
+        <v>13.29584407806396</v>
       </c>
       <c r="C38" t="n">
-        <v>13.41994085226088</v>
+        <v>13.41993892711028</v>
       </c>
       <c r="D38" t="n">
-        <v>12.89697077491564</v>
+        <v>12.89696892478745</v>
       </c>
       <c r="E38" t="n">
-        <v>13.25152632972913</v>
+        <v>13.25152442873835</v>
       </c>
       <c r="F38" t="n">
         <v>586400</v>
@@ -1292,16 +1292,16 @@
         <v>44154</v>
       </c>
       <c r="B44" t="n">
-        <v>12.99447250366211</v>
+        <v>12.99447154998779</v>
       </c>
       <c r="C44" t="n">
-        <v>13.0742477096854</v>
+        <v>13.07424675015632</v>
       </c>
       <c r="D44" t="n">
-        <v>12.48036655965319</v>
+        <v>12.4803656437095</v>
       </c>
       <c r="E44" t="n">
-        <v>12.74185158147306</v>
+        <v>12.74185064633879</v>
       </c>
       <c r="F44" t="n">
         <v>711400</v>
@@ -1332,16 +1332,16 @@
         <v>44159</v>
       </c>
       <c r="B46" t="n">
-        <v>13.73903846740723</v>
+        <v>13.73903942108154</v>
       </c>
       <c r="C46" t="n">
-        <v>13.82767776339226</v>
+        <v>13.82767872321933</v>
       </c>
       <c r="D46" t="n">
-        <v>13.27368427680326</v>
+        <v>13.27368519817572</v>
       </c>
       <c r="E46" t="n">
-        <v>13.47312142477911</v>
+        <v>13.4731223599952</v>
       </c>
       <c r="F46" t="n">
         <v>798800</v>
@@ -1352,16 +1352,16 @@
         <v>44160</v>
       </c>
       <c r="B47" t="n">
-        <v>13.65039920806885</v>
+        <v>13.65040016174316</v>
       </c>
       <c r="C47" t="n">
-        <v>13.77449405371565</v>
+        <v>13.77449501605975</v>
       </c>
       <c r="D47" t="n">
-        <v>13.34016336194231</v>
+        <v>13.34016429394225</v>
       </c>
       <c r="E47" t="n">
-        <v>13.61494365864504</v>
+        <v>13.61494460984229</v>
       </c>
       <c r="F47" t="n">
         <v>724200</v>
@@ -1432,16 +1432,16 @@
         <v>44166</v>
       </c>
       <c r="B51" t="n">
-        <v>14.1822338104248</v>
+        <v>14.18223476409912</v>
       </c>
       <c r="C51" t="n">
-        <v>14.40383121371269</v>
+        <v>14.40383218228817</v>
       </c>
       <c r="D51" t="n">
-        <v>13.47755400034316</v>
+        <v>13.47755490663178</v>
       </c>
       <c r="E51" t="n">
-        <v>13.73460695434403</v>
+        <v>13.73460787791799</v>
       </c>
       <c r="F51" t="n">
         <v>2351000</v>
@@ -1452,16 +1452,16 @@
         <v>44167</v>
       </c>
       <c r="B52" t="n">
-        <v>14.1822338104248</v>
+        <v>14.18223476409912</v>
       </c>
       <c r="C52" t="n">
-        <v>14.37280771250471</v>
+        <v>14.37280867899403</v>
       </c>
       <c r="D52" t="n">
-        <v>13.93404495543393</v>
+        <v>13.93404589241896</v>
       </c>
       <c r="E52" t="n">
-        <v>14.1822338104248</v>
+        <v>14.18223476409912</v>
       </c>
       <c r="F52" t="n">
         <v>767800</v>
@@ -1472,16 +1472,16 @@
         <v>44168</v>
       </c>
       <c r="B53" t="n">
-        <v>14.35951232910156</v>
+        <v>14.3595142364502</v>
       </c>
       <c r="C53" t="n">
-        <v>14.44371873324512</v>
+        <v>14.44372065177874</v>
       </c>
       <c r="D53" t="n">
-        <v>14.05813888173424</v>
+        <v>14.05814074905197</v>
       </c>
       <c r="E53" t="n">
-        <v>14.31519183429916</v>
+        <v>14.31519373576078</v>
       </c>
       <c r="F53" t="n">
         <v>1033200</v>
@@ -1492,16 +1492,16 @@
         <v>44169</v>
       </c>
       <c r="B54" t="n">
-        <v>14.07143497467041</v>
+        <v>14.07143592834473</v>
       </c>
       <c r="C54" t="n">
-        <v>14.44814988040786</v>
+        <v>14.44815085961357</v>
       </c>
       <c r="D54" t="n">
-        <v>13.94734012569418</v>
+        <v>13.94734107095812</v>
       </c>
       <c r="E54" t="n">
-        <v>14.44814988040786</v>
+        <v>14.44815085961357</v>
       </c>
       <c r="F54" t="n">
         <v>751600</v>
@@ -1532,16 +1532,16 @@
         <v>44173</v>
       </c>
       <c r="B56" t="n">
-        <v>14.09359455108643</v>
+        <v>14.09359550476074</v>
       </c>
       <c r="C56" t="n">
-        <v>14.53678935892345</v>
+        <v>14.53679034258752</v>
       </c>
       <c r="D56" t="n">
-        <v>13.89858944427358</v>
+        <v>13.89859038475245</v>
       </c>
       <c r="E56" t="n">
-        <v>14.09359455108643</v>
+        <v>14.09359550476074</v>
       </c>
       <c r="F56" t="n">
         <v>767200</v>
@@ -1552,16 +1552,16 @@
         <v>44174</v>
       </c>
       <c r="B57" t="n">
-        <v>13.88972568511963</v>
+        <v>13.88972473144531</v>
       </c>
       <c r="C57" t="n">
-        <v>14.2487140968875</v>
+        <v>14.24871311856489</v>
       </c>
       <c r="D57" t="n">
-        <v>13.65926417652651</v>
+        <v>13.65926323867578</v>
       </c>
       <c r="E57" t="n">
-        <v>14.1467786461421</v>
+        <v>14.14677767481842</v>
       </c>
       <c r="F57" t="n">
         <v>570800</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.004958152771</v>
+        <v>14.00495624542236</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10246072049168</v>
+        <v>14.10245879986408</v>
       </c>
       <c r="D58" t="n">
-        <v>13.51744362351329</v>
+        <v>13.51744178255972</v>
       </c>
       <c r="E58" t="n">
-        <v>13.88529533420892</v>
+        <v>13.88529344315728</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1632,16 +1632,16 @@
         <v>44180</v>
       </c>
       <c r="B61" t="n">
-        <v>14.08473205566406</v>
+        <v>14.08473014831543</v>
       </c>
       <c r="C61" t="n">
-        <v>14.124619658143</v>
+        <v>14.12461774539281</v>
       </c>
       <c r="D61" t="n">
-        <v>13.57062611852114</v>
+        <v>13.57062428079252</v>
       </c>
       <c r="E61" t="n">
-        <v>13.75676798164717</v>
+        <v>13.75676611871129</v>
       </c>
       <c r="F61" t="n">
         <v>732800</v>
@@ -1652,16 +1652,16 @@
         <v>44181</v>
       </c>
       <c r="B62" t="n">
-        <v>13.91631698608398</v>
+        <v>13.9163179397583</v>
       </c>
       <c r="C62" t="n">
-        <v>14.17780199388652</v>
+        <v>14.1778029654802</v>
       </c>
       <c r="D62" t="n">
-        <v>13.71687982704398</v>
+        <v>13.71688076705103</v>
       </c>
       <c r="E62" t="n">
-        <v>14.13791439301312</v>
+        <v>14.13791536187333</v>
       </c>
       <c r="F62" t="n">
         <v>564600</v>
@@ -1672,16 +1672,16 @@
         <v>44182</v>
       </c>
       <c r="B63" t="n">
-        <v>13.73903846740723</v>
+        <v>13.73903942108154</v>
       </c>
       <c r="C63" t="n">
-        <v>14.13348155935396</v>
+        <v>14.13348254040794</v>
       </c>
       <c r="D63" t="n">
-        <v>13.67255941808194</v>
+        <v>13.67256036714172</v>
       </c>
       <c r="E63" t="n">
-        <v>13.91631621405031</v>
+        <v>13.91631718003009</v>
       </c>
       <c r="F63" t="n">
         <v>633000</v>
@@ -1712,16 +1712,16 @@
         <v>44186</v>
       </c>
       <c r="B65" t="n">
-        <v>13.14958953857422</v>
+        <v>13.14959239959717</v>
       </c>
       <c r="C65" t="n">
-        <v>13.3401634347651</v>
+        <v>13.34016633725218</v>
       </c>
       <c r="D65" t="n">
-        <v>12.76844174619245</v>
+        <v>12.76844452428714</v>
       </c>
       <c r="E65" t="n">
-        <v>13.14958953857422</v>
+        <v>13.14959239959717</v>
       </c>
       <c r="F65" t="n">
         <v>872000</v>
@@ -1732,16 +1732,16 @@
         <v>44187</v>
       </c>
       <c r="B66" t="n">
-        <v>13.00776863098145</v>
+        <v>13.00776767730713</v>
       </c>
       <c r="C66" t="n">
-        <v>13.60608182981131</v>
+        <v>13.60608083227121</v>
       </c>
       <c r="D66" t="n">
-        <v>12.94572077899828</v>
+        <v>12.94571982987305</v>
       </c>
       <c r="E66" t="n">
-        <v>13.22493399960485</v>
+        <v>13.22493303000889</v>
       </c>
       <c r="F66" t="n">
         <v>911600</v>
@@ -1752,16 +1752,16 @@
         <v>44188</v>
       </c>
       <c r="B67" t="n">
-        <v>14.04484272003174</v>
+        <v>14.04484558105469</v>
       </c>
       <c r="C67" t="n">
-        <v>14.1512093650741</v>
+        <v>14.1512122477646</v>
       </c>
       <c r="D67" t="n">
-        <v>13.40220995524134</v>
+        <v>13.40221268535595</v>
       </c>
       <c r="E67" t="n">
-        <v>13.45539370042599</v>
+        <v>13.45539644137447</v>
       </c>
       <c r="F67" t="n">
         <v>2040000</v>
@@ -1772,16 +1772,16 @@
         <v>44193</v>
       </c>
       <c r="B68" t="n">
-        <v>15.11294078826904</v>
+        <v>15.11294269561768</v>
       </c>
       <c r="C68" t="n">
-        <v>15.1306689846002</v>
+        <v>15.13067089418624</v>
       </c>
       <c r="D68" t="n">
-        <v>14.07586581737739</v>
+        <v>14.07586759384061</v>
       </c>
       <c r="E68" t="n">
-        <v>14.13348076479979</v>
+        <v>14.13348254853438</v>
       </c>
       <c r="F68" t="n">
         <v>1671800</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.1971492767334</v>
+        <v>15.19715023040771</v>
       </c>
       <c r="C69" t="n">
-        <v>15.34783556821876</v>
+        <v>15.34783653134916</v>
       </c>
       <c r="D69" t="n">
-        <v>14.74952160615018</v>
+        <v>14.74952253173429</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510227859012</v>
+        <v>15.13510322837077</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1812,16 +1812,16 @@
         <v>44195</v>
       </c>
       <c r="B70" t="n">
-        <v>15.72011947631836</v>
+        <v>15.72012138366699</v>
       </c>
       <c r="C70" t="n">
-        <v>15.91512457198337</v>
+        <v>15.9151265029923</v>
       </c>
       <c r="D70" t="n">
-        <v>15.25033239823193</v>
+        <v>15.2503342485805</v>
       </c>
       <c r="E70" t="n">
-        <v>15.37885929091415</v>
+        <v>15.37886115685711</v>
       </c>
       <c r="F70" t="n">
         <v>2946000</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884963989258</v>
+        <v>14.98884773254395</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171924035773</v>
+        <v>15.94171721175532</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952401596354</v>
+        <v>14.74952213906937</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069573621739</v>
+        <v>15.91069371156276</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.58997249603271</v>
+        <v>14.58997344970703</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135701596139</v>
+        <v>15.28135801482809</v>
       </c>
       <c r="D73" t="n">
-        <v>14.58997249603271</v>
+        <v>14.58997344970703</v>
       </c>
       <c r="E73" t="n">
-        <v>15.13953481043562</v>
+        <v>15.1395358000321</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1892,16 +1892,16 @@
         <v>44203</v>
       </c>
       <c r="B74" t="n">
-        <v>14.40513134002686</v>
+        <v>14.40513038635254</v>
       </c>
       <c r="C74" t="n">
-        <v>14.96995146169153</v>
+        <v>14.96995047062398</v>
       </c>
       <c r="D74" t="n">
-        <v>14.39623633458149</v>
+        <v>14.39623538149606</v>
       </c>
       <c r="E74" t="n">
-        <v>14.68531807363505</v>
+        <v>14.68531710141131</v>
       </c>
       <c r="F74" t="n">
         <v>1215000</v>
@@ -1912,16 +1912,16 @@
         <v>44204</v>
       </c>
       <c r="B75" t="n">
-        <v>15.06334781646729</v>
+        <v>15.06334400177002</v>
       </c>
       <c r="C75" t="n">
-        <v>15.27237622168966</v>
+        <v>15.27237235405728</v>
       </c>
       <c r="D75" t="n">
-        <v>14.38734261131419</v>
+        <v>14.38733896781096</v>
       </c>
       <c r="E75" t="n">
-        <v>14.38734261131419</v>
+        <v>14.38733896781096</v>
       </c>
       <c r="F75" t="n">
         <v>1077600</v>
@@ -1932,16 +1932,16 @@
         <v>44207</v>
       </c>
       <c r="B76" t="n">
-        <v>15.83274555206299</v>
+        <v>15.8327465057373</v>
       </c>
       <c r="C76" t="n">
-        <v>15.83274555206299</v>
+        <v>15.8327465057373</v>
       </c>
       <c r="D76" t="n">
-        <v>14.80539709311043</v>
+        <v>14.80539798490314</v>
       </c>
       <c r="E76" t="n">
-        <v>14.95216043158278</v>
+        <v>14.95216133221568</v>
       </c>
       <c r="F76" t="n">
         <v>1758200</v>
@@ -1952,16 +1952,16 @@
         <v>44208</v>
       </c>
       <c r="B77" t="n">
-        <v>15.99285316467285</v>
+        <v>15.99285221099854</v>
       </c>
       <c r="C77" t="n">
-        <v>16.31306657107592</v>
+        <v>16.31306559830687</v>
       </c>
       <c r="D77" t="n">
-        <v>15.34353304306556</v>
+        <v>15.34353212811103</v>
       </c>
       <c r="E77" t="n">
-        <v>15.90390480772213</v>
+        <v>15.90390385935192</v>
       </c>
       <c r="F77" t="n">
         <v>2193200</v>
@@ -1972,16 +1972,16 @@
         <v>44209</v>
       </c>
       <c r="B78" t="n">
-        <v>15.72156143188477</v>
+        <v>15.72156047821045</v>
       </c>
       <c r="C78" t="n">
-        <v>16.7177799754675</v>
+        <v>16.71777896136228</v>
       </c>
       <c r="D78" t="n">
-        <v>15.41469138192811</v>
+        <v>15.41469044686861</v>
       </c>
       <c r="E78" t="n">
-        <v>15.9661698375192</v>
+        <v>15.96616886900687</v>
       </c>
       <c r="F78" t="n">
         <v>1238200</v>
@@ -1992,16 +1992,16 @@
         <v>44210</v>
       </c>
       <c r="B79" t="n">
-        <v>16.08624649047852</v>
+        <v>16.08624839782715</v>
       </c>
       <c r="C79" t="n">
-        <v>16.2552481813217</v>
+        <v>16.25525010870889</v>
       </c>
       <c r="D79" t="n">
-        <v>15.65929645771021</v>
+        <v>15.65929831443531</v>
       </c>
       <c r="E79" t="n">
-        <v>15.94837816337235</v>
+        <v>15.94838005437391</v>
       </c>
       <c r="F79" t="n">
         <v>1217000</v>
@@ -2012,16 +2012,16 @@
         <v>44211</v>
       </c>
       <c r="B80" t="n">
-        <v>15.88166618347168</v>
+        <v>15.88167095184326</v>
       </c>
       <c r="C80" t="n">
-        <v>16.09069454203798</v>
+        <v>16.09069937316902</v>
       </c>
       <c r="D80" t="n">
-        <v>15.61037449168528</v>
+        <v>15.61037917860321</v>
       </c>
       <c r="E80" t="n">
-        <v>16.08624619163735</v>
+        <v>16.0862510214328</v>
       </c>
       <c r="F80" t="n">
         <v>728000</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422393798828</v>
+        <v>16.38422775268555</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538227998573</v>
+        <v>16.45538611125061</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169386673051</v>
+        <v>15.92169757373807</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93503722223226</v>
+        <v>15.93504093234652</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2052,16 +2052,16 @@
         <v>44215</v>
       </c>
       <c r="B82" t="n">
-        <v>16.63327980041504</v>
+        <v>16.63327789306641</v>
       </c>
       <c r="C82" t="n">
-        <v>17.07801988388551</v>
+        <v>17.07801792553825</v>
       </c>
       <c r="D82" t="n">
-        <v>16.0951430100387</v>
+        <v>16.09514116439855</v>
       </c>
       <c r="E82" t="n">
-        <v>17.07801988388551</v>
+        <v>17.07801792553825</v>
       </c>
       <c r="F82" t="n">
         <v>1918400</v>
@@ -2072,16 +2072,16 @@
         <v>44216</v>
       </c>
       <c r="B83" t="n">
-        <v>16.2552490234375</v>
+        <v>16.25524711608887</v>
       </c>
       <c r="C83" t="n">
-        <v>16.81117410424281</v>
+        <v>16.81117213166337</v>
       </c>
       <c r="D83" t="n">
-        <v>16.0106423271929</v>
+        <v>16.01064044854579</v>
       </c>
       <c r="E83" t="n">
-        <v>16.69998908808175</v>
+        <v>16.69998712854847</v>
       </c>
       <c r="F83" t="n">
         <v>1073000</v>
@@ -2092,16 +2092,16 @@
         <v>44217</v>
       </c>
       <c r="B84" t="n">
-        <v>15.85498523712158</v>
+        <v>15.8549861907959</v>
       </c>
       <c r="C84" t="n">
-        <v>16.36643533398266</v>
+        <v>16.3664363184206</v>
       </c>
       <c r="D84" t="n">
-        <v>15.53032347129166</v>
+        <v>15.53032440543763</v>
       </c>
       <c r="E84" t="n">
-        <v>16.25969866009376</v>
+        <v>16.25969963811151</v>
       </c>
       <c r="F84" t="n">
         <v>928200</v>
@@ -2112,16 +2112,16 @@
         <v>44218</v>
       </c>
       <c r="B85" t="n">
-        <v>15.40135097503662</v>
+        <v>15.40134906768799</v>
       </c>
       <c r="C85" t="n">
-        <v>15.8416427478974</v>
+        <v>15.84164078602173</v>
       </c>
       <c r="D85" t="n">
-        <v>15.17453256164258</v>
+        <v>15.17453068238381</v>
       </c>
       <c r="E85" t="n">
-        <v>15.60593102498302</v>
+        <v>15.60592909229859</v>
       </c>
       <c r="F85" t="n">
         <v>1029200</v>
@@ -2132,16 +2132,16 @@
         <v>44222</v>
       </c>
       <c r="B86" t="n">
-        <v>14.67197513580322</v>
+        <v>14.67197608947754</v>
       </c>
       <c r="C86" t="n">
-        <v>15.52587522559741</v>
+        <v>15.525876234775</v>
       </c>
       <c r="D86" t="n">
-        <v>14.6363951171208</v>
+        <v>14.63639606848242</v>
       </c>
       <c r="E86" t="n">
-        <v>15.38355854396505</v>
+        <v>15.38355954389209</v>
       </c>
       <c r="F86" t="n">
         <v>1156000</v>
@@ -2152,16 +2152,16 @@
         <v>44223</v>
       </c>
       <c r="B87" t="n">
-        <v>15.00553131103516</v>
+        <v>15.00553035736084</v>
       </c>
       <c r="C87" t="n">
-        <v>15.57034972966033</v>
+        <v>15.57034874008907</v>
       </c>
       <c r="D87" t="n">
-        <v>14.53410620714105</v>
+        <v>14.53410528342808</v>
       </c>
       <c r="E87" t="n">
-        <v>14.74313459133305</v>
+        <v>14.74313365433532</v>
       </c>
       <c r="F87" t="n">
         <v>1909000</v>
@@ -2172,16 +2172,16 @@
         <v>44224</v>
       </c>
       <c r="B88" t="n">
-        <v>15.6592960357666</v>
+        <v>15.65929985046387</v>
       </c>
       <c r="C88" t="n">
-        <v>15.98840440416715</v>
+        <v>15.98840829903717</v>
       </c>
       <c r="D88" t="n">
-        <v>14.95215932080804</v>
+        <v>14.95216296324262</v>
       </c>
       <c r="E88" t="n">
-        <v>15.13450266509051</v>
+        <v>15.134506351945</v>
       </c>
       <c r="F88" t="n">
         <v>3941600</v>
@@ -2192,16 +2192,16 @@
         <v>44225</v>
       </c>
       <c r="B89" t="n">
-        <v>15.74379920959473</v>
+        <v>15.74379825592041</v>
       </c>
       <c r="C89" t="n">
-        <v>16.55322600399441</v>
+        <v>16.55322500128939</v>
       </c>
       <c r="D89" t="n">
-        <v>15.38800579515856</v>
+        <v>15.38800486303628</v>
       </c>
       <c r="E89" t="n">
-        <v>16.01064257387312</v>
+        <v>16.01064160403487</v>
       </c>
       <c r="F89" t="n">
         <v>3936400</v>
@@ -2212,16 +2212,16 @@
         <v>44228</v>
       </c>
       <c r="B90" t="n">
-        <v>16.76670265197754</v>
+        <v>16.76670074462891</v>
       </c>
       <c r="C90" t="n">
-        <v>17.02909938733217</v>
+        <v>17.02909745013378</v>
       </c>
       <c r="D90" t="n">
-        <v>15.65929902065404</v>
+        <v>15.65929723928157</v>
       </c>
       <c r="E90" t="n">
-        <v>16.01064411819733</v>
+        <v>16.0106422968565</v>
       </c>
       <c r="F90" t="n">
         <v>3072200</v>
@@ -2232,16 +2232,16 @@
         <v>44229</v>
       </c>
       <c r="B91" t="n">
-        <v>17.08246803283691</v>
+        <v>17.08246612548828</v>
       </c>
       <c r="C91" t="n">
-        <v>17.32262810609502</v>
+        <v>17.32262617193124</v>
       </c>
       <c r="D91" t="n">
-        <v>16.76670295311732</v>
+        <v>16.76670108102554</v>
       </c>
       <c r="E91" t="n">
-        <v>16.76670295311732</v>
+        <v>16.76670108102554</v>
       </c>
       <c r="F91" t="n">
         <v>2620800</v>
@@ -2272,16 +2272,16 @@
         <v>44231</v>
       </c>
       <c r="B93" t="n">
-        <v>17.8874454498291</v>
+        <v>17.88744735717773</v>
       </c>
       <c r="C93" t="n">
-        <v>18.36331717015739</v>
+        <v>18.3633191282485</v>
       </c>
       <c r="D93" t="n">
-        <v>17.61615374642633</v>
+        <v>17.61615562484698</v>
       </c>
       <c r="E93" t="n">
-        <v>17.79404874945122</v>
+        <v>17.79405064684091</v>
       </c>
       <c r="F93" t="n">
         <v>1940600</v>
@@ -2312,16 +2312,16 @@
         <v>44235</v>
       </c>
       <c r="B95" t="n">
-        <v>19.23056221008301</v>
+        <v>19.23056030273438</v>
       </c>
       <c r="C95" t="n">
-        <v>19.36843055199105</v>
+        <v>19.36842863096819</v>
       </c>
       <c r="D95" t="n">
-        <v>18.46560871350112</v>
+        <v>18.46560688202301</v>
       </c>
       <c r="E95" t="n">
-        <v>18.81250544030044</v>
+        <v>18.81250357441601</v>
       </c>
       <c r="F95" t="n">
         <v>1758400</v>
@@ -2392,16 +2392,16 @@
         <v>44239</v>
       </c>
       <c r="B99" t="n">
-        <v>18.51897621154785</v>
+        <v>18.51897811889648</v>
       </c>
       <c r="C99" t="n">
-        <v>18.72355623622481</v>
+        <v>18.72355816464402</v>
       </c>
       <c r="D99" t="n">
-        <v>18.16318449546863</v>
+        <v>18.16318636617275</v>
       </c>
       <c r="E99" t="n">
-        <v>18.58123954979312</v>
+        <v>18.58124146355452</v>
       </c>
       <c r="F99" t="n">
         <v>849600</v>
@@ -2412,16 +2412,16 @@
         <v>44244</v>
       </c>
       <c r="B100" t="n">
-        <v>18.52787208557129</v>
+        <v>18.52787017822266</v>
       </c>
       <c r="C100" t="n">
-        <v>18.68797878945395</v>
+        <v>18.68797686562316</v>
       </c>
       <c r="D100" t="n">
-        <v>18.20765867780597</v>
+        <v>18.20765680342165</v>
       </c>
       <c r="E100" t="n">
-        <v>18.5189770801835</v>
+        <v>18.51897517375056</v>
       </c>
       <c r="F100" t="n">
         <v>743200</v>
@@ -2432,16 +2432,16 @@
         <v>44245</v>
       </c>
       <c r="B101" t="n">
-        <v>18.24323654174805</v>
+        <v>18.24323844909668</v>
       </c>
       <c r="C101" t="n">
-        <v>19.03487326559868</v>
+        <v>19.03487525571373</v>
       </c>
       <c r="D101" t="n">
-        <v>17.90523316318246</v>
+        <v>17.9052350351925</v>
       </c>
       <c r="E101" t="n">
-        <v>18.6924232331395</v>
+        <v>18.69242518745105</v>
       </c>
       <c r="F101" t="n">
         <v>1007600</v>
@@ -2452,16 +2452,16 @@
         <v>44246</v>
       </c>
       <c r="B102" t="n">
-        <v>18.27881813049316</v>
+        <v>18.27881622314453</v>
       </c>
       <c r="C102" t="n">
-        <v>18.57234653985784</v>
+        <v>18.57234460188025</v>
       </c>
       <c r="D102" t="n">
-        <v>17.92302637619491</v>
+        <v>17.92302450597225</v>
       </c>
       <c r="E102" t="n">
-        <v>18.23434479741172</v>
+        <v>18.23434289470377</v>
       </c>
       <c r="F102" t="n">
         <v>881800</v>
@@ -2512,16 +2512,16 @@
         <v>44251</v>
       </c>
       <c r="B105" t="n">
-        <v>17.68731307983398</v>
+        <v>17.68731117248535</v>
       </c>
       <c r="C105" t="n">
-        <v>18.09647313665348</v>
+        <v>18.09647118518221</v>
       </c>
       <c r="D105" t="n">
-        <v>17.54499639080558</v>
+        <v>17.54499449880396</v>
       </c>
       <c r="E105" t="n">
-        <v>17.70510309009973</v>
+        <v>17.70510118083267</v>
       </c>
       <c r="F105" t="n">
         <v>1411000</v>
@@ -2532,16 +2532,16 @@
         <v>44252</v>
       </c>
       <c r="B106" t="n">
-        <v>16.9445972442627</v>
+        <v>16.94459533691406</v>
       </c>
       <c r="C106" t="n">
-        <v>17.79405077305967</v>
+        <v>17.7940487700933</v>
       </c>
       <c r="D106" t="n">
-        <v>16.63772718397596</v>
+        <v>16.6377253111698</v>
       </c>
       <c r="E106" t="n">
-        <v>17.68731409841596</v>
+        <v>17.68731210746428</v>
       </c>
       <c r="F106" t="n">
         <v>1207600</v>
@@ -2552,16 +2552,16 @@
         <v>44253</v>
       </c>
       <c r="B107" t="n">
-        <v>16.69999122619629</v>
+        <v>16.69999313354492</v>
       </c>
       <c r="C107" t="n">
-        <v>17.20699469335504</v>
+        <v>17.20699665860983</v>
       </c>
       <c r="D107" t="n">
-        <v>16.40201615907802</v>
+        <v>16.40201803239415</v>
       </c>
       <c r="E107" t="n">
-        <v>17.13583634176344</v>
+        <v>17.13583829889106</v>
       </c>
       <c r="F107" t="n">
         <v>1586600</v>
@@ -2632,16 +2632,16 @@
         <v>44259</v>
       </c>
       <c r="B111" t="n">
-        <v>16.0506706237793</v>
+        <v>16.05066871643066</v>
       </c>
       <c r="C111" t="n">
-        <v>16.75780746592523</v>
+        <v>16.75780547454543</v>
       </c>
       <c r="D111" t="n">
-        <v>15.79272054586055</v>
+        <v>15.79271866916489</v>
       </c>
       <c r="E111" t="n">
-        <v>16.23301400085849</v>
+        <v>16.23301207184145</v>
       </c>
       <c r="F111" t="n">
         <v>1300400</v>
@@ -2712,16 +2712,16 @@
         <v>44265</v>
       </c>
       <c r="B115" t="n">
-        <v>14.64529132843018</v>
+        <v>14.64529037475586</v>
       </c>
       <c r="C115" t="n">
-        <v>15.05445139769713</v>
+        <v>15.05445041737906</v>
       </c>
       <c r="D115" t="n">
-        <v>14.28505124405912</v>
+        <v>14.28505031384297</v>
       </c>
       <c r="E115" t="n">
-        <v>15.05445139769713</v>
+        <v>15.05445041737906</v>
       </c>
       <c r="F115" t="n">
         <v>3352600</v>
@@ -2732,16 +2732,16 @@
         <v>44266</v>
       </c>
       <c r="B116" t="n">
-        <v>15.8194055557251</v>
+        <v>15.81940460205078</v>
       </c>
       <c r="C116" t="n">
-        <v>15.99285392694427</v>
+        <v>15.99285296281361</v>
       </c>
       <c r="D116" t="n">
-        <v>15.15674374278266</v>
+        <v>15.15674282905697</v>
       </c>
       <c r="E116" t="n">
-        <v>15.15674374278266</v>
+        <v>15.15674282905697</v>
       </c>
       <c r="F116" t="n">
         <v>2295400</v>
@@ -2752,16 +2752,16 @@
         <v>44267</v>
       </c>
       <c r="B117" t="n">
-        <v>15.61037731170654</v>
+        <v>15.61037445068359</v>
       </c>
       <c r="C117" t="n">
-        <v>15.96172240868904</v>
+        <v>15.96171948327262</v>
       </c>
       <c r="D117" t="n">
-        <v>15.4191389270983</v>
+        <v>15.41913610112494</v>
       </c>
       <c r="E117" t="n">
-        <v>15.96172240868904</v>
+        <v>15.96171948327262</v>
       </c>
       <c r="F117" t="n">
         <v>1034800</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708683013916</v>
+        <v>15.67708778381348</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619521504051</v>
+        <v>16.00619618873527</v>
       </c>
       <c r="D118" t="n">
-        <v>15.49474347671438</v>
+        <v>15.49474441929632</v>
       </c>
       <c r="E118" t="n">
-        <v>15.61482349431831</v>
+        <v>15.614824444205</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2792,16 +2792,16 @@
         <v>44271</v>
       </c>
       <c r="B119" t="n">
-        <v>16.46872329711914</v>
+        <v>16.46872138977051</v>
       </c>
       <c r="C119" t="n">
-        <v>16.8378583482222</v>
+        <v>16.83785639812166</v>
       </c>
       <c r="D119" t="n">
-        <v>15.68153321514211</v>
+        <v>15.68153139896302</v>
       </c>
       <c r="E119" t="n">
-        <v>15.68598156565223</v>
+        <v>15.68597974895794</v>
       </c>
       <c r="F119" t="n">
         <v>1963400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880424499512</v>
+        <v>16.58880233764648</v>
       </c>
       <c r="C120" t="n">
-        <v>16.7578059463568</v>
+        <v>16.75780401957668</v>
       </c>
       <c r="D120" t="n">
-        <v>16.07735418324739</v>
+        <v>16.0773523347043</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298585477987</v>
+        <v>16.19298399294167</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2832,16 +2832,16 @@
         <v>44273</v>
       </c>
       <c r="B121" t="n">
-        <v>16.21967315673828</v>
+        <v>16.21967124938965</v>
       </c>
       <c r="C121" t="n">
-        <v>17.29149680698328</v>
+        <v>17.2914947735938</v>
       </c>
       <c r="D121" t="n">
-        <v>16.07735645022393</v>
+        <v>16.077354559611</v>
       </c>
       <c r="E121" t="n">
-        <v>16.58880658408833</v>
+        <v>16.58880463333153</v>
       </c>
       <c r="F121" t="n">
         <v>1568800</v>
@@ -2892,16 +2892,16 @@
         <v>44278</v>
       </c>
       <c r="B124" t="n">
-        <v>16.09959030151367</v>
+        <v>16.0995922088623</v>
       </c>
       <c r="C124" t="n">
-        <v>16.49985533236855</v>
+        <v>16.49985728713733</v>
       </c>
       <c r="D124" t="n">
-        <v>15.87277192380211</v>
+        <v>15.87277380427914</v>
       </c>
       <c r="E124" t="n">
-        <v>16.45538200556756</v>
+        <v>16.4553839550675</v>
       </c>
       <c r="F124" t="n">
         <v>855200</v>
@@ -2912,16 +2912,16 @@
         <v>44279</v>
       </c>
       <c r="B125" t="n">
-        <v>15.41024303436279</v>
+        <v>15.41024398803711</v>
       </c>
       <c r="C125" t="n">
-        <v>16.2107747654813</v>
+        <v>16.21077576869711</v>
       </c>
       <c r="D125" t="n">
-        <v>15.21455633135589</v>
+        <v>15.21455727291999</v>
       </c>
       <c r="E125" t="n">
-        <v>16.05066807994787</v>
+        <v>16.05066907325537</v>
       </c>
       <c r="F125" t="n">
         <v>1010400</v>
@@ -2952,16 +2952,16 @@
         <v>44281</v>
       </c>
       <c r="B127" t="n">
-        <v>15.85498523712158</v>
+        <v>15.8549861907959</v>
       </c>
       <c r="C127" t="n">
-        <v>16.41535701641043</v>
+        <v>16.415358003791</v>
       </c>
       <c r="D127" t="n">
-        <v>15.67264186405827</v>
+        <v>15.67264280676466</v>
       </c>
       <c r="E127" t="n">
-        <v>16.10403860722825</v>
+        <v>16.10403957588308</v>
       </c>
       <c r="F127" t="n">
         <v>1078200</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.58369255065918</v>
+        <v>15.58369064331055</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174760813446</v>
+        <v>16.00174564961845</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245418372239</v>
+        <v>15.39245229978017</v>
       </c>
       <c r="E128" t="n">
-        <v>15.7437992482387</v>
+        <v>15.74379732129399</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514427185059</v>
+        <v>16.09514045715332</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23746097399444</v>
+        <v>16.23745712556681</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48585078476289</v>
+        <v>15.48584711447378</v>
       </c>
       <c r="E129" t="n">
-        <v>15.58814080839448</v>
+        <v>15.5881371138617</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3012,16 +3012,16 @@
         <v>44286</v>
       </c>
       <c r="B130" t="n">
-        <v>16.61549186706543</v>
+        <v>16.61548614501953</v>
       </c>
       <c r="C130" t="n">
-        <v>16.71778189546542</v>
+        <v>16.71777613819286</v>
       </c>
       <c r="D130" t="n">
-        <v>15.94393330700381</v>
+        <v>15.94392781622937</v>
       </c>
       <c r="E130" t="n">
-        <v>16.10848837997462</v>
+        <v>16.10848283253066</v>
       </c>
       <c r="F130" t="n">
         <v>1491400</v>
@@ -3092,16 +3092,16 @@
         <v>44293</v>
       </c>
       <c r="B134" t="n">
-        <v>17.37154769897461</v>
+        <v>17.37154960632324</v>
       </c>
       <c r="C134" t="n">
-        <v>17.63839106164878</v>
+        <v>17.63839299829608</v>
       </c>
       <c r="D134" t="n">
-        <v>17.11359764471402</v>
+        <v>17.11359952374044</v>
       </c>
       <c r="E134" t="n">
-        <v>17.47828436542479</v>
+        <v>17.47828628449281</v>
       </c>
       <c r="F134" t="n">
         <v>869400</v>
@@ -3112,16 +3112,16 @@
         <v>44294</v>
       </c>
       <c r="B135" t="n">
-        <v>17.60725975036621</v>
+        <v>17.60726165771484</v>
       </c>
       <c r="C135" t="n">
-        <v>17.90968313903537</v>
+        <v>17.90968507914474</v>
       </c>
       <c r="D135" t="n">
-        <v>17.2737046919707</v>
+        <v>17.27370656318618</v>
       </c>
       <c r="E135" t="n">
-        <v>17.38044305713872</v>
+        <v>17.38044493991689</v>
       </c>
       <c r="F135" t="n">
         <v>710000</v>
@@ -3132,16 +3132,16 @@
         <v>44295</v>
       </c>
       <c r="B136" t="n">
-        <v>18.03421020507812</v>
+        <v>18.03421401977539</v>
       </c>
       <c r="C136" t="n">
-        <v>18.25658024878204</v>
+        <v>18.25658411051627</v>
       </c>
       <c r="D136" t="n">
-        <v>17.41157510063643</v>
+        <v>17.41157878363042</v>
       </c>
       <c r="E136" t="n">
-        <v>17.64283845312556</v>
+        <v>17.64284218503768</v>
       </c>
       <c r="F136" t="n">
         <v>1023600</v>
@@ -3152,16 +3152,16 @@
         <v>44298</v>
       </c>
       <c r="B137" t="n">
-        <v>17.74513244628906</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="C137" t="n">
-        <v>18.05644919023704</v>
+        <v>18.05644724942629</v>
       </c>
       <c r="D137" t="n">
-        <v>17.58947237776606</v>
+        <v>17.58947048714867</v>
       </c>
       <c r="E137" t="n">
-        <v>18.05644919023704</v>
+        <v>18.05644724942629</v>
       </c>
       <c r="F137" t="n">
         <v>810600</v>
@@ -3172,16 +3172,16 @@
         <v>44299</v>
       </c>
       <c r="B138" t="n">
-        <v>17.40712356567383</v>
+        <v>17.40712547302246</v>
       </c>
       <c r="C138" t="n">
-        <v>17.74067857021755</v>
+        <v>17.74068051411476</v>
       </c>
       <c r="D138" t="n">
-        <v>17.20254357005865</v>
+        <v>17.20254545499086</v>
       </c>
       <c r="E138" t="n">
-        <v>17.74067857021755</v>
+        <v>17.74068051411476</v>
       </c>
       <c r="F138" t="n">
         <v>699800</v>
@@ -3232,16 +3232,16 @@
         <v>44302</v>
       </c>
       <c r="B141" t="n">
-        <v>17.74513244628906</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="C141" t="n">
-        <v>17.74513244628906</v>
+        <v>17.74513053894043</v>
       </c>
       <c r="D141" t="n">
-        <v>17.12249556529509</v>
+        <v>17.12249372487104</v>
       </c>
       <c r="E141" t="n">
-        <v>17.38489231844339</v>
+        <v>17.38489044981543</v>
       </c>
       <c r="F141" t="n">
         <v>774600</v>
@@ -3252,16 +3252,16 @@
         <v>44305</v>
       </c>
       <c r="B142" t="n">
-        <v>18.0119743347168</v>
+        <v>18.01197242736816</v>
       </c>
       <c r="C142" t="n">
-        <v>18.17652769928423</v>
+        <v>18.17652577451049</v>
       </c>
       <c r="D142" t="n">
-        <v>17.70065592048599</v>
+        <v>17.70065404610391</v>
       </c>
       <c r="E142" t="n">
-        <v>17.70065592048599</v>
+        <v>17.70065404610391</v>
       </c>
       <c r="F142" t="n">
         <v>952400</v>
@@ -3272,16 +3272,16 @@
         <v>44306</v>
       </c>
       <c r="B143" t="n">
-        <v>17.81184196472168</v>
+        <v>17.81184005737305</v>
       </c>
       <c r="C143" t="n">
-        <v>18.40779381004686</v>
+        <v>18.40779183888181</v>
       </c>
       <c r="D143" t="n">
-        <v>17.62949857828519</v>
+        <v>17.62949669046246</v>
       </c>
       <c r="E143" t="n">
-        <v>18.01642201847014</v>
+        <v>18.01642008921442</v>
       </c>
       <c r="F143" t="n">
         <v>1050400</v>
@@ -3312,16 +3312,16 @@
         <v>44309</v>
       </c>
       <c r="B145" t="n">
-        <v>17.21144104003906</v>
+        <v>17.2114429473877</v>
       </c>
       <c r="C145" t="n">
-        <v>17.57167941077477</v>
+        <v>17.57168135804453</v>
       </c>
       <c r="D145" t="n">
-        <v>16.88233264191577</v>
+        <v>16.88233451279305</v>
       </c>
       <c r="E145" t="n">
-        <v>17.52275942819921</v>
+        <v>17.52276137004772</v>
       </c>
       <c r="F145" t="n">
         <v>903000</v>
@@ -3352,16 +3352,16 @@
         <v>44313</v>
       </c>
       <c r="B147" t="n">
-        <v>17.33596992492676</v>
+        <v>17.33596801757812</v>
       </c>
       <c r="C147" t="n">
-        <v>17.78071005136372</v>
+        <v>17.78070809508361</v>
       </c>
       <c r="D147" t="n">
-        <v>17.01130983621365</v>
+        <v>17.01130796458497</v>
       </c>
       <c r="E147" t="n">
-        <v>17.0468898606721</v>
+        <v>17.04688798512881</v>
       </c>
       <c r="F147" t="n">
         <v>1372600</v>
@@ -3412,16 +3412,16 @@
         <v>44316</v>
       </c>
       <c r="B150" t="n">
-        <v>19.34006118774414</v>
+        <v>19.34005928039551</v>
       </c>
       <c r="C150" t="n">
-        <v>19.34006118774414</v>
+        <v>19.34005928039551</v>
       </c>
       <c r="D150" t="n">
-        <v>18.38334087467527</v>
+        <v>18.38333906167997</v>
       </c>
       <c r="E150" t="n">
-        <v>18.86617264318869</v>
+        <v>18.86617078257573</v>
       </c>
       <c r="F150" t="n">
         <v>2355400</v>
@@ -3432,16 +3432,16 @@
         <v>44319</v>
       </c>
       <c r="B151" t="n">
-        <v>19.44736099243164</v>
+        <v>19.44735717773438</v>
       </c>
       <c r="C151" t="n">
-        <v>19.67089387740212</v>
+        <v>19.67089001885776</v>
       </c>
       <c r="D151" t="n">
-        <v>18.83935127244465</v>
+        <v>18.83934757701153</v>
       </c>
       <c r="E151" t="n">
-        <v>19.62618798257625</v>
+        <v>19.62618413280117</v>
       </c>
       <c r="F151" t="n">
         <v>2225200</v>
@@ -3452,16 +3452,16 @@
         <v>44320</v>
       </c>
       <c r="B152" t="n">
-        <v>19.79606437683105</v>
+        <v>19.79606819152832</v>
       </c>
       <c r="C152" t="n">
-        <v>20.00618575620603</v>
+        <v>20.00618961139364</v>
       </c>
       <c r="D152" t="n">
-        <v>19.25958701697824</v>
+        <v>19.25959072829643</v>
       </c>
       <c r="E152" t="n">
-        <v>19.45182365749287</v>
+        <v>19.45182740585503</v>
       </c>
       <c r="F152" t="n">
         <v>1635200</v>
@@ -3472,16 +3472,16 @@
         <v>44321</v>
       </c>
       <c r="B153" t="n">
-        <v>20.46219825744629</v>
+        <v>20.46219635009766</v>
       </c>
       <c r="C153" t="n">
-        <v>21.00761898287081</v>
+        <v>21.00761702468171</v>
       </c>
       <c r="D153" t="n">
-        <v>19.89442458705298</v>
+        <v>19.8944227326284</v>
       </c>
       <c r="E153" t="n">
-        <v>20.09113289036689</v>
+        <v>20.09113101760648</v>
       </c>
       <c r="F153" t="n">
         <v>1994000</v>
@@ -3492,16 +3492,16 @@
         <v>44322</v>
       </c>
       <c r="B154" t="n">
-        <v>20.43090057373047</v>
+        <v>20.4309024810791</v>
       </c>
       <c r="C154" t="n">
-        <v>20.65443339903295</v>
+        <v>20.65443532724973</v>
       </c>
       <c r="D154" t="n">
-        <v>20.16266016011543</v>
+        <v>20.16266204242219</v>
       </c>
       <c r="E154" t="n">
-        <v>20.46219503283921</v>
+        <v>20.46219694310937</v>
       </c>
       <c r="F154" t="n">
         <v>1030200</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.83326148986816</v>
+        <v>20.8332633972168</v>
       </c>
       <c r="C155" t="n">
-        <v>20.877969084305</v>
+        <v>20.87797099574675</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384283351365</v>
+        <v>20.36384469788557</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902756541763</v>
+        <v>20.86902947604076</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3532,16 +3532,16 @@
         <v>44326</v>
       </c>
       <c r="B156" t="n">
-        <v>20.36384201049805</v>
+        <v>20.36384010314941</v>
       </c>
       <c r="C156" t="n">
-        <v>20.94502707132523</v>
+        <v>20.94502510954077</v>
       </c>
       <c r="D156" t="n">
-        <v>20.25207558705358</v>
+        <v>20.25207369017338</v>
       </c>
       <c r="E156" t="n">
-        <v>20.83326064788076</v>
+        <v>20.83325869656473</v>
       </c>
       <c r="F156" t="n">
         <v>979800</v>
@@ -3572,16 +3572,16 @@
         <v>44328</v>
       </c>
       <c r="B158" t="n">
-        <v>20.15819358825684</v>
+        <v>20.1581916809082</v>
       </c>
       <c r="C158" t="n">
-        <v>20.59631779366714</v>
+        <v>20.59631584486362</v>
       </c>
       <c r="D158" t="n">
-        <v>19.57253687514265</v>
+        <v>19.57253502320829</v>
       </c>
       <c r="E158" t="n">
-        <v>20.59631779366714</v>
+        <v>20.59631584486362</v>
       </c>
       <c r="F158" t="n">
         <v>1344400</v>
@@ -3592,16 +3592,16 @@
         <v>44329</v>
       </c>
       <c r="B159" t="n">
-        <v>20.9047908782959</v>
+        <v>20.90478897094727</v>
       </c>
       <c r="C159" t="n">
-        <v>20.97185141384942</v>
+        <v>20.9718495003822</v>
       </c>
       <c r="D159" t="n">
-        <v>20.15819199587331</v>
+        <v>20.1581901566442</v>
       </c>
       <c r="E159" t="n">
-        <v>20.25654699323974</v>
+        <v>20.25654514503674</v>
       </c>
       <c r="F159" t="n">
         <v>1469200</v>
@@ -3612,16 +3612,16 @@
         <v>44330</v>
       </c>
       <c r="B160" t="n">
-        <v>20.29678153991699</v>
+        <v>20.29678344726562</v>
       </c>
       <c r="C160" t="n">
-        <v>21.23561873883424</v>
+        <v>21.23562073440818</v>
       </c>
       <c r="D160" t="n">
-        <v>20.22972100909998</v>
+        <v>20.22972291014674</v>
       </c>
       <c r="E160" t="n">
-        <v>21.01655581619614</v>
+        <v>21.01655779118409</v>
       </c>
       <c r="F160" t="n">
         <v>1009800</v>
@@ -3632,16 +3632,16 @@
         <v>44333</v>
       </c>
       <c r="B161" t="n">
-        <v>20.98526573181152</v>
+        <v>20.98526191711426</v>
       </c>
       <c r="C161" t="n">
-        <v>21.13279824819994</v>
+        <v>21.13279440668424</v>
       </c>
       <c r="D161" t="n">
-        <v>20.03748681748824</v>
+        <v>20.03748317507803</v>
       </c>
       <c r="E161" t="n">
-        <v>20.16266468199684</v>
+        <v>20.16266101683182</v>
       </c>
       <c r="F161" t="n">
         <v>1096800</v>
@@ -3652,16 +3652,16 @@
         <v>44334</v>
       </c>
       <c r="B162" t="n">
-        <v>21.12385177612305</v>
+        <v>21.12385368347168</v>
       </c>
       <c r="C162" t="n">
-        <v>21.74080284519728</v>
+        <v>21.74080480825265</v>
       </c>
       <c r="D162" t="n">
-        <v>20.88243591795225</v>
+        <v>20.88243780350257</v>
       </c>
       <c r="E162" t="n">
-        <v>21.15067632883762</v>
+        <v>21.15067823860833</v>
       </c>
       <c r="F162" t="n">
         <v>1192600</v>
@@ -3672,16 +3672,16 @@
         <v>44335</v>
       </c>
       <c r="B163" t="n">
-        <v>21.36974143981934</v>
+        <v>21.3697395324707</v>
       </c>
       <c r="C163" t="n">
-        <v>21.49044939093096</v>
+        <v>21.49044747280858</v>
       </c>
       <c r="D163" t="n">
-        <v>20.88691134079327</v>
+        <v>20.88690947653946</v>
       </c>
       <c r="E163" t="n">
-        <v>21.20432759811249</v>
+        <v>21.2043257055278</v>
       </c>
       <c r="F163" t="n">
         <v>1135200</v>
@@ -3712,16 +3712,16 @@
         <v>44337</v>
       </c>
       <c r="B165" t="n">
-        <v>21.94645500183105</v>
+        <v>21.94645309448242</v>
       </c>
       <c r="C165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04033647282705</v>
       </c>
       <c r="D165" t="n">
-        <v>21.50385921408051</v>
+        <v>21.50385734519752</v>
       </c>
       <c r="E165" t="n">
-        <v>22.04033838833501</v>
+        <v>22.04033647282705</v>
       </c>
       <c r="F165" t="n">
         <v>653400</v>
@@ -3732,16 +3732,16 @@
         <v>44340</v>
       </c>
       <c r="B166" t="n">
-        <v>21.87045478820801</v>
+        <v>21.87045288085938</v>
       </c>
       <c r="C166" t="n">
-        <v>22.12081221204925</v>
+        <v>22.12081028286665</v>
       </c>
       <c r="D166" t="n">
-        <v>21.50386102444573</v>
+        <v>21.50385914906818</v>
       </c>
       <c r="E166" t="n">
-        <v>21.67821809245792</v>
+        <v>21.67821620187448</v>
       </c>
       <c r="F166" t="n">
         <v>900600</v>
@@ -3752,16 +3752,16 @@
         <v>44341</v>
       </c>
       <c r="B167" t="n">
-        <v>22.17893028259277</v>
+        <v>22.17892837524414</v>
       </c>
       <c r="C167" t="n">
-        <v>22.3622271566051</v>
+        <v>22.36222523349326</v>
       </c>
       <c r="D167" t="n">
-        <v>21.77210055220345</v>
+        <v>21.77209867984146</v>
       </c>
       <c r="E167" t="n">
-        <v>21.98222027751199</v>
+        <v>21.98221838708007</v>
       </c>
       <c r="F167" t="n">
         <v>773000</v>
@@ -3772,16 +3772,16 @@
         <v>44342</v>
       </c>
       <c r="B168" t="n">
-        <v>22.1744556427002</v>
+        <v>22.17445945739746</v>
       </c>
       <c r="C168" t="n">
-        <v>22.42481302160963</v>
+        <v>22.42481687937616</v>
       </c>
       <c r="D168" t="n">
-        <v>21.53515162431978</v>
+        <v>21.53515532903684</v>
       </c>
       <c r="E168" t="n">
-        <v>22.1744556427002</v>
+        <v>22.17445945739746</v>
       </c>
       <c r="F168" t="n">
         <v>837000</v>
@@ -3792,16 +3792,16 @@
         <v>44343</v>
       </c>
       <c r="B169" t="n">
-        <v>22.3443431854248</v>
+        <v>22.34434127807617</v>
       </c>
       <c r="C169" t="n">
-        <v>22.3443431854248</v>
+        <v>22.34434127807617</v>
       </c>
       <c r="D169" t="n">
-        <v>21.80339410488992</v>
+        <v>21.80339224371756</v>
       </c>
       <c r="E169" t="n">
-        <v>22.27281274258895</v>
+        <v>22.27281084134627</v>
       </c>
       <c r="F169" t="n">
         <v>1342400</v>
@@ -3812,16 +3812,16 @@
         <v>44344</v>
       </c>
       <c r="B170" t="n">
-        <v>22.21469306945801</v>
+        <v>22.21469497680664</v>
       </c>
       <c r="C170" t="n">
-        <v>22.54552242370129</v>
+        <v>22.54552435945486</v>
       </c>
       <c r="D170" t="n">
-        <v>21.94198443666828</v>
+        <v>21.94198632060221</v>
       </c>
       <c r="E170" t="n">
-        <v>22.29516502845177</v>
+        <v>22.29516694270971</v>
       </c>
       <c r="F170" t="n">
         <v>840600</v>
@@ -3832,16 +3832,16 @@
         <v>44347</v>
       </c>
       <c r="B171" t="n">
-        <v>23.22953414916992</v>
+        <v>23.22953224182129</v>
       </c>
       <c r="C171" t="n">
-        <v>23.22953414916992</v>
+        <v>23.22953224182129</v>
       </c>
       <c r="D171" t="n">
-        <v>22.24151932802007</v>
+        <v>22.24151750179612</v>
       </c>
       <c r="E171" t="n">
-        <v>22.24151932802007</v>
+        <v>22.24151750179612</v>
       </c>
       <c r="F171" t="n">
         <v>1311400</v>
@@ -3852,16 +3852,16 @@
         <v>44348</v>
       </c>
       <c r="B172" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C172" t="n">
-        <v>24.09237101528835</v>
+        <v>24.09236907591068</v>
       </c>
       <c r="D172" t="n">
-        <v>23.10435619826109</v>
+        <v>23.10435433841622</v>
       </c>
       <c r="E172" t="n">
-        <v>23.32341744272831</v>
+        <v>23.32341556524954</v>
       </c>
       <c r="F172" t="n">
         <v>1770600</v>
@@ -3872,16 +3872,16 @@
         <v>44349</v>
       </c>
       <c r="B173" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C173" t="n">
-        <v>24.03872360721357</v>
+        <v>24.03872167215439</v>
       </c>
       <c r="D173" t="n">
-        <v>23.4709499467094</v>
+        <v>23.47094805735462</v>
       </c>
       <c r="E173" t="n">
-        <v>24.03872360721357</v>
+        <v>24.03872167215439</v>
       </c>
       <c r="F173" t="n">
         <v>823800</v>
@@ -3892,16 +3892,16 @@
         <v>44351</v>
       </c>
       <c r="B174" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C174" t="n">
-        <v>23.91801565998005</v>
+        <v>23.91801373463757</v>
       </c>
       <c r="D174" t="n">
-        <v>23.39941950080291</v>
+        <v>23.39941761720616</v>
       </c>
       <c r="E174" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="F174" t="n">
         <v>902800</v>
@@ -3912,16 +3912,16 @@
         <v>44354</v>
       </c>
       <c r="B175" t="n">
-        <v>23.51565551757812</v>
+        <v>23.51565361022949</v>
       </c>
       <c r="C175" t="n">
-        <v>23.95378141142314</v>
+        <v>23.95377946853823</v>
       </c>
       <c r="D175" t="n">
-        <v>23.24741677541455</v>
+        <v>23.24741488982269</v>
       </c>
       <c r="E175" t="n">
-        <v>23.56483301823953</v>
+        <v>23.56483110690212</v>
       </c>
       <c r="F175" t="n">
         <v>1060000</v>
@@ -3952,16 +3952,16 @@
         <v>44356</v>
       </c>
       <c r="B177" t="n">
-        <v>23.51565551757812</v>
+        <v>23.51565361022949</v>
       </c>
       <c r="C177" t="n">
-        <v>23.60059909341884</v>
+        <v>23.60059717918046</v>
       </c>
       <c r="D177" t="n">
-        <v>23.18035623716349</v>
+        <v>23.1803543570109</v>
       </c>
       <c r="E177" t="n">
-        <v>23.44412507263982</v>
+        <v>23.444123171093</v>
       </c>
       <c r="F177" t="n">
         <v>621600</v>
@@ -3972,16 +3972,16 @@
         <v>44357</v>
       </c>
       <c r="B178" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="C178" t="n">
-        <v>23.89119110323249</v>
+        <v>23.89118918004931</v>
       </c>
       <c r="D178" t="n">
-        <v>23.44859700212994</v>
+        <v>23.44859511457452</v>
       </c>
       <c r="E178" t="n">
-        <v>23.69448280334473</v>
+        <v>23.69448089599609</v>
       </c>
       <c r="F178" t="n">
         <v>946600</v>
@@ -4012,16 +4012,16 @@
         <v>44361</v>
       </c>
       <c r="B180" t="n">
-        <v>24.5886116027832</v>
+        <v>24.58861351013184</v>
       </c>
       <c r="C180" t="n">
-        <v>24.76743855115333</v>
+        <v>24.76744047237364</v>
       </c>
       <c r="D180" t="n">
-        <v>23.26082603049845</v>
+        <v>23.26082783485022</v>
       </c>
       <c r="E180" t="n">
-        <v>23.45753601478963</v>
+        <v>23.45753783440027</v>
       </c>
       <c r="F180" t="n">
         <v>1774600</v>
@@ -4052,16 +4052,16 @@
         <v>44363</v>
       </c>
       <c r="B182" t="n">
-        <v>24.49919891357422</v>
+        <v>24.49920082092285</v>
       </c>
       <c r="C182" t="n">
-        <v>24.58414248421078</v>
+        <v>24.58414439817256</v>
       </c>
       <c r="D182" t="n">
-        <v>23.90013083438584</v>
+        <v>23.90013269509492</v>
       </c>
       <c r="E182" t="n">
-        <v>24.36507955070941</v>
+        <v>24.36508144761637</v>
       </c>
       <c r="F182" t="n">
         <v>781400</v>
@@ -4072,16 +4072,16 @@
         <v>44364</v>
       </c>
       <c r="B183" t="n">
-        <v>24.5886116027832</v>
+        <v>24.58861351013184</v>
       </c>
       <c r="C183" t="n">
-        <v>24.71378944339019</v>
+        <v>24.71379136044892</v>
       </c>
       <c r="D183" t="n">
-        <v>23.96719060059827</v>
+        <v>23.96719245974302</v>
       </c>
       <c r="E183" t="n">
-        <v>24.63331748716565</v>
+        <v>24.63331939798214</v>
       </c>
       <c r="F183" t="n">
         <v>897400</v>
@@ -4092,16 +4092,16 @@
         <v>44365</v>
       </c>
       <c r="B184" t="n">
-        <v>24.89708518981934</v>
+        <v>24.89708709716797</v>
       </c>
       <c r="C184" t="n">
-        <v>25.19214844770217</v>
+        <v>25.19215037765539</v>
       </c>
       <c r="D184" t="n">
-        <v>24.25778118016986</v>
+        <v>24.25778303854185</v>
       </c>
       <c r="E184" t="n">
-        <v>24.67802397850789</v>
+        <v>24.6780258690744</v>
       </c>
       <c r="F184" t="n">
         <v>1737600</v>
@@ -4132,16 +4132,16 @@
         <v>44369</v>
       </c>
       <c r="B186" t="n">
-        <v>24.5886116027832</v>
+        <v>24.58861351013184</v>
       </c>
       <c r="C186" t="n">
-        <v>25.26815161900145</v>
+        <v>25.26815357906228</v>
       </c>
       <c r="D186" t="n">
-        <v>24.54390571840076</v>
+        <v>24.54390762228154</v>
       </c>
       <c r="E186" t="n">
-        <v>25.23238554715936</v>
+        <v>25.2323875044458</v>
       </c>
       <c r="F186" t="n">
         <v>871000</v>
@@ -4152,16 +4152,16 @@
         <v>44370</v>
       </c>
       <c r="B187" t="n">
-        <v>24.72273445129395</v>
+        <v>24.72273254394531</v>
       </c>
       <c r="C187" t="n">
-        <v>24.87920847956124</v>
+        <v>24.87920656014071</v>
       </c>
       <c r="D187" t="n">
-        <v>24.28014033500109</v>
+        <v>24.28013846179841</v>
       </c>
       <c r="E187" t="n">
-        <v>24.71379293207121</v>
+        <v>24.71379102541241</v>
       </c>
       <c r="F187" t="n">
         <v>1264600</v>
@@ -4192,16 +4192,16 @@
         <v>44372</v>
       </c>
       <c r="B189" t="n">
-        <v>24.35167121887207</v>
+        <v>24.35166931152344</v>
       </c>
       <c r="C189" t="n">
-        <v>24.58861551354074</v>
+        <v>24.5886135876334</v>
       </c>
       <c r="D189" t="n">
-        <v>24.0029587846305</v>
+        <v>24.00295690459483</v>
       </c>
       <c r="E189" t="n">
-        <v>24.27119924984866</v>
+        <v>24.27119734880301</v>
       </c>
       <c r="F189" t="n">
         <v>926400</v>
@@ -4212,16 +4212,16 @@
         <v>44375</v>
       </c>
       <c r="B190" t="n">
-        <v>24.48579025268555</v>
+        <v>24.48578834533691</v>
       </c>
       <c r="C190" t="n">
-        <v>25.0133279508625</v>
+        <v>25.01332600242071</v>
       </c>
       <c r="D190" t="n">
-        <v>24.06107746782506</v>
+        <v>24.06107559355992</v>
       </c>
       <c r="E190" t="n">
-        <v>24.06107746782506</v>
+        <v>24.06107559355992</v>
       </c>
       <c r="F190" t="n">
         <v>1351800</v>
@@ -4232,16 +4232,16 @@
         <v>44376</v>
       </c>
       <c r="B191" t="n">
-        <v>24.49919891357422</v>
+        <v>24.49920082092285</v>
       </c>
       <c r="C191" t="n">
-        <v>24.70484871699495</v>
+        <v>24.70485064035414</v>
       </c>
       <c r="D191" t="n">
-        <v>23.49330113395778</v>
+        <v>23.49330296299373</v>
       </c>
       <c r="E191" t="n">
-        <v>24.46790445241977</v>
+        <v>24.46790635733202</v>
       </c>
       <c r="F191" t="n">
         <v>1326200</v>
@@ -4312,16 +4312,16 @@
         <v>44382</v>
       </c>
       <c r="B195" t="n">
-        <v>26.53334808349609</v>
+        <v>26.53334617614746</v>
       </c>
       <c r="C195" t="n">
-        <v>26.77923557792692</v>
+        <v>26.77923365290268</v>
       </c>
       <c r="D195" t="n">
-        <v>26.17122596518936</v>
+        <v>26.17122408387186</v>
       </c>
       <c r="E195" t="n">
-        <v>26.3813456803117</v>
+        <v>26.38134378388976</v>
       </c>
       <c r="F195" t="n">
         <v>581600</v>
@@ -4332,16 +4332,16 @@
         <v>44383</v>
       </c>
       <c r="B196" t="n">
-        <v>26.19804954528809</v>
+        <v>26.19804763793945</v>
       </c>
       <c r="C196" t="n">
-        <v>26.53334882294324</v>
+        <v>26.53334689118315</v>
       </c>
       <c r="D196" t="n">
-        <v>25.66157206537609</v>
+        <v>25.66157019708569</v>
       </c>
       <c r="E196" t="n">
-        <v>26.53334882294324</v>
+        <v>26.53334689118315</v>
       </c>
       <c r="F196" t="n">
         <v>905000</v>
@@ -4352,16 +4352,16 @@
         <v>44384</v>
       </c>
       <c r="B197" t="n">
-        <v>26.5244083404541</v>
+        <v>26.52441024780273</v>
       </c>
       <c r="C197" t="n">
-        <v>26.9357079587326</v>
+        <v>26.93570989565746</v>
       </c>
       <c r="D197" t="n">
-        <v>26.10863711021764</v>
+        <v>26.1086389876685</v>
       </c>
       <c r="E197" t="n">
-        <v>26.19804888433364</v>
+        <v>26.19805076821403</v>
       </c>
       <c r="F197" t="n">
         <v>915800</v>
@@ -4372,16 +4372,16 @@
         <v>44385</v>
       </c>
       <c r="B198" t="n">
-        <v>26.5244083404541</v>
+        <v>26.52441024780273</v>
       </c>
       <c r="C198" t="n">
-        <v>26.5244083404541</v>
+        <v>26.52441024780273</v>
       </c>
       <c r="D198" t="n">
-        <v>25.82251363461749</v>
+        <v>25.82251549149344</v>
       </c>
       <c r="E198" t="n">
-        <v>26.23828486485395</v>
+        <v>26.23828675162768</v>
       </c>
       <c r="F198" t="n">
         <v>1041800</v>
@@ -4392,16 +4392,16 @@
         <v>44389</v>
       </c>
       <c r="B199" t="n">
-        <v>27.5437183380127</v>
+        <v>27.54371643066406</v>
       </c>
       <c r="C199" t="n">
-        <v>27.57501280090645</v>
+        <v>27.57501089139074</v>
       </c>
       <c r="D199" t="n">
-        <v>26.56911496538337</v>
+        <v>26.56911312552412</v>
       </c>
       <c r="E199" t="n">
-        <v>26.81500076187162</v>
+        <v>26.81499890498525</v>
       </c>
       <c r="F199" t="n">
         <v>886400</v>
@@ -4412,16 +4412,16 @@
         <v>44390</v>
       </c>
       <c r="B200" t="n">
-        <v>27.66442489624023</v>
+        <v>27.6644229888916</v>
       </c>
       <c r="C200" t="n">
-        <v>27.70466087586113</v>
+        <v>27.70465896573839</v>
       </c>
       <c r="D200" t="n">
-        <v>27.1681817160559</v>
+        <v>27.16817984292119</v>
       </c>
       <c r="E200" t="n">
-        <v>27.33806715283528</v>
+        <v>27.33806526798767</v>
       </c>
       <c r="F200" t="n">
         <v>796200</v>
@@ -4432,16 +4432,16 @@
         <v>44391</v>
       </c>
       <c r="B201" t="n">
-        <v>28.17408180236816</v>
+        <v>28.1740837097168</v>
       </c>
       <c r="C201" t="n">
-        <v>28.33502573399738</v>
+        <v>28.33502765224171</v>
       </c>
       <c r="D201" t="n">
-        <v>27.44089429643097</v>
+        <v>27.44089615414376</v>
       </c>
       <c r="E201" t="n">
-        <v>27.67336867484868</v>
+        <v>27.67337054829968</v>
       </c>
       <c r="F201" t="n">
         <v>880600</v>
@@ -4472,16 +4472,16 @@
         <v>44393</v>
       </c>
       <c r="B203" t="n">
-        <v>28.79103088378906</v>
+        <v>28.79102897644043</v>
       </c>
       <c r="C203" t="n">
-        <v>29.03244676372463</v>
+        <v>29.03244484038268</v>
       </c>
       <c r="D203" t="n">
-        <v>28.15172681585982</v>
+        <v>28.15172495086382</v>
       </c>
       <c r="E203" t="n">
-        <v>28.72844196056582</v>
+        <v>28.72844005736358</v>
       </c>
       <c r="F203" t="n">
         <v>1048600</v>
@@ -4512,16 +4512,16 @@
         <v>44397</v>
       </c>
       <c r="B205" t="n">
-        <v>29.3990421295166</v>
+        <v>29.39904022216797</v>
       </c>
       <c r="C205" t="n">
-        <v>29.60469194740947</v>
+        <v>29.60469002671871</v>
       </c>
       <c r="D205" t="n">
-        <v>28.66138302371869</v>
+        <v>28.66138116422784</v>
       </c>
       <c r="E205" t="n">
-        <v>28.84020999040314</v>
+        <v>28.84020811931037</v>
       </c>
       <c r="F205" t="n">
         <v>665800</v>
@@ -4572,16 +4572,16 @@
         <v>44400</v>
       </c>
       <c r="B208" t="n">
-        <v>30.31105613708496</v>
+        <v>30.31105422973633</v>
       </c>
       <c r="C208" t="n">
-        <v>30.62400076597767</v>
+        <v>30.62399883893674</v>
       </c>
       <c r="D208" t="n">
-        <v>29.97128524654384</v>
+        <v>29.97128336057558</v>
       </c>
       <c r="E208" t="n">
-        <v>30.2395239871434</v>
+        <v>30.23952208429599</v>
       </c>
       <c r="F208" t="n">
         <v>819000</v>
@@ -4592,16 +4592,16 @@
         <v>44403</v>
       </c>
       <c r="B209" t="n">
-        <v>30.08752250671387</v>
+        <v>30.08752059936523</v>
       </c>
       <c r="C209" t="n">
-        <v>30.48987890178793</v>
+        <v>30.48987696893258</v>
       </c>
       <c r="D209" t="n">
-        <v>29.56445305360459</v>
+        <v>29.56445117941508</v>
       </c>
       <c r="E209" t="n">
-        <v>30.48987890178793</v>
+        <v>30.48987696893258</v>
       </c>
       <c r="F209" t="n">
         <v>1240800</v>
@@ -4612,16 +4612,16 @@
         <v>44404</v>
       </c>
       <c r="B210" t="n">
-        <v>29.40797805786133</v>
+        <v>29.40797996520996</v>
       </c>
       <c r="C210" t="n">
-        <v>30.19928617237645</v>
+        <v>30.1992881310479</v>
       </c>
       <c r="D210" t="n">
-        <v>29.30068325636174</v>
+        <v>29.30068515675142</v>
       </c>
       <c r="E210" t="n">
-        <v>29.98916477009458</v>
+        <v>29.98916671513793</v>
       </c>
       <c r="F210" t="n">
         <v>1032400</v>
@@ -4632,16 +4632,16 @@
         <v>44405</v>
       </c>
       <c r="B211" t="n">
-        <v>29.43927383422852</v>
+        <v>29.43927192687988</v>
       </c>
       <c r="C211" t="n">
-        <v>30.57034943923792</v>
+        <v>30.57034745860774</v>
       </c>
       <c r="D211" t="n">
-        <v>28.7329092535022</v>
+        <v>28.7329073919184</v>
       </c>
       <c r="E211" t="n">
-        <v>29.52868901517891</v>
+        <v>29.52868710203713</v>
       </c>
       <c r="F211" t="n">
         <v>1257400</v>
@@ -4652,16 +4652,16 @@
         <v>44406</v>
       </c>
       <c r="B212" t="n">
-        <v>30.84753608703613</v>
+        <v>30.84753227233887</v>
       </c>
       <c r="C212" t="n">
-        <v>31.5136630851845</v>
+        <v>31.51365918811201</v>
       </c>
       <c r="D212" t="n">
-        <v>29.56445618420886</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="E212" t="n">
-        <v>29.56445618420886</v>
+        <v>29.56445252818104</v>
       </c>
       <c r="F212" t="n">
         <v>1386000</v>
@@ -4672,16 +4672,16 @@
         <v>44407</v>
       </c>
       <c r="B213" t="n">
-        <v>31.13812828063965</v>
+        <v>31.13812255859375</v>
       </c>
       <c r="C213" t="n">
-        <v>31.58072239125372</v>
+        <v>31.58071658787525</v>
       </c>
       <c r="D213" t="n">
-        <v>30.41388058167417</v>
+        <v>30.41387499271843</v>
       </c>
       <c r="E213" t="n">
-        <v>30.80282898848094</v>
+        <v>30.80282332805076</v>
       </c>
       <c r="F213" t="n">
         <v>1548200</v>
@@ -4692,16 +4692,16 @@
         <v>44410</v>
       </c>
       <c r="B214" t="n">
-        <v>31.24989318847656</v>
+        <v>31.2498893737793</v>
       </c>
       <c r="C214" t="n">
-        <v>31.98755227744596</v>
+        <v>31.98754837270211</v>
       </c>
       <c r="D214" t="n">
-        <v>31.03977176322897</v>
+        <v>31.03976797418139</v>
       </c>
       <c r="E214" t="n">
-        <v>31.58072085224903</v>
+        <v>31.5807169971674</v>
       </c>
       <c r="F214" t="n">
         <v>1185600</v>
@@ -4712,16 +4712,16 @@
         <v>44411</v>
       </c>
       <c r="B215" t="n">
-        <v>30.62400054931641</v>
+        <v>30.62399864196777</v>
       </c>
       <c r="C215" t="n">
-        <v>31.14259840020176</v>
+        <v>31.1425964605534</v>
       </c>
       <c r="D215" t="n">
-        <v>30.20375769848453</v>
+        <v>30.2037558173098</v>
       </c>
       <c r="E215" t="n">
-        <v>31.13812678815189</v>
+        <v>31.13812484878203</v>
       </c>
       <c r="F215" t="n">
         <v>1467200</v>
@@ -4752,16 +4752,16 @@
         <v>44413</v>
       </c>
       <c r="B217" t="n">
-        <v>29.48398399353027</v>
+        <v>29.48397827148438</v>
       </c>
       <c r="C217" t="n">
-        <v>30.38705869242438</v>
+        <v>30.38705279511604</v>
       </c>
       <c r="D217" t="n">
-        <v>29.13974487677855</v>
+        <v>29.13973922154018</v>
       </c>
       <c r="E217" t="n">
-        <v>29.82375490871703</v>
+        <v>29.82374912073076</v>
       </c>
       <c r="F217" t="n">
         <v>1197200</v>
@@ -4792,16 +4792,16 @@
         <v>44417</v>
       </c>
       <c r="B219" t="n">
-        <v>30.23952484130859</v>
+        <v>30.23952102661133</v>
       </c>
       <c r="C219" t="n">
-        <v>30.4049403845904</v>
+        <v>30.40493654902606</v>
       </c>
       <c r="D219" t="n">
-        <v>29.54210341388179</v>
+        <v>29.54209968716381</v>
       </c>
       <c r="E219" t="n">
-        <v>29.85951966382196</v>
+        <v>29.85951589706211</v>
       </c>
       <c r="F219" t="n">
         <v>1023000</v>
@@ -4832,16 +4832,16 @@
         <v>44419</v>
       </c>
       <c r="B221" t="n">
-        <v>29.11291885375977</v>
+        <v>29.1129207611084</v>
       </c>
       <c r="C221" t="n">
-        <v>30.38258377149235</v>
+        <v>30.38258576202377</v>
       </c>
       <c r="D221" t="n">
-        <v>28.14725532970356</v>
+        <v>28.14725717378623</v>
       </c>
       <c r="E221" t="n">
-        <v>29.68516238912321</v>
+        <v>29.68516433396269</v>
       </c>
       <c r="F221" t="n">
         <v>1237750</v>
@@ -4852,16 +4852,16 @@
         <v>44420</v>
       </c>
       <c r="B222" t="n">
-        <v>29.32750511169434</v>
+        <v>29.32751083374023</v>
       </c>
       <c r="C222" t="n">
-        <v>31.18729979924009</v>
+        <v>31.18730588414776</v>
       </c>
       <c r="D222" t="n">
-        <v>28.46913990706097</v>
+        <v>28.46914546163251</v>
       </c>
       <c r="E222" t="n">
-        <v>28.48702294184585</v>
+        <v>28.48702849990652</v>
       </c>
       <c r="F222" t="n">
         <v>1567750</v>
@@ -4912,16 +4912,16 @@
         <v>44425</v>
       </c>
       <c r="B225" t="n">
-        <v>25.66156959533691</v>
+        <v>25.66157150268555</v>
       </c>
       <c r="C225" t="n">
-        <v>25.66156959533691</v>
+        <v>25.66157150268555</v>
       </c>
       <c r="D225" t="n">
-        <v>23.42624129279607</v>
+        <v>23.42624303399936</v>
       </c>
       <c r="E225" t="n">
-        <v>24.67802480113491</v>
+        <v>24.67802663537957</v>
       </c>
       <c r="F225" t="n">
         <v>4282800</v>
@@ -4952,16 +4952,16 @@
         <v>44427</v>
       </c>
       <c r="B227" t="n">
-        <v>26.4662914276123</v>
+        <v>26.46628761291504</v>
       </c>
       <c r="C227" t="n">
-        <v>26.73453018213193</v>
+        <v>26.73452632877229</v>
       </c>
       <c r="D227" t="n">
-        <v>24.30249323678068</v>
+        <v>24.3024897339607</v>
       </c>
       <c r="E227" t="n">
-        <v>24.85685378423334</v>
+        <v>24.85685020151106</v>
       </c>
       <c r="F227" t="n">
         <v>1738450</v>
@@ -4972,16 +4972,16 @@
         <v>44428</v>
       </c>
       <c r="B228" t="n">
-        <v>26.64511489868164</v>
+        <v>26.64511680603027</v>
       </c>
       <c r="C228" t="n">
-        <v>26.87758926611801</v>
+        <v>26.87759119010796</v>
       </c>
       <c r="D228" t="n">
-        <v>25.73310217156392</v>
+        <v>25.73310401362756</v>
       </c>
       <c r="E228" t="n">
-        <v>26.34111008783564</v>
+        <v>26.34111197342256</v>
       </c>
       <c r="F228" t="n">
         <v>1186050</v>
@@ -4992,16 +4992,16 @@
         <v>44431</v>
       </c>
       <c r="B229" t="n">
-        <v>26.85970878601074</v>
+        <v>26.85970687866211</v>
       </c>
       <c r="C229" t="n">
-        <v>27.41406931365822</v>
+        <v>27.41406736694361</v>
       </c>
       <c r="D229" t="n">
-        <v>26.28746351516839</v>
+        <v>26.28746164845576</v>
       </c>
       <c r="E229" t="n">
-        <v>26.71664618923489</v>
+        <v>26.71664429204535</v>
       </c>
       <c r="F229" t="n">
         <v>1094150</v>
@@ -5012,16 +5012,16 @@
         <v>44432</v>
       </c>
       <c r="B230" t="n">
-        <v>27.48559761047363</v>
+        <v>27.48559951782227</v>
       </c>
       <c r="C230" t="n">
-        <v>27.84324981090064</v>
+        <v>27.84325174306836</v>
       </c>
       <c r="D230" t="n">
-        <v>27.00276756625223</v>
+        <v>27.00276944009512</v>
       </c>
       <c r="E230" t="n">
-        <v>27.64654152702084</v>
+        <v>27.64654344553809</v>
       </c>
       <c r="F230" t="n">
         <v>835550</v>
@@ -5032,16 +5032,16 @@
         <v>44433</v>
       </c>
       <c r="B231" t="n">
-        <v>27.89690017700195</v>
+        <v>27.89689636230469</v>
       </c>
       <c r="C231" t="n">
-        <v>28.41549631734295</v>
+        <v>28.41549243173145</v>
       </c>
       <c r="D231" t="n">
-        <v>27.27100751898821</v>
+        <v>27.27100378987718</v>
       </c>
       <c r="E231" t="n">
-        <v>27.48559884891342</v>
+        <v>27.4855950904586</v>
       </c>
       <c r="F231" t="n">
         <v>1098800</v>
@@ -5072,16 +5072,16 @@
         <v>44435</v>
       </c>
       <c r="B233" t="n">
-        <v>28.96985626220703</v>
+        <v>28.9698600769043</v>
       </c>
       <c r="C233" t="n">
-        <v>29.11291713761476</v>
+        <v>29.11292097115001</v>
       </c>
       <c r="D233" t="n">
-        <v>27.00276666722057</v>
+        <v>27.00277022289511</v>
       </c>
       <c r="E233" t="n">
-        <v>27.44983232922475</v>
+        <v>27.44983594376807</v>
       </c>
       <c r="F233" t="n">
         <v>1634000</v>
@@ -5192,16 +5192,16 @@
         <v>44445</v>
       </c>
       <c r="B239" t="n">
-        <v>25.76886558532715</v>
+        <v>25.76886749267578</v>
       </c>
       <c r="C239" t="n">
-        <v>25.89404343029868</v>
+        <v>25.89404534691268</v>
       </c>
       <c r="D239" t="n">
-        <v>24.87473422314136</v>
+        <v>24.87473606430857</v>
       </c>
       <c r="E239" t="n">
-        <v>24.87473422314136</v>
+        <v>24.87473606430857</v>
       </c>
       <c r="F239" t="n">
         <v>528250</v>
@@ -5252,16 +5252,16 @@
         <v>44449</v>
       </c>
       <c r="B242" t="n">
-        <v>25.19662284851074</v>
+        <v>25.19662094116211</v>
       </c>
       <c r="C242" t="n">
-        <v>26.19804905049173</v>
+        <v>26.19804706733655</v>
       </c>
       <c r="D242" t="n">
-        <v>24.64226063620605</v>
+        <v>24.64225877082185</v>
       </c>
       <c r="E242" t="n">
-        <v>26.00134075860054</v>
+        <v>26.0013387903359</v>
       </c>
       <c r="F242" t="n">
         <v>1514650</v>
@@ -5272,16 +5272,16 @@
         <v>44452</v>
       </c>
       <c r="B243" t="n">
-        <v>26.48417472839355</v>
+        <v>26.48417282104492</v>
       </c>
       <c r="C243" t="n">
-        <v>26.82394393451239</v>
+        <v>26.82394200269411</v>
       </c>
       <c r="D243" t="n">
-        <v>25.16085886483809</v>
+        <v>25.16085705279258</v>
       </c>
       <c r="E243" t="n">
-        <v>25.37545021166373</v>
+        <v>25.3754483841637</v>
       </c>
       <c r="F243" t="n">
         <v>1238850</v>
@@ -5312,16 +5312,16 @@
         <v>44454</v>
       </c>
       <c r="B245" t="n">
-        <v>26.3232307434082</v>
+        <v>26.32322883605957</v>
       </c>
       <c r="C245" t="n">
-        <v>26.53782208983838</v>
+        <v>26.53782016694073</v>
       </c>
       <c r="D245" t="n">
-        <v>25.66157366556005</v>
+        <v>25.66157180615427</v>
       </c>
       <c r="E245" t="n">
-        <v>26.30534770485058</v>
+        <v>26.30534579879773</v>
       </c>
       <c r="F245" t="n">
         <v>552000</v>
@@ -5372,16 +5372,16 @@
         <v>44459</v>
       </c>
       <c r="B248" t="n">
-        <v>24.17731285095215</v>
+        <v>24.17731094360352</v>
       </c>
       <c r="C248" t="n">
-        <v>24.58861245893628</v>
+        <v>24.58861051914021</v>
       </c>
       <c r="D248" t="n">
-        <v>23.71236413333686</v>
+        <v>23.71236226266804</v>
       </c>
       <c r="E248" t="n">
-        <v>24.37402113667235</v>
+        <v>24.3740192138054</v>
       </c>
       <c r="F248" t="n">
         <v>1148950</v>
@@ -5412,16 +5412,16 @@
         <v>44461</v>
       </c>
       <c r="B250" t="n">
-        <v>25.48274230957031</v>
+        <v>25.48274421691895</v>
       </c>
       <c r="C250" t="n">
-        <v>26.37687361867804</v>
+        <v>26.37687559295119</v>
       </c>
       <c r="D250" t="n">
-        <v>25.2323849290689</v>
+        <v>25.23238681767862</v>
       </c>
       <c r="E250" t="n">
-        <v>25.92980796412418</v>
+        <v>25.92980990493507</v>
       </c>
       <c r="F250" t="n">
         <v>900000</v>
@@ -5472,16 +5472,16 @@
         <v>44466</v>
       </c>
       <c r="B253" t="n">
-        <v>26.01922225952148</v>
+        <v>26.01922416687012</v>
       </c>
       <c r="C253" t="n">
-        <v>26.34110838130097</v>
+        <v>26.34111031224558</v>
       </c>
       <c r="D253" t="n">
-        <v>25.57215659081981</v>
+        <v>25.57215846539613</v>
       </c>
       <c r="E253" t="n">
-        <v>26.21593053979895</v>
+        <v>26.21593246156736</v>
       </c>
       <c r="F253" t="n">
         <v>663500</v>
@@ -5512,16 +5512,16 @@
         <v>44468</v>
       </c>
       <c r="B255" t="n">
-        <v>24.67802810668945</v>
+        <v>24.67802619934082</v>
       </c>
       <c r="C255" t="n">
-        <v>25.39333257714754</v>
+        <v>25.39333061451349</v>
       </c>
       <c r="D255" t="n">
-        <v>24.46343676555203</v>
+        <v>24.46343487478902</v>
       </c>
       <c r="E255" t="n">
-        <v>25.10721078896431</v>
+        <v>25.10720884844443</v>
       </c>
       <c r="F255" t="n">
         <v>580300</v>
@@ -5572,16 +5572,16 @@
         <v>44473</v>
       </c>
       <c r="B258" t="n">
-        <v>23.87331008911133</v>
+        <v>23.8733081817627</v>
       </c>
       <c r="C258" t="n">
-        <v>25.10721072380433</v>
+        <v>25.10720871787369</v>
       </c>
       <c r="D258" t="n">
-        <v>23.87331008911133</v>
+        <v>23.8733081817627</v>
       </c>
       <c r="E258" t="n">
-        <v>25.01779723887402</v>
+        <v>25.01779524008704</v>
       </c>
       <c r="F258" t="n">
         <v>576500</v>
@@ -5592,16 +5592,16 @@
         <v>44474</v>
       </c>
       <c r="B259" t="n">
-        <v>23.40836143493652</v>
+        <v>23.40835952758789</v>
       </c>
       <c r="C259" t="n">
-        <v>23.98060501233891</v>
+        <v>23.98060305836301</v>
       </c>
       <c r="D259" t="n">
-        <v>23.08647356993749</v>
+        <v>23.08647168881676</v>
       </c>
       <c r="E259" t="n">
-        <v>23.90907456516361</v>
+        <v>23.90907261701612</v>
       </c>
       <c r="F259" t="n">
         <v>1237200</v>
@@ -5632,16 +5632,16 @@
         <v>44476</v>
       </c>
       <c r="B261" t="n">
-        <v>23.62295150756836</v>
+        <v>23.62295341491699</v>
       </c>
       <c r="C261" t="n">
-        <v>24.26672549756607</v>
+        <v>24.26672745689388</v>
       </c>
       <c r="D261" t="n">
-        <v>23.42624321475746</v>
+        <v>23.42624510622361</v>
       </c>
       <c r="E261" t="n">
-        <v>24.1594306852766</v>
+        <v>24.15943263594128</v>
       </c>
       <c r="F261" t="n">
         <v>699850</v>
@@ -5652,16 +5652,16 @@
         <v>44477</v>
       </c>
       <c r="B262" t="n">
-        <v>24.05213356018066</v>
+        <v>24.0521354675293</v>
       </c>
       <c r="C262" t="n">
-        <v>24.53496531955127</v>
+        <v>24.53496726518875</v>
       </c>
       <c r="D262" t="n">
-        <v>23.69448135254702</v>
+        <v>23.69448323153362</v>
       </c>
       <c r="E262" t="n">
-        <v>23.81965919886374</v>
+        <v>23.81966108777701</v>
       </c>
       <c r="F262" t="n">
         <v>982950</v>
@@ -5672,16 +5672,16 @@
         <v>44480</v>
       </c>
       <c r="B263" t="n">
-        <v>24.0879020690918</v>
+        <v>24.08789825439453</v>
       </c>
       <c r="C263" t="n">
-        <v>24.60649824894896</v>
+        <v>24.60649435212385</v>
       </c>
       <c r="D263" t="n">
-        <v>23.73024982529728</v>
+        <v>23.73024606723985</v>
       </c>
       <c r="E263" t="n">
-        <v>24.0342529534573</v>
+        <v>24.03424914725622</v>
       </c>
       <c r="F263" t="n">
         <v>770500</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35613822937012</v>
+        <v>24.35613632202148</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991219957796</v>
+        <v>24.99991024181488</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848602369909</v>
+        <v>23.99848414435849</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307734710171</v>
+        <v>24.21307545095629</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5732,16 +5732,16 @@
         <v>44484</v>
       </c>
       <c r="B266" t="n">
-        <v>26.16228294372559</v>
+        <v>26.16228485107422</v>
       </c>
       <c r="C266" t="n">
-        <v>26.59146557320656</v>
+        <v>26.59146751184455</v>
       </c>
       <c r="D266" t="n">
-        <v>24.44555072038149</v>
+        <v>24.44555250257259</v>
       </c>
       <c r="E266" t="n">
-        <v>24.76743854520231</v>
+        <v>24.76744035086049</v>
       </c>
       <c r="F266" t="n">
         <v>2075800</v>
@@ -5812,16 +5812,16 @@
         <v>44490</v>
       </c>
       <c r="B270" t="n">
-        <v>22.44269943237305</v>
+        <v>22.44269752502441</v>
       </c>
       <c r="C270" t="n">
-        <v>23.46200872584448</v>
+        <v>23.46200673186731</v>
       </c>
       <c r="D270" t="n">
-        <v>21.67374585004456</v>
+        <v>21.67374400804736</v>
       </c>
       <c r="E270" t="n">
-        <v>22.88976515132303</v>
+        <v>22.8897632059794</v>
       </c>
       <c r="F270" t="n">
         <v>1908000</v>
@@ -5852,16 +5852,16 @@
         <v>44494</v>
       </c>
       <c r="B272" t="n">
-        <v>21.62009811401367</v>
+        <v>21.6201000213623</v>
       </c>
       <c r="C272" t="n">
-        <v>22.28175516339335</v>
+        <v>22.28175712911409</v>
       </c>
       <c r="D272" t="n">
-        <v>20.79749713538103</v>
+        <v>20.79749897015891</v>
       </c>
       <c r="E272" t="n">
-        <v>20.83326150553705</v>
+        <v>20.8332633434701</v>
       </c>
       <c r="F272" t="n">
         <v>1833600</v>
@@ -5872,16 +5872,16 @@
         <v>44495</v>
       </c>
       <c r="B273" t="n">
-        <v>20.29678153991699</v>
+        <v>20.29678344726562</v>
       </c>
       <c r="C273" t="n">
-        <v>21.53068200467281</v>
+        <v>21.53068402797473</v>
       </c>
       <c r="D273" t="n">
-        <v>20.17160199608659</v>
+        <v>20.17160389167173</v>
       </c>
       <c r="E273" t="n">
-        <v>21.45915156766407</v>
+        <v>21.45915358424406</v>
       </c>
       <c r="F273" t="n">
         <v>1532000</v>
@@ -5892,16 +5892,16 @@
         <v>44496</v>
       </c>
       <c r="B274" t="n">
-        <v>20.49348831176758</v>
+        <v>20.49349021911621</v>
       </c>
       <c r="C274" t="n">
-        <v>21.10149783444344</v>
+        <v>21.1014997983801</v>
       </c>
       <c r="D274" t="n">
-        <v>20.31466137965585</v>
+        <v>20.31466327036089</v>
       </c>
       <c r="E274" t="n">
-        <v>20.42195788000689</v>
+        <v>20.42195978069811</v>
       </c>
       <c r="F274" t="n">
         <v>1013650</v>
@@ -5932,16 +5932,16 @@
         <v>44498</v>
       </c>
       <c r="B276" t="n">
-        <v>18.32969284057617</v>
+        <v>18.3296947479248</v>
       </c>
       <c r="C276" t="n">
-        <v>20.52925516284361</v>
+        <v>20.52925729907399</v>
       </c>
       <c r="D276" t="n">
-        <v>18.09721848282576</v>
+        <v>18.0972203659836</v>
       </c>
       <c r="E276" t="n">
-        <v>20.24313340112624</v>
+        <v>20.2431355075834</v>
       </c>
       <c r="F276" t="n">
         <v>3577000</v>
@@ -6032,16 +6032,16 @@
         <v>44508</v>
       </c>
       <c r="B281" t="n">
-        <v>20.13583946228027</v>
+        <v>20.13583755493164</v>
       </c>
       <c r="C281" t="n">
-        <v>20.86902693468137</v>
+        <v>20.86902495788224</v>
       </c>
       <c r="D281" t="n">
-        <v>19.86759902002748</v>
+        <v>19.86759713808767</v>
       </c>
       <c r="E281" t="n">
-        <v>20.86902693468137</v>
+        <v>20.86902495788224</v>
       </c>
       <c r="F281" t="n">
         <v>919700</v>
@@ -6052,16 +6052,16 @@
         <v>44509</v>
       </c>
       <c r="B282" t="n">
-        <v>20.67231750488281</v>
+        <v>20.67231941223145</v>
       </c>
       <c r="C282" t="n">
-        <v>21.36973886447393</v>
+        <v>21.36974083617073</v>
       </c>
       <c r="D282" t="n">
-        <v>20.29678227071059</v>
+        <v>20.29678414341015</v>
       </c>
       <c r="E282" t="n">
-        <v>20.29678227071059</v>
+        <v>20.29678414341015</v>
       </c>
       <c r="F282" t="n">
         <v>912150</v>
@@ -6092,16 +6092,16 @@
         <v>44511</v>
       </c>
       <c r="B284" t="n">
-        <v>21.94198608398438</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C284" t="n">
-        <v>22.99705973754176</v>
+        <v>22.99705773847886</v>
       </c>
       <c r="D284" t="n">
-        <v>21.78104215391382</v>
+        <v>21.78104026055555</v>
       </c>
       <c r="E284" t="n">
-        <v>21.95986741644305</v>
+        <v>21.95986550754004</v>
       </c>
       <c r="F284" t="n">
         <v>2031350</v>
@@ -6132,16 +6132,16 @@
         <v>44516</v>
       </c>
       <c r="B286" t="n">
-        <v>20.63655090332031</v>
+        <v>20.63655471801758</v>
       </c>
       <c r="C286" t="n">
-        <v>21.87045138086964</v>
+        <v>21.87045542365525</v>
       </c>
       <c r="D286" t="n">
-        <v>19.77818565031559</v>
+        <v>19.77818930634276</v>
       </c>
       <c r="E286" t="n">
-        <v>21.76315657695413</v>
+        <v>21.76316059990614</v>
       </c>
       <c r="F286" t="n">
         <v>1709550</v>
@@ -6172,16 +6172,16 @@
         <v>44518</v>
       </c>
       <c r="B288" t="n">
-        <v>20.33254623413086</v>
+        <v>20.33254814147949</v>
       </c>
       <c r="C288" t="n">
-        <v>20.70808146084758</v>
+        <v>20.7080834034243</v>
       </c>
       <c r="D288" t="n">
-        <v>19.68877229065369</v>
+        <v>19.68877413761139</v>
       </c>
       <c r="E288" t="n">
-        <v>19.68877229065369</v>
+        <v>19.68877413761139</v>
       </c>
       <c r="F288" t="n">
         <v>766850</v>
@@ -6192,16 +6192,16 @@
         <v>44519</v>
       </c>
       <c r="B289" t="n">
-        <v>20.99420356750488</v>
+        <v>20.99420547485352</v>
       </c>
       <c r="C289" t="n">
-        <v>21.24456095801091</v>
+        <v>21.24456288810481</v>
       </c>
       <c r="D289" t="n">
-        <v>20.11795525886409</v>
+        <v>20.11795708660452</v>
       </c>
       <c r="E289" t="n">
-        <v>20.31466354077727</v>
+        <v>20.31466538638888</v>
       </c>
       <c r="F289" t="n">
         <v>767750</v>
@@ -6212,16 +6212,16 @@
         <v>44522</v>
       </c>
       <c r="B290" t="n">
-        <v>20.18948745727539</v>
+        <v>20.18948554992676</v>
       </c>
       <c r="C290" t="n">
-        <v>21.44127110802875</v>
+        <v>21.44126908242115</v>
       </c>
       <c r="D290" t="n">
-        <v>19.97489612046799</v>
+        <v>19.97489423339231</v>
       </c>
       <c r="E290" t="n">
-        <v>20.869027543209</v>
+        <v>20.86902557166261</v>
       </c>
       <c r="F290" t="n">
         <v>852100</v>
@@ -6232,16 +6232,16 @@
         <v>44523</v>
       </c>
       <c r="B291" t="n">
-        <v>19.24170684814453</v>
+        <v>19.24170875549316</v>
       </c>
       <c r="C291" t="n">
-        <v>20.45772431098796</v>
+        <v>20.45772633887523</v>
       </c>
       <c r="D291" t="n">
-        <v>19.02711553117216</v>
+        <v>19.02711741724927</v>
       </c>
       <c r="E291" t="n">
-        <v>20.20736862723029</v>
+        <v>20.20737063030087</v>
       </c>
       <c r="F291" t="n">
         <v>1896750</v>
@@ -6252,16 +6252,16 @@
         <v>44524</v>
       </c>
       <c r="B292" t="n">
-        <v>19.58147621154785</v>
+        <v>19.58147811889648</v>
       </c>
       <c r="C292" t="n">
-        <v>20.33254668150708</v>
+        <v>20.3325486620143</v>
       </c>
       <c r="D292" t="n">
-        <v>19.02711572993332</v>
+        <v>19.02711758328404</v>
       </c>
       <c r="E292" t="n">
-        <v>19.04499706080266</v>
+        <v>19.04499891589514</v>
       </c>
       <c r="F292" t="n">
         <v>1594900</v>
@@ -6272,16 +6272,16 @@
         <v>44525</v>
       </c>
       <c r="B293" t="n">
-        <v>20.29678153991699</v>
+        <v>20.29678344726562</v>
       </c>
       <c r="C293" t="n">
-        <v>20.43984241393447</v>
+        <v>20.43984433472696</v>
       </c>
       <c r="D293" t="n">
-        <v>19.65300590141818</v>
+        <v>19.65300774826931</v>
       </c>
       <c r="E293" t="n">
-        <v>19.65300590141818</v>
+        <v>19.65300774826931</v>
       </c>
       <c r="F293" t="n">
         <v>787900</v>
@@ -6332,16 +6332,16 @@
         <v>44530</v>
       </c>
       <c r="B296" t="n">
-        <v>18.83040618896484</v>
+        <v>18.83040809631348</v>
       </c>
       <c r="C296" t="n">
-        <v>19.25959054300976</v>
+        <v>19.25959249383086</v>
       </c>
       <c r="D296" t="n">
-        <v>18.06145436986738</v>
+        <v>18.06145619932819</v>
       </c>
       <c r="E296" t="n">
-        <v>19.04499751327718</v>
+        <v>19.04499944236196</v>
       </c>
       <c r="F296" t="n">
         <v>1327800</v>
@@ -6432,16 +6432,16 @@
         <v>44537</v>
       </c>
       <c r="B301" t="n">
-        <v>19.93912696838379</v>
+        <v>19.93912887573242</v>
       </c>
       <c r="C301" t="n">
-        <v>20.72596345402377</v>
+        <v>20.72596543664007</v>
       </c>
       <c r="D301" t="n">
-        <v>19.90336260381111</v>
+        <v>19.90336450773857</v>
       </c>
       <c r="E301" t="n">
-        <v>20.35042824620016</v>
+        <v>20.35043019289329</v>
       </c>
       <c r="F301" t="n">
         <v>881500</v>
@@ -6452,16 +6452,16 @@
         <v>44538</v>
       </c>
       <c r="B302" t="n">
-        <v>21.42338562011719</v>
+        <v>21.42338752746582</v>
       </c>
       <c r="C302" t="n">
-        <v>21.51279909324929</v>
+        <v>21.51280100855851</v>
       </c>
       <c r="D302" t="n">
-        <v>19.86759732713109</v>
+        <v>19.86759909596611</v>
       </c>
       <c r="E302" t="n">
-        <v>20.18948514823861</v>
+        <v>20.18948694573167</v>
       </c>
       <c r="F302" t="n">
         <v>984450</v>
@@ -6472,16 +6472,16 @@
         <v>44539</v>
       </c>
       <c r="B303" t="n">
-        <v>20.9047908782959</v>
+        <v>20.90478897094727</v>
       </c>
       <c r="C303" t="n">
-        <v>21.36973960440232</v>
+        <v>21.36973765463187</v>
       </c>
       <c r="D303" t="n">
-        <v>20.72596562585361</v>
+        <v>20.72596373482095</v>
       </c>
       <c r="E303" t="n">
-        <v>21.24456175715069</v>
+        <v>21.24455981880144</v>
       </c>
       <c r="F303" t="n">
         <v>669550</v>
@@ -6492,16 +6492,16 @@
         <v>44540</v>
       </c>
       <c r="B304" t="n">
-        <v>21.81680297851562</v>
+        <v>21.81680679321289</v>
       </c>
       <c r="C304" t="n">
-        <v>22.19233818584029</v>
+        <v>22.19234206620039</v>
       </c>
       <c r="D304" t="n">
-        <v>21.06573256386629</v>
+        <v>21.06573624723789</v>
       </c>
       <c r="E304" t="n">
-        <v>22.1386907863425</v>
+        <v>22.13869465732228</v>
       </c>
       <c r="F304" t="n">
         <v>899500</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78104019165039</v>
+        <v>21.78104209899902</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422762443386</v>
+        <v>22.51422959598714</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550495712469</v>
+        <v>21.40550683158799</v>
       </c>
       <c r="E305" t="n">
-        <v>22.13869238990815</v>
+        <v>22.13869432857611</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6572,16 +6572,16 @@
         <v>44546</v>
       </c>
       <c r="B308" t="n">
-        <v>21.94198608398438</v>
+        <v>21.94198417663574</v>
       </c>
       <c r="C308" t="n">
-        <v>22.97917840508309</v>
+        <v>22.97917640757456</v>
       </c>
       <c r="D308" t="n">
-        <v>21.53068473986848</v>
+        <v>21.53068286827299</v>
       </c>
       <c r="E308" t="n">
-        <v>22.5321126906295</v>
+        <v>22.53211073198299</v>
       </c>
       <c r="F308" t="n">
         <v>888550</v>
@@ -6592,16 +6592,16 @@
         <v>44547</v>
       </c>
       <c r="B309" t="n">
-        <v>22.37116813659668</v>
+        <v>22.37116622924805</v>
       </c>
       <c r="C309" t="n">
-        <v>22.72882035710008</v>
+        <v>22.72881841925829</v>
       </c>
       <c r="D309" t="n">
-        <v>21.42338762048728</v>
+        <v>21.42338579394568</v>
       </c>
       <c r="E309" t="n">
-        <v>21.56645021410895</v>
+        <v>21.56644837536995</v>
       </c>
       <c r="F309" t="n">
         <v>2194100</v>
@@ -6612,16 +6612,16 @@
         <v>44550</v>
       </c>
       <c r="B310" t="n">
-        <v>22.01351547241211</v>
+        <v>22.01351356506348</v>
       </c>
       <c r="C310" t="n">
-        <v>22.42481509134622</v>
+        <v>22.42481314836077</v>
       </c>
       <c r="D310" t="n">
-        <v>21.13726541806416</v>
+        <v>21.13726358663772</v>
       </c>
       <c r="E310" t="n">
-        <v>22.35328464868723</v>
+        <v>22.35328271189949</v>
       </c>
       <c r="F310" t="n">
         <v>1565700</v>
@@ -6632,16 +6632,16 @@
         <v>44551</v>
       </c>
       <c r="B311" t="n">
-        <v>21.38762283325195</v>
+        <v>21.38762092590332</v>
       </c>
       <c r="C311" t="n">
-        <v>22.19234074001621</v>
+        <v>22.19233876090282</v>
       </c>
       <c r="D311" t="n">
-        <v>21.38762283325195</v>
+        <v>21.38762092590332</v>
       </c>
       <c r="E311" t="n">
-        <v>22.0313968175793</v>
+        <v>22.0313948528189</v>
       </c>
       <c r="F311" t="n">
         <v>785250</v>
@@ -6652,16 +6652,16 @@
         <v>44552</v>
       </c>
       <c r="B312" t="n">
-        <v>21.45915222167969</v>
+        <v>21.45915603637695</v>
       </c>
       <c r="C312" t="n">
-        <v>21.78104005073934</v>
+        <v>21.78104392265717</v>
       </c>
       <c r="D312" t="n">
-        <v>20.65443435445074</v>
+        <v>20.65443802609692</v>
       </c>
       <c r="E312" t="n">
-        <v>21.42338614937519</v>
+        <v>21.42338995771449</v>
       </c>
       <c r="F312" t="n">
         <v>1154200</v>
@@ -6672,16 +6672,16 @@
         <v>44553</v>
       </c>
       <c r="B313" t="n">
-        <v>21.17614936828613</v>
+        <v>21.1761531829834</v>
       </c>
       <c r="C313" t="n">
-        <v>21.69923988180597</v>
+        <v>21.6992437907334</v>
       </c>
       <c r="D313" t="n">
-        <v>20.79735956744761</v>
+        <v>20.79736331390923</v>
       </c>
       <c r="E313" t="n">
-        <v>21.69923988180597</v>
+        <v>21.6992437907334</v>
       </c>
       <c r="F313" t="n">
         <v>605250</v>
@@ -6692,16 +6692,16 @@
         <v>44557</v>
       </c>
       <c r="B314" t="n">
-        <v>20.92362403869629</v>
+        <v>20.92362594604492</v>
       </c>
       <c r="C314" t="n">
-        <v>21.35652617792996</v>
+        <v>21.35652812474094</v>
       </c>
       <c r="D314" t="n">
-        <v>20.58090855498616</v>
+        <v>20.58091043109365</v>
       </c>
       <c r="E314" t="n">
-        <v>21.08596105075877</v>
+        <v>21.08596297290567</v>
       </c>
       <c r="F314" t="n">
         <v>929800</v>
@@ -6712,16 +6712,16 @@
         <v>44558</v>
       </c>
       <c r="B315" t="n">
-        <v>20.76128959655762</v>
+        <v>20.76128768920898</v>
       </c>
       <c r="C315" t="n">
-        <v>21.2483041737824</v>
+        <v>21.24830222169153</v>
       </c>
       <c r="D315" t="n">
-        <v>20.58091280783701</v>
+        <v>20.58091091705966</v>
       </c>
       <c r="E315" t="n">
-        <v>20.90559033945389</v>
+        <v>20.90558841884829</v>
       </c>
       <c r="F315" t="n">
         <v>793100</v>
@@ -6732,16 +6732,16 @@
         <v>44559</v>
       </c>
       <c r="B316" t="n">
-        <v>20.29231071472168</v>
+        <v>20.29230880737305</v>
       </c>
       <c r="C316" t="n">
-        <v>20.90558971377646</v>
+        <v>20.90558774878349</v>
       </c>
       <c r="D316" t="n">
-        <v>20.05782158448306</v>
+        <v>20.05781969917492</v>
       </c>
       <c r="E316" t="n">
-        <v>20.70717490808197</v>
+        <v>20.70717296173873</v>
       </c>
       <c r="F316" t="n">
         <v>541350</v>
@@ -6752,16 +6752,16 @@
         <v>44560</v>
       </c>
       <c r="B317" t="n">
-        <v>21.06792640686035</v>
+        <v>21.06792449951172</v>
       </c>
       <c r="C317" t="n">
-        <v>21.15811306946891</v>
+        <v>21.15811115395539</v>
       </c>
       <c r="D317" t="n">
-        <v>19.93155691194919</v>
+        <v>19.93155510747982</v>
       </c>
       <c r="E317" t="n">
-        <v>20.2923087229844</v>
+        <v>20.29230688585499</v>
       </c>
       <c r="F317" t="n">
         <v>1399700</v>
@@ -6772,16 +6772,16 @@
         <v>44564</v>
       </c>
       <c r="B318" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C318" t="n">
-        <v>21.32045357690026</v>
+        <v>21.32045154948475</v>
       </c>
       <c r="D318" t="n">
-        <v>19.8774462134759</v>
+        <v>19.87744432327959</v>
       </c>
       <c r="E318" t="n">
-        <v>21.26634123082196</v>
+        <v>21.26633920855213</v>
       </c>
       <c r="F318" t="n">
         <v>905200</v>
@@ -6832,16 +6832,16 @@
         <v>44567</v>
       </c>
       <c r="B321" t="n">
-        <v>17.58666610717773</v>
+        <v>17.58666801452637</v>
       </c>
       <c r="C321" t="n">
-        <v>18.03760626377203</v>
+        <v>18.03760822002704</v>
       </c>
       <c r="D321" t="n">
-        <v>16.86516254470693</v>
+        <v>16.86516437380543</v>
       </c>
       <c r="E321" t="n">
-        <v>18.03760626377203</v>
+        <v>18.03760822002704</v>
       </c>
       <c r="F321" t="n">
         <v>2077850</v>
@@ -6872,16 +6872,16 @@
         <v>44571</v>
       </c>
       <c r="B323" t="n">
-        <v>16.36010932922363</v>
+        <v>16.36011123657227</v>
       </c>
       <c r="C323" t="n">
-        <v>17.13572699636531</v>
+        <v>17.13572899413958</v>
       </c>
       <c r="D323" t="n">
-        <v>16.10758392704749</v>
+        <v>16.10758580495536</v>
       </c>
       <c r="E323" t="n">
-        <v>17.11768897615265</v>
+        <v>17.11769097182395</v>
       </c>
       <c r="F323" t="n">
         <v>1820150</v>
@@ -6952,16 +6952,16 @@
         <v>44575</v>
       </c>
       <c r="B327" t="n">
-        <v>17.00946617126465</v>
+        <v>17.00946426391602</v>
       </c>
       <c r="C327" t="n">
-        <v>17.02750247326626</v>
+        <v>17.02750056389514</v>
       </c>
       <c r="D327" t="n">
-        <v>16.17973607217368</v>
+        <v>16.17973425786645</v>
       </c>
       <c r="E327" t="n">
-        <v>16.55852593741522</v>
+        <v>16.55852408063256</v>
       </c>
       <c r="F327" t="n">
         <v>789200</v>
@@ -6972,16 +6972,16 @@
         <v>44578</v>
       </c>
       <c r="B328" t="n">
-        <v>16.88320159912109</v>
+        <v>16.88319969177246</v>
       </c>
       <c r="C328" t="n">
-        <v>17.11769072524505</v>
+        <v>17.11768879140545</v>
       </c>
       <c r="D328" t="n">
-        <v>16.6306761711418</v>
+        <v>16.63067429232176</v>
       </c>
       <c r="E328" t="n">
-        <v>16.86516529726576</v>
+        <v>16.86516339195475</v>
       </c>
       <c r="F328" t="n">
         <v>496050</v>
@@ -7012,16 +7012,16 @@
         <v>44580</v>
       </c>
       <c r="B330" t="n">
-        <v>16.41422462463379</v>
+        <v>16.41422271728516</v>
       </c>
       <c r="C330" t="n">
-        <v>16.72086411051511</v>
+        <v>16.72086216753467</v>
       </c>
       <c r="D330" t="n">
-        <v>16.19777180619957</v>
+        <v>16.19776992400296</v>
       </c>
       <c r="E330" t="n">
-        <v>16.41422462463379</v>
+        <v>16.41422271728516</v>
       </c>
       <c r="F330" t="n">
         <v>847250</v>
@@ -7092,16 +7092,16 @@
         <v>44586</v>
       </c>
       <c r="B334" t="n">
-        <v>18.72303581237793</v>
+        <v>18.72303771972656</v>
       </c>
       <c r="C334" t="n">
-        <v>18.75911013098741</v>
+        <v>18.759112042011</v>
       </c>
       <c r="D334" t="n">
-        <v>17.65881675029495</v>
+        <v>17.65881854922971</v>
       </c>
       <c r="E334" t="n">
-        <v>17.71292908830928</v>
+        <v>17.71293089275656</v>
       </c>
       <c r="F334" t="n">
         <v>1122500</v>
@@ -7112,16 +7112,16 @@
         <v>44587</v>
       </c>
       <c r="B335" t="n">
-        <v>19.3543529510498</v>
+        <v>19.35435485839844</v>
       </c>
       <c r="C335" t="n">
-        <v>19.80529316020046</v>
+        <v>19.80529511198872</v>
       </c>
       <c r="D335" t="n">
-        <v>18.84930039845718</v>
+        <v>18.84930225603348</v>
       </c>
       <c r="E335" t="n">
-        <v>18.92145076311327</v>
+        <v>18.9214526277999</v>
       </c>
       <c r="F335" t="n">
         <v>1494250</v>
@@ -7132,16 +7132,16 @@
         <v>44588</v>
       </c>
       <c r="B336" t="n">
-        <v>19.33631706237793</v>
+        <v>19.3363151550293</v>
       </c>
       <c r="C336" t="n">
-        <v>19.91351999193534</v>
+        <v>19.91351802765098</v>
       </c>
       <c r="D336" t="n">
-        <v>19.08378992059635</v>
+        <v>19.08378803815718</v>
       </c>
       <c r="E336" t="n">
-        <v>19.64295654875541</v>
+        <v>19.64295461115963</v>
       </c>
       <c r="F336" t="n">
         <v>815000</v>
@@ -7152,16 +7152,16 @@
         <v>44589</v>
       </c>
       <c r="B337" t="n">
-        <v>19.67902946472168</v>
+        <v>19.67903137207031</v>
       </c>
       <c r="C337" t="n">
-        <v>19.67902946472168</v>
+        <v>19.67903137207031</v>
       </c>
       <c r="D337" t="n">
-        <v>18.84929945270756</v>
+        <v>18.84930127963634</v>
       </c>
       <c r="E337" t="n">
-        <v>19.30023963923261</v>
+        <v>19.30024150986784</v>
       </c>
       <c r="F337" t="n">
         <v>645650</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96762847900391</v>
+        <v>19.96763038635254</v>
       </c>
       <c r="C338" t="n">
-        <v>20.274267906142</v>
+        <v>20.27426984278146</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44453799509775</v>
+        <v>19.44453985247972</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706508809386</v>
+        <v>19.69706696959773</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7192,16 +7192,16 @@
         <v>44593</v>
       </c>
       <c r="B339" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C339" t="n">
-        <v>20.38249879067443</v>
+        <v>20.38249685245139</v>
       </c>
       <c r="D339" t="n">
-        <v>19.75118177902592</v>
+        <v>19.75117990083641</v>
       </c>
       <c r="E339" t="n">
-        <v>20.29231040041029</v>
+        <v>20.29230847076349</v>
       </c>
       <c r="F339" t="n">
         <v>629350</v>
@@ -7212,16 +7212,16 @@
         <v>44594</v>
       </c>
       <c r="B340" t="n">
-        <v>20.22015762329102</v>
+        <v>20.22015953063965</v>
       </c>
       <c r="C340" t="n">
-        <v>20.86951085947065</v>
+        <v>20.86951282807217</v>
       </c>
       <c r="D340" t="n">
-        <v>19.85940582541344</v>
+        <v>19.85940769873269</v>
       </c>
       <c r="E340" t="n">
-        <v>20.25623194297864</v>
+        <v>20.25623385373013</v>
       </c>
       <c r="F340" t="n">
         <v>1270900</v>
@@ -7232,16 +7232,16 @@
         <v>44595</v>
       </c>
       <c r="B341" t="n">
-        <v>20.12996864318848</v>
+        <v>20.12997055053711</v>
       </c>
       <c r="C341" t="n">
-        <v>20.67109718396025</v>
+        <v>20.67109914258173</v>
       </c>
       <c r="D341" t="n">
-        <v>19.93155559032558</v>
+        <v>19.93155747887424</v>
       </c>
       <c r="E341" t="n">
-        <v>20.43660809228581</v>
+        <v>20.43661002868905</v>
       </c>
       <c r="F341" t="n">
         <v>747450</v>
@@ -7252,16 +7252,16 @@
         <v>44596</v>
       </c>
       <c r="B342" t="n">
-        <v>19.40846633911133</v>
+        <v>19.40846824645996</v>
       </c>
       <c r="C342" t="n">
-        <v>20.18408230211611</v>
+        <v>20.18408428568767</v>
       </c>
       <c r="D342" t="n">
-        <v>19.26416561482205</v>
+        <v>19.26416750798967</v>
       </c>
       <c r="E342" t="n">
-        <v>20.18408230211611</v>
+        <v>20.18408428568767</v>
       </c>
       <c r="F342" t="n">
         <v>774000</v>
@@ -7272,16 +7272,16 @@
         <v>44599</v>
       </c>
       <c r="B343" t="n">
-        <v>19.7331428527832</v>
+        <v>19.73314476013184</v>
       </c>
       <c r="C343" t="n">
-        <v>19.94959566757971</v>
+        <v>19.94959759585004</v>
       </c>
       <c r="D343" t="n">
-        <v>19.06575154772842</v>
+        <v>19.06575339056894</v>
       </c>
       <c r="E343" t="n">
-        <v>19.31827868485741</v>
+        <v>19.31828055210647</v>
       </c>
       <c r="F343" t="n">
         <v>708000</v>
@@ -7332,16 +7332,16 @@
         <v>44602</v>
       </c>
       <c r="B346" t="n">
-        <v>19.98567008972168</v>
+        <v>19.98566818237305</v>
       </c>
       <c r="C346" t="n">
-        <v>20.59894905424028</v>
+        <v>20.59894708836287</v>
       </c>
       <c r="D346" t="n">
-        <v>19.82333133791377</v>
+        <v>19.82332944605806</v>
       </c>
       <c r="E346" t="n">
-        <v>20.18408316404224</v>
+        <v>20.18408123775789</v>
       </c>
       <c r="F346" t="n">
         <v>563100</v>
@@ -7372,16 +7372,16 @@
         <v>44606</v>
       </c>
       <c r="B348" t="n">
-        <v>20.00370788574219</v>
+        <v>20.00370597839355</v>
       </c>
       <c r="C348" t="n">
-        <v>20.14800861456807</v>
+        <v>20.1480066934604</v>
       </c>
       <c r="D348" t="n">
-        <v>19.26416622045944</v>
+        <v>19.26416438362593</v>
       </c>
       <c r="E348" t="n">
-        <v>19.26416622045944</v>
+        <v>19.26416438362593</v>
       </c>
       <c r="F348" t="n">
         <v>683300</v>
@@ -7392,16 +7392,16 @@
         <v>44607</v>
       </c>
       <c r="B349" t="n">
-        <v>20.52680015563965</v>
+        <v>20.52679824829102</v>
       </c>
       <c r="C349" t="n">
-        <v>20.70717522149135</v>
+        <v>20.70717329738229</v>
       </c>
       <c r="D349" t="n">
-        <v>20.11193423579974</v>
+        <v>20.11193236700041</v>
       </c>
       <c r="E349" t="n">
-        <v>20.20212262882585</v>
+        <v>20.20212075164623</v>
       </c>
       <c r="F349" t="n">
         <v>560950</v>
@@ -7412,16 +7412,16 @@
         <v>44608</v>
       </c>
       <c r="B350" t="n">
-        <v>20.74324798583984</v>
+        <v>20.74324989318848</v>
       </c>
       <c r="C350" t="n">
-        <v>20.76128600563211</v>
+        <v>20.76128791463935</v>
       </c>
       <c r="D350" t="n">
-        <v>20.27426979244236</v>
+        <v>20.27427165666829</v>
       </c>
       <c r="E350" t="n">
-        <v>20.74324798583984</v>
+        <v>20.74324989318848</v>
       </c>
       <c r="F350" t="n">
         <v>576900</v>
@@ -7432,16 +7432,16 @@
         <v>44609</v>
       </c>
       <c r="B351" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="C351" t="n">
-        <v>20.72521260943759</v>
+        <v>20.72521063862504</v>
       </c>
       <c r="D351" t="n">
-        <v>20.05782127380371</v>
+        <v>20.05781936645508</v>
       </c>
       <c r="E351" t="n">
-        <v>20.72521260943759</v>
+        <v>20.72521063862504</v>
       </c>
       <c r="F351" t="n">
         <v>544250</v>
@@ -7472,16 +7472,16 @@
         <v>44613</v>
       </c>
       <c r="B353" t="n">
-        <v>18.66892242431641</v>
+        <v>18.66892623901367</v>
       </c>
       <c r="C353" t="n">
-        <v>19.94959248662468</v>
+        <v>19.9495965630065</v>
       </c>
       <c r="D353" t="n">
-        <v>18.66892242431641</v>
+        <v>18.66892623901367</v>
       </c>
       <c r="E353" t="n">
-        <v>19.85940411487337</v>
+        <v>19.85940817282663</v>
       </c>
       <c r="F353" t="n">
         <v>728950</v>
@@ -7492,16 +7492,16 @@
         <v>44614</v>
       </c>
       <c r="B354" t="n">
-        <v>19.69706726074219</v>
+        <v>19.69706916809082</v>
       </c>
       <c r="C354" t="n">
-        <v>19.80529194096369</v>
+        <v>19.80529385879217</v>
       </c>
       <c r="D354" t="n">
-        <v>18.9935999585013</v>
+        <v>18.99360179773027</v>
       </c>
       <c r="E354" t="n">
-        <v>19.0837883388194</v>
+        <v>19.08379018678169</v>
       </c>
       <c r="F354" t="n">
         <v>1292450</v>
@@ -7532,16 +7532,16 @@
         <v>44616</v>
       </c>
       <c r="B356" t="n">
-        <v>19.33631706237793</v>
+        <v>19.3363151550293</v>
       </c>
       <c r="C356" t="n">
-        <v>19.42650545017138</v>
+        <v>19.4265035339265</v>
       </c>
       <c r="D356" t="n">
-        <v>18.27209787085614</v>
+        <v>18.27209606848287</v>
       </c>
       <c r="E356" t="n">
-        <v>18.52462501263771</v>
+        <v>18.52462318535499</v>
       </c>
       <c r="F356" t="n">
         <v>1831750</v>
@@ -7552,16 +7552,16 @@
         <v>44617</v>
       </c>
       <c r="B357" t="n">
-        <v>19.02967643737793</v>
+        <v>19.0296745300293</v>
       </c>
       <c r="C357" t="n">
-        <v>19.62491735291844</v>
+        <v>19.62491538590869</v>
       </c>
       <c r="D357" t="n">
-        <v>18.6508866074703</v>
+        <v>18.65088473808786</v>
       </c>
       <c r="E357" t="n">
-        <v>19.28220184384947</v>
+        <v>19.28219991119016</v>
       </c>
       <c r="F357" t="n">
         <v>1262850</v>
@@ -7572,16 +7572,16 @@
         <v>44622</v>
       </c>
       <c r="B358" t="n">
-        <v>18.83126068115234</v>
+        <v>18.83126449584961</v>
       </c>
       <c r="C358" t="n">
-        <v>18.90341103931001</v>
+        <v>18.90341486862296</v>
       </c>
       <c r="D358" t="n">
-        <v>18.23601979630157</v>
+        <v>18.23602349041934</v>
       </c>
       <c r="E358" t="n">
-        <v>18.74107402360544</v>
+        <v>18.74107782003336</v>
       </c>
       <c r="F358" t="n">
         <v>1044650</v>
@@ -7592,16 +7592,16 @@
         <v>44623</v>
       </c>
       <c r="B359" t="n">
-        <v>18.5787353515625</v>
+        <v>18.57873725891113</v>
       </c>
       <c r="C359" t="n">
-        <v>19.46257767208202</v>
+        <v>19.46257967016855</v>
       </c>
       <c r="D359" t="n">
-        <v>18.54265931225955</v>
+        <v>18.54266121590451</v>
       </c>
       <c r="E359" t="n">
-        <v>18.72303606837384</v>
+        <v>18.72303799053682</v>
       </c>
       <c r="F359" t="n">
         <v>930450</v>
@@ -7612,16 +7612,16 @@
         <v>44624</v>
       </c>
       <c r="B360" t="n">
-        <v>17.91134452819824</v>
+        <v>17.91134262084961</v>
       </c>
       <c r="C360" t="n">
-        <v>18.75911082938567</v>
+        <v>18.75910883175985</v>
       </c>
       <c r="D360" t="n">
-        <v>17.55059100747137</v>
+        <v>17.55058913853877</v>
       </c>
       <c r="E360" t="n">
-        <v>18.57873578922251</v>
+        <v>18.57873381080452</v>
       </c>
       <c r="F360" t="n">
         <v>1669200</v>
@@ -7652,16 +7652,16 @@
         <v>44628</v>
       </c>
       <c r="B362" t="n">
-        <v>17.38825416564941</v>
+        <v>17.38825607299805</v>
       </c>
       <c r="C362" t="n">
-        <v>17.58666722792311</v>
+        <v>17.58666915703602</v>
       </c>
       <c r="D362" t="n">
-        <v>16.54048613557037</v>
+        <v>16.54048794992582</v>
       </c>
       <c r="E362" t="n">
-        <v>16.84712559921172</v>
+        <v>16.847127447203</v>
       </c>
       <c r="F362" t="n">
         <v>1040800</v>
@@ -7732,16 +7732,16 @@
         <v>44634</v>
       </c>
       <c r="B366" t="n">
-        <v>17.31610488891602</v>
+        <v>17.31610298156738</v>
       </c>
       <c r="C366" t="n">
-        <v>17.67685671572668</v>
+        <v>17.67685476864166</v>
       </c>
       <c r="D366" t="n">
-        <v>16.88320097654281</v>
+        <v>16.88319911687804</v>
       </c>
       <c r="E366" t="n">
-        <v>17.35217921149688</v>
+        <v>17.35217730017471</v>
       </c>
       <c r="F366" t="n">
         <v>989600</v>
@@ -7752,16 +7752,16 @@
         <v>44635</v>
       </c>
       <c r="B367" t="n">
-        <v>17.46040725708008</v>
+        <v>17.46040534973145</v>
       </c>
       <c r="C367" t="n">
-        <v>17.56863195517241</v>
+        <v>17.56863003600147</v>
       </c>
       <c r="D367" t="n">
-        <v>16.93731662909899</v>
+        <v>16.93731477889199</v>
       </c>
       <c r="E367" t="n">
-        <v>17.04554132719132</v>
+        <v>17.04553946516202</v>
       </c>
       <c r="F367" t="n">
         <v>763850</v>
@@ -7832,16 +7832,16 @@
         <v>44641</v>
       </c>
       <c r="B371" t="n">
-        <v>18.56069755554199</v>
+        <v>18.56069946289062</v>
       </c>
       <c r="C371" t="n">
-        <v>18.86733701251073</v>
+        <v>18.86733895137048</v>
       </c>
       <c r="D371" t="n">
-        <v>18.23602007870444</v>
+        <v>18.23602195268832</v>
       </c>
       <c r="E371" t="n">
-        <v>18.65088593468579</v>
+        <v>18.65088785130242</v>
       </c>
       <c r="F371" t="n">
         <v>689900</v>
@@ -7852,16 +7852,16 @@
         <v>44642</v>
       </c>
       <c r="B372" t="n">
-        <v>19.40846633911133</v>
+        <v>19.40846824645996</v>
       </c>
       <c r="C372" t="n">
-        <v>19.46257868066973</v>
+        <v>19.4625805933362</v>
       </c>
       <c r="D372" t="n">
-        <v>18.68696099746462</v>
+        <v>18.686962833908</v>
       </c>
       <c r="E372" t="n">
-        <v>18.70499901805086</v>
+        <v>18.70500085626691</v>
       </c>
       <c r="F372" t="n">
         <v>868000</v>
@@ -7872,16 +7872,16 @@
         <v>44643</v>
       </c>
       <c r="B373" t="n">
-        <v>19.60687828063965</v>
+        <v>19.60688018798828</v>
       </c>
       <c r="C373" t="n">
-        <v>19.8052913351097</v>
+        <v>19.80529326175987</v>
       </c>
       <c r="D373" t="n">
-        <v>18.92144901947007</v>
+        <v>18.92145086014044</v>
       </c>
       <c r="E373" t="n">
-        <v>19.48061558417691</v>
+        <v>19.48061747924276</v>
       </c>
       <c r="F373" t="n">
         <v>823600</v>
@@ -7892,16 +7892,16 @@
         <v>44644</v>
       </c>
       <c r="B374" t="n">
-        <v>20.79736137390137</v>
+        <v>20.79736328125</v>
       </c>
       <c r="C374" t="n">
-        <v>20.79736137390137</v>
+        <v>20.79736328125</v>
       </c>
       <c r="D374" t="n">
-        <v>19.49865484696414</v>
+        <v>19.49865663520698</v>
       </c>
       <c r="E374" t="n">
-        <v>19.71510593478701</v>
+        <v>19.71510774288082</v>
       </c>
       <c r="F374" t="n">
         <v>1624000</v>
@@ -7952,16 +7952,16 @@
         <v>44649</v>
       </c>
       <c r="B377" t="n">
-        <v>21.91569328308105</v>
+        <v>21.91569519042969</v>
       </c>
       <c r="C377" t="n">
-        <v>22.36663348824898</v>
+        <v>22.36663543484347</v>
       </c>
       <c r="D377" t="n">
-        <v>21.66316786911525</v>
+        <v>21.6631697544863</v>
       </c>
       <c r="E377" t="n">
-        <v>21.66316786911525</v>
+        <v>21.6631697544863</v>
       </c>
       <c r="F377" t="n">
         <v>1103500</v>
@@ -7972,16 +7972,16 @@
         <v>44650</v>
       </c>
       <c r="B378" t="n">
-        <v>21.4106388092041</v>
+        <v>21.41064071655273</v>
       </c>
       <c r="C378" t="n">
-        <v>22.02391770830417</v>
+        <v>22.02391967028623</v>
       </c>
       <c r="D378" t="n">
-        <v>21.28437611357769</v>
+        <v>21.28437800967832</v>
       </c>
       <c r="E378" t="n">
-        <v>21.93372933134236</v>
+        <v>21.93373128529007</v>
       </c>
       <c r="F378" t="n">
         <v>851150</v>
@@ -7992,16 +7992,16 @@
         <v>44651</v>
       </c>
       <c r="B379" t="n">
-        <v>21.17614936828613</v>
+        <v>21.1761531829834</v>
       </c>
       <c r="C379" t="n">
-        <v>21.77139023814663</v>
+        <v>21.77139416007131</v>
       </c>
       <c r="D379" t="n">
-        <v>21.04988667474002</v>
+        <v>21.04989046669217</v>
       </c>
       <c r="E379" t="n">
-        <v>21.6090515063301</v>
+        <v>21.60905539901088</v>
       </c>
       <c r="F379" t="n">
         <v>849150</v>
@@ -8032,16 +8032,16 @@
         <v>44655</v>
       </c>
       <c r="B381" t="n">
-        <v>21.89765739440918</v>
+        <v>21.89765548706055</v>
       </c>
       <c r="C381" t="n">
-        <v>21.91569369560312</v>
+        <v>21.91569178668347</v>
       </c>
       <c r="D381" t="n">
-        <v>21.32045275119318</v>
+        <v>21.32045089412073</v>
       </c>
       <c r="E381" t="n">
-        <v>21.78943098624356</v>
+        <v>21.78942908832175</v>
       </c>
       <c r="F381" t="n">
         <v>503500</v>
@@ -8052,16 +8052,16 @@
         <v>44656</v>
       </c>
       <c r="B382" t="n">
-        <v>20.7071704864502</v>
+        <v>20.70717430114746</v>
       </c>
       <c r="C382" t="n">
-        <v>21.87961588728935</v>
+        <v>21.87961991797578</v>
       </c>
       <c r="D382" t="n">
-        <v>20.59894581572666</v>
+        <v>20.59894961048666</v>
       </c>
       <c r="E382" t="n">
-        <v>21.78942751488632</v>
+        <v>21.78943152895814</v>
       </c>
       <c r="F382" t="n">
         <v>1118400</v>
@@ -8072,16 +8072,16 @@
         <v>44657</v>
       </c>
       <c r="B383" t="n">
-        <v>20.0217456817627</v>
+        <v>20.02174377441406</v>
       </c>
       <c r="C383" t="n">
-        <v>20.58091056962541</v>
+        <v>20.58090860900858</v>
       </c>
       <c r="D383" t="n">
-        <v>19.58884177995242</v>
+        <v>19.58883991384388</v>
       </c>
       <c r="E383" t="n">
-        <v>20.58091056962541</v>
+        <v>20.58090860900858</v>
       </c>
       <c r="F383" t="n">
         <v>1237700</v>
@@ -8152,16 +8152,16 @@
         <v>44663</v>
       </c>
       <c r="B387" t="n">
-        <v>19.13789939880371</v>
+        <v>19.13790130615234</v>
       </c>
       <c r="C387" t="n">
-        <v>19.84136665398996</v>
+        <v>19.84136863144855</v>
       </c>
       <c r="D387" t="n">
-        <v>18.99359868802707</v>
+        <v>18.9936005809942</v>
       </c>
       <c r="E387" t="n">
-        <v>19.33631416627171</v>
+        <v>19.33631609339504</v>
       </c>
       <c r="F387" t="n">
         <v>1155250</v>
@@ -8192,16 +8192,16 @@
         <v>44665</v>
       </c>
       <c r="B389" t="n">
-        <v>19.57080459594727</v>
+        <v>19.5708065032959</v>
       </c>
       <c r="C389" t="n">
-        <v>19.67902927636525</v>
+        <v>19.67903119426134</v>
       </c>
       <c r="D389" t="n">
-        <v>19.01163801312008</v>
+        <v>19.01163986597297</v>
       </c>
       <c r="E389" t="n">
-        <v>19.17397675394734</v>
+        <v>19.17397862262157</v>
       </c>
       <c r="F389" t="n">
         <v>760550</v>
@@ -8212,16 +8212,16 @@
         <v>44669</v>
       </c>
       <c r="B390" t="n">
-        <v>19.55276870727539</v>
+        <v>19.55276679992676</v>
       </c>
       <c r="C390" t="n">
-        <v>20.0037089386417</v>
+        <v>20.0037069873044</v>
       </c>
       <c r="D390" t="n">
-        <v>19.49865636116756</v>
+        <v>19.49865445909752</v>
       </c>
       <c r="E390" t="n">
-        <v>19.67903142159381</v>
+        <v>19.6790295019284</v>
       </c>
       <c r="F390" t="n">
         <v>1023750</v>
@@ -8252,16 +8252,16 @@
         <v>44671</v>
       </c>
       <c r="B392" t="n">
-        <v>20.61698722839355</v>
+        <v>20.61698532104492</v>
       </c>
       <c r="C392" t="n">
-        <v>20.79736228269439</v>
+        <v>20.79736035865864</v>
       </c>
       <c r="D392" t="n">
-        <v>20.11193294787024</v>
+        <v>20.11193108724592</v>
       </c>
       <c r="E392" t="n">
-        <v>20.34642206664169</v>
+        <v>20.34642018432397</v>
       </c>
       <c r="F392" t="n">
         <v>1230400</v>
@@ -8272,16 +8272,16 @@
         <v>44673</v>
       </c>
       <c r="B393" t="n">
-        <v>19.55276870727539</v>
+        <v>19.55276679992676</v>
       </c>
       <c r="C393" t="n">
-        <v>20.49072349401308</v>
+        <v>20.4907214951681</v>
       </c>
       <c r="D393" t="n">
-        <v>19.35435390454591</v>
+        <v>19.3543520165524</v>
       </c>
       <c r="E393" t="n">
-        <v>20.09389732895506</v>
+        <v>20.09389536881999</v>
       </c>
       <c r="F393" t="n">
         <v>931750</v>
@@ -8292,16 +8292,16 @@
         <v>44676</v>
       </c>
       <c r="B394" t="n">
-        <v>19.30024147033691</v>
+        <v>19.30023956298828</v>
       </c>
       <c r="C394" t="n">
-        <v>19.57080664004192</v>
+        <v>19.57080470595465</v>
       </c>
       <c r="D394" t="n">
-        <v>18.61481211536489</v>
+        <v>18.61481027575389</v>
       </c>
       <c r="E394" t="n">
-        <v>19.28220344831649</v>
+        <v>19.28220154275046</v>
       </c>
       <c r="F394" t="n">
         <v>1378800</v>
@@ -8312,16 +8312,16 @@
         <v>44677</v>
       </c>
       <c r="B395" t="n">
-        <v>19.06575202941895</v>
+        <v>19.06575012207031</v>
       </c>
       <c r="C395" t="n">
-        <v>19.39042953961619</v>
+        <v>19.39042759978664</v>
       </c>
       <c r="D395" t="n">
-        <v>18.68696217425563</v>
+        <v>18.68696030480135</v>
       </c>
       <c r="E395" t="n">
-        <v>19.19201646127367</v>
+        <v>19.19201454129347</v>
       </c>
       <c r="F395" t="n">
         <v>972150</v>
@@ -8332,16 +8332,16 @@
         <v>44678</v>
       </c>
       <c r="B396" t="n">
-        <v>19.49865531921387</v>
+        <v>19.49865341186523</v>
       </c>
       <c r="C396" t="n">
-        <v>19.55276766243008</v>
+        <v>19.55276574978821</v>
       </c>
       <c r="D396" t="n">
-        <v>19.10182745516075</v>
+        <v>19.10182558662962</v>
       </c>
       <c r="E396" t="n">
-        <v>19.46257927693614</v>
+        <v>19.46257737311645</v>
       </c>
       <c r="F396" t="n">
         <v>619300</v>
@@ -8352,16 +8352,16 @@
         <v>44679</v>
       </c>
       <c r="B397" t="n">
-        <v>21.04988861083984</v>
+        <v>21.04988670349121</v>
       </c>
       <c r="C397" t="n">
-        <v>21.10400095302237</v>
+        <v>21.10399904077057</v>
       </c>
       <c r="D397" t="n">
-        <v>19.30024015840165</v>
+        <v>19.30023840959018</v>
       </c>
       <c r="E397" t="n">
-        <v>19.84136874082794</v>
+        <v>19.84136694298433</v>
       </c>
       <c r="F397" t="n">
         <v>1501350</v>
@@ -8372,16 +8372,16 @@
         <v>44680</v>
       </c>
       <c r="B398" t="n">
-        <v>21.04988861083984</v>
+        <v>21.04988670349121</v>
       </c>
       <c r="C398" t="n">
-        <v>21.60905349386008</v>
+        <v>21.60905153584503</v>
       </c>
       <c r="D398" t="n">
-        <v>20.90558788488621</v>
+        <v>20.90558599061279</v>
       </c>
       <c r="E398" t="n">
-        <v>21.60905349386008</v>
+        <v>21.60905153584503</v>
       </c>
       <c r="F398" t="n">
         <v>1651000</v>
@@ -8412,16 +8412,16 @@
         <v>44684</v>
       </c>
       <c r="B400" t="n">
-        <v>19.84136772155762</v>
+        <v>19.84136962890625</v>
       </c>
       <c r="C400" t="n">
-        <v>20.63502167353181</v>
+        <v>20.63502365717432</v>
       </c>
       <c r="D400" t="n">
-        <v>19.75117934241958</v>
+        <v>19.75118124109841</v>
       </c>
       <c r="E400" t="n">
-        <v>20.47268465532364</v>
+        <v>20.4726866233607</v>
       </c>
       <c r="F400" t="n">
         <v>1374100</v>
@@ -8432,16 +8432,16 @@
         <v>44685</v>
       </c>
       <c r="B401" t="n">
-        <v>20.47268486022949</v>
+        <v>20.47268676757812</v>
       </c>
       <c r="C401" t="n">
-        <v>20.56287152006993</v>
+        <v>20.56287343582085</v>
       </c>
       <c r="D401" t="n">
-        <v>19.17397666016394</v>
+        <v>19.17397844651773</v>
       </c>
       <c r="E401" t="n">
-        <v>19.84136792014478</v>
+        <v>19.84136976867643</v>
       </c>
       <c r="F401" t="n">
         <v>1413100</v>
@@ -8452,16 +8452,16 @@
         <v>44686</v>
       </c>
       <c r="B402" t="n">
-        <v>20.09389495849609</v>
+        <v>20.09389305114746</v>
       </c>
       <c r="C402" t="n">
-        <v>20.47268477696631</v>
+        <v>20.47268283366227</v>
       </c>
       <c r="D402" t="n">
-        <v>19.73314143980044</v>
+        <v>19.73313956669518</v>
       </c>
       <c r="E402" t="n">
-        <v>20.41857071704181</v>
+        <v>20.41856877887437</v>
       </c>
       <c r="F402" t="n">
         <v>1134600</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.51902961730957</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C403" t="n">
-        <v>19.93473065890365</v>
+        <v>19.93473455484336</v>
       </c>
       <c r="D403" t="n">
-        <v>18.81989711218194</v>
+        <v>18.8199007902444</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019330479591</v>
+        <v>19.67019714903581</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8492,16 +8492,16 @@
         <v>44690</v>
       </c>
       <c r="B404" t="n">
-        <v>18.7821102142334</v>
+        <v>18.78210830688477</v>
       </c>
       <c r="C404" t="n">
-        <v>19.53793065186498</v>
+        <v>19.53792866776176</v>
       </c>
       <c r="D404" t="n">
-        <v>18.38530498003061</v>
+        <v>18.38530311297808</v>
       </c>
       <c r="E404" t="n">
-        <v>19.25449731199797</v>
+        <v>19.25449535667779</v>
       </c>
       <c r="F404" t="n">
         <v>2367350</v>
@@ -8532,16 +8532,16 @@
         <v>44692</v>
       </c>
       <c r="B406" t="n">
-        <v>19.10333251953125</v>
+        <v>19.10333061218262</v>
       </c>
       <c r="C406" t="n">
-        <v>19.57571959095203</v>
+        <v>19.57571763643849</v>
       </c>
       <c r="D406" t="n">
-        <v>18.93327468751125</v>
+        <v>18.93327279714184</v>
       </c>
       <c r="E406" t="n">
-        <v>19.14112435021147</v>
+        <v>19.14112243908956</v>
       </c>
       <c r="F406" t="n">
         <v>1048200</v>
@@ -8552,16 +8552,16 @@
         <v>44693</v>
       </c>
       <c r="B407" t="n">
-        <v>19.33007621765137</v>
+        <v>19.330078125</v>
       </c>
       <c r="C407" t="n">
-        <v>19.7079872796457</v>
+        <v>19.70798922428379</v>
       </c>
       <c r="D407" t="n">
-        <v>18.81989916718061</v>
+        <v>18.81990102418875</v>
       </c>
       <c r="E407" t="n">
-        <v>18.93327284618161</v>
+        <v>18.93327471437663</v>
       </c>
       <c r="F407" t="n">
         <v>1412250</v>
@@ -8632,16 +8632,16 @@
         <v>44699</v>
       </c>
       <c r="B411" t="n">
-        <v>20.36932563781738</v>
+        <v>20.36932754516602</v>
       </c>
       <c r="C411" t="n">
-        <v>20.76613076461962</v>
+        <v>20.76613270912441</v>
       </c>
       <c r="D411" t="n">
-        <v>20.10479008795808</v>
+        <v>20.10479197053606</v>
       </c>
       <c r="E411" t="n">
-        <v>20.44490748092194</v>
+        <v>20.44490939534792</v>
       </c>
       <c r="F411" t="n">
         <v>1338150</v>
@@ -8672,16 +8672,16 @@
         <v>44701</v>
       </c>
       <c r="B413" t="n">
-        <v>20.65276336669922</v>
+        <v>20.65276145935059</v>
       </c>
       <c r="C413" t="n">
-        <v>21.08735860801926</v>
+        <v>21.08735666053437</v>
       </c>
       <c r="D413" t="n">
-        <v>20.25595815409612</v>
+        <v>20.25595628339371</v>
       </c>
       <c r="E413" t="n">
-        <v>21.03067266393701</v>
+        <v>21.03067072168725</v>
       </c>
       <c r="F413" t="n">
         <v>1756800</v>
@@ -8772,16 +8772,16 @@
         <v>44708</v>
       </c>
       <c r="B418" t="n">
-        <v>22.78795051574707</v>
+        <v>22.7879524230957</v>
       </c>
       <c r="C418" t="n">
-        <v>22.86353236646209</v>
+        <v>22.86353428013691</v>
       </c>
       <c r="D418" t="n">
-        <v>21.35189355014821</v>
+        <v>21.35189533729906</v>
       </c>
       <c r="E418" t="n">
-        <v>21.59753501547539</v>
+        <v>21.5975368231864</v>
       </c>
       <c r="F418" t="n">
         <v>2973300</v>
@@ -8792,16 +8792,16 @@
         <v>44711</v>
       </c>
       <c r="B419" t="n">
-        <v>22.14550590515137</v>
+        <v>22.14550399780273</v>
       </c>
       <c r="C419" t="n">
-        <v>23.22254782665845</v>
+        <v>23.22254582654633</v>
       </c>
       <c r="D419" t="n">
-        <v>22.14550590515137</v>
+        <v>22.14550399780273</v>
       </c>
       <c r="E419" t="n">
-        <v>22.97690633890859</v>
+        <v>22.97690435995308</v>
       </c>
       <c r="F419" t="n">
         <v>1234700</v>
@@ -8852,16 +8852,16 @@
         <v>44714</v>
       </c>
       <c r="B422" t="n">
-        <v>23.37371063232422</v>
+        <v>23.37370872497559</v>
       </c>
       <c r="C422" t="n">
-        <v>24.31848471674483</v>
+        <v>24.31848273230045</v>
       </c>
       <c r="D422" t="n">
-        <v>23.24144283714967</v>
+        <v>23.24144094059439</v>
       </c>
       <c r="E422" t="n">
-        <v>23.43039657282566</v>
+        <v>23.43039466085132</v>
       </c>
       <c r="F422" t="n">
         <v>1968350</v>
@@ -8892,16 +8892,16 @@
         <v>44718</v>
       </c>
       <c r="B424" t="n">
-        <v>22.03212928771973</v>
+        <v>22.03213119506836</v>
       </c>
       <c r="C424" t="n">
-        <v>22.63678406822239</v>
+        <v>22.63678602791673</v>
       </c>
       <c r="D424" t="n">
-        <v>21.52195226717395</v>
+        <v>21.52195413035593</v>
       </c>
       <c r="E424" t="n">
-        <v>22.52341219788483</v>
+        <v>22.52341414776443</v>
       </c>
       <c r="F424" t="n">
         <v>1535250</v>
@@ -8912,16 +8912,16 @@
         <v>44719</v>
       </c>
       <c r="B425" t="n">
-        <v>21.59753608703613</v>
+        <v>21.5975341796875</v>
       </c>
       <c r="C425" t="n">
-        <v>21.93765353112191</v>
+        <v>21.93765159373639</v>
       </c>
       <c r="D425" t="n">
-        <v>21.25741684093681</v>
+        <v>21.25741496362521</v>
       </c>
       <c r="E425" t="n">
-        <v>21.72980388184651</v>
+        <v>21.72980196281688</v>
       </c>
       <c r="F425" t="n">
         <v>1412350</v>
@@ -8992,16 +8992,16 @@
         <v>44725</v>
       </c>
       <c r="B429" t="n">
-        <v>19.25449371337891</v>
+        <v>19.25449562072754</v>
       </c>
       <c r="C429" t="n">
-        <v>20.01031400974947</v>
+        <v>20.0103159919696</v>
       </c>
       <c r="D429" t="n">
-        <v>18.98995814136063</v>
+        <v>18.98996002250438</v>
       </c>
       <c r="E429" t="n">
-        <v>19.95362807317604</v>
+        <v>19.95363004978087</v>
       </c>
       <c r="F429" t="n">
         <v>2646600</v>
@@ -9052,16 +9052,16 @@
         <v>44729</v>
       </c>
       <c r="B432" t="n">
-        <v>19.19780731201172</v>
+        <v>19.19780921936035</v>
       </c>
       <c r="C432" t="n">
-        <v>19.51903061483979</v>
+        <v>19.51903255410274</v>
       </c>
       <c r="D432" t="n">
-        <v>18.68763029117579</v>
+        <v>18.6876321478371</v>
       </c>
       <c r="E432" t="n">
-        <v>19.17891139960691</v>
+        <v>19.17891330507819</v>
       </c>
       <c r="F432" t="n">
         <v>2517400</v>
@@ -9072,16 +9072,16 @@
         <v>44732</v>
       </c>
       <c r="B433" t="n">
-        <v>18.6120491027832</v>
+        <v>18.61205101013184</v>
       </c>
       <c r="C433" t="n">
-        <v>19.4812412820424</v>
+        <v>19.48124327846519</v>
       </c>
       <c r="D433" t="n">
-        <v>18.51757133942631</v>
+        <v>18.51757323709293</v>
       </c>
       <c r="E433" t="n">
-        <v>19.14112205476297</v>
+        <v>19.14112401633059</v>
       </c>
       <c r="F433" t="n">
         <v>828950</v>
@@ -9112,16 +9112,16 @@
         <v>44734</v>
       </c>
       <c r="B435" t="n">
-        <v>18.6120491027832</v>
+        <v>18.61205101013184</v>
       </c>
       <c r="C435" t="n">
-        <v>18.83879465363167</v>
+        <v>18.83879658421702</v>
       </c>
       <c r="D435" t="n">
-        <v>18.15855619907281</v>
+        <v>18.15855805994783</v>
       </c>
       <c r="E435" t="n">
-        <v>18.38530174992128</v>
+        <v>18.38530363403301</v>
       </c>
       <c r="F435" t="n">
         <v>1143850</v>
@@ -9172,16 +9172,16 @@
         <v>44739</v>
       </c>
       <c r="B438" t="n">
-        <v>18.55536270141602</v>
+        <v>18.55536460876465</v>
       </c>
       <c r="C438" t="n">
-        <v>18.70652641288067</v>
+        <v>18.70652833576777</v>
       </c>
       <c r="D438" t="n">
-        <v>18.38530307551488</v>
+        <v>18.38530496538269</v>
       </c>
       <c r="E438" t="n">
-        <v>18.57425861585249</v>
+        <v>18.57426052514348</v>
       </c>
       <c r="F438" t="n">
         <v>799000</v>
@@ -9212,16 +9212,16 @@
         <v>44741</v>
       </c>
       <c r="B440" t="n">
-        <v>17.81843948364258</v>
+        <v>17.81843757629395</v>
       </c>
       <c r="C440" t="n">
-        <v>18.13966281064456</v>
+        <v>18.13966086891105</v>
       </c>
       <c r="D440" t="n">
-        <v>17.51611207046742</v>
+        <v>17.51611019548098</v>
       </c>
       <c r="E440" t="n">
-        <v>18.13966281064456</v>
+        <v>18.13966086891105</v>
       </c>
       <c r="F440" t="n">
         <v>939650</v>
@@ -9252,16 +9252,16 @@
         <v>44743</v>
       </c>
       <c r="B442" t="n">
-        <v>17.59169387817383</v>
+        <v>17.5916919708252</v>
       </c>
       <c r="C442" t="n">
-        <v>17.72396167059182</v>
+        <v>17.72395974890228</v>
       </c>
       <c r="D442" t="n">
-        <v>17.06261910447483</v>
+        <v>17.06261725449021</v>
       </c>
       <c r="E442" t="n">
-        <v>17.2515746382264</v>
+        <v>17.25157276775461</v>
       </c>
       <c r="F442" t="n">
         <v>2016600</v>
@@ -9352,16 +9352,16 @@
         <v>44750</v>
       </c>
       <c r="B447" t="n">
-        <v>17.72396278381348</v>
+        <v>17.72396087646484</v>
       </c>
       <c r="C447" t="n">
-        <v>18.12076798800384</v>
+        <v>18.12076603795336</v>
       </c>
       <c r="D447" t="n">
-        <v>17.64838092596834</v>
+        <v>17.64837902675339</v>
       </c>
       <c r="E447" t="n">
-        <v>17.8184405566233</v>
+        <v>17.81843863910753</v>
       </c>
       <c r="F447" t="n">
         <v>701700</v>
@@ -9372,16 +9372,16 @@
         <v>44753</v>
       </c>
       <c r="B448" t="n">
-        <v>16.76029205322266</v>
+        <v>16.76029014587402</v>
       </c>
       <c r="C448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61058636528556</v>
       </c>
       <c r="D448" t="n">
-        <v>16.62802425795465</v>
+        <v>16.62802236565831</v>
       </c>
       <c r="E448" t="n">
-        <v>17.61058836939931</v>
+        <v>17.61058636528556</v>
       </c>
       <c r="F448" t="n">
         <v>1587350</v>
@@ -9392,16 +9392,16 @@
         <v>44754</v>
       </c>
       <c r="B449" t="n">
-        <v>16.60912895202637</v>
+        <v>16.60912704467773</v>
       </c>
       <c r="C449" t="n">
-        <v>16.87366635426378</v>
+        <v>16.87366441653637</v>
       </c>
       <c r="D449" t="n">
-        <v>16.19342783480004</v>
+        <v>16.19342597518942</v>
       </c>
       <c r="E449" t="n">
-        <v>16.79808449676932</v>
+        <v>16.79808256772154</v>
       </c>
       <c r="F449" t="n">
         <v>1842850</v>
@@ -9412,16 +9412,16 @@
         <v>44755</v>
       </c>
       <c r="B450" t="n">
-        <v>16.87366676330566</v>
+        <v>16.87366485595703</v>
       </c>
       <c r="C450" t="n">
-        <v>17.024830481959</v>
+        <v>17.02482855752328</v>
       </c>
       <c r="D450" t="n">
-        <v>16.3445919460053</v>
+        <v>16.3445900984617</v>
       </c>
       <c r="E450" t="n">
-        <v>16.51465157999372</v>
+        <v>16.51464971322709</v>
       </c>
       <c r="F450" t="n">
         <v>919750</v>
@@ -9432,16 +9432,16 @@
         <v>44756</v>
       </c>
       <c r="B451" t="n">
-        <v>17.02482986450195</v>
+        <v>17.02482795715332</v>
       </c>
       <c r="C451" t="n">
-        <v>17.13820174837335</v>
+        <v>17.13819982832328</v>
       </c>
       <c r="D451" t="n">
-        <v>16.53354689568962</v>
+        <v>16.53354504338107</v>
       </c>
       <c r="E451" t="n">
-        <v>16.70360652351032</v>
+        <v>16.70360465214942</v>
       </c>
       <c r="F451" t="n">
         <v>750250</v>
@@ -9452,16 +9452,16 @@
         <v>44757</v>
       </c>
       <c r="B452" t="n">
-        <v>16.59023284912109</v>
+        <v>16.59023094177246</v>
       </c>
       <c r="C452" t="n">
-        <v>17.15709767491168</v>
+        <v>17.15709570239164</v>
       </c>
       <c r="D452" t="n">
-        <v>16.59023284912109</v>
+        <v>16.59023094177246</v>
       </c>
       <c r="E452" t="n">
-        <v>17.06261990361098</v>
+        <v>17.06261794195288</v>
       </c>
       <c r="F452" t="n">
         <v>1098550</v>
@@ -9472,16 +9472,16 @@
         <v>44760</v>
       </c>
       <c r="B453" t="n">
-        <v>16.94924926757812</v>
+        <v>16.94924736022949</v>
       </c>
       <c r="C453" t="n">
-        <v>17.34605449464563</v>
+        <v>17.34605254264335</v>
       </c>
       <c r="D453" t="n">
-        <v>16.74139779501045</v>
+        <v>16.74139591105195</v>
       </c>
       <c r="E453" t="n">
-        <v>16.74139779501045</v>
+        <v>16.74139591105195</v>
       </c>
       <c r="F453" t="n">
         <v>809650</v>
@@ -9512,16 +9512,16 @@
         <v>44762</v>
       </c>
       <c r="B455" t="n">
-        <v>17.9696044921875</v>
+        <v>17.96960258483887</v>
       </c>
       <c r="C455" t="n">
-        <v>18.02629043576155</v>
+        <v>18.02628852239609</v>
       </c>
       <c r="D455" t="n">
-        <v>17.2326800176703</v>
+        <v>17.23267818854108</v>
       </c>
       <c r="E455" t="n">
-        <v>17.2515759328662</v>
+        <v>17.25157410173131</v>
       </c>
       <c r="F455" t="n">
         <v>812650</v>
@@ -9572,16 +9572,16 @@
         <v>44767</v>
       </c>
       <c r="B458" t="n">
-        <v>17.95070838928223</v>
+        <v>17.95070648193359</v>
       </c>
       <c r="C458" t="n">
-        <v>18.30972176418187</v>
+        <v>18.30971981868635</v>
       </c>
       <c r="D458" t="n">
-        <v>17.87512653130264</v>
+        <v>17.87512463198494</v>
       </c>
       <c r="E458" t="n">
-        <v>18.177453963221</v>
+        <v>18.17745203177956</v>
       </c>
       <c r="F458" t="n">
         <v>615900</v>
@@ -9592,16 +9592,16 @@
         <v>44768</v>
       </c>
       <c r="B459" t="n">
-        <v>17.40273666381836</v>
+        <v>17.40273857116699</v>
       </c>
       <c r="C459" t="n">
-        <v>18.15855512180728</v>
+        <v>18.158557111994</v>
       </c>
       <c r="D459" t="n">
-        <v>17.25157297222058</v>
+        <v>17.25157486300159</v>
       </c>
       <c r="E459" t="n">
-        <v>18.04518325411562</v>
+        <v>18.04518523187672</v>
       </c>
       <c r="F459" t="n">
         <v>578050</v>
@@ -9612,16 +9612,16 @@
         <v>44769</v>
       </c>
       <c r="B460" t="n">
-        <v>18.23413848876953</v>
+        <v>18.23414039611816</v>
       </c>
       <c r="C460" t="n">
-        <v>18.38530219297798</v>
+        <v>18.38530411613882</v>
       </c>
       <c r="D460" t="n">
-        <v>17.34605217704824</v>
+        <v>17.34605399150023</v>
       </c>
       <c r="E460" t="n">
-        <v>17.4405281406684</v>
+        <v>17.44052996500288</v>
       </c>
       <c r="F460" t="n">
         <v>704800</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.51902961730957</v>
+        <v>19.51903343200684</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65129739335679</v>
+        <v>19.65130123390378</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431526843877</v>
+        <v>18.74431893172991</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658304448599</v>
+        <v>18.87658673362685</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9692,16 +9692,16 @@
         <v>44775</v>
       </c>
       <c r="B464" t="n">
-        <v>19.08443832397461</v>
+        <v>19.08443641662598</v>
       </c>
       <c r="C464" t="n">
-        <v>19.38676576005906</v>
+        <v>19.38676382249504</v>
       </c>
       <c r="D464" t="n">
-        <v>18.895482775415</v>
+        <v>18.89548088695107</v>
       </c>
       <c r="E464" t="n">
-        <v>19.12222835247834</v>
+        <v>19.12222644135287</v>
       </c>
       <c r="F464" t="n">
         <v>867500</v>
@@ -9712,16 +9712,16 @@
         <v>44776</v>
       </c>
       <c r="B465" t="n">
-        <v>19.68909072875977</v>
+        <v>19.6890926361084</v>
       </c>
       <c r="C465" t="n">
-        <v>19.74577666541846</v>
+        <v>19.74577857825845</v>
       </c>
       <c r="D465" t="n">
-        <v>19.02774819369244</v>
+        <v>19.02775003697459</v>
       </c>
       <c r="E465" t="n">
-        <v>19.08443593236457</v>
+        <v>19.08443778113825</v>
       </c>
       <c r="F465" t="n">
         <v>1095050</v>
@@ -9732,16 +9732,16 @@
         <v>44777</v>
       </c>
       <c r="B466" t="n">
-        <v>21.3141040802002</v>
+        <v>21.31410217285156</v>
       </c>
       <c r="C466" t="n">
-        <v>21.46526779834239</v>
+        <v>21.46526587746648</v>
       </c>
       <c r="D466" t="n">
-        <v>19.78357098350703</v>
+        <v>19.78356921312217</v>
       </c>
       <c r="E466" t="n">
-        <v>19.89694287110684</v>
+        <v>19.89694109057661</v>
       </c>
       <c r="F466" t="n">
         <v>1697500</v>
@@ -9792,16 +9792,16 @@
         <v>44782</v>
       </c>
       <c r="B469" t="n">
-        <v>20.8795051574707</v>
+        <v>20.87950706481934</v>
       </c>
       <c r="C469" t="n">
-        <v>21.84317504212628</v>
+        <v>21.84317703750642</v>
       </c>
       <c r="D469" t="n">
-        <v>20.72834146599689</v>
+        <v>20.72834335953668</v>
       </c>
       <c r="E469" t="n">
-        <v>21.7486972844518</v>
+        <v>21.74869927120138</v>
       </c>
       <c r="F469" t="n">
         <v>1406900</v>
@@ -9812,16 +9812,16 @@
         <v>44783</v>
       </c>
       <c r="B470" t="n">
-        <v>21.82428359985352</v>
+        <v>21.82428169250488</v>
       </c>
       <c r="C470" t="n">
-        <v>22.12661104471852</v>
+        <v>22.12660911094776</v>
       </c>
       <c r="D470" t="n">
-        <v>21.08735910148479</v>
+        <v>21.08735725854019</v>
       </c>
       <c r="E470" t="n">
-        <v>21.16294096270104</v>
+        <v>21.16293911315091</v>
       </c>
       <c r="F470" t="n">
         <v>1851300</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75015830993652</v>
+        <v>22.75016021728516</v>
       </c>
       <c r="C474" t="n">
-        <v>23.12806755720854</v>
+        <v>23.12806949624067</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341276157331</v>
+        <v>22.52341464991185</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027753348805</v>
+        <v>23.09027946935192</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9912,16 +9912,16 @@
         <v>44790</v>
       </c>
       <c r="B475" t="n">
-        <v>22.80684471130371</v>
+        <v>22.80684661865234</v>
       </c>
       <c r="C475" t="n">
-        <v>23.09027800404387</v>
+        <v>23.09027993509618</v>
       </c>
       <c r="D475" t="n">
-        <v>22.23998172985033</v>
+        <v>22.2399835897919</v>
       </c>
       <c r="E475" t="n">
-        <v>22.48562139407294</v>
+        <v>22.4856232745575</v>
       </c>
       <c r="F475" t="n">
         <v>781800</v>
@@ -9932,16 +9932,16 @@
         <v>44791</v>
       </c>
       <c r="B476" t="n">
-        <v>22.25887489318848</v>
+        <v>22.25887680053711</v>
       </c>
       <c r="C476" t="n">
-        <v>23.14696295606662</v>
+        <v>23.14696493951494</v>
       </c>
       <c r="D476" t="n">
-        <v>21.84317563142713</v>
+        <v>21.84317750315476</v>
       </c>
       <c r="E476" t="n">
-        <v>22.9957992605146</v>
+        <v>22.99580123100981</v>
       </c>
       <c r="F476" t="n">
         <v>1546750</v>
@@ -9952,16 +9952,16 @@
         <v>44792</v>
       </c>
       <c r="B477" t="n">
-        <v>21.16293907165527</v>
+        <v>21.16293716430664</v>
       </c>
       <c r="C477" t="n">
-        <v>22.16439909378708</v>
+        <v>22.16439709618003</v>
       </c>
       <c r="D477" t="n">
-        <v>20.97398533650574</v>
+        <v>20.97398344618691</v>
       </c>
       <c r="E477" t="n">
-        <v>22.16439909378708</v>
+        <v>22.16439709618003</v>
       </c>
       <c r="F477" t="n">
         <v>1251050</v>
@@ -10012,16 +10012,16 @@
         <v>44797</v>
       </c>
       <c r="B480" t="n">
-        <v>20.80392456054688</v>
+        <v>20.80392646789551</v>
       </c>
       <c r="C480" t="n">
-        <v>21.16293789884462</v>
+        <v>21.16293983910836</v>
       </c>
       <c r="D480" t="n">
-        <v>20.48270124637937</v>
+        <v>20.48270312427755</v>
       </c>
       <c r="E480" t="n">
-        <v>20.76613273440319</v>
+        <v>20.76613463828699</v>
       </c>
       <c r="F480" t="n">
         <v>1050450</v>
@@ -10032,16 +10032,16 @@
         <v>44798</v>
       </c>
       <c r="B481" t="n">
-        <v>20.8795051574707</v>
+        <v>20.87950706481934</v>
       </c>
       <c r="C481" t="n">
-        <v>21.21962256228011</v>
+        <v>21.21962450069856</v>
       </c>
       <c r="D481" t="n">
-        <v>20.57717777452308</v>
+        <v>20.57717965425402</v>
       </c>
       <c r="E481" t="n">
-        <v>20.91729517933248</v>
+        <v>20.91729709013325</v>
       </c>
       <c r="F481" t="n">
         <v>1364800</v>
@@ -10052,16 +10052,16 @@
         <v>44799</v>
       </c>
       <c r="B482" t="n">
-        <v>20.46380805969238</v>
+        <v>20.46380615234375</v>
       </c>
       <c r="C482" t="n">
-        <v>21.10625477362032</v>
+        <v>21.10625280639183</v>
       </c>
       <c r="D482" t="n">
-        <v>20.2748525078264</v>
+        <v>20.27485061808954</v>
       </c>
       <c r="E482" t="n">
-        <v>20.97398696852234</v>
+        <v>20.97398501362199</v>
       </c>
       <c r="F482" t="n">
         <v>564750</v>
@@ -10152,16 +10152,16 @@
         <v>44806</v>
       </c>
       <c r="B487" t="n">
-        <v>20.97398567199707</v>
+        <v>20.97398376464844</v>
       </c>
       <c r="C487" t="n">
-        <v>21.20073123901156</v>
+        <v>21.20072931104297</v>
       </c>
       <c r="D487" t="n">
-        <v>20.55828456479703</v>
+        <v>20.55828269525176</v>
       </c>
       <c r="E487" t="n">
-        <v>20.8795079019043</v>
+        <v>20.87950600314736</v>
       </c>
       <c r="F487" t="n">
         <v>1001300</v>
@@ -10172,16 +10172,16 @@
         <v>44809</v>
       </c>
       <c r="B488" t="n">
-        <v>21.72980117797852</v>
+        <v>21.72980499267578</v>
       </c>
       <c r="C488" t="n">
-        <v>21.84317484657557</v>
+        <v>21.84317868117574</v>
       </c>
       <c r="D488" t="n">
-        <v>20.87950497054724</v>
+        <v>20.8795086359738</v>
       </c>
       <c r="E488" t="n">
-        <v>21.01177274889936</v>
+        <v>21.01177643754573</v>
       </c>
       <c r="F488" t="n">
         <v>878600</v>
@@ -10192,16 +10192,16 @@
         <v>44810</v>
       </c>
       <c r="B489" t="n">
-        <v>20.55828285217285</v>
+        <v>20.55828475952148</v>
       </c>
       <c r="C489" t="n">
-        <v>21.67311648196554</v>
+        <v>21.67311849274579</v>
       </c>
       <c r="D489" t="n">
-        <v>20.3504332168947</v>
+        <v>20.35043510495954</v>
       </c>
       <c r="E489" t="n">
-        <v>21.55974280689618</v>
+        <v>21.55974480715789</v>
       </c>
       <c r="F489" t="n">
         <v>1564950</v>
@@ -10232,16 +10232,16 @@
         <v>44813</v>
       </c>
       <c r="B491" t="n">
-        <v>20.25595664978027</v>
+        <v>20.25595474243164</v>
       </c>
       <c r="C491" t="n">
-        <v>20.29374667569073</v>
+        <v>20.2937447647837</v>
       </c>
       <c r="D491" t="n">
-        <v>19.42455445558783</v>
+        <v>19.42455262652599</v>
       </c>
       <c r="E491" t="n">
-        <v>19.9158374065185</v>
+        <v>19.9158355311963</v>
       </c>
       <c r="F491" t="n">
         <v>1292000</v>
@@ -10252,16 +10252,16 @@
         <v>44816</v>
       </c>
       <c r="B492" t="n">
-        <v>20.65276336669922</v>
+        <v>20.65276145935059</v>
       </c>
       <c r="C492" t="n">
-        <v>21.12515043874988</v>
+        <v>21.12514848777479</v>
       </c>
       <c r="D492" t="n">
-        <v>20.42601778835654</v>
+        <v>20.42601590194859</v>
       </c>
       <c r="E492" t="n">
-        <v>20.44491190170818</v>
+        <v>20.44491001355529</v>
       </c>
       <c r="F492" t="n">
         <v>1299050</v>
@@ -10272,16 +10272,16 @@
         <v>44817</v>
       </c>
       <c r="B493" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577903747559</v>
       </c>
       <c r="C493" t="n">
-        <v>20.27485008942426</v>
+        <v>20.27485204787884</v>
       </c>
       <c r="D493" t="n">
-        <v>19.57571751413516</v>
+        <v>19.57571940505684</v>
       </c>
       <c r="E493" t="n">
-        <v>20.12368638676789</v>
+        <v>20.12368833062077</v>
       </c>
       <c r="F493" t="n">
         <v>1035100</v>
@@ -10312,16 +10312,16 @@
         <v>44819</v>
       </c>
       <c r="B495" t="n">
-        <v>20.4071216583252</v>
+        <v>20.40711975097656</v>
       </c>
       <c r="C495" t="n">
-        <v>20.61497131911616</v>
+        <v>20.61496939234089</v>
       </c>
       <c r="D495" t="n">
-        <v>19.99142053472962</v>
+        <v>19.99141866623443</v>
       </c>
       <c r="E495" t="n">
-        <v>20.44491168664462</v>
+        <v>20.44490977576395</v>
       </c>
       <c r="F495" t="n">
         <v>753500</v>
@@ -10352,16 +10352,16 @@
         <v>44823</v>
       </c>
       <c r="B497" t="n">
-        <v>20.36932563781738</v>
+        <v>20.36932754516602</v>
       </c>
       <c r="C497" t="n">
-        <v>20.5204893240265</v>
+        <v>20.52049124552984</v>
       </c>
       <c r="D497" t="n">
-        <v>19.85914864736495</v>
+        <v>19.85915050694149</v>
       </c>
       <c r="E497" t="n">
-        <v>19.93473049046951</v>
+        <v>19.93473235712339</v>
       </c>
       <c r="F497" t="n">
         <v>718850</v>
@@ -10372,16 +10372,16 @@
         <v>44824</v>
       </c>
       <c r="B498" t="n">
-        <v>19.84025382995605</v>
+        <v>19.84025573730469</v>
       </c>
       <c r="C498" t="n">
-        <v>20.63386412731537</v>
+        <v>20.63386611095796</v>
       </c>
       <c r="D498" t="n">
-        <v>19.74577607036311</v>
+        <v>19.7457779686291</v>
       </c>
       <c r="E498" t="n">
-        <v>20.3693267608578</v>
+        <v>20.36932871906902</v>
       </c>
       <c r="F498" t="n">
         <v>1041050</v>
@@ -10412,16 +10412,16 @@
         <v>44826</v>
       </c>
       <c r="B500" t="n">
-        <v>19.93473434448242</v>
+        <v>19.93473052978516</v>
       </c>
       <c r="C500" t="n">
-        <v>19.97252437233406</v>
+        <v>19.97252055040532</v>
       </c>
       <c r="D500" t="n">
-        <v>18.81990059164773</v>
+        <v>18.81989699028429</v>
       </c>
       <c r="E500" t="n">
-        <v>19.34897359566612</v>
+        <v>19.34896989305964</v>
       </c>
       <c r="F500" t="n">
         <v>1035500</v>
@@ -10432,16 +10432,16 @@
         <v>44827</v>
       </c>
       <c r="B501" t="n">
-        <v>19.57571792602539</v>
+        <v>19.57571983337402</v>
       </c>
       <c r="C501" t="n">
-        <v>19.68909160640989</v>
+        <v>19.68909352480502</v>
       </c>
       <c r="D501" t="n">
-        <v>19.21670457516592</v>
+        <v>19.21670644753429</v>
       </c>
       <c r="E501" t="n">
-        <v>19.3489723672699</v>
+        <v>19.34897425252572</v>
       </c>
       <c r="F501" t="n">
         <v>673550</v>
@@ -10452,16 +10452,16 @@
         <v>44830</v>
       </c>
       <c r="B502" t="n">
-        <v>18.7065258026123</v>
+        <v>18.70652389526367</v>
       </c>
       <c r="C502" t="n">
-        <v>19.48124205111187</v>
+        <v>19.48124006477188</v>
       </c>
       <c r="D502" t="n">
-        <v>18.6309439493457</v>
+        <v>18.63094204970352</v>
       </c>
       <c r="E502" t="n">
-        <v>19.34897245638518</v>
+        <v>19.34897048353161</v>
       </c>
       <c r="F502" t="n">
         <v>1198500</v>
@@ -10492,16 +10492,16 @@
         <v>44832</v>
       </c>
       <c r="B504" t="n">
-        <v>18.44198989868164</v>
+        <v>18.44199180603027</v>
       </c>
       <c r="C504" t="n">
-        <v>18.66873545456541</v>
+        <v>18.66873738536503</v>
       </c>
       <c r="D504" t="n">
-        <v>18.15855660231681</v>
+        <v>18.15855848035157</v>
       </c>
       <c r="E504" t="n">
-        <v>18.49867583714921</v>
+        <v>18.49867775036054</v>
       </c>
       <c r="F504" t="n">
         <v>784750</v>
@@ -10512,16 +10512,16 @@
         <v>44833</v>
       </c>
       <c r="B505" t="n">
-        <v>18.21524238586426</v>
+        <v>18.21524429321289</v>
       </c>
       <c r="C505" t="n">
-        <v>18.30971833915579</v>
+        <v>18.30972025639716</v>
       </c>
       <c r="D505" t="n">
-        <v>17.85622727610854</v>
+        <v>17.8562291458641</v>
       </c>
       <c r="E505" t="n">
-        <v>18.29082422970546</v>
+        <v>18.2908261449684</v>
       </c>
       <c r="F505" t="n">
         <v>1182750</v>
@@ -10532,16 +10532,16 @@
         <v>44834</v>
       </c>
       <c r="B506" t="n">
-        <v>18.25303649902344</v>
+        <v>18.2530345916748</v>
       </c>
       <c r="C506" t="n">
-        <v>18.51757391278236</v>
+        <v>18.51757197779093</v>
       </c>
       <c r="D506" t="n">
-        <v>17.95070905587821</v>
+        <v>17.95070718012124</v>
       </c>
       <c r="E506" t="n">
-        <v>18.21524646963713</v>
+        <v>18.21524456623737</v>
       </c>
       <c r="F506" t="n">
         <v>981200</v>
@@ -10552,16 +10552,16 @@
         <v>44837</v>
       </c>
       <c r="B507" t="n">
-        <v>19.27338981628418</v>
+        <v>19.27339172363281</v>
       </c>
       <c r="C507" t="n">
-        <v>19.27338981628418</v>
+        <v>19.27339172363281</v>
       </c>
       <c r="D507" t="n">
-        <v>18.76321277806593</v>
+        <v>18.76321463492602</v>
       </c>
       <c r="E507" t="n">
-        <v>18.89548056537928</v>
+        <v>18.89548243532896</v>
       </c>
       <c r="F507" t="n">
         <v>1581550</v>
@@ -10572,16 +10572,16 @@
         <v>44838</v>
       </c>
       <c r="B508" t="n">
-        <v>19.72688102722168</v>
+        <v>19.72688484191895</v>
       </c>
       <c r="C508" t="n">
-        <v>20.08589616909064</v>
+        <v>20.08590005321267</v>
       </c>
       <c r="D508" t="n">
-        <v>19.46234545112188</v>
+        <v>19.46234921466442</v>
       </c>
       <c r="E508" t="n">
-        <v>19.63240506547944</v>
+        <v>19.63240886190736</v>
       </c>
       <c r="F508" t="n">
         <v>1320250</v>
@@ -10592,16 +10592,16 @@
         <v>44839</v>
       </c>
       <c r="B509" t="n">
-        <v>19.63240814208984</v>
+        <v>19.63240623474121</v>
       </c>
       <c r="C509" t="n">
-        <v>19.8402578133139</v>
+        <v>19.84025588577203</v>
       </c>
       <c r="D509" t="n">
-        <v>19.38676663863574</v>
+        <v>19.38676475515193</v>
       </c>
       <c r="E509" t="n">
-        <v>19.72688411863749</v>
+        <v>19.72688220211023</v>
       </c>
       <c r="F509" t="n">
         <v>721150</v>
@@ -10632,16 +10632,16 @@
         <v>44841</v>
       </c>
       <c r="B511" t="n">
-        <v>19.63240814208984</v>
+        <v>19.63240623474121</v>
       </c>
       <c r="C511" t="n">
-        <v>20.38822676655345</v>
+        <v>20.38822478577472</v>
       </c>
       <c r="D511" t="n">
-        <v>19.55682627964348</v>
+        <v>19.55682437963786</v>
       </c>
       <c r="E511" t="n">
-        <v>20.38822676655345</v>
+        <v>20.38822478577472</v>
       </c>
       <c r="F511" t="n">
         <v>673950</v>
@@ -10692,16 +10692,16 @@
         <v>44847</v>
       </c>
       <c r="B514" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577903747559</v>
       </c>
       <c r="C514" t="n">
-        <v>19.99141859744693</v>
+        <v>19.99142052852337</v>
       </c>
       <c r="D514" t="n">
-        <v>19.10333049283063</v>
+        <v>19.10333233812196</v>
       </c>
       <c r="E514" t="n">
-        <v>19.3489719601506</v>
+        <v>19.34897382916973</v>
       </c>
       <c r="F514" t="n">
         <v>1432800</v>
@@ -10772,16 +10772,16 @@
         <v>44853</v>
       </c>
       <c r="B518" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577903747559</v>
       </c>
       <c r="C518" t="n">
-        <v>19.76467304346237</v>
+        <v>19.76467495263626</v>
       </c>
       <c r="D518" t="n">
-        <v>19.27339010882242</v>
+        <v>19.2733919705407</v>
       </c>
       <c r="E518" t="n">
-        <v>19.46234563814962</v>
+        <v>19.46234751812012</v>
       </c>
       <c r="F518" t="n">
         <v>599800</v>
@@ -10792,16 +10792,16 @@
         <v>44854</v>
       </c>
       <c r="B519" t="n">
-        <v>19.48124313354492</v>
+        <v>19.48124122619629</v>
       </c>
       <c r="C519" t="n">
-        <v>19.84025650600569</v>
+        <v>19.84025456350717</v>
       </c>
       <c r="D519" t="n">
-        <v>19.19780981653667</v>
+        <v>19.19780793693812</v>
       </c>
       <c r="E519" t="n">
-        <v>19.84025650600569</v>
+        <v>19.84025456350717</v>
       </c>
       <c r="F519" t="n">
         <v>1274100</v>
@@ -10812,16 +10812,16 @@
         <v>44855</v>
       </c>
       <c r="B520" t="n">
-        <v>19.74577713012695</v>
+        <v>19.74577903747559</v>
       </c>
       <c r="C520" t="n">
-        <v>19.93473265945416</v>
+        <v>19.934734585055</v>
       </c>
       <c r="D520" t="n">
-        <v>19.17891234415881</v>
+        <v>19.17891419675099</v>
       </c>
       <c r="E520" t="n">
-        <v>19.33007604681519</v>
+        <v>19.33007791400906</v>
       </c>
       <c r="F520" t="n">
         <v>2036950</v>
@@ -10872,16 +10872,16 @@
         <v>44860</v>
       </c>
       <c r="B523" t="n">
-        <v>18.38530158996582</v>
+        <v>18.38530540466309</v>
       </c>
       <c r="C523" t="n">
-        <v>19.3111815003919</v>
+        <v>19.31118550719652</v>
       </c>
       <c r="D523" t="n">
-        <v>18.06408008056859</v>
+        <v>18.06408382861681</v>
       </c>
       <c r="E523" t="n">
-        <v>18.98995818898124</v>
+        <v>18.98996212913643</v>
       </c>
       <c r="F523" t="n">
         <v>1458850</v>
@@ -10892,16 +10892,16 @@
         <v>44861</v>
       </c>
       <c r="B524" t="n">
-        <v>19.50013542175293</v>
+        <v>19.50013732910156</v>
       </c>
       <c r="C524" t="n">
-        <v>19.74577688603637</v>
+        <v>19.7457788174117</v>
       </c>
       <c r="D524" t="n">
-        <v>18.40419769003509</v>
+        <v>18.40419949018779</v>
       </c>
       <c r="E524" t="n">
-        <v>18.49867545353079</v>
+        <v>18.49867726292455</v>
       </c>
       <c r="F524" t="n">
         <v>1150900</v>
@@ -10932,16 +10932,16 @@
         <v>44865</v>
       </c>
       <c r="B526" t="n">
-        <v>20.46380805969238</v>
+        <v>20.46380615234375</v>
       </c>
       <c r="C526" t="n">
-        <v>20.50159989087106</v>
+        <v>20.50159798</v>
       </c>
       <c r="D526" t="n">
-        <v>18.76321530095325</v>
+        <v>18.76321355210998</v>
       </c>
       <c r="E526" t="n">
-        <v>18.78210941452889</v>
+        <v>18.78210766392458</v>
       </c>
       <c r="F526" t="n">
         <v>2299050</v>
@@ -11012,16 +11012,16 @@
         <v>44872</v>
       </c>
       <c r="B530" t="n">
-        <v>20.44491004943848</v>
+        <v>20.44491195678711</v>
       </c>
       <c r="C530" t="n">
-        <v>21.52195370150519</v>
+        <v>21.52195570933349</v>
       </c>
       <c r="D530" t="n">
-        <v>20.23706040529189</v>
+        <v>20.23706229324979</v>
       </c>
       <c r="E530" t="n">
-        <v>21.29520814370522</v>
+        <v>21.29521013037995</v>
       </c>
       <c r="F530" t="n">
         <v>1164150</v>
@@ -11032,16 +11032,16 @@
         <v>44873</v>
       </c>
       <c r="B531" t="n">
-        <v>19.9536304473877</v>
+        <v>19.95362854003906</v>
       </c>
       <c r="C531" t="n">
-        <v>20.35043565464299</v>
+        <v>20.35043370936413</v>
       </c>
       <c r="D531" t="n">
-        <v>19.25449600440303</v>
+        <v>19.254494163884</v>
       </c>
       <c r="E531" t="n">
-        <v>20.35043565464299</v>
+        <v>20.35043370936413</v>
       </c>
       <c r="F531" t="n">
         <v>2602700</v>
@@ -11052,16 +11052,16 @@
         <v>44874</v>
       </c>
       <c r="B532" t="n">
-        <v>18.7821102142334</v>
+        <v>18.78210830688477</v>
       </c>
       <c r="C532" t="n">
-        <v>20.06700369679745</v>
+        <v>20.06700165896615</v>
       </c>
       <c r="D532" t="n">
-        <v>18.61205237272972</v>
+        <v>18.61205048265069</v>
       </c>
       <c r="E532" t="n">
-        <v>19.85915402250599</v>
+        <v>19.85915200578211</v>
       </c>
       <c r="F532" t="n">
         <v>1714900</v>
@@ -11072,16 +11072,16 @@
         <v>44875</v>
       </c>
       <c r="B533" t="n">
-        <v>16.94924926757812</v>
+        <v>16.94924736022949</v>
       </c>
       <c r="C533" t="n">
-        <v>18.51757425979405</v>
+        <v>18.51757217595721</v>
       </c>
       <c r="D533" t="n">
-        <v>16.2501165916999</v>
+        <v>16.25011476302671</v>
       </c>
       <c r="E533" t="n">
-        <v>18.51757425979405</v>
+        <v>18.51757217595721</v>
       </c>
       <c r="F533" t="n">
         <v>6247350</v>
@@ -11092,16 +11092,16 @@
         <v>44876</v>
       </c>
       <c r="B534" t="n">
-        <v>15.5131893157959</v>
+        <v>15.51319026947021</v>
       </c>
       <c r="C534" t="n">
-        <v>16.96814035410347</v>
+        <v>16.96814139722099</v>
       </c>
       <c r="D534" t="n">
-        <v>15.05969732248658</v>
+        <v>15.05969824828244</v>
       </c>
       <c r="E534" t="n">
-        <v>16.94924624343426</v>
+        <v>16.94924728539026</v>
       </c>
       <c r="F534" t="n">
         <v>6426800</v>
@@ -11152,16 +11152,16 @@
         <v>44882</v>
       </c>
       <c r="B537" t="n">
-        <v>13.88817882537842</v>
+        <v>13.8881778717041</v>
       </c>
       <c r="C537" t="n">
-        <v>14.26608899878738</v>
+        <v>14.2660880191627</v>
       </c>
       <c r="D537" t="n">
-        <v>13.07567343921034</v>
+        <v>13.07567254132919</v>
       </c>
       <c r="E537" t="n">
-        <v>14.26608899878738</v>
+        <v>14.2660880191627</v>
       </c>
       <c r="F537" t="n">
         <v>5220400</v>
@@ -11172,16 +11172,16 @@
         <v>44883</v>
       </c>
       <c r="B538" t="n">
-        <v>13.83149147033691</v>
+        <v>13.83149242401123</v>
       </c>
       <c r="C538" t="n">
-        <v>14.88963822584258</v>
+        <v>14.88963925247558</v>
       </c>
       <c r="D538" t="n">
-        <v>13.73701371139616</v>
+        <v>13.73701465855629</v>
       </c>
       <c r="E538" t="n">
-        <v>14.26608753965234</v>
+        <v>14.26608852329183</v>
       </c>
       <c r="F538" t="n">
         <v>3266800</v>
@@ -11232,16 +11232,16 @@
         <v>44888</v>
       </c>
       <c r="B541" t="n">
-        <v>14.02044773101807</v>
+        <v>14.02044677734375</v>
       </c>
       <c r="C541" t="n">
-        <v>14.07713367222323</v>
+        <v>14.07713271469312</v>
       </c>
       <c r="D541" t="n">
-        <v>13.62364253855478</v>
+        <v>13.62364161187125</v>
       </c>
       <c r="E541" t="n">
-        <v>14.05823865882377</v>
+        <v>14.05823770257891</v>
       </c>
       <c r="F541" t="n">
         <v>1795300</v>
@@ -11252,16 +11252,16 @@
         <v>44889</v>
       </c>
       <c r="B542" t="n">
-        <v>14.94632530212402</v>
+        <v>14.94632625579834</v>
       </c>
       <c r="C542" t="n">
-        <v>15.11638492080524</v>
+        <v>15.11638588533049</v>
       </c>
       <c r="D542" t="n">
-        <v>14.22829770315091</v>
+        <v>14.22829861101032</v>
       </c>
       <c r="E542" t="n">
-        <v>14.30387955567439</v>
+        <v>14.30388046835643</v>
       </c>
       <c r="F542" t="n">
         <v>1608000</v>
@@ -11272,16 +11272,16 @@
         <v>44890</v>
       </c>
       <c r="B543" t="n">
-        <v>14.11492538452148</v>
+        <v>14.11492443084717</v>
       </c>
       <c r="C543" t="n">
-        <v>14.90853581355609</v>
+        <v>14.90853480626151</v>
       </c>
       <c r="D543" t="n">
-        <v>13.94486665044753</v>
+        <v>13.94486570826322</v>
       </c>
       <c r="E543" t="n">
-        <v>14.90853581355609</v>
+        <v>14.90853480626151</v>
       </c>
       <c r="F543" t="n">
         <v>1492900</v>
@@ -11292,16 +11292,16 @@
         <v>44893</v>
       </c>
       <c r="B544" t="n">
-        <v>13.98265647888184</v>
+        <v>13.98265552520752</v>
       </c>
       <c r="C544" t="n">
-        <v>14.28498389431492</v>
+        <v>14.28498292002064</v>
       </c>
       <c r="D544" t="n">
-        <v>13.90707462502356</v>
+        <v>13.90707367650424</v>
       </c>
       <c r="E544" t="n">
-        <v>14.13382018659838</v>
+        <v>14.13381922261408</v>
       </c>
       <c r="F544" t="n">
         <v>1713550</v>
@@ -11332,16 +11332,16 @@
         <v>44895</v>
       </c>
       <c r="B546" t="n">
-        <v>14.41725254058838</v>
+        <v>14.41725158691406</v>
       </c>
       <c r="C546" t="n">
-        <v>14.60620717459865</v>
+        <v>14.60620620842533</v>
       </c>
       <c r="D546" t="n">
-        <v>13.83149272465316</v>
+        <v>13.83149180972576</v>
       </c>
       <c r="E546" t="n">
-        <v>14.41725254058838</v>
+        <v>14.41725158691406</v>
       </c>
       <c r="F546" t="n">
         <v>1926400</v>
@@ -11352,16 +11352,16 @@
         <v>44896</v>
       </c>
       <c r="B547" t="n">
-        <v>14.1527156829834</v>
+        <v>14.15271472930908</v>
       </c>
       <c r="C547" t="n">
-        <v>14.51172995157667</v>
+        <v>14.51172897371034</v>
       </c>
       <c r="D547" t="n">
-        <v>14.03934289832344</v>
+        <v>14.0393419522887</v>
       </c>
       <c r="E547" t="n">
-        <v>14.30388029687014</v>
+        <v>14.30387933300967</v>
       </c>
       <c r="F547" t="n">
         <v>1145350</v>
@@ -11392,16 +11392,16 @@
         <v>44900</v>
       </c>
       <c r="B549" t="n">
-        <v>13.41579055786133</v>
+        <v>13.41579151153564</v>
       </c>
       <c r="C549" t="n">
-        <v>14.22829677075448</v>
+        <v>14.22829778218658</v>
       </c>
       <c r="D549" t="n">
-        <v>13.30241778650555</v>
+        <v>13.30241873212065</v>
       </c>
       <c r="E549" t="n">
-        <v>14.22829677075448</v>
+        <v>14.22829778218658</v>
       </c>
       <c r="F549" t="n">
         <v>1514950</v>
@@ -11412,16 +11412,16 @@
         <v>44901</v>
       </c>
       <c r="B550" t="n">
-        <v>13.15125370025635</v>
+        <v>13.15125560760498</v>
       </c>
       <c r="C550" t="n">
-        <v>13.66143160668842</v>
+        <v>13.66143358802902</v>
       </c>
       <c r="D550" t="n">
-        <v>12.67886671648566</v>
+        <v>12.67886855532321</v>
       </c>
       <c r="E550" t="n">
-        <v>13.54805883870426</v>
+        <v>13.54806080360221</v>
       </c>
       <c r="F550" t="n">
         <v>4313950</v>
@@ -11532,16 +11532,16 @@
         <v>44909</v>
       </c>
       <c r="B556" t="n">
-        <v>11.50734806060791</v>
+        <v>11.50734901428223</v>
       </c>
       <c r="C556" t="n">
-        <v>11.62072083694312</v>
+        <v>11.62072180001323</v>
       </c>
       <c r="D556" t="n">
-        <v>11.07275196748624</v>
+        <v>11.0727528851433</v>
       </c>
       <c r="E556" t="n">
-        <v>11.50734806060791</v>
+        <v>11.50734901428223</v>
       </c>
       <c r="F556" t="n">
         <v>4449300</v>
@@ -11572,16 +11572,16 @@
         <v>44911</v>
       </c>
       <c r="B558" t="n">
-        <v>11.31839275360107</v>
+        <v>11.31839370727539</v>
       </c>
       <c r="C558" t="n">
-        <v>11.71519792903348</v>
+        <v>11.71519891614213</v>
       </c>
       <c r="D558" t="n">
-        <v>11.09164719649877</v>
+        <v>11.09164813106777</v>
       </c>
       <c r="E558" t="n">
-        <v>11.63961607666605</v>
+        <v>11.63961705740626</v>
       </c>
       <c r="F558" t="n">
         <v>4251600</v>
@@ -11632,16 +11632,16 @@
         <v>44916</v>
       </c>
       <c r="B561" t="n">
-        <v>12.65997219085693</v>
+        <v>12.65997314453125</v>
       </c>
       <c r="C561" t="n">
-        <v>12.81113679906094</v>
+        <v>12.81113776412247</v>
       </c>
       <c r="D561" t="n">
-        <v>12.22537608216148</v>
+        <v>12.22537700309772</v>
       </c>
       <c r="E561" t="n">
-        <v>12.62218126405762</v>
+        <v>12.62218221488515</v>
       </c>
       <c r="F561" t="n">
         <v>1430400</v>
@@ -11672,16 +11672,16 @@
         <v>44918</v>
       </c>
       <c r="B563" t="n">
-        <v>13.39689636230469</v>
+        <v>13.39689540863037</v>
       </c>
       <c r="C563" t="n">
-        <v>13.66143284491103</v>
+        <v>13.66143187240536</v>
       </c>
       <c r="D563" t="n">
-        <v>12.88671840963194</v>
+        <v>12.88671749227526</v>
       </c>
       <c r="E563" t="n">
-        <v>12.90561342217188</v>
+        <v>12.90561250347013</v>
       </c>
       <c r="F563" t="n">
         <v>1442850</v>
@@ -11712,16 +11712,16 @@
         <v>44922</v>
       </c>
       <c r="B565" t="n">
-        <v>12.35764503479004</v>
+        <v>12.35764408111572</v>
       </c>
       <c r="C565" t="n">
-        <v>13.24573318464882</v>
+        <v>13.24573216243824</v>
       </c>
       <c r="D565" t="n">
-        <v>12.22537633772409</v>
+        <v>12.22537539425732</v>
       </c>
       <c r="E565" t="n">
-        <v>13.24573318464882</v>
+        <v>13.24573216243824</v>
       </c>
       <c r="F565" t="n">
         <v>2491300</v>
@@ -11772,16 +11772,16 @@
         <v>44928</v>
       </c>
       <c r="B568" t="n">
-        <v>12.21331119537354</v>
+        <v>12.21331214904785</v>
       </c>
       <c r="C568" t="n">
-        <v>12.83073010946179</v>
+        <v>12.83073111134716</v>
       </c>
       <c r="D568" t="n">
-        <v>11.98177944759996</v>
+        <v>11.98178038319516</v>
       </c>
       <c r="E568" t="n">
-        <v>12.83073010946179</v>
+        <v>12.83073111134716</v>
       </c>
       <c r="F568" t="n">
         <v>1499800</v>
@@ -11852,16 +11852,16 @@
         <v>44932</v>
       </c>
       <c r="B572" t="n">
-        <v>13.08155632019043</v>
+        <v>13.08155727386475</v>
       </c>
       <c r="C572" t="n">
-        <v>13.13943879575224</v>
+        <v>13.13943975364632</v>
       </c>
       <c r="D572" t="n">
-        <v>12.44484264883297</v>
+        <v>12.44484355608945</v>
       </c>
       <c r="E572" t="n">
-        <v>12.73425778671811</v>
+        <v>12.7342587150736</v>
       </c>
       <c r="F572" t="n">
         <v>1382000</v>
@@ -11992,16 +11992,16 @@
         <v>44943</v>
       </c>
       <c r="B579" t="n">
-        <v>13.06226253509521</v>
+        <v>13.0622615814209</v>
       </c>
       <c r="C579" t="n">
-        <v>13.29379429488402</v>
+        <v>13.2937933243056</v>
       </c>
       <c r="D579" t="n">
-        <v>12.86931940193787</v>
+        <v>12.86931846235032</v>
       </c>
       <c r="E579" t="n">
-        <v>13.0043791351353</v>
+        <v>13.00437818568704</v>
       </c>
       <c r="F579" t="n">
         <v>1398800</v>
@@ -12132,16 +12132,16 @@
         <v>44952</v>
       </c>
       <c r="B586" t="n">
-        <v>14.56722068786621</v>
+        <v>14.56721973419189</v>
       </c>
       <c r="C586" t="n">
-        <v>14.68298656676003</v>
+        <v>14.68298560550685</v>
       </c>
       <c r="D586" t="n">
-        <v>14.20062827802307</v>
+        <v>14.20062734834852</v>
       </c>
       <c r="E586" t="n">
-        <v>14.49004343527033</v>
+        <v>14.49004248664859</v>
       </c>
       <c r="F586" t="n">
         <v>1715850</v>
@@ -12152,16 +12152,16 @@
         <v>44953</v>
       </c>
       <c r="B587" t="n">
-        <v>14.35498142242432</v>
+        <v>14.35498237609863</v>
       </c>
       <c r="C587" t="n">
-        <v>14.64439655223626</v>
+        <v>14.6443975251379</v>
       </c>
       <c r="D587" t="n">
-        <v>14.29709802845179</v>
+        <v>14.29709897828062</v>
       </c>
       <c r="E587" t="n">
-        <v>14.56721930695646</v>
+        <v>14.56722027473081</v>
       </c>
       <c r="F587" t="n">
         <v>1566450</v>
@@ -12252,16 +12252,16 @@
         <v>44960</v>
       </c>
       <c r="B592" t="n">
-        <v>14.27780532836914</v>
+        <v>14.27780437469482</v>
       </c>
       <c r="C592" t="n">
-        <v>14.58651433437969</v>
+        <v>14.58651336008541</v>
       </c>
       <c r="D592" t="n">
-        <v>14.12345082536386</v>
+        <v>14.12344988199953</v>
       </c>
       <c r="E592" t="n">
-        <v>14.56722048151674</v>
+        <v>14.56721950851117</v>
       </c>
       <c r="F592" t="n">
         <v>1563350</v>
@@ -12272,16 +12272,16 @@
         <v>44963</v>
       </c>
       <c r="B593" t="n">
-        <v>14.27780532836914</v>
+        <v>14.27780437469482</v>
       </c>
       <c r="C593" t="n">
-        <v>14.35498257987178</v>
+        <v>14.35498162104247</v>
       </c>
       <c r="D593" t="n">
-        <v>13.91121292371891</v>
+        <v>13.91121199453083</v>
       </c>
       <c r="E593" t="n">
-        <v>14.18133330397814</v>
+        <v>14.18133235674759</v>
       </c>
       <c r="F593" t="n">
         <v>1305850</v>
@@ -12312,16 +12312,16 @@
         <v>44965</v>
       </c>
       <c r="B595" t="n">
-        <v>14.74086856842041</v>
+        <v>14.74086761474609</v>
       </c>
       <c r="C595" t="n">
-        <v>14.81804581851486</v>
+        <v>14.81804485984749</v>
       </c>
       <c r="D595" t="n">
-        <v>14.25851029531742</v>
+        <v>14.25850937284972</v>
       </c>
       <c r="E595" t="n">
-        <v>14.35498231794817</v>
+        <v>14.35498138923913</v>
       </c>
       <c r="F595" t="n">
         <v>1645600</v>
@@ -12332,16 +12332,16 @@
         <v>44966</v>
       </c>
       <c r="B596" t="n">
-        <v>13.64109230041504</v>
+        <v>13.64109134674072</v>
       </c>
       <c r="C596" t="n">
-        <v>14.74086857474552</v>
+        <v>14.74086754418378</v>
       </c>
       <c r="D596" t="n">
-        <v>13.64109230041504</v>
+        <v>13.64109134674072</v>
       </c>
       <c r="E596" t="n">
-        <v>14.74086857474552</v>
+        <v>14.74086754418378</v>
       </c>
       <c r="F596" t="n">
         <v>2708250</v>
@@ -12372,16 +12372,16 @@
         <v>44970</v>
       </c>
       <c r="B598" t="n">
-        <v>14.12344932556152</v>
+        <v>14.12345027923584</v>
       </c>
       <c r="C598" t="n">
-        <v>14.62510140705705</v>
+        <v>14.62510239460502</v>
       </c>
       <c r="D598" t="n">
-        <v>13.9690939189222</v>
+        <v>13.9690948621738</v>
       </c>
       <c r="E598" t="n">
-        <v>14.04627208225452</v>
+        <v>14.04627303071751</v>
       </c>
       <c r="F598" t="n">
         <v>1583800</v>
@@ -12412,16 +12412,16 @@
         <v>44972</v>
       </c>
       <c r="B600" t="n">
-        <v>14.83734130859375</v>
+        <v>14.83734035491943</v>
       </c>
       <c r="C600" t="n">
-        <v>15.04957921663013</v>
+        <v>15.04957824931416</v>
       </c>
       <c r="D600" t="n">
-        <v>13.7375640615239</v>
+        <v>13.73756317853808</v>
       </c>
       <c r="E600" t="n">
-        <v>14.00768536994309</v>
+        <v>14.00768446959514</v>
       </c>
       <c r="F600" t="n">
         <v>2808050</v>
@@ -12432,16 +12432,16 @@
         <v>44973</v>
       </c>
       <c r="B601" t="n">
-        <v>14.79875183105469</v>
+        <v>14.79875087738037</v>
       </c>
       <c r="C601" t="n">
-        <v>14.99169495453137</v>
+        <v>14.99169398842324</v>
       </c>
       <c r="D601" t="n">
-        <v>14.58651393521765</v>
+        <v>14.58651299522056</v>
       </c>
       <c r="E601" t="n">
-        <v>14.81804568338966</v>
+        <v>14.818044728472</v>
       </c>
       <c r="F601" t="n">
         <v>1393950</v>
@@ -12532,16 +12532,16 @@
         <v>44984</v>
       </c>
       <c r="B606" t="n">
-        <v>13.64109230041504</v>
+        <v>13.64109134674072</v>
       </c>
       <c r="C606" t="n">
-        <v>13.81474065318936</v>
+        <v>13.81473968737496</v>
       </c>
       <c r="D606" t="n">
-        <v>13.25520512975183</v>
+        <v>13.25520420305561</v>
       </c>
       <c r="E606" t="n">
-        <v>13.79544680067017</v>
+        <v>13.79544583620464</v>
       </c>
       <c r="F606" t="n">
         <v>2165600</v>
@@ -12592,16 +12592,16 @@
         <v>44987</v>
       </c>
       <c r="B609" t="n">
-        <v>13.29379367828369</v>
+        <v>13.29379272460938</v>
       </c>
       <c r="C609" t="n">
-        <v>13.69897469913348</v>
+        <v>13.69897371639216</v>
       </c>
       <c r="D609" t="n">
-        <v>13.23591120103394</v>
+        <v>13.23591025151202</v>
       </c>
       <c r="E609" t="n">
-        <v>13.48673680249183</v>
+        <v>13.4867358349761</v>
       </c>
       <c r="F609" t="n">
         <v>2574150</v>
@@ -12632,16 +12632,16 @@
         <v>44991</v>
       </c>
       <c r="B611" t="n">
-        <v>14.12344932556152</v>
+        <v>14.12345027923584</v>
       </c>
       <c r="C611" t="n">
-        <v>14.25850904133613</v>
+        <v>14.25851000413024</v>
       </c>
       <c r="D611" t="n">
-        <v>13.35167597246616</v>
+        <v>13.35167687402712</v>
       </c>
       <c r="E611" t="n">
-        <v>13.35167597246616</v>
+        <v>13.35167687402712</v>
       </c>
       <c r="F611" t="n">
         <v>2062900</v>
@@ -12712,16 +12712,16 @@
         <v>44995</v>
       </c>
       <c r="B615" t="n">
-        <v>15.43546485900879</v>
+        <v>15.43546390533447</v>
       </c>
       <c r="C615" t="n">
-        <v>15.97570561385987</v>
+        <v>15.97570462680699</v>
       </c>
       <c r="D615" t="n">
-        <v>15.33899283562982</v>
+        <v>15.33899188791599</v>
       </c>
       <c r="E615" t="n">
-        <v>15.97570561385987</v>
+        <v>15.97570462680699</v>
       </c>
       <c r="F615" t="n">
         <v>1980300</v>
@@ -12752,16 +12752,16 @@
         <v>44999</v>
       </c>
       <c r="B617" t="n">
-        <v>14.97240161895752</v>
+        <v>14.9724006652832</v>
       </c>
       <c r="C617" t="n">
-        <v>15.89852864361015</v>
+        <v>15.89852763094573</v>
       </c>
       <c r="D617" t="n">
-        <v>14.77945756879614</v>
+        <v>14.77945662741149</v>
       </c>
       <c r="E617" t="n">
-        <v>15.53193715636452</v>
+        <v>15.53193616705032</v>
       </c>
       <c r="F617" t="n">
         <v>2100150</v>
@@ -12792,16 +12792,16 @@
         <v>45001</v>
       </c>
       <c r="B619" t="n">
-        <v>15.76346874237061</v>
+        <v>15.76346778869629</v>
       </c>
       <c r="C619" t="n">
-        <v>15.91782324481321</v>
+        <v>15.9178222818006</v>
       </c>
       <c r="D619" t="n">
-        <v>15.20393321100345</v>
+        <v>15.20393229118048</v>
       </c>
       <c r="E619" t="n">
-        <v>15.28111046222475</v>
+        <v>15.28110953773264</v>
       </c>
       <c r="F619" t="n">
         <v>2813350</v>
@@ -12812,16 +12812,16 @@
         <v>45002</v>
       </c>
       <c r="B620" t="n">
-        <v>15.24252223968506</v>
+        <v>15.24252128601074</v>
       </c>
       <c r="C620" t="n">
-        <v>15.80205686582306</v>
+        <v>15.80205587714051</v>
       </c>
       <c r="D620" t="n">
-        <v>15.14605021309463</v>
+        <v>15.14604926545625</v>
       </c>
       <c r="E620" t="n">
-        <v>15.80205686582306</v>
+        <v>15.80205587714051</v>
       </c>
       <c r="F620" t="n">
         <v>4012850</v>
@@ -12872,16 +12872,16 @@
         <v>45007</v>
       </c>
       <c r="B623" t="n">
-        <v>14.37427616119385</v>
+        <v>14.37427520751953</v>
       </c>
       <c r="C623" t="n">
-        <v>14.85663443398593</v>
+        <v>14.85663344830912</v>
       </c>
       <c r="D623" t="n">
-        <v>13.83403541088094</v>
+        <v>13.83403449304938</v>
       </c>
       <c r="E623" t="n">
-        <v>13.85332926337942</v>
+        <v>13.85332834426779</v>
       </c>
       <c r="F623" t="n">
         <v>2838400</v>
@@ -12932,16 +12932,16 @@
         <v>45012</v>
       </c>
       <c r="B626" t="n">
-        <v>13.98839092254639</v>
+        <v>13.98838996887207</v>
       </c>
       <c r="C626" t="n">
-        <v>14.12345157990428</v>
+        <v>14.12345061702205</v>
       </c>
       <c r="D626" t="n">
-        <v>13.56391601660446</v>
+        <v>13.5639150918692</v>
       </c>
       <c r="E626" t="n">
-        <v>13.83403641129478</v>
+        <v>13.83403546814375</v>
       </c>
       <c r="F626" t="n">
         <v>1142000</v>
@@ -12972,16 +12972,16 @@
         <v>45014</v>
       </c>
       <c r="B628" t="n">
-        <v>14.14274501800537</v>
+        <v>14.14274406433105</v>
       </c>
       <c r="C628" t="n">
-        <v>14.41286540475423</v>
+        <v>14.41286443286514</v>
       </c>
       <c r="D628" t="n">
-        <v>13.75685875122129</v>
+        <v>13.75685782356807</v>
       </c>
       <c r="E628" t="n">
-        <v>14.41286540475423</v>
+        <v>14.41286443286514</v>
       </c>
       <c r="F628" t="n">
         <v>1398800</v>
@@ -13092,16 +13092,16 @@
         <v>45022</v>
       </c>
       <c r="B634" t="n">
-        <v>14.14274501800537</v>
+        <v>14.14274406433105</v>
       </c>
       <c r="C634" t="n">
-        <v>14.297099524719</v>
+        <v>14.29709856063625</v>
       </c>
       <c r="D634" t="n">
-        <v>13.77615260454778</v>
+        <v>13.77615167559354</v>
       </c>
       <c r="E634" t="n">
-        <v>13.85332985790459</v>
+        <v>13.85332892374614</v>
       </c>
       <c r="F634" t="n">
         <v>1739850</v>
@@ -13152,16 +13152,16 @@
         <v>45028</v>
       </c>
       <c r="B637" t="n">
-        <v>15.454758644104</v>
+        <v>15.45475959777832</v>
       </c>
       <c r="C637" t="n">
-        <v>15.78276239860189</v>
+        <v>15.7827633725165</v>
       </c>
       <c r="D637" t="n">
-        <v>15.14604874103375</v>
+        <v>15.14604967565836</v>
       </c>
       <c r="E637" t="n">
-        <v>15.31969800400918</v>
+        <v>15.31969894934925</v>
       </c>
       <c r="F637" t="n">
         <v>3667400</v>
@@ -13172,16 +13172,16 @@
         <v>45029</v>
       </c>
       <c r="B638" t="n">
-        <v>15.70558643341064</v>
+        <v>15.70558547973633</v>
       </c>
       <c r="C638" t="n">
-        <v>15.93711818957249</v>
+        <v>15.93711722183911</v>
       </c>
       <c r="D638" t="n">
-        <v>15.10746134995442</v>
+        <v>15.10746043259944</v>
       </c>
       <c r="E638" t="n">
-        <v>15.49334761022416</v>
+        <v>15.49334666943741</v>
       </c>
       <c r="F638" t="n">
         <v>2173500</v>
@@ -13292,16 +13292,16 @@
         <v>45040</v>
       </c>
       <c r="B644" t="n">
-        <v>14.74086856842041</v>
+        <v>14.74086761474609</v>
       </c>
       <c r="C644" t="n">
-        <v>15.08816711387082</v>
+        <v>15.0881661377277</v>
       </c>
       <c r="D644" t="n">
-        <v>14.62510269327874</v>
+        <v>14.62510174709401</v>
       </c>
       <c r="E644" t="n">
-        <v>14.93381169365653</v>
+        <v>14.93381072749958</v>
       </c>
       <c r="F644" t="n">
         <v>897550</v>
@@ -13372,16 +13372,16 @@
         <v>45044</v>
       </c>
       <c r="B648" t="n">
-        <v>14.79875183105469</v>
+        <v>14.79875087738037</v>
       </c>
       <c r="C648" t="n">
-        <v>14.856634308085</v>
+        <v>14.85663335068057</v>
       </c>
       <c r="D648" t="n">
-        <v>14.33568741468527</v>
+        <v>14.33568649085217</v>
       </c>
       <c r="E648" t="n">
-        <v>14.83734045575002</v>
+        <v>14.83733949958894</v>
       </c>
       <c r="F648" t="n">
         <v>3490000</v>
@@ -13412,16 +13412,16 @@
         <v>45049</v>
       </c>
       <c r="B650" t="n">
-        <v>14.74086856842041</v>
+        <v>14.74086761474609</v>
       </c>
       <c r="C650" t="n">
-        <v>14.81804581851486</v>
+        <v>14.81804485984749</v>
       </c>
       <c r="D650" t="n">
-        <v>14.21992167027019</v>
+        <v>14.21992075029902</v>
       </c>
       <c r="E650" t="n">
-        <v>14.43215956804262</v>
+        <v>14.43215863434052</v>
       </c>
       <c r="F650" t="n">
         <v>2516550</v>
@@ -29752,19 +29752,39 @@
         <v>46246</v>
       </c>
       <c r="B1467" t="n">
-        <v>6.21</v>
+        <v>6.210000038146973</v>
       </c>
       <c r="C1467" t="n">
-        <v>6.27</v>
+        <v>6.269999980926514</v>
       </c>
       <c r="D1467" t="n">
-        <v>6.08</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="E1467" t="n">
         <v>6.25</v>
       </c>
       <c r="F1467" t="n">
         <v>2934800</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>2594900</v>
       </c>
     </row>
   </sheetData>

--- a/database/SIMH3.xlsx
+++ b/database/SIMH3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1468"/>
+  <dimension ref="A1:F1470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44095</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59559535980225</v>
+        <v>12.59559631347656</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80832864589193</v>
+        <v>12.80832961567333</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45377316907579</v>
+        <v>12.45377411201205</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46706847112706</v>
+        <v>12.46706941506998</v>
       </c>
       <c r="F3" t="n">
         <v>1323800</v>
@@ -552,16 +552,16 @@
         <v>44099</v>
       </c>
       <c r="B7" t="n">
-        <v>12.36513614654541</v>
+        <v>12.36513519287109</v>
       </c>
       <c r="C7" t="n">
-        <v>12.49366305880876</v>
+        <v>12.49366209522167</v>
       </c>
       <c r="D7" t="n">
-        <v>12.3208164924778</v>
+        <v>12.32081554222169</v>
       </c>
       <c r="E7" t="n">
-        <v>12.45377545468063</v>
+        <v>12.45377449416991</v>
       </c>
       <c r="F7" t="n">
         <v>1068200</v>
@@ -672,16 +672,16 @@
         <v>44109</v>
       </c>
       <c r="B13" t="n">
-        <v>11.6560230255127</v>
+        <v>11.65602397918701</v>
       </c>
       <c r="C13" t="n">
-        <v>11.6560230255127</v>
+        <v>11.65602397918701</v>
       </c>
       <c r="D13" t="n">
-        <v>11.12862181655362</v>
+        <v>11.12862272707694</v>
       </c>
       <c r="E13" t="n">
-        <v>11.43442562316206</v>
+        <v>11.43442655870568</v>
       </c>
       <c r="F13" t="n">
         <v>595400</v>
@@ -692,16 +692,16 @@
         <v>44110</v>
       </c>
       <c r="B14" t="n">
-        <v>11.43885803222656</v>
+        <v>11.43885707855225</v>
       </c>
       <c r="C14" t="n">
-        <v>12.05489940494884</v>
+        <v>12.05489839991425</v>
       </c>
       <c r="D14" t="n">
-        <v>11.38124307774816</v>
+        <v>11.38124212887729</v>
       </c>
       <c r="E14" t="n">
-        <v>11.58954433818795</v>
+        <v>11.5895433719507</v>
       </c>
       <c r="F14" t="n">
         <v>472800</v>
@@ -732,16 +732,16 @@
         <v>44112</v>
       </c>
       <c r="B16" t="n">
-        <v>11.52306365966797</v>
+        <v>11.52306461334229</v>
       </c>
       <c r="C16" t="n">
-        <v>11.90421142045391</v>
+        <v>11.90421240567286</v>
       </c>
       <c r="D16" t="n">
-        <v>11.39010557095641</v>
+        <v>11.39010651362682</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68261404238337</v>
+        <v>11.68261500926243</v>
       </c>
       <c r="F16" t="n">
         <v>595200</v>
@@ -792,16 +792,16 @@
         <v>44118</v>
       </c>
       <c r="B19" t="n">
-        <v>12.1302433013916</v>
+        <v>12.13024234771729</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63105310519763</v>
+        <v>12.63105211214986</v>
       </c>
       <c r="D19" t="n">
-        <v>12.00614844025086</v>
+        <v>12.00614749633282</v>
       </c>
       <c r="E19" t="n">
-        <v>12.18785825940122</v>
+        <v>12.18785730119724</v>
       </c>
       <c r="F19" t="n">
         <v>441800</v>
@@ -812,16 +812,16 @@
         <v>44119</v>
       </c>
       <c r="B20" t="n">
-        <v>11.9795560836792</v>
+        <v>11.97955703735352</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39615859870633</v>
+        <v>12.39615958554575</v>
       </c>
       <c r="D20" t="n">
-        <v>11.78011807996524</v>
+        <v>11.7801190177626</v>
       </c>
       <c r="E20" t="n">
-        <v>12.0283069382216</v>
+        <v>12.02830789577689</v>
       </c>
       <c r="F20" t="n">
         <v>483400</v>
@@ -852,16 +852,16 @@
         <v>44123</v>
       </c>
       <c r="B22" t="n">
-        <v>12.53798198699951</v>
+        <v>12.53798294067383</v>
       </c>
       <c r="C22" t="n">
-        <v>12.78617085195148</v>
+        <v>12.78617182450374</v>
       </c>
       <c r="D22" t="n">
-        <v>12.30752047545202</v>
+        <v>12.30752141159678</v>
       </c>
       <c r="E22" t="n">
-        <v>12.40945508217713</v>
+        <v>12.40945602607532</v>
       </c>
       <c r="F22" t="n">
         <v>521200</v>
@@ -872,16 +872,16 @@
         <v>44124</v>
       </c>
       <c r="B23" t="n">
-        <v>12.8526496887207</v>
+        <v>12.85264873504639</v>
       </c>
       <c r="C23" t="n">
-        <v>12.87037788715177</v>
+        <v>12.87037693216201</v>
       </c>
       <c r="D23" t="n">
-        <v>12.41388692147603</v>
+        <v>12.41388600035818</v>
       </c>
       <c r="E23" t="n">
-        <v>12.53798177451245</v>
+        <v>12.53798084418668</v>
       </c>
       <c r="F23" t="n">
         <v>729200</v>
@@ -892,16 +892,16 @@
         <v>44125</v>
       </c>
       <c r="B24" t="n">
-        <v>12.8526496887207</v>
+        <v>12.85264873504639</v>
       </c>
       <c r="C24" t="n">
-        <v>12.94572019450274</v>
+        <v>12.94571923392254</v>
       </c>
       <c r="D24" t="n">
-        <v>12.51138947686584</v>
+        <v>12.51138854851324</v>
       </c>
       <c r="E24" t="n">
-        <v>12.8526496887207</v>
+        <v>12.85264873504639</v>
       </c>
       <c r="F24" t="n">
         <v>501200</v>
@@ -912,16 +912,16 @@
         <v>44126</v>
       </c>
       <c r="B25" t="n">
-        <v>13.06981563568115</v>
+        <v>13.06981468200684</v>
       </c>
       <c r="C25" t="n">
-        <v>13.21163784820361</v>
+        <v>13.21163688418085</v>
       </c>
       <c r="D25" t="n">
-        <v>12.69753190514617</v>
+        <v>12.69753097863653</v>
       </c>
       <c r="E25" t="n">
-        <v>12.75071565750562</v>
+        <v>12.75071472711529</v>
       </c>
       <c r="F25" t="n">
         <v>963600</v>
@@ -932,16 +932,16 @@
         <v>44127</v>
       </c>
       <c r="B26" t="n">
-        <v>12.94128894805908</v>
+        <v>12.94128799438477</v>
       </c>
       <c r="C26" t="n">
-        <v>13.18061370880962</v>
+        <v>13.18061273749889</v>
       </c>
       <c r="D26" t="n">
-        <v>12.86151374603323</v>
+        <v>12.86151279823773</v>
       </c>
       <c r="E26" t="n">
-        <v>13.08754320333081</v>
+        <v>13.08754223887867</v>
       </c>
       <c r="F26" t="n">
         <v>543600</v>
@@ -952,16 +952,16 @@
         <v>44130</v>
       </c>
       <c r="B27" t="n">
-        <v>12.60002899169922</v>
+        <v>12.6000280380249</v>
       </c>
       <c r="C27" t="n">
-        <v>12.87480930941692</v>
+        <v>12.87480833494496</v>
       </c>
       <c r="D27" t="n">
-        <v>12.41831918133934</v>
+        <v>12.41831824141832</v>
       </c>
       <c r="E27" t="n">
-        <v>12.84821785664712</v>
+        <v>12.84821688418782</v>
       </c>
       <c r="F27" t="n">
         <v>307600</v>
@@ -972,16 +972,16 @@
         <v>44131</v>
       </c>
       <c r="B28" t="n">
-        <v>12.22774600982666</v>
+        <v>12.22774410247803</v>
       </c>
       <c r="C28" t="n">
-        <v>12.77730752376721</v>
+        <v>12.77730553069506</v>
       </c>
       <c r="D28" t="n">
-        <v>12.19229045555073</v>
+        <v>12.19228855373264</v>
       </c>
       <c r="E28" t="n">
-        <v>12.67537291088978</v>
+        <v>12.67537093371793</v>
       </c>
       <c r="F28" t="n">
         <v>652400</v>
@@ -992,16 +992,16 @@
         <v>44132</v>
       </c>
       <c r="B29" t="n">
-        <v>11.43885803222656</v>
+        <v>11.43885707855225</v>
       </c>
       <c r="C29" t="n">
-        <v>11.92637250178829</v>
+        <v>11.92637150746918</v>
       </c>
       <c r="D29" t="n">
-        <v>11.3014678751419</v>
+        <v>11.301466932922</v>
       </c>
       <c r="E29" t="n">
-        <v>11.92637250178829</v>
+        <v>11.92637150746918</v>
       </c>
       <c r="F29" t="n">
         <v>860400</v>
@@ -1012,16 +1012,16 @@
         <v>44133</v>
       </c>
       <c r="B30" t="n">
-        <v>11.70477390289307</v>
+        <v>11.70477676391602</v>
       </c>
       <c r="C30" t="n">
-        <v>11.87761959408865</v>
+        <v>11.87762249736064</v>
       </c>
       <c r="D30" t="n">
-        <v>11.00895824360864</v>
+        <v>11.00896093455188</v>
       </c>
       <c r="E30" t="n">
-        <v>11.3945372232491</v>
+        <v>11.39454000844023</v>
       </c>
       <c r="F30" t="n">
         <v>683400</v>
@@ -1032,16 +1032,16 @@
         <v>44134</v>
       </c>
       <c r="B31" t="n">
-        <v>11.38567543029785</v>
+        <v>11.38567447662354</v>
       </c>
       <c r="C31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.81114107243664</v>
       </c>
       <c r="D31" t="n">
-        <v>11.00895965537159</v>
+        <v>11.00895873325132</v>
       </c>
       <c r="E31" t="n">
-        <v>11.81114206174842</v>
+        <v>11.81114107243664</v>
       </c>
       <c r="F31" t="n">
         <v>907200</v>
@@ -1092,16 +1092,16 @@
         <v>44140</v>
       </c>
       <c r="B34" t="n">
-        <v>12.79503440856934</v>
+        <v>12.79503631591797</v>
       </c>
       <c r="C34" t="n">
-        <v>13.02992711450884</v>
+        <v>13.0299290568728</v>
       </c>
       <c r="D34" t="n">
-        <v>12.63991605755662</v>
+        <v>12.63991794178185</v>
       </c>
       <c r="E34" t="n">
-        <v>12.78617030957958</v>
+        <v>12.78617221560685</v>
       </c>
       <c r="F34" t="n">
         <v>682600</v>
@@ -1112,16 +1112,16 @@
         <v>44141</v>
       </c>
       <c r="B35" t="n">
-        <v>13.55733013153076</v>
+        <v>13.55733108520508</v>
       </c>
       <c r="C35" t="n">
-        <v>13.69472029430994</v>
+        <v>13.6947212576488</v>
       </c>
       <c r="D35" t="n">
-        <v>12.65764430809807</v>
+        <v>12.65764519848505</v>
       </c>
       <c r="E35" t="n">
-        <v>12.74185156382011</v>
+        <v>12.74185246013055</v>
       </c>
       <c r="F35" t="n">
         <v>948200</v>
@@ -1132,16 +1132,16 @@
         <v>44144</v>
       </c>
       <c r="B36" t="n">
-        <v>13.29584407806396</v>
+        <v>13.29584503173828</v>
       </c>
       <c r="C36" t="n">
-        <v>13.96950038089769</v>
+        <v>13.96950138289152</v>
       </c>
       <c r="D36" t="n">
-        <v>13.12299837555377</v>
+        <v>13.12299931683034</v>
       </c>
       <c r="E36" t="n">
-        <v>13.7390388806661</v>
+        <v>13.73903986612956</v>
       </c>
       <c r="F36" t="n">
         <v>650800</v>
@@ -1152,16 +1152,16 @@
         <v>44145</v>
       </c>
       <c r="B37" t="n">
-        <v>13.15845489501953</v>
+        <v>13.15845394134521</v>
       </c>
       <c r="C37" t="n">
-        <v>13.57948948130297</v>
+        <v>13.57948849711368</v>
       </c>
       <c r="D37" t="n">
-        <v>13.07867968942368</v>
+        <v>13.07867874153117</v>
       </c>
       <c r="E37" t="n">
-        <v>13.07867968942368</v>
+        <v>13.07867874153117</v>
       </c>
       <c r="F37" t="n">
         <v>489600</v>
@@ -1172,16 +1172,16 @@
         <v>44146</v>
       </c>
       <c r="B38" t="n">
-        <v>13.29584407806396</v>
+        <v>13.29584503173828</v>
       </c>
       <c r="C38" t="n">
-        <v>13.41993892711028</v>
+        <v>13.41993988968558</v>
       </c>
       <c r="D38" t="n">
-        <v>12.89696892478745</v>
+        <v>12.89696984985155</v>
       </c>
       <c r="E38" t="n">
-        <v>13.25152442873835</v>
+        <v>13.25152537923374</v>
       </c>
       <c r="F38" t="n">
         <v>586400</v>
@@ -1192,16 +1192,16 @@
         <v>44147</v>
       </c>
       <c r="B39" t="n">
-        <v>12.94128894805908</v>
+        <v>12.94128799438477</v>
       </c>
       <c r="C39" t="n">
-        <v>13.35345941631429</v>
+        <v>13.35345843226615</v>
       </c>
       <c r="D39" t="n">
-        <v>12.7507150421811</v>
+        <v>12.75071410255063</v>
       </c>
       <c r="E39" t="n">
-        <v>13.12299875475041</v>
+        <v>13.12299778768546</v>
       </c>
       <c r="F39" t="n">
         <v>656600</v>
@@ -1272,16 +1272,16 @@
         <v>44153</v>
       </c>
       <c r="B43" t="n">
-        <v>12.74185180664062</v>
+        <v>12.74184989929199</v>
       </c>
       <c r="C43" t="n">
-        <v>13.18947870198273</v>
+        <v>13.18947672762809</v>
       </c>
       <c r="D43" t="n">
-        <v>12.66207659920759</v>
+        <v>12.66207470380063</v>
       </c>
       <c r="E43" t="n">
-        <v>13.11413554444342</v>
+        <v>13.11413358136703</v>
       </c>
       <c r="F43" t="n">
         <v>532400</v>
@@ -1292,16 +1292,16 @@
         <v>44154</v>
       </c>
       <c r="B44" t="n">
-        <v>12.99447154998779</v>
+        <v>12.99447250366211</v>
       </c>
       <c r="C44" t="n">
-        <v>13.07424675015632</v>
+        <v>13.0742477096854</v>
       </c>
       <c r="D44" t="n">
-        <v>12.4803656437095</v>
+        <v>12.48036655965319</v>
       </c>
       <c r="E44" t="n">
-        <v>12.74185064633879</v>
+        <v>12.74185158147306</v>
       </c>
       <c r="F44" t="n">
         <v>711400</v>
@@ -1352,16 +1352,16 @@
         <v>44160</v>
       </c>
       <c r="B47" t="n">
-        <v>13.65040016174316</v>
+        <v>13.65039920806885</v>
       </c>
       <c r="C47" t="n">
-        <v>13.77449501605975</v>
+        <v>13.77449405371565</v>
       </c>
       <c r="D47" t="n">
-        <v>13.34016429394225</v>
+        <v>13.34016336194231</v>
       </c>
       <c r="E47" t="n">
-        <v>13.61494460984229</v>
+        <v>13.61494365864504</v>
       </c>
       <c r="F47" t="n">
         <v>724200</v>
@@ -1392,16 +1392,16 @@
         <v>44162</v>
       </c>
       <c r="B49" t="n">
-        <v>13.39334678649902</v>
+        <v>13.39334869384766</v>
       </c>
       <c r="C49" t="n">
-        <v>13.71687963861983</v>
+        <v>13.71688159204283</v>
       </c>
       <c r="D49" t="n">
-        <v>13.38891473698208</v>
+        <v>13.38891664369954</v>
       </c>
       <c r="E49" t="n">
-        <v>13.53073778554325</v>
+        <v>13.53073971245775</v>
       </c>
       <c r="F49" t="n">
         <v>510000</v>
@@ -1412,16 +1412,16 @@
         <v>44165</v>
       </c>
       <c r="B50" t="n">
-        <v>13.13629341125488</v>
+        <v>13.13629531860352</v>
       </c>
       <c r="C50" t="n">
-        <v>13.73017450228043</v>
+        <v>13.73017649585873</v>
       </c>
       <c r="D50" t="n">
-        <v>13.13629341125488</v>
+        <v>13.13629531860352</v>
       </c>
       <c r="E50" t="n">
-        <v>13.38891430834409</v>
+        <v>13.38891625237249</v>
       </c>
       <c r="F50" t="n">
         <v>1093200</v>
@@ -1472,16 +1472,16 @@
         <v>44168</v>
       </c>
       <c r="B53" t="n">
-        <v>14.3595142364502</v>
+        <v>14.35951328277588</v>
       </c>
       <c r="C53" t="n">
-        <v>14.44372065177874</v>
+        <v>14.44371969251193</v>
       </c>
       <c r="D53" t="n">
-        <v>14.05814074905197</v>
+        <v>14.0581398153931</v>
       </c>
       <c r="E53" t="n">
-        <v>14.31519373576078</v>
+        <v>14.31519278502997</v>
       </c>
       <c r="F53" t="n">
         <v>1033200</v>
@@ -1512,16 +1512,16 @@
         <v>44172</v>
       </c>
       <c r="B55" t="n">
-        <v>14.25314521789551</v>
+        <v>14.25314712524414</v>
       </c>
       <c r="C55" t="n">
-        <v>14.36837512619167</v>
+        <v>14.36837704896031</v>
       </c>
       <c r="D55" t="n">
-        <v>13.82767860020407</v>
+        <v>13.82768045061698</v>
       </c>
       <c r="E55" t="n">
-        <v>14.06257131172358</v>
+        <v>14.06257319356971</v>
       </c>
       <c r="F55" t="n">
         <v>782600</v>
@@ -1532,16 +1532,16 @@
         <v>44173</v>
       </c>
       <c r="B56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="C56" t="n">
-        <v>14.53679034258752</v>
+        <v>14.53678935892345</v>
       </c>
       <c r="D56" t="n">
-        <v>13.89859038475245</v>
+        <v>13.89858944427358</v>
       </c>
       <c r="E56" t="n">
-        <v>14.09359550476074</v>
+        <v>14.09359455108643</v>
       </c>
       <c r="F56" t="n">
         <v>767200</v>
@@ -1552,16 +1552,16 @@
         <v>44174</v>
       </c>
       <c r="B57" t="n">
-        <v>13.88972473144531</v>
+        <v>13.88972663879395</v>
       </c>
       <c r="C57" t="n">
-        <v>14.24871311856489</v>
+        <v>14.24871507521011</v>
       </c>
       <c r="D57" t="n">
-        <v>13.65926323867578</v>
+        <v>13.65926511437724</v>
       </c>
       <c r="E57" t="n">
-        <v>14.14677767481842</v>
+        <v>14.14677961746578</v>
       </c>
       <c r="F57" t="n">
         <v>570800</v>
@@ -1572,16 +1572,16 @@
         <v>44175</v>
       </c>
       <c r="B58" t="n">
-        <v>14.00495624542236</v>
+        <v>14.00495529174805</v>
       </c>
       <c r="C58" t="n">
-        <v>14.10245879986408</v>
+        <v>14.10245783955028</v>
       </c>
       <c r="D58" t="n">
-        <v>13.51744178255972</v>
+        <v>13.51744086208294</v>
       </c>
       <c r="E58" t="n">
-        <v>13.88529344315728</v>
+        <v>13.88529249763146</v>
       </c>
       <c r="F58" t="n">
         <v>539600</v>
@@ -1632,16 +1632,16 @@
         <v>44180</v>
       </c>
       <c r="B61" t="n">
-        <v>14.08473014831543</v>
+        <v>14.08473205566406</v>
       </c>
       <c r="C61" t="n">
-        <v>14.12461774539281</v>
+        <v>14.124619658143</v>
       </c>
       <c r="D61" t="n">
-        <v>13.57062428079252</v>
+        <v>13.57062611852114</v>
       </c>
       <c r="E61" t="n">
-        <v>13.75676611871129</v>
+        <v>13.75676798164717</v>
       </c>
       <c r="F61" t="n">
         <v>732800</v>
@@ -1652,16 +1652,16 @@
         <v>44181</v>
       </c>
       <c r="B62" t="n">
-        <v>13.9163179397583</v>
+        <v>13.91631698608398</v>
       </c>
       <c r="C62" t="n">
-        <v>14.1778029654802</v>
+        <v>14.17780199388652</v>
       </c>
       <c r="D62" t="n">
-        <v>13.71688076705103</v>
+        <v>13.71687982704398</v>
       </c>
       <c r="E62" t="n">
-        <v>14.13791536187333</v>
+        <v>14.13791439301312</v>
       </c>
       <c r="F62" t="n">
         <v>564600</v>
@@ -1712,16 +1712,16 @@
         <v>44186</v>
       </c>
       <c r="B65" t="n">
-        <v>13.14959239959717</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="C65" t="n">
-        <v>13.34016633725218</v>
+        <v>13.3401644022608</v>
       </c>
       <c r="D65" t="n">
-        <v>12.76844452428714</v>
+        <v>12.76844267222401</v>
       </c>
       <c r="E65" t="n">
-        <v>13.14959239959717</v>
+        <v>13.14959049224854</v>
       </c>
       <c r="F65" t="n">
         <v>872000</v>
@@ -1752,16 +1752,16 @@
         <v>44188</v>
       </c>
       <c r="B67" t="n">
-        <v>14.04484558105469</v>
+        <v>14.04484367370605</v>
       </c>
       <c r="C67" t="n">
-        <v>14.1512122477646</v>
+        <v>14.15121032597093</v>
       </c>
       <c r="D67" t="n">
-        <v>13.40221268535595</v>
+        <v>13.40221086527954</v>
       </c>
       <c r="E67" t="n">
-        <v>13.45539644137447</v>
+        <v>13.45539461407549</v>
       </c>
       <c r="F67" t="n">
         <v>2040000</v>
@@ -1792,16 +1792,16 @@
         <v>44194</v>
       </c>
       <c r="B69" t="n">
-        <v>15.19715023040771</v>
+        <v>15.19715213775635</v>
       </c>
       <c r="C69" t="n">
-        <v>15.34783653134916</v>
+        <v>15.34783845760998</v>
       </c>
       <c r="D69" t="n">
-        <v>14.74952253173429</v>
+        <v>14.74952438290252</v>
       </c>
       <c r="E69" t="n">
-        <v>15.13510322837077</v>
+        <v>15.13510512793207</v>
       </c>
       <c r="F69" t="n">
         <v>1536600</v>
@@ -1812,16 +1812,16 @@
         <v>44195</v>
       </c>
       <c r="B70" t="n">
-        <v>15.72012138366699</v>
+        <v>15.72011947631836</v>
       </c>
       <c r="C70" t="n">
-        <v>15.9151265029923</v>
+        <v>15.91512457198337</v>
       </c>
       <c r="D70" t="n">
-        <v>15.2503342485805</v>
+        <v>15.25033239823193</v>
       </c>
       <c r="E70" t="n">
-        <v>15.37886115685711</v>
+        <v>15.37885929091415</v>
       </c>
       <c r="F70" t="n">
         <v>2946000</v>
@@ -1832,16 +1832,16 @@
         <v>44200</v>
       </c>
       <c r="B71" t="n">
-        <v>14.98884773254395</v>
+        <v>14.98885059356689</v>
       </c>
       <c r="C71" t="n">
-        <v>15.94171721175532</v>
+        <v>15.94172025465893</v>
       </c>
       <c r="D71" t="n">
-        <v>14.74952213906937</v>
+        <v>14.74952495441062</v>
       </c>
       <c r="E71" t="n">
-        <v>15.91069371156276</v>
+        <v>15.9106967485447</v>
       </c>
       <c r="F71" t="n">
         <v>2835800</v>
@@ -1852,16 +1852,16 @@
         <v>44201</v>
       </c>
       <c r="B72" t="n">
-        <v>15.13953495025635</v>
+        <v>15.13953399658203</v>
       </c>
       <c r="C72" t="n">
-        <v>15.45863576096341</v>
+        <v>15.45863478718819</v>
       </c>
       <c r="D72" t="n">
-        <v>14.36394401696318</v>
+        <v>14.36394311214514</v>
       </c>
       <c r="E72" t="n">
-        <v>14.84702643732623</v>
+        <v>14.8470255020777</v>
       </c>
       <c r="F72" t="n">
         <v>1878200</v>
@@ -1872,16 +1872,16 @@
         <v>44202</v>
       </c>
       <c r="B73" t="n">
-        <v>14.58997344970703</v>
+        <v>14.58997249603271</v>
       </c>
       <c r="C73" t="n">
-        <v>15.28135801482809</v>
+        <v>15.28135701596139</v>
       </c>
       <c r="D73" t="n">
-        <v>14.58997344970703</v>
+        <v>14.58997249603271</v>
       </c>
       <c r="E73" t="n">
-        <v>15.1395358000321</v>
+        <v>15.13953481043562</v>
       </c>
       <c r="F73" t="n">
         <v>1708600</v>
@@ -1892,16 +1892,16 @@
         <v>44203</v>
       </c>
       <c r="B74" t="n">
-        <v>14.40513038635254</v>
+        <v>14.40513134002686</v>
       </c>
       <c r="C74" t="n">
-        <v>14.96995047062398</v>
+        <v>14.96995146169153</v>
       </c>
       <c r="D74" t="n">
-        <v>14.39623538149606</v>
+        <v>14.39623633458149</v>
       </c>
       <c r="E74" t="n">
-        <v>14.68531710141131</v>
+        <v>14.68531807363505</v>
       </c>
       <c r="F74" t="n">
         <v>1215000</v>
@@ -1912,16 +1912,16 @@
         <v>44204</v>
       </c>
       <c r="B75" t="n">
-        <v>15.06334400177002</v>
+        <v>15.06334686279297</v>
       </c>
       <c r="C75" t="n">
-        <v>15.27237235405728</v>
+        <v>15.27237525478156</v>
       </c>
       <c r="D75" t="n">
-        <v>14.38733896781096</v>
+        <v>14.38734170043839</v>
       </c>
       <c r="E75" t="n">
-        <v>14.38733896781096</v>
+        <v>14.38734170043839</v>
       </c>
       <c r="F75" t="n">
         <v>1077600</v>
@@ -1952,16 +1952,16 @@
         <v>44208</v>
       </c>
       <c r="B77" t="n">
-        <v>15.99285221099854</v>
+        <v>15.99285411834717</v>
       </c>
       <c r="C77" t="n">
-        <v>16.31306559830687</v>
+        <v>16.31306754384497</v>
       </c>
       <c r="D77" t="n">
-        <v>15.34353212811103</v>
+        <v>15.34353395802008</v>
       </c>
       <c r="E77" t="n">
-        <v>15.90390385935192</v>
+        <v>15.90390575609234</v>
       </c>
       <c r="F77" t="n">
         <v>2193200</v>
@@ -2012,16 +2012,16 @@
         <v>44211</v>
       </c>
       <c r="B80" t="n">
-        <v>15.88167095184326</v>
+        <v>15.881667137146</v>
       </c>
       <c r="C80" t="n">
-        <v>16.09069937316902</v>
+        <v>16.09069550826418</v>
       </c>
       <c r="D80" t="n">
-        <v>15.61037917860321</v>
+        <v>15.61037542906886</v>
       </c>
       <c r="E80" t="n">
-        <v>16.0862510214328</v>
+        <v>16.08624715759644</v>
       </c>
       <c r="F80" t="n">
         <v>728000</v>
@@ -2032,16 +2032,16 @@
         <v>44214</v>
       </c>
       <c r="B81" t="n">
-        <v>16.38422775268555</v>
+        <v>16.38422203063965</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45538611125061</v>
+        <v>16.45538036435329</v>
       </c>
       <c r="D81" t="n">
-        <v>15.92169757373807</v>
+        <v>15.92169201322673</v>
       </c>
       <c r="E81" t="n">
-        <v>15.93504093234652</v>
+        <v>15.93503536717513</v>
       </c>
       <c r="F81" t="n">
         <v>883000</v>
@@ -2052,16 +2052,16 @@
         <v>44215</v>
       </c>
       <c r="B82" t="n">
-        <v>16.63327789306641</v>
+        <v>16.63327598571777</v>
       </c>
       <c r="C82" t="n">
-        <v>17.07801792553825</v>
+        <v>17.07801596719099</v>
       </c>
       <c r="D82" t="n">
-        <v>16.09514116439855</v>
+        <v>16.0951393187584</v>
       </c>
       <c r="E82" t="n">
-        <v>17.07801792553825</v>
+        <v>17.07801596719099</v>
       </c>
       <c r="F82" t="n">
         <v>1918400</v>
@@ -2072,16 +2072,16 @@
         <v>44216</v>
       </c>
       <c r="B83" t="n">
-        <v>16.25524711608887</v>
+        <v>16.25525093078613</v>
       </c>
       <c r="C83" t="n">
-        <v>16.81117213166337</v>
+        <v>16.81117607682225</v>
       </c>
       <c r="D83" t="n">
-        <v>16.01064044854579</v>
+        <v>16.01064420584002</v>
       </c>
       <c r="E83" t="n">
-        <v>16.69998712854847</v>
+        <v>16.69999104761502</v>
       </c>
       <c r="F83" t="n">
         <v>1073000</v>
@@ -2092,16 +2092,16 @@
         <v>44217</v>
       </c>
       <c r="B84" t="n">
-        <v>15.8549861907959</v>
+        <v>15.85498523712158</v>
       </c>
       <c r="C84" t="n">
-        <v>16.3664363184206</v>
+        <v>16.36643533398266</v>
       </c>
       <c r="D84" t="n">
-        <v>15.53032440543763</v>
+        <v>15.53032347129166</v>
       </c>
       <c r="E84" t="n">
-        <v>16.25969963811151</v>
+        <v>16.25969866009376</v>
       </c>
       <c r="F84" t="n">
         <v>928200</v>
@@ -2112,16 +2112,16 @@
         <v>44218</v>
       </c>
       <c r="B85" t="n">
-        <v>15.40134906768799</v>
+        <v>15.4013500213623</v>
       </c>
       <c r="C85" t="n">
-        <v>15.84164078602173</v>
+        <v>15.84164176695957</v>
       </c>
       <c r="D85" t="n">
-        <v>15.17453068238381</v>
+        <v>15.17453162201319</v>
       </c>
       <c r="E85" t="n">
-        <v>15.60592909229859</v>
+        <v>15.60593005864081</v>
       </c>
       <c r="F85" t="n">
         <v>1029200</v>
@@ -2172,16 +2172,16 @@
         <v>44224</v>
       </c>
       <c r="B88" t="n">
-        <v>15.65929985046387</v>
+        <v>15.65929698944092</v>
       </c>
       <c r="C88" t="n">
-        <v>15.98840829903717</v>
+        <v>15.98840537788466</v>
       </c>
       <c r="D88" t="n">
-        <v>14.95216296324262</v>
+        <v>14.95216023141669</v>
       </c>
       <c r="E88" t="n">
-        <v>15.134506351945</v>
+        <v>15.13450358680413</v>
       </c>
       <c r="F88" t="n">
         <v>3941600</v>
@@ -2192,16 +2192,16 @@
         <v>44225</v>
       </c>
       <c r="B89" t="n">
-        <v>15.74379825592041</v>
+        <v>15.74379730224609</v>
       </c>
       <c r="C89" t="n">
-        <v>16.55322500128939</v>
+        <v>16.55322399858438</v>
       </c>
       <c r="D89" t="n">
-        <v>15.38800486303628</v>
+        <v>15.38800393091401</v>
       </c>
       <c r="E89" t="n">
-        <v>16.01064160403487</v>
+        <v>16.01064063419663</v>
       </c>
       <c r="F89" t="n">
         <v>3936400</v>
@@ -2232,16 +2232,16 @@
         <v>44229</v>
       </c>
       <c r="B91" t="n">
-        <v>17.08246612548828</v>
+        <v>17.08246421813965</v>
       </c>
       <c r="C91" t="n">
-        <v>17.32262617193124</v>
+        <v>17.32262423776745</v>
       </c>
       <c r="D91" t="n">
-        <v>16.76670108102554</v>
+        <v>16.76669920893377</v>
       </c>
       <c r="E91" t="n">
-        <v>16.76670108102554</v>
+        <v>16.76669920893377</v>
       </c>
       <c r="F91" t="n">
         <v>2620800</v>
@@ -2272,16 +2272,16 @@
         <v>44231</v>
       </c>
       <c r="B93" t="n">
-        <v>17.88744735717773</v>
+        <v>17.8874454498291</v>
       </c>
       <c r="C93" t="n">
-        <v>18.3633191282485</v>
+        <v>18.36331717015739</v>
       </c>
       <c r="D93" t="n">
-        <v>17.61615562484698</v>
+        <v>17.61615374642633</v>
       </c>
       <c r="E93" t="n">
-        <v>17.79405064684091</v>
+        <v>17.79404874945122</v>
       </c>
       <c r="F93" t="n">
         <v>1940600</v>
@@ -2292,16 +2292,16 @@
         <v>44232</v>
       </c>
       <c r="B94" t="n">
-        <v>18.80805778503418</v>
+        <v>18.80806159973145</v>
       </c>
       <c r="C94" t="n">
-        <v>19.56856289018561</v>
+        <v>19.56856685913042</v>
       </c>
       <c r="D94" t="n">
-        <v>17.78960262744146</v>
+        <v>17.78960623557311</v>
       </c>
       <c r="E94" t="n">
-        <v>17.99863100120949</v>
+        <v>17.99863465173679</v>
       </c>
       <c r="F94" t="n">
         <v>14342200</v>
@@ -2312,16 +2312,16 @@
         <v>44235</v>
       </c>
       <c r="B95" t="n">
-        <v>19.23056030273438</v>
+        <v>19.23056221008301</v>
       </c>
       <c r="C95" t="n">
-        <v>19.36842863096819</v>
+        <v>19.36843055199105</v>
       </c>
       <c r="D95" t="n">
-        <v>18.46560688202301</v>
+        <v>18.46560871350112</v>
       </c>
       <c r="E95" t="n">
-        <v>18.81250357441601</v>
+        <v>18.81250544030044</v>
       </c>
       <c r="F95" t="n">
         <v>1758400</v>
@@ -2352,16 +2352,16 @@
         <v>44237</v>
       </c>
       <c r="B97" t="n">
-        <v>18.55900382995605</v>
+        <v>18.55900192260742</v>
       </c>
       <c r="C97" t="n">
-        <v>18.98150725653792</v>
+        <v>18.9815053057677</v>
       </c>
       <c r="D97" t="n">
-        <v>18.24323877190336</v>
+        <v>18.24323689700658</v>
       </c>
       <c r="E97" t="n">
-        <v>18.87032223357157</v>
+        <v>18.87032029422808</v>
       </c>
       <c r="F97" t="n">
         <v>979000</v>
@@ -2372,16 +2372,16 @@
         <v>44238</v>
       </c>
       <c r="B98" t="n">
-        <v>18.63460922241211</v>
+        <v>18.63461112976074</v>
       </c>
       <c r="C98" t="n">
-        <v>19.14605927430059</v>
+        <v>19.14606123399878</v>
       </c>
       <c r="D98" t="n">
-        <v>18.4344758557824</v>
+        <v>18.43447774264635</v>
       </c>
       <c r="E98" t="n">
-        <v>18.55900252988591</v>
+        <v>18.55900442949581</v>
       </c>
       <c r="F98" t="n">
         <v>912400</v>
@@ -2392,16 +2392,16 @@
         <v>44239</v>
       </c>
       <c r="B99" t="n">
-        <v>18.51897811889648</v>
+        <v>18.51897621154785</v>
       </c>
       <c r="C99" t="n">
-        <v>18.72355816464402</v>
+        <v>18.72355623622481</v>
       </c>
       <c r="D99" t="n">
-        <v>18.16318636617275</v>
+        <v>18.16318449546863</v>
       </c>
       <c r="E99" t="n">
-        <v>18.58124146355452</v>
+        <v>18.58123954979312</v>
       </c>
       <c r="F99" t="n">
         <v>849600</v>
@@ -2432,16 +2432,16 @@
         <v>44245</v>
       </c>
       <c r="B101" t="n">
-        <v>18.24323844909668</v>
+        <v>18.24323654174805</v>
       </c>
       <c r="C101" t="n">
-        <v>19.03487525571373</v>
+        <v>19.03487326559868</v>
       </c>
       <c r="D101" t="n">
-        <v>17.9052350351925</v>
+        <v>17.90523316318246</v>
       </c>
       <c r="E101" t="n">
-        <v>18.69242518745105</v>
+        <v>18.6924232331395</v>
       </c>
       <c r="F101" t="n">
         <v>1007600</v>
@@ -2452,16 +2452,16 @@
         <v>44246</v>
       </c>
       <c r="B102" t="n">
-        <v>18.27881622314453</v>
+        <v>18.2788143157959</v>
       </c>
       <c r="C102" t="n">
-        <v>18.57234460188025</v>
+        <v>18.57234266390267</v>
       </c>
       <c r="D102" t="n">
-        <v>17.92302450597225</v>
+        <v>17.92302263574959</v>
       </c>
       <c r="E102" t="n">
-        <v>18.23434289470377</v>
+        <v>18.23434099199582</v>
       </c>
       <c r="F102" t="n">
         <v>881800</v>
@@ -2472,16 +2472,16 @@
         <v>44249</v>
       </c>
       <c r="B103" t="n">
-        <v>17.81628799438477</v>
+        <v>17.8162899017334</v>
       </c>
       <c r="C103" t="n">
-        <v>18.46115974514026</v>
+        <v>18.46116172152658</v>
       </c>
       <c r="D103" t="n">
-        <v>16.95793951491647</v>
+        <v>16.95794133037336</v>
       </c>
       <c r="E103" t="n">
-        <v>17.34486290467952</v>
+        <v>17.34486476155905</v>
       </c>
       <c r="F103" t="n">
         <v>2023200</v>
@@ -2512,16 +2512,16 @@
         <v>44251</v>
       </c>
       <c r="B105" t="n">
-        <v>17.68731117248535</v>
+        <v>17.68731307983398</v>
       </c>
       <c r="C105" t="n">
-        <v>18.09647118518221</v>
+        <v>18.09647313665348</v>
       </c>
       <c r="D105" t="n">
-        <v>17.54499449880396</v>
+        <v>17.54499639080558</v>
       </c>
       <c r="E105" t="n">
-        <v>17.70510118083267</v>
+        <v>17.70510309009973</v>
       </c>
       <c r="F105" t="n">
         <v>1411000</v>
@@ -2532,16 +2532,16 @@
         <v>44252</v>
       </c>
       <c r="B106" t="n">
-        <v>16.94459533691406</v>
+        <v>16.9445972442627</v>
       </c>
       <c r="C106" t="n">
-        <v>17.7940487700933</v>
+        <v>17.79405077305967</v>
       </c>
       <c r="D106" t="n">
-        <v>16.6377253111698</v>
+        <v>16.63772718397596</v>
       </c>
       <c r="E106" t="n">
-        <v>17.68731210746428</v>
+        <v>17.68731409841596</v>
       </c>
       <c r="F106" t="n">
         <v>1207600</v>
@@ -2552,16 +2552,16 @@
         <v>44253</v>
       </c>
       <c r="B107" t="n">
-        <v>16.69999313354492</v>
+        <v>16.69998931884766</v>
       </c>
       <c r="C107" t="n">
-        <v>17.20699665860983</v>
+        <v>17.20699272810024</v>
       </c>
       <c r="D107" t="n">
-        <v>16.40201803239415</v>
+        <v>16.40201428576187</v>
       </c>
       <c r="E107" t="n">
-        <v>17.13583829889106</v>
+        <v>17.13583438463582</v>
       </c>
       <c r="F107" t="n">
         <v>1586600</v>
@@ -2612,16 +2612,16 @@
         <v>44258</v>
       </c>
       <c r="B110" t="n">
-        <v>16.19298362731934</v>
+        <v>16.19298553466797</v>
       </c>
       <c r="C110" t="n">
-        <v>16.80227696339255</v>
+        <v>16.80227894250898</v>
       </c>
       <c r="D110" t="n">
-        <v>15.61926860968948</v>
+        <v>15.61927044946103</v>
       </c>
       <c r="E110" t="n">
-        <v>16.80227696339255</v>
+        <v>16.80227894250898</v>
       </c>
       <c r="F110" t="n">
         <v>1368800</v>
@@ -2632,16 +2632,16 @@
         <v>44259</v>
       </c>
       <c r="B111" t="n">
-        <v>16.05066871643066</v>
+        <v>16.0506706237793</v>
       </c>
       <c r="C111" t="n">
-        <v>16.75780547454543</v>
+        <v>16.75780746592523</v>
       </c>
       <c r="D111" t="n">
-        <v>15.79271866916489</v>
+        <v>15.79272054586055</v>
       </c>
       <c r="E111" t="n">
-        <v>16.23301207184145</v>
+        <v>16.23301400085849</v>
       </c>
       <c r="F111" t="n">
         <v>1300400</v>
@@ -2672,16 +2672,16 @@
         <v>44263</v>
       </c>
       <c r="B113" t="n">
-        <v>14.91213321685791</v>
+        <v>14.91213417053223</v>
       </c>
       <c r="C113" t="n">
-        <v>16.05956335121808</v>
+        <v>16.05956437827389</v>
       </c>
       <c r="D113" t="n">
-        <v>14.76536988371221</v>
+        <v>14.76537082800059</v>
       </c>
       <c r="E113" t="n">
-        <v>16.0106416746533</v>
+        <v>16.01064269858043</v>
       </c>
       <c r="F113" t="n">
         <v>3236800</v>
@@ -2732,16 +2732,16 @@
         <v>44266</v>
       </c>
       <c r="B116" t="n">
-        <v>15.81940460205078</v>
+        <v>15.8194055557251</v>
       </c>
       <c r="C116" t="n">
-        <v>15.99285296281361</v>
+        <v>15.99285392694427</v>
       </c>
       <c r="D116" t="n">
-        <v>15.15674282905697</v>
+        <v>15.15674374278266</v>
       </c>
       <c r="E116" t="n">
-        <v>15.15674282905697</v>
+        <v>15.15674374278266</v>
       </c>
       <c r="F116" t="n">
         <v>2295400</v>
@@ -2752,16 +2752,16 @@
         <v>44267</v>
       </c>
       <c r="B117" t="n">
-        <v>15.61037445068359</v>
+        <v>15.61037635803223</v>
       </c>
       <c r="C117" t="n">
-        <v>15.96171948327262</v>
+        <v>15.96172143355023</v>
       </c>
       <c r="D117" t="n">
-        <v>15.41913610112494</v>
+        <v>15.41913798510718</v>
       </c>
       <c r="E117" t="n">
-        <v>15.96171948327262</v>
+        <v>15.96172143355023</v>
       </c>
       <c r="F117" t="n">
         <v>1034800</v>
@@ -2772,16 +2772,16 @@
         <v>44270</v>
       </c>
       <c r="B118" t="n">
-        <v>15.67708778381348</v>
+        <v>15.67708492279053</v>
       </c>
       <c r="C118" t="n">
-        <v>16.00619618873527</v>
+        <v>16.006193267651</v>
       </c>
       <c r="D118" t="n">
-        <v>15.49474441929632</v>
+        <v>15.4947415915505</v>
       </c>
       <c r="E118" t="n">
-        <v>15.614824444205</v>
+        <v>15.61482159454493</v>
       </c>
       <c r="F118" t="n">
         <v>1150400</v>
@@ -2792,16 +2792,16 @@
         <v>44271</v>
       </c>
       <c r="B119" t="n">
-        <v>16.46872138977051</v>
+        <v>16.46872520446777</v>
       </c>
       <c r="C119" t="n">
-        <v>16.83785639812166</v>
+        <v>16.83786029832273</v>
       </c>
       <c r="D119" t="n">
-        <v>15.68153139896302</v>
+        <v>15.6815350313212</v>
       </c>
       <c r="E119" t="n">
-        <v>15.68597974895794</v>
+        <v>15.68598338234651</v>
       </c>
       <c r="F119" t="n">
         <v>1963400</v>
@@ -2812,16 +2812,16 @@
         <v>44272</v>
       </c>
       <c r="B120" t="n">
-        <v>16.58880233764648</v>
+        <v>16.58880424499512</v>
       </c>
       <c r="C120" t="n">
-        <v>16.75780401957668</v>
+        <v>16.7578059463568</v>
       </c>
       <c r="D120" t="n">
-        <v>16.0773523347043</v>
+        <v>16.07735418324739</v>
       </c>
       <c r="E120" t="n">
-        <v>16.19298399294167</v>
+        <v>16.19298585477987</v>
       </c>
       <c r="F120" t="n">
         <v>1461600</v>
@@ -2872,16 +2872,16 @@
         <v>44277</v>
       </c>
       <c r="B123" t="n">
-        <v>16.54433059692383</v>
+        <v>16.54433250427246</v>
       </c>
       <c r="C123" t="n">
-        <v>16.58435727024774</v>
+        <v>16.58435918221094</v>
       </c>
       <c r="D123" t="n">
-        <v>15.92169383334038</v>
+        <v>15.921695668907</v>
       </c>
       <c r="E123" t="n">
-        <v>16.26414388365641</v>
+        <v>16.26414575870311</v>
       </c>
       <c r="F123" t="n">
         <v>938000</v>
@@ -2892,16 +2892,16 @@
         <v>44278</v>
       </c>
       <c r="B124" t="n">
-        <v>16.0995922088623</v>
+        <v>16.09959030151367</v>
       </c>
       <c r="C124" t="n">
-        <v>16.49985728713733</v>
+        <v>16.49985533236855</v>
       </c>
       <c r="D124" t="n">
-        <v>15.87277380427914</v>
+        <v>15.87277192380211</v>
       </c>
       <c r="E124" t="n">
-        <v>16.4553839550675</v>
+        <v>16.45538200556756</v>
       </c>
       <c r="F124" t="n">
         <v>855200</v>
@@ -2912,16 +2912,16 @@
         <v>44279</v>
       </c>
       <c r="B125" t="n">
-        <v>15.41024398803711</v>
+        <v>15.41024494171143</v>
       </c>
       <c r="C125" t="n">
-        <v>16.21077576869711</v>
+        <v>16.21077677191293</v>
       </c>
       <c r="D125" t="n">
-        <v>15.21455727291999</v>
+        <v>15.21455821448409</v>
       </c>
       <c r="E125" t="n">
-        <v>16.05066907325537</v>
+        <v>16.05067006656286</v>
       </c>
       <c r="F125" t="n">
         <v>1010400</v>
@@ -2952,16 +2952,16 @@
         <v>44281</v>
       </c>
       <c r="B127" t="n">
-        <v>15.8549861907959</v>
+        <v>15.85498523712158</v>
       </c>
       <c r="C127" t="n">
-        <v>16.415358003791</v>
+        <v>16.41535701641043</v>
       </c>
       <c r="D127" t="n">
-        <v>15.67264280676466</v>
+        <v>15.67264186405827</v>
       </c>
       <c r="E127" t="n">
-        <v>16.10403957588308</v>
+        <v>16.10403860722825</v>
       </c>
       <c r="F127" t="n">
         <v>1078200</v>
@@ -2972,16 +2972,16 @@
         <v>44284</v>
       </c>
       <c r="B128" t="n">
-        <v>15.58369064331055</v>
+        <v>15.58369255065918</v>
       </c>
       <c r="C128" t="n">
-        <v>16.00174564961845</v>
+        <v>16.00174760813446</v>
       </c>
       <c r="D128" t="n">
-        <v>15.39245229978017</v>
+        <v>15.39245418372239</v>
       </c>
       <c r="E128" t="n">
-        <v>15.74379732129399</v>
+        <v>15.7437992482387</v>
       </c>
       <c r="F128" t="n">
         <v>646800</v>
@@ -2992,16 +2992,16 @@
         <v>44285</v>
       </c>
       <c r="B129" t="n">
-        <v>16.09514045715332</v>
+        <v>16.09514617919922</v>
       </c>
       <c r="C129" t="n">
-        <v>16.23745712556681</v>
+        <v>16.23746289820826</v>
       </c>
       <c r="D129" t="n">
-        <v>15.48584711447378</v>
+        <v>15.48585261990744</v>
       </c>
       <c r="E129" t="n">
-        <v>15.5881371138617</v>
+        <v>15.58814265566087</v>
       </c>
       <c r="F129" t="n">
         <v>990200</v>
@@ -3012,16 +3012,16 @@
         <v>44286</v>
       </c>
       <c r="B130" t="n">
-        <v>16.61548614501953</v>
+        <v>16.6154899597168</v>
       </c>
       <c r="C130" t="n">
-        <v>16.71777613819286</v>
+        <v>16.71777997637457</v>
       </c>
       <c r="D130" t="n">
-        <v>15.94392781622937</v>
+        <v>15.94393147674567</v>
       </c>
       <c r="E130" t="n">
-        <v>16.10848283253066</v>
+        <v>16.10848653082663</v>
       </c>
       <c r="F130" t="n">
         <v>1491400</v>
@@ -3032,16 +3032,16 @@
         <v>44287</v>
       </c>
       <c r="B131" t="n">
-        <v>16.59325218200684</v>
+        <v>16.59325408935547</v>
       </c>
       <c r="C131" t="n">
-        <v>17.0424388943022</v>
+        <v>17.04244085328361</v>
       </c>
       <c r="D131" t="n">
-        <v>16.48651382155865</v>
+        <v>16.48651571663801</v>
       </c>
       <c r="E131" t="n">
-        <v>17.03799224020167</v>
+        <v>17.03799419867195</v>
       </c>
       <c r="F131" t="n">
         <v>1225400</v>
@@ -3052,16 +3052,16 @@
         <v>44291</v>
       </c>
       <c r="B132" t="n">
-        <v>16.86454200744629</v>
+        <v>16.86454582214355</v>
       </c>
       <c r="C132" t="n">
-        <v>17.01130703938433</v>
+        <v>17.01131088727931</v>
       </c>
       <c r="D132" t="n">
-        <v>16.60214700467584</v>
+        <v>16.60215076002032</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90012202605503</v>
+        <v>16.90012584880036</v>
       </c>
       <c r="F132" t="n">
         <v>838600</v>
@@ -3092,16 +3092,16 @@
         <v>44293</v>
       </c>
       <c r="B134" t="n">
-        <v>17.37154960632324</v>
+        <v>17.37155151367188</v>
       </c>
       <c r="C134" t="n">
-        <v>17.63839299829608</v>
+        <v>17.63839493494339</v>
       </c>
       <c r="D134" t="n">
-        <v>17.11359952374044</v>
+        <v>17.11360140276686</v>
       </c>
       <c r="E134" t="n">
-        <v>17.47828628449281</v>
+        <v>17.47828820356084</v>
       </c>
       <c r="F134" t="n">
         <v>869400</v>
@@ -3132,16 +3132,16 @@
         <v>44295</v>
       </c>
       <c r="B136" t="n">
-        <v>18.03421401977539</v>
+        <v>18.03420829772949</v>
       </c>
       <c r="C136" t="n">
-        <v>18.25658411051627</v>
+        <v>18.25657831791493</v>
       </c>
       <c r="D136" t="n">
-        <v>17.41157878363042</v>
+        <v>17.41157325913943</v>
       </c>
       <c r="E136" t="n">
-        <v>17.64284218503768</v>
+        <v>17.6428365871695</v>
       </c>
       <c r="F136" t="n">
         <v>1023600</v>
@@ -3152,16 +3152,16 @@
         <v>44298</v>
       </c>
       <c r="B137" t="n">
-        <v>17.74513053894043</v>
+        <v>17.7451286315918</v>
       </c>
       <c r="C137" t="n">
-        <v>18.05644724942629</v>
+        <v>18.05644530861555</v>
       </c>
       <c r="D137" t="n">
-        <v>17.58947048714867</v>
+        <v>17.58946859653127</v>
       </c>
       <c r="E137" t="n">
-        <v>18.05644724942629</v>
+        <v>18.05644530861555</v>
       </c>
       <c r="F137" t="n">
         <v>810600</v>
@@ -3172,16 +3172,16 @@
         <v>44299</v>
       </c>
       <c r="B138" t="n">
-        <v>17.40712547302246</v>
+        <v>17.40712738037109</v>
       </c>
       <c r="C138" t="n">
-        <v>17.74068051411476</v>
+        <v>17.74068245801198</v>
       </c>
       <c r="D138" t="n">
-        <v>17.20254545499086</v>
+        <v>17.20254733992308</v>
       </c>
       <c r="E138" t="n">
-        <v>17.74068051411476</v>
+        <v>17.74068245801198</v>
       </c>
       <c r="F138" t="n">
         <v>699800</v>
@@ -3192,16 +3192,16 @@
         <v>44300</v>
       </c>
       <c r="B139" t="n">
-        <v>17.16251945495605</v>
+        <v>17.16252326965332</v>
       </c>
       <c r="C139" t="n">
-        <v>17.71399789099429</v>
+        <v>17.71400182826816</v>
       </c>
       <c r="D139" t="n">
-        <v>17.07801945199119</v>
+        <v>17.07802324790672</v>
       </c>
       <c r="E139" t="n">
-        <v>17.37154783179656</v>
+        <v>17.37155169295437</v>
       </c>
       <c r="F139" t="n">
         <v>861200</v>
@@ -3212,16 +3212,16 @@
         <v>44301</v>
       </c>
       <c r="B140" t="n">
-        <v>17.38044357299805</v>
+        <v>17.38044166564941</v>
       </c>
       <c r="C140" t="n">
-        <v>17.60281361852843</v>
+        <v>17.60281168677666</v>
       </c>
       <c r="D140" t="n">
-        <v>17.17141518730387</v>
+        <v>17.17141330289424</v>
       </c>
       <c r="E140" t="n">
-        <v>17.17141518730387</v>
+        <v>17.17141330289424</v>
       </c>
       <c r="F140" t="n">
         <v>924800</v>
@@ -3232,16 +3232,16 @@
         <v>44302</v>
       </c>
       <c r="B141" t="n">
-        <v>17.74513053894043</v>
+        <v>17.7451286315918</v>
       </c>
       <c r="C141" t="n">
-        <v>17.74513053894043</v>
+        <v>17.7451286315918</v>
       </c>
       <c r="D141" t="n">
-        <v>17.12249372487104</v>
+        <v>17.12249188444699</v>
       </c>
       <c r="E141" t="n">
-        <v>17.38489044981543</v>
+        <v>17.38488858118748</v>
       </c>
       <c r="F141" t="n">
         <v>774600</v>
@@ -3252,16 +3252,16 @@
         <v>44305</v>
       </c>
       <c r="B142" t="n">
-        <v>18.01197242736816</v>
+        <v>18.0119743347168</v>
       </c>
       <c r="C142" t="n">
-        <v>18.17652577451049</v>
+        <v>18.17652769928423</v>
       </c>
       <c r="D142" t="n">
-        <v>17.70065404610391</v>
+        <v>17.70065592048599</v>
       </c>
       <c r="E142" t="n">
-        <v>17.70065404610391</v>
+        <v>17.70065592048599</v>
       </c>
       <c r="F142" t="n">
         <v>952400</v>
@@ -3272,16 +3272,16 @@
         <v>44306</v>
       </c>
       <c r="B143" t="n">
-        <v>17.81184005737305</v>
+        <v>17.81183815002441</v>
       </c>
       <c r="C143" t="n">
-        <v>18.40779183888181</v>
+        <v>18.40778986771676</v>
       </c>
       <c r="D143" t="n">
-        <v>17.62949669046246</v>
+        <v>17.62949480263974</v>
       </c>
       <c r="E143" t="n">
-        <v>18.01642008921442</v>
+        <v>18.01641815995871</v>
       </c>
       <c r="F143" t="n">
         <v>1050400</v>
@@ -3292,16 +3292,16 @@
         <v>44308</v>
       </c>
       <c r="B144" t="n">
-        <v>17.32707405090332</v>
+        <v>17.32707214355469</v>
       </c>
       <c r="C144" t="n">
-        <v>17.97639419580525</v>
+        <v>17.97639221698004</v>
       </c>
       <c r="D144" t="n">
-        <v>17.26925905887769</v>
+        <v>17.26925715789328</v>
       </c>
       <c r="E144" t="n">
-        <v>17.94971087534692</v>
+        <v>17.94970889945899</v>
       </c>
       <c r="F144" t="n">
         <v>1084000</v>
@@ -3312,16 +3312,16 @@
         <v>44309</v>
       </c>
       <c r="B145" t="n">
-        <v>17.2114429473877</v>
+        <v>17.21144104003906</v>
       </c>
       <c r="C145" t="n">
-        <v>17.57168135804453</v>
+        <v>17.57167941077477</v>
       </c>
       <c r="D145" t="n">
-        <v>16.88233451279305</v>
+        <v>16.88233264191577</v>
       </c>
       <c r="E145" t="n">
-        <v>17.52276137004772</v>
+        <v>17.52275942819921</v>
       </c>
       <c r="F145" t="n">
         <v>903000</v>
@@ -3332,16 +3332,16 @@
         <v>44312</v>
       </c>
       <c r="B146" t="n">
-        <v>17.08691215515137</v>
+        <v>17.0869140625</v>
       </c>
       <c r="C146" t="n">
-        <v>17.31817718810049</v>
+        <v>17.31817912126438</v>
       </c>
       <c r="D146" t="n">
-        <v>16.90012214577824</v>
+        <v>16.90012403227619</v>
       </c>
       <c r="E146" t="n">
-        <v>17.31817718810049</v>
+        <v>17.31817912126438</v>
       </c>
       <c r="F146" t="n">
         <v>836400</v>
@@ -3352,16 +3352,16 @@
         <v>44313</v>
       </c>
       <c r="B147" t="n">
-        <v>17.33596801757812</v>
+        <v>17.33596992492676</v>
       </c>
       <c r="C147" t="n">
-        <v>17.78070809508361</v>
+        <v>17.78071005136372</v>
       </c>
       <c r="D147" t="n">
-        <v>17.01130796458497</v>
+        <v>17.01130983621365</v>
       </c>
       <c r="E147" t="n">
-        <v>17.04688798512881</v>
+        <v>17.0468898606721</v>
       </c>
       <c r="F147" t="n">
         <v>1372600</v>
@@ -3392,16 +3392,16 @@
         <v>44315</v>
       </c>
       <c r="B149" t="n">
-        <v>18.93703269958496</v>
+        <v>18.93703460693359</v>
       </c>
       <c r="C149" t="n">
-        <v>19.07045437919426</v>
+        <v>19.0704562999812</v>
       </c>
       <c r="D149" t="n">
-        <v>18.13205257468259</v>
+        <v>18.13205440095317</v>
       </c>
       <c r="E149" t="n">
-        <v>18.57234428704813</v>
+        <v>18.57234615766514</v>
       </c>
       <c r="F149" t="n">
         <v>2301200</v>
@@ -3452,16 +3452,16 @@
         <v>44320</v>
       </c>
       <c r="B152" t="n">
-        <v>19.79606819152832</v>
+        <v>19.79606437683105</v>
       </c>
       <c r="C152" t="n">
-        <v>20.00618961139364</v>
+        <v>20.00618575620603</v>
       </c>
       <c r="D152" t="n">
-        <v>19.25959072829643</v>
+        <v>19.25958701697824</v>
       </c>
       <c r="E152" t="n">
-        <v>19.45182740585503</v>
+        <v>19.45182365749287</v>
       </c>
       <c r="F152" t="n">
         <v>1635200</v>
@@ -3492,16 +3492,16 @@
         <v>44322</v>
       </c>
       <c r="B154" t="n">
-        <v>20.4309024810791</v>
+        <v>20.43090057373047</v>
       </c>
       <c r="C154" t="n">
-        <v>20.65443532724973</v>
+        <v>20.65443339903295</v>
       </c>
       <c r="D154" t="n">
-        <v>20.16266204242219</v>
+        <v>20.16266016011543</v>
       </c>
       <c r="E154" t="n">
-        <v>20.46219694310937</v>
+        <v>20.46219503283921</v>
       </c>
       <c r="F154" t="n">
         <v>1030200</v>
@@ -3512,16 +3512,16 @@
         <v>44323</v>
       </c>
       <c r="B155" t="n">
-        <v>20.8332633972168</v>
+        <v>20.83326148986816</v>
       </c>
       <c r="C155" t="n">
-        <v>20.87797099574675</v>
+        <v>20.877969084305</v>
       </c>
       <c r="D155" t="n">
-        <v>20.36384469788557</v>
+        <v>20.36384283351365</v>
       </c>
       <c r="E155" t="n">
-        <v>20.86902947604076</v>
+        <v>20.86902756541763</v>
       </c>
       <c r="F155" t="n">
         <v>1109600</v>
@@ -3532,16 +3532,16 @@
         <v>44326</v>
       </c>
       <c r="B156" t="n">
-        <v>20.36384010314941</v>
+        <v>20.36384201049805</v>
       </c>
       <c r="C156" t="n">
-        <v>20.94502510954077</v>
+        <v>20.94502707132523</v>
       </c>
       <c r="D156" t="n">
-        <v>20.25207369017338</v>
+        <v>20.25207558705358</v>
       </c>
       <c r="E156" t="n">
-        <v>20.83325869656473</v>
+        <v>20.83326064788076</v>
       </c>
       <c r="F156" t="n">
         <v>979800</v>
@@ -3552,16 +3552,16 @@
         <v>44327</v>
       </c>
       <c r="B157" t="n">
-        <v>20.60078620910645</v>
+        <v>20.60078811645508</v>
       </c>
       <c r="C157" t="n">
-        <v>20.60972602144025</v>
+        <v>20.60972792961658</v>
       </c>
       <c r="D157" t="n">
-        <v>19.78265524153291</v>
+        <v>19.7826570731339</v>
       </c>
       <c r="E157" t="n">
-        <v>20.25207383838357</v>
+        <v>20.25207571344624</v>
       </c>
       <c r="F157" t="n">
         <v>1012800</v>
@@ -3592,16 +3592,16 @@
         <v>44329</v>
       </c>
       <c r="B159" t="n">
-        <v>20.90478897094727</v>
+        <v>20.90479278564453</v>
       </c>
       <c r="C159" t="n">
-        <v>20.9718495003822</v>
+        <v>20.97185332731664</v>
       </c>
       <c r="D159" t="n">
-        <v>20.1581901566442</v>
+        <v>20.15819383510242</v>
       </c>
       <c r="E159" t="n">
-        <v>20.25654514503674</v>
+        <v>20.25654884144274</v>
       </c>
       <c r="F159" t="n">
         <v>1469200</v>
@@ -3652,16 +3652,16 @@
         <v>44334</v>
       </c>
       <c r="B162" t="n">
-        <v>21.12385368347168</v>
+        <v>21.12385177612305</v>
       </c>
       <c r="C162" t="n">
-        <v>21.74080480825265</v>
+        <v>21.74080284519728</v>
       </c>
       <c r="D162" t="n">
-        <v>20.88243780350257</v>
+        <v>20.88243591795225</v>
       </c>
       <c r="E162" t="n">
-        <v>21.15067823860833</v>
+        <v>21.15067632883762</v>
       </c>
       <c r="F162" t="n">
         <v>1192600</v>
@@ -3692,16 +3692,16 @@
         <v>44336</v>
       </c>
       <c r="B164" t="n">
-        <v>21.86151313781738</v>
+        <v>21.86151504516602</v>
       </c>
       <c r="C164" t="n">
-        <v>21.93751348726187</v>
+        <v>21.9375154012413</v>
       </c>
       <c r="D164" t="n">
-        <v>21.37868136927493</v>
+        <v>21.378683234498</v>
       </c>
       <c r="E164" t="n">
-        <v>21.49044779287232</v>
+        <v>21.49044966784666</v>
       </c>
       <c r="F164" t="n">
         <v>917400</v>
@@ -3712,16 +3712,16 @@
         <v>44337</v>
       </c>
       <c r="B165" t="n">
-        <v>21.94645309448242</v>
+        <v>21.94645690917969</v>
       </c>
       <c r="C165" t="n">
-        <v>22.04033647282705</v>
+        <v>22.04034030384297</v>
       </c>
       <c r="D165" t="n">
-        <v>21.50385734519752</v>
+        <v>21.5038610829635</v>
       </c>
       <c r="E165" t="n">
-        <v>22.04033647282705</v>
+        <v>22.04034030384297</v>
       </c>
       <c r="F165" t="n">
         <v>653400</v>
@@ -3792,16 +3792,16 @@
         <v>44343</v>
       </c>
       <c r="B169" t="n">
-        <v>22.34434127807617</v>
+        <v>22.3443431854248</v>
       </c>
       <c r="C169" t="n">
-        <v>22.34434127807617</v>
+        <v>22.3443431854248</v>
       </c>
       <c r="D169" t="n">
-        <v>21.80339224371756</v>
+        <v>21.80339410488992</v>
       </c>
       <c r="E169" t="n">
-        <v>22.27281084134627</v>
+        <v>22.27281274258895</v>
       </c>
       <c r="F169" t="n">
         <v>1342400</v>
@@ -3812,16 +3812,16 @@
         <v>44344</v>
       </c>
       <c r="B170" t="n">
-        <v>22.21469497680664</v>
+        <v>22.21469306945801</v>
       </c>
       <c r="C170" t="n">
-        <v>22.54552435945486</v>
+        <v>22.54552242370129</v>
       </c>
       <c r="D170" t="n">
-        <v>21.94198632060221</v>
+        <v>21.94198443666828</v>
       </c>
       <c r="E170" t="n">
-        <v>22.29516694270971</v>
+        <v>22.29516502845177</v>
       </c>
       <c r="F170" t="n">
         <v>840600</v>
@@ -3832,16 +3832,16 @@
         <v>44347</v>
       </c>
       <c r="B171" t="n">
-        <v>23.22953224182129</v>
+        <v>23.22953414916992</v>
       </c>
       <c r="C171" t="n">
-        <v>23.22953224182129</v>
+        <v>23.22953414916992</v>
       </c>
       <c r="D171" t="n">
-        <v>22.24151750179612</v>
+        <v>22.24151932802007</v>
       </c>
       <c r="E171" t="n">
-        <v>22.24151750179612</v>
+        <v>22.24151932802007</v>
       </c>
       <c r="F171" t="n">
         <v>1311400</v>
@@ -3912,16 +3912,16 @@
         <v>44354</v>
       </c>
       <c r="B175" t="n">
-        <v>23.51565361022949</v>
+        <v>23.51565551757812</v>
       </c>
       <c r="C175" t="n">
-        <v>23.95377946853823</v>
+        <v>23.95378141142314</v>
       </c>
       <c r="D175" t="n">
-        <v>23.24741488982269</v>
+        <v>23.24741677541455</v>
       </c>
       <c r="E175" t="n">
-        <v>23.56483110690212</v>
+        <v>23.56483301823953</v>
       </c>
       <c r="F175" t="n">
         <v>1060000</v>
@@ -3952,16 +3952,16 @@
         <v>44356</v>
       </c>
       <c r="B177" t="n">
-        <v>23.51565361022949</v>
+        <v>23.51565551757812</v>
       </c>
       <c r="C177" t="n">
-        <v>23.60059717918046</v>
+        <v>23.60059909341884</v>
       </c>
       <c r="D177" t="n">
-        <v>23.1803543570109</v>
+        <v>23.18035623716349</v>
       </c>
       <c r="E177" t="n">
-        <v>23.444123171093</v>
+        <v>23.44412507263982</v>
       </c>
       <c r="F177" t="n">
         <v>621600</v>
@@ -3992,16 +3992,16 @@
         <v>44358</v>
       </c>
       <c r="B179" t="n">
-        <v>23.3055362701416</v>
+        <v>23.30553436279297</v>
       </c>
       <c r="C179" t="n">
-        <v>23.5648334987982</v>
+        <v>23.56483157022843</v>
       </c>
       <c r="D179" t="n">
-        <v>22.55893563704099</v>
+        <v>22.55893379079491</v>
       </c>
       <c r="E179" t="n">
-        <v>23.5648334987982</v>
+        <v>23.56483157022843</v>
       </c>
       <c r="F179" t="n">
         <v>855400</v>
@@ -4092,16 +4092,16 @@
         <v>44365</v>
       </c>
       <c r="B184" t="n">
-        <v>24.89708709716797</v>
+        <v>24.8970890045166</v>
       </c>
       <c r="C184" t="n">
-        <v>25.19215037765539</v>
+        <v>25.19215230760862</v>
       </c>
       <c r="D184" t="n">
-        <v>24.25778303854185</v>
+        <v>24.25778489691384</v>
       </c>
       <c r="E184" t="n">
-        <v>24.6780258690744</v>
+        <v>24.6780277596409</v>
       </c>
       <c r="F184" t="n">
         <v>1737600</v>
@@ -4192,16 +4192,16 @@
         <v>44372</v>
       </c>
       <c r="B189" t="n">
-        <v>24.35166931152344</v>
+        <v>24.35167121887207</v>
       </c>
       <c r="C189" t="n">
-        <v>24.5886135876334</v>
+        <v>24.58861551354074</v>
       </c>
       <c r="D189" t="n">
-        <v>24.00295690459483</v>
+        <v>24.0029587846305</v>
       </c>
       <c r="E189" t="n">
-        <v>24.27119734880301</v>
+        <v>24.27119924984866</v>
       </c>
       <c r="F189" t="n">
         <v>926400</v>
@@ -4212,16 +4212,16 @@
         <v>44375</v>
       </c>
       <c r="B190" t="n">
-        <v>24.48578834533691</v>
+        <v>24.48578643798828</v>
       </c>
       <c r="C190" t="n">
-        <v>25.01332600242071</v>
+        <v>25.01332405397893</v>
       </c>
       <c r="D190" t="n">
-        <v>24.06107559355992</v>
+        <v>24.06107371929478</v>
       </c>
       <c r="E190" t="n">
-        <v>24.06107559355992</v>
+        <v>24.06107371929478</v>
       </c>
       <c r="F190" t="n">
         <v>1351800</v>
@@ -4252,16 +4252,16 @@
         <v>44377</v>
       </c>
       <c r="B192" t="n">
-        <v>24.86579322814941</v>
+        <v>24.86579513549805</v>
       </c>
       <c r="C192" t="n">
-        <v>24.86579322814941</v>
+        <v>24.86579513549805</v>
       </c>
       <c r="D192" t="n">
-        <v>24.12813586207488</v>
+        <v>24.12813771284097</v>
       </c>
       <c r="E192" t="n">
-        <v>24.16837184243678</v>
+        <v>24.16837369628921</v>
       </c>
       <c r="F192" t="n">
         <v>1430400</v>
@@ -4272,16 +4272,16 @@
         <v>44378</v>
       </c>
       <c r="B193" t="n">
-        <v>24.92838287353516</v>
+        <v>24.92838096618652</v>
       </c>
       <c r="C193" t="n">
-        <v>25.96557687450705</v>
+        <v>25.96557488779945</v>
       </c>
       <c r="D193" t="n">
-        <v>24.91050154151692</v>
+        <v>24.91049963553645</v>
       </c>
       <c r="E193" t="n">
-        <v>25.2592122444671</v>
+        <v>25.25921031180567</v>
       </c>
       <c r="F193" t="n">
         <v>1991200</v>
@@ -4292,16 +4292,16 @@
         <v>44379</v>
       </c>
       <c r="B194" t="n">
-        <v>26.42605400085449</v>
+        <v>26.42605590820312</v>
       </c>
       <c r="C194" t="n">
-        <v>26.7702947971231</v>
+        <v>26.77029672931794</v>
       </c>
       <c r="D194" t="n">
-        <v>25.41568455613461</v>
+        <v>25.41568639055798</v>
       </c>
       <c r="E194" t="n">
-        <v>25.41568455613461</v>
+        <v>25.41568639055798</v>
       </c>
       <c r="F194" t="n">
         <v>2268600</v>
@@ -4312,16 +4312,16 @@
         <v>44382</v>
       </c>
       <c r="B195" t="n">
-        <v>26.53334617614746</v>
+        <v>26.53334999084473</v>
       </c>
       <c r="C195" t="n">
-        <v>26.77923365290268</v>
+        <v>26.77923750295117</v>
       </c>
       <c r="D195" t="n">
-        <v>26.17122408387186</v>
+        <v>26.17122784650686</v>
       </c>
       <c r="E195" t="n">
-        <v>26.38134378388976</v>
+        <v>26.38134757673365</v>
       </c>
       <c r="F195" t="n">
         <v>581600</v>
@@ -4332,16 +4332,16 @@
         <v>44383</v>
       </c>
       <c r="B196" t="n">
-        <v>26.19804763793945</v>
+        <v>26.19804954528809</v>
       </c>
       <c r="C196" t="n">
-        <v>26.53334689118315</v>
+        <v>26.53334882294324</v>
       </c>
       <c r="D196" t="n">
-        <v>25.66157019708569</v>
+        <v>25.66157206537609</v>
       </c>
       <c r="E196" t="n">
-        <v>26.53334689118315</v>
+        <v>26.53334882294324</v>
       </c>
       <c r="F196" t="n">
         <v>905000</v>
@@ -4352,16 +4352,16 @@
         <v>44384</v>
       </c>
       <c r="B197" t="n">
-        <v>26.52441024780273</v>
+        <v>26.52440643310547</v>
       </c>
       <c r="C197" t="n">
-        <v>26.93570989565746</v>
+        <v>26.93570602180775</v>
       </c>
       <c r="D197" t="n">
-        <v>26.1086389876685</v>
+        <v>26.10863523276678</v>
       </c>
       <c r="E197" t="n">
-        <v>26.19805076821403</v>
+        <v>26.19804700045325</v>
       </c>
       <c r="F197" t="n">
         <v>915800</v>
@@ -4372,16 +4372,16 @@
         <v>44385</v>
       </c>
       <c r="B198" t="n">
-        <v>26.52441024780273</v>
+        <v>26.52440643310547</v>
       </c>
       <c r="C198" t="n">
-        <v>26.52441024780273</v>
+        <v>26.52440643310547</v>
       </c>
       <c r="D198" t="n">
-        <v>25.82251549149344</v>
+        <v>25.82251177774154</v>
       </c>
       <c r="E198" t="n">
-        <v>26.23828675162768</v>
+        <v>26.23828297808023</v>
       </c>
       <c r="F198" t="n">
         <v>1041800</v>
@@ -4392,16 +4392,16 @@
         <v>44389</v>
       </c>
       <c r="B199" t="n">
-        <v>27.54371643066406</v>
+        <v>27.5437183380127</v>
       </c>
       <c r="C199" t="n">
-        <v>27.57501089139074</v>
+        <v>27.57501280090645</v>
       </c>
       <c r="D199" t="n">
-        <v>26.56911312552412</v>
+        <v>26.56911496538337</v>
       </c>
       <c r="E199" t="n">
-        <v>26.81499890498525</v>
+        <v>26.81500076187162</v>
       </c>
       <c r="F199" t="n">
         <v>886400</v>
@@ -4412,16 +4412,16 @@
         <v>44390</v>
       </c>
       <c r="B200" t="n">
-        <v>27.6644229888916</v>
+        <v>27.66442680358887</v>
       </c>
       <c r="C200" t="n">
-        <v>27.70465896573839</v>
+        <v>27.70466278598387</v>
       </c>
       <c r="D200" t="n">
-        <v>27.16817984292119</v>
+        <v>27.1681835891906</v>
       </c>
       <c r="E200" t="n">
-        <v>27.33806526798767</v>
+        <v>27.33806903768288</v>
       </c>
       <c r="F200" t="n">
         <v>796200</v>
@@ -4432,16 +4432,16 @@
         <v>44391</v>
       </c>
       <c r="B201" t="n">
-        <v>28.1740837097168</v>
+        <v>28.17407989501953</v>
       </c>
       <c r="C201" t="n">
-        <v>28.33502765224171</v>
+        <v>28.33502381575305</v>
       </c>
       <c r="D201" t="n">
-        <v>27.44089615414376</v>
+        <v>27.44089243871817</v>
       </c>
       <c r="E201" t="n">
-        <v>27.67337054829968</v>
+        <v>27.67336680139767</v>
       </c>
       <c r="F201" t="n">
         <v>880600</v>
@@ -4452,16 +4452,16 @@
         <v>44392</v>
       </c>
       <c r="B202" t="n">
-        <v>28.47808456420898</v>
+        <v>28.47808265686035</v>
       </c>
       <c r="C202" t="n">
-        <v>28.76420462521192</v>
+        <v>28.7642026987001</v>
       </c>
       <c r="D202" t="n">
-        <v>27.81195594110106</v>
+        <v>27.81195407836707</v>
       </c>
       <c r="E202" t="n">
-        <v>28.21431574102132</v>
+        <v>28.21431385133887</v>
       </c>
       <c r="F202" t="n">
         <v>1015800</v>
@@ -4472,16 +4472,16 @@
         <v>44393</v>
       </c>
       <c r="B203" t="n">
-        <v>28.79102897644043</v>
+        <v>28.79103088378906</v>
       </c>
       <c r="C203" t="n">
-        <v>29.03244484038268</v>
+        <v>29.03244676372463</v>
       </c>
       <c r="D203" t="n">
-        <v>28.15172495086382</v>
+        <v>28.15172681585982</v>
       </c>
       <c r="E203" t="n">
-        <v>28.72844005736358</v>
+        <v>28.72844196056582</v>
       </c>
       <c r="F203" t="n">
         <v>1048600</v>
@@ -4492,16 +4492,16 @@
         <v>44396</v>
       </c>
       <c r="B204" t="n">
-        <v>28.77314758300781</v>
+        <v>28.77314949035645</v>
       </c>
       <c r="C204" t="n">
-        <v>29.12185826943477</v>
+        <v>29.12186019989915</v>
       </c>
       <c r="D204" t="n">
-        <v>28.02207710038034</v>
+        <v>28.02207895794112</v>
       </c>
       <c r="E204" t="n">
-        <v>28.3842009169608</v>
+        <v>28.38420279852648</v>
       </c>
       <c r="F204" t="n">
         <v>866800</v>
@@ -4512,16 +4512,16 @@
         <v>44397</v>
       </c>
       <c r="B205" t="n">
-        <v>29.39904022216797</v>
+        <v>29.39904403686523</v>
       </c>
       <c r="C205" t="n">
-        <v>29.60469002671871</v>
+        <v>29.60469386810024</v>
       </c>
       <c r="D205" t="n">
-        <v>28.66138116422784</v>
+        <v>28.66138488320953</v>
       </c>
       <c r="E205" t="n">
-        <v>28.84020811931037</v>
+        <v>28.8402118614959</v>
       </c>
       <c r="F205" t="n">
         <v>665800</v>
@@ -4532,16 +4532,16 @@
         <v>44398</v>
       </c>
       <c r="B206" t="n">
-        <v>29.60469055175781</v>
+        <v>29.60468673706055</v>
       </c>
       <c r="C206" t="n">
-        <v>29.78351751001183</v>
+        <v>29.78351367227192</v>
       </c>
       <c r="D206" t="n">
-        <v>29.05926986396128</v>
+        <v>29.05926611954392</v>
       </c>
       <c r="E206" t="n">
-        <v>29.52869020302303</v>
+        <v>29.52868639811875</v>
       </c>
       <c r="F206" t="n">
         <v>1050200</v>
@@ -4552,16 +4552,16 @@
         <v>44399</v>
       </c>
       <c r="B207" t="n">
-        <v>30.17693519592285</v>
+        <v>30.17693138122559</v>
       </c>
       <c r="C207" t="n">
-        <v>30.65082375345648</v>
+        <v>30.65081987885448</v>
       </c>
       <c r="D207" t="n">
-        <v>29.62257467476647</v>
+        <v>29.62257093014648</v>
       </c>
       <c r="E207" t="n">
-        <v>29.69410341418633</v>
+        <v>29.69409966052432</v>
       </c>
       <c r="F207" t="n">
         <v>1168200</v>
@@ -4572,16 +4572,16 @@
         <v>44400</v>
       </c>
       <c r="B208" t="n">
-        <v>30.31105422973633</v>
+        <v>30.31105613708496</v>
       </c>
       <c r="C208" t="n">
-        <v>30.62399883893674</v>
+        <v>30.62400076597767</v>
       </c>
       <c r="D208" t="n">
-        <v>29.97128336057558</v>
+        <v>29.97128524654384</v>
       </c>
       <c r="E208" t="n">
-        <v>30.23952208429599</v>
+        <v>30.2395239871434</v>
       </c>
       <c r="F208" t="n">
         <v>819000</v>
@@ -4592,16 +4592,16 @@
         <v>44403</v>
       </c>
       <c r="B209" t="n">
-        <v>30.08752059936523</v>
+        <v>30.08752632141113</v>
       </c>
       <c r="C209" t="n">
-        <v>30.48987696893258</v>
+        <v>30.48988276749863</v>
       </c>
       <c r="D209" t="n">
-        <v>29.56445117941508</v>
+        <v>29.56445680198361</v>
       </c>
       <c r="E209" t="n">
-        <v>30.48987696893258</v>
+        <v>30.48988276749863</v>
       </c>
       <c r="F209" t="n">
         <v>1240800</v>
@@ -4612,16 +4612,16 @@
         <v>44404</v>
       </c>
       <c r="B210" t="n">
-        <v>29.40797996520996</v>
+        <v>29.40797805786133</v>
       </c>
       <c r="C210" t="n">
-        <v>30.1992881310479</v>
+        <v>30.19928617237645</v>
       </c>
       <c r="D210" t="n">
-        <v>29.30068515675142</v>
+        <v>29.30068325636174</v>
       </c>
       <c r="E210" t="n">
-        <v>29.98916671513793</v>
+        <v>29.98916477009458</v>
       </c>
       <c r="F210" t="n">
         <v>1032400</v>
@@ -4632,16 +4632,16 @@
         <v>44405</v>
       </c>
       <c r="B211" t="n">
-        <v>29.43927192687988</v>
+        <v>29.43927383422852</v>
       </c>
       <c r="C211" t="n">
-        <v>30.57034745860774</v>
+        <v>30.57034943923792</v>
       </c>
       <c r="D211" t="n">
-        <v>28.7329073919184</v>
+        <v>28.7329092535022</v>
       </c>
       <c r="E211" t="n">
-        <v>29.52868710203713</v>
+        <v>29.52868901517891</v>
       </c>
       <c r="F211" t="n">
         <v>1257400</v>
@@ -4652,16 +4652,16 @@
         <v>44406</v>
       </c>
       <c r="B212" t="n">
-        <v>30.84753227233887</v>
+        <v>30.8475341796875</v>
       </c>
       <c r="C212" t="n">
-        <v>31.51365918811201</v>
+        <v>31.51366113664825</v>
       </c>
       <c r="D212" t="n">
-        <v>29.56445252818104</v>
+        <v>29.56445435619494</v>
       </c>
       <c r="E212" t="n">
-        <v>29.56445252818104</v>
+        <v>29.56445435619494</v>
       </c>
       <c r="F212" t="n">
         <v>1386000</v>
@@ -4672,16 +4672,16 @@
         <v>44407</v>
       </c>
       <c r="B213" t="n">
-        <v>31.13812255859375</v>
+        <v>31.13812828063965</v>
       </c>
       <c r="C213" t="n">
-        <v>31.58071658787525</v>
+        <v>31.58072239125372</v>
       </c>
       <c r="D213" t="n">
-        <v>30.41387499271843</v>
+        <v>30.41388058167417</v>
       </c>
       <c r="E213" t="n">
-        <v>30.80282332805076</v>
+        <v>30.80282898848094</v>
       </c>
       <c r="F213" t="n">
         <v>1548200</v>
@@ -4692,16 +4692,16 @@
         <v>44410</v>
       </c>
       <c r="B214" t="n">
-        <v>31.2498893737793</v>
+        <v>31.24989128112793</v>
       </c>
       <c r="C214" t="n">
-        <v>31.98754837270211</v>
+        <v>31.98755032507403</v>
       </c>
       <c r="D214" t="n">
-        <v>31.03976797418139</v>
+        <v>31.03976986870518</v>
       </c>
       <c r="E214" t="n">
-        <v>31.5807169971674</v>
+        <v>31.58071892470821</v>
       </c>
       <c r="F214" t="n">
         <v>1185600</v>
@@ -4732,16 +4732,16 @@
         <v>44412</v>
       </c>
       <c r="B216" t="n">
-        <v>29.78798484802246</v>
+        <v>29.78798675537109</v>
       </c>
       <c r="C216" t="n">
-        <v>30.84753173103446</v>
+        <v>30.84753370622673</v>
       </c>
       <c r="D216" t="n">
-        <v>29.75669038704778</v>
+        <v>29.7566922923926</v>
       </c>
       <c r="E216" t="n">
-        <v>30.62399889240378</v>
+        <v>30.62400085328306</v>
       </c>
       <c r="F216" t="n">
         <v>1263400</v>
@@ -4752,16 +4752,16 @@
         <v>44413</v>
       </c>
       <c r="B217" t="n">
-        <v>29.48397827148438</v>
+        <v>29.48398208618164</v>
       </c>
       <c r="C217" t="n">
-        <v>30.38705279511604</v>
+        <v>30.38705672665493</v>
       </c>
       <c r="D217" t="n">
-        <v>29.13973922154018</v>
+        <v>29.13974299169909</v>
       </c>
       <c r="E217" t="n">
-        <v>29.82374912073076</v>
+        <v>29.82375297938827</v>
       </c>
       <c r="F217" t="n">
         <v>1197200</v>
@@ -4772,16 +4772,16 @@
         <v>44414</v>
       </c>
       <c r="B218" t="n">
-        <v>29.46162986755371</v>
+        <v>29.46162796020508</v>
       </c>
       <c r="C218" t="n">
-        <v>29.99810733512132</v>
+        <v>29.99810539304109</v>
       </c>
       <c r="D218" t="n">
-        <v>29.10397594861493</v>
+        <v>29.10397406442085</v>
       </c>
       <c r="E218" t="n">
-        <v>29.975756096963</v>
+        <v>29.97575415632978</v>
       </c>
       <c r="F218" t="n">
         <v>684400</v>
@@ -4792,16 +4792,16 @@
         <v>44417</v>
       </c>
       <c r="B219" t="n">
-        <v>30.23952102661133</v>
+        <v>30.23952484130859</v>
       </c>
       <c r="C219" t="n">
-        <v>30.40493654902606</v>
+        <v>30.4049403845904</v>
       </c>
       <c r="D219" t="n">
-        <v>29.54209968716381</v>
+        <v>29.54210341388179</v>
       </c>
       <c r="E219" t="n">
-        <v>29.85951589706211</v>
+        <v>29.85951966382196</v>
       </c>
       <c r="F219" t="n">
         <v>1023000</v>
@@ -4832,16 +4832,16 @@
         <v>44419</v>
       </c>
       <c r="B221" t="n">
-        <v>29.1129207611084</v>
+        <v>29.11291885375977</v>
       </c>
       <c r="C221" t="n">
-        <v>30.38258576202377</v>
+        <v>30.38258377149235</v>
       </c>
       <c r="D221" t="n">
-        <v>28.14725717378623</v>
+        <v>28.14725532970356</v>
       </c>
       <c r="E221" t="n">
-        <v>29.68516433396269</v>
+        <v>29.68516238912321</v>
       </c>
       <c r="F221" t="n">
         <v>1237750</v>
@@ -4852,16 +4852,16 @@
         <v>44420</v>
       </c>
       <c r="B222" t="n">
-        <v>29.32751083374023</v>
+        <v>29.32750701904297</v>
       </c>
       <c r="C222" t="n">
-        <v>31.18730588414776</v>
+        <v>31.18730182754265</v>
       </c>
       <c r="D222" t="n">
-        <v>28.46914546163251</v>
+        <v>28.46914175858482</v>
       </c>
       <c r="E222" t="n">
-        <v>28.48702849990652</v>
+        <v>28.48702479453274</v>
       </c>
       <c r="F222" t="n">
         <v>1567750</v>
@@ -4872,16 +4872,16 @@
         <v>44421</v>
       </c>
       <c r="B223" t="n">
-        <v>28.34396553039551</v>
+        <v>28.34396743774414</v>
       </c>
       <c r="C223" t="n">
-        <v>29.59574742040596</v>
+        <v>29.59574941199067</v>
       </c>
       <c r="D223" t="n">
-        <v>27.18159370895106</v>
+        <v>27.18159553808027</v>
       </c>
       <c r="E223" t="n">
-        <v>29.50633564641969</v>
+        <v>29.50633763198762</v>
       </c>
       <c r="F223" t="n">
         <v>1962050</v>
@@ -4912,16 +4912,16 @@
         <v>44425</v>
       </c>
       <c r="B225" t="n">
-        <v>25.66157150268555</v>
+        <v>25.66156959533691</v>
       </c>
       <c r="C225" t="n">
-        <v>25.66157150268555</v>
+        <v>25.66156959533691</v>
       </c>
       <c r="D225" t="n">
-        <v>23.42624303399936</v>
+        <v>23.42624129279607</v>
       </c>
       <c r="E225" t="n">
-        <v>24.67802663537957</v>
+        <v>24.67802480113491</v>
       </c>
       <c r="F225" t="n">
         <v>4282800</v>
@@ -4952,16 +4952,16 @@
         <v>44427</v>
       </c>
       <c r="B227" t="n">
-        <v>26.46628761291504</v>
+        <v>26.4662914276123</v>
       </c>
       <c r="C227" t="n">
-        <v>26.73452632877229</v>
+        <v>26.73453018213193</v>
       </c>
       <c r="D227" t="n">
-        <v>24.3024897339607</v>
+        <v>24.30249323678068</v>
       </c>
       <c r="E227" t="n">
-        <v>24.85685020151106</v>
+        <v>24.85685378423334</v>
       </c>
       <c r="F227" t="n">
         <v>1738450</v>
@@ -4972,16 +4972,16 @@
         <v>44428</v>
       </c>
       <c r="B228" t="n">
-        <v>26.64511680603027</v>
+        <v>26.64511299133301</v>
       </c>
       <c r="C228" t="n">
-        <v>26.87759119010796</v>
+        <v>26.87758734212807</v>
       </c>
       <c r="D228" t="n">
-        <v>25.73310401362756</v>
+        <v>25.73310032950029</v>
       </c>
       <c r="E228" t="n">
-        <v>26.34111197342256</v>
+        <v>26.34110820224871</v>
       </c>
       <c r="F228" t="n">
         <v>1186050</v>
@@ -5032,16 +5032,16 @@
         <v>44433</v>
       </c>
       <c r="B231" t="n">
-        <v>27.89689636230469</v>
+        <v>27.89690017700195</v>
       </c>
       <c r="C231" t="n">
-        <v>28.41549243173145</v>
+        <v>28.41549631734295</v>
       </c>
       <c r="D231" t="n">
-        <v>27.27100378987718</v>
+        <v>27.27100751898821</v>
       </c>
       <c r="E231" t="n">
-        <v>27.4855950904586</v>
+        <v>27.48559884891342</v>
       </c>
       <c r="F231" t="n">
         <v>1098800</v>
@@ -5072,16 +5072,16 @@
         <v>44435</v>
       </c>
       <c r="B233" t="n">
-        <v>28.9698600769043</v>
+        <v>28.96985626220703</v>
       </c>
       <c r="C233" t="n">
-        <v>29.11292097115001</v>
+        <v>29.11291713761476</v>
       </c>
       <c r="D233" t="n">
-        <v>27.00277022289511</v>
+        <v>27.00276666722057</v>
       </c>
       <c r="E233" t="n">
-        <v>27.44983594376807</v>
+        <v>27.44983232922475</v>
       </c>
       <c r="F233" t="n">
         <v>1634000</v>
@@ -5112,16 +5112,16 @@
         <v>44439</v>
       </c>
       <c r="B235" t="n">
-        <v>26.55570220947266</v>
+        <v>26.55570030212402</v>
       </c>
       <c r="C235" t="n">
-        <v>27.86113318312228</v>
+        <v>27.86113118201179</v>
       </c>
       <c r="D235" t="n">
-        <v>25.87616216775989</v>
+        <v>25.87616030921885</v>
       </c>
       <c r="E235" t="n">
-        <v>27.68230622804304</v>
+        <v>27.6823042397767</v>
       </c>
       <c r="F235" t="n">
         <v>1705500</v>
@@ -5152,16 +5152,16 @@
         <v>44441</v>
       </c>
       <c r="B237" t="n">
-        <v>25.35756492614746</v>
+        <v>25.35756683349609</v>
       </c>
       <c r="C237" t="n">
-        <v>26.66299584222149</v>
+        <v>26.6629978477622</v>
       </c>
       <c r="D237" t="n">
-        <v>25.10720754116251</v>
+        <v>25.10720942967972</v>
       </c>
       <c r="E237" t="n">
-        <v>26.59146540442867</v>
+        <v>26.59146740458899</v>
       </c>
       <c r="F237" t="n">
         <v>1706000</v>
@@ -5192,16 +5192,16 @@
         <v>44445</v>
       </c>
       <c r="B239" t="n">
-        <v>25.76886749267578</v>
+        <v>25.76886558532715</v>
       </c>
       <c r="C239" t="n">
-        <v>25.89404534691268</v>
+        <v>25.89404343029868</v>
       </c>
       <c r="D239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="E239" t="n">
-        <v>24.87473606430857</v>
+        <v>24.87473422314136</v>
       </c>
       <c r="F239" t="n">
         <v>528250</v>
@@ -5252,16 +5252,16 @@
         <v>44449</v>
       </c>
       <c r="B242" t="n">
-        <v>25.19662094116211</v>
+        <v>25.19662666320801</v>
       </c>
       <c r="C242" t="n">
-        <v>26.19804706733655</v>
+        <v>26.19805301680208</v>
       </c>
       <c r="D242" t="n">
-        <v>24.64225877082185</v>
+        <v>24.64226436697445</v>
       </c>
       <c r="E242" t="n">
-        <v>26.0013387903359</v>
+        <v>26.00134469512981</v>
       </c>
       <c r="F242" t="n">
         <v>1514650</v>
@@ -5352,16 +5352,16 @@
         <v>44456</v>
       </c>
       <c r="B247" t="n">
-        <v>24.98203086853027</v>
+        <v>24.98203277587891</v>
       </c>
       <c r="C247" t="n">
-        <v>26.00134008105472</v>
+        <v>26.00134206622641</v>
       </c>
       <c r="D247" t="n">
-        <v>24.98203086853027</v>
+        <v>24.98203277587891</v>
       </c>
       <c r="E247" t="n">
-        <v>25.64368787538125</v>
+        <v>25.64368983324662</v>
       </c>
       <c r="F247" t="n">
         <v>2806100</v>
@@ -5372,16 +5372,16 @@
         <v>44459</v>
       </c>
       <c r="B248" t="n">
-        <v>24.17731094360352</v>
+        <v>24.17731475830078</v>
       </c>
       <c r="C248" t="n">
-        <v>24.58861051914021</v>
+        <v>24.58861439873235</v>
       </c>
       <c r="D248" t="n">
-        <v>23.71236226266804</v>
+        <v>23.71236600400568</v>
       </c>
       <c r="E248" t="n">
-        <v>24.3740192138054</v>
+        <v>24.37402305953931</v>
       </c>
       <c r="F248" t="n">
         <v>1148950</v>
@@ -5412,16 +5412,16 @@
         <v>44461</v>
       </c>
       <c r="B250" t="n">
-        <v>25.48274421691895</v>
+        <v>25.48274612426758</v>
       </c>
       <c r="C250" t="n">
-        <v>26.37687559295119</v>
+        <v>26.37687756722434</v>
       </c>
       <c r="D250" t="n">
-        <v>25.23238681767862</v>
+        <v>25.23238870628835</v>
       </c>
       <c r="E250" t="n">
-        <v>25.92980990493507</v>
+        <v>25.92981184574596</v>
       </c>
       <c r="F250" t="n">
         <v>900000</v>
@@ -5432,16 +5432,16 @@
         <v>44462</v>
       </c>
       <c r="B251" t="n">
-        <v>26.28746223449707</v>
+        <v>26.2874641418457</v>
       </c>
       <c r="C251" t="n">
-        <v>26.69876355617164</v>
+        <v>26.6987654933632</v>
       </c>
       <c r="D251" t="n">
-        <v>25.32180041218233</v>
+        <v>25.3218022494651</v>
       </c>
       <c r="E251" t="n">
-        <v>25.32180041218233</v>
+        <v>25.3218022494651</v>
       </c>
       <c r="F251" t="n">
         <v>1394250</v>
@@ -5452,16 +5452,16 @@
         <v>44463</v>
       </c>
       <c r="B252" t="n">
-        <v>25.89404487609863</v>
+        <v>25.89404296875</v>
       </c>
       <c r="C252" t="n">
-        <v>26.1980496926496</v>
+        <v>26.19804776290805</v>
       </c>
       <c r="D252" t="n">
-        <v>25.39333176283482</v>
+        <v>25.39332989236859</v>
       </c>
       <c r="E252" t="n">
-        <v>26.1980496926496</v>
+        <v>26.19804776290805</v>
       </c>
       <c r="F252" t="n">
         <v>1097400</v>
@@ -5492,16 +5492,16 @@
         <v>44467</v>
       </c>
       <c r="B254" t="n">
-        <v>24.83897018432617</v>
+        <v>24.83896827697754</v>
       </c>
       <c r="C254" t="n">
-        <v>25.80463200005482</v>
+        <v>25.80463001855441</v>
       </c>
       <c r="D254" t="n">
-        <v>24.44555190223813</v>
+        <v>24.44555002509952</v>
       </c>
       <c r="E254" t="n">
-        <v>25.75098288971082</v>
+        <v>25.75098091233005</v>
       </c>
       <c r="F254" t="n">
         <v>1020250</v>
@@ -5572,16 +5572,16 @@
         <v>44473</v>
       </c>
       <c r="B258" t="n">
-        <v>23.8733081817627</v>
+        <v>23.87330627441406</v>
       </c>
       <c r="C258" t="n">
-        <v>25.10720871787369</v>
+        <v>25.10720671194305</v>
       </c>
       <c r="D258" t="n">
-        <v>23.8733081817627</v>
+        <v>23.87330627441406</v>
       </c>
       <c r="E258" t="n">
-        <v>25.01779524008704</v>
+        <v>25.01779324130006</v>
       </c>
       <c r="F258" t="n">
         <v>576500</v>
@@ -5632,16 +5632,16 @@
         <v>44476</v>
       </c>
       <c r="B261" t="n">
-        <v>23.62295341491699</v>
+        <v>23.62294960021973</v>
       </c>
       <c r="C261" t="n">
-        <v>24.26672745689388</v>
+        <v>24.26672353823827</v>
       </c>
       <c r="D261" t="n">
-        <v>23.42624510622361</v>
+        <v>23.42624132329132</v>
       </c>
       <c r="E261" t="n">
-        <v>24.15943263594128</v>
+        <v>24.15942873461192</v>
       </c>
       <c r="F261" t="n">
         <v>699850</v>
@@ -5672,16 +5672,16 @@
         <v>44480</v>
       </c>
       <c r="B263" t="n">
-        <v>24.08789825439453</v>
+        <v>24.08790016174316</v>
       </c>
       <c r="C263" t="n">
-        <v>24.60649435212385</v>
+        <v>24.60649630053641</v>
       </c>
       <c r="D263" t="n">
-        <v>23.73024606723985</v>
+        <v>23.73024794626857</v>
       </c>
       <c r="E263" t="n">
-        <v>24.03424914725622</v>
+        <v>24.03425105035676</v>
       </c>
       <c r="F263" t="n">
         <v>770500</v>
@@ -5692,16 +5692,16 @@
         <v>44482</v>
       </c>
       <c r="B264" t="n">
-        <v>24.35613632202148</v>
+        <v>24.35613822937012</v>
       </c>
       <c r="C264" t="n">
-        <v>24.99991024181488</v>
+        <v>24.99991219957796</v>
       </c>
       <c r="D264" t="n">
-        <v>23.99848414435849</v>
+        <v>23.99848602369909</v>
       </c>
       <c r="E264" t="n">
-        <v>24.21307545095629</v>
+        <v>24.21307734710171</v>
       </c>
       <c r="F264" t="n">
         <v>670150</v>
@@ -5752,16 +5752,16 @@
         <v>44487</v>
       </c>
       <c r="B267" t="n">
-        <v>26.28746223449707</v>
+        <v>26.2874641418457</v>
       </c>
       <c r="C267" t="n">
-        <v>27.37830360971465</v>
+        <v>27.37830559621184</v>
       </c>
       <c r="D267" t="n">
-        <v>25.6973356600503</v>
+        <v>25.69733752458091</v>
       </c>
       <c r="E267" t="n">
-        <v>26.6093500770754</v>
+        <v>26.60935200777937</v>
       </c>
       <c r="F267" t="n">
         <v>1715900</v>
@@ -5792,16 +5792,16 @@
         <v>44489</v>
       </c>
       <c r="B269" t="n">
-        <v>23.89119148254395</v>
+        <v>23.89118957519531</v>
       </c>
       <c r="C269" t="n">
-        <v>24.94626685548099</v>
+        <v>24.94626486390061</v>
       </c>
       <c r="D269" t="n">
-        <v>23.19377005023805</v>
+        <v>23.19376819856792</v>
       </c>
       <c r="E269" t="n">
-        <v>24.8568533703232</v>
+        <v>24.85685138588114</v>
       </c>
       <c r="F269" t="n">
         <v>1327650</v>
@@ -5812,16 +5812,16 @@
         <v>44490</v>
       </c>
       <c r="B270" t="n">
-        <v>22.44269752502441</v>
+        <v>22.44269943237305</v>
       </c>
       <c r="C270" t="n">
-        <v>23.46200673186731</v>
+        <v>23.46200872584448</v>
       </c>
       <c r="D270" t="n">
-        <v>21.67374400804736</v>
+        <v>21.67374585004456</v>
       </c>
       <c r="E270" t="n">
-        <v>22.8897632059794</v>
+        <v>22.88976515132303</v>
       </c>
       <c r="F270" t="n">
         <v>1908000</v>
@@ -5832,16 +5832,16 @@
         <v>44491</v>
       </c>
       <c r="B271" t="n">
-        <v>21.08361625671387</v>
+        <v>21.0836181640625</v>
       </c>
       <c r="C271" t="n">
-        <v>21.99563060373434</v>
+        <v>21.99563259358919</v>
       </c>
       <c r="D271" t="n">
-        <v>19.81394972618147</v>
+        <v>19.81395151866856</v>
       </c>
       <c r="E271" t="n">
-        <v>21.99563060373434</v>
+        <v>21.99563259358919</v>
       </c>
       <c r="F271" t="n">
         <v>3185950</v>
@@ -5852,16 +5852,16 @@
         <v>44494</v>
       </c>
       <c r="B272" t="n">
-        <v>21.6201000213623</v>
+        <v>21.62009620666504</v>
       </c>
       <c r="C272" t="n">
-        <v>22.28175712911409</v>
+        <v>22.28175319767261</v>
       </c>
       <c r="D272" t="n">
-        <v>20.79749897015891</v>
+        <v>20.79749530060315</v>
       </c>
       <c r="E272" t="n">
-        <v>20.8332633434701</v>
+        <v>20.833259667604</v>
       </c>
       <c r="F272" t="n">
         <v>1833600</v>
@@ -5892,16 +5892,16 @@
         <v>44496</v>
       </c>
       <c r="B274" t="n">
-        <v>20.49349021911621</v>
+        <v>20.49349212646484</v>
       </c>
       <c r="C274" t="n">
-        <v>21.1014997983801</v>
+        <v>21.10150176231677</v>
       </c>
       <c r="D274" t="n">
-        <v>20.31466327036089</v>
+        <v>20.31466516106592</v>
       </c>
       <c r="E274" t="n">
-        <v>20.42195978069811</v>
+        <v>20.42196168138934</v>
       </c>
       <c r="F274" t="n">
         <v>1013650</v>
@@ -5952,16 +5952,16 @@
         <v>44501</v>
       </c>
       <c r="B277" t="n">
-        <v>18.77675819396973</v>
+        <v>18.77676010131836</v>
       </c>
       <c r="C277" t="n">
-        <v>19.40265081593679</v>
+        <v>19.40265278686379</v>
       </c>
       <c r="D277" t="n">
-        <v>18.68734471862869</v>
+        <v>18.68734661689468</v>
       </c>
       <c r="E277" t="n">
-        <v>18.77675819396973</v>
+        <v>18.77676010131836</v>
       </c>
       <c r="F277" t="n">
         <v>1843300</v>
@@ -5992,16 +5992,16 @@
         <v>44504</v>
       </c>
       <c r="B279" t="n">
-        <v>19.97489547729492</v>
+        <v>19.97489738464355</v>
       </c>
       <c r="C279" t="n">
-        <v>21.31609256822115</v>
+        <v>21.31609460363706</v>
       </c>
       <c r="D279" t="n">
-        <v>19.58147718643888</v>
+        <v>19.58147905622107</v>
       </c>
       <c r="E279" t="n">
-        <v>20.04642592059417</v>
+        <v>20.04642783477306</v>
       </c>
       <c r="F279" t="n">
         <v>1953350</v>
@@ -6012,16 +6012,16 @@
         <v>44505</v>
       </c>
       <c r="B280" t="n">
-        <v>20.42196083068848</v>
+        <v>20.42196273803711</v>
       </c>
       <c r="C280" t="n">
-        <v>20.94055696223821</v>
+        <v>20.94055891802213</v>
       </c>
       <c r="D280" t="n">
-        <v>19.99277817811358</v>
+        <v>19.99278004537787</v>
       </c>
       <c r="E280" t="n">
-        <v>20.20736950440103</v>
+        <v>20.20737139170749</v>
       </c>
       <c r="F280" t="n">
         <v>901950</v>
@@ -6032,16 +6032,16 @@
         <v>44508</v>
       </c>
       <c r="B281" t="n">
-        <v>20.13583755493164</v>
+        <v>20.13584136962891</v>
       </c>
       <c r="C281" t="n">
-        <v>20.86902495788224</v>
+        <v>20.8690289114805</v>
       </c>
       <c r="D281" t="n">
-        <v>19.86759713808767</v>
+        <v>19.86760090196729</v>
       </c>
       <c r="E281" t="n">
-        <v>20.86902495788224</v>
+        <v>20.8690289114805</v>
       </c>
       <c r="F281" t="n">
         <v>919700</v>
@@ -6052,16 +6052,16 @@
         <v>44509</v>
       </c>
       <c r="B282" t="n">
-        <v>20.67231941223145</v>
+        <v>20.67231750488281</v>
       </c>
       <c r="C282" t="n">
-        <v>21.36974083617073</v>
+        <v>21.36973886447393</v>
       </c>
       <c r="D282" t="n">
-        <v>20.29678414341015</v>
+        <v>20.29678227071059</v>
       </c>
       <c r="E282" t="n">
-        <v>20.29678414341015</v>
+        <v>20.29678227071059</v>
       </c>
       <c r="F282" t="n">
         <v>912150</v>
@@ -6072,16 +6072,16 @@
         <v>44510</v>
       </c>
       <c r="B283" t="n">
-        <v>21.08361625671387</v>
+        <v>21.0836181640625</v>
       </c>
       <c r="C283" t="n">
-        <v>21.65585975033293</v>
+        <v>21.65586170945009</v>
       </c>
       <c r="D283" t="n">
-        <v>20.49348972756417</v>
+        <v>20.49349158152647</v>
       </c>
       <c r="E283" t="n">
-        <v>20.88690798213735</v>
+        <v>20.88690987169059</v>
       </c>
       <c r="F283" t="n">
         <v>1309800</v>
@@ -6092,16 +6092,16 @@
         <v>44511</v>
       </c>
       <c r="B284" t="n">
-        <v>21.94198417663574</v>
+        <v>21.94198226928711</v>
       </c>
       <c r="C284" t="n">
-        <v>22.99705773847886</v>
+        <v>22.99705573941596</v>
       </c>
       <c r="D284" t="n">
-        <v>21.78104026055555</v>
+        <v>21.78103836719727</v>
       </c>
       <c r="E284" t="n">
-        <v>21.95986550754004</v>
+        <v>21.95986359863704</v>
       </c>
       <c r="F284" t="n">
         <v>2031350</v>
@@ -6112,16 +6112,16 @@
         <v>44512</v>
       </c>
       <c r="B285" t="n">
-        <v>21.08361625671387</v>
+        <v>21.0836181640625</v>
       </c>
       <c r="C285" t="n">
-        <v>22.12080844160848</v>
+        <v>22.12081044278765</v>
       </c>
       <c r="D285" t="n">
-        <v>21.08361625671387</v>
+        <v>21.0836181640625</v>
       </c>
       <c r="E285" t="n">
-        <v>21.76315625809657</v>
+        <v>21.76315822692041</v>
       </c>
       <c r="F285" t="n">
         <v>1307150</v>
@@ -6132,16 +6132,16 @@
         <v>44516</v>
       </c>
       <c r="B286" t="n">
-        <v>20.63655471801758</v>
+        <v>20.63655090332031</v>
       </c>
       <c r="C286" t="n">
-        <v>21.87045542365525</v>
+        <v>21.87045138086964</v>
       </c>
       <c r="D286" t="n">
-        <v>19.77818930634276</v>
+        <v>19.77818565031559</v>
       </c>
       <c r="E286" t="n">
-        <v>21.76316059990614</v>
+        <v>21.76315657695413</v>
       </c>
       <c r="F286" t="n">
         <v>1709550</v>
@@ -6192,16 +6192,16 @@
         <v>44519</v>
       </c>
       <c r="B289" t="n">
-        <v>20.99420547485352</v>
+        <v>20.99420356750488</v>
       </c>
       <c r="C289" t="n">
-        <v>21.24456288810481</v>
+        <v>21.24456095801091</v>
       </c>
       <c r="D289" t="n">
-        <v>20.11795708660452</v>
+        <v>20.11795525886409</v>
       </c>
       <c r="E289" t="n">
-        <v>20.31466538638888</v>
+        <v>20.31466354077727</v>
       </c>
       <c r="F289" t="n">
         <v>767750</v>
@@ -6212,16 +6212,16 @@
         <v>44522</v>
       </c>
       <c r="B290" t="n">
-        <v>20.18948554992676</v>
+        <v>20.18948745727539</v>
       </c>
       <c r="C290" t="n">
-        <v>21.44126908242115</v>
+        <v>21.44127110802875</v>
       </c>
       <c r="D290" t="n">
-        <v>19.97489423339231</v>
+        <v>19.97489612046799</v>
       </c>
       <c r="E290" t="n">
-        <v>20.86902557166261</v>
+        <v>20.869027543209</v>
       </c>
       <c r="F290" t="n">
         <v>852100</v>
@@ -6232,16 +6232,16 @@
         <v>44523</v>
       </c>
       <c r="B291" t="n">
-        <v>19.24170875549316</v>
+        <v>19.24170684814453</v>
       </c>
       <c r="C291" t="n">
-        <v>20.45772633887523</v>
+        <v>20.45772431098796</v>
       </c>
       <c r="D291" t="n">
-        <v>19.02711741724927</v>
+        <v>19.02711553117216</v>
       </c>
       <c r="E291" t="n">
-        <v>20.20737063030087</v>
+        <v>20.20736862723029</v>
       </c>
       <c r="F291" t="n">
         <v>1896750</v>
@@ -6252,16 +6252,16 @@
         <v>44524</v>
       </c>
       <c r="B292" t="n">
-        <v>19.58147811889648</v>
+        <v>19.58147430419922</v>
       </c>
       <c r="C292" t="n">
-        <v>20.3325486620143</v>
+        <v>20.33254470099985</v>
       </c>
       <c r="D292" t="n">
-        <v>19.02711758328404</v>
+        <v>19.02711387658259</v>
       </c>
       <c r="E292" t="n">
-        <v>19.04499891589514</v>
+        <v>19.04499520571019</v>
       </c>
       <c r="F292" t="n">
         <v>1594900</v>
@@ -6312,16 +6312,16 @@
         <v>44529</v>
       </c>
       <c r="B295" t="n">
-        <v>19.20594024658203</v>
+        <v>19.20594215393066</v>
       </c>
       <c r="C295" t="n">
-        <v>20.33254590870044</v>
+        <v>20.33254792793267</v>
       </c>
       <c r="D295" t="n">
-        <v>19.06287937254352</v>
+        <v>19.06288126568472</v>
       </c>
       <c r="E295" t="n">
-        <v>20.33254590870044</v>
+        <v>20.33254792793267</v>
       </c>
       <c r="F295" t="n">
         <v>830750</v>
@@ -6332,16 +6332,16 @@
         <v>44530</v>
       </c>
       <c r="B296" t="n">
-        <v>18.83040809631348</v>
+        <v>18.83040618896484</v>
       </c>
       <c r="C296" t="n">
-        <v>19.25959249383086</v>
+        <v>19.25959054300976</v>
       </c>
       <c r="D296" t="n">
-        <v>18.06145619932819</v>
+        <v>18.06145436986738</v>
       </c>
       <c r="E296" t="n">
-        <v>19.04499944236196</v>
+        <v>19.04499751327718</v>
       </c>
       <c r="F296" t="n">
         <v>1327800</v>
@@ -6372,16 +6372,16 @@
         <v>44532</v>
       </c>
       <c r="B298" t="n">
-        <v>18.59793281555176</v>
+        <v>18.59793090820312</v>
       </c>
       <c r="C298" t="n">
-        <v>18.86617326425185</v>
+        <v>18.86617132939327</v>
       </c>
       <c r="D298" t="n">
-        <v>18.11510273656414</v>
+        <v>18.11510087873313</v>
       </c>
       <c r="E298" t="n">
-        <v>18.22239755170791</v>
+        <v>18.22239568287305</v>
       </c>
       <c r="F298" t="n">
         <v>961350</v>
@@ -6412,16 +6412,16 @@
         <v>44536</v>
       </c>
       <c r="B300" t="n">
-        <v>19.97489547729492</v>
+        <v>19.97489738464355</v>
       </c>
       <c r="C300" t="n">
-        <v>20.38619509991056</v>
+        <v>20.38619704653308</v>
       </c>
       <c r="D300" t="n">
-        <v>19.56359414925899</v>
+        <v>19.56359601733358</v>
       </c>
       <c r="E300" t="n">
-        <v>20.08219028953366</v>
+        <v>20.08219220712758</v>
       </c>
       <c r="F300" t="n">
         <v>963750</v>
@@ -6432,16 +6432,16 @@
         <v>44537</v>
       </c>
       <c r="B301" t="n">
-        <v>19.93912887573242</v>
+        <v>19.93912696838379</v>
       </c>
       <c r="C301" t="n">
-        <v>20.72596543664007</v>
+        <v>20.72596345402377</v>
       </c>
       <c r="D301" t="n">
-        <v>19.90336450773857</v>
+        <v>19.90336260381111</v>
       </c>
       <c r="E301" t="n">
-        <v>20.35043019289329</v>
+        <v>20.35042824620016</v>
       </c>
       <c r="F301" t="n">
         <v>881500</v>
@@ -6452,16 +6452,16 @@
         <v>44538</v>
       </c>
       <c r="B302" t="n">
-        <v>21.42338752746582</v>
+        <v>21.42338562011719</v>
       </c>
       <c r="C302" t="n">
-        <v>21.51280100855851</v>
+        <v>21.51279909324929</v>
       </c>
       <c r="D302" t="n">
-        <v>19.86759909596611</v>
+        <v>19.86759732713109</v>
       </c>
       <c r="E302" t="n">
-        <v>20.18948694573167</v>
+        <v>20.18948514823861</v>
       </c>
       <c r="F302" t="n">
         <v>984450</v>
@@ -6472,16 +6472,16 @@
         <v>44539</v>
       </c>
       <c r="B303" t="n">
-        <v>20.90478897094727</v>
+        <v>20.90479278564453</v>
       </c>
       <c r="C303" t="n">
-        <v>21.36973765463187</v>
+        <v>21.36974155417278</v>
       </c>
       <c r="D303" t="n">
-        <v>20.72596373482095</v>
+        <v>20.72596751688626</v>
       </c>
       <c r="E303" t="n">
-        <v>21.24455981880144</v>
+        <v>21.24456369549995</v>
       </c>
       <c r="F303" t="n">
         <v>669550</v>
@@ -6492,16 +6492,16 @@
         <v>44540</v>
       </c>
       <c r="B304" t="n">
-        <v>21.81680679321289</v>
+        <v>21.81680297851562</v>
       </c>
       <c r="C304" t="n">
-        <v>22.19234206620039</v>
+        <v>22.19233818584029</v>
       </c>
       <c r="D304" t="n">
-        <v>21.06573624723789</v>
+        <v>21.06573256386629</v>
       </c>
       <c r="E304" t="n">
-        <v>22.13869465732228</v>
+        <v>22.1386907863425</v>
       </c>
       <c r="F304" t="n">
         <v>899500</v>
@@ -6512,16 +6512,16 @@
         <v>44543</v>
       </c>
       <c r="B305" t="n">
-        <v>21.78104209899902</v>
+        <v>21.78104019165039</v>
       </c>
       <c r="C305" t="n">
-        <v>22.51422959598714</v>
+        <v>22.51422762443386</v>
       </c>
       <c r="D305" t="n">
-        <v>21.40550683158799</v>
+        <v>21.40550495712469</v>
       </c>
       <c r="E305" t="n">
-        <v>22.13869432857611</v>
+        <v>22.13869238990815</v>
       </c>
       <c r="F305" t="n">
         <v>1400500</v>
@@ -6532,16 +6532,16 @@
         <v>44544</v>
       </c>
       <c r="B306" t="n">
-        <v>21.49491882324219</v>
+        <v>21.49491691589355</v>
       </c>
       <c r="C306" t="n">
-        <v>22.06716235084257</v>
+        <v>22.06716039271598</v>
       </c>
       <c r="D306" t="n">
-        <v>21.22667839061434</v>
+        <v>21.22667650706798</v>
       </c>
       <c r="E306" t="n">
-        <v>21.95986583670738</v>
+        <v>21.95986388810174</v>
       </c>
       <c r="F306" t="n">
         <v>979700</v>
@@ -6552,16 +6552,16 @@
         <v>44545</v>
       </c>
       <c r="B307" t="n">
-        <v>22.03139495849609</v>
+        <v>22.03139686584473</v>
       </c>
       <c r="C307" t="n">
-        <v>22.37116581172973</v>
+        <v>22.37116774849373</v>
       </c>
       <c r="D307" t="n">
-        <v>21.11938231734611</v>
+        <v>21.11938414573805</v>
       </c>
       <c r="E307" t="n">
-        <v>21.45915146515961</v>
+        <v>21.45915332296677</v>
       </c>
       <c r="F307" t="n">
         <v>1028800</v>
@@ -6572,16 +6572,16 @@
         <v>44546</v>
       </c>
       <c r="B308" t="n">
-        <v>21.94198417663574</v>
+        <v>21.94198226928711</v>
       </c>
       <c r="C308" t="n">
-        <v>22.97917640757456</v>
+        <v>22.97917441006602</v>
       </c>
       <c r="D308" t="n">
-        <v>21.53068286827299</v>
+        <v>21.53068099667751</v>
       </c>
       <c r="E308" t="n">
-        <v>22.53211073198299</v>
+        <v>22.53210877333649</v>
       </c>
       <c r="F308" t="n">
         <v>888550</v>
@@ -6592,16 +6592,16 @@
         <v>44547</v>
       </c>
       <c r="B309" t="n">
-        <v>22.37116622924805</v>
+        <v>22.37116813659668</v>
       </c>
       <c r="C309" t="n">
-        <v>22.72881841925829</v>
+        <v>22.72882035710008</v>
       </c>
       <c r="D309" t="n">
-        <v>21.42338579394568</v>
+        <v>21.42338762048728</v>
       </c>
       <c r="E309" t="n">
-        <v>21.56644837536995</v>
+        <v>21.56645021410895</v>
       </c>
       <c r="F309" t="n">
         <v>2194100</v>
@@ -6612,16 +6612,16 @@
         <v>44550</v>
       </c>
       <c r="B310" t="n">
-        <v>22.01351356506348</v>
+        <v>22.01351547241211</v>
       </c>
       <c r="C310" t="n">
-        <v>22.42481314836077</v>
+        <v>22.42481509134622</v>
       </c>
       <c r="D310" t="n">
-        <v>21.13726358663772</v>
+        <v>21.13726541806416</v>
       </c>
       <c r="E310" t="n">
-        <v>22.35328271189949</v>
+        <v>22.35328464868723</v>
       </c>
       <c r="F310" t="n">
         <v>1565700</v>
@@ -6632,16 +6632,16 @@
         <v>44551</v>
       </c>
       <c r="B311" t="n">
-        <v>21.38762092590332</v>
+        <v>21.38762283325195</v>
       </c>
       <c r="C311" t="n">
-        <v>22.19233876090282</v>
+        <v>22.19234074001621</v>
       </c>
       <c r="D311" t="n">
-        <v>21.38762092590332</v>
+        <v>21.38762283325195</v>
       </c>
       <c r="E311" t="n">
-        <v>22.0313948528189</v>
+        <v>22.0313968175793</v>
       </c>
       <c r="F311" t="n">
         <v>785250</v>
@@ -6652,16 +6652,16 @@
         <v>44552</v>
       </c>
       <c r="B312" t="n">
-        <v>21.45915603637695</v>
+        <v>21.45915412902832</v>
       </c>
       <c r="C312" t="n">
-        <v>21.78104392265717</v>
+        <v>21.78104198669826</v>
       </c>
       <c r="D312" t="n">
-        <v>20.65443802609692</v>
+        <v>20.65443619027383</v>
       </c>
       <c r="E312" t="n">
-        <v>21.42338995771449</v>
+        <v>21.42338805354484</v>
       </c>
       <c r="F312" t="n">
         <v>1154200</v>
@@ -6672,16 +6672,16 @@
         <v>44553</v>
       </c>
       <c r="B313" t="n">
-        <v>21.1761531829834</v>
+        <v>21.17615127563477</v>
       </c>
       <c r="C313" t="n">
-        <v>21.6992437907334</v>
+        <v>21.69924183626969</v>
       </c>
       <c r="D313" t="n">
-        <v>20.79736331390923</v>
+        <v>20.79736144067842</v>
       </c>
       <c r="E313" t="n">
-        <v>21.6992437907334</v>
+        <v>21.69924183626969</v>
       </c>
       <c r="F313" t="n">
         <v>605250</v>
@@ -6712,16 +6712,16 @@
         <v>44558</v>
       </c>
       <c r="B315" t="n">
-        <v>20.76128768920898</v>
+        <v>20.76128959655762</v>
       </c>
       <c r="C315" t="n">
-        <v>21.24830222169153</v>
+        <v>21.2483041737824</v>
       </c>
       <c r="D315" t="n">
-        <v>20.58091091705966</v>
+        <v>20.58091280783701</v>
       </c>
       <c r="E315" t="n">
-        <v>20.90558841884829</v>
+        <v>20.90559033945389</v>
       </c>
       <c r="F315" t="n">
         <v>793100</v>
@@ -6812,16 +6812,16 @@
         <v>44566</v>
       </c>
       <c r="B320" t="n">
-        <v>17.78508186340332</v>
+        <v>17.78507995605469</v>
       </c>
       <c r="C320" t="n">
-        <v>18.88537711386832</v>
+        <v>18.8853750885193</v>
       </c>
       <c r="D320" t="n">
-        <v>17.55059273986488</v>
+        <v>17.55059085766387</v>
       </c>
       <c r="E320" t="n">
-        <v>18.77715070292733</v>
+        <v>18.77714868918498</v>
       </c>
       <c r="F320" t="n">
         <v>2337000</v>
@@ -6832,16 +6832,16 @@
         <v>44567</v>
       </c>
       <c r="B321" t="n">
-        <v>17.58666801452637</v>
+        <v>17.58666610717773</v>
       </c>
       <c r="C321" t="n">
-        <v>18.03760822002704</v>
+        <v>18.03760626377203</v>
       </c>
       <c r="D321" t="n">
-        <v>16.86516437380543</v>
+        <v>16.86516254470693</v>
       </c>
       <c r="E321" t="n">
-        <v>18.03760822002704</v>
+        <v>18.03760626377203</v>
       </c>
       <c r="F321" t="n">
         <v>2077850</v>
@@ -6872,16 +6872,16 @@
         <v>44571</v>
       </c>
       <c r="B323" t="n">
-        <v>16.36011123657227</v>
+        <v>16.36010932922363</v>
       </c>
       <c r="C323" t="n">
-        <v>17.13572899413958</v>
+        <v>17.13572699636531</v>
       </c>
       <c r="D323" t="n">
-        <v>16.10758580495536</v>
+        <v>16.10758392704749</v>
       </c>
       <c r="E323" t="n">
-        <v>17.11769097182395</v>
+        <v>17.11768897615265</v>
       </c>
       <c r="F323" t="n">
         <v>1820150</v>
@@ -6892,16 +6892,16 @@
         <v>44572</v>
       </c>
       <c r="B324" t="n">
-        <v>16.77497482299805</v>
+        <v>16.77497673034668</v>
       </c>
       <c r="C324" t="n">
-        <v>17.04553823941727</v>
+        <v>17.04554017752951</v>
       </c>
       <c r="D324" t="n">
-        <v>16.17973393071556</v>
+        <v>16.1797357703841</v>
       </c>
       <c r="E324" t="n">
-        <v>16.19777023032999</v>
+        <v>16.19777207204929</v>
       </c>
       <c r="F324" t="n">
         <v>629400</v>
@@ -6932,16 +6932,16 @@
         <v>44574</v>
       </c>
       <c r="B326" t="n">
-        <v>16.64871406555176</v>
+        <v>16.64871215820312</v>
       </c>
       <c r="C326" t="n">
-        <v>17.62274670733157</v>
+        <v>17.62274468839355</v>
       </c>
       <c r="D326" t="n">
-        <v>16.5765636906274</v>
+        <v>16.57656179154462</v>
       </c>
       <c r="E326" t="n">
-        <v>17.58667065976908</v>
+        <v>17.58666864496408</v>
       </c>
       <c r="F326" t="n">
         <v>921200</v>
@@ -6972,16 +6972,16 @@
         <v>44578</v>
       </c>
       <c r="B328" t="n">
-        <v>16.88319969177246</v>
+        <v>16.88320159912109</v>
       </c>
       <c r="C328" t="n">
-        <v>17.11768879140545</v>
+        <v>17.11769072524505</v>
       </c>
       <c r="D328" t="n">
-        <v>16.63067429232176</v>
+        <v>16.6306761711418</v>
       </c>
       <c r="E328" t="n">
-        <v>16.86516339195475</v>
+        <v>16.86516529726576</v>
       </c>
       <c r="F328" t="n">
         <v>496050</v>
@@ -7012,16 +7012,16 @@
         <v>44580</v>
       </c>
       <c r="B330" t="n">
-        <v>16.41422271728516</v>
+        <v>16.41422462463379</v>
       </c>
       <c r="C330" t="n">
-        <v>16.72086216753467</v>
+        <v>16.72086411051511</v>
       </c>
       <c r="D330" t="n">
-        <v>16.19776992400296</v>
+        <v>16.19777180619957</v>
       </c>
       <c r="E330" t="n">
-        <v>16.41422271728516</v>
+        <v>16.41422462463379</v>
       </c>
       <c r="F330" t="n">
         <v>847250</v>
@@ -7112,16 +7112,16 @@
         <v>44587</v>
       </c>
       <c r="B335" t="n">
-        <v>19.35435485839844</v>
+        <v>19.3543529510498</v>
       </c>
       <c r="C335" t="n">
-        <v>19.80529511198872</v>
+        <v>19.80529316020046</v>
       </c>
       <c r="D335" t="n">
-        <v>18.84930225603348</v>
+        <v>18.84930039845718</v>
       </c>
       <c r="E335" t="n">
-        <v>18.9214526277999</v>
+        <v>18.92145076311327</v>
       </c>
       <c r="F335" t="n">
         <v>1494250</v>
@@ -7152,16 +7152,16 @@
         <v>44589</v>
       </c>
       <c r="B337" t="n">
-        <v>19.67903137207031</v>
+        <v>19.67902946472168</v>
       </c>
       <c r="C337" t="n">
-        <v>19.67903137207031</v>
+        <v>19.67902946472168</v>
       </c>
       <c r="D337" t="n">
-        <v>18.84930127963634</v>
+        <v>18.84929945270756</v>
       </c>
       <c r="E337" t="n">
-        <v>19.30024150986784</v>
+        <v>19.30023963923261</v>
       </c>
       <c r="F337" t="n">
         <v>645650</v>
@@ -7172,16 +7172,16 @@
         <v>44592</v>
       </c>
       <c r="B338" t="n">
-        <v>19.96763038635254</v>
+        <v>19.96762847900391</v>
       </c>
       <c r="C338" t="n">
-        <v>20.27426984278146</v>
+        <v>20.274267906142</v>
       </c>
       <c r="D338" t="n">
-        <v>19.44453985247972</v>
+        <v>19.44453799509775</v>
       </c>
       <c r="E338" t="n">
-        <v>19.69706696959773</v>
+        <v>19.69706508809386</v>
       </c>
       <c r="F338" t="n">
         <v>1270500</v>
@@ -7252,16 +7252,16 @@
         <v>44596</v>
       </c>
       <c r="B342" t="n">
-        <v>19.40846824645996</v>
+        <v>19.40846633911133</v>
       </c>
       <c r="C342" t="n">
-        <v>20.18408428568767</v>
+        <v>20.18408230211611</v>
       </c>
       <c r="D342" t="n">
-        <v>19.26416750798967</v>
+        <v>19.26416561482205</v>
       </c>
       <c r="E342" t="n">
-        <v>20.18408428568767</v>
+        <v>20.18408230211611</v>
       </c>
       <c r="F342" t="n">
         <v>774000</v>
@@ -7272,16 +7272,16 @@
         <v>44599</v>
       </c>
       <c r="B343" t="n">
-        <v>19.73314476013184</v>
+        <v>19.7331428527832</v>
       </c>
       <c r="C343" t="n">
-        <v>19.94959759585004</v>
+        <v>19.94959566757971</v>
       </c>
       <c r="D343" t="n">
-        <v>19.06575339056894</v>
+        <v>19.06575154772842</v>
       </c>
       <c r="E343" t="n">
-        <v>19.31828055210647</v>
+        <v>19.31827868485741</v>
       </c>
       <c r="F343" t="n">
         <v>708000</v>
@@ -7312,16 +7312,16 @@
         <v>44601</v>
       </c>
       <c r="B345" t="n">
-        <v>19.91351890563965</v>
+        <v>19.91351699829102</v>
       </c>
       <c r="C345" t="n">
-        <v>20.18408233406016</v>
+        <v>20.18408040079654</v>
       </c>
       <c r="D345" t="n">
-        <v>19.42650439044265</v>
+        <v>19.42650252974105</v>
       </c>
       <c r="E345" t="n">
-        <v>19.48061673208669</v>
+        <v>19.48061486620212</v>
       </c>
       <c r="F345" t="n">
         <v>427500</v>
@@ -7332,16 +7332,16 @@
         <v>44602</v>
       </c>
       <c r="B346" t="n">
-        <v>19.98566818237305</v>
+        <v>19.98567008972168</v>
       </c>
       <c r="C346" t="n">
-        <v>20.59894708836287</v>
+        <v>20.59894905424028</v>
       </c>
       <c r="D346" t="n">
-        <v>19.82332944605806</v>
+        <v>19.82333133791377</v>
       </c>
       <c r="E346" t="n">
-        <v>20.18408123775789</v>
+        <v>20.18408316404224</v>
       </c>
       <c r="F346" t="n">
         <v>563100</v>
@@ -7372,16 +7372,16 @@
         <v>44606</v>
       </c>
       <c r="B348" t="n">
-        <v>20.00370597839355</v>
+        <v>20.00370788574219</v>
       </c>
       <c r="C348" t="n">
-        <v>20.1480066934604</v>
+        <v>20.14800861456807</v>
       </c>
       <c r="D348" t="n">
-        <v>19.26416438362593</v>
+        <v>19.26416622045944</v>
       </c>
       <c r="E348" t="n">
-        <v>19.26416438362593</v>
+        <v>19.26416622045944</v>
       </c>
       <c r="F348" t="n">
         <v>683300</v>
@@ -7392,16 +7392,16 @@
         <v>44607</v>
       </c>
       <c r="B349" t="n">
-        <v>20.52679824829102</v>
+        <v>20.52679634094238</v>
       </c>
       <c r="C349" t="n">
-        <v>20.70717329738229</v>
+        <v>20.70717137327322</v>
       </c>
       <c r="D349" t="n">
-        <v>20.11193236700041</v>
+        <v>20.11193049820109</v>
       </c>
       <c r="E349" t="n">
-        <v>20.20212075164623</v>
+        <v>20.2021188744666</v>
       </c>
       <c r="F349" t="n">
         <v>560950</v>
@@ -7412,16 +7412,16 @@
         <v>44608</v>
       </c>
       <c r="B350" t="n">
-        <v>20.74324989318848</v>
+        <v>20.74324607849121</v>
       </c>
       <c r="C350" t="n">
-        <v>20.76128791463935</v>
+        <v>20.76128409662488</v>
       </c>
       <c r="D350" t="n">
-        <v>20.27427165666829</v>
+        <v>20.27426792821643</v>
       </c>
       <c r="E350" t="n">
-        <v>20.74324989318848</v>
+        <v>20.74324607849121</v>
       </c>
       <c r="F350" t="n">
         <v>576900</v>
@@ -7472,16 +7472,16 @@
         <v>44613</v>
       </c>
       <c r="B353" t="n">
-        <v>18.66892623901367</v>
+        <v>18.66892433166504</v>
       </c>
       <c r="C353" t="n">
-        <v>19.9495965630065</v>
+        <v>19.94959452481559</v>
       </c>
       <c r="D353" t="n">
-        <v>18.66892623901367</v>
+        <v>18.66892433166504</v>
       </c>
       <c r="E353" t="n">
-        <v>19.85940817282663</v>
+        <v>19.85940614385</v>
       </c>
       <c r="F353" t="n">
         <v>728950</v>
@@ -7512,16 +7512,16 @@
         <v>44615</v>
       </c>
       <c r="B355" t="n">
-        <v>19.66099166870117</v>
+        <v>19.66098976135254</v>
       </c>
       <c r="C355" t="n">
-        <v>20.49072169018069</v>
+        <v>20.49071970233843</v>
       </c>
       <c r="D355" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276508916316</v>
       </c>
       <c r="E355" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940452736665</v>
       </c>
       <c r="F355" t="n">
         <v>1327750</v>
@@ -7552,16 +7552,16 @@
         <v>44617</v>
       </c>
       <c r="B357" t="n">
-        <v>19.0296745300293</v>
+        <v>19.02967643737793</v>
       </c>
       <c r="C357" t="n">
-        <v>19.62491538590869</v>
+        <v>19.62491735291844</v>
       </c>
       <c r="D357" t="n">
-        <v>18.65088473808786</v>
+        <v>18.6508866074703</v>
       </c>
       <c r="E357" t="n">
-        <v>19.28219991119016</v>
+        <v>19.28220184384947</v>
       </c>
       <c r="F357" t="n">
         <v>1262850</v>
@@ -7572,16 +7572,16 @@
         <v>44622</v>
       </c>
       <c r="B358" t="n">
-        <v>18.83126449584961</v>
+        <v>18.83126258850098</v>
       </c>
       <c r="C358" t="n">
-        <v>18.90341486862296</v>
+        <v>18.90341295396648</v>
       </c>
       <c r="D358" t="n">
-        <v>18.23602349041934</v>
+        <v>18.23602164336046</v>
       </c>
       <c r="E358" t="n">
-        <v>18.74107782003336</v>
+        <v>18.74107592181939</v>
       </c>
       <c r="F358" t="n">
         <v>1044650</v>
@@ -7592,16 +7592,16 @@
         <v>44623</v>
       </c>
       <c r="B359" t="n">
-        <v>18.57873725891113</v>
+        <v>18.5787353515625</v>
       </c>
       <c r="C359" t="n">
-        <v>19.46257967016855</v>
+        <v>19.46257767208202</v>
       </c>
       <c r="D359" t="n">
-        <v>18.54266121590451</v>
+        <v>18.54265931225955</v>
       </c>
       <c r="E359" t="n">
-        <v>18.72303799053682</v>
+        <v>18.72303606837384</v>
       </c>
       <c r="F359" t="n">
         <v>930450</v>
@@ -7612,16 +7612,16 @@
         <v>44624</v>
       </c>
       <c r="B360" t="n">
-        <v>17.91134262084961</v>
+        <v>17.91134452819824</v>
       </c>
       <c r="C360" t="n">
-        <v>18.75910883175985</v>
+        <v>18.75911082938567</v>
       </c>
       <c r="D360" t="n">
-        <v>17.55058913853877</v>
+        <v>17.55059100747137</v>
       </c>
       <c r="E360" t="n">
-        <v>18.57873381080452</v>
+        <v>18.57873578922251</v>
       </c>
       <c r="F360" t="n">
         <v>1669200</v>
@@ -7632,16 +7632,16 @@
         <v>44627</v>
       </c>
       <c r="B361" t="n">
-        <v>16.77497482299805</v>
+        <v>16.77497673034668</v>
       </c>
       <c r="C361" t="n">
-        <v>18.00153092699214</v>
+        <v>18.00153297380269</v>
       </c>
       <c r="D361" t="n">
-        <v>16.77497482299805</v>
+        <v>16.77497673034668</v>
       </c>
       <c r="E361" t="n">
-        <v>17.60470481227065</v>
+        <v>17.60470681396126</v>
       </c>
       <c r="F361" t="n">
         <v>1173850</v>
@@ -7732,16 +7732,16 @@
         <v>44634</v>
       </c>
       <c r="B366" t="n">
-        <v>17.31610298156738</v>
+        <v>17.31610488891602</v>
       </c>
       <c r="C366" t="n">
-        <v>17.67685476864166</v>
+        <v>17.67685671572668</v>
       </c>
       <c r="D366" t="n">
-        <v>16.88319911687804</v>
+        <v>16.88320097654281</v>
       </c>
       <c r="E366" t="n">
-        <v>17.35217730017471</v>
+        <v>17.35217921149688</v>
       </c>
       <c r="F366" t="n">
         <v>989600</v>
@@ -7812,16 +7812,16 @@
         <v>44638</v>
       </c>
       <c r="B370" t="n">
-        <v>18.43443489074707</v>
+        <v>18.4344367980957</v>
       </c>
       <c r="C370" t="n">
-        <v>18.90341136679641</v>
+        <v>18.90341332266845</v>
       </c>
       <c r="D370" t="n">
-        <v>18.01956903400312</v>
+        <v>18.01957089842698</v>
       </c>
       <c r="E370" t="n">
-        <v>18.16386975281834</v>
+        <v>18.16387163217251</v>
       </c>
       <c r="F370" t="n">
         <v>2000150</v>
@@ -7832,16 +7832,16 @@
         <v>44641</v>
       </c>
       <c r="B371" t="n">
-        <v>18.56069946289062</v>
+        <v>18.56069755554199</v>
       </c>
       <c r="C371" t="n">
-        <v>18.86733895137048</v>
+        <v>18.86733701251073</v>
       </c>
       <c r="D371" t="n">
-        <v>18.23602195268832</v>
+        <v>18.23602007870444</v>
       </c>
       <c r="E371" t="n">
-        <v>18.65088785130242</v>
+        <v>18.65088593468579</v>
       </c>
       <c r="F371" t="n">
         <v>689900</v>
@@ -7852,16 +7852,16 @@
         <v>44642</v>
       </c>
       <c r="B372" t="n">
-        <v>19.40846824645996</v>
+        <v>19.40846633911133</v>
       </c>
       <c r="C372" t="n">
-        <v>19.4625805933362</v>
+        <v>19.46257868066973</v>
       </c>
       <c r="D372" t="n">
-        <v>18.686962833908</v>
+        <v>18.68696099746462</v>
       </c>
       <c r="E372" t="n">
-        <v>18.70500085626691</v>
+        <v>18.70499901805086</v>
       </c>
       <c r="F372" t="n">
         <v>868000</v>
@@ -7892,16 +7892,16 @@
         <v>44644</v>
       </c>
       <c r="B374" t="n">
-        <v>20.79736328125</v>
+        <v>20.79736137390137</v>
       </c>
       <c r="C374" t="n">
-        <v>20.79736328125</v>
+        <v>20.79736137390137</v>
       </c>
       <c r="D374" t="n">
-        <v>19.49865663520698</v>
+        <v>19.49865484696414</v>
       </c>
       <c r="E374" t="n">
-        <v>19.71510774288082</v>
+        <v>19.71510593478701</v>
       </c>
       <c r="F374" t="n">
         <v>1624000</v>
@@ -7912,16 +7912,16 @@
         <v>44645</v>
       </c>
       <c r="B375" t="n">
-        <v>21.19418907165527</v>
+        <v>21.19419097900391</v>
       </c>
       <c r="C375" t="n">
-        <v>21.4467161990152</v>
+        <v>21.44671812908974</v>
       </c>
       <c r="D375" t="n">
-        <v>20.81539924071555</v>
+        <v>20.81540111397539</v>
       </c>
       <c r="E375" t="n">
-        <v>20.92362564392704</v>
+        <v>20.9236275269266</v>
       </c>
       <c r="F375" t="n">
         <v>911550</v>
@@ -7952,16 +7952,16 @@
         <v>44649</v>
       </c>
       <c r="B377" t="n">
-        <v>21.91569519042969</v>
+        <v>21.91569328308105</v>
       </c>
       <c r="C377" t="n">
-        <v>22.36663543484347</v>
+        <v>22.36663348824898</v>
       </c>
       <c r="D377" t="n">
-        <v>21.6631697544863</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="E377" t="n">
-        <v>21.6631697544863</v>
+        <v>21.66316786911525</v>
       </c>
       <c r="F377" t="n">
         <v>1103500</v>
@@ -7992,16 +7992,16 @@
         <v>44651</v>
       </c>
       <c r="B379" t="n">
-        <v>21.1761531829834</v>
+        <v>21.17615127563477</v>
       </c>
       <c r="C379" t="n">
-        <v>21.77139416007131</v>
+        <v>21.77139219910897</v>
       </c>
       <c r="D379" t="n">
-        <v>21.04989046669217</v>
+        <v>21.0498885707161</v>
       </c>
       <c r="E379" t="n">
-        <v>21.60905539901088</v>
+        <v>21.60905345267049</v>
       </c>
       <c r="F379" t="n">
         <v>849150</v>
@@ -8052,16 +8052,16 @@
         <v>44656</v>
       </c>
       <c r="B382" t="n">
-        <v>20.70717430114746</v>
+        <v>20.70717239379883</v>
       </c>
       <c r="C382" t="n">
-        <v>21.87961991797578</v>
+        <v>21.87961790263256</v>
       </c>
       <c r="D382" t="n">
-        <v>20.59894961048666</v>
+        <v>20.59894771310666</v>
       </c>
       <c r="E382" t="n">
-        <v>21.78943152895814</v>
+        <v>21.78942952192223</v>
       </c>
       <c r="F382" t="n">
         <v>1118400</v>
@@ -8072,16 +8072,16 @@
         <v>44657</v>
       </c>
       <c r="B383" t="n">
-        <v>20.02174377441406</v>
+        <v>20.0217456817627</v>
       </c>
       <c r="C383" t="n">
-        <v>20.58090860900858</v>
+        <v>20.58091056962541</v>
       </c>
       <c r="D383" t="n">
-        <v>19.58883991384388</v>
+        <v>19.58884177995242</v>
       </c>
       <c r="E383" t="n">
-        <v>20.58090860900858</v>
+        <v>20.58091056962541</v>
       </c>
       <c r="F383" t="n">
         <v>1237700</v>
@@ -8092,16 +8092,16 @@
         <v>44658</v>
       </c>
       <c r="B384" t="n">
-        <v>19.66099166870117</v>
+        <v>19.66098976135254</v>
       </c>
       <c r="C384" t="n">
-        <v>20.00370717768201</v>
+        <v>20.00370523708592</v>
       </c>
       <c r="D384" t="n">
-        <v>19.55276698601272</v>
+        <v>19.55276508916316</v>
       </c>
       <c r="E384" t="n">
-        <v>19.85940645396386</v>
+        <v>19.85940452736665</v>
       </c>
       <c r="F384" t="n">
         <v>978600</v>
@@ -8132,16 +8132,16 @@
         <v>44662</v>
       </c>
       <c r="B386" t="n">
-        <v>18.93948745727539</v>
+        <v>18.93948936462402</v>
       </c>
       <c r="C386" t="n">
-        <v>19.37238961487934</v>
+        <v>19.37239156582447</v>
       </c>
       <c r="D386" t="n">
-        <v>18.86733709767473</v>
+        <v>18.86733899775728</v>
       </c>
       <c r="E386" t="n">
-        <v>19.24612691562825</v>
+        <v>19.24612885385778</v>
       </c>
       <c r="F386" t="n">
         <v>1033000</v>
@@ -8232,16 +8232,16 @@
         <v>44670</v>
       </c>
       <c r="B391" t="n">
-        <v>20.32838439941406</v>
+        <v>20.3283863067627</v>
       </c>
       <c r="C391" t="n">
-        <v>20.34642069949194</v>
+        <v>20.34642260853286</v>
       </c>
       <c r="D391" t="n">
-        <v>19.01163816251292</v>
+        <v>19.01163994631538</v>
       </c>
       <c r="E391" t="n">
-        <v>19.55276672945585</v>
+        <v>19.55276856403071</v>
       </c>
       <c r="F391" t="n">
         <v>1459950</v>
@@ -8332,16 +8332,16 @@
         <v>44678</v>
       </c>
       <c r="B396" t="n">
-        <v>19.49865341186523</v>
+        <v>19.49865531921387</v>
       </c>
       <c r="C396" t="n">
-        <v>19.55276574978821</v>
+        <v>19.55276766243008</v>
       </c>
       <c r="D396" t="n">
-        <v>19.10182558662962</v>
+        <v>19.10182745516075</v>
       </c>
       <c r="E396" t="n">
-        <v>19.46257737311645</v>
+        <v>19.46257927693614</v>
       </c>
       <c r="F396" t="n">
         <v>619300</v>
@@ -8352,16 +8352,16 @@
         <v>44679</v>
       </c>
       <c r="B397" t="n">
-        <v>21.04988670349121</v>
+        <v>21.04988861083984</v>
       </c>
       <c r="C397" t="n">
-        <v>21.10399904077057</v>
+        <v>21.10400095302237</v>
       </c>
       <c r="D397" t="n">
-        <v>19.30023840959018</v>
+        <v>19.30024015840165</v>
       </c>
       <c r="E397" t="n">
-        <v>19.84136694298433</v>
+        <v>19.84136874082794</v>
       </c>
       <c r="F397" t="n">
         <v>1501350</v>
@@ -8372,16 +8372,16 @@
         <v>44680</v>
       </c>
       <c r="B398" t="n">
-        <v>21.04988670349121</v>
+        <v>21.04988861083984</v>
       </c>
       <c r="C398" t="n">
-        <v>21.60905153584503</v>
+        <v>21.60905349386008</v>
       </c>
       <c r="D398" t="n">
-        <v>20.90558599061279</v>
+        <v>20.90558788488621</v>
       </c>
       <c r="E398" t="n">
-        <v>21.60905153584503</v>
+        <v>21.60905349386008</v>
       </c>
       <c r="F398" t="n">
         <v>1651000</v>
@@ -8412,16 +8412,16 @@
         <v>44684</v>
       </c>
       <c r="B400" t="n">
-        <v>19.84136962890625</v>
+        <v>19.84136772155762</v>
       </c>
       <c r="C400" t="n">
-        <v>20.63502365717432</v>
+        <v>20.63502167353181</v>
       </c>
       <c r="D400" t="n">
-        <v>19.75118124109841</v>
+        <v>19.75117934241958</v>
       </c>
       <c r="E400" t="n">
-        <v>20.4726866233607</v>
+        <v>20.47268465532364</v>
       </c>
       <c r="F400" t="n">
         <v>1374100</v>
@@ -8452,16 +8452,16 @@
         <v>44686</v>
       </c>
       <c r="B402" t="n">
-        <v>20.09389305114746</v>
+        <v>20.09389495849609</v>
       </c>
       <c r="C402" t="n">
-        <v>20.47268283366227</v>
+        <v>20.47268477696631</v>
       </c>
       <c r="D402" t="n">
-        <v>19.73313956669518</v>
+        <v>19.73314143980044</v>
       </c>
       <c r="E402" t="n">
-        <v>20.41856877887437</v>
+        <v>20.41857071704181</v>
       </c>
       <c r="F402" t="n">
         <v>1134600</v>
@@ -8472,16 +8472,16 @@
         <v>44687</v>
       </c>
       <c r="B403" t="n">
-        <v>19.51903343200684</v>
+        <v>19.5190315246582</v>
       </c>
       <c r="C403" t="n">
-        <v>19.93473455484336</v>
+        <v>19.9347326068735</v>
       </c>
       <c r="D403" t="n">
-        <v>18.8199007902444</v>
+        <v>18.81989895121317</v>
       </c>
       <c r="E403" t="n">
-        <v>19.67019714903581</v>
+        <v>19.67019522691586</v>
       </c>
       <c r="F403" t="n">
         <v>2332850</v>
@@ -8492,16 +8492,16 @@
         <v>44690</v>
       </c>
       <c r="B404" t="n">
-        <v>18.78210830688477</v>
+        <v>18.7821102142334</v>
       </c>
       <c r="C404" t="n">
-        <v>19.53792866776176</v>
+        <v>19.53793065186498</v>
       </c>
       <c r="D404" t="n">
-        <v>18.38530311297808</v>
+        <v>18.38530498003061</v>
       </c>
       <c r="E404" t="n">
-        <v>19.25449535667779</v>
+        <v>19.25449731199797</v>
       </c>
       <c r="F404" t="n">
         <v>2367350</v>
@@ -8552,16 +8552,16 @@
         <v>44693</v>
       </c>
       <c r="B407" t="n">
-        <v>19.330078125</v>
+        <v>19.33007621765137</v>
       </c>
       <c r="C407" t="n">
-        <v>19.70798922428379</v>
+        <v>19.7079872796457</v>
       </c>
       <c r="D407" t="n">
-        <v>18.81990102418875</v>
+        <v>18.81989916718061</v>
       </c>
       <c r="E407" t="n">
-        <v>18.93327471437663</v>
+        <v>18.93327284618161</v>
       </c>
       <c r="F407" t="n">
         <v>1412250</v>
@@ -8652,16 +8652,16 @@
         <v>44700</v>
       </c>
       <c r="B412" t="n">
-        <v>20.78503036499023</v>
+        <v>20.7850284576416</v>
       </c>
       <c r="C412" t="n">
-        <v>20.91729816339582</v>
+        <v>20.91729624390957</v>
       </c>
       <c r="D412" t="n">
-        <v>20.01031588516278</v>
+        <v>20.0103140489062</v>
       </c>
       <c r="E412" t="n">
-        <v>20.36932925312662</v>
+        <v>20.36932738392501</v>
       </c>
       <c r="F412" t="n">
         <v>1388850</v>
@@ -8672,16 +8672,16 @@
         <v>44701</v>
       </c>
       <c r="B413" t="n">
-        <v>20.65276145935059</v>
+        <v>20.65276336669922</v>
       </c>
       <c r="C413" t="n">
-        <v>21.08735666053437</v>
+        <v>21.08735860801926</v>
       </c>
       <c r="D413" t="n">
-        <v>20.25595628339371</v>
+        <v>20.25595815409612</v>
       </c>
       <c r="E413" t="n">
-        <v>21.03067072168725</v>
+        <v>21.03067266393701</v>
       </c>
       <c r="F413" t="n">
         <v>1756800</v>
@@ -8732,16 +8732,16 @@
         <v>44706</v>
       </c>
       <c r="B416" t="n">
-        <v>20.78503036499023</v>
+        <v>20.7850284576416</v>
       </c>
       <c r="C416" t="n">
-        <v>20.80392627962349</v>
+        <v>20.80392437054087</v>
       </c>
       <c r="D416" t="n">
-        <v>20.0858977416822</v>
+        <v>20.08589589848982</v>
       </c>
       <c r="E416" t="n">
-        <v>20.25595736935429</v>
+        <v>20.2559555105563</v>
       </c>
       <c r="F416" t="n">
         <v>1116800</v>
@@ -8792,16 +8792,16 @@
         <v>44711</v>
       </c>
       <c r="B419" t="n">
-        <v>22.14550399780273</v>
+        <v>22.14550590515137</v>
       </c>
       <c r="C419" t="n">
-        <v>23.22254582654633</v>
+        <v>23.22254782665845</v>
       </c>
       <c r="D419" t="n">
-        <v>22.14550399780273</v>
+        <v>22.14550590515137</v>
       </c>
       <c r="E419" t="n">
-        <v>22.97690435995308</v>
+        <v>22.97690633890859</v>
       </c>
       <c r="F419" t="n">
         <v>1234700</v>
@@ -8812,16 +8812,16 @@
         <v>44712</v>
       </c>
       <c r="B420" t="n">
-        <v>22.52341461181641</v>
+        <v>22.52341270446777</v>
       </c>
       <c r="C420" t="n">
-        <v>22.76905609322542</v>
+        <v>22.76905416507515</v>
       </c>
       <c r="D420" t="n">
-        <v>21.99434162217354</v>
+        <v>21.99433975962836</v>
       </c>
       <c r="E420" t="n">
-        <v>22.23998310358255</v>
+        <v>22.23998122023573</v>
       </c>
       <c r="F420" t="n">
         <v>1969900</v>
@@ -8852,16 +8852,16 @@
         <v>44714</v>
       </c>
       <c r="B422" t="n">
-        <v>23.37370872497559</v>
+        <v>23.37371063232422</v>
       </c>
       <c r="C422" t="n">
-        <v>24.31848273230045</v>
+        <v>24.31848471674483</v>
       </c>
       <c r="D422" t="n">
-        <v>23.24144094059439</v>
+        <v>23.24144283714967</v>
       </c>
       <c r="E422" t="n">
-        <v>23.43039466085132</v>
+        <v>23.43039657282566</v>
       </c>
       <c r="F422" t="n">
         <v>1968350</v>
@@ -8872,16 +8872,16 @@
         <v>44715</v>
       </c>
       <c r="B423" t="n">
-        <v>22.4100399017334</v>
+        <v>22.41003799438477</v>
       </c>
       <c r="C423" t="n">
-        <v>23.26033799154877</v>
+        <v>23.26033601183012</v>
       </c>
       <c r="D423" t="n">
-        <v>22.29666802443368</v>
+        <v>22.29666612673428</v>
       </c>
       <c r="E423" t="n">
-        <v>23.26033799154877</v>
+        <v>23.26033601183012</v>
       </c>
       <c r="F423" t="n">
         <v>1510900</v>
@@ -8932,16 +8932,16 @@
         <v>44720</v>
       </c>
       <c r="B426" t="n">
-        <v>21.20072937011719</v>
+        <v>21.20073127746582</v>
       </c>
       <c r="C426" t="n">
-        <v>21.82428007494298</v>
+        <v>21.82428203839009</v>
       </c>
       <c r="D426" t="n">
-        <v>21.03066975934408</v>
+        <v>21.0306716513931</v>
       </c>
       <c r="E426" t="n">
-        <v>21.48416085339676</v>
+        <v>21.48416278624464</v>
       </c>
       <c r="F426" t="n">
         <v>863650</v>
@@ -9012,16 +9012,16 @@
         <v>44726</v>
       </c>
       <c r="B430" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C430" t="n">
-        <v>19.51903189147468</v>
+        <v>19.51902994454667</v>
       </c>
       <c r="D430" t="n">
-        <v>18.89548115744023</v>
+        <v>18.89547927270836</v>
       </c>
       <c r="E430" t="n">
-        <v>19.51903189147468</v>
+        <v>19.51902994454667</v>
       </c>
       <c r="F430" t="n">
         <v>1027150</v>
@@ -9092,16 +9092,16 @@
         <v>44733</v>
       </c>
       <c r="B434" t="n">
-        <v>18.63094520568848</v>
+        <v>18.63094329833984</v>
       </c>
       <c r="C434" t="n">
-        <v>19.02775041259933</v>
+        <v>19.02774846462764</v>
       </c>
       <c r="D434" t="n">
-        <v>18.40419963059851</v>
+        <v>18.40419774646302</v>
       </c>
       <c r="E434" t="n">
-        <v>18.89548261096693</v>
+        <v>18.8954806765362</v>
       </c>
       <c r="F434" t="n">
         <v>881100</v>
@@ -9132,16 +9132,16 @@
         <v>44735</v>
       </c>
       <c r="B436" t="n">
-        <v>18.81989860534668</v>
+        <v>18.81990051269531</v>
       </c>
       <c r="C436" t="n">
-        <v>18.89548045508649</v>
+        <v>18.89548237009515</v>
       </c>
       <c r="D436" t="n">
-        <v>18.49867529344914</v>
+        <v>18.4986771682426</v>
       </c>
       <c r="E436" t="n">
-        <v>18.72542084266856</v>
+        <v>18.72542274044211</v>
       </c>
       <c r="F436" t="n">
         <v>1280500</v>
@@ -9152,16 +9152,16 @@
         <v>44736</v>
       </c>
       <c r="B437" t="n">
-        <v>18.47978019714355</v>
+        <v>18.47977828979492</v>
       </c>
       <c r="C437" t="n">
-        <v>18.95216722939579</v>
+        <v>18.9521652732908</v>
       </c>
       <c r="D437" t="n">
-        <v>18.23413872413077</v>
+        <v>18.23413684213547</v>
       </c>
       <c r="E437" t="n">
-        <v>18.95216722939579</v>
+        <v>18.9521652732908</v>
       </c>
       <c r="F437" t="n">
         <v>1255000</v>
@@ -9212,16 +9212,16 @@
         <v>44741</v>
       </c>
       <c r="B440" t="n">
-        <v>17.81843757629395</v>
+        <v>17.81843948364258</v>
       </c>
       <c r="C440" t="n">
-        <v>18.13966086891105</v>
+        <v>18.13966281064456</v>
       </c>
       <c r="D440" t="n">
-        <v>17.51611019548098</v>
+        <v>17.51611207046742</v>
       </c>
       <c r="E440" t="n">
-        <v>18.13966086891105</v>
+        <v>18.13966281064456</v>
       </c>
       <c r="F440" t="n">
         <v>939650</v>
@@ -9232,16 +9232,16 @@
         <v>44742</v>
       </c>
       <c r="B441" t="n">
-        <v>17.53500556945801</v>
+        <v>17.53500747680664</v>
       </c>
       <c r="C441" t="n">
-        <v>17.74285701026197</v>
+        <v>17.74285894021939</v>
       </c>
       <c r="D441" t="n">
-        <v>17.30826001750107</v>
+        <v>17.30826190018573</v>
       </c>
       <c r="E441" t="n">
-        <v>17.55390148262445</v>
+        <v>17.55390339202846</v>
       </c>
       <c r="F441" t="n">
         <v>1152750</v>
@@ -9252,16 +9252,16 @@
         <v>44743</v>
       </c>
       <c r="B442" t="n">
-        <v>17.5916919708252</v>
+        <v>17.59169387817383</v>
       </c>
       <c r="C442" t="n">
-        <v>17.72395974890228</v>
+        <v>17.72396167059182</v>
       </c>
       <c r="D442" t="n">
-        <v>17.06261725449021</v>
+        <v>17.06261910447483</v>
       </c>
       <c r="E442" t="n">
-        <v>17.25157276775461</v>
+        <v>17.2515746382264</v>
       </c>
       <c r="F442" t="n">
         <v>2016600</v>
@@ -9272,16 +9272,16 @@
         <v>44746</v>
       </c>
       <c r="B443" t="n">
-        <v>17.28936576843262</v>
+        <v>17.28936386108398</v>
       </c>
       <c r="C443" t="n">
-        <v>17.64838094509635</v>
+        <v>17.64837899814145</v>
       </c>
       <c r="D443" t="n">
-        <v>17.25157574047591</v>
+        <v>17.25157383729624</v>
       </c>
       <c r="E443" t="n">
-        <v>17.44052948428672</v>
+        <v>17.44052756026183</v>
       </c>
       <c r="F443" t="n">
         <v>903450</v>
@@ -9372,16 +9372,16 @@
         <v>44753</v>
       </c>
       <c r="B448" t="n">
-        <v>16.76029014587402</v>
+        <v>16.76029205322266</v>
       </c>
       <c r="C448" t="n">
-        <v>17.61058636528556</v>
+        <v>17.61058836939931</v>
       </c>
       <c r="D448" t="n">
-        <v>16.62802236565831</v>
+        <v>16.62802425795465</v>
       </c>
       <c r="E448" t="n">
-        <v>17.61058636528556</v>
+        <v>17.61058836939931</v>
       </c>
       <c r="F448" t="n">
         <v>1587350</v>
@@ -9412,16 +9412,16 @@
         <v>44755</v>
       </c>
       <c r="B450" t="n">
-        <v>16.87366485595703</v>
+        <v>16.87366676330566</v>
       </c>
       <c r="C450" t="n">
-        <v>17.02482855752328</v>
+        <v>17.024830481959</v>
       </c>
       <c r="D450" t="n">
-        <v>16.3445900984617</v>
+        <v>16.3445919460053</v>
       </c>
       <c r="E450" t="n">
-        <v>16.51464971322709</v>
+        <v>16.51465157999372</v>
       </c>
       <c r="F450" t="n">
         <v>919750</v>
@@ -9492,16 +9492,16 @@
         <v>44761</v>
       </c>
       <c r="B454" t="n">
-        <v>17.28936576843262</v>
+        <v>17.28936386108398</v>
       </c>
       <c r="C454" t="n">
-        <v>17.51611314422741</v>
+        <v>17.51611121186419</v>
       </c>
       <c r="D454" t="n">
-        <v>17.1004120246218</v>
+        <v>17.10041013811839</v>
       </c>
       <c r="E454" t="n">
-        <v>17.1004120246218</v>
+        <v>17.10041013811839</v>
       </c>
       <c r="F454" t="n">
         <v>816100</v>
@@ -9512,16 +9512,16 @@
         <v>44762</v>
       </c>
       <c r="B455" t="n">
-        <v>17.96960258483887</v>
+        <v>17.9696044921875</v>
       </c>
       <c r="C455" t="n">
-        <v>18.02628852239609</v>
+        <v>18.02629043576155</v>
       </c>
       <c r="D455" t="n">
-        <v>17.23267818854108</v>
+        <v>17.2326800176703</v>
       </c>
       <c r="E455" t="n">
-        <v>17.25157410173131</v>
+        <v>17.2515759328662</v>
       </c>
       <c r="F455" t="n">
         <v>812650</v>
@@ -9532,16 +9532,16 @@
         <v>44763</v>
       </c>
       <c r="B456" t="n">
-        <v>18.02628898620605</v>
+        <v>18.02629089355469</v>
       </c>
       <c r="C456" t="n">
-        <v>18.23413863060609</v>
+        <v>18.23414055994714</v>
       </c>
       <c r="D456" t="n">
-        <v>17.66727563642172</v>
+        <v>17.66727750578341</v>
       </c>
       <c r="E456" t="n">
-        <v>18.04518489988247</v>
+        <v>18.04518680923047</v>
       </c>
       <c r="F456" t="n">
         <v>845300</v>
@@ -9572,16 +9572,16 @@
         <v>44767</v>
       </c>
       <c r="B458" t="n">
-        <v>17.95070648193359</v>
+        <v>17.95070457458496</v>
       </c>
       <c r="C458" t="n">
-        <v>18.30971981868635</v>
+        <v>18.30971787319083</v>
       </c>
       <c r="D458" t="n">
-        <v>17.87512463198494</v>
+        <v>17.87512273266724</v>
       </c>
       <c r="E458" t="n">
-        <v>18.17745203177956</v>
+        <v>18.17745010033813</v>
       </c>
       <c r="F458" t="n">
         <v>615900</v>
@@ -9592,16 +9592,16 @@
         <v>44768</v>
       </c>
       <c r="B459" t="n">
-        <v>17.40273857116699</v>
+        <v>17.40273666381836</v>
       </c>
       <c r="C459" t="n">
-        <v>18.158557111994</v>
+        <v>18.15855512180728</v>
       </c>
       <c r="D459" t="n">
-        <v>17.25157486300159</v>
+        <v>17.25157297222058</v>
       </c>
       <c r="E459" t="n">
-        <v>18.04518523187672</v>
+        <v>18.04518325411562</v>
       </c>
       <c r="F459" t="n">
         <v>578050</v>
@@ -9652,16 +9652,16 @@
         <v>44771</v>
       </c>
       <c r="B462" t="n">
-        <v>19.51903343200684</v>
+        <v>19.5190315246582</v>
       </c>
       <c r="C462" t="n">
-        <v>19.65130123390378</v>
+        <v>19.65129931363029</v>
       </c>
       <c r="D462" t="n">
-        <v>18.74431893172991</v>
+        <v>18.74431710008434</v>
       </c>
       <c r="E462" t="n">
-        <v>18.87658673362685</v>
+        <v>18.87658488905642</v>
       </c>
       <c r="F462" t="n">
         <v>1207650</v>
@@ -9672,16 +9672,16 @@
         <v>44774</v>
       </c>
       <c r="B463" t="n">
-        <v>19.12222671508789</v>
+        <v>19.12222480773926</v>
       </c>
       <c r="C463" t="n">
-        <v>19.74577744912234</v>
+        <v>19.74577547957757</v>
       </c>
       <c r="D463" t="n">
-        <v>19.04664486253867</v>
+        <v>19.04664296272896</v>
       </c>
       <c r="E463" t="n">
-        <v>19.50013597783399</v>
+        <v>19.50013403279076</v>
       </c>
       <c r="F463" t="n">
         <v>811600</v>
@@ -9692,16 +9692,16 @@
         <v>44775</v>
       </c>
       <c r="B464" t="n">
-        <v>19.08443641662598</v>
+        <v>19.08443832397461</v>
       </c>
       <c r="C464" t="n">
-        <v>19.38676382249504</v>
+        <v>19.38676576005906</v>
       </c>
       <c r="D464" t="n">
-        <v>18.89548088695107</v>
+        <v>18.895482775415</v>
       </c>
       <c r="E464" t="n">
-        <v>19.12222644135287</v>
+        <v>19.12222835247834</v>
       </c>
       <c r="F464" t="n">
         <v>867500</v>
@@ -9712,16 +9712,16 @@
         <v>44776</v>
       </c>
       <c r="B465" t="n">
-        <v>19.6890926361084</v>
+        <v>19.68909072875977</v>
       </c>
       <c r="C465" t="n">
-        <v>19.74577857825845</v>
+        <v>19.74577666541846</v>
       </c>
       <c r="D465" t="n">
-        <v>19.02775003697459</v>
+        <v>19.02774819369244</v>
       </c>
       <c r="E465" t="n">
-        <v>19.08443778113825</v>
+        <v>19.08443593236457</v>
       </c>
       <c r="F465" t="n">
         <v>1095050</v>
@@ -9832,16 +9832,16 @@
         <v>44784</v>
       </c>
       <c r="B471" t="n">
-        <v>22.01323699951172</v>
+        <v>22.01323509216309</v>
       </c>
       <c r="C471" t="n">
-        <v>22.0888188595181</v>
+        <v>22.08881694562063</v>
       </c>
       <c r="D471" t="n">
-        <v>21.54084992396843</v>
+        <v>21.54084805755003</v>
       </c>
       <c r="E471" t="n">
-        <v>21.82428325050261</v>
+        <v>21.82428135952598</v>
       </c>
       <c r="F471" t="n">
         <v>1242750</v>
@@ -9892,16 +9892,16 @@
         <v>44789</v>
       </c>
       <c r="B474" t="n">
-        <v>22.75016021728516</v>
+        <v>22.75015830993652</v>
       </c>
       <c r="C474" t="n">
-        <v>23.12806949624067</v>
+        <v>23.12806755720854</v>
       </c>
       <c r="D474" t="n">
-        <v>22.52341464991185</v>
+        <v>22.52341276157331</v>
       </c>
       <c r="E474" t="n">
-        <v>23.09027946935192</v>
+        <v>23.09027753348805</v>
       </c>
       <c r="F474" t="n">
         <v>703400</v>
@@ -9912,16 +9912,16 @@
         <v>44790</v>
       </c>
       <c r="B475" t="n">
-        <v>22.80684661865234</v>
+        <v>22.80684471130371</v>
       </c>
       <c r="C475" t="n">
-        <v>23.09027993509618</v>
+        <v>23.09027800404387</v>
       </c>
       <c r="D475" t="n">
-        <v>22.2399835897919</v>
+        <v>22.23998172985033</v>
       </c>
       <c r="E475" t="n">
-        <v>22.4856232745575</v>
+        <v>22.48562139407294</v>
       </c>
       <c r="F475" t="n">
         <v>781800</v>
@@ -9972,16 +9972,16 @@
         <v>44795</v>
       </c>
       <c r="B478" t="n">
-        <v>20.67165756225586</v>
+        <v>20.67165565490723</v>
       </c>
       <c r="C478" t="n">
-        <v>20.86061311263301</v>
+        <v>20.86061118784968</v>
       </c>
       <c r="D478" t="n">
-        <v>20.46380789845194</v>
+        <v>20.46380601028133</v>
       </c>
       <c r="E478" t="n">
-        <v>20.80392716832534</v>
+        <v>20.80392524877235</v>
       </c>
       <c r="F478" t="n">
         <v>1246950</v>
@@ -10012,16 +10012,16 @@
         <v>44797</v>
       </c>
       <c r="B480" t="n">
-        <v>20.80392646789551</v>
+        <v>20.80392456054688</v>
       </c>
       <c r="C480" t="n">
-        <v>21.16293983910836</v>
+        <v>21.16293789884462</v>
       </c>
       <c r="D480" t="n">
-        <v>20.48270312427755</v>
+        <v>20.48270124637937</v>
       </c>
       <c r="E480" t="n">
-        <v>20.76613463828699</v>
+        <v>20.76613273440319</v>
       </c>
       <c r="F480" t="n">
         <v>1050450</v>
@@ -10072,16 +10072,16 @@
         <v>44802</v>
       </c>
       <c r="B483" t="n">
-        <v>20.91729736328125</v>
+        <v>20.91729545593262</v>
       </c>
       <c r="C483" t="n">
-        <v>21.12514881226926</v>
+        <v>21.12514688596765</v>
       </c>
       <c r="D483" t="n">
-        <v>20.10479288728027</v>
+        <v>20.10479105402004</v>
       </c>
       <c r="E483" t="n">
-        <v>20.40712030179352</v>
+        <v>20.4071184409655</v>
       </c>
       <c r="F483" t="n">
         <v>1048850</v>
@@ -10132,16 +10132,16 @@
         <v>44805</v>
       </c>
       <c r="B486" t="n">
-        <v>20.78503036499023</v>
+        